--- a/StepCat_Blank_Profitability_Analysis_Template.xlsx
+++ b/StepCat_Blank_Profitability_Analysis_Template.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instructions" sheetId="1" r:id="R9f54f66dd30845b0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Game Records" sheetId="2" r:id="R2dbf444f3c5f45c3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="3" r:id="R39ca524425454938"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Game Comparisons" sheetId="4" r:id="R017d682e2497455e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Best Results" sheetId="5" r:id="R8bc1f2fbef8949e0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instructions" sheetId="1" r:id="R5bf20db32989475d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Game Records" sheetId="2" r:id="R340eaf7fae294dc5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="3" r:id="R2adb6b4d42fc4e7f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Game Comparisons" sheetId="4" r:id="R2e99b9e554fc40c5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Best Results" sheetId="5" r:id="R0f5bb510876a415f"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -114,7 +114,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="106">
+  <x:cellXfs count="107">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -377,6 +377,7 @@
     <x:xf numFmtId="202" fontId="3" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center" wrapText="1"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -388,7 +389,7 @@
         <x:color rgb="FF274E13"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFD9EAD3"/>
         </x:patternFill>
       </x:fill>
@@ -399,7 +400,7 @@
         <x:color rgb="FF7F6000"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFF2CC"/>
         </x:patternFill>
       </x:fill>
@@ -410,7 +411,7 @@
         <x:color rgb="FF990000"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFF4CCCC"/>
         </x:patternFill>
       </x:fill>
@@ -421,7 +422,7 @@
         <x:color rgb="FF990000"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFF4CCCC"/>
         </x:patternFill>
       </x:fill>
@@ -432,7 +433,7 @@
         <x:color rgb="FF134F5C"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFD9EAF7"/>
         </x:patternFill>
       </x:fill>
@@ -747,15 +748,15 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>3</xdr:col>
+      <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>12</xdr:row>
+      <xdr:row>27</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>28</xdr:row>
+      <xdr:row>44</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -769,7 +770,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rc048802c71914070"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R6f1c4fb419ee43a7"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -804,7 +805,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R5778ecf950fb4638"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R4758196ef5154484"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1257,7 +1258,7 @@
     </x:row>
     <x:row r="26" ht="28" customHeight="1">
       <x:c r="A26" s="32" t="str">
-        <x:v>• Profit is recorded when a challenge ends. This template does not calculate or describe weekly payouts.</x:v>
+        <x:v>• Profit is recorded only when a challenge ends; Challenge Length is used for comparison, not weekly payout.</x:v>
       </x:c>
       <x:c r="B26" s="32"/>
       <x:c r="C26" s="32"/>
@@ -18078,7 +18079,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1b676da679b247b1"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbb01edc0559f47ea"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -18283,7 +18284,7 @@
       <x:c r="G21" s="23"/>
       <x:c r="H21" s="23"/>
     </x:row>
-    <x:row r="22">
+    <x:row r="22" ht="26" customHeight="1">
       <x:c r="A22" s="32" t="str">
         <x:v>Total Profit adds positive Profit amounts. Net Profit After Losses subtracts forfeited Entry Fees. Average Profit per Game uses Net Profit, so losses are included. Challenge Length is compared on the Game Comparisons sheet, but this template does not describe profit as a weekly payout.</x:v>
       </x:c>
@@ -18295,7 +18296,7 @@
       <x:c r="G22" s="32"/>
       <x:c r="H22" s="32"/>
     </x:row>
-    <x:row r="23">
+    <x:row r="23" ht="26" customHeight="1">
       <x:c r="A23" s="32"/>
       <x:c r="B23" s="32"/>
       <x:c r="C23" s="32"/>
@@ -18305,7 +18306,7 @@
       <x:c r="G23" s="32"/>
       <x:c r="H23" s="32"/>
     </x:row>
-    <x:row r="24">
+    <x:row r="24" ht="26" customHeight="1">
       <x:c r="A24" s="32"/>
       <x:c r="B24" s="32"/>
       <x:c r="C24" s="32"/>
@@ -18315,7 +18316,7 @@
       <x:c r="G24" s="32"/>
       <x:c r="H24" s="32"/>
     </x:row>
-    <x:row r="25">
+    <x:row r="25" ht="26" customHeight="1">
       <x:c r="A25" s="32"/>
       <x:c r="B25" s="32"/>
       <x:c r="C25" s="32"/>
@@ -18325,6 +18326,7 @@
       <x:c r="G25" s="32"/>
       <x:c r="H25" s="32"/>
     </x:row>
+    <x:row r="27" ht="12" customHeight="1"/>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:H1"/>
@@ -18350,7 +18352,7 @@
     <x:mergeCell ref="A22:H25"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfbc762e05e98440b"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Raea93e168a1a4241"/>
 </x:worksheet>
 </file>
 
@@ -18435,27 +18437,27 @@
         <x:v>Member</x:v>
       </x:c>
       <x:c r="B6" s="50" t="n">
-        <x:f>COUNTIFS('Game Records'!$L$5:$L$504,"Member",'Game Records'!$K$5:$K$504,"&lt;&gt;Subscription")</x:f>
+        <x:f>COUNTIFS('Game Records'!$A$5:$A$504,"&lt;&gt;",'Game Records'!$L$5:$L$504,"Member",'Game Records'!$K$5:$K$504,"&lt;&gt;Subscription")</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="C6" s="58" t="n">
-        <x:f>SUMIFS('Game Records'!$U$5:$U$504,'Game Records'!$L$5:$L$504,"Member")</x:f>
+        <x:f>SUMIFS('Game Records'!$U$5:$U$504,'Game Records'!$A$5:$A$504,"&lt;&gt;",'Game Records'!$L$5:$L$504,"Member")</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="D6" s="58" t="str">
         <x:f>IF(B6=0,"",C6/B6)</x:f>
       </x:c>
       <x:c r="E6" s="60" t="str">
-        <x:f>IF(COUNTIFS('Game Records'!$L$5:$L$504,"Member",'Game Records'!$J$5:$J$504,"&lt;&gt;")=0,"",SUMIFS('Game Records'!$J$5:$J$504,'Game Records'!$L$5:$L$504,"Member")/COUNTIFS('Game Records'!$L$5:$L$504,"Member",'Game Records'!$J$5:$J$504,"&lt;&gt;"))</x:f>
+        <x:f>IF(COUNTIFS('Game Records'!$A$5:$A$504,"&lt;&gt;",'Game Records'!$L$5:$L$504,"Member",'Game Records'!$J$5:$J$504,"&lt;&gt;")=0,"",SUMIFS('Game Records'!$J$5:$J$504,'Game Records'!$A$5:$A$504,"&lt;&gt;",'Game Records'!$L$5:$L$504,"Member")/COUNTIFS('Game Records'!$A$5:$A$504,"&lt;&gt;",'Game Records'!$L$5:$L$504,"Member",'Game Records'!$J$5:$J$504,"&lt;&gt;"))</x:f>
       </x:c>
       <x:c r="F6" s="60" t="str">
-        <x:f>IF(B6=0,"",COUNTIFS('Game Records'!$L$5:$L$504,"Member",'Game Records'!$K$5:$K$504,"Profit")/B6)</x:f>
+        <x:f>IF(B6=0,"",COUNTIFS('Game Records'!$A$5:$A$504,"&lt;&gt;",'Game Records'!$L$5:$L$504,"Member",'Game Records'!$K$5:$K$504,"Profit")/B6)</x:f>
       </x:c>
       <x:c r="G6" s="60" t="str">
-        <x:f>IF(B6=0,"",COUNTIFS('Game Records'!$L$5:$L$504,"Member",'Game Records'!$K$5:$K$504,"Draw")/B6)</x:f>
+        <x:f>IF(B6=0,"",COUNTIFS('Game Records'!$A$5:$A$504,"&lt;&gt;",'Game Records'!$L$5:$L$504,"Member",'Game Records'!$K$5:$K$504,"Draw")/B6)</x:f>
       </x:c>
       <x:c r="H6" s="60" t="str">
-        <x:f>IF(B6=0,"",COUNTIFS('Game Records'!$L$5:$L$504,"Member",'Game Records'!$K$5:$K$504,"Disqualified")+COUNTIFS('Game Records'!$L$5:$L$504,"Member",'Game Records'!$K$5:$K$504,"Loss")/B6)</x:f>
+        <x:f>IF(B6=0,"",(COUNTIFS('Game Records'!$A$5:$A$504,"&lt;&gt;",'Game Records'!$L$5:$L$504,"Member",'Game Records'!$K$5:$K$504,"Disqualified")+COUNTIFS('Game Records'!$A$5:$A$504,"&lt;&gt;",'Game Records'!$L$5:$L$504,"Member",'Game Records'!$K$5:$K$504,"Loss"))/B6)</x:f>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -18463,27 +18465,27 @@
         <x:v>Non-Member</x:v>
       </x:c>
       <x:c r="B7" s="50" t="n">
-        <x:f>COUNTIFS('Game Records'!$L$5:$L$504,"Non-Member",'Game Records'!$K$5:$K$504,"&lt;&gt;Subscription")</x:f>
+        <x:f>COUNTIFS('Game Records'!$A$5:$A$504,"&lt;&gt;",'Game Records'!$L$5:$L$504,"Non-Member",'Game Records'!$K$5:$K$504,"&lt;&gt;Subscription")</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="C7" s="58" t="n">
-        <x:f>SUMIFS('Game Records'!$U$5:$U$504,'Game Records'!$L$5:$L$504,"Non-Member")</x:f>
+        <x:f>SUMIFS('Game Records'!$U$5:$U$504,'Game Records'!$A$5:$A$504,"&lt;&gt;",'Game Records'!$L$5:$L$504,"Non-Member")</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="D7" s="58" t="str">
         <x:f>IF(B7=0,"",C7/B7)</x:f>
       </x:c>
       <x:c r="E7" s="60" t="str">
-        <x:f>IF(COUNTIFS('Game Records'!$L$5:$L$504,"Non-Member",'Game Records'!$J$5:$J$504,"&lt;&gt;")=0,"",SUMIFS('Game Records'!$J$5:$J$504,'Game Records'!$L$5:$L$504,"Non-Member")/COUNTIFS('Game Records'!$L$5:$L$504,"Non-Member",'Game Records'!$J$5:$J$504,"&lt;&gt;"))</x:f>
+        <x:f>IF(COUNTIFS('Game Records'!$A$5:$A$504,"&lt;&gt;",'Game Records'!$L$5:$L$504,"Non-Member",'Game Records'!$J$5:$J$504,"&lt;&gt;")=0,"",SUMIFS('Game Records'!$J$5:$J$504,'Game Records'!$A$5:$A$504,"&lt;&gt;",'Game Records'!$L$5:$L$504,"Non-Member")/COUNTIFS('Game Records'!$A$5:$A$504,"&lt;&gt;",'Game Records'!$L$5:$L$504,"Non-Member",'Game Records'!$J$5:$J$504,"&lt;&gt;"))</x:f>
       </x:c>
       <x:c r="F7" s="60" t="str">
-        <x:f>IF(B7=0,"",COUNTIFS('Game Records'!$L$5:$L$504,"Non-Member",'Game Records'!$K$5:$K$504,"Profit")/B7)</x:f>
+        <x:f>IF(B7=0,"",COUNTIFS('Game Records'!$A$5:$A$504,"&lt;&gt;",'Game Records'!$L$5:$L$504,"Non-Member",'Game Records'!$K$5:$K$504,"Profit")/B7)</x:f>
       </x:c>
       <x:c r="G7" s="60" t="str">
-        <x:f>IF(B7=0,"",COUNTIFS('Game Records'!$L$5:$L$504,"Non-Member",'Game Records'!$K$5:$K$504,"Draw")/B7)</x:f>
+        <x:f>IF(B7=0,"",COUNTIFS('Game Records'!$A$5:$A$504,"&lt;&gt;",'Game Records'!$L$5:$L$504,"Non-Member",'Game Records'!$K$5:$K$504,"Draw")/B7)</x:f>
       </x:c>
       <x:c r="H7" s="60" t="str">
-        <x:f>IF(B7=0,"",COUNTIFS('Game Records'!$L$5:$L$504,"Non-Member",'Game Records'!$K$5:$K$504,"Disqualified")+COUNTIFS('Game Records'!$L$5:$L$504,"Non-Member",'Game Records'!$K$5:$K$504,"Loss")/B7)</x:f>
+        <x:f>IF(B7=0,"",(COUNTIFS('Game Records'!$A$5:$A$504,"&lt;&gt;",'Game Records'!$L$5:$L$504,"Non-Member",'Game Records'!$K$5:$K$504,"Disqualified")+COUNTIFS('Game Records'!$A$5:$A$504,"&lt;&gt;",'Game Records'!$L$5:$L$504,"Non-Member",'Game Records'!$K$5:$K$504,"Loss"))/B7)</x:f>
       </x:c>
     </x:row>
     <x:row r="8">
@@ -18549,27 +18551,27 @@
         <x:v>1 Week</x:v>
       </x:c>
       <x:c r="B12" s="50" t="n">
-        <x:f>COUNTIFS('Game Records'!$Q$5:$Q$504,1,'Game Records'!$K$5:$K$504,"&lt;&gt;Subscription")</x:f>
+        <x:f>COUNTIFS('Game Records'!$A$5:$A$504,"&lt;&gt;",'Game Records'!$Q$5:$Q$504,1,'Game Records'!$K$5:$K$504,"&lt;&gt;Subscription")</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="C12" s="58" t="n">
-        <x:f>SUMIFS('Game Records'!$U$5:$U$504,'Game Records'!$Q$5:$Q$504,1)</x:f>
+        <x:f>SUMIFS('Game Records'!$U$5:$U$504,'Game Records'!$A$5:$A$504,"&lt;&gt;",'Game Records'!$Q$5:$Q$504,1)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="D12" s="58" t="str">
         <x:f>IF(B12=0,"",C12/B12)</x:f>
       </x:c>
       <x:c r="E12" s="60" t="str">
-        <x:f>IF(COUNTIFS('Game Records'!$Q$5:$Q$504,1,'Game Records'!$J$5:$J$504,"&lt;&gt;")=0,"",SUMIFS('Game Records'!$J$5:$J$504,'Game Records'!$Q$5:$Q$504,1)/COUNTIFS('Game Records'!$Q$5:$Q$504,1,'Game Records'!$J$5:$J$504,"&lt;&gt;"))</x:f>
+        <x:f>IF(COUNTIFS('Game Records'!$A$5:$A$504,"&lt;&gt;",'Game Records'!$Q$5:$Q$504,1,'Game Records'!$J$5:$J$504,"&lt;&gt;")=0,"",SUMIFS('Game Records'!$J$5:$J$504,'Game Records'!$A$5:$A$504,"&lt;&gt;",'Game Records'!$Q$5:$Q$504,1)/COUNTIFS('Game Records'!$A$5:$A$504,"&lt;&gt;",'Game Records'!$Q$5:$Q$504,1,'Game Records'!$J$5:$J$504,"&lt;&gt;"))</x:f>
       </x:c>
       <x:c r="F12" s="60" t="str">
-        <x:f>IF(B12=0,"",COUNTIFS('Game Records'!$Q$5:$Q$504,1,'Game Records'!$K$5:$K$504,"Profit")/B12)</x:f>
+        <x:f>IF(B12=0,"",COUNTIFS('Game Records'!$A$5:$A$504,"&lt;&gt;",'Game Records'!$Q$5:$Q$504,1,'Game Records'!$K$5:$K$504,"Profit")/B12)</x:f>
       </x:c>
       <x:c r="G12" s="60" t="str">
-        <x:f>IF(B12=0,"",COUNTIFS('Game Records'!$Q$5:$Q$504,1,'Game Records'!$K$5:$K$504,"Draw")/B12)</x:f>
+        <x:f>IF(B12=0,"",COUNTIFS('Game Records'!$A$5:$A$504,"&lt;&gt;",'Game Records'!$Q$5:$Q$504,1,'Game Records'!$K$5:$K$504,"Draw")/B12)</x:f>
       </x:c>
       <x:c r="H12" s="60" t="str">
-        <x:f>IF(B12=0,"",COUNTIFS('Game Records'!$Q$5:$Q$504,1,'Game Records'!$K$5:$K$504,"Disqualified")+COUNTIFS('Game Records'!$Q$5:$Q$504,1,'Game Records'!$K$5:$K$504,"Loss")/B12)</x:f>
+        <x:f>IF(B12=0,"",(COUNTIFS('Game Records'!$A$5:$A$504,"&lt;&gt;",'Game Records'!$Q$5:$Q$504,1,'Game Records'!$K$5:$K$504,"Disqualified")+COUNTIFS('Game Records'!$A$5:$A$504,"&lt;&gt;",'Game Records'!$Q$5:$Q$504,1,'Game Records'!$K$5:$K$504,"Loss"))/B12)</x:f>
       </x:c>
     </x:row>
     <x:row r="13">
@@ -18577,27 +18579,27 @@
         <x:v>2 Weeks</x:v>
       </x:c>
       <x:c r="B13" s="50" t="n">
-        <x:f>COUNTIFS('Game Records'!$Q$5:$Q$504,2,'Game Records'!$K$5:$K$504,"&lt;&gt;Subscription")</x:f>
+        <x:f>COUNTIFS('Game Records'!$A$5:$A$504,"&lt;&gt;",'Game Records'!$Q$5:$Q$504,2,'Game Records'!$K$5:$K$504,"&lt;&gt;Subscription")</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="C13" s="58" t="n">
-        <x:f>SUMIFS('Game Records'!$U$5:$U$504,'Game Records'!$Q$5:$Q$504,2)</x:f>
+        <x:f>SUMIFS('Game Records'!$U$5:$U$504,'Game Records'!$A$5:$A$504,"&lt;&gt;",'Game Records'!$Q$5:$Q$504,2)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="D13" s="58" t="str">
         <x:f>IF(B13=0,"",C13/B13)</x:f>
       </x:c>
       <x:c r="E13" s="60" t="str">
-        <x:f>IF(COUNTIFS('Game Records'!$Q$5:$Q$504,2,'Game Records'!$J$5:$J$504,"&lt;&gt;")=0,"",SUMIFS('Game Records'!$J$5:$J$504,'Game Records'!$Q$5:$Q$504,2)/COUNTIFS('Game Records'!$Q$5:$Q$504,2,'Game Records'!$J$5:$J$504,"&lt;&gt;"))</x:f>
+        <x:f>IF(COUNTIFS('Game Records'!$A$5:$A$504,"&lt;&gt;",'Game Records'!$Q$5:$Q$504,2,'Game Records'!$J$5:$J$504,"&lt;&gt;")=0,"",SUMIFS('Game Records'!$J$5:$J$504,'Game Records'!$A$5:$A$504,"&lt;&gt;",'Game Records'!$Q$5:$Q$504,2)/COUNTIFS('Game Records'!$A$5:$A$504,"&lt;&gt;",'Game Records'!$Q$5:$Q$504,2,'Game Records'!$J$5:$J$504,"&lt;&gt;"))</x:f>
       </x:c>
       <x:c r="F13" s="60" t="str">
-        <x:f>IF(B13=0,"",COUNTIFS('Game Records'!$Q$5:$Q$504,2,'Game Records'!$K$5:$K$504,"Profit")/B13)</x:f>
+        <x:f>IF(B13=0,"",COUNTIFS('Game Records'!$A$5:$A$504,"&lt;&gt;",'Game Records'!$Q$5:$Q$504,2,'Game Records'!$K$5:$K$504,"Profit")/B13)</x:f>
       </x:c>
       <x:c r="G13" s="60" t="str">
-        <x:f>IF(B13=0,"",COUNTIFS('Game Records'!$Q$5:$Q$504,2,'Game Records'!$K$5:$K$504,"Draw")/B13)</x:f>
+        <x:f>IF(B13=0,"",COUNTIFS('Game Records'!$A$5:$A$504,"&lt;&gt;",'Game Records'!$Q$5:$Q$504,2,'Game Records'!$K$5:$K$504,"Draw")/B13)</x:f>
       </x:c>
       <x:c r="H13" s="60" t="str">
-        <x:f>IF(B13=0,"",COUNTIFS('Game Records'!$Q$5:$Q$504,2,'Game Records'!$K$5:$K$504,"Disqualified")+COUNTIFS('Game Records'!$Q$5:$Q$504,2,'Game Records'!$K$5:$K$504,"Loss")/B13)</x:f>
+        <x:f>IF(B13=0,"",(COUNTIFS('Game Records'!$A$5:$A$504,"&lt;&gt;",'Game Records'!$Q$5:$Q$504,2,'Game Records'!$K$5:$K$504,"Disqualified")+COUNTIFS('Game Records'!$A$5:$A$504,"&lt;&gt;",'Game Records'!$Q$5:$Q$504,2,'Game Records'!$K$5:$K$504,"Loss"))/B13)</x:f>
       </x:c>
     </x:row>
     <x:row r="14">
@@ -18605,27 +18607,27 @@
         <x:v>3 Weeks</x:v>
       </x:c>
       <x:c r="B14" s="50" t="n">
-        <x:f>COUNTIFS('Game Records'!$Q$5:$Q$504,3,'Game Records'!$K$5:$K$504,"&lt;&gt;Subscription")</x:f>
+        <x:f>COUNTIFS('Game Records'!$A$5:$A$504,"&lt;&gt;",'Game Records'!$Q$5:$Q$504,3,'Game Records'!$K$5:$K$504,"&lt;&gt;Subscription")</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="C14" s="58" t="n">
-        <x:f>SUMIFS('Game Records'!$U$5:$U$504,'Game Records'!$Q$5:$Q$504,3)</x:f>
+        <x:f>SUMIFS('Game Records'!$U$5:$U$504,'Game Records'!$A$5:$A$504,"&lt;&gt;",'Game Records'!$Q$5:$Q$504,3)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="D14" s="58" t="str">
         <x:f>IF(B14=0,"",C14/B14)</x:f>
       </x:c>
       <x:c r="E14" s="60" t="str">
-        <x:f>IF(COUNTIFS('Game Records'!$Q$5:$Q$504,3,'Game Records'!$J$5:$J$504,"&lt;&gt;")=0,"",SUMIFS('Game Records'!$J$5:$J$504,'Game Records'!$Q$5:$Q$504,3)/COUNTIFS('Game Records'!$Q$5:$Q$504,3,'Game Records'!$J$5:$J$504,"&lt;&gt;"))</x:f>
+        <x:f>IF(COUNTIFS('Game Records'!$A$5:$A$504,"&lt;&gt;",'Game Records'!$Q$5:$Q$504,3,'Game Records'!$J$5:$J$504,"&lt;&gt;")=0,"",SUMIFS('Game Records'!$J$5:$J$504,'Game Records'!$A$5:$A$504,"&lt;&gt;",'Game Records'!$Q$5:$Q$504,3)/COUNTIFS('Game Records'!$A$5:$A$504,"&lt;&gt;",'Game Records'!$Q$5:$Q$504,3,'Game Records'!$J$5:$J$504,"&lt;&gt;"))</x:f>
       </x:c>
       <x:c r="F14" s="60" t="str">
-        <x:f>IF(B14=0,"",COUNTIFS('Game Records'!$Q$5:$Q$504,3,'Game Records'!$K$5:$K$504,"Profit")/B14)</x:f>
+        <x:f>IF(B14=0,"",COUNTIFS('Game Records'!$A$5:$A$504,"&lt;&gt;",'Game Records'!$Q$5:$Q$504,3,'Game Records'!$K$5:$K$504,"Profit")/B14)</x:f>
       </x:c>
       <x:c r="G14" s="60" t="str">
-        <x:f>IF(B14=0,"",COUNTIFS('Game Records'!$Q$5:$Q$504,3,'Game Records'!$K$5:$K$504,"Draw")/B14)</x:f>
+        <x:f>IF(B14=0,"",COUNTIFS('Game Records'!$A$5:$A$504,"&lt;&gt;",'Game Records'!$Q$5:$Q$504,3,'Game Records'!$K$5:$K$504,"Draw")/B14)</x:f>
       </x:c>
       <x:c r="H14" s="60" t="str">
-        <x:f>IF(B14=0,"",COUNTIFS('Game Records'!$Q$5:$Q$504,3,'Game Records'!$K$5:$K$504,"Disqualified")+COUNTIFS('Game Records'!$Q$5:$Q$504,3,'Game Records'!$K$5:$K$504,"Loss")/B14)</x:f>
+        <x:f>IF(B14=0,"",(COUNTIFS('Game Records'!$A$5:$A$504,"&lt;&gt;",'Game Records'!$Q$5:$Q$504,3,'Game Records'!$K$5:$K$504,"Disqualified")+COUNTIFS('Game Records'!$A$5:$A$504,"&lt;&gt;",'Game Records'!$Q$5:$Q$504,3,'Game Records'!$K$5:$K$504,"Loss"))/B14)</x:f>
       </x:c>
     </x:row>
     <x:row r="15">
@@ -18633,27 +18635,27 @@
         <x:v>4 Weeks</x:v>
       </x:c>
       <x:c r="B15" s="50" t="n">
-        <x:f>COUNTIFS('Game Records'!$Q$5:$Q$504,4,'Game Records'!$K$5:$K$504,"&lt;&gt;Subscription")</x:f>
+        <x:f>COUNTIFS('Game Records'!$A$5:$A$504,"&lt;&gt;",'Game Records'!$Q$5:$Q$504,4,'Game Records'!$K$5:$K$504,"&lt;&gt;Subscription")</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="C15" s="58" t="n">
-        <x:f>SUMIFS('Game Records'!$U$5:$U$504,'Game Records'!$Q$5:$Q$504,4)</x:f>
+        <x:f>SUMIFS('Game Records'!$U$5:$U$504,'Game Records'!$A$5:$A$504,"&lt;&gt;",'Game Records'!$Q$5:$Q$504,4)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="D15" s="58" t="str">
         <x:f>IF(B15=0,"",C15/B15)</x:f>
       </x:c>
       <x:c r="E15" s="60" t="str">
-        <x:f>IF(COUNTIFS('Game Records'!$Q$5:$Q$504,4,'Game Records'!$J$5:$J$504,"&lt;&gt;")=0,"",SUMIFS('Game Records'!$J$5:$J$504,'Game Records'!$Q$5:$Q$504,4)/COUNTIFS('Game Records'!$Q$5:$Q$504,4,'Game Records'!$J$5:$J$504,"&lt;&gt;"))</x:f>
+        <x:f>IF(COUNTIFS('Game Records'!$A$5:$A$504,"&lt;&gt;",'Game Records'!$Q$5:$Q$504,4,'Game Records'!$J$5:$J$504,"&lt;&gt;")=0,"",SUMIFS('Game Records'!$J$5:$J$504,'Game Records'!$A$5:$A$504,"&lt;&gt;",'Game Records'!$Q$5:$Q$504,4)/COUNTIFS('Game Records'!$A$5:$A$504,"&lt;&gt;",'Game Records'!$Q$5:$Q$504,4,'Game Records'!$J$5:$J$504,"&lt;&gt;"))</x:f>
       </x:c>
       <x:c r="F15" s="60" t="str">
-        <x:f>IF(B15=0,"",COUNTIFS('Game Records'!$Q$5:$Q$504,4,'Game Records'!$K$5:$K$504,"Profit")/B15)</x:f>
+        <x:f>IF(B15=0,"",COUNTIFS('Game Records'!$A$5:$A$504,"&lt;&gt;",'Game Records'!$Q$5:$Q$504,4,'Game Records'!$K$5:$K$504,"Profit")/B15)</x:f>
       </x:c>
       <x:c r="G15" s="60" t="str">
-        <x:f>IF(B15=0,"",COUNTIFS('Game Records'!$Q$5:$Q$504,4,'Game Records'!$K$5:$K$504,"Draw")/B15)</x:f>
+        <x:f>IF(B15=0,"",COUNTIFS('Game Records'!$A$5:$A$504,"&lt;&gt;",'Game Records'!$Q$5:$Q$504,4,'Game Records'!$K$5:$K$504,"Draw")/B15)</x:f>
       </x:c>
       <x:c r="H15" s="60" t="str">
-        <x:f>IF(B15=0,"",COUNTIFS('Game Records'!$Q$5:$Q$504,4,'Game Records'!$K$5:$K$504,"Disqualified")+COUNTIFS('Game Records'!$Q$5:$Q$504,4,'Game Records'!$K$5:$K$504,"Loss")/B15)</x:f>
+        <x:f>IF(B15=0,"",(COUNTIFS('Game Records'!$A$5:$A$504,"&lt;&gt;",'Game Records'!$Q$5:$Q$504,4,'Game Records'!$K$5:$K$504,"Disqualified")+COUNTIFS('Game Records'!$A$5:$A$504,"&lt;&gt;",'Game Records'!$Q$5:$Q$504,4,'Game Records'!$K$5:$K$504,"Loss"))/B15)</x:f>
       </x:c>
     </x:row>
     <x:row r="16">
@@ -18661,27 +18663,27 @@
         <x:v>5 Weeks</x:v>
       </x:c>
       <x:c r="B16" s="50" t="n">
-        <x:f>COUNTIFS('Game Records'!$Q$5:$Q$504,5,'Game Records'!$K$5:$K$504,"&lt;&gt;Subscription")</x:f>
+        <x:f>COUNTIFS('Game Records'!$A$5:$A$504,"&lt;&gt;",'Game Records'!$Q$5:$Q$504,5,'Game Records'!$K$5:$K$504,"&lt;&gt;Subscription")</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="C16" s="58" t="n">
-        <x:f>SUMIFS('Game Records'!$U$5:$U$504,'Game Records'!$Q$5:$Q$504,5)</x:f>
+        <x:f>SUMIFS('Game Records'!$U$5:$U$504,'Game Records'!$A$5:$A$504,"&lt;&gt;",'Game Records'!$Q$5:$Q$504,5)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="D16" s="58" t="str">
         <x:f>IF(B16=0,"",C16/B16)</x:f>
       </x:c>
       <x:c r="E16" s="60" t="str">
-        <x:f>IF(COUNTIFS('Game Records'!$Q$5:$Q$504,5,'Game Records'!$J$5:$J$504,"&lt;&gt;")=0,"",SUMIFS('Game Records'!$J$5:$J$504,'Game Records'!$Q$5:$Q$504,5)/COUNTIFS('Game Records'!$Q$5:$Q$504,5,'Game Records'!$J$5:$J$504,"&lt;&gt;"))</x:f>
+        <x:f>IF(COUNTIFS('Game Records'!$A$5:$A$504,"&lt;&gt;",'Game Records'!$Q$5:$Q$504,5,'Game Records'!$J$5:$J$504,"&lt;&gt;")=0,"",SUMIFS('Game Records'!$J$5:$J$504,'Game Records'!$A$5:$A$504,"&lt;&gt;",'Game Records'!$Q$5:$Q$504,5)/COUNTIFS('Game Records'!$A$5:$A$504,"&lt;&gt;",'Game Records'!$Q$5:$Q$504,5,'Game Records'!$J$5:$J$504,"&lt;&gt;"))</x:f>
       </x:c>
       <x:c r="F16" s="60" t="str">
-        <x:f>IF(B16=0,"",COUNTIFS('Game Records'!$Q$5:$Q$504,5,'Game Records'!$K$5:$K$504,"Profit")/B16)</x:f>
+        <x:f>IF(B16=0,"",COUNTIFS('Game Records'!$A$5:$A$504,"&lt;&gt;",'Game Records'!$Q$5:$Q$504,5,'Game Records'!$K$5:$K$504,"Profit")/B16)</x:f>
       </x:c>
       <x:c r="G16" s="60" t="str">
-        <x:f>IF(B16=0,"",COUNTIFS('Game Records'!$Q$5:$Q$504,5,'Game Records'!$K$5:$K$504,"Draw")/B16)</x:f>
+        <x:f>IF(B16=0,"",COUNTIFS('Game Records'!$A$5:$A$504,"&lt;&gt;",'Game Records'!$Q$5:$Q$504,5,'Game Records'!$K$5:$K$504,"Draw")/B16)</x:f>
       </x:c>
       <x:c r="H16" s="60" t="str">
-        <x:f>IF(B16=0,"",COUNTIFS('Game Records'!$Q$5:$Q$504,5,'Game Records'!$K$5:$K$504,"Disqualified")+COUNTIFS('Game Records'!$Q$5:$Q$504,5,'Game Records'!$K$5:$K$504,"Loss")/B16)</x:f>
+        <x:f>IF(B16=0,"",(COUNTIFS('Game Records'!$A$5:$A$504,"&lt;&gt;",'Game Records'!$Q$5:$Q$504,5,'Game Records'!$K$5:$K$504,"Disqualified")+COUNTIFS('Game Records'!$A$5:$A$504,"&lt;&gt;",'Game Records'!$Q$5:$Q$504,5,'Game Records'!$K$5:$K$504,"Loss"))/B16)</x:f>
       </x:c>
     </x:row>
     <x:row r="17">
@@ -18689,27 +18691,27 @@
         <x:v>6 Weeks</x:v>
       </x:c>
       <x:c r="B17" s="50" t="n">
-        <x:f>COUNTIFS('Game Records'!$Q$5:$Q$504,6,'Game Records'!$K$5:$K$504,"&lt;&gt;Subscription")</x:f>
+        <x:f>COUNTIFS('Game Records'!$A$5:$A$504,"&lt;&gt;",'Game Records'!$Q$5:$Q$504,6,'Game Records'!$K$5:$K$504,"&lt;&gt;Subscription")</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="C17" s="58" t="n">
-        <x:f>SUMIFS('Game Records'!$U$5:$U$504,'Game Records'!$Q$5:$Q$504,6)</x:f>
+        <x:f>SUMIFS('Game Records'!$U$5:$U$504,'Game Records'!$A$5:$A$504,"&lt;&gt;",'Game Records'!$Q$5:$Q$504,6)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="D17" s="58" t="str">
         <x:f>IF(B17=0,"",C17/B17)</x:f>
       </x:c>
       <x:c r="E17" s="60" t="str">
-        <x:f>IF(COUNTIFS('Game Records'!$Q$5:$Q$504,6,'Game Records'!$J$5:$J$504,"&lt;&gt;")=0,"",SUMIFS('Game Records'!$J$5:$J$504,'Game Records'!$Q$5:$Q$504,6)/COUNTIFS('Game Records'!$Q$5:$Q$504,6,'Game Records'!$J$5:$J$504,"&lt;&gt;"))</x:f>
+        <x:f>IF(COUNTIFS('Game Records'!$A$5:$A$504,"&lt;&gt;",'Game Records'!$Q$5:$Q$504,6,'Game Records'!$J$5:$J$504,"&lt;&gt;")=0,"",SUMIFS('Game Records'!$J$5:$J$504,'Game Records'!$A$5:$A$504,"&lt;&gt;",'Game Records'!$Q$5:$Q$504,6)/COUNTIFS('Game Records'!$A$5:$A$504,"&lt;&gt;",'Game Records'!$Q$5:$Q$504,6,'Game Records'!$J$5:$J$504,"&lt;&gt;"))</x:f>
       </x:c>
       <x:c r="F17" s="60" t="str">
-        <x:f>IF(B17=0,"",COUNTIFS('Game Records'!$Q$5:$Q$504,6,'Game Records'!$K$5:$K$504,"Profit")/B17)</x:f>
+        <x:f>IF(B17=0,"",COUNTIFS('Game Records'!$A$5:$A$504,"&lt;&gt;",'Game Records'!$Q$5:$Q$504,6,'Game Records'!$K$5:$K$504,"Profit")/B17)</x:f>
       </x:c>
       <x:c r="G17" s="60" t="str">
-        <x:f>IF(B17=0,"",COUNTIFS('Game Records'!$Q$5:$Q$504,6,'Game Records'!$K$5:$K$504,"Draw")/B17)</x:f>
+        <x:f>IF(B17=0,"",COUNTIFS('Game Records'!$A$5:$A$504,"&lt;&gt;",'Game Records'!$Q$5:$Q$504,6,'Game Records'!$K$5:$K$504,"Draw")/B17)</x:f>
       </x:c>
       <x:c r="H17" s="60" t="str">
-        <x:f>IF(B17=0,"",COUNTIFS('Game Records'!$Q$5:$Q$504,6,'Game Records'!$K$5:$K$504,"Disqualified")+COUNTIFS('Game Records'!$Q$5:$Q$504,6,'Game Records'!$K$5:$K$504,"Loss")/B17)</x:f>
+        <x:f>IF(B17=0,"",(COUNTIFS('Game Records'!$A$5:$A$504,"&lt;&gt;",'Game Records'!$Q$5:$Q$504,6,'Game Records'!$K$5:$K$504,"Disqualified")+COUNTIFS('Game Records'!$A$5:$A$504,"&lt;&gt;",'Game Records'!$Q$5:$Q$504,6,'Game Records'!$K$5:$K$504,"Loss"))/B17)</x:f>
       </x:c>
     </x:row>
     <x:row r="18">
@@ -18717,27 +18719,27 @@
         <x:v>7 Weeks</x:v>
       </x:c>
       <x:c r="B18" s="50" t="n">
-        <x:f>COUNTIFS('Game Records'!$Q$5:$Q$504,7,'Game Records'!$K$5:$K$504,"&lt;&gt;Subscription")</x:f>
+        <x:f>COUNTIFS('Game Records'!$A$5:$A$504,"&lt;&gt;",'Game Records'!$Q$5:$Q$504,7,'Game Records'!$K$5:$K$504,"&lt;&gt;Subscription")</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="C18" s="58" t="n">
-        <x:f>SUMIFS('Game Records'!$U$5:$U$504,'Game Records'!$Q$5:$Q$504,7)</x:f>
+        <x:f>SUMIFS('Game Records'!$U$5:$U$504,'Game Records'!$A$5:$A$504,"&lt;&gt;",'Game Records'!$Q$5:$Q$504,7)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="D18" s="58" t="str">
         <x:f>IF(B18=0,"",C18/B18)</x:f>
       </x:c>
       <x:c r="E18" s="60" t="str">
-        <x:f>IF(COUNTIFS('Game Records'!$Q$5:$Q$504,7,'Game Records'!$J$5:$J$504,"&lt;&gt;")=0,"",SUMIFS('Game Records'!$J$5:$J$504,'Game Records'!$Q$5:$Q$504,7)/COUNTIFS('Game Records'!$Q$5:$Q$504,7,'Game Records'!$J$5:$J$504,"&lt;&gt;"))</x:f>
+        <x:f>IF(COUNTIFS('Game Records'!$A$5:$A$504,"&lt;&gt;",'Game Records'!$Q$5:$Q$504,7,'Game Records'!$J$5:$J$504,"&lt;&gt;")=0,"",SUMIFS('Game Records'!$J$5:$J$504,'Game Records'!$A$5:$A$504,"&lt;&gt;",'Game Records'!$Q$5:$Q$504,7)/COUNTIFS('Game Records'!$A$5:$A$504,"&lt;&gt;",'Game Records'!$Q$5:$Q$504,7,'Game Records'!$J$5:$J$504,"&lt;&gt;"))</x:f>
       </x:c>
       <x:c r="F18" s="60" t="str">
-        <x:f>IF(B18=0,"",COUNTIFS('Game Records'!$Q$5:$Q$504,7,'Game Records'!$K$5:$K$504,"Profit")/B18)</x:f>
+        <x:f>IF(B18=0,"",COUNTIFS('Game Records'!$A$5:$A$504,"&lt;&gt;",'Game Records'!$Q$5:$Q$504,7,'Game Records'!$K$5:$K$504,"Profit")/B18)</x:f>
       </x:c>
       <x:c r="G18" s="60" t="str">
-        <x:f>IF(B18=0,"",COUNTIFS('Game Records'!$Q$5:$Q$504,7,'Game Records'!$K$5:$K$504,"Draw")/B18)</x:f>
+        <x:f>IF(B18=0,"",COUNTIFS('Game Records'!$A$5:$A$504,"&lt;&gt;",'Game Records'!$Q$5:$Q$504,7,'Game Records'!$K$5:$K$504,"Draw")/B18)</x:f>
       </x:c>
       <x:c r="H18" s="60" t="str">
-        <x:f>IF(B18=0,"",COUNTIFS('Game Records'!$Q$5:$Q$504,7,'Game Records'!$K$5:$K$504,"Disqualified")+COUNTIFS('Game Records'!$Q$5:$Q$504,7,'Game Records'!$K$5:$K$504,"Loss")/B18)</x:f>
+        <x:f>IF(B18=0,"",(COUNTIFS('Game Records'!$A$5:$A$504,"&lt;&gt;",'Game Records'!$Q$5:$Q$504,7,'Game Records'!$K$5:$K$504,"Disqualified")+COUNTIFS('Game Records'!$A$5:$A$504,"&lt;&gt;",'Game Records'!$Q$5:$Q$504,7,'Game Records'!$K$5:$K$504,"Loss"))/B18)</x:f>
       </x:c>
     </x:row>
     <x:row r="19">
@@ -18745,27 +18747,27 @@
         <x:v>8+ Weeks</x:v>
       </x:c>
       <x:c r="B19" s="50" t="n">
-        <x:f>COUNTIFS('Game Records'!$Q$5:$Q$504,"&gt;=8",'Game Records'!$K$5:$K$504,"&lt;&gt;Subscription")</x:f>
+        <x:f>COUNTIFS('Game Records'!$A$5:$A$504,"&lt;&gt;",'Game Records'!$Q$5:$Q$504,"&gt;=8",'Game Records'!$K$5:$K$504,"&lt;&gt;Subscription")</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="C19" s="58" t="n">
-        <x:f>SUMIFS('Game Records'!$U$5:$U$504,'Game Records'!$Q$5:$Q$504,"&gt;=8")</x:f>
+        <x:f>SUMIFS('Game Records'!$U$5:$U$504,'Game Records'!$A$5:$A$504,"&lt;&gt;",'Game Records'!$Q$5:$Q$504,"&gt;=8")</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="D19" s="58" t="str">
         <x:f>IF(B19=0,"",C19/B19)</x:f>
       </x:c>
       <x:c r="E19" s="60" t="str">
-        <x:f>IF(COUNTIFS('Game Records'!$Q$5:$Q$504,"&gt;=8",'Game Records'!$J$5:$J$504,"&lt;&gt;")=0,"",SUMIFS('Game Records'!$J$5:$J$504,'Game Records'!$Q$5:$Q$504,"&gt;=8")/COUNTIFS('Game Records'!$Q$5:$Q$504,"&gt;=8",'Game Records'!$J$5:$J$504,"&lt;&gt;"))</x:f>
+        <x:f>IF(COUNTIFS('Game Records'!$A$5:$A$504,"&lt;&gt;",'Game Records'!$Q$5:$Q$504,"&gt;=8",'Game Records'!$J$5:$J$504,"&lt;&gt;")=0,"",SUMIFS('Game Records'!$J$5:$J$504,'Game Records'!$A$5:$A$504,"&lt;&gt;",'Game Records'!$Q$5:$Q$504,"&gt;=8")/COUNTIFS('Game Records'!$A$5:$A$504,"&lt;&gt;",'Game Records'!$Q$5:$Q$504,"&gt;=8",'Game Records'!$J$5:$J$504,"&lt;&gt;"))</x:f>
       </x:c>
       <x:c r="F19" s="60" t="str">
-        <x:f>IF(B19=0,"",COUNTIFS('Game Records'!$Q$5:$Q$504,"&gt;=8",'Game Records'!$K$5:$K$504,"Profit")/B19)</x:f>
+        <x:f>IF(B19=0,"",COUNTIFS('Game Records'!$A$5:$A$504,"&lt;&gt;",'Game Records'!$Q$5:$Q$504,"&gt;=8",'Game Records'!$K$5:$K$504,"Profit")/B19)</x:f>
       </x:c>
       <x:c r="G19" s="60" t="str">
-        <x:f>IF(B19=0,"",COUNTIFS('Game Records'!$Q$5:$Q$504,"&gt;=8",'Game Records'!$K$5:$K$504,"Draw")/B19)</x:f>
+        <x:f>IF(B19=0,"",COUNTIFS('Game Records'!$A$5:$A$504,"&lt;&gt;",'Game Records'!$Q$5:$Q$504,"&gt;=8",'Game Records'!$K$5:$K$504,"Draw")/B19)</x:f>
       </x:c>
       <x:c r="H19" s="60" t="str">
-        <x:f>IF(B19=0,"",COUNTIFS('Game Records'!$Q$5:$Q$504,"&gt;=8",'Game Records'!$K$5:$K$504,"Disqualified")+COUNTIFS('Game Records'!$Q$5:$Q$504,"&gt;=8",'Game Records'!$K$5:$K$504,"Loss")/B19)</x:f>
+        <x:f>IF(B19=0,"",(COUNTIFS('Game Records'!$A$5:$A$504,"&lt;&gt;",'Game Records'!$Q$5:$Q$504,"&gt;=8",'Game Records'!$K$5:$K$504,"Disqualified")+COUNTIFS('Game Records'!$A$5:$A$504,"&lt;&gt;",'Game Records'!$Q$5:$Q$504,"&gt;=8",'Game Records'!$K$5:$K$504,"Loss"))/B19)</x:f>
       </x:c>
     </x:row>
     <x:row r="20">
@@ -18831,27 +18833,27 @@
         <x:v>Free</x:v>
       </x:c>
       <x:c r="B24" s="50" t="n">
-        <x:f>COUNTIFS('Game Records'!$E$5:$E$504,"0",'Game Records'!$K$5:$K$504,"&lt;&gt;Subscription")</x:f>
+        <x:f>COUNTIFS('Game Records'!$A$5:$A$504,"&lt;&gt;",'Game Records'!$E$5:$E$504,0,'Game Records'!$K$5:$K$504,"&lt;&gt;Subscription")</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="C24" s="58" t="n">
-        <x:f>SUMIFS('Game Records'!$U$5:$U$504,'Game Records'!$E$5:$E$504,"0")</x:f>
+        <x:f>SUMIFS('Game Records'!$U$5:$U$504,'Game Records'!$A$5:$A$504,"&lt;&gt;",'Game Records'!$E$5:$E$504,0)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="D24" s="58" t="str">
         <x:f>IF(B24=0,"",C24/B24)</x:f>
       </x:c>
       <x:c r="E24" s="60" t="str">
-        <x:f>IF(COUNTIFS('Game Records'!$E$5:$E$504,"0",'Game Records'!$J$5:$J$504,"&lt;&gt;")=0,"",SUMIFS('Game Records'!$J$5:$J$504,'Game Records'!$E$5:$E$504,"0")/COUNTIFS('Game Records'!$E$5:$E$504,"0",'Game Records'!$J$5:$J$504,"&lt;&gt;"))</x:f>
+        <x:f>IF(COUNTIFS('Game Records'!$A$5:$A$504,"&lt;&gt;",'Game Records'!$E$5:$E$504,0,'Game Records'!$J$5:$J$504,"&lt;&gt;")=0,"",SUMIFS('Game Records'!$J$5:$J$504,'Game Records'!$A$5:$A$504,"&lt;&gt;",'Game Records'!$E$5:$E$504,0)/COUNTIFS('Game Records'!$A$5:$A$504,"&lt;&gt;",'Game Records'!$E$5:$E$504,0,'Game Records'!$J$5:$J$504,"&lt;&gt;"))</x:f>
       </x:c>
       <x:c r="F24" s="60" t="str">
-        <x:f>IF(B24=0,"",COUNTIFS('Game Records'!$E$5:$E$504,"0",'Game Records'!$K$5:$K$504,"Profit")/B24)</x:f>
+        <x:f>IF(B24=0,"",COUNTIFS('Game Records'!$A$5:$A$504,"&lt;&gt;",'Game Records'!$E$5:$E$504,0,'Game Records'!$K$5:$K$504,"Profit")/B24)</x:f>
       </x:c>
       <x:c r="G24" s="60" t="str">
-        <x:f>IF(B24=0,"",COUNTIFS('Game Records'!$E$5:$E$504,"0",'Game Records'!$K$5:$K$504,"Draw")/B24)</x:f>
+        <x:f>IF(B24=0,"",COUNTIFS('Game Records'!$A$5:$A$504,"&lt;&gt;",'Game Records'!$E$5:$E$504,0,'Game Records'!$K$5:$K$504,"Draw")/B24)</x:f>
       </x:c>
       <x:c r="H24" s="60" t="str">
-        <x:f>IF(B24=0,"",COUNTIFS('Game Records'!$E$5:$E$504,"0",'Game Records'!$K$5:$K$504,"Disqualified")+COUNTIFS('Game Records'!$E$5:$E$504,"0",'Game Records'!$K$5:$K$504,"Loss")/B24)</x:f>
+        <x:f>IF(B24=0,"",(COUNTIFS('Game Records'!$A$5:$A$504,"&lt;&gt;",'Game Records'!$E$5:$E$504,0,'Game Records'!$K$5:$K$504,"Disqualified")+COUNTIFS('Game Records'!$A$5:$A$504,"&lt;&gt;",'Game Records'!$E$5:$E$504,0,'Game Records'!$K$5:$K$504,"Loss"))/B24)</x:f>
       </x:c>
     </x:row>
     <x:row r="25">
@@ -18859,27 +18861,27 @@
         <x:v>$20–$30</x:v>
       </x:c>
       <x:c r="B25" s="50" t="n">
-        <x:f>COUNTIFS('Game Records'!$E$5:$E$504,"&gt;=20",'Game Records'!$E$5:$E$504,"&lt;=30",'Game Records'!$K$5:$K$504,"&lt;&gt;Subscription")</x:f>
+        <x:f>COUNTIFS('Game Records'!$A$5:$A$504,"&lt;&gt;",'Game Records'!$E$5:$E$504,"&gt;=20",'Game Records'!$E$5:$E$504,"&lt;=30",'Game Records'!$K$5:$K$504,"&lt;&gt;Subscription")</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="C25" s="58" t="n">
-        <x:f>SUMIFS('Game Records'!$U$5:$U$504,'Game Records'!$E$5:$E$504,"&gt;=20",'Game Records'!$E$5:$E$504,"&lt;=30")</x:f>
+        <x:f>SUMIFS('Game Records'!$U$5:$U$504,'Game Records'!$A$5:$A$504,"&lt;&gt;",'Game Records'!$E$5:$E$504,"&gt;=20",'Game Records'!$E$5:$E$504,"&lt;=30")</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="D25" s="58" t="str">
         <x:f>IF(B25=0,"",C25/B25)</x:f>
       </x:c>
       <x:c r="E25" s="60" t="str">
-        <x:f>IF(COUNTIFS('Game Records'!$E$5:$E$504,"&gt;=20",'Game Records'!$E$5:$E$504,"&lt;=30",'Game Records'!$J$5:$J$504,"&lt;&gt;")=0,"",SUMIFS('Game Records'!$J$5:$J$504,'Game Records'!$E$5:$E$504,"&gt;=20",'Game Records'!$E$5:$E$504,"&lt;=30")/COUNTIFS('Game Records'!$E$5:$E$504,"&gt;=20",'Game Records'!$E$5:$E$504,"&lt;=30",'Game Records'!$J$5:$J$504,"&lt;&gt;"))</x:f>
+        <x:f>IF(COUNTIFS('Game Records'!$A$5:$A$504,"&lt;&gt;",'Game Records'!$E$5:$E$504,"&gt;=20",'Game Records'!$E$5:$E$504,"&lt;=30",'Game Records'!$J$5:$J$504,"&lt;&gt;")=0,"",SUMIFS('Game Records'!$J$5:$J$504,'Game Records'!$A$5:$A$504,"&lt;&gt;",'Game Records'!$E$5:$E$504,"&gt;=20",'Game Records'!$E$5:$E$504,"&lt;=30")/COUNTIFS('Game Records'!$A$5:$A$504,"&lt;&gt;",'Game Records'!$E$5:$E$504,"&gt;=20",'Game Records'!$E$5:$E$504,"&lt;=30",'Game Records'!$J$5:$J$504,"&lt;&gt;"))</x:f>
       </x:c>
       <x:c r="F25" s="60" t="str">
-        <x:f>IF(B25=0,"",COUNTIFS('Game Records'!$E$5:$E$504,"&gt;=20",'Game Records'!$E$5:$E$504,"&lt;=30",'Game Records'!$K$5:$K$504,"Profit")/B25)</x:f>
+        <x:f>IF(B25=0,"",COUNTIFS('Game Records'!$A$5:$A$504,"&lt;&gt;",'Game Records'!$E$5:$E$504,"&gt;=20",'Game Records'!$E$5:$E$504,"&lt;=30",'Game Records'!$K$5:$K$504,"Profit")/B25)</x:f>
       </x:c>
       <x:c r="G25" s="60" t="str">
-        <x:f>IF(B25=0,"",COUNTIFS('Game Records'!$E$5:$E$504,"&gt;=20",'Game Records'!$E$5:$E$504,"&lt;=30",'Game Records'!$K$5:$K$504,"Draw")/B25)</x:f>
+        <x:f>IF(B25=0,"",COUNTIFS('Game Records'!$A$5:$A$504,"&lt;&gt;",'Game Records'!$E$5:$E$504,"&gt;=20",'Game Records'!$E$5:$E$504,"&lt;=30",'Game Records'!$K$5:$K$504,"Draw")/B25)</x:f>
       </x:c>
       <x:c r="H25" s="60" t="str">
-        <x:f>IF(B25=0,"",COUNTIFS('Game Records'!$E$5:$E$504,"&gt;=20",'Game Records'!$E$5:$E$504,"&lt;=30",'Game Records'!$K$5:$K$504,"Disqualified")+COUNTIFS('Game Records'!$E$5:$E$504,"&gt;=20",'Game Records'!$E$5:$E$504,"&lt;=30",'Game Records'!$K$5:$K$504,"Loss")/B25)</x:f>
+        <x:f>IF(B25=0,"",(COUNTIFS('Game Records'!$A$5:$A$504,"&lt;&gt;",'Game Records'!$E$5:$E$504,"&gt;=20",'Game Records'!$E$5:$E$504,"&lt;=30",'Game Records'!$K$5:$K$504,"Disqualified")+COUNTIFS('Game Records'!$A$5:$A$504,"&lt;&gt;",'Game Records'!$E$5:$E$504,"&gt;=20",'Game Records'!$E$5:$E$504,"&lt;=30",'Game Records'!$K$5:$K$504,"Loss"))/B25)</x:f>
       </x:c>
     </x:row>
     <x:row r="26">
@@ -18887,27 +18889,27 @@
         <x:v>$40–$50</x:v>
       </x:c>
       <x:c r="B26" s="50" t="n">
-        <x:f>COUNTIFS('Game Records'!$E$5:$E$504,"&gt;=40",'Game Records'!$E$5:$E$504,"&lt;=50",'Game Records'!$K$5:$K$504,"&lt;&gt;Subscription")</x:f>
+        <x:f>COUNTIFS('Game Records'!$A$5:$A$504,"&lt;&gt;",'Game Records'!$E$5:$E$504,"&gt;=40",'Game Records'!$E$5:$E$504,"&lt;=50",'Game Records'!$K$5:$K$504,"&lt;&gt;Subscription")</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="C26" s="58" t="n">
-        <x:f>SUMIFS('Game Records'!$U$5:$U$504,'Game Records'!$E$5:$E$504,"&gt;=40",'Game Records'!$E$5:$E$504,"&lt;=50")</x:f>
+        <x:f>SUMIFS('Game Records'!$U$5:$U$504,'Game Records'!$A$5:$A$504,"&lt;&gt;",'Game Records'!$E$5:$E$504,"&gt;=40",'Game Records'!$E$5:$E$504,"&lt;=50")</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="D26" s="58" t="str">
         <x:f>IF(B26=0,"",C26/B26)</x:f>
       </x:c>
       <x:c r="E26" s="60" t="str">
-        <x:f>IF(COUNTIFS('Game Records'!$E$5:$E$504,"&gt;=40",'Game Records'!$E$5:$E$504,"&lt;=50",'Game Records'!$J$5:$J$504,"&lt;&gt;")=0,"",SUMIFS('Game Records'!$J$5:$J$504,'Game Records'!$E$5:$E$504,"&gt;=40",'Game Records'!$E$5:$E$504,"&lt;=50")/COUNTIFS('Game Records'!$E$5:$E$504,"&gt;=40",'Game Records'!$E$5:$E$504,"&lt;=50",'Game Records'!$J$5:$J$504,"&lt;&gt;"))</x:f>
+        <x:f>IF(COUNTIFS('Game Records'!$A$5:$A$504,"&lt;&gt;",'Game Records'!$E$5:$E$504,"&gt;=40",'Game Records'!$E$5:$E$504,"&lt;=50",'Game Records'!$J$5:$J$504,"&lt;&gt;")=0,"",SUMIFS('Game Records'!$J$5:$J$504,'Game Records'!$A$5:$A$504,"&lt;&gt;",'Game Records'!$E$5:$E$504,"&gt;=40",'Game Records'!$E$5:$E$504,"&lt;=50")/COUNTIFS('Game Records'!$A$5:$A$504,"&lt;&gt;",'Game Records'!$E$5:$E$504,"&gt;=40",'Game Records'!$E$5:$E$504,"&lt;=50",'Game Records'!$J$5:$J$504,"&lt;&gt;"))</x:f>
       </x:c>
       <x:c r="F26" s="60" t="str">
-        <x:f>IF(B26=0,"",COUNTIFS('Game Records'!$E$5:$E$504,"&gt;=40",'Game Records'!$E$5:$E$504,"&lt;=50",'Game Records'!$K$5:$K$504,"Profit")/B26)</x:f>
+        <x:f>IF(B26=0,"",COUNTIFS('Game Records'!$A$5:$A$504,"&lt;&gt;",'Game Records'!$E$5:$E$504,"&gt;=40",'Game Records'!$E$5:$E$504,"&lt;=50",'Game Records'!$K$5:$K$504,"Profit")/B26)</x:f>
       </x:c>
       <x:c r="G26" s="60" t="str">
-        <x:f>IF(B26=0,"",COUNTIFS('Game Records'!$E$5:$E$504,"&gt;=40",'Game Records'!$E$5:$E$504,"&lt;=50",'Game Records'!$K$5:$K$504,"Draw")/B26)</x:f>
+        <x:f>IF(B26=0,"",COUNTIFS('Game Records'!$A$5:$A$504,"&lt;&gt;",'Game Records'!$E$5:$E$504,"&gt;=40",'Game Records'!$E$5:$E$504,"&lt;=50",'Game Records'!$K$5:$K$504,"Draw")/B26)</x:f>
       </x:c>
       <x:c r="H26" s="60" t="str">
-        <x:f>IF(B26=0,"",COUNTIFS('Game Records'!$E$5:$E$504,"&gt;=40",'Game Records'!$E$5:$E$504,"&lt;=50",'Game Records'!$K$5:$K$504,"Disqualified")+COUNTIFS('Game Records'!$E$5:$E$504,"&gt;=40",'Game Records'!$E$5:$E$504,"&lt;=50",'Game Records'!$K$5:$K$504,"Loss")/B26)</x:f>
+        <x:f>IF(B26=0,"",(COUNTIFS('Game Records'!$A$5:$A$504,"&lt;&gt;",'Game Records'!$E$5:$E$504,"&gt;=40",'Game Records'!$E$5:$E$504,"&lt;=50",'Game Records'!$K$5:$K$504,"Disqualified")+COUNTIFS('Game Records'!$A$5:$A$504,"&lt;&gt;",'Game Records'!$E$5:$E$504,"&gt;=40",'Game Records'!$E$5:$E$504,"&lt;=50",'Game Records'!$K$5:$K$504,"Loss"))/B26)</x:f>
       </x:c>
     </x:row>
     <x:row r="27">
@@ -18915,27 +18917,27 @@
         <x:v>$60</x:v>
       </x:c>
       <x:c r="B27" s="50" t="n">
-        <x:f>COUNTIFS('Game Records'!$E$5:$E$504,"=60",'Game Records'!$K$5:$K$504,"&lt;&gt;Subscription")</x:f>
+        <x:f>COUNTIFS('Game Records'!$A$5:$A$504,"&lt;&gt;",'Game Records'!$E$5:$E$504,60,'Game Records'!$K$5:$K$504,"&lt;&gt;Subscription")</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="C27" s="58" t="n">
-        <x:f>SUMIFS('Game Records'!$U$5:$U$504,'Game Records'!$E$5:$E$504,"=60")</x:f>
+        <x:f>SUMIFS('Game Records'!$U$5:$U$504,'Game Records'!$A$5:$A$504,"&lt;&gt;",'Game Records'!$E$5:$E$504,60)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="D27" s="58" t="str">
         <x:f>IF(B27=0,"",C27/B27)</x:f>
       </x:c>
       <x:c r="E27" s="60" t="str">
-        <x:f>IF(COUNTIFS('Game Records'!$E$5:$E$504,"=60",'Game Records'!$J$5:$J$504,"&lt;&gt;")=0,"",SUMIFS('Game Records'!$J$5:$J$504,'Game Records'!$E$5:$E$504,"=60")/COUNTIFS('Game Records'!$E$5:$E$504,"=60",'Game Records'!$J$5:$J$504,"&lt;&gt;"))</x:f>
+        <x:f>IF(COUNTIFS('Game Records'!$A$5:$A$504,"&lt;&gt;",'Game Records'!$E$5:$E$504,60,'Game Records'!$J$5:$J$504,"&lt;&gt;")=0,"",SUMIFS('Game Records'!$J$5:$J$504,'Game Records'!$A$5:$A$504,"&lt;&gt;",'Game Records'!$E$5:$E$504,60)/COUNTIFS('Game Records'!$A$5:$A$504,"&lt;&gt;",'Game Records'!$E$5:$E$504,60,'Game Records'!$J$5:$J$504,"&lt;&gt;"))</x:f>
       </x:c>
       <x:c r="F27" s="60" t="str">
-        <x:f>IF(B27=0,"",COUNTIFS('Game Records'!$E$5:$E$504,"=60",'Game Records'!$K$5:$K$504,"Profit")/B27)</x:f>
+        <x:f>IF(B27=0,"",COUNTIFS('Game Records'!$A$5:$A$504,"&lt;&gt;",'Game Records'!$E$5:$E$504,60,'Game Records'!$K$5:$K$504,"Profit")/B27)</x:f>
       </x:c>
       <x:c r="G27" s="60" t="str">
-        <x:f>IF(B27=0,"",COUNTIFS('Game Records'!$E$5:$E$504,"=60",'Game Records'!$K$5:$K$504,"Draw")/B27)</x:f>
+        <x:f>IF(B27=0,"",COUNTIFS('Game Records'!$A$5:$A$504,"&lt;&gt;",'Game Records'!$E$5:$E$504,60,'Game Records'!$K$5:$K$504,"Draw")/B27)</x:f>
       </x:c>
       <x:c r="H27" s="60" t="str">
-        <x:f>IF(B27=0,"",COUNTIFS('Game Records'!$E$5:$E$504,"=60",'Game Records'!$K$5:$K$504,"Disqualified")+COUNTIFS('Game Records'!$E$5:$E$504,"=60",'Game Records'!$K$5:$K$504,"Loss")/B27)</x:f>
+        <x:f>IF(B27=0,"",(COUNTIFS('Game Records'!$A$5:$A$504,"&lt;&gt;",'Game Records'!$E$5:$E$504,60,'Game Records'!$K$5:$K$504,"Disqualified")+COUNTIFS('Game Records'!$A$5:$A$504,"&lt;&gt;",'Game Records'!$E$5:$E$504,60,'Game Records'!$K$5:$K$504,"Loss"))/B27)</x:f>
       </x:c>
     </x:row>
     <x:row r="28">
@@ -18943,27 +18945,27 @@
         <x:v>$100+</x:v>
       </x:c>
       <x:c r="B28" s="50" t="n">
-        <x:f>COUNTIFS('Game Records'!$E$5:$E$504,"&gt;=100",'Game Records'!$K$5:$K$504,"&lt;&gt;Subscription")</x:f>
+        <x:f>COUNTIFS('Game Records'!$A$5:$A$504,"&lt;&gt;",'Game Records'!$E$5:$E$504,"&gt;=100",'Game Records'!$K$5:$K$504,"&lt;&gt;Subscription")</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="C28" s="58" t="n">
-        <x:f>SUMIFS('Game Records'!$U$5:$U$504,'Game Records'!$E$5:$E$504,"&gt;=100")</x:f>
+        <x:f>SUMIFS('Game Records'!$U$5:$U$504,'Game Records'!$A$5:$A$504,"&lt;&gt;",'Game Records'!$E$5:$E$504,"&gt;=100")</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="D28" s="58" t="str">
         <x:f>IF(B28=0,"",C28/B28)</x:f>
       </x:c>
       <x:c r="E28" s="60" t="str">
-        <x:f>IF(COUNTIFS('Game Records'!$E$5:$E$504,"&gt;=100",'Game Records'!$J$5:$J$504,"&lt;&gt;")=0,"",SUMIFS('Game Records'!$J$5:$J$504,'Game Records'!$E$5:$E$504,"&gt;=100")/COUNTIFS('Game Records'!$E$5:$E$504,"&gt;=100",'Game Records'!$J$5:$J$504,"&lt;&gt;"))</x:f>
+        <x:f>IF(COUNTIFS('Game Records'!$A$5:$A$504,"&lt;&gt;",'Game Records'!$E$5:$E$504,"&gt;=100",'Game Records'!$J$5:$J$504,"&lt;&gt;")=0,"",SUMIFS('Game Records'!$J$5:$J$504,'Game Records'!$A$5:$A$504,"&lt;&gt;",'Game Records'!$E$5:$E$504,"&gt;=100")/COUNTIFS('Game Records'!$A$5:$A$504,"&lt;&gt;",'Game Records'!$E$5:$E$504,"&gt;=100",'Game Records'!$J$5:$J$504,"&lt;&gt;"))</x:f>
       </x:c>
       <x:c r="F28" s="60" t="str">
-        <x:f>IF(B28=0,"",COUNTIFS('Game Records'!$E$5:$E$504,"&gt;=100",'Game Records'!$K$5:$K$504,"Profit")/B28)</x:f>
+        <x:f>IF(B28=0,"",COUNTIFS('Game Records'!$A$5:$A$504,"&lt;&gt;",'Game Records'!$E$5:$E$504,"&gt;=100",'Game Records'!$K$5:$K$504,"Profit")/B28)</x:f>
       </x:c>
       <x:c r="G28" s="60" t="str">
-        <x:f>IF(B28=0,"",COUNTIFS('Game Records'!$E$5:$E$504,"&gt;=100",'Game Records'!$K$5:$K$504,"Draw")/B28)</x:f>
+        <x:f>IF(B28=0,"",COUNTIFS('Game Records'!$A$5:$A$504,"&lt;&gt;",'Game Records'!$E$5:$E$504,"&gt;=100",'Game Records'!$K$5:$K$504,"Draw")/B28)</x:f>
       </x:c>
       <x:c r="H28" s="60" t="str">
-        <x:f>IF(B28=0,"",COUNTIFS('Game Records'!$E$5:$E$504,"&gt;=100",'Game Records'!$K$5:$K$504,"Disqualified")+COUNTIFS('Game Records'!$E$5:$E$504,"&gt;=100",'Game Records'!$K$5:$K$504,"Loss")/B28)</x:f>
+        <x:f>IF(B28=0,"",(COUNTIFS('Game Records'!$A$5:$A$504,"&lt;&gt;",'Game Records'!$E$5:$E$504,"&gt;=100",'Game Records'!$K$5:$K$504,"Disqualified")+COUNTIFS('Game Records'!$A$5:$A$504,"&lt;&gt;",'Game Records'!$E$5:$E$504,"&gt;=100",'Game Records'!$K$5:$K$504,"Loss"))/B28)</x:f>
       </x:c>
     </x:row>
     <x:row r="29">
@@ -19029,27 +19031,27 @@
         <x:v>Cash</x:v>
       </x:c>
       <x:c r="B33" s="50" t="n">
-        <x:f>COUNTIFS('Game Records'!$D$5:$D$504,"*Cash*",'Game Records'!$K$5:$K$504,"&lt;&gt;Subscription")</x:f>
+        <x:f>COUNTIFS('Game Records'!$A$5:$A$504,"&lt;&gt;",'Game Records'!$D$5:$D$504,"*Cash*",'Game Records'!$K$5:$K$504,"&lt;&gt;Subscription")</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="C33" s="58" t="n">
-        <x:f>SUMIFS('Game Records'!$U$5:$U$504,'Game Records'!$D$5:$D$504,"*Cash*")</x:f>
+        <x:f>SUMIFS('Game Records'!$U$5:$U$504,'Game Records'!$A$5:$A$504,"&lt;&gt;",'Game Records'!$D$5:$D$504,"*Cash*")</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="D33" s="58" t="str">
         <x:f>IF(B33=0,"",C33/B33)</x:f>
       </x:c>
       <x:c r="E33" s="60" t="str">
-        <x:f>IF(COUNTIFS('Game Records'!$D$5:$D$504,"*Cash*",'Game Records'!$J$5:$J$504,"&lt;&gt;")=0,"",SUMIFS('Game Records'!$J$5:$J$504,'Game Records'!$D$5:$D$504,"*Cash*")/COUNTIFS('Game Records'!$D$5:$D$504,"*Cash*",'Game Records'!$J$5:$J$504,"&lt;&gt;"))</x:f>
+        <x:f>IF(COUNTIFS('Game Records'!$A$5:$A$504,"&lt;&gt;",'Game Records'!$D$5:$D$504,"*Cash*",'Game Records'!$J$5:$J$504,"&lt;&gt;")=0,"",SUMIFS('Game Records'!$J$5:$J$504,'Game Records'!$A$5:$A$504,"&lt;&gt;",'Game Records'!$D$5:$D$504,"*Cash*")/COUNTIFS('Game Records'!$A$5:$A$504,"&lt;&gt;",'Game Records'!$D$5:$D$504,"*Cash*",'Game Records'!$J$5:$J$504,"&lt;&gt;"))</x:f>
       </x:c>
       <x:c r="F33" s="60" t="str">
-        <x:f>IF(B33=0,"",COUNTIFS('Game Records'!$D$5:$D$504,"*Cash*",'Game Records'!$K$5:$K$504,"Profit")/B33)</x:f>
+        <x:f>IF(B33=0,"",COUNTIFS('Game Records'!$A$5:$A$504,"&lt;&gt;",'Game Records'!$D$5:$D$504,"*Cash*",'Game Records'!$K$5:$K$504,"Profit")/B33)</x:f>
       </x:c>
       <x:c r="G33" s="60" t="str">
-        <x:f>IF(B33=0,"",COUNTIFS('Game Records'!$D$5:$D$504,"*Cash*",'Game Records'!$K$5:$K$504,"Draw")/B33)</x:f>
+        <x:f>IF(B33=0,"",COUNTIFS('Game Records'!$A$5:$A$504,"&lt;&gt;",'Game Records'!$D$5:$D$504,"*Cash*",'Game Records'!$K$5:$K$504,"Draw")/B33)</x:f>
       </x:c>
       <x:c r="H33" s="60" t="str">
-        <x:f>IF(B33=0,"",COUNTIFS('Game Records'!$D$5:$D$504,"*Cash*",'Game Records'!$K$5:$K$504,"Disqualified")+COUNTIFS('Game Records'!$D$5:$D$504,"*Cash*",'Game Records'!$K$5:$K$504,"Loss")/B33)</x:f>
+        <x:f>IF(B33=0,"",(COUNTIFS('Game Records'!$A$5:$A$504,"&lt;&gt;",'Game Records'!$D$5:$D$504,"*Cash*",'Game Records'!$K$5:$K$504,"Disqualified")+COUNTIFS('Game Records'!$A$5:$A$504,"&lt;&gt;",'Game Records'!$D$5:$D$504,"*Cash*",'Game Records'!$K$5:$K$504,"Loss"))/B33)</x:f>
       </x:c>
     </x:row>
     <x:row r="34">
@@ -19057,27 +19059,27 @@
         <x:v>Points</x:v>
       </x:c>
       <x:c r="B34" s="50" t="n">
-        <x:f>COUNTIFS('Game Records'!$D$5:$D$504,"*Points*",'Game Records'!$K$5:$K$504,"&lt;&gt;Subscription")</x:f>
+        <x:f>COUNTIFS('Game Records'!$A$5:$A$504,"&lt;&gt;",'Game Records'!$D$5:$D$504,"*Points*",'Game Records'!$K$5:$K$504,"&lt;&gt;Subscription")</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="C34" s="58" t="n">
-        <x:f>SUMIFS('Game Records'!$U$5:$U$504,'Game Records'!$D$5:$D$504,"*Points*")</x:f>
+        <x:f>SUMIFS('Game Records'!$U$5:$U$504,'Game Records'!$A$5:$A$504,"&lt;&gt;",'Game Records'!$D$5:$D$504,"*Points*")</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="D34" s="58" t="str">
         <x:f>IF(B34=0,"",C34/B34)</x:f>
       </x:c>
       <x:c r="E34" s="60" t="str">
-        <x:f>IF(COUNTIFS('Game Records'!$D$5:$D$504,"*Points*",'Game Records'!$J$5:$J$504,"&lt;&gt;")=0,"",SUMIFS('Game Records'!$J$5:$J$504,'Game Records'!$D$5:$D$504,"*Points*")/COUNTIFS('Game Records'!$D$5:$D$504,"*Points*",'Game Records'!$J$5:$J$504,"&lt;&gt;"))</x:f>
+        <x:f>IF(COUNTIFS('Game Records'!$A$5:$A$504,"&lt;&gt;",'Game Records'!$D$5:$D$504,"*Points*",'Game Records'!$J$5:$J$504,"&lt;&gt;")=0,"",SUMIFS('Game Records'!$J$5:$J$504,'Game Records'!$A$5:$A$504,"&lt;&gt;",'Game Records'!$D$5:$D$504,"*Points*")/COUNTIFS('Game Records'!$A$5:$A$504,"&lt;&gt;",'Game Records'!$D$5:$D$504,"*Points*",'Game Records'!$J$5:$J$504,"&lt;&gt;"))</x:f>
       </x:c>
       <x:c r="F34" s="60" t="str">
-        <x:f>IF(B34=0,"",COUNTIFS('Game Records'!$D$5:$D$504,"*Points*",'Game Records'!$K$5:$K$504,"Profit")/B34)</x:f>
+        <x:f>IF(B34=0,"",COUNTIFS('Game Records'!$A$5:$A$504,"&lt;&gt;",'Game Records'!$D$5:$D$504,"*Points*",'Game Records'!$K$5:$K$504,"Profit")/B34)</x:f>
       </x:c>
       <x:c r="G34" s="60" t="str">
-        <x:f>IF(B34=0,"",COUNTIFS('Game Records'!$D$5:$D$504,"*Points*",'Game Records'!$K$5:$K$504,"Draw")/B34)</x:f>
+        <x:f>IF(B34=0,"",COUNTIFS('Game Records'!$A$5:$A$504,"&lt;&gt;",'Game Records'!$D$5:$D$504,"*Points*",'Game Records'!$K$5:$K$504,"Draw")/B34)</x:f>
       </x:c>
       <x:c r="H34" s="60" t="str">
-        <x:f>IF(B34=0,"",COUNTIFS('Game Records'!$D$5:$D$504,"*Points*",'Game Records'!$K$5:$K$504,"Disqualified")+COUNTIFS('Game Records'!$D$5:$D$504,"*Points*",'Game Records'!$K$5:$K$504,"Loss")/B34)</x:f>
+        <x:f>IF(B34=0,"",(COUNTIFS('Game Records'!$A$5:$A$504,"&lt;&gt;",'Game Records'!$D$5:$D$504,"*Points*",'Game Records'!$K$5:$K$504,"Disqualified")+COUNTIFS('Game Records'!$A$5:$A$504,"&lt;&gt;",'Game Records'!$D$5:$D$504,"*Points*",'Game Records'!$K$5:$K$504,"Loss"))/B34)</x:f>
       </x:c>
     </x:row>
     <x:row r="35">
@@ -19085,27 +19087,27 @@
         <x:v>Hybrid</x:v>
       </x:c>
       <x:c r="B35" s="50" t="n">
-        <x:f>COUNTIFS('Game Records'!$D$5:$D$504,"*Hybrid*",'Game Records'!$K$5:$K$504,"&lt;&gt;Subscription")</x:f>
+        <x:f>COUNTIFS('Game Records'!$A$5:$A$504,"&lt;&gt;",'Game Records'!$D$5:$D$504,"*Hybrid*",'Game Records'!$K$5:$K$504,"&lt;&gt;Subscription")</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="C35" s="58" t="n">
-        <x:f>SUMIFS('Game Records'!$U$5:$U$504,'Game Records'!$D$5:$D$504,"*Hybrid*")</x:f>
+        <x:f>SUMIFS('Game Records'!$U$5:$U$504,'Game Records'!$A$5:$A$504,"&lt;&gt;",'Game Records'!$D$5:$D$504,"*Hybrid*")</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="D35" s="58" t="str">
         <x:f>IF(B35=0,"",C35/B35)</x:f>
       </x:c>
       <x:c r="E35" s="60" t="str">
-        <x:f>IF(COUNTIFS('Game Records'!$D$5:$D$504,"*Hybrid*",'Game Records'!$J$5:$J$504,"&lt;&gt;")=0,"",SUMIFS('Game Records'!$J$5:$J$504,'Game Records'!$D$5:$D$504,"*Hybrid*")/COUNTIFS('Game Records'!$D$5:$D$504,"*Hybrid*",'Game Records'!$J$5:$J$504,"&lt;&gt;"))</x:f>
+        <x:f>IF(COUNTIFS('Game Records'!$A$5:$A$504,"&lt;&gt;",'Game Records'!$D$5:$D$504,"*Hybrid*",'Game Records'!$J$5:$J$504,"&lt;&gt;")=0,"",SUMIFS('Game Records'!$J$5:$J$504,'Game Records'!$A$5:$A$504,"&lt;&gt;",'Game Records'!$D$5:$D$504,"*Hybrid*")/COUNTIFS('Game Records'!$A$5:$A$504,"&lt;&gt;",'Game Records'!$D$5:$D$504,"*Hybrid*",'Game Records'!$J$5:$J$504,"&lt;&gt;"))</x:f>
       </x:c>
       <x:c r="F35" s="60" t="str">
-        <x:f>IF(B35=0,"",COUNTIFS('Game Records'!$D$5:$D$504,"*Hybrid*",'Game Records'!$K$5:$K$504,"Profit")/B35)</x:f>
+        <x:f>IF(B35=0,"",COUNTIFS('Game Records'!$A$5:$A$504,"&lt;&gt;",'Game Records'!$D$5:$D$504,"*Hybrid*",'Game Records'!$K$5:$K$504,"Profit")/B35)</x:f>
       </x:c>
       <x:c r="G35" s="60" t="str">
-        <x:f>IF(B35=0,"",COUNTIFS('Game Records'!$D$5:$D$504,"*Hybrid*",'Game Records'!$K$5:$K$504,"Draw")/B35)</x:f>
+        <x:f>IF(B35=0,"",COUNTIFS('Game Records'!$A$5:$A$504,"&lt;&gt;",'Game Records'!$D$5:$D$504,"*Hybrid*",'Game Records'!$K$5:$K$504,"Draw")/B35)</x:f>
       </x:c>
       <x:c r="H35" s="60" t="str">
-        <x:f>IF(B35=0,"",COUNTIFS('Game Records'!$D$5:$D$504,"*Hybrid*",'Game Records'!$K$5:$K$504,"Disqualified")+COUNTIFS('Game Records'!$D$5:$D$504,"*Hybrid*",'Game Records'!$K$5:$K$504,"Loss")/B35)</x:f>
+        <x:f>IF(B35=0,"",(COUNTIFS('Game Records'!$A$5:$A$504,"&lt;&gt;",'Game Records'!$D$5:$D$504,"*Hybrid*",'Game Records'!$K$5:$K$504,"Disqualified")+COUNTIFS('Game Records'!$A$5:$A$504,"&lt;&gt;",'Game Records'!$D$5:$D$504,"*Hybrid*",'Game Records'!$K$5:$K$504,"Loss"))/B35)</x:f>
       </x:c>
     </x:row>
     <x:row r="36">
@@ -19113,27 +19115,27 @@
         <x:v>Free Game</x:v>
       </x:c>
       <x:c r="B36" s="50" t="n">
-        <x:f>COUNTIFS('Game Records'!$D$5:$D$504,"*Free*",'Game Records'!$K$5:$K$504,"&lt;&gt;Subscription")</x:f>
+        <x:f>COUNTIFS('Game Records'!$A$5:$A$504,"&lt;&gt;",'Game Records'!$D$5:$D$504,"*Free*",'Game Records'!$K$5:$K$504,"&lt;&gt;Subscription")</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="C36" s="58" t="n">
-        <x:f>SUMIFS('Game Records'!$U$5:$U$504,'Game Records'!$D$5:$D$504,"*Free*")</x:f>
+        <x:f>SUMIFS('Game Records'!$U$5:$U$504,'Game Records'!$A$5:$A$504,"&lt;&gt;",'Game Records'!$D$5:$D$504,"*Free*")</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="D36" s="58" t="str">
         <x:f>IF(B36=0,"",C36/B36)</x:f>
       </x:c>
       <x:c r="E36" s="60" t="str">
-        <x:f>IF(COUNTIFS('Game Records'!$D$5:$D$504,"*Free*",'Game Records'!$J$5:$J$504,"&lt;&gt;")=0,"",SUMIFS('Game Records'!$J$5:$J$504,'Game Records'!$D$5:$D$504,"*Free*")/COUNTIFS('Game Records'!$D$5:$D$504,"*Free*",'Game Records'!$J$5:$J$504,"&lt;&gt;"))</x:f>
+        <x:f>IF(COUNTIFS('Game Records'!$A$5:$A$504,"&lt;&gt;",'Game Records'!$D$5:$D$504,"*Free*",'Game Records'!$J$5:$J$504,"&lt;&gt;")=0,"",SUMIFS('Game Records'!$J$5:$J$504,'Game Records'!$A$5:$A$504,"&lt;&gt;",'Game Records'!$D$5:$D$504,"*Free*")/COUNTIFS('Game Records'!$A$5:$A$504,"&lt;&gt;",'Game Records'!$D$5:$D$504,"*Free*",'Game Records'!$J$5:$J$504,"&lt;&gt;"))</x:f>
       </x:c>
       <x:c r="F36" s="60" t="str">
-        <x:f>IF(B36=0,"",COUNTIFS('Game Records'!$D$5:$D$504,"*Free*",'Game Records'!$K$5:$K$504,"Profit")/B36)</x:f>
+        <x:f>IF(B36=0,"",COUNTIFS('Game Records'!$A$5:$A$504,"&lt;&gt;",'Game Records'!$D$5:$D$504,"*Free*",'Game Records'!$K$5:$K$504,"Profit")/B36)</x:f>
       </x:c>
       <x:c r="G36" s="60" t="str">
-        <x:f>IF(B36=0,"",COUNTIFS('Game Records'!$D$5:$D$504,"*Free*",'Game Records'!$K$5:$K$504,"Draw")/B36)</x:f>
+        <x:f>IF(B36=0,"",COUNTIFS('Game Records'!$A$5:$A$504,"&lt;&gt;",'Game Records'!$D$5:$D$504,"*Free*",'Game Records'!$K$5:$K$504,"Draw")/B36)</x:f>
       </x:c>
       <x:c r="H36" s="60" t="str">
-        <x:f>IF(B36=0,"",COUNTIFS('Game Records'!$D$5:$D$504,"*Free*",'Game Records'!$K$5:$K$504,"Disqualified")+COUNTIFS('Game Records'!$D$5:$D$504,"*Free*",'Game Records'!$K$5:$K$504,"Loss")/B36)</x:f>
+        <x:f>IF(B36=0,"",(COUNTIFS('Game Records'!$A$5:$A$504,"&lt;&gt;",'Game Records'!$D$5:$D$504,"*Free*",'Game Records'!$K$5:$K$504,"Disqualified")+COUNTIFS('Game Records'!$A$5:$A$504,"&lt;&gt;",'Game Records'!$D$5:$D$504,"*Free*",'Game Records'!$K$5:$K$504,"Loss"))/B36)</x:f>
       </x:c>
     </x:row>
     <x:row r="37">
@@ -19199,31 +19201,27 @@
         <x:v>Under 200</x:v>
       </x:c>
       <x:c r="B41" s="50" t="n">
-        <x:f>COUNTIFS('Game Records'!$O$5:$O$504,"&lt;200",'Game Records'!$K$5:$K$504,"&lt;&gt;Subscription")</x:f>
-        <x:v>500</x:v>
+        <x:f>COUNTIFS('Game Records'!$A$5:$A$504,"&lt;&gt;",'Game Records'!$O$5:$O$504,"&gt;0",'Game Records'!$O$5:$O$504,"&lt;200",'Game Records'!$K$5:$K$504,"&lt;&gt;Subscription")</x:f>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C41" s="58" t="n">
-        <x:f>SUMIFS('Game Records'!$U$5:$U$504,'Game Records'!$O$5:$O$504,"&lt;200")</x:f>
+        <x:f>SUMIFS('Game Records'!$U$5:$U$504,'Game Records'!$A$5:$A$504,"&lt;&gt;",'Game Records'!$O$5:$O$504,"&gt;0",'Game Records'!$O$5:$O$504,"&lt;200")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="D41" s="58" t="n">
+      <x:c r="D41" s="58" t="str">
         <x:f>IF(B41=0,"",C41/B41)</x:f>
-        <x:v>0</x:v>
       </x:c>
       <x:c r="E41" s="60" t="str">
-        <x:f>IF(COUNTIFS('Game Records'!$O$5:$O$504,"&lt;200",'Game Records'!$J$5:$J$504,"&lt;&gt;")=0,"",SUMIFS('Game Records'!$J$5:$J$504,'Game Records'!$O$5:$O$504,"&lt;200")/COUNTIFS('Game Records'!$O$5:$O$504,"&lt;200",'Game Records'!$J$5:$J$504,"&lt;&gt;"))</x:f>
-      </x:c>
-      <x:c r="F41" s="60" t="n">
-        <x:f>IF(B41=0,"",COUNTIFS('Game Records'!$O$5:$O$504,"&lt;200",'Game Records'!$K$5:$K$504,"Profit")/B41)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G41" s="60" t="n">
-        <x:f>IF(B41=0,"",COUNTIFS('Game Records'!$O$5:$O$504,"&lt;200",'Game Records'!$K$5:$K$504,"Draw")/B41)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H41" s="60" t="n">
-        <x:f>IF(B41=0,"",COUNTIFS('Game Records'!$O$5:$O$504,"&lt;200",'Game Records'!$K$5:$K$504,"Disqualified")+COUNTIFS('Game Records'!$O$5:$O$504,"&lt;200",'Game Records'!$K$5:$K$504,"Loss")/B41)</x:f>
-        <x:v>0</x:v>
+        <x:f>IF(COUNTIFS('Game Records'!$A$5:$A$504,"&lt;&gt;",'Game Records'!$O$5:$O$504,"&gt;0",'Game Records'!$O$5:$O$504,"&lt;200",'Game Records'!$J$5:$J$504,"&lt;&gt;")=0,"",SUMIFS('Game Records'!$J$5:$J$504,'Game Records'!$A$5:$A$504,"&lt;&gt;",'Game Records'!$O$5:$O$504,"&gt;0",'Game Records'!$O$5:$O$504,"&lt;200")/COUNTIFS('Game Records'!$A$5:$A$504,"&lt;&gt;",'Game Records'!$O$5:$O$504,"&gt;0",'Game Records'!$O$5:$O$504,"&lt;200",'Game Records'!$J$5:$J$504,"&lt;&gt;"))</x:f>
+      </x:c>
+      <x:c r="F41" s="60" t="str">
+        <x:f>IF(B41=0,"",COUNTIFS('Game Records'!$A$5:$A$504,"&lt;&gt;",'Game Records'!$O$5:$O$504,"&gt;0",'Game Records'!$O$5:$O$504,"&lt;200",'Game Records'!$K$5:$K$504,"Profit")/B41)</x:f>
+      </x:c>
+      <x:c r="G41" s="60" t="str">
+        <x:f>IF(B41=0,"",COUNTIFS('Game Records'!$A$5:$A$504,"&lt;&gt;",'Game Records'!$O$5:$O$504,"&gt;0",'Game Records'!$O$5:$O$504,"&lt;200",'Game Records'!$K$5:$K$504,"Draw")/B41)</x:f>
+      </x:c>
+      <x:c r="H41" s="60" t="str">
+        <x:f>IF(B41=0,"",(COUNTIFS('Game Records'!$A$5:$A$504,"&lt;&gt;",'Game Records'!$O$5:$O$504,"&gt;0",'Game Records'!$O$5:$O$504,"&lt;200",'Game Records'!$K$5:$K$504,"Disqualified")+COUNTIFS('Game Records'!$A$5:$A$504,"&lt;&gt;",'Game Records'!$O$5:$O$504,"&gt;0",'Game Records'!$O$5:$O$504,"&lt;200",'Game Records'!$K$5:$K$504,"Loss"))/B41)</x:f>
       </x:c>
     </x:row>
     <x:row r="42">
@@ -19231,27 +19229,27 @@
         <x:v>200–499</x:v>
       </x:c>
       <x:c r="B42" s="50" t="n">
-        <x:f>COUNTIFS('Game Records'!$O$5:$O$504,"&gt;=200",'Game Records'!$O$5:$O$504,"&lt;=499",'Game Records'!$K$5:$K$504,"&lt;&gt;Subscription")</x:f>
+        <x:f>COUNTIFS('Game Records'!$A$5:$A$504,"&lt;&gt;",'Game Records'!$O$5:$O$504,"&gt;=200",'Game Records'!$O$5:$O$504,"&lt;=499",'Game Records'!$K$5:$K$504,"&lt;&gt;Subscription")</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="C42" s="58" t="n">
-        <x:f>SUMIFS('Game Records'!$U$5:$U$504,'Game Records'!$O$5:$O$504,"&gt;=200",'Game Records'!$O$5:$O$504,"&lt;=499")</x:f>
+        <x:f>SUMIFS('Game Records'!$U$5:$U$504,'Game Records'!$A$5:$A$504,"&lt;&gt;",'Game Records'!$O$5:$O$504,"&gt;=200",'Game Records'!$O$5:$O$504,"&lt;=499")</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="D42" s="58" t="str">
         <x:f>IF(B42=0,"",C42/B42)</x:f>
       </x:c>
       <x:c r="E42" s="60" t="str">
-        <x:f>IF(COUNTIFS('Game Records'!$O$5:$O$504,"&gt;=200",'Game Records'!$O$5:$O$504,"&lt;=499",'Game Records'!$J$5:$J$504,"&lt;&gt;")=0,"",SUMIFS('Game Records'!$J$5:$J$504,'Game Records'!$O$5:$O$504,"&gt;=200",'Game Records'!$O$5:$O$504,"&lt;=499")/COUNTIFS('Game Records'!$O$5:$O$504,"&gt;=200",'Game Records'!$O$5:$O$504,"&lt;=499",'Game Records'!$J$5:$J$504,"&lt;&gt;"))</x:f>
+        <x:f>IF(COUNTIFS('Game Records'!$A$5:$A$504,"&lt;&gt;",'Game Records'!$O$5:$O$504,"&gt;=200",'Game Records'!$O$5:$O$504,"&lt;=499",'Game Records'!$J$5:$J$504,"&lt;&gt;")=0,"",SUMIFS('Game Records'!$J$5:$J$504,'Game Records'!$A$5:$A$504,"&lt;&gt;",'Game Records'!$O$5:$O$504,"&gt;=200",'Game Records'!$O$5:$O$504,"&lt;=499")/COUNTIFS('Game Records'!$A$5:$A$504,"&lt;&gt;",'Game Records'!$O$5:$O$504,"&gt;=200",'Game Records'!$O$5:$O$504,"&lt;=499",'Game Records'!$J$5:$J$504,"&lt;&gt;"))</x:f>
       </x:c>
       <x:c r="F42" s="60" t="str">
-        <x:f>IF(B42=0,"",COUNTIFS('Game Records'!$O$5:$O$504,"&gt;=200",'Game Records'!$O$5:$O$504,"&lt;=499",'Game Records'!$K$5:$K$504,"Profit")/B42)</x:f>
+        <x:f>IF(B42=0,"",COUNTIFS('Game Records'!$A$5:$A$504,"&lt;&gt;",'Game Records'!$O$5:$O$504,"&gt;=200",'Game Records'!$O$5:$O$504,"&lt;=499",'Game Records'!$K$5:$K$504,"Profit")/B42)</x:f>
       </x:c>
       <x:c r="G42" s="60" t="str">
-        <x:f>IF(B42=0,"",COUNTIFS('Game Records'!$O$5:$O$504,"&gt;=200",'Game Records'!$O$5:$O$504,"&lt;=499",'Game Records'!$K$5:$K$504,"Draw")/B42)</x:f>
+        <x:f>IF(B42=0,"",COUNTIFS('Game Records'!$A$5:$A$504,"&lt;&gt;",'Game Records'!$O$5:$O$504,"&gt;=200",'Game Records'!$O$5:$O$504,"&lt;=499",'Game Records'!$K$5:$K$504,"Draw")/B42)</x:f>
       </x:c>
       <x:c r="H42" s="60" t="str">
-        <x:f>IF(B42=0,"",COUNTIFS('Game Records'!$O$5:$O$504,"&gt;=200",'Game Records'!$O$5:$O$504,"&lt;=499",'Game Records'!$K$5:$K$504,"Disqualified")+COUNTIFS('Game Records'!$O$5:$O$504,"&gt;=200",'Game Records'!$O$5:$O$504,"&lt;=499",'Game Records'!$K$5:$K$504,"Loss")/B42)</x:f>
+        <x:f>IF(B42=0,"",(COUNTIFS('Game Records'!$A$5:$A$504,"&lt;&gt;",'Game Records'!$O$5:$O$504,"&gt;=200",'Game Records'!$O$5:$O$504,"&lt;=499",'Game Records'!$K$5:$K$504,"Disqualified")+COUNTIFS('Game Records'!$A$5:$A$504,"&lt;&gt;",'Game Records'!$O$5:$O$504,"&gt;=200",'Game Records'!$O$5:$O$504,"&lt;=499",'Game Records'!$K$5:$K$504,"Loss"))/B42)</x:f>
       </x:c>
     </x:row>
     <x:row r="43">
@@ -19259,27 +19257,27 @@
         <x:v>500–999</x:v>
       </x:c>
       <x:c r="B43" s="50" t="n">
-        <x:f>COUNTIFS('Game Records'!$O$5:$O$504,"&gt;=500",'Game Records'!$O$5:$O$504,"&lt;=999",'Game Records'!$K$5:$K$504,"&lt;&gt;Subscription")</x:f>
+        <x:f>COUNTIFS('Game Records'!$A$5:$A$504,"&lt;&gt;",'Game Records'!$O$5:$O$504,"&gt;=500",'Game Records'!$O$5:$O$504,"&lt;=999",'Game Records'!$K$5:$K$504,"&lt;&gt;Subscription")</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="C43" s="58" t="n">
-        <x:f>SUMIFS('Game Records'!$U$5:$U$504,'Game Records'!$O$5:$O$504,"&gt;=500",'Game Records'!$O$5:$O$504,"&lt;=999")</x:f>
+        <x:f>SUMIFS('Game Records'!$U$5:$U$504,'Game Records'!$A$5:$A$504,"&lt;&gt;",'Game Records'!$O$5:$O$504,"&gt;=500",'Game Records'!$O$5:$O$504,"&lt;=999")</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="D43" s="58" t="str">
         <x:f>IF(B43=0,"",C43/B43)</x:f>
       </x:c>
       <x:c r="E43" s="60" t="str">
-        <x:f>IF(COUNTIFS('Game Records'!$O$5:$O$504,"&gt;=500",'Game Records'!$O$5:$O$504,"&lt;=999",'Game Records'!$J$5:$J$504,"&lt;&gt;")=0,"",SUMIFS('Game Records'!$J$5:$J$504,'Game Records'!$O$5:$O$504,"&gt;=500",'Game Records'!$O$5:$O$504,"&lt;=999")/COUNTIFS('Game Records'!$O$5:$O$504,"&gt;=500",'Game Records'!$O$5:$O$504,"&lt;=999",'Game Records'!$J$5:$J$504,"&lt;&gt;"))</x:f>
+        <x:f>IF(COUNTIFS('Game Records'!$A$5:$A$504,"&lt;&gt;",'Game Records'!$O$5:$O$504,"&gt;=500",'Game Records'!$O$5:$O$504,"&lt;=999",'Game Records'!$J$5:$J$504,"&lt;&gt;")=0,"",SUMIFS('Game Records'!$J$5:$J$504,'Game Records'!$A$5:$A$504,"&lt;&gt;",'Game Records'!$O$5:$O$504,"&gt;=500",'Game Records'!$O$5:$O$504,"&lt;=999")/COUNTIFS('Game Records'!$A$5:$A$504,"&lt;&gt;",'Game Records'!$O$5:$O$504,"&gt;=500",'Game Records'!$O$5:$O$504,"&lt;=999",'Game Records'!$J$5:$J$504,"&lt;&gt;"))</x:f>
       </x:c>
       <x:c r="F43" s="60" t="str">
-        <x:f>IF(B43=0,"",COUNTIFS('Game Records'!$O$5:$O$504,"&gt;=500",'Game Records'!$O$5:$O$504,"&lt;=999",'Game Records'!$K$5:$K$504,"Profit")/B43)</x:f>
+        <x:f>IF(B43=0,"",COUNTIFS('Game Records'!$A$5:$A$504,"&lt;&gt;",'Game Records'!$O$5:$O$504,"&gt;=500",'Game Records'!$O$5:$O$504,"&lt;=999",'Game Records'!$K$5:$K$504,"Profit")/B43)</x:f>
       </x:c>
       <x:c r="G43" s="60" t="str">
-        <x:f>IF(B43=0,"",COUNTIFS('Game Records'!$O$5:$O$504,"&gt;=500",'Game Records'!$O$5:$O$504,"&lt;=999",'Game Records'!$K$5:$K$504,"Draw")/B43)</x:f>
+        <x:f>IF(B43=0,"",COUNTIFS('Game Records'!$A$5:$A$504,"&lt;&gt;",'Game Records'!$O$5:$O$504,"&gt;=500",'Game Records'!$O$5:$O$504,"&lt;=999",'Game Records'!$K$5:$K$504,"Draw")/B43)</x:f>
       </x:c>
       <x:c r="H43" s="60" t="str">
-        <x:f>IF(B43=0,"",COUNTIFS('Game Records'!$O$5:$O$504,"&gt;=500",'Game Records'!$O$5:$O$504,"&lt;=999",'Game Records'!$K$5:$K$504,"Disqualified")+COUNTIFS('Game Records'!$O$5:$O$504,"&gt;=500",'Game Records'!$O$5:$O$504,"&lt;=999",'Game Records'!$K$5:$K$504,"Loss")/B43)</x:f>
+        <x:f>IF(B43=0,"",(COUNTIFS('Game Records'!$A$5:$A$504,"&lt;&gt;",'Game Records'!$O$5:$O$504,"&gt;=500",'Game Records'!$O$5:$O$504,"&lt;=999",'Game Records'!$K$5:$K$504,"Disqualified")+COUNTIFS('Game Records'!$A$5:$A$504,"&lt;&gt;",'Game Records'!$O$5:$O$504,"&gt;=500",'Game Records'!$O$5:$O$504,"&lt;=999",'Game Records'!$K$5:$K$504,"Loss"))/B43)</x:f>
       </x:c>
     </x:row>
     <x:row r="44">
@@ -19287,27 +19285,27 @@
         <x:v>1,000–2,999</x:v>
       </x:c>
       <x:c r="B44" s="50" t="n">
-        <x:f>COUNTIFS('Game Records'!$O$5:$O$504,"&gt;=1000",'Game Records'!$O$5:$O$504,"&lt;=2999",'Game Records'!$K$5:$K$504,"&lt;&gt;Subscription")</x:f>
+        <x:f>COUNTIFS('Game Records'!$A$5:$A$504,"&lt;&gt;",'Game Records'!$O$5:$O$504,"&gt;=1000",'Game Records'!$O$5:$O$504,"&lt;=2999",'Game Records'!$K$5:$K$504,"&lt;&gt;Subscription")</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="C44" s="58" t="n">
-        <x:f>SUMIFS('Game Records'!$U$5:$U$504,'Game Records'!$O$5:$O$504,"&gt;=1000",'Game Records'!$O$5:$O$504,"&lt;=2999")</x:f>
+        <x:f>SUMIFS('Game Records'!$U$5:$U$504,'Game Records'!$A$5:$A$504,"&lt;&gt;",'Game Records'!$O$5:$O$504,"&gt;=1000",'Game Records'!$O$5:$O$504,"&lt;=2999")</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="D44" s="58" t="str">
         <x:f>IF(B44=0,"",C44/B44)</x:f>
       </x:c>
       <x:c r="E44" s="60" t="str">
-        <x:f>IF(COUNTIFS('Game Records'!$O$5:$O$504,"&gt;=1000",'Game Records'!$O$5:$O$504,"&lt;=2999",'Game Records'!$J$5:$J$504,"&lt;&gt;")=0,"",SUMIFS('Game Records'!$J$5:$J$504,'Game Records'!$O$5:$O$504,"&gt;=1000",'Game Records'!$O$5:$O$504,"&lt;=2999")/COUNTIFS('Game Records'!$O$5:$O$504,"&gt;=1000",'Game Records'!$O$5:$O$504,"&lt;=2999",'Game Records'!$J$5:$J$504,"&lt;&gt;"))</x:f>
+        <x:f>IF(COUNTIFS('Game Records'!$A$5:$A$504,"&lt;&gt;",'Game Records'!$O$5:$O$504,"&gt;=1000",'Game Records'!$O$5:$O$504,"&lt;=2999",'Game Records'!$J$5:$J$504,"&lt;&gt;")=0,"",SUMIFS('Game Records'!$J$5:$J$504,'Game Records'!$A$5:$A$504,"&lt;&gt;",'Game Records'!$O$5:$O$504,"&gt;=1000",'Game Records'!$O$5:$O$504,"&lt;=2999")/COUNTIFS('Game Records'!$A$5:$A$504,"&lt;&gt;",'Game Records'!$O$5:$O$504,"&gt;=1000",'Game Records'!$O$5:$O$504,"&lt;=2999",'Game Records'!$J$5:$J$504,"&lt;&gt;"))</x:f>
       </x:c>
       <x:c r="F44" s="60" t="str">
-        <x:f>IF(B44=0,"",COUNTIFS('Game Records'!$O$5:$O$504,"&gt;=1000",'Game Records'!$O$5:$O$504,"&lt;=2999",'Game Records'!$K$5:$K$504,"Profit")/B44)</x:f>
+        <x:f>IF(B44=0,"",COUNTIFS('Game Records'!$A$5:$A$504,"&lt;&gt;",'Game Records'!$O$5:$O$504,"&gt;=1000",'Game Records'!$O$5:$O$504,"&lt;=2999",'Game Records'!$K$5:$K$504,"Profit")/B44)</x:f>
       </x:c>
       <x:c r="G44" s="60" t="str">
-        <x:f>IF(B44=0,"",COUNTIFS('Game Records'!$O$5:$O$504,"&gt;=1000",'Game Records'!$O$5:$O$504,"&lt;=2999",'Game Records'!$K$5:$K$504,"Draw")/B44)</x:f>
+        <x:f>IF(B44=0,"",COUNTIFS('Game Records'!$A$5:$A$504,"&lt;&gt;",'Game Records'!$O$5:$O$504,"&gt;=1000",'Game Records'!$O$5:$O$504,"&lt;=2999",'Game Records'!$K$5:$K$504,"Draw")/B44)</x:f>
       </x:c>
       <x:c r="H44" s="60" t="str">
-        <x:f>IF(B44=0,"",COUNTIFS('Game Records'!$O$5:$O$504,"&gt;=1000",'Game Records'!$O$5:$O$504,"&lt;=2999",'Game Records'!$K$5:$K$504,"Disqualified")+COUNTIFS('Game Records'!$O$5:$O$504,"&gt;=1000",'Game Records'!$O$5:$O$504,"&lt;=2999",'Game Records'!$K$5:$K$504,"Loss")/B44)</x:f>
+        <x:f>IF(B44=0,"",(COUNTIFS('Game Records'!$A$5:$A$504,"&lt;&gt;",'Game Records'!$O$5:$O$504,"&gt;=1000",'Game Records'!$O$5:$O$504,"&lt;=2999",'Game Records'!$K$5:$K$504,"Disqualified")+COUNTIFS('Game Records'!$A$5:$A$504,"&lt;&gt;",'Game Records'!$O$5:$O$504,"&gt;=1000",'Game Records'!$O$5:$O$504,"&lt;=2999",'Game Records'!$K$5:$K$504,"Loss"))/B44)</x:f>
       </x:c>
     </x:row>
     <x:row r="45">
@@ -19315,27 +19313,27 @@
         <x:v>3,000+</x:v>
       </x:c>
       <x:c r="B45" s="50" t="n">
-        <x:f>COUNTIFS('Game Records'!$O$5:$O$504,"&gt;=3000",'Game Records'!$K$5:$K$504,"&lt;&gt;Subscription")</x:f>
+        <x:f>COUNTIFS('Game Records'!$A$5:$A$504,"&lt;&gt;",'Game Records'!$O$5:$O$504,"&gt;=3000",'Game Records'!$K$5:$K$504,"&lt;&gt;Subscription")</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="C45" s="58" t="n">
-        <x:f>SUMIFS('Game Records'!$U$5:$U$504,'Game Records'!$O$5:$O$504,"&gt;=3000")</x:f>
+        <x:f>SUMIFS('Game Records'!$U$5:$U$504,'Game Records'!$A$5:$A$504,"&lt;&gt;",'Game Records'!$O$5:$O$504,"&gt;=3000")</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="D45" s="58" t="str">
         <x:f>IF(B45=0,"",C45/B45)</x:f>
       </x:c>
       <x:c r="E45" s="60" t="str">
-        <x:f>IF(COUNTIFS('Game Records'!$O$5:$O$504,"&gt;=3000",'Game Records'!$J$5:$J$504,"&lt;&gt;")=0,"",SUMIFS('Game Records'!$J$5:$J$504,'Game Records'!$O$5:$O$504,"&gt;=3000")/COUNTIFS('Game Records'!$O$5:$O$504,"&gt;=3000",'Game Records'!$J$5:$J$504,"&lt;&gt;"))</x:f>
+        <x:f>IF(COUNTIFS('Game Records'!$A$5:$A$504,"&lt;&gt;",'Game Records'!$O$5:$O$504,"&gt;=3000",'Game Records'!$J$5:$J$504,"&lt;&gt;")=0,"",SUMIFS('Game Records'!$J$5:$J$504,'Game Records'!$A$5:$A$504,"&lt;&gt;",'Game Records'!$O$5:$O$504,"&gt;=3000")/COUNTIFS('Game Records'!$A$5:$A$504,"&lt;&gt;",'Game Records'!$O$5:$O$504,"&gt;=3000",'Game Records'!$J$5:$J$504,"&lt;&gt;"))</x:f>
       </x:c>
       <x:c r="F45" s="60" t="str">
-        <x:f>IF(B45=0,"",COUNTIFS('Game Records'!$O$5:$O$504,"&gt;=3000",'Game Records'!$K$5:$K$504,"Profit")/B45)</x:f>
+        <x:f>IF(B45=0,"",COUNTIFS('Game Records'!$A$5:$A$504,"&lt;&gt;",'Game Records'!$O$5:$O$504,"&gt;=3000",'Game Records'!$K$5:$K$504,"Profit")/B45)</x:f>
       </x:c>
       <x:c r="G45" s="60" t="str">
-        <x:f>IF(B45=0,"",COUNTIFS('Game Records'!$O$5:$O$504,"&gt;=3000",'Game Records'!$K$5:$K$504,"Draw")/B45)</x:f>
+        <x:f>IF(B45=0,"",COUNTIFS('Game Records'!$A$5:$A$504,"&lt;&gt;",'Game Records'!$O$5:$O$504,"&gt;=3000",'Game Records'!$K$5:$K$504,"Draw")/B45)</x:f>
       </x:c>
       <x:c r="H45" s="60" t="str">
-        <x:f>IF(B45=0,"",COUNTIFS('Game Records'!$O$5:$O$504,"&gt;=3000",'Game Records'!$K$5:$K$504,"Disqualified")+COUNTIFS('Game Records'!$O$5:$O$504,"&gt;=3000",'Game Records'!$K$5:$K$504,"Loss")/B45)</x:f>
+        <x:f>IF(B45=0,"",(COUNTIFS('Game Records'!$A$5:$A$504,"&lt;&gt;",'Game Records'!$O$5:$O$504,"&gt;=3000",'Game Records'!$K$5:$K$504,"Disqualified")+COUNTIFS('Game Records'!$A$5:$A$504,"&lt;&gt;",'Game Records'!$O$5:$O$504,"&gt;=3000",'Game Records'!$K$5:$K$504,"Loss"))/B45)</x:f>
       </x:c>
     </x:row>
     <x:row r="46">
@@ -19401,31 +19399,27 @@
         <x:v>Under 10%</x:v>
       </x:c>
       <x:c r="B50" s="50" t="n">
-        <x:f>COUNTIFS('Game Records'!$W$5:$W$504,"&lt;0.1",'Game Records'!$K$5:$K$504,"&lt;&gt;Subscription")</x:f>
-        <x:v>500</x:v>
+        <x:f>COUNTIFS('Game Records'!$A$5:$A$504,"&lt;&gt;",'Game Records'!$V$5:$V$504,"&lt;&gt;",'Game Records'!$W$5:$W$504,"&gt;=0",'Game Records'!$W$5:$W$504,"&lt;0.1",'Game Records'!$K$5:$K$504,"&lt;&gt;Subscription")</x:f>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C50" s="58" t="n">
-        <x:f>SUMIFS('Game Records'!$U$5:$U$504,'Game Records'!$W$5:$W$504,"&lt;0.1")</x:f>
+        <x:f>SUMIFS('Game Records'!$U$5:$U$504,'Game Records'!$A$5:$A$504,"&lt;&gt;",'Game Records'!$V$5:$V$504,"&lt;&gt;",'Game Records'!$W$5:$W$504,"&gt;=0",'Game Records'!$W$5:$W$504,"&lt;0.1")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="D50" s="58" t="n">
+      <x:c r="D50" s="58" t="str">
         <x:f>IF(B50=0,"",C50/B50)</x:f>
-        <x:v>0</x:v>
       </x:c>
       <x:c r="E50" s="60" t="str">
-        <x:f>IF(COUNTIFS('Game Records'!$W$5:$W$504,"&lt;0.1",'Game Records'!$J$5:$J$504,"&lt;&gt;")=0,"",SUMIFS('Game Records'!$J$5:$J$504,'Game Records'!$W$5:$W$504,"&lt;0.1")/COUNTIFS('Game Records'!$W$5:$W$504,"&lt;0.1",'Game Records'!$J$5:$J$504,"&lt;&gt;"))</x:f>
-      </x:c>
-      <x:c r="F50" s="60" t="n">
-        <x:f>IF(B50=0,"",COUNTIFS('Game Records'!$W$5:$W$504,"&lt;0.1",'Game Records'!$K$5:$K$504,"Profit")/B50)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G50" s="60" t="n">
-        <x:f>IF(B50=0,"",COUNTIFS('Game Records'!$W$5:$W$504,"&lt;0.1",'Game Records'!$K$5:$K$504,"Draw")/B50)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H50" s="60" t="n">
-        <x:f>IF(B50=0,"",COUNTIFS('Game Records'!$W$5:$W$504,"&lt;0.1",'Game Records'!$K$5:$K$504,"Disqualified")+COUNTIFS('Game Records'!$W$5:$W$504,"&lt;0.1",'Game Records'!$K$5:$K$504,"Loss")/B50)</x:f>
-        <x:v>0</x:v>
+        <x:f>IF(COUNTIFS('Game Records'!$A$5:$A$504,"&lt;&gt;",'Game Records'!$V$5:$V$504,"&lt;&gt;",'Game Records'!$W$5:$W$504,"&gt;=0",'Game Records'!$W$5:$W$504,"&lt;0.1",'Game Records'!$J$5:$J$504,"&lt;&gt;")=0,"",SUMIFS('Game Records'!$J$5:$J$504,'Game Records'!$A$5:$A$504,"&lt;&gt;",'Game Records'!$V$5:$V$504,"&lt;&gt;",'Game Records'!$W$5:$W$504,"&gt;=0",'Game Records'!$W$5:$W$504,"&lt;0.1")/COUNTIFS('Game Records'!$A$5:$A$504,"&lt;&gt;",'Game Records'!$V$5:$V$504,"&lt;&gt;",'Game Records'!$W$5:$W$504,"&gt;=0",'Game Records'!$W$5:$W$504,"&lt;0.1",'Game Records'!$J$5:$J$504,"&lt;&gt;"))</x:f>
+      </x:c>
+      <x:c r="F50" s="60" t="str">
+        <x:f>IF(B50=0,"",COUNTIFS('Game Records'!$A$5:$A$504,"&lt;&gt;",'Game Records'!$V$5:$V$504,"&lt;&gt;",'Game Records'!$W$5:$W$504,"&gt;=0",'Game Records'!$W$5:$W$504,"&lt;0.1",'Game Records'!$K$5:$K$504,"Profit")/B50)</x:f>
+      </x:c>
+      <x:c r="G50" s="60" t="str">
+        <x:f>IF(B50=0,"",COUNTIFS('Game Records'!$A$5:$A$504,"&lt;&gt;",'Game Records'!$V$5:$V$504,"&lt;&gt;",'Game Records'!$W$5:$W$504,"&gt;=0",'Game Records'!$W$5:$W$504,"&lt;0.1",'Game Records'!$K$5:$K$504,"Draw")/B50)</x:f>
+      </x:c>
+      <x:c r="H50" s="60" t="str">
+        <x:f>IF(B50=0,"",(COUNTIFS('Game Records'!$A$5:$A$504,"&lt;&gt;",'Game Records'!$V$5:$V$504,"&lt;&gt;",'Game Records'!$W$5:$W$504,"&gt;=0",'Game Records'!$W$5:$W$504,"&lt;0.1",'Game Records'!$K$5:$K$504,"Disqualified")+COUNTIFS('Game Records'!$A$5:$A$504,"&lt;&gt;",'Game Records'!$V$5:$V$504,"&lt;&gt;",'Game Records'!$W$5:$W$504,"&gt;=0",'Game Records'!$W$5:$W$504,"&lt;0.1",'Game Records'!$K$5:$K$504,"Loss"))/B50)</x:f>
       </x:c>
     </x:row>
     <x:row r="51">
@@ -19433,27 +19427,27 @@
         <x:v>10–19.9%</x:v>
       </x:c>
       <x:c r="B51" s="50" t="n">
-        <x:f>COUNTIFS('Game Records'!$W$5:$W$504,"&gt;=0.1",'Game Records'!$W$5:$W$504,"&lt;0.2",'Game Records'!$K$5:$K$504,"&lt;&gt;Subscription")</x:f>
+        <x:f>COUNTIFS('Game Records'!$A$5:$A$504,"&lt;&gt;",'Game Records'!$V$5:$V$504,"&lt;&gt;",'Game Records'!$W$5:$W$504,"&gt;=0.1",'Game Records'!$W$5:$W$504,"&lt;0.2",'Game Records'!$K$5:$K$504,"&lt;&gt;Subscription")</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="C51" s="58" t="n">
-        <x:f>SUMIFS('Game Records'!$U$5:$U$504,'Game Records'!$W$5:$W$504,"&gt;=0.1",'Game Records'!$W$5:$W$504,"&lt;0.2")</x:f>
+        <x:f>SUMIFS('Game Records'!$U$5:$U$504,'Game Records'!$A$5:$A$504,"&lt;&gt;",'Game Records'!$V$5:$V$504,"&lt;&gt;",'Game Records'!$W$5:$W$504,"&gt;=0.1",'Game Records'!$W$5:$W$504,"&lt;0.2")</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="D51" s="58" t="str">
         <x:f>IF(B51=0,"",C51/B51)</x:f>
       </x:c>
       <x:c r="E51" s="60" t="str">
-        <x:f>IF(COUNTIFS('Game Records'!$W$5:$W$504,"&gt;=0.1",'Game Records'!$W$5:$W$504,"&lt;0.2",'Game Records'!$J$5:$J$504,"&lt;&gt;")=0,"",SUMIFS('Game Records'!$J$5:$J$504,'Game Records'!$W$5:$W$504,"&gt;=0.1",'Game Records'!$W$5:$W$504,"&lt;0.2")/COUNTIFS('Game Records'!$W$5:$W$504,"&gt;=0.1",'Game Records'!$W$5:$W$504,"&lt;0.2",'Game Records'!$J$5:$J$504,"&lt;&gt;"))</x:f>
+        <x:f>IF(COUNTIFS('Game Records'!$A$5:$A$504,"&lt;&gt;",'Game Records'!$V$5:$V$504,"&lt;&gt;",'Game Records'!$W$5:$W$504,"&gt;=0.1",'Game Records'!$W$5:$W$504,"&lt;0.2",'Game Records'!$J$5:$J$504,"&lt;&gt;")=0,"",SUMIFS('Game Records'!$J$5:$J$504,'Game Records'!$A$5:$A$504,"&lt;&gt;",'Game Records'!$V$5:$V$504,"&lt;&gt;",'Game Records'!$W$5:$W$504,"&gt;=0.1",'Game Records'!$W$5:$W$504,"&lt;0.2")/COUNTIFS('Game Records'!$A$5:$A$504,"&lt;&gt;",'Game Records'!$V$5:$V$504,"&lt;&gt;",'Game Records'!$W$5:$W$504,"&gt;=0.1",'Game Records'!$W$5:$W$504,"&lt;0.2",'Game Records'!$J$5:$J$504,"&lt;&gt;"))</x:f>
       </x:c>
       <x:c r="F51" s="60" t="str">
-        <x:f>IF(B51=0,"",COUNTIFS('Game Records'!$W$5:$W$504,"&gt;=0.1",'Game Records'!$W$5:$W$504,"&lt;0.2",'Game Records'!$K$5:$K$504,"Profit")/B51)</x:f>
+        <x:f>IF(B51=0,"",COUNTIFS('Game Records'!$A$5:$A$504,"&lt;&gt;",'Game Records'!$V$5:$V$504,"&lt;&gt;",'Game Records'!$W$5:$W$504,"&gt;=0.1",'Game Records'!$W$5:$W$504,"&lt;0.2",'Game Records'!$K$5:$K$504,"Profit")/B51)</x:f>
       </x:c>
       <x:c r="G51" s="60" t="str">
-        <x:f>IF(B51=0,"",COUNTIFS('Game Records'!$W$5:$W$504,"&gt;=0.1",'Game Records'!$W$5:$W$504,"&lt;0.2",'Game Records'!$K$5:$K$504,"Draw")/B51)</x:f>
+        <x:f>IF(B51=0,"",COUNTIFS('Game Records'!$A$5:$A$504,"&lt;&gt;",'Game Records'!$V$5:$V$504,"&lt;&gt;",'Game Records'!$W$5:$W$504,"&gt;=0.1",'Game Records'!$W$5:$W$504,"&lt;0.2",'Game Records'!$K$5:$K$504,"Draw")/B51)</x:f>
       </x:c>
       <x:c r="H51" s="60" t="str">
-        <x:f>IF(B51=0,"",COUNTIFS('Game Records'!$W$5:$W$504,"&gt;=0.1",'Game Records'!$W$5:$W$504,"&lt;0.2",'Game Records'!$K$5:$K$504,"Disqualified")+COUNTIFS('Game Records'!$W$5:$W$504,"&gt;=0.1",'Game Records'!$W$5:$W$504,"&lt;0.2",'Game Records'!$K$5:$K$504,"Loss")/B51)</x:f>
+        <x:f>IF(B51=0,"",(COUNTIFS('Game Records'!$A$5:$A$504,"&lt;&gt;",'Game Records'!$V$5:$V$504,"&lt;&gt;",'Game Records'!$W$5:$W$504,"&gt;=0.1",'Game Records'!$W$5:$W$504,"&lt;0.2",'Game Records'!$K$5:$K$504,"Disqualified")+COUNTIFS('Game Records'!$A$5:$A$504,"&lt;&gt;",'Game Records'!$V$5:$V$504,"&lt;&gt;",'Game Records'!$W$5:$W$504,"&gt;=0.1",'Game Records'!$W$5:$W$504,"&lt;0.2",'Game Records'!$K$5:$K$504,"Loss"))/B51)</x:f>
       </x:c>
     </x:row>
     <x:row r="52">
@@ -19461,27 +19455,27 @@
         <x:v>20–29.9%</x:v>
       </x:c>
       <x:c r="B52" s="50" t="n">
-        <x:f>COUNTIFS('Game Records'!$W$5:$W$504,"&gt;=0.2",'Game Records'!$W$5:$W$504,"&lt;0.3",'Game Records'!$K$5:$K$504,"&lt;&gt;Subscription")</x:f>
+        <x:f>COUNTIFS('Game Records'!$A$5:$A$504,"&lt;&gt;",'Game Records'!$V$5:$V$504,"&lt;&gt;",'Game Records'!$W$5:$W$504,"&gt;=0.2",'Game Records'!$W$5:$W$504,"&lt;0.3",'Game Records'!$K$5:$K$504,"&lt;&gt;Subscription")</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="C52" s="58" t="n">
-        <x:f>SUMIFS('Game Records'!$U$5:$U$504,'Game Records'!$W$5:$W$504,"&gt;=0.2",'Game Records'!$W$5:$W$504,"&lt;0.3")</x:f>
+        <x:f>SUMIFS('Game Records'!$U$5:$U$504,'Game Records'!$A$5:$A$504,"&lt;&gt;",'Game Records'!$V$5:$V$504,"&lt;&gt;",'Game Records'!$W$5:$W$504,"&gt;=0.2",'Game Records'!$W$5:$W$504,"&lt;0.3")</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="D52" s="58" t="str">
         <x:f>IF(B52=0,"",C52/B52)</x:f>
       </x:c>
       <x:c r="E52" s="60" t="str">
-        <x:f>IF(COUNTIFS('Game Records'!$W$5:$W$504,"&gt;=0.2",'Game Records'!$W$5:$W$504,"&lt;0.3",'Game Records'!$J$5:$J$504,"&lt;&gt;")=0,"",SUMIFS('Game Records'!$J$5:$J$504,'Game Records'!$W$5:$W$504,"&gt;=0.2",'Game Records'!$W$5:$W$504,"&lt;0.3")/COUNTIFS('Game Records'!$W$5:$W$504,"&gt;=0.2",'Game Records'!$W$5:$W$504,"&lt;0.3",'Game Records'!$J$5:$J$504,"&lt;&gt;"))</x:f>
+        <x:f>IF(COUNTIFS('Game Records'!$A$5:$A$504,"&lt;&gt;",'Game Records'!$V$5:$V$504,"&lt;&gt;",'Game Records'!$W$5:$W$504,"&gt;=0.2",'Game Records'!$W$5:$W$504,"&lt;0.3",'Game Records'!$J$5:$J$504,"&lt;&gt;")=0,"",SUMIFS('Game Records'!$J$5:$J$504,'Game Records'!$A$5:$A$504,"&lt;&gt;",'Game Records'!$V$5:$V$504,"&lt;&gt;",'Game Records'!$W$5:$W$504,"&gt;=0.2",'Game Records'!$W$5:$W$504,"&lt;0.3")/COUNTIFS('Game Records'!$A$5:$A$504,"&lt;&gt;",'Game Records'!$V$5:$V$504,"&lt;&gt;",'Game Records'!$W$5:$W$504,"&gt;=0.2",'Game Records'!$W$5:$W$504,"&lt;0.3",'Game Records'!$J$5:$J$504,"&lt;&gt;"))</x:f>
       </x:c>
       <x:c r="F52" s="60" t="str">
-        <x:f>IF(B52=0,"",COUNTIFS('Game Records'!$W$5:$W$504,"&gt;=0.2",'Game Records'!$W$5:$W$504,"&lt;0.3",'Game Records'!$K$5:$K$504,"Profit")/B52)</x:f>
+        <x:f>IF(B52=0,"",COUNTIFS('Game Records'!$A$5:$A$504,"&lt;&gt;",'Game Records'!$V$5:$V$504,"&lt;&gt;",'Game Records'!$W$5:$W$504,"&gt;=0.2",'Game Records'!$W$5:$W$504,"&lt;0.3",'Game Records'!$K$5:$K$504,"Profit")/B52)</x:f>
       </x:c>
       <x:c r="G52" s="60" t="str">
-        <x:f>IF(B52=0,"",COUNTIFS('Game Records'!$W$5:$W$504,"&gt;=0.2",'Game Records'!$W$5:$W$504,"&lt;0.3",'Game Records'!$K$5:$K$504,"Draw")/B52)</x:f>
+        <x:f>IF(B52=0,"",COUNTIFS('Game Records'!$A$5:$A$504,"&lt;&gt;",'Game Records'!$V$5:$V$504,"&lt;&gt;",'Game Records'!$W$5:$W$504,"&gt;=0.2",'Game Records'!$W$5:$W$504,"&lt;0.3",'Game Records'!$K$5:$K$504,"Draw")/B52)</x:f>
       </x:c>
       <x:c r="H52" s="60" t="str">
-        <x:f>IF(B52=0,"",COUNTIFS('Game Records'!$W$5:$W$504,"&gt;=0.2",'Game Records'!$W$5:$W$504,"&lt;0.3",'Game Records'!$K$5:$K$504,"Disqualified")+COUNTIFS('Game Records'!$W$5:$W$504,"&gt;=0.2",'Game Records'!$W$5:$W$504,"&lt;0.3",'Game Records'!$K$5:$K$504,"Loss")/B52)</x:f>
+        <x:f>IF(B52=0,"",(COUNTIFS('Game Records'!$A$5:$A$504,"&lt;&gt;",'Game Records'!$V$5:$V$504,"&lt;&gt;",'Game Records'!$W$5:$W$504,"&gt;=0.2",'Game Records'!$W$5:$W$504,"&lt;0.3",'Game Records'!$K$5:$K$504,"Disqualified")+COUNTIFS('Game Records'!$A$5:$A$504,"&lt;&gt;",'Game Records'!$V$5:$V$504,"&lt;&gt;",'Game Records'!$W$5:$W$504,"&gt;=0.2",'Game Records'!$W$5:$W$504,"&lt;0.3",'Game Records'!$K$5:$K$504,"Loss"))/B52)</x:f>
       </x:c>
     </x:row>
     <x:row r="53">
@@ -19489,27 +19483,27 @@
         <x:v>30%+</x:v>
       </x:c>
       <x:c r="B53" s="50" t="n">
-        <x:f>COUNTIFS('Game Records'!$W$5:$W$504,"&gt;=0.3",'Game Records'!$K$5:$K$504,"&lt;&gt;Subscription")</x:f>
+        <x:f>COUNTIFS('Game Records'!$A$5:$A$504,"&lt;&gt;",'Game Records'!$V$5:$V$504,"&lt;&gt;",'Game Records'!$W$5:$W$504,"&gt;=0.3",'Game Records'!$K$5:$K$504,"&lt;&gt;Subscription")</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="C53" s="58" t="n">
-        <x:f>SUMIFS('Game Records'!$U$5:$U$504,'Game Records'!$W$5:$W$504,"&gt;=0.3")</x:f>
+        <x:f>SUMIFS('Game Records'!$U$5:$U$504,'Game Records'!$A$5:$A$504,"&lt;&gt;",'Game Records'!$V$5:$V$504,"&lt;&gt;",'Game Records'!$W$5:$W$504,"&gt;=0.3")</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="D53" s="58" t="str">
         <x:f>IF(B53=0,"",C53/B53)</x:f>
       </x:c>
       <x:c r="E53" s="60" t="str">
-        <x:f>IF(COUNTIFS('Game Records'!$W$5:$W$504,"&gt;=0.3",'Game Records'!$J$5:$J$504,"&lt;&gt;")=0,"",SUMIFS('Game Records'!$J$5:$J$504,'Game Records'!$W$5:$W$504,"&gt;=0.3")/COUNTIFS('Game Records'!$W$5:$W$504,"&gt;=0.3",'Game Records'!$J$5:$J$504,"&lt;&gt;"))</x:f>
+        <x:f>IF(COUNTIFS('Game Records'!$A$5:$A$504,"&lt;&gt;",'Game Records'!$V$5:$V$504,"&lt;&gt;",'Game Records'!$W$5:$W$504,"&gt;=0.3",'Game Records'!$J$5:$J$504,"&lt;&gt;")=0,"",SUMIFS('Game Records'!$J$5:$J$504,'Game Records'!$A$5:$A$504,"&lt;&gt;",'Game Records'!$V$5:$V$504,"&lt;&gt;",'Game Records'!$W$5:$W$504,"&gt;=0.3")/COUNTIFS('Game Records'!$A$5:$A$504,"&lt;&gt;",'Game Records'!$V$5:$V$504,"&lt;&gt;",'Game Records'!$W$5:$W$504,"&gt;=0.3",'Game Records'!$J$5:$J$504,"&lt;&gt;"))</x:f>
       </x:c>
       <x:c r="F53" s="60" t="str">
-        <x:f>IF(B53=0,"",COUNTIFS('Game Records'!$W$5:$W$504,"&gt;=0.3",'Game Records'!$K$5:$K$504,"Profit")/B53)</x:f>
+        <x:f>IF(B53=0,"",COUNTIFS('Game Records'!$A$5:$A$504,"&lt;&gt;",'Game Records'!$V$5:$V$504,"&lt;&gt;",'Game Records'!$W$5:$W$504,"&gt;=0.3",'Game Records'!$K$5:$K$504,"Profit")/B53)</x:f>
       </x:c>
       <x:c r="G53" s="60" t="str">
-        <x:f>IF(B53=0,"",COUNTIFS('Game Records'!$W$5:$W$504,"&gt;=0.3",'Game Records'!$K$5:$K$504,"Draw")/B53)</x:f>
+        <x:f>IF(B53=0,"",COUNTIFS('Game Records'!$A$5:$A$504,"&lt;&gt;",'Game Records'!$V$5:$V$504,"&lt;&gt;",'Game Records'!$W$5:$W$504,"&gt;=0.3",'Game Records'!$K$5:$K$504,"Draw")/B53)</x:f>
       </x:c>
       <x:c r="H53" s="60" t="str">
-        <x:f>IF(B53=0,"",COUNTIFS('Game Records'!$W$5:$W$504,"&gt;=0.3",'Game Records'!$K$5:$K$504,"Disqualified")+COUNTIFS('Game Records'!$W$5:$W$504,"&gt;=0.3",'Game Records'!$K$5:$K$504,"Loss")/B53)</x:f>
+        <x:f>IF(B53=0,"",(COUNTIFS('Game Records'!$A$5:$A$504,"&lt;&gt;",'Game Records'!$V$5:$V$504,"&lt;&gt;",'Game Records'!$W$5:$W$504,"&gt;=0.3",'Game Records'!$K$5:$K$504,"Disqualified")+COUNTIFS('Game Records'!$A$5:$A$504,"&lt;&gt;",'Game Records'!$V$5:$V$504,"&lt;&gt;",'Game Records'!$W$5:$W$504,"&gt;=0.3",'Game Records'!$K$5:$K$504,"Loss"))/B53)</x:f>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -19524,7 +19518,7 @@
     <x:mergeCell ref="A48:H48"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2e94c69d6e504f0b"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R07a762a4981e4e07"/>
 </x:worksheet>
 </file>
 

--- a/StepCat_Blank_Profitability_Analysis_Template.xlsx
+++ b/StepCat_Blank_Profitability_Analysis_Template.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instructions" sheetId="1" r:id="R5bf20db32989475d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Game Records" sheetId="2" r:id="R340eaf7fae294dc5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="3" r:id="R2adb6b4d42fc4e7f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Game Comparisons" sheetId="4" r:id="R2e99b9e554fc40c5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Best Results" sheetId="5" r:id="R0f5bb510876a415f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instructions" sheetId="1" r:id="Rde3eab50dd724f12"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Game Records" sheetId="2" r:id="Re97a74b5d7434030"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="3" r:id="R59566356a4cb4fb7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Game Comparisons" sheetId="4" r:id="R6180fe6c8d4a473f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Best Results" sheetId="5" r:id="R64488d50d4294b3c"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -770,7 +770,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R6f1c4fb419ee43a7"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rd094fb9437b24331"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -805,7 +805,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R4758196ef5154484"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R769e911d58404c18"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1433,7 +1433,7 @@
     </x:row>
     <x:row r="2" ht="28" customHeight="1">
       <x:c r="A2" s="14" t="str">
-        <x:v>Paste StepCat rows into A5:P. The template calculates the blue analysis columns.</x:v>
+        <x:v>Paste completed StepCat rows into A5:K, or manually update in-progress rows. For manual/pre-StepCat rows, ROI and Result formulas can calculate from Entry Fee plus Profit, Draw, or Lost.</x:v>
       </x:c>
       <x:c r="B2" s="14"/>
       <x:c r="C2" s="14"/>
@@ -1539,8 +1539,12 @@
       <x:c r="G5" s="58"/>
       <x:c r="H5" s="58"/>
       <x:c r="I5" s="58"/>
-      <x:c r="J5" s="60"/>
-      <x:c r="K5" s="50"/>
+      <x:c r="J5" s="60" t="str">
+        <x:f>IF(A5="","",IF(K5="Subscription","",IF(E5=0,"",IF(ISNUMBER(G5),G5/E5,IF(ISNUMBER(I5),-ABS(I5)/E5,IF(ISNUMBER(H5),0,IF(AND(ISNUMBER(F5),ISNUMBER(E5),E5&gt;0,F5&gt;E5),(F5-E5)/E5,IF(AND(ISNUMBER(F5),ISNUMBER(E5),E5&gt;0,F5=E5),0,IF(AND(ISNUMBER(F5),ISNUMBER(E5),E5&gt;0,F5=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K5" s="50" t="str">
+        <x:f>IF(A5="","",IF(AND(ISNUMBER(E5),E5=0,OR(ISNUMBER(SEARCH("Free",D5&amp;"")),AND(ISNUMBER(F5),F5=0))),"Subscription",IF(ISNUMBER(G5),"Profit",IF(ISNUMBER(I5),"Loss",IF(ISNUMBER(H5),"Draw",IF(AND(ISNUMBER(F5),ISNUMBER(E5),E5&gt;0,F5&gt;E5),"Profit",IF(AND(ISNUMBER(F5),ISNUMBER(E5),E5&gt;0,F5=E5),"Draw",IF(AND(ISNUMBER(F5),ISNUMBER(E5),E5&gt;0,F5=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L5" s="50"/>
       <x:c r="M5" s="58"/>
       <x:c r="N5" s="58"/>
@@ -1572,8 +1576,12 @@
       <x:c r="G6" s="58"/>
       <x:c r="H6" s="58"/>
       <x:c r="I6" s="58"/>
-      <x:c r="J6" s="60"/>
-      <x:c r="K6" s="50"/>
+      <x:c r="J6" s="60" t="str">
+        <x:f>IF(A6="","",IF(K6="Subscription","",IF(E6=0,"",IF(ISNUMBER(G6),G6/E6,IF(ISNUMBER(I6),-ABS(I6)/E6,IF(ISNUMBER(H6),0,IF(AND(ISNUMBER(F6),ISNUMBER(E6),E6&gt;0,F6&gt;E6),(F6-E6)/E6,IF(AND(ISNUMBER(F6),ISNUMBER(E6),E6&gt;0,F6=E6),0,IF(AND(ISNUMBER(F6),ISNUMBER(E6),E6&gt;0,F6=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K6" s="50" t="str">
+        <x:f>IF(A6="","",IF(AND(ISNUMBER(E6),E6=0,OR(ISNUMBER(SEARCH("Free",D6&amp;"")),AND(ISNUMBER(F6),F6=0))),"Subscription",IF(ISNUMBER(G6),"Profit",IF(ISNUMBER(I6),"Loss",IF(ISNUMBER(H6),"Draw",IF(AND(ISNUMBER(F6),ISNUMBER(E6),E6&gt;0,F6&gt;E6),"Profit",IF(AND(ISNUMBER(F6),ISNUMBER(E6),E6&gt;0,F6=E6),"Draw",IF(AND(ISNUMBER(F6),ISNUMBER(E6),E6&gt;0,F6=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L6" s="50"/>
       <x:c r="M6" s="58"/>
       <x:c r="N6" s="58"/>
@@ -1605,8 +1613,12 @@
       <x:c r="G7" s="58"/>
       <x:c r="H7" s="58"/>
       <x:c r="I7" s="58"/>
-      <x:c r="J7" s="60"/>
-      <x:c r="K7" s="50"/>
+      <x:c r="J7" s="60" t="str">
+        <x:f>IF(A7="","",IF(K7="Subscription","",IF(E7=0,"",IF(ISNUMBER(G7),G7/E7,IF(ISNUMBER(I7),-ABS(I7)/E7,IF(ISNUMBER(H7),0,IF(AND(ISNUMBER(F7),ISNUMBER(E7),E7&gt;0,F7&gt;E7),(F7-E7)/E7,IF(AND(ISNUMBER(F7),ISNUMBER(E7),E7&gt;0,F7=E7),0,IF(AND(ISNUMBER(F7),ISNUMBER(E7),E7&gt;0,F7=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K7" s="50" t="str">
+        <x:f>IF(A7="","",IF(AND(ISNUMBER(E7),E7=0,OR(ISNUMBER(SEARCH("Free",D7&amp;"")),AND(ISNUMBER(F7),F7=0))),"Subscription",IF(ISNUMBER(G7),"Profit",IF(ISNUMBER(I7),"Loss",IF(ISNUMBER(H7),"Draw",IF(AND(ISNUMBER(F7),ISNUMBER(E7),E7&gt;0,F7&gt;E7),"Profit",IF(AND(ISNUMBER(F7),ISNUMBER(E7),E7&gt;0,F7=E7),"Draw",IF(AND(ISNUMBER(F7),ISNUMBER(E7),E7&gt;0,F7=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L7" s="50"/>
       <x:c r="M7" s="58"/>
       <x:c r="N7" s="58"/>
@@ -1638,8 +1650,12 @@
       <x:c r="G8" s="58"/>
       <x:c r="H8" s="58"/>
       <x:c r="I8" s="58"/>
-      <x:c r="J8" s="60"/>
-      <x:c r="K8" s="50"/>
+      <x:c r="J8" s="60" t="str">
+        <x:f>IF(A8="","",IF(K8="Subscription","",IF(E8=0,"",IF(ISNUMBER(G8),G8/E8,IF(ISNUMBER(I8),-ABS(I8)/E8,IF(ISNUMBER(H8),0,IF(AND(ISNUMBER(F8),ISNUMBER(E8),E8&gt;0,F8&gt;E8),(F8-E8)/E8,IF(AND(ISNUMBER(F8),ISNUMBER(E8),E8&gt;0,F8=E8),0,IF(AND(ISNUMBER(F8),ISNUMBER(E8),E8&gt;0,F8=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K8" s="50" t="str">
+        <x:f>IF(A8="","",IF(AND(ISNUMBER(E8),E8=0,OR(ISNUMBER(SEARCH("Free",D8&amp;"")),AND(ISNUMBER(F8),F8=0))),"Subscription",IF(ISNUMBER(G8),"Profit",IF(ISNUMBER(I8),"Loss",IF(ISNUMBER(H8),"Draw",IF(AND(ISNUMBER(F8),ISNUMBER(E8),E8&gt;0,F8&gt;E8),"Profit",IF(AND(ISNUMBER(F8),ISNUMBER(E8),E8&gt;0,F8=E8),"Draw",IF(AND(ISNUMBER(F8),ISNUMBER(E8),E8&gt;0,F8=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L8" s="50"/>
       <x:c r="M8" s="58"/>
       <x:c r="N8" s="58"/>
@@ -1671,8 +1687,12 @@
       <x:c r="G9" s="58"/>
       <x:c r="H9" s="58"/>
       <x:c r="I9" s="58"/>
-      <x:c r="J9" s="60"/>
-      <x:c r="K9" s="50"/>
+      <x:c r="J9" s="60" t="str">
+        <x:f>IF(A9="","",IF(K9="Subscription","",IF(E9=0,"",IF(ISNUMBER(G9),G9/E9,IF(ISNUMBER(I9),-ABS(I9)/E9,IF(ISNUMBER(H9),0,IF(AND(ISNUMBER(F9),ISNUMBER(E9),E9&gt;0,F9&gt;E9),(F9-E9)/E9,IF(AND(ISNUMBER(F9),ISNUMBER(E9),E9&gt;0,F9=E9),0,IF(AND(ISNUMBER(F9),ISNUMBER(E9),E9&gt;0,F9=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K9" s="50" t="str">
+        <x:f>IF(A9="","",IF(AND(ISNUMBER(E9),E9=0,OR(ISNUMBER(SEARCH("Free",D9&amp;"")),AND(ISNUMBER(F9),F9=0))),"Subscription",IF(ISNUMBER(G9),"Profit",IF(ISNUMBER(I9),"Loss",IF(ISNUMBER(H9),"Draw",IF(AND(ISNUMBER(F9),ISNUMBER(E9),E9&gt;0,F9&gt;E9),"Profit",IF(AND(ISNUMBER(F9),ISNUMBER(E9),E9&gt;0,F9=E9),"Draw",IF(AND(ISNUMBER(F9),ISNUMBER(E9),E9&gt;0,F9=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L9" s="50"/>
       <x:c r="M9" s="58"/>
       <x:c r="N9" s="58"/>
@@ -1704,8 +1724,12 @@
       <x:c r="G10" s="58"/>
       <x:c r="H10" s="58"/>
       <x:c r="I10" s="58"/>
-      <x:c r="J10" s="60"/>
-      <x:c r="K10" s="50"/>
+      <x:c r="J10" s="60" t="str">
+        <x:f>IF(A10="","",IF(K10="Subscription","",IF(E10=0,"",IF(ISNUMBER(G10),G10/E10,IF(ISNUMBER(I10),-ABS(I10)/E10,IF(ISNUMBER(H10),0,IF(AND(ISNUMBER(F10),ISNUMBER(E10),E10&gt;0,F10&gt;E10),(F10-E10)/E10,IF(AND(ISNUMBER(F10),ISNUMBER(E10),E10&gt;0,F10=E10),0,IF(AND(ISNUMBER(F10),ISNUMBER(E10),E10&gt;0,F10=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K10" s="50" t="str">
+        <x:f>IF(A10="","",IF(AND(ISNUMBER(E10),E10=0,OR(ISNUMBER(SEARCH("Free",D10&amp;"")),AND(ISNUMBER(F10),F10=0))),"Subscription",IF(ISNUMBER(G10),"Profit",IF(ISNUMBER(I10),"Loss",IF(ISNUMBER(H10),"Draw",IF(AND(ISNUMBER(F10),ISNUMBER(E10),E10&gt;0,F10&gt;E10),"Profit",IF(AND(ISNUMBER(F10),ISNUMBER(E10),E10&gt;0,F10=E10),"Draw",IF(AND(ISNUMBER(F10),ISNUMBER(E10),E10&gt;0,F10=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L10" s="50"/>
       <x:c r="M10" s="58"/>
       <x:c r="N10" s="58"/>
@@ -1737,8 +1761,12 @@
       <x:c r="G11" s="58"/>
       <x:c r="H11" s="58"/>
       <x:c r="I11" s="58"/>
-      <x:c r="J11" s="60"/>
-      <x:c r="K11" s="50"/>
+      <x:c r="J11" s="60" t="str">
+        <x:f>IF(A11="","",IF(K11="Subscription","",IF(E11=0,"",IF(ISNUMBER(G11),G11/E11,IF(ISNUMBER(I11),-ABS(I11)/E11,IF(ISNUMBER(H11),0,IF(AND(ISNUMBER(F11),ISNUMBER(E11),E11&gt;0,F11&gt;E11),(F11-E11)/E11,IF(AND(ISNUMBER(F11),ISNUMBER(E11),E11&gt;0,F11=E11),0,IF(AND(ISNUMBER(F11),ISNUMBER(E11),E11&gt;0,F11=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K11" s="50" t="str">
+        <x:f>IF(A11="","",IF(AND(ISNUMBER(E11),E11=0,OR(ISNUMBER(SEARCH("Free",D11&amp;"")),AND(ISNUMBER(F11),F11=0))),"Subscription",IF(ISNUMBER(G11),"Profit",IF(ISNUMBER(I11),"Loss",IF(ISNUMBER(H11),"Draw",IF(AND(ISNUMBER(F11),ISNUMBER(E11),E11&gt;0,F11&gt;E11),"Profit",IF(AND(ISNUMBER(F11),ISNUMBER(E11),E11&gt;0,F11=E11),"Draw",IF(AND(ISNUMBER(F11),ISNUMBER(E11),E11&gt;0,F11=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L11" s="50"/>
       <x:c r="M11" s="58"/>
       <x:c r="N11" s="58"/>
@@ -1770,8 +1798,12 @@
       <x:c r="G12" s="58"/>
       <x:c r="H12" s="58"/>
       <x:c r="I12" s="58"/>
-      <x:c r="J12" s="60"/>
-      <x:c r="K12" s="50"/>
+      <x:c r="J12" s="60" t="str">
+        <x:f>IF(A12="","",IF(K12="Subscription","",IF(E12=0,"",IF(ISNUMBER(G12),G12/E12,IF(ISNUMBER(I12),-ABS(I12)/E12,IF(ISNUMBER(H12),0,IF(AND(ISNUMBER(F12),ISNUMBER(E12),E12&gt;0,F12&gt;E12),(F12-E12)/E12,IF(AND(ISNUMBER(F12),ISNUMBER(E12),E12&gt;0,F12=E12),0,IF(AND(ISNUMBER(F12),ISNUMBER(E12),E12&gt;0,F12=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K12" s="50" t="str">
+        <x:f>IF(A12="","",IF(AND(ISNUMBER(E12),E12=0,OR(ISNUMBER(SEARCH("Free",D12&amp;"")),AND(ISNUMBER(F12),F12=0))),"Subscription",IF(ISNUMBER(G12),"Profit",IF(ISNUMBER(I12),"Loss",IF(ISNUMBER(H12),"Draw",IF(AND(ISNUMBER(F12),ISNUMBER(E12),E12&gt;0,F12&gt;E12),"Profit",IF(AND(ISNUMBER(F12),ISNUMBER(E12),E12&gt;0,F12=E12),"Draw",IF(AND(ISNUMBER(F12),ISNUMBER(E12),E12&gt;0,F12=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L12" s="50"/>
       <x:c r="M12" s="58"/>
       <x:c r="N12" s="58"/>
@@ -1803,8 +1835,12 @@
       <x:c r="G13" s="58"/>
       <x:c r="H13" s="58"/>
       <x:c r="I13" s="58"/>
-      <x:c r="J13" s="60"/>
-      <x:c r="K13" s="50"/>
+      <x:c r="J13" s="60" t="str">
+        <x:f>IF(A13="","",IF(K13="Subscription","",IF(E13=0,"",IF(ISNUMBER(G13),G13/E13,IF(ISNUMBER(I13),-ABS(I13)/E13,IF(ISNUMBER(H13),0,IF(AND(ISNUMBER(F13),ISNUMBER(E13),E13&gt;0,F13&gt;E13),(F13-E13)/E13,IF(AND(ISNUMBER(F13),ISNUMBER(E13),E13&gt;0,F13=E13),0,IF(AND(ISNUMBER(F13),ISNUMBER(E13),E13&gt;0,F13=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K13" s="50" t="str">
+        <x:f>IF(A13="","",IF(AND(ISNUMBER(E13),E13=0,OR(ISNUMBER(SEARCH("Free",D13&amp;"")),AND(ISNUMBER(F13),F13=0))),"Subscription",IF(ISNUMBER(G13),"Profit",IF(ISNUMBER(I13),"Loss",IF(ISNUMBER(H13),"Draw",IF(AND(ISNUMBER(F13),ISNUMBER(E13),E13&gt;0,F13&gt;E13),"Profit",IF(AND(ISNUMBER(F13),ISNUMBER(E13),E13&gt;0,F13=E13),"Draw",IF(AND(ISNUMBER(F13),ISNUMBER(E13),E13&gt;0,F13=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L13" s="50"/>
       <x:c r="M13" s="58"/>
       <x:c r="N13" s="58"/>
@@ -1836,8 +1872,12 @@
       <x:c r="G14" s="58"/>
       <x:c r="H14" s="58"/>
       <x:c r="I14" s="58"/>
-      <x:c r="J14" s="60"/>
-      <x:c r="K14" s="50"/>
+      <x:c r="J14" s="60" t="str">
+        <x:f>IF(A14="","",IF(K14="Subscription","",IF(E14=0,"",IF(ISNUMBER(G14),G14/E14,IF(ISNUMBER(I14),-ABS(I14)/E14,IF(ISNUMBER(H14),0,IF(AND(ISNUMBER(F14),ISNUMBER(E14),E14&gt;0,F14&gt;E14),(F14-E14)/E14,IF(AND(ISNUMBER(F14),ISNUMBER(E14),E14&gt;0,F14=E14),0,IF(AND(ISNUMBER(F14),ISNUMBER(E14),E14&gt;0,F14=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K14" s="50" t="str">
+        <x:f>IF(A14="","",IF(AND(ISNUMBER(E14),E14=0,OR(ISNUMBER(SEARCH("Free",D14&amp;"")),AND(ISNUMBER(F14),F14=0))),"Subscription",IF(ISNUMBER(G14),"Profit",IF(ISNUMBER(I14),"Loss",IF(ISNUMBER(H14),"Draw",IF(AND(ISNUMBER(F14),ISNUMBER(E14),E14&gt;0,F14&gt;E14),"Profit",IF(AND(ISNUMBER(F14),ISNUMBER(E14),E14&gt;0,F14=E14),"Draw",IF(AND(ISNUMBER(F14),ISNUMBER(E14),E14&gt;0,F14=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L14" s="50"/>
       <x:c r="M14" s="58"/>
       <x:c r="N14" s="58"/>
@@ -1869,8 +1909,12 @@
       <x:c r="G15" s="58"/>
       <x:c r="H15" s="58"/>
       <x:c r="I15" s="58"/>
-      <x:c r="J15" s="60"/>
-      <x:c r="K15" s="50"/>
+      <x:c r="J15" s="60" t="str">
+        <x:f>IF(A15="","",IF(K15="Subscription","",IF(E15=0,"",IF(ISNUMBER(G15),G15/E15,IF(ISNUMBER(I15),-ABS(I15)/E15,IF(ISNUMBER(H15),0,IF(AND(ISNUMBER(F15),ISNUMBER(E15),E15&gt;0,F15&gt;E15),(F15-E15)/E15,IF(AND(ISNUMBER(F15),ISNUMBER(E15),E15&gt;0,F15=E15),0,IF(AND(ISNUMBER(F15),ISNUMBER(E15),E15&gt;0,F15=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K15" s="50" t="str">
+        <x:f>IF(A15="","",IF(AND(ISNUMBER(E15),E15=0,OR(ISNUMBER(SEARCH("Free",D15&amp;"")),AND(ISNUMBER(F15),F15=0))),"Subscription",IF(ISNUMBER(G15),"Profit",IF(ISNUMBER(I15),"Loss",IF(ISNUMBER(H15),"Draw",IF(AND(ISNUMBER(F15),ISNUMBER(E15),E15&gt;0,F15&gt;E15),"Profit",IF(AND(ISNUMBER(F15),ISNUMBER(E15),E15&gt;0,F15=E15),"Draw",IF(AND(ISNUMBER(F15),ISNUMBER(E15),E15&gt;0,F15=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L15" s="50"/>
       <x:c r="M15" s="58"/>
       <x:c r="N15" s="58"/>
@@ -1902,8 +1946,12 @@
       <x:c r="G16" s="58"/>
       <x:c r="H16" s="58"/>
       <x:c r="I16" s="58"/>
-      <x:c r="J16" s="60"/>
-      <x:c r="K16" s="50"/>
+      <x:c r="J16" s="60" t="str">
+        <x:f>IF(A16="","",IF(K16="Subscription","",IF(E16=0,"",IF(ISNUMBER(G16),G16/E16,IF(ISNUMBER(I16),-ABS(I16)/E16,IF(ISNUMBER(H16),0,IF(AND(ISNUMBER(F16),ISNUMBER(E16),E16&gt;0,F16&gt;E16),(F16-E16)/E16,IF(AND(ISNUMBER(F16),ISNUMBER(E16),E16&gt;0,F16=E16),0,IF(AND(ISNUMBER(F16),ISNUMBER(E16),E16&gt;0,F16=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K16" s="50" t="str">
+        <x:f>IF(A16="","",IF(AND(ISNUMBER(E16),E16=0,OR(ISNUMBER(SEARCH("Free",D16&amp;"")),AND(ISNUMBER(F16),F16=0))),"Subscription",IF(ISNUMBER(G16),"Profit",IF(ISNUMBER(I16),"Loss",IF(ISNUMBER(H16),"Draw",IF(AND(ISNUMBER(F16),ISNUMBER(E16),E16&gt;0,F16&gt;E16),"Profit",IF(AND(ISNUMBER(F16),ISNUMBER(E16),E16&gt;0,F16=E16),"Draw",IF(AND(ISNUMBER(F16),ISNUMBER(E16),E16&gt;0,F16=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L16" s="50"/>
       <x:c r="M16" s="58"/>
       <x:c r="N16" s="58"/>
@@ -1935,8 +1983,12 @@
       <x:c r="G17" s="58"/>
       <x:c r="H17" s="58"/>
       <x:c r="I17" s="58"/>
-      <x:c r="J17" s="60"/>
-      <x:c r="K17" s="50"/>
+      <x:c r="J17" s="60" t="str">
+        <x:f>IF(A17="","",IF(K17="Subscription","",IF(E17=0,"",IF(ISNUMBER(G17),G17/E17,IF(ISNUMBER(I17),-ABS(I17)/E17,IF(ISNUMBER(H17),0,IF(AND(ISNUMBER(F17),ISNUMBER(E17),E17&gt;0,F17&gt;E17),(F17-E17)/E17,IF(AND(ISNUMBER(F17),ISNUMBER(E17),E17&gt;0,F17=E17),0,IF(AND(ISNUMBER(F17),ISNUMBER(E17),E17&gt;0,F17=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K17" s="50" t="str">
+        <x:f>IF(A17="","",IF(AND(ISNUMBER(E17),E17=0,OR(ISNUMBER(SEARCH("Free",D17&amp;"")),AND(ISNUMBER(F17),F17=0))),"Subscription",IF(ISNUMBER(G17),"Profit",IF(ISNUMBER(I17),"Loss",IF(ISNUMBER(H17),"Draw",IF(AND(ISNUMBER(F17),ISNUMBER(E17),E17&gt;0,F17&gt;E17),"Profit",IF(AND(ISNUMBER(F17),ISNUMBER(E17),E17&gt;0,F17=E17),"Draw",IF(AND(ISNUMBER(F17),ISNUMBER(E17),E17&gt;0,F17=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L17" s="50"/>
       <x:c r="M17" s="58"/>
       <x:c r="N17" s="58"/>
@@ -1968,8 +2020,12 @@
       <x:c r="G18" s="58"/>
       <x:c r="H18" s="58"/>
       <x:c r="I18" s="58"/>
-      <x:c r="J18" s="60"/>
-      <x:c r="K18" s="50"/>
+      <x:c r="J18" s="60" t="str">
+        <x:f>IF(A18="","",IF(K18="Subscription","",IF(E18=0,"",IF(ISNUMBER(G18),G18/E18,IF(ISNUMBER(I18),-ABS(I18)/E18,IF(ISNUMBER(H18),0,IF(AND(ISNUMBER(F18),ISNUMBER(E18),E18&gt;0,F18&gt;E18),(F18-E18)/E18,IF(AND(ISNUMBER(F18),ISNUMBER(E18),E18&gt;0,F18=E18),0,IF(AND(ISNUMBER(F18),ISNUMBER(E18),E18&gt;0,F18=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K18" s="50" t="str">
+        <x:f>IF(A18="","",IF(AND(ISNUMBER(E18),E18=0,OR(ISNUMBER(SEARCH("Free",D18&amp;"")),AND(ISNUMBER(F18),F18=0))),"Subscription",IF(ISNUMBER(G18),"Profit",IF(ISNUMBER(I18),"Loss",IF(ISNUMBER(H18),"Draw",IF(AND(ISNUMBER(F18),ISNUMBER(E18),E18&gt;0,F18&gt;E18),"Profit",IF(AND(ISNUMBER(F18),ISNUMBER(E18),E18&gt;0,F18=E18),"Draw",IF(AND(ISNUMBER(F18),ISNUMBER(E18),E18&gt;0,F18=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L18" s="50"/>
       <x:c r="M18" s="58"/>
       <x:c r="N18" s="58"/>
@@ -2001,8 +2057,12 @@
       <x:c r="G19" s="58"/>
       <x:c r="H19" s="58"/>
       <x:c r="I19" s="58"/>
-      <x:c r="J19" s="60"/>
-      <x:c r="K19" s="50"/>
+      <x:c r="J19" s="60" t="str">
+        <x:f>IF(A19="","",IF(K19="Subscription","",IF(E19=0,"",IF(ISNUMBER(G19),G19/E19,IF(ISNUMBER(I19),-ABS(I19)/E19,IF(ISNUMBER(H19),0,IF(AND(ISNUMBER(F19),ISNUMBER(E19),E19&gt;0,F19&gt;E19),(F19-E19)/E19,IF(AND(ISNUMBER(F19),ISNUMBER(E19),E19&gt;0,F19=E19),0,IF(AND(ISNUMBER(F19),ISNUMBER(E19),E19&gt;0,F19=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K19" s="50" t="str">
+        <x:f>IF(A19="","",IF(AND(ISNUMBER(E19),E19=0,OR(ISNUMBER(SEARCH("Free",D19&amp;"")),AND(ISNUMBER(F19),F19=0))),"Subscription",IF(ISNUMBER(G19),"Profit",IF(ISNUMBER(I19),"Loss",IF(ISNUMBER(H19),"Draw",IF(AND(ISNUMBER(F19),ISNUMBER(E19),E19&gt;0,F19&gt;E19),"Profit",IF(AND(ISNUMBER(F19),ISNUMBER(E19),E19&gt;0,F19=E19),"Draw",IF(AND(ISNUMBER(F19),ISNUMBER(E19),E19&gt;0,F19=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L19" s="50"/>
       <x:c r="M19" s="58"/>
       <x:c r="N19" s="58"/>
@@ -2034,8 +2094,12 @@
       <x:c r="G20" s="58"/>
       <x:c r="H20" s="58"/>
       <x:c r="I20" s="58"/>
-      <x:c r="J20" s="60"/>
-      <x:c r="K20" s="50"/>
+      <x:c r="J20" s="60" t="str">
+        <x:f>IF(A20="","",IF(K20="Subscription","",IF(E20=0,"",IF(ISNUMBER(G20),G20/E20,IF(ISNUMBER(I20),-ABS(I20)/E20,IF(ISNUMBER(H20),0,IF(AND(ISNUMBER(F20),ISNUMBER(E20),E20&gt;0,F20&gt;E20),(F20-E20)/E20,IF(AND(ISNUMBER(F20),ISNUMBER(E20),E20&gt;0,F20=E20),0,IF(AND(ISNUMBER(F20),ISNUMBER(E20),E20&gt;0,F20=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K20" s="50" t="str">
+        <x:f>IF(A20="","",IF(AND(ISNUMBER(E20),E20=0,OR(ISNUMBER(SEARCH("Free",D20&amp;"")),AND(ISNUMBER(F20),F20=0))),"Subscription",IF(ISNUMBER(G20),"Profit",IF(ISNUMBER(I20),"Loss",IF(ISNUMBER(H20),"Draw",IF(AND(ISNUMBER(F20),ISNUMBER(E20),E20&gt;0,F20&gt;E20),"Profit",IF(AND(ISNUMBER(F20),ISNUMBER(E20),E20&gt;0,F20=E20),"Draw",IF(AND(ISNUMBER(F20),ISNUMBER(E20),E20&gt;0,F20=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L20" s="50"/>
       <x:c r="M20" s="58"/>
       <x:c r="N20" s="58"/>
@@ -2067,8 +2131,12 @@
       <x:c r="G21" s="58"/>
       <x:c r="H21" s="58"/>
       <x:c r="I21" s="58"/>
-      <x:c r="J21" s="60"/>
-      <x:c r="K21" s="50"/>
+      <x:c r="J21" s="60" t="str">
+        <x:f>IF(A21="","",IF(K21="Subscription","",IF(E21=0,"",IF(ISNUMBER(G21),G21/E21,IF(ISNUMBER(I21),-ABS(I21)/E21,IF(ISNUMBER(H21),0,IF(AND(ISNUMBER(F21),ISNUMBER(E21),E21&gt;0,F21&gt;E21),(F21-E21)/E21,IF(AND(ISNUMBER(F21),ISNUMBER(E21),E21&gt;0,F21=E21),0,IF(AND(ISNUMBER(F21),ISNUMBER(E21),E21&gt;0,F21=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K21" s="50" t="str">
+        <x:f>IF(A21="","",IF(AND(ISNUMBER(E21),E21=0,OR(ISNUMBER(SEARCH("Free",D21&amp;"")),AND(ISNUMBER(F21),F21=0))),"Subscription",IF(ISNUMBER(G21),"Profit",IF(ISNUMBER(I21),"Loss",IF(ISNUMBER(H21),"Draw",IF(AND(ISNUMBER(F21),ISNUMBER(E21),E21&gt;0,F21&gt;E21),"Profit",IF(AND(ISNUMBER(F21),ISNUMBER(E21),E21&gt;0,F21=E21),"Draw",IF(AND(ISNUMBER(F21),ISNUMBER(E21),E21&gt;0,F21=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L21" s="50"/>
       <x:c r="M21" s="58"/>
       <x:c r="N21" s="58"/>
@@ -2100,8 +2168,12 @@
       <x:c r="G22" s="58"/>
       <x:c r="H22" s="58"/>
       <x:c r="I22" s="58"/>
-      <x:c r="J22" s="60"/>
-      <x:c r="K22" s="50"/>
+      <x:c r="J22" s="60" t="str">
+        <x:f>IF(A22="","",IF(K22="Subscription","",IF(E22=0,"",IF(ISNUMBER(G22),G22/E22,IF(ISNUMBER(I22),-ABS(I22)/E22,IF(ISNUMBER(H22),0,IF(AND(ISNUMBER(F22),ISNUMBER(E22),E22&gt;0,F22&gt;E22),(F22-E22)/E22,IF(AND(ISNUMBER(F22),ISNUMBER(E22),E22&gt;0,F22=E22),0,IF(AND(ISNUMBER(F22),ISNUMBER(E22),E22&gt;0,F22=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K22" s="50" t="str">
+        <x:f>IF(A22="","",IF(AND(ISNUMBER(E22),E22=0,OR(ISNUMBER(SEARCH("Free",D22&amp;"")),AND(ISNUMBER(F22),F22=0))),"Subscription",IF(ISNUMBER(G22),"Profit",IF(ISNUMBER(I22),"Loss",IF(ISNUMBER(H22),"Draw",IF(AND(ISNUMBER(F22),ISNUMBER(E22),E22&gt;0,F22&gt;E22),"Profit",IF(AND(ISNUMBER(F22),ISNUMBER(E22),E22&gt;0,F22=E22),"Draw",IF(AND(ISNUMBER(F22),ISNUMBER(E22),E22&gt;0,F22=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L22" s="50"/>
       <x:c r="M22" s="58"/>
       <x:c r="N22" s="58"/>
@@ -2133,8 +2205,12 @@
       <x:c r="G23" s="58"/>
       <x:c r="H23" s="58"/>
       <x:c r="I23" s="58"/>
-      <x:c r="J23" s="60"/>
-      <x:c r="K23" s="50"/>
+      <x:c r="J23" s="60" t="str">
+        <x:f>IF(A23="","",IF(K23="Subscription","",IF(E23=0,"",IF(ISNUMBER(G23),G23/E23,IF(ISNUMBER(I23),-ABS(I23)/E23,IF(ISNUMBER(H23),0,IF(AND(ISNUMBER(F23),ISNUMBER(E23),E23&gt;0,F23&gt;E23),(F23-E23)/E23,IF(AND(ISNUMBER(F23),ISNUMBER(E23),E23&gt;0,F23=E23),0,IF(AND(ISNUMBER(F23),ISNUMBER(E23),E23&gt;0,F23=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K23" s="50" t="str">
+        <x:f>IF(A23="","",IF(AND(ISNUMBER(E23),E23=0,OR(ISNUMBER(SEARCH("Free",D23&amp;"")),AND(ISNUMBER(F23),F23=0))),"Subscription",IF(ISNUMBER(G23),"Profit",IF(ISNUMBER(I23),"Loss",IF(ISNUMBER(H23),"Draw",IF(AND(ISNUMBER(F23),ISNUMBER(E23),E23&gt;0,F23&gt;E23),"Profit",IF(AND(ISNUMBER(F23),ISNUMBER(E23),E23&gt;0,F23=E23),"Draw",IF(AND(ISNUMBER(F23),ISNUMBER(E23),E23&gt;0,F23=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L23" s="50"/>
       <x:c r="M23" s="58"/>
       <x:c r="N23" s="58"/>
@@ -2166,8 +2242,12 @@
       <x:c r="G24" s="58"/>
       <x:c r="H24" s="58"/>
       <x:c r="I24" s="58"/>
-      <x:c r="J24" s="60"/>
-      <x:c r="K24" s="50"/>
+      <x:c r="J24" s="60" t="str">
+        <x:f>IF(A24="","",IF(K24="Subscription","",IF(E24=0,"",IF(ISNUMBER(G24),G24/E24,IF(ISNUMBER(I24),-ABS(I24)/E24,IF(ISNUMBER(H24),0,IF(AND(ISNUMBER(F24),ISNUMBER(E24),E24&gt;0,F24&gt;E24),(F24-E24)/E24,IF(AND(ISNUMBER(F24),ISNUMBER(E24),E24&gt;0,F24=E24),0,IF(AND(ISNUMBER(F24),ISNUMBER(E24),E24&gt;0,F24=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K24" s="50" t="str">
+        <x:f>IF(A24="","",IF(AND(ISNUMBER(E24),E24=0,OR(ISNUMBER(SEARCH("Free",D24&amp;"")),AND(ISNUMBER(F24),F24=0))),"Subscription",IF(ISNUMBER(G24),"Profit",IF(ISNUMBER(I24),"Loss",IF(ISNUMBER(H24),"Draw",IF(AND(ISNUMBER(F24),ISNUMBER(E24),E24&gt;0,F24&gt;E24),"Profit",IF(AND(ISNUMBER(F24),ISNUMBER(E24),E24&gt;0,F24=E24),"Draw",IF(AND(ISNUMBER(F24),ISNUMBER(E24),E24&gt;0,F24=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L24" s="50"/>
       <x:c r="M24" s="58"/>
       <x:c r="N24" s="58"/>
@@ -2199,8 +2279,12 @@
       <x:c r="G25" s="58"/>
       <x:c r="H25" s="58"/>
       <x:c r="I25" s="58"/>
-      <x:c r="J25" s="60"/>
-      <x:c r="K25" s="50"/>
+      <x:c r="J25" s="60" t="str">
+        <x:f>IF(A25="","",IF(K25="Subscription","",IF(E25=0,"",IF(ISNUMBER(G25),G25/E25,IF(ISNUMBER(I25),-ABS(I25)/E25,IF(ISNUMBER(H25),0,IF(AND(ISNUMBER(F25),ISNUMBER(E25),E25&gt;0,F25&gt;E25),(F25-E25)/E25,IF(AND(ISNUMBER(F25),ISNUMBER(E25),E25&gt;0,F25=E25),0,IF(AND(ISNUMBER(F25),ISNUMBER(E25),E25&gt;0,F25=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K25" s="50" t="str">
+        <x:f>IF(A25="","",IF(AND(ISNUMBER(E25),E25=0,OR(ISNUMBER(SEARCH("Free",D25&amp;"")),AND(ISNUMBER(F25),F25=0))),"Subscription",IF(ISNUMBER(G25),"Profit",IF(ISNUMBER(I25),"Loss",IF(ISNUMBER(H25),"Draw",IF(AND(ISNUMBER(F25),ISNUMBER(E25),E25&gt;0,F25&gt;E25),"Profit",IF(AND(ISNUMBER(F25),ISNUMBER(E25),E25&gt;0,F25=E25),"Draw",IF(AND(ISNUMBER(F25),ISNUMBER(E25),E25&gt;0,F25=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L25" s="50"/>
       <x:c r="M25" s="58"/>
       <x:c r="N25" s="58"/>
@@ -2232,8 +2316,12 @@
       <x:c r="G26" s="58"/>
       <x:c r="H26" s="58"/>
       <x:c r="I26" s="58"/>
-      <x:c r="J26" s="60"/>
-      <x:c r="K26" s="50"/>
+      <x:c r="J26" s="60" t="str">
+        <x:f>IF(A26="","",IF(K26="Subscription","",IF(E26=0,"",IF(ISNUMBER(G26),G26/E26,IF(ISNUMBER(I26),-ABS(I26)/E26,IF(ISNUMBER(H26),0,IF(AND(ISNUMBER(F26),ISNUMBER(E26),E26&gt;0,F26&gt;E26),(F26-E26)/E26,IF(AND(ISNUMBER(F26),ISNUMBER(E26),E26&gt;0,F26=E26),0,IF(AND(ISNUMBER(F26),ISNUMBER(E26),E26&gt;0,F26=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K26" s="50" t="str">
+        <x:f>IF(A26="","",IF(AND(ISNUMBER(E26),E26=0,OR(ISNUMBER(SEARCH("Free",D26&amp;"")),AND(ISNUMBER(F26),F26=0))),"Subscription",IF(ISNUMBER(G26),"Profit",IF(ISNUMBER(I26),"Loss",IF(ISNUMBER(H26),"Draw",IF(AND(ISNUMBER(F26),ISNUMBER(E26),E26&gt;0,F26&gt;E26),"Profit",IF(AND(ISNUMBER(F26),ISNUMBER(E26),E26&gt;0,F26=E26),"Draw",IF(AND(ISNUMBER(F26),ISNUMBER(E26),E26&gt;0,F26=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L26" s="50"/>
       <x:c r="M26" s="58"/>
       <x:c r="N26" s="58"/>
@@ -2265,8 +2353,12 @@
       <x:c r="G27" s="58"/>
       <x:c r="H27" s="58"/>
       <x:c r="I27" s="58"/>
-      <x:c r="J27" s="60"/>
-      <x:c r="K27" s="50"/>
+      <x:c r="J27" s="60" t="str">
+        <x:f>IF(A27="","",IF(K27="Subscription","",IF(E27=0,"",IF(ISNUMBER(G27),G27/E27,IF(ISNUMBER(I27),-ABS(I27)/E27,IF(ISNUMBER(H27),0,IF(AND(ISNUMBER(F27),ISNUMBER(E27),E27&gt;0,F27&gt;E27),(F27-E27)/E27,IF(AND(ISNUMBER(F27),ISNUMBER(E27),E27&gt;0,F27=E27),0,IF(AND(ISNUMBER(F27),ISNUMBER(E27),E27&gt;0,F27=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K27" s="50" t="str">
+        <x:f>IF(A27="","",IF(AND(ISNUMBER(E27),E27=0,OR(ISNUMBER(SEARCH("Free",D27&amp;"")),AND(ISNUMBER(F27),F27=0))),"Subscription",IF(ISNUMBER(G27),"Profit",IF(ISNUMBER(I27),"Loss",IF(ISNUMBER(H27),"Draw",IF(AND(ISNUMBER(F27),ISNUMBER(E27),E27&gt;0,F27&gt;E27),"Profit",IF(AND(ISNUMBER(F27),ISNUMBER(E27),E27&gt;0,F27=E27),"Draw",IF(AND(ISNUMBER(F27),ISNUMBER(E27),E27&gt;0,F27=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L27" s="50"/>
       <x:c r="M27" s="58"/>
       <x:c r="N27" s="58"/>
@@ -2298,8 +2390,12 @@
       <x:c r="G28" s="58"/>
       <x:c r="H28" s="58"/>
       <x:c r="I28" s="58"/>
-      <x:c r="J28" s="60"/>
-      <x:c r="K28" s="50"/>
+      <x:c r="J28" s="60" t="str">
+        <x:f>IF(A28="","",IF(K28="Subscription","",IF(E28=0,"",IF(ISNUMBER(G28),G28/E28,IF(ISNUMBER(I28),-ABS(I28)/E28,IF(ISNUMBER(H28),0,IF(AND(ISNUMBER(F28),ISNUMBER(E28),E28&gt;0,F28&gt;E28),(F28-E28)/E28,IF(AND(ISNUMBER(F28),ISNUMBER(E28),E28&gt;0,F28=E28),0,IF(AND(ISNUMBER(F28),ISNUMBER(E28),E28&gt;0,F28=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K28" s="50" t="str">
+        <x:f>IF(A28="","",IF(AND(ISNUMBER(E28),E28=0,OR(ISNUMBER(SEARCH("Free",D28&amp;"")),AND(ISNUMBER(F28),F28=0))),"Subscription",IF(ISNUMBER(G28),"Profit",IF(ISNUMBER(I28),"Loss",IF(ISNUMBER(H28),"Draw",IF(AND(ISNUMBER(F28),ISNUMBER(E28),E28&gt;0,F28&gt;E28),"Profit",IF(AND(ISNUMBER(F28),ISNUMBER(E28),E28&gt;0,F28=E28),"Draw",IF(AND(ISNUMBER(F28),ISNUMBER(E28),E28&gt;0,F28=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L28" s="50"/>
       <x:c r="M28" s="58"/>
       <x:c r="N28" s="58"/>
@@ -2331,8 +2427,12 @@
       <x:c r="G29" s="58"/>
       <x:c r="H29" s="58"/>
       <x:c r="I29" s="58"/>
-      <x:c r="J29" s="60"/>
-      <x:c r="K29" s="50"/>
+      <x:c r="J29" s="60" t="str">
+        <x:f>IF(A29="","",IF(K29="Subscription","",IF(E29=0,"",IF(ISNUMBER(G29),G29/E29,IF(ISNUMBER(I29),-ABS(I29)/E29,IF(ISNUMBER(H29),0,IF(AND(ISNUMBER(F29),ISNUMBER(E29),E29&gt;0,F29&gt;E29),(F29-E29)/E29,IF(AND(ISNUMBER(F29),ISNUMBER(E29),E29&gt;0,F29=E29),0,IF(AND(ISNUMBER(F29),ISNUMBER(E29),E29&gt;0,F29=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K29" s="50" t="str">
+        <x:f>IF(A29="","",IF(AND(ISNUMBER(E29),E29=0,OR(ISNUMBER(SEARCH("Free",D29&amp;"")),AND(ISNUMBER(F29),F29=0))),"Subscription",IF(ISNUMBER(G29),"Profit",IF(ISNUMBER(I29),"Loss",IF(ISNUMBER(H29),"Draw",IF(AND(ISNUMBER(F29),ISNUMBER(E29),E29&gt;0,F29&gt;E29),"Profit",IF(AND(ISNUMBER(F29),ISNUMBER(E29),E29&gt;0,F29=E29),"Draw",IF(AND(ISNUMBER(F29),ISNUMBER(E29),E29&gt;0,F29=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L29" s="50"/>
       <x:c r="M29" s="58"/>
       <x:c r="N29" s="58"/>
@@ -2364,8 +2464,12 @@
       <x:c r="G30" s="58"/>
       <x:c r="H30" s="58"/>
       <x:c r="I30" s="58"/>
-      <x:c r="J30" s="60"/>
-      <x:c r="K30" s="50"/>
+      <x:c r="J30" s="60" t="str">
+        <x:f>IF(A30="","",IF(K30="Subscription","",IF(E30=0,"",IF(ISNUMBER(G30),G30/E30,IF(ISNUMBER(I30),-ABS(I30)/E30,IF(ISNUMBER(H30),0,IF(AND(ISNUMBER(F30),ISNUMBER(E30),E30&gt;0,F30&gt;E30),(F30-E30)/E30,IF(AND(ISNUMBER(F30),ISNUMBER(E30),E30&gt;0,F30=E30),0,IF(AND(ISNUMBER(F30),ISNUMBER(E30),E30&gt;0,F30=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K30" s="50" t="str">
+        <x:f>IF(A30="","",IF(AND(ISNUMBER(E30),E30=0,OR(ISNUMBER(SEARCH("Free",D30&amp;"")),AND(ISNUMBER(F30),F30=0))),"Subscription",IF(ISNUMBER(G30),"Profit",IF(ISNUMBER(I30),"Loss",IF(ISNUMBER(H30),"Draw",IF(AND(ISNUMBER(F30),ISNUMBER(E30),E30&gt;0,F30&gt;E30),"Profit",IF(AND(ISNUMBER(F30),ISNUMBER(E30),E30&gt;0,F30=E30),"Draw",IF(AND(ISNUMBER(F30),ISNUMBER(E30),E30&gt;0,F30=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L30" s="50"/>
       <x:c r="M30" s="58"/>
       <x:c r="N30" s="58"/>
@@ -2397,8 +2501,12 @@
       <x:c r="G31" s="58"/>
       <x:c r="H31" s="58"/>
       <x:c r="I31" s="58"/>
-      <x:c r="J31" s="60"/>
-      <x:c r="K31" s="50"/>
+      <x:c r="J31" s="60" t="str">
+        <x:f>IF(A31="","",IF(K31="Subscription","",IF(E31=0,"",IF(ISNUMBER(G31),G31/E31,IF(ISNUMBER(I31),-ABS(I31)/E31,IF(ISNUMBER(H31),0,IF(AND(ISNUMBER(F31),ISNUMBER(E31),E31&gt;0,F31&gt;E31),(F31-E31)/E31,IF(AND(ISNUMBER(F31),ISNUMBER(E31),E31&gt;0,F31=E31),0,IF(AND(ISNUMBER(F31),ISNUMBER(E31),E31&gt;0,F31=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K31" s="50" t="str">
+        <x:f>IF(A31="","",IF(AND(ISNUMBER(E31),E31=0,OR(ISNUMBER(SEARCH("Free",D31&amp;"")),AND(ISNUMBER(F31),F31=0))),"Subscription",IF(ISNUMBER(G31),"Profit",IF(ISNUMBER(I31),"Loss",IF(ISNUMBER(H31),"Draw",IF(AND(ISNUMBER(F31),ISNUMBER(E31),E31&gt;0,F31&gt;E31),"Profit",IF(AND(ISNUMBER(F31),ISNUMBER(E31),E31&gt;0,F31=E31),"Draw",IF(AND(ISNUMBER(F31),ISNUMBER(E31),E31&gt;0,F31=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L31" s="50"/>
       <x:c r="M31" s="58"/>
       <x:c r="N31" s="58"/>
@@ -2430,8 +2538,12 @@
       <x:c r="G32" s="58"/>
       <x:c r="H32" s="58"/>
       <x:c r="I32" s="58"/>
-      <x:c r="J32" s="60"/>
-      <x:c r="K32" s="50"/>
+      <x:c r="J32" s="60" t="str">
+        <x:f>IF(A32="","",IF(K32="Subscription","",IF(E32=0,"",IF(ISNUMBER(G32),G32/E32,IF(ISNUMBER(I32),-ABS(I32)/E32,IF(ISNUMBER(H32),0,IF(AND(ISNUMBER(F32),ISNUMBER(E32),E32&gt;0,F32&gt;E32),(F32-E32)/E32,IF(AND(ISNUMBER(F32),ISNUMBER(E32),E32&gt;0,F32=E32),0,IF(AND(ISNUMBER(F32),ISNUMBER(E32),E32&gt;0,F32=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K32" s="50" t="str">
+        <x:f>IF(A32="","",IF(AND(ISNUMBER(E32),E32=0,OR(ISNUMBER(SEARCH("Free",D32&amp;"")),AND(ISNUMBER(F32),F32=0))),"Subscription",IF(ISNUMBER(G32),"Profit",IF(ISNUMBER(I32),"Loss",IF(ISNUMBER(H32),"Draw",IF(AND(ISNUMBER(F32),ISNUMBER(E32),E32&gt;0,F32&gt;E32),"Profit",IF(AND(ISNUMBER(F32),ISNUMBER(E32),E32&gt;0,F32=E32),"Draw",IF(AND(ISNUMBER(F32),ISNUMBER(E32),E32&gt;0,F32=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L32" s="50"/>
       <x:c r="M32" s="58"/>
       <x:c r="N32" s="58"/>
@@ -2463,8 +2575,12 @@
       <x:c r="G33" s="58"/>
       <x:c r="H33" s="58"/>
       <x:c r="I33" s="58"/>
-      <x:c r="J33" s="60"/>
-      <x:c r="K33" s="50"/>
+      <x:c r="J33" s="60" t="str">
+        <x:f>IF(A33="","",IF(K33="Subscription","",IF(E33=0,"",IF(ISNUMBER(G33),G33/E33,IF(ISNUMBER(I33),-ABS(I33)/E33,IF(ISNUMBER(H33),0,IF(AND(ISNUMBER(F33),ISNUMBER(E33),E33&gt;0,F33&gt;E33),(F33-E33)/E33,IF(AND(ISNUMBER(F33),ISNUMBER(E33),E33&gt;0,F33=E33),0,IF(AND(ISNUMBER(F33),ISNUMBER(E33),E33&gt;0,F33=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K33" s="50" t="str">
+        <x:f>IF(A33="","",IF(AND(ISNUMBER(E33),E33=0,OR(ISNUMBER(SEARCH("Free",D33&amp;"")),AND(ISNUMBER(F33),F33=0))),"Subscription",IF(ISNUMBER(G33),"Profit",IF(ISNUMBER(I33),"Loss",IF(ISNUMBER(H33),"Draw",IF(AND(ISNUMBER(F33),ISNUMBER(E33),E33&gt;0,F33&gt;E33),"Profit",IF(AND(ISNUMBER(F33),ISNUMBER(E33),E33&gt;0,F33=E33),"Draw",IF(AND(ISNUMBER(F33),ISNUMBER(E33),E33&gt;0,F33=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L33" s="50"/>
       <x:c r="M33" s="58"/>
       <x:c r="N33" s="58"/>
@@ -2496,8 +2612,12 @@
       <x:c r="G34" s="58"/>
       <x:c r="H34" s="58"/>
       <x:c r="I34" s="58"/>
-      <x:c r="J34" s="60"/>
-      <x:c r="K34" s="50"/>
+      <x:c r="J34" s="60" t="str">
+        <x:f>IF(A34="","",IF(K34="Subscription","",IF(E34=0,"",IF(ISNUMBER(G34),G34/E34,IF(ISNUMBER(I34),-ABS(I34)/E34,IF(ISNUMBER(H34),0,IF(AND(ISNUMBER(F34),ISNUMBER(E34),E34&gt;0,F34&gt;E34),(F34-E34)/E34,IF(AND(ISNUMBER(F34),ISNUMBER(E34),E34&gt;0,F34=E34),0,IF(AND(ISNUMBER(F34),ISNUMBER(E34),E34&gt;0,F34=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K34" s="50" t="str">
+        <x:f>IF(A34="","",IF(AND(ISNUMBER(E34),E34=0,OR(ISNUMBER(SEARCH("Free",D34&amp;"")),AND(ISNUMBER(F34),F34=0))),"Subscription",IF(ISNUMBER(G34),"Profit",IF(ISNUMBER(I34),"Loss",IF(ISNUMBER(H34),"Draw",IF(AND(ISNUMBER(F34),ISNUMBER(E34),E34&gt;0,F34&gt;E34),"Profit",IF(AND(ISNUMBER(F34),ISNUMBER(E34),E34&gt;0,F34=E34),"Draw",IF(AND(ISNUMBER(F34),ISNUMBER(E34),E34&gt;0,F34=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L34" s="50"/>
       <x:c r="M34" s="58"/>
       <x:c r="N34" s="58"/>
@@ -2529,8 +2649,12 @@
       <x:c r="G35" s="58"/>
       <x:c r="H35" s="58"/>
       <x:c r="I35" s="58"/>
-      <x:c r="J35" s="60"/>
-      <x:c r="K35" s="50"/>
+      <x:c r="J35" s="60" t="str">
+        <x:f>IF(A35="","",IF(K35="Subscription","",IF(E35=0,"",IF(ISNUMBER(G35),G35/E35,IF(ISNUMBER(I35),-ABS(I35)/E35,IF(ISNUMBER(H35),0,IF(AND(ISNUMBER(F35),ISNUMBER(E35),E35&gt;0,F35&gt;E35),(F35-E35)/E35,IF(AND(ISNUMBER(F35),ISNUMBER(E35),E35&gt;0,F35=E35),0,IF(AND(ISNUMBER(F35),ISNUMBER(E35),E35&gt;0,F35=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K35" s="50" t="str">
+        <x:f>IF(A35="","",IF(AND(ISNUMBER(E35),E35=0,OR(ISNUMBER(SEARCH("Free",D35&amp;"")),AND(ISNUMBER(F35),F35=0))),"Subscription",IF(ISNUMBER(G35),"Profit",IF(ISNUMBER(I35),"Loss",IF(ISNUMBER(H35),"Draw",IF(AND(ISNUMBER(F35),ISNUMBER(E35),E35&gt;0,F35&gt;E35),"Profit",IF(AND(ISNUMBER(F35),ISNUMBER(E35),E35&gt;0,F35=E35),"Draw",IF(AND(ISNUMBER(F35),ISNUMBER(E35),E35&gt;0,F35=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L35" s="50"/>
       <x:c r="M35" s="58"/>
       <x:c r="N35" s="58"/>
@@ -2562,8 +2686,12 @@
       <x:c r="G36" s="58"/>
       <x:c r="H36" s="58"/>
       <x:c r="I36" s="58"/>
-      <x:c r="J36" s="60"/>
-      <x:c r="K36" s="50"/>
+      <x:c r="J36" s="60" t="str">
+        <x:f>IF(A36="","",IF(K36="Subscription","",IF(E36=0,"",IF(ISNUMBER(G36),G36/E36,IF(ISNUMBER(I36),-ABS(I36)/E36,IF(ISNUMBER(H36),0,IF(AND(ISNUMBER(F36),ISNUMBER(E36),E36&gt;0,F36&gt;E36),(F36-E36)/E36,IF(AND(ISNUMBER(F36),ISNUMBER(E36),E36&gt;0,F36=E36),0,IF(AND(ISNUMBER(F36),ISNUMBER(E36),E36&gt;0,F36=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K36" s="50" t="str">
+        <x:f>IF(A36="","",IF(AND(ISNUMBER(E36),E36=0,OR(ISNUMBER(SEARCH("Free",D36&amp;"")),AND(ISNUMBER(F36),F36=0))),"Subscription",IF(ISNUMBER(G36),"Profit",IF(ISNUMBER(I36),"Loss",IF(ISNUMBER(H36),"Draw",IF(AND(ISNUMBER(F36),ISNUMBER(E36),E36&gt;0,F36&gt;E36),"Profit",IF(AND(ISNUMBER(F36),ISNUMBER(E36),E36&gt;0,F36=E36),"Draw",IF(AND(ISNUMBER(F36),ISNUMBER(E36),E36&gt;0,F36=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L36" s="50"/>
       <x:c r="M36" s="58"/>
       <x:c r="N36" s="58"/>
@@ -2595,8 +2723,12 @@
       <x:c r="G37" s="58"/>
       <x:c r="H37" s="58"/>
       <x:c r="I37" s="58"/>
-      <x:c r="J37" s="60"/>
-      <x:c r="K37" s="50"/>
+      <x:c r="J37" s="60" t="str">
+        <x:f>IF(A37="","",IF(K37="Subscription","",IF(E37=0,"",IF(ISNUMBER(G37),G37/E37,IF(ISNUMBER(I37),-ABS(I37)/E37,IF(ISNUMBER(H37),0,IF(AND(ISNUMBER(F37),ISNUMBER(E37),E37&gt;0,F37&gt;E37),(F37-E37)/E37,IF(AND(ISNUMBER(F37),ISNUMBER(E37),E37&gt;0,F37=E37),0,IF(AND(ISNUMBER(F37),ISNUMBER(E37),E37&gt;0,F37=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K37" s="50" t="str">
+        <x:f>IF(A37="","",IF(AND(ISNUMBER(E37),E37=0,OR(ISNUMBER(SEARCH("Free",D37&amp;"")),AND(ISNUMBER(F37),F37=0))),"Subscription",IF(ISNUMBER(G37),"Profit",IF(ISNUMBER(I37),"Loss",IF(ISNUMBER(H37),"Draw",IF(AND(ISNUMBER(F37),ISNUMBER(E37),E37&gt;0,F37&gt;E37),"Profit",IF(AND(ISNUMBER(F37),ISNUMBER(E37),E37&gt;0,F37=E37),"Draw",IF(AND(ISNUMBER(F37),ISNUMBER(E37),E37&gt;0,F37=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L37" s="50"/>
       <x:c r="M37" s="58"/>
       <x:c r="N37" s="58"/>
@@ -2628,8 +2760,12 @@
       <x:c r="G38" s="58"/>
       <x:c r="H38" s="58"/>
       <x:c r="I38" s="58"/>
-      <x:c r="J38" s="60"/>
-      <x:c r="K38" s="50"/>
+      <x:c r="J38" s="60" t="str">
+        <x:f>IF(A38="","",IF(K38="Subscription","",IF(E38=0,"",IF(ISNUMBER(G38),G38/E38,IF(ISNUMBER(I38),-ABS(I38)/E38,IF(ISNUMBER(H38),0,IF(AND(ISNUMBER(F38),ISNUMBER(E38),E38&gt;0,F38&gt;E38),(F38-E38)/E38,IF(AND(ISNUMBER(F38),ISNUMBER(E38),E38&gt;0,F38=E38),0,IF(AND(ISNUMBER(F38),ISNUMBER(E38),E38&gt;0,F38=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K38" s="50" t="str">
+        <x:f>IF(A38="","",IF(AND(ISNUMBER(E38),E38=0,OR(ISNUMBER(SEARCH("Free",D38&amp;"")),AND(ISNUMBER(F38),F38=0))),"Subscription",IF(ISNUMBER(G38),"Profit",IF(ISNUMBER(I38),"Loss",IF(ISNUMBER(H38),"Draw",IF(AND(ISNUMBER(F38),ISNUMBER(E38),E38&gt;0,F38&gt;E38),"Profit",IF(AND(ISNUMBER(F38),ISNUMBER(E38),E38&gt;0,F38=E38),"Draw",IF(AND(ISNUMBER(F38),ISNUMBER(E38),E38&gt;0,F38=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L38" s="50"/>
       <x:c r="M38" s="58"/>
       <x:c r="N38" s="58"/>
@@ -2661,8 +2797,12 @@
       <x:c r="G39" s="58"/>
       <x:c r="H39" s="58"/>
       <x:c r="I39" s="58"/>
-      <x:c r="J39" s="60"/>
-      <x:c r="K39" s="50"/>
+      <x:c r="J39" s="60" t="str">
+        <x:f>IF(A39="","",IF(K39="Subscription","",IF(E39=0,"",IF(ISNUMBER(G39),G39/E39,IF(ISNUMBER(I39),-ABS(I39)/E39,IF(ISNUMBER(H39),0,IF(AND(ISNUMBER(F39),ISNUMBER(E39),E39&gt;0,F39&gt;E39),(F39-E39)/E39,IF(AND(ISNUMBER(F39),ISNUMBER(E39),E39&gt;0,F39=E39),0,IF(AND(ISNUMBER(F39),ISNUMBER(E39),E39&gt;0,F39=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K39" s="50" t="str">
+        <x:f>IF(A39="","",IF(AND(ISNUMBER(E39),E39=0,OR(ISNUMBER(SEARCH("Free",D39&amp;"")),AND(ISNUMBER(F39),F39=0))),"Subscription",IF(ISNUMBER(G39),"Profit",IF(ISNUMBER(I39),"Loss",IF(ISNUMBER(H39),"Draw",IF(AND(ISNUMBER(F39),ISNUMBER(E39),E39&gt;0,F39&gt;E39),"Profit",IF(AND(ISNUMBER(F39),ISNUMBER(E39),E39&gt;0,F39=E39),"Draw",IF(AND(ISNUMBER(F39),ISNUMBER(E39),E39&gt;0,F39=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L39" s="50"/>
       <x:c r="M39" s="58"/>
       <x:c r="N39" s="58"/>
@@ -2694,8 +2834,12 @@
       <x:c r="G40" s="58"/>
       <x:c r="H40" s="58"/>
       <x:c r="I40" s="58"/>
-      <x:c r="J40" s="60"/>
-      <x:c r="K40" s="50"/>
+      <x:c r="J40" s="60" t="str">
+        <x:f>IF(A40="","",IF(K40="Subscription","",IF(E40=0,"",IF(ISNUMBER(G40),G40/E40,IF(ISNUMBER(I40),-ABS(I40)/E40,IF(ISNUMBER(H40),0,IF(AND(ISNUMBER(F40),ISNUMBER(E40),E40&gt;0,F40&gt;E40),(F40-E40)/E40,IF(AND(ISNUMBER(F40),ISNUMBER(E40),E40&gt;0,F40=E40),0,IF(AND(ISNUMBER(F40),ISNUMBER(E40),E40&gt;0,F40=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K40" s="50" t="str">
+        <x:f>IF(A40="","",IF(AND(ISNUMBER(E40),E40=0,OR(ISNUMBER(SEARCH("Free",D40&amp;"")),AND(ISNUMBER(F40),F40=0))),"Subscription",IF(ISNUMBER(G40),"Profit",IF(ISNUMBER(I40),"Loss",IF(ISNUMBER(H40),"Draw",IF(AND(ISNUMBER(F40),ISNUMBER(E40),E40&gt;0,F40&gt;E40),"Profit",IF(AND(ISNUMBER(F40),ISNUMBER(E40),E40&gt;0,F40=E40),"Draw",IF(AND(ISNUMBER(F40),ISNUMBER(E40),E40&gt;0,F40=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L40" s="50"/>
       <x:c r="M40" s="58"/>
       <x:c r="N40" s="58"/>
@@ -2727,8 +2871,12 @@
       <x:c r="G41" s="58"/>
       <x:c r="H41" s="58"/>
       <x:c r="I41" s="58"/>
-      <x:c r="J41" s="60"/>
-      <x:c r="K41" s="50"/>
+      <x:c r="J41" s="60" t="str">
+        <x:f>IF(A41="","",IF(K41="Subscription","",IF(E41=0,"",IF(ISNUMBER(G41),G41/E41,IF(ISNUMBER(I41),-ABS(I41)/E41,IF(ISNUMBER(H41),0,IF(AND(ISNUMBER(F41),ISNUMBER(E41),E41&gt;0,F41&gt;E41),(F41-E41)/E41,IF(AND(ISNUMBER(F41),ISNUMBER(E41),E41&gt;0,F41=E41),0,IF(AND(ISNUMBER(F41),ISNUMBER(E41),E41&gt;0,F41=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K41" s="50" t="str">
+        <x:f>IF(A41="","",IF(AND(ISNUMBER(E41),E41=0,OR(ISNUMBER(SEARCH("Free",D41&amp;"")),AND(ISNUMBER(F41),F41=0))),"Subscription",IF(ISNUMBER(G41),"Profit",IF(ISNUMBER(I41),"Loss",IF(ISNUMBER(H41),"Draw",IF(AND(ISNUMBER(F41),ISNUMBER(E41),E41&gt;0,F41&gt;E41),"Profit",IF(AND(ISNUMBER(F41),ISNUMBER(E41),E41&gt;0,F41=E41),"Draw",IF(AND(ISNUMBER(F41),ISNUMBER(E41),E41&gt;0,F41=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L41" s="50"/>
       <x:c r="M41" s="58"/>
       <x:c r="N41" s="58"/>
@@ -2760,8 +2908,12 @@
       <x:c r="G42" s="58"/>
       <x:c r="H42" s="58"/>
       <x:c r="I42" s="58"/>
-      <x:c r="J42" s="60"/>
-      <x:c r="K42" s="50"/>
+      <x:c r="J42" s="60" t="str">
+        <x:f>IF(A42="","",IF(K42="Subscription","",IF(E42=0,"",IF(ISNUMBER(G42),G42/E42,IF(ISNUMBER(I42),-ABS(I42)/E42,IF(ISNUMBER(H42),0,IF(AND(ISNUMBER(F42),ISNUMBER(E42),E42&gt;0,F42&gt;E42),(F42-E42)/E42,IF(AND(ISNUMBER(F42),ISNUMBER(E42),E42&gt;0,F42=E42),0,IF(AND(ISNUMBER(F42),ISNUMBER(E42),E42&gt;0,F42=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K42" s="50" t="str">
+        <x:f>IF(A42="","",IF(AND(ISNUMBER(E42),E42=0,OR(ISNUMBER(SEARCH("Free",D42&amp;"")),AND(ISNUMBER(F42),F42=0))),"Subscription",IF(ISNUMBER(G42),"Profit",IF(ISNUMBER(I42),"Loss",IF(ISNUMBER(H42),"Draw",IF(AND(ISNUMBER(F42),ISNUMBER(E42),E42&gt;0,F42&gt;E42),"Profit",IF(AND(ISNUMBER(F42),ISNUMBER(E42),E42&gt;0,F42=E42),"Draw",IF(AND(ISNUMBER(F42),ISNUMBER(E42),E42&gt;0,F42=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L42" s="50"/>
       <x:c r="M42" s="58"/>
       <x:c r="N42" s="58"/>
@@ -2793,8 +2945,12 @@
       <x:c r="G43" s="58"/>
       <x:c r="H43" s="58"/>
       <x:c r="I43" s="58"/>
-      <x:c r="J43" s="60"/>
-      <x:c r="K43" s="50"/>
+      <x:c r="J43" s="60" t="str">
+        <x:f>IF(A43="","",IF(K43="Subscription","",IF(E43=0,"",IF(ISNUMBER(G43),G43/E43,IF(ISNUMBER(I43),-ABS(I43)/E43,IF(ISNUMBER(H43),0,IF(AND(ISNUMBER(F43),ISNUMBER(E43),E43&gt;0,F43&gt;E43),(F43-E43)/E43,IF(AND(ISNUMBER(F43),ISNUMBER(E43),E43&gt;0,F43=E43),0,IF(AND(ISNUMBER(F43),ISNUMBER(E43),E43&gt;0,F43=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K43" s="50" t="str">
+        <x:f>IF(A43="","",IF(AND(ISNUMBER(E43),E43=0,OR(ISNUMBER(SEARCH("Free",D43&amp;"")),AND(ISNUMBER(F43),F43=0))),"Subscription",IF(ISNUMBER(G43),"Profit",IF(ISNUMBER(I43),"Loss",IF(ISNUMBER(H43),"Draw",IF(AND(ISNUMBER(F43),ISNUMBER(E43),E43&gt;0,F43&gt;E43),"Profit",IF(AND(ISNUMBER(F43),ISNUMBER(E43),E43&gt;0,F43=E43),"Draw",IF(AND(ISNUMBER(F43),ISNUMBER(E43),E43&gt;0,F43=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L43" s="50"/>
       <x:c r="M43" s="58"/>
       <x:c r="N43" s="58"/>
@@ -2826,8 +2982,12 @@
       <x:c r="G44" s="58"/>
       <x:c r="H44" s="58"/>
       <x:c r="I44" s="58"/>
-      <x:c r="J44" s="60"/>
-      <x:c r="K44" s="50"/>
+      <x:c r="J44" s="60" t="str">
+        <x:f>IF(A44="","",IF(K44="Subscription","",IF(E44=0,"",IF(ISNUMBER(G44),G44/E44,IF(ISNUMBER(I44),-ABS(I44)/E44,IF(ISNUMBER(H44),0,IF(AND(ISNUMBER(F44),ISNUMBER(E44),E44&gt;0,F44&gt;E44),(F44-E44)/E44,IF(AND(ISNUMBER(F44),ISNUMBER(E44),E44&gt;0,F44=E44),0,IF(AND(ISNUMBER(F44),ISNUMBER(E44),E44&gt;0,F44=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K44" s="50" t="str">
+        <x:f>IF(A44="","",IF(AND(ISNUMBER(E44),E44=0,OR(ISNUMBER(SEARCH("Free",D44&amp;"")),AND(ISNUMBER(F44),F44=0))),"Subscription",IF(ISNUMBER(G44),"Profit",IF(ISNUMBER(I44),"Loss",IF(ISNUMBER(H44),"Draw",IF(AND(ISNUMBER(F44),ISNUMBER(E44),E44&gt;0,F44&gt;E44),"Profit",IF(AND(ISNUMBER(F44),ISNUMBER(E44),E44&gt;0,F44=E44),"Draw",IF(AND(ISNUMBER(F44),ISNUMBER(E44),E44&gt;0,F44=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L44" s="50"/>
       <x:c r="M44" s="58"/>
       <x:c r="N44" s="58"/>
@@ -2859,8 +3019,12 @@
       <x:c r="G45" s="58"/>
       <x:c r="H45" s="58"/>
       <x:c r="I45" s="58"/>
-      <x:c r="J45" s="60"/>
-      <x:c r="K45" s="50"/>
+      <x:c r="J45" s="60" t="str">
+        <x:f>IF(A45="","",IF(K45="Subscription","",IF(E45=0,"",IF(ISNUMBER(G45),G45/E45,IF(ISNUMBER(I45),-ABS(I45)/E45,IF(ISNUMBER(H45),0,IF(AND(ISNUMBER(F45),ISNUMBER(E45),E45&gt;0,F45&gt;E45),(F45-E45)/E45,IF(AND(ISNUMBER(F45),ISNUMBER(E45),E45&gt;0,F45=E45),0,IF(AND(ISNUMBER(F45),ISNUMBER(E45),E45&gt;0,F45=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K45" s="50" t="str">
+        <x:f>IF(A45="","",IF(AND(ISNUMBER(E45),E45=0,OR(ISNUMBER(SEARCH("Free",D45&amp;"")),AND(ISNUMBER(F45),F45=0))),"Subscription",IF(ISNUMBER(G45),"Profit",IF(ISNUMBER(I45),"Loss",IF(ISNUMBER(H45),"Draw",IF(AND(ISNUMBER(F45),ISNUMBER(E45),E45&gt;0,F45&gt;E45),"Profit",IF(AND(ISNUMBER(F45),ISNUMBER(E45),E45&gt;0,F45=E45),"Draw",IF(AND(ISNUMBER(F45),ISNUMBER(E45),E45&gt;0,F45=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L45" s="50"/>
       <x:c r="M45" s="58"/>
       <x:c r="N45" s="58"/>
@@ -2892,8 +3056,12 @@
       <x:c r="G46" s="58"/>
       <x:c r="H46" s="58"/>
       <x:c r="I46" s="58"/>
-      <x:c r="J46" s="60"/>
-      <x:c r="K46" s="50"/>
+      <x:c r="J46" s="60" t="str">
+        <x:f>IF(A46="","",IF(K46="Subscription","",IF(E46=0,"",IF(ISNUMBER(G46),G46/E46,IF(ISNUMBER(I46),-ABS(I46)/E46,IF(ISNUMBER(H46),0,IF(AND(ISNUMBER(F46),ISNUMBER(E46),E46&gt;0,F46&gt;E46),(F46-E46)/E46,IF(AND(ISNUMBER(F46),ISNUMBER(E46),E46&gt;0,F46=E46),0,IF(AND(ISNUMBER(F46),ISNUMBER(E46),E46&gt;0,F46=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K46" s="50" t="str">
+        <x:f>IF(A46="","",IF(AND(ISNUMBER(E46),E46=0,OR(ISNUMBER(SEARCH("Free",D46&amp;"")),AND(ISNUMBER(F46),F46=0))),"Subscription",IF(ISNUMBER(G46),"Profit",IF(ISNUMBER(I46),"Loss",IF(ISNUMBER(H46),"Draw",IF(AND(ISNUMBER(F46),ISNUMBER(E46),E46&gt;0,F46&gt;E46),"Profit",IF(AND(ISNUMBER(F46),ISNUMBER(E46),E46&gt;0,F46=E46),"Draw",IF(AND(ISNUMBER(F46),ISNUMBER(E46),E46&gt;0,F46=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L46" s="50"/>
       <x:c r="M46" s="58"/>
       <x:c r="N46" s="58"/>
@@ -2925,8 +3093,12 @@
       <x:c r="G47" s="58"/>
       <x:c r="H47" s="58"/>
       <x:c r="I47" s="58"/>
-      <x:c r="J47" s="60"/>
-      <x:c r="K47" s="50"/>
+      <x:c r="J47" s="60" t="str">
+        <x:f>IF(A47="","",IF(K47="Subscription","",IF(E47=0,"",IF(ISNUMBER(G47),G47/E47,IF(ISNUMBER(I47),-ABS(I47)/E47,IF(ISNUMBER(H47),0,IF(AND(ISNUMBER(F47),ISNUMBER(E47),E47&gt;0,F47&gt;E47),(F47-E47)/E47,IF(AND(ISNUMBER(F47),ISNUMBER(E47),E47&gt;0,F47=E47),0,IF(AND(ISNUMBER(F47),ISNUMBER(E47),E47&gt;0,F47=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K47" s="50" t="str">
+        <x:f>IF(A47="","",IF(AND(ISNUMBER(E47),E47=0,OR(ISNUMBER(SEARCH("Free",D47&amp;"")),AND(ISNUMBER(F47),F47=0))),"Subscription",IF(ISNUMBER(G47),"Profit",IF(ISNUMBER(I47),"Loss",IF(ISNUMBER(H47),"Draw",IF(AND(ISNUMBER(F47),ISNUMBER(E47),E47&gt;0,F47&gt;E47),"Profit",IF(AND(ISNUMBER(F47),ISNUMBER(E47),E47&gt;0,F47=E47),"Draw",IF(AND(ISNUMBER(F47),ISNUMBER(E47),E47&gt;0,F47=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L47" s="50"/>
       <x:c r="M47" s="58"/>
       <x:c r="N47" s="58"/>
@@ -2958,8 +3130,12 @@
       <x:c r="G48" s="58"/>
       <x:c r="H48" s="58"/>
       <x:c r="I48" s="58"/>
-      <x:c r="J48" s="60"/>
-      <x:c r="K48" s="50"/>
+      <x:c r="J48" s="60" t="str">
+        <x:f>IF(A48="","",IF(K48="Subscription","",IF(E48=0,"",IF(ISNUMBER(G48),G48/E48,IF(ISNUMBER(I48),-ABS(I48)/E48,IF(ISNUMBER(H48),0,IF(AND(ISNUMBER(F48),ISNUMBER(E48),E48&gt;0,F48&gt;E48),(F48-E48)/E48,IF(AND(ISNUMBER(F48),ISNUMBER(E48),E48&gt;0,F48=E48),0,IF(AND(ISNUMBER(F48),ISNUMBER(E48),E48&gt;0,F48=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K48" s="50" t="str">
+        <x:f>IF(A48="","",IF(AND(ISNUMBER(E48),E48=0,OR(ISNUMBER(SEARCH("Free",D48&amp;"")),AND(ISNUMBER(F48),F48=0))),"Subscription",IF(ISNUMBER(G48),"Profit",IF(ISNUMBER(I48),"Loss",IF(ISNUMBER(H48),"Draw",IF(AND(ISNUMBER(F48),ISNUMBER(E48),E48&gt;0,F48&gt;E48),"Profit",IF(AND(ISNUMBER(F48),ISNUMBER(E48),E48&gt;0,F48=E48),"Draw",IF(AND(ISNUMBER(F48),ISNUMBER(E48),E48&gt;0,F48=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L48" s="50"/>
       <x:c r="M48" s="58"/>
       <x:c r="N48" s="58"/>
@@ -2991,8 +3167,12 @@
       <x:c r="G49" s="58"/>
       <x:c r="H49" s="58"/>
       <x:c r="I49" s="58"/>
-      <x:c r="J49" s="60"/>
-      <x:c r="K49" s="50"/>
+      <x:c r="J49" s="60" t="str">
+        <x:f>IF(A49="","",IF(K49="Subscription","",IF(E49=0,"",IF(ISNUMBER(G49),G49/E49,IF(ISNUMBER(I49),-ABS(I49)/E49,IF(ISNUMBER(H49),0,IF(AND(ISNUMBER(F49),ISNUMBER(E49),E49&gt;0,F49&gt;E49),(F49-E49)/E49,IF(AND(ISNUMBER(F49),ISNUMBER(E49),E49&gt;0,F49=E49),0,IF(AND(ISNUMBER(F49),ISNUMBER(E49),E49&gt;0,F49=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K49" s="50" t="str">
+        <x:f>IF(A49="","",IF(AND(ISNUMBER(E49),E49=0,OR(ISNUMBER(SEARCH("Free",D49&amp;"")),AND(ISNUMBER(F49),F49=0))),"Subscription",IF(ISNUMBER(G49),"Profit",IF(ISNUMBER(I49),"Loss",IF(ISNUMBER(H49),"Draw",IF(AND(ISNUMBER(F49),ISNUMBER(E49),E49&gt;0,F49&gt;E49),"Profit",IF(AND(ISNUMBER(F49),ISNUMBER(E49),E49&gt;0,F49=E49),"Draw",IF(AND(ISNUMBER(F49),ISNUMBER(E49),E49&gt;0,F49=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L49" s="50"/>
       <x:c r="M49" s="58"/>
       <x:c r="N49" s="58"/>
@@ -3024,8 +3204,12 @@
       <x:c r="G50" s="58"/>
       <x:c r="H50" s="58"/>
       <x:c r="I50" s="58"/>
-      <x:c r="J50" s="60"/>
-      <x:c r="K50" s="50"/>
+      <x:c r="J50" s="60" t="str">
+        <x:f>IF(A50="","",IF(K50="Subscription","",IF(E50=0,"",IF(ISNUMBER(G50),G50/E50,IF(ISNUMBER(I50),-ABS(I50)/E50,IF(ISNUMBER(H50),0,IF(AND(ISNUMBER(F50),ISNUMBER(E50),E50&gt;0,F50&gt;E50),(F50-E50)/E50,IF(AND(ISNUMBER(F50),ISNUMBER(E50),E50&gt;0,F50=E50),0,IF(AND(ISNUMBER(F50),ISNUMBER(E50),E50&gt;0,F50=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K50" s="50" t="str">
+        <x:f>IF(A50="","",IF(AND(ISNUMBER(E50),E50=0,OR(ISNUMBER(SEARCH("Free",D50&amp;"")),AND(ISNUMBER(F50),F50=0))),"Subscription",IF(ISNUMBER(G50),"Profit",IF(ISNUMBER(I50),"Loss",IF(ISNUMBER(H50),"Draw",IF(AND(ISNUMBER(F50),ISNUMBER(E50),E50&gt;0,F50&gt;E50),"Profit",IF(AND(ISNUMBER(F50),ISNUMBER(E50),E50&gt;0,F50=E50),"Draw",IF(AND(ISNUMBER(F50),ISNUMBER(E50),E50&gt;0,F50=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L50" s="50"/>
       <x:c r="M50" s="58"/>
       <x:c r="N50" s="58"/>
@@ -3057,8 +3241,12 @@
       <x:c r="G51" s="58"/>
       <x:c r="H51" s="58"/>
       <x:c r="I51" s="58"/>
-      <x:c r="J51" s="60"/>
-      <x:c r="K51" s="50"/>
+      <x:c r="J51" s="60" t="str">
+        <x:f>IF(A51="","",IF(K51="Subscription","",IF(E51=0,"",IF(ISNUMBER(G51),G51/E51,IF(ISNUMBER(I51),-ABS(I51)/E51,IF(ISNUMBER(H51),0,IF(AND(ISNUMBER(F51),ISNUMBER(E51),E51&gt;0,F51&gt;E51),(F51-E51)/E51,IF(AND(ISNUMBER(F51),ISNUMBER(E51),E51&gt;0,F51=E51),0,IF(AND(ISNUMBER(F51),ISNUMBER(E51),E51&gt;0,F51=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K51" s="50" t="str">
+        <x:f>IF(A51="","",IF(AND(ISNUMBER(E51),E51=0,OR(ISNUMBER(SEARCH("Free",D51&amp;"")),AND(ISNUMBER(F51),F51=0))),"Subscription",IF(ISNUMBER(G51),"Profit",IF(ISNUMBER(I51),"Loss",IF(ISNUMBER(H51),"Draw",IF(AND(ISNUMBER(F51),ISNUMBER(E51),E51&gt;0,F51&gt;E51),"Profit",IF(AND(ISNUMBER(F51),ISNUMBER(E51),E51&gt;0,F51=E51),"Draw",IF(AND(ISNUMBER(F51),ISNUMBER(E51),E51&gt;0,F51=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L51" s="50"/>
       <x:c r="M51" s="58"/>
       <x:c r="N51" s="58"/>
@@ -3090,8 +3278,12 @@
       <x:c r="G52" s="58"/>
       <x:c r="H52" s="58"/>
       <x:c r="I52" s="58"/>
-      <x:c r="J52" s="60"/>
-      <x:c r="K52" s="50"/>
+      <x:c r="J52" s="60" t="str">
+        <x:f>IF(A52="","",IF(K52="Subscription","",IF(E52=0,"",IF(ISNUMBER(G52),G52/E52,IF(ISNUMBER(I52),-ABS(I52)/E52,IF(ISNUMBER(H52),0,IF(AND(ISNUMBER(F52),ISNUMBER(E52),E52&gt;0,F52&gt;E52),(F52-E52)/E52,IF(AND(ISNUMBER(F52),ISNUMBER(E52),E52&gt;0,F52=E52),0,IF(AND(ISNUMBER(F52),ISNUMBER(E52),E52&gt;0,F52=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K52" s="50" t="str">
+        <x:f>IF(A52="","",IF(AND(ISNUMBER(E52),E52=0,OR(ISNUMBER(SEARCH("Free",D52&amp;"")),AND(ISNUMBER(F52),F52=0))),"Subscription",IF(ISNUMBER(G52),"Profit",IF(ISNUMBER(I52),"Loss",IF(ISNUMBER(H52),"Draw",IF(AND(ISNUMBER(F52),ISNUMBER(E52),E52&gt;0,F52&gt;E52),"Profit",IF(AND(ISNUMBER(F52),ISNUMBER(E52),E52&gt;0,F52=E52),"Draw",IF(AND(ISNUMBER(F52),ISNUMBER(E52),E52&gt;0,F52=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L52" s="50"/>
       <x:c r="M52" s="58"/>
       <x:c r="N52" s="58"/>
@@ -3123,8 +3315,12 @@
       <x:c r="G53" s="58"/>
       <x:c r="H53" s="58"/>
       <x:c r="I53" s="58"/>
-      <x:c r="J53" s="60"/>
-      <x:c r="K53" s="50"/>
+      <x:c r="J53" s="60" t="str">
+        <x:f>IF(A53="","",IF(K53="Subscription","",IF(E53=0,"",IF(ISNUMBER(G53),G53/E53,IF(ISNUMBER(I53),-ABS(I53)/E53,IF(ISNUMBER(H53),0,IF(AND(ISNUMBER(F53),ISNUMBER(E53),E53&gt;0,F53&gt;E53),(F53-E53)/E53,IF(AND(ISNUMBER(F53),ISNUMBER(E53),E53&gt;0,F53=E53),0,IF(AND(ISNUMBER(F53),ISNUMBER(E53),E53&gt;0,F53=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K53" s="50" t="str">
+        <x:f>IF(A53="","",IF(AND(ISNUMBER(E53),E53=0,OR(ISNUMBER(SEARCH("Free",D53&amp;"")),AND(ISNUMBER(F53),F53=0))),"Subscription",IF(ISNUMBER(G53),"Profit",IF(ISNUMBER(I53),"Loss",IF(ISNUMBER(H53),"Draw",IF(AND(ISNUMBER(F53),ISNUMBER(E53),E53&gt;0,F53&gt;E53),"Profit",IF(AND(ISNUMBER(F53),ISNUMBER(E53),E53&gt;0,F53=E53),"Draw",IF(AND(ISNUMBER(F53),ISNUMBER(E53),E53&gt;0,F53=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L53" s="50"/>
       <x:c r="M53" s="58"/>
       <x:c r="N53" s="58"/>
@@ -3156,8 +3352,12 @@
       <x:c r="G54" s="58"/>
       <x:c r="H54" s="58"/>
       <x:c r="I54" s="58"/>
-      <x:c r="J54" s="60"/>
-      <x:c r="K54" s="50"/>
+      <x:c r="J54" s="60" t="str">
+        <x:f>IF(A54="","",IF(K54="Subscription","",IF(E54=0,"",IF(ISNUMBER(G54),G54/E54,IF(ISNUMBER(I54),-ABS(I54)/E54,IF(ISNUMBER(H54),0,IF(AND(ISNUMBER(F54),ISNUMBER(E54),E54&gt;0,F54&gt;E54),(F54-E54)/E54,IF(AND(ISNUMBER(F54),ISNUMBER(E54),E54&gt;0,F54=E54),0,IF(AND(ISNUMBER(F54),ISNUMBER(E54),E54&gt;0,F54=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K54" s="50" t="str">
+        <x:f>IF(A54="","",IF(AND(ISNUMBER(E54),E54=0,OR(ISNUMBER(SEARCH("Free",D54&amp;"")),AND(ISNUMBER(F54),F54=0))),"Subscription",IF(ISNUMBER(G54),"Profit",IF(ISNUMBER(I54),"Loss",IF(ISNUMBER(H54),"Draw",IF(AND(ISNUMBER(F54),ISNUMBER(E54),E54&gt;0,F54&gt;E54),"Profit",IF(AND(ISNUMBER(F54),ISNUMBER(E54),E54&gt;0,F54=E54),"Draw",IF(AND(ISNUMBER(F54),ISNUMBER(E54),E54&gt;0,F54=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L54" s="50"/>
       <x:c r="M54" s="58"/>
       <x:c r="N54" s="58"/>
@@ -3189,8 +3389,12 @@
       <x:c r="G55" s="58"/>
       <x:c r="H55" s="58"/>
       <x:c r="I55" s="58"/>
-      <x:c r="J55" s="60"/>
-      <x:c r="K55" s="50"/>
+      <x:c r="J55" s="60" t="str">
+        <x:f>IF(A55="","",IF(K55="Subscription","",IF(E55=0,"",IF(ISNUMBER(G55),G55/E55,IF(ISNUMBER(I55),-ABS(I55)/E55,IF(ISNUMBER(H55),0,IF(AND(ISNUMBER(F55),ISNUMBER(E55),E55&gt;0,F55&gt;E55),(F55-E55)/E55,IF(AND(ISNUMBER(F55),ISNUMBER(E55),E55&gt;0,F55=E55),0,IF(AND(ISNUMBER(F55),ISNUMBER(E55),E55&gt;0,F55=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K55" s="50" t="str">
+        <x:f>IF(A55="","",IF(AND(ISNUMBER(E55),E55=0,OR(ISNUMBER(SEARCH("Free",D55&amp;"")),AND(ISNUMBER(F55),F55=0))),"Subscription",IF(ISNUMBER(G55),"Profit",IF(ISNUMBER(I55),"Loss",IF(ISNUMBER(H55),"Draw",IF(AND(ISNUMBER(F55),ISNUMBER(E55),E55&gt;0,F55&gt;E55),"Profit",IF(AND(ISNUMBER(F55),ISNUMBER(E55),E55&gt;0,F55=E55),"Draw",IF(AND(ISNUMBER(F55),ISNUMBER(E55),E55&gt;0,F55=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L55" s="50"/>
       <x:c r="M55" s="58"/>
       <x:c r="N55" s="58"/>
@@ -3222,8 +3426,12 @@
       <x:c r="G56" s="58"/>
       <x:c r="H56" s="58"/>
       <x:c r="I56" s="58"/>
-      <x:c r="J56" s="60"/>
-      <x:c r="K56" s="50"/>
+      <x:c r="J56" s="60" t="str">
+        <x:f>IF(A56="","",IF(K56="Subscription","",IF(E56=0,"",IF(ISNUMBER(G56),G56/E56,IF(ISNUMBER(I56),-ABS(I56)/E56,IF(ISNUMBER(H56),0,IF(AND(ISNUMBER(F56),ISNUMBER(E56),E56&gt;0,F56&gt;E56),(F56-E56)/E56,IF(AND(ISNUMBER(F56),ISNUMBER(E56),E56&gt;0,F56=E56),0,IF(AND(ISNUMBER(F56),ISNUMBER(E56),E56&gt;0,F56=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K56" s="50" t="str">
+        <x:f>IF(A56="","",IF(AND(ISNUMBER(E56),E56=0,OR(ISNUMBER(SEARCH("Free",D56&amp;"")),AND(ISNUMBER(F56),F56=0))),"Subscription",IF(ISNUMBER(G56),"Profit",IF(ISNUMBER(I56),"Loss",IF(ISNUMBER(H56),"Draw",IF(AND(ISNUMBER(F56),ISNUMBER(E56),E56&gt;0,F56&gt;E56),"Profit",IF(AND(ISNUMBER(F56),ISNUMBER(E56),E56&gt;0,F56=E56),"Draw",IF(AND(ISNUMBER(F56),ISNUMBER(E56),E56&gt;0,F56=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L56" s="50"/>
       <x:c r="M56" s="58"/>
       <x:c r="N56" s="58"/>
@@ -3255,8 +3463,12 @@
       <x:c r="G57" s="58"/>
       <x:c r="H57" s="58"/>
       <x:c r="I57" s="58"/>
-      <x:c r="J57" s="60"/>
-      <x:c r="K57" s="50"/>
+      <x:c r="J57" s="60" t="str">
+        <x:f>IF(A57="","",IF(K57="Subscription","",IF(E57=0,"",IF(ISNUMBER(G57),G57/E57,IF(ISNUMBER(I57),-ABS(I57)/E57,IF(ISNUMBER(H57),0,IF(AND(ISNUMBER(F57),ISNUMBER(E57),E57&gt;0,F57&gt;E57),(F57-E57)/E57,IF(AND(ISNUMBER(F57),ISNUMBER(E57),E57&gt;0,F57=E57),0,IF(AND(ISNUMBER(F57),ISNUMBER(E57),E57&gt;0,F57=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K57" s="50" t="str">
+        <x:f>IF(A57="","",IF(AND(ISNUMBER(E57),E57=0,OR(ISNUMBER(SEARCH("Free",D57&amp;"")),AND(ISNUMBER(F57),F57=0))),"Subscription",IF(ISNUMBER(G57),"Profit",IF(ISNUMBER(I57),"Loss",IF(ISNUMBER(H57),"Draw",IF(AND(ISNUMBER(F57),ISNUMBER(E57),E57&gt;0,F57&gt;E57),"Profit",IF(AND(ISNUMBER(F57),ISNUMBER(E57),E57&gt;0,F57=E57),"Draw",IF(AND(ISNUMBER(F57),ISNUMBER(E57),E57&gt;0,F57=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L57" s="50"/>
       <x:c r="M57" s="58"/>
       <x:c r="N57" s="58"/>
@@ -3288,8 +3500,12 @@
       <x:c r="G58" s="58"/>
       <x:c r="H58" s="58"/>
       <x:c r="I58" s="58"/>
-      <x:c r="J58" s="60"/>
-      <x:c r="K58" s="50"/>
+      <x:c r="J58" s="60" t="str">
+        <x:f>IF(A58="","",IF(K58="Subscription","",IF(E58=0,"",IF(ISNUMBER(G58),G58/E58,IF(ISNUMBER(I58),-ABS(I58)/E58,IF(ISNUMBER(H58),0,IF(AND(ISNUMBER(F58),ISNUMBER(E58),E58&gt;0,F58&gt;E58),(F58-E58)/E58,IF(AND(ISNUMBER(F58),ISNUMBER(E58),E58&gt;0,F58=E58),0,IF(AND(ISNUMBER(F58),ISNUMBER(E58),E58&gt;0,F58=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K58" s="50" t="str">
+        <x:f>IF(A58="","",IF(AND(ISNUMBER(E58),E58=0,OR(ISNUMBER(SEARCH("Free",D58&amp;"")),AND(ISNUMBER(F58),F58=0))),"Subscription",IF(ISNUMBER(G58),"Profit",IF(ISNUMBER(I58),"Loss",IF(ISNUMBER(H58),"Draw",IF(AND(ISNUMBER(F58),ISNUMBER(E58),E58&gt;0,F58&gt;E58),"Profit",IF(AND(ISNUMBER(F58),ISNUMBER(E58),E58&gt;0,F58=E58),"Draw",IF(AND(ISNUMBER(F58),ISNUMBER(E58),E58&gt;0,F58=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L58" s="50"/>
       <x:c r="M58" s="58"/>
       <x:c r="N58" s="58"/>
@@ -3321,8 +3537,12 @@
       <x:c r="G59" s="58"/>
       <x:c r="H59" s="58"/>
       <x:c r="I59" s="58"/>
-      <x:c r="J59" s="60"/>
-      <x:c r="K59" s="50"/>
+      <x:c r="J59" s="60" t="str">
+        <x:f>IF(A59="","",IF(K59="Subscription","",IF(E59=0,"",IF(ISNUMBER(G59),G59/E59,IF(ISNUMBER(I59),-ABS(I59)/E59,IF(ISNUMBER(H59),0,IF(AND(ISNUMBER(F59),ISNUMBER(E59),E59&gt;0,F59&gt;E59),(F59-E59)/E59,IF(AND(ISNUMBER(F59),ISNUMBER(E59),E59&gt;0,F59=E59),0,IF(AND(ISNUMBER(F59),ISNUMBER(E59),E59&gt;0,F59=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K59" s="50" t="str">
+        <x:f>IF(A59="","",IF(AND(ISNUMBER(E59),E59=0,OR(ISNUMBER(SEARCH("Free",D59&amp;"")),AND(ISNUMBER(F59),F59=0))),"Subscription",IF(ISNUMBER(G59),"Profit",IF(ISNUMBER(I59),"Loss",IF(ISNUMBER(H59),"Draw",IF(AND(ISNUMBER(F59),ISNUMBER(E59),E59&gt;0,F59&gt;E59),"Profit",IF(AND(ISNUMBER(F59),ISNUMBER(E59),E59&gt;0,F59=E59),"Draw",IF(AND(ISNUMBER(F59),ISNUMBER(E59),E59&gt;0,F59=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L59" s="50"/>
       <x:c r="M59" s="58"/>
       <x:c r="N59" s="58"/>
@@ -3354,8 +3574,12 @@
       <x:c r="G60" s="58"/>
       <x:c r="H60" s="58"/>
       <x:c r="I60" s="58"/>
-      <x:c r="J60" s="60"/>
-      <x:c r="K60" s="50"/>
+      <x:c r="J60" s="60" t="str">
+        <x:f>IF(A60="","",IF(K60="Subscription","",IF(E60=0,"",IF(ISNUMBER(G60),G60/E60,IF(ISNUMBER(I60),-ABS(I60)/E60,IF(ISNUMBER(H60),0,IF(AND(ISNUMBER(F60),ISNUMBER(E60),E60&gt;0,F60&gt;E60),(F60-E60)/E60,IF(AND(ISNUMBER(F60),ISNUMBER(E60),E60&gt;0,F60=E60),0,IF(AND(ISNUMBER(F60),ISNUMBER(E60),E60&gt;0,F60=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K60" s="50" t="str">
+        <x:f>IF(A60="","",IF(AND(ISNUMBER(E60),E60=0,OR(ISNUMBER(SEARCH("Free",D60&amp;"")),AND(ISNUMBER(F60),F60=0))),"Subscription",IF(ISNUMBER(G60),"Profit",IF(ISNUMBER(I60),"Loss",IF(ISNUMBER(H60),"Draw",IF(AND(ISNUMBER(F60),ISNUMBER(E60),E60&gt;0,F60&gt;E60),"Profit",IF(AND(ISNUMBER(F60),ISNUMBER(E60),E60&gt;0,F60=E60),"Draw",IF(AND(ISNUMBER(F60),ISNUMBER(E60),E60&gt;0,F60=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L60" s="50"/>
       <x:c r="M60" s="58"/>
       <x:c r="N60" s="58"/>
@@ -3387,8 +3611,12 @@
       <x:c r="G61" s="58"/>
       <x:c r="H61" s="58"/>
       <x:c r="I61" s="58"/>
-      <x:c r="J61" s="60"/>
-      <x:c r="K61" s="50"/>
+      <x:c r="J61" s="60" t="str">
+        <x:f>IF(A61="","",IF(K61="Subscription","",IF(E61=0,"",IF(ISNUMBER(G61),G61/E61,IF(ISNUMBER(I61),-ABS(I61)/E61,IF(ISNUMBER(H61),0,IF(AND(ISNUMBER(F61),ISNUMBER(E61),E61&gt;0,F61&gt;E61),(F61-E61)/E61,IF(AND(ISNUMBER(F61),ISNUMBER(E61),E61&gt;0,F61=E61),0,IF(AND(ISNUMBER(F61),ISNUMBER(E61),E61&gt;0,F61=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K61" s="50" t="str">
+        <x:f>IF(A61="","",IF(AND(ISNUMBER(E61),E61=0,OR(ISNUMBER(SEARCH("Free",D61&amp;"")),AND(ISNUMBER(F61),F61=0))),"Subscription",IF(ISNUMBER(G61),"Profit",IF(ISNUMBER(I61),"Loss",IF(ISNUMBER(H61),"Draw",IF(AND(ISNUMBER(F61),ISNUMBER(E61),E61&gt;0,F61&gt;E61),"Profit",IF(AND(ISNUMBER(F61),ISNUMBER(E61),E61&gt;0,F61=E61),"Draw",IF(AND(ISNUMBER(F61),ISNUMBER(E61),E61&gt;0,F61=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L61" s="50"/>
       <x:c r="M61" s="58"/>
       <x:c r="N61" s="58"/>
@@ -3420,8 +3648,12 @@
       <x:c r="G62" s="58"/>
       <x:c r="H62" s="58"/>
       <x:c r="I62" s="58"/>
-      <x:c r="J62" s="60"/>
-      <x:c r="K62" s="50"/>
+      <x:c r="J62" s="60" t="str">
+        <x:f>IF(A62="","",IF(K62="Subscription","",IF(E62=0,"",IF(ISNUMBER(G62),G62/E62,IF(ISNUMBER(I62),-ABS(I62)/E62,IF(ISNUMBER(H62),0,IF(AND(ISNUMBER(F62),ISNUMBER(E62),E62&gt;0,F62&gt;E62),(F62-E62)/E62,IF(AND(ISNUMBER(F62),ISNUMBER(E62),E62&gt;0,F62=E62),0,IF(AND(ISNUMBER(F62),ISNUMBER(E62),E62&gt;0,F62=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K62" s="50" t="str">
+        <x:f>IF(A62="","",IF(AND(ISNUMBER(E62),E62=0,OR(ISNUMBER(SEARCH("Free",D62&amp;"")),AND(ISNUMBER(F62),F62=0))),"Subscription",IF(ISNUMBER(G62),"Profit",IF(ISNUMBER(I62),"Loss",IF(ISNUMBER(H62),"Draw",IF(AND(ISNUMBER(F62),ISNUMBER(E62),E62&gt;0,F62&gt;E62),"Profit",IF(AND(ISNUMBER(F62),ISNUMBER(E62),E62&gt;0,F62=E62),"Draw",IF(AND(ISNUMBER(F62),ISNUMBER(E62),E62&gt;0,F62=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L62" s="50"/>
       <x:c r="M62" s="58"/>
       <x:c r="N62" s="58"/>
@@ -3453,8 +3685,12 @@
       <x:c r="G63" s="58"/>
       <x:c r="H63" s="58"/>
       <x:c r="I63" s="58"/>
-      <x:c r="J63" s="60"/>
-      <x:c r="K63" s="50"/>
+      <x:c r="J63" s="60" t="str">
+        <x:f>IF(A63="","",IF(K63="Subscription","",IF(E63=0,"",IF(ISNUMBER(G63),G63/E63,IF(ISNUMBER(I63),-ABS(I63)/E63,IF(ISNUMBER(H63),0,IF(AND(ISNUMBER(F63),ISNUMBER(E63),E63&gt;0,F63&gt;E63),(F63-E63)/E63,IF(AND(ISNUMBER(F63),ISNUMBER(E63),E63&gt;0,F63=E63),0,IF(AND(ISNUMBER(F63),ISNUMBER(E63),E63&gt;0,F63=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K63" s="50" t="str">
+        <x:f>IF(A63="","",IF(AND(ISNUMBER(E63),E63=0,OR(ISNUMBER(SEARCH("Free",D63&amp;"")),AND(ISNUMBER(F63),F63=0))),"Subscription",IF(ISNUMBER(G63),"Profit",IF(ISNUMBER(I63),"Loss",IF(ISNUMBER(H63),"Draw",IF(AND(ISNUMBER(F63),ISNUMBER(E63),E63&gt;0,F63&gt;E63),"Profit",IF(AND(ISNUMBER(F63),ISNUMBER(E63),E63&gt;0,F63=E63),"Draw",IF(AND(ISNUMBER(F63),ISNUMBER(E63),E63&gt;0,F63=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L63" s="50"/>
       <x:c r="M63" s="58"/>
       <x:c r="N63" s="58"/>
@@ -3486,8 +3722,12 @@
       <x:c r="G64" s="58"/>
       <x:c r="H64" s="58"/>
       <x:c r="I64" s="58"/>
-      <x:c r="J64" s="60"/>
-      <x:c r="K64" s="50"/>
+      <x:c r="J64" s="60" t="str">
+        <x:f>IF(A64="","",IF(K64="Subscription","",IF(E64=0,"",IF(ISNUMBER(G64),G64/E64,IF(ISNUMBER(I64),-ABS(I64)/E64,IF(ISNUMBER(H64),0,IF(AND(ISNUMBER(F64),ISNUMBER(E64),E64&gt;0,F64&gt;E64),(F64-E64)/E64,IF(AND(ISNUMBER(F64),ISNUMBER(E64),E64&gt;0,F64=E64),0,IF(AND(ISNUMBER(F64),ISNUMBER(E64),E64&gt;0,F64=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K64" s="50" t="str">
+        <x:f>IF(A64="","",IF(AND(ISNUMBER(E64),E64=0,OR(ISNUMBER(SEARCH("Free",D64&amp;"")),AND(ISNUMBER(F64),F64=0))),"Subscription",IF(ISNUMBER(G64),"Profit",IF(ISNUMBER(I64),"Loss",IF(ISNUMBER(H64),"Draw",IF(AND(ISNUMBER(F64),ISNUMBER(E64),E64&gt;0,F64&gt;E64),"Profit",IF(AND(ISNUMBER(F64),ISNUMBER(E64),E64&gt;0,F64=E64),"Draw",IF(AND(ISNUMBER(F64),ISNUMBER(E64),E64&gt;0,F64=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L64" s="50"/>
       <x:c r="M64" s="58"/>
       <x:c r="N64" s="58"/>
@@ -3519,8 +3759,12 @@
       <x:c r="G65" s="58"/>
       <x:c r="H65" s="58"/>
       <x:c r="I65" s="58"/>
-      <x:c r="J65" s="60"/>
-      <x:c r="K65" s="50"/>
+      <x:c r="J65" s="60" t="str">
+        <x:f>IF(A65="","",IF(K65="Subscription","",IF(E65=0,"",IF(ISNUMBER(G65),G65/E65,IF(ISNUMBER(I65),-ABS(I65)/E65,IF(ISNUMBER(H65),0,IF(AND(ISNUMBER(F65),ISNUMBER(E65),E65&gt;0,F65&gt;E65),(F65-E65)/E65,IF(AND(ISNUMBER(F65),ISNUMBER(E65),E65&gt;0,F65=E65),0,IF(AND(ISNUMBER(F65),ISNUMBER(E65),E65&gt;0,F65=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K65" s="50" t="str">
+        <x:f>IF(A65="","",IF(AND(ISNUMBER(E65),E65=0,OR(ISNUMBER(SEARCH("Free",D65&amp;"")),AND(ISNUMBER(F65),F65=0))),"Subscription",IF(ISNUMBER(G65),"Profit",IF(ISNUMBER(I65),"Loss",IF(ISNUMBER(H65),"Draw",IF(AND(ISNUMBER(F65),ISNUMBER(E65),E65&gt;0,F65&gt;E65),"Profit",IF(AND(ISNUMBER(F65),ISNUMBER(E65),E65&gt;0,F65=E65),"Draw",IF(AND(ISNUMBER(F65),ISNUMBER(E65),E65&gt;0,F65=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L65" s="50"/>
       <x:c r="M65" s="58"/>
       <x:c r="N65" s="58"/>
@@ -3552,8 +3796,12 @@
       <x:c r="G66" s="58"/>
       <x:c r="H66" s="58"/>
       <x:c r="I66" s="58"/>
-      <x:c r="J66" s="60"/>
-      <x:c r="K66" s="50"/>
+      <x:c r="J66" s="60" t="str">
+        <x:f>IF(A66="","",IF(K66="Subscription","",IF(E66=0,"",IF(ISNUMBER(G66),G66/E66,IF(ISNUMBER(I66),-ABS(I66)/E66,IF(ISNUMBER(H66),0,IF(AND(ISNUMBER(F66),ISNUMBER(E66),E66&gt;0,F66&gt;E66),(F66-E66)/E66,IF(AND(ISNUMBER(F66),ISNUMBER(E66),E66&gt;0,F66=E66),0,IF(AND(ISNUMBER(F66),ISNUMBER(E66),E66&gt;0,F66=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K66" s="50" t="str">
+        <x:f>IF(A66="","",IF(AND(ISNUMBER(E66),E66=0,OR(ISNUMBER(SEARCH("Free",D66&amp;"")),AND(ISNUMBER(F66),F66=0))),"Subscription",IF(ISNUMBER(G66),"Profit",IF(ISNUMBER(I66),"Loss",IF(ISNUMBER(H66),"Draw",IF(AND(ISNUMBER(F66),ISNUMBER(E66),E66&gt;0,F66&gt;E66),"Profit",IF(AND(ISNUMBER(F66),ISNUMBER(E66),E66&gt;0,F66=E66),"Draw",IF(AND(ISNUMBER(F66),ISNUMBER(E66),E66&gt;0,F66=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L66" s="50"/>
       <x:c r="M66" s="58"/>
       <x:c r="N66" s="58"/>
@@ -3585,8 +3833,12 @@
       <x:c r="G67" s="58"/>
       <x:c r="H67" s="58"/>
       <x:c r="I67" s="58"/>
-      <x:c r="J67" s="60"/>
-      <x:c r="K67" s="50"/>
+      <x:c r="J67" s="60" t="str">
+        <x:f>IF(A67="","",IF(K67="Subscription","",IF(E67=0,"",IF(ISNUMBER(G67),G67/E67,IF(ISNUMBER(I67),-ABS(I67)/E67,IF(ISNUMBER(H67),0,IF(AND(ISNUMBER(F67),ISNUMBER(E67),E67&gt;0,F67&gt;E67),(F67-E67)/E67,IF(AND(ISNUMBER(F67),ISNUMBER(E67),E67&gt;0,F67=E67),0,IF(AND(ISNUMBER(F67),ISNUMBER(E67),E67&gt;0,F67=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K67" s="50" t="str">
+        <x:f>IF(A67="","",IF(AND(ISNUMBER(E67),E67=0,OR(ISNUMBER(SEARCH("Free",D67&amp;"")),AND(ISNUMBER(F67),F67=0))),"Subscription",IF(ISNUMBER(G67),"Profit",IF(ISNUMBER(I67),"Loss",IF(ISNUMBER(H67),"Draw",IF(AND(ISNUMBER(F67),ISNUMBER(E67),E67&gt;0,F67&gt;E67),"Profit",IF(AND(ISNUMBER(F67),ISNUMBER(E67),E67&gt;0,F67=E67),"Draw",IF(AND(ISNUMBER(F67),ISNUMBER(E67),E67&gt;0,F67=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L67" s="50"/>
       <x:c r="M67" s="58"/>
       <x:c r="N67" s="58"/>
@@ -3618,8 +3870,12 @@
       <x:c r="G68" s="58"/>
       <x:c r="H68" s="58"/>
       <x:c r="I68" s="58"/>
-      <x:c r="J68" s="60"/>
-      <x:c r="K68" s="50"/>
+      <x:c r="J68" s="60" t="str">
+        <x:f>IF(A68="","",IF(K68="Subscription","",IF(E68=0,"",IF(ISNUMBER(G68),G68/E68,IF(ISNUMBER(I68),-ABS(I68)/E68,IF(ISNUMBER(H68),0,IF(AND(ISNUMBER(F68),ISNUMBER(E68),E68&gt;0,F68&gt;E68),(F68-E68)/E68,IF(AND(ISNUMBER(F68),ISNUMBER(E68),E68&gt;0,F68=E68),0,IF(AND(ISNUMBER(F68),ISNUMBER(E68),E68&gt;0,F68=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K68" s="50" t="str">
+        <x:f>IF(A68="","",IF(AND(ISNUMBER(E68),E68=0,OR(ISNUMBER(SEARCH("Free",D68&amp;"")),AND(ISNUMBER(F68),F68=0))),"Subscription",IF(ISNUMBER(G68),"Profit",IF(ISNUMBER(I68),"Loss",IF(ISNUMBER(H68),"Draw",IF(AND(ISNUMBER(F68),ISNUMBER(E68),E68&gt;0,F68&gt;E68),"Profit",IF(AND(ISNUMBER(F68),ISNUMBER(E68),E68&gt;0,F68=E68),"Draw",IF(AND(ISNUMBER(F68),ISNUMBER(E68),E68&gt;0,F68=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L68" s="50"/>
       <x:c r="M68" s="58"/>
       <x:c r="N68" s="58"/>
@@ -3651,8 +3907,12 @@
       <x:c r="G69" s="58"/>
       <x:c r="H69" s="58"/>
       <x:c r="I69" s="58"/>
-      <x:c r="J69" s="60"/>
-      <x:c r="K69" s="50"/>
+      <x:c r="J69" s="60" t="str">
+        <x:f>IF(A69="","",IF(K69="Subscription","",IF(E69=0,"",IF(ISNUMBER(G69),G69/E69,IF(ISNUMBER(I69),-ABS(I69)/E69,IF(ISNUMBER(H69),0,IF(AND(ISNUMBER(F69),ISNUMBER(E69),E69&gt;0,F69&gt;E69),(F69-E69)/E69,IF(AND(ISNUMBER(F69),ISNUMBER(E69),E69&gt;0,F69=E69),0,IF(AND(ISNUMBER(F69),ISNUMBER(E69),E69&gt;0,F69=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K69" s="50" t="str">
+        <x:f>IF(A69="","",IF(AND(ISNUMBER(E69),E69=0,OR(ISNUMBER(SEARCH("Free",D69&amp;"")),AND(ISNUMBER(F69),F69=0))),"Subscription",IF(ISNUMBER(G69),"Profit",IF(ISNUMBER(I69),"Loss",IF(ISNUMBER(H69),"Draw",IF(AND(ISNUMBER(F69),ISNUMBER(E69),E69&gt;0,F69&gt;E69),"Profit",IF(AND(ISNUMBER(F69),ISNUMBER(E69),E69&gt;0,F69=E69),"Draw",IF(AND(ISNUMBER(F69),ISNUMBER(E69),E69&gt;0,F69=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L69" s="50"/>
       <x:c r="M69" s="58"/>
       <x:c r="N69" s="58"/>
@@ -3684,8 +3944,12 @@
       <x:c r="G70" s="58"/>
       <x:c r="H70" s="58"/>
       <x:c r="I70" s="58"/>
-      <x:c r="J70" s="60"/>
-      <x:c r="K70" s="50"/>
+      <x:c r="J70" s="60" t="str">
+        <x:f>IF(A70="","",IF(K70="Subscription","",IF(E70=0,"",IF(ISNUMBER(G70),G70/E70,IF(ISNUMBER(I70),-ABS(I70)/E70,IF(ISNUMBER(H70),0,IF(AND(ISNUMBER(F70),ISNUMBER(E70),E70&gt;0,F70&gt;E70),(F70-E70)/E70,IF(AND(ISNUMBER(F70),ISNUMBER(E70),E70&gt;0,F70=E70),0,IF(AND(ISNUMBER(F70),ISNUMBER(E70),E70&gt;0,F70=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K70" s="50" t="str">
+        <x:f>IF(A70="","",IF(AND(ISNUMBER(E70),E70=0,OR(ISNUMBER(SEARCH("Free",D70&amp;"")),AND(ISNUMBER(F70),F70=0))),"Subscription",IF(ISNUMBER(G70),"Profit",IF(ISNUMBER(I70),"Loss",IF(ISNUMBER(H70),"Draw",IF(AND(ISNUMBER(F70),ISNUMBER(E70),E70&gt;0,F70&gt;E70),"Profit",IF(AND(ISNUMBER(F70),ISNUMBER(E70),E70&gt;0,F70=E70),"Draw",IF(AND(ISNUMBER(F70),ISNUMBER(E70),E70&gt;0,F70=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L70" s="50"/>
       <x:c r="M70" s="58"/>
       <x:c r="N70" s="58"/>
@@ -3717,8 +3981,12 @@
       <x:c r="G71" s="58"/>
       <x:c r="H71" s="58"/>
       <x:c r="I71" s="58"/>
-      <x:c r="J71" s="60"/>
-      <x:c r="K71" s="50"/>
+      <x:c r="J71" s="60" t="str">
+        <x:f>IF(A71="","",IF(K71="Subscription","",IF(E71=0,"",IF(ISNUMBER(G71),G71/E71,IF(ISNUMBER(I71),-ABS(I71)/E71,IF(ISNUMBER(H71),0,IF(AND(ISNUMBER(F71),ISNUMBER(E71),E71&gt;0,F71&gt;E71),(F71-E71)/E71,IF(AND(ISNUMBER(F71),ISNUMBER(E71),E71&gt;0,F71=E71),0,IF(AND(ISNUMBER(F71),ISNUMBER(E71),E71&gt;0,F71=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K71" s="50" t="str">
+        <x:f>IF(A71="","",IF(AND(ISNUMBER(E71),E71=0,OR(ISNUMBER(SEARCH("Free",D71&amp;"")),AND(ISNUMBER(F71),F71=0))),"Subscription",IF(ISNUMBER(G71),"Profit",IF(ISNUMBER(I71),"Loss",IF(ISNUMBER(H71),"Draw",IF(AND(ISNUMBER(F71),ISNUMBER(E71),E71&gt;0,F71&gt;E71),"Profit",IF(AND(ISNUMBER(F71),ISNUMBER(E71),E71&gt;0,F71=E71),"Draw",IF(AND(ISNUMBER(F71),ISNUMBER(E71),E71&gt;0,F71=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L71" s="50"/>
       <x:c r="M71" s="58"/>
       <x:c r="N71" s="58"/>
@@ -3750,8 +4018,12 @@
       <x:c r="G72" s="58"/>
       <x:c r="H72" s="58"/>
       <x:c r="I72" s="58"/>
-      <x:c r="J72" s="60"/>
-      <x:c r="K72" s="50"/>
+      <x:c r="J72" s="60" t="str">
+        <x:f>IF(A72="","",IF(K72="Subscription","",IF(E72=0,"",IF(ISNUMBER(G72),G72/E72,IF(ISNUMBER(I72),-ABS(I72)/E72,IF(ISNUMBER(H72),0,IF(AND(ISNUMBER(F72),ISNUMBER(E72),E72&gt;0,F72&gt;E72),(F72-E72)/E72,IF(AND(ISNUMBER(F72),ISNUMBER(E72),E72&gt;0,F72=E72),0,IF(AND(ISNUMBER(F72),ISNUMBER(E72),E72&gt;0,F72=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K72" s="50" t="str">
+        <x:f>IF(A72="","",IF(AND(ISNUMBER(E72),E72=0,OR(ISNUMBER(SEARCH("Free",D72&amp;"")),AND(ISNUMBER(F72),F72=0))),"Subscription",IF(ISNUMBER(G72),"Profit",IF(ISNUMBER(I72),"Loss",IF(ISNUMBER(H72),"Draw",IF(AND(ISNUMBER(F72),ISNUMBER(E72),E72&gt;0,F72&gt;E72),"Profit",IF(AND(ISNUMBER(F72),ISNUMBER(E72),E72&gt;0,F72=E72),"Draw",IF(AND(ISNUMBER(F72),ISNUMBER(E72),E72&gt;0,F72=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L72" s="50"/>
       <x:c r="M72" s="58"/>
       <x:c r="N72" s="58"/>
@@ -3783,8 +4055,12 @@
       <x:c r="G73" s="58"/>
       <x:c r="H73" s="58"/>
       <x:c r="I73" s="58"/>
-      <x:c r="J73" s="60"/>
-      <x:c r="K73" s="50"/>
+      <x:c r="J73" s="60" t="str">
+        <x:f>IF(A73="","",IF(K73="Subscription","",IF(E73=0,"",IF(ISNUMBER(G73),G73/E73,IF(ISNUMBER(I73),-ABS(I73)/E73,IF(ISNUMBER(H73),0,IF(AND(ISNUMBER(F73),ISNUMBER(E73),E73&gt;0,F73&gt;E73),(F73-E73)/E73,IF(AND(ISNUMBER(F73),ISNUMBER(E73),E73&gt;0,F73=E73),0,IF(AND(ISNUMBER(F73),ISNUMBER(E73),E73&gt;0,F73=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K73" s="50" t="str">
+        <x:f>IF(A73="","",IF(AND(ISNUMBER(E73),E73=0,OR(ISNUMBER(SEARCH("Free",D73&amp;"")),AND(ISNUMBER(F73),F73=0))),"Subscription",IF(ISNUMBER(G73),"Profit",IF(ISNUMBER(I73),"Loss",IF(ISNUMBER(H73),"Draw",IF(AND(ISNUMBER(F73),ISNUMBER(E73),E73&gt;0,F73&gt;E73),"Profit",IF(AND(ISNUMBER(F73),ISNUMBER(E73),E73&gt;0,F73=E73),"Draw",IF(AND(ISNUMBER(F73),ISNUMBER(E73),E73&gt;0,F73=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L73" s="50"/>
       <x:c r="M73" s="58"/>
       <x:c r="N73" s="58"/>
@@ -3816,8 +4092,12 @@
       <x:c r="G74" s="58"/>
       <x:c r="H74" s="58"/>
       <x:c r="I74" s="58"/>
-      <x:c r="J74" s="60"/>
-      <x:c r="K74" s="50"/>
+      <x:c r="J74" s="60" t="str">
+        <x:f>IF(A74="","",IF(K74="Subscription","",IF(E74=0,"",IF(ISNUMBER(G74),G74/E74,IF(ISNUMBER(I74),-ABS(I74)/E74,IF(ISNUMBER(H74),0,IF(AND(ISNUMBER(F74),ISNUMBER(E74),E74&gt;0,F74&gt;E74),(F74-E74)/E74,IF(AND(ISNUMBER(F74),ISNUMBER(E74),E74&gt;0,F74=E74),0,IF(AND(ISNUMBER(F74),ISNUMBER(E74),E74&gt;0,F74=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K74" s="50" t="str">
+        <x:f>IF(A74="","",IF(AND(ISNUMBER(E74),E74=0,OR(ISNUMBER(SEARCH("Free",D74&amp;"")),AND(ISNUMBER(F74),F74=0))),"Subscription",IF(ISNUMBER(G74),"Profit",IF(ISNUMBER(I74),"Loss",IF(ISNUMBER(H74),"Draw",IF(AND(ISNUMBER(F74),ISNUMBER(E74),E74&gt;0,F74&gt;E74),"Profit",IF(AND(ISNUMBER(F74),ISNUMBER(E74),E74&gt;0,F74=E74),"Draw",IF(AND(ISNUMBER(F74),ISNUMBER(E74),E74&gt;0,F74=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L74" s="50"/>
       <x:c r="M74" s="58"/>
       <x:c r="N74" s="58"/>
@@ -3849,8 +4129,12 @@
       <x:c r="G75" s="58"/>
       <x:c r="H75" s="58"/>
       <x:c r="I75" s="58"/>
-      <x:c r="J75" s="60"/>
-      <x:c r="K75" s="50"/>
+      <x:c r="J75" s="60" t="str">
+        <x:f>IF(A75="","",IF(K75="Subscription","",IF(E75=0,"",IF(ISNUMBER(G75),G75/E75,IF(ISNUMBER(I75),-ABS(I75)/E75,IF(ISNUMBER(H75),0,IF(AND(ISNUMBER(F75),ISNUMBER(E75),E75&gt;0,F75&gt;E75),(F75-E75)/E75,IF(AND(ISNUMBER(F75),ISNUMBER(E75),E75&gt;0,F75=E75),0,IF(AND(ISNUMBER(F75),ISNUMBER(E75),E75&gt;0,F75=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K75" s="50" t="str">
+        <x:f>IF(A75="","",IF(AND(ISNUMBER(E75),E75=0,OR(ISNUMBER(SEARCH("Free",D75&amp;"")),AND(ISNUMBER(F75),F75=0))),"Subscription",IF(ISNUMBER(G75),"Profit",IF(ISNUMBER(I75),"Loss",IF(ISNUMBER(H75),"Draw",IF(AND(ISNUMBER(F75),ISNUMBER(E75),E75&gt;0,F75&gt;E75),"Profit",IF(AND(ISNUMBER(F75),ISNUMBER(E75),E75&gt;0,F75=E75),"Draw",IF(AND(ISNUMBER(F75),ISNUMBER(E75),E75&gt;0,F75=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L75" s="50"/>
       <x:c r="M75" s="58"/>
       <x:c r="N75" s="58"/>
@@ -3882,8 +4166,12 @@
       <x:c r="G76" s="58"/>
       <x:c r="H76" s="58"/>
       <x:c r="I76" s="58"/>
-      <x:c r="J76" s="60"/>
-      <x:c r="K76" s="50"/>
+      <x:c r="J76" s="60" t="str">
+        <x:f>IF(A76="","",IF(K76="Subscription","",IF(E76=0,"",IF(ISNUMBER(G76),G76/E76,IF(ISNUMBER(I76),-ABS(I76)/E76,IF(ISNUMBER(H76),0,IF(AND(ISNUMBER(F76),ISNUMBER(E76),E76&gt;0,F76&gt;E76),(F76-E76)/E76,IF(AND(ISNUMBER(F76),ISNUMBER(E76),E76&gt;0,F76=E76),0,IF(AND(ISNUMBER(F76),ISNUMBER(E76),E76&gt;0,F76=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K76" s="50" t="str">
+        <x:f>IF(A76="","",IF(AND(ISNUMBER(E76),E76=0,OR(ISNUMBER(SEARCH("Free",D76&amp;"")),AND(ISNUMBER(F76),F76=0))),"Subscription",IF(ISNUMBER(G76),"Profit",IF(ISNUMBER(I76),"Loss",IF(ISNUMBER(H76),"Draw",IF(AND(ISNUMBER(F76),ISNUMBER(E76),E76&gt;0,F76&gt;E76),"Profit",IF(AND(ISNUMBER(F76),ISNUMBER(E76),E76&gt;0,F76=E76),"Draw",IF(AND(ISNUMBER(F76),ISNUMBER(E76),E76&gt;0,F76=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L76" s="50"/>
       <x:c r="M76" s="58"/>
       <x:c r="N76" s="58"/>
@@ -3915,8 +4203,12 @@
       <x:c r="G77" s="58"/>
       <x:c r="H77" s="58"/>
       <x:c r="I77" s="58"/>
-      <x:c r="J77" s="60"/>
-      <x:c r="K77" s="50"/>
+      <x:c r="J77" s="60" t="str">
+        <x:f>IF(A77="","",IF(K77="Subscription","",IF(E77=0,"",IF(ISNUMBER(G77),G77/E77,IF(ISNUMBER(I77),-ABS(I77)/E77,IF(ISNUMBER(H77),0,IF(AND(ISNUMBER(F77),ISNUMBER(E77),E77&gt;0,F77&gt;E77),(F77-E77)/E77,IF(AND(ISNUMBER(F77),ISNUMBER(E77),E77&gt;0,F77=E77),0,IF(AND(ISNUMBER(F77),ISNUMBER(E77),E77&gt;0,F77=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K77" s="50" t="str">
+        <x:f>IF(A77="","",IF(AND(ISNUMBER(E77),E77=0,OR(ISNUMBER(SEARCH("Free",D77&amp;"")),AND(ISNUMBER(F77),F77=0))),"Subscription",IF(ISNUMBER(G77),"Profit",IF(ISNUMBER(I77),"Loss",IF(ISNUMBER(H77),"Draw",IF(AND(ISNUMBER(F77),ISNUMBER(E77),E77&gt;0,F77&gt;E77),"Profit",IF(AND(ISNUMBER(F77),ISNUMBER(E77),E77&gt;0,F77=E77),"Draw",IF(AND(ISNUMBER(F77),ISNUMBER(E77),E77&gt;0,F77=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L77" s="50"/>
       <x:c r="M77" s="58"/>
       <x:c r="N77" s="58"/>
@@ -3948,8 +4240,12 @@
       <x:c r="G78" s="58"/>
       <x:c r="H78" s="58"/>
       <x:c r="I78" s="58"/>
-      <x:c r="J78" s="60"/>
-      <x:c r="K78" s="50"/>
+      <x:c r="J78" s="60" t="str">
+        <x:f>IF(A78="","",IF(K78="Subscription","",IF(E78=0,"",IF(ISNUMBER(G78),G78/E78,IF(ISNUMBER(I78),-ABS(I78)/E78,IF(ISNUMBER(H78),0,IF(AND(ISNUMBER(F78),ISNUMBER(E78),E78&gt;0,F78&gt;E78),(F78-E78)/E78,IF(AND(ISNUMBER(F78),ISNUMBER(E78),E78&gt;0,F78=E78),0,IF(AND(ISNUMBER(F78),ISNUMBER(E78),E78&gt;0,F78=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K78" s="50" t="str">
+        <x:f>IF(A78="","",IF(AND(ISNUMBER(E78),E78=0,OR(ISNUMBER(SEARCH("Free",D78&amp;"")),AND(ISNUMBER(F78),F78=0))),"Subscription",IF(ISNUMBER(G78),"Profit",IF(ISNUMBER(I78),"Loss",IF(ISNUMBER(H78),"Draw",IF(AND(ISNUMBER(F78),ISNUMBER(E78),E78&gt;0,F78&gt;E78),"Profit",IF(AND(ISNUMBER(F78),ISNUMBER(E78),E78&gt;0,F78=E78),"Draw",IF(AND(ISNUMBER(F78),ISNUMBER(E78),E78&gt;0,F78=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L78" s="50"/>
       <x:c r="M78" s="58"/>
       <x:c r="N78" s="58"/>
@@ -3981,8 +4277,12 @@
       <x:c r="G79" s="58"/>
       <x:c r="H79" s="58"/>
       <x:c r="I79" s="58"/>
-      <x:c r="J79" s="60"/>
-      <x:c r="K79" s="50"/>
+      <x:c r="J79" s="60" t="str">
+        <x:f>IF(A79="","",IF(K79="Subscription","",IF(E79=0,"",IF(ISNUMBER(G79),G79/E79,IF(ISNUMBER(I79),-ABS(I79)/E79,IF(ISNUMBER(H79),0,IF(AND(ISNUMBER(F79),ISNUMBER(E79),E79&gt;0,F79&gt;E79),(F79-E79)/E79,IF(AND(ISNUMBER(F79),ISNUMBER(E79),E79&gt;0,F79=E79),0,IF(AND(ISNUMBER(F79),ISNUMBER(E79),E79&gt;0,F79=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K79" s="50" t="str">
+        <x:f>IF(A79="","",IF(AND(ISNUMBER(E79),E79=0,OR(ISNUMBER(SEARCH("Free",D79&amp;"")),AND(ISNUMBER(F79),F79=0))),"Subscription",IF(ISNUMBER(G79),"Profit",IF(ISNUMBER(I79),"Loss",IF(ISNUMBER(H79),"Draw",IF(AND(ISNUMBER(F79),ISNUMBER(E79),E79&gt;0,F79&gt;E79),"Profit",IF(AND(ISNUMBER(F79),ISNUMBER(E79),E79&gt;0,F79=E79),"Draw",IF(AND(ISNUMBER(F79),ISNUMBER(E79),E79&gt;0,F79=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L79" s="50"/>
       <x:c r="M79" s="58"/>
       <x:c r="N79" s="58"/>
@@ -4014,8 +4314,12 @@
       <x:c r="G80" s="58"/>
       <x:c r="H80" s="58"/>
       <x:c r="I80" s="58"/>
-      <x:c r="J80" s="60"/>
-      <x:c r="K80" s="50"/>
+      <x:c r="J80" s="60" t="str">
+        <x:f>IF(A80="","",IF(K80="Subscription","",IF(E80=0,"",IF(ISNUMBER(G80),G80/E80,IF(ISNUMBER(I80),-ABS(I80)/E80,IF(ISNUMBER(H80),0,IF(AND(ISNUMBER(F80),ISNUMBER(E80),E80&gt;0,F80&gt;E80),(F80-E80)/E80,IF(AND(ISNUMBER(F80),ISNUMBER(E80),E80&gt;0,F80=E80),0,IF(AND(ISNUMBER(F80),ISNUMBER(E80),E80&gt;0,F80=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K80" s="50" t="str">
+        <x:f>IF(A80="","",IF(AND(ISNUMBER(E80),E80=0,OR(ISNUMBER(SEARCH("Free",D80&amp;"")),AND(ISNUMBER(F80),F80=0))),"Subscription",IF(ISNUMBER(G80),"Profit",IF(ISNUMBER(I80),"Loss",IF(ISNUMBER(H80),"Draw",IF(AND(ISNUMBER(F80),ISNUMBER(E80),E80&gt;0,F80&gt;E80),"Profit",IF(AND(ISNUMBER(F80),ISNUMBER(E80),E80&gt;0,F80=E80),"Draw",IF(AND(ISNUMBER(F80),ISNUMBER(E80),E80&gt;0,F80=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L80" s="50"/>
       <x:c r="M80" s="58"/>
       <x:c r="N80" s="58"/>
@@ -4047,8 +4351,12 @@
       <x:c r="G81" s="58"/>
       <x:c r="H81" s="58"/>
       <x:c r="I81" s="58"/>
-      <x:c r="J81" s="60"/>
-      <x:c r="K81" s="50"/>
+      <x:c r="J81" s="60" t="str">
+        <x:f>IF(A81="","",IF(K81="Subscription","",IF(E81=0,"",IF(ISNUMBER(G81),G81/E81,IF(ISNUMBER(I81),-ABS(I81)/E81,IF(ISNUMBER(H81),0,IF(AND(ISNUMBER(F81),ISNUMBER(E81),E81&gt;0,F81&gt;E81),(F81-E81)/E81,IF(AND(ISNUMBER(F81),ISNUMBER(E81),E81&gt;0,F81=E81),0,IF(AND(ISNUMBER(F81),ISNUMBER(E81),E81&gt;0,F81=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K81" s="50" t="str">
+        <x:f>IF(A81="","",IF(AND(ISNUMBER(E81),E81=0,OR(ISNUMBER(SEARCH("Free",D81&amp;"")),AND(ISNUMBER(F81),F81=0))),"Subscription",IF(ISNUMBER(G81),"Profit",IF(ISNUMBER(I81),"Loss",IF(ISNUMBER(H81),"Draw",IF(AND(ISNUMBER(F81),ISNUMBER(E81),E81&gt;0,F81&gt;E81),"Profit",IF(AND(ISNUMBER(F81),ISNUMBER(E81),E81&gt;0,F81=E81),"Draw",IF(AND(ISNUMBER(F81),ISNUMBER(E81),E81&gt;0,F81=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L81" s="50"/>
       <x:c r="M81" s="58"/>
       <x:c r="N81" s="58"/>
@@ -4080,8 +4388,12 @@
       <x:c r="G82" s="58"/>
       <x:c r="H82" s="58"/>
       <x:c r="I82" s="58"/>
-      <x:c r="J82" s="60"/>
-      <x:c r="K82" s="50"/>
+      <x:c r="J82" s="60" t="str">
+        <x:f>IF(A82="","",IF(K82="Subscription","",IF(E82=0,"",IF(ISNUMBER(G82),G82/E82,IF(ISNUMBER(I82),-ABS(I82)/E82,IF(ISNUMBER(H82),0,IF(AND(ISNUMBER(F82),ISNUMBER(E82),E82&gt;0,F82&gt;E82),(F82-E82)/E82,IF(AND(ISNUMBER(F82),ISNUMBER(E82),E82&gt;0,F82=E82),0,IF(AND(ISNUMBER(F82),ISNUMBER(E82),E82&gt;0,F82=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K82" s="50" t="str">
+        <x:f>IF(A82="","",IF(AND(ISNUMBER(E82),E82=0,OR(ISNUMBER(SEARCH("Free",D82&amp;"")),AND(ISNUMBER(F82),F82=0))),"Subscription",IF(ISNUMBER(G82),"Profit",IF(ISNUMBER(I82),"Loss",IF(ISNUMBER(H82),"Draw",IF(AND(ISNUMBER(F82),ISNUMBER(E82),E82&gt;0,F82&gt;E82),"Profit",IF(AND(ISNUMBER(F82),ISNUMBER(E82),E82&gt;0,F82=E82),"Draw",IF(AND(ISNUMBER(F82),ISNUMBER(E82),E82&gt;0,F82=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L82" s="50"/>
       <x:c r="M82" s="58"/>
       <x:c r="N82" s="58"/>
@@ -4113,8 +4425,12 @@
       <x:c r="G83" s="58"/>
       <x:c r="H83" s="58"/>
       <x:c r="I83" s="58"/>
-      <x:c r="J83" s="60"/>
-      <x:c r="K83" s="50"/>
+      <x:c r="J83" s="60" t="str">
+        <x:f>IF(A83="","",IF(K83="Subscription","",IF(E83=0,"",IF(ISNUMBER(G83),G83/E83,IF(ISNUMBER(I83),-ABS(I83)/E83,IF(ISNUMBER(H83),0,IF(AND(ISNUMBER(F83),ISNUMBER(E83),E83&gt;0,F83&gt;E83),(F83-E83)/E83,IF(AND(ISNUMBER(F83),ISNUMBER(E83),E83&gt;0,F83=E83),0,IF(AND(ISNUMBER(F83),ISNUMBER(E83),E83&gt;0,F83=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K83" s="50" t="str">
+        <x:f>IF(A83="","",IF(AND(ISNUMBER(E83),E83=0,OR(ISNUMBER(SEARCH("Free",D83&amp;"")),AND(ISNUMBER(F83),F83=0))),"Subscription",IF(ISNUMBER(G83),"Profit",IF(ISNUMBER(I83),"Loss",IF(ISNUMBER(H83),"Draw",IF(AND(ISNUMBER(F83),ISNUMBER(E83),E83&gt;0,F83&gt;E83),"Profit",IF(AND(ISNUMBER(F83),ISNUMBER(E83),E83&gt;0,F83=E83),"Draw",IF(AND(ISNUMBER(F83),ISNUMBER(E83),E83&gt;0,F83=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L83" s="50"/>
       <x:c r="M83" s="58"/>
       <x:c r="N83" s="58"/>
@@ -4146,8 +4462,12 @@
       <x:c r="G84" s="58"/>
       <x:c r="H84" s="58"/>
       <x:c r="I84" s="58"/>
-      <x:c r="J84" s="60"/>
-      <x:c r="K84" s="50"/>
+      <x:c r="J84" s="60" t="str">
+        <x:f>IF(A84="","",IF(K84="Subscription","",IF(E84=0,"",IF(ISNUMBER(G84),G84/E84,IF(ISNUMBER(I84),-ABS(I84)/E84,IF(ISNUMBER(H84),0,IF(AND(ISNUMBER(F84),ISNUMBER(E84),E84&gt;0,F84&gt;E84),(F84-E84)/E84,IF(AND(ISNUMBER(F84),ISNUMBER(E84),E84&gt;0,F84=E84),0,IF(AND(ISNUMBER(F84),ISNUMBER(E84),E84&gt;0,F84=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K84" s="50" t="str">
+        <x:f>IF(A84="","",IF(AND(ISNUMBER(E84),E84=0,OR(ISNUMBER(SEARCH("Free",D84&amp;"")),AND(ISNUMBER(F84),F84=0))),"Subscription",IF(ISNUMBER(G84),"Profit",IF(ISNUMBER(I84),"Loss",IF(ISNUMBER(H84),"Draw",IF(AND(ISNUMBER(F84),ISNUMBER(E84),E84&gt;0,F84&gt;E84),"Profit",IF(AND(ISNUMBER(F84),ISNUMBER(E84),E84&gt;0,F84=E84),"Draw",IF(AND(ISNUMBER(F84),ISNUMBER(E84),E84&gt;0,F84=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L84" s="50"/>
       <x:c r="M84" s="58"/>
       <x:c r="N84" s="58"/>
@@ -4179,8 +4499,12 @@
       <x:c r="G85" s="58"/>
       <x:c r="H85" s="58"/>
       <x:c r="I85" s="58"/>
-      <x:c r="J85" s="60"/>
-      <x:c r="K85" s="50"/>
+      <x:c r="J85" s="60" t="str">
+        <x:f>IF(A85="","",IF(K85="Subscription","",IF(E85=0,"",IF(ISNUMBER(G85),G85/E85,IF(ISNUMBER(I85),-ABS(I85)/E85,IF(ISNUMBER(H85),0,IF(AND(ISNUMBER(F85),ISNUMBER(E85),E85&gt;0,F85&gt;E85),(F85-E85)/E85,IF(AND(ISNUMBER(F85),ISNUMBER(E85),E85&gt;0,F85=E85),0,IF(AND(ISNUMBER(F85),ISNUMBER(E85),E85&gt;0,F85=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K85" s="50" t="str">
+        <x:f>IF(A85="","",IF(AND(ISNUMBER(E85),E85=0,OR(ISNUMBER(SEARCH("Free",D85&amp;"")),AND(ISNUMBER(F85),F85=0))),"Subscription",IF(ISNUMBER(G85),"Profit",IF(ISNUMBER(I85),"Loss",IF(ISNUMBER(H85),"Draw",IF(AND(ISNUMBER(F85),ISNUMBER(E85),E85&gt;0,F85&gt;E85),"Profit",IF(AND(ISNUMBER(F85),ISNUMBER(E85),E85&gt;0,F85=E85),"Draw",IF(AND(ISNUMBER(F85),ISNUMBER(E85),E85&gt;0,F85=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L85" s="50"/>
       <x:c r="M85" s="58"/>
       <x:c r="N85" s="58"/>
@@ -4212,8 +4536,12 @@
       <x:c r="G86" s="58"/>
       <x:c r="H86" s="58"/>
       <x:c r="I86" s="58"/>
-      <x:c r="J86" s="60"/>
-      <x:c r="K86" s="50"/>
+      <x:c r="J86" s="60" t="str">
+        <x:f>IF(A86="","",IF(K86="Subscription","",IF(E86=0,"",IF(ISNUMBER(G86),G86/E86,IF(ISNUMBER(I86),-ABS(I86)/E86,IF(ISNUMBER(H86),0,IF(AND(ISNUMBER(F86),ISNUMBER(E86),E86&gt;0,F86&gt;E86),(F86-E86)/E86,IF(AND(ISNUMBER(F86),ISNUMBER(E86),E86&gt;0,F86=E86),0,IF(AND(ISNUMBER(F86),ISNUMBER(E86),E86&gt;0,F86=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K86" s="50" t="str">
+        <x:f>IF(A86="","",IF(AND(ISNUMBER(E86),E86=0,OR(ISNUMBER(SEARCH("Free",D86&amp;"")),AND(ISNUMBER(F86),F86=0))),"Subscription",IF(ISNUMBER(G86),"Profit",IF(ISNUMBER(I86),"Loss",IF(ISNUMBER(H86),"Draw",IF(AND(ISNUMBER(F86),ISNUMBER(E86),E86&gt;0,F86&gt;E86),"Profit",IF(AND(ISNUMBER(F86),ISNUMBER(E86),E86&gt;0,F86=E86),"Draw",IF(AND(ISNUMBER(F86),ISNUMBER(E86),E86&gt;0,F86=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L86" s="50"/>
       <x:c r="M86" s="58"/>
       <x:c r="N86" s="58"/>
@@ -4245,8 +4573,12 @@
       <x:c r="G87" s="58"/>
       <x:c r="H87" s="58"/>
       <x:c r="I87" s="58"/>
-      <x:c r="J87" s="60"/>
-      <x:c r="K87" s="50"/>
+      <x:c r="J87" s="60" t="str">
+        <x:f>IF(A87="","",IF(K87="Subscription","",IF(E87=0,"",IF(ISNUMBER(G87),G87/E87,IF(ISNUMBER(I87),-ABS(I87)/E87,IF(ISNUMBER(H87),0,IF(AND(ISNUMBER(F87),ISNUMBER(E87),E87&gt;0,F87&gt;E87),(F87-E87)/E87,IF(AND(ISNUMBER(F87),ISNUMBER(E87),E87&gt;0,F87=E87),0,IF(AND(ISNUMBER(F87),ISNUMBER(E87),E87&gt;0,F87=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K87" s="50" t="str">
+        <x:f>IF(A87="","",IF(AND(ISNUMBER(E87),E87=0,OR(ISNUMBER(SEARCH("Free",D87&amp;"")),AND(ISNUMBER(F87),F87=0))),"Subscription",IF(ISNUMBER(G87),"Profit",IF(ISNUMBER(I87),"Loss",IF(ISNUMBER(H87),"Draw",IF(AND(ISNUMBER(F87),ISNUMBER(E87),E87&gt;0,F87&gt;E87),"Profit",IF(AND(ISNUMBER(F87),ISNUMBER(E87),E87&gt;0,F87=E87),"Draw",IF(AND(ISNUMBER(F87),ISNUMBER(E87),E87&gt;0,F87=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L87" s="50"/>
       <x:c r="M87" s="58"/>
       <x:c r="N87" s="58"/>
@@ -4278,8 +4610,12 @@
       <x:c r="G88" s="58"/>
       <x:c r="H88" s="58"/>
       <x:c r="I88" s="58"/>
-      <x:c r="J88" s="60"/>
-      <x:c r="K88" s="50"/>
+      <x:c r="J88" s="60" t="str">
+        <x:f>IF(A88="","",IF(K88="Subscription","",IF(E88=0,"",IF(ISNUMBER(G88),G88/E88,IF(ISNUMBER(I88),-ABS(I88)/E88,IF(ISNUMBER(H88),0,IF(AND(ISNUMBER(F88),ISNUMBER(E88),E88&gt;0,F88&gt;E88),(F88-E88)/E88,IF(AND(ISNUMBER(F88),ISNUMBER(E88),E88&gt;0,F88=E88),0,IF(AND(ISNUMBER(F88),ISNUMBER(E88),E88&gt;0,F88=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K88" s="50" t="str">
+        <x:f>IF(A88="","",IF(AND(ISNUMBER(E88),E88=0,OR(ISNUMBER(SEARCH("Free",D88&amp;"")),AND(ISNUMBER(F88),F88=0))),"Subscription",IF(ISNUMBER(G88),"Profit",IF(ISNUMBER(I88),"Loss",IF(ISNUMBER(H88),"Draw",IF(AND(ISNUMBER(F88),ISNUMBER(E88),E88&gt;0,F88&gt;E88),"Profit",IF(AND(ISNUMBER(F88),ISNUMBER(E88),E88&gt;0,F88=E88),"Draw",IF(AND(ISNUMBER(F88),ISNUMBER(E88),E88&gt;0,F88=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L88" s="50"/>
       <x:c r="M88" s="58"/>
       <x:c r="N88" s="58"/>
@@ -4311,8 +4647,12 @@
       <x:c r="G89" s="58"/>
       <x:c r="H89" s="58"/>
       <x:c r="I89" s="58"/>
-      <x:c r="J89" s="60"/>
-      <x:c r="K89" s="50"/>
+      <x:c r="J89" s="60" t="str">
+        <x:f>IF(A89="","",IF(K89="Subscription","",IF(E89=0,"",IF(ISNUMBER(G89),G89/E89,IF(ISNUMBER(I89),-ABS(I89)/E89,IF(ISNUMBER(H89),0,IF(AND(ISNUMBER(F89),ISNUMBER(E89),E89&gt;0,F89&gt;E89),(F89-E89)/E89,IF(AND(ISNUMBER(F89),ISNUMBER(E89),E89&gt;0,F89=E89),0,IF(AND(ISNUMBER(F89),ISNUMBER(E89),E89&gt;0,F89=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K89" s="50" t="str">
+        <x:f>IF(A89="","",IF(AND(ISNUMBER(E89),E89=0,OR(ISNUMBER(SEARCH("Free",D89&amp;"")),AND(ISNUMBER(F89),F89=0))),"Subscription",IF(ISNUMBER(G89),"Profit",IF(ISNUMBER(I89),"Loss",IF(ISNUMBER(H89),"Draw",IF(AND(ISNUMBER(F89),ISNUMBER(E89),E89&gt;0,F89&gt;E89),"Profit",IF(AND(ISNUMBER(F89),ISNUMBER(E89),E89&gt;0,F89=E89),"Draw",IF(AND(ISNUMBER(F89),ISNUMBER(E89),E89&gt;0,F89=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L89" s="50"/>
       <x:c r="M89" s="58"/>
       <x:c r="N89" s="58"/>
@@ -4344,8 +4684,12 @@
       <x:c r="G90" s="58"/>
       <x:c r="H90" s="58"/>
       <x:c r="I90" s="58"/>
-      <x:c r="J90" s="60"/>
-      <x:c r="K90" s="50"/>
+      <x:c r="J90" s="60" t="str">
+        <x:f>IF(A90="","",IF(K90="Subscription","",IF(E90=0,"",IF(ISNUMBER(G90),G90/E90,IF(ISNUMBER(I90),-ABS(I90)/E90,IF(ISNUMBER(H90),0,IF(AND(ISNUMBER(F90),ISNUMBER(E90),E90&gt;0,F90&gt;E90),(F90-E90)/E90,IF(AND(ISNUMBER(F90),ISNUMBER(E90),E90&gt;0,F90=E90),0,IF(AND(ISNUMBER(F90),ISNUMBER(E90),E90&gt;0,F90=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K90" s="50" t="str">
+        <x:f>IF(A90="","",IF(AND(ISNUMBER(E90),E90=0,OR(ISNUMBER(SEARCH("Free",D90&amp;"")),AND(ISNUMBER(F90),F90=0))),"Subscription",IF(ISNUMBER(G90),"Profit",IF(ISNUMBER(I90),"Loss",IF(ISNUMBER(H90),"Draw",IF(AND(ISNUMBER(F90),ISNUMBER(E90),E90&gt;0,F90&gt;E90),"Profit",IF(AND(ISNUMBER(F90),ISNUMBER(E90),E90&gt;0,F90=E90),"Draw",IF(AND(ISNUMBER(F90),ISNUMBER(E90),E90&gt;0,F90=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L90" s="50"/>
       <x:c r="M90" s="58"/>
       <x:c r="N90" s="58"/>
@@ -4377,8 +4721,12 @@
       <x:c r="G91" s="58"/>
       <x:c r="H91" s="58"/>
       <x:c r="I91" s="58"/>
-      <x:c r="J91" s="60"/>
-      <x:c r="K91" s="50"/>
+      <x:c r="J91" s="60" t="str">
+        <x:f>IF(A91="","",IF(K91="Subscription","",IF(E91=0,"",IF(ISNUMBER(G91),G91/E91,IF(ISNUMBER(I91),-ABS(I91)/E91,IF(ISNUMBER(H91),0,IF(AND(ISNUMBER(F91),ISNUMBER(E91),E91&gt;0,F91&gt;E91),(F91-E91)/E91,IF(AND(ISNUMBER(F91),ISNUMBER(E91),E91&gt;0,F91=E91),0,IF(AND(ISNUMBER(F91),ISNUMBER(E91),E91&gt;0,F91=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K91" s="50" t="str">
+        <x:f>IF(A91="","",IF(AND(ISNUMBER(E91),E91=0,OR(ISNUMBER(SEARCH("Free",D91&amp;"")),AND(ISNUMBER(F91),F91=0))),"Subscription",IF(ISNUMBER(G91),"Profit",IF(ISNUMBER(I91),"Loss",IF(ISNUMBER(H91),"Draw",IF(AND(ISNUMBER(F91),ISNUMBER(E91),E91&gt;0,F91&gt;E91),"Profit",IF(AND(ISNUMBER(F91),ISNUMBER(E91),E91&gt;0,F91=E91),"Draw",IF(AND(ISNUMBER(F91),ISNUMBER(E91),E91&gt;0,F91=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L91" s="50"/>
       <x:c r="M91" s="58"/>
       <x:c r="N91" s="58"/>
@@ -4410,8 +4758,12 @@
       <x:c r="G92" s="58"/>
       <x:c r="H92" s="58"/>
       <x:c r="I92" s="58"/>
-      <x:c r="J92" s="60"/>
-      <x:c r="K92" s="50"/>
+      <x:c r="J92" s="60" t="str">
+        <x:f>IF(A92="","",IF(K92="Subscription","",IF(E92=0,"",IF(ISNUMBER(G92),G92/E92,IF(ISNUMBER(I92),-ABS(I92)/E92,IF(ISNUMBER(H92),0,IF(AND(ISNUMBER(F92),ISNUMBER(E92),E92&gt;0,F92&gt;E92),(F92-E92)/E92,IF(AND(ISNUMBER(F92),ISNUMBER(E92),E92&gt;0,F92=E92),0,IF(AND(ISNUMBER(F92),ISNUMBER(E92),E92&gt;0,F92=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K92" s="50" t="str">
+        <x:f>IF(A92="","",IF(AND(ISNUMBER(E92),E92=0,OR(ISNUMBER(SEARCH("Free",D92&amp;"")),AND(ISNUMBER(F92),F92=0))),"Subscription",IF(ISNUMBER(G92),"Profit",IF(ISNUMBER(I92),"Loss",IF(ISNUMBER(H92),"Draw",IF(AND(ISNUMBER(F92),ISNUMBER(E92),E92&gt;0,F92&gt;E92),"Profit",IF(AND(ISNUMBER(F92),ISNUMBER(E92),E92&gt;0,F92=E92),"Draw",IF(AND(ISNUMBER(F92),ISNUMBER(E92),E92&gt;0,F92=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L92" s="50"/>
       <x:c r="M92" s="58"/>
       <x:c r="N92" s="58"/>
@@ -4443,8 +4795,12 @@
       <x:c r="G93" s="58"/>
       <x:c r="H93" s="58"/>
       <x:c r="I93" s="58"/>
-      <x:c r="J93" s="60"/>
-      <x:c r="K93" s="50"/>
+      <x:c r="J93" s="60" t="str">
+        <x:f>IF(A93="","",IF(K93="Subscription","",IF(E93=0,"",IF(ISNUMBER(G93),G93/E93,IF(ISNUMBER(I93),-ABS(I93)/E93,IF(ISNUMBER(H93),0,IF(AND(ISNUMBER(F93),ISNUMBER(E93),E93&gt;0,F93&gt;E93),(F93-E93)/E93,IF(AND(ISNUMBER(F93),ISNUMBER(E93),E93&gt;0,F93=E93),0,IF(AND(ISNUMBER(F93),ISNUMBER(E93),E93&gt;0,F93=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K93" s="50" t="str">
+        <x:f>IF(A93="","",IF(AND(ISNUMBER(E93),E93=0,OR(ISNUMBER(SEARCH("Free",D93&amp;"")),AND(ISNUMBER(F93),F93=0))),"Subscription",IF(ISNUMBER(G93),"Profit",IF(ISNUMBER(I93),"Loss",IF(ISNUMBER(H93),"Draw",IF(AND(ISNUMBER(F93),ISNUMBER(E93),E93&gt;0,F93&gt;E93),"Profit",IF(AND(ISNUMBER(F93),ISNUMBER(E93),E93&gt;0,F93=E93),"Draw",IF(AND(ISNUMBER(F93),ISNUMBER(E93),E93&gt;0,F93=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L93" s="50"/>
       <x:c r="M93" s="58"/>
       <x:c r="N93" s="58"/>
@@ -4476,8 +4832,12 @@
       <x:c r="G94" s="58"/>
       <x:c r="H94" s="58"/>
       <x:c r="I94" s="58"/>
-      <x:c r="J94" s="60"/>
-      <x:c r="K94" s="50"/>
+      <x:c r="J94" s="60" t="str">
+        <x:f>IF(A94="","",IF(K94="Subscription","",IF(E94=0,"",IF(ISNUMBER(G94),G94/E94,IF(ISNUMBER(I94),-ABS(I94)/E94,IF(ISNUMBER(H94),0,IF(AND(ISNUMBER(F94),ISNUMBER(E94),E94&gt;0,F94&gt;E94),(F94-E94)/E94,IF(AND(ISNUMBER(F94),ISNUMBER(E94),E94&gt;0,F94=E94),0,IF(AND(ISNUMBER(F94),ISNUMBER(E94),E94&gt;0,F94=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K94" s="50" t="str">
+        <x:f>IF(A94="","",IF(AND(ISNUMBER(E94),E94=0,OR(ISNUMBER(SEARCH("Free",D94&amp;"")),AND(ISNUMBER(F94),F94=0))),"Subscription",IF(ISNUMBER(G94),"Profit",IF(ISNUMBER(I94),"Loss",IF(ISNUMBER(H94),"Draw",IF(AND(ISNUMBER(F94),ISNUMBER(E94),E94&gt;0,F94&gt;E94),"Profit",IF(AND(ISNUMBER(F94),ISNUMBER(E94),E94&gt;0,F94=E94),"Draw",IF(AND(ISNUMBER(F94),ISNUMBER(E94),E94&gt;0,F94=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L94" s="50"/>
       <x:c r="M94" s="58"/>
       <x:c r="N94" s="58"/>
@@ -4509,8 +4869,12 @@
       <x:c r="G95" s="58"/>
       <x:c r="H95" s="58"/>
       <x:c r="I95" s="58"/>
-      <x:c r="J95" s="60"/>
-      <x:c r="K95" s="50"/>
+      <x:c r="J95" s="60" t="str">
+        <x:f>IF(A95="","",IF(K95="Subscription","",IF(E95=0,"",IF(ISNUMBER(G95),G95/E95,IF(ISNUMBER(I95),-ABS(I95)/E95,IF(ISNUMBER(H95),0,IF(AND(ISNUMBER(F95),ISNUMBER(E95),E95&gt;0,F95&gt;E95),(F95-E95)/E95,IF(AND(ISNUMBER(F95),ISNUMBER(E95),E95&gt;0,F95=E95),0,IF(AND(ISNUMBER(F95),ISNUMBER(E95),E95&gt;0,F95=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K95" s="50" t="str">
+        <x:f>IF(A95="","",IF(AND(ISNUMBER(E95),E95=0,OR(ISNUMBER(SEARCH("Free",D95&amp;"")),AND(ISNUMBER(F95),F95=0))),"Subscription",IF(ISNUMBER(G95),"Profit",IF(ISNUMBER(I95),"Loss",IF(ISNUMBER(H95),"Draw",IF(AND(ISNUMBER(F95),ISNUMBER(E95),E95&gt;0,F95&gt;E95),"Profit",IF(AND(ISNUMBER(F95),ISNUMBER(E95),E95&gt;0,F95=E95),"Draw",IF(AND(ISNUMBER(F95),ISNUMBER(E95),E95&gt;0,F95=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L95" s="50"/>
       <x:c r="M95" s="58"/>
       <x:c r="N95" s="58"/>
@@ -4542,8 +4906,12 @@
       <x:c r="G96" s="58"/>
       <x:c r="H96" s="58"/>
       <x:c r="I96" s="58"/>
-      <x:c r="J96" s="60"/>
-      <x:c r="K96" s="50"/>
+      <x:c r="J96" s="60" t="str">
+        <x:f>IF(A96="","",IF(K96="Subscription","",IF(E96=0,"",IF(ISNUMBER(G96),G96/E96,IF(ISNUMBER(I96),-ABS(I96)/E96,IF(ISNUMBER(H96),0,IF(AND(ISNUMBER(F96),ISNUMBER(E96),E96&gt;0,F96&gt;E96),(F96-E96)/E96,IF(AND(ISNUMBER(F96),ISNUMBER(E96),E96&gt;0,F96=E96),0,IF(AND(ISNUMBER(F96),ISNUMBER(E96),E96&gt;0,F96=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K96" s="50" t="str">
+        <x:f>IF(A96="","",IF(AND(ISNUMBER(E96),E96=0,OR(ISNUMBER(SEARCH("Free",D96&amp;"")),AND(ISNUMBER(F96),F96=0))),"Subscription",IF(ISNUMBER(G96),"Profit",IF(ISNUMBER(I96),"Loss",IF(ISNUMBER(H96),"Draw",IF(AND(ISNUMBER(F96),ISNUMBER(E96),E96&gt;0,F96&gt;E96),"Profit",IF(AND(ISNUMBER(F96),ISNUMBER(E96),E96&gt;0,F96=E96),"Draw",IF(AND(ISNUMBER(F96),ISNUMBER(E96),E96&gt;0,F96=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L96" s="50"/>
       <x:c r="M96" s="58"/>
       <x:c r="N96" s="58"/>
@@ -4575,8 +4943,12 @@
       <x:c r="G97" s="58"/>
       <x:c r="H97" s="58"/>
       <x:c r="I97" s="58"/>
-      <x:c r="J97" s="60"/>
-      <x:c r="K97" s="50"/>
+      <x:c r="J97" s="60" t="str">
+        <x:f>IF(A97="","",IF(K97="Subscription","",IF(E97=0,"",IF(ISNUMBER(G97),G97/E97,IF(ISNUMBER(I97),-ABS(I97)/E97,IF(ISNUMBER(H97),0,IF(AND(ISNUMBER(F97),ISNUMBER(E97),E97&gt;0,F97&gt;E97),(F97-E97)/E97,IF(AND(ISNUMBER(F97),ISNUMBER(E97),E97&gt;0,F97=E97),0,IF(AND(ISNUMBER(F97),ISNUMBER(E97),E97&gt;0,F97=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K97" s="50" t="str">
+        <x:f>IF(A97="","",IF(AND(ISNUMBER(E97),E97=0,OR(ISNUMBER(SEARCH("Free",D97&amp;"")),AND(ISNUMBER(F97),F97=0))),"Subscription",IF(ISNUMBER(G97),"Profit",IF(ISNUMBER(I97),"Loss",IF(ISNUMBER(H97),"Draw",IF(AND(ISNUMBER(F97),ISNUMBER(E97),E97&gt;0,F97&gt;E97),"Profit",IF(AND(ISNUMBER(F97),ISNUMBER(E97),E97&gt;0,F97=E97),"Draw",IF(AND(ISNUMBER(F97),ISNUMBER(E97),E97&gt;0,F97=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L97" s="50"/>
       <x:c r="M97" s="58"/>
       <x:c r="N97" s="58"/>
@@ -4608,8 +4980,12 @@
       <x:c r="G98" s="58"/>
       <x:c r="H98" s="58"/>
       <x:c r="I98" s="58"/>
-      <x:c r="J98" s="60"/>
-      <x:c r="K98" s="50"/>
+      <x:c r="J98" s="60" t="str">
+        <x:f>IF(A98="","",IF(K98="Subscription","",IF(E98=0,"",IF(ISNUMBER(G98),G98/E98,IF(ISNUMBER(I98),-ABS(I98)/E98,IF(ISNUMBER(H98),0,IF(AND(ISNUMBER(F98),ISNUMBER(E98),E98&gt;0,F98&gt;E98),(F98-E98)/E98,IF(AND(ISNUMBER(F98),ISNUMBER(E98),E98&gt;0,F98=E98),0,IF(AND(ISNUMBER(F98),ISNUMBER(E98),E98&gt;0,F98=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K98" s="50" t="str">
+        <x:f>IF(A98="","",IF(AND(ISNUMBER(E98),E98=0,OR(ISNUMBER(SEARCH("Free",D98&amp;"")),AND(ISNUMBER(F98),F98=0))),"Subscription",IF(ISNUMBER(G98),"Profit",IF(ISNUMBER(I98),"Loss",IF(ISNUMBER(H98),"Draw",IF(AND(ISNUMBER(F98),ISNUMBER(E98),E98&gt;0,F98&gt;E98),"Profit",IF(AND(ISNUMBER(F98),ISNUMBER(E98),E98&gt;0,F98=E98),"Draw",IF(AND(ISNUMBER(F98),ISNUMBER(E98),E98&gt;0,F98=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L98" s="50"/>
       <x:c r="M98" s="58"/>
       <x:c r="N98" s="58"/>
@@ -4641,8 +5017,12 @@
       <x:c r="G99" s="58"/>
       <x:c r="H99" s="58"/>
       <x:c r="I99" s="58"/>
-      <x:c r="J99" s="60"/>
-      <x:c r="K99" s="50"/>
+      <x:c r="J99" s="60" t="str">
+        <x:f>IF(A99="","",IF(K99="Subscription","",IF(E99=0,"",IF(ISNUMBER(G99),G99/E99,IF(ISNUMBER(I99),-ABS(I99)/E99,IF(ISNUMBER(H99),0,IF(AND(ISNUMBER(F99),ISNUMBER(E99),E99&gt;0,F99&gt;E99),(F99-E99)/E99,IF(AND(ISNUMBER(F99),ISNUMBER(E99),E99&gt;0,F99=E99),0,IF(AND(ISNUMBER(F99),ISNUMBER(E99),E99&gt;0,F99=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K99" s="50" t="str">
+        <x:f>IF(A99="","",IF(AND(ISNUMBER(E99),E99=0,OR(ISNUMBER(SEARCH("Free",D99&amp;"")),AND(ISNUMBER(F99),F99=0))),"Subscription",IF(ISNUMBER(G99),"Profit",IF(ISNUMBER(I99),"Loss",IF(ISNUMBER(H99),"Draw",IF(AND(ISNUMBER(F99),ISNUMBER(E99),E99&gt;0,F99&gt;E99),"Profit",IF(AND(ISNUMBER(F99),ISNUMBER(E99),E99&gt;0,F99=E99),"Draw",IF(AND(ISNUMBER(F99),ISNUMBER(E99),E99&gt;0,F99=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L99" s="50"/>
       <x:c r="M99" s="58"/>
       <x:c r="N99" s="58"/>
@@ -4674,8 +5054,12 @@
       <x:c r="G100" s="58"/>
       <x:c r="H100" s="58"/>
       <x:c r="I100" s="58"/>
-      <x:c r="J100" s="60"/>
-      <x:c r="K100" s="50"/>
+      <x:c r="J100" s="60" t="str">
+        <x:f>IF(A100="","",IF(K100="Subscription","",IF(E100=0,"",IF(ISNUMBER(G100),G100/E100,IF(ISNUMBER(I100),-ABS(I100)/E100,IF(ISNUMBER(H100),0,IF(AND(ISNUMBER(F100),ISNUMBER(E100),E100&gt;0,F100&gt;E100),(F100-E100)/E100,IF(AND(ISNUMBER(F100),ISNUMBER(E100),E100&gt;0,F100=E100),0,IF(AND(ISNUMBER(F100),ISNUMBER(E100),E100&gt;0,F100=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K100" s="50" t="str">
+        <x:f>IF(A100="","",IF(AND(ISNUMBER(E100),E100=0,OR(ISNUMBER(SEARCH("Free",D100&amp;"")),AND(ISNUMBER(F100),F100=0))),"Subscription",IF(ISNUMBER(G100),"Profit",IF(ISNUMBER(I100),"Loss",IF(ISNUMBER(H100),"Draw",IF(AND(ISNUMBER(F100),ISNUMBER(E100),E100&gt;0,F100&gt;E100),"Profit",IF(AND(ISNUMBER(F100),ISNUMBER(E100),E100&gt;0,F100=E100),"Draw",IF(AND(ISNUMBER(F100),ISNUMBER(E100),E100&gt;0,F100=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L100" s="50"/>
       <x:c r="M100" s="58"/>
       <x:c r="N100" s="58"/>
@@ -4707,8 +5091,12 @@
       <x:c r="G101" s="58"/>
       <x:c r="H101" s="58"/>
       <x:c r="I101" s="58"/>
-      <x:c r="J101" s="60"/>
-      <x:c r="K101" s="50"/>
+      <x:c r="J101" s="60" t="str">
+        <x:f>IF(A101="","",IF(K101="Subscription","",IF(E101=0,"",IF(ISNUMBER(G101),G101/E101,IF(ISNUMBER(I101),-ABS(I101)/E101,IF(ISNUMBER(H101),0,IF(AND(ISNUMBER(F101),ISNUMBER(E101),E101&gt;0,F101&gt;E101),(F101-E101)/E101,IF(AND(ISNUMBER(F101),ISNUMBER(E101),E101&gt;0,F101=E101),0,IF(AND(ISNUMBER(F101),ISNUMBER(E101),E101&gt;0,F101=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K101" s="50" t="str">
+        <x:f>IF(A101="","",IF(AND(ISNUMBER(E101),E101=0,OR(ISNUMBER(SEARCH("Free",D101&amp;"")),AND(ISNUMBER(F101),F101=0))),"Subscription",IF(ISNUMBER(G101),"Profit",IF(ISNUMBER(I101),"Loss",IF(ISNUMBER(H101),"Draw",IF(AND(ISNUMBER(F101),ISNUMBER(E101),E101&gt;0,F101&gt;E101),"Profit",IF(AND(ISNUMBER(F101),ISNUMBER(E101),E101&gt;0,F101=E101),"Draw",IF(AND(ISNUMBER(F101),ISNUMBER(E101),E101&gt;0,F101=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L101" s="50"/>
       <x:c r="M101" s="58"/>
       <x:c r="N101" s="58"/>
@@ -4740,8 +5128,12 @@
       <x:c r="G102" s="58"/>
       <x:c r="H102" s="58"/>
       <x:c r="I102" s="58"/>
-      <x:c r="J102" s="60"/>
-      <x:c r="K102" s="50"/>
+      <x:c r="J102" s="60" t="str">
+        <x:f>IF(A102="","",IF(K102="Subscription","",IF(E102=0,"",IF(ISNUMBER(G102),G102/E102,IF(ISNUMBER(I102),-ABS(I102)/E102,IF(ISNUMBER(H102),0,IF(AND(ISNUMBER(F102),ISNUMBER(E102),E102&gt;0,F102&gt;E102),(F102-E102)/E102,IF(AND(ISNUMBER(F102),ISNUMBER(E102),E102&gt;0,F102=E102),0,IF(AND(ISNUMBER(F102),ISNUMBER(E102),E102&gt;0,F102=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K102" s="50" t="str">
+        <x:f>IF(A102="","",IF(AND(ISNUMBER(E102),E102=0,OR(ISNUMBER(SEARCH("Free",D102&amp;"")),AND(ISNUMBER(F102),F102=0))),"Subscription",IF(ISNUMBER(G102),"Profit",IF(ISNUMBER(I102),"Loss",IF(ISNUMBER(H102),"Draw",IF(AND(ISNUMBER(F102),ISNUMBER(E102),E102&gt;0,F102&gt;E102),"Profit",IF(AND(ISNUMBER(F102),ISNUMBER(E102),E102&gt;0,F102=E102),"Draw",IF(AND(ISNUMBER(F102),ISNUMBER(E102),E102&gt;0,F102=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L102" s="50"/>
       <x:c r="M102" s="58"/>
       <x:c r="N102" s="58"/>
@@ -4773,8 +5165,12 @@
       <x:c r="G103" s="58"/>
       <x:c r="H103" s="58"/>
       <x:c r="I103" s="58"/>
-      <x:c r="J103" s="60"/>
-      <x:c r="K103" s="50"/>
+      <x:c r="J103" s="60" t="str">
+        <x:f>IF(A103="","",IF(K103="Subscription","",IF(E103=0,"",IF(ISNUMBER(G103),G103/E103,IF(ISNUMBER(I103),-ABS(I103)/E103,IF(ISNUMBER(H103),0,IF(AND(ISNUMBER(F103),ISNUMBER(E103),E103&gt;0,F103&gt;E103),(F103-E103)/E103,IF(AND(ISNUMBER(F103),ISNUMBER(E103),E103&gt;0,F103=E103),0,IF(AND(ISNUMBER(F103),ISNUMBER(E103),E103&gt;0,F103=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K103" s="50" t="str">
+        <x:f>IF(A103="","",IF(AND(ISNUMBER(E103),E103=0,OR(ISNUMBER(SEARCH("Free",D103&amp;"")),AND(ISNUMBER(F103),F103=0))),"Subscription",IF(ISNUMBER(G103),"Profit",IF(ISNUMBER(I103),"Loss",IF(ISNUMBER(H103),"Draw",IF(AND(ISNUMBER(F103),ISNUMBER(E103),E103&gt;0,F103&gt;E103),"Profit",IF(AND(ISNUMBER(F103),ISNUMBER(E103),E103&gt;0,F103=E103),"Draw",IF(AND(ISNUMBER(F103),ISNUMBER(E103),E103&gt;0,F103=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L103" s="50"/>
       <x:c r="M103" s="58"/>
       <x:c r="N103" s="58"/>
@@ -4806,8 +5202,12 @@
       <x:c r="G104" s="58"/>
       <x:c r="H104" s="58"/>
       <x:c r="I104" s="58"/>
-      <x:c r="J104" s="60"/>
-      <x:c r="K104" s="50"/>
+      <x:c r="J104" s="60" t="str">
+        <x:f>IF(A104="","",IF(K104="Subscription","",IF(E104=0,"",IF(ISNUMBER(G104),G104/E104,IF(ISNUMBER(I104),-ABS(I104)/E104,IF(ISNUMBER(H104),0,IF(AND(ISNUMBER(F104),ISNUMBER(E104),E104&gt;0,F104&gt;E104),(F104-E104)/E104,IF(AND(ISNUMBER(F104),ISNUMBER(E104),E104&gt;0,F104=E104),0,IF(AND(ISNUMBER(F104),ISNUMBER(E104),E104&gt;0,F104=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K104" s="50" t="str">
+        <x:f>IF(A104="","",IF(AND(ISNUMBER(E104),E104=0,OR(ISNUMBER(SEARCH("Free",D104&amp;"")),AND(ISNUMBER(F104),F104=0))),"Subscription",IF(ISNUMBER(G104),"Profit",IF(ISNUMBER(I104),"Loss",IF(ISNUMBER(H104),"Draw",IF(AND(ISNUMBER(F104),ISNUMBER(E104),E104&gt;0,F104&gt;E104),"Profit",IF(AND(ISNUMBER(F104),ISNUMBER(E104),E104&gt;0,F104=E104),"Draw",IF(AND(ISNUMBER(F104),ISNUMBER(E104),E104&gt;0,F104=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L104" s="50"/>
       <x:c r="M104" s="58"/>
       <x:c r="N104" s="58"/>
@@ -4839,8 +5239,12 @@
       <x:c r="G105" s="58"/>
       <x:c r="H105" s="58"/>
       <x:c r="I105" s="58"/>
-      <x:c r="J105" s="60"/>
-      <x:c r="K105" s="50"/>
+      <x:c r="J105" s="60" t="str">
+        <x:f>IF(A105="","",IF(K105="Subscription","",IF(E105=0,"",IF(ISNUMBER(G105),G105/E105,IF(ISNUMBER(I105),-ABS(I105)/E105,IF(ISNUMBER(H105),0,IF(AND(ISNUMBER(F105),ISNUMBER(E105),E105&gt;0,F105&gt;E105),(F105-E105)/E105,IF(AND(ISNUMBER(F105),ISNUMBER(E105),E105&gt;0,F105=E105),0,IF(AND(ISNUMBER(F105),ISNUMBER(E105),E105&gt;0,F105=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K105" s="50" t="str">
+        <x:f>IF(A105="","",IF(AND(ISNUMBER(E105),E105=0,OR(ISNUMBER(SEARCH("Free",D105&amp;"")),AND(ISNUMBER(F105),F105=0))),"Subscription",IF(ISNUMBER(G105),"Profit",IF(ISNUMBER(I105),"Loss",IF(ISNUMBER(H105),"Draw",IF(AND(ISNUMBER(F105),ISNUMBER(E105),E105&gt;0,F105&gt;E105),"Profit",IF(AND(ISNUMBER(F105),ISNUMBER(E105),E105&gt;0,F105=E105),"Draw",IF(AND(ISNUMBER(F105),ISNUMBER(E105),E105&gt;0,F105=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L105" s="50"/>
       <x:c r="M105" s="58"/>
       <x:c r="N105" s="58"/>
@@ -4872,8 +5276,12 @@
       <x:c r="G106" s="58"/>
       <x:c r="H106" s="58"/>
       <x:c r="I106" s="58"/>
-      <x:c r="J106" s="60"/>
-      <x:c r="K106" s="50"/>
+      <x:c r="J106" s="60" t="str">
+        <x:f>IF(A106="","",IF(K106="Subscription","",IF(E106=0,"",IF(ISNUMBER(G106),G106/E106,IF(ISNUMBER(I106),-ABS(I106)/E106,IF(ISNUMBER(H106),0,IF(AND(ISNUMBER(F106),ISNUMBER(E106),E106&gt;0,F106&gt;E106),(F106-E106)/E106,IF(AND(ISNUMBER(F106),ISNUMBER(E106),E106&gt;0,F106=E106),0,IF(AND(ISNUMBER(F106),ISNUMBER(E106),E106&gt;0,F106=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K106" s="50" t="str">
+        <x:f>IF(A106="","",IF(AND(ISNUMBER(E106),E106=0,OR(ISNUMBER(SEARCH("Free",D106&amp;"")),AND(ISNUMBER(F106),F106=0))),"Subscription",IF(ISNUMBER(G106),"Profit",IF(ISNUMBER(I106),"Loss",IF(ISNUMBER(H106),"Draw",IF(AND(ISNUMBER(F106),ISNUMBER(E106),E106&gt;0,F106&gt;E106),"Profit",IF(AND(ISNUMBER(F106),ISNUMBER(E106),E106&gt;0,F106=E106),"Draw",IF(AND(ISNUMBER(F106),ISNUMBER(E106),E106&gt;0,F106=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L106" s="50"/>
       <x:c r="M106" s="58"/>
       <x:c r="N106" s="58"/>
@@ -4905,8 +5313,12 @@
       <x:c r="G107" s="58"/>
       <x:c r="H107" s="58"/>
       <x:c r="I107" s="58"/>
-      <x:c r="J107" s="60"/>
-      <x:c r="K107" s="50"/>
+      <x:c r="J107" s="60" t="str">
+        <x:f>IF(A107="","",IF(K107="Subscription","",IF(E107=0,"",IF(ISNUMBER(G107),G107/E107,IF(ISNUMBER(I107),-ABS(I107)/E107,IF(ISNUMBER(H107),0,IF(AND(ISNUMBER(F107),ISNUMBER(E107),E107&gt;0,F107&gt;E107),(F107-E107)/E107,IF(AND(ISNUMBER(F107),ISNUMBER(E107),E107&gt;0,F107=E107),0,IF(AND(ISNUMBER(F107),ISNUMBER(E107),E107&gt;0,F107=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K107" s="50" t="str">
+        <x:f>IF(A107="","",IF(AND(ISNUMBER(E107),E107=0,OR(ISNUMBER(SEARCH("Free",D107&amp;"")),AND(ISNUMBER(F107),F107=0))),"Subscription",IF(ISNUMBER(G107),"Profit",IF(ISNUMBER(I107),"Loss",IF(ISNUMBER(H107),"Draw",IF(AND(ISNUMBER(F107),ISNUMBER(E107),E107&gt;0,F107&gt;E107),"Profit",IF(AND(ISNUMBER(F107),ISNUMBER(E107),E107&gt;0,F107=E107),"Draw",IF(AND(ISNUMBER(F107),ISNUMBER(E107),E107&gt;0,F107=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L107" s="50"/>
       <x:c r="M107" s="58"/>
       <x:c r="N107" s="58"/>
@@ -4938,8 +5350,12 @@
       <x:c r="G108" s="58"/>
       <x:c r="H108" s="58"/>
       <x:c r="I108" s="58"/>
-      <x:c r="J108" s="60"/>
-      <x:c r="K108" s="50"/>
+      <x:c r="J108" s="60" t="str">
+        <x:f>IF(A108="","",IF(K108="Subscription","",IF(E108=0,"",IF(ISNUMBER(G108),G108/E108,IF(ISNUMBER(I108),-ABS(I108)/E108,IF(ISNUMBER(H108),0,IF(AND(ISNUMBER(F108),ISNUMBER(E108),E108&gt;0,F108&gt;E108),(F108-E108)/E108,IF(AND(ISNUMBER(F108),ISNUMBER(E108),E108&gt;0,F108=E108),0,IF(AND(ISNUMBER(F108),ISNUMBER(E108),E108&gt;0,F108=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K108" s="50" t="str">
+        <x:f>IF(A108="","",IF(AND(ISNUMBER(E108),E108=0,OR(ISNUMBER(SEARCH("Free",D108&amp;"")),AND(ISNUMBER(F108),F108=0))),"Subscription",IF(ISNUMBER(G108),"Profit",IF(ISNUMBER(I108),"Loss",IF(ISNUMBER(H108),"Draw",IF(AND(ISNUMBER(F108),ISNUMBER(E108),E108&gt;0,F108&gt;E108),"Profit",IF(AND(ISNUMBER(F108),ISNUMBER(E108),E108&gt;0,F108=E108),"Draw",IF(AND(ISNUMBER(F108),ISNUMBER(E108),E108&gt;0,F108=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L108" s="50"/>
       <x:c r="M108" s="58"/>
       <x:c r="N108" s="58"/>
@@ -4971,8 +5387,12 @@
       <x:c r="G109" s="58"/>
       <x:c r="H109" s="58"/>
       <x:c r="I109" s="58"/>
-      <x:c r="J109" s="60"/>
-      <x:c r="K109" s="50"/>
+      <x:c r="J109" s="60" t="str">
+        <x:f>IF(A109="","",IF(K109="Subscription","",IF(E109=0,"",IF(ISNUMBER(G109),G109/E109,IF(ISNUMBER(I109),-ABS(I109)/E109,IF(ISNUMBER(H109),0,IF(AND(ISNUMBER(F109),ISNUMBER(E109),E109&gt;0,F109&gt;E109),(F109-E109)/E109,IF(AND(ISNUMBER(F109),ISNUMBER(E109),E109&gt;0,F109=E109),0,IF(AND(ISNUMBER(F109),ISNUMBER(E109),E109&gt;0,F109=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K109" s="50" t="str">
+        <x:f>IF(A109="","",IF(AND(ISNUMBER(E109),E109=0,OR(ISNUMBER(SEARCH("Free",D109&amp;"")),AND(ISNUMBER(F109),F109=0))),"Subscription",IF(ISNUMBER(G109),"Profit",IF(ISNUMBER(I109),"Loss",IF(ISNUMBER(H109),"Draw",IF(AND(ISNUMBER(F109),ISNUMBER(E109),E109&gt;0,F109&gt;E109),"Profit",IF(AND(ISNUMBER(F109),ISNUMBER(E109),E109&gt;0,F109=E109),"Draw",IF(AND(ISNUMBER(F109),ISNUMBER(E109),E109&gt;0,F109=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L109" s="50"/>
       <x:c r="M109" s="58"/>
       <x:c r="N109" s="58"/>
@@ -5004,8 +5424,12 @@
       <x:c r="G110" s="58"/>
       <x:c r="H110" s="58"/>
       <x:c r="I110" s="58"/>
-      <x:c r="J110" s="60"/>
-      <x:c r="K110" s="50"/>
+      <x:c r="J110" s="60" t="str">
+        <x:f>IF(A110="","",IF(K110="Subscription","",IF(E110=0,"",IF(ISNUMBER(G110),G110/E110,IF(ISNUMBER(I110),-ABS(I110)/E110,IF(ISNUMBER(H110),0,IF(AND(ISNUMBER(F110),ISNUMBER(E110),E110&gt;0,F110&gt;E110),(F110-E110)/E110,IF(AND(ISNUMBER(F110),ISNUMBER(E110),E110&gt;0,F110=E110),0,IF(AND(ISNUMBER(F110),ISNUMBER(E110),E110&gt;0,F110=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K110" s="50" t="str">
+        <x:f>IF(A110="","",IF(AND(ISNUMBER(E110),E110=0,OR(ISNUMBER(SEARCH("Free",D110&amp;"")),AND(ISNUMBER(F110),F110=0))),"Subscription",IF(ISNUMBER(G110),"Profit",IF(ISNUMBER(I110),"Loss",IF(ISNUMBER(H110),"Draw",IF(AND(ISNUMBER(F110),ISNUMBER(E110),E110&gt;0,F110&gt;E110),"Profit",IF(AND(ISNUMBER(F110),ISNUMBER(E110),E110&gt;0,F110=E110),"Draw",IF(AND(ISNUMBER(F110),ISNUMBER(E110),E110&gt;0,F110=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L110" s="50"/>
       <x:c r="M110" s="58"/>
       <x:c r="N110" s="58"/>
@@ -5037,8 +5461,12 @@
       <x:c r="G111" s="58"/>
       <x:c r="H111" s="58"/>
       <x:c r="I111" s="58"/>
-      <x:c r="J111" s="60"/>
-      <x:c r="K111" s="50"/>
+      <x:c r="J111" s="60" t="str">
+        <x:f>IF(A111="","",IF(K111="Subscription","",IF(E111=0,"",IF(ISNUMBER(G111),G111/E111,IF(ISNUMBER(I111),-ABS(I111)/E111,IF(ISNUMBER(H111),0,IF(AND(ISNUMBER(F111),ISNUMBER(E111),E111&gt;0,F111&gt;E111),(F111-E111)/E111,IF(AND(ISNUMBER(F111),ISNUMBER(E111),E111&gt;0,F111=E111),0,IF(AND(ISNUMBER(F111),ISNUMBER(E111),E111&gt;0,F111=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K111" s="50" t="str">
+        <x:f>IF(A111="","",IF(AND(ISNUMBER(E111),E111=0,OR(ISNUMBER(SEARCH("Free",D111&amp;"")),AND(ISNUMBER(F111),F111=0))),"Subscription",IF(ISNUMBER(G111),"Profit",IF(ISNUMBER(I111),"Loss",IF(ISNUMBER(H111),"Draw",IF(AND(ISNUMBER(F111),ISNUMBER(E111),E111&gt;0,F111&gt;E111),"Profit",IF(AND(ISNUMBER(F111),ISNUMBER(E111),E111&gt;0,F111=E111),"Draw",IF(AND(ISNUMBER(F111),ISNUMBER(E111),E111&gt;0,F111=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L111" s="50"/>
       <x:c r="M111" s="58"/>
       <x:c r="N111" s="58"/>
@@ -5070,8 +5498,12 @@
       <x:c r="G112" s="58"/>
       <x:c r="H112" s="58"/>
       <x:c r="I112" s="58"/>
-      <x:c r="J112" s="60"/>
-      <x:c r="K112" s="50"/>
+      <x:c r="J112" s="60" t="str">
+        <x:f>IF(A112="","",IF(K112="Subscription","",IF(E112=0,"",IF(ISNUMBER(G112),G112/E112,IF(ISNUMBER(I112),-ABS(I112)/E112,IF(ISNUMBER(H112),0,IF(AND(ISNUMBER(F112),ISNUMBER(E112),E112&gt;0,F112&gt;E112),(F112-E112)/E112,IF(AND(ISNUMBER(F112),ISNUMBER(E112),E112&gt;0,F112=E112),0,IF(AND(ISNUMBER(F112),ISNUMBER(E112),E112&gt;0,F112=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K112" s="50" t="str">
+        <x:f>IF(A112="","",IF(AND(ISNUMBER(E112),E112=0,OR(ISNUMBER(SEARCH("Free",D112&amp;"")),AND(ISNUMBER(F112),F112=0))),"Subscription",IF(ISNUMBER(G112),"Profit",IF(ISNUMBER(I112),"Loss",IF(ISNUMBER(H112),"Draw",IF(AND(ISNUMBER(F112),ISNUMBER(E112),E112&gt;0,F112&gt;E112),"Profit",IF(AND(ISNUMBER(F112),ISNUMBER(E112),E112&gt;0,F112=E112),"Draw",IF(AND(ISNUMBER(F112),ISNUMBER(E112),E112&gt;0,F112=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L112" s="50"/>
       <x:c r="M112" s="58"/>
       <x:c r="N112" s="58"/>
@@ -5103,8 +5535,12 @@
       <x:c r="G113" s="58"/>
       <x:c r="H113" s="58"/>
       <x:c r="I113" s="58"/>
-      <x:c r="J113" s="60"/>
-      <x:c r="K113" s="50"/>
+      <x:c r="J113" s="60" t="str">
+        <x:f>IF(A113="","",IF(K113="Subscription","",IF(E113=0,"",IF(ISNUMBER(G113),G113/E113,IF(ISNUMBER(I113),-ABS(I113)/E113,IF(ISNUMBER(H113),0,IF(AND(ISNUMBER(F113),ISNUMBER(E113),E113&gt;0,F113&gt;E113),(F113-E113)/E113,IF(AND(ISNUMBER(F113),ISNUMBER(E113),E113&gt;0,F113=E113),0,IF(AND(ISNUMBER(F113),ISNUMBER(E113),E113&gt;0,F113=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K113" s="50" t="str">
+        <x:f>IF(A113="","",IF(AND(ISNUMBER(E113),E113=0,OR(ISNUMBER(SEARCH("Free",D113&amp;"")),AND(ISNUMBER(F113),F113=0))),"Subscription",IF(ISNUMBER(G113),"Profit",IF(ISNUMBER(I113),"Loss",IF(ISNUMBER(H113),"Draw",IF(AND(ISNUMBER(F113),ISNUMBER(E113),E113&gt;0,F113&gt;E113),"Profit",IF(AND(ISNUMBER(F113),ISNUMBER(E113),E113&gt;0,F113=E113),"Draw",IF(AND(ISNUMBER(F113),ISNUMBER(E113),E113&gt;0,F113=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L113" s="50"/>
       <x:c r="M113" s="58"/>
       <x:c r="N113" s="58"/>
@@ -5136,8 +5572,12 @@
       <x:c r="G114" s="58"/>
       <x:c r="H114" s="58"/>
       <x:c r="I114" s="58"/>
-      <x:c r="J114" s="60"/>
-      <x:c r="K114" s="50"/>
+      <x:c r="J114" s="60" t="str">
+        <x:f>IF(A114="","",IF(K114="Subscription","",IF(E114=0,"",IF(ISNUMBER(G114),G114/E114,IF(ISNUMBER(I114),-ABS(I114)/E114,IF(ISNUMBER(H114),0,IF(AND(ISNUMBER(F114),ISNUMBER(E114),E114&gt;0,F114&gt;E114),(F114-E114)/E114,IF(AND(ISNUMBER(F114),ISNUMBER(E114),E114&gt;0,F114=E114),0,IF(AND(ISNUMBER(F114),ISNUMBER(E114),E114&gt;0,F114=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K114" s="50" t="str">
+        <x:f>IF(A114="","",IF(AND(ISNUMBER(E114),E114=0,OR(ISNUMBER(SEARCH("Free",D114&amp;"")),AND(ISNUMBER(F114),F114=0))),"Subscription",IF(ISNUMBER(G114),"Profit",IF(ISNUMBER(I114),"Loss",IF(ISNUMBER(H114),"Draw",IF(AND(ISNUMBER(F114),ISNUMBER(E114),E114&gt;0,F114&gt;E114),"Profit",IF(AND(ISNUMBER(F114),ISNUMBER(E114),E114&gt;0,F114=E114),"Draw",IF(AND(ISNUMBER(F114),ISNUMBER(E114),E114&gt;0,F114=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L114" s="50"/>
       <x:c r="M114" s="58"/>
       <x:c r="N114" s="58"/>
@@ -5169,8 +5609,12 @@
       <x:c r="G115" s="58"/>
       <x:c r="H115" s="58"/>
       <x:c r="I115" s="58"/>
-      <x:c r="J115" s="60"/>
-      <x:c r="K115" s="50"/>
+      <x:c r="J115" s="60" t="str">
+        <x:f>IF(A115="","",IF(K115="Subscription","",IF(E115=0,"",IF(ISNUMBER(G115),G115/E115,IF(ISNUMBER(I115),-ABS(I115)/E115,IF(ISNUMBER(H115),0,IF(AND(ISNUMBER(F115),ISNUMBER(E115),E115&gt;0,F115&gt;E115),(F115-E115)/E115,IF(AND(ISNUMBER(F115),ISNUMBER(E115),E115&gt;0,F115=E115),0,IF(AND(ISNUMBER(F115),ISNUMBER(E115),E115&gt;0,F115=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K115" s="50" t="str">
+        <x:f>IF(A115="","",IF(AND(ISNUMBER(E115),E115=0,OR(ISNUMBER(SEARCH("Free",D115&amp;"")),AND(ISNUMBER(F115),F115=0))),"Subscription",IF(ISNUMBER(G115),"Profit",IF(ISNUMBER(I115),"Loss",IF(ISNUMBER(H115),"Draw",IF(AND(ISNUMBER(F115),ISNUMBER(E115),E115&gt;0,F115&gt;E115),"Profit",IF(AND(ISNUMBER(F115),ISNUMBER(E115),E115&gt;0,F115=E115),"Draw",IF(AND(ISNUMBER(F115),ISNUMBER(E115),E115&gt;0,F115=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L115" s="50"/>
       <x:c r="M115" s="58"/>
       <x:c r="N115" s="58"/>
@@ -5202,8 +5646,12 @@
       <x:c r="G116" s="58"/>
       <x:c r="H116" s="58"/>
       <x:c r="I116" s="58"/>
-      <x:c r="J116" s="60"/>
-      <x:c r="K116" s="50"/>
+      <x:c r="J116" s="60" t="str">
+        <x:f>IF(A116="","",IF(K116="Subscription","",IF(E116=0,"",IF(ISNUMBER(G116),G116/E116,IF(ISNUMBER(I116),-ABS(I116)/E116,IF(ISNUMBER(H116),0,IF(AND(ISNUMBER(F116),ISNUMBER(E116),E116&gt;0,F116&gt;E116),(F116-E116)/E116,IF(AND(ISNUMBER(F116),ISNUMBER(E116),E116&gt;0,F116=E116),0,IF(AND(ISNUMBER(F116),ISNUMBER(E116),E116&gt;0,F116=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K116" s="50" t="str">
+        <x:f>IF(A116="","",IF(AND(ISNUMBER(E116),E116=0,OR(ISNUMBER(SEARCH("Free",D116&amp;"")),AND(ISNUMBER(F116),F116=0))),"Subscription",IF(ISNUMBER(G116),"Profit",IF(ISNUMBER(I116),"Loss",IF(ISNUMBER(H116),"Draw",IF(AND(ISNUMBER(F116),ISNUMBER(E116),E116&gt;0,F116&gt;E116),"Profit",IF(AND(ISNUMBER(F116),ISNUMBER(E116),E116&gt;0,F116=E116),"Draw",IF(AND(ISNUMBER(F116),ISNUMBER(E116),E116&gt;0,F116=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L116" s="50"/>
       <x:c r="M116" s="58"/>
       <x:c r="N116" s="58"/>
@@ -5235,8 +5683,12 @@
       <x:c r="G117" s="58"/>
       <x:c r="H117" s="58"/>
       <x:c r="I117" s="58"/>
-      <x:c r="J117" s="60"/>
-      <x:c r="K117" s="50"/>
+      <x:c r="J117" s="60" t="str">
+        <x:f>IF(A117="","",IF(K117="Subscription","",IF(E117=0,"",IF(ISNUMBER(G117),G117/E117,IF(ISNUMBER(I117),-ABS(I117)/E117,IF(ISNUMBER(H117),0,IF(AND(ISNUMBER(F117),ISNUMBER(E117),E117&gt;0,F117&gt;E117),(F117-E117)/E117,IF(AND(ISNUMBER(F117),ISNUMBER(E117),E117&gt;0,F117=E117),0,IF(AND(ISNUMBER(F117),ISNUMBER(E117),E117&gt;0,F117=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K117" s="50" t="str">
+        <x:f>IF(A117="","",IF(AND(ISNUMBER(E117),E117=0,OR(ISNUMBER(SEARCH("Free",D117&amp;"")),AND(ISNUMBER(F117),F117=0))),"Subscription",IF(ISNUMBER(G117),"Profit",IF(ISNUMBER(I117),"Loss",IF(ISNUMBER(H117),"Draw",IF(AND(ISNUMBER(F117),ISNUMBER(E117),E117&gt;0,F117&gt;E117),"Profit",IF(AND(ISNUMBER(F117),ISNUMBER(E117),E117&gt;0,F117=E117),"Draw",IF(AND(ISNUMBER(F117),ISNUMBER(E117),E117&gt;0,F117=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L117" s="50"/>
       <x:c r="M117" s="58"/>
       <x:c r="N117" s="58"/>
@@ -5268,8 +5720,12 @@
       <x:c r="G118" s="58"/>
       <x:c r="H118" s="58"/>
       <x:c r="I118" s="58"/>
-      <x:c r="J118" s="60"/>
-      <x:c r="K118" s="50"/>
+      <x:c r="J118" s="60" t="str">
+        <x:f>IF(A118="","",IF(K118="Subscription","",IF(E118=0,"",IF(ISNUMBER(G118),G118/E118,IF(ISNUMBER(I118),-ABS(I118)/E118,IF(ISNUMBER(H118),0,IF(AND(ISNUMBER(F118),ISNUMBER(E118),E118&gt;0,F118&gt;E118),(F118-E118)/E118,IF(AND(ISNUMBER(F118),ISNUMBER(E118),E118&gt;0,F118=E118),0,IF(AND(ISNUMBER(F118),ISNUMBER(E118),E118&gt;0,F118=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K118" s="50" t="str">
+        <x:f>IF(A118="","",IF(AND(ISNUMBER(E118),E118=0,OR(ISNUMBER(SEARCH("Free",D118&amp;"")),AND(ISNUMBER(F118),F118=0))),"Subscription",IF(ISNUMBER(G118),"Profit",IF(ISNUMBER(I118),"Loss",IF(ISNUMBER(H118),"Draw",IF(AND(ISNUMBER(F118),ISNUMBER(E118),E118&gt;0,F118&gt;E118),"Profit",IF(AND(ISNUMBER(F118),ISNUMBER(E118),E118&gt;0,F118=E118),"Draw",IF(AND(ISNUMBER(F118),ISNUMBER(E118),E118&gt;0,F118=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L118" s="50"/>
       <x:c r="M118" s="58"/>
       <x:c r="N118" s="58"/>
@@ -5301,8 +5757,12 @@
       <x:c r="G119" s="58"/>
       <x:c r="H119" s="58"/>
       <x:c r="I119" s="58"/>
-      <x:c r="J119" s="60"/>
-      <x:c r="K119" s="50"/>
+      <x:c r="J119" s="60" t="str">
+        <x:f>IF(A119="","",IF(K119="Subscription","",IF(E119=0,"",IF(ISNUMBER(G119),G119/E119,IF(ISNUMBER(I119),-ABS(I119)/E119,IF(ISNUMBER(H119),0,IF(AND(ISNUMBER(F119),ISNUMBER(E119),E119&gt;0,F119&gt;E119),(F119-E119)/E119,IF(AND(ISNUMBER(F119),ISNUMBER(E119),E119&gt;0,F119=E119),0,IF(AND(ISNUMBER(F119),ISNUMBER(E119),E119&gt;0,F119=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K119" s="50" t="str">
+        <x:f>IF(A119="","",IF(AND(ISNUMBER(E119),E119=0,OR(ISNUMBER(SEARCH("Free",D119&amp;"")),AND(ISNUMBER(F119),F119=0))),"Subscription",IF(ISNUMBER(G119),"Profit",IF(ISNUMBER(I119),"Loss",IF(ISNUMBER(H119),"Draw",IF(AND(ISNUMBER(F119),ISNUMBER(E119),E119&gt;0,F119&gt;E119),"Profit",IF(AND(ISNUMBER(F119),ISNUMBER(E119),E119&gt;0,F119=E119),"Draw",IF(AND(ISNUMBER(F119),ISNUMBER(E119),E119&gt;0,F119=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L119" s="50"/>
       <x:c r="M119" s="58"/>
       <x:c r="N119" s="58"/>
@@ -5334,8 +5794,12 @@
       <x:c r="G120" s="58"/>
       <x:c r="H120" s="58"/>
       <x:c r="I120" s="58"/>
-      <x:c r="J120" s="60"/>
-      <x:c r="K120" s="50"/>
+      <x:c r="J120" s="60" t="str">
+        <x:f>IF(A120="","",IF(K120="Subscription","",IF(E120=0,"",IF(ISNUMBER(G120),G120/E120,IF(ISNUMBER(I120),-ABS(I120)/E120,IF(ISNUMBER(H120),0,IF(AND(ISNUMBER(F120),ISNUMBER(E120),E120&gt;0,F120&gt;E120),(F120-E120)/E120,IF(AND(ISNUMBER(F120),ISNUMBER(E120),E120&gt;0,F120=E120),0,IF(AND(ISNUMBER(F120),ISNUMBER(E120),E120&gt;0,F120=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K120" s="50" t="str">
+        <x:f>IF(A120="","",IF(AND(ISNUMBER(E120),E120=0,OR(ISNUMBER(SEARCH("Free",D120&amp;"")),AND(ISNUMBER(F120),F120=0))),"Subscription",IF(ISNUMBER(G120),"Profit",IF(ISNUMBER(I120),"Loss",IF(ISNUMBER(H120),"Draw",IF(AND(ISNUMBER(F120),ISNUMBER(E120),E120&gt;0,F120&gt;E120),"Profit",IF(AND(ISNUMBER(F120),ISNUMBER(E120),E120&gt;0,F120=E120),"Draw",IF(AND(ISNUMBER(F120),ISNUMBER(E120),E120&gt;0,F120=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L120" s="50"/>
       <x:c r="M120" s="58"/>
       <x:c r="N120" s="58"/>
@@ -5367,8 +5831,12 @@
       <x:c r="G121" s="58"/>
       <x:c r="H121" s="58"/>
       <x:c r="I121" s="58"/>
-      <x:c r="J121" s="60"/>
-      <x:c r="K121" s="50"/>
+      <x:c r="J121" s="60" t="str">
+        <x:f>IF(A121="","",IF(K121="Subscription","",IF(E121=0,"",IF(ISNUMBER(G121),G121/E121,IF(ISNUMBER(I121),-ABS(I121)/E121,IF(ISNUMBER(H121),0,IF(AND(ISNUMBER(F121),ISNUMBER(E121),E121&gt;0,F121&gt;E121),(F121-E121)/E121,IF(AND(ISNUMBER(F121),ISNUMBER(E121),E121&gt;0,F121=E121),0,IF(AND(ISNUMBER(F121),ISNUMBER(E121),E121&gt;0,F121=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K121" s="50" t="str">
+        <x:f>IF(A121="","",IF(AND(ISNUMBER(E121),E121=0,OR(ISNUMBER(SEARCH("Free",D121&amp;"")),AND(ISNUMBER(F121),F121=0))),"Subscription",IF(ISNUMBER(G121),"Profit",IF(ISNUMBER(I121),"Loss",IF(ISNUMBER(H121),"Draw",IF(AND(ISNUMBER(F121),ISNUMBER(E121),E121&gt;0,F121&gt;E121),"Profit",IF(AND(ISNUMBER(F121),ISNUMBER(E121),E121&gt;0,F121=E121),"Draw",IF(AND(ISNUMBER(F121),ISNUMBER(E121),E121&gt;0,F121=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L121" s="50"/>
       <x:c r="M121" s="58"/>
       <x:c r="N121" s="58"/>
@@ -5400,8 +5868,12 @@
       <x:c r="G122" s="58"/>
       <x:c r="H122" s="58"/>
       <x:c r="I122" s="58"/>
-      <x:c r="J122" s="60"/>
-      <x:c r="K122" s="50"/>
+      <x:c r="J122" s="60" t="str">
+        <x:f>IF(A122="","",IF(K122="Subscription","",IF(E122=0,"",IF(ISNUMBER(G122),G122/E122,IF(ISNUMBER(I122),-ABS(I122)/E122,IF(ISNUMBER(H122),0,IF(AND(ISNUMBER(F122),ISNUMBER(E122),E122&gt;0,F122&gt;E122),(F122-E122)/E122,IF(AND(ISNUMBER(F122),ISNUMBER(E122),E122&gt;0,F122=E122),0,IF(AND(ISNUMBER(F122),ISNUMBER(E122),E122&gt;0,F122=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K122" s="50" t="str">
+        <x:f>IF(A122="","",IF(AND(ISNUMBER(E122),E122=0,OR(ISNUMBER(SEARCH("Free",D122&amp;"")),AND(ISNUMBER(F122),F122=0))),"Subscription",IF(ISNUMBER(G122),"Profit",IF(ISNUMBER(I122),"Loss",IF(ISNUMBER(H122),"Draw",IF(AND(ISNUMBER(F122),ISNUMBER(E122),E122&gt;0,F122&gt;E122),"Profit",IF(AND(ISNUMBER(F122),ISNUMBER(E122),E122&gt;0,F122=E122),"Draw",IF(AND(ISNUMBER(F122),ISNUMBER(E122),E122&gt;0,F122=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L122" s="50"/>
       <x:c r="M122" s="58"/>
       <x:c r="N122" s="58"/>
@@ -5433,8 +5905,12 @@
       <x:c r="G123" s="58"/>
       <x:c r="H123" s="58"/>
       <x:c r="I123" s="58"/>
-      <x:c r="J123" s="60"/>
-      <x:c r="K123" s="50"/>
+      <x:c r="J123" s="60" t="str">
+        <x:f>IF(A123="","",IF(K123="Subscription","",IF(E123=0,"",IF(ISNUMBER(G123),G123/E123,IF(ISNUMBER(I123),-ABS(I123)/E123,IF(ISNUMBER(H123),0,IF(AND(ISNUMBER(F123),ISNUMBER(E123),E123&gt;0,F123&gt;E123),(F123-E123)/E123,IF(AND(ISNUMBER(F123),ISNUMBER(E123),E123&gt;0,F123=E123),0,IF(AND(ISNUMBER(F123),ISNUMBER(E123),E123&gt;0,F123=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K123" s="50" t="str">
+        <x:f>IF(A123="","",IF(AND(ISNUMBER(E123),E123=0,OR(ISNUMBER(SEARCH("Free",D123&amp;"")),AND(ISNUMBER(F123),F123=0))),"Subscription",IF(ISNUMBER(G123),"Profit",IF(ISNUMBER(I123),"Loss",IF(ISNUMBER(H123),"Draw",IF(AND(ISNUMBER(F123),ISNUMBER(E123),E123&gt;0,F123&gt;E123),"Profit",IF(AND(ISNUMBER(F123),ISNUMBER(E123),E123&gt;0,F123=E123),"Draw",IF(AND(ISNUMBER(F123),ISNUMBER(E123),E123&gt;0,F123=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L123" s="50"/>
       <x:c r="M123" s="58"/>
       <x:c r="N123" s="58"/>
@@ -5466,8 +5942,12 @@
       <x:c r="G124" s="58"/>
       <x:c r="H124" s="58"/>
       <x:c r="I124" s="58"/>
-      <x:c r="J124" s="60"/>
-      <x:c r="K124" s="50"/>
+      <x:c r="J124" s="60" t="str">
+        <x:f>IF(A124="","",IF(K124="Subscription","",IF(E124=0,"",IF(ISNUMBER(G124),G124/E124,IF(ISNUMBER(I124),-ABS(I124)/E124,IF(ISNUMBER(H124),0,IF(AND(ISNUMBER(F124),ISNUMBER(E124),E124&gt;0,F124&gt;E124),(F124-E124)/E124,IF(AND(ISNUMBER(F124),ISNUMBER(E124),E124&gt;0,F124=E124),0,IF(AND(ISNUMBER(F124),ISNUMBER(E124),E124&gt;0,F124=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K124" s="50" t="str">
+        <x:f>IF(A124="","",IF(AND(ISNUMBER(E124),E124=0,OR(ISNUMBER(SEARCH("Free",D124&amp;"")),AND(ISNUMBER(F124),F124=0))),"Subscription",IF(ISNUMBER(G124),"Profit",IF(ISNUMBER(I124),"Loss",IF(ISNUMBER(H124),"Draw",IF(AND(ISNUMBER(F124),ISNUMBER(E124),E124&gt;0,F124&gt;E124),"Profit",IF(AND(ISNUMBER(F124),ISNUMBER(E124),E124&gt;0,F124=E124),"Draw",IF(AND(ISNUMBER(F124),ISNUMBER(E124),E124&gt;0,F124=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L124" s="50"/>
       <x:c r="M124" s="58"/>
       <x:c r="N124" s="58"/>
@@ -5499,8 +5979,12 @@
       <x:c r="G125" s="58"/>
       <x:c r="H125" s="58"/>
       <x:c r="I125" s="58"/>
-      <x:c r="J125" s="60"/>
-      <x:c r="K125" s="50"/>
+      <x:c r="J125" s="60" t="str">
+        <x:f>IF(A125="","",IF(K125="Subscription","",IF(E125=0,"",IF(ISNUMBER(G125),G125/E125,IF(ISNUMBER(I125),-ABS(I125)/E125,IF(ISNUMBER(H125),0,IF(AND(ISNUMBER(F125),ISNUMBER(E125),E125&gt;0,F125&gt;E125),(F125-E125)/E125,IF(AND(ISNUMBER(F125),ISNUMBER(E125),E125&gt;0,F125=E125),0,IF(AND(ISNUMBER(F125),ISNUMBER(E125),E125&gt;0,F125=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K125" s="50" t="str">
+        <x:f>IF(A125="","",IF(AND(ISNUMBER(E125),E125=0,OR(ISNUMBER(SEARCH("Free",D125&amp;"")),AND(ISNUMBER(F125),F125=0))),"Subscription",IF(ISNUMBER(G125),"Profit",IF(ISNUMBER(I125),"Loss",IF(ISNUMBER(H125),"Draw",IF(AND(ISNUMBER(F125),ISNUMBER(E125),E125&gt;0,F125&gt;E125),"Profit",IF(AND(ISNUMBER(F125),ISNUMBER(E125),E125&gt;0,F125=E125),"Draw",IF(AND(ISNUMBER(F125),ISNUMBER(E125),E125&gt;0,F125=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L125" s="50"/>
       <x:c r="M125" s="58"/>
       <x:c r="N125" s="58"/>
@@ -5532,8 +6016,12 @@
       <x:c r="G126" s="58"/>
       <x:c r="H126" s="58"/>
       <x:c r="I126" s="58"/>
-      <x:c r="J126" s="60"/>
-      <x:c r="K126" s="50"/>
+      <x:c r="J126" s="60" t="str">
+        <x:f>IF(A126="","",IF(K126="Subscription","",IF(E126=0,"",IF(ISNUMBER(G126),G126/E126,IF(ISNUMBER(I126),-ABS(I126)/E126,IF(ISNUMBER(H126),0,IF(AND(ISNUMBER(F126),ISNUMBER(E126),E126&gt;0,F126&gt;E126),(F126-E126)/E126,IF(AND(ISNUMBER(F126),ISNUMBER(E126),E126&gt;0,F126=E126),0,IF(AND(ISNUMBER(F126),ISNUMBER(E126),E126&gt;0,F126=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K126" s="50" t="str">
+        <x:f>IF(A126="","",IF(AND(ISNUMBER(E126),E126=0,OR(ISNUMBER(SEARCH("Free",D126&amp;"")),AND(ISNUMBER(F126),F126=0))),"Subscription",IF(ISNUMBER(G126),"Profit",IF(ISNUMBER(I126),"Loss",IF(ISNUMBER(H126),"Draw",IF(AND(ISNUMBER(F126),ISNUMBER(E126),E126&gt;0,F126&gt;E126),"Profit",IF(AND(ISNUMBER(F126),ISNUMBER(E126),E126&gt;0,F126=E126),"Draw",IF(AND(ISNUMBER(F126),ISNUMBER(E126),E126&gt;0,F126=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L126" s="50"/>
       <x:c r="M126" s="58"/>
       <x:c r="N126" s="58"/>
@@ -5565,8 +6053,12 @@
       <x:c r="G127" s="58"/>
       <x:c r="H127" s="58"/>
       <x:c r="I127" s="58"/>
-      <x:c r="J127" s="60"/>
-      <x:c r="K127" s="50"/>
+      <x:c r="J127" s="60" t="str">
+        <x:f>IF(A127="","",IF(K127="Subscription","",IF(E127=0,"",IF(ISNUMBER(G127),G127/E127,IF(ISNUMBER(I127),-ABS(I127)/E127,IF(ISNUMBER(H127),0,IF(AND(ISNUMBER(F127),ISNUMBER(E127),E127&gt;0,F127&gt;E127),(F127-E127)/E127,IF(AND(ISNUMBER(F127),ISNUMBER(E127),E127&gt;0,F127=E127),0,IF(AND(ISNUMBER(F127),ISNUMBER(E127),E127&gt;0,F127=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K127" s="50" t="str">
+        <x:f>IF(A127="","",IF(AND(ISNUMBER(E127),E127=0,OR(ISNUMBER(SEARCH("Free",D127&amp;"")),AND(ISNUMBER(F127),F127=0))),"Subscription",IF(ISNUMBER(G127),"Profit",IF(ISNUMBER(I127),"Loss",IF(ISNUMBER(H127),"Draw",IF(AND(ISNUMBER(F127),ISNUMBER(E127),E127&gt;0,F127&gt;E127),"Profit",IF(AND(ISNUMBER(F127),ISNUMBER(E127),E127&gt;0,F127=E127),"Draw",IF(AND(ISNUMBER(F127),ISNUMBER(E127),E127&gt;0,F127=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L127" s="50"/>
       <x:c r="M127" s="58"/>
       <x:c r="N127" s="58"/>
@@ -5598,8 +6090,12 @@
       <x:c r="G128" s="58"/>
       <x:c r="H128" s="58"/>
       <x:c r="I128" s="58"/>
-      <x:c r="J128" s="60"/>
-      <x:c r="K128" s="50"/>
+      <x:c r="J128" s="60" t="str">
+        <x:f>IF(A128="","",IF(K128="Subscription","",IF(E128=0,"",IF(ISNUMBER(G128),G128/E128,IF(ISNUMBER(I128),-ABS(I128)/E128,IF(ISNUMBER(H128),0,IF(AND(ISNUMBER(F128),ISNUMBER(E128),E128&gt;0,F128&gt;E128),(F128-E128)/E128,IF(AND(ISNUMBER(F128),ISNUMBER(E128),E128&gt;0,F128=E128),0,IF(AND(ISNUMBER(F128),ISNUMBER(E128),E128&gt;0,F128=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K128" s="50" t="str">
+        <x:f>IF(A128="","",IF(AND(ISNUMBER(E128),E128=0,OR(ISNUMBER(SEARCH("Free",D128&amp;"")),AND(ISNUMBER(F128),F128=0))),"Subscription",IF(ISNUMBER(G128),"Profit",IF(ISNUMBER(I128),"Loss",IF(ISNUMBER(H128),"Draw",IF(AND(ISNUMBER(F128),ISNUMBER(E128),E128&gt;0,F128&gt;E128),"Profit",IF(AND(ISNUMBER(F128),ISNUMBER(E128),E128&gt;0,F128=E128),"Draw",IF(AND(ISNUMBER(F128),ISNUMBER(E128),E128&gt;0,F128=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L128" s="50"/>
       <x:c r="M128" s="58"/>
       <x:c r="N128" s="58"/>
@@ -5631,8 +6127,12 @@
       <x:c r="G129" s="58"/>
       <x:c r="H129" s="58"/>
       <x:c r="I129" s="58"/>
-      <x:c r="J129" s="60"/>
-      <x:c r="K129" s="50"/>
+      <x:c r="J129" s="60" t="str">
+        <x:f>IF(A129="","",IF(K129="Subscription","",IF(E129=0,"",IF(ISNUMBER(G129),G129/E129,IF(ISNUMBER(I129),-ABS(I129)/E129,IF(ISNUMBER(H129),0,IF(AND(ISNUMBER(F129),ISNUMBER(E129),E129&gt;0,F129&gt;E129),(F129-E129)/E129,IF(AND(ISNUMBER(F129),ISNUMBER(E129),E129&gt;0,F129=E129),0,IF(AND(ISNUMBER(F129),ISNUMBER(E129),E129&gt;0,F129=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K129" s="50" t="str">
+        <x:f>IF(A129="","",IF(AND(ISNUMBER(E129),E129=0,OR(ISNUMBER(SEARCH("Free",D129&amp;"")),AND(ISNUMBER(F129),F129=0))),"Subscription",IF(ISNUMBER(G129),"Profit",IF(ISNUMBER(I129),"Loss",IF(ISNUMBER(H129),"Draw",IF(AND(ISNUMBER(F129),ISNUMBER(E129),E129&gt;0,F129&gt;E129),"Profit",IF(AND(ISNUMBER(F129),ISNUMBER(E129),E129&gt;0,F129=E129),"Draw",IF(AND(ISNUMBER(F129),ISNUMBER(E129),E129&gt;0,F129=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L129" s="50"/>
       <x:c r="M129" s="58"/>
       <x:c r="N129" s="58"/>
@@ -5664,8 +6164,12 @@
       <x:c r="G130" s="58"/>
       <x:c r="H130" s="58"/>
       <x:c r="I130" s="58"/>
-      <x:c r="J130" s="60"/>
-      <x:c r="K130" s="50"/>
+      <x:c r="J130" s="60" t="str">
+        <x:f>IF(A130="","",IF(K130="Subscription","",IF(E130=0,"",IF(ISNUMBER(G130),G130/E130,IF(ISNUMBER(I130),-ABS(I130)/E130,IF(ISNUMBER(H130),0,IF(AND(ISNUMBER(F130),ISNUMBER(E130),E130&gt;0,F130&gt;E130),(F130-E130)/E130,IF(AND(ISNUMBER(F130),ISNUMBER(E130),E130&gt;0,F130=E130),0,IF(AND(ISNUMBER(F130),ISNUMBER(E130),E130&gt;0,F130=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K130" s="50" t="str">
+        <x:f>IF(A130="","",IF(AND(ISNUMBER(E130),E130=0,OR(ISNUMBER(SEARCH("Free",D130&amp;"")),AND(ISNUMBER(F130),F130=0))),"Subscription",IF(ISNUMBER(G130),"Profit",IF(ISNUMBER(I130),"Loss",IF(ISNUMBER(H130),"Draw",IF(AND(ISNUMBER(F130),ISNUMBER(E130),E130&gt;0,F130&gt;E130),"Profit",IF(AND(ISNUMBER(F130),ISNUMBER(E130),E130&gt;0,F130=E130),"Draw",IF(AND(ISNUMBER(F130),ISNUMBER(E130),E130&gt;0,F130=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L130" s="50"/>
       <x:c r="M130" s="58"/>
       <x:c r="N130" s="58"/>
@@ -5697,8 +6201,12 @@
       <x:c r="G131" s="58"/>
       <x:c r="H131" s="58"/>
       <x:c r="I131" s="58"/>
-      <x:c r="J131" s="60"/>
-      <x:c r="K131" s="50"/>
+      <x:c r="J131" s="60" t="str">
+        <x:f>IF(A131="","",IF(K131="Subscription","",IF(E131=0,"",IF(ISNUMBER(G131),G131/E131,IF(ISNUMBER(I131),-ABS(I131)/E131,IF(ISNUMBER(H131),0,IF(AND(ISNUMBER(F131),ISNUMBER(E131),E131&gt;0,F131&gt;E131),(F131-E131)/E131,IF(AND(ISNUMBER(F131),ISNUMBER(E131),E131&gt;0,F131=E131),0,IF(AND(ISNUMBER(F131),ISNUMBER(E131),E131&gt;0,F131=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K131" s="50" t="str">
+        <x:f>IF(A131="","",IF(AND(ISNUMBER(E131),E131=0,OR(ISNUMBER(SEARCH("Free",D131&amp;"")),AND(ISNUMBER(F131),F131=0))),"Subscription",IF(ISNUMBER(G131),"Profit",IF(ISNUMBER(I131),"Loss",IF(ISNUMBER(H131),"Draw",IF(AND(ISNUMBER(F131),ISNUMBER(E131),E131&gt;0,F131&gt;E131),"Profit",IF(AND(ISNUMBER(F131),ISNUMBER(E131),E131&gt;0,F131=E131),"Draw",IF(AND(ISNUMBER(F131),ISNUMBER(E131),E131&gt;0,F131=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L131" s="50"/>
       <x:c r="M131" s="58"/>
       <x:c r="N131" s="58"/>
@@ -5730,8 +6238,12 @@
       <x:c r="G132" s="58"/>
       <x:c r="H132" s="58"/>
       <x:c r="I132" s="58"/>
-      <x:c r="J132" s="60"/>
-      <x:c r="K132" s="50"/>
+      <x:c r="J132" s="60" t="str">
+        <x:f>IF(A132="","",IF(K132="Subscription","",IF(E132=0,"",IF(ISNUMBER(G132),G132/E132,IF(ISNUMBER(I132),-ABS(I132)/E132,IF(ISNUMBER(H132),0,IF(AND(ISNUMBER(F132),ISNUMBER(E132),E132&gt;0,F132&gt;E132),(F132-E132)/E132,IF(AND(ISNUMBER(F132),ISNUMBER(E132),E132&gt;0,F132=E132),0,IF(AND(ISNUMBER(F132),ISNUMBER(E132),E132&gt;0,F132=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K132" s="50" t="str">
+        <x:f>IF(A132="","",IF(AND(ISNUMBER(E132),E132=0,OR(ISNUMBER(SEARCH("Free",D132&amp;"")),AND(ISNUMBER(F132),F132=0))),"Subscription",IF(ISNUMBER(G132),"Profit",IF(ISNUMBER(I132),"Loss",IF(ISNUMBER(H132),"Draw",IF(AND(ISNUMBER(F132),ISNUMBER(E132),E132&gt;0,F132&gt;E132),"Profit",IF(AND(ISNUMBER(F132),ISNUMBER(E132),E132&gt;0,F132=E132),"Draw",IF(AND(ISNUMBER(F132),ISNUMBER(E132),E132&gt;0,F132=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L132" s="50"/>
       <x:c r="M132" s="58"/>
       <x:c r="N132" s="58"/>
@@ -5763,8 +6275,12 @@
       <x:c r="G133" s="58"/>
       <x:c r="H133" s="58"/>
       <x:c r="I133" s="58"/>
-      <x:c r="J133" s="60"/>
-      <x:c r="K133" s="50"/>
+      <x:c r="J133" s="60" t="str">
+        <x:f>IF(A133="","",IF(K133="Subscription","",IF(E133=0,"",IF(ISNUMBER(G133),G133/E133,IF(ISNUMBER(I133),-ABS(I133)/E133,IF(ISNUMBER(H133),0,IF(AND(ISNUMBER(F133),ISNUMBER(E133),E133&gt;0,F133&gt;E133),(F133-E133)/E133,IF(AND(ISNUMBER(F133),ISNUMBER(E133),E133&gt;0,F133=E133),0,IF(AND(ISNUMBER(F133),ISNUMBER(E133),E133&gt;0,F133=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K133" s="50" t="str">
+        <x:f>IF(A133="","",IF(AND(ISNUMBER(E133),E133=0,OR(ISNUMBER(SEARCH("Free",D133&amp;"")),AND(ISNUMBER(F133),F133=0))),"Subscription",IF(ISNUMBER(G133),"Profit",IF(ISNUMBER(I133),"Loss",IF(ISNUMBER(H133),"Draw",IF(AND(ISNUMBER(F133),ISNUMBER(E133),E133&gt;0,F133&gt;E133),"Profit",IF(AND(ISNUMBER(F133),ISNUMBER(E133),E133&gt;0,F133=E133),"Draw",IF(AND(ISNUMBER(F133),ISNUMBER(E133),E133&gt;0,F133=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L133" s="50"/>
       <x:c r="M133" s="58"/>
       <x:c r="N133" s="58"/>
@@ -5796,8 +6312,12 @@
       <x:c r="G134" s="58"/>
       <x:c r="H134" s="58"/>
       <x:c r="I134" s="58"/>
-      <x:c r="J134" s="60"/>
-      <x:c r="K134" s="50"/>
+      <x:c r="J134" s="60" t="str">
+        <x:f>IF(A134="","",IF(K134="Subscription","",IF(E134=0,"",IF(ISNUMBER(G134),G134/E134,IF(ISNUMBER(I134),-ABS(I134)/E134,IF(ISNUMBER(H134),0,IF(AND(ISNUMBER(F134),ISNUMBER(E134),E134&gt;0,F134&gt;E134),(F134-E134)/E134,IF(AND(ISNUMBER(F134),ISNUMBER(E134),E134&gt;0,F134=E134),0,IF(AND(ISNUMBER(F134),ISNUMBER(E134),E134&gt;0,F134=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K134" s="50" t="str">
+        <x:f>IF(A134="","",IF(AND(ISNUMBER(E134),E134=0,OR(ISNUMBER(SEARCH("Free",D134&amp;"")),AND(ISNUMBER(F134),F134=0))),"Subscription",IF(ISNUMBER(G134),"Profit",IF(ISNUMBER(I134),"Loss",IF(ISNUMBER(H134),"Draw",IF(AND(ISNUMBER(F134),ISNUMBER(E134),E134&gt;0,F134&gt;E134),"Profit",IF(AND(ISNUMBER(F134),ISNUMBER(E134),E134&gt;0,F134=E134),"Draw",IF(AND(ISNUMBER(F134),ISNUMBER(E134),E134&gt;0,F134=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L134" s="50"/>
       <x:c r="M134" s="58"/>
       <x:c r="N134" s="58"/>
@@ -5829,8 +6349,12 @@
       <x:c r="G135" s="58"/>
       <x:c r="H135" s="58"/>
       <x:c r="I135" s="58"/>
-      <x:c r="J135" s="60"/>
-      <x:c r="K135" s="50"/>
+      <x:c r="J135" s="60" t="str">
+        <x:f>IF(A135="","",IF(K135="Subscription","",IF(E135=0,"",IF(ISNUMBER(G135),G135/E135,IF(ISNUMBER(I135),-ABS(I135)/E135,IF(ISNUMBER(H135),0,IF(AND(ISNUMBER(F135),ISNUMBER(E135),E135&gt;0,F135&gt;E135),(F135-E135)/E135,IF(AND(ISNUMBER(F135),ISNUMBER(E135),E135&gt;0,F135=E135),0,IF(AND(ISNUMBER(F135),ISNUMBER(E135),E135&gt;0,F135=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K135" s="50" t="str">
+        <x:f>IF(A135="","",IF(AND(ISNUMBER(E135),E135=0,OR(ISNUMBER(SEARCH("Free",D135&amp;"")),AND(ISNUMBER(F135),F135=0))),"Subscription",IF(ISNUMBER(G135),"Profit",IF(ISNUMBER(I135),"Loss",IF(ISNUMBER(H135),"Draw",IF(AND(ISNUMBER(F135),ISNUMBER(E135),E135&gt;0,F135&gt;E135),"Profit",IF(AND(ISNUMBER(F135),ISNUMBER(E135),E135&gt;0,F135=E135),"Draw",IF(AND(ISNUMBER(F135),ISNUMBER(E135),E135&gt;0,F135=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L135" s="50"/>
       <x:c r="M135" s="58"/>
       <x:c r="N135" s="58"/>
@@ -5862,8 +6386,12 @@
       <x:c r="G136" s="58"/>
       <x:c r="H136" s="58"/>
       <x:c r="I136" s="58"/>
-      <x:c r="J136" s="60"/>
-      <x:c r="K136" s="50"/>
+      <x:c r="J136" s="60" t="str">
+        <x:f>IF(A136="","",IF(K136="Subscription","",IF(E136=0,"",IF(ISNUMBER(G136),G136/E136,IF(ISNUMBER(I136),-ABS(I136)/E136,IF(ISNUMBER(H136),0,IF(AND(ISNUMBER(F136),ISNUMBER(E136),E136&gt;0,F136&gt;E136),(F136-E136)/E136,IF(AND(ISNUMBER(F136),ISNUMBER(E136),E136&gt;0,F136=E136),0,IF(AND(ISNUMBER(F136),ISNUMBER(E136),E136&gt;0,F136=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K136" s="50" t="str">
+        <x:f>IF(A136="","",IF(AND(ISNUMBER(E136),E136=0,OR(ISNUMBER(SEARCH("Free",D136&amp;"")),AND(ISNUMBER(F136),F136=0))),"Subscription",IF(ISNUMBER(G136),"Profit",IF(ISNUMBER(I136),"Loss",IF(ISNUMBER(H136),"Draw",IF(AND(ISNUMBER(F136),ISNUMBER(E136),E136&gt;0,F136&gt;E136),"Profit",IF(AND(ISNUMBER(F136),ISNUMBER(E136),E136&gt;0,F136=E136),"Draw",IF(AND(ISNUMBER(F136),ISNUMBER(E136),E136&gt;0,F136=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L136" s="50"/>
       <x:c r="M136" s="58"/>
       <x:c r="N136" s="58"/>
@@ -5895,8 +6423,12 @@
       <x:c r="G137" s="58"/>
       <x:c r="H137" s="58"/>
       <x:c r="I137" s="58"/>
-      <x:c r="J137" s="60"/>
-      <x:c r="K137" s="50"/>
+      <x:c r="J137" s="60" t="str">
+        <x:f>IF(A137="","",IF(K137="Subscription","",IF(E137=0,"",IF(ISNUMBER(G137),G137/E137,IF(ISNUMBER(I137),-ABS(I137)/E137,IF(ISNUMBER(H137),0,IF(AND(ISNUMBER(F137),ISNUMBER(E137),E137&gt;0,F137&gt;E137),(F137-E137)/E137,IF(AND(ISNUMBER(F137),ISNUMBER(E137),E137&gt;0,F137=E137),0,IF(AND(ISNUMBER(F137),ISNUMBER(E137),E137&gt;0,F137=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K137" s="50" t="str">
+        <x:f>IF(A137="","",IF(AND(ISNUMBER(E137),E137=0,OR(ISNUMBER(SEARCH("Free",D137&amp;"")),AND(ISNUMBER(F137),F137=0))),"Subscription",IF(ISNUMBER(G137),"Profit",IF(ISNUMBER(I137),"Loss",IF(ISNUMBER(H137),"Draw",IF(AND(ISNUMBER(F137),ISNUMBER(E137),E137&gt;0,F137&gt;E137),"Profit",IF(AND(ISNUMBER(F137),ISNUMBER(E137),E137&gt;0,F137=E137),"Draw",IF(AND(ISNUMBER(F137),ISNUMBER(E137),E137&gt;0,F137=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L137" s="50"/>
       <x:c r="M137" s="58"/>
       <x:c r="N137" s="58"/>
@@ -5928,8 +6460,12 @@
       <x:c r="G138" s="58"/>
       <x:c r="H138" s="58"/>
       <x:c r="I138" s="58"/>
-      <x:c r="J138" s="60"/>
-      <x:c r="K138" s="50"/>
+      <x:c r="J138" s="60" t="str">
+        <x:f>IF(A138="","",IF(K138="Subscription","",IF(E138=0,"",IF(ISNUMBER(G138),G138/E138,IF(ISNUMBER(I138),-ABS(I138)/E138,IF(ISNUMBER(H138),0,IF(AND(ISNUMBER(F138),ISNUMBER(E138),E138&gt;0,F138&gt;E138),(F138-E138)/E138,IF(AND(ISNUMBER(F138),ISNUMBER(E138),E138&gt;0,F138=E138),0,IF(AND(ISNUMBER(F138),ISNUMBER(E138),E138&gt;0,F138=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K138" s="50" t="str">
+        <x:f>IF(A138="","",IF(AND(ISNUMBER(E138),E138=0,OR(ISNUMBER(SEARCH("Free",D138&amp;"")),AND(ISNUMBER(F138),F138=0))),"Subscription",IF(ISNUMBER(G138),"Profit",IF(ISNUMBER(I138),"Loss",IF(ISNUMBER(H138),"Draw",IF(AND(ISNUMBER(F138),ISNUMBER(E138),E138&gt;0,F138&gt;E138),"Profit",IF(AND(ISNUMBER(F138),ISNUMBER(E138),E138&gt;0,F138=E138),"Draw",IF(AND(ISNUMBER(F138),ISNUMBER(E138),E138&gt;0,F138=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L138" s="50"/>
       <x:c r="M138" s="58"/>
       <x:c r="N138" s="58"/>
@@ -5961,8 +6497,12 @@
       <x:c r="G139" s="58"/>
       <x:c r="H139" s="58"/>
       <x:c r="I139" s="58"/>
-      <x:c r="J139" s="60"/>
-      <x:c r="K139" s="50"/>
+      <x:c r="J139" s="60" t="str">
+        <x:f>IF(A139="","",IF(K139="Subscription","",IF(E139=0,"",IF(ISNUMBER(G139),G139/E139,IF(ISNUMBER(I139),-ABS(I139)/E139,IF(ISNUMBER(H139),0,IF(AND(ISNUMBER(F139),ISNUMBER(E139),E139&gt;0,F139&gt;E139),(F139-E139)/E139,IF(AND(ISNUMBER(F139),ISNUMBER(E139),E139&gt;0,F139=E139),0,IF(AND(ISNUMBER(F139),ISNUMBER(E139),E139&gt;0,F139=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K139" s="50" t="str">
+        <x:f>IF(A139="","",IF(AND(ISNUMBER(E139),E139=0,OR(ISNUMBER(SEARCH("Free",D139&amp;"")),AND(ISNUMBER(F139),F139=0))),"Subscription",IF(ISNUMBER(G139),"Profit",IF(ISNUMBER(I139),"Loss",IF(ISNUMBER(H139),"Draw",IF(AND(ISNUMBER(F139),ISNUMBER(E139),E139&gt;0,F139&gt;E139),"Profit",IF(AND(ISNUMBER(F139),ISNUMBER(E139),E139&gt;0,F139=E139),"Draw",IF(AND(ISNUMBER(F139),ISNUMBER(E139),E139&gt;0,F139=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L139" s="50"/>
       <x:c r="M139" s="58"/>
       <x:c r="N139" s="58"/>
@@ -5994,8 +6534,12 @@
       <x:c r="G140" s="58"/>
       <x:c r="H140" s="58"/>
       <x:c r="I140" s="58"/>
-      <x:c r="J140" s="60"/>
-      <x:c r="K140" s="50"/>
+      <x:c r="J140" s="60" t="str">
+        <x:f>IF(A140="","",IF(K140="Subscription","",IF(E140=0,"",IF(ISNUMBER(G140),G140/E140,IF(ISNUMBER(I140),-ABS(I140)/E140,IF(ISNUMBER(H140),0,IF(AND(ISNUMBER(F140),ISNUMBER(E140),E140&gt;0,F140&gt;E140),(F140-E140)/E140,IF(AND(ISNUMBER(F140),ISNUMBER(E140),E140&gt;0,F140=E140),0,IF(AND(ISNUMBER(F140),ISNUMBER(E140),E140&gt;0,F140=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K140" s="50" t="str">
+        <x:f>IF(A140="","",IF(AND(ISNUMBER(E140),E140=0,OR(ISNUMBER(SEARCH("Free",D140&amp;"")),AND(ISNUMBER(F140),F140=0))),"Subscription",IF(ISNUMBER(G140),"Profit",IF(ISNUMBER(I140),"Loss",IF(ISNUMBER(H140),"Draw",IF(AND(ISNUMBER(F140),ISNUMBER(E140),E140&gt;0,F140&gt;E140),"Profit",IF(AND(ISNUMBER(F140),ISNUMBER(E140),E140&gt;0,F140=E140),"Draw",IF(AND(ISNUMBER(F140),ISNUMBER(E140),E140&gt;0,F140=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L140" s="50"/>
       <x:c r="M140" s="58"/>
       <x:c r="N140" s="58"/>
@@ -6027,8 +6571,12 @@
       <x:c r="G141" s="58"/>
       <x:c r="H141" s="58"/>
       <x:c r="I141" s="58"/>
-      <x:c r="J141" s="60"/>
-      <x:c r="K141" s="50"/>
+      <x:c r="J141" s="60" t="str">
+        <x:f>IF(A141="","",IF(K141="Subscription","",IF(E141=0,"",IF(ISNUMBER(G141),G141/E141,IF(ISNUMBER(I141),-ABS(I141)/E141,IF(ISNUMBER(H141),0,IF(AND(ISNUMBER(F141),ISNUMBER(E141),E141&gt;0,F141&gt;E141),(F141-E141)/E141,IF(AND(ISNUMBER(F141),ISNUMBER(E141),E141&gt;0,F141=E141),0,IF(AND(ISNUMBER(F141),ISNUMBER(E141),E141&gt;0,F141=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K141" s="50" t="str">
+        <x:f>IF(A141="","",IF(AND(ISNUMBER(E141),E141=0,OR(ISNUMBER(SEARCH("Free",D141&amp;"")),AND(ISNUMBER(F141),F141=0))),"Subscription",IF(ISNUMBER(G141),"Profit",IF(ISNUMBER(I141),"Loss",IF(ISNUMBER(H141),"Draw",IF(AND(ISNUMBER(F141),ISNUMBER(E141),E141&gt;0,F141&gt;E141),"Profit",IF(AND(ISNUMBER(F141),ISNUMBER(E141),E141&gt;0,F141=E141),"Draw",IF(AND(ISNUMBER(F141),ISNUMBER(E141),E141&gt;0,F141=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L141" s="50"/>
       <x:c r="M141" s="58"/>
       <x:c r="N141" s="58"/>
@@ -6060,8 +6608,12 @@
       <x:c r="G142" s="58"/>
       <x:c r="H142" s="58"/>
       <x:c r="I142" s="58"/>
-      <x:c r="J142" s="60"/>
-      <x:c r="K142" s="50"/>
+      <x:c r="J142" s="60" t="str">
+        <x:f>IF(A142="","",IF(K142="Subscription","",IF(E142=0,"",IF(ISNUMBER(G142),G142/E142,IF(ISNUMBER(I142),-ABS(I142)/E142,IF(ISNUMBER(H142),0,IF(AND(ISNUMBER(F142),ISNUMBER(E142),E142&gt;0,F142&gt;E142),(F142-E142)/E142,IF(AND(ISNUMBER(F142),ISNUMBER(E142),E142&gt;0,F142=E142),0,IF(AND(ISNUMBER(F142),ISNUMBER(E142),E142&gt;0,F142=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K142" s="50" t="str">
+        <x:f>IF(A142="","",IF(AND(ISNUMBER(E142),E142=0,OR(ISNUMBER(SEARCH("Free",D142&amp;"")),AND(ISNUMBER(F142),F142=0))),"Subscription",IF(ISNUMBER(G142),"Profit",IF(ISNUMBER(I142),"Loss",IF(ISNUMBER(H142),"Draw",IF(AND(ISNUMBER(F142),ISNUMBER(E142),E142&gt;0,F142&gt;E142),"Profit",IF(AND(ISNUMBER(F142),ISNUMBER(E142),E142&gt;0,F142=E142),"Draw",IF(AND(ISNUMBER(F142),ISNUMBER(E142),E142&gt;0,F142=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L142" s="50"/>
       <x:c r="M142" s="58"/>
       <x:c r="N142" s="58"/>
@@ -6093,8 +6645,12 @@
       <x:c r="G143" s="58"/>
       <x:c r="H143" s="58"/>
       <x:c r="I143" s="58"/>
-      <x:c r="J143" s="60"/>
-      <x:c r="K143" s="50"/>
+      <x:c r="J143" s="60" t="str">
+        <x:f>IF(A143="","",IF(K143="Subscription","",IF(E143=0,"",IF(ISNUMBER(G143),G143/E143,IF(ISNUMBER(I143),-ABS(I143)/E143,IF(ISNUMBER(H143),0,IF(AND(ISNUMBER(F143),ISNUMBER(E143),E143&gt;0,F143&gt;E143),(F143-E143)/E143,IF(AND(ISNUMBER(F143),ISNUMBER(E143),E143&gt;0,F143=E143),0,IF(AND(ISNUMBER(F143),ISNUMBER(E143),E143&gt;0,F143=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K143" s="50" t="str">
+        <x:f>IF(A143="","",IF(AND(ISNUMBER(E143),E143=0,OR(ISNUMBER(SEARCH("Free",D143&amp;"")),AND(ISNUMBER(F143),F143=0))),"Subscription",IF(ISNUMBER(G143),"Profit",IF(ISNUMBER(I143),"Loss",IF(ISNUMBER(H143),"Draw",IF(AND(ISNUMBER(F143),ISNUMBER(E143),E143&gt;0,F143&gt;E143),"Profit",IF(AND(ISNUMBER(F143),ISNUMBER(E143),E143&gt;0,F143=E143),"Draw",IF(AND(ISNUMBER(F143),ISNUMBER(E143),E143&gt;0,F143=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L143" s="50"/>
       <x:c r="M143" s="58"/>
       <x:c r="N143" s="58"/>
@@ -6126,8 +6682,12 @@
       <x:c r="G144" s="58"/>
       <x:c r="H144" s="58"/>
       <x:c r="I144" s="58"/>
-      <x:c r="J144" s="60"/>
-      <x:c r="K144" s="50"/>
+      <x:c r="J144" s="60" t="str">
+        <x:f>IF(A144="","",IF(K144="Subscription","",IF(E144=0,"",IF(ISNUMBER(G144),G144/E144,IF(ISNUMBER(I144),-ABS(I144)/E144,IF(ISNUMBER(H144),0,IF(AND(ISNUMBER(F144),ISNUMBER(E144),E144&gt;0,F144&gt;E144),(F144-E144)/E144,IF(AND(ISNUMBER(F144),ISNUMBER(E144),E144&gt;0,F144=E144),0,IF(AND(ISNUMBER(F144),ISNUMBER(E144),E144&gt;0,F144=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K144" s="50" t="str">
+        <x:f>IF(A144="","",IF(AND(ISNUMBER(E144),E144=0,OR(ISNUMBER(SEARCH("Free",D144&amp;"")),AND(ISNUMBER(F144),F144=0))),"Subscription",IF(ISNUMBER(G144),"Profit",IF(ISNUMBER(I144),"Loss",IF(ISNUMBER(H144),"Draw",IF(AND(ISNUMBER(F144),ISNUMBER(E144),E144&gt;0,F144&gt;E144),"Profit",IF(AND(ISNUMBER(F144),ISNUMBER(E144),E144&gt;0,F144=E144),"Draw",IF(AND(ISNUMBER(F144),ISNUMBER(E144),E144&gt;0,F144=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L144" s="50"/>
       <x:c r="M144" s="58"/>
       <x:c r="N144" s="58"/>
@@ -6159,8 +6719,12 @@
       <x:c r="G145" s="58"/>
       <x:c r="H145" s="58"/>
       <x:c r="I145" s="58"/>
-      <x:c r="J145" s="60"/>
-      <x:c r="K145" s="50"/>
+      <x:c r="J145" s="60" t="str">
+        <x:f>IF(A145="","",IF(K145="Subscription","",IF(E145=0,"",IF(ISNUMBER(G145),G145/E145,IF(ISNUMBER(I145),-ABS(I145)/E145,IF(ISNUMBER(H145),0,IF(AND(ISNUMBER(F145),ISNUMBER(E145),E145&gt;0,F145&gt;E145),(F145-E145)/E145,IF(AND(ISNUMBER(F145),ISNUMBER(E145),E145&gt;0,F145=E145),0,IF(AND(ISNUMBER(F145),ISNUMBER(E145),E145&gt;0,F145=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K145" s="50" t="str">
+        <x:f>IF(A145="","",IF(AND(ISNUMBER(E145),E145=0,OR(ISNUMBER(SEARCH("Free",D145&amp;"")),AND(ISNUMBER(F145),F145=0))),"Subscription",IF(ISNUMBER(G145),"Profit",IF(ISNUMBER(I145),"Loss",IF(ISNUMBER(H145),"Draw",IF(AND(ISNUMBER(F145),ISNUMBER(E145),E145&gt;0,F145&gt;E145),"Profit",IF(AND(ISNUMBER(F145),ISNUMBER(E145),E145&gt;0,F145=E145),"Draw",IF(AND(ISNUMBER(F145),ISNUMBER(E145),E145&gt;0,F145=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L145" s="50"/>
       <x:c r="M145" s="58"/>
       <x:c r="N145" s="58"/>
@@ -6192,8 +6756,12 @@
       <x:c r="G146" s="58"/>
       <x:c r="H146" s="58"/>
       <x:c r="I146" s="58"/>
-      <x:c r="J146" s="60"/>
-      <x:c r="K146" s="50"/>
+      <x:c r="J146" s="60" t="str">
+        <x:f>IF(A146="","",IF(K146="Subscription","",IF(E146=0,"",IF(ISNUMBER(G146),G146/E146,IF(ISNUMBER(I146),-ABS(I146)/E146,IF(ISNUMBER(H146),0,IF(AND(ISNUMBER(F146),ISNUMBER(E146),E146&gt;0,F146&gt;E146),(F146-E146)/E146,IF(AND(ISNUMBER(F146),ISNUMBER(E146),E146&gt;0,F146=E146),0,IF(AND(ISNUMBER(F146),ISNUMBER(E146),E146&gt;0,F146=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K146" s="50" t="str">
+        <x:f>IF(A146="","",IF(AND(ISNUMBER(E146),E146=0,OR(ISNUMBER(SEARCH("Free",D146&amp;"")),AND(ISNUMBER(F146),F146=0))),"Subscription",IF(ISNUMBER(G146),"Profit",IF(ISNUMBER(I146),"Loss",IF(ISNUMBER(H146),"Draw",IF(AND(ISNUMBER(F146),ISNUMBER(E146),E146&gt;0,F146&gt;E146),"Profit",IF(AND(ISNUMBER(F146),ISNUMBER(E146),E146&gt;0,F146=E146),"Draw",IF(AND(ISNUMBER(F146),ISNUMBER(E146),E146&gt;0,F146=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L146" s="50"/>
       <x:c r="M146" s="58"/>
       <x:c r="N146" s="58"/>
@@ -6225,8 +6793,12 @@
       <x:c r="G147" s="58"/>
       <x:c r="H147" s="58"/>
       <x:c r="I147" s="58"/>
-      <x:c r="J147" s="60"/>
-      <x:c r="K147" s="50"/>
+      <x:c r="J147" s="60" t="str">
+        <x:f>IF(A147="","",IF(K147="Subscription","",IF(E147=0,"",IF(ISNUMBER(G147),G147/E147,IF(ISNUMBER(I147),-ABS(I147)/E147,IF(ISNUMBER(H147),0,IF(AND(ISNUMBER(F147),ISNUMBER(E147),E147&gt;0,F147&gt;E147),(F147-E147)/E147,IF(AND(ISNUMBER(F147),ISNUMBER(E147),E147&gt;0,F147=E147),0,IF(AND(ISNUMBER(F147),ISNUMBER(E147),E147&gt;0,F147=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K147" s="50" t="str">
+        <x:f>IF(A147="","",IF(AND(ISNUMBER(E147),E147=0,OR(ISNUMBER(SEARCH("Free",D147&amp;"")),AND(ISNUMBER(F147),F147=0))),"Subscription",IF(ISNUMBER(G147),"Profit",IF(ISNUMBER(I147),"Loss",IF(ISNUMBER(H147),"Draw",IF(AND(ISNUMBER(F147),ISNUMBER(E147),E147&gt;0,F147&gt;E147),"Profit",IF(AND(ISNUMBER(F147),ISNUMBER(E147),E147&gt;0,F147=E147),"Draw",IF(AND(ISNUMBER(F147),ISNUMBER(E147),E147&gt;0,F147=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L147" s="50"/>
       <x:c r="M147" s="58"/>
       <x:c r="N147" s="58"/>
@@ -6258,8 +6830,12 @@
       <x:c r="G148" s="58"/>
       <x:c r="H148" s="58"/>
       <x:c r="I148" s="58"/>
-      <x:c r="J148" s="60"/>
-      <x:c r="K148" s="50"/>
+      <x:c r="J148" s="60" t="str">
+        <x:f>IF(A148="","",IF(K148="Subscription","",IF(E148=0,"",IF(ISNUMBER(G148),G148/E148,IF(ISNUMBER(I148),-ABS(I148)/E148,IF(ISNUMBER(H148),0,IF(AND(ISNUMBER(F148),ISNUMBER(E148),E148&gt;0,F148&gt;E148),(F148-E148)/E148,IF(AND(ISNUMBER(F148),ISNUMBER(E148),E148&gt;0,F148=E148),0,IF(AND(ISNUMBER(F148),ISNUMBER(E148),E148&gt;0,F148=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K148" s="50" t="str">
+        <x:f>IF(A148="","",IF(AND(ISNUMBER(E148),E148=0,OR(ISNUMBER(SEARCH("Free",D148&amp;"")),AND(ISNUMBER(F148),F148=0))),"Subscription",IF(ISNUMBER(G148),"Profit",IF(ISNUMBER(I148),"Loss",IF(ISNUMBER(H148),"Draw",IF(AND(ISNUMBER(F148),ISNUMBER(E148),E148&gt;0,F148&gt;E148),"Profit",IF(AND(ISNUMBER(F148),ISNUMBER(E148),E148&gt;0,F148=E148),"Draw",IF(AND(ISNUMBER(F148),ISNUMBER(E148),E148&gt;0,F148=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L148" s="50"/>
       <x:c r="M148" s="58"/>
       <x:c r="N148" s="58"/>
@@ -6291,8 +6867,12 @@
       <x:c r="G149" s="58"/>
       <x:c r="H149" s="58"/>
       <x:c r="I149" s="58"/>
-      <x:c r="J149" s="60"/>
-      <x:c r="K149" s="50"/>
+      <x:c r="J149" s="60" t="str">
+        <x:f>IF(A149="","",IF(K149="Subscription","",IF(E149=0,"",IF(ISNUMBER(G149),G149/E149,IF(ISNUMBER(I149),-ABS(I149)/E149,IF(ISNUMBER(H149),0,IF(AND(ISNUMBER(F149),ISNUMBER(E149),E149&gt;0,F149&gt;E149),(F149-E149)/E149,IF(AND(ISNUMBER(F149),ISNUMBER(E149),E149&gt;0,F149=E149),0,IF(AND(ISNUMBER(F149),ISNUMBER(E149),E149&gt;0,F149=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K149" s="50" t="str">
+        <x:f>IF(A149="","",IF(AND(ISNUMBER(E149),E149=0,OR(ISNUMBER(SEARCH("Free",D149&amp;"")),AND(ISNUMBER(F149),F149=0))),"Subscription",IF(ISNUMBER(G149),"Profit",IF(ISNUMBER(I149),"Loss",IF(ISNUMBER(H149),"Draw",IF(AND(ISNUMBER(F149),ISNUMBER(E149),E149&gt;0,F149&gt;E149),"Profit",IF(AND(ISNUMBER(F149),ISNUMBER(E149),E149&gt;0,F149=E149),"Draw",IF(AND(ISNUMBER(F149),ISNUMBER(E149),E149&gt;0,F149=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L149" s="50"/>
       <x:c r="M149" s="58"/>
       <x:c r="N149" s="58"/>
@@ -6324,8 +6904,12 @@
       <x:c r="G150" s="58"/>
       <x:c r="H150" s="58"/>
       <x:c r="I150" s="58"/>
-      <x:c r="J150" s="60"/>
-      <x:c r="K150" s="50"/>
+      <x:c r="J150" s="60" t="str">
+        <x:f>IF(A150="","",IF(K150="Subscription","",IF(E150=0,"",IF(ISNUMBER(G150),G150/E150,IF(ISNUMBER(I150),-ABS(I150)/E150,IF(ISNUMBER(H150),0,IF(AND(ISNUMBER(F150),ISNUMBER(E150),E150&gt;0,F150&gt;E150),(F150-E150)/E150,IF(AND(ISNUMBER(F150),ISNUMBER(E150),E150&gt;0,F150=E150),0,IF(AND(ISNUMBER(F150),ISNUMBER(E150),E150&gt;0,F150=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K150" s="50" t="str">
+        <x:f>IF(A150="","",IF(AND(ISNUMBER(E150),E150=0,OR(ISNUMBER(SEARCH("Free",D150&amp;"")),AND(ISNUMBER(F150),F150=0))),"Subscription",IF(ISNUMBER(G150),"Profit",IF(ISNUMBER(I150),"Loss",IF(ISNUMBER(H150),"Draw",IF(AND(ISNUMBER(F150),ISNUMBER(E150),E150&gt;0,F150&gt;E150),"Profit",IF(AND(ISNUMBER(F150),ISNUMBER(E150),E150&gt;0,F150=E150),"Draw",IF(AND(ISNUMBER(F150),ISNUMBER(E150),E150&gt;0,F150=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L150" s="50"/>
       <x:c r="M150" s="58"/>
       <x:c r="N150" s="58"/>
@@ -6357,8 +6941,12 @@
       <x:c r="G151" s="58"/>
       <x:c r="H151" s="58"/>
       <x:c r="I151" s="58"/>
-      <x:c r="J151" s="60"/>
-      <x:c r="K151" s="50"/>
+      <x:c r="J151" s="60" t="str">
+        <x:f>IF(A151="","",IF(K151="Subscription","",IF(E151=0,"",IF(ISNUMBER(G151),G151/E151,IF(ISNUMBER(I151),-ABS(I151)/E151,IF(ISNUMBER(H151),0,IF(AND(ISNUMBER(F151),ISNUMBER(E151),E151&gt;0,F151&gt;E151),(F151-E151)/E151,IF(AND(ISNUMBER(F151),ISNUMBER(E151),E151&gt;0,F151=E151),0,IF(AND(ISNUMBER(F151),ISNUMBER(E151),E151&gt;0,F151=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K151" s="50" t="str">
+        <x:f>IF(A151="","",IF(AND(ISNUMBER(E151),E151=0,OR(ISNUMBER(SEARCH("Free",D151&amp;"")),AND(ISNUMBER(F151),F151=0))),"Subscription",IF(ISNUMBER(G151),"Profit",IF(ISNUMBER(I151),"Loss",IF(ISNUMBER(H151),"Draw",IF(AND(ISNUMBER(F151),ISNUMBER(E151),E151&gt;0,F151&gt;E151),"Profit",IF(AND(ISNUMBER(F151),ISNUMBER(E151),E151&gt;0,F151=E151),"Draw",IF(AND(ISNUMBER(F151),ISNUMBER(E151),E151&gt;0,F151=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L151" s="50"/>
       <x:c r="M151" s="58"/>
       <x:c r="N151" s="58"/>
@@ -6390,8 +6978,12 @@
       <x:c r="G152" s="58"/>
       <x:c r="H152" s="58"/>
       <x:c r="I152" s="58"/>
-      <x:c r="J152" s="60"/>
-      <x:c r="K152" s="50"/>
+      <x:c r="J152" s="60" t="str">
+        <x:f>IF(A152="","",IF(K152="Subscription","",IF(E152=0,"",IF(ISNUMBER(G152),G152/E152,IF(ISNUMBER(I152),-ABS(I152)/E152,IF(ISNUMBER(H152),0,IF(AND(ISNUMBER(F152),ISNUMBER(E152),E152&gt;0,F152&gt;E152),(F152-E152)/E152,IF(AND(ISNUMBER(F152),ISNUMBER(E152),E152&gt;0,F152=E152),0,IF(AND(ISNUMBER(F152),ISNUMBER(E152),E152&gt;0,F152=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K152" s="50" t="str">
+        <x:f>IF(A152="","",IF(AND(ISNUMBER(E152),E152=0,OR(ISNUMBER(SEARCH("Free",D152&amp;"")),AND(ISNUMBER(F152),F152=0))),"Subscription",IF(ISNUMBER(G152),"Profit",IF(ISNUMBER(I152),"Loss",IF(ISNUMBER(H152),"Draw",IF(AND(ISNUMBER(F152),ISNUMBER(E152),E152&gt;0,F152&gt;E152),"Profit",IF(AND(ISNUMBER(F152),ISNUMBER(E152),E152&gt;0,F152=E152),"Draw",IF(AND(ISNUMBER(F152),ISNUMBER(E152),E152&gt;0,F152=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L152" s="50"/>
       <x:c r="M152" s="58"/>
       <x:c r="N152" s="58"/>
@@ -6423,8 +7015,12 @@
       <x:c r="G153" s="58"/>
       <x:c r="H153" s="58"/>
       <x:c r="I153" s="58"/>
-      <x:c r="J153" s="60"/>
-      <x:c r="K153" s="50"/>
+      <x:c r="J153" s="60" t="str">
+        <x:f>IF(A153="","",IF(K153="Subscription","",IF(E153=0,"",IF(ISNUMBER(G153),G153/E153,IF(ISNUMBER(I153),-ABS(I153)/E153,IF(ISNUMBER(H153),0,IF(AND(ISNUMBER(F153),ISNUMBER(E153),E153&gt;0,F153&gt;E153),(F153-E153)/E153,IF(AND(ISNUMBER(F153),ISNUMBER(E153),E153&gt;0,F153=E153),0,IF(AND(ISNUMBER(F153),ISNUMBER(E153),E153&gt;0,F153=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K153" s="50" t="str">
+        <x:f>IF(A153="","",IF(AND(ISNUMBER(E153),E153=0,OR(ISNUMBER(SEARCH("Free",D153&amp;"")),AND(ISNUMBER(F153),F153=0))),"Subscription",IF(ISNUMBER(G153),"Profit",IF(ISNUMBER(I153),"Loss",IF(ISNUMBER(H153),"Draw",IF(AND(ISNUMBER(F153),ISNUMBER(E153),E153&gt;0,F153&gt;E153),"Profit",IF(AND(ISNUMBER(F153),ISNUMBER(E153),E153&gt;0,F153=E153),"Draw",IF(AND(ISNUMBER(F153),ISNUMBER(E153),E153&gt;0,F153=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L153" s="50"/>
       <x:c r="M153" s="58"/>
       <x:c r="N153" s="58"/>
@@ -6456,8 +7052,12 @@
       <x:c r="G154" s="58"/>
       <x:c r="H154" s="58"/>
       <x:c r="I154" s="58"/>
-      <x:c r="J154" s="60"/>
-      <x:c r="K154" s="50"/>
+      <x:c r="J154" s="60" t="str">
+        <x:f>IF(A154="","",IF(K154="Subscription","",IF(E154=0,"",IF(ISNUMBER(G154),G154/E154,IF(ISNUMBER(I154),-ABS(I154)/E154,IF(ISNUMBER(H154),0,IF(AND(ISNUMBER(F154),ISNUMBER(E154),E154&gt;0,F154&gt;E154),(F154-E154)/E154,IF(AND(ISNUMBER(F154),ISNUMBER(E154),E154&gt;0,F154=E154),0,IF(AND(ISNUMBER(F154),ISNUMBER(E154),E154&gt;0,F154=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K154" s="50" t="str">
+        <x:f>IF(A154="","",IF(AND(ISNUMBER(E154),E154=0,OR(ISNUMBER(SEARCH("Free",D154&amp;"")),AND(ISNUMBER(F154),F154=0))),"Subscription",IF(ISNUMBER(G154),"Profit",IF(ISNUMBER(I154),"Loss",IF(ISNUMBER(H154),"Draw",IF(AND(ISNUMBER(F154),ISNUMBER(E154),E154&gt;0,F154&gt;E154),"Profit",IF(AND(ISNUMBER(F154),ISNUMBER(E154),E154&gt;0,F154=E154),"Draw",IF(AND(ISNUMBER(F154),ISNUMBER(E154),E154&gt;0,F154=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L154" s="50"/>
       <x:c r="M154" s="58"/>
       <x:c r="N154" s="58"/>
@@ -6489,8 +7089,12 @@
       <x:c r="G155" s="58"/>
       <x:c r="H155" s="58"/>
       <x:c r="I155" s="58"/>
-      <x:c r="J155" s="60"/>
-      <x:c r="K155" s="50"/>
+      <x:c r="J155" s="60" t="str">
+        <x:f>IF(A155="","",IF(K155="Subscription","",IF(E155=0,"",IF(ISNUMBER(G155),G155/E155,IF(ISNUMBER(I155),-ABS(I155)/E155,IF(ISNUMBER(H155),0,IF(AND(ISNUMBER(F155),ISNUMBER(E155),E155&gt;0,F155&gt;E155),(F155-E155)/E155,IF(AND(ISNUMBER(F155),ISNUMBER(E155),E155&gt;0,F155=E155),0,IF(AND(ISNUMBER(F155),ISNUMBER(E155),E155&gt;0,F155=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K155" s="50" t="str">
+        <x:f>IF(A155="","",IF(AND(ISNUMBER(E155),E155=0,OR(ISNUMBER(SEARCH("Free",D155&amp;"")),AND(ISNUMBER(F155),F155=0))),"Subscription",IF(ISNUMBER(G155),"Profit",IF(ISNUMBER(I155),"Loss",IF(ISNUMBER(H155),"Draw",IF(AND(ISNUMBER(F155),ISNUMBER(E155),E155&gt;0,F155&gt;E155),"Profit",IF(AND(ISNUMBER(F155),ISNUMBER(E155),E155&gt;0,F155=E155),"Draw",IF(AND(ISNUMBER(F155),ISNUMBER(E155),E155&gt;0,F155=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L155" s="50"/>
       <x:c r="M155" s="58"/>
       <x:c r="N155" s="58"/>
@@ -6522,8 +7126,12 @@
       <x:c r="G156" s="58"/>
       <x:c r="H156" s="58"/>
       <x:c r="I156" s="58"/>
-      <x:c r="J156" s="60"/>
-      <x:c r="K156" s="50"/>
+      <x:c r="J156" s="60" t="str">
+        <x:f>IF(A156="","",IF(K156="Subscription","",IF(E156=0,"",IF(ISNUMBER(G156),G156/E156,IF(ISNUMBER(I156),-ABS(I156)/E156,IF(ISNUMBER(H156),0,IF(AND(ISNUMBER(F156),ISNUMBER(E156),E156&gt;0,F156&gt;E156),(F156-E156)/E156,IF(AND(ISNUMBER(F156),ISNUMBER(E156),E156&gt;0,F156=E156),0,IF(AND(ISNUMBER(F156),ISNUMBER(E156),E156&gt;0,F156=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K156" s="50" t="str">
+        <x:f>IF(A156="","",IF(AND(ISNUMBER(E156),E156=0,OR(ISNUMBER(SEARCH("Free",D156&amp;"")),AND(ISNUMBER(F156),F156=0))),"Subscription",IF(ISNUMBER(G156),"Profit",IF(ISNUMBER(I156),"Loss",IF(ISNUMBER(H156),"Draw",IF(AND(ISNUMBER(F156),ISNUMBER(E156),E156&gt;0,F156&gt;E156),"Profit",IF(AND(ISNUMBER(F156),ISNUMBER(E156),E156&gt;0,F156=E156),"Draw",IF(AND(ISNUMBER(F156),ISNUMBER(E156),E156&gt;0,F156=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L156" s="50"/>
       <x:c r="M156" s="58"/>
       <x:c r="N156" s="58"/>
@@ -6555,8 +7163,12 @@
       <x:c r="G157" s="58"/>
       <x:c r="H157" s="58"/>
       <x:c r="I157" s="58"/>
-      <x:c r="J157" s="60"/>
-      <x:c r="K157" s="50"/>
+      <x:c r="J157" s="60" t="str">
+        <x:f>IF(A157="","",IF(K157="Subscription","",IF(E157=0,"",IF(ISNUMBER(G157),G157/E157,IF(ISNUMBER(I157),-ABS(I157)/E157,IF(ISNUMBER(H157),0,IF(AND(ISNUMBER(F157),ISNUMBER(E157),E157&gt;0,F157&gt;E157),(F157-E157)/E157,IF(AND(ISNUMBER(F157),ISNUMBER(E157),E157&gt;0,F157=E157),0,IF(AND(ISNUMBER(F157),ISNUMBER(E157),E157&gt;0,F157=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K157" s="50" t="str">
+        <x:f>IF(A157="","",IF(AND(ISNUMBER(E157),E157=0,OR(ISNUMBER(SEARCH("Free",D157&amp;"")),AND(ISNUMBER(F157),F157=0))),"Subscription",IF(ISNUMBER(G157),"Profit",IF(ISNUMBER(I157),"Loss",IF(ISNUMBER(H157),"Draw",IF(AND(ISNUMBER(F157),ISNUMBER(E157),E157&gt;0,F157&gt;E157),"Profit",IF(AND(ISNUMBER(F157),ISNUMBER(E157),E157&gt;0,F157=E157),"Draw",IF(AND(ISNUMBER(F157),ISNUMBER(E157),E157&gt;0,F157=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L157" s="50"/>
       <x:c r="M157" s="58"/>
       <x:c r="N157" s="58"/>
@@ -6588,8 +7200,12 @@
       <x:c r="G158" s="58"/>
       <x:c r="H158" s="58"/>
       <x:c r="I158" s="58"/>
-      <x:c r="J158" s="60"/>
-      <x:c r="K158" s="50"/>
+      <x:c r="J158" s="60" t="str">
+        <x:f>IF(A158="","",IF(K158="Subscription","",IF(E158=0,"",IF(ISNUMBER(G158),G158/E158,IF(ISNUMBER(I158),-ABS(I158)/E158,IF(ISNUMBER(H158),0,IF(AND(ISNUMBER(F158),ISNUMBER(E158),E158&gt;0,F158&gt;E158),(F158-E158)/E158,IF(AND(ISNUMBER(F158),ISNUMBER(E158),E158&gt;0,F158=E158),0,IF(AND(ISNUMBER(F158),ISNUMBER(E158),E158&gt;0,F158=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K158" s="50" t="str">
+        <x:f>IF(A158="","",IF(AND(ISNUMBER(E158),E158=0,OR(ISNUMBER(SEARCH("Free",D158&amp;"")),AND(ISNUMBER(F158),F158=0))),"Subscription",IF(ISNUMBER(G158),"Profit",IF(ISNUMBER(I158),"Loss",IF(ISNUMBER(H158),"Draw",IF(AND(ISNUMBER(F158),ISNUMBER(E158),E158&gt;0,F158&gt;E158),"Profit",IF(AND(ISNUMBER(F158),ISNUMBER(E158),E158&gt;0,F158=E158),"Draw",IF(AND(ISNUMBER(F158),ISNUMBER(E158),E158&gt;0,F158=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L158" s="50"/>
       <x:c r="M158" s="58"/>
       <x:c r="N158" s="58"/>
@@ -6621,8 +7237,12 @@
       <x:c r="G159" s="58"/>
       <x:c r="H159" s="58"/>
       <x:c r="I159" s="58"/>
-      <x:c r="J159" s="60"/>
-      <x:c r="K159" s="50"/>
+      <x:c r="J159" s="60" t="str">
+        <x:f>IF(A159="","",IF(K159="Subscription","",IF(E159=0,"",IF(ISNUMBER(G159),G159/E159,IF(ISNUMBER(I159),-ABS(I159)/E159,IF(ISNUMBER(H159),0,IF(AND(ISNUMBER(F159),ISNUMBER(E159),E159&gt;0,F159&gt;E159),(F159-E159)/E159,IF(AND(ISNUMBER(F159),ISNUMBER(E159),E159&gt;0,F159=E159),0,IF(AND(ISNUMBER(F159),ISNUMBER(E159),E159&gt;0,F159=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K159" s="50" t="str">
+        <x:f>IF(A159="","",IF(AND(ISNUMBER(E159),E159=0,OR(ISNUMBER(SEARCH("Free",D159&amp;"")),AND(ISNUMBER(F159),F159=0))),"Subscription",IF(ISNUMBER(G159),"Profit",IF(ISNUMBER(I159),"Loss",IF(ISNUMBER(H159),"Draw",IF(AND(ISNUMBER(F159),ISNUMBER(E159),E159&gt;0,F159&gt;E159),"Profit",IF(AND(ISNUMBER(F159),ISNUMBER(E159),E159&gt;0,F159=E159),"Draw",IF(AND(ISNUMBER(F159),ISNUMBER(E159),E159&gt;0,F159=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L159" s="50"/>
       <x:c r="M159" s="58"/>
       <x:c r="N159" s="58"/>
@@ -6654,8 +7274,12 @@
       <x:c r="G160" s="58"/>
       <x:c r="H160" s="58"/>
       <x:c r="I160" s="58"/>
-      <x:c r="J160" s="60"/>
-      <x:c r="K160" s="50"/>
+      <x:c r="J160" s="60" t="str">
+        <x:f>IF(A160="","",IF(K160="Subscription","",IF(E160=0,"",IF(ISNUMBER(G160),G160/E160,IF(ISNUMBER(I160),-ABS(I160)/E160,IF(ISNUMBER(H160),0,IF(AND(ISNUMBER(F160),ISNUMBER(E160),E160&gt;0,F160&gt;E160),(F160-E160)/E160,IF(AND(ISNUMBER(F160),ISNUMBER(E160),E160&gt;0,F160=E160),0,IF(AND(ISNUMBER(F160),ISNUMBER(E160),E160&gt;0,F160=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K160" s="50" t="str">
+        <x:f>IF(A160="","",IF(AND(ISNUMBER(E160),E160=0,OR(ISNUMBER(SEARCH("Free",D160&amp;"")),AND(ISNUMBER(F160),F160=0))),"Subscription",IF(ISNUMBER(G160),"Profit",IF(ISNUMBER(I160),"Loss",IF(ISNUMBER(H160),"Draw",IF(AND(ISNUMBER(F160),ISNUMBER(E160),E160&gt;0,F160&gt;E160),"Profit",IF(AND(ISNUMBER(F160),ISNUMBER(E160),E160&gt;0,F160=E160),"Draw",IF(AND(ISNUMBER(F160),ISNUMBER(E160),E160&gt;0,F160=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L160" s="50"/>
       <x:c r="M160" s="58"/>
       <x:c r="N160" s="58"/>
@@ -6687,8 +7311,12 @@
       <x:c r="G161" s="58"/>
       <x:c r="H161" s="58"/>
       <x:c r="I161" s="58"/>
-      <x:c r="J161" s="60"/>
-      <x:c r="K161" s="50"/>
+      <x:c r="J161" s="60" t="str">
+        <x:f>IF(A161="","",IF(K161="Subscription","",IF(E161=0,"",IF(ISNUMBER(G161),G161/E161,IF(ISNUMBER(I161),-ABS(I161)/E161,IF(ISNUMBER(H161),0,IF(AND(ISNUMBER(F161),ISNUMBER(E161),E161&gt;0,F161&gt;E161),(F161-E161)/E161,IF(AND(ISNUMBER(F161),ISNUMBER(E161),E161&gt;0,F161=E161),0,IF(AND(ISNUMBER(F161),ISNUMBER(E161),E161&gt;0,F161=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K161" s="50" t="str">
+        <x:f>IF(A161="","",IF(AND(ISNUMBER(E161),E161=0,OR(ISNUMBER(SEARCH("Free",D161&amp;"")),AND(ISNUMBER(F161),F161=0))),"Subscription",IF(ISNUMBER(G161),"Profit",IF(ISNUMBER(I161),"Loss",IF(ISNUMBER(H161),"Draw",IF(AND(ISNUMBER(F161),ISNUMBER(E161),E161&gt;0,F161&gt;E161),"Profit",IF(AND(ISNUMBER(F161),ISNUMBER(E161),E161&gt;0,F161=E161),"Draw",IF(AND(ISNUMBER(F161),ISNUMBER(E161),E161&gt;0,F161=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L161" s="50"/>
       <x:c r="M161" s="58"/>
       <x:c r="N161" s="58"/>
@@ -6720,8 +7348,12 @@
       <x:c r="G162" s="58"/>
       <x:c r="H162" s="58"/>
       <x:c r="I162" s="58"/>
-      <x:c r="J162" s="60"/>
-      <x:c r="K162" s="50"/>
+      <x:c r="J162" s="60" t="str">
+        <x:f>IF(A162="","",IF(K162="Subscription","",IF(E162=0,"",IF(ISNUMBER(G162),G162/E162,IF(ISNUMBER(I162),-ABS(I162)/E162,IF(ISNUMBER(H162),0,IF(AND(ISNUMBER(F162),ISNUMBER(E162),E162&gt;0,F162&gt;E162),(F162-E162)/E162,IF(AND(ISNUMBER(F162),ISNUMBER(E162),E162&gt;0,F162=E162),0,IF(AND(ISNUMBER(F162),ISNUMBER(E162),E162&gt;0,F162=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K162" s="50" t="str">
+        <x:f>IF(A162="","",IF(AND(ISNUMBER(E162),E162=0,OR(ISNUMBER(SEARCH("Free",D162&amp;"")),AND(ISNUMBER(F162),F162=0))),"Subscription",IF(ISNUMBER(G162),"Profit",IF(ISNUMBER(I162),"Loss",IF(ISNUMBER(H162),"Draw",IF(AND(ISNUMBER(F162),ISNUMBER(E162),E162&gt;0,F162&gt;E162),"Profit",IF(AND(ISNUMBER(F162),ISNUMBER(E162),E162&gt;0,F162=E162),"Draw",IF(AND(ISNUMBER(F162),ISNUMBER(E162),E162&gt;0,F162=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L162" s="50"/>
       <x:c r="M162" s="58"/>
       <x:c r="N162" s="58"/>
@@ -6753,8 +7385,12 @@
       <x:c r="G163" s="58"/>
       <x:c r="H163" s="58"/>
       <x:c r="I163" s="58"/>
-      <x:c r="J163" s="60"/>
-      <x:c r="K163" s="50"/>
+      <x:c r="J163" s="60" t="str">
+        <x:f>IF(A163="","",IF(K163="Subscription","",IF(E163=0,"",IF(ISNUMBER(G163),G163/E163,IF(ISNUMBER(I163),-ABS(I163)/E163,IF(ISNUMBER(H163),0,IF(AND(ISNUMBER(F163),ISNUMBER(E163),E163&gt;0,F163&gt;E163),(F163-E163)/E163,IF(AND(ISNUMBER(F163),ISNUMBER(E163),E163&gt;0,F163=E163),0,IF(AND(ISNUMBER(F163),ISNUMBER(E163),E163&gt;0,F163=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K163" s="50" t="str">
+        <x:f>IF(A163="","",IF(AND(ISNUMBER(E163),E163=0,OR(ISNUMBER(SEARCH("Free",D163&amp;"")),AND(ISNUMBER(F163),F163=0))),"Subscription",IF(ISNUMBER(G163),"Profit",IF(ISNUMBER(I163),"Loss",IF(ISNUMBER(H163),"Draw",IF(AND(ISNUMBER(F163),ISNUMBER(E163),E163&gt;0,F163&gt;E163),"Profit",IF(AND(ISNUMBER(F163),ISNUMBER(E163),E163&gt;0,F163=E163),"Draw",IF(AND(ISNUMBER(F163),ISNUMBER(E163),E163&gt;0,F163=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L163" s="50"/>
       <x:c r="M163" s="58"/>
       <x:c r="N163" s="58"/>
@@ -6786,8 +7422,12 @@
       <x:c r="G164" s="58"/>
       <x:c r="H164" s="58"/>
       <x:c r="I164" s="58"/>
-      <x:c r="J164" s="60"/>
-      <x:c r="K164" s="50"/>
+      <x:c r="J164" s="60" t="str">
+        <x:f>IF(A164="","",IF(K164="Subscription","",IF(E164=0,"",IF(ISNUMBER(G164),G164/E164,IF(ISNUMBER(I164),-ABS(I164)/E164,IF(ISNUMBER(H164),0,IF(AND(ISNUMBER(F164),ISNUMBER(E164),E164&gt;0,F164&gt;E164),(F164-E164)/E164,IF(AND(ISNUMBER(F164),ISNUMBER(E164),E164&gt;0,F164=E164),0,IF(AND(ISNUMBER(F164),ISNUMBER(E164),E164&gt;0,F164=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K164" s="50" t="str">
+        <x:f>IF(A164="","",IF(AND(ISNUMBER(E164),E164=0,OR(ISNUMBER(SEARCH("Free",D164&amp;"")),AND(ISNUMBER(F164),F164=0))),"Subscription",IF(ISNUMBER(G164),"Profit",IF(ISNUMBER(I164),"Loss",IF(ISNUMBER(H164),"Draw",IF(AND(ISNUMBER(F164),ISNUMBER(E164),E164&gt;0,F164&gt;E164),"Profit",IF(AND(ISNUMBER(F164),ISNUMBER(E164),E164&gt;0,F164=E164),"Draw",IF(AND(ISNUMBER(F164),ISNUMBER(E164),E164&gt;0,F164=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L164" s="50"/>
       <x:c r="M164" s="58"/>
       <x:c r="N164" s="58"/>
@@ -6819,8 +7459,12 @@
       <x:c r="G165" s="58"/>
       <x:c r="H165" s="58"/>
       <x:c r="I165" s="58"/>
-      <x:c r="J165" s="60"/>
-      <x:c r="K165" s="50"/>
+      <x:c r="J165" s="60" t="str">
+        <x:f>IF(A165="","",IF(K165="Subscription","",IF(E165=0,"",IF(ISNUMBER(G165),G165/E165,IF(ISNUMBER(I165),-ABS(I165)/E165,IF(ISNUMBER(H165),0,IF(AND(ISNUMBER(F165),ISNUMBER(E165),E165&gt;0,F165&gt;E165),(F165-E165)/E165,IF(AND(ISNUMBER(F165),ISNUMBER(E165),E165&gt;0,F165=E165),0,IF(AND(ISNUMBER(F165),ISNUMBER(E165),E165&gt;0,F165=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K165" s="50" t="str">
+        <x:f>IF(A165="","",IF(AND(ISNUMBER(E165),E165=0,OR(ISNUMBER(SEARCH("Free",D165&amp;"")),AND(ISNUMBER(F165),F165=0))),"Subscription",IF(ISNUMBER(G165),"Profit",IF(ISNUMBER(I165),"Loss",IF(ISNUMBER(H165),"Draw",IF(AND(ISNUMBER(F165),ISNUMBER(E165),E165&gt;0,F165&gt;E165),"Profit",IF(AND(ISNUMBER(F165),ISNUMBER(E165),E165&gt;0,F165=E165),"Draw",IF(AND(ISNUMBER(F165),ISNUMBER(E165),E165&gt;0,F165=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L165" s="50"/>
       <x:c r="M165" s="58"/>
       <x:c r="N165" s="58"/>
@@ -6852,8 +7496,12 @@
       <x:c r="G166" s="58"/>
       <x:c r="H166" s="58"/>
       <x:c r="I166" s="58"/>
-      <x:c r="J166" s="60"/>
-      <x:c r="K166" s="50"/>
+      <x:c r="J166" s="60" t="str">
+        <x:f>IF(A166="","",IF(K166="Subscription","",IF(E166=0,"",IF(ISNUMBER(G166),G166/E166,IF(ISNUMBER(I166),-ABS(I166)/E166,IF(ISNUMBER(H166),0,IF(AND(ISNUMBER(F166),ISNUMBER(E166),E166&gt;0,F166&gt;E166),(F166-E166)/E166,IF(AND(ISNUMBER(F166),ISNUMBER(E166),E166&gt;0,F166=E166),0,IF(AND(ISNUMBER(F166),ISNUMBER(E166),E166&gt;0,F166=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K166" s="50" t="str">
+        <x:f>IF(A166="","",IF(AND(ISNUMBER(E166),E166=0,OR(ISNUMBER(SEARCH("Free",D166&amp;"")),AND(ISNUMBER(F166),F166=0))),"Subscription",IF(ISNUMBER(G166),"Profit",IF(ISNUMBER(I166),"Loss",IF(ISNUMBER(H166),"Draw",IF(AND(ISNUMBER(F166),ISNUMBER(E166),E166&gt;0,F166&gt;E166),"Profit",IF(AND(ISNUMBER(F166),ISNUMBER(E166),E166&gt;0,F166=E166),"Draw",IF(AND(ISNUMBER(F166),ISNUMBER(E166),E166&gt;0,F166=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L166" s="50"/>
       <x:c r="M166" s="58"/>
       <x:c r="N166" s="58"/>
@@ -6885,8 +7533,12 @@
       <x:c r="G167" s="58"/>
       <x:c r="H167" s="58"/>
       <x:c r="I167" s="58"/>
-      <x:c r="J167" s="60"/>
-      <x:c r="K167" s="50"/>
+      <x:c r="J167" s="60" t="str">
+        <x:f>IF(A167="","",IF(K167="Subscription","",IF(E167=0,"",IF(ISNUMBER(G167),G167/E167,IF(ISNUMBER(I167),-ABS(I167)/E167,IF(ISNUMBER(H167),0,IF(AND(ISNUMBER(F167),ISNUMBER(E167),E167&gt;0,F167&gt;E167),(F167-E167)/E167,IF(AND(ISNUMBER(F167),ISNUMBER(E167),E167&gt;0,F167=E167),0,IF(AND(ISNUMBER(F167),ISNUMBER(E167),E167&gt;0,F167=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K167" s="50" t="str">
+        <x:f>IF(A167="","",IF(AND(ISNUMBER(E167),E167=0,OR(ISNUMBER(SEARCH("Free",D167&amp;"")),AND(ISNUMBER(F167),F167=0))),"Subscription",IF(ISNUMBER(G167),"Profit",IF(ISNUMBER(I167),"Loss",IF(ISNUMBER(H167),"Draw",IF(AND(ISNUMBER(F167),ISNUMBER(E167),E167&gt;0,F167&gt;E167),"Profit",IF(AND(ISNUMBER(F167),ISNUMBER(E167),E167&gt;0,F167=E167),"Draw",IF(AND(ISNUMBER(F167),ISNUMBER(E167),E167&gt;0,F167=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L167" s="50"/>
       <x:c r="M167" s="58"/>
       <x:c r="N167" s="58"/>
@@ -6918,8 +7570,12 @@
       <x:c r="G168" s="58"/>
       <x:c r="H168" s="58"/>
       <x:c r="I168" s="58"/>
-      <x:c r="J168" s="60"/>
-      <x:c r="K168" s="50"/>
+      <x:c r="J168" s="60" t="str">
+        <x:f>IF(A168="","",IF(K168="Subscription","",IF(E168=0,"",IF(ISNUMBER(G168),G168/E168,IF(ISNUMBER(I168),-ABS(I168)/E168,IF(ISNUMBER(H168),0,IF(AND(ISNUMBER(F168),ISNUMBER(E168),E168&gt;0,F168&gt;E168),(F168-E168)/E168,IF(AND(ISNUMBER(F168),ISNUMBER(E168),E168&gt;0,F168=E168),0,IF(AND(ISNUMBER(F168),ISNUMBER(E168),E168&gt;0,F168=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K168" s="50" t="str">
+        <x:f>IF(A168="","",IF(AND(ISNUMBER(E168),E168=0,OR(ISNUMBER(SEARCH("Free",D168&amp;"")),AND(ISNUMBER(F168),F168=0))),"Subscription",IF(ISNUMBER(G168),"Profit",IF(ISNUMBER(I168),"Loss",IF(ISNUMBER(H168),"Draw",IF(AND(ISNUMBER(F168),ISNUMBER(E168),E168&gt;0,F168&gt;E168),"Profit",IF(AND(ISNUMBER(F168),ISNUMBER(E168),E168&gt;0,F168=E168),"Draw",IF(AND(ISNUMBER(F168),ISNUMBER(E168),E168&gt;0,F168=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L168" s="50"/>
       <x:c r="M168" s="58"/>
       <x:c r="N168" s="58"/>
@@ -6951,8 +7607,12 @@
       <x:c r="G169" s="58"/>
       <x:c r="H169" s="58"/>
       <x:c r="I169" s="58"/>
-      <x:c r="J169" s="60"/>
-      <x:c r="K169" s="50"/>
+      <x:c r="J169" s="60" t="str">
+        <x:f>IF(A169="","",IF(K169="Subscription","",IF(E169=0,"",IF(ISNUMBER(G169),G169/E169,IF(ISNUMBER(I169),-ABS(I169)/E169,IF(ISNUMBER(H169),0,IF(AND(ISNUMBER(F169),ISNUMBER(E169),E169&gt;0,F169&gt;E169),(F169-E169)/E169,IF(AND(ISNUMBER(F169),ISNUMBER(E169),E169&gt;0,F169=E169),0,IF(AND(ISNUMBER(F169),ISNUMBER(E169),E169&gt;0,F169=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K169" s="50" t="str">
+        <x:f>IF(A169="","",IF(AND(ISNUMBER(E169),E169=0,OR(ISNUMBER(SEARCH("Free",D169&amp;"")),AND(ISNUMBER(F169),F169=0))),"Subscription",IF(ISNUMBER(G169),"Profit",IF(ISNUMBER(I169),"Loss",IF(ISNUMBER(H169),"Draw",IF(AND(ISNUMBER(F169),ISNUMBER(E169),E169&gt;0,F169&gt;E169),"Profit",IF(AND(ISNUMBER(F169),ISNUMBER(E169),E169&gt;0,F169=E169),"Draw",IF(AND(ISNUMBER(F169),ISNUMBER(E169),E169&gt;0,F169=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L169" s="50"/>
       <x:c r="M169" s="58"/>
       <x:c r="N169" s="58"/>
@@ -6984,8 +7644,12 @@
       <x:c r="G170" s="58"/>
       <x:c r="H170" s="58"/>
       <x:c r="I170" s="58"/>
-      <x:c r="J170" s="60"/>
-      <x:c r="K170" s="50"/>
+      <x:c r="J170" s="60" t="str">
+        <x:f>IF(A170="","",IF(K170="Subscription","",IF(E170=0,"",IF(ISNUMBER(G170),G170/E170,IF(ISNUMBER(I170),-ABS(I170)/E170,IF(ISNUMBER(H170),0,IF(AND(ISNUMBER(F170),ISNUMBER(E170),E170&gt;0,F170&gt;E170),(F170-E170)/E170,IF(AND(ISNUMBER(F170),ISNUMBER(E170),E170&gt;0,F170=E170),0,IF(AND(ISNUMBER(F170),ISNUMBER(E170),E170&gt;0,F170=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K170" s="50" t="str">
+        <x:f>IF(A170="","",IF(AND(ISNUMBER(E170),E170=0,OR(ISNUMBER(SEARCH("Free",D170&amp;"")),AND(ISNUMBER(F170),F170=0))),"Subscription",IF(ISNUMBER(G170),"Profit",IF(ISNUMBER(I170),"Loss",IF(ISNUMBER(H170),"Draw",IF(AND(ISNUMBER(F170),ISNUMBER(E170),E170&gt;0,F170&gt;E170),"Profit",IF(AND(ISNUMBER(F170),ISNUMBER(E170),E170&gt;0,F170=E170),"Draw",IF(AND(ISNUMBER(F170),ISNUMBER(E170),E170&gt;0,F170=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L170" s="50"/>
       <x:c r="M170" s="58"/>
       <x:c r="N170" s="58"/>
@@ -7017,8 +7681,12 @@
       <x:c r="G171" s="58"/>
       <x:c r="H171" s="58"/>
       <x:c r="I171" s="58"/>
-      <x:c r="J171" s="60"/>
-      <x:c r="K171" s="50"/>
+      <x:c r="J171" s="60" t="str">
+        <x:f>IF(A171="","",IF(K171="Subscription","",IF(E171=0,"",IF(ISNUMBER(G171),G171/E171,IF(ISNUMBER(I171),-ABS(I171)/E171,IF(ISNUMBER(H171),0,IF(AND(ISNUMBER(F171),ISNUMBER(E171),E171&gt;0,F171&gt;E171),(F171-E171)/E171,IF(AND(ISNUMBER(F171),ISNUMBER(E171),E171&gt;0,F171=E171),0,IF(AND(ISNUMBER(F171),ISNUMBER(E171),E171&gt;0,F171=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K171" s="50" t="str">
+        <x:f>IF(A171="","",IF(AND(ISNUMBER(E171),E171=0,OR(ISNUMBER(SEARCH("Free",D171&amp;"")),AND(ISNUMBER(F171),F171=0))),"Subscription",IF(ISNUMBER(G171),"Profit",IF(ISNUMBER(I171),"Loss",IF(ISNUMBER(H171),"Draw",IF(AND(ISNUMBER(F171),ISNUMBER(E171),E171&gt;0,F171&gt;E171),"Profit",IF(AND(ISNUMBER(F171),ISNUMBER(E171),E171&gt;0,F171=E171),"Draw",IF(AND(ISNUMBER(F171),ISNUMBER(E171),E171&gt;0,F171=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L171" s="50"/>
       <x:c r="M171" s="58"/>
       <x:c r="N171" s="58"/>
@@ -7050,8 +7718,12 @@
       <x:c r="G172" s="58"/>
       <x:c r="H172" s="58"/>
       <x:c r="I172" s="58"/>
-      <x:c r="J172" s="60"/>
-      <x:c r="K172" s="50"/>
+      <x:c r="J172" s="60" t="str">
+        <x:f>IF(A172="","",IF(K172="Subscription","",IF(E172=0,"",IF(ISNUMBER(G172),G172/E172,IF(ISNUMBER(I172),-ABS(I172)/E172,IF(ISNUMBER(H172),0,IF(AND(ISNUMBER(F172),ISNUMBER(E172),E172&gt;0,F172&gt;E172),(F172-E172)/E172,IF(AND(ISNUMBER(F172),ISNUMBER(E172),E172&gt;0,F172=E172),0,IF(AND(ISNUMBER(F172),ISNUMBER(E172),E172&gt;0,F172=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K172" s="50" t="str">
+        <x:f>IF(A172="","",IF(AND(ISNUMBER(E172),E172=0,OR(ISNUMBER(SEARCH("Free",D172&amp;"")),AND(ISNUMBER(F172),F172=0))),"Subscription",IF(ISNUMBER(G172),"Profit",IF(ISNUMBER(I172),"Loss",IF(ISNUMBER(H172),"Draw",IF(AND(ISNUMBER(F172),ISNUMBER(E172),E172&gt;0,F172&gt;E172),"Profit",IF(AND(ISNUMBER(F172),ISNUMBER(E172),E172&gt;0,F172=E172),"Draw",IF(AND(ISNUMBER(F172),ISNUMBER(E172),E172&gt;0,F172=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L172" s="50"/>
       <x:c r="M172" s="58"/>
       <x:c r="N172" s="58"/>
@@ -7083,8 +7755,12 @@
       <x:c r="G173" s="58"/>
       <x:c r="H173" s="58"/>
       <x:c r="I173" s="58"/>
-      <x:c r="J173" s="60"/>
-      <x:c r="K173" s="50"/>
+      <x:c r="J173" s="60" t="str">
+        <x:f>IF(A173="","",IF(K173="Subscription","",IF(E173=0,"",IF(ISNUMBER(G173),G173/E173,IF(ISNUMBER(I173),-ABS(I173)/E173,IF(ISNUMBER(H173),0,IF(AND(ISNUMBER(F173),ISNUMBER(E173),E173&gt;0,F173&gt;E173),(F173-E173)/E173,IF(AND(ISNUMBER(F173),ISNUMBER(E173),E173&gt;0,F173=E173),0,IF(AND(ISNUMBER(F173),ISNUMBER(E173),E173&gt;0,F173=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K173" s="50" t="str">
+        <x:f>IF(A173="","",IF(AND(ISNUMBER(E173),E173=0,OR(ISNUMBER(SEARCH("Free",D173&amp;"")),AND(ISNUMBER(F173),F173=0))),"Subscription",IF(ISNUMBER(G173),"Profit",IF(ISNUMBER(I173),"Loss",IF(ISNUMBER(H173),"Draw",IF(AND(ISNUMBER(F173),ISNUMBER(E173),E173&gt;0,F173&gt;E173),"Profit",IF(AND(ISNUMBER(F173),ISNUMBER(E173),E173&gt;0,F173=E173),"Draw",IF(AND(ISNUMBER(F173),ISNUMBER(E173),E173&gt;0,F173=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L173" s="50"/>
       <x:c r="M173" s="58"/>
       <x:c r="N173" s="58"/>
@@ -7116,8 +7792,12 @@
       <x:c r="G174" s="58"/>
       <x:c r="H174" s="58"/>
       <x:c r="I174" s="58"/>
-      <x:c r="J174" s="60"/>
-      <x:c r="K174" s="50"/>
+      <x:c r="J174" s="60" t="str">
+        <x:f>IF(A174="","",IF(K174="Subscription","",IF(E174=0,"",IF(ISNUMBER(G174),G174/E174,IF(ISNUMBER(I174),-ABS(I174)/E174,IF(ISNUMBER(H174),0,IF(AND(ISNUMBER(F174),ISNUMBER(E174),E174&gt;0,F174&gt;E174),(F174-E174)/E174,IF(AND(ISNUMBER(F174),ISNUMBER(E174),E174&gt;0,F174=E174),0,IF(AND(ISNUMBER(F174),ISNUMBER(E174),E174&gt;0,F174=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K174" s="50" t="str">
+        <x:f>IF(A174="","",IF(AND(ISNUMBER(E174),E174=0,OR(ISNUMBER(SEARCH("Free",D174&amp;"")),AND(ISNUMBER(F174),F174=0))),"Subscription",IF(ISNUMBER(G174),"Profit",IF(ISNUMBER(I174),"Loss",IF(ISNUMBER(H174),"Draw",IF(AND(ISNUMBER(F174),ISNUMBER(E174),E174&gt;0,F174&gt;E174),"Profit",IF(AND(ISNUMBER(F174),ISNUMBER(E174),E174&gt;0,F174=E174),"Draw",IF(AND(ISNUMBER(F174),ISNUMBER(E174),E174&gt;0,F174=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L174" s="50"/>
       <x:c r="M174" s="58"/>
       <x:c r="N174" s="58"/>
@@ -7149,8 +7829,12 @@
       <x:c r="G175" s="58"/>
       <x:c r="H175" s="58"/>
       <x:c r="I175" s="58"/>
-      <x:c r="J175" s="60"/>
-      <x:c r="K175" s="50"/>
+      <x:c r="J175" s="60" t="str">
+        <x:f>IF(A175="","",IF(K175="Subscription","",IF(E175=0,"",IF(ISNUMBER(G175),G175/E175,IF(ISNUMBER(I175),-ABS(I175)/E175,IF(ISNUMBER(H175),0,IF(AND(ISNUMBER(F175),ISNUMBER(E175),E175&gt;0,F175&gt;E175),(F175-E175)/E175,IF(AND(ISNUMBER(F175),ISNUMBER(E175),E175&gt;0,F175=E175),0,IF(AND(ISNUMBER(F175),ISNUMBER(E175),E175&gt;0,F175=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K175" s="50" t="str">
+        <x:f>IF(A175="","",IF(AND(ISNUMBER(E175),E175=0,OR(ISNUMBER(SEARCH("Free",D175&amp;"")),AND(ISNUMBER(F175),F175=0))),"Subscription",IF(ISNUMBER(G175),"Profit",IF(ISNUMBER(I175),"Loss",IF(ISNUMBER(H175),"Draw",IF(AND(ISNUMBER(F175),ISNUMBER(E175),E175&gt;0,F175&gt;E175),"Profit",IF(AND(ISNUMBER(F175),ISNUMBER(E175),E175&gt;0,F175=E175),"Draw",IF(AND(ISNUMBER(F175),ISNUMBER(E175),E175&gt;0,F175=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L175" s="50"/>
       <x:c r="M175" s="58"/>
       <x:c r="N175" s="58"/>
@@ -7182,8 +7866,12 @@
       <x:c r="G176" s="58"/>
       <x:c r="H176" s="58"/>
       <x:c r="I176" s="58"/>
-      <x:c r="J176" s="60"/>
-      <x:c r="K176" s="50"/>
+      <x:c r="J176" s="60" t="str">
+        <x:f>IF(A176="","",IF(K176="Subscription","",IF(E176=0,"",IF(ISNUMBER(G176),G176/E176,IF(ISNUMBER(I176),-ABS(I176)/E176,IF(ISNUMBER(H176),0,IF(AND(ISNUMBER(F176),ISNUMBER(E176),E176&gt;0,F176&gt;E176),(F176-E176)/E176,IF(AND(ISNUMBER(F176),ISNUMBER(E176),E176&gt;0,F176=E176),0,IF(AND(ISNUMBER(F176),ISNUMBER(E176),E176&gt;0,F176=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K176" s="50" t="str">
+        <x:f>IF(A176="","",IF(AND(ISNUMBER(E176),E176=0,OR(ISNUMBER(SEARCH("Free",D176&amp;"")),AND(ISNUMBER(F176),F176=0))),"Subscription",IF(ISNUMBER(G176),"Profit",IF(ISNUMBER(I176),"Loss",IF(ISNUMBER(H176),"Draw",IF(AND(ISNUMBER(F176),ISNUMBER(E176),E176&gt;0,F176&gt;E176),"Profit",IF(AND(ISNUMBER(F176),ISNUMBER(E176),E176&gt;0,F176=E176),"Draw",IF(AND(ISNUMBER(F176),ISNUMBER(E176),E176&gt;0,F176=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L176" s="50"/>
       <x:c r="M176" s="58"/>
       <x:c r="N176" s="58"/>
@@ -7215,8 +7903,12 @@
       <x:c r="G177" s="58"/>
       <x:c r="H177" s="58"/>
       <x:c r="I177" s="58"/>
-      <x:c r="J177" s="60"/>
-      <x:c r="K177" s="50"/>
+      <x:c r="J177" s="60" t="str">
+        <x:f>IF(A177="","",IF(K177="Subscription","",IF(E177=0,"",IF(ISNUMBER(G177),G177/E177,IF(ISNUMBER(I177),-ABS(I177)/E177,IF(ISNUMBER(H177),0,IF(AND(ISNUMBER(F177),ISNUMBER(E177),E177&gt;0,F177&gt;E177),(F177-E177)/E177,IF(AND(ISNUMBER(F177),ISNUMBER(E177),E177&gt;0,F177=E177),0,IF(AND(ISNUMBER(F177),ISNUMBER(E177),E177&gt;0,F177=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K177" s="50" t="str">
+        <x:f>IF(A177="","",IF(AND(ISNUMBER(E177),E177=0,OR(ISNUMBER(SEARCH("Free",D177&amp;"")),AND(ISNUMBER(F177),F177=0))),"Subscription",IF(ISNUMBER(G177),"Profit",IF(ISNUMBER(I177),"Loss",IF(ISNUMBER(H177),"Draw",IF(AND(ISNUMBER(F177),ISNUMBER(E177),E177&gt;0,F177&gt;E177),"Profit",IF(AND(ISNUMBER(F177),ISNUMBER(E177),E177&gt;0,F177=E177),"Draw",IF(AND(ISNUMBER(F177),ISNUMBER(E177),E177&gt;0,F177=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L177" s="50"/>
       <x:c r="M177" s="58"/>
       <x:c r="N177" s="58"/>
@@ -7248,8 +7940,12 @@
       <x:c r="G178" s="58"/>
       <x:c r="H178" s="58"/>
       <x:c r="I178" s="58"/>
-      <x:c r="J178" s="60"/>
-      <x:c r="K178" s="50"/>
+      <x:c r="J178" s="60" t="str">
+        <x:f>IF(A178="","",IF(K178="Subscription","",IF(E178=0,"",IF(ISNUMBER(G178),G178/E178,IF(ISNUMBER(I178),-ABS(I178)/E178,IF(ISNUMBER(H178),0,IF(AND(ISNUMBER(F178),ISNUMBER(E178),E178&gt;0,F178&gt;E178),(F178-E178)/E178,IF(AND(ISNUMBER(F178),ISNUMBER(E178),E178&gt;0,F178=E178),0,IF(AND(ISNUMBER(F178),ISNUMBER(E178),E178&gt;0,F178=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K178" s="50" t="str">
+        <x:f>IF(A178="","",IF(AND(ISNUMBER(E178),E178=0,OR(ISNUMBER(SEARCH("Free",D178&amp;"")),AND(ISNUMBER(F178),F178=0))),"Subscription",IF(ISNUMBER(G178),"Profit",IF(ISNUMBER(I178),"Loss",IF(ISNUMBER(H178),"Draw",IF(AND(ISNUMBER(F178),ISNUMBER(E178),E178&gt;0,F178&gt;E178),"Profit",IF(AND(ISNUMBER(F178),ISNUMBER(E178),E178&gt;0,F178=E178),"Draw",IF(AND(ISNUMBER(F178),ISNUMBER(E178),E178&gt;0,F178=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L178" s="50"/>
       <x:c r="M178" s="58"/>
       <x:c r="N178" s="58"/>
@@ -7281,8 +7977,12 @@
       <x:c r="G179" s="58"/>
       <x:c r="H179" s="58"/>
       <x:c r="I179" s="58"/>
-      <x:c r="J179" s="60"/>
-      <x:c r="K179" s="50"/>
+      <x:c r="J179" s="60" t="str">
+        <x:f>IF(A179="","",IF(K179="Subscription","",IF(E179=0,"",IF(ISNUMBER(G179),G179/E179,IF(ISNUMBER(I179),-ABS(I179)/E179,IF(ISNUMBER(H179),0,IF(AND(ISNUMBER(F179),ISNUMBER(E179),E179&gt;0,F179&gt;E179),(F179-E179)/E179,IF(AND(ISNUMBER(F179),ISNUMBER(E179),E179&gt;0,F179=E179),0,IF(AND(ISNUMBER(F179),ISNUMBER(E179),E179&gt;0,F179=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K179" s="50" t="str">
+        <x:f>IF(A179="","",IF(AND(ISNUMBER(E179),E179=0,OR(ISNUMBER(SEARCH("Free",D179&amp;"")),AND(ISNUMBER(F179),F179=0))),"Subscription",IF(ISNUMBER(G179),"Profit",IF(ISNUMBER(I179),"Loss",IF(ISNUMBER(H179),"Draw",IF(AND(ISNUMBER(F179),ISNUMBER(E179),E179&gt;0,F179&gt;E179),"Profit",IF(AND(ISNUMBER(F179),ISNUMBER(E179),E179&gt;0,F179=E179),"Draw",IF(AND(ISNUMBER(F179),ISNUMBER(E179),E179&gt;0,F179=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L179" s="50"/>
       <x:c r="M179" s="58"/>
       <x:c r="N179" s="58"/>
@@ -7314,8 +8014,12 @@
       <x:c r="G180" s="58"/>
       <x:c r="H180" s="58"/>
       <x:c r="I180" s="58"/>
-      <x:c r="J180" s="60"/>
-      <x:c r="K180" s="50"/>
+      <x:c r="J180" s="60" t="str">
+        <x:f>IF(A180="","",IF(K180="Subscription","",IF(E180=0,"",IF(ISNUMBER(G180),G180/E180,IF(ISNUMBER(I180),-ABS(I180)/E180,IF(ISNUMBER(H180),0,IF(AND(ISNUMBER(F180),ISNUMBER(E180),E180&gt;0,F180&gt;E180),(F180-E180)/E180,IF(AND(ISNUMBER(F180),ISNUMBER(E180),E180&gt;0,F180=E180),0,IF(AND(ISNUMBER(F180),ISNUMBER(E180),E180&gt;0,F180=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K180" s="50" t="str">
+        <x:f>IF(A180="","",IF(AND(ISNUMBER(E180),E180=0,OR(ISNUMBER(SEARCH("Free",D180&amp;"")),AND(ISNUMBER(F180),F180=0))),"Subscription",IF(ISNUMBER(G180),"Profit",IF(ISNUMBER(I180),"Loss",IF(ISNUMBER(H180),"Draw",IF(AND(ISNUMBER(F180),ISNUMBER(E180),E180&gt;0,F180&gt;E180),"Profit",IF(AND(ISNUMBER(F180),ISNUMBER(E180),E180&gt;0,F180=E180),"Draw",IF(AND(ISNUMBER(F180),ISNUMBER(E180),E180&gt;0,F180=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L180" s="50"/>
       <x:c r="M180" s="58"/>
       <x:c r="N180" s="58"/>
@@ -7347,8 +8051,12 @@
       <x:c r="G181" s="58"/>
       <x:c r="H181" s="58"/>
       <x:c r="I181" s="58"/>
-      <x:c r="J181" s="60"/>
-      <x:c r="K181" s="50"/>
+      <x:c r="J181" s="60" t="str">
+        <x:f>IF(A181="","",IF(K181="Subscription","",IF(E181=0,"",IF(ISNUMBER(G181),G181/E181,IF(ISNUMBER(I181),-ABS(I181)/E181,IF(ISNUMBER(H181),0,IF(AND(ISNUMBER(F181),ISNUMBER(E181),E181&gt;0,F181&gt;E181),(F181-E181)/E181,IF(AND(ISNUMBER(F181),ISNUMBER(E181),E181&gt;0,F181=E181),0,IF(AND(ISNUMBER(F181),ISNUMBER(E181),E181&gt;0,F181=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K181" s="50" t="str">
+        <x:f>IF(A181="","",IF(AND(ISNUMBER(E181),E181=0,OR(ISNUMBER(SEARCH("Free",D181&amp;"")),AND(ISNUMBER(F181),F181=0))),"Subscription",IF(ISNUMBER(G181),"Profit",IF(ISNUMBER(I181),"Loss",IF(ISNUMBER(H181),"Draw",IF(AND(ISNUMBER(F181),ISNUMBER(E181),E181&gt;0,F181&gt;E181),"Profit",IF(AND(ISNUMBER(F181),ISNUMBER(E181),E181&gt;0,F181=E181),"Draw",IF(AND(ISNUMBER(F181),ISNUMBER(E181),E181&gt;0,F181=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L181" s="50"/>
       <x:c r="M181" s="58"/>
       <x:c r="N181" s="58"/>
@@ -7380,8 +8088,12 @@
       <x:c r="G182" s="58"/>
       <x:c r="H182" s="58"/>
       <x:c r="I182" s="58"/>
-      <x:c r="J182" s="60"/>
-      <x:c r="K182" s="50"/>
+      <x:c r="J182" s="60" t="str">
+        <x:f>IF(A182="","",IF(K182="Subscription","",IF(E182=0,"",IF(ISNUMBER(G182),G182/E182,IF(ISNUMBER(I182),-ABS(I182)/E182,IF(ISNUMBER(H182),0,IF(AND(ISNUMBER(F182),ISNUMBER(E182),E182&gt;0,F182&gt;E182),(F182-E182)/E182,IF(AND(ISNUMBER(F182),ISNUMBER(E182),E182&gt;0,F182=E182),0,IF(AND(ISNUMBER(F182),ISNUMBER(E182),E182&gt;0,F182=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K182" s="50" t="str">
+        <x:f>IF(A182="","",IF(AND(ISNUMBER(E182),E182=0,OR(ISNUMBER(SEARCH("Free",D182&amp;"")),AND(ISNUMBER(F182),F182=0))),"Subscription",IF(ISNUMBER(G182),"Profit",IF(ISNUMBER(I182),"Loss",IF(ISNUMBER(H182),"Draw",IF(AND(ISNUMBER(F182),ISNUMBER(E182),E182&gt;0,F182&gt;E182),"Profit",IF(AND(ISNUMBER(F182),ISNUMBER(E182),E182&gt;0,F182=E182),"Draw",IF(AND(ISNUMBER(F182),ISNUMBER(E182),E182&gt;0,F182=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L182" s="50"/>
       <x:c r="M182" s="58"/>
       <x:c r="N182" s="58"/>
@@ -7413,8 +8125,12 @@
       <x:c r="G183" s="58"/>
       <x:c r="H183" s="58"/>
       <x:c r="I183" s="58"/>
-      <x:c r="J183" s="60"/>
-      <x:c r="K183" s="50"/>
+      <x:c r="J183" s="60" t="str">
+        <x:f>IF(A183="","",IF(K183="Subscription","",IF(E183=0,"",IF(ISNUMBER(G183),G183/E183,IF(ISNUMBER(I183),-ABS(I183)/E183,IF(ISNUMBER(H183),0,IF(AND(ISNUMBER(F183),ISNUMBER(E183),E183&gt;0,F183&gt;E183),(F183-E183)/E183,IF(AND(ISNUMBER(F183),ISNUMBER(E183),E183&gt;0,F183=E183),0,IF(AND(ISNUMBER(F183),ISNUMBER(E183),E183&gt;0,F183=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K183" s="50" t="str">
+        <x:f>IF(A183="","",IF(AND(ISNUMBER(E183),E183=0,OR(ISNUMBER(SEARCH("Free",D183&amp;"")),AND(ISNUMBER(F183),F183=0))),"Subscription",IF(ISNUMBER(G183),"Profit",IF(ISNUMBER(I183),"Loss",IF(ISNUMBER(H183),"Draw",IF(AND(ISNUMBER(F183),ISNUMBER(E183),E183&gt;0,F183&gt;E183),"Profit",IF(AND(ISNUMBER(F183),ISNUMBER(E183),E183&gt;0,F183=E183),"Draw",IF(AND(ISNUMBER(F183),ISNUMBER(E183),E183&gt;0,F183=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L183" s="50"/>
       <x:c r="M183" s="58"/>
       <x:c r="N183" s="58"/>
@@ -7446,8 +8162,12 @@
       <x:c r="G184" s="58"/>
       <x:c r="H184" s="58"/>
       <x:c r="I184" s="58"/>
-      <x:c r="J184" s="60"/>
-      <x:c r="K184" s="50"/>
+      <x:c r="J184" s="60" t="str">
+        <x:f>IF(A184="","",IF(K184="Subscription","",IF(E184=0,"",IF(ISNUMBER(G184),G184/E184,IF(ISNUMBER(I184),-ABS(I184)/E184,IF(ISNUMBER(H184),0,IF(AND(ISNUMBER(F184),ISNUMBER(E184),E184&gt;0,F184&gt;E184),(F184-E184)/E184,IF(AND(ISNUMBER(F184),ISNUMBER(E184),E184&gt;0,F184=E184),0,IF(AND(ISNUMBER(F184),ISNUMBER(E184),E184&gt;0,F184=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K184" s="50" t="str">
+        <x:f>IF(A184="","",IF(AND(ISNUMBER(E184),E184=0,OR(ISNUMBER(SEARCH("Free",D184&amp;"")),AND(ISNUMBER(F184),F184=0))),"Subscription",IF(ISNUMBER(G184),"Profit",IF(ISNUMBER(I184),"Loss",IF(ISNUMBER(H184),"Draw",IF(AND(ISNUMBER(F184),ISNUMBER(E184),E184&gt;0,F184&gt;E184),"Profit",IF(AND(ISNUMBER(F184),ISNUMBER(E184),E184&gt;0,F184=E184),"Draw",IF(AND(ISNUMBER(F184),ISNUMBER(E184),E184&gt;0,F184=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L184" s="50"/>
       <x:c r="M184" s="58"/>
       <x:c r="N184" s="58"/>
@@ -7479,8 +8199,12 @@
       <x:c r="G185" s="58"/>
       <x:c r="H185" s="58"/>
       <x:c r="I185" s="58"/>
-      <x:c r="J185" s="60"/>
-      <x:c r="K185" s="50"/>
+      <x:c r="J185" s="60" t="str">
+        <x:f>IF(A185="","",IF(K185="Subscription","",IF(E185=0,"",IF(ISNUMBER(G185),G185/E185,IF(ISNUMBER(I185),-ABS(I185)/E185,IF(ISNUMBER(H185),0,IF(AND(ISNUMBER(F185),ISNUMBER(E185),E185&gt;0,F185&gt;E185),(F185-E185)/E185,IF(AND(ISNUMBER(F185),ISNUMBER(E185),E185&gt;0,F185=E185),0,IF(AND(ISNUMBER(F185),ISNUMBER(E185),E185&gt;0,F185=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K185" s="50" t="str">
+        <x:f>IF(A185="","",IF(AND(ISNUMBER(E185),E185=0,OR(ISNUMBER(SEARCH("Free",D185&amp;"")),AND(ISNUMBER(F185),F185=0))),"Subscription",IF(ISNUMBER(G185),"Profit",IF(ISNUMBER(I185),"Loss",IF(ISNUMBER(H185),"Draw",IF(AND(ISNUMBER(F185),ISNUMBER(E185),E185&gt;0,F185&gt;E185),"Profit",IF(AND(ISNUMBER(F185),ISNUMBER(E185),E185&gt;0,F185=E185),"Draw",IF(AND(ISNUMBER(F185),ISNUMBER(E185),E185&gt;0,F185=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L185" s="50"/>
       <x:c r="M185" s="58"/>
       <x:c r="N185" s="58"/>
@@ -7512,8 +8236,12 @@
       <x:c r="G186" s="58"/>
       <x:c r="H186" s="58"/>
       <x:c r="I186" s="58"/>
-      <x:c r="J186" s="60"/>
-      <x:c r="K186" s="50"/>
+      <x:c r="J186" s="60" t="str">
+        <x:f>IF(A186="","",IF(K186="Subscription","",IF(E186=0,"",IF(ISNUMBER(G186),G186/E186,IF(ISNUMBER(I186),-ABS(I186)/E186,IF(ISNUMBER(H186),0,IF(AND(ISNUMBER(F186),ISNUMBER(E186),E186&gt;0,F186&gt;E186),(F186-E186)/E186,IF(AND(ISNUMBER(F186),ISNUMBER(E186),E186&gt;0,F186=E186),0,IF(AND(ISNUMBER(F186),ISNUMBER(E186),E186&gt;0,F186=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K186" s="50" t="str">
+        <x:f>IF(A186="","",IF(AND(ISNUMBER(E186),E186=0,OR(ISNUMBER(SEARCH("Free",D186&amp;"")),AND(ISNUMBER(F186),F186=0))),"Subscription",IF(ISNUMBER(G186),"Profit",IF(ISNUMBER(I186),"Loss",IF(ISNUMBER(H186),"Draw",IF(AND(ISNUMBER(F186),ISNUMBER(E186),E186&gt;0,F186&gt;E186),"Profit",IF(AND(ISNUMBER(F186),ISNUMBER(E186),E186&gt;0,F186=E186),"Draw",IF(AND(ISNUMBER(F186),ISNUMBER(E186),E186&gt;0,F186=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L186" s="50"/>
       <x:c r="M186" s="58"/>
       <x:c r="N186" s="58"/>
@@ -7545,8 +8273,12 @@
       <x:c r="G187" s="58"/>
       <x:c r="H187" s="58"/>
       <x:c r="I187" s="58"/>
-      <x:c r="J187" s="60"/>
-      <x:c r="K187" s="50"/>
+      <x:c r="J187" s="60" t="str">
+        <x:f>IF(A187="","",IF(K187="Subscription","",IF(E187=0,"",IF(ISNUMBER(G187),G187/E187,IF(ISNUMBER(I187),-ABS(I187)/E187,IF(ISNUMBER(H187),0,IF(AND(ISNUMBER(F187),ISNUMBER(E187),E187&gt;0,F187&gt;E187),(F187-E187)/E187,IF(AND(ISNUMBER(F187),ISNUMBER(E187),E187&gt;0,F187=E187),0,IF(AND(ISNUMBER(F187),ISNUMBER(E187),E187&gt;0,F187=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K187" s="50" t="str">
+        <x:f>IF(A187="","",IF(AND(ISNUMBER(E187),E187=0,OR(ISNUMBER(SEARCH("Free",D187&amp;"")),AND(ISNUMBER(F187),F187=0))),"Subscription",IF(ISNUMBER(G187),"Profit",IF(ISNUMBER(I187),"Loss",IF(ISNUMBER(H187),"Draw",IF(AND(ISNUMBER(F187),ISNUMBER(E187),E187&gt;0,F187&gt;E187),"Profit",IF(AND(ISNUMBER(F187),ISNUMBER(E187),E187&gt;0,F187=E187),"Draw",IF(AND(ISNUMBER(F187),ISNUMBER(E187),E187&gt;0,F187=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L187" s="50"/>
       <x:c r="M187" s="58"/>
       <x:c r="N187" s="58"/>
@@ -7578,8 +8310,12 @@
       <x:c r="G188" s="58"/>
       <x:c r="H188" s="58"/>
       <x:c r="I188" s="58"/>
-      <x:c r="J188" s="60"/>
-      <x:c r="K188" s="50"/>
+      <x:c r="J188" s="60" t="str">
+        <x:f>IF(A188="","",IF(K188="Subscription","",IF(E188=0,"",IF(ISNUMBER(G188),G188/E188,IF(ISNUMBER(I188),-ABS(I188)/E188,IF(ISNUMBER(H188),0,IF(AND(ISNUMBER(F188),ISNUMBER(E188),E188&gt;0,F188&gt;E188),(F188-E188)/E188,IF(AND(ISNUMBER(F188),ISNUMBER(E188),E188&gt;0,F188=E188),0,IF(AND(ISNUMBER(F188),ISNUMBER(E188),E188&gt;0,F188=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K188" s="50" t="str">
+        <x:f>IF(A188="","",IF(AND(ISNUMBER(E188),E188=0,OR(ISNUMBER(SEARCH("Free",D188&amp;"")),AND(ISNUMBER(F188),F188=0))),"Subscription",IF(ISNUMBER(G188),"Profit",IF(ISNUMBER(I188),"Loss",IF(ISNUMBER(H188),"Draw",IF(AND(ISNUMBER(F188),ISNUMBER(E188),E188&gt;0,F188&gt;E188),"Profit",IF(AND(ISNUMBER(F188),ISNUMBER(E188),E188&gt;0,F188=E188),"Draw",IF(AND(ISNUMBER(F188),ISNUMBER(E188),E188&gt;0,F188=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L188" s="50"/>
       <x:c r="M188" s="58"/>
       <x:c r="N188" s="58"/>
@@ -7611,8 +8347,12 @@
       <x:c r="G189" s="58"/>
       <x:c r="H189" s="58"/>
       <x:c r="I189" s="58"/>
-      <x:c r="J189" s="60"/>
-      <x:c r="K189" s="50"/>
+      <x:c r="J189" s="60" t="str">
+        <x:f>IF(A189="","",IF(K189="Subscription","",IF(E189=0,"",IF(ISNUMBER(G189),G189/E189,IF(ISNUMBER(I189),-ABS(I189)/E189,IF(ISNUMBER(H189),0,IF(AND(ISNUMBER(F189),ISNUMBER(E189),E189&gt;0,F189&gt;E189),(F189-E189)/E189,IF(AND(ISNUMBER(F189),ISNUMBER(E189),E189&gt;0,F189=E189),0,IF(AND(ISNUMBER(F189),ISNUMBER(E189),E189&gt;0,F189=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K189" s="50" t="str">
+        <x:f>IF(A189="","",IF(AND(ISNUMBER(E189),E189=0,OR(ISNUMBER(SEARCH("Free",D189&amp;"")),AND(ISNUMBER(F189),F189=0))),"Subscription",IF(ISNUMBER(G189),"Profit",IF(ISNUMBER(I189),"Loss",IF(ISNUMBER(H189),"Draw",IF(AND(ISNUMBER(F189),ISNUMBER(E189),E189&gt;0,F189&gt;E189),"Profit",IF(AND(ISNUMBER(F189),ISNUMBER(E189),E189&gt;0,F189=E189),"Draw",IF(AND(ISNUMBER(F189),ISNUMBER(E189),E189&gt;0,F189=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L189" s="50"/>
       <x:c r="M189" s="58"/>
       <x:c r="N189" s="58"/>
@@ -7644,8 +8384,12 @@
       <x:c r="G190" s="58"/>
       <x:c r="H190" s="58"/>
       <x:c r="I190" s="58"/>
-      <x:c r="J190" s="60"/>
-      <x:c r="K190" s="50"/>
+      <x:c r="J190" s="60" t="str">
+        <x:f>IF(A190="","",IF(K190="Subscription","",IF(E190=0,"",IF(ISNUMBER(G190),G190/E190,IF(ISNUMBER(I190),-ABS(I190)/E190,IF(ISNUMBER(H190),0,IF(AND(ISNUMBER(F190),ISNUMBER(E190),E190&gt;0,F190&gt;E190),(F190-E190)/E190,IF(AND(ISNUMBER(F190),ISNUMBER(E190),E190&gt;0,F190=E190),0,IF(AND(ISNUMBER(F190),ISNUMBER(E190),E190&gt;0,F190=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K190" s="50" t="str">
+        <x:f>IF(A190="","",IF(AND(ISNUMBER(E190),E190=0,OR(ISNUMBER(SEARCH("Free",D190&amp;"")),AND(ISNUMBER(F190),F190=0))),"Subscription",IF(ISNUMBER(G190),"Profit",IF(ISNUMBER(I190),"Loss",IF(ISNUMBER(H190),"Draw",IF(AND(ISNUMBER(F190),ISNUMBER(E190),E190&gt;0,F190&gt;E190),"Profit",IF(AND(ISNUMBER(F190),ISNUMBER(E190),E190&gt;0,F190=E190),"Draw",IF(AND(ISNUMBER(F190),ISNUMBER(E190),E190&gt;0,F190=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L190" s="50"/>
       <x:c r="M190" s="58"/>
       <x:c r="N190" s="58"/>
@@ -7677,8 +8421,12 @@
       <x:c r="G191" s="58"/>
       <x:c r="H191" s="58"/>
       <x:c r="I191" s="58"/>
-      <x:c r="J191" s="60"/>
-      <x:c r="K191" s="50"/>
+      <x:c r="J191" s="60" t="str">
+        <x:f>IF(A191="","",IF(K191="Subscription","",IF(E191=0,"",IF(ISNUMBER(G191),G191/E191,IF(ISNUMBER(I191),-ABS(I191)/E191,IF(ISNUMBER(H191),0,IF(AND(ISNUMBER(F191),ISNUMBER(E191),E191&gt;0,F191&gt;E191),(F191-E191)/E191,IF(AND(ISNUMBER(F191),ISNUMBER(E191),E191&gt;0,F191=E191),0,IF(AND(ISNUMBER(F191),ISNUMBER(E191),E191&gt;0,F191=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K191" s="50" t="str">
+        <x:f>IF(A191="","",IF(AND(ISNUMBER(E191),E191=0,OR(ISNUMBER(SEARCH("Free",D191&amp;"")),AND(ISNUMBER(F191),F191=0))),"Subscription",IF(ISNUMBER(G191),"Profit",IF(ISNUMBER(I191),"Loss",IF(ISNUMBER(H191),"Draw",IF(AND(ISNUMBER(F191),ISNUMBER(E191),E191&gt;0,F191&gt;E191),"Profit",IF(AND(ISNUMBER(F191),ISNUMBER(E191),E191&gt;0,F191=E191),"Draw",IF(AND(ISNUMBER(F191),ISNUMBER(E191),E191&gt;0,F191=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L191" s="50"/>
       <x:c r="M191" s="58"/>
       <x:c r="N191" s="58"/>
@@ -7710,8 +8458,12 @@
       <x:c r="G192" s="58"/>
       <x:c r="H192" s="58"/>
       <x:c r="I192" s="58"/>
-      <x:c r="J192" s="60"/>
-      <x:c r="K192" s="50"/>
+      <x:c r="J192" s="60" t="str">
+        <x:f>IF(A192="","",IF(K192="Subscription","",IF(E192=0,"",IF(ISNUMBER(G192),G192/E192,IF(ISNUMBER(I192),-ABS(I192)/E192,IF(ISNUMBER(H192),0,IF(AND(ISNUMBER(F192),ISNUMBER(E192),E192&gt;0,F192&gt;E192),(F192-E192)/E192,IF(AND(ISNUMBER(F192),ISNUMBER(E192),E192&gt;0,F192=E192),0,IF(AND(ISNUMBER(F192),ISNUMBER(E192),E192&gt;0,F192=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K192" s="50" t="str">
+        <x:f>IF(A192="","",IF(AND(ISNUMBER(E192),E192=0,OR(ISNUMBER(SEARCH("Free",D192&amp;"")),AND(ISNUMBER(F192),F192=0))),"Subscription",IF(ISNUMBER(G192),"Profit",IF(ISNUMBER(I192),"Loss",IF(ISNUMBER(H192),"Draw",IF(AND(ISNUMBER(F192),ISNUMBER(E192),E192&gt;0,F192&gt;E192),"Profit",IF(AND(ISNUMBER(F192),ISNUMBER(E192),E192&gt;0,F192=E192),"Draw",IF(AND(ISNUMBER(F192),ISNUMBER(E192),E192&gt;0,F192=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L192" s="50"/>
       <x:c r="M192" s="58"/>
       <x:c r="N192" s="58"/>
@@ -7743,8 +8495,12 @@
       <x:c r="G193" s="58"/>
       <x:c r="H193" s="58"/>
       <x:c r="I193" s="58"/>
-      <x:c r="J193" s="60"/>
-      <x:c r="K193" s="50"/>
+      <x:c r="J193" s="60" t="str">
+        <x:f>IF(A193="","",IF(K193="Subscription","",IF(E193=0,"",IF(ISNUMBER(G193),G193/E193,IF(ISNUMBER(I193),-ABS(I193)/E193,IF(ISNUMBER(H193),0,IF(AND(ISNUMBER(F193),ISNUMBER(E193),E193&gt;0,F193&gt;E193),(F193-E193)/E193,IF(AND(ISNUMBER(F193),ISNUMBER(E193),E193&gt;0,F193=E193),0,IF(AND(ISNUMBER(F193),ISNUMBER(E193),E193&gt;0,F193=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K193" s="50" t="str">
+        <x:f>IF(A193="","",IF(AND(ISNUMBER(E193),E193=0,OR(ISNUMBER(SEARCH("Free",D193&amp;"")),AND(ISNUMBER(F193),F193=0))),"Subscription",IF(ISNUMBER(G193),"Profit",IF(ISNUMBER(I193),"Loss",IF(ISNUMBER(H193),"Draw",IF(AND(ISNUMBER(F193),ISNUMBER(E193),E193&gt;0,F193&gt;E193),"Profit",IF(AND(ISNUMBER(F193),ISNUMBER(E193),E193&gt;0,F193=E193),"Draw",IF(AND(ISNUMBER(F193),ISNUMBER(E193),E193&gt;0,F193=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L193" s="50"/>
       <x:c r="M193" s="58"/>
       <x:c r="N193" s="58"/>
@@ -7776,8 +8532,12 @@
       <x:c r="G194" s="58"/>
       <x:c r="H194" s="58"/>
       <x:c r="I194" s="58"/>
-      <x:c r="J194" s="60"/>
-      <x:c r="K194" s="50"/>
+      <x:c r="J194" s="60" t="str">
+        <x:f>IF(A194="","",IF(K194="Subscription","",IF(E194=0,"",IF(ISNUMBER(G194),G194/E194,IF(ISNUMBER(I194),-ABS(I194)/E194,IF(ISNUMBER(H194),0,IF(AND(ISNUMBER(F194),ISNUMBER(E194),E194&gt;0,F194&gt;E194),(F194-E194)/E194,IF(AND(ISNUMBER(F194),ISNUMBER(E194),E194&gt;0,F194=E194),0,IF(AND(ISNUMBER(F194),ISNUMBER(E194),E194&gt;0,F194=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K194" s="50" t="str">
+        <x:f>IF(A194="","",IF(AND(ISNUMBER(E194),E194=0,OR(ISNUMBER(SEARCH("Free",D194&amp;"")),AND(ISNUMBER(F194),F194=0))),"Subscription",IF(ISNUMBER(G194),"Profit",IF(ISNUMBER(I194),"Loss",IF(ISNUMBER(H194),"Draw",IF(AND(ISNUMBER(F194),ISNUMBER(E194),E194&gt;0,F194&gt;E194),"Profit",IF(AND(ISNUMBER(F194),ISNUMBER(E194),E194&gt;0,F194=E194),"Draw",IF(AND(ISNUMBER(F194),ISNUMBER(E194),E194&gt;0,F194=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L194" s="50"/>
       <x:c r="M194" s="58"/>
       <x:c r="N194" s="58"/>
@@ -7809,8 +8569,12 @@
       <x:c r="G195" s="58"/>
       <x:c r="H195" s="58"/>
       <x:c r="I195" s="58"/>
-      <x:c r="J195" s="60"/>
-      <x:c r="K195" s="50"/>
+      <x:c r="J195" s="60" t="str">
+        <x:f>IF(A195="","",IF(K195="Subscription","",IF(E195=0,"",IF(ISNUMBER(G195),G195/E195,IF(ISNUMBER(I195),-ABS(I195)/E195,IF(ISNUMBER(H195),0,IF(AND(ISNUMBER(F195),ISNUMBER(E195),E195&gt;0,F195&gt;E195),(F195-E195)/E195,IF(AND(ISNUMBER(F195),ISNUMBER(E195),E195&gt;0,F195=E195),0,IF(AND(ISNUMBER(F195),ISNUMBER(E195),E195&gt;0,F195=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K195" s="50" t="str">
+        <x:f>IF(A195="","",IF(AND(ISNUMBER(E195),E195=0,OR(ISNUMBER(SEARCH("Free",D195&amp;"")),AND(ISNUMBER(F195),F195=0))),"Subscription",IF(ISNUMBER(G195),"Profit",IF(ISNUMBER(I195),"Loss",IF(ISNUMBER(H195),"Draw",IF(AND(ISNUMBER(F195),ISNUMBER(E195),E195&gt;0,F195&gt;E195),"Profit",IF(AND(ISNUMBER(F195),ISNUMBER(E195),E195&gt;0,F195=E195),"Draw",IF(AND(ISNUMBER(F195),ISNUMBER(E195),E195&gt;0,F195=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L195" s="50"/>
       <x:c r="M195" s="58"/>
       <x:c r="N195" s="58"/>
@@ -7842,8 +8606,12 @@
       <x:c r="G196" s="58"/>
       <x:c r="H196" s="58"/>
       <x:c r="I196" s="58"/>
-      <x:c r="J196" s="60"/>
-      <x:c r="K196" s="50"/>
+      <x:c r="J196" s="60" t="str">
+        <x:f>IF(A196="","",IF(K196="Subscription","",IF(E196=0,"",IF(ISNUMBER(G196),G196/E196,IF(ISNUMBER(I196),-ABS(I196)/E196,IF(ISNUMBER(H196),0,IF(AND(ISNUMBER(F196),ISNUMBER(E196),E196&gt;0,F196&gt;E196),(F196-E196)/E196,IF(AND(ISNUMBER(F196),ISNUMBER(E196),E196&gt;0,F196=E196),0,IF(AND(ISNUMBER(F196),ISNUMBER(E196),E196&gt;0,F196=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K196" s="50" t="str">
+        <x:f>IF(A196="","",IF(AND(ISNUMBER(E196),E196=0,OR(ISNUMBER(SEARCH("Free",D196&amp;"")),AND(ISNUMBER(F196),F196=0))),"Subscription",IF(ISNUMBER(G196),"Profit",IF(ISNUMBER(I196),"Loss",IF(ISNUMBER(H196),"Draw",IF(AND(ISNUMBER(F196),ISNUMBER(E196),E196&gt;0,F196&gt;E196),"Profit",IF(AND(ISNUMBER(F196),ISNUMBER(E196),E196&gt;0,F196=E196),"Draw",IF(AND(ISNUMBER(F196),ISNUMBER(E196),E196&gt;0,F196=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L196" s="50"/>
       <x:c r="M196" s="58"/>
       <x:c r="N196" s="58"/>
@@ -7875,8 +8643,12 @@
       <x:c r="G197" s="58"/>
       <x:c r="H197" s="58"/>
       <x:c r="I197" s="58"/>
-      <x:c r="J197" s="60"/>
-      <x:c r="K197" s="50"/>
+      <x:c r="J197" s="60" t="str">
+        <x:f>IF(A197="","",IF(K197="Subscription","",IF(E197=0,"",IF(ISNUMBER(G197),G197/E197,IF(ISNUMBER(I197),-ABS(I197)/E197,IF(ISNUMBER(H197),0,IF(AND(ISNUMBER(F197),ISNUMBER(E197),E197&gt;0,F197&gt;E197),(F197-E197)/E197,IF(AND(ISNUMBER(F197),ISNUMBER(E197),E197&gt;0,F197=E197),0,IF(AND(ISNUMBER(F197),ISNUMBER(E197),E197&gt;0,F197=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K197" s="50" t="str">
+        <x:f>IF(A197="","",IF(AND(ISNUMBER(E197),E197=0,OR(ISNUMBER(SEARCH("Free",D197&amp;"")),AND(ISNUMBER(F197),F197=0))),"Subscription",IF(ISNUMBER(G197),"Profit",IF(ISNUMBER(I197),"Loss",IF(ISNUMBER(H197),"Draw",IF(AND(ISNUMBER(F197),ISNUMBER(E197),E197&gt;0,F197&gt;E197),"Profit",IF(AND(ISNUMBER(F197),ISNUMBER(E197),E197&gt;0,F197=E197),"Draw",IF(AND(ISNUMBER(F197),ISNUMBER(E197),E197&gt;0,F197=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L197" s="50"/>
       <x:c r="M197" s="58"/>
       <x:c r="N197" s="58"/>
@@ -7908,8 +8680,12 @@
       <x:c r="G198" s="58"/>
       <x:c r="H198" s="58"/>
       <x:c r="I198" s="58"/>
-      <x:c r="J198" s="60"/>
-      <x:c r="K198" s="50"/>
+      <x:c r="J198" s="60" t="str">
+        <x:f>IF(A198="","",IF(K198="Subscription","",IF(E198=0,"",IF(ISNUMBER(G198),G198/E198,IF(ISNUMBER(I198),-ABS(I198)/E198,IF(ISNUMBER(H198),0,IF(AND(ISNUMBER(F198),ISNUMBER(E198),E198&gt;0,F198&gt;E198),(F198-E198)/E198,IF(AND(ISNUMBER(F198),ISNUMBER(E198),E198&gt;0,F198=E198),0,IF(AND(ISNUMBER(F198),ISNUMBER(E198),E198&gt;0,F198=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K198" s="50" t="str">
+        <x:f>IF(A198="","",IF(AND(ISNUMBER(E198),E198=0,OR(ISNUMBER(SEARCH("Free",D198&amp;"")),AND(ISNUMBER(F198),F198=0))),"Subscription",IF(ISNUMBER(G198),"Profit",IF(ISNUMBER(I198),"Loss",IF(ISNUMBER(H198),"Draw",IF(AND(ISNUMBER(F198),ISNUMBER(E198),E198&gt;0,F198&gt;E198),"Profit",IF(AND(ISNUMBER(F198),ISNUMBER(E198),E198&gt;0,F198=E198),"Draw",IF(AND(ISNUMBER(F198),ISNUMBER(E198),E198&gt;0,F198=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L198" s="50"/>
       <x:c r="M198" s="58"/>
       <x:c r="N198" s="58"/>
@@ -7941,8 +8717,12 @@
       <x:c r="G199" s="58"/>
       <x:c r="H199" s="58"/>
       <x:c r="I199" s="58"/>
-      <x:c r="J199" s="60"/>
-      <x:c r="K199" s="50"/>
+      <x:c r="J199" s="60" t="str">
+        <x:f>IF(A199="","",IF(K199="Subscription","",IF(E199=0,"",IF(ISNUMBER(G199),G199/E199,IF(ISNUMBER(I199),-ABS(I199)/E199,IF(ISNUMBER(H199),0,IF(AND(ISNUMBER(F199),ISNUMBER(E199),E199&gt;0,F199&gt;E199),(F199-E199)/E199,IF(AND(ISNUMBER(F199),ISNUMBER(E199),E199&gt;0,F199=E199),0,IF(AND(ISNUMBER(F199),ISNUMBER(E199),E199&gt;0,F199=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K199" s="50" t="str">
+        <x:f>IF(A199="","",IF(AND(ISNUMBER(E199),E199=0,OR(ISNUMBER(SEARCH("Free",D199&amp;"")),AND(ISNUMBER(F199),F199=0))),"Subscription",IF(ISNUMBER(G199),"Profit",IF(ISNUMBER(I199),"Loss",IF(ISNUMBER(H199),"Draw",IF(AND(ISNUMBER(F199),ISNUMBER(E199),E199&gt;0,F199&gt;E199),"Profit",IF(AND(ISNUMBER(F199),ISNUMBER(E199),E199&gt;0,F199=E199),"Draw",IF(AND(ISNUMBER(F199),ISNUMBER(E199),E199&gt;0,F199=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L199" s="50"/>
       <x:c r="M199" s="58"/>
       <x:c r="N199" s="58"/>
@@ -7974,8 +8754,12 @@
       <x:c r="G200" s="58"/>
       <x:c r="H200" s="58"/>
       <x:c r="I200" s="58"/>
-      <x:c r="J200" s="60"/>
-      <x:c r="K200" s="50"/>
+      <x:c r="J200" s="60" t="str">
+        <x:f>IF(A200="","",IF(K200="Subscription","",IF(E200=0,"",IF(ISNUMBER(G200),G200/E200,IF(ISNUMBER(I200),-ABS(I200)/E200,IF(ISNUMBER(H200),0,IF(AND(ISNUMBER(F200),ISNUMBER(E200),E200&gt;0,F200&gt;E200),(F200-E200)/E200,IF(AND(ISNUMBER(F200),ISNUMBER(E200),E200&gt;0,F200=E200),0,IF(AND(ISNUMBER(F200),ISNUMBER(E200),E200&gt;0,F200=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K200" s="50" t="str">
+        <x:f>IF(A200="","",IF(AND(ISNUMBER(E200),E200=0,OR(ISNUMBER(SEARCH("Free",D200&amp;"")),AND(ISNUMBER(F200),F200=0))),"Subscription",IF(ISNUMBER(G200),"Profit",IF(ISNUMBER(I200),"Loss",IF(ISNUMBER(H200),"Draw",IF(AND(ISNUMBER(F200),ISNUMBER(E200),E200&gt;0,F200&gt;E200),"Profit",IF(AND(ISNUMBER(F200),ISNUMBER(E200),E200&gt;0,F200=E200),"Draw",IF(AND(ISNUMBER(F200),ISNUMBER(E200),E200&gt;0,F200=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L200" s="50"/>
       <x:c r="M200" s="58"/>
       <x:c r="N200" s="58"/>
@@ -8007,8 +8791,12 @@
       <x:c r="G201" s="58"/>
       <x:c r="H201" s="58"/>
       <x:c r="I201" s="58"/>
-      <x:c r="J201" s="60"/>
-      <x:c r="K201" s="50"/>
+      <x:c r="J201" s="60" t="str">
+        <x:f>IF(A201="","",IF(K201="Subscription","",IF(E201=0,"",IF(ISNUMBER(G201),G201/E201,IF(ISNUMBER(I201),-ABS(I201)/E201,IF(ISNUMBER(H201),0,IF(AND(ISNUMBER(F201),ISNUMBER(E201),E201&gt;0,F201&gt;E201),(F201-E201)/E201,IF(AND(ISNUMBER(F201),ISNUMBER(E201),E201&gt;0,F201=E201),0,IF(AND(ISNUMBER(F201),ISNUMBER(E201),E201&gt;0,F201=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K201" s="50" t="str">
+        <x:f>IF(A201="","",IF(AND(ISNUMBER(E201),E201=0,OR(ISNUMBER(SEARCH("Free",D201&amp;"")),AND(ISNUMBER(F201),F201=0))),"Subscription",IF(ISNUMBER(G201),"Profit",IF(ISNUMBER(I201),"Loss",IF(ISNUMBER(H201),"Draw",IF(AND(ISNUMBER(F201),ISNUMBER(E201),E201&gt;0,F201&gt;E201),"Profit",IF(AND(ISNUMBER(F201),ISNUMBER(E201),E201&gt;0,F201=E201),"Draw",IF(AND(ISNUMBER(F201),ISNUMBER(E201),E201&gt;0,F201=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L201" s="50"/>
       <x:c r="M201" s="58"/>
       <x:c r="N201" s="58"/>
@@ -8040,8 +8828,12 @@
       <x:c r="G202" s="58"/>
       <x:c r="H202" s="58"/>
       <x:c r="I202" s="58"/>
-      <x:c r="J202" s="60"/>
-      <x:c r="K202" s="50"/>
+      <x:c r="J202" s="60" t="str">
+        <x:f>IF(A202="","",IF(K202="Subscription","",IF(E202=0,"",IF(ISNUMBER(G202),G202/E202,IF(ISNUMBER(I202),-ABS(I202)/E202,IF(ISNUMBER(H202),0,IF(AND(ISNUMBER(F202),ISNUMBER(E202),E202&gt;0,F202&gt;E202),(F202-E202)/E202,IF(AND(ISNUMBER(F202),ISNUMBER(E202),E202&gt;0,F202=E202),0,IF(AND(ISNUMBER(F202),ISNUMBER(E202),E202&gt;0,F202=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K202" s="50" t="str">
+        <x:f>IF(A202="","",IF(AND(ISNUMBER(E202),E202=0,OR(ISNUMBER(SEARCH("Free",D202&amp;"")),AND(ISNUMBER(F202),F202=0))),"Subscription",IF(ISNUMBER(G202),"Profit",IF(ISNUMBER(I202),"Loss",IF(ISNUMBER(H202),"Draw",IF(AND(ISNUMBER(F202),ISNUMBER(E202),E202&gt;0,F202&gt;E202),"Profit",IF(AND(ISNUMBER(F202),ISNUMBER(E202),E202&gt;0,F202=E202),"Draw",IF(AND(ISNUMBER(F202),ISNUMBER(E202),E202&gt;0,F202=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L202" s="50"/>
       <x:c r="M202" s="58"/>
       <x:c r="N202" s="58"/>
@@ -8073,8 +8865,12 @@
       <x:c r="G203" s="58"/>
       <x:c r="H203" s="58"/>
       <x:c r="I203" s="58"/>
-      <x:c r="J203" s="60"/>
-      <x:c r="K203" s="50"/>
+      <x:c r="J203" s="60" t="str">
+        <x:f>IF(A203="","",IF(K203="Subscription","",IF(E203=0,"",IF(ISNUMBER(G203),G203/E203,IF(ISNUMBER(I203),-ABS(I203)/E203,IF(ISNUMBER(H203),0,IF(AND(ISNUMBER(F203),ISNUMBER(E203),E203&gt;0,F203&gt;E203),(F203-E203)/E203,IF(AND(ISNUMBER(F203),ISNUMBER(E203),E203&gt;0,F203=E203),0,IF(AND(ISNUMBER(F203),ISNUMBER(E203),E203&gt;0,F203=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K203" s="50" t="str">
+        <x:f>IF(A203="","",IF(AND(ISNUMBER(E203),E203=0,OR(ISNUMBER(SEARCH("Free",D203&amp;"")),AND(ISNUMBER(F203),F203=0))),"Subscription",IF(ISNUMBER(G203),"Profit",IF(ISNUMBER(I203),"Loss",IF(ISNUMBER(H203),"Draw",IF(AND(ISNUMBER(F203),ISNUMBER(E203),E203&gt;0,F203&gt;E203),"Profit",IF(AND(ISNUMBER(F203),ISNUMBER(E203),E203&gt;0,F203=E203),"Draw",IF(AND(ISNUMBER(F203),ISNUMBER(E203),E203&gt;0,F203=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L203" s="50"/>
       <x:c r="M203" s="58"/>
       <x:c r="N203" s="58"/>
@@ -8106,8 +8902,12 @@
       <x:c r="G204" s="58"/>
       <x:c r="H204" s="58"/>
       <x:c r="I204" s="58"/>
-      <x:c r="J204" s="60"/>
-      <x:c r="K204" s="50"/>
+      <x:c r="J204" s="60" t="str">
+        <x:f>IF(A204="","",IF(K204="Subscription","",IF(E204=0,"",IF(ISNUMBER(G204),G204/E204,IF(ISNUMBER(I204),-ABS(I204)/E204,IF(ISNUMBER(H204),0,IF(AND(ISNUMBER(F204),ISNUMBER(E204),E204&gt;0,F204&gt;E204),(F204-E204)/E204,IF(AND(ISNUMBER(F204),ISNUMBER(E204),E204&gt;0,F204=E204),0,IF(AND(ISNUMBER(F204),ISNUMBER(E204),E204&gt;0,F204=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K204" s="50" t="str">
+        <x:f>IF(A204="","",IF(AND(ISNUMBER(E204),E204=0,OR(ISNUMBER(SEARCH("Free",D204&amp;"")),AND(ISNUMBER(F204),F204=0))),"Subscription",IF(ISNUMBER(G204),"Profit",IF(ISNUMBER(I204),"Loss",IF(ISNUMBER(H204),"Draw",IF(AND(ISNUMBER(F204),ISNUMBER(E204),E204&gt;0,F204&gt;E204),"Profit",IF(AND(ISNUMBER(F204),ISNUMBER(E204),E204&gt;0,F204=E204),"Draw",IF(AND(ISNUMBER(F204),ISNUMBER(E204),E204&gt;0,F204=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L204" s="50"/>
       <x:c r="M204" s="58"/>
       <x:c r="N204" s="58"/>
@@ -8139,8 +8939,12 @@
       <x:c r="G205" s="58"/>
       <x:c r="H205" s="58"/>
       <x:c r="I205" s="58"/>
-      <x:c r="J205" s="60"/>
-      <x:c r="K205" s="50"/>
+      <x:c r="J205" s="60" t="str">
+        <x:f>IF(A205="","",IF(K205="Subscription","",IF(E205=0,"",IF(ISNUMBER(G205),G205/E205,IF(ISNUMBER(I205),-ABS(I205)/E205,IF(ISNUMBER(H205),0,IF(AND(ISNUMBER(F205),ISNUMBER(E205),E205&gt;0,F205&gt;E205),(F205-E205)/E205,IF(AND(ISNUMBER(F205),ISNUMBER(E205),E205&gt;0,F205=E205),0,IF(AND(ISNUMBER(F205),ISNUMBER(E205),E205&gt;0,F205=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K205" s="50" t="str">
+        <x:f>IF(A205="","",IF(AND(ISNUMBER(E205),E205=0,OR(ISNUMBER(SEARCH("Free",D205&amp;"")),AND(ISNUMBER(F205),F205=0))),"Subscription",IF(ISNUMBER(G205),"Profit",IF(ISNUMBER(I205),"Loss",IF(ISNUMBER(H205),"Draw",IF(AND(ISNUMBER(F205),ISNUMBER(E205),E205&gt;0,F205&gt;E205),"Profit",IF(AND(ISNUMBER(F205),ISNUMBER(E205),E205&gt;0,F205=E205),"Draw",IF(AND(ISNUMBER(F205),ISNUMBER(E205),E205&gt;0,F205=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L205" s="50"/>
       <x:c r="M205" s="58"/>
       <x:c r="N205" s="58"/>
@@ -8172,8 +8976,12 @@
       <x:c r="G206" s="58"/>
       <x:c r="H206" s="58"/>
       <x:c r="I206" s="58"/>
-      <x:c r="J206" s="60"/>
-      <x:c r="K206" s="50"/>
+      <x:c r="J206" s="60" t="str">
+        <x:f>IF(A206="","",IF(K206="Subscription","",IF(E206=0,"",IF(ISNUMBER(G206),G206/E206,IF(ISNUMBER(I206),-ABS(I206)/E206,IF(ISNUMBER(H206),0,IF(AND(ISNUMBER(F206),ISNUMBER(E206),E206&gt;0,F206&gt;E206),(F206-E206)/E206,IF(AND(ISNUMBER(F206),ISNUMBER(E206),E206&gt;0,F206=E206),0,IF(AND(ISNUMBER(F206),ISNUMBER(E206),E206&gt;0,F206=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K206" s="50" t="str">
+        <x:f>IF(A206="","",IF(AND(ISNUMBER(E206),E206=0,OR(ISNUMBER(SEARCH("Free",D206&amp;"")),AND(ISNUMBER(F206),F206=0))),"Subscription",IF(ISNUMBER(G206),"Profit",IF(ISNUMBER(I206),"Loss",IF(ISNUMBER(H206),"Draw",IF(AND(ISNUMBER(F206),ISNUMBER(E206),E206&gt;0,F206&gt;E206),"Profit",IF(AND(ISNUMBER(F206),ISNUMBER(E206),E206&gt;0,F206=E206),"Draw",IF(AND(ISNUMBER(F206),ISNUMBER(E206),E206&gt;0,F206=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L206" s="50"/>
       <x:c r="M206" s="58"/>
       <x:c r="N206" s="58"/>
@@ -8205,8 +9013,12 @@
       <x:c r="G207" s="58"/>
       <x:c r="H207" s="58"/>
       <x:c r="I207" s="58"/>
-      <x:c r="J207" s="60"/>
-      <x:c r="K207" s="50"/>
+      <x:c r="J207" s="60" t="str">
+        <x:f>IF(A207="","",IF(K207="Subscription","",IF(E207=0,"",IF(ISNUMBER(G207),G207/E207,IF(ISNUMBER(I207),-ABS(I207)/E207,IF(ISNUMBER(H207),0,IF(AND(ISNUMBER(F207),ISNUMBER(E207),E207&gt;0,F207&gt;E207),(F207-E207)/E207,IF(AND(ISNUMBER(F207),ISNUMBER(E207),E207&gt;0,F207=E207),0,IF(AND(ISNUMBER(F207),ISNUMBER(E207),E207&gt;0,F207=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K207" s="50" t="str">
+        <x:f>IF(A207="","",IF(AND(ISNUMBER(E207),E207=0,OR(ISNUMBER(SEARCH("Free",D207&amp;"")),AND(ISNUMBER(F207),F207=0))),"Subscription",IF(ISNUMBER(G207),"Profit",IF(ISNUMBER(I207),"Loss",IF(ISNUMBER(H207),"Draw",IF(AND(ISNUMBER(F207),ISNUMBER(E207),E207&gt;0,F207&gt;E207),"Profit",IF(AND(ISNUMBER(F207),ISNUMBER(E207),E207&gt;0,F207=E207),"Draw",IF(AND(ISNUMBER(F207),ISNUMBER(E207),E207&gt;0,F207=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L207" s="50"/>
       <x:c r="M207" s="58"/>
       <x:c r="N207" s="58"/>
@@ -8238,8 +9050,12 @@
       <x:c r="G208" s="58"/>
       <x:c r="H208" s="58"/>
       <x:c r="I208" s="58"/>
-      <x:c r="J208" s="60"/>
-      <x:c r="K208" s="50"/>
+      <x:c r="J208" s="60" t="str">
+        <x:f>IF(A208="","",IF(K208="Subscription","",IF(E208=0,"",IF(ISNUMBER(G208),G208/E208,IF(ISNUMBER(I208),-ABS(I208)/E208,IF(ISNUMBER(H208),0,IF(AND(ISNUMBER(F208),ISNUMBER(E208),E208&gt;0,F208&gt;E208),(F208-E208)/E208,IF(AND(ISNUMBER(F208),ISNUMBER(E208),E208&gt;0,F208=E208),0,IF(AND(ISNUMBER(F208),ISNUMBER(E208),E208&gt;0,F208=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K208" s="50" t="str">
+        <x:f>IF(A208="","",IF(AND(ISNUMBER(E208),E208=0,OR(ISNUMBER(SEARCH("Free",D208&amp;"")),AND(ISNUMBER(F208),F208=0))),"Subscription",IF(ISNUMBER(G208),"Profit",IF(ISNUMBER(I208),"Loss",IF(ISNUMBER(H208),"Draw",IF(AND(ISNUMBER(F208),ISNUMBER(E208),E208&gt;0,F208&gt;E208),"Profit",IF(AND(ISNUMBER(F208),ISNUMBER(E208),E208&gt;0,F208=E208),"Draw",IF(AND(ISNUMBER(F208),ISNUMBER(E208),E208&gt;0,F208=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L208" s="50"/>
       <x:c r="M208" s="58"/>
       <x:c r="N208" s="58"/>
@@ -8271,8 +9087,12 @@
       <x:c r="G209" s="58"/>
       <x:c r="H209" s="58"/>
       <x:c r="I209" s="58"/>
-      <x:c r="J209" s="60"/>
-      <x:c r="K209" s="50"/>
+      <x:c r="J209" s="60" t="str">
+        <x:f>IF(A209="","",IF(K209="Subscription","",IF(E209=0,"",IF(ISNUMBER(G209),G209/E209,IF(ISNUMBER(I209),-ABS(I209)/E209,IF(ISNUMBER(H209),0,IF(AND(ISNUMBER(F209),ISNUMBER(E209),E209&gt;0,F209&gt;E209),(F209-E209)/E209,IF(AND(ISNUMBER(F209),ISNUMBER(E209),E209&gt;0,F209=E209),0,IF(AND(ISNUMBER(F209),ISNUMBER(E209),E209&gt;0,F209=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K209" s="50" t="str">
+        <x:f>IF(A209="","",IF(AND(ISNUMBER(E209),E209=0,OR(ISNUMBER(SEARCH("Free",D209&amp;"")),AND(ISNUMBER(F209),F209=0))),"Subscription",IF(ISNUMBER(G209),"Profit",IF(ISNUMBER(I209),"Loss",IF(ISNUMBER(H209),"Draw",IF(AND(ISNUMBER(F209),ISNUMBER(E209),E209&gt;0,F209&gt;E209),"Profit",IF(AND(ISNUMBER(F209),ISNUMBER(E209),E209&gt;0,F209=E209),"Draw",IF(AND(ISNUMBER(F209),ISNUMBER(E209),E209&gt;0,F209=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L209" s="50"/>
       <x:c r="M209" s="58"/>
       <x:c r="N209" s="58"/>
@@ -8304,8 +9124,12 @@
       <x:c r="G210" s="58"/>
       <x:c r="H210" s="58"/>
       <x:c r="I210" s="58"/>
-      <x:c r="J210" s="60"/>
-      <x:c r="K210" s="50"/>
+      <x:c r="J210" s="60" t="str">
+        <x:f>IF(A210="","",IF(K210="Subscription","",IF(E210=0,"",IF(ISNUMBER(G210),G210/E210,IF(ISNUMBER(I210),-ABS(I210)/E210,IF(ISNUMBER(H210),0,IF(AND(ISNUMBER(F210),ISNUMBER(E210),E210&gt;0,F210&gt;E210),(F210-E210)/E210,IF(AND(ISNUMBER(F210),ISNUMBER(E210),E210&gt;0,F210=E210),0,IF(AND(ISNUMBER(F210),ISNUMBER(E210),E210&gt;0,F210=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K210" s="50" t="str">
+        <x:f>IF(A210="","",IF(AND(ISNUMBER(E210),E210=0,OR(ISNUMBER(SEARCH("Free",D210&amp;"")),AND(ISNUMBER(F210),F210=0))),"Subscription",IF(ISNUMBER(G210),"Profit",IF(ISNUMBER(I210),"Loss",IF(ISNUMBER(H210),"Draw",IF(AND(ISNUMBER(F210),ISNUMBER(E210),E210&gt;0,F210&gt;E210),"Profit",IF(AND(ISNUMBER(F210),ISNUMBER(E210),E210&gt;0,F210=E210),"Draw",IF(AND(ISNUMBER(F210),ISNUMBER(E210),E210&gt;0,F210=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L210" s="50"/>
       <x:c r="M210" s="58"/>
       <x:c r="N210" s="58"/>
@@ -8337,8 +9161,12 @@
       <x:c r="G211" s="58"/>
       <x:c r="H211" s="58"/>
       <x:c r="I211" s="58"/>
-      <x:c r="J211" s="60"/>
-      <x:c r="K211" s="50"/>
+      <x:c r="J211" s="60" t="str">
+        <x:f>IF(A211="","",IF(K211="Subscription","",IF(E211=0,"",IF(ISNUMBER(G211),G211/E211,IF(ISNUMBER(I211),-ABS(I211)/E211,IF(ISNUMBER(H211),0,IF(AND(ISNUMBER(F211),ISNUMBER(E211),E211&gt;0,F211&gt;E211),(F211-E211)/E211,IF(AND(ISNUMBER(F211),ISNUMBER(E211),E211&gt;0,F211=E211),0,IF(AND(ISNUMBER(F211),ISNUMBER(E211),E211&gt;0,F211=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K211" s="50" t="str">
+        <x:f>IF(A211="","",IF(AND(ISNUMBER(E211),E211=0,OR(ISNUMBER(SEARCH("Free",D211&amp;"")),AND(ISNUMBER(F211),F211=0))),"Subscription",IF(ISNUMBER(G211),"Profit",IF(ISNUMBER(I211),"Loss",IF(ISNUMBER(H211),"Draw",IF(AND(ISNUMBER(F211),ISNUMBER(E211),E211&gt;0,F211&gt;E211),"Profit",IF(AND(ISNUMBER(F211),ISNUMBER(E211),E211&gt;0,F211=E211),"Draw",IF(AND(ISNUMBER(F211),ISNUMBER(E211),E211&gt;0,F211=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L211" s="50"/>
       <x:c r="M211" s="58"/>
       <x:c r="N211" s="58"/>
@@ -8370,8 +9198,12 @@
       <x:c r="G212" s="58"/>
       <x:c r="H212" s="58"/>
       <x:c r="I212" s="58"/>
-      <x:c r="J212" s="60"/>
-      <x:c r="K212" s="50"/>
+      <x:c r="J212" s="60" t="str">
+        <x:f>IF(A212="","",IF(K212="Subscription","",IF(E212=0,"",IF(ISNUMBER(G212),G212/E212,IF(ISNUMBER(I212),-ABS(I212)/E212,IF(ISNUMBER(H212),0,IF(AND(ISNUMBER(F212),ISNUMBER(E212),E212&gt;0,F212&gt;E212),(F212-E212)/E212,IF(AND(ISNUMBER(F212),ISNUMBER(E212),E212&gt;0,F212=E212),0,IF(AND(ISNUMBER(F212),ISNUMBER(E212),E212&gt;0,F212=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K212" s="50" t="str">
+        <x:f>IF(A212="","",IF(AND(ISNUMBER(E212),E212=0,OR(ISNUMBER(SEARCH("Free",D212&amp;"")),AND(ISNUMBER(F212),F212=0))),"Subscription",IF(ISNUMBER(G212),"Profit",IF(ISNUMBER(I212),"Loss",IF(ISNUMBER(H212),"Draw",IF(AND(ISNUMBER(F212),ISNUMBER(E212),E212&gt;0,F212&gt;E212),"Profit",IF(AND(ISNUMBER(F212),ISNUMBER(E212),E212&gt;0,F212=E212),"Draw",IF(AND(ISNUMBER(F212),ISNUMBER(E212),E212&gt;0,F212=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L212" s="50"/>
       <x:c r="M212" s="58"/>
       <x:c r="N212" s="58"/>
@@ -8403,8 +9235,12 @@
       <x:c r="G213" s="58"/>
       <x:c r="H213" s="58"/>
       <x:c r="I213" s="58"/>
-      <x:c r="J213" s="60"/>
-      <x:c r="K213" s="50"/>
+      <x:c r="J213" s="60" t="str">
+        <x:f>IF(A213="","",IF(K213="Subscription","",IF(E213=0,"",IF(ISNUMBER(G213),G213/E213,IF(ISNUMBER(I213),-ABS(I213)/E213,IF(ISNUMBER(H213),0,IF(AND(ISNUMBER(F213),ISNUMBER(E213),E213&gt;0,F213&gt;E213),(F213-E213)/E213,IF(AND(ISNUMBER(F213),ISNUMBER(E213),E213&gt;0,F213=E213),0,IF(AND(ISNUMBER(F213),ISNUMBER(E213),E213&gt;0,F213=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K213" s="50" t="str">
+        <x:f>IF(A213="","",IF(AND(ISNUMBER(E213),E213=0,OR(ISNUMBER(SEARCH("Free",D213&amp;"")),AND(ISNUMBER(F213),F213=0))),"Subscription",IF(ISNUMBER(G213),"Profit",IF(ISNUMBER(I213),"Loss",IF(ISNUMBER(H213),"Draw",IF(AND(ISNUMBER(F213),ISNUMBER(E213),E213&gt;0,F213&gt;E213),"Profit",IF(AND(ISNUMBER(F213),ISNUMBER(E213),E213&gt;0,F213=E213),"Draw",IF(AND(ISNUMBER(F213),ISNUMBER(E213),E213&gt;0,F213=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L213" s="50"/>
       <x:c r="M213" s="58"/>
       <x:c r="N213" s="58"/>
@@ -8436,8 +9272,12 @@
       <x:c r="G214" s="58"/>
       <x:c r="H214" s="58"/>
       <x:c r="I214" s="58"/>
-      <x:c r="J214" s="60"/>
-      <x:c r="K214" s="50"/>
+      <x:c r="J214" s="60" t="str">
+        <x:f>IF(A214="","",IF(K214="Subscription","",IF(E214=0,"",IF(ISNUMBER(G214),G214/E214,IF(ISNUMBER(I214),-ABS(I214)/E214,IF(ISNUMBER(H214),0,IF(AND(ISNUMBER(F214),ISNUMBER(E214),E214&gt;0,F214&gt;E214),(F214-E214)/E214,IF(AND(ISNUMBER(F214),ISNUMBER(E214),E214&gt;0,F214=E214),0,IF(AND(ISNUMBER(F214),ISNUMBER(E214),E214&gt;0,F214=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K214" s="50" t="str">
+        <x:f>IF(A214="","",IF(AND(ISNUMBER(E214),E214=0,OR(ISNUMBER(SEARCH("Free",D214&amp;"")),AND(ISNUMBER(F214),F214=0))),"Subscription",IF(ISNUMBER(G214),"Profit",IF(ISNUMBER(I214),"Loss",IF(ISNUMBER(H214),"Draw",IF(AND(ISNUMBER(F214),ISNUMBER(E214),E214&gt;0,F214&gt;E214),"Profit",IF(AND(ISNUMBER(F214),ISNUMBER(E214),E214&gt;0,F214=E214),"Draw",IF(AND(ISNUMBER(F214),ISNUMBER(E214),E214&gt;0,F214=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L214" s="50"/>
       <x:c r="M214" s="58"/>
       <x:c r="N214" s="58"/>
@@ -8469,8 +9309,12 @@
       <x:c r="G215" s="58"/>
       <x:c r="H215" s="58"/>
       <x:c r="I215" s="58"/>
-      <x:c r="J215" s="60"/>
-      <x:c r="K215" s="50"/>
+      <x:c r="J215" s="60" t="str">
+        <x:f>IF(A215="","",IF(K215="Subscription","",IF(E215=0,"",IF(ISNUMBER(G215),G215/E215,IF(ISNUMBER(I215),-ABS(I215)/E215,IF(ISNUMBER(H215),0,IF(AND(ISNUMBER(F215),ISNUMBER(E215),E215&gt;0,F215&gt;E215),(F215-E215)/E215,IF(AND(ISNUMBER(F215),ISNUMBER(E215),E215&gt;0,F215=E215),0,IF(AND(ISNUMBER(F215),ISNUMBER(E215),E215&gt;0,F215=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K215" s="50" t="str">
+        <x:f>IF(A215="","",IF(AND(ISNUMBER(E215),E215=0,OR(ISNUMBER(SEARCH("Free",D215&amp;"")),AND(ISNUMBER(F215),F215=0))),"Subscription",IF(ISNUMBER(G215),"Profit",IF(ISNUMBER(I215),"Loss",IF(ISNUMBER(H215),"Draw",IF(AND(ISNUMBER(F215),ISNUMBER(E215),E215&gt;0,F215&gt;E215),"Profit",IF(AND(ISNUMBER(F215),ISNUMBER(E215),E215&gt;0,F215=E215),"Draw",IF(AND(ISNUMBER(F215),ISNUMBER(E215),E215&gt;0,F215=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L215" s="50"/>
       <x:c r="M215" s="58"/>
       <x:c r="N215" s="58"/>
@@ -8502,8 +9346,12 @@
       <x:c r="G216" s="58"/>
       <x:c r="H216" s="58"/>
       <x:c r="I216" s="58"/>
-      <x:c r="J216" s="60"/>
-      <x:c r="K216" s="50"/>
+      <x:c r="J216" s="60" t="str">
+        <x:f>IF(A216="","",IF(K216="Subscription","",IF(E216=0,"",IF(ISNUMBER(G216),G216/E216,IF(ISNUMBER(I216),-ABS(I216)/E216,IF(ISNUMBER(H216),0,IF(AND(ISNUMBER(F216),ISNUMBER(E216),E216&gt;0,F216&gt;E216),(F216-E216)/E216,IF(AND(ISNUMBER(F216),ISNUMBER(E216),E216&gt;0,F216=E216),0,IF(AND(ISNUMBER(F216),ISNUMBER(E216),E216&gt;0,F216=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K216" s="50" t="str">
+        <x:f>IF(A216="","",IF(AND(ISNUMBER(E216),E216=0,OR(ISNUMBER(SEARCH("Free",D216&amp;"")),AND(ISNUMBER(F216),F216=0))),"Subscription",IF(ISNUMBER(G216),"Profit",IF(ISNUMBER(I216),"Loss",IF(ISNUMBER(H216),"Draw",IF(AND(ISNUMBER(F216),ISNUMBER(E216),E216&gt;0,F216&gt;E216),"Profit",IF(AND(ISNUMBER(F216),ISNUMBER(E216),E216&gt;0,F216=E216),"Draw",IF(AND(ISNUMBER(F216),ISNUMBER(E216),E216&gt;0,F216=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L216" s="50"/>
       <x:c r="M216" s="58"/>
       <x:c r="N216" s="58"/>
@@ -8535,8 +9383,12 @@
       <x:c r="G217" s="58"/>
       <x:c r="H217" s="58"/>
       <x:c r="I217" s="58"/>
-      <x:c r="J217" s="60"/>
-      <x:c r="K217" s="50"/>
+      <x:c r="J217" s="60" t="str">
+        <x:f>IF(A217="","",IF(K217="Subscription","",IF(E217=0,"",IF(ISNUMBER(G217),G217/E217,IF(ISNUMBER(I217),-ABS(I217)/E217,IF(ISNUMBER(H217),0,IF(AND(ISNUMBER(F217),ISNUMBER(E217),E217&gt;0,F217&gt;E217),(F217-E217)/E217,IF(AND(ISNUMBER(F217),ISNUMBER(E217),E217&gt;0,F217=E217),0,IF(AND(ISNUMBER(F217),ISNUMBER(E217),E217&gt;0,F217=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K217" s="50" t="str">
+        <x:f>IF(A217="","",IF(AND(ISNUMBER(E217),E217=0,OR(ISNUMBER(SEARCH("Free",D217&amp;"")),AND(ISNUMBER(F217),F217=0))),"Subscription",IF(ISNUMBER(G217),"Profit",IF(ISNUMBER(I217),"Loss",IF(ISNUMBER(H217),"Draw",IF(AND(ISNUMBER(F217),ISNUMBER(E217),E217&gt;0,F217&gt;E217),"Profit",IF(AND(ISNUMBER(F217),ISNUMBER(E217),E217&gt;0,F217=E217),"Draw",IF(AND(ISNUMBER(F217),ISNUMBER(E217),E217&gt;0,F217=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L217" s="50"/>
       <x:c r="M217" s="58"/>
       <x:c r="N217" s="58"/>
@@ -8568,8 +9420,12 @@
       <x:c r="G218" s="58"/>
       <x:c r="H218" s="58"/>
       <x:c r="I218" s="58"/>
-      <x:c r="J218" s="60"/>
-      <x:c r="K218" s="50"/>
+      <x:c r="J218" s="60" t="str">
+        <x:f>IF(A218="","",IF(K218="Subscription","",IF(E218=0,"",IF(ISNUMBER(G218),G218/E218,IF(ISNUMBER(I218),-ABS(I218)/E218,IF(ISNUMBER(H218),0,IF(AND(ISNUMBER(F218),ISNUMBER(E218),E218&gt;0,F218&gt;E218),(F218-E218)/E218,IF(AND(ISNUMBER(F218),ISNUMBER(E218),E218&gt;0,F218=E218),0,IF(AND(ISNUMBER(F218),ISNUMBER(E218),E218&gt;0,F218=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K218" s="50" t="str">
+        <x:f>IF(A218="","",IF(AND(ISNUMBER(E218),E218=0,OR(ISNUMBER(SEARCH("Free",D218&amp;"")),AND(ISNUMBER(F218),F218=0))),"Subscription",IF(ISNUMBER(G218),"Profit",IF(ISNUMBER(I218),"Loss",IF(ISNUMBER(H218),"Draw",IF(AND(ISNUMBER(F218),ISNUMBER(E218),E218&gt;0,F218&gt;E218),"Profit",IF(AND(ISNUMBER(F218),ISNUMBER(E218),E218&gt;0,F218=E218),"Draw",IF(AND(ISNUMBER(F218),ISNUMBER(E218),E218&gt;0,F218=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L218" s="50"/>
       <x:c r="M218" s="58"/>
       <x:c r="N218" s="58"/>
@@ -8601,8 +9457,12 @@
       <x:c r="G219" s="58"/>
       <x:c r="H219" s="58"/>
       <x:c r="I219" s="58"/>
-      <x:c r="J219" s="60"/>
-      <x:c r="K219" s="50"/>
+      <x:c r="J219" s="60" t="str">
+        <x:f>IF(A219="","",IF(K219="Subscription","",IF(E219=0,"",IF(ISNUMBER(G219),G219/E219,IF(ISNUMBER(I219),-ABS(I219)/E219,IF(ISNUMBER(H219),0,IF(AND(ISNUMBER(F219),ISNUMBER(E219),E219&gt;0,F219&gt;E219),(F219-E219)/E219,IF(AND(ISNUMBER(F219),ISNUMBER(E219),E219&gt;0,F219=E219),0,IF(AND(ISNUMBER(F219),ISNUMBER(E219),E219&gt;0,F219=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K219" s="50" t="str">
+        <x:f>IF(A219="","",IF(AND(ISNUMBER(E219),E219=0,OR(ISNUMBER(SEARCH("Free",D219&amp;"")),AND(ISNUMBER(F219),F219=0))),"Subscription",IF(ISNUMBER(G219),"Profit",IF(ISNUMBER(I219),"Loss",IF(ISNUMBER(H219),"Draw",IF(AND(ISNUMBER(F219),ISNUMBER(E219),E219&gt;0,F219&gt;E219),"Profit",IF(AND(ISNUMBER(F219),ISNUMBER(E219),E219&gt;0,F219=E219),"Draw",IF(AND(ISNUMBER(F219),ISNUMBER(E219),E219&gt;0,F219=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L219" s="50"/>
       <x:c r="M219" s="58"/>
       <x:c r="N219" s="58"/>
@@ -8634,8 +9494,12 @@
       <x:c r="G220" s="58"/>
       <x:c r="H220" s="58"/>
       <x:c r="I220" s="58"/>
-      <x:c r="J220" s="60"/>
-      <x:c r="K220" s="50"/>
+      <x:c r="J220" s="60" t="str">
+        <x:f>IF(A220="","",IF(K220="Subscription","",IF(E220=0,"",IF(ISNUMBER(G220),G220/E220,IF(ISNUMBER(I220),-ABS(I220)/E220,IF(ISNUMBER(H220),0,IF(AND(ISNUMBER(F220),ISNUMBER(E220),E220&gt;0,F220&gt;E220),(F220-E220)/E220,IF(AND(ISNUMBER(F220),ISNUMBER(E220),E220&gt;0,F220=E220),0,IF(AND(ISNUMBER(F220),ISNUMBER(E220),E220&gt;0,F220=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K220" s="50" t="str">
+        <x:f>IF(A220="","",IF(AND(ISNUMBER(E220),E220=0,OR(ISNUMBER(SEARCH("Free",D220&amp;"")),AND(ISNUMBER(F220),F220=0))),"Subscription",IF(ISNUMBER(G220),"Profit",IF(ISNUMBER(I220),"Loss",IF(ISNUMBER(H220),"Draw",IF(AND(ISNUMBER(F220),ISNUMBER(E220),E220&gt;0,F220&gt;E220),"Profit",IF(AND(ISNUMBER(F220),ISNUMBER(E220),E220&gt;0,F220=E220),"Draw",IF(AND(ISNUMBER(F220),ISNUMBER(E220),E220&gt;0,F220=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L220" s="50"/>
       <x:c r="M220" s="58"/>
       <x:c r="N220" s="58"/>
@@ -8667,8 +9531,12 @@
       <x:c r="G221" s="58"/>
       <x:c r="H221" s="58"/>
       <x:c r="I221" s="58"/>
-      <x:c r="J221" s="60"/>
-      <x:c r="K221" s="50"/>
+      <x:c r="J221" s="60" t="str">
+        <x:f>IF(A221="","",IF(K221="Subscription","",IF(E221=0,"",IF(ISNUMBER(G221),G221/E221,IF(ISNUMBER(I221),-ABS(I221)/E221,IF(ISNUMBER(H221),0,IF(AND(ISNUMBER(F221),ISNUMBER(E221),E221&gt;0,F221&gt;E221),(F221-E221)/E221,IF(AND(ISNUMBER(F221),ISNUMBER(E221),E221&gt;0,F221=E221),0,IF(AND(ISNUMBER(F221),ISNUMBER(E221),E221&gt;0,F221=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K221" s="50" t="str">
+        <x:f>IF(A221="","",IF(AND(ISNUMBER(E221),E221=0,OR(ISNUMBER(SEARCH("Free",D221&amp;"")),AND(ISNUMBER(F221),F221=0))),"Subscription",IF(ISNUMBER(G221),"Profit",IF(ISNUMBER(I221),"Loss",IF(ISNUMBER(H221),"Draw",IF(AND(ISNUMBER(F221),ISNUMBER(E221),E221&gt;0,F221&gt;E221),"Profit",IF(AND(ISNUMBER(F221),ISNUMBER(E221),E221&gt;0,F221=E221),"Draw",IF(AND(ISNUMBER(F221),ISNUMBER(E221),E221&gt;0,F221=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L221" s="50"/>
       <x:c r="M221" s="58"/>
       <x:c r="N221" s="58"/>
@@ -8700,8 +9568,12 @@
       <x:c r="G222" s="58"/>
       <x:c r="H222" s="58"/>
       <x:c r="I222" s="58"/>
-      <x:c r="J222" s="60"/>
-      <x:c r="K222" s="50"/>
+      <x:c r="J222" s="60" t="str">
+        <x:f>IF(A222="","",IF(K222="Subscription","",IF(E222=0,"",IF(ISNUMBER(G222),G222/E222,IF(ISNUMBER(I222),-ABS(I222)/E222,IF(ISNUMBER(H222),0,IF(AND(ISNUMBER(F222),ISNUMBER(E222),E222&gt;0,F222&gt;E222),(F222-E222)/E222,IF(AND(ISNUMBER(F222),ISNUMBER(E222),E222&gt;0,F222=E222),0,IF(AND(ISNUMBER(F222),ISNUMBER(E222),E222&gt;0,F222=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K222" s="50" t="str">
+        <x:f>IF(A222="","",IF(AND(ISNUMBER(E222),E222=0,OR(ISNUMBER(SEARCH("Free",D222&amp;"")),AND(ISNUMBER(F222),F222=0))),"Subscription",IF(ISNUMBER(G222),"Profit",IF(ISNUMBER(I222),"Loss",IF(ISNUMBER(H222),"Draw",IF(AND(ISNUMBER(F222),ISNUMBER(E222),E222&gt;0,F222&gt;E222),"Profit",IF(AND(ISNUMBER(F222),ISNUMBER(E222),E222&gt;0,F222=E222),"Draw",IF(AND(ISNUMBER(F222),ISNUMBER(E222),E222&gt;0,F222=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L222" s="50"/>
       <x:c r="M222" s="58"/>
       <x:c r="N222" s="58"/>
@@ -8733,8 +9605,12 @@
       <x:c r="G223" s="58"/>
       <x:c r="H223" s="58"/>
       <x:c r="I223" s="58"/>
-      <x:c r="J223" s="60"/>
-      <x:c r="K223" s="50"/>
+      <x:c r="J223" s="60" t="str">
+        <x:f>IF(A223="","",IF(K223="Subscription","",IF(E223=0,"",IF(ISNUMBER(G223),G223/E223,IF(ISNUMBER(I223),-ABS(I223)/E223,IF(ISNUMBER(H223),0,IF(AND(ISNUMBER(F223),ISNUMBER(E223),E223&gt;0,F223&gt;E223),(F223-E223)/E223,IF(AND(ISNUMBER(F223),ISNUMBER(E223),E223&gt;0,F223=E223),0,IF(AND(ISNUMBER(F223),ISNUMBER(E223),E223&gt;0,F223=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K223" s="50" t="str">
+        <x:f>IF(A223="","",IF(AND(ISNUMBER(E223),E223=0,OR(ISNUMBER(SEARCH("Free",D223&amp;"")),AND(ISNUMBER(F223),F223=0))),"Subscription",IF(ISNUMBER(G223),"Profit",IF(ISNUMBER(I223),"Loss",IF(ISNUMBER(H223),"Draw",IF(AND(ISNUMBER(F223),ISNUMBER(E223),E223&gt;0,F223&gt;E223),"Profit",IF(AND(ISNUMBER(F223),ISNUMBER(E223),E223&gt;0,F223=E223),"Draw",IF(AND(ISNUMBER(F223),ISNUMBER(E223),E223&gt;0,F223=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L223" s="50"/>
       <x:c r="M223" s="58"/>
       <x:c r="N223" s="58"/>
@@ -8766,8 +9642,12 @@
       <x:c r="G224" s="58"/>
       <x:c r="H224" s="58"/>
       <x:c r="I224" s="58"/>
-      <x:c r="J224" s="60"/>
-      <x:c r="K224" s="50"/>
+      <x:c r="J224" s="60" t="str">
+        <x:f>IF(A224="","",IF(K224="Subscription","",IF(E224=0,"",IF(ISNUMBER(G224),G224/E224,IF(ISNUMBER(I224),-ABS(I224)/E224,IF(ISNUMBER(H224),0,IF(AND(ISNUMBER(F224),ISNUMBER(E224),E224&gt;0,F224&gt;E224),(F224-E224)/E224,IF(AND(ISNUMBER(F224),ISNUMBER(E224),E224&gt;0,F224=E224),0,IF(AND(ISNUMBER(F224),ISNUMBER(E224),E224&gt;0,F224=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K224" s="50" t="str">
+        <x:f>IF(A224="","",IF(AND(ISNUMBER(E224),E224=0,OR(ISNUMBER(SEARCH("Free",D224&amp;"")),AND(ISNUMBER(F224),F224=0))),"Subscription",IF(ISNUMBER(G224),"Profit",IF(ISNUMBER(I224),"Loss",IF(ISNUMBER(H224),"Draw",IF(AND(ISNUMBER(F224),ISNUMBER(E224),E224&gt;0,F224&gt;E224),"Profit",IF(AND(ISNUMBER(F224),ISNUMBER(E224),E224&gt;0,F224=E224),"Draw",IF(AND(ISNUMBER(F224),ISNUMBER(E224),E224&gt;0,F224=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L224" s="50"/>
       <x:c r="M224" s="58"/>
       <x:c r="N224" s="58"/>
@@ -8799,8 +9679,12 @@
       <x:c r="G225" s="58"/>
       <x:c r="H225" s="58"/>
       <x:c r="I225" s="58"/>
-      <x:c r="J225" s="60"/>
-      <x:c r="K225" s="50"/>
+      <x:c r="J225" s="60" t="str">
+        <x:f>IF(A225="","",IF(K225="Subscription","",IF(E225=0,"",IF(ISNUMBER(G225),G225/E225,IF(ISNUMBER(I225),-ABS(I225)/E225,IF(ISNUMBER(H225),0,IF(AND(ISNUMBER(F225),ISNUMBER(E225),E225&gt;0,F225&gt;E225),(F225-E225)/E225,IF(AND(ISNUMBER(F225),ISNUMBER(E225),E225&gt;0,F225=E225),0,IF(AND(ISNUMBER(F225),ISNUMBER(E225),E225&gt;0,F225=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K225" s="50" t="str">
+        <x:f>IF(A225="","",IF(AND(ISNUMBER(E225),E225=0,OR(ISNUMBER(SEARCH("Free",D225&amp;"")),AND(ISNUMBER(F225),F225=0))),"Subscription",IF(ISNUMBER(G225),"Profit",IF(ISNUMBER(I225),"Loss",IF(ISNUMBER(H225),"Draw",IF(AND(ISNUMBER(F225),ISNUMBER(E225),E225&gt;0,F225&gt;E225),"Profit",IF(AND(ISNUMBER(F225),ISNUMBER(E225),E225&gt;0,F225=E225),"Draw",IF(AND(ISNUMBER(F225),ISNUMBER(E225),E225&gt;0,F225=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L225" s="50"/>
       <x:c r="M225" s="58"/>
       <x:c r="N225" s="58"/>
@@ -8832,8 +9716,12 @@
       <x:c r="G226" s="58"/>
       <x:c r="H226" s="58"/>
       <x:c r="I226" s="58"/>
-      <x:c r="J226" s="60"/>
-      <x:c r="K226" s="50"/>
+      <x:c r="J226" s="60" t="str">
+        <x:f>IF(A226="","",IF(K226="Subscription","",IF(E226=0,"",IF(ISNUMBER(G226),G226/E226,IF(ISNUMBER(I226),-ABS(I226)/E226,IF(ISNUMBER(H226),0,IF(AND(ISNUMBER(F226),ISNUMBER(E226),E226&gt;0,F226&gt;E226),(F226-E226)/E226,IF(AND(ISNUMBER(F226),ISNUMBER(E226),E226&gt;0,F226=E226),0,IF(AND(ISNUMBER(F226),ISNUMBER(E226),E226&gt;0,F226=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K226" s="50" t="str">
+        <x:f>IF(A226="","",IF(AND(ISNUMBER(E226),E226=0,OR(ISNUMBER(SEARCH("Free",D226&amp;"")),AND(ISNUMBER(F226),F226=0))),"Subscription",IF(ISNUMBER(G226),"Profit",IF(ISNUMBER(I226),"Loss",IF(ISNUMBER(H226),"Draw",IF(AND(ISNUMBER(F226),ISNUMBER(E226),E226&gt;0,F226&gt;E226),"Profit",IF(AND(ISNUMBER(F226),ISNUMBER(E226),E226&gt;0,F226=E226),"Draw",IF(AND(ISNUMBER(F226),ISNUMBER(E226),E226&gt;0,F226=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L226" s="50"/>
       <x:c r="M226" s="58"/>
       <x:c r="N226" s="58"/>
@@ -8865,8 +9753,12 @@
       <x:c r="G227" s="58"/>
       <x:c r="H227" s="58"/>
       <x:c r="I227" s="58"/>
-      <x:c r="J227" s="60"/>
-      <x:c r="K227" s="50"/>
+      <x:c r="J227" s="60" t="str">
+        <x:f>IF(A227="","",IF(K227="Subscription","",IF(E227=0,"",IF(ISNUMBER(G227),G227/E227,IF(ISNUMBER(I227),-ABS(I227)/E227,IF(ISNUMBER(H227),0,IF(AND(ISNUMBER(F227),ISNUMBER(E227),E227&gt;0,F227&gt;E227),(F227-E227)/E227,IF(AND(ISNUMBER(F227),ISNUMBER(E227),E227&gt;0,F227=E227),0,IF(AND(ISNUMBER(F227),ISNUMBER(E227),E227&gt;0,F227=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K227" s="50" t="str">
+        <x:f>IF(A227="","",IF(AND(ISNUMBER(E227),E227=0,OR(ISNUMBER(SEARCH("Free",D227&amp;"")),AND(ISNUMBER(F227),F227=0))),"Subscription",IF(ISNUMBER(G227),"Profit",IF(ISNUMBER(I227),"Loss",IF(ISNUMBER(H227),"Draw",IF(AND(ISNUMBER(F227),ISNUMBER(E227),E227&gt;0,F227&gt;E227),"Profit",IF(AND(ISNUMBER(F227),ISNUMBER(E227),E227&gt;0,F227=E227),"Draw",IF(AND(ISNUMBER(F227),ISNUMBER(E227),E227&gt;0,F227=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L227" s="50"/>
       <x:c r="M227" s="58"/>
       <x:c r="N227" s="58"/>
@@ -8898,8 +9790,12 @@
       <x:c r="G228" s="58"/>
       <x:c r="H228" s="58"/>
       <x:c r="I228" s="58"/>
-      <x:c r="J228" s="60"/>
-      <x:c r="K228" s="50"/>
+      <x:c r="J228" s="60" t="str">
+        <x:f>IF(A228="","",IF(K228="Subscription","",IF(E228=0,"",IF(ISNUMBER(G228),G228/E228,IF(ISNUMBER(I228),-ABS(I228)/E228,IF(ISNUMBER(H228),0,IF(AND(ISNUMBER(F228),ISNUMBER(E228),E228&gt;0,F228&gt;E228),(F228-E228)/E228,IF(AND(ISNUMBER(F228),ISNUMBER(E228),E228&gt;0,F228=E228),0,IF(AND(ISNUMBER(F228),ISNUMBER(E228),E228&gt;0,F228=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K228" s="50" t="str">
+        <x:f>IF(A228="","",IF(AND(ISNUMBER(E228),E228=0,OR(ISNUMBER(SEARCH("Free",D228&amp;"")),AND(ISNUMBER(F228),F228=0))),"Subscription",IF(ISNUMBER(G228),"Profit",IF(ISNUMBER(I228),"Loss",IF(ISNUMBER(H228),"Draw",IF(AND(ISNUMBER(F228),ISNUMBER(E228),E228&gt;0,F228&gt;E228),"Profit",IF(AND(ISNUMBER(F228),ISNUMBER(E228),E228&gt;0,F228=E228),"Draw",IF(AND(ISNUMBER(F228),ISNUMBER(E228),E228&gt;0,F228=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L228" s="50"/>
       <x:c r="M228" s="58"/>
       <x:c r="N228" s="58"/>
@@ -8931,8 +9827,12 @@
       <x:c r="G229" s="58"/>
       <x:c r="H229" s="58"/>
       <x:c r="I229" s="58"/>
-      <x:c r="J229" s="60"/>
-      <x:c r="K229" s="50"/>
+      <x:c r="J229" s="60" t="str">
+        <x:f>IF(A229="","",IF(K229="Subscription","",IF(E229=0,"",IF(ISNUMBER(G229),G229/E229,IF(ISNUMBER(I229),-ABS(I229)/E229,IF(ISNUMBER(H229),0,IF(AND(ISNUMBER(F229),ISNUMBER(E229),E229&gt;0,F229&gt;E229),(F229-E229)/E229,IF(AND(ISNUMBER(F229),ISNUMBER(E229),E229&gt;0,F229=E229),0,IF(AND(ISNUMBER(F229),ISNUMBER(E229),E229&gt;0,F229=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K229" s="50" t="str">
+        <x:f>IF(A229="","",IF(AND(ISNUMBER(E229),E229=0,OR(ISNUMBER(SEARCH("Free",D229&amp;"")),AND(ISNUMBER(F229),F229=0))),"Subscription",IF(ISNUMBER(G229),"Profit",IF(ISNUMBER(I229),"Loss",IF(ISNUMBER(H229),"Draw",IF(AND(ISNUMBER(F229),ISNUMBER(E229),E229&gt;0,F229&gt;E229),"Profit",IF(AND(ISNUMBER(F229),ISNUMBER(E229),E229&gt;0,F229=E229),"Draw",IF(AND(ISNUMBER(F229),ISNUMBER(E229),E229&gt;0,F229=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L229" s="50"/>
       <x:c r="M229" s="58"/>
       <x:c r="N229" s="58"/>
@@ -8964,8 +9864,12 @@
       <x:c r="G230" s="58"/>
       <x:c r="H230" s="58"/>
       <x:c r="I230" s="58"/>
-      <x:c r="J230" s="60"/>
-      <x:c r="K230" s="50"/>
+      <x:c r="J230" s="60" t="str">
+        <x:f>IF(A230="","",IF(K230="Subscription","",IF(E230=0,"",IF(ISNUMBER(G230),G230/E230,IF(ISNUMBER(I230),-ABS(I230)/E230,IF(ISNUMBER(H230),0,IF(AND(ISNUMBER(F230),ISNUMBER(E230),E230&gt;0,F230&gt;E230),(F230-E230)/E230,IF(AND(ISNUMBER(F230),ISNUMBER(E230),E230&gt;0,F230=E230),0,IF(AND(ISNUMBER(F230),ISNUMBER(E230),E230&gt;0,F230=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K230" s="50" t="str">
+        <x:f>IF(A230="","",IF(AND(ISNUMBER(E230),E230=0,OR(ISNUMBER(SEARCH("Free",D230&amp;"")),AND(ISNUMBER(F230),F230=0))),"Subscription",IF(ISNUMBER(G230),"Profit",IF(ISNUMBER(I230),"Loss",IF(ISNUMBER(H230),"Draw",IF(AND(ISNUMBER(F230),ISNUMBER(E230),E230&gt;0,F230&gt;E230),"Profit",IF(AND(ISNUMBER(F230),ISNUMBER(E230),E230&gt;0,F230=E230),"Draw",IF(AND(ISNUMBER(F230),ISNUMBER(E230),E230&gt;0,F230=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L230" s="50"/>
       <x:c r="M230" s="58"/>
       <x:c r="N230" s="58"/>
@@ -8997,8 +9901,12 @@
       <x:c r="G231" s="58"/>
       <x:c r="H231" s="58"/>
       <x:c r="I231" s="58"/>
-      <x:c r="J231" s="60"/>
-      <x:c r="K231" s="50"/>
+      <x:c r="J231" s="60" t="str">
+        <x:f>IF(A231="","",IF(K231="Subscription","",IF(E231=0,"",IF(ISNUMBER(G231),G231/E231,IF(ISNUMBER(I231),-ABS(I231)/E231,IF(ISNUMBER(H231),0,IF(AND(ISNUMBER(F231),ISNUMBER(E231),E231&gt;0,F231&gt;E231),(F231-E231)/E231,IF(AND(ISNUMBER(F231),ISNUMBER(E231),E231&gt;0,F231=E231),0,IF(AND(ISNUMBER(F231),ISNUMBER(E231),E231&gt;0,F231=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K231" s="50" t="str">
+        <x:f>IF(A231="","",IF(AND(ISNUMBER(E231),E231=0,OR(ISNUMBER(SEARCH("Free",D231&amp;"")),AND(ISNUMBER(F231),F231=0))),"Subscription",IF(ISNUMBER(G231),"Profit",IF(ISNUMBER(I231),"Loss",IF(ISNUMBER(H231),"Draw",IF(AND(ISNUMBER(F231),ISNUMBER(E231),E231&gt;0,F231&gt;E231),"Profit",IF(AND(ISNUMBER(F231),ISNUMBER(E231),E231&gt;0,F231=E231),"Draw",IF(AND(ISNUMBER(F231),ISNUMBER(E231),E231&gt;0,F231=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L231" s="50"/>
       <x:c r="M231" s="58"/>
       <x:c r="N231" s="58"/>
@@ -9030,8 +9938,12 @@
       <x:c r="G232" s="58"/>
       <x:c r="H232" s="58"/>
       <x:c r="I232" s="58"/>
-      <x:c r="J232" s="60"/>
-      <x:c r="K232" s="50"/>
+      <x:c r="J232" s="60" t="str">
+        <x:f>IF(A232="","",IF(K232="Subscription","",IF(E232=0,"",IF(ISNUMBER(G232),G232/E232,IF(ISNUMBER(I232),-ABS(I232)/E232,IF(ISNUMBER(H232),0,IF(AND(ISNUMBER(F232),ISNUMBER(E232),E232&gt;0,F232&gt;E232),(F232-E232)/E232,IF(AND(ISNUMBER(F232),ISNUMBER(E232),E232&gt;0,F232=E232),0,IF(AND(ISNUMBER(F232),ISNUMBER(E232),E232&gt;0,F232=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K232" s="50" t="str">
+        <x:f>IF(A232="","",IF(AND(ISNUMBER(E232),E232=0,OR(ISNUMBER(SEARCH("Free",D232&amp;"")),AND(ISNUMBER(F232),F232=0))),"Subscription",IF(ISNUMBER(G232),"Profit",IF(ISNUMBER(I232),"Loss",IF(ISNUMBER(H232),"Draw",IF(AND(ISNUMBER(F232),ISNUMBER(E232),E232&gt;0,F232&gt;E232),"Profit",IF(AND(ISNUMBER(F232),ISNUMBER(E232),E232&gt;0,F232=E232),"Draw",IF(AND(ISNUMBER(F232),ISNUMBER(E232),E232&gt;0,F232=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L232" s="50"/>
       <x:c r="M232" s="58"/>
       <x:c r="N232" s="58"/>
@@ -9063,8 +9975,12 @@
       <x:c r="G233" s="58"/>
       <x:c r="H233" s="58"/>
       <x:c r="I233" s="58"/>
-      <x:c r="J233" s="60"/>
-      <x:c r="K233" s="50"/>
+      <x:c r="J233" s="60" t="str">
+        <x:f>IF(A233="","",IF(K233="Subscription","",IF(E233=0,"",IF(ISNUMBER(G233),G233/E233,IF(ISNUMBER(I233),-ABS(I233)/E233,IF(ISNUMBER(H233),0,IF(AND(ISNUMBER(F233),ISNUMBER(E233),E233&gt;0,F233&gt;E233),(F233-E233)/E233,IF(AND(ISNUMBER(F233),ISNUMBER(E233),E233&gt;0,F233=E233),0,IF(AND(ISNUMBER(F233),ISNUMBER(E233),E233&gt;0,F233=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K233" s="50" t="str">
+        <x:f>IF(A233="","",IF(AND(ISNUMBER(E233),E233=0,OR(ISNUMBER(SEARCH("Free",D233&amp;"")),AND(ISNUMBER(F233),F233=0))),"Subscription",IF(ISNUMBER(G233),"Profit",IF(ISNUMBER(I233),"Loss",IF(ISNUMBER(H233),"Draw",IF(AND(ISNUMBER(F233),ISNUMBER(E233),E233&gt;0,F233&gt;E233),"Profit",IF(AND(ISNUMBER(F233),ISNUMBER(E233),E233&gt;0,F233=E233),"Draw",IF(AND(ISNUMBER(F233),ISNUMBER(E233),E233&gt;0,F233=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L233" s="50"/>
       <x:c r="M233" s="58"/>
       <x:c r="N233" s="58"/>
@@ -9096,8 +10012,12 @@
       <x:c r="G234" s="58"/>
       <x:c r="H234" s="58"/>
       <x:c r="I234" s="58"/>
-      <x:c r="J234" s="60"/>
-      <x:c r="K234" s="50"/>
+      <x:c r="J234" s="60" t="str">
+        <x:f>IF(A234="","",IF(K234="Subscription","",IF(E234=0,"",IF(ISNUMBER(G234),G234/E234,IF(ISNUMBER(I234),-ABS(I234)/E234,IF(ISNUMBER(H234),0,IF(AND(ISNUMBER(F234),ISNUMBER(E234),E234&gt;0,F234&gt;E234),(F234-E234)/E234,IF(AND(ISNUMBER(F234),ISNUMBER(E234),E234&gt;0,F234=E234),0,IF(AND(ISNUMBER(F234),ISNUMBER(E234),E234&gt;0,F234=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K234" s="50" t="str">
+        <x:f>IF(A234="","",IF(AND(ISNUMBER(E234),E234=0,OR(ISNUMBER(SEARCH("Free",D234&amp;"")),AND(ISNUMBER(F234),F234=0))),"Subscription",IF(ISNUMBER(G234),"Profit",IF(ISNUMBER(I234),"Loss",IF(ISNUMBER(H234),"Draw",IF(AND(ISNUMBER(F234),ISNUMBER(E234),E234&gt;0,F234&gt;E234),"Profit",IF(AND(ISNUMBER(F234),ISNUMBER(E234),E234&gt;0,F234=E234),"Draw",IF(AND(ISNUMBER(F234),ISNUMBER(E234),E234&gt;0,F234=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L234" s="50"/>
       <x:c r="M234" s="58"/>
       <x:c r="N234" s="58"/>
@@ -9129,8 +10049,12 @@
       <x:c r="G235" s="58"/>
       <x:c r="H235" s="58"/>
       <x:c r="I235" s="58"/>
-      <x:c r="J235" s="60"/>
-      <x:c r="K235" s="50"/>
+      <x:c r="J235" s="60" t="str">
+        <x:f>IF(A235="","",IF(K235="Subscription","",IF(E235=0,"",IF(ISNUMBER(G235),G235/E235,IF(ISNUMBER(I235),-ABS(I235)/E235,IF(ISNUMBER(H235),0,IF(AND(ISNUMBER(F235),ISNUMBER(E235),E235&gt;0,F235&gt;E235),(F235-E235)/E235,IF(AND(ISNUMBER(F235),ISNUMBER(E235),E235&gt;0,F235=E235),0,IF(AND(ISNUMBER(F235),ISNUMBER(E235),E235&gt;0,F235=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K235" s="50" t="str">
+        <x:f>IF(A235="","",IF(AND(ISNUMBER(E235),E235=0,OR(ISNUMBER(SEARCH("Free",D235&amp;"")),AND(ISNUMBER(F235),F235=0))),"Subscription",IF(ISNUMBER(G235),"Profit",IF(ISNUMBER(I235),"Loss",IF(ISNUMBER(H235),"Draw",IF(AND(ISNUMBER(F235),ISNUMBER(E235),E235&gt;0,F235&gt;E235),"Profit",IF(AND(ISNUMBER(F235),ISNUMBER(E235),E235&gt;0,F235=E235),"Draw",IF(AND(ISNUMBER(F235),ISNUMBER(E235),E235&gt;0,F235=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L235" s="50"/>
       <x:c r="M235" s="58"/>
       <x:c r="N235" s="58"/>
@@ -9162,8 +10086,12 @@
       <x:c r="G236" s="58"/>
       <x:c r="H236" s="58"/>
       <x:c r="I236" s="58"/>
-      <x:c r="J236" s="60"/>
-      <x:c r="K236" s="50"/>
+      <x:c r="J236" s="60" t="str">
+        <x:f>IF(A236="","",IF(K236="Subscription","",IF(E236=0,"",IF(ISNUMBER(G236),G236/E236,IF(ISNUMBER(I236),-ABS(I236)/E236,IF(ISNUMBER(H236),0,IF(AND(ISNUMBER(F236),ISNUMBER(E236),E236&gt;0,F236&gt;E236),(F236-E236)/E236,IF(AND(ISNUMBER(F236),ISNUMBER(E236),E236&gt;0,F236=E236),0,IF(AND(ISNUMBER(F236),ISNUMBER(E236),E236&gt;0,F236=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K236" s="50" t="str">
+        <x:f>IF(A236="","",IF(AND(ISNUMBER(E236),E236=0,OR(ISNUMBER(SEARCH("Free",D236&amp;"")),AND(ISNUMBER(F236),F236=0))),"Subscription",IF(ISNUMBER(G236),"Profit",IF(ISNUMBER(I236),"Loss",IF(ISNUMBER(H236),"Draw",IF(AND(ISNUMBER(F236),ISNUMBER(E236),E236&gt;0,F236&gt;E236),"Profit",IF(AND(ISNUMBER(F236),ISNUMBER(E236),E236&gt;0,F236=E236),"Draw",IF(AND(ISNUMBER(F236),ISNUMBER(E236),E236&gt;0,F236=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L236" s="50"/>
       <x:c r="M236" s="58"/>
       <x:c r="N236" s="58"/>
@@ -9195,8 +10123,12 @@
       <x:c r="G237" s="58"/>
       <x:c r="H237" s="58"/>
       <x:c r="I237" s="58"/>
-      <x:c r="J237" s="60"/>
-      <x:c r="K237" s="50"/>
+      <x:c r="J237" s="60" t="str">
+        <x:f>IF(A237="","",IF(K237="Subscription","",IF(E237=0,"",IF(ISNUMBER(G237),G237/E237,IF(ISNUMBER(I237),-ABS(I237)/E237,IF(ISNUMBER(H237),0,IF(AND(ISNUMBER(F237),ISNUMBER(E237),E237&gt;0,F237&gt;E237),(F237-E237)/E237,IF(AND(ISNUMBER(F237),ISNUMBER(E237),E237&gt;0,F237=E237),0,IF(AND(ISNUMBER(F237),ISNUMBER(E237),E237&gt;0,F237=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K237" s="50" t="str">
+        <x:f>IF(A237="","",IF(AND(ISNUMBER(E237),E237=0,OR(ISNUMBER(SEARCH("Free",D237&amp;"")),AND(ISNUMBER(F237),F237=0))),"Subscription",IF(ISNUMBER(G237),"Profit",IF(ISNUMBER(I237),"Loss",IF(ISNUMBER(H237),"Draw",IF(AND(ISNUMBER(F237),ISNUMBER(E237),E237&gt;0,F237&gt;E237),"Profit",IF(AND(ISNUMBER(F237),ISNUMBER(E237),E237&gt;0,F237=E237),"Draw",IF(AND(ISNUMBER(F237),ISNUMBER(E237),E237&gt;0,F237=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L237" s="50"/>
       <x:c r="M237" s="58"/>
       <x:c r="N237" s="58"/>
@@ -9228,8 +10160,12 @@
       <x:c r="G238" s="58"/>
       <x:c r="H238" s="58"/>
       <x:c r="I238" s="58"/>
-      <x:c r="J238" s="60"/>
-      <x:c r="K238" s="50"/>
+      <x:c r="J238" s="60" t="str">
+        <x:f>IF(A238="","",IF(K238="Subscription","",IF(E238=0,"",IF(ISNUMBER(G238),G238/E238,IF(ISNUMBER(I238),-ABS(I238)/E238,IF(ISNUMBER(H238),0,IF(AND(ISNUMBER(F238),ISNUMBER(E238),E238&gt;0,F238&gt;E238),(F238-E238)/E238,IF(AND(ISNUMBER(F238),ISNUMBER(E238),E238&gt;0,F238=E238),0,IF(AND(ISNUMBER(F238),ISNUMBER(E238),E238&gt;0,F238=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K238" s="50" t="str">
+        <x:f>IF(A238="","",IF(AND(ISNUMBER(E238),E238=0,OR(ISNUMBER(SEARCH("Free",D238&amp;"")),AND(ISNUMBER(F238),F238=0))),"Subscription",IF(ISNUMBER(G238),"Profit",IF(ISNUMBER(I238),"Loss",IF(ISNUMBER(H238),"Draw",IF(AND(ISNUMBER(F238),ISNUMBER(E238),E238&gt;0,F238&gt;E238),"Profit",IF(AND(ISNUMBER(F238),ISNUMBER(E238),E238&gt;0,F238=E238),"Draw",IF(AND(ISNUMBER(F238),ISNUMBER(E238),E238&gt;0,F238=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L238" s="50"/>
       <x:c r="M238" s="58"/>
       <x:c r="N238" s="58"/>
@@ -9261,8 +10197,12 @@
       <x:c r="G239" s="58"/>
       <x:c r="H239" s="58"/>
       <x:c r="I239" s="58"/>
-      <x:c r="J239" s="60"/>
-      <x:c r="K239" s="50"/>
+      <x:c r="J239" s="60" t="str">
+        <x:f>IF(A239="","",IF(K239="Subscription","",IF(E239=0,"",IF(ISNUMBER(G239),G239/E239,IF(ISNUMBER(I239),-ABS(I239)/E239,IF(ISNUMBER(H239),0,IF(AND(ISNUMBER(F239),ISNUMBER(E239),E239&gt;0,F239&gt;E239),(F239-E239)/E239,IF(AND(ISNUMBER(F239),ISNUMBER(E239),E239&gt;0,F239=E239),0,IF(AND(ISNUMBER(F239),ISNUMBER(E239),E239&gt;0,F239=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K239" s="50" t="str">
+        <x:f>IF(A239="","",IF(AND(ISNUMBER(E239),E239=0,OR(ISNUMBER(SEARCH("Free",D239&amp;"")),AND(ISNUMBER(F239),F239=0))),"Subscription",IF(ISNUMBER(G239),"Profit",IF(ISNUMBER(I239),"Loss",IF(ISNUMBER(H239),"Draw",IF(AND(ISNUMBER(F239),ISNUMBER(E239),E239&gt;0,F239&gt;E239),"Profit",IF(AND(ISNUMBER(F239),ISNUMBER(E239),E239&gt;0,F239=E239),"Draw",IF(AND(ISNUMBER(F239),ISNUMBER(E239),E239&gt;0,F239=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L239" s="50"/>
       <x:c r="M239" s="58"/>
       <x:c r="N239" s="58"/>
@@ -9294,8 +10234,12 @@
       <x:c r="G240" s="58"/>
       <x:c r="H240" s="58"/>
       <x:c r="I240" s="58"/>
-      <x:c r="J240" s="60"/>
-      <x:c r="K240" s="50"/>
+      <x:c r="J240" s="60" t="str">
+        <x:f>IF(A240="","",IF(K240="Subscription","",IF(E240=0,"",IF(ISNUMBER(G240),G240/E240,IF(ISNUMBER(I240),-ABS(I240)/E240,IF(ISNUMBER(H240),0,IF(AND(ISNUMBER(F240),ISNUMBER(E240),E240&gt;0,F240&gt;E240),(F240-E240)/E240,IF(AND(ISNUMBER(F240),ISNUMBER(E240),E240&gt;0,F240=E240),0,IF(AND(ISNUMBER(F240),ISNUMBER(E240),E240&gt;0,F240=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K240" s="50" t="str">
+        <x:f>IF(A240="","",IF(AND(ISNUMBER(E240),E240=0,OR(ISNUMBER(SEARCH("Free",D240&amp;"")),AND(ISNUMBER(F240),F240=0))),"Subscription",IF(ISNUMBER(G240),"Profit",IF(ISNUMBER(I240),"Loss",IF(ISNUMBER(H240),"Draw",IF(AND(ISNUMBER(F240),ISNUMBER(E240),E240&gt;0,F240&gt;E240),"Profit",IF(AND(ISNUMBER(F240),ISNUMBER(E240),E240&gt;0,F240=E240),"Draw",IF(AND(ISNUMBER(F240),ISNUMBER(E240),E240&gt;0,F240=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L240" s="50"/>
       <x:c r="M240" s="58"/>
       <x:c r="N240" s="58"/>
@@ -9327,8 +10271,12 @@
       <x:c r="G241" s="58"/>
       <x:c r="H241" s="58"/>
       <x:c r="I241" s="58"/>
-      <x:c r="J241" s="60"/>
-      <x:c r="K241" s="50"/>
+      <x:c r="J241" s="60" t="str">
+        <x:f>IF(A241="","",IF(K241="Subscription","",IF(E241=0,"",IF(ISNUMBER(G241),G241/E241,IF(ISNUMBER(I241),-ABS(I241)/E241,IF(ISNUMBER(H241),0,IF(AND(ISNUMBER(F241),ISNUMBER(E241),E241&gt;0,F241&gt;E241),(F241-E241)/E241,IF(AND(ISNUMBER(F241),ISNUMBER(E241),E241&gt;0,F241=E241),0,IF(AND(ISNUMBER(F241),ISNUMBER(E241),E241&gt;0,F241=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K241" s="50" t="str">
+        <x:f>IF(A241="","",IF(AND(ISNUMBER(E241),E241=0,OR(ISNUMBER(SEARCH("Free",D241&amp;"")),AND(ISNUMBER(F241),F241=0))),"Subscription",IF(ISNUMBER(G241),"Profit",IF(ISNUMBER(I241),"Loss",IF(ISNUMBER(H241),"Draw",IF(AND(ISNUMBER(F241),ISNUMBER(E241),E241&gt;0,F241&gt;E241),"Profit",IF(AND(ISNUMBER(F241),ISNUMBER(E241),E241&gt;0,F241=E241),"Draw",IF(AND(ISNUMBER(F241),ISNUMBER(E241),E241&gt;0,F241=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L241" s="50"/>
       <x:c r="M241" s="58"/>
       <x:c r="N241" s="58"/>
@@ -9360,8 +10308,12 @@
       <x:c r="G242" s="58"/>
       <x:c r="H242" s="58"/>
       <x:c r="I242" s="58"/>
-      <x:c r="J242" s="60"/>
-      <x:c r="K242" s="50"/>
+      <x:c r="J242" s="60" t="str">
+        <x:f>IF(A242="","",IF(K242="Subscription","",IF(E242=0,"",IF(ISNUMBER(G242),G242/E242,IF(ISNUMBER(I242),-ABS(I242)/E242,IF(ISNUMBER(H242),0,IF(AND(ISNUMBER(F242),ISNUMBER(E242),E242&gt;0,F242&gt;E242),(F242-E242)/E242,IF(AND(ISNUMBER(F242),ISNUMBER(E242),E242&gt;0,F242=E242),0,IF(AND(ISNUMBER(F242),ISNUMBER(E242),E242&gt;0,F242=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K242" s="50" t="str">
+        <x:f>IF(A242="","",IF(AND(ISNUMBER(E242),E242=0,OR(ISNUMBER(SEARCH("Free",D242&amp;"")),AND(ISNUMBER(F242),F242=0))),"Subscription",IF(ISNUMBER(G242),"Profit",IF(ISNUMBER(I242),"Loss",IF(ISNUMBER(H242),"Draw",IF(AND(ISNUMBER(F242),ISNUMBER(E242),E242&gt;0,F242&gt;E242),"Profit",IF(AND(ISNUMBER(F242),ISNUMBER(E242),E242&gt;0,F242=E242),"Draw",IF(AND(ISNUMBER(F242),ISNUMBER(E242),E242&gt;0,F242=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L242" s="50"/>
       <x:c r="M242" s="58"/>
       <x:c r="N242" s="58"/>
@@ -9393,8 +10345,12 @@
       <x:c r="G243" s="58"/>
       <x:c r="H243" s="58"/>
       <x:c r="I243" s="58"/>
-      <x:c r="J243" s="60"/>
-      <x:c r="K243" s="50"/>
+      <x:c r="J243" s="60" t="str">
+        <x:f>IF(A243="","",IF(K243="Subscription","",IF(E243=0,"",IF(ISNUMBER(G243),G243/E243,IF(ISNUMBER(I243),-ABS(I243)/E243,IF(ISNUMBER(H243),0,IF(AND(ISNUMBER(F243),ISNUMBER(E243),E243&gt;0,F243&gt;E243),(F243-E243)/E243,IF(AND(ISNUMBER(F243),ISNUMBER(E243),E243&gt;0,F243=E243),0,IF(AND(ISNUMBER(F243),ISNUMBER(E243),E243&gt;0,F243=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K243" s="50" t="str">
+        <x:f>IF(A243="","",IF(AND(ISNUMBER(E243),E243=0,OR(ISNUMBER(SEARCH("Free",D243&amp;"")),AND(ISNUMBER(F243),F243=0))),"Subscription",IF(ISNUMBER(G243),"Profit",IF(ISNUMBER(I243),"Loss",IF(ISNUMBER(H243),"Draw",IF(AND(ISNUMBER(F243),ISNUMBER(E243),E243&gt;0,F243&gt;E243),"Profit",IF(AND(ISNUMBER(F243),ISNUMBER(E243),E243&gt;0,F243=E243),"Draw",IF(AND(ISNUMBER(F243),ISNUMBER(E243),E243&gt;0,F243=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L243" s="50"/>
       <x:c r="M243" s="58"/>
       <x:c r="N243" s="58"/>
@@ -9426,8 +10382,12 @@
       <x:c r="G244" s="58"/>
       <x:c r="H244" s="58"/>
       <x:c r="I244" s="58"/>
-      <x:c r="J244" s="60"/>
-      <x:c r="K244" s="50"/>
+      <x:c r="J244" s="60" t="str">
+        <x:f>IF(A244="","",IF(K244="Subscription","",IF(E244=0,"",IF(ISNUMBER(G244),G244/E244,IF(ISNUMBER(I244),-ABS(I244)/E244,IF(ISNUMBER(H244),0,IF(AND(ISNUMBER(F244),ISNUMBER(E244),E244&gt;0,F244&gt;E244),(F244-E244)/E244,IF(AND(ISNUMBER(F244),ISNUMBER(E244),E244&gt;0,F244=E244),0,IF(AND(ISNUMBER(F244),ISNUMBER(E244),E244&gt;0,F244=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K244" s="50" t="str">
+        <x:f>IF(A244="","",IF(AND(ISNUMBER(E244),E244=0,OR(ISNUMBER(SEARCH("Free",D244&amp;"")),AND(ISNUMBER(F244),F244=0))),"Subscription",IF(ISNUMBER(G244),"Profit",IF(ISNUMBER(I244),"Loss",IF(ISNUMBER(H244),"Draw",IF(AND(ISNUMBER(F244),ISNUMBER(E244),E244&gt;0,F244&gt;E244),"Profit",IF(AND(ISNUMBER(F244),ISNUMBER(E244),E244&gt;0,F244=E244),"Draw",IF(AND(ISNUMBER(F244),ISNUMBER(E244),E244&gt;0,F244=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L244" s="50"/>
       <x:c r="M244" s="58"/>
       <x:c r="N244" s="58"/>
@@ -9459,8 +10419,12 @@
       <x:c r="G245" s="58"/>
       <x:c r="H245" s="58"/>
       <x:c r="I245" s="58"/>
-      <x:c r="J245" s="60"/>
-      <x:c r="K245" s="50"/>
+      <x:c r="J245" s="60" t="str">
+        <x:f>IF(A245="","",IF(K245="Subscription","",IF(E245=0,"",IF(ISNUMBER(G245),G245/E245,IF(ISNUMBER(I245),-ABS(I245)/E245,IF(ISNUMBER(H245),0,IF(AND(ISNUMBER(F245),ISNUMBER(E245),E245&gt;0,F245&gt;E245),(F245-E245)/E245,IF(AND(ISNUMBER(F245),ISNUMBER(E245),E245&gt;0,F245=E245),0,IF(AND(ISNUMBER(F245),ISNUMBER(E245),E245&gt;0,F245=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K245" s="50" t="str">
+        <x:f>IF(A245="","",IF(AND(ISNUMBER(E245),E245=0,OR(ISNUMBER(SEARCH("Free",D245&amp;"")),AND(ISNUMBER(F245),F245=0))),"Subscription",IF(ISNUMBER(G245),"Profit",IF(ISNUMBER(I245),"Loss",IF(ISNUMBER(H245),"Draw",IF(AND(ISNUMBER(F245),ISNUMBER(E245),E245&gt;0,F245&gt;E245),"Profit",IF(AND(ISNUMBER(F245),ISNUMBER(E245),E245&gt;0,F245=E245),"Draw",IF(AND(ISNUMBER(F245),ISNUMBER(E245),E245&gt;0,F245=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L245" s="50"/>
       <x:c r="M245" s="58"/>
       <x:c r="N245" s="58"/>
@@ -9492,8 +10456,12 @@
       <x:c r="G246" s="58"/>
       <x:c r="H246" s="58"/>
       <x:c r="I246" s="58"/>
-      <x:c r="J246" s="60"/>
-      <x:c r="K246" s="50"/>
+      <x:c r="J246" s="60" t="str">
+        <x:f>IF(A246="","",IF(K246="Subscription","",IF(E246=0,"",IF(ISNUMBER(G246),G246/E246,IF(ISNUMBER(I246),-ABS(I246)/E246,IF(ISNUMBER(H246),0,IF(AND(ISNUMBER(F246),ISNUMBER(E246),E246&gt;0,F246&gt;E246),(F246-E246)/E246,IF(AND(ISNUMBER(F246),ISNUMBER(E246),E246&gt;0,F246=E246),0,IF(AND(ISNUMBER(F246),ISNUMBER(E246),E246&gt;0,F246=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K246" s="50" t="str">
+        <x:f>IF(A246="","",IF(AND(ISNUMBER(E246),E246=0,OR(ISNUMBER(SEARCH("Free",D246&amp;"")),AND(ISNUMBER(F246),F246=0))),"Subscription",IF(ISNUMBER(G246),"Profit",IF(ISNUMBER(I246),"Loss",IF(ISNUMBER(H246),"Draw",IF(AND(ISNUMBER(F246),ISNUMBER(E246),E246&gt;0,F246&gt;E246),"Profit",IF(AND(ISNUMBER(F246),ISNUMBER(E246),E246&gt;0,F246=E246),"Draw",IF(AND(ISNUMBER(F246),ISNUMBER(E246),E246&gt;0,F246=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L246" s="50"/>
       <x:c r="M246" s="58"/>
       <x:c r="N246" s="58"/>
@@ -9525,8 +10493,12 @@
       <x:c r="G247" s="58"/>
       <x:c r="H247" s="58"/>
       <x:c r="I247" s="58"/>
-      <x:c r="J247" s="60"/>
-      <x:c r="K247" s="50"/>
+      <x:c r="J247" s="60" t="str">
+        <x:f>IF(A247="","",IF(K247="Subscription","",IF(E247=0,"",IF(ISNUMBER(G247),G247/E247,IF(ISNUMBER(I247),-ABS(I247)/E247,IF(ISNUMBER(H247),0,IF(AND(ISNUMBER(F247),ISNUMBER(E247),E247&gt;0,F247&gt;E247),(F247-E247)/E247,IF(AND(ISNUMBER(F247),ISNUMBER(E247),E247&gt;0,F247=E247),0,IF(AND(ISNUMBER(F247),ISNUMBER(E247),E247&gt;0,F247=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K247" s="50" t="str">
+        <x:f>IF(A247="","",IF(AND(ISNUMBER(E247),E247=0,OR(ISNUMBER(SEARCH("Free",D247&amp;"")),AND(ISNUMBER(F247),F247=0))),"Subscription",IF(ISNUMBER(G247),"Profit",IF(ISNUMBER(I247),"Loss",IF(ISNUMBER(H247),"Draw",IF(AND(ISNUMBER(F247),ISNUMBER(E247),E247&gt;0,F247&gt;E247),"Profit",IF(AND(ISNUMBER(F247),ISNUMBER(E247),E247&gt;0,F247=E247),"Draw",IF(AND(ISNUMBER(F247),ISNUMBER(E247),E247&gt;0,F247=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L247" s="50"/>
       <x:c r="M247" s="58"/>
       <x:c r="N247" s="58"/>
@@ -9558,8 +10530,12 @@
       <x:c r="G248" s="58"/>
       <x:c r="H248" s="58"/>
       <x:c r="I248" s="58"/>
-      <x:c r="J248" s="60"/>
-      <x:c r="K248" s="50"/>
+      <x:c r="J248" s="60" t="str">
+        <x:f>IF(A248="","",IF(K248="Subscription","",IF(E248=0,"",IF(ISNUMBER(G248),G248/E248,IF(ISNUMBER(I248),-ABS(I248)/E248,IF(ISNUMBER(H248),0,IF(AND(ISNUMBER(F248),ISNUMBER(E248),E248&gt;0,F248&gt;E248),(F248-E248)/E248,IF(AND(ISNUMBER(F248),ISNUMBER(E248),E248&gt;0,F248=E248),0,IF(AND(ISNUMBER(F248),ISNUMBER(E248),E248&gt;0,F248=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K248" s="50" t="str">
+        <x:f>IF(A248="","",IF(AND(ISNUMBER(E248),E248=0,OR(ISNUMBER(SEARCH("Free",D248&amp;"")),AND(ISNUMBER(F248),F248=0))),"Subscription",IF(ISNUMBER(G248),"Profit",IF(ISNUMBER(I248),"Loss",IF(ISNUMBER(H248),"Draw",IF(AND(ISNUMBER(F248),ISNUMBER(E248),E248&gt;0,F248&gt;E248),"Profit",IF(AND(ISNUMBER(F248),ISNUMBER(E248),E248&gt;0,F248=E248),"Draw",IF(AND(ISNUMBER(F248),ISNUMBER(E248),E248&gt;0,F248=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L248" s="50"/>
       <x:c r="M248" s="58"/>
       <x:c r="N248" s="58"/>
@@ -9591,8 +10567,12 @@
       <x:c r="G249" s="58"/>
       <x:c r="H249" s="58"/>
       <x:c r="I249" s="58"/>
-      <x:c r="J249" s="60"/>
-      <x:c r="K249" s="50"/>
+      <x:c r="J249" s="60" t="str">
+        <x:f>IF(A249="","",IF(K249="Subscription","",IF(E249=0,"",IF(ISNUMBER(G249),G249/E249,IF(ISNUMBER(I249),-ABS(I249)/E249,IF(ISNUMBER(H249),0,IF(AND(ISNUMBER(F249),ISNUMBER(E249),E249&gt;0,F249&gt;E249),(F249-E249)/E249,IF(AND(ISNUMBER(F249),ISNUMBER(E249),E249&gt;0,F249=E249),0,IF(AND(ISNUMBER(F249),ISNUMBER(E249),E249&gt;0,F249=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K249" s="50" t="str">
+        <x:f>IF(A249="","",IF(AND(ISNUMBER(E249),E249=0,OR(ISNUMBER(SEARCH("Free",D249&amp;"")),AND(ISNUMBER(F249),F249=0))),"Subscription",IF(ISNUMBER(G249),"Profit",IF(ISNUMBER(I249),"Loss",IF(ISNUMBER(H249),"Draw",IF(AND(ISNUMBER(F249),ISNUMBER(E249),E249&gt;0,F249&gt;E249),"Profit",IF(AND(ISNUMBER(F249),ISNUMBER(E249),E249&gt;0,F249=E249),"Draw",IF(AND(ISNUMBER(F249),ISNUMBER(E249),E249&gt;0,F249=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L249" s="50"/>
       <x:c r="M249" s="58"/>
       <x:c r="N249" s="58"/>
@@ -9624,8 +10604,12 @@
       <x:c r="G250" s="58"/>
       <x:c r="H250" s="58"/>
       <x:c r="I250" s="58"/>
-      <x:c r="J250" s="60"/>
-      <x:c r="K250" s="50"/>
+      <x:c r="J250" s="60" t="str">
+        <x:f>IF(A250="","",IF(K250="Subscription","",IF(E250=0,"",IF(ISNUMBER(G250),G250/E250,IF(ISNUMBER(I250),-ABS(I250)/E250,IF(ISNUMBER(H250),0,IF(AND(ISNUMBER(F250),ISNUMBER(E250),E250&gt;0,F250&gt;E250),(F250-E250)/E250,IF(AND(ISNUMBER(F250),ISNUMBER(E250),E250&gt;0,F250=E250),0,IF(AND(ISNUMBER(F250),ISNUMBER(E250),E250&gt;0,F250=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K250" s="50" t="str">
+        <x:f>IF(A250="","",IF(AND(ISNUMBER(E250),E250=0,OR(ISNUMBER(SEARCH("Free",D250&amp;"")),AND(ISNUMBER(F250),F250=0))),"Subscription",IF(ISNUMBER(G250),"Profit",IF(ISNUMBER(I250),"Loss",IF(ISNUMBER(H250),"Draw",IF(AND(ISNUMBER(F250),ISNUMBER(E250),E250&gt;0,F250&gt;E250),"Profit",IF(AND(ISNUMBER(F250),ISNUMBER(E250),E250&gt;0,F250=E250),"Draw",IF(AND(ISNUMBER(F250),ISNUMBER(E250),E250&gt;0,F250=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L250" s="50"/>
       <x:c r="M250" s="58"/>
       <x:c r="N250" s="58"/>
@@ -9657,8 +10641,12 @@
       <x:c r="G251" s="58"/>
       <x:c r="H251" s="58"/>
       <x:c r="I251" s="58"/>
-      <x:c r="J251" s="60"/>
-      <x:c r="K251" s="50"/>
+      <x:c r="J251" s="60" t="str">
+        <x:f>IF(A251="","",IF(K251="Subscription","",IF(E251=0,"",IF(ISNUMBER(G251),G251/E251,IF(ISNUMBER(I251),-ABS(I251)/E251,IF(ISNUMBER(H251),0,IF(AND(ISNUMBER(F251),ISNUMBER(E251),E251&gt;0,F251&gt;E251),(F251-E251)/E251,IF(AND(ISNUMBER(F251),ISNUMBER(E251),E251&gt;0,F251=E251),0,IF(AND(ISNUMBER(F251),ISNUMBER(E251),E251&gt;0,F251=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K251" s="50" t="str">
+        <x:f>IF(A251="","",IF(AND(ISNUMBER(E251),E251=0,OR(ISNUMBER(SEARCH("Free",D251&amp;"")),AND(ISNUMBER(F251),F251=0))),"Subscription",IF(ISNUMBER(G251),"Profit",IF(ISNUMBER(I251),"Loss",IF(ISNUMBER(H251),"Draw",IF(AND(ISNUMBER(F251),ISNUMBER(E251),E251&gt;0,F251&gt;E251),"Profit",IF(AND(ISNUMBER(F251),ISNUMBER(E251),E251&gt;0,F251=E251),"Draw",IF(AND(ISNUMBER(F251),ISNUMBER(E251),E251&gt;0,F251=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L251" s="50"/>
       <x:c r="M251" s="58"/>
       <x:c r="N251" s="58"/>
@@ -9690,8 +10678,12 @@
       <x:c r="G252" s="58"/>
       <x:c r="H252" s="58"/>
       <x:c r="I252" s="58"/>
-      <x:c r="J252" s="60"/>
-      <x:c r="K252" s="50"/>
+      <x:c r="J252" s="60" t="str">
+        <x:f>IF(A252="","",IF(K252="Subscription","",IF(E252=0,"",IF(ISNUMBER(G252),G252/E252,IF(ISNUMBER(I252),-ABS(I252)/E252,IF(ISNUMBER(H252),0,IF(AND(ISNUMBER(F252),ISNUMBER(E252),E252&gt;0,F252&gt;E252),(F252-E252)/E252,IF(AND(ISNUMBER(F252),ISNUMBER(E252),E252&gt;0,F252=E252),0,IF(AND(ISNUMBER(F252),ISNUMBER(E252),E252&gt;0,F252=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K252" s="50" t="str">
+        <x:f>IF(A252="","",IF(AND(ISNUMBER(E252),E252=0,OR(ISNUMBER(SEARCH("Free",D252&amp;"")),AND(ISNUMBER(F252),F252=0))),"Subscription",IF(ISNUMBER(G252),"Profit",IF(ISNUMBER(I252),"Loss",IF(ISNUMBER(H252),"Draw",IF(AND(ISNUMBER(F252),ISNUMBER(E252),E252&gt;0,F252&gt;E252),"Profit",IF(AND(ISNUMBER(F252),ISNUMBER(E252),E252&gt;0,F252=E252),"Draw",IF(AND(ISNUMBER(F252),ISNUMBER(E252),E252&gt;0,F252=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L252" s="50"/>
       <x:c r="M252" s="58"/>
       <x:c r="N252" s="58"/>
@@ -9723,8 +10715,12 @@
       <x:c r="G253" s="58"/>
       <x:c r="H253" s="58"/>
       <x:c r="I253" s="58"/>
-      <x:c r="J253" s="60"/>
-      <x:c r="K253" s="50"/>
+      <x:c r="J253" s="60" t="str">
+        <x:f>IF(A253="","",IF(K253="Subscription","",IF(E253=0,"",IF(ISNUMBER(G253),G253/E253,IF(ISNUMBER(I253),-ABS(I253)/E253,IF(ISNUMBER(H253),0,IF(AND(ISNUMBER(F253),ISNUMBER(E253),E253&gt;0,F253&gt;E253),(F253-E253)/E253,IF(AND(ISNUMBER(F253),ISNUMBER(E253),E253&gt;0,F253=E253),0,IF(AND(ISNUMBER(F253),ISNUMBER(E253),E253&gt;0,F253=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K253" s="50" t="str">
+        <x:f>IF(A253="","",IF(AND(ISNUMBER(E253),E253=0,OR(ISNUMBER(SEARCH("Free",D253&amp;"")),AND(ISNUMBER(F253),F253=0))),"Subscription",IF(ISNUMBER(G253),"Profit",IF(ISNUMBER(I253),"Loss",IF(ISNUMBER(H253),"Draw",IF(AND(ISNUMBER(F253),ISNUMBER(E253),E253&gt;0,F253&gt;E253),"Profit",IF(AND(ISNUMBER(F253),ISNUMBER(E253),E253&gt;0,F253=E253),"Draw",IF(AND(ISNUMBER(F253),ISNUMBER(E253),E253&gt;0,F253=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L253" s="50"/>
       <x:c r="M253" s="58"/>
       <x:c r="N253" s="58"/>
@@ -9756,8 +10752,12 @@
       <x:c r="G254" s="58"/>
       <x:c r="H254" s="58"/>
       <x:c r="I254" s="58"/>
-      <x:c r="J254" s="60"/>
-      <x:c r="K254" s="50"/>
+      <x:c r="J254" s="60" t="str">
+        <x:f>IF(A254="","",IF(K254="Subscription","",IF(E254=0,"",IF(ISNUMBER(G254),G254/E254,IF(ISNUMBER(I254),-ABS(I254)/E254,IF(ISNUMBER(H254),0,IF(AND(ISNUMBER(F254),ISNUMBER(E254),E254&gt;0,F254&gt;E254),(F254-E254)/E254,IF(AND(ISNUMBER(F254),ISNUMBER(E254),E254&gt;0,F254=E254),0,IF(AND(ISNUMBER(F254),ISNUMBER(E254),E254&gt;0,F254=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K254" s="50" t="str">
+        <x:f>IF(A254="","",IF(AND(ISNUMBER(E254),E254=0,OR(ISNUMBER(SEARCH("Free",D254&amp;"")),AND(ISNUMBER(F254),F254=0))),"Subscription",IF(ISNUMBER(G254),"Profit",IF(ISNUMBER(I254),"Loss",IF(ISNUMBER(H254),"Draw",IF(AND(ISNUMBER(F254),ISNUMBER(E254),E254&gt;0,F254&gt;E254),"Profit",IF(AND(ISNUMBER(F254),ISNUMBER(E254),E254&gt;0,F254=E254),"Draw",IF(AND(ISNUMBER(F254),ISNUMBER(E254),E254&gt;0,F254=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L254" s="50"/>
       <x:c r="M254" s="58"/>
       <x:c r="N254" s="58"/>
@@ -9789,8 +10789,12 @@
       <x:c r="G255" s="58"/>
       <x:c r="H255" s="58"/>
       <x:c r="I255" s="58"/>
-      <x:c r="J255" s="60"/>
-      <x:c r="K255" s="50"/>
+      <x:c r="J255" s="60" t="str">
+        <x:f>IF(A255="","",IF(K255="Subscription","",IF(E255=0,"",IF(ISNUMBER(G255),G255/E255,IF(ISNUMBER(I255),-ABS(I255)/E255,IF(ISNUMBER(H255),0,IF(AND(ISNUMBER(F255),ISNUMBER(E255),E255&gt;0,F255&gt;E255),(F255-E255)/E255,IF(AND(ISNUMBER(F255),ISNUMBER(E255),E255&gt;0,F255=E255),0,IF(AND(ISNUMBER(F255),ISNUMBER(E255),E255&gt;0,F255=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K255" s="50" t="str">
+        <x:f>IF(A255="","",IF(AND(ISNUMBER(E255),E255=0,OR(ISNUMBER(SEARCH("Free",D255&amp;"")),AND(ISNUMBER(F255),F255=0))),"Subscription",IF(ISNUMBER(G255),"Profit",IF(ISNUMBER(I255),"Loss",IF(ISNUMBER(H255),"Draw",IF(AND(ISNUMBER(F255),ISNUMBER(E255),E255&gt;0,F255&gt;E255),"Profit",IF(AND(ISNUMBER(F255),ISNUMBER(E255),E255&gt;0,F255=E255),"Draw",IF(AND(ISNUMBER(F255),ISNUMBER(E255),E255&gt;0,F255=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L255" s="50"/>
       <x:c r="M255" s="58"/>
       <x:c r="N255" s="58"/>
@@ -9822,8 +10826,12 @@
       <x:c r="G256" s="58"/>
       <x:c r="H256" s="58"/>
       <x:c r="I256" s="58"/>
-      <x:c r="J256" s="60"/>
-      <x:c r="K256" s="50"/>
+      <x:c r="J256" s="60" t="str">
+        <x:f>IF(A256="","",IF(K256="Subscription","",IF(E256=0,"",IF(ISNUMBER(G256),G256/E256,IF(ISNUMBER(I256),-ABS(I256)/E256,IF(ISNUMBER(H256),0,IF(AND(ISNUMBER(F256),ISNUMBER(E256),E256&gt;0,F256&gt;E256),(F256-E256)/E256,IF(AND(ISNUMBER(F256),ISNUMBER(E256),E256&gt;0,F256=E256),0,IF(AND(ISNUMBER(F256),ISNUMBER(E256),E256&gt;0,F256=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K256" s="50" t="str">
+        <x:f>IF(A256="","",IF(AND(ISNUMBER(E256),E256=0,OR(ISNUMBER(SEARCH("Free",D256&amp;"")),AND(ISNUMBER(F256),F256=0))),"Subscription",IF(ISNUMBER(G256),"Profit",IF(ISNUMBER(I256),"Loss",IF(ISNUMBER(H256),"Draw",IF(AND(ISNUMBER(F256),ISNUMBER(E256),E256&gt;0,F256&gt;E256),"Profit",IF(AND(ISNUMBER(F256),ISNUMBER(E256),E256&gt;0,F256=E256),"Draw",IF(AND(ISNUMBER(F256),ISNUMBER(E256),E256&gt;0,F256=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L256" s="50"/>
       <x:c r="M256" s="58"/>
       <x:c r="N256" s="58"/>
@@ -9855,8 +10863,12 @@
       <x:c r="G257" s="58"/>
       <x:c r="H257" s="58"/>
       <x:c r="I257" s="58"/>
-      <x:c r="J257" s="60"/>
-      <x:c r="K257" s="50"/>
+      <x:c r="J257" s="60" t="str">
+        <x:f>IF(A257="","",IF(K257="Subscription","",IF(E257=0,"",IF(ISNUMBER(G257),G257/E257,IF(ISNUMBER(I257),-ABS(I257)/E257,IF(ISNUMBER(H257),0,IF(AND(ISNUMBER(F257),ISNUMBER(E257),E257&gt;0,F257&gt;E257),(F257-E257)/E257,IF(AND(ISNUMBER(F257),ISNUMBER(E257),E257&gt;0,F257=E257),0,IF(AND(ISNUMBER(F257),ISNUMBER(E257),E257&gt;0,F257=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K257" s="50" t="str">
+        <x:f>IF(A257="","",IF(AND(ISNUMBER(E257),E257=0,OR(ISNUMBER(SEARCH("Free",D257&amp;"")),AND(ISNUMBER(F257),F257=0))),"Subscription",IF(ISNUMBER(G257),"Profit",IF(ISNUMBER(I257),"Loss",IF(ISNUMBER(H257),"Draw",IF(AND(ISNUMBER(F257),ISNUMBER(E257),E257&gt;0,F257&gt;E257),"Profit",IF(AND(ISNUMBER(F257),ISNUMBER(E257),E257&gt;0,F257=E257),"Draw",IF(AND(ISNUMBER(F257),ISNUMBER(E257),E257&gt;0,F257=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L257" s="50"/>
       <x:c r="M257" s="58"/>
       <x:c r="N257" s="58"/>
@@ -9888,8 +10900,12 @@
       <x:c r="G258" s="58"/>
       <x:c r="H258" s="58"/>
       <x:c r="I258" s="58"/>
-      <x:c r="J258" s="60"/>
-      <x:c r="K258" s="50"/>
+      <x:c r="J258" s="60" t="str">
+        <x:f>IF(A258="","",IF(K258="Subscription","",IF(E258=0,"",IF(ISNUMBER(G258),G258/E258,IF(ISNUMBER(I258),-ABS(I258)/E258,IF(ISNUMBER(H258),0,IF(AND(ISNUMBER(F258),ISNUMBER(E258),E258&gt;0,F258&gt;E258),(F258-E258)/E258,IF(AND(ISNUMBER(F258),ISNUMBER(E258),E258&gt;0,F258=E258),0,IF(AND(ISNUMBER(F258),ISNUMBER(E258),E258&gt;0,F258=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K258" s="50" t="str">
+        <x:f>IF(A258="","",IF(AND(ISNUMBER(E258),E258=0,OR(ISNUMBER(SEARCH("Free",D258&amp;"")),AND(ISNUMBER(F258),F258=0))),"Subscription",IF(ISNUMBER(G258),"Profit",IF(ISNUMBER(I258),"Loss",IF(ISNUMBER(H258),"Draw",IF(AND(ISNUMBER(F258),ISNUMBER(E258),E258&gt;0,F258&gt;E258),"Profit",IF(AND(ISNUMBER(F258),ISNUMBER(E258),E258&gt;0,F258=E258),"Draw",IF(AND(ISNUMBER(F258),ISNUMBER(E258),E258&gt;0,F258=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L258" s="50"/>
       <x:c r="M258" s="58"/>
       <x:c r="N258" s="58"/>
@@ -9921,8 +10937,12 @@
       <x:c r="G259" s="58"/>
       <x:c r="H259" s="58"/>
       <x:c r="I259" s="58"/>
-      <x:c r="J259" s="60"/>
-      <x:c r="K259" s="50"/>
+      <x:c r="J259" s="60" t="str">
+        <x:f>IF(A259="","",IF(K259="Subscription","",IF(E259=0,"",IF(ISNUMBER(G259),G259/E259,IF(ISNUMBER(I259),-ABS(I259)/E259,IF(ISNUMBER(H259),0,IF(AND(ISNUMBER(F259),ISNUMBER(E259),E259&gt;0,F259&gt;E259),(F259-E259)/E259,IF(AND(ISNUMBER(F259),ISNUMBER(E259),E259&gt;0,F259=E259),0,IF(AND(ISNUMBER(F259),ISNUMBER(E259),E259&gt;0,F259=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K259" s="50" t="str">
+        <x:f>IF(A259="","",IF(AND(ISNUMBER(E259),E259=0,OR(ISNUMBER(SEARCH("Free",D259&amp;"")),AND(ISNUMBER(F259),F259=0))),"Subscription",IF(ISNUMBER(G259),"Profit",IF(ISNUMBER(I259),"Loss",IF(ISNUMBER(H259),"Draw",IF(AND(ISNUMBER(F259),ISNUMBER(E259),E259&gt;0,F259&gt;E259),"Profit",IF(AND(ISNUMBER(F259),ISNUMBER(E259),E259&gt;0,F259=E259),"Draw",IF(AND(ISNUMBER(F259),ISNUMBER(E259),E259&gt;0,F259=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L259" s="50"/>
       <x:c r="M259" s="58"/>
       <x:c r="N259" s="58"/>
@@ -9954,8 +10974,12 @@
       <x:c r="G260" s="58"/>
       <x:c r="H260" s="58"/>
       <x:c r="I260" s="58"/>
-      <x:c r="J260" s="60"/>
-      <x:c r="K260" s="50"/>
+      <x:c r="J260" s="60" t="str">
+        <x:f>IF(A260="","",IF(K260="Subscription","",IF(E260=0,"",IF(ISNUMBER(G260),G260/E260,IF(ISNUMBER(I260),-ABS(I260)/E260,IF(ISNUMBER(H260),0,IF(AND(ISNUMBER(F260),ISNUMBER(E260),E260&gt;0,F260&gt;E260),(F260-E260)/E260,IF(AND(ISNUMBER(F260),ISNUMBER(E260),E260&gt;0,F260=E260),0,IF(AND(ISNUMBER(F260),ISNUMBER(E260),E260&gt;0,F260=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K260" s="50" t="str">
+        <x:f>IF(A260="","",IF(AND(ISNUMBER(E260),E260=0,OR(ISNUMBER(SEARCH("Free",D260&amp;"")),AND(ISNUMBER(F260),F260=0))),"Subscription",IF(ISNUMBER(G260),"Profit",IF(ISNUMBER(I260),"Loss",IF(ISNUMBER(H260),"Draw",IF(AND(ISNUMBER(F260),ISNUMBER(E260),E260&gt;0,F260&gt;E260),"Profit",IF(AND(ISNUMBER(F260),ISNUMBER(E260),E260&gt;0,F260=E260),"Draw",IF(AND(ISNUMBER(F260),ISNUMBER(E260),E260&gt;0,F260=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L260" s="50"/>
       <x:c r="M260" s="58"/>
       <x:c r="N260" s="58"/>
@@ -9987,8 +11011,12 @@
       <x:c r="G261" s="58"/>
       <x:c r="H261" s="58"/>
       <x:c r="I261" s="58"/>
-      <x:c r="J261" s="60"/>
-      <x:c r="K261" s="50"/>
+      <x:c r="J261" s="60" t="str">
+        <x:f>IF(A261="","",IF(K261="Subscription","",IF(E261=0,"",IF(ISNUMBER(G261),G261/E261,IF(ISNUMBER(I261),-ABS(I261)/E261,IF(ISNUMBER(H261),0,IF(AND(ISNUMBER(F261),ISNUMBER(E261),E261&gt;0,F261&gt;E261),(F261-E261)/E261,IF(AND(ISNUMBER(F261),ISNUMBER(E261),E261&gt;0,F261=E261),0,IF(AND(ISNUMBER(F261),ISNUMBER(E261),E261&gt;0,F261=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K261" s="50" t="str">
+        <x:f>IF(A261="","",IF(AND(ISNUMBER(E261),E261=0,OR(ISNUMBER(SEARCH("Free",D261&amp;"")),AND(ISNUMBER(F261),F261=0))),"Subscription",IF(ISNUMBER(G261),"Profit",IF(ISNUMBER(I261),"Loss",IF(ISNUMBER(H261),"Draw",IF(AND(ISNUMBER(F261),ISNUMBER(E261),E261&gt;0,F261&gt;E261),"Profit",IF(AND(ISNUMBER(F261),ISNUMBER(E261),E261&gt;0,F261=E261),"Draw",IF(AND(ISNUMBER(F261),ISNUMBER(E261),E261&gt;0,F261=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L261" s="50"/>
       <x:c r="M261" s="58"/>
       <x:c r="N261" s="58"/>
@@ -10020,8 +11048,12 @@
       <x:c r="G262" s="58"/>
       <x:c r="H262" s="58"/>
       <x:c r="I262" s="58"/>
-      <x:c r="J262" s="60"/>
-      <x:c r="K262" s="50"/>
+      <x:c r="J262" s="60" t="str">
+        <x:f>IF(A262="","",IF(K262="Subscription","",IF(E262=0,"",IF(ISNUMBER(G262),G262/E262,IF(ISNUMBER(I262),-ABS(I262)/E262,IF(ISNUMBER(H262),0,IF(AND(ISNUMBER(F262),ISNUMBER(E262),E262&gt;0,F262&gt;E262),(F262-E262)/E262,IF(AND(ISNUMBER(F262),ISNUMBER(E262),E262&gt;0,F262=E262),0,IF(AND(ISNUMBER(F262),ISNUMBER(E262),E262&gt;0,F262=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K262" s="50" t="str">
+        <x:f>IF(A262="","",IF(AND(ISNUMBER(E262),E262=0,OR(ISNUMBER(SEARCH("Free",D262&amp;"")),AND(ISNUMBER(F262),F262=0))),"Subscription",IF(ISNUMBER(G262),"Profit",IF(ISNUMBER(I262),"Loss",IF(ISNUMBER(H262),"Draw",IF(AND(ISNUMBER(F262),ISNUMBER(E262),E262&gt;0,F262&gt;E262),"Profit",IF(AND(ISNUMBER(F262),ISNUMBER(E262),E262&gt;0,F262=E262),"Draw",IF(AND(ISNUMBER(F262),ISNUMBER(E262),E262&gt;0,F262=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L262" s="50"/>
       <x:c r="M262" s="58"/>
       <x:c r="N262" s="58"/>
@@ -10053,8 +11085,12 @@
       <x:c r="G263" s="58"/>
       <x:c r="H263" s="58"/>
       <x:c r="I263" s="58"/>
-      <x:c r="J263" s="60"/>
-      <x:c r="K263" s="50"/>
+      <x:c r="J263" s="60" t="str">
+        <x:f>IF(A263="","",IF(K263="Subscription","",IF(E263=0,"",IF(ISNUMBER(G263),G263/E263,IF(ISNUMBER(I263),-ABS(I263)/E263,IF(ISNUMBER(H263),0,IF(AND(ISNUMBER(F263),ISNUMBER(E263),E263&gt;0,F263&gt;E263),(F263-E263)/E263,IF(AND(ISNUMBER(F263),ISNUMBER(E263),E263&gt;0,F263=E263),0,IF(AND(ISNUMBER(F263),ISNUMBER(E263),E263&gt;0,F263=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K263" s="50" t="str">
+        <x:f>IF(A263="","",IF(AND(ISNUMBER(E263),E263=0,OR(ISNUMBER(SEARCH("Free",D263&amp;"")),AND(ISNUMBER(F263),F263=0))),"Subscription",IF(ISNUMBER(G263),"Profit",IF(ISNUMBER(I263),"Loss",IF(ISNUMBER(H263),"Draw",IF(AND(ISNUMBER(F263),ISNUMBER(E263),E263&gt;0,F263&gt;E263),"Profit",IF(AND(ISNUMBER(F263),ISNUMBER(E263),E263&gt;0,F263=E263),"Draw",IF(AND(ISNUMBER(F263),ISNUMBER(E263),E263&gt;0,F263=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L263" s="50"/>
       <x:c r="M263" s="58"/>
       <x:c r="N263" s="58"/>
@@ -10086,8 +11122,12 @@
       <x:c r="G264" s="58"/>
       <x:c r="H264" s="58"/>
       <x:c r="I264" s="58"/>
-      <x:c r="J264" s="60"/>
-      <x:c r="K264" s="50"/>
+      <x:c r="J264" s="60" t="str">
+        <x:f>IF(A264="","",IF(K264="Subscription","",IF(E264=0,"",IF(ISNUMBER(G264),G264/E264,IF(ISNUMBER(I264),-ABS(I264)/E264,IF(ISNUMBER(H264),0,IF(AND(ISNUMBER(F264),ISNUMBER(E264),E264&gt;0,F264&gt;E264),(F264-E264)/E264,IF(AND(ISNUMBER(F264),ISNUMBER(E264),E264&gt;0,F264=E264),0,IF(AND(ISNUMBER(F264),ISNUMBER(E264),E264&gt;0,F264=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K264" s="50" t="str">
+        <x:f>IF(A264="","",IF(AND(ISNUMBER(E264),E264=0,OR(ISNUMBER(SEARCH("Free",D264&amp;"")),AND(ISNUMBER(F264),F264=0))),"Subscription",IF(ISNUMBER(G264),"Profit",IF(ISNUMBER(I264),"Loss",IF(ISNUMBER(H264),"Draw",IF(AND(ISNUMBER(F264),ISNUMBER(E264),E264&gt;0,F264&gt;E264),"Profit",IF(AND(ISNUMBER(F264),ISNUMBER(E264),E264&gt;0,F264=E264),"Draw",IF(AND(ISNUMBER(F264),ISNUMBER(E264),E264&gt;0,F264=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L264" s="50"/>
       <x:c r="M264" s="58"/>
       <x:c r="N264" s="58"/>
@@ -10119,8 +11159,12 @@
       <x:c r="G265" s="58"/>
       <x:c r="H265" s="58"/>
       <x:c r="I265" s="58"/>
-      <x:c r="J265" s="60"/>
-      <x:c r="K265" s="50"/>
+      <x:c r="J265" s="60" t="str">
+        <x:f>IF(A265="","",IF(K265="Subscription","",IF(E265=0,"",IF(ISNUMBER(G265),G265/E265,IF(ISNUMBER(I265),-ABS(I265)/E265,IF(ISNUMBER(H265),0,IF(AND(ISNUMBER(F265),ISNUMBER(E265),E265&gt;0,F265&gt;E265),(F265-E265)/E265,IF(AND(ISNUMBER(F265),ISNUMBER(E265),E265&gt;0,F265=E265),0,IF(AND(ISNUMBER(F265),ISNUMBER(E265),E265&gt;0,F265=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K265" s="50" t="str">
+        <x:f>IF(A265="","",IF(AND(ISNUMBER(E265),E265=0,OR(ISNUMBER(SEARCH("Free",D265&amp;"")),AND(ISNUMBER(F265),F265=0))),"Subscription",IF(ISNUMBER(G265),"Profit",IF(ISNUMBER(I265),"Loss",IF(ISNUMBER(H265),"Draw",IF(AND(ISNUMBER(F265),ISNUMBER(E265),E265&gt;0,F265&gt;E265),"Profit",IF(AND(ISNUMBER(F265),ISNUMBER(E265),E265&gt;0,F265=E265),"Draw",IF(AND(ISNUMBER(F265),ISNUMBER(E265),E265&gt;0,F265=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L265" s="50"/>
       <x:c r="M265" s="58"/>
       <x:c r="N265" s="58"/>
@@ -10152,8 +11196,12 @@
       <x:c r="G266" s="58"/>
       <x:c r="H266" s="58"/>
       <x:c r="I266" s="58"/>
-      <x:c r="J266" s="60"/>
-      <x:c r="K266" s="50"/>
+      <x:c r="J266" s="60" t="str">
+        <x:f>IF(A266="","",IF(K266="Subscription","",IF(E266=0,"",IF(ISNUMBER(G266),G266/E266,IF(ISNUMBER(I266),-ABS(I266)/E266,IF(ISNUMBER(H266),0,IF(AND(ISNUMBER(F266),ISNUMBER(E266),E266&gt;0,F266&gt;E266),(F266-E266)/E266,IF(AND(ISNUMBER(F266),ISNUMBER(E266),E266&gt;0,F266=E266),0,IF(AND(ISNUMBER(F266),ISNUMBER(E266),E266&gt;0,F266=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K266" s="50" t="str">
+        <x:f>IF(A266="","",IF(AND(ISNUMBER(E266),E266=0,OR(ISNUMBER(SEARCH("Free",D266&amp;"")),AND(ISNUMBER(F266),F266=0))),"Subscription",IF(ISNUMBER(G266),"Profit",IF(ISNUMBER(I266),"Loss",IF(ISNUMBER(H266),"Draw",IF(AND(ISNUMBER(F266),ISNUMBER(E266),E266&gt;0,F266&gt;E266),"Profit",IF(AND(ISNUMBER(F266),ISNUMBER(E266),E266&gt;0,F266=E266),"Draw",IF(AND(ISNUMBER(F266),ISNUMBER(E266),E266&gt;0,F266=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L266" s="50"/>
       <x:c r="M266" s="58"/>
       <x:c r="N266" s="58"/>
@@ -10185,8 +11233,12 @@
       <x:c r="G267" s="58"/>
       <x:c r="H267" s="58"/>
       <x:c r="I267" s="58"/>
-      <x:c r="J267" s="60"/>
-      <x:c r="K267" s="50"/>
+      <x:c r="J267" s="60" t="str">
+        <x:f>IF(A267="","",IF(K267="Subscription","",IF(E267=0,"",IF(ISNUMBER(G267),G267/E267,IF(ISNUMBER(I267),-ABS(I267)/E267,IF(ISNUMBER(H267),0,IF(AND(ISNUMBER(F267),ISNUMBER(E267),E267&gt;0,F267&gt;E267),(F267-E267)/E267,IF(AND(ISNUMBER(F267),ISNUMBER(E267),E267&gt;0,F267=E267),0,IF(AND(ISNUMBER(F267),ISNUMBER(E267),E267&gt;0,F267=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K267" s="50" t="str">
+        <x:f>IF(A267="","",IF(AND(ISNUMBER(E267),E267=0,OR(ISNUMBER(SEARCH("Free",D267&amp;"")),AND(ISNUMBER(F267),F267=0))),"Subscription",IF(ISNUMBER(G267),"Profit",IF(ISNUMBER(I267),"Loss",IF(ISNUMBER(H267),"Draw",IF(AND(ISNUMBER(F267),ISNUMBER(E267),E267&gt;0,F267&gt;E267),"Profit",IF(AND(ISNUMBER(F267),ISNUMBER(E267),E267&gt;0,F267=E267),"Draw",IF(AND(ISNUMBER(F267),ISNUMBER(E267),E267&gt;0,F267=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L267" s="50"/>
       <x:c r="M267" s="58"/>
       <x:c r="N267" s="58"/>
@@ -10218,8 +11270,12 @@
       <x:c r="G268" s="58"/>
       <x:c r="H268" s="58"/>
       <x:c r="I268" s="58"/>
-      <x:c r="J268" s="60"/>
-      <x:c r="K268" s="50"/>
+      <x:c r="J268" s="60" t="str">
+        <x:f>IF(A268="","",IF(K268="Subscription","",IF(E268=0,"",IF(ISNUMBER(G268),G268/E268,IF(ISNUMBER(I268),-ABS(I268)/E268,IF(ISNUMBER(H268),0,IF(AND(ISNUMBER(F268),ISNUMBER(E268),E268&gt;0,F268&gt;E268),(F268-E268)/E268,IF(AND(ISNUMBER(F268),ISNUMBER(E268),E268&gt;0,F268=E268),0,IF(AND(ISNUMBER(F268),ISNUMBER(E268),E268&gt;0,F268=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K268" s="50" t="str">
+        <x:f>IF(A268="","",IF(AND(ISNUMBER(E268),E268=0,OR(ISNUMBER(SEARCH("Free",D268&amp;"")),AND(ISNUMBER(F268),F268=0))),"Subscription",IF(ISNUMBER(G268),"Profit",IF(ISNUMBER(I268),"Loss",IF(ISNUMBER(H268),"Draw",IF(AND(ISNUMBER(F268),ISNUMBER(E268),E268&gt;0,F268&gt;E268),"Profit",IF(AND(ISNUMBER(F268),ISNUMBER(E268),E268&gt;0,F268=E268),"Draw",IF(AND(ISNUMBER(F268),ISNUMBER(E268),E268&gt;0,F268=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L268" s="50"/>
       <x:c r="M268" s="58"/>
       <x:c r="N268" s="58"/>
@@ -10251,8 +11307,12 @@
       <x:c r="G269" s="58"/>
       <x:c r="H269" s="58"/>
       <x:c r="I269" s="58"/>
-      <x:c r="J269" s="60"/>
-      <x:c r="K269" s="50"/>
+      <x:c r="J269" s="60" t="str">
+        <x:f>IF(A269="","",IF(K269="Subscription","",IF(E269=0,"",IF(ISNUMBER(G269),G269/E269,IF(ISNUMBER(I269),-ABS(I269)/E269,IF(ISNUMBER(H269),0,IF(AND(ISNUMBER(F269),ISNUMBER(E269),E269&gt;0,F269&gt;E269),(F269-E269)/E269,IF(AND(ISNUMBER(F269),ISNUMBER(E269),E269&gt;0,F269=E269),0,IF(AND(ISNUMBER(F269),ISNUMBER(E269),E269&gt;0,F269=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K269" s="50" t="str">
+        <x:f>IF(A269="","",IF(AND(ISNUMBER(E269),E269=0,OR(ISNUMBER(SEARCH("Free",D269&amp;"")),AND(ISNUMBER(F269),F269=0))),"Subscription",IF(ISNUMBER(G269),"Profit",IF(ISNUMBER(I269),"Loss",IF(ISNUMBER(H269),"Draw",IF(AND(ISNUMBER(F269),ISNUMBER(E269),E269&gt;0,F269&gt;E269),"Profit",IF(AND(ISNUMBER(F269),ISNUMBER(E269),E269&gt;0,F269=E269),"Draw",IF(AND(ISNUMBER(F269),ISNUMBER(E269),E269&gt;0,F269=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L269" s="50"/>
       <x:c r="M269" s="58"/>
       <x:c r="N269" s="58"/>
@@ -10284,8 +11344,12 @@
       <x:c r="G270" s="58"/>
       <x:c r="H270" s="58"/>
       <x:c r="I270" s="58"/>
-      <x:c r="J270" s="60"/>
-      <x:c r="K270" s="50"/>
+      <x:c r="J270" s="60" t="str">
+        <x:f>IF(A270="","",IF(K270="Subscription","",IF(E270=0,"",IF(ISNUMBER(G270),G270/E270,IF(ISNUMBER(I270),-ABS(I270)/E270,IF(ISNUMBER(H270),0,IF(AND(ISNUMBER(F270),ISNUMBER(E270),E270&gt;0,F270&gt;E270),(F270-E270)/E270,IF(AND(ISNUMBER(F270),ISNUMBER(E270),E270&gt;0,F270=E270),0,IF(AND(ISNUMBER(F270),ISNUMBER(E270),E270&gt;0,F270=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K270" s="50" t="str">
+        <x:f>IF(A270="","",IF(AND(ISNUMBER(E270),E270=0,OR(ISNUMBER(SEARCH("Free",D270&amp;"")),AND(ISNUMBER(F270),F270=0))),"Subscription",IF(ISNUMBER(G270),"Profit",IF(ISNUMBER(I270),"Loss",IF(ISNUMBER(H270),"Draw",IF(AND(ISNUMBER(F270),ISNUMBER(E270),E270&gt;0,F270&gt;E270),"Profit",IF(AND(ISNUMBER(F270),ISNUMBER(E270),E270&gt;0,F270=E270),"Draw",IF(AND(ISNUMBER(F270),ISNUMBER(E270),E270&gt;0,F270=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L270" s="50"/>
       <x:c r="M270" s="58"/>
       <x:c r="N270" s="58"/>
@@ -10317,8 +11381,12 @@
       <x:c r="G271" s="58"/>
       <x:c r="H271" s="58"/>
       <x:c r="I271" s="58"/>
-      <x:c r="J271" s="60"/>
-      <x:c r="K271" s="50"/>
+      <x:c r="J271" s="60" t="str">
+        <x:f>IF(A271="","",IF(K271="Subscription","",IF(E271=0,"",IF(ISNUMBER(G271),G271/E271,IF(ISNUMBER(I271),-ABS(I271)/E271,IF(ISNUMBER(H271),0,IF(AND(ISNUMBER(F271),ISNUMBER(E271),E271&gt;0,F271&gt;E271),(F271-E271)/E271,IF(AND(ISNUMBER(F271),ISNUMBER(E271),E271&gt;0,F271=E271),0,IF(AND(ISNUMBER(F271),ISNUMBER(E271),E271&gt;0,F271=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K271" s="50" t="str">
+        <x:f>IF(A271="","",IF(AND(ISNUMBER(E271),E271=0,OR(ISNUMBER(SEARCH("Free",D271&amp;"")),AND(ISNUMBER(F271),F271=0))),"Subscription",IF(ISNUMBER(G271),"Profit",IF(ISNUMBER(I271),"Loss",IF(ISNUMBER(H271),"Draw",IF(AND(ISNUMBER(F271),ISNUMBER(E271),E271&gt;0,F271&gt;E271),"Profit",IF(AND(ISNUMBER(F271),ISNUMBER(E271),E271&gt;0,F271=E271),"Draw",IF(AND(ISNUMBER(F271),ISNUMBER(E271),E271&gt;0,F271=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L271" s="50"/>
       <x:c r="M271" s="58"/>
       <x:c r="N271" s="58"/>
@@ -10350,8 +11418,12 @@
       <x:c r="G272" s="58"/>
       <x:c r="H272" s="58"/>
       <x:c r="I272" s="58"/>
-      <x:c r="J272" s="60"/>
-      <x:c r="K272" s="50"/>
+      <x:c r="J272" s="60" t="str">
+        <x:f>IF(A272="","",IF(K272="Subscription","",IF(E272=0,"",IF(ISNUMBER(G272),G272/E272,IF(ISNUMBER(I272),-ABS(I272)/E272,IF(ISNUMBER(H272),0,IF(AND(ISNUMBER(F272),ISNUMBER(E272),E272&gt;0,F272&gt;E272),(F272-E272)/E272,IF(AND(ISNUMBER(F272),ISNUMBER(E272),E272&gt;0,F272=E272),0,IF(AND(ISNUMBER(F272),ISNUMBER(E272),E272&gt;0,F272=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K272" s="50" t="str">
+        <x:f>IF(A272="","",IF(AND(ISNUMBER(E272),E272=0,OR(ISNUMBER(SEARCH("Free",D272&amp;"")),AND(ISNUMBER(F272),F272=0))),"Subscription",IF(ISNUMBER(G272),"Profit",IF(ISNUMBER(I272),"Loss",IF(ISNUMBER(H272),"Draw",IF(AND(ISNUMBER(F272),ISNUMBER(E272),E272&gt;0,F272&gt;E272),"Profit",IF(AND(ISNUMBER(F272),ISNUMBER(E272),E272&gt;0,F272=E272),"Draw",IF(AND(ISNUMBER(F272),ISNUMBER(E272),E272&gt;0,F272=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L272" s="50"/>
       <x:c r="M272" s="58"/>
       <x:c r="N272" s="58"/>
@@ -10383,8 +11455,12 @@
       <x:c r="G273" s="58"/>
       <x:c r="H273" s="58"/>
       <x:c r="I273" s="58"/>
-      <x:c r="J273" s="60"/>
-      <x:c r="K273" s="50"/>
+      <x:c r="J273" s="60" t="str">
+        <x:f>IF(A273="","",IF(K273="Subscription","",IF(E273=0,"",IF(ISNUMBER(G273),G273/E273,IF(ISNUMBER(I273),-ABS(I273)/E273,IF(ISNUMBER(H273),0,IF(AND(ISNUMBER(F273),ISNUMBER(E273),E273&gt;0,F273&gt;E273),(F273-E273)/E273,IF(AND(ISNUMBER(F273),ISNUMBER(E273),E273&gt;0,F273=E273),0,IF(AND(ISNUMBER(F273),ISNUMBER(E273),E273&gt;0,F273=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K273" s="50" t="str">
+        <x:f>IF(A273="","",IF(AND(ISNUMBER(E273),E273=0,OR(ISNUMBER(SEARCH("Free",D273&amp;"")),AND(ISNUMBER(F273),F273=0))),"Subscription",IF(ISNUMBER(G273),"Profit",IF(ISNUMBER(I273),"Loss",IF(ISNUMBER(H273),"Draw",IF(AND(ISNUMBER(F273),ISNUMBER(E273),E273&gt;0,F273&gt;E273),"Profit",IF(AND(ISNUMBER(F273),ISNUMBER(E273),E273&gt;0,F273=E273),"Draw",IF(AND(ISNUMBER(F273),ISNUMBER(E273),E273&gt;0,F273=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L273" s="50"/>
       <x:c r="M273" s="58"/>
       <x:c r="N273" s="58"/>
@@ -10416,8 +11492,12 @@
       <x:c r="G274" s="58"/>
       <x:c r="H274" s="58"/>
       <x:c r="I274" s="58"/>
-      <x:c r="J274" s="60"/>
-      <x:c r="K274" s="50"/>
+      <x:c r="J274" s="60" t="str">
+        <x:f>IF(A274="","",IF(K274="Subscription","",IF(E274=0,"",IF(ISNUMBER(G274),G274/E274,IF(ISNUMBER(I274),-ABS(I274)/E274,IF(ISNUMBER(H274),0,IF(AND(ISNUMBER(F274),ISNUMBER(E274),E274&gt;0,F274&gt;E274),(F274-E274)/E274,IF(AND(ISNUMBER(F274),ISNUMBER(E274),E274&gt;0,F274=E274),0,IF(AND(ISNUMBER(F274),ISNUMBER(E274),E274&gt;0,F274=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K274" s="50" t="str">
+        <x:f>IF(A274="","",IF(AND(ISNUMBER(E274),E274=0,OR(ISNUMBER(SEARCH("Free",D274&amp;"")),AND(ISNUMBER(F274),F274=0))),"Subscription",IF(ISNUMBER(G274),"Profit",IF(ISNUMBER(I274),"Loss",IF(ISNUMBER(H274),"Draw",IF(AND(ISNUMBER(F274),ISNUMBER(E274),E274&gt;0,F274&gt;E274),"Profit",IF(AND(ISNUMBER(F274),ISNUMBER(E274),E274&gt;0,F274=E274),"Draw",IF(AND(ISNUMBER(F274),ISNUMBER(E274),E274&gt;0,F274=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L274" s="50"/>
       <x:c r="M274" s="58"/>
       <x:c r="N274" s="58"/>
@@ -10449,8 +11529,12 @@
       <x:c r="G275" s="58"/>
       <x:c r="H275" s="58"/>
       <x:c r="I275" s="58"/>
-      <x:c r="J275" s="60"/>
-      <x:c r="K275" s="50"/>
+      <x:c r="J275" s="60" t="str">
+        <x:f>IF(A275="","",IF(K275="Subscription","",IF(E275=0,"",IF(ISNUMBER(G275),G275/E275,IF(ISNUMBER(I275),-ABS(I275)/E275,IF(ISNUMBER(H275),0,IF(AND(ISNUMBER(F275),ISNUMBER(E275),E275&gt;0,F275&gt;E275),(F275-E275)/E275,IF(AND(ISNUMBER(F275),ISNUMBER(E275),E275&gt;0,F275=E275),0,IF(AND(ISNUMBER(F275),ISNUMBER(E275),E275&gt;0,F275=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K275" s="50" t="str">
+        <x:f>IF(A275="","",IF(AND(ISNUMBER(E275),E275=0,OR(ISNUMBER(SEARCH("Free",D275&amp;"")),AND(ISNUMBER(F275),F275=0))),"Subscription",IF(ISNUMBER(G275),"Profit",IF(ISNUMBER(I275),"Loss",IF(ISNUMBER(H275),"Draw",IF(AND(ISNUMBER(F275),ISNUMBER(E275),E275&gt;0,F275&gt;E275),"Profit",IF(AND(ISNUMBER(F275),ISNUMBER(E275),E275&gt;0,F275=E275),"Draw",IF(AND(ISNUMBER(F275),ISNUMBER(E275),E275&gt;0,F275=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L275" s="50"/>
       <x:c r="M275" s="58"/>
       <x:c r="N275" s="58"/>
@@ -10482,8 +11566,12 @@
       <x:c r="G276" s="58"/>
       <x:c r="H276" s="58"/>
       <x:c r="I276" s="58"/>
-      <x:c r="J276" s="60"/>
-      <x:c r="K276" s="50"/>
+      <x:c r="J276" s="60" t="str">
+        <x:f>IF(A276="","",IF(K276="Subscription","",IF(E276=0,"",IF(ISNUMBER(G276),G276/E276,IF(ISNUMBER(I276),-ABS(I276)/E276,IF(ISNUMBER(H276),0,IF(AND(ISNUMBER(F276),ISNUMBER(E276),E276&gt;0,F276&gt;E276),(F276-E276)/E276,IF(AND(ISNUMBER(F276),ISNUMBER(E276),E276&gt;0,F276=E276),0,IF(AND(ISNUMBER(F276),ISNUMBER(E276),E276&gt;0,F276=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K276" s="50" t="str">
+        <x:f>IF(A276="","",IF(AND(ISNUMBER(E276),E276=0,OR(ISNUMBER(SEARCH("Free",D276&amp;"")),AND(ISNUMBER(F276),F276=0))),"Subscription",IF(ISNUMBER(G276),"Profit",IF(ISNUMBER(I276),"Loss",IF(ISNUMBER(H276),"Draw",IF(AND(ISNUMBER(F276),ISNUMBER(E276),E276&gt;0,F276&gt;E276),"Profit",IF(AND(ISNUMBER(F276),ISNUMBER(E276),E276&gt;0,F276=E276),"Draw",IF(AND(ISNUMBER(F276),ISNUMBER(E276),E276&gt;0,F276=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L276" s="50"/>
       <x:c r="M276" s="58"/>
       <x:c r="N276" s="58"/>
@@ -10515,8 +11603,12 @@
       <x:c r="G277" s="58"/>
       <x:c r="H277" s="58"/>
       <x:c r="I277" s="58"/>
-      <x:c r="J277" s="60"/>
-      <x:c r="K277" s="50"/>
+      <x:c r="J277" s="60" t="str">
+        <x:f>IF(A277="","",IF(K277="Subscription","",IF(E277=0,"",IF(ISNUMBER(G277),G277/E277,IF(ISNUMBER(I277),-ABS(I277)/E277,IF(ISNUMBER(H277),0,IF(AND(ISNUMBER(F277),ISNUMBER(E277),E277&gt;0,F277&gt;E277),(F277-E277)/E277,IF(AND(ISNUMBER(F277),ISNUMBER(E277),E277&gt;0,F277=E277),0,IF(AND(ISNUMBER(F277),ISNUMBER(E277),E277&gt;0,F277=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K277" s="50" t="str">
+        <x:f>IF(A277="","",IF(AND(ISNUMBER(E277),E277=0,OR(ISNUMBER(SEARCH("Free",D277&amp;"")),AND(ISNUMBER(F277),F277=0))),"Subscription",IF(ISNUMBER(G277),"Profit",IF(ISNUMBER(I277),"Loss",IF(ISNUMBER(H277),"Draw",IF(AND(ISNUMBER(F277),ISNUMBER(E277),E277&gt;0,F277&gt;E277),"Profit",IF(AND(ISNUMBER(F277),ISNUMBER(E277),E277&gt;0,F277=E277),"Draw",IF(AND(ISNUMBER(F277),ISNUMBER(E277),E277&gt;0,F277=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L277" s="50"/>
       <x:c r="M277" s="58"/>
       <x:c r="N277" s="58"/>
@@ -10548,8 +11640,12 @@
       <x:c r="G278" s="58"/>
       <x:c r="H278" s="58"/>
       <x:c r="I278" s="58"/>
-      <x:c r="J278" s="60"/>
-      <x:c r="K278" s="50"/>
+      <x:c r="J278" s="60" t="str">
+        <x:f>IF(A278="","",IF(K278="Subscription","",IF(E278=0,"",IF(ISNUMBER(G278),G278/E278,IF(ISNUMBER(I278),-ABS(I278)/E278,IF(ISNUMBER(H278),0,IF(AND(ISNUMBER(F278),ISNUMBER(E278),E278&gt;0,F278&gt;E278),(F278-E278)/E278,IF(AND(ISNUMBER(F278),ISNUMBER(E278),E278&gt;0,F278=E278),0,IF(AND(ISNUMBER(F278),ISNUMBER(E278),E278&gt;0,F278=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K278" s="50" t="str">
+        <x:f>IF(A278="","",IF(AND(ISNUMBER(E278),E278=0,OR(ISNUMBER(SEARCH("Free",D278&amp;"")),AND(ISNUMBER(F278),F278=0))),"Subscription",IF(ISNUMBER(G278),"Profit",IF(ISNUMBER(I278),"Loss",IF(ISNUMBER(H278),"Draw",IF(AND(ISNUMBER(F278),ISNUMBER(E278),E278&gt;0,F278&gt;E278),"Profit",IF(AND(ISNUMBER(F278),ISNUMBER(E278),E278&gt;0,F278=E278),"Draw",IF(AND(ISNUMBER(F278),ISNUMBER(E278),E278&gt;0,F278=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L278" s="50"/>
       <x:c r="M278" s="58"/>
       <x:c r="N278" s="58"/>
@@ -10581,8 +11677,12 @@
       <x:c r="G279" s="58"/>
       <x:c r="H279" s="58"/>
       <x:c r="I279" s="58"/>
-      <x:c r="J279" s="60"/>
-      <x:c r="K279" s="50"/>
+      <x:c r="J279" s="60" t="str">
+        <x:f>IF(A279="","",IF(K279="Subscription","",IF(E279=0,"",IF(ISNUMBER(G279),G279/E279,IF(ISNUMBER(I279),-ABS(I279)/E279,IF(ISNUMBER(H279),0,IF(AND(ISNUMBER(F279),ISNUMBER(E279),E279&gt;0,F279&gt;E279),(F279-E279)/E279,IF(AND(ISNUMBER(F279),ISNUMBER(E279),E279&gt;0,F279=E279),0,IF(AND(ISNUMBER(F279),ISNUMBER(E279),E279&gt;0,F279=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K279" s="50" t="str">
+        <x:f>IF(A279="","",IF(AND(ISNUMBER(E279),E279=0,OR(ISNUMBER(SEARCH("Free",D279&amp;"")),AND(ISNUMBER(F279),F279=0))),"Subscription",IF(ISNUMBER(G279),"Profit",IF(ISNUMBER(I279),"Loss",IF(ISNUMBER(H279),"Draw",IF(AND(ISNUMBER(F279),ISNUMBER(E279),E279&gt;0,F279&gt;E279),"Profit",IF(AND(ISNUMBER(F279),ISNUMBER(E279),E279&gt;0,F279=E279),"Draw",IF(AND(ISNUMBER(F279),ISNUMBER(E279),E279&gt;0,F279=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L279" s="50"/>
       <x:c r="M279" s="58"/>
       <x:c r="N279" s="58"/>
@@ -10614,8 +11714,12 @@
       <x:c r="G280" s="58"/>
       <x:c r="H280" s="58"/>
       <x:c r="I280" s="58"/>
-      <x:c r="J280" s="60"/>
-      <x:c r="K280" s="50"/>
+      <x:c r="J280" s="60" t="str">
+        <x:f>IF(A280="","",IF(K280="Subscription","",IF(E280=0,"",IF(ISNUMBER(G280),G280/E280,IF(ISNUMBER(I280),-ABS(I280)/E280,IF(ISNUMBER(H280),0,IF(AND(ISNUMBER(F280),ISNUMBER(E280),E280&gt;0,F280&gt;E280),(F280-E280)/E280,IF(AND(ISNUMBER(F280),ISNUMBER(E280),E280&gt;0,F280=E280),0,IF(AND(ISNUMBER(F280),ISNUMBER(E280),E280&gt;0,F280=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K280" s="50" t="str">
+        <x:f>IF(A280="","",IF(AND(ISNUMBER(E280),E280=0,OR(ISNUMBER(SEARCH("Free",D280&amp;"")),AND(ISNUMBER(F280),F280=0))),"Subscription",IF(ISNUMBER(G280),"Profit",IF(ISNUMBER(I280),"Loss",IF(ISNUMBER(H280),"Draw",IF(AND(ISNUMBER(F280),ISNUMBER(E280),E280&gt;0,F280&gt;E280),"Profit",IF(AND(ISNUMBER(F280),ISNUMBER(E280),E280&gt;0,F280=E280),"Draw",IF(AND(ISNUMBER(F280),ISNUMBER(E280),E280&gt;0,F280=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L280" s="50"/>
       <x:c r="M280" s="58"/>
       <x:c r="N280" s="58"/>
@@ -10647,8 +11751,12 @@
       <x:c r="G281" s="58"/>
       <x:c r="H281" s="58"/>
       <x:c r="I281" s="58"/>
-      <x:c r="J281" s="60"/>
-      <x:c r="K281" s="50"/>
+      <x:c r="J281" s="60" t="str">
+        <x:f>IF(A281="","",IF(K281="Subscription","",IF(E281=0,"",IF(ISNUMBER(G281),G281/E281,IF(ISNUMBER(I281),-ABS(I281)/E281,IF(ISNUMBER(H281),0,IF(AND(ISNUMBER(F281),ISNUMBER(E281),E281&gt;0,F281&gt;E281),(F281-E281)/E281,IF(AND(ISNUMBER(F281),ISNUMBER(E281),E281&gt;0,F281=E281),0,IF(AND(ISNUMBER(F281),ISNUMBER(E281),E281&gt;0,F281=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K281" s="50" t="str">
+        <x:f>IF(A281="","",IF(AND(ISNUMBER(E281),E281=0,OR(ISNUMBER(SEARCH("Free",D281&amp;"")),AND(ISNUMBER(F281),F281=0))),"Subscription",IF(ISNUMBER(G281),"Profit",IF(ISNUMBER(I281),"Loss",IF(ISNUMBER(H281),"Draw",IF(AND(ISNUMBER(F281),ISNUMBER(E281),E281&gt;0,F281&gt;E281),"Profit",IF(AND(ISNUMBER(F281),ISNUMBER(E281),E281&gt;0,F281=E281),"Draw",IF(AND(ISNUMBER(F281),ISNUMBER(E281),E281&gt;0,F281=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L281" s="50"/>
       <x:c r="M281" s="58"/>
       <x:c r="N281" s="58"/>
@@ -10680,8 +11788,12 @@
       <x:c r="G282" s="58"/>
       <x:c r="H282" s="58"/>
       <x:c r="I282" s="58"/>
-      <x:c r="J282" s="60"/>
-      <x:c r="K282" s="50"/>
+      <x:c r="J282" s="60" t="str">
+        <x:f>IF(A282="","",IF(K282="Subscription","",IF(E282=0,"",IF(ISNUMBER(G282),G282/E282,IF(ISNUMBER(I282),-ABS(I282)/E282,IF(ISNUMBER(H282),0,IF(AND(ISNUMBER(F282),ISNUMBER(E282),E282&gt;0,F282&gt;E282),(F282-E282)/E282,IF(AND(ISNUMBER(F282),ISNUMBER(E282),E282&gt;0,F282=E282),0,IF(AND(ISNUMBER(F282),ISNUMBER(E282),E282&gt;0,F282=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K282" s="50" t="str">
+        <x:f>IF(A282="","",IF(AND(ISNUMBER(E282),E282=0,OR(ISNUMBER(SEARCH("Free",D282&amp;"")),AND(ISNUMBER(F282),F282=0))),"Subscription",IF(ISNUMBER(G282),"Profit",IF(ISNUMBER(I282),"Loss",IF(ISNUMBER(H282),"Draw",IF(AND(ISNUMBER(F282),ISNUMBER(E282),E282&gt;0,F282&gt;E282),"Profit",IF(AND(ISNUMBER(F282),ISNUMBER(E282),E282&gt;0,F282=E282),"Draw",IF(AND(ISNUMBER(F282),ISNUMBER(E282),E282&gt;0,F282=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L282" s="50"/>
       <x:c r="M282" s="58"/>
       <x:c r="N282" s="58"/>
@@ -10713,8 +11825,12 @@
       <x:c r="G283" s="58"/>
       <x:c r="H283" s="58"/>
       <x:c r="I283" s="58"/>
-      <x:c r="J283" s="60"/>
-      <x:c r="K283" s="50"/>
+      <x:c r="J283" s="60" t="str">
+        <x:f>IF(A283="","",IF(K283="Subscription","",IF(E283=0,"",IF(ISNUMBER(G283),G283/E283,IF(ISNUMBER(I283),-ABS(I283)/E283,IF(ISNUMBER(H283),0,IF(AND(ISNUMBER(F283),ISNUMBER(E283),E283&gt;0,F283&gt;E283),(F283-E283)/E283,IF(AND(ISNUMBER(F283),ISNUMBER(E283),E283&gt;0,F283=E283),0,IF(AND(ISNUMBER(F283),ISNUMBER(E283),E283&gt;0,F283=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K283" s="50" t="str">
+        <x:f>IF(A283="","",IF(AND(ISNUMBER(E283),E283=0,OR(ISNUMBER(SEARCH("Free",D283&amp;"")),AND(ISNUMBER(F283),F283=0))),"Subscription",IF(ISNUMBER(G283),"Profit",IF(ISNUMBER(I283),"Loss",IF(ISNUMBER(H283),"Draw",IF(AND(ISNUMBER(F283),ISNUMBER(E283),E283&gt;0,F283&gt;E283),"Profit",IF(AND(ISNUMBER(F283),ISNUMBER(E283),E283&gt;0,F283=E283),"Draw",IF(AND(ISNUMBER(F283),ISNUMBER(E283),E283&gt;0,F283=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L283" s="50"/>
       <x:c r="M283" s="58"/>
       <x:c r="N283" s="58"/>
@@ -10746,8 +11862,12 @@
       <x:c r="G284" s="58"/>
       <x:c r="H284" s="58"/>
       <x:c r="I284" s="58"/>
-      <x:c r="J284" s="60"/>
-      <x:c r="K284" s="50"/>
+      <x:c r="J284" s="60" t="str">
+        <x:f>IF(A284="","",IF(K284="Subscription","",IF(E284=0,"",IF(ISNUMBER(G284),G284/E284,IF(ISNUMBER(I284),-ABS(I284)/E284,IF(ISNUMBER(H284),0,IF(AND(ISNUMBER(F284),ISNUMBER(E284),E284&gt;0,F284&gt;E284),(F284-E284)/E284,IF(AND(ISNUMBER(F284),ISNUMBER(E284),E284&gt;0,F284=E284),0,IF(AND(ISNUMBER(F284),ISNUMBER(E284),E284&gt;0,F284=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K284" s="50" t="str">
+        <x:f>IF(A284="","",IF(AND(ISNUMBER(E284),E284=0,OR(ISNUMBER(SEARCH("Free",D284&amp;"")),AND(ISNUMBER(F284),F284=0))),"Subscription",IF(ISNUMBER(G284),"Profit",IF(ISNUMBER(I284),"Loss",IF(ISNUMBER(H284),"Draw",IF(AND(ISNUMBER(F284),ISNUMBER(E284),E284&gt;0,F284&gt;E284),"Profit",IF(AND(ISNUMBER(F284),ISNUMBER(E284),E284&gt;0,F284=E284),"Draw",IF(AND(ISNUMBER(F284),ISNUMBER(E284),E284&gt;0,F284=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L284" s="50"/>
       <x:c r="M284" s="58"/>
       <x:c r="N284" s="58"/>
@@ -10779,8 +11899,12 @@
       <x:c r="G285" s="58"/>
       <x:c r="H285" s="58"/>
       <x:c r="I285" s="58"/>
-      <x:c r="J285" s="60"/>
-      <x:c r="K285" s="50"/>
+      <x:c r="J285" s="60" t="str">
+        <x:f>IF(A285="","",IF(K285="Subscription","",IF(E285=0,"",IF(ISNUMBER(G285),G285/E285,IF(ISNUMBER(I285),-ABS(I285)/E285,IF(ISNUMBER(H285),0,IF(AND(ISNUMBER(F285),ISNUMBER(E285),E285&gt;0,F285&gt;E285),(F285-E285)/E285,IF(AND(ISNUMBER(F285),ISNUMBER(E285),E285&gt;0,F285=E285),0,IF(AND(ISNUMBER(F285),ISNUMBER(E285),E285&gt;0,F285=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K285" s="50" t="str">
+        <x:f>IF(A285="","",IF(AND(ISNUMBER(E285),E285=0,OR(ISNUMBER(SEARCH("Free",D285&amp;"")),AND(ISNUMBER(F285),F285=0))),"Subscription",IF(ISNUMBER(G285),"Profit",IF(ISNUMBER(I285),"Loss",IF(ISNUMBER(H285),"Draw",IF(AND(ISNUMBER(F285),ISNUMBER(E285),E285&gt;0,F285&gt;E285),"Profit",IF(AND(ISNUMBER(F285),ISNUMBER(E285),E285&gt;0,F285=E285),"Draw",IF(AND(ISNUMBER(F285),ISNUMBER(E285),E285&gt;0,F285=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L285" s="50"/>
       <x:c r="M285" s="58"/>
       <x:c r="N285" s="58"/>
@@ -10812,8 +11936,12 @@
       <x:c r="G286" s="58"/>
       <x:c r="H286" s="58"/>
       <x:c r="I286" s="58"/>
-      <x:c r="J286" s="60"/>
-      <x:c r="K286" s="50"/>
+      <x:c r="J286" s="60" t="str">
+        <x:f>IF(A286="","",IF(K286="Subscription","",IF(E286=0,"",IF(ISNUMBER(G286),G286/E286,IF(ISNUMBER(I286),-ABS(I286)/E286,IF(ISNUMBER(H286),0,IF(AND(ISNUMBER(F286),ISNUMBER(E286),E286&gt;0,F286&gt;E286),(F286-E286)/E286,IF(AND(ISNUMBER(F286),ISNUMBER(E286),E286&gt;0,F286=E286),0,IF(AND(ISNUMBER(F286),ISNUMBER(E286),E286&gt;0,F286=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K286" s="50" t="str">
+        <x:f>IF(A286="","",IF(AND(ISNUMBER(E286),E286=0,OR(ISNUMBER(SEARCH("Free",D286&amp;"")),AND(ISNUMBER(F286),F286=0))),"Subscription",IF(ISNUMBER(G286),"Profit",IF(ISNUMBER(I286),"Loss",IF(ISNUMBER(H286),"Draw",IF(AND(ISNUMBER(F286),ISNUMBER(E286),E286&gt;0,F286&gt;E286),"Profit",IF(AND(ISNUMBER(F286),ISNUMBER(E286),E286&gt;0,F286=E286),"Draw",IF(AND(ISNUMBER(F286),ISNUMBER(E286),E286&gt;0,F286=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L286" s="50"/>
       <x:c r="M286" s="58"/>
       <x:c r="N286" s="58"/>
@@ -10845,8 +11973,12 @@
       <x:c r="G287" s="58"/>
       <x:c r="H287" s="58"/>
       <x:c r="I287" s="58"/>
-      <x:c r="J287" s="60"/>
-      <x:c r="K287" s="50"/>
+      <x:c r="J287" s="60" t="str">
+        <x:f>IF(A287="","",IF(K287="Subscription","",IF(E287=0,"",IF(ISNUMBER(G287),G287/E287,IF(ISNUMBER(I287),-ABS(I287)/E287,IF(ISNUMBER(H287),0,IF(AND(ISNUMBER(F287),ISNUMBER(E287),E287&gt;0,F287&gt;E287),(F287-E287)/E287,IF(AND(ISNUMBER(F287),ISNUMBER(E287),E287&gt;0,F287=E287),0,IF(AND(ISNUMBER(F287),ISNUMBER(E287),E287&gt;0,F287=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K287" s="50" t="str">
+        <x:f>IF(A287="","",IF(AND(ISNUMBER(E287),E287=0,OR(ISNUMBER(SEARCH("Free",D287&amp;"")),AND(ISNUMBER(F287),F287=0))),"Subscription",IF(ISNUMBER(G287),"Profit",IF(ISNUMBER(I287),"Loss",IF(ISNUMBER(H287),"Draw",IF(AND(ISNUMBER(F287),ISNUMBER(E287),E287&gt;0,F287&gt;E287),"Profit",IF(AND(ISNUMBER(F287),ISNUMBER(E287),E287&gt;0,F287=E287),"Draw",IF(AND(ISNUMBER(F287),ISNUMBER(E287),E287&gt;0,F287=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L287" s="50"/>
       <x:c r="M287" s="58"/>
       <x:c r="N287" s="58"/>
@@ -10878,8 +12010,12 @@
       <x:c r="G288" s="58"/>
       <x:c r="H288" s="58"/>
       <x:c r="I288" s="58"/>
-      <x:c r="J288" s="60"/>
-      <x:c r="K288" s="50"/>
+      <x:c r="J288" s="60" t="str">
+        <x:f>IF(A288="","",IF(K288="Subscription","",IF(E288=0,"",IF(ISNUMBER(G288),G288/E288,IF(ISNUMBER(I288),-ABS(I288)/E288,IF(ISNUMBER(H288),0,IF(AND(ISNUMBER(F288),ISNUMBER(E288),E288&gt;0,F288&gt;E288),(F288-E288)/E288,IF(AND(ISNUMBER(F288),ISNUMBER(E288),E288&gt;0,F288=E288),0,IF(AND(ISNUMBER(F288),ISNUMBER(E288),E288&gt;0,F288=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K288" s="50" t="str">
+        <x:f>IF(A288="","",IF(AND(ISNUMBER(E288),E288=0,OR(ISNUMBER(SEARCH("Free",D288&amp;"")),AND(ISNUMBER(F288),F288=0))),"Subscription",IF(ISNUMBER(G288),"Profit",IF(ISNUMBER(I288),"Loss",IF(ISNUMBER(H288),"Draw",IF(AND(ISNUMBER(F288),ISNUMBER(E288),E288&gt;0,F288&gt;E288),"Profit",IF(AND(ISNUMBER(F288),ISNUMBER(E288),E288&gt;0,F288=E288),"Draw",IF(AND(ISNUMBER(F288),ISNUMBER(E288),E288&gt;0,F288=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L288" s="50"/>
       <x:c r="M288" s="58"/>
       <x:c r="N288" s="58"/>
@@ -10911,8 +12047,12 @@
       <x:c r="G289" s="58"/>
       <x:c r="H289" s="58"/>
       <x:c r="I289" s="58"/>
-      <x:c r="J289" s="60"/>
-      <x:c r="K289" s="50"/>
+      <x:c r="J289" s="60" t="str">
+        <x:f>IF(A289="","",IF(K289="Subscription","",IF(E289=0,"",IF(ISNUMBER(G289),G289/E289,IF(ISNUMBER(I289),-ABS(I289)/E289,IF(ISNUMBER(H289),0,IF(AND(ISNUMBER(F289),ISNUMBER(E289),E289&gt;0,F289&gt;E289),(F289-E289)/E289,IF(AND(ISNUMBER(F289),ISNUMBER(E289),E289&gt;0,F289=E289),0,IF(AND(ISNUMBER(F289),ISNUMBER(E289),E289&gt;0,F289=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K289" s="50" t="str">
+        <x:f>IF(A289="","",IF(AND(ISNUMBER(E289),E289=0,OR(ISNUMBER(SEARCH("Free",D289&amp;"")),AND(ISNUMBER(F289),F289=0))),"Subscription",IF(ISNUMBER(G289),"Profit",IF(ISNUMBER(I289),"Loss",IF(ISNUMBER(H289),"Draw",IF(AND(ISNUMBER(F289),ISNUMBER(E289),E289&gt;0,F289&gt;E289),"Profit",IF(AND(ISNUMBER(F289),ISNUMBER(E289),E289&gt;0,F289=E289),"Draw",IF(AND(ISNUMBER(F289),ISNUMBER(E289),E289&gt;0,F289=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L289" s="50"/>
       <x:c r="M289" s="58"/>
       <x:c r="N289" s="58"/>
@@ -10944,8 +12084,12 @@
       <x:c r="G290" s="58"/>
       <x:c r="H290" s="58"/>
       <x:c r="I290" s="58"/>
-      <x:c r="J290" s="60"/>
-      <x:c r="K290" s="50"/>
+      <x:c r="J290" s="60" t="str">
+        <x:f>IF(A290="","",IF(K290="Subscription","",IF(E290=0,"",IF(ISNUMBER(G290),G290/E290,IF(ISNUMBER(I290),-ABS(I290)/E290,IF(ISNUMBER(H290),0,IF(AND(ISNUMBER(F290),ISNUMBER(E290),E290&gt;0,F290&gt;E290),(F290-E290)/E290,IF(AND(ISNUMBER(F290),ISNUMBER(E290),E290&gt;0,F290=E290),0,IF(AND(ISNUMBER(F290),ISNUMBER(E290),E290&gt;0,F290=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K290" s="50" t="str">
+        <x:f>IF(A290="","",IF(AND(ISNUMBER(E290),E290=0,OR(ISNUMBER(SEARCH("Free",D290&amp;"")),AND(ISNUMBER(F290),F290=0))),"Subscription",IF(ISNUMBER(G290),"Profit",IF(ISNUMBER(I290),"Loss",IF(ISNUMBER(H290),"Draw",IF(AND(ISNUMBER(F290),ISNUMBER(E290),E290&gt;0,F290&gt;E290),"Profit",IF(AND(ISNUMBER(F290),ISNUMBER(E290),E290&gt;0,F290=E290),"Draw",IF(AND(ISNUMBER(F290),ISNUMBER(E290),E290&gt;0,F290=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L290" s="50"/>
       <x:c r="M290" s="58"/>
       <x:c r="N290" s="58"/>
@@ -10977,8 +12121,12 @@
       <x:c r="G291" s="58"/>
       <x:c r="H291" s="58"/>
       <x:c r="I291" s="58"/>
-      <x:c r="J291" s="60"/>
-      <x:c r="K291" s="50"/>
+      <x:c r="J291" s="60" t="str">
+        <x:f>IF(A291="","",IF(K291="Subscription","",IF(E291=0,"",IF(ISNUMBER(G291),G291/E291,IF(ISNUMBER(I291),-ABS(I291)/E291,IF(ISNUMBER(H291),0,IF(AND(ISNUMBER(F291),ISNUMBER(E291),E291&gt;0,F291&gt;E291),(F291-E291)/E291,IF(AND(ISNUMBER(F291),ISNUMBER(E291),E291&gt;0,F291=E291),0,IF(AND(ISNUMBER(F291),ISNUMBER(E291),E291&gt;0,F291=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K291" s="50" t="str">
+        <x:f>IF(A291="","",IF(AND(ISNUMBER(E291),E291=0,OR(ISNUMBER(SEARCH("Free",D291&amp;"")),AND(ISNUMBER(F291),F291=0))),"Subscription",IF(ISNUMBER(G291),"Profit",IF(ISNUMBER(I291),"Loss",IF(ISNUMBER(H291),"Draw",IF(AND(ISNUMBER(F291),ISNUMBER(E291),E291&gt;0,F291&gt;E291),"Profit",IF(AND(ISNUMBER(F291),ISNUMBER(E291),E291&gt;0,F291=E291),"Draw",IF(AND(ISNUMBER(F291),ISNUMBER(E291),E291&gt;0,F291=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L291" s="50"/>
       <x:c r="M291" s="58"/>
       <x:c r="N291" s="58"/>
@@ -11010,8 +12158,12 @@
       <x:c r="G292" s="58"/>
       <x:c r="H292" s="58"/>
       <x:c r="I292" s="58"/>
-      <x:c r="J292" s="60"/>
-      <x:c r="K292" s="50"/>
+      <x:c r="J292" s="60" t="str">
+        <x:f>IF(A292="","",IF(K292="Subscription","",IF(E292=0,"",IF(ISNUMBER(G292),G292/E292,IF(ISNUMBER(I292),-ABS(I292)/E292,IF(ISNUMBER(H292),0,IF(AND(ISNUMBER(F292),ISNUMBER(E292),E292&gt;0,F292&gt;E292),(F292-E292)/E292,IF(AND(ISNUMBER(F292),ISNUMBER(E292),E292&gt;0,F292=E292),0,IF(AND(ISNUMBER(F292),ISNUMBER(E292),E292&gt;0,F292=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K292" s="50" t="str">
+        <x:f>IF(A292="","",IF(AND(ISNUMBER(E292),E292=0,OR(ISNUMBER(SEARCH("Free",D292&amp;"")),AND(ISNUMBER(F292),F292=0))),"Subscription",IF(ISNUMBER(G292),"Profit",IF(ISNUMBER(I292),"Loss",IF(ISNUMBER(H292),"Draw",IF(AND(ISNUMBER(F292),ISNUMBER(E292),E292&gt;0,F292&gt;E292),"Profit",IF(AND(ISNUMBER(F292),ISNUMBER(E292),E292&gt;0,F292=E292),"Draw",IF(AND(ISNUMBER(F292),ISNUMBER(E292),E292&gt;0,F292=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L292" s="50"/>
       <x:c r="M292" s="58"/>
       <x:c r="N292" s="58"/>
@@ -11043,8 +12195,12 @@
       <x:c r="G293" s="58"/>
       <x:c r="H293" s="58"/>
       <x:c r="I293" s="58"/>
-      <x:c r="J293" s="60"/>
-      <x:c r="K293" s="50"/>
+      <x:c r="J293" s="60" t="str">
+        <x:f>IF(A293="","",IF(K293="Subscription","",IF(E293=0,"",IF(ISNUMBER(G293),G293/E293,IF(ISNUMBER(I293),-ABS(I293)/E293,IF(ISNUMBER(H293),0,IF(AND(ISNUMBER(F293),ISNUMBER(E293),E293&gt;0,F293&gt;E293),(F293-E293)/E293,IF(AND(ISNUMBER(F293),ISNUMBER(E293),E293&gt;0,F293=E293),0,IF(AND(ISNUMBER(F293),ISNUMBER(E293),E293&gt;0,F293=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K293" s="50" t="str">
+        <x:f>IF(A293="","",IF(AND(ISNUMBER(E293),E293=0,OR(ISNUMBER(SEARCH("Free",D293&amp;"")),AND(ISNUMBER(F293),F293=0))),"Subscription",IF(ISNUMBER(G293),"Profit",IF(ISNUMBER(I293),"Loss",IF(ISNUMBER(H293),"Draw",IF(AND(ISNUMBER(F293),ISNUMBER(E293),E293&gt;0,F293&gt;E293),"Profit",IF(AND(ISNUMBER(F293),ISNUMBER(E293),E293&gt;0,F293=E293),"Draw",IF(AND(ISNUMBER(F293),ISNUMBER(E293),E293&gt;0,F293=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L293" s="50"/>
       <x:c r="M293" s="58"/>
       <x:c r="N293" s="58"/>
@@ -11076,8 +12232,12 @@
       <x:c r="G294" s="58"/>
       <x:c r="H294" s="58"/>
       <x:c r="I294" s="58"/>
-      <x:c r="J294" s="60"/>
-      <x:c r="K294" s="50"/>
+      <x:c r="J294" s="60" t="str">
+        <x:f>IF(A294="","",IF(K294="Subscription","",IF(E294=0,"",IF(ISNUMBER(G294),G294/E294,IF(ISNUMBER(I294),-ABS(I294)/E294,IF(ISNUMBER(H294),0,IF(AND(ISNUMBER(F294),ISNUMBER(E294),E294&gt;0,F294&gt;E294),(F294-E294)/E294,IF(AND(ISNUMBER(F294),ISNUMBER(E294),E294&gt;0,F294=E294),0,IF(AND(ISNUMBER(F294),ISNUMBER(E294),E294&gt;0,F294=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K294" s="50" t="str">
+        <x:f>IF(A294="","",IF(AND(ISNUMBER(E294),E294=0,OR(ISNUMBER(SEARCH("Free",D294&amp;"")),AND(ISNUMBER(F294),F294=0))),"Subscription",IF(ISNUMBER(G294),"Profit",IF(ISNUMBER(I294),"Loss",IF(ISNUMBER(H294),"Draw",IF(AND(ISNUMBER(F294),ISNUMBER(E294),E294&gt;0,F294&gt;E294),"Profit",IF(AND(ISNUMBER(F294),ISNUMBER(E294),E294&gt;0,F294=E294),"Draw",IF(AND(ISNUMBER(F294),ISNUMBER(E294),E294&gt;0,F294=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L294" s="50"/>
       <x:c r="M294" s="58"/>
       <x:c r="N294" s="58"/>
@@ -11109,8 +12269,12 @@
       <x:c r="G295" s="58"/>
       <x:c r="H295" s="58"/>
       <x:c r="I295" s="58"/>
-      <x:c r="J295" s="60"/>
-      <x:c r="K295" s="50"/>
+      <x:c r="J295" s="60" t="str">
+        <x:f>IF(A295="","",IF(K295="Subscription","",IF(E295=0,"",IF(ISNUMBER(G295),G295/E295,IF(ISNUMBER(I295),-ABS(I295)/E295,IF(ISNUMBER(H295),0,IF(AND(ISNUMBER(F295),ISNUMBER(E295),E295&gt;0,F295&gt;E295),(F295-E295)/E295,IF(AND(ISNUMBER(F295),ISNUMBER(E295),E295&gt;0,F295=E295),0,IF(AND(ISNUMBER(F295),ISNUMBER(E295),E295&gt;0,F295=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K295" s="50" t="str">
+        <x:f>IF(A295="","",IF(AND(ISNUMBER(E295),E295=0,OR(ISNUMBER(SEARCH("Free",D295&amp;"")),AND(ISNUMBER(F295),F295=0))),"Subscription",IF(ISNUMBER(G295),"Profit",IF(ISNUMBER(I295),"Loss",IF(ISNUMBER(H295),"Draw",IF(AND(ISNUMBER(F295),ISNUMBER(E295),E295&gt;0,F295&gt;E295),"Profit",IF(AND(ISNUMBER(F295),ISNUMBER(E295),E295&gt;0,F295=E295),"Draw",IF(AND(ISNUMBER(F295),ISNUMBER(E295),E295&gt;0,F295=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L295" s="50"/>
       <x:c r="M295" s="58"/>
       <x:c r="N295" s="58"/>
@@ -11142,8 +12306,12 @@
       <x:c r="G296" s="58"/>
       <x:c r="H296" s="58"/>
       <x:c r="I296" s="58"/>
-      <x:c r="J296" s="60"/>
-      <x:c r="K296" s="50"/>
+      <x:c r="J296" s="60" t="str">
+        <x:f>IF(A296="","",IF(K296="Subscription","",IF(E296=0,"",IF(ISNUMBER(G296),G296/E296,IF(ISNUMBER(I296),-ABS(I296)/E296,IF(ISNUMBER(H296),0,IF(AND(ISNUMBER(F296),ISNUMBER(E296),E296&gt;0,F296&gt;E296),(F296-E296)/E296,IF(AND(ISNUMBER(F296),ISNUMBER(E296),E296&gt;0,F296=E296),0,IF(AND(ISNUMBER(F296),ISNUMBER(E296),E296&gt;0,F296=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K296" s="50" t="str">
+        <x:f>IF(A296="","",IF(AND(ISNUMBER(E296),E296=0,OR(ISNUMBER(SEARCH("Free",D296&amp;"")),AND(ISNUMBER(F296),F296=0))),"Subscription",IF(ISNUMBER(G296),"Profit",IF(ISNUMBER(I296),"Loss",IF(ISNUMBER(H296),"Draw",IF(AND(ISNUMBER(F296),ISNUMBER(E296),E296&gt;0,F296&gt;E296),"Profit",IF(AND(ISNUMBER(F296),ISNUMBER(E296),E296&gt;0,F296=E296),"Draw",IF(AND(ISNUMBER(F296),ISNUMBER(E296),E296&gt;0,F296=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L296" s="50"/>
       <x:c r="M296" s="58"/>
       <x:c r="N296" s="58"/>
@@ -11175,8 +12343,12 @@
       <x:c r="G297" s="58"/>
       <x:c r="H297" s="58"/>
       <x:c r="I297" s="58"/>
-      <x:c r="J297" s="60"/>
-      <x:c r="K297" s="50"/>
+      <x:c r="J297" s="60" t="str">
+        <x:f>IF(A297="","",IF(K297="Subscription","",IF(E297=0,"",IF(ISNUMBER(G297),G297/E297,IF(ISNUMBER(I297),-ABS(I297)/E297,IF(ISNUMBER(H297),0,IF(AND(ISNUMBER(F297),ISNUMBER(E297),E297&gt;0,F297&gt;E297),(F297-E297)/E297,IF(AND(ISNUMBER(F297),ISNUMBER(E297),E297&gt;0,F297=E297),0,IF(AND(ISNUMBER(F297),ISNUMBER(E297),E297&gt;0,F297=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K297" s="50" t="str">
+        <x:f>IF(A297="","",IF(AND(ISNUMBER(E297),E297=0,OR(ISNUMBER(SEARCH("Free",D297&amp;"")),AND(ISNUMBER(F297),F297=0))),"Subscription",IF(ISNUMBER(G297),"Profit",IF(ISNUMBER(I297),"Loss",IF(ISNUMBER(H297),"Draw",IF(AND(ISNUMBER(F297),ISNUMBER(E297),E297&gt;0,F297&gt;E297),"Profit",IF(AND(ISNUMBER(F297),ISNUMBER(E297),E297&gt;0,F297=E297),"Draw",IF(AND(ISNUMBER(F297),ISNUMBER(E297),E297&gt;0,F297=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L297" s="50"/>
       <x:c r="M297" s="58"/>
       <x:c r="N297" s="58"/>
@@ -11208,8 +12380,12 @@
       <x:c r="G298" s="58"/>
       <x:c r="H298" s="58"/>
       <x:c r="I298" s="58"/>
-      <x:c r="J298" s="60"/>
-      <x:c r="K298" s="50"/>
+      <x:c r="J298" s="60" t="str">
+        <x:f>IF(A298="","",IF(K298="Subscription","",IF(E298=0,"",IF(ISNUMBER(G298),G298/E298,IF(ISNUMBER(I298),-ABS(I298)/E298,IF(ISNUMBER(H298),0,IF(AND(ISNUMBER(F298),ISNUMBER(E298),E298&gt;0,F298&gt;E298),(F298-E298)/E298,IF(AND(ISNUMBER(F298),ISNUMBER(E298),E298&gt;0,F298=E298),0,IF(AND(ISNUMBER(F298),ISNUMBER(E298),E298&gt;0,F298=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K298" s="50" t="str">
+        <x:f>IF(A298="","",IF(AND(ISNUMBER(E298),E298=0,OR(ISNUMBER(SEARCH("Free",D298&amp;"")),AND(ISNUMBER(F298),F298=0))),"Subscription",IF(ISNUMBER(G298),"Profit",IF(ISNUMBER(I298),"Loss",IF(ISNUMBER(H298),"Draw",IF(AND(ISNUMBER(F298),ISNUMBER(E298),E298&gt;0,F298&gt;E298),"Profit",IF(AND(ISNUMBER(F298),ISNUMBER(E298),E298&gt;0,F298=E298),"Draw",IF(AND(ISNUMBER(F298),ISNUMBER(E298),E298&gt;0,F298=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L298" s="50"/>
       <x:c r="M298" s="58"/>
       <x:c r="N298" s="58"/>
@@ -11241,8 +12417,12 @@
       <x:c r="G299" s="58"/>
       <x:c r="H299" s="58"/>
       <x:c r="I299" s="58"/>
-      <x:c r="J299" s="60"/>
-      <x:c r="K299" s="50"/>
+      <x:c r="J299" s="60" t="str">
+        <x:f>IF(A299="","",IF(K299="Subscription","",IF(E299=0,"",IF(ISNUMBER(G299),G299/E299,IF(ISNUMBER(I299),-ABS(I299)/E299,IF(ISNUMBER(H299),0,IF(AND(ISNUMBER(F299),ISNUMBER(E299),E299&gt;0,F299&gt;E299),(F299-E299)/E299,IF(AND(ISNUMBER(F299),ISNUMBER(E299),E299&gt;0,F299=E299),0,IF(AND(ISNUMBER(F299),ISNUMBER(E299),E299&gt;0,F299=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K299" s="50" t="str">
+        <x:f>IF(A299="","",IF(AND(ISNUMBER(E299),E299=0,OR(ISNUMBER(SEARCH("Free",D299&amp;"")),AND(ISNUMBER(F299),F299=0))),"Subscription",IF(ISNUMBER(G299),"Profit",IF(ISNUMBER(I299),"Loss",IF(ISNUMBER(H299),"Draw",IF(AND(ISNUMBER(F299),ISNUMBER(E299),E299&gt;0,F299&gt;E299),"Profit",IF(AND(ISNUMBER(F299),ISNUMBER(E299),E299&gt;0,F299=E299),"Draw",IF(AND(ISNUMBER(F299),ISNUMBER(E299),E299&gt;0,F299=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L299" s="50"/>
       <x:c r="M299" s="58"/>
       <x:c r="N299" s="58"/>
@@ -11274,8 +12454,12 @@
       <x:c r="G300" s="58"/>
       <x:c r="H300" s="58"/>
       <x:c r="I300" s="58"/>
-      <x:c r="J300" s="60"/>
-      <x:c r="K300" s="50"/>
+      <x:c r="J300" s="60" t="str">
+        <x:f>IF(A300="","",IF(K300="Subscription","",IF(E300=0,"",IF(ISNUMBER(G300),G300/E300,IF(ISNUMBER(I300),-ABS(I300)/E300,IF(ISNUMBER(H300),0,IF(AND(ISNUMBER(F300),ISNUMBER(E300),E300&gt;0,F300&gt;E300),(F300-E300)/E300,IF(AND(ISNUMBER(F300),ISNUMBER(E300),E300&gt;0,F300=E300),0,IF(AND(ISNUMBER(F300),ISNUMBER(E300),E300&gt;0,F300=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K300" s="50" t="str">
+        <x:f>IF(A300="","",IF(AND(ISNUMBER(E300),E300=0,OR(ISNUMBER(SEARCH("Free",D300&amp;"")),AND(ISNUMBER(F300),F300=0))),"Subscription",IF(ISNUMBER(G300),"Profit",IF(ISNUMBER(I300),"Loss",IF(ISNUMBER(H300),"Draw",IF(AND(ISNUMBER(F300),ISNUMBER(E300),E300&gt;0,F300&gt;E300),"Profit",IF(AND(ISNUMBER(F300),ISNUMBER(E300),E300&gt;0,F300=E300),"Draw",IF(AND(ISNUMBER(F300),ISNUMBER(E300),E300&gt;0,F300=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L300" s="50"/>
       <x:c r="M300" s="58"/>
       <x:c r="N300" s="58"/>
@@ -11307,8 +12491,12 @@
       <x:c r="G301" s="58"/>
       <x:c r="H301" s="58"/>
       <x:c r="I301" s="58"/>
-      <x:c r="J301" s="60"/>
-      <x:c r="K301" s="50"/>
+      <x:c r="J301" s="60" t="str">
+        <x:f>IF(A301="","",IF(K301="Subscription","",IF(E301=0,"",IF(ISNUMBER(G301),G301/E301,IF(ISNUMBER(I301),-ABS(I301)/E301,IF(ISNUMBER(H301),0,IF(AND(ISNUMBER(F301),ISNUMBER(E301),E301&gt;0,F301&gt;E301),(F301-E301)/E301,IF(AND(ISNUMBER(F301),ISNUMBER(E301),E301&gt;0,F301=E301),0,IF(AND(ISNUMBER(F301),ISNUMBER(E301),E301&gt;0,F301=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K301" s="50" t="str">
+        <x:f>IF(A301="","",IF(AND(ISNUMBER(E301),E301=0,OR(ISNUMBER(SEARCH("Free",D301&amp;"")),AND(ISNUMBER(F301),F301=0))),"Subscription",IF(ISNUMBER(G301),"Profit",IF(ISNUMBER(I301),"Loss",IF(ISNUMBER(H301),"Draw",IF(AND(ISNUMBER(F301),ISNUMBER(E301),E301&gt;0,F301&gt;E301),"Profit",IF(AND(ISNUMBER(F301),ISNUMBER(E301),E301&gt;0,F301=E301),"Draw",IF(AND(ISNUMBER(F301),ISNUMBER(E301),E301&gt;0,F301=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L301" s="50"/>
       <x:c r="M301" s="58"/>
       <x:c r="N301" s="58"/>
@@ -11340,8 +12528,12 @@
       <x:c r="G302" s="58"/>
       <x:c r="H302" s="58"/>
       <x:c r="I302" s="58"/>
-      <x:c r="J302" s="60"/>
-      <x:c r="K302" s="50"/>
+      <x:c r="J302" s="60" t="str">
+        <x:f>IF(A302="","",IF(K302="Subscription","",IF(E302=0,"",IF(ISNUMBER(G302),G302/E302,IF(ISNUMBER(I302),-ABS(I302)/E302,IF(ISNUMBER(H302),0,IF(AND(ISNUMBER(F302),ISNUMBER(E302),E302&gt;0,F302&gt;E302),(F302-E302)/E302,IF(AND(ISNUMBER(F302),ISNUMBER(E302),E302&gt;0,F302=E302),0,IF(AND(ISNUMBER(F302),ISNUMBER(E302),E302&gt;0,F302=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K302" s="50" t="str">
+        <x:f>IF(A302="","",IF(AND(ISNUMBER(E302),E302=0,OR(ISNUMBER(SEARCH("Free",D302&amp;"")),AND(ISNUMBER(F302),F302=0))),"Subscription",IF(ISNUMBER(G302),"Profit",IF(ISNUMBER(I302),"Loss",IF(ISNUMBER(H302),"Draw",IF(AND(ISNUMBER(F302),ISNUMBER(E302),E302&gt;0,F302&gt;E302),"Profit",IF(AND(ISNUMBER(F302),ISNUMBER(E302),E302&gt;0,F302=E302),"Draw",IF(AND(ISNUMBER(F302),ISNUMBER(E302),E302&gt;0,F302=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L302" s="50"/>
       <x:c r="M302" s="58"/>
       <x:c r="N302" s="58"/>
@@ -11373,8 +12565,12 @@
       <x:c r="G303" s="58"/>
       <x:c r="H303" s="58"/>
       <x:c r="I303" s="58"/>
-      <x:c r="J303" s="60"/>
-      <x:c r="K303" s="50"/>
+      <x:c r="J303" s="60" t="str">
+        <x:f>IF(A303="","",IF(K303="Subscription","",IF(E303=0,"",IF(ISNUMBER(G303),G303/E303,IF(ISNUMBER(I303),-ABS(I303)/E303,IF(ISNUMBER(H303),0,IF(AND(ISNUMBER(F303),ISNUMBER(E303),E303&gt;0,F303&gt;E303),(F303-E303)/E303,IF(AND(ISNUMBER(F303),ISNUMBER(E303),E303&gt;0,F303=E303),0,IF(AND(ISNUMBER(F303),ISNUMBER(E303),E303&gt;0,F303=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K303" s="50" t="str">
+        <x:f>IF(A303="","",IF(AND(ISNUMBER(E303),E303=0,OR(ISNUMBER(SEARCH("Free",D303&amp;"")),AND(ISNUMBER(F303),F303=0))),"Subscription",IF(ISNUMBER(G303),"Profit",IF(ISNUMBER(I303),"Loss",IF(ISNUMBER(H303),"Draw",IF(AND(ISNUMBER(F303),ISNUMBER(E303),E303&gt;0,F303&gt;E303),"Profit",IF(AND(ISNUMBER(F303),ISNUMBER(E303),E303&gt;0,F303=E303),"Draw",IF(AND(ISNUMBER(F303),ISNUMBER(E303),E303&gt;0,F303=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L303" s="50"/>
       <x:c r="M303" s="58"/>
       <x:c r="N303" s="58"/>
@@ -11406,8 +12602,12 @@
       <x:c r="G304" s="58"/>
       <x:c r="H304" s="58"/>
       <x:c r="I304" s="58"/>
-      <x:c r="J304" s="60"/>
-      <x:c r="K304" s="50"/>
+      <x:c r="J304" s="60" t="str">
+        <x:f>IF(A304="","",IF(K304="Subscription","",IF(E304=0,"",IF(ISNUMBER(G304),G304/E304,IF(ISNUMBER(I304),-ABS(I304)/E304,IF(ISNUMBER(H304),0,IF(AND(ISNUMBER(F304),ISNUMBER(E304),E304&gt;0,F304&gt;E304),(F304-E304)/E304,IF(AND(ISNUMBER(F304),ISNUMBER(E304),E304&gt;0,F304=E304),0,IF(AND(ISNUMBER(F304),ISNUMBER(E304),E304&gt;0,F304=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K304" s="50" t="str">
+        <x:f>IF(A304="","",IF(AND(ISNUMBER(E304),E304=0,OR(ISNUMBER(SEARCH("Free",D304&amp;"")),AND(ISNUMBER(F304),F304=0))),"Subscription",IF(ISNUMBER(G304),"Profit",IF(ISNUMBER(I304),"Loss",IF(ISNUMBER(H304),"Draw",IF(AND(ISNUMBER(F304),ISNUMBER(E304),E304&gt;0,F304&gt;E304),"Profit",IF(AND(ISNUMBER(F304),ISNUMBER(E304),E304&gt;0,F304=E304),"Draw",IF(AND(ISNUMBER(F304),ISNUMBER(E304),E304&gt;0,F304=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L304" s="50"/>
       <x:c r="M304" s="58"/>
       <x:c r="N304" s="58"/>
@@ -11439,8 +12639,12 @@
       <x:c r="G305" s="58"/>
       <x:c r="H305" s="58"/>
       <x:c r="I305" s="58"/>
-      <x:c r="J305" s="60"/>
-      <x:c r="K305" s="50"/>
+      <x:c r="J305" s="60" t="str">
+        <x:f>IF(A305="","",IF(K305="Subscription","",IF(E305=0,"",IF(ISNUMBER(G305),G305/E305,IF(ISNUMBER(I305),-ABS(I305)/E305,IF(ISNUMBER(H305),0,IF(AND(ISNUMBER(F305),ISNUMBER(E305),E305&gt;0,F305&gt;E305),(F305-E305)/E305,IF(AND(ISNUMBER(F305),ISNUMBER(E305),E305&gt;0,F305=E305),0,IF(AND(ISNUMBER(F305),ISNUMBER(E305),E305&gt;0,F305=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K305" s="50" t="str">
+        <x:f>IF(A305="","",IF(AND(ISNUMBER(E305),E305=0,OR(ISNUMBER(SEARCH("Free",D305&amp;"")),AND(ISNUMBER(F305),F305=0))),"Subscription",IF(ISNUMBER(G305),"Profit",IF(ISNUMBER(I305),"Loss",IF(ISNUMBER(H305),"Draw",IF(AND(ISNUMBER(F305),ISNUMBER(E305),E305&gt;0,F305&gt;E305),"Profit",IF(AND(ISNUMBER(F305),ISNUMBER(E305),E305&gt;0,F305=E305),"Draw",IF(AND(ISNUMBER(F305),ISNUMBER(E305),E305&gt;0,F305=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L305" s="50"/>
       <x:c r="M305" s="58"/>
       <x:c r="N305" s="58"/>
@@ -11472,8 +12676,12 @@
       <x:c r="G306" s="58"/>
       <x:c r="H306" s="58"/>
       <x:c r="I306" s="58"/>
-      <x:c r="J306" s="60"/>
-      <x:c r="K306" s="50"/>
+      <x:c r="J306" s="60" t="str">
+        <x:f>IF(A306="","",IF(K306="Subscription","",IF(E306=0,"",IF(ISNUMBER(G306),G306/E306,IF(ISNUMBER(I306),-ABS(I306)/E306,IF(ISNUMBER(H306),0,IF(AND(ISNUMBER(F306),ISNUMBER(E306),E306&gt;0,F306&gt;E306),(F306-E306)/E306,IF(AND(ISNUMBER(F306),ISNUMBER(E306),E306&gt;0,F306=E306),0,IF(AND(ISNUMBER(F306),ISNUMBER(E306),E306&gt;0,F306=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K306" s="50" t="str">
+        <x:f>IF(A306="","",IF(AND(ISNUMBER(E306),E306=0,OR(ISNUMBER(SEARCH("Free",D306&amp;"")),AND(ISNUMBER(F306),F306=0))),"Subscription",IF(ISNUMBER(G306),"Profit",IF(ISNUMBER(I306),"Loss",IF(ISNUMBER(H306),"Draw",IF(AND(ISNUMBER(F306),ISNUMBER(E306),E306&gt;0,F306&gt;E306),"Profit",IF(AND(ISNUMBER(F306),ISNUMBER(E306),E306&gt;0,F306=E306),"Draw",IF(AND(ISNUMBER(F306),ISNUMBER(E306),E306&gt;0,F306=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L306" s="50"/>
       <x:c r="M306" s="58"/>
       <x:c r="N306" s="58"/>
@@ -11505,8 +12713,12 @@
       <x:c r="G307" s="58"/>
       <x:c r="H307" s="58"/>
       <x:c r="I307" s="58"/>
-      <x:c r="J307" s="60"/>
-      <x:c r="K307" s="50"/>
+      <x:c r="J307" s="60" t="str">
+        <x:f>IF(A307="","",IF(K307="Subscription","",IF(E307=0,"",IF(ISNUMBER(G307),G307/E307,IF(ISNUMBER(I307),-ABS(I307)/E307,IF(ISNUMBER(H307),0,IF(AND(ISNUMBER(F307),ISNUMBER(E307),E307&gt;0,F307&gt;E307),(F307-E307)/E307,IF(AND(ISNUMBER(F307),ISNUMBER(E307),E307&gt;0,F307=E307),0,IF(AND(ISNUMBER(F307),ISNUMBER(E307),E307&gt;0,F307=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K307" s="50" t="str">
+        <x:f>IF(A307="","",IF(AND(ISNUMBER(E307),E307=0,OR(ISNUMBER(SEARCH("Free",D307&amp;"")),AND(ISNUMBER(F307),F307=0))),"Subscription",IF(ISNUMBER(G307),"Profit",IF(ISNUMBER(I307),"Loss",IF(ISNUMBER(H307),"Draw",IF(AND(ISNUMBER(F307),ISNUMBER(E307),E307&gt;0,F307&gt;E307),"Profit",IF(AND(ISNUMBER(F307),ISNUMBER(E307),E307&gt;0,F307=E307),"Draw",IF(AND(ISNUMBER(F307),ISNUMBER(E307),E307&gt;0,F307=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L307" s="50"/>
       <x:c r="M307" s="58"/>
       <x:c r="N307" s="58"/>
@@ -11538,8 +12750,12 @@
       <x:c r="G308" s="58"/>
       <x:c r="H308" s="58"/>
       <x:c r="I308" s="58"/>
-      <x:c r="J308" s="60"/>
-      <x:c r="K308" s="50"/>
+      <x:c r="J308" s="60" t="str">
+        <x:f>IF(A308="","",IF(K308="Subscription","",IF(E308=0,"",IF(ISNUMBER(G308),G308/E308,IF(ISNUMBER(I308),-ABS(I308)/E308,IF(ISNUMBER(H308),0,IF(AND(ISNUMBER(F308),ISNUMBER(E308),E308&gt;0,F308&gt;E308),(F308-E308)/E308,IF(AND(ISNUMBER(F308),ISNUMBER(E308),E308&gt;0,F308=E308),0,IF(AND(ISNUMBER(F308),ISNUMBER(E308),E308&gt;0,F308=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K308" s="50" t="str">
+        <x:f>IF(A308="","",IF(AND(ISNUMBER(E308),E308=0,OR(ISNUMBER(SEARCH("Free",D308&amp;"")),AND(ISNUMBER(F308),F308=0))),"Subscription",IF(ISNUMBER(G308),"Profit",IF(ISNUMBER(I308),"Loss",IF(ISNUMBER(H308),"Draw",IF(AND(ISNUMBER(F308),ISNUMBER(E308),E308&gt;0,F308&gt;E308),"Profit",IF(AND(ISNUMBER(F308),ISNUMBER(E308),E308&gt;0,F308=E308),"Draw",IF(AND(ISNUMBER(F308),ISNUMBER(E308),E308&gt;0,F308=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L308" s="50"/>
       <x:c r="M308" s="58"/>
       <x:c r="N308" s="58"/>
@@ -11571,8 +12787,12 @@
       <x:c r="G309" s="58"/>
       <x:c r="H309" s="58"/>
       <x:c r="I309" s="58"/>
-      <x:c r="J309" s="60"/>
-      <x:c r="K309" s="50"/>
+      <x:c r="J309" s="60" t="str">
+        <x:f>IF(A309="","",IF(K309="Subscription","",IF(E309=0,"",IF(ISNUMBER(G309),G309/E309,IF(ISNUMBER(I309),-ABS(I309)/E309,IF(ISNUMBER(H309),0,IF(AND(ISNUMBER(F309),ISNUMBER(E309),E309&gt;0,F309&gt;E309),(F309-E309)/E309,IF(AND(ISNUMBER(F309),ISNUMBER(E309),E309&gt;0,F309=E309),0,IF(AND(ISNUMBER(F309),ISNUMBER(E309),E309&gt;0,F309=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K309" s="50" t="str">
+        <x:f>IF(A309="","",IF(AND(ISNUMBER(E309),E309=0,OR(ISNUMBER(SEARCH("Free",D309&amp;"")),AND(ISNUMBER(F309),F309=0))),"Subscription",IF(ISNUMBER(G309),"Profit",IF(ISNUMBER(I309),"Loss",IF(ISNUMBER(H309),"Draw",IF(AND(ISNUMBER(F309),ISNUMBER(E309),E309&gt;0,F309&gt;E309),"Profit",IF(AND(ISNUMBER(F309),ISNUMBER(E309),E309&gt;0,F309=E309),"Draw",IF(AND(ISNUMBER(F309),ISNUMBER(E309),E309&gt;0,F309=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L309" s="50"/>
       <x:c r="M309" s="58"/>
       <x:c r="N309" s="58"/>
@@ -11604,8 +12824,12 @@
       <x:c r="G310" s="58"/>
       <x:c r="H310" s="58"/>
       <x:c r="I310" s="58"/>
-      <x:c r="J310" s="60"/>
-      <x:c r="K310" s="50"/>
+      <x:c r="J310" s="60" t="str">
+        <x:f>IF(A310="","",IF(K310="Subscription","",IF(E310=0,"",IF(ISNUMBER(G310),G310/E310,IF(ISNUMBER(I310),-ABS(I310)/E310,IF(ISNUMBER(H310),0,IF(AND(ISNUMBER(F310),ISNUMBER(E310),E310&gt;0,F310&gt;E310),(F310-E310)/E310,IF(AND(ISNUMBER(F310),ISNUMBER(E310),E310&gt;0,F310=E310),0,IF(AND(ISNUMBER(F310),ISNUMBER(E310),E310&gt;0,F310=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K310" s="50" t="str">
+        <x:f>IF(A310="","",IF(AND(ISNUMBER(E310),E310=0,OR(ISNUMBER(SEARCH("Free",D310&amp;"")),AND(ISNUMBER(F310),F310=0))),"Subscription",IF(ISNUMBER(G310),"Profit",IF(ISNUMBER(I310),"Loss",IF(ISNUMBER(H310),"Draw",IF(AND(ISNUMBER(F310),ISNUMBER(E310),E310&gt;0,F310&gt;E310),"Profit",IF(AND(ISNUMBER(F310),ISNUMBER(E310),E310&gt;0,F310=E310),"Draw",IF(AND(ISNUMBER(F310),ISNUMBER(E310),E310&gt;0,F310=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L310" s="50"/>
       <x:c r="M310" s="58"/>
       <x:c r="N310" s="58"/>
@@ -11637,8 +12861,12 @@
       <x:c r="G311" s="58"/>
       <x:c r="H311" s="58"/>
       <x:c r="I311" s="58"/>
-      <x:c r="J311" s="60"/>
-      <x:c r="K311" s="50"/>
+      <x:c r="J311" s="60" t="str">
+        <x:f>IF(A311="","",IF(K311="Subscription","",IF(E311=0,"",IF(ISNUMBER(G311),G311/E311,IF(ISNUMBER(I311),-ABS(I311)/E311,IF(ISNUMBER(H311),0,IF(AND(ISNUMBER(F311),ISNUMBER(E311),E311&gt;0,F311&gt;E311),(F311-E311)/E311,IF(AND(ISNUMBER(F311),ISNUMBER(E311),E311&gt;0,F311=E311),0,IF(AND(ISNUMBER(F311),ISNUMBER(E311),E311&gt;0,F311=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K311" s="50" t="str">
+        <x:f>IF(A311="","",IF(AND(ISNUMBER(E311),E311=0,OR(ISNUMBER(SEARCH("Free",D311&amp;"")),AND(ISNUMBER(F311),F311=0))),"Subscription",IF(ISNUMBER(G311),"Profit",IF(ISNUMBER(I311),"Loss",IF(ISNUMBER(H311),"Draw",IF(AND(ISNUMBER(F311),ISNUMBER(E311),E311&gt;0,F311&gt;E311),"Profit",IF(AND(ISNUMBER(F311),ISNUMBER(E311),E311&gt;0,F311=E311),"Draw",IF(AND(ISNUMBER(F311),ISNUMBER(E311),E311&gt;0,F311=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L311" s="50"/>
       <x:c r="M311" s="58"/>
       <x:c r="N311" s="58"/>
@@ -11670,8 +12898,12 @@
       <x:c r="G312" s="58"/>
       <x:c r="H312" s="58"/>
       <x:c r="I312" s="58"/>
-      <x:c r="J312" s="60"/>
-      <x:c r="K312" s="50"/>
+      <x:c r="J312" s="60" t="str">
+        <x:f>IF(A312="","",IF(K312="Subscription","",IF(E312=0,"",IF(ISNUMBER(G312),G312/E312,IF(ISNUMBER(I312),-ABS(I312)/E312,IF(ISNUMBER(H312),0,IF(AND(ISNUMBER(F312),ISNUMBER(E312),E312&gt;0,F312&gt;E312),(F312-E312)/E312,IF(AND(ISNUMBER(F312),ISNUMBER(E312),E312&gt;0,F312=E312),0,IF(AND(ISNUMBER(F312),ISNUMBER(E312),E312&gt;0,F312=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K312" s="50" t="str">
+        <x:f>IF(A312="","",IF(AND(ISNUMBER(E312),E312=0,OR(ISNUMBER(SEARCH("Free",D312&amp;"")),AND(ISNUMBER(F312),F312=0))),"Subscription",IF(ISNUMBER(G312),"Profit",IF(ISNUMBER(I312),"Loss",IF(ISNUMBER(H312),"Draw",IF(AND(ISNUMBER(F312),ISNUMBER(E312),E312&gt;0,F312&gt;E312),"Profit",IF(AND(ISNUMBER(F312),ISNUMBER(E312),E312&gt;0,F312=E312),"Draw",IF(AND(ISNUMBER(F312),ISNUMBER(E312),E312&gt;0,F312=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L312" s="50"/>
       <x:c r="M312" s="58"/>
       <x:c r="N312" s="58"/>
@@ -11703,8 +12935,12 @@
       <x:c r="G313" s="58"/>
       <x:c r="H313" s="58"/>
       <x:c r="I313" s="58"/>
-      <x:c r="J313" s="60"/>
-      <x:c r="K313" s="50"/>
+      <x:c r="J313" s="60" t="str">
+        <x:f>IF(A313="","",IF(K313="Subscription","",IF(E313=0,"",IF(ISNUMBER(G313),G313/E313,IF(ISNUMBER(I313),-ABS(I313)/E313,IF(ISNUMBER(H313),0,IF(AND(ISNUMBER(F313),ISNUMBER(E313),E313&gt;0,F313&gt;E313),(F313-E313)/E313,IF(AND(ISNUMBER(F313),ISNUMBER(E313),E313&gt;0,F313=E313),0,IF(AND(ISNUMBER(F313),ISNUMBER(E313),E313&gt;0,F313=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K313" s="50" t="str">
+        <x:f>IF(A313="","",IF(AND(ISNUMBER(E313),E313=0,OR(ISNUMBER(SEARCH("Free",D313&amp;"")),AND(ISNUMBER(F313),F313=0))),"Subscription",IF(ISNUMBER(G313),"Profit",IF(ISNUMBER(I313),"Loss",IF(ISNUMBER(H313),"Draw",IF(AND(ISNUMBER(F313),ISNUMBER(E313),E313&gt;0,F313&gt;E313),"Profit",IF(AND(ISNUMBER(F313),ISNUMBER(E313),E313&gt;0,F313=E313),"Draw",IF(AND(ISNUMBER(F313),ISNUMBER(E313),E313&gt;0,F313=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L313" s="50"/>
       <x:c r="M313" s="58"/>
       <x:c r="N313" s="58"/>
@@ -11736,8 +12972,12 @@
       <x:c r="G314" s="58"/>
       <x:c r="H314" s="58"/>
       <x:c r="I314" s="58"/>
-      <x:c r="J314" s="60"/>
-      <x:c r="K314" s="50"/>
+      <x:c r="J314" s="60" t="str">
+        <x:f>IF(A314="","",IF(K314="Subscription","",IF(E314=0,"",IF(ISNUMBER(G314),G314/E314,IF(ISNUMBER(I314),-ABS(I314)/E314,IF(ISNUMBER(H314),0,IF(AND(ISNUMBER(F314),ISNUMBER(E314),E314&gt;0,F314&gt;E314),(F314-E314)/E314,IF(AND(ISNUMBER(F314),ISNUMBER(E314),E314&gt;0,F314=E314),0,IF(AND(ISNUMBER(F314),ISNUMBER(E314),E314&gt;0,F314=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K314" s="50" t="str">
+        <x:f>IF(A314="","",IF(AND(ISNUMBER(E314),E314=0,OR(ISNUMBER(SEARCH("Free",D314&amp;"")),AND(ISNUMBER(F314),F314=0))),"Subscription",IF(ISNUMBER(G314),"Profit",IF(ISNUMBER(I314),"Loss",IF(ISNUMBER(H314),"Draw",IF(AND(ISNUMBER(F314),ISNUMBER(E314),E314&gt;0,F314&gt;E314),"Profit",IF(AND(ISNUMBER(F314),ISNUMBER(E314),E314&gt;0,F314=E314),"Draw",IF(AND(ISNUMBER(F314),ISNUMBER(E314),E314&gt;0,F314=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L314" s="50"/>
       <x:c r="M314" s="58"/>
       <x:c r="N314" s="58"/>
@@ -11769,8 +13009,12 @@
       <x:c r="G315" s="58"/>
       <x:c r="H315" s="58"/>
       <x:c r="I315" s="58"/>
-      <x:c r="J315" s="60"/>
-      <x:c r="K315" s="50"/>
+      <x:c r="J315" s="60" t="str">
+        <x:f>IF(A315="","",IF(K315="Subscription","",IF(E315=0,"",IF(ISNUMBER(G315),G315/E315,IF(ISNUMBER(I315),-ABS(I315)/E315,IF(ISNUMBER(H315),0,IF(AND(ISNUMBER(F315),ISNUMBER(E315),E315&gt;0,F315&gt;E315),(F315-E315)/E315,IF(AND(ISNUMBER(F315),ISNUMBER(E315),E315&gt;0,F315=E315),0,IF(AND(ISNUMBER(F315),ISNUMBER(E315),E315&gt;0,F315=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K315" s="50" t="str">
+        <x:f>IF(A315="","",IF(AND(ISNUMBER(E315),E315=0,OR(ISNUMBER(SEARCH("Free",D315&amp;"")),AND(ISNUMBER(F315),F315=0))),"Subscription",IF(ISNUMBER(G315),"Profit",IF(ISNUMBER(I315),"Loss",IF(ISNUMBER(H315),"Draw",IF(AND(ISNUMBER(F315),ISNUMBER(E315),E315&gt;0,F315&gt;E315),"Profit",IF(AND(ISNUMBER(F315),ISNUMBER(E315),E315&gt;0,F315=E315),"Draw",IF(AND(ISNUMBER(F315),ISNUMBER(E315),E315&gt;0,F315=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L315" s="50"/>
       <x:c r="M315" s="58"/>
       <x:c r="N315" s="58"/>
@@ -11802,8 +13046,12 @@
       <x:c r="G316" s="58"/>
       <x:c r="H316" s="58"/>
       <x:c r="I316" s="58"/>
-      <x:c r="J316" s="60"/>
-      <x:c r="K316" s="50"/>
+      <x:c r="J316" s="60" t="str">
+        <x:f>IF(A316="","",IF(K316="Subscription","",IF(E316=0,"",IF(ISNUMBER(G316),G316/E316,IF(ISNUMBER(I316),-ABS(I316)/E316,IF(ISNUMBER(H316),0,IF(AND(ISNUMBER(F316),ISNUMBER(E316),E316&gt;0,F316&gt;E316),(F316-E316)/E316,IF(AND(ISNUMBER(F316),ISNUMBER(E316),E316&gt;0,F316=E316),0,IF(AND(ISNUMBER(F316),ISNUMBER(E316),E316&gt;0,F316=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K316" s="50" t="str">
+        <x:f>IF(A316="","",IF(AND(ISNUMBER(E316),E316=0,OR(ISNUMBER(SEARCH("Free",D316&amp;"")),AND(ISNUMBER(F316),F316=0))),"Subscription",IF(ISNUMBER(G316),"Profit",IF(ISNUMBER(I316),"Loss",IF(ISNUMBER(H316),"Draw",IF(AND(ISNUMBER(F316),ISNUMBER(E316),E316&gt;0,F316&gt;E316),"Profit",IF(AND(ISNUMBER(F316),ISNUMBER(E316),E316&gt;0,F316=E316),"Draw",IF(AND(ISNUMBER(F316),ISNUMBER(E316),E316&gt;0,F316=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L316" s="50"/>
       <x:c r="M316" s="58"/>
       <x:c r="N316" s="58"/>
@@ -11835,8 +13083,12 @@
       <x:c r="G317" s="58"/>
       <x:c r="H317" s="58"/>
       <x:c r="I317" s="58"/>
-      <x:c r="J317" s="60"/>
-      <x:c r="K317" s="50"/>
+      <x:c r="J317" s="60" t="str">
+        <x:f>IF(A317="","",IF(K317="Subscription","",IF(E317=0,"",IF(ISNUMBER(G317),G317/E317,IF(ISNUMBER(I317),-ABS(I317)/E317,IF(ISNUMBER(H317),0,IF(AND(ISNUMBER(F317),ISNUMBER(E317),E317&gt;0,F317&gt;E317),(F317-E317)/E317,IF(AND(ISNUMBER(F317),ISNUMBER(E317),E317&gt;0,F317=E317),0,IF(AND(ISNUMBER(F317),ISNUMBER(E317),E317&gt;0,F317=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K317" s="50" t="str">
+        <x:f>IF(A317="","",IF(AND(ISNUMBER(E317),E317=0,OR(ISNUMBER(SEARCH("Free",D317&amp;"")),AND(ISNUMBER(F317),F317=0))),"Subscription",IF(ISNUMBER(G317),"Profit",IF(ISNUMBER(I317),"Loss",IF(ISNUMBER(H317),"Draw",IF(AND(ISNUMBER(F317),ISNUMBER(E317),E317&gt;0,F317&gt;E317),"Profit",IF(AND(ISNUMBER(F317),ISNUMBER(E317),E317&gt;0,F317=E317),"Draw",IF(AND(ISNUMBER(F317),ISNUMBER(E317),E317&gt;0,F317=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L317" s="50"/>
       <x:c r="M317" s="58"/>
       <x:c r="N317" s="58"/>
@@ -11868,8 +13120,12 @@
       <x:c r="G318" s="58"/>
       <x:c r="H318" s="58"/>
       <x:c r="I318" s="58"/>
-      <x:c r="J318" s="60"/>
-      <x:c r="K318" s="50"/>
+      <x:c r="J318" s="60" t="str">
+        <x:f>IF(A318="","",IF(K318="Subscription","",IF(E318=0,"",IF(ISNUMBER(G318),G318/E318,IF(ISNUMBER(I318),-ABS(I318)/E318,IF(ISNUMBER(H318),0,IF(AND(ISNUMBER(F318),ISNUMBER(E318),E318&gt;0,F318&gt;E318),(F318-E318)/E318,IF(AND(ISNUMBER(F318),ISNUMBER(E318),E318&gt;0,F318=E318),0,IF(AND(ISNUMBER(F318),ISNUMBER(E318),E318&gt;0,F318=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K318" s="50" t="str">
+        <x:f>IF(A318="","",IF(AND(ISNUMBER(E318),E318=0,OR(ISNUMBER(SEARCH("Free",D318&amp;"")),AND(ISNUMBER(F318),F318=0))),"Subscription",IF(ISNUMBER(G318),"Profit",IF(ISNUMBER(I318),"Loss",IF(ISNUMBER(H318),"Draw",IF(AND(ISNUMBER(F318),ISNUMBER(E318),E318&gt;0,F318&gt;E318),"Profit",IF(AND(ISNUMBER(F318),ISNUMBER(E318),E318&gt;0,F318=E318),"Draw",IF(AND(ISNUMBER(F318),ISNUMBER(E318),E318&gt;0,F318=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L318" s="50"/>
       <x:c r="M318" s="58"/>
       <x:c r="N318" s="58"/>
@@ -11901,8 +13157,12 @@
       <x:c r="G319" s="58"/>
       <x:c r="H319" s="58"/>
       <x:c r="I319" s="58"/>
-      <x:c r="J319" s="60"/>
-      <x:c r="K319" s="50"/>
+      <x:c r="J319" s="60" t="str">
+        <x:f>IF(A319="","",IF(K319="Subscription","",IF(E319=0,"",IF(ISNUMBER(G319),G319/E319,IF(ISNUMBER(I319),-ABS(I319)/E319,IF(ISNUMBER(H319),0,IF(AND(ISNUMBER(F319),ISNUMBER(E319),E319&gt;0,F319&gt;E319),(F319-E319)/E319,IF(AND(ISNUMBER(F319),ISNUMBER(E319),E319&gt;0,F319=E319),0,IF(AND(ISNUMBER(F319),ISNUMBER(E319),E319&gt;0,F319=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K319" s="50" t="str">
+        <x:f>IF(A319="","",IF(AND(ISNUMBER(E319),E319=0,OR(ISNUMBER(SEARCH("Free",D319&amp;"")),AND(ISNUMBER(F319),F319=0))),"Subscription",IF(ISNUMBER(G319),"Profit",IF(ISNUMBER(I319),"Loss",IF(ISNUMBER(H319),"Draw",IF(AND(ISNUMBER(F319),ISNUMBER(E319),E319&gt;0,F319&gt;E319),"Profit",IF(AND(ISNUMBER(F319),ISNUMBER(E319),E319&gt;0,F319=E319),"Draw",IF(AND(ISNUMBER(F319),ISNUMBER(E319),E319&gt;0,F319=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L319" s="50"/>
       <x:c r="M319" s="58"/>
       <x:c r="N319" s="58"/>
@@ -11934,8 +13194,12 @@
       <x:c r="G320" s="58"/>
       <x:c r="H320" s="58"/>
       <x:c r="I320" s="58"/>
-      <x:c r="J320" s="60"/>
-      <x:c r="K320" s="50"/>
+      <x:c r="J320" s="60" t="str">
+        <x:f>IF(A320="","",IF(K320="Subscription","",IF(E320=0,"",IF(ISNUMBER(G320),G320/E320,IF(ISNUMBER(I320),-ABS(I320)/E320,IF(ISNUMBER(H320),0,IF(AND(ISNUMBER(F320),ISNUMBER(E320),E320&gt;0,F320&gt;E320),(F320-E320)/E320,IF(AND(ISNUMBER(F320),ISNUMBER(E320),E320&gt;0,F320=E320),0,IF(AND(ISNUMBER(F320),ISNUMBER(E320),E320&gt;0,F320=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K320" s="50" t="str">
+        <x:f>IF(A320="","",IF(AND(ISNUMBER(E320),E320=0,OR(ISNUMBER(SEARCH("Free",D320&amp;"")),AND(ISNUMBER(F320),F320=0))),"Subscription",IF(ISNUMBER(G320),"Profit",IF(ISNUMBER(I320),"Loss",IF(ISNUMBER(H320),"Draw",IF(AND(ISNUMBER(F320),ISNUMBER(E320),E320&gt;0,F320&gt;E320),"Profit",IF(AND(ISNUMBER(F320),ISNUMBER(E320),E320&gt;0,F320=E320),"Draw",IF(AND(ISNUMBER(F320),ISNUMBER(E320),E320&gt;0,F320=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L320" s="50"/>
       <x:c r="M320" s="58"/>
       <x:c r="N320" s="58"/>
@@ -11967,8 +13231,12 @@
       <x:c r="G321" s="58"/>
       <x:c r="H321" s="58"/>
       <x:c r="I321" s="58"/>
-      <x:c r="J321" s="60"/>
-      <x:c r="K321" s="50"/>
+      <x:c r="J321" s="60" t="str">
+        <x:f>IF(A321="","",IF(K321="Subscription","",IF(E321=0,"",IF(ISNUMBER(G321),G321/E321,IF(ISNUMBER(I321),-ABS(I321)/E321,IF(ISNUMBER(H321),0,IF(AND(ISNUMBER(F321),ISNUMBER(E321),E321&gt;0,F321&gt;E321),(F321-E321)/E321,IF(AND(ISNUMBER(F321),ISNUMBER(E321),E321&gt;0,F321=E321),0,IF(AND(ISNUMBER(F321),ISNUMBER(E321),E321&gt;0,F321=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K321" s="50" t="str">
+        <x:f>IF(A321="","",IF(AND(ISNUMBER(E321),E321=0,OR(ISNUMBER(SEARCH("Free",D321&amp;"")),AND(ISNUMBER(F321),F321=0))),"Subscription",IF(ISNUMBER(G321),"Profit",IF(ISNUMBER(I321),"Loss",IF(ISNUMBER(H321),"Draw",IF(AND(ISNUMBER(F321),ISNUMBER(E321),E321&gt;0,F321&gt;E321),"Profit",IF(AND(ISNUMBER(F321),ISNUMBER(E321),E321&gt;0,F321=E321),"Draw",IF(AND(ISNUMBER(F321),ISNUMBER(E321),E321&gt;0,F321=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L321" s="50"/>
       <x:c r="M321" s="58"/>
       <x:c r="N321" s="58"/>
@@ -12000,8 +13268,12 @@
       <x:c r="G322" s="58"/>
       <x:c r="H322" s="58"/>
       <x:c r="I322" s="58"/>
-      <x:c r="J322" s="60"/>
-      <x:c r="K322" s="50"/>
+      <x:c r="J322" s="60" t="str">
+        <x:f>IF(A322="","",IF(K322="Subscription","",IF(E322=0,"",IF(ISNUMBER(G322),G322/E322,IF(ISNUMBER(I322),-ABS(I322)/E322,IF(ISNUMBER(H322),0,IF(AND(ISNUMBER(F322),ISNUMBER(E322),E322&gt;0,F322&gt;E322),(F322-E322)/E322,IF(AND(ISNUMBER(F322),ISNUMBER(E322),E322&gt;0,F322=E322),0,IF(AND(ISNUMBER(F322),ISNUMBER(E322),E322&gt;0,F322=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K322" s="50" t="str">
+        <x:f>IF(A322="","",IF(AND(ISNUMBER(E322),E322=0,OR(ISNUMBER(SEARCH("Free",D322&amp;"")),AND(ISNUMBER(F322),F322=0))),"Subscription",IF(ISNUMBER(G322),"Profit",IF(ISNUMBER(I322),"Loss",IF(ISNUMBER(H322),"Draw",IF(AND(ISNUMBER(F322),ISNUMBER(E322),E322&gt;0,F322&gt;E322),"Profit",IF(AND(ISNUMBER(F322),ISNUMBER(E322),E322&gt;0,F322=E322),"Draw",IF(AND(ISNUMBER(F322),ISNUMBER(E322),E322&gt;0,F322=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L322" s="50"/>
       <x:c r="M322" s="58"/>
       <x:c r="N322" s="58"/>
@@ -12033,8 +13305,12 @@
       <x:c r="G323" s="58"/>
       <x:c r="H323" s="58"/>
       <x:c r="I323" s="58"/>
-      <x:c r="J323" s="60"/>
-      <x:c r="K323" s="50"/>
+      <x:c r="J323" s="60" t="str">
+        <x:f>IF(A323="","",IF(K323="Subscription","",IF(E323=0,"",IF(ISNUMBER(G323),G323/E323,IF(ISNUMBER(I323),-ABS(I323)/E323,IF(ISNUMBER(H323),0,IF(AND(ISNUMBER(F323),ISNUMBER(E323),E323&gt;0,F323&gt;E323),(F323-E323)/E323,IF(AND(ISNUMBER(F323),ISNUMBER(E323),E323&gt;0,F323=E323),0,IF(AND(ISNUMBER(F323),ISNUMBER(E323),E323&gt;0,F323=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K323" s="50" t="str">
+        <x:f>IF(A323="","",IF(AND(ISNUMBER(E323),E323=0,OR(ISNUMBER(SEARCH("Free",D323&amp;"")),AND(ISNUMBER(F323),F323=0))),"Subscription",IF(ISNUMBER(G323),"Profit",IF(ISNUMBER(I323),"Loss",IF(ISNUMBER(H323),"Draw",IF(AND(ISNUMBER(F323),ISNUMBER(E323),E323&gt;0,F323&gt;E323),"Profit",IF(AND(ISNUMBER(F323),ISNUMBER(E323),E323&gt;0,F323=E323),"Draw",IF(AND(ISNUMBER(F323),ISNUMBER(E323),E323&gt;0,F323=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L323" s="50"/>
       <x:c r="M323" s="58"/>
       <x:c r="N323" s="58"/>
@@ -12066,8 +13342,12 @@
       <x:c r="G324" s="58"/>
       <x:c r="H324" s="58"/>
       <x:c r="I324" s="58"/>
-      <x:c r="J324" s="60"/>
-      <x:c r="K324" s="50"/>
+      <x:c r="J324" s="60" t="str">
+        <x:f>IF(A324="","",IF(K324="Subscription","",IF(E324=0,"",IF(ISNUMBER(G324),G324/E324,IF(ISNUMBER(I324),-ABS(I324)/E324,IF(ISNUMBER(H324),0,IF(AND(ISNUMBER(F324),ISNUMBER(E324),E324&gt;0,F324&gt;E324),(F324-E324)/E324,IF(AND(ISNUMBER(F324),ISNUMBER(E324),E324&gt;0,F324=E324),0,IF(AND(ISNUMBER(F324),ISNUMBER(E324),E324&gt;0,F324=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K324" s="50" t="str">
+        <x:f>IF(A324="","",IF(AND(ISNUMBER(E324),E324=0,OR(ISNUMBER(SEARCH("Free",D324&amp;"")),AND(ISNUMBER(F324),F324=0))),"Subscription",IF(ISNUMBER(G324),"Profit",IF(ISNUMBER(I324),"Loss",IF(ISNUMBER(H324),"Draw",IF(AND(ISNUMBER(F324),ISNUMBER(E324),E324&gt;0,F324&gt;E324),"Profit",IF(AND(ISNUMBER(F324),ISNUMBER(E324),E324&gt;0,F324=E324),"Draw",IF(AND(ISNUMBER(F324),ISNUMBER(E324),E324&gt;0,F324=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L324" s="50"/>
       <x:c r="M324" s="58"/>
       <x:c r="N324" s="58"/>
@@ -12099,8 +13379,12 @@
       <x:c r="G325" s="58"/>
       <x:c r="H325" s="58"/>
       <x:c r="I325" s="58"/>
-      <x:c r="J325" s="60"/>
-      <x:c r="K325" s="50"/>
+      <x:c r="J325" s="60" t="str">
+        <x:f>IF(A325="","",IF(K325="Subscription","",IF(E325=0,"",IF(ISNUMBER(G325),G325/E325,IF(ISNUMBER(I325),-ABS(I325)/E325,IF(ISNUMBER(H325),0,IF(AND(ISNUMBER(F325),ISNUMBER(E325),E325&gt;0,F325&gt;E325),(F325-E325)/E325,IF(AND(ISNUMBER(F325),ISNUMBER(E325),E325&gt;0,F325=E325),0,IF(AND(ISNUMBER(F325),ISNUMBER(E325),E325&gt;0,F325=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K325" s="50" t="str">
+        <x:f>IF(A325="","",IF(AND(ISNUMBER(E325),E325=0,OR(ISNUMBER(SEARCH("Free",D325&amp;"")),AND(ISNUMBER(F325),F325=0))),"Subscription",IF(ISNUMBER(G325),"Profit",IF(ISNUMBER(I325),"Loss",IF(ISNUMBER(H325),"Draw",IF(AND(ISNUMBER(F325),ISNUMBER(E325),E325&gt;0,F325&gt;E325),"Profit",IF(AND(ISNUMBER(F325),ISNUMBER(E325),E325&gt;0,F325=E325),"Draw",IF(AND(ISNUMBER(F325),ISNUMBER(E325),E325&gt;0,F325=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L325" s="50"/>
       <x:c r="M325" s="58"/>
       <x:c r="N325" s="58"/>
@@ -12132,8 +13416,12 @@
       <x:c r="G326" s="58"/>
       <x:c r="H326" s="58"/>
       <x:c r="I326" s="58"/>
-      <x:c r="J326" s="60"/>
-      <x:c r="K326" s="50"/>
+      <x:c r="J326" s="60" t="str">
+        <x:f>IF(A326="","",IF(K326="Subscription","",IF(E326=0,"",IF(ISNUMBER(G326),G326/E326,IF(ISNUMBER(I326),-ABS(I326)/E326,IF(ISNUMBER(H326),0,IF(AND(ISNUMBER(F326),ISNUMBER(E326),E326&gt;0,F326&gt;E326),(F326-E326)/E326,IF(AND(ISNUMBER(F326),ISNUMBER(E326),E326&gt;0,F326=E326),0,IF(AND(ISNUMBER(F326),ISNUMBER(E326),E326&gt;0,F326=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K326" s="50" t="str">
+        <x:f>IF(A326="","",IF(AND(ISNUMBER(E326),E326=0,OR(ISNUMBER(SEARCH("Free",D326&amp;"")),AND(ISNUMBER(F326),F326=0))),"Subscription",IF(ISNUMBER(G326),"Profit",IF(ISNUMBER(I326),"Loss",IF(ISNUMBER(H326),"Draw",IF(AND(ISNUMBER(F326),ISNUMBER(E326),E326&gt;0,F326&gt;E326),"Profit",IF(AND(ISNUMBER(F326),ISNUMBER(E326),E326&gt;0,F326=E326),"Draw",IF(AND(ISNUMBER(F326),ISNUMBER(E326),E326&gt;0,F326=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L326" s="50"/>
       <x:c r="M326" s="58"/>
       <x:c r="N326" s="58"/>
@@ -12165,8 +13453,12 @@
       <x:c r="G327" s="58"/>
       <x:c r="H327" s="58"/>
       <x:c r="I327" s="58"/>
-      <x:c r="J327" s="60"/>
-      <x:c r="K327" s="50"/>
+      <x:c r="J327" s="60" t="str">
+        <x:f>IF(A327="","",IF(K327="Subscription","",IF(E327=0,"",IF(ISNUMBER(G327),G327/E327,IF(ISNUMBER(I327),-ABS(I327)/E327,IF(ISNUMBER(H327),0,IF(AND(ISNUMBER(F327),ISNUMBER(E327),E327&gt;0,F327&gt;E327),(F327-E327)/E327,IF(AND(ISNUMBER(F327),ISNUMBER(E327),E327&gt;0,F327=E327),0,IF(AND(ISNUMBER(F327),ISNUMBER(E327),E327&gt;0,F327=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K327" s="50" t="str">
+        <x:f>IF(A327="","",IF(AND(ISNUMBER(E327),E327=0,OR(ISNUMBER(SEARCH("Free",D327&amp;"")),AND(ISNUMBER(F327),F327=0))),"Subscription",IF(ISNUMBER(G327),"Profit",IF(ISNUMBER(I327),"Loss",IF(ISNUMBER(H327),"Draw",IF(AND(ISNUMBER(F327),ISNUMBER(E327),E327&gt;0,F327&gt;E327),"Profit",IF(AND(ISNUMBER(F327),ISNUMBER(E327),E327&gt;0,F327=E327),"Draw",IF(AND(ISNUMBER(F327),ISNUMBER(E327),E327&gt;0,F327=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L327" s="50"/>
       <x:c r="M327" s="58"/>
       <x:c r="N327" s="58"/>
@@ -12198,8 +13490,12 @@
       <x:c r="G328" s="58"/>
       <x:c r="H328" s="58"/>
       <x:c r="I328" s="58"/>
-      <x:c r="J328" s="60"/>
-      <x:c r="K328" s="50"/>
+      <x:c r="J328" s="60" t="str">
+        <x:f>IF(A328="","",IF(K328="Subscription","",IF(E328=0,"",IF(ISNUMBER(G328),G328/E328,IF(ISNUMBER(I328),-ABS(I328)/E328,IF(ISNUMBER(H328),0,IF(AND(ISNUMBER(F328),ISNUMBER(E328),E328&gt;0,F328&gt;E328),(F328-E328)/E328,IF(AND(ISNUMBER(F328),ISNUMBER(E328),E328&gt;0,F328=E328),0,IF(AND(ISNUMBER(F328),ISNUMBER(E328),E328&gt;0,F328=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K328" s="50" t="str">
+        <x:f>IF(A328="","",IF(AND(ISNUMBER(E328),E328=0,OR(ISNUMBER(SEARCH("Free",D328&amp;"")),AND(ISNUMBER(F328),F328=0))),"Subscription",IF(ISNUMBER(G328),"Profit",IF(ISNUMBER(I328),"Loss",IF(ISNUMBER(H328),"Draw",IF(AND(ISNUMBER(F328),ISNUMBER(E328),E328&gt;0,F328&gt;E328),"Profit",IF(AND(ISNUMBER(F328),ISNUMBER(E328),E328&gt;0,F328=E328),"Draw",IF(AND(ISNUMBER(F328),ISNUMBER(E328),E328&gt;0,F328=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L328" s="50"/>
       <x:c r="M328" s="58"/>
       <x:c r="N328" s="58"/>
@@ -12231,8 +13527,12 @@
       <x:c r="G329" s="58"/>
       <x:c r="H329" s="58"/>
       <x:c r="I329" s="58"/>
-      <x:c r="J329" s="60"/>
-      <x:c r="K329" s="50"/>
+      <x:c r="J329" s="60" t="str">
+        <x:f>IF(A329="","",IF(K329="Subscription","",IF(E329=0,"",IF(ISNUMBER(G329),G329/E329,IF(ISNUMBER(I329),-ABS(I329)/E329,IF(ISNUMBER(H329),0,IF(AND(ISNUMBER(F329),ISNUMBER(E329),E329&gt;0,F329&gt;E329),(F329-E329)/E329,IF(AND(ISNUMBER(F329),ISNUMBER(E329),E329&gt;0,F329=E329),0,IF(AND(ISNUMBER(F329),ISNUMBER(E329),E329&gt;0,F329=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K329" s="50" t="str">
+        <x:f>IF(A329="","",IF(AND(ISNUMBER(E329),E329=0,OR(ISNUMBER(SEARCH("Free",D329&amp;"")),AND(ISNUMBER(F329),F329=0))),"Subscription",IF(ISNUMBER(G329),"Profit",IF(ISNUMBER(I329),"Loss",IF(ISNUMBER(H329),"Draw",IF(AND(ISNUMBER(F329),ISNUMBER(E329),E329&gt;0,F329&gt;E329),"Profit",IF(AND(ISNUMBER(F329),ISNUMBER(E329),E329&gt;0,F329=E329),"Draw",IF(AND(ISNUMBER(F329),ISNUMBER(E329),E329&gt;0,F329=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L329" s="50"/>
       <x:c r="M329" s="58"/>
       <x:c r="N329" s="58"/>
@@ -12264,8 +13564,12 @@
       <x:c r="G330" s="58"/>
       <x:c r="H330" s="58"/>
       <x:c r="I330" s="58"/>
-      <x:c r="J330" s="60"/>
-      <x:c r="K330" s="50"/>
+      <x:c r="J330" s="60" t="str">
+        <x:f>IF(A330="","",IF(K330="Subscription","",IF(E330=0,"",IF(ISNUMBER(G330),G330/E330,IF(ISNUMBER(I330),-ABS(I330)/E330,IF(ISNUMBER(H330),0,IF(AND(ISNUMBER(F330),ISNUMBER(E330),E330&gt;0,F330&gt;E330),(F330-E330)/E330,IF(AND(ISNUMBER(F330),ISNUMBER(E330),E330&gt;0,F330=E330),0,IF(AND(ISNUMBER(F330),ISNUMBER(E330),E330&gt;0,F330=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K330" s="50" t="str">
+        <x:f>IF(A330="","",IF(AND(ISNUMBER(E330),E330=0,OR(ISNUMBER(SEARCH("Free",D330&amp;"")),AND(ISNUMBER(F330),F330=0))),"Subscription",IF(ISNUMBER(G330),"Profit",IF(ISNUMBER(I330),"Loss",IF(ISNUMBER(H330),"Draw",IF(AND(ISNUMBER(F330),ISNUMBER(E330),E330&gt;0,F330&gt;E330),"Profit",IF(AND(ISNUMBER(F330),ISNUMBER(E330),E330&gt;0,F330=E330),"Draw",IF(AND(ISNUMBER(F330),ISNUMBER(E330),E330&gt;0,F330=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L330" s="50"/>
       <x:c r="M330" s="58"/>
       <x:c r="N330" s="58"/>
@@ -12297,8 +13601,12 @@
       <x:c r="G331" s="58"/>
       <x:c r="H331" s="58"/>
       <x:c r="I331" s="58"/>
-      <x:c r="J331" s="60"/>
-      <x:c r="K331" s="50"/>
+      <x:c r="J331" s="60" t="str">
+        <x:f>IF(A331="","",IF(K331="Subscription","",IF(E331=0,"",IF(ISNUMBER(G331),G331/E331,IF(ISNUMBER(I331),-ABS(I331)/E331,IF(ISNUMBER(H331),0,IF(AND(ISNUMBER(F331),ISNUMBER(E331),E331&gt;0,F331&gt;E331),(F331-E331)/E331,IF(AND(ISNUMBER(F331),ISNUMBER(E331),E331&gt;0,F331=E331),0,IF(AND(ISNUMBER(F331),ISNUMBER(E331),E331&gt;0,F331=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K331" s="50" t="str">
+        <x:f>IF(A331="","",IF(AND(ISNUMBER(E331),E331=0,OR(ISNUMBER(SEARCH("Free",D331&amp;"")),AND(ISNUMBER(F331),F331=0))),"Subscription",IF(ISNUMBER(G331),"Profit",IF(ISNUMBER(I331),"Loss",IF(ISNUMBER(H331),"Draw",IF(AND(ISNUMBER(F331),ISNUMBER(E331),E331&gt;0,F331&gt;E331),"Profit",IF(AND(ISNUMBER(F331),ISNUMBER(E331),E331&gt;0,F331=E331),"Draw",IF(AND(ISNUMBER(F331),ISNUMBER(E331),E331&gt;0,F331=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L331" s="50"/>
       <x:c r="M331" s="58"/>
       <x:c r="N331" s="58"/>
@@ -12330,8 +13638,12 @@
       <x:c r="G332" s="58"/>
       <x:c r="H332" s="58"/>
       <x:c r="I332" s="58"/>
-      <x:c r="J332" s="60"/>
-      <x:c r="K332" s="50"/>
+      <x:c r="J332" s="60" t="str">
+        <x:f>IF(A332="","",IF(K332="Subscription","",IF(E332=0,"",IF(ISNUMBER(G332),G332/E332,IF(ISNUMBER(I332),-ABS(I332)/E332,IF(ISNUMBER(H332),0,IF(AND(ISNUMBER(F332),ISNUMBER(E332),E332&gt;0,F332&gt;E332),(F332-E332)/E332,IF(AND(ISNUMBER(F332),ISNUMBER(E332),E332&gt;0,F332=E332),0,IF(AND(ISNUMBER(F332),ISNUMBER(E332),E332&gt;0,F332=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K332" s="50" t="str">
+        <x:f>IF(A332="","",IF(AND(ISNUMBER(E332),E332=0,OR(ISNUMBER(SEARCH("Free",D332&amp;"")),AND(ISNUMBER(F332),F332=0))),"Subscription",IF(ISNUMBER(G332),"Profit",IF(ISNUMBER(I332),"Loss",IF(ISNUMBER(H332),"Draw",IF(AND(ISNUMBER(F332),ISNUMBER(E332),E332&gt;0,F332&gt;E332),"Profit",IF(AND(ISNUMBER(F332),ISNUMBER(E332),E332&gt;0,F332=E332),"Draw",IF(AND(ISNUMBER(F332),ISNUMBER(E332),E332&gt;0,F332=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L332" s="50"/>
       <x:c r="M332" s="58"/>
       <x:c r="N332" s="58"/>
@@ -12363,8 +13675,12 @@
       <x:c r="G333" s="58"/>
       <x:c r="H333" s="58"/>
       <x:c r="I333" s="58"/>
-      <x:c r="J333" s="60"/>
-      <x:c r="K333" s="50"/>
+      <x:c r="J333" s="60" t="str">
+        <x:f>IF(A333="","",IF(K333="Subscription","",IF(E333=0,"",IF(ISNUMBER(G333),G333/E333,IF(ISNUMBER(I333),-ABS(I333)/E333,IF(ISNUMBER(H333),0,IF(AND(ISNUMBER(F333),ISNUMBER(E333),E333&gt;0,F333&gt;E333),(F333-E333)/E333,IF(AND(ISNUMBER(F333),ISNUMBER(E333),E333&gt;0,F333=E333),0,IF(AND(ISNUMBER(F333),ISNUMBER(E333),E333&gt;0,F333=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K333" s="50" t="str">
+        <x:f>IF(A333="","",IF(AND(ISNUMBER(E333),E333=0,OR(ISNUMBER(SEARCH("Free",D333&amp;"")),AND(ISNUMBER(F333),F333=0))),"Subscription",IF(ISNUMBER(G333),"Profit",IF(ISNUMBER(I333),"Loss",IF(ISNUMBER(H333),"Draw",IF(AND(ISNUMBER(F333),ISNUMBER(E333),E333&gt;0,F333&gt;E333),"Profit",IF(AND(ISNUMBER(F333),ISNUMBER(E333),E333&gt;0,F333=E333),"Draw",IF(AND(ISNUMBER(F333),ISNUMBER(E333),E333&gt;0,F333=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L333" s="50"/>
       <x:c r="M333" s="58"/>
       <x:c r="N333" s="58"/>
@@ -12396,8 +13712,12 @@
       <x:c r="G334" s="58"/>
       <x:c r="H334" s="58"/>
       <x:c r="I334" s="58"/>
-      <x:c r="J334" s="60"/>
-      <x:c r="K334" s="50"/>
+      <x:c r="J334" s="60" t="str">
+        <x:f>IF(A334="","",IF(K334="Subscription","",IF(E334=0,"",IF(ISNUMBER(G334),G334/E334,IF(ISNUMBER(I334),-ABS(I334)/E334,IF(ISNUMBER(H334),0,IF(AND(ISNUMBER(F334),ISNUMBER(E334),E334&gt;0,F334&gt;E334),(F334-E334)/E334,IF(AND(ISNUMBER(F334),ISNUMBER(E334),E334&gt;0,F334=E334),0,IF(AND(ISNUMBER(F334),ISNUMBER(E334),E334&gt;0,F334=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K334" s="50" t="str">
+        <x:f>IF(A334="","",IF(AND(ISNUMBER(E334),E334=0,OR(ISNUMBER(SEARCH("Free",D334&amp;"")),AND(ISNUMBER(F334),F334=0))),"Subscription",IF(ISNUMBER(G334),"Profit",IF(ISNUMBER(I334),"Loss",IF(ISNUMBER(H334),"Draw",IF(AND(ISNUMBER(F334),ISNUMBER(E334),E334&gt;0,F334&gt;E334),"Profit",IF(AND(ISNUMBER(F334),ISNUMBER(E334),E334&gt;0,F334=E334),"Draw",IF(AND(ISNUMBER(F334),ISNUMBER(E334),E334&gt;0,F334=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L334" s="50"/>
       <x:c r="M334" s="58"/>
       <x:c r="N334" s="58"/>
@@ -12429,8 +13749,12 @@
       <x:c r="G335" s="58"/>
       <x:c r="H335" s="58"/>
       <x:c r="I335" s="58"/>
-      <x:c r="J335" s="60"/>
-      <x:c r="K335" s="50"/>
+      <x:c r="J335" s="60" t="str">
+        <x:f>IF(A335="","",IF(K335="Subscription","",IF(E335=0,"",IF(ISNUMBER(G335),G335/E335,IF(ISNUMBER(I335),-ABS(I335)/E335,IF(ISNUMBER(H335),0,IF(AND(ISNUMBER(F335),ISNUMBER(E335),E335&gt;0,F335&gt;E335),(F335-E335)/E335,IF(AND(ISNUMBER(F335),ISNUMBER(E335),E335&gt;0,F335=E335),0,IF(AND(ISNUMBER(F335),ISNUMBER(E335),E335&gt;0,F335=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K335" s="50" t="str">
+        <x:f>IF(A335="","",IF(AND(ISNUMBER(E335),E335=0,OR(ISNUMBER(SEARCH("Free",D335&amp;"")),AND(ISNUMBER(F335),F335=0))),"Subscription",IF(ISNUMBER(G335),"Profit",IF(ISNUMBER(I335),"Loss",IF(ISNUMBER(H335),"Draw",IF(AND(ISNUMBER(F335),ISNUMBER(E335),E335&gt;0,F335&gt;E335),"Profit",IF(AND(ISNUMBER(F335),ISNUMBER(E335),E335&gt;0,F335=E335),"Draw",IF(AND(ISNUMBER(F335),ISNUMBER(E335),E335&gt;0,F335=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L335" s="50"/>
       <x:c r="M335" s="58"/>
       <x:c r="N335" s="58"/>
@@ -12462,8 +13786,12 @@
       <x:c r="G336" s="58"/>
       <x:c r="H336" s="58"/>
       <x:c r="I336" s="58"/>
-      <x:c r="J336" s="60"/>
-      <x:c r="K336" s="50"/>
+      <x:c r="J336" s="60" t="str">
+        <x:f>IF(A336="","",IF(K336="Subscription","",IF(E336=0,"",IF(ISNUMBER(G336),G336/E336,IF(ISNUMBER(I336),-ABS(I336)/E336,IF(ISNUMBER(H336),0,IF(AND(ISNUMBER(F336),ISNUMBER(E336),E336&gt;0,F336&gt;E336),(F336-E336)/E336,IF(AND(ISNUMBER(F336),ISNUMBER(E336),E336&gt;0,F336=E336),0,IF(AND(ISNUMBER(F336),ISNUMBER(E336),E336&gt;0,F336=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K336" s="50" t="str">
+        <x:f>IF(A336="","",IF(AND(ISNUMBER(E336),E336=0,OR(ISNUMBER(SEARCH("Free",D336&amp;"")),AND(ISNUMBER(F336),F336=0))),"Subscription",IF(ISNUMBER(G336),"Profit",IF(ISNUMBER(I336),"Loss",IF(ISNUMBER(H336),"Draw",IF(AND(ISNUMBER(F336),ISNUMBER(E336),E336&gt;0,F336&gt;E336),"Profit",IF(AND(ISNUMBER(F336),ISNUMBER(E336),E336&gt;0,F336=E336),"Draw",IF(AND(ISNUMBER(F336),ISNUMBER(E336),E336&gt;0,F336=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L336" s="50"/>
       <x:c r="M336" s="58"/>
       <x:c r="N336" s="58"/>
@@ -12495,8 +13823,12 @@
       <x:c r="G337" s="58"/>
       <x:c r="H337" s="58"/>
       <x:c r="I337" s="58"/>
-      <x:c r="J337" s="60"/>
-      <x:c r="K337" s="50"/>
+      <x:c r="J337" s="60" t="str">
+        <x:f>IF(A337="","",IF(K337="Subscription","",IF(E337=0,"",IF(ISNUMBER(G337),G337/E337,IF(ISNUMBER(I337),-ABS(I337)/E337,IF(ISNUMBER(H337),0,IF(AND(ISNUMBER(F337),ISNUMBER(E337),E337&gt;0,F337&gt;E337),(F337-E337)/E337,IF(AND(ISNUMBER(F337),ISNUMBER(E337),E337&gt;0,F337=E337),0,IF(AND(ISNUMBER(F337),ISNUMBER(E337),E337&gt;0,F337=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K337" s="50" t="str">
+        <x:f>IF(A337="","",IF(AND(ISNUMBER(E337),E337=0,OR(ISNUMBER(SEARCH("Free",D337&amp;"")),AND(ISNUMBER(F337),F337=0))),"Subscription",IF(ISNUMBER(G337),"Profit",IF(ISNUMBER(I337),"Loss",IF(ISNUMBER(H337),"Draw",IF(AND(ISNUMBER(F337),ISNUMBER(E337),E337&gt;0,F337&gt;E337),"Profit",IF(AND(ISNUMBER(F337),ISNUMBER(E337),E337&gt;0,F337=E337),"Draw",IF(AND(ISNUMBER(F337),ISNUMBER(E337),E337&gt;0,F337=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L337" s="50"/>
       <x:c r="M337" s="58"/>
       <x:c r="N337" s="58"/>
@@ -12528,8 +13860,12 @@
       <x:c r="G338" s="58"/>
       <x:c r="H338" s="58"/>
       <x:c r="I338" s="58"/>
-      <x:c r="J338" s="60"/>
-      <x:c r="K338" s="50"/>
+      <x:c r="J338" s="60" t="str">
+        <x:f>IF(A338="","",IF(K338="Subscription","",IF(E338=0,"",IF(ISNUMBER(G338),G338/E338,IF(ISNUMBER(I338),-ABS(I338)/E338,IF(ISNUMBER(H338),0,IF(AND(ISNUMBER(F338),ISNUMBER(E338),E338&gt;0,F338&gt;E338),(F338-E338)/E338,IF(AND(ISNUMBER(F338),ISNUMBER(E338),E338&gt;0,F338=E338),0,IF(AND(ISNUMBER(F338),ISNUMBER(E338),E338&gt;0,F338=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K338" s="50" t="str">
+        <x:f>IF(A338="","",IF(AND(ISNUMBER(E338),E338=0,OR(ISNUMBER(SEARCH("Free",D338&amp;"")),AND(ISNUMBER(F338),F338=0))),"Subscription",IF(ISNUMBER(G338),"Profit",IF(ISNUMBER(I338),"Loss",IF(ISNUMBER(H338),"Draw",IF(AND(ISNUMBER(F338),ISNUMBER(E338),E338&gt;0,F338&gt;E338),"Profit",IF(AND(ISNUMBER(F338),ISNUMBER(E338),E338&gt;0,F338=E338),"Draw",IF(AND(ISNUMBER(F338),ISNUMBER(E338),E338&gt;0,F338=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L338" s="50"/>
       <x:c r="M338" s="58"/>
       <x:c r="N338" s="58"/>
@@ -12561,8 +13897,12 @@
       <x:c r="G339" s="58"/>
       <x:c r="H339" s="58"/>
       <x:c r="I339" s="58"/>
-      <x:c r="J339" s="60"/>
-      <x:c r="K339" s="50"/>
+      <x:c r="J339" s="60" t="str">
+        <x:f>IF(A339="","",IF(K339="Subscription","",IF(E339=0,"",IF(ISNUMBER(G339),G339/E339,IF(ISNUMBER(I339),-ABS(I339)/E339,IF(ISNUMBER(H339),0,IF(AND(ISNUMBER(F339),ISNUMBER(E339),E339&gt;0,F339&gt;E339),(F339-E339)/E339,IF(AND(ISNUMBER(F339),ISNUMBER(E339),E339&gt;0,F339=E339),0,IF(AND(ISNUMBER(F339),ISNUMBER(E339),E339&gt;0,F339=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K339" s="50" t="str">
+        <x:f>IF(A339="","",IF(AND(ISNUMBER(E339),E339=0,OR(ISNUMBER(SEARCH("Free",D339&amp;"")),AND(ISNUMBER(F339),F339=0))),"Subscription",IF(ISNUMBER(G339),"Profit",IF(ISNUMBER(I339),"Loss",IF(ISNUMBER(H339),"Draw",IF(AND(ISNUMBER(F339),ISNUMBER(E339),E339&gt;0,F339&gt;E339),"Profit",IF(AND(ISNUMBER(F339),ISNUMBER(E339),E339&gt;0,F339=E339),"Draw",IF(AND(ISNUMBER(F339),ISNUMBER(E339),E339&gt;0,F339=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L339" s="50"/>
       <x:c r="M339" s="58"/>
       <x:c r="N339" s="58"/>
@@ -12594,8 +13934,12 @@
       <x:c r="G340" s="58"/>
       <x:c r="H340" s="58"/>
       <x:c r="I340" s="58"/>
-      <x:c r="J340" s="60"/>
-      <x:c r="K340" s="50"/>
+      <x:c r="J340" s="60" t="str">
+        <x:f>IF(A340="","",IF(K340="Subscription","",IF(E340=0,"",IF(ISNUMBER(G340),G340/E340,IF(ISNUMBER(I340),-ABS(I340)/E340,IF(ISNUMBER(H340),0,IF(AND(ISNUMBER(F340),ISNUMBER(E340),E340&gt;0,F340&gt;E340),(F340-E340)/E340,IF(AND(ISNUMBER(F340),ISNUMBER(E340),E340&gt;0,F340=E340),0,IF(AND(ISNUMBER(F340),ISNUMBER(E340),E340&gt;0,F340=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K340" s="50" t="str">
+        <x:f>IF(A340="","",IF(AND(ISNUMBER(E340),E340=0,OR(ISNUMBER(SEARCH("Free",D340&amp;"")),AND(ISNUMBER(F340),F340=0))),"Subscription",IF(ISNUMBER(G340),"Profit",IF(ISNUMBER(I340),"Loss",IF(ISNUMBER(H340),"Draw",IF(AND(ISNUMBER(F340),ISNUMBER(E340),E340&gt;0,F340&gt;E340),"Profit",IF(AND(ISNUMBER(F340),ISNUMBER(E340),E340&gt;0,F340=E340),"Draw",IF(AND(ISNUMBER(F340),ISNUMBER(E340),E340&gt;0,F340=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L340" s="50"/>
       <x:c r="M340" s="58"/>
       <x:c r="N340" s="58"/>
@@ -12627,8 +13971,12 @@
       <x:c r="G341" s="58"/>
       <x:c r="H341" s="58"/>
       <x:c r="I341" s="58"/>
-      <x:c r="J341" s="60"/>
-      <x:c r="K341" s="50"/>
+      <x:c r="J341" s="60" t="str">
+        <x:f>IF(A341="","",IF(K341="Subscription","",IF(E341=0,"",IF(ISNUMBER(G341),G341/E341,IF(ISNUMBER(I341),-ABS(I341)/E341,IF(ISNUMBER(H341),0,IF(AND(ISNUMBER(F341),ISNUMBER(E341),E341&gt;0,F341&gt;E341),(F341-E341)/E341,IF(AND(ISNUMBER(F341),ISNUMBER(E341),E341&gt;0,F341=E341),0,IF(AND(ISNUMBER(F341),ISNUMBER(E341),E341&gt;0,F341=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K341" s="50" t="str">
+        <x:f>IF(A341="","",IF(AND(ISNUMBER(E341),E341=0,OR(ISNUMBER(SEARCH("Free",D341&amp;"")),AND(ISNUMBER(F341),F341=0))),"Subscription",IF(ISNUMBER(G341),"Profit",IF(ISNUMBER(I341),"Loss",IF(ISNUMBER(H341),"Draw",IF(AND(ISNUMBER(F341),ISNUMBER(E341),E341&gt;0,F341&gt;E341),"Profit",IF(AND(ISNUMBER(F341),ISNUMBER(E341),E341&gt;0,F341=E341),"Draw",IF(AND(ISNUMBER(F341),ISNUMBER(E341),E341&gt;0,F341=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L341" s="50"/>
       <x:c r="M341" s="58"/>
       <x:c r="N341" s="58"/>
@@ -12660,8 +14008,12 @@
       <x:c r="G342" s="58"/>
       <x:c r="H342" s="58"/>
       <x:c r="I342" s="58"/>
-      <x:c r="J342" s="60"/>
-      <x:c r="K342" s="50"/>
+      <x:c r="J342" s="60" t="str">
+        <x:f>IF(A342="","",IF(K342="Subscription","",IF(E342=0,"",IF(ISNUMBER(G342),G342/E342,IF(ISNUMBER(I342),-ABS(I342)/E342,IF(ISNUMBER(H342),0,IF(AND(ISNUMBER(F342),ISNUMBER(E342),E342&gt;0,F342&gt;E342),(F342-E342)/E342,IF(AND(ISNUMBER(F342),ISNUMBER(E342),E342&gt;0,F342=E342),0,IF(AND(ISNUMBER(F342),ISNUMBER(E342),E342&gt;0,F342=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K342" s="50" t="str">
+        <x:f>IF(A342="","",IF(AND(ISNUMBER(E342),E342=0,OR(ISNUMBER(SEARCH("Free",D342&amp;"")),AND(ISNUMBER(F342),F342=0))),"Subscription",IF(ISNUMBER(G342),"Profit",IF(ISNUMBER(I342),"Loss",IF(ISNUMBER(H342),"Draw",IF(AND(ISNUMBER(F342),ISNUMBER(E342),E342&gt;0,F342&gt;E342),"Profit",IF(AND(ISNUMBER(F342),ISNUMBER(E342),E342&gt;0,F342=E342),"Draw",IF(AND(ISNUMBER(F342),ISNUMBER(E342),E342&gt;0,F342=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L342" s="50"/>
       <x:c r="M342" s="58"/>
       <x:c r="N342" s="58"/>
@@ -12693,8 +14045,12 @@
       <x:c r="G343" s="58"/>
       <x:c r="H343" s="58"/>
       <x:c r="I343" s="58"/>
-      <x:c r="J343" s="60"/>
-      <x:c r="K343" s="50"/>
+      <x:c r="J343" s="60" t="str">
+        <x:f>IF(A343="","",IF(K343="Subscription","",IF(E343=0,"",IF(ISNUMBER(G343),G343/E343,IF(ISNUMBER(I343),-ABS(I343)/E343,IF(ISNUMBER(H343),0,IF(AND(ISNUMBER(F343),ISNUMBER(E343),E343&gt;0,F343&gt;E343),(F343-E343)/E343,IF(AND(ISNUMBER(F343),ISNUMBER(E343),E343&gt;0,F343=E343),0,IF(AND(ISNUMBER(F343),ISNUMBER(E343),E343&gt;0,F343=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K343" s="50" t="str">
+        <x:f>IF(A343="","",IF(AND(ISNUMBER(E343),E343=0,OR(ISNUMBER(SEARCH("Free",D343&amp;"")),AND(ISNUMBER(F343),F343=0))),"Subscription",IF(ISNUMBER(G343),"Profit",IF(ISNUMBER(I343),"Loss",IF(ISNUMBER(H343),"Draw",IF(AND(ISNUMBER(F343),ISNUMBER(E343),E343&gt;0,F343&gt;E343),"Profit",IF(AND(ISNUMBER(F343),ISNUMBER(E343),E343&gt;0,F343=E343),"Draw",IF(AND(ISNUMBER(F343),ISNUMBER(E343),E343&gt;0,F343=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L343" s="50"/>
       <x:c r="M343" s="58"/>
       <x:c r="N343" s="58"/>
@@ -12726,8 +14082,12 @@
       <x:c r="G344" s="58"/>
       <x:c r="H344" s="58"/>
       <x:c r="I344" s="58"/>
-      <x:c r="J344" s="60"/>
-      <x:c r="K344" s="50"/>
+      <x:c r="J344" s="60" t="str">
+        <x:f>IF(A344="","",IF(K344="Subscription","",IF(E344=0,"",IF(ISNUMBER(G344),G344/E344,IF(ISNUMBER(I344),-ABS(I344)/E344,IF(ISNUMBER(H344),0,IF(AND(ISNUMBER(F344),ISNUMBER(E344),E344&gt;0,F344&gt;E344),(F344-E344)/E344,IF(AND(ISNUMBER(F344),ISNUMBER(E344),E344&gt;0,F344=E344),0,IF(AND(ISNUMBER(F344),ISNUMBER(E344),E344&gt;0,F344=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K344" s="50" t="str">
+        <x:f>IF(A344="","",IF(AND(ISNUMBER(E344),E344=0,OR(ISNUMBER(SEARCH("Free",D344&amp;"")),AND(ISNUMBER(F344),F344=0))),"Subscription",IF(ISNUMBER(G344),"Profit",IF(ISNUMBER(I344),"Loss",IF(ISNUMBER(H344),"Draw",IF(AND(ISNUMBER(F344),ISNUMBER(E344),E344&gt;0,F344&gt;E344),"Profit",IF(AND(ISNUMBER(F344),ISNUMBER(E344),E344&gt;0,F344=E344),"Draw",IF(AND(ISNUMBER(F344),ISNUMBER(E344),E344&gt;0,F344=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L344" s="50"/>
       <x:c r="M344" s="58"/>
       <x:c r="N344" s="58"/>
@@ -12759,8 +14119,12 @@
       <x:c r="G345" s="58"/>
       <x:c r="H345" s="58"/>
       <x:c r="I345" s="58"/>
-      <x:c r="J345" s="60"/>
-      <x:c r="K345" s="50"/>
+      <x:c r="J345" s="60" t="str">
+        <x:f>IF(A345="","",IF(K345="Subscription","",IF(E345=0,"",IF(ISNUMBER(G345),G345/E345,IF(ISNUMBER(I345),-ABS(I345)/E345,IF(ISNUMBER(H345),0,IF(AND(ISNUMBER(F345),ISNUMBER(E345),E345&gt;0,F345&gt;E345),(F345-E345)/E345,IF(AND(ISNUMBER(F345),ISNUMBER(E345),E345&gt;0,F345=E345),0,IF(AND(ISNUMBER(F345),ISNUMBER(E345),E345&gt;0,F345=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K345" s="50" t="str">
+        <x:f>IF(A345="","",IF(AND(ISNUMBER(E345),E345=0,OR(ISNUMBER(SEARCH("Free",D345&amp;"")),AND(ISNUMBER(F345),F345=0))),"Subscription",IF(ISNUMBER(G345),"Profit",IF(ISNUMBER(I345),"Loss",IF(ISNUMBER(H345),"Draw",IF(AND(ISNUMBER(F345),ISNUMBER(E345),E345&gt;0,F345&gt;E345),"Profit",IF(AND(ISNUMBER(F345),ISNUMBER(E345),E345&gt;0,F345=E345),"Draw",IF(AND(ISNUMBER(F345),ISNUMBER(E345),E345&gt;0,F345=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L345" s="50"/>
       <x:c r="M345" s="58"/>
       <x:c r="N345" s="58"/>
@@ -12792,8 +14156,12 @@
       <x:c r="G346" s="58"/>
       <x:c r="H346" s="58"/>
       <x:c r="I346" s="58"/>
-      <x:c r="J346" s="60"/>
-      <x:c r="K346" s="50"/>
+      <x:c r="J346" s="60" t="str">
+        <x:f>IF(A346="","",IF(K346="Subscription","",IF(E346=0,"",IF(ISNUMBER(G346),G346/E346,IF(ISNUMBER(I346),-ABS(I346)/E346,IF(ISNUMBER(H346),0,IF(AND(ISNUMBER(F346),ISNUMBER(E346),E346&gt;0,F346&gt;E346),(F346-E346)/E346,IF(AND(ISNUMBER(F346),ISNUMBER(E346),E346&gt;0,F346=E346),0,IF(AND(ISNUMBER(F346),ISNUMBER(E346),E346&gt;0,F346=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K346" s="50" t="str">
+        <x:f>IF(A346="","",IF(AND(ISNUMBER(E346),E346=0,OR(ISNUMBER(SEARCH("Free",D346&amp;"")),AND(ISNUMBER(F346),F346=0))),"Subscription",IF(ISNUMBER(G346),"Profit",IF(ISNUMBER(I346),"Loss",IF(ISNUMBER(H346),"Draw",IF(AND(ISNUMBER(F346),ISNUMBER(E346),E346&gt;0,F346&gt;E346),"Profit",IF(AND(ISNUMBER(F346),ISNUMBER(E346),E346&gt;0,F346=E346),"Draw",IF(AND(ISNUMBER(F346),ISNUMBER(E346),E346&gt;0,F346=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L346" s="50"/>
       <x:c r="M346" s="58"/>
       <x:c r="N346" s="58"/>
@@ -12825,8 +14193,12 @@
       <x:c r="G347" s="58"/>
       <x:c r="H347" s="58"/>
       <x:c r="I347" s="58"/>
-      <x:c r="J347" s="60"/>
-      <x:c r="K347" s="50"/>
+      <x:c r="J347" s="60" t="str">
+        <x:f>IF(A347="","",IF(K347="Subscription","",IF(E347=0,"",IF(ISNUMBER(G347),G347/E347,IF(ISNUMBER(I347),-ABS(I347)/E347,IF(ISNUMBER(H347),0,IF(AND(ISNUMBER(F347),ISNUMBER(E347),E347&gt;0,F347&gt;E347),(F347-E347)/E347,IF(AND(ISNUMBER(F347),ISNUMBER(E347),E347&gt;0,F347=E347),0,IF(AND(ISNUMBER(F347),ISNUMBER(E347),E347&gt;0,F347=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K347" s="50" t="str">
+        <x:f>IF(A347="","",IF(AND(ISNUMBER(E347),E347=0,OR(ISNUMBER(SEARCH("Free",D347&amp;"")),AND(ISNUMBER(F347),F347=0))),"Subscription",IF(ISNUMBER(G347),"Profit",IF(ISNUMBER(I347),"Loss",IF(ISNUMBER(H347),"Draw",IF(AND(ISNUMBER(F347),ISNUMBER(E347),E347&gt;0,F347&gt;E347),"Profit",IF(AND(ISNUMBER(F347),ISNUMBER(E347),E347&gt;0,F347=E347),"Draw",IF(AND(ISNUMBER(F347),ISNUMBER(E347),E347&gt;0,F347=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L347" s="50"/>
       <x:c r="M347" s="58"/>
       <x:c r="N347" s="58"/>
@@ -12858,8 +14230,12 @@
       <x:c r="G348" s="58"/>
       <x:c r="H348" s="58"/>
       <x:c r="I348" s="58"/>
-      <x:c r="J348" s="60"/>
-      <x:c r="K348" s="50"/>
+      <x:c r="J348" s="60" t="str">
+        <x:f>IF(A348="","",IF(K348="Subscription","",IF(E348=0,"",IF(ISNUMBER(G348),G348/E348,IF(ISNUMBER(I348),-ABS(I348)/E348,IF(ISNUMBER(H348),0,IF(AND(ISNUMBER(F348),ISNUMBER(E348),E348&gt;0,F348&gt;E348),(F348-E348)/E348,IF(AND(ISNUMBER(F348),ISNUMBER(E348),E348&gt;0,F348=E348),0,IF(AND(ISNUMBER(F348),ISNUMBER(E348),E348&gt;0,F348=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K348" s="50" t="str">
+        <x:f>IF(A348="","",IF(AND(ISNUMBER(E348),E348=0,OR(ISNUMBER(SEARCH("Free",D348&amp;"")),AND(ISNUMBER(F348),F348=0))),"Subscription",IF(ISNUMBER(G348),"Profit",IF(ISNUMBER(I348),"Loss",IF(ISNUMBER(H348),"Draw",IF(AND(ISNUMBER(F348),ISNUMBER(E348),E348&gt;0,F348&gt;E348),"Profit",IF(AND(ISNUMBER(F348),ISNUMBER(E348),E348&gt;0,F348=E348),"Draw",IF(AND(ISNUMBER(F348),ISNUMBER(E348),E348&gt;0,F348=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L348" s="50"/>
       <x:c r="M348" s="58"/>
       <x:c r="N348" s="58"/>
@@ -12891,8 +14267,12 @@
       <x:c r="G349" s="58"/>
       <x:c r="H349" s="58"/>
       <x:c r="I349" s="58"/>
-      <x:c r="J349" s="60"/>
-      <x:c r="K349" s="50"/>
+      <x:c r="J349" s="60" t="str">
+        <x:f>IF(A349="","",IF(K349="Subscription","",IF(E349=0,"",IF(ISNUMBER(G349),G349/E349,IF(ISNUMBER(I349),-ABS(I349)/E349,IF(ISNUMBER(H349),0,IF(AND(ISNUMBER(F349),ISNUMBER(E349),E349&gt;0,F349&gt;E349),(F349-E349)/E349,IF(AND(ISNUMBER(F349),ISNUMBER(E349),E349&gt;0,F349=E349),0,IF(AND(ISNUMBER(F349),ISNUMBER(E349),E349&gt;0,F349=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K349" s="50" t="str">
+        <x:f>IF(A349="","",IF(AND(ISNUMBER(E349),E349=0,OR(ISNUMBER(SEARCH("Free",D349&amp;"")),AND(ISNUMBER(F349),F349=0))),"Subscription",IF(ISNUMBER(G349),"Profit",IF(ISNUMBER(I349),"Loss",IF(ISNUMBER(H349),"Draw",IF(AND(ISNUMBER(F349),ISNUMBER(E349),E349&gt;0,F349&gt;E349),"Profit",IF(AND(ISNUMBER(F349),ISNUMBER(E349),E349&gt;0,F349=E349),"Draw",IF(AND(ISNUMBER(F349),ISNUMBER(E349),E349&gt;0,F349=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L349" s="50"/>
       <x:c r="M349" s="58"/>
       <x:c r="N349" s="58"/>
@@ -12924,8 +14304,12 @@
       <x:c r="G350" s="58"/>
       <x:c r="H350" s="58"/>
       <x:c r="I350" s="58"/>
-      <x:c r="J350" s="60"/>
-      <x:c r="K350" s="50"/>
+      <x:c r="J350" s="60" t="str">
+        <x:f>IF(A350="","",IF(K350="Subscription","",IF(E350=0,"",IF(ISNUMBER(G350),G350/E350,IF(ISNUMBER(I350),-ABS(I350)/E350,IF(ISNUMBER(H350),0,IF(AND(ISNUMBER(F350),ISNUMBER(E350),E350&gt;0,F350&gt;E350),(F350-E350)/E350,IF(AND(ISNUMBER(F350),ISNUMBER(E350),E350&gt;0,F350=E350),0,IF(AND(ISNUMBER(F350),ISNUMBER(E350),E350&gt;0,F350=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K350" s="50" t="str">
+        <x:f>IF(A350="","",IF(AND(ISNUMBER(E350),E350=0,OR(ISNUMBER(SEARCH("Free",D350&amp;"")),AND(ISNUMBER(F350),F350=0))),"Subscription",IF(ISNUMBER(G350),"Profit",IF(ISNUMBER(I350),"Loss",IF(ISNUMBER(H350),"Draw",IF(AND(ISNUMBER(F350),ISNUMBER(E350),E350&gt;0,F350&gt;E350),"Profit",IF(AND(ISNUMBER(F350),ISNUMBER(E350),E350&gt;0,F350=E350),"Draw",IF(AND(ISNUMBER(F350),ISNUMBER(E350),E350&gt;0,F350=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L350" s="50"/>
       <x:c r="M350" s="58"/>
       <x:c r="N350" s="58"/>
@@ -12957,8 +14341,12 @@
       <x:c r="G351" s="58"/>
       <x:c r="H351" s="58"/>
       <x:c r="I351" s="58"/>
-      <x:c r="J351" s="60"/>
-      <x:c r="K351" s="50"/>
+      <x:c r="J351" s="60" t="str">
+        <x:f>IF(A351="","",IF(K351="Subscription","",IF(E351=0,"",IF(ISNUMBER(G351),G351/E351,IF(ISNUMBER(I351),-ABS(I351)/E351,IF(ISNUMBER(H351),0,IF(AND(ISNUMBER(F351),ISNUMBER(E351),E351&gt;0,F351&gt;E351),(F351-E351)/E351,IF(AND(ISNUMBER(F351),ISNUMBER(E351),E351&gt;0,F351=E351),0,IF(AND(ISNUMBER(F351),ISNUMBER(E351),E351&gt;0,F351=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K351" s="50" t="str">
+        <x:f>IF(A351="","",IF(AND(ISNUMBER(E351),E351=0,OR(ISNUMBER(SEARCH("Free",D351&amp;"")),AND(ISNUMBER(F351),F351=0))),"Subscription",IF(ISNUMBER(G351),"Profit",IF(ISNUMBER(I351),"Loss",IF(ISNUMBER(H351),"Draw",IF(AND(ISNUMBER(F351),ISNUMBER(E351),E351&gt;0,F351&gt;E351),"Profit",IF(AND(ISNUMBER(F351),ISNUMBER(E351),E351&gt;0,F351=E351),"Draw",IF(AND(ISNUMBER(F351),ISNUMBER(E351),E351&gt;0,F351=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L351" s="50"/>
       <x:c r="M351" s="58"/>
       <x:c r="N351" s="58"/>
@@ -12990,8 +14378,12 @@
       <x:c r="G352" s="58"/>
       <x:c r="H352" s="58"/>
       <x:c r="I352" s="58"/>
-      <x:c r="J352" s="60"/>
-      <x:c r="K352" s="50"/>
+      <x:c r="J352" s="60" t="str">
+        <x:f>IF(A352="","",IF(K352="Subscription","",IF(E352=0,"",IF(ISNUMBER(G352),G352/E352,IF(ISNUMBER(I352),-ABS(I352)/E352,IF(ISNUMBER(H352),0,IF(AND(ISNUMBER(F352),ISNUMBER(E352),E352&gt;0,F352&gt;E352),(F352-E352)/E352,IF(AND(ISNUMBER(F352),ISNUMBER(E352),E352&gt;0,F352=E352),0,IF(AND(ISNUMBER(F352),ISNUMBER(E352),E352&gt;0,F352=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K352" s="50" t="str">
+        <x:f>IF(A352="","",IF(AND(ISNUMBER(E352),E352=0,OR(ISNUMBER(SEARCH("Free",D352&amp;"")),AND(ISNUMBER(F352),F352=0))),"Subscription",IF(ISNUMBER(G352),"Profit",IF(ISNUMBER(I352),"Loss",IF(ISNUMBER(H352),"Draw",IF(AND(ISNUMBER(F352),ISNUMBER(E352),E352&gt;0,F352&gt;E352),"Profit",IF(AND(ISNUMBER(F352),ISNUMBER(E352),E352&gt;0,F352=E352),"Draw",IF(AND(ISNUMBER(F352),ISNUMBER(E352),E352&gt;0,F352=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L352" s="50"/>
       <x:c r="M352" s="58"/>
       <x:c r="N352" s="58"/>
@@ -13023,8 +14415,12 @@
       <x:c r="G353" s="58"/>
       <x:c r="H353" s="58"/>
       <x:c r="I353" s="58"/>
-      <x:c r="J353" s="60"/>
-      <x:c r="K353" s="50"/>
+      <x:c r="J353" s="60" t="str">
+        <x:f>IF(A353="","",IF(K353="Subscription","",IF(E353=0,"",IF(ISNUMBER(G353),G353/E353,IF(ISNUMBER(I353),-ABS(I353)/E353,IF(ISNUMBER(H353),0,IF(AND(ISNUMBER(F353),ISNUMBER(E353),E353&gt;0,F353&gt;E353),(F353-E353)/E353,IF(AND(ISNUMBER(F353),ISNUMBER(E353),E353&gt;0,F353=E353),0,IF(AND(ISNUMBER(F353),ISNUMBER(E353),E353&gt;0,F353=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K353" s="50" t="str">
+        <x:f>IF(A353="","",IF(AND(ISNUMBER(E353),E353=0,OR(ISNUMBER(SEARCH("Free",D353&amp;"")),AND(ISNUMBER(F353),F353=0))),"Subscription",IF(ISNUMBER(G353),"Profit",IF(ISNUMBER(I353),"Loss",IF(ISNUMBER(H353),"Draw",IF(AND(ISNUMBER(F353),ISNUMBER(E353),E353&gt;0,F353&gt;E353),"Profit",IF(AND(ISNUMBER(F353),ISNUMBER(E353),E353&gt;0,F353=E353),"Draw",IF(AND(ISNUMBER(F353),ISNUMBER(E353),E353&gt;0,F353=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L353" s="50"/>
       <x:c r="M353" s="58"/>
       <x:c r="N353" s="58"/>
@@ -13056,8 +14452,12 @@
       <x:c r="G354" s="58"/>
       <x:c r="H354" s="58"/>
       <x:c r="I354" s="58"/>
-      <x:c r="J354" s="60"/>
-      <x:c r="K354" s="50"/>
+      <x:c r="J354" s="60" t="str">
+        <x:f>IF(A354="","",IF(K354="Subscription","",IF(E354=0,"",IF(ISNUMBER(G354),G354/E354,IF(ISNUMBER(I354),-ABS(I354)/E354,IF(ISNUMBER(H354),0,IF(AND(ISNUMBER(F354),ISNUMBER(E354),E354&gt;0,F354&gt;E354),(F354-E354)/E354,IF(AND(ISNUMBER(F354),ISNUMBER(E354),E354&gt;0,F354=E354),0,IF(AND(ISNUMBER(F354),ISNUMBER(E354),E354&gt;0,F354=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K354" s="50" t="str">
+        <x:f>IF(A354="","",IF(AND(ISNUMBER(E354),E354=0,OR(ISNUMBER(SEARCH("Free",D354&amp;"")),AND(ISNUMBER(F354),F354=0))),"Subscription",IF(ISNUMBER(G354),"Profit",IF(ISNUMBER(I354),"Loss",IF(ISNUMBER(H354),"Draw",IF(AND(ISNUMBER(F354),ISNUMBER(E354),E354&gt;0,F354&gt;E354),"Profit",IF(AND(ISNUMBER(F354),ISNUMBER(E354),E354&gt;0,F354=E354),"Draw",IF(AND(ISNUMBER(F354),ISNUMBER(E354),E354&gt;0,F354=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L354" s="50"/>
       <x:c r="M354" s="58"/>
       <x:c r="N354" s="58"/>
@@ -13089,8 +14489,12 @@
       <x:c r="G355" s="58"/>
       <x:c r="H355" s="58"/>
       <x:c r="I355" s="58"/>
-      <x:c r="J355" s="60"/>
-      <x:c r="K355" s="50"/>
+      <x:c r="J355" s="60" t="str">
+        <x:f>IF(A355="","",IF(K355="Subscription","",IF(E355=0,"",IF(ISNUMBER(G355),G355/E355,IF(ISNUMBER(I355),-ABS(I355)/E355,IF(ISNUMBER(H355),0,IF(AND(ISNUMBER(F355),ISNUMBER(E355),E355&gt;0,F355&gt;E355),(F355-E355)/E355,IF(AND(ISNUMBER(F355),ISNUMBER(E355),E355&gt;0,F355=E355),0,IF(AND(ISNUMBER(F355),ISNUMBER(E355),E355&gt;0,F355=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K355" s="50" t="str">
+        <x:f>IF(A355="","",IF(AND(ISNUMBER(E355),E355=0,OR(ISNUMBER(SEARCH("Free",D355&amp;"")),AND(ISNUMBER(F355),F355=0))),"Subscription",IF(ISNUMBER(G355),"Profit",IF(ISNUMBER(I355),"Loss",IF(ISNUMBER(H355),"Draw",IF(AND(ISNUMBER(F355),ISNUMBER(E355),E355&gt;0,F355&gt;E355),"Profit",IF(AND(ISNUMBER(F355),ISNUMBER(E355),E355&gt;0,F355=E355),"Draw",IF(AND(ISNUMBER(F355),ISNUMBER(E355),E355&gt;0,F355=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L355" s="50"/>
       <x:c r="M355" s="58"/>
       <x:c r="N355" s="58"/>
@@ -13122,8 +14526,12 @@
       <x:c r="G356" s="58"/>
       <x:c r="H356" s="58"/>
       <x:c r="I356" s="58"/>
-      <x:c r="J356" s="60"/>
-      <x:c r="K356" s="50"/>
+      <x:c r="J356" s="60" t="str">
+        <x:f>IF(A356="","",IF(K356="Subscription","",IF(E356=0,"",IF(ISNUMBER(G356),G356/E356,IF(ISNUMBER(I356),-ABS(I356)/E356,IF(ISNUMBER(H356),0,IF(AND(ISNUMBER(F356),ISNUMBER(E356),E356&gt;0,F356&gt;E356),(F356-E356)/E356,IF(AND(ISNUMBER(F356),ISNUMBER(E356),E356&gt;0,F356=E356),0,IF(AND(ISNUMBER(F356),ISNUMBER(E356),E356&gt;0,F356=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K356" s="50" t="str">
+        <x:f>IF(A356="","",IF(AND(ISNUMBER(E356),E356=0,OR(ISNUMBER(SEARCH("Free",D356&amp;"")),AND(ISNUMBER(F356),F356=0))),"Subscription",IF(ISNUMBER(G356),"Profit",IF(ISNUMBER(I356),"Loss",IF(ISNUMBER(H356),"Draw",IF(AND(ISNUMBER(F356),ISNUMBER(E356),E356&gt;0,F356&gt;E356),"Profit",IF(AND(ISNUMBER(F356),ISNUMBER(E356),E356&gt;0,F356=E356),"Draw",IF(AND(ISNUMBER(F356),ISNUMBER(E356),E356&gt;0,F356=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L356" s="50"/>
       <x:c r="M356" s="58"/>
       <x:c r="N356" s="58"/>
@@ -13155,8 +14563,12 @@
       <x:c r="G357" s="58"/>
       <x:c r="H357" s="58"/>
       <x:c r="I357" s="58"/>
-      <x:c r="J357" s="60"/>
-      <x:c r="K357" s="50"/>
+      <x:c r="J357" s="60" t="str">
+        <x:f>IF(A357="","",IF(K357="Subscription","",IF(E357=0,"",IF(ISNUMBER(G357),G357/E357,IF(ISNUMBER(I357),-ABS(I357)/E357,IF(ISNUMBER(H357),0,IF(AND(ISNUMBER(F357),ISNUMBER(E357),E357&gt;0,F357&gt;E357),(F357-E357)/E357,IF(AND(ISNUMBER(F357),ISNUMBER(E357),E357&gt;0,F357=E357),0,IF(AND(ISNUMBER(F357),ISNUMBER(E357),E357&gt;0,F357=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K357" s="50" t="str">
+        <x:f>IF(A357="","",IF(AND(ISNUMBER(E357),E357=0,OR(ISNUMBER(SEARCH("Free",D357&amp;"")),AND(ISNUMBER(F357),F357=0))),"Subscription",IF(ISNUMBER(G357),"Profit",IF(ISNUMBER(I357),"Loss",IF(ISNUMBER(H357),"Draw",IF(AND(ISNUMBER(F357),ISNUMBER(E357),E357&gt;0,F357&gt;E357),"Profit",IF(AND(ISNUMBER(F357),ISNUMBER(E357),E357&gt;0,F357=E357),"Draw",IF(AND(ISNUMBER(F357),ISNUMBER(E357),E357&gt;0,F357=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L357" s="50"/>
       <x:c r="M357" s="58"/>
       <x:c r="N357" s="58"/>
@@ -13188,8 +14600,12 @@
       <x:c r="G358" s="58"/>
       <x:c r="H358" s="58"/>
       <x:c r="I358" s="58"/>
-      <x:c r="J358" s="60"/>
-      <x:c r="K358" s="50"/>
+      <x:c r="J358" s="60" t="str">
+        <x:f>IF(A358="","",IF(K358="Subscription","",IF(E358=0,"",IF(ISNUMBER(G358),G358/E358,IF(ISNUMBER(I358),-ABS(I358)/E358,IF(ISNUMBER(H358),0,IF(AND(ISNUMBER(F358),ISNUMBER(E358),E358&gt;0,F358&gt;E358),(F358-E358)/E358,IF(AND(ISNUMBER(F358),ISNUMBER(E358),E358&gt;0,F358=E358),0,IF(AND(ISNUMBER(F358),ISNUMBER(E358),E358&gt;0,F358=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K358" s="50" t="str">
+        <x:f>IF(A358="","",IF(AND(ISNUMBER(E358),E358=0,OR(ISNUMBER(SEARCH("Free",D358&amp;"")),AND(ISNUMBER(F358),F358=0))),"Subscription",IF(ISNUMBER(G358),"Profit",IF(ISNUMBER(I358),"Loss",IF(ISNUMBER(H358),"Draw",IF(AND(ISNUMBER(F358),ISNUMBER(E358),E358&gt;0,F358&gt;E358),"Profit",IF(AND(ISNUMBER(F358),ISNUMBER(E358),E358&gt;0,F358=E358),"Draw",IF(AND(ISNUMBER(F358),ISNUMBER(E358),E358&gt;0,F358=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L358" s="50"/>
       <x:c r="M358" s="58"/>
       <x:c r="N358" s="58"/>
@@ -13221,8 +14637,12 @@
       <x:c r="G359" s="58"/>
       <x:c r="H359" s="58"/>
       <x:c r="I359" s="58"/>
-      <x:c r="J359" s="60"/>
-      <x:c r="K359" s="50"/>
+      <x:c r="J359" s="60" t="str">
+        <x:f>IF(A359="","",IF(K359="Subscription","",IF(E359=0,"",IF(ISNUMBER(G359),G359/E359,IF(ISNUMBER(I359),-ABS(I359)/E359,IF(ISNUMBER(H359),0,IF(AND(ISNUMBER(F359),ISNUMBER(E359),E359&gt;0,F359&gt;E359),(F359-E359)/E359,IF(AND(ISNUMBER(F359),ISNUMBER(E359),E359&gt;0,F359=E359),0,IF(AND(ISNUMBER(F359),ISNUMBER(E359),E359&gt;0,F359=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K359" s="50" t="str">
+        <x:f>IF(A359="","",IF(AND(ISNUMBER(E359),E359=0,OR(ISNUMBER(SEARCH("Free",D359&amp;"")),AND(ISNUMBER(F359),F359=0))),"Subscription",IF(ISNUMBER(G359),"Profit",IF(ISNUMBER(I359),"Loss",IF(ISNUMBER(H359),"Draw",IF(AND(ISNUMBER(F359),ISNUMBER(E359),E359&gt;0,F359&gt;E359),"Profit",IF(AND(ISNUMBER(F359),ISNUMBER(E359),E359&gt;0,F359=E359),"Draw",IF(AND(ISNUMBER(F359),ISNUMBER(E359),E359&gt;0,F359=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L359" s="50"/>
       <x:c r="M359" s="58"/>
       <x:c r="N359" s="58"/>
@@ -13254,8 +14674,12 @@
       <x:c r="G360" s="58"/>
       <x:c r="H360" s="58"/>
       <x:c r="I360" s="58"/>
-      <x:c r="J360" s="60"/>
-      <x:c r="K360" s="50"/>
+      <x:c r="J360" s="60" t="str">
+        <x:f>IF(A360="","",IF(K360="Subscription","",IF(E360=0,"",IF(ISNUMBER(G360),G360/E360,IF(ISNUMBER(I360),-ABS(I360)/E360,IF(ISNUMBER(H360),0,IF(AND(ISNUMBER(F360),ISNUMBER(E360),E360&gt;0,F360&gt;E360),(F360-E360)/E360,IF(AND(ISNUMBER(F360),ISNUMBER(E360),E360&gt;0,F360=E360),0,IF(AND(ISNUMBER(F360),ISNUMBER(E360),E360&gt;0,F360=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K360" s="50" t="str">
+        <x:f>IF(A360="","",IF(AND(ISNUMBER(E360),E360=0,OR(ISNUMBER(SEARCH("Free",D360&amp;"")),AND(ISNUMBER(F360),F360=0))),"Subscription",IF(ISNUMBER(G360),"Profit",IF(ISNUMBER(I360),"Loss",IF(ISNUMBER(H360),"Draw",IF(AND(ISNUMBER(F360),ISNUMBER(E360),E360&gt;0,F360&gt;E360),"Profit",IF(AND(ISNUMBER(F360),ISNUMBER(E360),E360&gt;0,F360=E360),"Draw",IF(AND(ISNUMBER(F360),ISNUMBER(E360),E360&gt;0,F360=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L360" s="50"/>
       <x:c r="M360" s="58"/>
       <x:c r="N360" s="58"/>
@@ -13287,8 +14711,12 @@
       <x:c r="G361" s="58"/>
       <x:c r="H361" s="58"/>
       <x:c r="I361" s="58"/>
-      <x:c r="J361" s="60"/>
-      <x:c r="K361" s="50"/>
+      <x:c r="J361" s="60" t="str">
+        <x:f>IF(A361="","",IF(K361="Subscription","",IF(E361=0,"",IF(ISNUMBER(G361),G361/E361,IF(ISNUMBER(I361),-ABS(I361)/E361,IF(ISNUMBER(H361),0,IF(AND(ISNUMBER(F361),ISNUMBER(E361),E361&gt;0,F361&gt;E361),(F361-E361)/E361,IF(AND(ISNUMBER(F361),ISNUMBER(E361),E361&gt;0,F361=E361),0,IF(AND(ISNUMBER(F361),ISNUMBER(E361),E361&gt;0,F361=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K361" s="50" t="str">
+        <x:f>IF(A361="","",IF(AND(ISNUMBER(E361),E361=0,OR(ISNUMBER(SEARCH("Free",D361&amp;"")),AND(ISNUMBER(F361),F361=0))),"Subscription",IF(ISNUMBER(G361),"Profit",IF(ISNUMBER(I361),"Loss",IF(ISNUMBER(H361),"Draw",IF(AND(ISNUMBER(F361),ISNUMBER(E361),E361&gt;0,F361&gt;E361),"Profit",IF(AND(ISNUMBER(F361),ISNUMBER(E361),E361&gt;0,F361=E361),"Draw",IF(AND(ISNUMBER(F361),ISNUMBER(E361),E361&gt;0,F361=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L361" s="50"/>
       <x:c r="M361" s="58"/>
       <x:c r="N361" s="58"/>
@@ -13320,8 +14748,12 @@
       <x:c r="G362" s="58"/>
       <x:c r="H362" s="58"/>
       <x:c r="I362" s="58"/>
-      <x:c r="J362" s="60"/>
-      <x:c r="K362" s="50"/>
+      <x:c r="J362" s="60" t="str">
+        <x:f>IF(A362="","",IF(K362="Subscription","",IF(E362=0,"",IF(ISNUMBER(G362),G362/E362,IF(ISNUMBER(I362),-ABS(I362)/E362,IF(ISNUMBER(H362),0,IF(AND(ISNUMBER(F362),ISNUMBER(E362),E362&gt;0,F362&gt;E362),(F362-E362)/E362,IF(AND(ISNUMBER(F362),ISNUMBER(E362),E362&gt;0,F362=E362),0,IF(AND(ISNUMBER(F362),ISNUMBER(E362),E362&gt;0,F362=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K362" s="50" t="str">
+        <x:f>IF(A362="","",IF(AND(ISNUMBER(E362),E362=0,OR(ISNUMBER(SEARCH("Free",D362&amp;"")),AND(ISNUMBER(F362),F362=0))),"Subscription",IF(ISNUMBER(G362),"Profit",IF(ISNUMBER(I362),"Loss",IF(ISNUMBER(H362),"Draw",IF(AND(ISNUMBER(F362),ISNUMBER(E362),E362&gt;0,F362&gt;E362),"Profit",IF(AND(ISNUMBER(F362),ISNUMBER(E362),E362&gt;0,F362=E362),"Draw",IF(AND(ISNUMBER(F362),ISNUMBER(E362),E362&gt;0,F362=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L362" s="50"/>
       <x:c r="M362" s="58"/>
       <x:c r="N362" s="58"/>
@@ -13353,8 +14785,12 @@
       <x:c r="G363" s="58"/>
       <x:c r="H363" s="58"/>
       <x:c r="I363" s="58"/>
-      <x:c r="J363" s="60"/>
-      <x:c r="K363" s="50"/>
+      <x:c r="J363" s="60" t="str">
+        <x:f>IF(A363="","",IF(K363="Subscription","",IF(E363=0,"",IF(ISNUMBER(G363),G363/E363,IF(ISNUMBER(I363),-ABS(I363)/E363,IF(ISNUMBER(H363),0,IF(AND(ISNUMBER(F363),ISNUMBER(E363),E363&gt;0,F363&gt;E363),(F363-E363)/E363,IF(AND(ISNUMBER(F363),ISNUMBER(E363),E363&gt;0,F363=E363),0,IF(AND(ISNUMBER(F363),ISNUMBER(E363),E363&gt;0,F363=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K363" s="50" t="str">
+        <x:f>IF(A363="","",IF(AND(ISNUMBER(E363),E363=0,OR(ISNUMBER(SEARCH("Free",D363&amp;"")),AND(ISNUMBER(F363),F363=0))),"Subscription",IF(ISNUMBER(G363),"Profit",IF(ISNUMBER(I363),"Loss",IF(ISNUMBER(H363),"Draw",IF(AND(ISNUMBER(F363),ISNUMBER(E363),E363&gt;0,F363&gt;E363),"Profit",IF(AND(ISNUMBER(F363),ISNUMBER(E363),E363&gt;0,F363=E363),"Draw",IF(AND(ISNUMBER(F363),ISNUMBER(E363),E363&gt;0,F363=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L363" s="50"/>
       <x:c r="M363" s="58"/>
       <x:c r="N363" s="58"/>
@@ -13386,8 +14822,12 @@
       <x:c r="G364" s="58"/>
       <x:c r="H364" s="58"/>
       <x:c r="I364" s="58"/>
-      <x:c r="J364" s="60"/>
-      <x:c r="K364" s="50"/>
+      <x:c r="J364" s="60" t="str">
+        <x:f>IF(A364="","",IF(K364="Subscription","",IF(E364=0,"",IF(ISNUMBER(G364),G364/E364,IF(ISNUMBER(I364),-ABS(I364)/E364,IF(ISNUMBER(H364),0,IF(AND(ISNUMBER(F364),ISNUMBER(E364),E364&gt;0,F364&gt;E364),(F364-E364)/E364,IF(AND(ISNUMBER(F364),ISNUMBER(E364),E364&gt;0,F364=E364),0,IF(AND(ISNUMBER(F364),ISNUMBER(E364),E364&gt;0,F364=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K364" s="50" t="str">
+        <x:f>IF(A364="","",IF(AND(ISNUMBER(E364),E364=0,OR(ISNUMBER(SEARCH("Free",D364&amp;"")),AND(ISNUMBER(F364),F364=0))),"Subscription",IF(ISNUMBER(G364),"Profit",IF(ISNUMBER(I364),"Loss",IF(ISNUMBER(H364),"Draw",IF(AND(ISNUMBER(F364),ISNUMBER(E364),E364&gt;0,F364&gt;E364),"Profit",IF(AND(ISNUMBER(F364),ISNUMBER(E364),E364&gt;0,F364=E364),"Draw",IF(AND(ISNUMBER(F364),ISNUMBER(E364),E364&gt;0,F364=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L364" s="50"/>
       <x:c r="M364" s="58"/>
       <x:c r="N364" s="58"/>
@@ -13419,8 +14859,12 @@
       <x:c r="G365" s="58"/>
       <x:c r="H365" s="58"/>
       <x:c r="I365" s="58"/>
-      <x:c r="J365" s="60"/>
-      <x:c r="K365" s="50"/>
+      <x:c r="J365" s="60" t="str">
+        <x:f>IF(A365="","",IF(K365="Subscription","",IF(E365=0,"",IF(ISNUMBER(G365),G365/E365,IF(ISNUMBER(I365),-ABS(I365)/E365,IF(ISNUMBER(H365),0,IF(AND(ISNUMBER(F365),ISNUMBER(E365),E365&gt;0,F365&gt;E365),(F365-E365)/E365,IF(AND(ISNUMBER(F365),ISNUMBER(E365),E365&gt;0,F365=E365),0,IF(AND(ISNUMBER(F365),ISNUMBER(E365),E365&gt;0,F365=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K365" s="50" t="str">
+        <x:f>IF(A365="","",IF(AND(ISNUMBER(E365),E365=0,OR(ISNUMBER(SEARCH("Free",D365&amp;"")),AND(ISNUMBER(F365),F365=0))),"Subscription",IF(ISNUMBER(G365),"Profit",IF(ISNUMBER(I365),"Loss",IF(ISNUMBER(H365),"Draw",IF(AND(ISNUMBER(F365),ISNUMBER(E365),E365&gt;0,F365&gt;E365),"Profit",IF(AND(ISNUMBER(F365),ISNUMBER(E365),E365&gt;0,F365=E365),"Draw",IF(AND(ISNUMBER(F365),ISNUMBER(E365),E365&gt;0,F365=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L365" s="50"/>
       <x:c r="M365" s="58"/>
       <x:c r="N365" s="58"/>
@@ -13452,8 +14896,12 @@
       <x:c r="G366" s="58"/>
       <x:c r="H366" s="58"/>
       <x:c r="I366" s="58"/>
-      <x:c r="J366" s="60"/>
-      <x:c r="K366" s="50"/>
+      <x:c r="J366" s="60" t="str">
+        <x:f>IF(A366="","",IF(K366="Subscription","",IF(E366=0,"",IF(ISNUMBER(G366),G366/E366,IF(ISNUMBER(I366),-ABS(I366)/E366,IF(ISNUMBER(H366),0,IF(AND(ISNUMBER(F366),ISNUMBER(E366),E366&gt;0,F366&gt;E366),(F366-E366)/E366,IF(AND(ISNUMBER(F366),ISNUMBER(E366),E366&gt;0,F366=E366),0,IF(AND(ISNUMBER(F366),ISNUMBER(E366),E366&gt;0,F366=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K366" s="50" t="str">
+        <x:f>IF(A366="","",IF(AND(ISNUMBER(E366),E366=0,OR(ISNUMBER(SEARCH("Free",D366&amp;"")),AND(ISNUMBER(F366),F366=0))),"Subscription",IF(ISNUMBER(G366),"Profit",IF(ISNUMBER(I366),"Loss",IF(ISNUMBER(H366),"Draw",IF(AND(ISNUMBER(F366),ISNUMBER(E366),E366&gt;0,F366&gt;E366),"Profit",IF(AND(ISNUMBER(F366),ISNUMBER(E366),E366&gt;0,F366=E366),"Draw",IF(AND(ISNUMBER(F366),ISNUMBER(E366),E366&gt;0,F366=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L366" s="50"/>
       <x:c r="M366" s="58"/>
       <x:c r="N366" s="58"/>
@@ -13485,8 +14933,12 @@
       <x:c r="G367" s="58"/>
       <x:c r="H367" s="58"/>
       <x:c r="I367" s="58"/>
-      <x:c r="J367" s="60"/>
-      <x:c r="K367" s="50"/>
+      <x:c r="J367" s="60" t="str">
+        <x:f>IF(A367="","",IF(K367="Subscription","",IF(E367=0,"",IF(ISNUMBER(G367),G367/E367,IF(ISNUMBER(I367),-ABS(I367)/E367,IF(ISNUMBER(H367),0,IF(AND(ISNUMBER(F367),ISNUMBER(E367),E367&gt;0,F367&gt;E367),(F367-E367)/E367,IF(AND(ISNUMBER(F367),ISNUMBER(E367),E367&gt;0,F367=E367),0,IF(AND(ISNUMBER(F367),ISNUMBER(E367),E367&gt;0,F367=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K367" s="50" t="str">
+        <x:f>IF(A367="","",IF(AND(ISNUMBER(E367),E367=0,OR(ISNUMBER(SEARCH("Free",D367&amp;"")),AND(ISNUMBER(F367),F367=0))),"Subscription",IF(ISNUMBER(G367),"Profit",IF(ISNUMBER(I367),"Loss",IF(ISNUMBER(H367),"Draw",IF(AND(ISNUMBER(F367),ISNUMBER(E367),E367&gt;0,F367&gt;E367),"Profit",IF(AND(ISNUMBER(F367),ISNUMBER(E367),E367&gt;0,F367=E367),"Draw",IF(AND(ISNUMBER(F367),ISNUMBER(E367),E367&gt;0,F367=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L367" s="50"/>
       <x:c r="M367" s="58"/>
       <x:c r="N367" s="58"/>
@@ -13518,8 +14970,12 @@
       <x:c r="G368" s="58"/>
       <x:c r="H368" s="58"/>
       <x:c r="I368" s="58"/>
-      <x:c r="J368" s="60"/>
-      <x:c r="K368" s="50"/>
+      <x:c r="J368" s="60" t="str">
+        <x:f>IF(A368="","",IF(K368="Subscription","",IF(E368=0,"",IF(ISNUMBER(G368),G368/E368,IF(ISNUMBER(I368),-ABS(I368)/E368,IF(ISNUMBER(H368),0,IF(AND(ISNUMBER(F368),ISNUMBER(E368),E368&gt;0,F368&gt;E368),(F368-E368)/E368,IF(AND(ISNUMBER(F368),ISNUMBER(E368),E368&gt;0,F368=E368),0,IF(AND(ISNUMBER(F368),ISNUMBER(E368),E368&gt;0,F368=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K368" s="50" t="str">
+        <x:f>IF(A368="","",IF(AND(ISNUMBER(E368),E368=0,OR(ISNUMBER(SEARCH("Free",D368&amp;"")),AND(ISNUMBER(F368),F368=0))),"Subscription",IF(ISNUMBER(G368),"Profit",IF(ISNUMBER(I368),"Loss",IF(ISNUMBER(H368),"Draw",IF(AND(ISNUMBER(F368),ISNUMBER(E368),E368&gt;0,F368&gt;E368),"Profit",IF(AND(ISNUMBER(F368),ISNUMBER(E368),E368&gt;0,F368=E368),"Draw",IF(AND(ISNUMBER(F368),ISNUMBER(E368),E368&gt;0,F368=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L368" s="50"/>
       <x:c r="M368" s="58"/>
       <x:c r="N368" s="58"/>
@@ -13551,8 +15007,12 @@
       <x:c r="G369" s="58"/>
       <x:c r="H369" s="58"/>
       <x:c r="I369" s="58"/>
-      <x:c r="J369" s="60"/>
-      <x:c r="K369" s="50"/>
+      <x:c r="J369" s="60" t="str">
+        <x:f>IF(A369="","",IF(K369="Subscription","",IF(E369=0,"",IF(ISNUMBER(G369),G369/E369,IF(ISNUMBER(I369),-ABS(I369)/E369,IF(ISNUMBER(H369),0,IF(AND(ISNUMBER(F369),ISNUMBER(E369),E369&gt;0,F369&gt;E369),(F369-E369)/E369,IF(AND(ISNUMBER(F369),ISNUMBER(E369),E369&gt;0,F369=E369),0,IF(AND(ISNUMBER(F369),ISNUMBER(E369),E369&gt;0,F369=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K369" s="50" t="str">
+        <x:f>IF(A369="","",IF(AND(ISNUMBER(E369),E369=0,OR(ISNUMBER(SEARCH("Free",D369&amp;"")),AND(ISNUMBER(F369),F369=0))),"Subscription",IF(ISNUMBER(G369),"Profit",IF(ISNUMBER(I369),"Loss",IF(ISNUMBER(H369),"Draw",IF(AND(ISNUMBER(F369),ISNUMBER(E369),E369&gt;0,F369&gt;E369),"Profit",IF(AND(ISNUMBER(F369),ISNUMBER(E369),E369&gt;0,F369=E369),"Draw",IF(AND(ISNUMBER(F369),ISNUMBER(E369),E369&gt;0,F369=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L369" s="50"/>
       <x:c r="M369" s="58"/>
       <x:c r="N369" s="58"/>
@@ -13584,8 +15044,12 @@
       <x:c r="G370" s="58"/>
       <x:c r="H370" s="58"/>
       <x:c r="I370" s="58"/>
-      <x:c r="J370" s="60"/>
-      <x:c r="K370" s="50"/>
+      <x:c r="J370" s="60" t="str">
+        <x:f>IF(A370="","",IF(K370="Subscription","",IF(E370=0,"",IF(ISNUMBER(G370),G370/E370,IF(ISNUMBER(I370),-ABS(I370)/E370,IF(ISNUMBER(H370),0,IF(AND(ISNUMBER(F370),ISNUMBER(E370),E370&gt;0,F370&gt;E370),(F370-E370)/E370,IF(AND(ISNUMBER(F370),ISNUMBER(E370),E370&gt;0,F370=E370),0,IF(AND(ISNUMBER(F370),ISNUMBER(E370),E370&gt;0,F370=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K370" s="50" t="str">
+        <x:f>IF(A370="","",IF(AND(ISNUMBER(E370),E370=0,OR(ISNUMBER(SEARCH("Free",D370&amp;"")),AND(ISNUMBER(F370),F370=0))),"Subscription",IF(ISNUMBER(G370),"Profit",IF(ISNUMBER(I370),"Loss",IF(ISNUMBER(H370),"Draw",IF(AND(ISNUMBER(F370),ISNUMBER(E370),E370&gt;0,F370&gt;E370),"Profit",IF(AND(ISNUMBER(F370),ISNUMBER(E370),E370&gt;0,F370=E370),"Draw",IF(AND(ISNUMBER(F370),ISNUMBER(E370),E370&gt;0,F370=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L370" s="50"/>
       <x:c r="M370" s="58"/>
       <x:c r="N370" s="58"/>
@@ -13617,8 +15081,12 @@
       <x:c r="G371" s="58"/>
       <x:c r="H371" s="58"/>
       <x:c r="I371" s="58"/>
-      <x:c r="J371" s="60"/>
-      <x:c r="K371" s="50"/>
+      <x:c r="J371" s="60" t="str">
+        <x:f>IF(A371="","",IF(K371="Subscription","",IF(E371=0,"",IF(ISNUMBER(G371),G371/E371,IF(ISNUMBER(I371),-ABS(I371)/E371,IF(ISNUMBER(H371),0,IF(AND(ISNUMBER(F371),ISNUMBER(E371),E371&gt;0,F371&gt;E371),(F371-E371)/E371,IF(AND(ISNUMBER(F371),ISNUMBER(E371),E371&gt;0,F371=E371),0,IF(AND(ISNUMBER(F371),ISNUMBER(E371),E371&gt;0,F371=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K371" s="50" t="str">
+        <x:f>IF(A371="","",IF(AND(ISNUMBER(E371),E371=0,OR(ISNUMBER(SEARCH("Free",D371&amp;"")),AND(ISNUMBER(F371),F371=0))),"Subscription",IF(ISNUMBER(G371),"Profit",IF(ISNUMBER(I371),"Loss",IF(ISNUMBER(H371),"Draw",IF(AND(ISNUMBER(F371),ISNUMBER(E371),E371&gt;0,F371&gt;E371),"Profit",IF(AND(ISNUMBER(F371),ISNUMBER(E371),E371&gt;0,F371=E371),"Draw",IF(AND(ISNUMBER(F371),ISNUMBER(E371),E371&gt;0,F371=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L371" s="50"/>
       <x:c r="M371" s="58"/>
       <x:c r="N371" s="58"/>
@@ -13650,8 +15118,12 @@
       <x:c r="G372" s="58"/>
       <x:c r="H372" s="58"/>
       <x:c r="I372" s="58"/>
-      <x:c r="J372" s="60"/>
-      <x:c r="K372" s="50"/>
+      <x:c r="J372" s="60" t="str">
+        <x:f>IF(A372="","",IF(K372="Subscription","",IF(E372=0,"",IF(ISNUMBER(G372),G372/E372,IF(ISNUMBER(I372),-ABS(I372)/E372,IF(ISNUMBER(H372),0,IF(AND(ISNUMBER(F372),ISNUMBER(E372),E372&gt;0,F372&gt;E372),(F372-E372)/E372,IF(AND(ISNUMBER(F372),ISNUMBER(E372),E372&gt;0,F372=E372),0,IF(AND(ISNUMBER(F372),ISNUMBER(E372),E372&gt;0,F372=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K372" s="50" t="str">
+        <x:f>IF(A372="","",IF(AND(ISNUMBER(E372),E372=0,OR(ISNUMBER(SEARCH("Free",D372&amp;"")),AND(ISNUMBER(F372),F372=0))),"Subscription",IF(ISNUMBER(G372),"Profit",IF(ISNUMBER(I372),"Loss",IF(ISNUMBER(H372),"Draw",IF(AND(ISNUMBER(F372),ISNUMBER(E372),E372&gt;0,F372&gt;E372),"Profit",IF(AND(ISNUMBER(F372),ISNUMBER(E372),E372&gt;0,F372=E372),"Draw",IF(AND(ISNUMBER(F372),ISNUMBER(E372),E372&gt;0,F372=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L372" s="50"/>
       <x:c r="M372" s="58"/>
       <x:c r="N372" s="58"/>
@@ -13683,8 +15155,12 @@
       <x:c r="G373" s="58"/>
       <x:c r="H373" s="58"/>
       <x:c r="I373" s="58"/>
-      <x:c r="J373" s="60"/>
-      <x:c r="K373" s="50"/>
+      <x:c r="J373" s="60" t="str">
+        <x:f>IF(A373="","",IF(K373="Subscription","",IF(E373=0,"",IF(ISNUMBER(G373),G373/E373,IF(ISNUMBER(I373),-ABS(I373)/E373,IF(ISNUMBER(H373),0,IF(AND(ISNUMBER(F373),ISNUMBER(E373),E373&gt;0,F373&gt;E373),(F373-E373)/E373,IF(AND(ISNUMBER(F373),ISNUMBER(E373),E373&gt;0,F373=E373),0,IF(AND(ISNUMBER(F373),ISNUMBER(E373),E373&gt;0,F373=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K373" s="50" t="str">
+        <x:f>IF(A373="","",IF(AND(ISNUMBER(E373),E373=0,OR(ISNUMBER(SEARCH("Free",D373&amp;"")),AND(ISNUMBER(F373),F373=0))),"Subscription",IF(ISNUMBER(G373),"Profit",IF(ISNUMBER(I373),"Loss",IF(ISNUMBER(H373),"Draw",IF(AND(ISNUMBER(F373),ISNUMBER(E373),E373&gt;0,F373&gt;E373),"Profit",IF(AND(ISNUMBER(F373),ISNUMBER(E373),E373&gt;0,F373=E373),"Draw",IF(AND(ISNUMBER(F373),ISNUMBER(E373),E373&gt;0,F373=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L373" s="50"/>
       <x:c r="M373" s="58"/>
       <x:c r="N373" s="58"/>
@@ -13716,8 +15192,12 @@
       <x:c r="G374" s="58"/>
       <x:c r="H374" s="58"/>
       <x:c r="I374" s="58"/>
-      <x:c r="J374" s="60"/>
-      <x:c r="K374" s="50"/>
+      <x:c r="J374" s="60" t="str">
+        <x:f>IF(A374="","",IF(K374="Subscription","",IF(E374=0,"",IF(ISNUMBER(G374),G374/E374,IF(ISNUMBER(I374),-ABS(I374)/E374,IF(ISNUMBER(H374),0,IF(AND(ISNUMBER(F374),ISNUMBER(E374),E374&gt;0,F374&gt;E374),(F374-E374)/E374,IF(AND(ISNUMBER(F374),ISNUMBER(E374),E374&gt;0,F374=E374),0,IF(AND(ISNUMBER(F374),ISNUMBER(E374),E374&gt;0,F374=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K374" s="50" t="str">
+        <x:f>IF(A374="","",IF(AND(ISNUMBER(E374),E374=0,OR(ISNUMBER(SEARCH("Free",D374&amp;"")),AND(ISNUMBER(F374),F374=0))),"Subscription",IF(ISNUMBER(G374),"Profit",IF(ISNUMBER(I374),"Loss",IF(ISNUMBER(H374),"Draw",IF(AND(ISNUMBER(F374),ISNUMBER(E374),E374&gt;0,F374&gt;E374),"Profit",IF(AND(ISNUMBER(F374),ISNUMBER(E374),E374&gt;0,F374=E374),"Draw",IF(AND(ISNUMBER(F374),ISNUMBER(E374),E374&gt;0,F374=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L374" s="50"/>
       <x:c r="M374" s="58"/>
       <x:c r="N374" s="58"/>
@@ -13749,8 +15229,12 @@
       <x:c r="G375" s="58"/>
       <x:c r="H375" s="58"/>
       <x:c r="I375" s="58"/>
-      <x:c r="J375" s="60"/>
-      <x:c r="K375" s="50"/>
+      <x:c r="J375" s="60" t="str">
+        <x:f>IF(A375="","",IF(K375="Subscription","",IF(E375=0,"",IF(ISNUMBER(G375),G375/E375,IF(ISNUMBER(I375),-ABS(I375)/E375,IF(ISNUMBER(H375),0,IF(AND(ISNUMBER(F375),ISNUMBER(E375),E375&gt;0,F375&gt;E375),(F375-E375)/E375,IF(AND(ISNUMBER(F375),ISNUMBER(E375),E375&gt;0,F375=E375),0,IF(AND(ISNUMBER(F375),ISNUMBER(E375),E375&gt;0,F375=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K375" s="50" t="str">
+        <x:f>IF(A375="","",IF(AND(ISNUMBER(E375),E375=0,OR(ISNUMBER(SEARCH("Free",D375&amp;"")),AND(ISNUMBER(F375),F375=0))),"Subscription",IF(ISNUMBER(G375),"Profit",IF(ISNUMBER(I375),"Loss",IF(ISNUMBER(H375),"Draw",IF(AND(ISNUMBER(F375),ISNUMBER(E375),E375&gt;0,F375&gt;E375),"Profit",IF(AND(ISNUMBER(F375),ISNUMBER(E375),E375&gt;0,F375=E375),"Draw",IF(AND(ISNUMBER(F375),ISNUMBER(E375),E375&gt;0,F375=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L375" s="50"/>
       <x:c r="M375" s="58"/>
       <x:c r="N375" s="58"/>
@@ -13782,8 +15266,12 @@
       <x:c r="G376" s="58"/>
       <x:c r="H376" s="58"/>
       <x:c r="I376" s="58"/>
-      <x:c r="J376" s="60"/>
-      <x:c r="K376" s="50"/>
+      <x:c r="J376" s="60" t="str">
+        <x:f>IF(A376="","",IF(K376="Subscription","",IF(E376=0,"",IF(ISNUMBER(G376),G376/E376,IF(ISNUMBER(I376),-ABS(I376)/E376,IF(ISNUMBER(H376),0,IF(AND(ISNUMBER(F376),ISNUMBER(E376),E376&gt;0,F376&gt;E376),(F376-E376)/E376,IF(AND(ISNUMBER(F376),ISNUMBER(E376),E376&gt;0,F376=E376),0,IF(AND(ISNUMBER(F376),ISNUMBER(E376),E376&gt;0,F376=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K376" s="50" t="str">
+        <x:f>IF(A376="","",IF(AND(ISNUMBER(E376),E376=0,OR(ISNUMBER(SEARCH("Free",D376&amp;"")),AND(ISNUMBER(F376),F376=0))),"Subscription",IF(ISNUMBER(G376),"Profit",IF(ISNUMBER(I376),"Loss",IF(ISNUMBER(H376),"Draw",IF(AND(ISNUMBER(F376),ISNUMBER(E376),E376&gt;0,F376&gt;E376),"Profit",IF(AND(ISNUMBER(F376),ISNUMBER(E376),E376&gt;0,F376=E376),"Draw",IF(AND(ISNUMBER(F376),ISNUMBER(E376),E376&gt;0,F376=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L376" s="50"/>
       <x:c r="M376" s="58"/>
       <x:c r="N376" s="58"/>
@@ -13815,8 +15303,12 @@
       <x:c r="G377" s="58"/>
       <x:c r="H377" s="58"/>
       <x:c r="I377" s="58"/>
-      <x:c r="J377" s="60"/>
-      <x:c r="K377" s="50"/>
+      <x:c r="J377" s="60" t="str">
+        <x:f>IF(A377="","",IF(K377="Subscription","",IF(E377=0,"",IF(ISNUMBER(G377),G377/E377,IF(ISNUMBER(I377),-ABS(I377)/E377,IF(ISNUMBER(H377),0,IF(AND(ISNUMBER(F377),ISNUMBER(E377),E377&gt;0,F377&gt;E377),(F377-E377)/E377,IF(AND(ISNUMBER(F377),ISNUMBER(E377),E377&gt;0,F377=E377),0,IF(AND(ISNUMBER(F377),ISNUMBER(E377),E377&gt;0,F377=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K377" s="50" t="str">
+        <x:f>IF(A377="","",IF(AND(ISNUMBER(E377),E377=0,OR(ISNUMBER(SEARCH("Free",D377&amp;"")),AND(ISNUMBER(F377),F377=0))),"Subscription",IF(ISNUMBER(G377),"Profit",IF(ISNUMBER(I377),"Loss",IF(ISNUMBER(H377),"Draw",IF(AND(ISNUMBER(F377),ISNUMBER(E377),E377&gt;0,F377&gt;E377),"Profit",IF(AND(ISNUMBER(F377),ISNUMBER(E377),E377&gt;0,F377=E377),"Draw",IF(AND(ISNUMBER(F377),ISNUMBER(E377),E377&gt;0,F377=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L377" s="50"/>
       <x:c r="M377" s="58"/>
       <x:c r="N377" s="58"/>
@@ -13848,8 +15340,12 @@
       <x:c r="G378" s="58"/>
       <x:c r="H378" s="58"/>
       <x:c r="I378" s="58"/>
-      <x:c r="J378" s="60"/>
-      <x:c r="K378" s="50"/>
+      <x:c r="J378" s="60" t="str">
+        <x:f>IF(A378="","",IF(K378="Subscription","",IF(E378=0,"",IF(ISNUMBER(G378),G378/E378,IF(ISNUMBER(I378),-ABS(I378)/E378,IF(ISNUMBER(H378),0,IF(AND(ISNUMBER(F378),ISNUMBER(E378),E378&gt;0,F378&gt;E378),(F378-E378)/E378,IF(AND(ISNUMBER(F378),ISNUMBER(E378),E378&gt;0,F378=E378),0,IF(AND(ISNUMBER(F378),ISNUMBER(E378),E378&gt;0,F378=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K378" s="50" t="str">
+        <x:f>IF(A378="","",IF(AND(ISNUMBER(E378),E378=0,OR(ISNUMBER(SEARCH("Free",D378&amp;"")),AND(ISNUMBER(F378),F378=0))),"Subscription",IF(ISNUMBER(G378),"Profit",IF(ISNUMBER(I378),"Loss",IF(ISNUMBER(H378),"Draw",IF(AND(ISNUMBER(F378),ISNUMBER(E378),E378&gt;0,F378&gt;E378),"Profit",IF(AND(ISNUMBER(F378),ISNUMBER(E378),E378&gt;0,F378=E378),"Draw",IF(AND(ISNUMBER(F378),ISNUMBER(E378),E378&gt;0,F378=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L378" s="50"/>
       <x:c r="M378" s="58"/>
       <x:c r="N378" s="58"/>
@@ -13881,8 +15377,12 @@
       <x:c r="G379" s="58"/>
       <x:c r="H379" s="58"/>
       <x:c r="I379" s="58"/>
-      <x:c r="J379" s="60"/>
-      <x:c r="K379" s="50"/>
+      <x:c r="J379" s="60" t="str">
+        <x:f>IF(A379="","",IF(K379="Subscription","",IF(E379=0,"",IF(ISNUMBER(G379),G379/E379,IF(ISNUMBER(I379),-ABS(I379)/E379,IF(ISNUMBER(H379),0,IF(AND(ISNUMBER(F379),ISNUMBER(E379),E379&gt;0,F379&gt;E379),(F379-E379)/E379,IF(AND(ISNUMBER(F379),ISNUMBER(E379),E379&gt;0,F379=E379),0,IF(AND(ISNUMBER(F379),ISNUMBER(E379),E379&gt;0,F379=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K379" s="50" t="str">
+        <x:f>IF(A379="","",IF(AND(ISNUMBER(E379),E379=0,OR(ISNUMBER(SEARCH("Free",D379&amp;"")),AND(ISNUMBER(F379),F379=0))),"Subscription",IF(ISNUMBER(G379),"Profit",IF(ISNUMBER(I379),"Loss",IF(ISNUMBER(H379),"Draw",IF(AND(ISNUMBER(F379),ISNUMBER(E379),E379&gt;0,F379&gt;E379),"Profit",IF(AND(ISNUMBER(F379),ISNUMBER(E379),E379&gt;0,F379=E379),"Draw",IF(AND(ISNUMBER(F379),ISNUMBER(E379),E379&gt;0,F379=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L379" s="50"/>
       <x:c r="M379" s="58"/>
       <x:c r="N379" s="58"/>
@@ -13914,8 +15414,12 @@
       <x:c r="G380" s="58"/>
       <x:c r="H380" s="58"/>
       <x:c r="I380" s="58"/>
-      <x:c r="J380" s="60"/>
-      <x:c r="K380" s="50"/>
+      <x:c r="J380" s="60" t="str">
+        <x:f>IF(A380="","",IF(K380="Subscription","",IF(E380=0,"",IF(ISNUMBER(G380),G380/E380,IF(ISNUMBER(I380),-ABS(I380)/E380,IF(ISNUMBER(H380),0,IF(AND(ISNUMBER(F380),ISNUMBER(E380),E380&gt;0,F380&gt;E380),(F380-E380)/E380,IF(AND(ISNUMBER(F380),ISNUMBER(E380),E380&gt;0,F380=E380),0,IF(AND(ISNUMBER(F380),ISNUMBER(E380),E380&gt;0,F380=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K380" s="50" t="str">
+        <x:f>IF(A380="","",IF(AND(ISNUMBER(E380),E380=0,OR(ISNUMBER(SEARCH("Free",D380&amp;"")),AND(ISNUMBER(F380),F380=0))),"Subscription",IF(ISNUMBER(G380),"Profit",IF(ISNUMBER(I380),"Loss",IF(ISNUMBER(H380),"Draw",IF(AND(ISNUMBER(F380),ISNUMBER(E380),E380&gt;0,F380&gt;E380),"Profit",IF(AND(ISNUMBER(F380),ISNUMBER(E380),E380&gt;0,F380=E380),"Draw",IF(AND(ISNUMBER(F380),ISNUMBER(E380),E380&gt;0,F380=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L380" s="50"/>
       <x:c r="M380" s="58"/>
       <x:c r="N380" s="58"/>
@@ -13947,8 +15451,12 @@
       <x:c r="G381" s="58"/>
       <x:c r="H381" s="58"/>
       <x:c r="I381" s="58"/>
-      <x:c r="J381" s="60"/>
-      <x:c r="K381" s="50"/>
+      <x:c r="J381" s="60" t="str">
+        <x:f>IF(A381="","",IF(K381="Subscription","",IF(E381=0,"",IF(ISNUMBER(G381),G381/E381,IF(ISNUMBER(I381),-ABS(I381)/E381,IF(ISNUMBER(H381),0,IF(AND(ISNUMBER(F381),ISNUMBER(E381),E381&gt;0,F381&gt;E381),(F381-E381)/E381,IF(AND(ISNUMBER(F381),ISNUMBER(E381),E381&gt;0,F381=E381),0,IF(AND(ISNUMBER(F381),ISNUMBER(E381),E381&gt;0,F381=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K381" s="50" t="str">
+        <x:f>IF(A381="","",IF(AND(ISNUMBER(E381),E381=0,OR(ISNUMBER(SEARCH("Free",D381&amp;"")),AND(ISNUMBER(F381),F381=0))),"Subscription",IF(ISNUMBER(G381),"Profit",IF(ISNUMBER(I381),"Loss",IF(ISNUMBER(H381),"Draw",IF(AND(ISNUMBER(F381),ISNUMBER(E381),E381&gt;0,F381&gt;E381),"Profit",IF(AND(ISNUMBER(F381),ISNUMBER(E381),E381&gt;0,F381=E381),"Draw",IF(AND(ISNUMBER(F381),ISNUMBER(E381),E381&gt;0,F381=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L381" s="50"/>
       <x:c r="M381" s="58"/>
       <x:c r="N381" s="58"/>
@@ -13980,8 +15488,12 @@
       <x:c r="G382" s="58"/>
       <x:c r="H382" s="58"/>
       <x:c r="I382" s="58"/>
-      <x:c r="J382" s="60"/>
-      <x:c r="K382" s="50"/>
+      <x:c r="J382" s="60" t="str">
+        <x:f>IF(A382="","",IF(K382="Subscription","",IF(E382=0,"",IF(ISNUMBER(G382),G382/E382,IF(ISNUMBER(I382),-ABS(I382)/E382,IF(ISNUMBER(H382),0,IF(AND(ISNUMBER(F382),ISNUMBER(E382),E382&gt;0,F382&gt;E382),(F382-E382)/E382,IF(AND(ISNUMBER(F382),ISNUMBER(E382),E382&gt;0,F382=E382),0,IF(AND(ISNUMBER(F382),ISNUMBER(E382),E382&gt;0,F382=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K382" s="50" t="str">
+        <x:f>IF(A382="","",IF(AND(ISNUMBER(E382),E382=0,OR(ISNUMBER(SEARCH("Free",D382&amp;"")),AND(ISNUMBER(F382),F382=0))),"Subscription",IF(ISNUMBER(G382),"Profit",IF(ISNUMBER(I382),"Loss",IF(ISNUMBER(H382),"Draw",IF(AND(ISNUMBER(F382),ISNUMBER(E382),E382&gt;0,F382&gt;E382),"Profit",IF(AND(ISNUMBER(F382),ISNUMBER(E382),E382&gt;0,F382=E382),"Draw",IF(AND(ISNUMBER(F382),ISNUMBER(E382),E382&gt;0,F382=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L382" s="50"/>
       <x:c r="M382" s="58"/>
       <x:c r="N382" s="58"/>
@@ -14013,8 +15525,12 @@
       <x:c r="G383" s="58"/>
       <x:c r="H383" s="58"/>
       <x:c r="I383" s="58"/>
-      <x:c r="J383" s="60"/>
-      <x:c r="K383" s="50"/>
+      <x:c r="J383" s="60" t="str">
+        <x:f>IF(A383="","",IF(K383="Subscription","",IF(E383=0,"",IF(ISNUMBER(G383),G383/E383,IF(ISNUMBER(I383),-ABS(I383)/E383,IF(ISNUMBER(H383),0,IF(AND(ISNUMBER(F383),ISNUMBER(E383),E383&gt;0,F383&gt;E383),(F383-E383)/E383,IF(AND(ISNUMBER(F383),ISNUMBER(E383),E383&gt;0,F383=E383),0,IF(AND(ISNUMBER(F383),ISNUMBER(E383),E383&gt;0,F383=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K383" s="50" t="str">
+        <x:f>IF(A383="","",IF(AND(ISNUMBER(E383),E383=0,OR(ISNUMBER(SEARCH("Free",D383&amp;"")),AND(ISNUMBER(F383),F383=0))),"Subscription",IF(ISNUMBER(G383),"Profit",IF(ISNUMBER(I383),"Loss",IF(ISNUMBER(H383),"Draw",IF(AND(ISNUMBER(F383),ISNUMBER(E383),E383&gt;0,F383&gt;E383),"Profit",IF(AND(ISNUMBER(F383),ISNUMBER(E383),E383&gt;0,F383=E383),"Draw",IF(AND(ISNUMBER(F383),ISNUMBER(E383),E383&gt;0,F383=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L383" s="50"/>
       <x:c r="M383" s="58"/>
       <x:c r="N383" s="58"/>
@@ -14046,8 +15562,12 @@
       <x:c r="G384" s="58"/>
       <x:c r="H384" s="58"/>
       <x:c r="I384" s="58"/>
-      <x:c r="J384" s="60"/>
-      <x:c r="K384" s="50"/>
+      <x:c r="J384" s="60" t="str">
+        <x:f>IF(A384="","",IF(K384="Subscription","",IF(E384=0,"",IF(ISNUMBER(G384),G384/E384,IF(ISNUMBER(I384),-ABS(I384)/E384,IF(ISNUMBER(H384),0,IF(AND(ISNUMBER(F384),ISNUMBER(E384),E384&gt;0,F384&gt;E384),(F384-E384)/E384,IF(AND(ISNUMBER(F384),ISNUMBER(E384),E384&gt;0,F384=E384),0,IF(AND(ISNUMBER(F384),ISNUMBER(E384),E384&gt;0,F384=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K384" s="50" t="str">
+        <x:f>IF(A384="","",IF(AND(ISNUMBER(E384),E384=0,OR(ISNUMBER(SEARCH("Free",D384&amp;"")),AND(ISNUMBER(F384),F384=0))),"Subscription",IF(ISNUMBER(G384),"Profit",IF(ISNUMBER(I384),"Loss",IF(ISNUMBER(H384),"Draw",IF(AND(ISNUMBER(F384),ISNUMBER(E384),E384&gt;0,F384&gt;E384),"Profit",IF(AND(ISNUMBER(F384),ISNUMBER(E384),E384&gt;0,F384=E384),"Draw",IF(AND(ISNUMBER(F384),ISNUMBER(E384),E384&gt;0,F384=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L384" s="50"/>
       <x:c r="M384" s="58"/>
       <x:c r="N384" s="58"/>
@@ -14079,8 +15599,12 @@
       <x:c r="G385" s="58"/>
       <x:c r="H385" s="58"/>
       <x:c r="I385" s="58"/>
-      <x:c r="J385" s="60"/>
-      <x:c r="K385" s="50"/>
+      <x:c r="J385" s="60" t="str">
+        <x:f>IF(A385="","",IF(K385="Subscription","",IF(E385=0,"",IF(ISNUMBER(G385),G385/E385,IF(ISNUMBER(I385),-ABS(I385)/E385,IF(ISNUMBER(H385),0,IF(AND(ISNUMBER(F385),ISNUMBER(E385),E385&gt;0,F385&gt;E385),(F385-E385)/E385,IF(AND(ISNUMBER(F385),ISNUMBER(E385),E385&gt;0,F385=E385),0,IF(AND(ISNUMBER(F385),ISNUMBER(E385),E385&gt;0,F385=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K385" s="50" t="str">
+        <x:f>IF(A385="","",IF(AND(ISNUMBER(E385),E385=0,OR(ISNUMBER(SEARCH("Free",D385&amp;"")),AND(ISNUMBER(F385),F385=0))),"Subscription",IF(ISNUMBER(G385),"Profit",IF(ISNUMBER(I385),"Loss",IF(ISNUMBER(H385),"Draw",IF(AND(ISNUMBER(F385),ISNUMBER(E385),E385&gt;0,F385&gt;E385),"Profit",IF(AND(ISNUMBER(F385),ISNUMBER(E385),E385&gt;0,F385=E385),"Draw",IF(AND(ISNUMBER(F385),ISNUMBER(E385),E385&gt;0,F385=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L385" s="50"/>
       <x:c r="M385" s="58"/>
       <x:c r="N385" s="58"/>
@@ -14112,8 +15636,12 @@
       <x:c r="G386" s="58"/>
       <x:c r="H386" s="58"/>
       <x:c r="I386" s="58"/>
-      <x:c r="J386" s="60"/>
-      <x:c r="K386" s="50"/>
+      <x:c r="J386" s="60" t="str">
+        <x:f>IF(A386="","",IF(K386="Subscription","",IF(E386=0,"",IF(ISNUMBER(G386),G386/E386,IF(ISNUMBER(I386),-ABS(I386)/E386,IF(ISNUMBER(H386),0,IF(AND(ISNUMBER(F386),ISNUMBER(E386),E386&gt;0,F386&gt;E386),(F386-E386)/E386,IF(AND(ISNUMBER(F386),ISNUMBER(E386),E386&gt;0,F386=E386),0,IF(AND(ISNUMBER(F386),ISNUMBER(E386),E386&gt;0,F386=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K386" s="50" t="str">
+        <x:f>IF(A386="","",IF(AND(ISNUMBER(E386),E386=0,OR(ISNUMBER(SEARCH("Free",D386&amp;"")),AND(ISNUMBER(F386),F386=0))),"Subscription",IF(ISNUMBER(G386),"Profit",IF(ISNUMBER(I386),"Loss",IF(ISNUMBER(H386),"Draw",IF(AND(ISNUMBER(F386),ISNUMBER(E386),E386&gt;0,F386&gt;E386),"Profit",IF(AND(ISNUMBER(F386),ISNUMBER(E386),E386&gt;0,F386=E386),"Draw",IF(AND(ISNUMBER(F386),ISNUMBER(E386),E386&gt;0,F386=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L386" s="50"/>
       <x:c r="M386" s="58"/>
       <x:c r="N386" s="58"/>
@@ -14145,8 +15673,12 @@
       <x:c r="G387" s="58"/>
       <x:c r="H387" s="58"/>
       <x:c r="I387" s="58"/>
-      <x:c r="J387" s="60"/>
-      <x:c r="K387" s="50"/>
+      <x:c r="J387" s="60" t="str">
+        <x:f>IF(A387="","",IF(K387="Subscription","",IF(E387=0,"",IF(ISNUMBER(G387),G387/E387,IF(ISNUMBER(I387),-ABS(I387)/E387,IF(ISNUMBER(H387),0,IF(AND(ISNUMBER(F387),ISNUMBER(E387),E387&gt;0,F387&gt;E387),(F387-E387)/E387,IF(AND(ISNUMBER(F387),ISNUMBER(E387),E387&gt;0,F387=E387),0,IF(AND(ISNUMBER(F387),ISNUMBER(E387),E387&gt;0,F387=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K387" s="50" t="str">
+        <x:f>IF(A387="","",IF(AND(ISNUMBER(E387),E387=0,OR(ISNUMBER(SEARCH("Free",D387&amp;"")),AND(ISNUMBER(F387),F387=0))),"Subscription",IF(ISNUMBER(G387),"Profit",IF(ISNUMBER(I387),"Loss",IF(ISNUMBER(H387),"Draw",IF(AND(ISNUMBER(F387),ISNUMBER(E387),E387&gt;0,F387&gt;E387),"Profit",IF(AND(ISNUMBER(F387),ISNUMBER(E387),E387&gt;0,F387=E387),"Draw",IF(AND(ISNUMBER(F387),ISNUMBER(E387),E387&gt;0,F387=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L387" s="50"/>
       <x:c r="M387" s="58"/>
       <x:c r="N387" s="58"/>
@@ -14178,8 +15710,12 @@
       <x:c r="G388" s="58"/>
       <x:c r="H388" s="58"/>
       <x:c r="I388" s="58"/>
-      <x:c r="J388" s="60"/>
-      <x:c r="K388" s="50"/>
+      <x:c r="J388" s="60" t="str">
+        <x:f>IF(A388="","",IF(K388="Subscription","",IF(E388=0,"",IF(ISNUMBER(G388),G388/E388,IF(ISNUMBER(I388),-ABS(I388)/E388,IF(ISNUMBER(H388),0,IF(AND(ISNUMBER(F388),ISNUMBER(E388),E388&gt;0,F388&gt;E388),(F388-E388)/E388,IF(AND(ISNUMBER(F388),ISNUMBER(E388),E388&gt;0,F388=E388),0,IF(AND(ISNUMBER(F388),ISNUMBER(E388),E388&gt;0,F388=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K388" s="50" t="str">
+        <x:f>IF(A388="","",IF(AND(ISNUMBER(E388),E388=0,OR(ISNUMBER(SEARCH("Free",D388&amp;"")),AND(ISNUMBER(F388),F388=0))),"Subscription",IF(ISNUMBER(G388),"Profit",IF(ISNUMBER(I388),"Loss",IF(ISNUMBER(H388),"Draw",IF(AND(ISNUMBER(F388),ISNUMBER(E388),E388&gt;0,F388&gt;E388),"Profit",IF(AND(ISNUMBER(F388),ISNUMBER(E388),E388&gt;0,F388=E388),"Draw",IF(AND(ISNUMBER(F388),ISNUMBER(E388),E388&gt;0,F388=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L388" s="50"/>
       <x:c r="M388" s="58"/>
       <x:c r="N388" s="58"/>
@@ -14211,8 +15747,12 @@
       <x:c r="G389" s="58"/>
       <x:c r="H389" s="58"/>
       <x:c r="I389" s="58"/>
-      <x:c r="J389" s="60"/>
-      <x:c r="K389" s="50"/>
+      <x:c r="J389" s="60" t="str">
+        <x:f>IF(A389="","",IF(K389="Subscription","",IF(E389=0,"",IF(ISNUMBER(G389),G389/E389,IF(ISNUMBER(I389),-ABS(I389)/E389,IF(ISNUMBER(H389),0,IF(AND(ISNUMBER(F389),ISNUMBER(E389),E389&gt;0,F389&gt;E389),(F389-E389)/E389,IF(AND(ISNUMBER(F389),ISNUMBER(E389),E389&gt;0,F389=E389),0,IF(AND(ISNUMBER(F389),ISNUMBER(E389),E389&gt;0,F389=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K389" s="50" t="str">
+        <x:f>IF(A389="","",IF(AND(ISNUMBER(E389),E389=0,OR(ISNUMBER(SEARCH("Free",D389&amp;"")),AND(ISNUMBER(F389),F389=0))),"Subscription",IF(ISNUMBER(G389),"Profit",IF(ISNUMBER(I389),"Loss",IF(ISNUMBER(H389),"Draw",IF(AND(ISNUMBER(F389),ISNUMBER(E389),E389&gt;0,F389&gt;E389),"Profit",IF(AND(ISNUMBER(F389),ISNUMBER(E389),E389&gt;0,F389=E389),"Draw",IF(AND(ISNUMBER(F389),ISNUMBER(E389),E389&gt;0,F389=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L389" s="50"/>
       <x:c r="M389" s="58"/>
       <x:c r="N389" s="58"/>
@@ -14244,8 +15784,12 @@
       <x:c r="G390" s="58"/>
       <x:c r="H390" s="58"/>
       <x:c r="I390" s="58"/>
-      <x:c r="J390" s="60"/>
-      <x:c r="K390" s="50"/>
+      <x:c r="J390" s="60" t="str">
+        <x:f>IF(A390="","",IF(K390="Subscription","",IF(E390=0,"",IF(ISNUMBER(G390),G390/E390,IF(ISNUMBER(I390),-ABS(I390)/E390,IF(ISNUMBER(H390),0,IF(AND(ISNUMBER(F390),ISNUMBER(E390),E390&gt;0,F390&gt;E390),(F390-E390)/E390,IF(AND(ISNUMBER(F390),ISNUMBER(E390),E390&gt;0,F390=E390),0,IF(AND(ISNUMBER(F390),ISNUMBER(E390),E390&gt;0,F390=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K390" s="50" t="str">
+        <x:f>IF(A390="","",IF(AND(ISNUMBER(E390),E390=0,OR(ISNUMBER(SEARCH("Free",D390&amp;"")),AND(ISNUMBER(F390),F390=0))),"Subscription",IF(ISNUMBER(G390),"Profit",IF(ISNUMBER(I390),"Loss",IF(ISNUMBER(H390),"Draw",IF(AND(ISNUMBER(F390),ISNUMBER(E390),E390&gt;0,F390&gt;E390),"Profit",IF(AND(ISNUMBER(F390),ISNUMBER(E390),E390&gt;0,F390=E390),"Draw",IF(AND(ISNUMBER(F390),ISNUMBER(E390),E390&gt;0,F390=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L390" s="50"/>
       <x:c r="M390" s="58"/>
       <x:c r="N390" s="58"/>
@@ -14277,8 +15821,12 @@
       <x:c r="G391" s="58"/>
       <x:c r="H391" s="58"/>
       <x:c r="I391" s="58"/>
-      <x:c r="J391" s="60"/>
-      <x:c r="K391" s="50"/>
+      <x:c r="J391" s="60" t="str">
+        <x:f>IF(A391="","",IF(K391="Subscription","",IF(E391=0,"",IF(ISNUMBER(G391),G391/E391,IF(ISNUMBER(I391),-ABS(I391)/E391,IF(ISNUMBER(H391),0,IF(AND(ISNUMBER(F391),ISNUMBER(E391),E391&gt;0,F391&gt;E391),(F391-E391)/E391,IF(AND(ISNUMBER(F391),ISNUMBER(E391),E391&gt;0,F391=E391),0,IF(AND(ISNUMBER(F391),ISNUMBER(E391),E391&gt;0,F391=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K391" s="50" t="str">
+        <x:f>IF(A391="","",IF(AND(ISNUMBER(E391),E391=0,OR(ISNUMBER(SEARCH("Free",D391&amp;"")),AND(ISNUMBER(F391),F391=0))),"Subscription",IF(ISNUMBER(G391),"Profit",IF(ISNUMBER(I391),"Loss",IF(ISNUMBER(H391),"Draw",IF(AND(ISNUMBER(F391),ISNUMBER(E391),E391&gt;0,F391&gt;E391),"Profit",IF(AND(ISNUMBER(F391),ISNUMBER(E391),E391&gt;0,F391=E391),"Draw",IF(AND(ISNUMBER(F391),ISNUMBER(E391),E391&gt;0,F391=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L391" s="50"/>
       <x:c r="M391" s="58"/>
       <x:c r="N391" s="58"/>
@@ -14310,8 +15858,12 @@
       <x:c r="G392" s="58"/>
       <x:c r="H392" s="58"/>
       <x:c r="I392" s="58"/>
-      <x:c r="J392" s="60"/>
-      <x:c r="K392" s="50"/>
+      <x:c r="J392" s="60" t="str">
+        <x:f>IF(A392="","",IF(K392="Subscription","",IF(E392=0,"",IF(ISNUMBER(G392),G392/E392,IF(ISNUMBER(I392),-ABS(I392)/E392,IF(ISNUMBER(H392),0,IF(AND(ISNUMBER(F392),ISNUMBER(E392),E392&gt;0,F392&gt;E392),(F392-E392)/E392,IF(AND(ISNUMBER(F392),ISNUMBER(E392),E392&gt;0,F392=E392),0,IF(AND(ISNUMBER(F392),ISNUMBER(E392),E392&gt;0,F392=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K392" s="50" t="str">
+        <x:f>IF(A392="","",IF(AND(ISNUMBER(E392),E392=0,OR(ISNUMBER(SEARCH("Free",D392&amp;"")),AND(ISNUMBER(F392),F392=0))),"Subscription",IF(ISNUMBER(G392),"Profit",IF(ISNUMBER(I392),"Loss",IF(ISNUMBER(H392),"Draw",IF(AND(ISNUMBER(F392),ISNUMBER(E392),E392&gt;0,F392&gt;E392),"Profit",IF(AND(ISNUMBER(F392),ISNUMBER(E392),E392&gt;0,F392=E392),"Draw",IF(AND(ISNUMBER(F392),ISNUMBER(E392),E392&gt;0,F392=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L392" s="50"/>
       <x:c r="M392" s="58"/>
       <x:c r="N392" s="58"/>
@@ -14343,8 +15895,12 @@
       <x:c r="G393" s="58"/>
       <x:c r="H393" s="58"/>
       <x:c r="I393" s="58"/>
-      <x:c r="J393" s="60"/>
-      <x:c r="K393" s="50"/>
+      <x:c r="J393" s="60" t="str">
+        <x:f>IF(A393="","",IF(K393="Subscription","",IF(E393=0,"",IF(ISNUMBER(G393),G393/E393,IF(ISNUMBER(I393),-ABS(I393)/E393,IF(ISNUMBER(H393),0,IF(AND(ISNUMBER(F393),ISNUMBER(E393),E393&gt;0,F393&gt;E393),(F393-E393)/E393,IF(AND(ISNUMBER(F393),ISNUMBER(E393),E393&gt;0,F393=E393),0,IF(AND(ISNUMBER(F393),ISNUMBER(E393),E393&gt;0,F393=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K393" s="50" t="str">
+        <x:f>IF(A393="","",IF(AND(ISNUMBER(E393),E393=0,OR(ISNUMBER(SEARCH("Free",D393&amp;"")),AND(ISNUMBER(F393),F393=0))),"Subscription",IF(ISNUMBER(G393),"Profit",IF(ISNUMBER(I393),"Loss",IF(ISNUMBER(H393),"Draw",IF(AND(ISNUMBER(F393),ISNUMBER(E393),E393&gt;0,F393&gt;E393),"Profit",IF(AND(ISNUMBER(F393),ISNUMBER(E393),E393&gt;0,F393=E393),"Draw",IF(AND(ISNUMBER(F393),ISNUMBER(E393),E393&gt;0,F393=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L393" s="50"/>
       <x:c r="M393" s="58"/>
       <x:c r="N393" s="58"/>
@@ -14376,8 +15932,12 @@
       <x:c r="G394" s="58"/>
       <x:c r="H394" s="58"/>
       <x:c r="I394" s="58"/>
-      <x:c r="J394" s="60"/>
-      <x:c r="K394" s="50"/>
+      <x:c r="J394" s="60" t="str">
+        <x:f>IF(A394="","",IF(K394="Subscription","",IF(E394=0,"",IF(ISNUMBER(G394),G394/E394,IF(ISNUMBER(I394),-ABS(I394)/E394,IF(ISNUMBER(H394),0,IF(AND(ISNUMBER(F394),ISNUMBER(E394),E394&gt;0,F394&gt;E394),(F394-E394)/E394,IF(AND(ISNUMBER(F394),ISNUMBER(E394),E394&gt;0,F394=E394),0,IF(AND(ISNUMBER(F394),ISNUMBER(E394),E394&gt;0,F394=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K394" s="50" t="str">
+        <x:f>IF(A394="","",IF(AND(ISNUMBER(E394),E394=0,OR(ISNUMBER(SEARCH("Free",D394&amp;"")),AND(ISNUMBER(F394),F394=0))),"Subscription",IF(ISNUMBER(G394),"Profit",IF(ISNUMBER(I394),"Loss",IF(ISNUMBER(H394),"Draw",IF(AND(ISNUMBER(F394),ISNUMBER(E394),E394&gt;0,F394&gt;E394),"Profit",IF(AND(ISNUMBER(F394),ISNUMBER(E394),E394&gt;0,F394=E394),"Draw",IF(AND(ISNUMBER(F394),ISNUMBER(E394),E394&gt;0,F394=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L394" s="50"/>
       <x:c r="M394" s="58"/>
       <x:c r="N394" s="58"/>
@@ -14409,8 +15969,12 @@
       <x:c r="G395" s="58"/>
       <x:c r="H395" s="58"/>
       <x:c r="I395" s="58"/>
-      <x:c r="J395" s="60"/>
-      <x:c r="K395" s="50"/>
+      <x:c r="J395" s="60" t="str">
+        <x:f>IF(A395="","",IF(K395="Subscription","",IF(E395=0,"",IF(ISNUMBER(G395),G395/E395,IF(ISNUMBER(I395),-ABS(I395)/E395,IF(ISNUMBER(H395),0,IF(AND(ISNUMBER(F395),ISNUMBER(E395),E395&gt;0,F395&gt;E395),(F395-E395)/E395,IF(AND(ISNUMBER(F395),ISNUMBER(E395),E395&gt;0,F395=E395),0,IF(AND(ISNUMBER(F395),ISNUMBER(E395),E395&gt;0,F395=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K395" s="50" t="str">
+        <x:f>IF(A395="","",IF(AND(ISNUMBER(E395),E395=0,OR(ISNUMBER(SEARCH("Free",D395&amp;"")),AND(ISNUMBER(F395),F395=0))),"Subscription",IF(ISNUMBER(G395),"Profit",IF(ISNUMBER(I395),"Loss",IF(ISNUMBER(H395),"Draw",IF(AND(ISNUMBER(F395),ISNUMBER(E395),E395&gt;0,F395&gt;E395),"Profit",IF(AND(ISNUMBER(F395),ISNUMBER(E395),E395&gt;0,F395=E395),"Draw",IF(AND(ISNUMBER(F395),ISNUMBER(E395),E395&gt;0,F395=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L395" s="50"/>
       <x:c r="M395" s="58"/>
       <x:c r="N395" s="58"/>
@@ -14442,8 +16006,12 @@
       <x:c r="G396" s="58"/>
       <x:c r="H396" s="58"/>
       <x:c r="I396" s="58"/>
-      <x:c r="J396" s="60"/>
-      <x:c r="K396" s="50"/>
+      <x:c r="J396" s="60" t="str">
+        <x:f>IF(A396="","",IF(K396="Subscription","",IF(E396=0,"",IF(ISNUMBER(G396),G396/E396,IF(ISNUMBER(I396),-ABS(I396)/E396,IF(ISNUMBER(H396),0,IF(AND(ISNUMBER(F396),ISNUMBER(E396),E396&gt;0,F396&gt;E396),(F396-E396)/E396,IF(AND(ISNUMBER(F396),ISNUMBER(E396),E396&gt;0,F396=E396),0,IF(AND(ISNUMBER(F396),ISNUMBER(E396),E396&gt;0,F396=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K396" s="50" t="str">
+        <x:f>IF(A396="","",IF(AND(ISNUMBER(E396),E396=0,OR(ISNUMBER(SEARCH("Free",D396&amp;"")),AND(ISNUMBER(F396),F396=0))),"Subscription",IF(ISNUMBER(G396),"Profit",IF(ISNUMBER(I396),"Loss",IF(ISNUMBER(H396),"Draw",IF(AND(ISNUMBER(F396),ISNUMBER(E396),E396&gt;0,F396&gt;E396),"Profit",IF(AND(ISNUMBER(F396),ISNUMBER(E396),E396&gt;0,F396=E396),"Draw",IF(AND(ISNUMBER(F396),ISNUMBER(E396),E396&gt;0,F396=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L396" s="50"/>
       <x:c r="M396" s="58"/>
       <x:c r="N396" s="58"/>
@@ -14475,8 +16043,12 @@
       <x:c r="G397" s="58"/>
       <x:c r="H397" s="58"/>
       <x:c r="I397" s="58"/>
-      <x:c r="J397" s="60"/>
-      <x:c r="K397" s="50"/>
+      <x:c r="J397" s="60" t="str">
+        <x:f>IF(A397="","",IF(K397="Subscription","",IF(E397=0,"",IF(ISNUMBER(G397),G397/E397,IF(ISNUMBER(I397),-ABS(I397)/E397,IF(ISNUMBER(H397),0,IF(AND(ISNUMBER(F397),ISNUMBER(E397),E397&gt;0,F397&gt;E397),(F397-E397)/E397,IF(AND(ISNUMBER(F397),ISNUMBER(E397),E397&gt;0,F397=E397),0,IF(AND(ISNUMBER(F397),ISNUMBER(E397),E397&gt;0,F397=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K397" s="50" t="str">
+        <x:f>IF(A397="","",IF(AND(ISNUMBER(E397),E397=0,OR(ISNUMBER(SEARCH("Free",D397&amp;"")),AND(ISNUMBER(F397),F397=0))),"Subscription",IF(ISNUMBER(G397),"Profit",IF(ISNUMBER(I397),"Loss",IF(ISNUMBER(H397),"Draw",IF(AND(ISNUMBER(F397),ISNUMBER(E397),E397&gt;0,F397&gt;E397),"Profit",IF(AND(ISNUMBER(F397),ISNUMBER(E397),E397&gt;0,F397=E397),"Draw",IF(AND(ISNUMBER(F397),ISNUMBER(E397),E397&gt;0,F397=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L397" s="50"/>
       <x:c r="M397" s="58"/>
       <x:c r="N397" s="58"/>
@@ -14508,8 +16080,12 @@
       <x:c r="G398" s="58"/>
       <x:c r="H398" s="58"/>
       <x:c r="I398" s="58"/>
-      <x:c r="J398" s="60"/>
-      <x:c r="K398" s="50"/>
+      <x:c r="J398" s="60" t="str">
+        <x:f>IF(A398="","",IF(K398="Subscription","",IF(E398=0,"",IF(ISNUMBER(G398),G398/E398,IF(ISNUMBER(I398),-ABS(I398)/E398,IF(ISNUMBER(H398),0,IF(AND(ISNUMBER(F398),ISNUMBER(E398),E398&gt;0,F398&gt;E398),(F398-E398)/E398,IF(AND(ISNUMBER(F398),ISNUMBER(E398),E398&gt;0,F398=E398),0,IF(AND(ISNUMBER(F398),ISNUMBER(E398),E398&gt;0,F398=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K398" s="50" t="str">
+        <x:f>IF(A398="","",IF(AND(ISNUMBER(E398),E398=0,OR(ISNUMBER(SEARCH("Free",D398&amp;"")),AND(ISNUMBER(F398),F398=0))),"Subscription",IF(ISNUMBER(G398),"Profit",IF(ISNUMBER(I398),"Loss",IF(ISNUMBER(H398),"Draw",IF(AND(ISNUMBER(F398),ISNUMBER(E398),E398&gt;0,F398&gt;E398),"Profit",IF(AND(ISNUMBER(F398),ISNUMBER(E398),E398&gt;0,F398=E398),"Draw",IF(AND(ISNUMBER(F398),ISNUMBER(E398),E398&gt;0,F398=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L398" s="50"/>
       <x:c r="M398" s="58"/>
       <x:c r="N398" s="58"/>
@@ -14541,8 +16117,12 @@
       <x:c r="G399" s="58"/>
       <x:c r="H399" s="58"/>
       <x:c r="I399" s="58"/>
-      <x:c r="J399" s="60"/>
-      <x:c r="K399" s="50"/>
+      <x:c r="J399" s="60" t="str">
+        <x:f>IF(A399="","",IF(K399="Subscription","",IF(E399=0,"",IF(ISNUMBER(G399),G399/E399,IF(ISNUMBER(I399),-ABS(I399)/E399,IF(ISNUMBER(H399),0,IF(AND(ISNUMBER(F399),ISNUMBER(E399),E399&gt;0,F399&gt;E399),(F399-E399)/E399,IF(AND(ISNUMBER(F399),ISNUMBER(E399),E399&gt;0,F399=E399),0,IF(AND(ISNUMBER(F399),ISNUMBER(E399),E399&gt;0,F399=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K399" s="50" t="str">
+        <x:f>IF(A399="","",IF(AND(ISNUMBER(E399),E399=0,OR(ISNUMBER(SEARCH("Free",D399&amp;"")),AND(ISNUMBER(F399),F399=0))),"Subscription",IF(ISNUMBER(G399),"Profit",IF(ISNUMBER(I399),"Loss",IF(ISNUMBER(H399),"Draw",IF(AND(ISNUMBER(F399),ISNUMBER(E399),E399&gt;0,F399&gt;E399),"Profit",IF(AND(ISNUMBER(F399),ISNUMBER(E399),E399&gt;0,F399=E399),"Draw",IF(AND(ISNUMBER(F399),ISNUMBER(E399),E399&gt;0,F399=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L399" s="50"/>
       <x:c r="M399" s="58"/>
       <x:c r="N399" s="58"/>
@@ -14574,8 +16154,12 @@
       <x:c r="G400" s="58"/>
       <x:c r="H400" s="58"/>
       <x:c r="I400" s="58"/>
-      <x:c r="J400" s="60"/>
-      <x:c r="K400" s="50"/>
+      <x:c r="J400" s="60" t="str">
+        <x:f>IF(A400="","",IF(K400="Subscription","",IF(E400=0,"",IF(ISNUMBER(G400),G400/E400,IF(ISNUMBER(I400),-ABS(I400)/E400,IF(ISNUMBER(H400),0,IF(AND(ISNUMBER(F400),ISNUMBER(E400),E400&gt;0,F400&gt;E400),(F400-E400)/E400,IF(AND(ISNUMBER(F400),ISNUMBER(E400),E400&gt;0,F400=E400),0,IF(AND(ISNUMBER(F400),ISNUMBER(E400),E400&gt;0,F400=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K400" s="50" t="str">
+        <x:f>IF(A400="","",IF(AND(ISNUMBER(E400),E400=0,OR(ISNUMBER(SEARCH("Free",D400&amp;"")),AND(ISNUMBER(F400),F400=0))),"Subscription",IF(ISNUMBER(G400),"Profit",IF(ISNUMBER(I400),"Loss",IF(ISNUMBER(H400),"Draw",IF(AND(ISNUMBER(F400),ISNUMBER(E400),E400&gt;0,F400&gt;E400),"Profit",IF(AND(ISNUMBER(F400),ISNUMBER(E400),E400&gt;0,F400=E400),"Draw",IF(AND(ISNUMBER(F400),ISNUMBER(E400),E400&gt;0,F400=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L400" s="50"/>
       <x:c r="M400" s="58"/>
       <x:c r="N400" s="58"/>
@@ -14607,8 +16191,12 @@
       <x:c r="G401" s="58"/>
       <x:c r="H401" s="58"/>
       <x:c r="I401" s="58"/>
-      <x:c r="J401" s="60"/>
-      <x:c r="K401" s="50"/>
+      <x:c r="J401" s="60" t="str">
+        <x:f>IF(A401="","",IF(K401="Subscription","",IF(E401=0,"",IF(ISNUMBER(G401),G401/E401,IF(ISNUMBER(I401),-ABS(I401)/E401,IF(ISNUMBER(H401),0,IF(AND(ISNUMBER(F401),ISNUMBER(E401),E401&gt;0,F401&gt;E401),(F401-E401)/E401,IF(AND(ISNUMBER(F401),ISNUMBER(E401),E401&gt;0,F401=E401),0,IF(AND(ISNUMBER(F401),ISNUMBER(E401),E401&gt;0,F401=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K401" s="50" t="str">
+        <x:f>IF(A401="","",IF(AND(ISNUMBER(E401),E401=0,OR(ISNUMBER(SEARCH("Free",D401&amp;"")),AND(ISNUMBER(F401),F401=0))),"Subscription",IF(ISNUMBER(G401),"Profit",IF(ISNUMBER(I401),"Loss",IF(ISNUMBER(H401),"Draw",IF(AND(ISNUMBER(F401),ISNUMBER(E401),E401&gt;0,F401&gt;E401),"Profit",IF(AND(ISNUMBER(F401),ISNUMBER(E401),E401&gt;0,F401=E401),"Draw",IF(AND(ISNUMBER(F401),ISNUMBER(E401),E401&gt;0,F401=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L401" s="50"/>
       <x:c r="M401" s="58"/>
       <x:c r="N401" s="58"/>
@@ -14640,8 +16228,12 @@
       <x:c r="G402" s="58"/>
       <x:c r="H402" s="58"/>
       <x:c r="I402" s="58"/>
-      <x:c r="J402" s="60"/>
-      <x:c r="K402" s="50"/>
+      <x:c r="J402" s="60" t="str">
+        <x:f>IF(A402="","",IF(K402="Subscription","",IF(E402=0,"",IF(ISNUMBER(G402),G402/E402,IF(ISNUMBER(I402),-ABS(I402)/E402,IF(ISNUMBER(H402),0,IF(AND(ISNUMBER(F402),ISNUMBER(E402),E402&gt;0,F402&gt;E402),(F402-E402)/E402,IF(AND(ISNUMBER(F402),ISNUMBER(E402),E402&gt;0,F402=E402),0,IF(AND(ISNUMBER(F402),ISNUMBER(E402),E402&gt;0,F402=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K402" s="50" t="str">
+        <x:f>IF(A402="","",IF(AND(ISNUMBER(E402),E402=0,OR(ISNUMBER(SEARCH("Free",D402&amp;"")),AND(ISNUMBER(F402),F402=0))),"Subscription",IF(ISNUMBER(G402),"Profit",IF(ISNUMBER(I402),"Loss",IF(ISNUMBER(H402),"Draw",IF(AND(ISNUMBER(F402),ISNUMBER(E402),E402&gt;0,F402&gt;E402),"Profit",IF(AND(ISNUMBER(F402),ISNUMBER(E402),E402&gt;0,F402=E402),"Draw",IF(AND(ISNUMBER(F402),ISNUMBER(E402),E402&gt;0,F402=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L402" s="50"/>
       <x:c r="M402" s="58"/>
       <x:c r="N402" s="58"/>
@@ -14673,8 +16265,12 @@
       <x:c r="G403" s="58"/>
       <x:c r="H403" s="58"/>
       <x:c r="I403" s="58"/>
-      <x:c r="J403" s="60"/>
-      <x:c r="K403" s="50"/>
+      <x:c r="J403" s="60" t="str">
+        <x:f>IF(A403="","",IF(K403="Subscription","",IF(E403=0,"",IF(ISNUMBER(G403),G403/E403,IF(ISNUMBER(I403),-ABS(I403)/E403,IF(ISNUMBER(H403),0,IF(AND(ISNUMBER(F403),ISNUMBER(E403),E403&gt;0,F403&gt;E403),(F403-E403)/E403,IF(AND(ISNUMBER(F403),ISNUMBER(E403),E403&gt;0,F403=E403),0,IF(AND(ISNUMBER(F403),ISNUMBER(E403),E403&gt;0,F403=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K403" s="50" t="str">
+        <x:f>IF(A403="","",IF(AND(ISNUMBER(E403),E403=0,OR(ISNUMBER(SEARCH("Free",D403&amp;"")),AND(ISNUMBER(F403),F403=0))),"Subscription",IF(ISNUMBER(G403),"Profit",IF(ISNUMBER(I403),"Loss",IF(ISNUMBER(H403),"Draw",IF(AND(ISNUMBER(F403),ISNUMBER(E403),E403&gt;0,F403&gt;E403),"Profit",IF(AND(ISNUMBER(F403),ISNUMBER(E403),E403&gt;0,F403=E403),"Draw",IF(AND(ISNUMBER(F403),ISNUMBER(E403),E403&gt;0,F403=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L403" s="50"/>
       <x:c r="M403" s="58"/>
       <x:c r="N403" s="58"/>
@@ -14706,8 +16302,12 @@
       <x:c r="G404" s="58"/>
       <x:c r="H404" s="58"/>
       <x:c r="I404" s="58"/>
-      <x:c r="J404" s="60"/>
-      <x:c r="K404" s="50"/>
+      <x:c r="J404" s="60" t="str">
+        <x:f>IF(A404="","",IF(K404="Subscription","",IF(E404=0,"",IF(ISNUMBER(G404),G404/E404,IF(ISNUMBER(I404),-ABS(I404)/E404,IF(ISNUMBER(H404),0,IF(AND(ISNUMBER(F404),ISNUMBER(E404),E404&gt;0,F404&gt;E404),(F404-E404)/E404,IF(AND(ISNUMBER(F404),ISNUMBER(E404),E404&gt;0,F404=E404),0,IF(AND(ISNUMBER(F404),ISNUMBER(E404),E404&gt;0,F404=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K404" s="50" t="str">
+        <x:f>IF(A404="","",IF(AND(ISNUMBER(E404),E404=0,OR(ISNUMBER(SEARCH("Free",D404&amp;"")),AND(ISNUMBER(F404),F404=0))),"Subscription",IF(ISNUMBER(G404),"Profit",IF(ISNUMBER(I404),"Loss",IF(ISNUMBER(H404),"Draw",IF(AND(ISNUMBER(F404),ISNUMBER(E404),E404&gt;0,F404&gt;E404),"Profit",IF(AND(ISNUMBER(F404),ISNUMBER(E404),E404&gt;0,F404=E404),"Draw",IF(AND(ISNUMBER(F404),ISNUMBER(E404),E404&gt;0,F404=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L404" s="50"/>
       <x:c r="M404" s="58"/>
       <x:c r="N404" s="58"/>
@@ -14739,8 +16339,12 @@
       <x:c r="G405" s="58"/>
       <x:c r="H405" s="58"/>
       <x:c r="I405" s="58"/>
-      <x:c r="J405" s="60"/>
-      <x:c r="K405" s="50"/>
+      <x:c r="J405" s="60" t="str">
+        <x:f>IF(A405="","",IF(K405="Subscription","",IF(E405=0,"",IF(ISNUMBER(G405),G405/E405,IF(ISNUMBER(I405),-ABS(I405)/E405,IF(ISNUMBER(H405),0,IF(AND(ISNUMBER(F405),ISNUMBER(E405),E405&gt;0,F405&gt;E405),(F405-E405)/E405,IF(AND(ISNUMBER(F405),ISNUMBER(E405),E405&gt;0,F405=E405),0,IF(AND(ISNUMBER(F405),ISNUMBER(E405),E405&gt;0,F405=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K405" s="50" t="str">
+        <x:f>IF(A405="","",IF(AND(ISNUMBER(E405),E405=0,OR(ISNUMBER(SEARCH("Free",D405&amp;"")),AND(ISNUMBER(F405),F405=0))),"Subscription",IF(ISNUMBER(G405),"Profit",IF(ISNUMBER(I405),"Loss",IF(ISNUMBER(H405),"Draw",IF(AND(ISNUMBER(F405),ISNUMBER(E405),E405&gt;0,F405&gt;E405),"Profit",IF(AND(ISNUMBER(F405),ISNUMBER(E405),E405&gt;0,F405=E405),"Draw",IF(AND(ISNUMBER(F405),ISNUMBER(E405),E405&gt;0,F405=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L405" s="50"/>
       <x:c r="M405" s="58"/>
       <x:c r="N405" s="58"/>
@@ -14772,8 +16376,12 @@
       <x:c r="G406" s="58"/>
       <x:c r="H406" s="58"/>
       <x:c r="I406" s="58"/>
-      <x:c r="J406" s="60"/>
-      <x:c r="K406" s="50"/>
+      <x:c r="J406" s="60" t="str">
+        <x:f>IF(A406="","",IF(K406="Subscription","",IF(E406=0,"",IF(ISNUMBER(G406),G406/E406,IF(ISNUMBER(I406),-ABS(I406)/E406,IF(ISNUMBER(H406),0,IF(AND(ISNUMBER(F406),ISNUMBER(E406),E406&gt;0,F406&gt;E406),(F406-E406)/E406,IF(AND(ISNUMBER(F406),ISNUMBER(E406),E406&gt;0,F406=E406),0,IF(AND(ISNUMBER(F406),ISNUMBER(E406),E406&gt;0,F406=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K406" s="50" t="str">
+        <x:f>IF(A406="","",IF(AND(ISNUMBER(E406),E406=0,OR(ISNUMBER(SEARCH("Free",D406&amp;"")),AND(ISNUMBER(F406),F406=0))),"Subscription",IF(ISNUMBER(G406),"Profit",IF(ISNUMBER(I406),"Loss",IF(ISNUMBER(H406),"Draw",IF(AND(ISNUMBER(F406),ISNUMBER(E406),E406&gt;0,F406&gt;E406),"Profit",IF(AND(ISNUMBER(F406),ISNUMBER(E406),E406&gt;0,F406=E406),"Draw",IF(AND(ISNUMBER(F406),ISNUMBER(E406),E406&gt;0,F406=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L406" s="50"/>
       <x:c r="M406" s="58"/>
       <x:c r="N406" s="58"/>
@@ -14805,8 +16413,12 @@
       <x:c r="G407" s="58"/>
       <x:c r="H407" s="58"/>
       <x:c r="I407" s="58"/>
-      <x:c r="J407" s="60"/>
-      <x:c r="K407" s="50"/>
+      <x:c r="J407" s="60" t="str">
+        <x:f>IF(A407="","",IF(K407="Subscription","",IF(E407=0,"",IF(ISNUMBER(G407),G407/E407,IF(ISNUMBER(I407),-ABS(I407)/E407,IF(ISNUMBER(H407),0,IF(AND(ISNUMBER(F407),ISNUMBER(E407),E407&gt;0,F407&gt;E407),(F407-E407)/E407,IF(AND(ISNUMBER(F407),ISNUMBER(E407),E407&gt;0,F407=E407),0,IF(AND(ISNUMBER(F407),ISNUMBER(E407),E407&gt;0,F407=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K407" s="50" t="str">
+        <x:f>IF(A407="","",IF(AND(ISNUMBER(E407),E407=0,OR(ISNUMBER(SEARCH("Free",D407&amp;"")),AND(ISNUMBER(F407),F407=0))),"Subscription",IF(ISNUMBER(G407),"Profit",IF(ISNUMBER(I407),"Loss",IF(ISNUMBER(H407),"Draw",IF(AND(ISNUMBER(F407),ISNUMBER(E407),E407&gt;0,F407&gt;E407),"Profit",IF(AND(ISNUMBER(F407),ISNUMBER(E407),E407&gt;0,F407=E407),"Draw",IF(AND(ISNUMBER(F407),ISNUMBER(E407),E407&gt;0,F407=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L407" s="50"/>
       <x:c r="M407" s="58"/>
       <x:c r="N407" s="58"/>
@@ -14838,8 +16450,12 @@
       <x:c r="G408" s="58"/>
       <x:c r="H408" s="58"/>
       <x:c r="I408" s="58"/>
-      <x:c r="J408" s="60"/>
-      <x:c r="K408" s="50"/>
+      <x:c r="J408" s="60" t="str">
+        <x:f>IF(A408="","",IF(K408="Subscription","",IF(E408=0,"",IF(ISNUMBER(G408),G408/E408,IF(ISNUMBER(I408),-ABS(I408)/E408,IF(ISNUMBER(H408),0,IF(AND(ISNUMBER(F408),ISNUMBER(E408),E408&gt;0,F408&gt;E408),(F408-E408)/E408,IF(AND(ISNUMBER(F408),ISNUMBER(E408),E408&gt;0,F408=E408),0,IF(AND(ISNUMBER(F408),ISNUMBER(E408),E408&gt;0,F408=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K408" s="50" t="str">
+        <x:f>IF(A408="","",IF(AND(ISNUMBER(E408),E408=0,OR(ISNUMBER(SEARCH("Free",D408&amp;"")),AND(ISNUMBER(F408),F408=0))),"Subscription",IF(ISNUMBER(G408),"Profit",IF(ISNUMBER(I408),"Loss",IF(ISNUMBER(H408),"Draw",IF(AND(ISNUMBER(F408),ISNUMBER(E408),E408&gt;0,F408&gt;E408),"Profit",IF(AND(ISNUMBER(F408),ISNUMBER(E408),E408&gt;0,F408=E408),"Draw",IF(AND(ISNUMBER(F408),ISNUMBER(E408),E408&gt;0,F408=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L408" s="50"/>
       <x:c r="M408" s="58"/>
       <x:c r="N408" s="58"/>
@@ -14871,8 +16487,12 @@
       <x:c r="G409" s="58"/>
       <x:c r="H409" s="58"/>
       <x:c r="I409" s="58"/>
-      <x:c r="J409" s="60"/>
-      <x:c r="K409" s="50"/>
+      <x:c r="J409" s="60" t="str">
+        <x:f>IF(A409="","",IF(K409="Subscription","",IF(E409=0,"",IF(ISNUMBER(G409),G409/E409,IF(ISNUMBER(I409),-ABS(I409)/E409,IF(ISNUMBER(H409),0,IF(AND(ISNUMBER(F409),ISNUMBER(E409),E409&gt;0,F409&gt;E409),(F409-E409)/E409,IF(AND(ISNUMBER(F409),ISNUMBER(E409),E409&gt;0,F409=E409),0,IF(AND(ISNUMBER(F409),ISNUMBER(E409),E409&gt;0,F409=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K409" s="50" t="str">
+        <x:f>IF(A409="","",IF(AND(ISNUMBER(E409),E409=0,OR(ISNUMBER(SEARCH("Free",D409&amp;"")),AND(ISNUMBER(F409),F409=0))),"Subscription",IF(ISNUMBER(G409),"Profit",IF(ISNUMBER(I409),"Loss",IF(ISNUMBER(H409),"Draw",IF(AND(ISNUMBER(F409),ISNUMBER(E409),E409&gt;0,F409&gt;E409),"Profit",IF(AND(ISNUMBER(F409),ISNUMBER(E409),E409&gt;0,F409=E409),"Draw",IF(AND(ISNUMBER(F409),ISNUMBER(E409),E409&gt;0,F409=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L409" s="50"/>
       <x:c r="M409" s="58"/>
       <x:c r="N409" s="58"/>
@@ -14904,8 +16524,12 @@
       <x:c r="G410" s="58"/>
       <x:c r="H410" s="58"/>
       <x:c r="I410" s="58"/>
-      <x:c r="J410" s="60"/>
-      <x:c r="K410" s="50"/>
+      <x:c r="J410" s="60" t="str">
+        <x:f>IF(A410="","",IF(K410="Subscription","",IF(E410=0,"",IF(ISNUMBER(G410),G410/E410,IF(ISNUMBER(I410),-ABS(I410)/E410,IF(ISNUMBER(H410),0,IF(AND(ISNUMBER(F410),ISNUMBER(E410),E410&gt;0,F410&gt;E410),(F410-E410)/E410,IF(AND(ISNUMBER(F410),ISNUMBER(E410),E410&gt;0,F410=E410),0,IF(AND(ISNUMBER(F410),ISNUMBER(E410),E410&gt;0,F410=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K410" s="50" t="str">
+        <x:f>IF(A410="","",IF(AND(ISNUMBER(E410),E410=0,OR(ISNUMBER(SEARCH("Free",D410&amp;"")),AND(ISNUMBER(F410),F410=0))),"Subscription",IF(ISNUMBER(G410),"Profit",IF(ISNUMBER(I410),"Loss",IF(ISNUMBER(H410),"Draw",IF(AND(ISNUMBER(F410),ISNUMBER(E410),E410&gt;0,F410&gt;E410),"Profit",IF(AND(ISNUMBER(F410),ISNUMBER(E410),E410&gt;0,F410=E410),"Draw",IF(AND(ISNUMBER(F410),ISNUMBER(E410),E410&gt;0,F410=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L410" s="50"/>
       <x:c r="M410" s="58"/>
       <x:c r="N410" s="58"/>
@@ -14937,8 +16561,12 @@
       <x:c r="G411" s="58"/>
       <x:c r="H411" s="58"/>
       <x:c r="I411" s="58"/>
-      <x:c r="J411" s="60"/>
-      <x:c r="K411" s="50"/>
+      <x:c r="J411" s="60" t="str">
+        <x:f>IF(A411="","",IF(K411="Subscription","",IF(E411=0,"",IF(ISNUMBER(G411),G411/E411,IF(ISNUMBER(I411),-ABS(I411)/E411,IF(ISNUMBER(H411),0,IF(AND(ISNUMBER(F411),ISNUMBER(E411),E411&gt;0,F411&gt;E411),(F411-E411)/E411,IF(AND(ISNUMBER(F411),ISNUMBER(E411),E411&gt;0,F411=E411),0,IF(AND(ISNUMBER(F411),ISNUMBER(E411),E411&gt;0,F411=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K411" s="50" t="str">
+        <x:f>IF(A411="","",IF(AND(ISNUMBER(E411),E411=0,OR(ISNUMBER(SEARCH("Free",D411&amp;"")),AND(ISNUMBER(F411),F411=0))),"Subscription",IF(ISNUMBER(G411),"Profit",IF(ISNUMBER(I411),"Loss",IF(ISNUMBER(H411),"Draw",IF(AND(ISNUMBER(F411),ISNUMBER(E411),E411&gt;0,F411&gt;E411),"Profit",IF(AND(ISNUMBER(F411),ISNUMBER(E411),E411&gt;0,F411=E411),"Draw",IF(AND(ISNUMBER(F411),ISNUMBER(E411),E411&gt;0,F411=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L411" s="50"/>
       <x:c r="M411" s="58"/>
       <x:c r="N411" s="58"/>
@@ -14970,8 +16598,12 @@
       <x:c r="G412" s="58"/>
       <x:c r="H412" s="58"/>
       <x:c r="I412" s="58"/>
-      <x:c r="J412" s="60"/>
-      <x:c r="K412" s="50"/>
+      <x:c r="J412" s="60" t="str">
+        <x:f>IF(A412="","",IF(K412="Subscription","",IF(E412=0,"",IF(ISNUMBER(G412),G412/E412,IF(ISNUMBER(I412),-ABS(I412)/E412,IF(ISNUMBER(H412),0,IF(AND(ISNUMBER(F412),ISNUMBER(E412),E412&gt;0,F412&gt;E412),(F412-E412)/E412,IF(AND(ISNUMBER(F412),ISNUMBER(E412),E412&gt;0,F412=E412),0,IF(AND(ISNUMBER(F412),ISNUMBER(E412),E412&gt;0,F412=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K412" s="50" t="str">
+        <x:f>IF(A412="","",IF(AND(ISNUMBER(E412),E412=0,OR(ISNUMBER(SEARCH("Free",D412&amp;"")),AND(ISNUMBER(F412),F412=0))),"Subscription",IF(ISNUMBER(G412),"Profit",IF(ISNUMBER(I412),"Loss",IF(ISNUMBER(H412),"Draw",IF(AND(ISNUMBER(F412),ISNUMBER(E412),E412&gt;0,F412&gt;E412),"Profit",IF(AND(ISNUMBER(F412),ISNUMBER(E412),E412&gt;0,F412=E412),"Draw",IF(AND(ISNUMBER(F412),ISNUMBER(E412),E412&gt;0,F412=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L412" s="50"/>
       <x:c r="M412" s="58"/>
       <x:c r="N412" s="58"/>
@@ -15003,8 +16635,12 @@
       <x:c r="G413" s="58"/>
       <x:c r="H413" s="58"/>
       <x:c r="I413" s="58"/>
-      <x:c r="J413" s="60"/>
-      <x:c r="K413" s="50"/>
+      <x:c r="J413" s="60" t="str">
+        <x:f>IF(A413="","",IF(K413="Subscription","",IF(E413=0,"",IF(ISNUMBER(G413),G413/E413,IF(ISNUMBER(I413),-ABS(I413)/E413,IF(ISNUMBER(H413),0,IF(AND(ISNUMBER(F413),ISNUMBER(E413),E413&gt;0,F413&gt;E413),(F413-E413)/E413,IF(AND(ISNUMBER(F413),ISNUMBER(E413),E413&gt;0,F413=E413),0,IF(AND(ISNUMBER(F413),ISNUMBER(E413),E413&gt;0,F413=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K413" s="50" t="str">
+        <x:f>IF(A413="","",IF(AND(ISNUMBER(E413),E413=0,OR(ISNUMBER(SEARCH("Free",D413&amp;"")),AND(ISNUMBER(F413),F413=0))),"Subscription",IF(ISNUMBER(G413),"Profit",IF(ISNUMBER(I413),"Loss",IF(ISNUMBER(H413),"Draw",IF(AND(ISNUMBER(F413),ISNUMBER(E413),E413&gt;0,F413&gt;E413),"Profit",IF(AND(ISNUMBER(F413),ISNUMBER(E413),E413&gt;0,F413=E413),"Draw",IF(AND(ISNUMBER(F413),ISNUMBER(E413),E413&gt;0,F413=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L413" s="50"/>
       <x:c r="M413" s="58"/>
       <x:c r="N413" s="58"/>
@@ -15036,8 +16672,12 @@
       <x:c r="G414" s="58"/>
       <x:c r="H414" s="58"/>
       <x:c r="I414" s="58"/>
-      <x:c r="J414" s="60"/>
-      <x:c r="K414" s="50"/>
+      <x:c r="J414" s="60" t="str">
+        <x:f>IF(A414="","",IF(K414="Subscription","",IF(E414=0,"",IF(ISNUMBER(G414),G414/E414,IF(ISNUMBER(I414),-ABS(I414)/E414,IF(ISNUMBER(H414),0,IF(AND(ISNUMBER(F414),ISNUMBER(E414),E414&gt;0,F414&gt;E414),(F414-E414)/E414,IF(AND(ISNUMBER(F414),ISNUMBER(E414),E414&gt;0,F414=E414),0,IF(AND(ISNUMBER(F414),ISNUMBER(E414),E414&gt;0,F414=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K414" s="50" t="str">
+        <x:f>IF(A414="","",IF(AND(ISNUMBER(E414),E414=0,OR(ISNUMBER(SEARCH("Free",D414&amp;"")),AND(ISNUMBER(F414),F414=0))),"Subscription",IF(ISNUMBER(G414),"Profit",IF(ISNUMBER(I414),"Loss",IF(ISNUMBER(H414),"Draw",IF(AND(ISNUMBER(F414),ISNUMBER(E414),E414&gt;0,F414&gt;E414),"Profit",IF(AND(ISNUMBER(F414),ISNUMBER(E414),E414&gt;0,F414=E414),"Draw",IF(AND(ISNUMBER(F414),ISNUMBER(E414),E414&gt;0,F414=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L414" s="50"/>
       <x:c r="M414" s="58"/>
       <x:c r="N414" s="58"/>
@@ -15069,8 +16709,12 @@
       <x:c r="G415" s="58"/>
       <x:c r="H415" s="58"/>
       <x:c r="I415" s="58"/>
-      <x:c r="J415" s="60"/>
-      <x:c r="K415" s="50"/>
+      <x:c r="J415" s="60" t="str">
+        <x:f>IF(A415="","",IF(K415="Subscription","",IF(E415=0,"",IF(ISNUMBER(G415),G415/E415,IF(ISNUMBER(I415),-ABS(I415)/E415,IF(ISNUMBER(H415),0,IF(AND(ISNUMBER(F415),ISNUMBER(E415),E415&gt;0,F415&gt;E415),(F415-E415)/E415,IF(AND(ISNUMBER(F415),ISNUMBER(E415),E415&gt;0,F415=E415),0,IF(AND(ISNUMBER(F415),ISNUMBER(E415),E415&gt;0,F415=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K415" s="50" t="str">
+        <x:f>IF(A415="","",IF(AND(ISNUMBER(E415),E415=0,OR(ISNUMBER(SEARCH("Free",D415&amp;"")),AND(ISNUMBER(F415),F415=0))),"Subscription",IF(ISNUMBER(G415),"Profit",IF(ISNUMBER(I415),"Loss",IF(ISNUMBER(H415),"Draw",IF(AND(ISNUMBER(F415),ISNUMBER(E415),E415&gt;0,F415&gt;E415),"Profit",IF(AND(ISNUMBER(F415),ISNUMBER(E415),E415&gt;0,F415=E415),"Draw",IF(AND(ISNUMBER(F415),ISNUMBER(E415),E415&gt;0,F415=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L415" s="50"/>
       <x:c r="M415" s="58"/>
       <x:c r="N415" s="58"/>
@@ -15102,8 +16746,12 @@
       <x:c r="G416" s="58"/>
       <x:c r="H416" s="58"/>
       <x:c r="I416" s="58"/>
-      <x:c r="J416" s="60"/>
-      <x:c r="K416" s="50"/>
+      <x:c r="J416" s="60" t="str">
+        <x:f>IF(A416="","",IF(K416="Subscription","",IF(E416=0,"",IF(ISNUMBER(G416),G416/E416,IF(ISNUMBER(I416),-ABS(I416)/E416,IF(ISNUMBER(H416),0,IF(AND(ISNUMBER(F416),ISNUMBER(E416),E416&gt;0,F416&gt;E416),(F416-E416)/E416,IF(AND(ISNUMBER(F416),ISNUMBER(E416),E416&gt;0,F416=E416),0,IF(AND(ISNUMBER(F416),ISNUMBER(E416),E416&gt;0,F416=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K416" s="50" t="str">
+        <x:f>IF(A416="","",IF(AND(ISNUMBER(E416),E416=0,OR(ISNUMBER(SEARCH("Free",D416&amp;"")),AND(ISNUMBER(F416),F416=0))),"Subscription",IF(ISNUMBER(G416),"Profit",IF(ISNUMBER(I416),"Loss",IF(ISNUMBER(H416),"Draw",IF(AND(ISNUMBER(F416),ISNUMBER(E416),E416&gt;0,F416&gt;E416),"Profit",IF(AND(ISNUMBER(F416),ISNUMBER(E416),E416&gt;0,F416=E416),"Draw",IF(AND(ISNUMBER(F416),ISNUMBER(E416),E416&gt;0,F416=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L416" s="50"/>
       <x:c r="M416" s="58"/>
       <x:c r="N416" s="58"/>
@@ -15135,8 +16783,12 @@
       <x:c r="G417" s="58"/>
       <x:c r="H417" s="58"/>
       <x:c r="I417" s="58"/>
-      <x:c r="J417" s="60"/>
-      <x:c r="K417" s="50"/>
+      <x:c r="J417" s="60" t="str">
+        <x:f>IF(A417="","",IF(K417="Subscription","",IF(E417=0,"",IF(ISNUMBER(G417),G417/E417,IF(ISNUMBER(I417),-ABS(I417)/E417,IF(ISNUMBER(H417),0,IF(AND(ISNUMBER(F417),ISNUMBER(E417),E417&gt;0,F417&gt;E417),(F417-E417)/E417,IF(AND(ISNUMBER(F417),ISNUMBER(E417),E417&gt;0,F417=E417),0,IF(AND(ISNUMBER(F417),ISNUMBER(E417),E417&gt;0,F417=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K417" s="50" t="str">
+        <x:f>IF(A417="","",IF(AND(ISNUMBER(E417),E417=0,OR(ISNUMBER(SEARCH("Free",D417&amp;"")),AND(ISNUMBER(F417),F417=0))),"Subscription",IF(ISNUMBER(G417),"Profit",IF(ISNUMBER(I417),"Loss",IF(ISNUMBER(H417),"Draw",IF(AND(ISNUMBER(F417),ISNUMBER(E417),E417&gt;0,F417&gt;E417),"Profit",IF(AND(ISNUMBER(F417),ISNUMBER(E417),E417&gt;0,F417=E417),"Draw",IF(AND(ISNUMBER(F417),ISNUMBER(E417),E417&gt;0,F417=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L417" s="50"/>
       <x:c r="M417" s="58"/>
       <x:c r="N417" s="58"/>
@@ -15168,8 +16820,12 @@
       <x:c r="G418" s="58"/>
       <x:c r="H418" s="58"/>
       <x:c r="I418" s="58"/>
-      <x:c r="J418" s="60"/>
-      <x:c r="K418" s="50"/>
+      <x:c r="J418" s="60" t="str">
+        <x:f>IF(A418="","",IF(K418="Subscription","",IF(E418=0,"",IF(ISNUMBER(G418),G418/E418,IF(ISNUMBER(I418),-ABS(I418)/E418,IF(ISNUMBER(H418),0,IF(AND(ISNUMBER(F418),ISNUMBER(E418),E418&gt;0,F418&gt;E418),(F418-E418)/E418,IF(AND(ISNUMBER(F418),ISNUMBER(E418),E418&gt;0,F418=E418),0,IF(AND(ISNUMBER(F418),ISNUMBER(E418),E418&gt;0,F418=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K418" s="50" t="str">
+        <x:f>IF(A418="","",IF(AND(ISNUMBER(E418),E418=0,OR(ISNUMBER(SEARCH("Free",D418&amp;"")),AND(ISNUMBER(F418),F418=0))),"Subscription",IF(ISNUMBER(G418),"Profit",IF(ISNUMBER(I418),"Loss",IF(ISNUMBER(H418),"Draw",IF(AND(ISNUMBER(F418),ISNUMBER(E418),E418&gt;0,F418&gt;E418),"Profit",IF(AND(ISNUMBER(F418),ISNUMBER(E418),E418&gt;0,F418=E418),"Draw",IF(AND(ISNUMBER(F418),ISNUMBER(E418),E418&gt;0,F418=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L418" s="50"/>
       <x:c r="M418" s="58"/>
       <x:c r="N418" s="58"/>
@@ -15201,8 +16857,12 @@
       <x:c r="G419" s="58"/>
       <x:c r="H419" s="58"/>
       <x:c r="I419" s="58"/>
-      <x:c r="J419" s="60"/>
-      <x:c r="K419" s="50"/>
+      <x:c r="J419" s="60" t="str">
+        <x:f>IF(A419="","",IF(K419="Subscription","",IF(E419=0,"",IF(ISNUMBER(G419),G419/E419,IF(ISNUMBER(I419),-ABS(I419)/E419,IF(ISNUMBER(H419),0,IF(AND(ISNUMBER(F419),ISNUMBER(E419),E419&gt;0,F419&gt;E419),(F419-E419)/E419,IF(AND(ISNUMBER(F419),ISNUMBER(E419),E419&gt;0,F419=E419),0,IF(AND(ISNUMBER(F419),ISNUMBER(E419),E419&gt;0,F419=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K419" s="50" t="str">
+        <x:f>IF(A419="","",IF(AND(ISNUMBER(E419),E419=0,OR(ISNUMBER(SEARCH("Free",D419&amp;"")),AND(ISNUMBER(F419),F419=0))),"Subscription",IF(ISNUMBER(G419),"Profit",IF(ISNUMBER(I419),"Loss",IF(ISNUMBER(H419),"Draw",IF(AND(ISNUMBER(F419),ISNUMBER(E419),E419&gt;0,F419&gt;E419),"Profit",IF(AND(ISNUMBER(F419),ISNUMBER(E419),E419&gt;0,F419=E419),"Draw",IF(AND(ISNUMBER(F419),ISNUMBER(E419),E419&gt;0,F419=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L419" s="50"/>
       <x:c r="M419" s="58"/>
       <x:c r="N419" s="58"/>
@@ -15234,8 +16894,12 @@
       <x:c r="G420" s="58"/>
       <x:c r="H420" s="58"/>
       <x:c r="I420" s="58"/>
-      <x:c r="J420" s="60"/>
-      <x:c r="K420" s="50"/>
+      <x:c r="J420" s="60" t="str">
+        <x:f>IF(A420="","",IF(K420="Subscription","",IF(E420=0,"",IF(ISNUMBER(G420),G420/E420,IF(ISNUMBER(I420),-ABS(I420)/E420,IF(ISNUMBER(H420),0,IF(AND(ISNUMBER(F420),ISNUMBER(E420),E420&gt;0,F420&gt;E420),(F420-E420)/E420,IF(AND(ISNUMBER(F420),ISNUMBER(E420),E420&gt;0,F420=E420),0,IF(AND(ISNUMBER(F420),ISNUMBER(E420),E420&gt;0,F420=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K420" s="50" t="str">
+        <x:f>IF(A420="","",IF(AND(ISNUMBER(E420),E420=0,OR(ISNUMBER(SEARCH("Free",D420&amp;"")),AND(ISNUMBER(F420),F420=0))),"Subscription",IF(ISNUMBER(G420),"Profit",IF(ISNUMBER(I420),"Loss",IF(ISNUMBER(H420),"Draw",IF(AND(ISNUMBER(F420),ISNUMBER(E420),E420&gt;0,F420&gt;E420),"Profit",IF(AND(ISNUMBER(F420),ISNUMBER(E420),E420&gt;0,F420=E420),"Draw",IF(AND(ISNUMBER(F420),ISNUMBER(E420),E420&gt;0,F420=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L420" s="50"/>
       <x:c r="M420" s="58"/>
       <x:c r="N420" s="58"/>
@@ -15267,8 +16931,12 @@
       <x:c r="G421" s="58"/>
       <x:c r="H421" s="58"/>
       <x:c r="I421" s="58"/>
-      <x:c r="J421" s="60"/>
-      <x:c r="K421" s="50"/>
+      <x:c r="J421" s="60" t="str">
+        <x:f>IF(A421="","",IF(K421="Subscription","",IF(E421=0,"",IF(ISNUMBER(G421),G421/E421,IF(ISNUMBER(I421),-ABS(I421)/E421,IF(ISNUMBER(H421),0,IF(AND(ISNUMBER(F421),ISNUMBER(E421),E421&gt;0,F421&gt;E421),(F421-E421)/E421,IF(AND(ISNUMBER(F421),ISNUMBER(E421),E421&gt;0,F421=E421),0,IF(AND(ISNUMBER(F421),ISNUMBER(E421),E421&gt;0,F421=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K421" s="50" t="str">
+        <x:f>IF(A421="","",IF(AND(ISNUMBER(E421),E421=0,OR(ISNUMBER(SEARCH("Free",D421&amp;"")),AND(ISNUMBER(F421),F421=0))),"Subscription",IF(ISNUMBER(G421),"Profit",IF(ISNUMBER(I421),"Loss",IF(ISNUMBER(H421),"Draw",IF(AND(ISNUMBER(F421),ISNUMBER(E421),E421&gt;0,F421&gt;E421),"Profit",IF(AND(ISNUMBER(F421),ISNUMBER(E421),E421&gt;0,F421=E421),"Draw",IF(AND(ISNUMBER(F421),ISNUMBER(E421),E421&gt;0,F421=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L421" s="50"/>
       <x:c r="M421" s="58"/>
       <x:c r="N421" s="58"/>
@@ -15300,8 +16968,12 @@
       <x:c r="G422" s="58"/>
       <x:c r="H422" s="58"/>
       <x:c r="I422" s="58"/>
-      <x:c r="J422" s="60"/>
-      <x:c r="K422" s="50"/>
+      <x:c r="J422" s="60" t="str">
+        <x:f>IF(A422="","",IF(K422="Subscription","",IF(E422=0,"",IF(ISNUMBER(G422),G422/E422,IF(ISNUMBER(I422),-ABS(I422)/E422,IF(ISNUMBER(H422),0,IF(AND(ISNUMBER(F422),ISNUMBER(E422),E422&gt;0,F422&gt;E422),(F422-E422)/E422,IF(AND(ISNUMBER(F422),ISNUMBER(E422),E422&gt;0,F422=E422),0,IF(AND(ISNUMBER(F422),ISNUMBER(E422),E422&gt;0,F422=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K422" s="50" t="str">
+        <x:f>IF(A422="","",IF(AND(ISNUMBER(E422),E422=0,OR(ISNUMBER(SEARCH("Free",D422&amp;"")),AND(ISNUMBER(F422),F422=0))),"Subscription",IF(ISNUMBER(G422),"Profit",IF(ISNUMBER(I422),"Loss",IF(ISNUMBER(H422),"Draw",IF(AND(ISNUMBER(F422),ISNUMBER(E422),E422&gt;0,F422&gt;E422),"Profit",IF(AND(ISNUMBER(F422),ISNUMBER(E422),E422&gt;0,F422=E422),"Draw",IF(AND(ISNUMBER(F422),ISNUMBER(E422),E422&gt;0,F422=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L422" s="50"/>
       <x:c r="M422" s="58"/>
       <x:c r="N422" s="58"/>
@@ -15333,8 +17005,12 @@
       <x:c r="G423" s="58"/>
       <x:c r="H423" s="58"/>
       <x:c r="I423" s="58"/>
-      <x:c r="J423" s="60"/>
-      <x:c r="K423" s="50"/>
+      <x:c r="J423" s="60" t="str">
+        <x:f>IF(A423="","",IF(K423="Subscription","",IF(E423=0,"",IF(ISNUMBER(G423),G423/E423,IF(ISNUMBER(I423),-ABS(I423)/E423,IF(ISNUMBER(H423),0,IF(AND(ISNUMBER(F423),ISNUMBER(E423),E423&gt;0,F423&gt;E423),(F423-E423)/E423,IF(AND(ISNUMBER(F423),ISNUMBER(E423),E423&gt;0,F423=E423),0,IF(AND(ISNUMBER(F423),ISNUMBER(E423),E423&gt;0,F423=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K423" s="50" t="str">
+        <x:f>IF(A423="","",IF(AND(ISNUMBER(E423),E423=0,OR(ISNUMBER(SEARCH("Free",D423&amp;"")),AND(ISNUMBER(F423),F423=0))),"Subscription",IF(ISNUMBER(G423),"Profit",IF(ISNUMBER(I423),"Loss",IF(ISNUMBER(H423),"Draw",IF(AND(ISNUMBER(F423),ISNUMBER(E423),E423&gt;0,F423&gt;E423),"Profit",IF(AND(ISNUMBER(F423),ISNUMBER(E423),E423&gt;0,F423=E423),"Draw",IF(AND(ISNUMBER(F423),ISNUMBER(E423),E423&gt;0,F423=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L423" s="50"/>
       <x:c r="M423" s="58"/>
       <x:c r="N423" s="58"/>
@@ -15366,8 +17042,12 @@
       <x:c r="G424" s="58"/>
       <x:c r="H424" s="58"/>
       <x:c r="I424" s="58"/>
-      <x:c r="J424" s="60"/>
-      <x:c r="K424" s="50"/>
+      <x:c r="J424" s="60" t="str">
+        <x:f>IF(A424="","",IF(K424="Subscription","",IF(E424=0,"",IF(ISNUMBER(G424),G424/E424,IF(ISNUMBER(I424),-ABS(I424)/E424,IF(ISNUMBER(H424),0,IF(AND(ISNUMBER(F424),ISNUMBER(E424),E424&gt;0,F424&gt;E424),(F424-E424)/E424,IF(AND(ISNUMBER(F424),ISNUMBER(E424),E424&gt;0,F424=E424),0,IF(AND(ISNUMBER(F424),ISNUMBER(E424),E424&gt;0,F424=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K424" s="50" t="str">
+        <x:f>IF(A424="","",IF(AND(ISNUMBER(E424),E424=0,OR(ISNUMBER(SEARCH("Free",D424&amp;"")),AND(ISNUMBER(F424),F424=0))),"Subscription",IF(ISNUMBER(G424),"Profit",IF(ISNUMBER(I424),"Loss",IF(ISNUMBER(H424),"Draw",IF(AND(ISNUMBER(F424),ISNUMBER(E424),E424&gt;0,F424&gt;E424),"Profit",IF(AND(ISNUMBER(F424),ISNUMBER(E424),E424&gt;0,F424=E424),"Draw",IF(AND(ISNUMBER(F424),ISNUMBER(E424),E424&gt;0,F424=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L424" s="50"/>
       <x:c r="M424" s="58"/>
       <x:c r="N424" s="58"/>
@@ -15399,8 +17079,12 @@
       <x:c r="G425" s="58"/>
       <x:c r="H425" s="58"/>
       <x:c r="I425" s="58"/>
-      <x:c r="J425" s="60"/>
-      <x:c r="K425" s="50"/>
+      <x:c r="J425" s="60" t="str">
+        <x:f>IF(A425="","",IF(K425="Subscription","",IF(E425=0,"",IF(ISNUMBER(G425),G425/E425,IF(ISNUMBER(I425),-ABS(I425)/E425,IF(ISNUMBER(H425),0,IF(AND(ISNUMBER(F425),ISNUMBER(E425),E425&gt;0,F425&gt;E425),(F425-E425)/E425,IF(AND(ISNUMBER(F425),ISNUMBER(E425),E425&gt;0,F425=E425),0,IF(AND(ISNUMBER(F425),ISNUMBER(E425),E425&gt;0,F425=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K425" s="50" t="str">
+        <x:f>IF(A425="","",IF(AND(ISNUMBER(E425),E425=0,OR(ISNUMBER(SEARCH("Free",D425&amp;"")),AND(ISNUMBER(F425),F425=0))),"Subscription",IF(ISNUMBER(G425),"Profit",IF(ISNUMBER(I425),"Loss",IF(ISNUMBER(H425),"Draw",IF(AND(ISNUMBER(F425),ISNUMBER(E425),E425&gt;0,F425&gt;E425),"Profit",IF(AND(ISNUMBER(F425),ISNUMBER(E425),E425&gt;0,F425=E425),"Draw",IF(AND(ISNUMBER(F425),ISNUMBER(E425),E425&gt;0,F425=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L425" s="50"/>
       <x:c r="M425" s="58"/>
       <x:c r="N425" s="58"/>
@@ -15432,8 +17116,12 @@
       <x:c r="G426" s="58"/>
       <x:c r="H426" s="58"/>
       <x:c r="I426" s="58"/>
-      <x:c r="J426" s="60"/>
-      <x:c r="K426" s="50"/>
+      <x:c r="J426" s="60" t="str">
+        <x:f>IF(A426="","",IF(K426="Subscription","",IF(E426=0,"",IF(ISNUMBER(G426),G426/E426,IF(ISNUMBER(I426),-ABS(I426)/E426,IF(ISNUMBER(H426),0,IF(AND(ISNUMBER(F426),ISNUMBER(E426),E426&gt;0,F426&gt;E426),(F426-E426)/E426,IF(AND(ISNUMBER(F426),ISNUMBER(E426),E426&gt;0,F426=E426),0,IF(AND(ISNUMBER(F426),ISNUMBER(E426),E426&gt;0,F426=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K426" s="50" t="str">
+        <x:f>IF(A426="","",IF(AND(ISNUMBER(E426),E426=0,OR(ISNUMBER(SEARCH("Free",D426&amp;"")),AND(ISNUMBER(F426),F426=0))),"Subscription",IF(ISNUMBER(G426),"Profit",IF(ISNUMBER(I426),"Loss",IF(ISNUMBER(H426),"Draw",IF(AND(ISNUMBER(F426),ISNUMBER(E426),E426&gt;0,F426&gt;E426),"Profit",IF(AND(ISNUMBER(F426),ISNUMBER(E426),E426&gt;0,F426=E426),"Draw",IF(AND(ISNUMBER(F426),ISNUMBER(E426),E426&gt;0,F426=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L426" s="50"/>
       <x:c r="M426" s="58"/>
       <x:c r="N426" s="58"/>
@@ -15465,8 +17153,12 @@
       <x:c r="G427" s="58"/>
       <x:c r="H427" s="58"/>
       <x:c r="I427" s="58"/>
-      <x:c r="J427" s="60"/>
-      <x:c r="K427" s="50"/>
+      <x:c r="J427" s="60" t="str">
+        <x:f>IF(A427="","",IF(K427="Subscription","",IF(E427=0,"",IF(ISNUMBER(G427),G427/E427,IF(ISNUMBER(I427),-ABS(I427)/E427,IF(ISNUMBER(H427),0,IF(AND(ISNUMBER(F427),ISNUMBER(E427),E427&gt;0,F427&gt;E427),(F427-E427)/E427,IF(AND(ISNUMBER(F427),ISNUMBER(E427),E427&gt;0,F427=E427),0,IF(AND(ISNUMBER(F427),ISNUMBER(E427),E427&gt;0,F427=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K427" s="50" t="str">
+        <x:f>IF(A427="","",IF(AND(ISNUMBER(E427),E427=0,OR(ISNUMBER(SEARCH("Free",D427&amp;"")),AND(ISNUMBER(F427),F427=0))),"Subscription",IF(ISNUMBER(G427),"Profit",IF(ISNUMBER(I427),"Loss",IF(ISNUMBER(H427),"Draw",IF(AND(ISNUMBER(F427),ISNUMBER(E427),E427&gt;0,F427&gt;E427),"Profit",IF(AND(ISNUMBER(F427),ISNUMBER(E427),E427&gt;0,F427=E427),"Draw",IF(AND(ISNUMBER(F427),ISNUMBER(E427),E427&gt;0,F427=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L427" s="50"/>
       <x:c r="M427" s="58"/>
       <x:c r="N427" s="58"/>
@@ -15498,8 +17190,12 @@
       <x:c r="G428" s="58"/>
       <x:c r="H428" s="58"/>
       <x:c r="I428" s="58"/>
-      <x:c r="J428" s="60"/>
-      <x:c r="K428" s="50"/>
+      <x:c r="J428" s="60" t="str">
+        <x:f>IF(A428="","",IF(K428="Subscription","",IF(E428=0,"",IF(ISNUMBER(G428),G428/E428,IF(ISNUMBER(I428),-ABS(I428)/E428,IF(ISNUMBER(H428),0,IF(AND(ISNUMBER(F428),ISNUMBER(E428),E428&gt;0,F428&gt;E428),(F428-E428)/E428,IF(AND(ISNUMBER(F428),ISNUMBER(E428),E428&gt;0,F428=E428),0,IF(AND(ISNUMBER(F428),ISNUMBER(E428),E428&gt;0,F428=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K428" s="50" t="str">
+        <x:f>IF(A428="","",IF(AND(ISNUMBER(E428),E428=0,OR(ISNUMBER(SEARCH("Free",D428&amp;"")),AND(ISNUMBER(F428),F428=0))),"Subscription",IF(ISNUMBER(G428),"Profit",IF(ISNUMBER(I428),"Loss",IF(ISNUMBER(H428),"Draw",IF(AND(ISNUMBER(F428),ISNUMBER(E428),E428&gt;0,F428&gt;E428),"Profit",IF(AND(ISNUMBER(F428),ISNUMBER(E428),E428&gt;0,F428=E428),"Draw",IF(AND(ISNUMBER(F428),ISNUMBER(E428),E428&gt;0,F428=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L428" s="50"/>
       <x:c r="M428" s="58"/>
       <x:c r="N428" s="58"/>
@@ -15531,8 +17227,12 @@
       <x:c r="G429" s="58"/>
       <x:c r="H429" s="58"/>
       <x:c r="I429" s="58"/>
-      <x:c r="J429" s="60"/>
-      <x:c r="K429" s="50"/>
+      <x:c r="J429" s="60" t="str">
+        <x:f>IF(A429="","",IF(K429="Subscription","",IF(E429=0,"",IF(ISNUMBER(G429),G429/E429,IF(ISNUMBER(I429),-ABS(I429)/E429,IF(ISNUMBER(H429),0,IF(AND(ISNUMBER(F429),ISNUMBER(E429),E429&gt;0,F429&gt;E429),(F429-E429)/E429,IF(AND(ISNUMBER(F429),ISNUMBER(E429),E429&gt;0,F429=E429),0,IF(AND(ISNUMBER(F429),ISNUMBER(E429),E429&gt;0,F429=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K429" s="50" t="str">
+        <x:f>IF(A429="","",IF(AND(ISNUMBER(E429),E429=0,OR(ISNUMBER(SEARCH("Free",D429&amp;"")),AND(ISNUMBER(F429),F429=0))),"Subscription",IF(ISNUMBER(G429),"Profit",IF(ISNUMBER(I429),"Loss",IF(ISNUMBER(H429),"Draw",IF(AND(ISNUMBER(F429),ISNUMBER(E429),E429&gt;0,F429&gt;E429),"Profit",IF(AND(ISNUMBER(F429),ISNUMBER(E429),E429&gt;0,F429=E429),"Draw",IF(AND(ISNUMBER(F429),ISNUMBER(E429),E429&gt;0,F429=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L429" s="50"/>
       <x:c r="M429" s="58"/>
       <x:c r="N429" s="58"/>
@@ -15564,8 +17264,12 @@
       <x:c r="G430" s="58"/>
       <x:c r="H430" s="58"/>
       <x:c r="I430" s="58"/>
-      <x:c r="J430" s="60"/>
-      <x:c r="K430" s="50"/>
+      <x:c r="J430" s="60" t="str">
+        <x:f>IF(A430="","",IF(K430="Subscription","",IF(E430=0,"",IF(ISNUMBER(G430),G430/E430,IF(ISNUMBER(I430),-ABS(I430)/E430,IF(ISNUMBER(H430),0,IF(AND(ISNUMBER(F430),ISNUMBER(E430),E430&gt;0,F430&gt;E430),(F430-E430)/E430,IF(AND(ISNUMBER(F430),ISNUMBER(E430),E430&gt;0,F430=E430),0,IF(AND(ISNUMBER(F430),ISNUMBER(E430),E430&gt;0,F430=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K430" s="50" t="str">
+        <x:f>IF(A430="","",IF(AND(ISNUMBER(E430),E430=0,OR(ISNUMBER(SEARCH("Free",D430&amp;"")),AND(ISNUMBER(F430),F430=0))),"Subscription",IF(ISNUMBER(G430),"Profit",IF(ISNUMBER(I430),"Loss",IF(ISNUMBER(H430),"Draw",IF(AND(ISNUMBER(F430),ISNUMBER(E430),E430&gt;0,F430&gt;E430),"Profit",IF(AND(ISNUMBER(F430),ISNUMBER(E430),E430&gt;0,F430=E430),"Draw",IF(AND(ISNUMBER(F430),ISNUMBER(E430),E430&gt;0,F430=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L430" s="50"/>
       <x:c r="M430" s="58"/>
       <x:c r="N430" s="58"/>
@@ -15597,8 +17301,12 @@
       <x:c r="G431" s="58"/>
       <x:c r="H431" s="58"/>
       <x:c r="I431" s="58"/>
-      <x:c r="J431" s="60"/>
-      <x:c r="K431" s="50"/>
+      <x:c r="J431" s="60" t="str">
+        <x:f>IF(A431="","",IF(K431="Subscription","",IF(E431=0,"",IF(ISNUMBER(G431),G431/E431,IF(ISNUMBER(I431),-ABS(I431)/E431,IF(ISNUMBER(H431),0,IF(AND(ISNUMBER(F431),ISNUMBER(E431),E431&gt;0,F431&gt;E431),(F431-E431)/E431,IF(AND(ISNUMBER(F431),ISNUMBER(E431),E431&gt;0,F431=E431),0,IF(AND(ISNUMBER(F431),ISNUMBER(E431),E431&gt;0,F431=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K431" s="50" t="str">
+        <x:f>IF(A431="","",IF(AND(ISNUMBER(E431),E431=0,OR(ISNUMBER(SEARCH("Free",D431&amp;"")),AND(ISNUMBER(F431),F431=0))),"Subscription",IF(ISNUMBER(G431),"Profit",IF(ISNUMBER(I431),"Loss",IF(ISNUMBER(H431),"Draw",IF(AND(ISNUMBER(F431),ISNUMBER(E431),E431&gt;0,F431&gt;E431),"Profit",IF(AND(ISNUMBER(F431),ISNUMBER(E431),E431&gt;0,F431=E431),"Draw",IF(AND(ISNUMBER(F431),ISNUMBER(E431),E431&gt;0,F431=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L431" s="50"/>
       <x:c r="M431" s="58"/>
       <x:c r="N431" s="58"/>
@@ -15630,8 +17338,12 @@
       <x:c r="G432" s="58"/>
       <x:c r="H432" s="58"/>
       <x:c r="I432" s="58"/>
-      <x:c r="J432" s="60"/>
-      <x:c r="K432" s="50"/>
+      <x:c r="J432" s="60" t="str">
+        <x:f>IF(A432="","",IF(K432="Subscription","",IF(E432=0,"",IF(ISNUMBER(G432),G432/E432,IF(ISNUMBER(I432),-ABS(I432)/E432,IF(ISNUMBER(H432),0,IF(AND(ISNUMBER(F432),ISNUMBER(E432),E432&gt;0,F432&gt;E432),(F432-E432)/E432,IF(AND(ISNUMBER(F432),ISNUMBER(E432),E432&gt;0,F432=E432),0,IF(AND(ISNUMBER(F432),ISNUMBER(E432),E432&gt;0,F432=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K432" s="50" t="str">
+        <x:f>IF(A432="","",IF(AND(ISNUMBER(E432),E432=0,OR(ISNUMBER(SEARCH("Free",D432&amp;"")),AND(ISNUMBER(F432),F432=0))),"Subscription",IF(ISNUMBER(G432),"Profit",IF(ISNUMBER(I432),"Loss",IF(ISNUMBER(H432),"Draw",IF(AND(ISNUMBER(F432),ISNUMBER(E432),E432&gt;0,F432&gt;E432),"Profit",IF(AND(ISNUMBER(F432),ISNUMBER(E432),E432&gt;0,F432=E432),"Draw",IF(AND(ISNUMBER(F432),ISNUMBER(E432),E432&gt;0,F432=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L432" s="50"/>
       <x:c r="M432" s="58"/>
       <x:c r="N432" s="58"/>
@@ -15663,8 +17375,12 @@
       <x:c r="G433" s="58"/>
       <x:c r="H433" s="58"/>
       <x:c r="I433" s="58"/>
-      <x:c r="J433" s="60"/>
-      <x:c r="K433" s="50"/>
+      <x:c r="J433" s="60" t="str">
+        <x:f>IF(A433="","",IF(K433="Subscription","",IF(E433=0,"",IF(ISNUMBER(G433),G433/E433,IF(ISNUMBER(I433),-ABS(I433)/E433,IF(ISNUMBER(H433),0,IF(AND(ISNUMBER(F433),ISNUMBER(E433),E433&gt;0,F433&gt;E433),(F433-E433)/E433,IF(AND(ISNUMBER(F433),ISNUMBER(E433),E433&gt;0,F433=E433),0,IF(AND(ISNUMBER(F433),ISNUMBER(E433),E433&gt;0,F433=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K433" s="50" t="str">
+        <x:f>IF(A433="","",IF(AND(ISNUMBER(E433),E433=0,OR(ISNUMBER(SEARCH("Free",D433&amp;"")),AND(ISNUMBER(F433),F433=0))),"Subscription",IF(ISNUMBER(G433),"Profit",IF(ISNUMBER(I433),"Loss",IF(ISNUMBER(H433),"Draw",IF(AND(ISNUMBER(F433),ISNUMBER(E433),E433&gt;0,F433&gt;E433),"Profit",IF(AND(ISNUMBER(F433),ISNUMBER(E433),E433&gt;0,F433=E433),"Draw",IF(AND(ISNUMBER(F433),ISNUMBER(E433),E433&gt;0,F433=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L433" s="50"/>
       <x:c r="M433" s="58"/>
       <x:c r="N433" s="58"/>
@@ -15696,8 +17412,12 @@
       <x:c r="G434" s="58"/>
       <x:c r="H434" s="58"/>
       <x:c r="I434" s="58"/>
-      <x:c r="J434" s="60"/>
-      <x:c r="K434" s="50"/>
+      <x:c r="J434" s="60" t="str">
+        <x:f>IF(A434="","",IF(K434="Subscription","",IF(E434=0,"",IF(ISNUMBER(G434),G434/E434,IF(ISNUMBER(I434),-ABS(I434)/E434,IF(ISNUMBER(H434),0,IF(AND(ISNUMBER(F434),ISNUMBER(E434),E434&gt;0,F434&gt;E434),(F434-E434)/E434,IF(AND(ISNUMBER(F434),ISNUMBER(E434),E434&gt;0,F434=E434),0,IF(AND(ISNUMBER(F434),ISNUMBER(E434),E434&gt;0,F434=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K434" s="50" t="str">
+        <x:f>IF(A434="","",IF(AND(ISNUMBER(E434),E434=0,OR(ISNUMBER(SEARCH("Free",D434&amp;"")),AND(ISNUMBER(F434),F434=0))),"Subscription",IF(ISNUMBER(G434),"Profit",IF(ISNUMBER(I434),"Loss",IF(ISNUMBER(H434),"Draw",IF(AND(ISNUMBER(F434),ISNUMBER(E434),E434&gt;0,F434&gt;E434),"Profit",IF(AND(ISNUMBER(F434),ISNUMBER(E434),E434&gt;0,F434=E434),"Draw",IF(AND(ISNUMBER(F434),ISNUMBER(E434),E434&gt;0,F434=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L434" s="50"/>
       <x:c r="M434" s="58"/>
       <x:c r="N434" s="58"/>
@@ -15729,8 +17449,12 @@
       <x:c r="G435" s="58"/>
       <x:c r="H435" s="58"/>
       <x:c r="I435" s="58"/>
-      <x:c r="J435" s="60"/>
-      <x:c r="K435" s="50"/>
+      <x:c r="J435" s="60" t="str">
+        <x:f>IF(A435="","",IF(K435="Subscription","",IF(E435=0,"",IF(ISNUMBER(G435),G435/E435,IF(ISNUMBER(I435),-ABS(I435)/E435,IF(ISNUMBER(H435),0,IF(AND(ISNUMBER(F435),ISNUMBER(E435),E435&gt;0,F435&gt;E435),(F435-E435)/E435,IF(AND(ISNUMBER(F435),ISNUMBER(E435),E435&gt;0,F435=E435),0,IF(AND(ISNUMBER(F435),ISNUMBER(E435),E435&gt;0,F435=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K435" s="50" t="str">
+        <x:f>IF(A435="","",IF(AND(ISNUMBER(E435),E435=0,OR(ISNUMBER(SEARCH("Free",D435&amp;"")),AND(ISNUMBER(F435),F435=0))),"Subscription",IF(ISNUMBER(G435),"Profit",IF(ISNUMBER(I435),"Loss",IF(ISNUMBER(H435),"Draw",IF(AND(ISNUMBER(F435),ISNUMBER(E435),E435&gt;0,F435&gt;E435),"Profit",IF(AND(ISNUMBER(F435),ISNUMBER(E435),E435&gt;0,F435=E435),"Draw",IF(AND(ISNUMBER(F435),ISNUMBER(E435),E435&gt;0,F435=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L435" s="50"/>
       <x:c r="M435" s="58"/>
       <x:c r="N435" s="58"/>
@@ -15762,8 +17486,12 @@
       <x:c r="G436" s="58"/>
       <x:c r="H436" s="58"/>
       <x:c r="I436" s="58"/>
-      <x:c r="J436" s="60"/>
-      <x:c r="K436" s="50"/>
+      <x:c r="J436" s="60" t="str">
+        <x:f>IF(A436="","",IF(K436="Subscription","",IF(E436=0,"",IF(ISNUMBER(G436),G436/E436,IF(ISNUMBER(I436),-ABS(I436)/E436,IF(ISNUMBER(H436),0,IF(AND(ISNUMBER(F436),ISNUMBER(E436),E436&gt;0,F436&gt;E436),(F436-E436)/E436,IF(AND(ISNUMBER(F436),ISNUMBER(E436),E436&gt;0,F436=E436),0,IF(AND(ISNUMBER(F436),ISNUMBER(E436),E436&gt;0,F436=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K436" s="50" t="str">
+        <x:f>IF(A436="","",IF(AND(ISNUMBER(E436),E436=0,OR(ISNUMBER(SEARCH("Free",D436&amp;"")),AND(ISNUMBER(F436),F436=0))),"Subscription",IF(ISNUMBER(G436),"Profit",IF(ISNUMBER(I436),"Loss",IF(ISNUMBER(H436),"Draw",IF(AND(ISNUMBER(F436),ISNUMBER(E436),E436&gt;0,F436&gt;E436),"Profit",IF(AND(ISNUMBER(F436),ISNUMBER(E436),E436&gt;0,F436=E436),"Draw",IF(AND(ISNUMBER(F436),ISNUMBER(E436),E436&gt;0,F436=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L436" s="50"/>
       <x:c r="M436" s="58"/>
       <x:c r="N436" s="58"/>
@@ -15795,8 +17523,12 @@
       <x:c r="G437" s="58"/>
       <x:c r="H437" s="58"/>
       <x:c r="I437" s="58"/>
-      <x:c r="J437" s="60"/>
-      <x:c r="K437" s="50"/>
+      <x:c r="J437" s="60" t="str">
+        <x:f>IF(A437="","",IF(K437="Subscription","",IF(E437=0,"",IF(ISNUMBER(G437),G437/E437,IF(ISNUMBER(I437),-ABS(I437)/E437,IF(ISNUMBER(H437),0,IF(AND(ISNUMBER(F437),ISNUMBER(E437),E437&gt;0,F437&gt;E437),(F437-E437)/E437,IF(AND(ISNUMBER(F437),ISNUMBER(E437),E437&gt;0,F437=E437),0,IF(AND(ISNUMBER(F437),ISNUMBER(E437),E437&gt;0,F437=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K437" s="50" t="str">
+        <x:f>IF(A437="","",IF(AND(ISNUMBER(E437),E437=0,OR(ISNUMBER(SEARCH("Free",D437&amp;"")),AND(ISNUMBER(F437),F437=0))),"Subscription",IF(ISNUMBER(G437),"Profit",IF(ISNUMBER(I437),"Loss",IF(ISNUMBER(H437),"Draw",IF(AND(ISNUMBER(F437),ISNUMBER(E437),E437&gt;0,F437&gt;E437),"Profit",IF(AND(ISNUMBER(F437),ISNUMBER(E437),E437&gt;0,F437=E437),"Draw",IF(AND(ISNUMBER(F437),ISNUMBER(E437),E437&gt;0,F437=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L437" s="50"/>
       <x:c r="M437" s="58"/>
       <x:c r="N437" s="58"/>
@@ -15828,8 +17560,12 @@
       <x:c r="G438" s="58"/>
       <x:c r="H438" s="58"/>
       <x:c r="I438" s="58"/>
-      <x:c r="J438" s="60"/>
-      <x:c r="K438" s="50"/>
+      <x:c r="J438" s="60" t="str">
+        <x:f>IF(A438="","",IF(K438="Subscription","",IF(E438=0,"",IF(ISNUMBER(G438),G438/E438,IF(ISNUMBER(I438),-ABS(I438)/E438,IF(ISNUMBER(H438),0,IF(AND(ISNUMBER(F438),ISNUMBER(E438),E438&gt;0,F438&gt;E438),(F438-E438)/E438,IF(AND(ISNUMBER(F438),ISNUMBER(E438),E438&gt;0,F438=E438),0,IF(AND(ISNUMBER(F438),ISNUMBER(E438),E438&gt;0,F438=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K438" s="50" t="str">
+        <x:f>IF(A438="","",IF(AND(ISNUMBER(E438),E438=0,OR(ISNUMBER(SEARCH("Free",D438&amp;"")),AND(ISNUMBER(F438),F438=0))),"Subscription",IF(ISNUMBER(G438),"Profit",IF(ISNUMBER(I438),"Loss",IF(ISNUMBER(H438),"Draw",IF(AND(ISNUMBER(F438),ISNUMBER(E438),E438&gt;0,F438&gt;E438),"Profit",IF(AND(ISNUMBER(F438),ISNUMBER(E438),E438&gt;0,F438=E438),"Draw",IF(AND(ISNUMBER(F438),ISNUMBER(E438),E438&gt;0,F438=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L438" s="50"/>
       <x:c r="M438" s="58"/>
       <x:c r="N438" s="58"/>
@@ -15861,8 +17597,12 @@
       <x:c r="G439" s="58"/>
       <x:c r="H439" s="58"/>
       <x:c r="I439" s="58"/>
-      <x:c r="J439" s="60"/>
-      <x:c r="K439" s="50"/>
+      <x:c r="J439" s="60" t="str">
+        <x:f>IF(A439="","",IF(K439="Subscription","",IF(E439=0,"",IF(ISNUMBER(G439),G439/E439,IF(ISNUMBER(I439),-ABS(I439)/E439,IF(ISNUMBER(H439),0,IF(AND(ISNUMBER(F439),ISNUMBER(E439),E439&gt;0,F439&gt;E439),(F439-E439)/E439,IF(AND(ISNUMBER(F439),ISNUMBER(E439),E439&gt;0,F439=E439),0,IF(AND(ISNUMBER(F439),ISNUMBER(E439),E439&gt;0,F439=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K439" s="50" t="str">
+        <x:f>IF(A439="","",IF(AND(ISNUMBER(E439),E439=0,OR(ISNUMBER(SEARCH("Free",D439&amp;"")),AND(ISNUMBER(F439),F439=0))),"Subscription",IF(ISNUMBER(G439),"Profit",IF(ISNUMBER(I439),"Loss",IF(ISNUMBER(H439),"Draw",IF(AND(ISNUMBER(F439),ISNUMBER(E439),E439&gt;0,F439&gt;E439),"Profit",IF(AND(ISNUMBER(F439),ISNUMBER(E439),E439&gt;0,F439=E439),"Draw",IF(AND(ISNUMBER(F439),ISNUMBER(E439),E439&gt;0,F439=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L439" s="50"/>
       <x:c r="M439" s="58"/>
       <x:c r="N439" s="58"/>
@@ -15894,8 +17634,12 @@
       <x:c r="G440" s="58"/>
       <x:c r="H440" s="58"/>
       <x:c r="I440" s="58"/>
-      <x:c r="J440" s="60"/>
-      <x:c r="K440" s="50"/>
+      <x:c r="J440" s="60" t="str">
+        <x:f>IF(A440="","",IF(K440="Subscription","",IF(E440=0,"",IF(ISNUMBER(G440),G440/E440,IF(ISNUMBER(I440),-ABS(I440)/E440,IF(ISNUMBER(H440),0,IF(AND(ISNUMBER(F440),ISNUMBER(E440),E440&gt;0,F440&gt;E440),(F440-E440)/E440,IF(AND(ISNUMBER(F440),ISNUMBER(E440),E440&gt;0,F440=E440),0,IF(AND(ISNUMBER(F440),ISNUMBER(E440),E440&gt;0,F440=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K440" s="50" t="str">
+        <x:f>IF(A440="","",IF(AND(ISNUMBER(E440),E440=0,OR(ISNUMBER(SEARCH("Free",D440&amp;"")),AND(ISNUMBER(F440),F440=0))),"Subscription",IF(ISNUMBER(G440),"Profit",IF(ISNUMBER(I440),"Loss",IF(ISNUMBER(H440),"Draw",IF(AND(ISNUMBER(F440),ISNUMBER(E440),E440&gt;0,F440&gt;E440),"Profit",IF(AND(ISNUMBER(F440),ISNUMBER(E440),E440&gt;0,F440=E440),"Draw",IF(AND(ISNUMBER(F440),ISNUMBER(E440),E440&gt;0,F440=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L440" s="50"/>
       <x:c r="M440" s="58"/>
       <x:c r="N440" s="58"/>
@@ -15927,8 +17671,12 @@
       <x:c r="G441" s="58"/>
       <x:c r="H441" s="58"/>
       <x:c r="I441" s="58"/>
-      <x:c r="J441" s="60"/>
-      <x:c r="K441" s="50"/>
+      <x:c r="J441" s="60" t="str">
+        <x:f>IF(A441="","",IF(K441="Subscription","",IF(E441=0,"",IF(ISNUMBER(G441),G441/E441,IF(ISNUMBER(I441),-ABS(I441)/E441,IF(ISNUMBER(H441),0,IF(AND(ISNUMBER(F441),ISNUMBER(E441),E441&gt;0,F441&gt;E441),(F441-E441)/E441,IF(AND(ISNUMBER(F441),ISNUMBER(E441),E441&gt;0,F441=E441),0,IF(AND(ISNUMBER(F441),ISNUMBER(E441),E441&gt;0,F441=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K441" s="50" t="str">
+        <x:f>IF(A441="","",IF(AND(ISNUMBER(E441),E441=0,OR(ISNUMBER(SEARCH("Free",D441&amp;"")),AND(ISNUMBER(F441),F441=0))),"Subscription",IF(ISNUMBER(G441),"Profit",IF(ISNUMBER(I441),"Loss",IF(ISNUMBER(H441),"Draw",IF(AND(ISNUMBER(F441),ISNUMBER(E441),E441&gt;0,F441&gt;E441),"Profit",IF(AND(ISNUMBER(F441),ISNUMBER(E441),E441&gt;0,F441=E441),"Draw",IF(AND(ISNUMBER(F441),ISNUMBER(E441),E441&gt;0,F441=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L441" s="50"/>
       <x:c r="M441" s="58"/>
       <x:c r="N441" s="58"/>
@@ -15960,8 +17708,12 @@
       <x:c r="G442" s="58"/>
       <x:c r="H442" s="58"/>
       <x:c r="I442" s="58"/>
-      <x:c r="J442" s="60"/>
-      <x:c r="K442" s="50"/>
+      <x:c r="J442" s="60" t="str">
+        <x:f>IF(A442="","",IF(K442="Subscription","",IF(E442=0,"",IF(ISNUMBER(G442),G442/E442,IF(ISNUMBER(I442),-ABS(I442)/E442,IF(ISNUMBER(H442),0,IF(AND(ISNUMBER(F442),ISNUMBER(E442),E442&gt;0,F442&gt;E442),(F442-E442)/E442,IF(AND(ISNUMBER(F442),ISNUMBER(E442),E442&gt;0,F442=E442),0,IF(AND(ISNUMBER(F442),ISNUMBER(E442),E442&gt;0,F442=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K442" s="50" t="str">
+        <x:f>IF(A442="","",IF(AND(ISNUMBER(E442),E442=0,OR(ISNUMBER(SEARCH("Free",D442&amp;"")),AND(ISNUMBER(F442),F442=0))),"Subscription",IF(ISNUMBER(G442),"Profit",IF(ISNUMBER(I442),"Loss",IF(ISNUMBER(H442),"Draw",IF(AND(ISNUMBER(F442),ISNUMBER(E442),E442&gt;0,F442&gt;E442),"Profit",IF(AND(ISNUMBER(F442),ISNUMBER(E442),E442&gt;0,F442=E442),"Draw",IF(AND(ISNUMBER(F442),ISNUMBER(E442),E442&gt;0,F442=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L442" s="50"/>
       <x:c r="M442" s="58"/>
       <x:c r="N442" s="58"/>
@@ -15993,8 +17745,12 @@
       <x:c r="G443" s="58"/>
       <x:c r="H443" s="58"/>
       <x:c r="I443" s="58"/>
-      <x:c r="J443" s="60"/>
-      <x:c r="K443" s="50"/>
+      <x:c r="J443" s="60" t="str">
+        <x:f>IF(A443="","",IF(K443="Subscription","",IF(E443=0,"",IF(ISNUMBER(G443),G443/E443,IF(ISNUMBER(I443),-ABS(I443)/E443,IF(ISNUMBER(H443),0,IF(AND(ISNUMBER(F443),ISNUMBER(E443),E443&gt;0,F443&gt;E443),(F443-E443)/E443,IF(AND(ISNUMBER(F443),ISNUMBER(E443),E443&gt;0,F443=E443),0,IF(AND(ISNUMBER(F443),ISNUMBER(E443),E443&gt;0,F443=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K443" s="50" t="str">
+        <x:f>IF(A443="","",IF(AND(ISNUMBER(E443),E443=0,OR(ISNUMBER(SEARCH("Free",D443&amp;"")),AND(ISNUMBER(F443),F443=0))),"Subscription",IF(ISNUMBER(G443),"Profit",IF(ISNUMBER(I443),"Loss",IF(ISNUMBER(H443),"Draw",IF(AND(ISNUMBER(F443),ISNUMBER(E443),E443&gt;0,F443&gt;E443),"Profit",IF(AND(ISNUMBER(F443),ISNUMBER(E443),E443&gt;0,F443=E443),"Draw",IF(AND(ISNUMBER(F443),ISNUMBER(E443),E443&gt;0,F443=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L443" s="50"/>
       <x:c r="M443" s="58"/>
       <x:c r="N443" s="58"/>
@@ -16026,8 +17782,12 @@
       <x:c r="G444" s="58"/>
       <x:c r="H444" s="58"/>
       <x:c r="I444" s="58"/>
-      <x:c r="J444" s="60"/>
-      <x:c r="K444" s="50"/>
+      <x:c r="J444" s="60" t="str">
+        <x:f>IF(A444="","",IF(K444="Subscription","",IF(E444=0,"",IF(ISNUMBER(G444),G444/E444,IF(ISNUMBER(I444),-ABS(I444)/E444,IF(ISNUMBER(H444),0,IF(AND(ISNUMBER(F444),ISNUMBER(E444),E444&gt;0,F444&gt;E444),(F444-E444)/E444,IF(AND(ISNUMBER(F444),ISNUMBER(E444),E444&gt;0,F444=E444),0,IF(AND(ISNUMBER(F444),ISNUMBER(E444),E444&gt;0,F444=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K444" s="50" t="str">
+        <x:f>IF(A444="","",IF(AND(ISNUMBER(E444),E444=0,OR(ISNUMBER(SEARCH("Free",D444&amp;"")),AND(ISNUMBER(F444),F444=0))),"Subscription",IF(ISNUMBER(G444),"Profit",IF(ISNUMBER(I444),"Loss",IF(ISNUMBER(H444),"Draw",IF(AND(ISNUMBER(F444),ISNUMBER(E444),E444&gt;0,F444&gt;E444),"Profit",IF(AND(ISNUMBER(F444),ISNUMBER(E444),E444&gt;0,F444=E444),"Draw",IF(AND(ISNUMBER(F444),ISNUMBER(E444),E444&gt;0,F444=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L444" s="50"/>
       <x:c r="M444" s="58"/>
       <x:c r="N444" s="58"/>
@@ -16059,8 +17819,12 @@
       <x:c r="G445" s="58"/>
       <x:c r="H445" s="58"/>
       <x:c r="I445" s="58"/>
-      <x:c r="J445" s="60"/>
-      <x:c r="K445" s="50"/>
+      <x:c r="J445" s="60" t="str">
+        <x:f>IF(A445="","",IF(K445="Subscription","",IF(E445=0,"",IF(ISNUMBER(G445),G445/E445,IF(ISNUMBER(I445),-ABS(I445)/E445,IF(ISNUMBER(H445),0,IF(AND(ISNUMBER(F445),ISNUMBER(E445),E445&gt;0,F445&gt;E445),(F445-E445)/E445,IF(AND(ISNUMBER(F445),ISNUMBER(E445),E445&gt;0,F445=E445),0,IF(AND(ISNUMBER(F445),ISNUMBER(E445),E445&gt;0,F445=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K445" s="50" t="str">
+        <x:f>IF(A445="","",IF(AND(ISNUMBER(E445),E445=0,OR(ISNUMBER(SEARCH("Free",D445&amp;"")),AND(ISNUMBER(F445),F445=0))),"Subscription",IF(ISNUMBER(G445),"Profit",IF(ISNUMBER(I445),"Loss",IF(ISNUMBER(H445),"Draw",IF(AND(ISNUMBER(F445),ISNUMBER(E445),E445&gt;0,F445&gt;E445),"Profit",IF(AND(ISNUMBER(F445),ISNUMBER(E445),E445&gt;0,F445=E445),"Draw",IF(AND(ISNUMBER(F445),ISNUMBER(E445),E445&gt;0,F445=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L445" s="50"/>
       <x:c r="M445" s="58"/>
       <x:c r="N445" s="58"/>
@@ -16092,8 +17856,12 @@
       <x:c r="G446" s="58"/>
       <x:c r="H446" s="58"/>
       <x:c r="I446" s="58"/>
-      <x:c r="J446" s="60"/>
-      <x:c r="K446" s="50"/>
+      <x:c r="J446" s="60" t="str">
+        <x:f>IF(A446="","",IF(K446="Subscription","",IF(E446=0,"",IF(ISNUMBER(G446),G446/E446,IF(ISNUMBER(I446),-ABS(I446)/E446,IF(ISNUMBER(H446),0,IF(AND(ISNUMBER(F446),ISNUMBER(E446),E446&gt;0,F446&gt;E446),(F446-E446)/E446,IF(AND(ISNUMBER(F446),ISNUMBER(E446),E446&gt;0,F446=E446),0,IF(AND(ISNUMBER(F446),ISNUMBER(E446),E446&gt;0,F446=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K446" s="50" t="str">
+        <x:f>IF(A446="","",IF(AND(ISNUMBER(E446),E446=0,OR(ISNUMBER(SEARCH("Free",D446&amp;"")),AND(ISNUMBER(F446),F446=0))),"Subscription",IF(ISNUMBER(G446),"Profit",IF(ISNUMBER(I446),"Loss",IF(ISNUMBER(H446),"Draw",IF(AND(ISNUMBER(F446),ISNUMBER(E446),E446&gt;0,F446&gt;E446),"Profit",IF(AND(ISNUMBER(F446),ISNUMBER(E446),E446&gt;0,F446=E446),"Draw",IF(AND(ISNUMBER(F446),ISNUMBER(E446),E446&gt;0,F446=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L446" s="50"/>
       <x:c r="M446" s="58"/>
       <x:c r="N446" s="58"/>
@@ -16125,8 +17893,12 @@
       <x:c r="G447" s="58"/>
       <x:c r="H447" s="58"/>
       <x:c r="I447" s="58"/>
-      <x:c r="J447" s="60"/>
-      <x:c r="K447" s="50"/>
+      <x:c r="J447" s="60" t="str">
+        <x:f>IF(A447="","",IF(K447="Subscription","",IF(E447=0,"",IF(ISNUMBER(G447),G447/E447,IF(ISNUMBER(I447),-ABS(I447)/E447,IF(ISNUMBER(H447),0,IF(AND(ISNUMBER(F447),ISNUMBER(E447),E447&gt;0,F447&gt;E447),(F447-E447)/E447,IF(AND(ISNUMBER(F447),ISNUMBER(E447),E447&gt;0,F447=E447),0,IF(AND(ISNUMBER(F447),ISNUMBER(E447),E447&gt;0,F447=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K447" s="50" t="str">
+        <x:f>IF(A447="","",IF(AND(ISNUMBER(E447),E447=0,OR(ISNUMBER(SEARCH("Free",D447&amp;"")),AND(ISNUMBER(F447),F447=0))),"Subscription",IF(ISNUMBER(G447),"Profit",IF(ISNUMBER(I447),"Loss",IF(ISNUMBER(H447),"Draw",IF(AND(ISNUMBER(F447),ISNUMBER(E447),E447&gt;0,F447&gt;E447),"Profit",IF(AND(ISNUMBER(F447),ISNUMBER(E447),E447&gt;0,F447=E447),"Draw",IF(AND(ISNUMBER(F447),ISNUMBER(E447),E447&gt;0,F447=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L447" s="50"/>
       <x:c r="M447" s="58"/>
       <x:c r="N447" s="58"/>
@@ -16158,8 +17930,12 @@
       <x:c r="G448" s="58"/>
       <x:c r="H448" s="58"/>
       <x:c r="I448" s="58"/>
-      <x:c r="J448" s="60"/>
-      <x:c r="K448" s="50"/>
+      <x:c r="J448" s="60" t="str">
+        <x:f>IF(A448="","",IF(K448="Subscription","",IF(E448=0,"",IF(ISNUMBER(G448),G448/E448,IF(ISNUMBER(I448),-ABS(I448)/E448,IF(ISNUMBER(H448),0,IF(AND(ISNUMBER(F448),ISNUMBER(E448),E448&gt;0,F448&gt;E448),(F448-E448)/E448,IF(AND(ISNUMBER(F448),ISNUMBER(E448),E448&gt;0,F448=E448),0,IF(AND(ISNUMBER(F448),ISNUMBER(E448),E448&gt;0,F448=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K448" s="50" t="str">
+        <x:f>IF(A448="","",IF(AND(ISNUMBER(E448),E448=0,OR(ISNUMBER(SEARCH("Free",D448&amp;"")),AND(ISNUMBER(F448),F448=0))),"Subscription",IF(ISNUMBER(G448),"Profit",IF(ISNUMBER(I448),"Loss",IF(ISNUMBER(H448),"Draw",IF(AND(ISNUMBER(F448),ISNUMBER(E448),E448&gt;0,F448&gt;E448),"Profit",IF(AND(ISNUMBER(F448),ISNUMBER(E448),E448&gt;0,F448=E448),"Draw",IF(AND(ISNUMBER(F448),ISNUMBER(E448),E448&gt;0,F448=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L448" s="50"/>
       <x:c r="M448" s="58"/>
       <x:c r="N448" s="58"/>
@@ -16191,8 +17967,12 @@
       <x:c r="G449" s="58"/>
       <x:c r="H449" s="58"/>
       <x:c r="I449" s="58"/>
-      <x:c r="J449" s="60"/>
-      <x:c r="K449" s="50"/>
+      <x:c r="J449" s="60" t="str">
+        <x:f>IF(A449="","",IF(K449="Subscription","",IF(E449=0,"",IF(ISNUMBER(G449),G449/E449,IF(ISNUMBER(I449),-ABS(I449)/E449,IF(ISNUMBER(H449),0,IF(AND(ISNUMBER(F449),ISNUMBER(E449),E449&gt;0,F449&gt;E449),(F449-E449)/E449,IF(AND(ISNUMBER(F449),ISNUMBER(E449),E449&gt;0,F449=E449),0,IF(AND(ISNUMBER(F449),ISNUMBER(E449),E449&gt;0,F449=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K449" s="50" t="str">
+        <x:f>IF(A449="","",IF(AND(ISNUMBER(E449),E449=0,OR(ISNUMBER(SEARCH("Free",D449&amp;"")),AND(ISNUMBER(F449),F449=0))),"Subscription",IF(ISNUMBER(G449),"Profit",IF(ISNUMBER(I449),"Loss",IF(ISNUMBER(H449),"Draw",IF(AND(ISNUMBER(F449),ISNUMBER(E449),E449&gt;0,F449&gt;E449),"Profit",IF(AND(ISNUMBER(F449),ISNUMBER(E449),E449&gt;0,F449=E449),"Draw",IF(AND(ISNUMBER(F449),ISNUMBER(E449),E449&gt;0,F449=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L449" s="50"/>
       <x:c r="M449" s="58"/>
       <x:c r="N449" s="58"/>
@@ -16224,8 +18004,12 @@
       <x:c r="G450" s="58"/>
       <x:c r="H450" s="58"/>
       <x:c r="I450" s="58"/>
-      <x:c r="J450" s="60"/>
-      <x:c r="K450" s="50"/>
+      <x:c r="J450" s="60" t="str">
+        <x:f>IF(A450="","",IF(K450="Subscription","",IF(E450=0,"",IF(ISNUMBER(G450),G450/E450,IF(ISNUMBER(I450),-ABS(I450)/E450,IF(ISNUMBER(H450),0,IF(AND(ISNUMBER(F450),ISNUMBER(E450),E450&gt;0,F450&gt;E450),(F450-E450)/E450,IF(AND(ISNUMBER(F450),ISNUMBER(E450),E450&gt;0,F450=E450),0,IF(AND(ISNUMBER(F450),ISNUMBER(E450),E450&gt;0,F450=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K450" s="50" t="str">
+        <x:f>IF(A450="","",IF(AND(ISNUMBER(E450),E450=0,OR(ISNUMBER(SEARCH("Free",D450&amp;"")),AND(ISNUMBER(F450),F450=0))),"Subscription",IF(ISNUMBER(G450),"Profit",IF(ISNUMBER(I450),"Loss",IF(ISNUMBER(H450),"Draw",IF(AND(ISNUMBER(F450),ISNUMBER(E450),E450&gt;0,F450&gt;E450),"Profit",IF(AND(ISNUMBER(F450),ISNUMBER(E450),E450&gt;0,F450=E450),"Draw",IF(AND(ISNUMBER(F450),ISNUMBER(E450),E450&gt;0,F450=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L450" s="50"/>
       <x:c r="M450" s="58"/>
       <x:c r="N450" s="58"/>
@@ -16257,8 +18041,12 @@
       <x:c r="G451" s="58"/>
       <x:c r="H451" s="58"/>
       <x:c r="I451" s="58"/>
-      <x:c r="J451" s="60"/>
-      <x:c r="K451" s="50"/>
+      <x:c r="J451" s="60" t="str">
+        <x:f>IF(A451="","",IF(K451="Subscription","",IF(E451=0,"",IF(ISNUMBER(G451),G451/E451,IF(ISNUMBER(I451),-ABS(I451)/E451,IF(ISNUMBER(H451),0,IF(AND(ISNUMBER(F451),ISNUMBER(E451),E451&gt;0,F451&gt;E451),(F451-E451)/E451,IF(AND(ISNUMBER(F451),ISNUMBER(E451),E451&gt;0,F451=E451),0,IF(AND(ISNUMBER(F451),ISNUMBER(E451),E451&gt;0,F451=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K451" s="50" t="str">
+        <x:f>IF(A451="","",IF(AND(ISNUMBER(E451),E451=0,OR(ISNUMBER(SEARCH("Free",D451&amp;"")),AND(ISNUMBER(F451),F451=0))),"Subscription",IF(ISNUMBER(G451),"Profit",IF(ISNUMBER(I451),"Loss",IF(ISNUMBER(H451),"Draw",IF(AND(ISNUMBER(F451),ISNUMBER(E451),E451&gt;0,F451&gt;E451),"Profit",IF(AND(ISNUMBER(F451),ISNUMBER(E451),E451&gt;0,F451=E451),"Draw",IF(AND(ISNUMBER(F451),ISNUMBER(E451),E451&gt;0,F451=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L451" s="50"/>
       <x:c r="M451" s="58"/>
       <x:c r="N451" s="58"/>
@@ -16290,8 +18078,12 @@
       <x:c r="G452" s="58"/>
       <x:c r="H452" s="58"/>
       <x:c r="I452" s="58"/>
-      <x:c r="J452" s="60"/>
-      <x:c r="K452" s="50"/>
+      <x:c r="J452" s="60" t="str">
+        <x:f>IF(A452="","",IF(K452="Subscription","",IF(E452=0,"",IF(ISNUMBER(G452),G452/E452,IF(ISNUMBER(I452),-ABS(I452)/E452,IF(ISNUMBER(H452),0,IF(AND(ISNUMBER(F452),ISNUMBER(E452),E452&gt;0,F452&gt;E452),(F452-E452)/E452,IF(AND(ISNUMBER(F452),ISNUMBER(E452),E452&gt;0,F452=E452),0,IF(AND(ISNUMBER(F452),ISNUMBER(E452),E452&gt;0,F452=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K452" s="50" t="str">
+        <x:f>IF(A452="","",IF(AND(ISNUMBER(E452),E452=0,OR(ISNUMBER(SEARCH("Free",D452&amp;"")),AND(ISNUMBER(F452),F452=0))),"Subscription",IF(ISNUMBER(G452),"Profit",IF(ISNUMBER(I452),"Loss",IF(ISNUMBER(H452),"Draw",IF(AND(ISNUMBER(F452),ISNUMBER(E452),E452&gt;0,F452&gt;E452),"Profit",IF(AND(ISNUMBER(F452),ISNUMBER(E452),E452&gt;0,F452=E452),"Draw",IF(AND(ISNUMBER(F452),ISNUMBER(E452),E452&gt;0,F452=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L452" s="50"/>
       <x:c r="M452" s="58"/>
       <x:c r="N452" s="58"/>
@@ -16323,8 +18115,12 @@
       <x:c r="G453" s="58"/>
       <x:c r="H453" s="58"/>
       <x:c r="I453" s="58"/>
-      <x:c r="J453" s="60"/>
-      <x:c r="K453" s="50"/>
+      <x:c r="J453" s="60" t="str">
+        <x:f>IF(A453="","",IF(K453="Subscription","",IF(E453=0,"",IF(ISNUMBER(G453),G453/E453,IF(ISNUMBER(I453),-ABS(I453)/E453,IF(ISNUMBER(H453),0,IF(AND(ISNUMBER(F453),ISNUMBER(E453),E453&gt;0,F453&gt;E453),(F453-E453)/E453,IF(AND(ISNUMBER(F453),ISNUMBER(E453),E453&gt;0,F453=E453),0,IF(AND(ISNUMBER(F453),ISNUMBER(E453),E453&gt;0,F453=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K453" s="50" t="str">
+        <x:f>IF(A453="","",IF(AND(ISNUMBER(E453),E453=0,OR(ISNUMBER(SEARCH("Free",D453&amp;"")),AND(ISNUMBER(F453),F453=0))),"Subscription",IF(ISNUMBER(G453),"Profit",IF(ISNUMBER(I453),"Loss",IF(ISNUMBER(H453),"Draw",IF(AND(ISNUMBER(F453),ISNUMBER(E453),E453&gt;0,F453&gt;E453),"Profit",IF(AND(ISNUMBER(F453),ISNUMBER(E453),E453&gt;0,F453=E453),"Draw",IF(AND(ISNUMBER(F453),ISNUMBER(E453),E453&gt;0,F453=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L453" s="50"/>
       <x:c r="M453" s="58"/>
       <x:c r="N453" s="58"/>
@@ -16356,8 +18152,12 @@
       <x:c r="G454" s="58"/>
       <x:c r="H454" s="58"/>
       <x:c r="I454" s="58"/>
-      <x:c r="J454" s="60"/>
-      <x:c r="K454" s="50"/>
+      <x:c r="J454" s="60" t="str">
+        <x:f>IF(A454="","",IF(K454="Subscription","",IF(E454=0,"",IF(ISNUMBER(G454),G454/E454,IF(ISNUMBER(I454),-ABS(I454)/E454,IF(ISNUMBER(H454),0,IF(AND(ISNUMBER(F454),ISNUMBER(E454),E454&gt;0,F454&gt;E454),(F454-E454)/E454,IF(AND(ISNUMBER(F454),ISNUMBER(E454),E454&gt;0,F454=E454),0,IF(AND(ISNUMBER(F454),ISNUMBER(E454),E454&gt;0,F454=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K454" s="50" t="str">
+        <x:f>IF(A454="","",IF(AND(ISNUMBER(E454),E454=0,OR(ISNUMBER(SEARCH("Free",D454&amp;"")),AND(ISNUMBER(F454),F454=0))),"Subscription",IF(ISNUMBER(G454),"Profit",IF(ISNUMBER(I454),"Loss",IF(ISNUMBER(H454),"Draw",IF(AND(ISNUMBER(F454),ISNUMBER(E454),E454&gt;0,F454&gt;E454),"Profit",IF(AND(ISNUMBER(F454),ISNUMBER(E454),E454&gt;0,F454=E454),"Draw",IF(AND(ISNUMBER(F454),ISNUMBER(E454),E454&gt;0,F454=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L454" s="50"/>
       <x:c r="M454" s="58"/>
       <x:c r="N454" s="58"/>
@@ -16389,8 +18189,12 @@
       <x:c r="G455" s="58"/>
       <x:c r="H455" s="58"/>
       <x:c r="I455" s="58"/>
-      <x:c r="J455" s="60"/>
-      <x:c r="K455" s="50"/>
+      <x:c r="J455" s="60" t="str">
+        <x:f>IF(A455="","",IF(K455="Subscription","",IF(E455=0,"",IF(ISNUMBER(G455),G455/E455,IF(ISNUMBER(I455),-ABS(I455)/E455,IF(ISNUMBER(H455),0,IF(AND(ISNUMBER(F455),ISNUMBER(E455),E455&gt;0,F455&gt;E455),(F455-E455)/E455,IF(AND(ISNUMBER(F455),ISNUMBER(E455),E455&gt;0,F455=E455),0,IF(AND(ISNUMBER(F455),ISNUMBER(E455),E455&gt;0,F455=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K455" s="50" t="str">
+        <x:f>IF(A455="","",IF(AND(ISNUMBER(E455),E455=0,OR(ISNUMBER(SEARCH("Free",D455&amp;"")),AND(ISNUMBER(F455),F455=0))),"Subscription",IF(ISNUMBER(G455),"Profit",IF(ISNUMBER(I455),"Loss",IF(ISNUMBER(H455),"Draw",IF(AND(ISNUMBER(F455),ISNUMBER(E455),E455&gt;0,F455&gt;E455),"Profit",IF(AND(ISNUMBER(F455),ISNUMBER(E455),E455&gt;0,F455=E455),"Draw",IF(AND(ISNUMBER(F455),ISNUMBER(E455),E455&gt;0,F455=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L455" s="50"/>
       <x:c r="M455" s="58"/>
       <x:c r="N455" s="58"/>
@@ -16422,8 +18226,12 @@
       <x:c r="G456" s="58"/>
       <x:c r="H456" s="58"/>
       <x:c r="I456" s="58"/>
-      <x:c r="J456" s="60"/>
-      <x:c r="K456" s="50"/>
+      <x:c r="J456" s="60" t="str">
+        <x:f>IF(A456="","",IF(K456="Subscription","",IF(E456=0,"",IF(ISNUMBER(G456),G456/E456,IF(ISNUMBER(I456),-ABS(I456)/E456,IF(ISNUMBER(H456),0,IF(AND(ISNUMBER(F456),ISNUMBER(E456),E456&gt;0,F456&gt;E456),(F456-E456)/E456,IF(AND(ISNUMBER(F456),ISNUMBER(E456),E456&gt;0,F456=E456),0,IF(AND(ISNUMBER(F456),ISNUMBER(E456),E456&gt;0,F456=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K456" s="50" t="str">
+        <x:f>IF(A456="","",IF(AND(ISNUMBER(E456),E456=0,OR(ISNUMBER(SEARCH("Free",D456&amp;"")),AND(ISNUMBER(F456),F456=0))),"Subscription",IF(ISNUMBER(G456),"Profit",IF(ISNUMBER(I456),"Loss",IF(ISNUMBER(H456),"Draw",IF(AND(ISNUMBER(F456),ISNUMBER(E456),E456&gt;0,F456&gt;E456),"Profit",IF(AND(ISNUMBER(F456),ISNUMBER(E456),E456&gt;0,F456=E456),"Draw",IF(AND(ISNUMBER(F456),ISNUMBER(E456),E456&gt;0,F456=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L456" s="50"/>
       <x:c r="M456" s="58"/>
       <x:c r="N456" s="58"/>
@@ -16455,8 +18263,12 @@
       <x:c r="G457" s="58"/>
       <x:c r="H457" s="58"/>
       <x:c r="I457" s="58"/>
-      <x:c r="J457" s="60"/>
-      <x:c r="K457" s="50"/>
+      <x:c r="J457" s="60" t="str">
+        <x:f>IF(A457="","",IF(K457="Subscription","",IF(E457=0,"",IF(ISNUMBER(G457),G457/E457,IF(ISNUMBER(I457),-ABS(I457)/E457,IF(ISNUMBER(H457),0,IF(AND(ISNUMBER(F457),ISNUMBER(E457),E457&gt;0,F457&gt;E457),(F457-E457)/E457,IF(AND(ISNUMBER(F457),ISNUMBER(E457),E457&gt;0,F457=E457),0,IF(AND(ISNUMBER(F457),ISNUMBER(E457),E457&gt;0,F457=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K457" s="50" t="str">
+        <x:f>IF(A457="","",IF(AND(ISNUMBER(E457),E457=0,OR(ISNUMBER(SEARCH("Free",D457&amp;"")),AND(ISNUMBER(F457),F457=0))),"Subscription",IF(ISNUMBER(G457),"Profit",IF(ISNUMBER(I457),"Loss",IF(ISNUMBER(H457),"Draw",IF(AND(ISNUMBER(F457),ISNUMBER(E457),E457&gt;0,F457&gt;E457),"Profit",IF(AND(ISNUMBER(F457),ISNUMBER(E457),E457&gt;0,F457=E457),"Draw",IF(AND(ISNUMBER(F457),ISNUMBER(E457),E457&gt;0,F457=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L457" s="50"/>
       <x:c r="M457" s="58"/>
       <x:c r="N457" s="58"/>
@@ -16488,8 +18300,12 @@
       <x:c r="G458" s="58"/>
       <x:c r="H458" s="58"/>
       <x:c r="I458" s="58"/>
-      <x:c r="J458" s="60"/>
-      <x:c r="K458" s="50"/>
+      <x:c r="J458" s="60" t="str">
+        <x:f>IF(A458="","",IF(K458="Subscription","",IF(E458=0,"",IF(ISNUMBER(G458),G458/E458,IF(ISNUMBER(I458),-ABS(I458)/E458,IF(ISNUMBER(H458),0,IF(AND(ISNUMBER(F458),ISNUMBER(E458),E458&gt;0,F458&gt;E458),(F458-E458)/E458,IF(AND(ISNUMBER(F458),ISNUMBER(E458),E458&gt;0,F458=E458),0,IF(AND(ISNUMBER(F458),ISNUMBER(E458),E458&gt;0,F458=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K458" s="50" t="str">
+        <x:f>IF(A458="","",IF(AND(ISNUMBER(E458),E458=0,OR(ISNUMBER(SEARCH("Free",D458&amp;"")),AND(ISNUMBER(F458),F458=0))),"Subscription",IF(ISNUMBER(G458),"Profit",IF(ISNUMBER(I458),"Loss",IF(ISNUMBER(H458),"Draw",IF(AND(ISNUMBER(F458),ISNUMBER(E458),E458&gt;0,F458&gt;E458),"Profit",IF(AND(ISNUMBER(F458),ISNUMBER(E458),E458&gt;0,F458=E458),"Draw",IF(AND(ISNUMBER(F458),ISNUMBER(E458),E458&gt;0,F458=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L458" s="50"/>
       <x:c r="M458" s="58"/>
       <x:c r="N458" s="58"/>
@@ -16521,8 +18337,12 @@
       <x:c r="G459" s="58"/>
       <x:c r="H459" s="58"/>
       <x:c r="I459" s="58"/>
-      <x:c r="J459" s="60"/>
-      <x:c r="K459" s="50"/>
+      <x:c r="J459" s="60" t="str">
+        <x:f>IF(A459="","",IF(K459="Subscription","",IF(E459=0,"",IF(ISNUMBER(G459),G459/E459,IF(ISNUMBER(I459),-ABS(I459)/E459,IF(ISNUMBER(H459),0,IF(AND(ISNUMBER(F459),ISNUMBER(E459),E459&gt;0,F459&gt;E459),(F459-E459)/E459,IF(AND(ISNUMBER(F459),ISNUMBER(E459),E459&gt;0,F459=E459),0,IF(AND(ISNUMBER(F459),ISNUMBER(E459),E459&gt;0,F459=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K459" s="50" t="str">
+        <x:f>IF(A459="","",IF(AND(ISNUMBER(E459),E459=0,OR(ISNUMBER(SEARCH("Free",D459&amp;"")),AND(ISNUMBER(F459),F459=0))),"Subscription",IF(ISNUMBER(G459),"Profit",IF(ISNUMBER(I459),"Loss",IF(ISNUMBER(H459),"Draw",IF(AND(ISNUMBER(F459),ISNUMBER(E459),E459&gt;0,F459&gt;E459),"Profit",IF(AND(ISNUMBER(F459),ISNUMBER(E459),E459&gt;0,F459=E459),"Draw",IF(AND(ISNUMBER(F459),ISNUMBER(E459),E459&gt;0,F459=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L459" s="50"/>
       <x:c r="M459" s="58"/>
       <x:c r="N459" s="58"/>
@@ -16554,8 +18374,12 @@
       <x:c r="G460" s="58"/>
       <x:c r="H460" s="58"/>
       <x:c r="I460" s="58"/>
-      <x:c r="J460" s="60"/>
-      <x:c r="K460" s="50"/>
+      <x:c r="J460" s="60" t="str">
+        <x:f>IF(A460="","",IF(K460="Subscription","",IF(E460=0,"",IF(ISNUMBER(G460),G460/E460,IF(ISNUMBER(I460),-ABS(I460)/E460,IF(ISNUMBER(H460),0,IF(AND(ISNUMBER(F460),ISNUMBER(E460),E460&gt;0,F460&gt;E460),(F460-E460)/E460,IF(AND(ISNUMBER(F460),ISNUMBER(E460),E460&gt;0,F460=E460),0,IF(AND(ISNUMBER(F460),ISNUMBER(E460),E460&gt;0,F460=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K460" s="50" t="str">
+        <x:f>IF(A460="","",IF(AND(ISNUMBER(E460),E460=0,OR(ISNUMBER(SEARCH("Free",D460&amp;"")),AND(ISNUMBER(F460),F460=0))),"Subscription",IF(ISNUMBER(G460),"Profit",IF(ISNUMBER(I460),"Loss",IF(ISNUMBER(H460),"Draw",IF(AND(ISNUMBER(F460),ISNUMBER(E460),E460&gt;0,F460&gt;E460),"Profit",IF(AND(ISNUMBER(F460),ISNUMBER(E460),E460&gt;0,F460=E460),"Draw",IF(AND(ISNUMBER(F460),ISNUMBER(E460),E460&gt;0,F460=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L460" s="50"/>
       <x:c r="M460" s="58"/>
       <x:c r="N460" s="58"/>
@@ -16587,8 +18411,12 @@
       <x:c r="G461" s="58"/>
       <x:c r="H461" s="58"/>
       <x:c r="I461" s="58"/>
-      <x:c r="J461" s="60"/>
-      <x:c r="K461" s="50"/>
+      <x:c r="J461" s="60" t="str">
+        <x:f>IF(A461="","",IF(K461="Subscription","",IF(E461=0,"",IF(ISNUMBER(G461),G461/E461,IF(ISNUMBER(I461),-ABS(I461)/E461,IF(ISNUMBER(H461),0,IF(AND(ISNUMBER(F461),ISNUMBER(E461),E461&gt;0,F461&gt;E461),(F461-E461)/E461,IF(AND(ISNUMBER(F461),ISNUMBER(E461),E461&gt;0,F461=E461),0,IF(AND(ISNUMBER(F461),ISNUMBER(E461),E461&gt;0,F461=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K461" s="50" t="str">
+        <x:f>IF(A461="","",IF(AND(ISNUMBER(E461),E461=0,OR(ISNUMBER(SEARCH("Free",D461&amp;"")),AND(ISNUMBER(F461),F461=0))),"Subscription",IF(ISNUMBER(G461),"Profit",IF(ISNUMBER(I461),"Loss",IF(ISNUMBER(H461),"Draw",IF(AND(ISNUMBER(F461),ISNUMBER(E461),E461&gt;0,F461&gt;E461),"Profit",IF(AND(ISNUMBER(F461),ISNUMBER(E461),E461&gt;0,F461=E461),"Draw",IF(AND(ISNUMBER(F461),ISNUMBER(E461),E461&gt;0,F461=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L461" s="50"/>
       <x:c r="M461" s="58"/>
       <x:c r="N461" s="58"/>
@@ -16620,8 +18448,12 @@
       <x:c r="G462" s="58"/>
       <x:c r="H462" s="58"/>
       <x:c r="I462" s="58"/>
-      <x:c r="J462" s="60"/>
-      <x:c r="K462" s="50"/>
+      <x:c r="J462" s="60" t="str">
+        <x:f>IF(A462="","",IF(K462="Subscription","",IF(E462=0,"",IF(ISNUMBER(G462),G462/E462,IF(ISNUMBER(I462),-ABS(I462)/E462,IF(ISNUMBER(H462),0,IF(AND(ISNUMBER(F462),ISNUMBER(E462),E462&gt;0,F462&gt;E462),(F462-E462)/E462,IF(AND(ISNUMBER(F462),ISNUMBER(E462),E462&gt;0,F462=E462),0,IF(AND(ISNUMBER(F462),ISNUMBER(E462),E462&gt;0,F462=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K462" s="50" t="str">
+        <x:f>IF(A462="","",IF(AND(ISNUMBER(E462),E462=0,OR(ISNUMBER(SEARCH("Free",D462&amp;"")),AND(ISNUMBER(F462),F462=0))),"Subscription",IF(ISNUMBER(G462),"Profit",IF(ISNUMBER(I462),"Loss",IF(ISNUMBER(H462),"Draw",IF(AND(ISNUMBER(F462),ISNUMBER(E462),E462&gt;0,F462&gt;E462),"Profit",IF(AND(ISNUMBER(F462),ISNUMBER(E462),E462&gt;0,F462=E462),"Draw",IF(AND(ISNUMBER(F462),ISNUMBER(E462),E462&gt;0,F462=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L462" s="50"/>
       <x:c r="M462" s="58"/>
       <x:c r="N462" s="58"/>
@@ -16653,8 +18485,12 @@
       <x:c r="G463" s="58"/>
       <x:c r="H463" s="58"/>
       <x:c r="I463" s="58"/>
-      <x:c r="J463" s="60"/>
-      <x:c r="K463" s="50"/>
+      <x:c r="J463" s="60" t="str">
+        <x:f>IF(A463="","",IF(K463="Subscription","",IF(E463=0,"",IF(ISNUMBER(G463),G463/E463,IF(ISNUMBER(I463),-ABS(I463)/E463,IF(ISNUMBER(H463),0,IF(AND(ISNUMBER(F463),ISNUMBER(E463),E463&gt;0,F463&gt;E463),(F463-E463)/E463,IF(AND(ISNUMBER(F463),ISNUMBER(E463),E463&gt;0,F463=E463),0,IF(AND(ISNUMBER(F463),ISNUMBER(E463),E463&gt;0,F463=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K463" s="50" t="str">
+        <x:f>IF(A463="","",IF(AND(ISNUMBER(E463),E463=0,OR(ISNUMBER(SEARCH("Free",D463&amp;"")),AND(ISNUMBER(F463),F463=0))),"Subscription",IF(ISNUMBER(G463),"Profit",IF(ISNUMBER(I463),"Loss",IF(ISNUMBER(H463),"Draw",IF(AND(ISNUMBER(F463),ISNUMBER(E463),E463&gt;0,F463&gt;E463),"Profit",IF(AND(ISNUMBER(F463),ISNUMBER(E463),E463&gt;0,F463=E463),"Draw",IF(AND(ISNUMBER(F463),ISNUMBER(E463),E463&gt;0,F463=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L463" s="50"/>
       <x:c r="M463" s="58"/>
       <x:c r="N463" s="58"/>
@@ -16686,8 +18522,12 @@
       <x:c r="G464" s="58"/>
       <x:c r="H464" s="58"/>
       <x:c r="I464" s="58"/>
-      <x:c r="J464" s="60"/>
-      <x:c r="K464" s="50"/>
+      <x:c r="J464" s="60" t="str">
+        <x:f>IF(A464="","",IF(K464="Subscription","",IF(E464=0,"",IF(ISNUMBER(G464),G464/E464,IF(ISNUMBER(I464),-ABS(I464)/E464,IF(ISNUMBER(H464),0,IF(AND(ISNUMBER(F464),ISNUMBER(E464),E464&gt;0,F464&gt;E464),(F464-E464)/E464,IF(AND(ISNUMBER(F464),ISNUMBER(E464),E464&gt;0,F464=E464),0,IF(AND(ISNUMBER(F464),ISNUMBER(E464),E464&gt;0,F464=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K464" s="50" t="str">
+        <x:f>IF(A464="","",IF(AND(ISNUMBER(E464),E464=0,OR(ISNUMBER(SEARCH("Free",D464&amp;"")),AND(ISNUMBER(F464),F464=0))),"Subscription",IF(ISNUMBER(G464),"Profit",IF(ISNUMBER(I464),"Loss",IF(ISNUMBER(H464),"Draw",IF(AND(ISNUMBER(F464),ISNUMBER(E464),E464&gt;0,F464&gt;E464),"Profit",IF(AND(ISNUMBER(F464),ISNUMBER(E464),E464&gt;0,F464=E464),"Draw",IF(AND(ISNUMBER(F464),ISNUMBER(E464),E464&gt;0,F464=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L464" s="50"/>
       <x:c r="M464" s="58"/>
       <x:c r="N464" s="58"/>
@@ -16719,8 +18559,12 @@
       <x:c r="G465" s="58"/>
       <x:c r="H465" s="58"/>
       <x:c r="I465" s="58"/>
-      <x:c r="J465" s="60"/>
-      <x:c r="K465" s="50"/>
+      <x:c r="J465" s="60" t="str">
+        <x:f>IF(A465="","",IF(K465="Subscription","",IF(E465=0,"",IF(ISNUMBER(G465),G465/E465,IF(ISNUMBER(I465),-ABS(I465)/E465,IF(ISNUMBER(H465),0,IF(AND(ISNUMBER(F465),ISNUMBER(E465),E465&gt;0,F465&gt;E465),(F465-E465)/E465,IF(AND(ISNUMBER(F465),ISNUMBER(E465),E465&gt;0,F465=E465),0,IF(AND(ISNUMBER(F465),ISNUMBER(E465),E465&gt;0,F465=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K465" s="50" t="str">
+        <x:f>IF(A465="","",IF(AND(ISNUMBER(E465),E465=0,OR(ISNUMBER(SEARCH("Free",D465&amp;"")),AND(ISNUMBER(F465),F465=0))),"Subscription",IF(ISNUMBER(G465),"Profit",IF(ISNUMBER(I465),"Loss",IF(ISNUMBER(H465),"Draw",IF(AND(ISNUMBER(F465),ISNUMBER(E465),E465&gt;0,F465&gt;E465),"Profit",IF(AND(ISNUMBER(F465),ISNUMBER(E465),E465&gt;0,F465=E465),"Draw",IF(AND(ISNUMBER(F465),ISNUMBER(E465),E465&gt;0,F465=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L465" s="50"/>
       <x:c r="M465" s="58"/>
       <x:c r="N465" s="58"/>
@@ -16752,8 +18596,12 @@
       <x:c r="G466" s="58"/>
       <x:c r="H466" s="58"/>
       <x:c r="I466" s="58"/>
-      <x:c r="J466" s="60"/>
-      <x:c r="K466" s="50"/>
+      <x:c r="J466" s="60" t="str">
+        <x:f>IF(A466="","",IF(K466="Subscription","",IF(E466=0,"",IF(ISNUMBER(G466),G466/E466,IF(ISNUMBER(I466),-ABS(I466)/E466,IF(ISNUMBER(H466),0,IF(AND(ISNUMBER(F466),ISNUMBER(E466),E466&gt;0,F466&gt;E466),(F466-E466)/E466,IF(AND(ISNUMBER(F466),ISNUMBER(E466),E466&gt;0,F466=E466),0,IF(AND(ISNUMBER(F466),ISNUMBER(E466),E466&gt;0,F466=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K466" s="50" t="str">
+        <x:f>IF(A466="","",IF(AND(ISNUMBER(E466),E466=0,OR(ISNUMBER(SEARCH("Free",D466&amp;"")),AND(ISNUMBER(F466),F466=0))),"Subscription",IF(ISNUMBER(G466),"Profit",IF(ISNUMBER(I466),"Loss",IF(ISNUMBER(H466),"Draw",IF(AND(ISNUMBER(F466),ISNUMBER(E466),E466&gt;0,F466&gt;E466),"Profit",IF(AND(ISNUMBER(F466),ISNUMBER(E466),E466&gt;0,F466=E466),"Draw",IF(AND(ISNUMBER(F466),ISNUMBER(E466),E466&gt;0,F466=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L466" s="50"/>
       <x:c r="M466" s="58"/>
       <x:c r="N466" s="58"/>
@@ -16785,8 +18633,12 @@
       <x:c r="G467" s="58"/>
       <x:c r="H467" s="58"/>
       <x:c r="I467" s="58"/>
-      <x:c r="J467" s="60"/>
-      <x:c r="K467" s="50"/>
+      <x:c r="J467" s="60" t="str">
+        <x:f>IF(A467="","",IF(K467="Subscription","",IF(E467=0,"",IF(ISNUMBER(G467),G467/E467,IF(ISNUMBER(I467),-ABS(I467)/E467,IF(ISNUMBER(H467),0,IF(AND(ISNUMBER(F467),ISNUMBER(E467),E467&gt;0,F467&gt;E467),(F467-E467)/E467,IF(AND(ISNUMBER(F467),ISNUMBER(E467),E467&gt;0,F467=E467),0,IF(AND(ISNUMBER(F467),ISNUMBER(E467),E467&gt;0,F467=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K467" s="50" t="str">
+        <x:f>IF(A467="","",IF(AND(ISNUMBER(E467),E467=0,OR(ISNUMBER(SEARCH("Free",D467&amp;"")),AND(ISNUMBER(F467),F467=0))),"Subscription",IF(ISNUMBER(G467),"Profit",IF(ISNUMBER(I467),"Loss",IF(ISNUMBER(H467),"Draw",IF(AND(ISNUMBER(F467),ISNUMBER(E467),E467&gt;0,F467&gt;E467),"Profit",IF(AND(ISNUMBER(F467),ISNUMBER(E467),E467&gt;0,F467=E467),"Draw",IF(AND(ISNUMBER(F467),ISNUMBER(E467),E467&gt;0,F467=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L467" s="50"/>
       <x:c r="M467" s="58"/>
       <x:c r="N467" s="58"/>
@@ -16818,8 +18670,12 @@
       <x:c r="G468" s="58"/>
       <x:c r="H468" s="58"/>
       <x:c r="I468" s="58"/>
-      <x:c r="J468" s="60"/>
-      <x:c r="K468" s="50"/>
+      <x:c r="J468" s="60" t="str">
+        <x:f>IF(A468="","",IF(K468="Subscription","",IF(E468=0,"",IF(ISNUMBER(G468),G468/E468,IF(ISNUMBER(I468),-ABS(I468)/E468,IF(ISNUMBER(H468),0,IF(AND(ISNUMBER(F468),ISNUMBER(E468),E468&gt;0,F468&gt;E468),(F468-E468)/E468,IF(AND(ISNUMBER(F468),ISNUMBER(E468),E468&gt;0,F468=E468),0,IF(AND(ISNUMBER(F468),ISNUMBER(E468),E468&gt;0,F468=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K468" s="50" t="str">
+        <x:f>IF(A468="","",IF(AND(ISNUMBER(E468),E468=0,OR(ISNUMBER(SEARCH("Free",D468&amp;"")),AND(ISNUMBER(F468),F468=0))),"Subscription",IF(ISNUMBER(G468),"Profit",IF(ISNUMBER(I468),"Loss",IF(ISNUMBER(H468),"Draw",IF(AND(ISNUMBER(F468),ISNUMBER(E468),E468&gt;0,F468&gt;E468),"Profit",IF(AND(ISNUMBER(F468),ISNUMBER(E468),E468&gt;0,F468=E468),"Draw",IF(AND(ISNUMBER(F468),ISNUMBER(E468),E468&gt;0,F468=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L468" s="50"/>
       <x:c r="M468" s="58"/>
       <x:c r="N468" s="58"/>
@@ -16851,8 +18707,12 @@
       <x:c r="G469" s="58"/>
       <x:c r="H469" s="58"/>
       <x:c r="I469" s="58"/>
-      <x:c r="J469" s="60"/>
-      <x:c r="K469" s="50"/>
+      <x:c r="J469" s="60" t="str">
+        <x:f>IF(A469="","",IF(K469="Subscription","",IF(E469=0,"",IF(ISNUMBER(G469),G469/E469,IF(ISNUMBER(I469),-ABS(I469)/E469,IF(ISNUMBER(H469),0,IF(AND(ISNUMBER(F469),ISNUMBER(E469),E469&gt;0,F469&gt;E469),(F469-E469)/E469,IF(AND(ISNUMBER(F469),ISNUMBER(E469),E469&gt;0,F469=E469),0,IF(AND(ISNUMBER(F469),ISNUMBER(E469),E469&gt;0,F469=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K469" s="50" t="str">
+        <x:f>IF(A469="","",IF(AND(ISNUMBER(E469),E469=0,OR(ISNUMBER(SEARCH("Free",D469&amp;"")),AND(ISNUMBER(F469),F469=0))),"Subscription",IF(ISNUMBER(G469),"Profit",IF(ISNUMBER(I469),"Loss",IF(ISNUMBER(H469),"Draw",IF(AND(ISNUMBER(F469),ISNUMBER(E469),E469&gt;0,F469&gt;E469),"Profit",IF(AND(ISNUMBER(F469),ISNUMBER(E469),E469&gt;0,F469=E469),"Draw",IF(AND(ISNUMBER(F469),ISNUMBER(E469),E469&gt;0,F469=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L469" s="50"/>
       <x:c r="M469" s="58"/>
       <x:c r="N469" s="58"/>
@@ -16884,8 +18744,12 @@
       <x:c r="G470" s="58"/>
       <x:c r="H470" s="58"/>
       <x:c r="I470" s="58"/>
-      <x:c r="J470" s="60"/>
-      <x:c r="K470" s="50"/>
+      <x:c r="J470" s="60" t="str">
+        <x:f>IF(A470="","",IF(K470="Subscription","",IF(E470=0,"",IF(ISNUMBER(G470),G470/E470,IF(ISNUMBER(I470),-ABS(I470)/E470,IF(ISNUMBER(H470),0,IF(AND(ISNUMBER(F470),ISNUMBER(E470),E470&gt;0,F470&gt;E470),(F470-E470)/E470,IF(AND(ISNUMBER(F470),ISNUMBER(E470),E470&gt;0,F470=E470),0,IF(AND(ISNUMBER(F470),ISNUMBER(E470),E470&gt;0,F470=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K470" s="50" t="str">
+        <x:f>IF(A470="","",IF(AND(ISNUMBER(E470),E470=0,OR(ISNUMBER(SEARCH("Free",D470&amp;"")),AND(ISNUMBER(F470),F470=0))),"Subscription",IF(ISNUMBER(G470),"Profit",IF(ISNUMBER(I470),"Loss",IF(ISNUMBER(H470),"Draw",IF(AND(ISNUMBER(F470),ISNUMBER(E470),E470&gt;0,F470&gt;E470),"Profit",IF(AND(ISNUMBER(F470),ISNUMBER(E470),E470&gt;0,F470=E470),"Draw",IF(AND(ISNUMBER(F470),ISNUMBER(E470),E470&gt;0,F470=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L470" s="50"/>
       <x:c r="M470" s="58"/>
       <x:c r="N470" s="58"/>
@@ -16917,8 +18781,12 @@
       <x:c r="G471" s="58"/>
       <x:c r="H471" s="58"/>
       <x:c r="I471" s="58"/>
-      <x:c r="J471" s="60"/>
-      <x:c r="K471" s="50"/>
+      <x:c r="J471" s="60" t="str">
+        <x:f>IF(A471="","",IF(K471="Subscription","",IF(E471=0,"",IF(ISNUMBER(G471),G471/E471,IF(ISNUMBER(I471),-ABS(I471)/E471,IF(ISNUMBER(H471),0,IF(AND(ISNUMBER(F471),ISNUMBER(E471),E471&gt;0,F471&gt;E471),(F471-E471)/E471,IF(AND(ISNUMBER(F471),ISNUMBER(E471),E471&gt;0,F471=E471),0,IF(AND(ISNUMBER(F471),ISNUMBER(E471),E471&gt;0,F471=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K471" s="50" t="str">
+        <x:f>IF(A471="","",IF(AND(ISNUMBER(E471),E471=0,OR(ISNUMBER(SEARCH("Free",D471&amp;"")),AND(ISNUMBER(F471),F471=0))),"Subscription",IF(ISNUMBER(G471),"Profit",IF(ISNUMBER(I471),"Loss",IF(ISNUMBER(H471),"Draw",IF(AND(ISNUMBER(F471),ISNUMBER(E471),E471&gt;0,F471&gt;E471),"Profit",IF(AND(ISNUMBER(F471),ISNUMBER(E471),E471&gt;0,F471=E471),"Draw",IF(AND(ISNUMBER(F471),ISNUMBER(E471),E471&gt;0,F471=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L471" s="50"/>
       <x:c r="M471" s="58"/>
       <x:c r="N471" s="58"/>
@@ -16950,8 +18818,12 @@
       <x:c r="G472" s="58"/>
       <x:c r="H472" s="58"/>
       <x:c r="I472" s="58"/>
-      <x:c r="J472" s="60"/>
-      <x:c r="K472" s="50"/>
+      <x:c r="J472" s="60" t="str">
+        <x:f>IF(A472="","",IF(K472="Subscription","",IF(E472=0,"",IF(ISNUMBER(G472),G472/E472,IF(ISNUMBER(I472),-ABS(I472)/E472,IF(ISNUMBER(H472),0,IF(AND(ISNUMBER(F472),ISNUMBER(E472),E472&gt;0,F472&gt;E472),(F472-E472)/E472,IF(AND(ISNUMBER(F472),ISNUMBER(E472),E472&gt;0,F472=E472),0,IF(AND(ISNUMBER(F472),ISNUMBER(E472),E472&gt;0,F472=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K472" s="50" t="str">
+        <x:f>IF(A472="","",IF(AND(ISNUMBER(E472),E472=0,OR(ISNUMBER(SEARCH("Free",D472&amp;"")),AND(ISNUMBER(F472),F472=0))),"Subscription",IF(ISNUMBER(G472),"Profit",IF(ISNUMBER(I472),"Loss",IF(ISNUMBER(H472),"Draw",IF(AND(ISNUMBER(F472),ISNUMBER(E472),E472&gt;0,F472&gt;E472),"Profit",IF(AND(ISNUMBER(F472),ISNUMBER(E472),E472&gt;0,F472=E472),"Draw",IF(AND(ISNUMBER(F472),ISNUMBER(E472),E472&gt;0,F472=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L472" s="50"/>
       <x:c r="M472" s="58"/>
       <x:c r="N472" s="58"/>
@@ -16983,8 +18855,12 @@
       <x:c r="G473" s="58"/>
       <x:c r="H473" s="58"/>
       <x:c r="I473" s="58"/>
-      <x:c r="J473" s="60"/>
-      <x:c r="K473" s="50"/>
+      <x:c r="J473" s="60" t="str">
+        <x:f>IF(A473="","",IF(K473="Subscription","",IF(E473=0,"",IF(ISNUMBER(G473),G473/E473,IF(ISNUMBER(I473),-ABS(I473)/E473,IF(ISNUMBER(H473),0,IF(AND(ISNUMBER(F473),ISNUMBER(E473),E473&gt;0,F473&gt;E473),(F473-E473)/E473,IF(AND(ISNUMBER(F473),ISNUMBER(E473),E473&gt;0,F473=E473),0,IF(AND(ISNUMBER(F473),ISNUMBER(E473),E473&gt;0,F473=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K473" s="50" t="str">
+        <x:f>IF(A473="","",IF(AND(ISNUMBER(E473),E473=0,OR(ISNUMBER(SEARCH("Free",D473&amp;"")),AND(ISNUMBER(F473),F473=0))),"Subscription",IF(ISNUMBER(G473),"Profit",IF(ISNUMBER(I473),"Loss",IF(ISNUMBER(H473),"Draw",IF(AND(ISNUMBER(F473),ISNUMBER(E473),E473&gt;0,F473&gt;E473),"Profit",IF(AND(ISNUMBER(F473),ISNUMBER(E473),E473&gt;0,F473=E473),"Draw",IF(AND(ISNUMBER(F473),ISNUMBER(E473),E473&gt;0,F473=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L473" s="50"/>
       <x:c r="M473" s="58"/>
       <x:c r="N473" s="58"/>
@@ -17016,8 +18892,12 @@
       <x:c r="G474" s="58"/>
       <x:c r="H474" s="58"/>
       <x:c r="I474" s="58"/>
-      <x:c r="J474" s="60"/>
-      <x:c r="K474" s="50"/>
+      <x:c r="J474" s="60" t="str">
+        <x:f>IF(A474="","",IF(K474="Subscription","",IF(E474=0,"",IF(ISNUMBER(G474),G474/E474,IF(ISNUMBER(I474),-ABS(I474)/E474,IF(ISNUMBER(H474),0,IF(AND(ISNUMBER(F474),ISNUMBER(E474),E474&gt;0,F474&gt;E474),(F474-E474)/E474,IF(AND(ISNUMBER(F474),ISNUMBER(E474),E474&gt;0,F474=E474),0,IF(AND(ISNUMBER(F474),ISNUMBER(E474),E474&gt;0,F474=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K474" s="50" t="str">
+        <x:f>IF(A474="","",IF(AND(ISNUMBER(E474),E474=0,OR(ISNUMBER(SEARCH("Free",D474&amp;"")),AND(ISNUMBER(F474),F474=0))),"Subscription",IF(ISNUMBER(G474),"Profit",IF(ISNUMBER(I474),"Loss",IF(ISNUMBER(H474),"Draw",IF(AND(ISNUMBER(F474),ISNUMBER(E474),E474&gt;0,F474&gt;E474),"Profit",IF(AND(ISNUMBER(F474),ISNUMBER(E474),E474&gt;0,F474=E474),"Draw",IF(AND(ISNUMBER(F474),ISNUMBER(E474),E474&gt;0,F474=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L474" s="50"/>
       <x:c r="M474" s="58"/>
       <x:c r="N474" s="58"/>
@@ -17049,8 +18929,12 @@
       <x:c r="G475" s="58"/>
       <x:c r="H475" s="58"/>
       <x:c r="I475" s="58"/>
-      <x:c r="J475" s="60"/>
-      <x:c r="K475" s="50"/>
+      <x:c r="J475" s="60" t="str">
+        <x:f>IF(A475="","",IF(K475="Subscription","",IF(E475=0,"",IF(ISNUMBER(G475),G475/E475,IF(ISNUMBER(I475),-ABS(I475)/E475,IF(ISNUMBER(H475),0,IF(AND(ISNUMBER(F475),ISNUMBER(E475),E475&gt;0,F475&gt;E475),(F475-E475)/E475,IF(AND(ISNUMBER(F475),ISNUMBER(E475),E475&gt;0,F475=E475),0,IF(AND(ISNUMBER(F475),ISNUMBER(E475),E475&gt;0,F475=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K475" s="50" t="str">
+        <x:f>IF(A475="","",IF(AND(ISNUMBER(E475),E475=0,OR(ISNUMBER(SEARCH("Free",D475&amp;"")),AND(ISNUMBER(F475),F475=0))),"Subscription",IF(ISNUMBER(G475),"Profit",IF(ISNUMBER(I475),"Loss",IF(ISNUMBER(H475),"Draw",IF(AND(ISNUMBER(F475),ISNUMBER(E475),E475&gt;0,F475&gt;E475),"Profit",IF(AND(ISNUMBER(F475),ISNUMBER(E475),E475&gt;0,F475=E475),"Draw",IF(AND(ISNUMBER(F475),ISNUMBER(E475),E475&gt;0,F475=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L475" s="50"/>
       <x:c r="M475" s="58"/>
       <x:c r="N475" s="58"/>
@@ -17082,8 +18966,12 @@
       <x:c r="G476" s="58"/>
       <x:c r="H476" s="58"/>
       <x:c r="I476" s="58"/>
-      <x:c r="J476" s="60"/>
-      <x:c r="K476" s="50"/>
+      <x:c r="J476" s="60" t="str">
+        <x:f>IF(A476="","",IF(K476="Subscription","",IF(E476=0,"",IF(ISNUMBER(G476),G476/E476,IF(ISNUMBER(I476),-ABS(I476)/E476,IF(ISNUMBER(H476),0,IF(AND(ISNUMBER(F476),ISNUMBER(E476),E476&gt;0,F476&gt;E476),(F476-E476)/E476,IF(AND(ISNUMBER(F476),ISNUMBER(E476),E476&gt;0,F476=E476),0,IF(AND(ISNUMBER(F476),ISNUMBER(E476),E476&gt;0,F476=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K476" s="50" t="str">
+        <x:f>IF(A476="","",IF(AND(ISNUMBER(E476),E476=0,OR(ISNUMBER(SEARCH("Free",D476&amp;"")),AND(ISNUMBER(F476),F476=0))),"Subscription",IF(ISNUMBER(G476),"Profit",IF(ISNUMBER(I476),"Loss",IF(ISNUMBER(H476),"Draw",IF(AND(ISNUMBER(F476),ISNUMBER(E476),E476&gt;0,F476&gt;E476),"Profit",IF(AND(ISNUMBER(F476),ISNUMBER(E476),E476&gt;0,F476=E476),"Draw",IF(AND(ISNUMBER(F476),ISNUMBER(E476),E476&gt;0,F476=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L476" s="50"/>
       <x:c r="M476" s="58"/>
       <x:c r="N476" s="58"/>
@@ -17115,8 +19003,12 @@
       <x:c r="G477" s="58"/>
       <x:c r="H477" s="58"/>
       <x:c r="I477" s="58"/>
-      <x:c r="J477" s="60"/>
-      <x:c r="K477" s="50"/>
+      <x:c r="J477" s="60" t="str">
+        <x:f>IF(A477="","",IF(K477="Subscription","",IF(E477=0,"",IF(ISNUMBER(G477),G477/E477,IF(ISNUMBER(I477),-ABS(I477)/E477,IF(ISNUMBER(H477),0,IF(AND(ISNUMBER(F477),ISNUMBER(E477),E477&gt;0,F477&gt;E477),(F477-E477)/E477,IF(AND(ISNUMBER(F477),ISNUMBER(E477),E477&gt;0,F477=E477),0,IF(AND(ISNUMBER(F477),ISNUMBER(E477),E477&gt;0,F477=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K477" s="50" t="str">
+        <x:f>IF(A477="","",IF(AND(ISNUMBER(E477),E477=0,OR(ISNUMBER(SEARCH("Free",D477&amp;"")),AND(ISNUMBER(F477),F477=0))),"Subscription",IF(ISNUMBER(G477),"Profit",IF(ISNUMBER(I477),"Loss",IF(ISNUMBER(H477),"Draw",IF(AND(ISNUMBER(F477),ISNUMBER(E477),E477&gt;0,F477&gt;E477),"Profit",IF(AND(ISNUMBER(F477),ISNUMBER(E477),E477&gt;0,F477=E477),"Draw",IF(AND(ISNUMBER(F477),ISNUMBER(E477),E477&gt;0,F477=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L477" s="50"/>
       <x:c r="M477" s="58"/>
       <x:c r="N477" s="58"/>
@@ -17148,8 +19040,12 @@
       <x:c r="G478" s="58"/>
       <x:c r="H478" s="58"/>
       <x:c r="I478" s="58"/>
-      <x:c r="J478" s="60"/>
-      <x:c r="K478" s="50"/>
+      <x:c r="J478" s="60" t="str">
+        <x:f>IF(A478="","",IF(K478="Subscription","",IF(E478=0,"",IF(ISNUMBER(G478),G478/E478,IF(ISNUMBER(I478),-ABS(I478)/E478,IF(ISNUMBER(H478),0,IF(AND(ISNUMBER(F478),ISNUMBER(E478),E478&gt;0,F478&gt;E478),(F478-E478)/E478,IF(AND(ISNUMBER(F478),ISNUMBER(E478),E478&gt;0,F478=E478),0,IF(AND(ISNUMBER(F478),ISNUMBER(E478),E478&gt;0,F478=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K478" s="50" t="str">
+        <x:f>IF(A478="","",IF(AND(ISNUMBER(E478),E478=0,OR(ISNUMBER(SEARCH("Free",D478&amp;"")),AND(ISNUMBER(F478),F478=0))),"Subscription",IF(ISNUMBER(G478),"Profit",IF(ISNUMBER(I478),"Loss",IF(ISNUMBER(H478),"Draw",IF(AND(ISNUMBER(F478),ISNUMBER(E478),E478&gt;0,F478&gt;E478),"Profit",IF(AND(ISNUMBER(F478),ISNUMBER(E478),E478&gt;0,F478=E478),"Draw",IF(AND(ISNUMBER(F478),ISNUMBER(E478),E478&gt;0,F478=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L478" s="50"/>
       <x:c r="M478" s="58"/>
       <x:c r="N478" s="58"/>
@@ -17181,8 +19077,12 @@
       <x:c r="G479" s="58"/>
       <x:c r="H479" s="58"/>
       <x:c r="I479" s="58"/>
-      <x:c r="J479" s="60"/>
-      <x:c r="K479" s="50"/>
+      <x:c r="J479" s="60" t="str">
+        <x:f>IF(A479="","",IF(K479="Subscription","",IF(E479=0,"",IF(ISNUMBER(G479),G479/E479,IF(ISNUMBER(I479),-ABS(I479)/E479,IF(ISNUMBER(H479),0,IF(AND(ISNUMBER(F479),ISNUMBER(E479),E479&gt;0,F479&gt;E479),(F479-E479)/E479,IF(AND(ISNUMBER(F479),ISNUMBER(E479),E479&gt;0,F479=E479),0,IF(AND(ISNUMBER(F479),ISNUMBER(E479),E479&gt;0,F479=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K479" s="50" t="str">
+        <x:f>IF(A479="","",IF(AND(ISNUMBER(E479),E479=0,OR(ISNUMBER(SEARCH("Free",D479&amp;"")),AND(ISNUMBER(F479),F479=0))),"Subscription",IF(ISNUMBER(G479),"Profit",IF(ISNUMBER(I479),"Loss",IF(ISNUMBER(H479),"Draw",IF(AND(ISNUMBER(F479),ISNUMBER(E479),E479&gt;0,F479&gt;E479),"Profit",IF(AND(ISNUMBER(F479),ISNUMBER(E479),E479&gt;0,F479=E479),"Draw",IF(AND(ISNUMBER(F479),ISNUMBER(E479),E479&gt;0,F479=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L479" s="50"/>
       <x:c r="M479" s="58"/>
       <x:c r="N479" s="58"/>
@@ -17214,8 +19114,12 @@
       <x:c r="G480" s="58"/>
       <x:c r="H480" s="58"/>
       <x:c r="I480" s="58"/>
-      <x:c r="J480" s="60"/>
-      <x:c r="K480" s="50"/>
+      <x:c r="J480" s="60" t="str">
+        <x:f>IF(A480="","",IF(K480="Subscription","",IF(E480=0,"",IF(ISNUMBER(G480),G480/E480,IF(ISNUMBER(I480),-ABS(I480)/E480,IF(ISNUMBER(H480),0,IF(AND(ISNUMBER(F480),ISNUMBER(E480),E480&gt;0,F480&gt;E480),(F480-E480)/E480,IF(AND(ISNUMBER(F480),ISNUMBER(E480),E480&gt;0,F480=E480),0,IF(AND(ISNUMBER(F480),ISNUMBER(E480),E480&gt;0,F480=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K480" s="50" t="str">
+        <x:f>IF(A480="","",IF(AND(ISNUMBER(E480),E480=0,OR(ISNUMBER(SEARCH("Free",D480&amp;"")),AND(ISNUMBER(F480),F480=0))),"Subscription",IF(ISNUMBER(G480),"Profit",IF(ISNUMBER(I480),"Loss",IF(ISNUMBER(H480),"Draw",IF(AND(ISNUMBER(F480),ISNUMBER(E480),E480&gt;0,F480&gt;E480),"Profit",IF(AND(ISNUMBER(F480),ISNUMBER(E480),E480&gt;0,F480=E480),"Draw",IF(AND(ISNUMBER(F480),ISNUMBER(E480),E480&gt;0,F480=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L480" s="50"/>
       <x:c r="M480" s="58"/>
       <x:c r="N480" s="58"/>
@@ -17247,8 +19151,12 @@
       <x:c r="G481" s="58"/>
       <x:c r="H481" s="58"/>
       <x:c r="I481" s="58"/>
-      <x:c r="J481" s="60"/>
-      <x:c r="K481" s="50"/>
+      <x:c r="J481" s="60" t="str">
+        <x:f>IF(A481="","",IF(K481="Subscription","",IF(E481=0,"",IF(ISNUMBER(G481),G481/E481,IF(ISNUMBER(I481),-ABS(I481)/E481,IF(ISNUMBER(H481),0,IF(AND(ISNUMBER(F481),ISNUMBER(E481),E481&gt;0,F481&gt;E481),(F481-E481)/E481,IF(AND(ISNUMBER(F481),ISNUMBER(E481),E481&gt;0,F481=E481),0,IF(AND(ISNUMBER(F481),ISNUMBER(E481),E481&gt;0,F481=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K481" s="50" t="str">
+        <x:f>IF(A481="","",IF(AND(ISNUMBER(E481),E481=0,OR(ISNUMBER(SEARCH("Free",D481&amp;"")),AND(ISNUMBER(F481),F481=0))),"Subscription",IF(ISNUMBER(G481),"Profit",IF(ISNUMBER(I481),"Loss",IF(ISNUMBER(H481),"Draw",IF(AND(ISNUMBER(F481),ISNUMBER(E481),E481&gt;0,F481&gt;E481),"Profit",IF(AND(ISNUMBER(F481),ISNUMBER(E481),E481&gt;0,F481=E481),"Draw",IF(AND(ISNUMBER(F481),ISNUMBER(E481),E481&gt;0,F481=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L481" s="50"/>
       <x:c r="M481" s="58"/>
       <x:c r="N481" s="58"/>
@@ -17280,8 +19188,12 @@
       <x:c r="G482" s="58"/>
       <x:c r="H482" s="58"/>
       <x:c r="I482" s="58"/>
-      <x:c r="J482" s="60"/>
-      <x:c r="K482" s="50"/>
+      <x:c r="J482" s="60" t="str">
+        <x:f>IF(A482="","",IF(K482="Subscription","",IF(E482=0,"",IF(ISNUMBER(G482),G482/E482,IF(ISNUMBER(I482),-ABS(I482)/E482,IF(ISNUMBER(H482),0,IF(AND(ISNUMBER(F482),ISNUMBER(E482),E482&gt;0,F482&gt;E482),(F482-E482)/E482,IF(AND(ISNUMBER(F482),ISNUMBER(E482),E482&gt;0,F482=E482),0,IF(AND(ISNUMBER(F482),ISNUMBER(E482),E482&gt;0,F482=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K482" s="50" t="str">
+        <x:f>IF(A482="","",IF(AND(ISNUMBER(E482),E482=0,OR(ISNUMBER(SEARCH("Free",D482&amp;"")),AND(ISNUMBER(F482),F482=0))),"Subscription",IF(ISNUMBER(G482),"Profit",IF(ISNUMBER(I482),"Loss",IF(ISNUMBER(H482),"Draw",IF(AND(ISNUMBER(F482),ISNUMBER(E482),E482&gt;0,F482&gt;E482),"Profit",IF(AND(ISNUMBER(F482),ISNUMBER(E482),E482&gt;0,F482=E482),"Draw",IF(AND(ISNUMBER(F482),ISNUMBER(E482),E482&gt;0,F482=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L482" s="50"/>
       <x:c r="M482" s="58"/>
       <x:c r="N482" s="58"/>
@@ -17313,8 +19225,12 @@
       <x:c r="G483" s="58"/>
       <x:c r="H483" s="58"/>
       <x:c r="I483" s="58"/>
-      <x:c r="J483" s="60"/>
-      <x:c r="K483" s="50"/>
+      <x:c r="J483" s="60" t="str">
+        <x:f>IF(A483="","",IF(K483="Subscription","",IF(E483=0,"",IF(ISNUMBER(G483),G483/E483,IF(ISNUMBER(I483),-ABS(I483)/E483,IF(ISNUMBER(H483),0,IF(AND(ISNUMBER(F483),ISNUMBER(E483),E483&gt;0,F483&gt;E483),(F483-E483)/E483,IF(AND(ISNUMBER(F483),ISNUMBER(E483),E483&gt;0,F483=E483),0,IF(AND(ISNUMBER(F483),ISNUMBER(E483),E483&gt;0,F483=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K483" s="50" t="str">
+        <x:f>IF(A483="","",IF(AND(ISNUMBER(E483),E483=0,OR(ISNUMBER(SEARCH("Free",D483&amp;"")),AND(ISNUMBER(F483),F483=0))),"Subscription",IF(ISNUMBER(G483),"Profit",IF(ISNUMBER(I483),"Loss",IF(ISNUMBER(H483),"Draw",IF(AND(ISNUMBER(F483),ISNUMBER(E483),E483&gt;0,F483&gt;E483),"Profit",IF(AND(ISNUMBER(F483),ISNUMBER(E483),E483&gt;0,F483=E483),"Draw",IF(AND(ISNUMBER(F483),ISNUMBER(E483),E483&gt;0,F483=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L483" s="50"/>
       <x:c r="M483" s="58"/>
       <x:c r="N483" s="58"/>
@@ -17346,8 +19262,12 @@
       <x:c r="G484" s="58"/>
       <x:c r="H484" s="58"/>
       <x:c r="I484" s="58"/>
-      <x:c r="J484" s="60"/>
-      <x:c r="K484" s="50"/>
+      <x:c r="J484" s="60" t="str">
+        <x:f>IF(A484="","",IF(K484="Subscription","",IF(E484=0,"",IF(ISNUMBER(G484),G484/E484,IF(ISNUMBER(I484),-ABS(I484)/E484,IF(ISNUMBER(H484),0,IF(AND(ISNUMBER(F484),ISNUMBER(E484),E484&gt;0,F484&gt;E484),(F484-E484)/E484,IF(AND(ISNUMBER(F484),ISNUMBER(E484),E484&gt;0,F484=E484),0,IF(AND(ISNUMBER(F484),ISNUMBER(E484),E484&gt;0,F484=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K484" s="50" t="str">
+        <x:f>IF(A484="","",IF(AND(ISNUMBER(E484),E484=0,OR(ISNUMBER(SEARCH("Free",D484&amp;"")),AND(ISNUMBER(F484),F484=0))),"Subscription",IF(ISNUMBER(G484),"Profit",IF(ISNUMBER(I484),"Loss",IF(ISNUMBER(H484),"Draw",IF(AND(ISNUMBER(F484),ISNUMBER(E484),E484&gt;0,F484&gt;E484),"Profit",IF(AND(ISNUMBER(F484),ISNUMBER(E484),E484&gt;0,F484=E484),"Draw",IF(AND(ISNUMBER(F484),ISNUMBER(E484),E484&gt;0,F484=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L484" s="50"/>
       <x:c r="M484" s="58"/>
       <x:c r="N484" s="58"/>
@@ -17379,8 +19299,12 @@
       <x:c r="G485" s="58"/>
       <x:c r="H485" s="58"/>
       <x:c r="I485" s="58"/>
-      <x:c r="J485" s="60"/>
-      <x:c r="K485" s="50"/>
+      <x:c r="J485" s="60" t="str">
+        <x:f>IF(A485="","",IF(K485="Subscription","",IF(E485=0,"",IF(ISNUMBER(G485),G485/E485,IF(ISNUMBER(I485),-ABS(I485)/E485,IF(ISNUMBER(H485),0,IF(AND(ISNUMBER(F485),ISNUMBER(E485),E485&gt;0,F485&gt;E485),(F485-E485)/E485,IF(AND(ISNUMBER(F485),ISNUMBER(E485),E485&gt;0,F485=E485),0,IF(AND(ISNUMBER(F485),ISNUMBER(E485),E485&gt;0,F485=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K485" s="50" t="str">
+        <x:f>IF(A485="","",IF(AND(ISNUMBER(E485),E485=0,OR(ISNUMBER(SEARCH("Free",D485&amp;"")),AND(ISNUMBER(F485),F485=0))),"Subscription",IF(ISNUMBER(G485),"Profit",IF(ISNUMBER(I485),"Loss",IF(ISNUMBER(H485),"Draw",IF(AND(ISNUMBER(F485),ISNUMBER(E485),E485&gt;0,F485&gt;E485),"Profit",IF(AND(ISNUMBER(F485),ISNUMBER(E485),E485&gt;0,F485=E485),"Draw",IF(AND(ISNUMBER(F485),ISNUMBER(E485),E485&gt;0,F485=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L485" s="50"/>
       <x:c r="M485" s="58"/>
       <x:c r="N485" s="58"/>
@@ -17412,8 +19336,12 @@
       <x:c r="G486" s="58"/>
       <x:c r="H486" s="58"/>
       <x:c r="I486" s="58"/>
-      <x:c r="J486" s="60"/>
-      <x:c r="K486" s="50"/>
+      <x:c r="J486" s="60" t="str">
+        <x:f>IF(A486="","",IF(K486="Subscription","",IF(E486=0,"",IF(ISNUMBER(G486),G486/E486,IF(ISNUMBER(I486),-ABS(I486)/E486,IF(ISNUMBER(H486),0,IF(AND(ISNUMBER(F486),ISNUMBER(E486),E486&gt;0,F486&gt;E486),(F486-E486)/E486,IF(AND(ISNUMBER(F486),ISNUMBER(E486),E486&gt;0,F486=E486),0,IF(AND(ISNUMBER(F486),ISNUMBER(E486),E486&gt;0,F486=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K486" s="50" t="str">
+        <x:f>IF(A486="","",IF(AND(ISNUMBER(E486),E486=0,OR(ISNUMBER(SEARCH("Free",D486&amp;"")),AND(ISNUMBER(F486),F486=0))),"Subscription",IF(ISNUMBER(G486),"Profit",IF(ISNUMBER(I486),"Loss",IF(ISNUMBER(H486),"Draw",IF(AND(ISNUMBER(F486),ISNUMBER(E486),E486&gt;0,F486&gt;E486),"Profit",IF(AND(ISNUMBER(F486),ISNUMBER(E486),E486&gt;0,F486=E486),"Draw",IF(AND(ISNUMBER(F486),ISNUMBER(E486),E486&gt;0,F486=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L486" s="50"/>
       <x:c r="M486" s="58"/>
       <x:c r="N486" s="58"/>
@@ -17445,8 +19373,12 @@
       <x:c r="G487" s="58"/>
       <x:c r="H487" s="58"/>
       <x:c r="I487" s="58"/>
-      <x:c r="J487" s="60"/>
-      <x:c r="K487" s="50"/>
+      <x:c r="J487" s="60" t="str">
+        <x:f>IF(A487="","",IF(K487="Subscription","",IF(E487=0,"",IF(ISNUMBER(G487),G487/E487,IF(ISNUMBER(I487),-ABS(I487)/E487,IF(ISNUMBER(H487),0,IF(AND(ISNUMBER(F487),ISNUMBER(E487),E487&gt;0,F487&gt;E487),(F487-E487)/E487,IF(AND(ISNUMBER(F487),ISNUMBER(E487),E487&gt;0,F487=E487),0,IF(AND(ISNUMBER(F487),ISNUMBER(E487),E487&gt;0,F487=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K487" s="50" t="str">
+        <x:f>IF(A487="","",IF(AND(ISNUMBER(E487),E487=0,OR(ISNUMBER(SEARCH("Free",D487&amp;"")),AND(ISNUMBER(F487),F487=0))),"Subscription",IF(ISNUMBER(G487),"Profit",IF(ISNUMBER(I487),"Loss",IF(ISNUMBER(H487),"Draw",IF(AND(ISNUMBER(F487),ISNUMBER(E487),E487&gt;0,F487&gt;E487),"Profit",IF(AND(ISNUMBER(F487),ISNUMBER(E487),E487&gt;0,F487=E487),"Draw",IF(AND(ISNUMBER(F487),ISNUMBER(E487),E487&gt;0,F487=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L487" s="50"/>
       <x:c r="M487" s="58"/>
       <x:c r="N487" s="58"/>
@@ -17478,8 +19410,12 @@
       <x:c r="G488" s="58"/>
       <x:c r="H488" s="58"/>
       <x:c r="I488" s="58"/>
-      <x:c r="J488" s="60"/>
-      <x:c r="K488" s="50"/>
+      <x:c r="J488" s="60" t="str">
+        <x:f>IF(A488="","",IF(K488="Subscription","",IF(E488=0,"",IF(ISNUMBER(G488),G488/E488,IF(ISNUMBER(I488),-ABS(I488)/E488,IF(ISNUMBER(H488),0,IF(AND(ISNUMBER(F488),ISNUMBER(E488),E488&gt;0,F488&gt;E488),(F488-E488)/E488,IF(AND(ISNUMBER(F488),ISNUMBER(E488),E488&gt;0,F488=E488),0,IF(AND(ISNUMBER(F488),ISNUMBER(E488),E488&gt;0,F488=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K488" s="50" t="str">
+        <x:f>IF(A488="","",IF(AND(ISNUMBER(E488),E488=0,OR(ISNUMBER(SEARCH("Free",D488&amp;"")),AND(ISNUMBER(F488),F488=0))),"Subscription",IF(ISNUMBER(G488),"Profit",IF(ISNUMBER(I488),"Loss",IF(ISNUMBER(H488),"Draw",IF(AND(ISNUMBER(F488),ISNUMBER(E488),E488&gt;0,F488&gt;E488),"Profit",IF(AND(ISNUMBER(F488),ISNUMBER(E488),E488&gt;0,F488=E488),"Draw",IF(AND(ISNUMBER(F488),ISNUMBER(E488),E488&gt;0,F488=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L488" s="50"/>
       <x:c r="M488" s="58"/>
       <x:c r="N488" s="58"/>
@@ -17511,8 +19447,12 @@
       <x:c r="G489" s="58"/>
       <x:c r="H489" s="58"/>
       <x:c r="I489" s="58"/>
-      <x:c r="J489" s="60"/>
-      <x:c r="K489" s="50"/>
+      <x:c r="J489" s="60" t="str">
+        <x:f>IF(A489="","",IF(K489="Subscription","",IF(E489=0,"",IF(ISNUMBER(G489),G489/E489,IF(ISNUMBER(I489),-ABS(I489)/E489,IF(ISNUMBER(H489),0,IF(AND(ISNUMBER(F489),ISNUMBER(E489),E489&gt;0,F489&gt;E489),(F489-E489)/E489,IF(AND(ISNUMBER(F489),ISNUMBER(E489),E489&gt;0,F489=E489),0,IF(AND(ISNUMBER(F489),ISNUMBER(E489),E489&gt;0,F489=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K489" s="50" t="str">
+        <x:f>IF(A489="","",IF(AND(ISNUMBER(E489),E489=0,OR(ISNUMBER(SEARCH("Free",D489&amp;"")),AND(ISNUMBER(F489),F489=0))),"Subscription",IF(ISNUMBER(G489),"Profit",IF(ISNUMBER(I489),"Loss",IF(ISNUMBER(H489),"Draw",IF(AND(ISNUMBER(F489),ISNUMBER(E489),E489&gt;0,F489&gt;E489),"Profit",IF(AND(ISNUMBER(F489),ISNUMBER(E489),E489&gt;0,F489=E489),"Draw",IF(AND(ISNUMBER(F489),ISNUMBER(E489),E489&gt;0,F489=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L489" s="50"/>
       <x:c r="M489" s="58"/>
       <x:c r="N489" s="58"/>
@@ -17544,8 +19484,12 @@
       <x:c r="G490" s="58"/>
       <x:c r="H490" s="58"/>
       <x:c r="I490" s="58"/>
-      <x:c r="J490" s="60"/>
-      <x:c r="K490" s="50"/>
+      <x:c r="J490" s="60" t="str">
+        <x:f>IF(A490="","",IF(K490="Subscription","",IF(E490=0,"",IF(ISNUMBER(G490),G490/E490,IF(ISNUMBER(I490),-ABS(I490)/E490,IF(ISNUMBER(H490),0,IF(AND(ISNUMBER(F490),ISNUMBER(E490),E490&gt;0,F490&gt;E490),(F490-E490)/E490,IF(AND(ISNUMBER(F490),ISNUMBER(E490),E490&gt;0,F490=E490),0,IF(AND(ISNUMBER(F490),ISNUMBER(E490),E490&gt;0,F490=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K490" s="50" t="str">
+        <x:f>IF(A490="","",IF(AND(ISNUMBER(E490),E490=0,OR(ISNUMBER(SEARCH("Free",D490&amp;"")),AND(ISNUMBER(F490),F490=0))),"Subscription",IF(ISNUMBER(G490),"Profit",IF(ISNUMBER(I490),"Loss",IF(ISNUMBER(H490),"Draw",IF(AND(ISNUMBER(F490),ISNUMBER(E490),E490&gt;0,F490&gt;E490),"Profit",IF(AND(ISNUMBER(F490),ISNUMBER(E490),E490&gt;0,F490=E490),"Draw",IF(AND(ISNUMBER(F490),ISNUMBER(E490),E490&gt;0,F490=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L490" s="50"/>
       <x:c r="M490" s="58"/>
       <x:c r="N490" s="58"/>
@@ -17577,8 +19521,12 @@
       <x:c r="G491" s="58"/>
       <x:c r="H491" s="58"/>
       <x:c r="I491" s="58"/>
-      <x:c r="J491" s="60"/>
-      <x:c r="K491" s="50"/>
+      <x:c r="J491" s="60" t="str">
+        <x:f>IF(A491="","",IF(K491="Subscription","",IF(E491=0,"",IF(ISNUMBER(G491),G491/E491,IF(ISNUMBER(I491),-ABS(I491)/E491,IF(ISNUMBER(H491),0,IF(AND(ISNUMBER(F491),ISNUMBER(E491),E491&gt;0,F491&gt;E491),(F491-E491)/E491,IF(AND(ISNUMBER(F491),ISNUMBER(E491),E491&gt;0,F491=E491),0,IF(AND(ISNUMBER(F491),ISNUMBER(E491),E491&gt;0,F491=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K491" s="50" t="str">
+        <x:f>IF(A491="","",IF(AND(ISNUMBER(E491),E491=0,OR(ISNUMBER(SEARCH("Free",D491&amp;"")),AND(ISNUMBER(F491),F491=0))),"Subscription",IF(ISNUMBER(G491),"Profit",IF(ISNUMBER(I491),"Loss",IF(ISNUMBER(H491),"Draw",IF(AND(ISNUMBER(F491),ISNUMBER(E491),E491&gt;0,F491&gt;E491),"Profit",IF(AND(ISNUMBER(F491),ISNUMBER(E491),E491&gt;0,F491=E491),"Draw",IF(AND(ISNUMBER(F491),ISNUMBER(E491),E491&gt;0,F491=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L491" s="50"/>
       <x:c r="M491" s="58"/>
       <x:c r="N491" s="58"/>
@@ -17610,8 +19558,12 @@
       <x:c r="G492" s="58"/>
       <x:c r="H492" s="58"/>
       <x:c r="I492" s="58"/>
-      <x:c r="J492" s="60"/>
-      <x:c r="K492" s="50"/>
+      <x:c r="J492" s="60" t="str">
+        <x:f>IF(A492="","",IF(K492="Subscription","",IF(E492=0,"",IF(ISNUMBER(G492),G492/E492,IF(ISNUMBER(I492),-ABS(I492)/E492,IF(ISNUMBER(H492),0,IF(AND(ISNUMBER(F492),ISNUMBER(E492),E492&gt;0,F492&gt;E492),(F492-E492)/E492,IF(AND(ISNUMBER(F492),ISNUMBER(E492),E492&gt;0,F492=E492),0,IF(AND(ISNUMBER(F492),ISNUMBER(E492),E492&gt;0,F492=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K492" s="50" t="str">
+        <x:f>IF(A492="","",IF(AND(ISNUMBER(E492),E492=0,OR(ISNUMBER(SEARCH("Free",D492&amp;"")),AND(ISNUMBER(F492),F492=0))),"Subscription",IF(ISNUMBER(G492),"Profit",IF(ISNUMBER(I492),"Loss",IF(ISNUMBER(H492),"Draw",IF(AND(ISNUMBER(F492),ISNUMBER(E492),E492&gt;0,F492&gt;E492),"Profit",IF(AND(ISNUMBER(F492),ISNUMBER(E492),E492&gt;0,F492=E492),"Draw",IF(AND(ISNUMBER(F492),ISNUMBER(E492),E492&gt;0,F492=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L492" s="50"/>
       <x:c r="M492" s="58"/>
       <x:c r="N492" s="58"/>
@@ -17643,8 +19595,12 @@
       <x:c r="G493" s="58"/>
       <x:c r="H493" s="58"/>
       <x:c r="I493" s="58"/>
-      <x:c r="J493" s="60"/>
-      <x:c r="K493" s="50"/>
+      <x:c r="J493" s="60" t="str">
+        <x:f>IF(A493="","",IF(K493="Subscription","",IF(E493=0,"",IF(ISNUMBER(G493),G493/E493,IF(ISNUMBER(I493),-ABS(I493)/E493,IF(ISNUMBER(H493),0,IF(AND(ISNUMBER(F493),ISNUMBER(E493),E493&gt;0,F493&gt;E493),(F493-E493)/E493,IF(AND(ISNUMBER(F493),ISNUMBER(E493),E493&gt;0,F493=E493),0,IF(AND(ISNUMBER(F493),ISNUMBER(E493),E493&gt;0,F493=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K493" s="50" t="str">
+        <x:f>IF(A493="","",IF(AND(ISNUMBER(E493),E493=0,OR(ISNUMBER(SEARCH("Free",D493&amp;"")),AND(ISNUMBER(F493),F493=0))),"Subscription",IF(ISNUMBER(G493),"Profit",IF(ISNUMBER(I493),"Loss",IF(ISNUMBER(H493),"Draw",IF(AND(ISNUMBER(F493),ISNUMBER(E493),E493&gt;0,F493&gt;E493),"Profit",IF(AND(ISNUMBER(F493),ISNUMBER(E493),E493&gt;0,F493=E493),"Draw",IF(AND(ISNUMBER(F493),ISNUMBER(E493),E493&gt;0,F493=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L493" s="50"/>
       <x:c r="M493" s="58"/>
       <x:c r="N493" s="58"/>
@@ -17676,8 +19632,12 @@
       <x:c r="G494" s="58"/>
       <x:c r="H494" s="58"/>
       <x:c r="I494" s="58"/>
-      <x:c r="J494" s="60"/>
-      <x:c r="K494" s="50"/>
+      <x:c r="J494" s="60" t="str">
+        <x:f>IF(A494="","",IF(K494="Subscription","",IF(E494=0,"",IF(ISNUMBER(G494),G494/E494,IF(ISNUMBER(I494),-ABS(I494)/E494,IF(ISNUMBER(H494),0,IF(AND(ISNUMBER(F494),ISNUMBER(E494),E494&gt;0,F494&gt;E494),(F494-E494)/E494,IF(AND(ISNUMBER(F494),ISNUMBER(E494),E494&gt;0,F494=E494),0,IF(AND(ISNUMBER(F494),ISNUMBER(E494),E494&gt;0,F494=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K494" s="50" t="str">
+        <x:f>IF(A494="","",IF(AND(ISNUMBER(E494),E494=0,OR(ISNUMBER(SEARCH("Free",D494&amp;"")),AND(ISNUMBER(F494),F494=0))),"Subscription",IF(ISNUMBER(G494),"Profit",IF(ISNUMBER(I494),"Loss",IF(ISNUMBER(H494),"Draw",IF(AND(ISNUMBER(F494),ISNUMBER(E494),E494&gt;0,F494&gt;E494),"Profit",IF(AND(ISNUMBER(F494),ISNUMBER(E494),E494&gt;0,F494=E494),"Draw",IF(AND(ISNUMBER(F494),ISNUMBER(E494),E494&gt;0,F494=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L494" s="50"/>
       <x:c r="M494" s="58"/>
       <x:c r="N494" s="58"/>
@@ -17709,8 +19669,12 @@
       <x:c r="G495" s="58"/>
       <x:c r="H495" s="58"/>
       <x:c r="I495" s="58"/>
-      <x:c r="J495" s="60"/>
-      <x:c r="K495" s="50"/>
+      <x:c r="J495" s="60" t="str">
+        <x:f>IF(A495="","",IF(K495="Subscription","",IF(E495=0,"",IF(ISNUMBER(G495),G495/E495,IF(ISNUMBER(I495),-ABS(I495)/E495,IF(ISNUMBER(H495),0,IF(AND(ISNUMBER(F495),ISNUMBER(E495),E495&gt;0,F495&gt;E495),(F495-E495)/E495,IF(AND(ISNUMBER(F495),ISNUMBER(E495),E495&gt;0,F495=E495),0,IF(AND(ISNUMBER(F495),ISNUMBER(E495),E495&gt;0,F495=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K495" s="50" t="str">
+        <x:f>IF(A495="","",IF(AND(ISNUMBER(E495),E495=0,OR(ISNUMBER(SEARCH("Free",D495&amp;"")),AND(ISNUMBER(F495),F495=0))),"Subscription",IF(ISNUMBER(G495),"Profit",IF(ISNUMBER(I495),"Loss",IF(ISNUMBER(H495),"Draw",IF(AND(ISNUMBER(F495),ISNUMBER(E495),E495&gt;0,F495&gt;E495),"Profit",IF(AND(ISNUMBER(F495),ISNUMBER(E495),E495&gt;0,F495=E495),"Draw",IF(AND(ISNUMBER(F495),ISNUMBER(E495),E495&gt;0,F495=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L495" s="50"/>
       <x:c r="M495" s="58"/>
       <x:c r="N495" s="58"/>
@@ -17742,8 +19706,12 @@
       <x:c r="G496" s="58"/>
       <x:c r="H496" s="58"/>
       <x:c r="I496" s="58"/>
-      <x:c r="J496" s="60"/>
-      <x:c r="K496" s="50"/>
+      <x:c r="J496" s="60" t="str">
+        <x:f>IF(A496="","",IF(K496="Subscription","",IF(E496=0,"",IF(ISNUMBER(G496),G496/E496,IF(ISNUMBER(I496),-ABS(I496)/E496,IF(ISNUMBER(H496),0,IF(AND(ISNUMBER(F496),ISNUMBER(E496),E496&gt;0,F496&gt;E496),(F496-E496)/E496,IF(AND(ISNUMBER(F496),ISNUMBER(E496),E496&gt;0,F496=E496),0,IF(AND(ISNUMBER(F496),ISNUMBER(E496),E496&gt;0,F496=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K496" s="50" t="str">
+        <x:f>IF(A496="","",IF(AND(ISNUMBER(E496),E496=0,OR(ISNUMBER(SEARCH("Free",D496&amp;"")),AND(ISNUMBER(F496),F496=0))),"Subscription",IF(ISNUMBER(G496),"Profit",IF(ISNUMBER(I496),"Loss",IF(ISNUMBER(H496),"Draw",IF(AND(ISNUMBER(F496),ISNUMBER(E496),E496&gt;0,F496&gt;E496),"Profit",IF(AND(ISNUMBER(F496),ISNUMBER(E496),E496&gt;0,F496=E496),"Draw",IF(AND(ISNUMBER(F496),ISNUMBER(E496),E496&gt;0,F496=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L496" s="50"/>
       <x:c r="M496" s="58"/>
       <x:c r="N496" s="58"/>
@@ -17775,8 +19743,12 @@
       <x:c r="G497" s="58"/>
       <x:c r="H497" s="58"/>
       <x:c r="I497" s="58"/>
-      <x:c r="J497" s="60"/>
-      <x:c r="K497" s="50"/>
+      <x:c r="J497" s="60" t="str">
+        <x:f>IF(A497="","",IF(K497="Subscription","",IF(E497=0,"",IF(ISNUMBER(G497),G497/E497,IF(ISNUMBER(I497),-ABS(I497)/E497,IF(ISNUMBER(H497),0,IF(AND(ISNUMBER(F497),ISNUMBER(E497),E497&gt;0,F497&gt;E497),(F497-E497)/E497,IF(AND(ISNUMBER(F497),ISNUMBER(E497),E497&gt;0,F497=E497),0,IF(AND(ISNUMBER(F497),ISNUMBER(E497),E497&gt;0,F497=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K497" s="50" t="str">
+        <x:f>IF(A497="","",IF(AND(ISNUMBER(E497),E497=0,OR(ISNUMBER(SEARCH("Free",D497&amp;"")),AND(ISNUMBER(F497),F497=0))),"Subscription",IF(ISNUMBER(G497),"Profit",IF(ISNUMBER(I497),"Loss",IF(ISNUMBER(H497),"Draw",IF(AND(ISNUMBER(F497),ISNUMBER(E497),E497&gt;0,F497&gt;E497),"Profit",IF(AND(ISNUMBER(F497),ISNUMBER(E497),E497&gt;0,F497=E497),"Draw",IF(AND(ISNUMBER(F497),ISNUMBER(E497),E497&gt;0,F497=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L497" s="50"/>
       <x:c r="M497" s="58"/>
       <x:c r="N497" s="58"/>
@@ -17808,8 +19780,12 @@
       <x:c r="G498" s="58"/>
       <x:c r="H498" s="58"/>
       <x:c r="I498" s="58"/>
-      <x:c r="J498" s="60"/>
-      <x:c r="K498" s="50"/>
+      <x:c r="J498" s="60" t="str">
+        <x:f>IF(A498="","",IF(K498="Subscription","",IF(E498=0,"",IF(ISNUMBER(G498),G498/E498,IF(ISNUMBER(I498),-ABS(I498)/E498,IF(ISNUMBER(H498),0,IF(AND(ISNUMBER(F498),ISNUMBER(E498),E498&gt;0,F498&gt;E498),(F498-E498)/E498,IF(AND(ISNUMBER(F498),ISNUMBER(E498),E498&gt;0,F498=E498),0,IF(AND(ISNUMBER(F498),ISNUMBER(E498),E498&gt;0,F498=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K498" s="50" t="str">
+        <x:f>IF(A498="","",IF(AND(ISNUMBER(E498),E498=0,OR(ISNUMBER(SEARCH("Free",D498&amp;"")),AND(ISNUMBER(F498),F498=0))),"Subscription",IF(ISNUMBER(G498),"Profit",IF(ISNUMBER(I498),"Loss",IF(ISNUMBER(H498),"Draw",IF(AND(ISNUMBER(F498),ISNUMBER(E498),E498&gt;0,F498&gt;E498),"Profit",IF(AND(ISNUMBER(F498),ISNUMBER(E498),E498&gt;0,F498=E498),"Draw",IF(AND(ISNUMBER(F498),ISNUMBER(E498),E498&gt;0,F498=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L498" s="50"/>
       <x:c r="M498" s="58"/>
       <x:c r="N498" s="58"/>
@@ -17841,8 +19817,12 @@
       <x:c r="G499" s="58"/>
       <x:c r="H499" s="58"/>
       <x:c r="I499" s="58"/>
-      <x:c r="J499" s="60"/>
-      <x:c r="K499" s="50"/>
+      <x:c r="J499" s="60" t="str">
+        <x:f>IF(A499="","",IF(K499="Subscription","",IF(E499=0,"",IF(ISNUMBER(G499),G499/E499,IF(ISNUMBER(I499),-ABS(I499)/E499,IF(ISNUMBER(H499),0,IF(AND(ISNUMBER(F499),ISNUMBER(E499),E499&gt;0,F499&gt;E499),(F499-E499)/E499,IF(AND(ISNUMBER(F499),ISNUMBER(E499),E499&gt;0,F499=E499),0,IF(AND(ISNUMBER(F499),ISNUMBER(E499),E499&gt;0,F499=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K499" s="50" t="str">
+        <x:f>IF(A499="","",IF(AND(ISNUMBER(E499),E499=0,OR(ISNUMBER(SEARCH("Free",D499&amp;"")),AND(ISNUMBER(F499),F499=0))),"Subscription",IF(ISNUMBER(G499),"Profit",IF(ISNUMBER(I499),"Loss",IF(ISNUMBER(H499),"Draw",IF(AND(ISNUMBER(F499),ISNUMBER(E499),E499&gt;0,F499&gt;E499),"Profit",IF(AND(ISNUMBER(F499),ISNUMBER(E499),E499&gt;0,F499=E499),"Draw",IF(AND(ISNUMBER(F499),ISNUMBER(E499),E499&gt;0,F499=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L499" s="50"/>
       <x:c r="M499" s="58"/>
       <x:c r="N499" s="58"/>
@@ -17874,8 +19854,12 @@
       <x:c r="G500" s="58"/>
       <x:c r="H500" s="58"/>
       <x:c r="I500" s="58"/>
-      <x:c r="J500" s="60"/>
-      <x:c r="K500" s="50"/>
+      <x:c r="J500" s="60" t="str">
+        <x:f>IF(A500="","",IF(K500="Subscription","",IF(E500=0,"",IF(ISNUMBER(G500),G500/E500,IF(ISNUMBER(I500),-ABS(I500)/E500,IF(ISNUMBER(H500),0,IF(AND(ISNUMBER(F500),ISNUMBER(E500),E500&gt;0,F500&gt;E500),(F500-E500)/E500,IF(AND(ISNUMBER(F500),ISNUMBER(E500),E500&gt;0,F500=E500),0,IF(AND(ISNUMBER(F500),ISNUMBER(E500),E500&gt;0,F500=0),-1,"")))))))))</x:f>
+      </x:c>
+      <x:c r="K500" s="50" t="str">
+        <x:f>IF(A500="","",IF(AND(ISNUMBER(E500),E500=0,OR(ISNUMBER(SEARCH("Free",D500&amp;"")),AND(ISNUMBER(F500),F500=0))),"Subscription",IF(ISNUMBER(G500),"Profit",IF(ISNUMBER(I500),"Loss",IF(ISNUMBER(H500),"Draw",IF(AND(ISNUMBER(F500),ISNUMBER(E500),E500&gt;0,F500&gt;E500),"Profit",IF(AND(ISNUMBER(F500),ISNUMBER(E500),E500&gt;0,F500=E500),"Draw",IF(AND(ISNUMBER(F500),ISNUMBER(E500),E500&gt;0,F500=0),"Loss",""))))))))</x:f>
+      </x:c>
       <x:c r="L500" s="50"/>
       <x:c r="M500" s="58"/>
       <x:c r="N500" s="58"/>
@@ -18079,7 +20063,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbb01edc0559f47ea"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb52e0862851145dd"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -18352,7 +20336,7 @@
     <x:mergeCell ref="A22:H25"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Raea93e168a1a4241"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1251be5e45c2476d"/>
 </x:worksheet>
 </file>
 
@@ -19518,7 +21502,7 @@
     <x:mergeCell ref="A48:H48"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R07a762a4981e4e07"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R072d216a6a55410d"/>
 </x:worksheet>
 </file>
 

--- a/StepCat_Blank_Profitability_Analysis_Template.xlsx
+++ b/StepCat_Blank_Profitability_Analysis_Template.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instructions" sheetId="1" r:id="Rde3eab50dd724f12"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Game Records" sheetId="2" r:id="Re97a74b5d7434030"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="3" r:id="R59566356a4cb4fb7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Game Comparisons" sheetId="4" r:id="R6180fe6c8d4a473f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Best Results" sheetId="5" r:id="R64488d50d4294b3c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instructions" sheetId="1" r:id="R3a83a39053264690"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Game Records" sheetId="2" r:id="Ra7c62eadc6dd4776"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="3" r:id="R660c75803cb44a91"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Game Comparisons" sheetId="4" r:id="R55ff3f2036ec4808"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Best Results" sheetId="5" r:id="R1c44143212064f2b"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -770,7 +770,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rd094fb9437b24331"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rbbf4d00caece4eb7"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -805,7 +805,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R769e911d58404c18"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R4ba1c6cc2e0c4442"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1006,7 +1006,7 @@
   <x:sheetData>
     <x:row r="1" ht="34" customHeight="1">
       <x:c r="A1" s="5" t="str">
-        <x:v>StepCat Profitability Analysis Template</x:v>
+        <x:v>StepCat v200 Profitability Analysis Template</x:v>
       </x:c>
       <x:c r="B1" s="5"/>
       <x:c r="C1" s="5"/>
@@ -1028,6 +1028,9 @@
       <x:c r="G2" s="14"/>
       <x:c r="H2" s="14"/>
     </x:row>
+    <x:row r="3">
+      <x:c r="A3"/>
+    </x:row>
     <x:row r="4">
       <x:c r="A4" s="23" t="str">
         <x:v>1. Prepare StepCat</x:v>
@@ -1042,7 +1045,7 @@
     </x:row>
     <x:row r="5" ht="28" customHeight="1">
       <x:c r="A5" s="32" t="str">
-        <x:v>• In Spreadsheet Copy Setup, include Game Type, Gross Pot, Adjusted Pot, Eligible Winners, and Total Players.</x:v>
+        <x:v>• Copy rows as plain values. The spreadsheet controls font size, alignment, borders, and formulas.</x:v>
       </x:c>
       <x:c r="B5" s="32"/>
       <x:c r="C5" s="32"/>
@@ -1066,7 +1069,7 @@
     </x:row>
     <x:row r="7" ht="28" customHeight="1">
       <x:c r="A7" s="32" t="str">
-        <x:v>• Paste StepCat rows into Game Records starting in cell A5. Columns A through P match the StepCat row order.</x:v>
+        <x:v>• Paste StepCat rows into Game Records starting in cell A5. Columns A through K match the core StepCat row order.</x:v>
       </x:c>
       <x:c r="B7" s="32"/>
       <x:c r="C7" s="32"/>
@@ -1076,9 +1079,12 @@
       <x:c r="G7" s="32"/>
       <x:c r="H7" s="32"/>
     </x:row>
+    <x:row r="8">
+      <x:c r="A8"/>
+    </x:row>
     <x:row r="9">
       <x:c r="A9" s="23" t="str">
-        <x:v>2. Analysis fields already included</x:v>
+        <x:v>2. For best estimate accuracy</x:v>
       </x:c>
       <x:c r="B9" s="23"/>
       <x:c r="C9" s="23"/>
@@ -1090,7 +1096,7 @@
     </x:row>
     <x:row r="10" ht="28" customHeight="1">
       <x:c r="A10" s="32" t="str">
-        <x:v>• Challenge Length is calculated from Start Date and End Date.</x:v>
+        <x:v>• Add new challenges after warm-up week ends and the challenge begins proper.</x:v>
       </x:c>
       <x:c r="B10" s="32"/>
       <x:c r="C10" s="32"/>
@@ -1102,7 +1108,7 @@
     </x:row>
     <x:row r="11" ht="28" customHeight="1">
       <x:c r="A11" s="32" t="str">
-        <x:v>• Count Source: Reported, Estimated, or Partly Estimated.</x:v>
+        <x:v>• Gross Pot and Total Players are usually more reliable after warm-up week.</x:v>
       </x:c>
       <x:c r="B11" s="32"/>
       <x:c r="C11" s="32"/>
@@ -1114,7 +1120,7 @@
     </x:row>
     <x:row r="12" ht="28" customHeight="1">
       <x:c r="A12" s="32" t="str">
-        <x:v>• Confidence: High, Medium, or Low for estimated counts.</x:v>
+        <x:v>• Update Eligible Winners as the challenge progresses; this drives estimate accuracy.</x:v>
       </x:c>
       <x:c r="B12" s="32"/>
       <x:c r="C12" s="32"/>
@@ -1125,9 +1131,7 @@
       <x:c r="H12" s="32"/>
     </x:row>
     <x:row r="13" ht="28" customHeight="1">
-      <x:c r="A13" s="32" t="str">
-        <x:v>• Notes can explain how an estimate was obtained.</x:v>
-      </x:c>
+      <x:c r="A13" s="32"/>
       <x:c r="B13" s="32"/>
       <x:c r="C13" s="32"/>
       <x:c r="D13" s="32"/>
@@ -1138,7 +1142,7 @@
     </x:row>
     <x:row r="14" ht="28" customHeight="1">
       <x:c r="A14" s="32" t="str">
-        <x:v>• Net Profit, Eliminated Players, and Elimination Rate calculate automatically.</x:v>
+        <x:v>3. Older and in-progress rows</x:v>
       </x:c>
       <x:c r="B14" s="32"/>
       <x:c r="C14" s="32"/>
@@ -1148,9 +1152,14 @@
       <x:c r="G14" s="32"/>
       <x:c r="H14" s="32"/>
     </x:row>
+    <x:row r="15">
+      <x:c r="A15" t="str">
+        <x:v>• Paste older entries into matching columns, or recalculate them in StepCat and paste over the matching row.</x:v>
+      </x:c>
+    </x:row>
     <x:row r="16">
       <x:c r="A16" s="23" t="str">
-        <x:v>3. Simple definitions</x:v>
+        <x:v>• Formula columns such as ROI, Result, Challenge Length, Net Profit, Eliminated Players, and Elimination Rate are included.</x:v>
       </x:c>
       <x:c r="B16" s="23"/>
       <x:c r="C16" s="23"/>
@@ -1162,7 +1171,7 @@
     </x:row>
     <x:row r="17" ht="28" customHeight="1">
       <x:c r="A17" s="32" t="str">
-        <x:v>• Earned: total amount returned when the challenge ended.</x:v>
+        <x:v>• For in-progress rows, enter known values now and update Earned, Profit, Draw, or Lost when the game finishes.</x:v>
       </x:c>
       <x:c r="B17" s="32"/>
       <x:c r="C17" s="32"/>
@@ -1173,9 +1182,7 @@
       <x:c r="H17" s="32"/>
     </x:row>
     <x:row r="18" ht="28" customHeight="1">
-      <x:c r="A18" s="32" t="str">
-        <x:v>• Profit: amount earned above the Entry Fee.</x:v>
-      </x:c>
+      <x:c r="A18" s="32"/>
       <x:c r="B18" s="32"/>
       <x:c r="C18" s="32"/>
       <x:c r="D18" s="32"/>
@@ -1186,7 +1193,7 @@
     </x:row>
     <x:row r="19" ht="28" customHeight="1">
       <x:c r="A19" s="32" t="str">
-        <x:v>• Draw: Entry Fee returned with no profit.</x:v>
+        <x:v>4. Simple definitions</x:v>
       </x:c>
       <x:c r="B19" s="32"/>
       <x:c r="C19" s="32"/>
@@ -1198,7 +1205,7 @@
     </x:row>
     <x:row r="20" ht="28" customHeight="1">
       <x:c r="A20" s="32" t="str">
-        <x:v>• Lost: Entry Fee forfeited.</x:v>
+        <x:v>• Earned: total amount returned when the challenge ended.</x:v>
       </x:c>
       <x:c r="B20" s="32"/>
       <x:c r="C20" s="32"/>
@@ -1210,7 +1217,7 @@
     </x:row>
     <x:row r="21" ht="28" customHeight="1">
       <x:c r="A21" s="32" t="str">
-        <x:v>• ROI: Profit compared with the Entry Fee.</x:v>
+        <x:v>• Profit: amount earned above the Entry Fee.</x:v>
       </x:c>
       <x:c r="B21" s="32"/>
       <x:c r="C21" s="32"/>
@@ -1222,7 +1229,7 @@
     </x:row>
     <x:row r="22" ht="28" customHeight="1">
       <x:c r="A22" s="32" t="str">
-        <x:v>• Result: Profit, Draw, Disqualified, Loss, or Subscription.</x:v>
+        <x:v>• Draw: Entry Fee returned with no profit.</x:v>
       </x:c>
       <x:c r="B22" s="32"/>
       <x:c r="C22" s="32"/>
@@ -1234,7 +1241,7 @@
     </x:row>
     <x:row r="23" ht="28" customHeight="1">
       <x:c r="A23" s="32" t="str">
-        <x:v>• Challenge Length: number of weeks between Start Date and End Date.</x:v>
+        <x:v>• Lost: Entry Fee forfeited.</x:v>
       </x:c>
       <x:c r="B23" s="32"/>
       <x:c r="C23" s="32"/>
@@ -1244,9 +1251,14 @@
       <x:c r="G23" s="32"/>
       <x:c r="H23" s="32"/>
     </x:row>
+    <x:row r="24">
+      <x:c r="A24" t="str">
+        <x:v>• ROI: Profit compared with the Entry Fee.</x:v>
+      </x:c>
+    </x:row>
     <x:row r="25">
       <x:c r="A25" s="23" t="str">
-        <x:v>4. Important note</x:v>
+        <x:v>• Result: Profit, Draw, Disqualified, or Subscription.</x:v>
       </x:c>
       <x:c r="B25" s="23"/>
       <x:c r="C25" s="23"/>
@@ -1258,7 +1270,7 @@
     </x:row>
     <x:row r="26" ht="28" customHeight="1">
       <x:c r="A26" s="32" t="str">
-        <x:v>• Profit is recorded only when a challenge ends; Challenge Length is used for comparison, not weekly payout.</x:v>
+        <x:v>• Challenge Length: number of weeks between Start Date and End Date.</x:v>
       </x:c>
       <x:c r="B26" s="32"/>
       <x:c r="C26" s="32"/>
@@ -1269,9 +1281,7 @@
       <x:c r="H26" s="32"/>
     </x:row>
     <x:row r="27" ht="28" customHeight="1">
-      <x:c r="A27" s="32" t="str">
-        <x:v>• Challenge Length is used only to compare completed games of different lengths.</x:v>
-      </x:c>
+      <x:c r="A27" s="32"/>
       <x:c r="B27" s="32"/>
       <x:c r="C27" s="32"/>
       <x:c r="D27" s="32"/>
@@ -1282,7 +1292,7 @@
     </x:row>
     <x:row r="28" ht="28" customHeight="1">
       <x:c r="A28" s="32" t="str">
-        <x:v>• Estimated player counts should be treated as directional rather than exact.</x:v>
+        <x:v>5. What updates automatically</x:v>
       </x:c>
       <x:c r="B28" s="32"/>
       <x:c r="C28" s="32"/>
@@ -1292,9 +1302,14 @@
       <x:c r="G28" s="32"/>
       <x:c r="H28" s="32"/>
     </x:row>
+    <x:row r="29">
+      <x:c r="A29" t="str">
+        <x:v>• Summary shows totals, averages, and result rates.</x:v>
+      </x:c>
+    </x:row>
     <x:row r="30">
       <x:c r="A30" s="23" t="str">
-        <x:v>5. What updates automatically</x:v>
+        <x:v>• Game Comparisons compares game type, challenge length, entry fee, payment type, player ranges, and elimination rates.</x:v>
       </x:c>
       <x:c r="B30" s="23"/>
       <x:c r="C30" s="23"/>
@@ -1306,7 +1321,7 @@
     </x:row>
     <x:row r="31" ht="28" customHeight="1">
       <x:c r="A31" s="32" t="str">
-        <x:v>• Summary shows totals, averages, and result rates.</x:v>
+        <x:v>• Best Results lists the highest Net Profit and ROI values.</x:v>
       </x:c>
       <x:c r="B31" s="32"/>
       <x:c r="C31" s="32"/>
@@ -1317,9 +1332,7 @@
       <x:c r="H31" s="32"/>
     </x:row>
     <x:row r="32" ht="28" customHeight="1">
-      <x:c r="A32" s="32" t="str">
-        <x:v>• Game Comparisons compares game type, challenge length, entry fee, payment type, player ranges, and elimination rates.</x:v>
-      </x:c>
+      <x:c r="A32" s="32"/>
       <x:c r="B32" s="32"/>
       <x:c r="C32" s="32"/>
       <x:c r="D32" s="32"/>
@@ -1330,7 +1343,7 @@
     </x:row>
     <x:row r="33" ht="28" customHeight="1">
       <x:c r="A33" s="32" t="str">
-        <x:v>• Best Results lists the highest Net Profit and ROI values.</x:v>
+        <x:v>The official posted game result should always be treated as authoritative.</x:v>
       </x:c>
       <x:c r="B33" s="32"/>
       <x:c r="C33" s="32"/>
@@ -1406,7 +1419,7 @@
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
       <x:c r="A1" s="5" t="str">
-        <x:v>Game Records</x:v>
+        <x:v>Game Records - StepCat v200</x:v>
       </x:c>
       <x:c r="B1" s="5"/>
       <x:c r="C1" s="5"/>
@@ -1433,7 +1446,7 @@
     </x:row>
     <x:row r="2" ht="28" customHeight="1">
       <x:c r="A2" s="14" t="str">
-        <x:v>Paste completed StepCat rows into A5:K, or manually update in-progress rows. For manual/pre-StepCat rows, ROI and Result formulas can calculate from Entry Fee plus Profit, Draw, or Lost.</x:v>
+        <x:v>Paste StepCat rows into A5:K, or paste older rows into matching columns. Built-in formulas calculate supported fields such as ROI, Result, Challenge Length, Net Profit, Eliminated Players, and Elimination Rate.</x:v>
       </x:c>
       <x:c r="B2" s="14"/>
       <x:c r="C2" s="14"/>
@@ -1543,7 +1556,7 @@
         <x:f>IF(A5="","",IF(K5="Subscription","",IF(E5=0,"",IF(ISNUMBER(G5),G5/E5,IF(ISNUMBER(I5),-ABS(I5)/E5,IF(ISNUMBER(H5),0,IF(AND(ISNUMBER(F5),ISNUMBER(E5),E5&gt;0,F5&gt;E5),(F5-E5)/E5,IF(AND(ISNUMBER(F5),ISNUMBER(E5),E5&gt;0,F5=E5),0,IF(AND(ISNUMBER(F5),ISNUMBER(E5),E5&gt;0,F5=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K5" s="50" t="str">
-        <x:f>IF(A5="","",IF(AND(ISNUMBER(E5),E5=0,OR(ISNUMBER(SEARCH("Free",D5&amp;"")),AND(ISNUMBER(F5),F5=0))),"Subscription",IF(ISNUMBER(G5),"Profit",IF(ISNUMBER(I5),"Loss",IF(ISNUMBER(H5),"Draw",IF(AND(ISNUMBER(F5),ISNUMBER(E5),E5&gt;0,F5&gt;E5),"Profit",IF(AND(ISNUMBER(F5),ISNUMBER(E5),E5&gt;0,F5=E5),"Draw",IF(AND(ISNUMBER(F5),ISNUMBER(E5),E5&gt;0,F5=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A5="","",IF(AND(ISNUMBER(E5),E5=0,OR(ISNUMBER(SEARCH("Free",D5&amp;"")),AND(ISNUMBER(F5),F5=0))),"Subscription",IF(ISNUMBER(G5),"Profit",IF(ISNUMBER(I5),"Disqualified",IF(ISNUMBER(H5),"Draw",IF(AND(ISNUMBER(F5),ISNUMBER(E5),E5&gt;0,F5&gt;E5),"Profit",IF(AND(ISNUMBER(F5),ISNUMBER(E5),E5&gt;0,F5=E5),"Draw",IF(AND(ISNUMBER(F5),ISNUMBER(E5),E5&gt;0,F5=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L5" s="50"/>
       <x:c r="M5" s="58"/>
@@ -1580,7 +1593,7 @@
         <x:f>IF(A6="","",IF(K6="Subscription","",IF(E6=0,"",IF(ISNUMBER(G6),G6/E6,IF(ISNUMBER(I6),-ABS(I6)/E6,IF(ISNUMBER(H6),0,IF(AND(ISNUMBER(F6),ISNUMBER(E6),E6&gt;0,F6&gt;E6),(F6-E6)/E6,IF(AND(ISNUMBER(F6),ISNUMBER(E6),E6&gt;0,F6=E6),0,IF(AND(ISNUMBER(F6),ISNUMBER(E6),E6&gt;0,F6=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K6" s="50" t="str">
-        <x:f>IF(A6="","",IF(AND(ISNUMBER(E6),E6=0,OR(ISNUMBER(SEARCH("Free",D6&amp;"")),AND(ISNUMBER(F6),F6=0))),"Subscription",IF(ISNUMBER(G6),"Profit",IF(ISNUMBER(I6),"Loss",IF(ISNUMBER(H6),"Draw",IF(AND(ISNUMBER(F6),ISNUMBER(E6),E6&gt;0,F6&gt;E6),"Profit",IF(AND(ISNUMBER(F6),ISNUMBER(E6),E6&gt;0,F6=E6),"Draw",IF(AND(ISNUMBER(F6),ISNUMBER(E6),E6&gt;0,F6=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A6="","",IF(AND(ISNUMBER(E6),E6=0,OR(ISNUMBER(SEARCH("Free",D6&amp;"")),AND(ISNUMBER(F6),F6=0))),"Subscription",IF(ISNUMBER(G6),"Profit",IF(ISNUMBER(I6),"Disqualified",IF(ISNUMBER(H6),"Draw",IF(AND(ISNUMBER(F6),ISNUMBER(E6),E6&gt;0,F6&gt;E6),"Profit",IF(AND(ISNUMBER(F6),ISNUMBER(E6),E6&gt;0,F6=E6),"Draw",IF(AND(ISNUMBER(F6),ISNUMBER(E6),E6&gt;0,F6=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L6" s="50"/>
       <x:c r="M6" s="58"/>
@@ -1617,7 +1630,7 @@
         <x:f>IF(A7="","",IF(K7="Subscription","",IF(E7=0,"",IF(ISNUMBER(G7),G7/E7,IF(ISNUMBER(I7),-ABS(I7)/E7,IF(ISNUMBER(H7),0,IF(AND(ISNUMBER(F7),ISNUMBER(E7),E7&gt;0,F7&gt;E7),(F7-E7)/E7,IF(AND(ISNUMBER(F7),ISNUMBER(E7),E7&gt;0,F7=E7),0,IF(AND(ISNUMBER(F7),ISNUMBER(E7),E7&gt;0,F7=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K7" s="50" t="str">
-        <x:f>IF(A7="","",IF(AND(ISNUMBER(E7),E7=0,OR(ISNUMBER(SEARCH("Free",D7&amp;"")),AND(ISNUMBER(F7),F7=0))),"Subscription",IF(ISNUMBER(G7),"Profit",IF(ISNUMBER(I7),"Loss",IF(ISNUMBER(H7),"Draw",IF(AND(ISNUMBER(F7),ISNUMBER(E7),E7&gt;0,F7&gt;E7),"Profit",IF(AND(ISNUMBER(F7),ISNUMBER(E7),E7&gt;0,F7=E7),"Draw",IF(AND(ISNUMBER(F7),ISNUMBER(E7),E7&gt;0,F7=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A7="","",IF(AND(ISNUMBER(E7),E7=0,OR(ISNUMBER(SEARCH("Free",D7&amp;"")),AND(ISNUMBER(F7),F7=0))),"Subscription",IF(ISNUMBER(G7),"Profit",IF(ISNUMBER(I7),"Disqualified",IF(ISNUMBER(H7),"Draw",IF(AND(ISNUMBER(F7),ISNUMBER(E7),E7&gt;0,F7&gt;E7),"Profit",IF(AND(ISNUMBER(F7),ISNUMBER(E7),E7&gt;0,F7=E7),"Draw",IF(AND(ISNUMBER(F7),ISNUMBER(E7),E7&gt;0,F7=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L7" s="50"/>
       <x:c r="M7" s="58"/>
@@ -1654,7 +1667,7 @@
         <x:f>IF(A8="","",IF(K8="Subscription","",IF(E8=0,"",IF(ISNUMBER(G8),G8/E8,IF(ISNUMBER(I8),-ABS(I8)/E8,IF(ISNUMBER(H8),0,IF(AND(ISNUMBER(F8),ISNUMBER(E8),E8&gt;0,F8&gt;E8),(F8-E8)/E8,IF(AND(ISNUMBER(F8),ISNUMBER(E8),E8&gt;0,F8=E8),0,IF(AND(ISNUMBER(F8),ISNUMBER(E8),E8&gt;0,F8=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K8" s="50" t="str">
-        <x:f>IF(A8="","",IF(AND(ISNUMBER(E8),E8=0,OR(ISNUMBER(SEARCH("Free",D8&amp;"")),AND(ISNUMBER(F8),F8=0))),"Subscription",IF(ISNUMBER(G8),"Profit",IF(ISNUMBER(I8),"Loss",IF(ISNUMBER(H8),"Draw",IF(AND(ISNUMBER(F8),ISNUMBER(E8),E8&gt;0,F8&gt;E8),"Profit",IF(AND(ISNUMBER(F8),ISNUMBER(E8),E8&gt;0,F8=E8),"Draw",IF(AND(ISNUMBER(F8),ISNUMBER(E8),E8&gt;0,F8=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A8="","",IF(AND(ISNUMBER(E8),E8=0,OR(ISNUMBER(SEARCH("Free",D8&amp;"")),AND(ISNUMBER(F8),F8=0))),"Subscription",IF(ISNUMBER(G8),"Profit",IF(ISNUMBER(I8),"Disqualified",IF(ISNUMBER(H8),"Draw",IF(AND(ISNUMBER(F8),ISNUMBER(E8),E8&gt;0,F8&gt;E8),"Profit",IF(AND(ISNUMBER(F8),ISNUMBER(E8),E8&gt;0,F8=E8),"Draw",IF(AND(ISNUMBER(F8),ISNUMBER(E8),E8&gt;0,F8=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L8" s="50"/>
       <x:c r="M8" s="58"/>
@@ -1691,7 +1704,7 @@
         <x:f>IF(A9="","",IF(K9="Subscription","",IF(E9=0,"",IF(ISNUMBER(G9),G9/E9,IF(ISNUMBER(I9),-ABS(I9)/E9,IF(ISNUMBER(H9),0,IF(AND(ISNUMBER(F9),ISNUMBER(E9),E9&gt;0,F9&gt;E9),(F9-E9)/E9,IF(AND(ISNUMBER(F9),ISNUMBER(E9),E9&gt;0,F9=E9),0,IF(AND(ISNUMBER(F9),ISNUMBER(E9),E9&gt;0,F9=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K9" s="50" t="str">
-        <x:f>IF(A9="","",IF(AND(ISNUMBER(E9),E9=0,OR(ISNUMBER(SEARCH("Free",D9&amp;"")),AND(ISNUMBER(F9),F9=0))),"Subscription",IF(ISNUMBER(G9),"Profit",IF(ISNUMBER(I9),"Loss",IF(ISNUMBER(H9),"Draw",IF(AND(ISNUMBER(F9),ISNUMBER(E9),E9&gt;0,F9&gt;E9),"Profit",IF(AND(ISNUMBER(F9),ISNUMBER(E9),E9&gt;0,F9=E9),"Draw",IF(AND(ISNUMBER(F9),ISNUMBER(E9),E9&gt;0,F9=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A9="","",IF(AND(ISNUMBER(E9),E9=0,OR(ISNUMBER(SEARCH("Free",D9&amp;"")),AND(ISNUMBER(F9),F9=0))),"Subscription",IF(ISNUMBER(G9),"Profit",IF(ISNUMBER(I9),"Disqualified",IF(ISNUMBER(H9),"Draw",IF(AND(ISNUMBER(F9),ISNUMBER(E9),E9&gt;0,F9&gt;E9),"Profit",IF(AND(ISNUMBER(F9),ISNUMBER(E9),E9&gt;0,F9=E9),"Draw",IF(AND(ISNUMBER(F9),ISNUMBER(E9),E9&gt;0,F9=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L9" s="50"/>
       <x:c r="M9" s="58"/>
@@ -1728,7 +1741,7 @@
         <x:f>IF(A10="","",IF(K10="Subscription","",IF(E10=0,"",IF(ISNUMBER(G10),G10/E10,IF(ISNUMBER(I10),-ABS(I10)/E10,IF(ISNUMBER(H10),0,IF(AND(ISNUMBER(F10),ISNUMBER(E10),E10&gt;0,F10&gt;E10),(F10-E10)/E10,IF(AND(ISNUMBER(F10),ISNUMBER(E10),E10&gt;0,F10=E10),0,IF(AND(ISNUMBER(F10),ISNUMBER(E10),E10&gt;0,F10=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K10" s="50" t="str">
-        <x:f>IF(A10="","",IF(AND(ISNUMBER(E10),E10=0,OR(ISNUMBER(SEARCH("Free",D10&amp;"")),AND(ISNUMBER(F10),F10=0))),"Subscription",IF(ISNUMBER(G10),"Profit",IF(ISNUMBER(I10),"Loss",IF(ISNUMBER(H10),"Draw",IF(AND(ISNUMBER(F10),ISNUMBER(E10),E10&gt;0,F10&gt;E10),"Profit",IF(AND(ISNUMBER(F10),ISNUMBER(E10),E10&gt;0,F10=E10),"Draw",IF(AND(ISNUMBER(F10),ISNUMBER(E10),E10&gt;0,F10=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A10="","",IF(AND(ISNUMBER(E10),E10=0,OR(ISNUMBER(SEARCH("Free",D10&amp;"")),AND(ISNUMBER(F10),F10=0))),"Subscription",IF(ISNUMBER(G10),"Profit",IF(ISNUMBER(I10),"Disqualified",IF(ISNUMBER(H10),"Draw",IF(AND(ISNUMBER(F10),ISNUMBER(E10),E10&gt;0,F10&gt;E10),"Profit",IF(AND(ISNUMBER(F10),ISNUMBER(E10),E10&gt;0,F10=E10),"Draw",IF(AND(ISNUMBER(F10),ISNUMBER(E10),E10&gt;0,F10=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L10" s="50"/>
       <x:c r="M10" s="58"/>
@@ -1765,7 +1778,7 @@
         <x:f>IF(A11="","",IF(K11="Subscription","",IF(E11=0,"",IF(ISNUMBER(G11),G11/E11,IF(ISNUMBER(I11),-ABS(I11)/E11,IF(ISNUMBER(H11),0,IF(AND(ISNUMBER(F11),ISNUMBER(E11),E11&gt;0,F11&gt;E11),(F11-E11)/E11,IF(AND(ISNUMBER(F11),ISNUMBER(E11),E11&gt;0,F11=E11),0,IF(AND(ISNUMBER(F11),ISNUMBER(E11),E11&gt;0,F11=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K11" s="50" t="str">
-        <x:f>IF(A11="","",IF(AND(ISNUMBER(E11),E11=0,OR(ISNUMBER(SEARCH("Free",D11&amp;"")),AND(ISNUMBER(F11),F11=0))),"Subscription",IF(ISNUMBER(G11),"Profit",IF(ISNUMBER(I11),"Loss",IF(ISNUMBER(H11),"Draw",IF(AND(ISNUMBER(F11),ISNUMBER(E11),E11&gt;0,F11&gt;E11),"Profit",IF(AND(ISNUMBER(F11),ISNUMBER(E11),E11&gt;0,F11=E11),"Draw",IF(AND(ISNUMBER(F11),ISNUMBER(E11),E11&gt;0,F11=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A11="","",IF(AND(ISNUMBER(E11),E11=0,OR(ISNUMBER(SEARCH("Free",D11&amp;"")),AND(ISNUMBER(F11),F11=0))),"Subscription",IF(ISNUMBER(G11),"Profit",IF(ISNUMBER(I11),"Disqualified",IF(ISNUMBER(H11),"Draw",IF(AND(ISNUMBER(F11),ISNUMBER(E11),E11&gt;0,F11&gt;E11),"Profit",IF(AND(ISNUMBER(F11),ISNUMBER(E11),E11&gt;0,F11=E11),"Draw",IF(AND(ISNUMBER(F11),ISNUMBER(E11),E11&gt;0,F11=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L11" s="50"/>
       <x:c r="M11" s="58"/>
@@ -1802,7 +1815,7 @@
         <x:f>IF(A12="","",IF(K12="Subscription","",IF(E12=0,"",IF(ISNUMBER(G12),G12/E12,IF(ISNUMBER(I12),-ABS(I12)/E12,IF(ISNUMBER(H12),0,IF(AND(ISNUMBER(F12),ISNUMBER(E12),E12&gt;0,F12&gt;E12),(F12-E12)/E12,IF(AND(ISNUMBER(F12),ISNUMBER(E12),E12&gt;0,F12=E12),0,IF(AND(ISNUMBER(F12),ISNUMBER(E12),E12&gt;0,F12=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K12" s="50" t="str">
-        <x:f>IF(A12="","",IF(AND(ISNUMBER(E12),E12=0,OR(ISNUMBER(SEARCH("Free",D12&amp;"")),AND(ISNUMBER(F12),F12=0))),"Subscription",IF(ISNUMBER(G12),"Profit",IF(ISNUMBER(I12),"Loss",IF(ISNUMBER(H12),"Draw",IF(AND(ISNUMBER(F12),ISNUMBER(E12),E12&gt;0,F12&gt;E12),"Profit",IF(AND(ISNUMBER(F12),ISNUMBER(E12),E12&gt;0,F12=E12),"Draw",IF(AND(ISNUMBER(F12),ISNUMBER(E12),E12&gt;0,F12=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A12="","",IF(AND(ISNUMBER(E12),E12=0,OR(ISNUMBER(SEARCH("Free",D12&amp;"")),AND(ISNUMBER(F12),F12=0))),"Subscription",IF(ISNUMBER(G12),"Profit",IF(ISNUMBER(I12),"Disqualified",IF(ISNUMBER(H12),"Draw",IF(AND(ISNUMBER(F12),ISNUMBER(E12),E12&gt;0,F12&gt;E12),"Profit",IF(AND(ISNUMBER(F12),ISNUMBER(E12),E12&gt;0,F12=E12),"Draw",IF(AND(ISNUMBER(F12),ISNUMBER(E12),E12&gt;0,F12=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L12" s="50"/>
       <x:c r="M12" s="58"/>
@@ -1839,7 +1852,7 @@
         <x:f>IF(A13="","",IF(K13="Subscription","",IF(E13=0,"",IF(ISNUMBER(G13),G13/E13,IF(ISNUMBER(I13),-ABS(I13)/E13,IF(ISNUMBER(H13),0,IF(AND(ISNUMBER(F13),ISNUMBER(E13),E13&gt;0,F13&gt;E13),(F13-E13)/E13,IF(AND(ISNUMBER(F13),ISNUMBER(E13),E13&gt;0,F13=E13),0,IF(AND(ISNUMBER(F13),ISNUMBER(E13),E13&gt;0,F13=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K13" s="50" t="str">
-        <x:f>IF(A13="","",IF(AND(ISNUMBER(E13),E13=0,OR(ISNUMBER(SEARCH("Free",D13&amp;"")),AND(ISNUMBER(F13),F13=0))),"Subscription",IF(ISNUMBER(G13),"Profit",IF(ISNUMBER(I13),"Loss",IF(ISNUMBER(H13),"Draw",IF(AND(ISNUMBER(F13),ISNUMBER(E13),E13&gt;0,F13&gt;E13),"Profit",IF(AND(ISNUMBER(F13),ISNUMBER(E13),E13&gt;0,F13=E13),"Draw",IF(AND(ISNUMBER(F13),ISNUMBER(E13),E13&gt;0,F13=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A13="","",IF(AND(ISNUMBER(E13),E13=0,OR(ISNUMBER(SEARCH("Free",D13&amp;"")),AND(ISNUMBER(F13),F13=0))),"Subscription",IF(ISNUMBER(G13),"Profit",IF(ISNUMBER(I13),"Disqualified",IF(ISNUMBER(H13),"Draw",IF(AND(ISNUMBER(F13),ISNUMBER(E13),E13&gt;0,F13&gt;E13),"Profit",IF(AND(ISNUMBER(F13),ISNUMBER(E13),E13&gt;0,F13=E13),"Draw",IF(AND(ISNUMBER(F13),ISNUMBER(E13),E13&gt;0,F13=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L13" s="50"/>
       <x:c r="M13" s="58"/>
@@ -1876,7 +1889,7 @@
         <x:f>IF(A14="","",IF(K14="Subscription","",IF(E14=0,"",IF(ISNUMBER(G14),G14/E14,IF(ISNUMBER(I14),-ABS(I14)/E14,IF(ISNUMBER(H14),0,IF(AND(ISNUMBER(F14),ISNUMBER(E14),E14&gt;0,F14&gt;E14),(F14-E14)/E14,IF(AND(ISNUMBER(F14),ISNUMBER(E14),E14&gt;0,F14=E14),0,IF(AND(ISNUMBER(F14),ISNUMBER(E14),E14&gt;0,F14=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K14" s="50" t="str">
-        <x:f>IF(A14="","",IF(AND(ISNUMBER(E14),E14=0,OR(ISNUMBER(SEARCH("Free",D14&amp;"")),AND(ISNUMBER(F14),F14=0))),"Subscription",IF(ISNUMBER(G14),"Profit",IF(ISNUMBER(I14),"Loss",IF(ISNUMBER(H14),"Draw",IF(AND(ISNUMBER(F14),ISNUMBER(E14),E14&gt;0,F14&gt;E14),"Profit",IF(AND(ISNUMBER(F14),ISNUMBER(E14),E14&gt;0,F14=E14),"Draw",IF(AND(ISNUMBER(F14),ISNUMBER(E14),E14&gt;0,F14=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A14="","",IF(AND(ISNUMBER(E14),E14=0,OR(ISNUMBER(SEARCH("Free",D14&amp;"")),AND(ISNUMBER(F14),F14=0))),"Subscription",IF(ISNUMBER(G14),"Profit",IF(ISNUMBER(I14),"Disqualified",IF(ISNUMBER(H14),"Draw",IF(AND(ISNUMBER(F14),ISNUMBER(E14),E14&gt;0,F14&gt;E14),"Profit",IF(AND(ISNUMBER(F14),ISNUMBER(E14),E14&gt;0,F14=E14),"Draw",IF(AND(ISNUMBER(F14),ISNUMBER(E14),E14&gt;0,F14=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L14" s="50"/>
       <x:c r="M14" s="58"/>
@@ -1913,7 +1926,7 @@
         <x:f>IF(A15="","",IF(K15="Subscription","",IF(E15=0,"",IF(ISNUMBER(G15),G15/E15,IF(ISNUMBER(I15),-ABS(I15)/E15,IF(ISNUMBER(H15),0,IF(AND(ISNUMBER(F15),ISNUMBER(E15),E15&gt;0,F15&gt;E15),(F15-E15)/E15,IF(AND(ISNUMBER(F15),ISNUMBER(E15),E15&gt;0,F15=E15),0,IF(AND(ISNUMBER(F15),ISNUMBER(E15),E15&gt;0,F15=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K15" s="50" t="str">
-        <x:f>IF(A15="","",IF(AND(ISNUMBER(E15),E15=0,OR(ISNUMBER(SEARCH("Free",D15&amp;"")),AND(ISNUMBER(F15),F15=0))),"Subscription",IF(ISNUMBER(G15),"Profit",IF(ISNUMBER(I15),"Loss",IF(ISNUMBER(H15),"Draw",IF(AND(ISNUMBER(F15),ISNUMBER(E15),E15&gt;0,F15&gt;E15),"Profit",IF(AND(ISNUMBER(F15),ISNUMBER(E15),E15&gt;0,F15=E15),"Draw",IF(AND(ISNUMBER(F15),ISNUMBER(E15),E15&gt;0,F15=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A15="","",IF(AND(ISNUMBER(E15),E15=0,OR(ISNUMBER(SEARCH("Free",D15&amp;"")),AND(ISNUMBER(F15),F15=0))),"Subscription",IF(ISNUMBER(G15),"Profit",IF(ISNUMBER(I15),"Disqualified",IF(ISNUMBER(H15),"Draw",IF(AND(ISNUMBER(F15),ISNUMBER(E15),E15&gt;0,F15&gt;E15),"Profit",IF(AND(ISNUMBER(F15),ISNUMBER(E15),E15&gt;0,F15=E15),"Draw",IF(AND(ISNUMBER(F15),ISNUMBER(E15),E15&gt;0,F15=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L15" s="50"/>
       <x:c r="M15" s="58"/>
@@ -1950,7 +1963,7 @@
         <x:f>IF(A16="","",IF(K16="Subscription","",IF(E16=0,"",IF(ISNUMBER(G16),G16/E16,IF(ISNUMBER(I16),-ABS(I16)/E16,IF(ISNUMBER(H16),0,IF(AND(ISNUMBER(F16),ISNUMBER(E16),E16&gt;0,F16&gt;E16),(F16-E16)/E16,IF(AND(ISNUMBER(F16),ISNUMBER(E16),E16&gt;0,F16=E16),0,IF(AND(ISNUMBER(F16),ISNUMBER(E16),E16&gt;0,F16=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K16" s="50" t="str">
-        <x:f>IF(A16="","",IF(AND(ISNUMBER(E16),E16=0,OR(ISNUMBER(SEARCH("Free",D16&amp;"")),AND(ISNUMBER(F16),F16=0))),"Subscription",IF(ISNUMBER(G16),"Profit",IF(ISNUMBER(I16),"Loss",IF(ISNUMBER(H16),"Draw",IF(AND(ISNUMBER(F16),ISNUMBER(E16),E16&gt;0,F16&gt;E16),"Profit",IF(AND(ISNUMBER(F16),ISNUMBER(E16),E16&gt;0,F16=E16),"Draw",IF(AND(ISNUMBER(F16),ISNUMBER(E16),E16&gt;0,F16=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A16="","",IF(AND(ISNUMBER(E16),E16=0,OR(ISNUMBER(SEARCH("Free",D16&amp;"")),AND(ISNUMBER(F16),F16=0))),"Subscription",IF(ISNUMBER(G16),"Profit",IF(ISNUMBER(I16),"Disqualified",IF(ISNUMBER(H16),"Draw",IF(AND(ISNUMBER(F16),ISNUMBER(E16),E16&gt;0,F16&gt;E16),"Profit",IF(AND(ISNUMBER(F16),ISNUMBER(E16),E16&gt;0,F16=E16),"Draw",IF(AND(ISNUMBER(F16),ISNUMBER(E16),E16&gt;0,F16=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L16" s="50"/>
       <x:c r="M16" s="58"/>
@@ -1987,7 +2000,7 @@
         <x:f>IF(A17="","",IF(K17="Subscription","",IF(E17=0,"",IF(ISNUMBER(G17),G17/E17,IF(ISNUMBER(I17),-ABS(I17)/E17,IF(ISNUMBER(H17),0,IF(AND(ISNUMBER(F17),ISNUMBER(E17),E17&gt;0,F17&gt;E17),(F17-E17)/E17,IF(AND(ISNUMBER(F17),ISNUMBER(E17),E17&gt;0,F17=E17),0,IF(AND(ISNUMBER(F17),ISNUMBER(E17),E17&gt;0,F17=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K17" s="50" t="str">
-        <x:f>IF(A17="","",IF(AND(ISNUMBER(E17),E17=0,OR(ISNUMBER(SEARCH("Free",D17&amp;"")),AND(ISNUMBER(F17),F17=0))),"Subscription",IF(ISNUMBER(G17),"Profit",IF(ISNUMBER(I17),"Loss",IF(ISNUMBER(H17),"Draw",IF(AND(ISNUMBER(F17),ISNUMBER(E17),E17&gt;0,F17&gt;E17),"Profit",IF(AND(ISNUMBER(F17),ISNUMBER(E17),E17&gt;0,F17=E17),"Draw",IF(AND(ISNUMBER(F17),ISNUMBER(E17),E17&gt;0,F17=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A17="","",IF(AND(ISNUMBER(E17),E17=0,OR(ISNUMBER(SEARCH("Free",D17&amp;"")),AND(ISNUMBER(F17),F17=0))),"Subscription",IF(ISNUMBER(G17),"Profit",IF(ISNUMBER(I17),"Disqualified",IF(ISNUMBER(H17),"Draw",IF(AND(ISNUMBER(F17),ISNUMBER(E17),E17&gt;0,F17&gt;E17),"Profit",IF(AND(ISNUMBER(F17),ISNUMBER(E17),E17&gt;0,F17=E17),"Draw",IF(AND(ISNUMBER(F17),ISNUMBER(E17),E17&gt;0,F17=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L17" s="50"/>
       <x:c r="M17" s="58"/>
@@ -2024,7 +2037,7 @@
         <x:f>IF(A18="","",IF(K18="Subscription","",IF(E18=0,"",IF(ISNUMBER(G18),G18/E18,IF(ISNUMBER(I18),-ABS(I18)/E18,IF(ISNUMBER(H18),0,IF(AND(ISNUMBER(F18),ISNUMBER(E18),E18&gt;0,F18&gt;E18),(F18-E18)/E18,IF(AND(ISNUMBER(F18),ISNUMBER(E18),E18&gt;0,F18=E18),0,IF(AND(ISNUMBER(F18),ISNUMBER(E18),E18&gt;0,F18=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K18" s="50" t="str">
-        <x:f>IF(A18="","",IF(AND(ISNUMBER(E18),E18=0,OR(ISNUMBER(SEARCH("Free",D18&amp;"")),AND(ISNUMBER(F18),F18=0))),"Subscription",IF(ISNUMBER(G18),"Profit",IF(ISNUMBER(I18),"Loss",IF(ISNUMBER(H18),"Draw",IF(AND(ISNUMBER(F18),ISNUMBER(E18),E18&gt;0,F18&gt;E18),"Profit",IF(AND(ISNUMBER(F18),ISNUMBER(E18),E18&gt;0,F18=E18),"Draw",IF(AND(ISNUMBER(F18),ISNUMBER(E18),E18&gt;0,F18=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A18="","",IF(AND(ISNUMBER(E18),E18=0,OR(ISNUMBER(SEARCH("Free",D18&amp;"")),AND(ISNUMBER(F18),F18=0))),"Subscription",IF(ISNUMBER(G18),"Profit",IF(ISNUMBER(I18),"Disqualified",IF(ISNUMBER(H18),"Draw",IF(AND(ISNUMBER(F18),ISNUMBER(E18),E18&gt;0,F18&gt;E18),"Profit",IF(AND(ISNUMBER(F18),ISNUMBER(E18),E18&gt;0,F18=E18),"Draw",IF(AND(ISNUMBER(F18),ISNUMBER(E18),E18&gt;0,F18=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L18" s="50"/>
       <x:c r="M18" s="58"/>
@@ -2061,7 +2074,7 @@
         <x:f>IF(A19="","",IF(K19="Subscription","",IF(E19=0,"",IF(ISNUMBER(G19),G19/E19,IF(ISNUMBER(I19),-ABS(I19)/E19,IF(ISNUMBER(H19),0,IF(AND(ISNUMBER(F19),ISNUMBER(E19),E19&gt;0,F19&gt;E19),(F19-E19)/E19,IF(AND(ISNUMBER(F19),ISNUMBER(E19),E19&gt;0,F19=E19),0,IF(AND(ISNUMBER(F19),ISNUMBER(E19),E19&gt;0,F19=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K19" s="50" t="str">
-        <x:f>IF(A19="","",IF(AND(ISNUMBER(E19),E19=0,OR(ISNUMBER(SEARCH("Free",D19&amp;"")),AND(ISNUMBER(F19),F19=0))),"Subscription",IF(ISNUMBER(G19),"Profit",IF(ISNUMBER(I19),"Loss",IF(ISNUMBER(H19),"Draw",IF(AND(ISNUMBER(F19),ISNUMBER(E19),E19&gt;0,F19&gt;E19),"Profit",IF(AND(ISNUMBER(F19),ISNUMBER(E19),E19&gt;0,F19=E19),"Draw",IF(AND(ISNUMBER(F19),ISNUMBER(E19),E19&gt;0,F19=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A19="","",IF(AND(ISNUMBER(E19),E19=0,OR(ISNUMBER(SEARCH("Free",D19&amp;"")),AND(ISNUMBER(F19),F19=0))),"Subscription",IF(ISNUMBER(G19),"Profit",IF(ISNUMBER(I19),"Disqualified",IF(ISNUMBER(H19),"Draw",IF(AND(ISNUMBER(F19),ISNUMBER(E19),E19&gt;0,F19&gt;E19),"Profit",IF(AND(ISNUMBER(F19),ISNUMBER(E19),E19&gt;0,F19=E19),"Draw",IF(AND(ISNUMBER(F19),ISNUMBER(E19),E19&gt;0,F19=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L19" s="50"/>
       <x:c r="M19" s="58"/>
@@ -2098,7 +2111,7 @@
         <x:f>IF(A20="","",IF(K20="Subscription","",IF(E20=0,"",IF(ISNUMBER(G20),G20/E20,IF(ISNUMBER(I20),-ABS(I20)/E20,IF(ISNUMBER(H20),0,IF(AND(ISNUMBER(F20),ISNUMBER(E20),E20&gt;0,F20&gt;E20),(F20-E20)/E20,IF(AND(ISNUMBER(F20),ISNUMBER(E20),E20&gt;0,F20=E20),0,IF(AND(ISNUMBER(F20),ISNUMBER(E20),E20&gt;0,F20=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K20" s="50" t="str">
-        <x:f>IF(A20="","",IF(AND(ISNUMBER(E20),E20=0,OR(ISNUMBER(SEARCH("Free",D20&amp;"")),AND(ISNUMBER(F20),F20=0))),"Subscription",IF(ISNUMBER(G20),"Profit",IF(ISNUMBER(I20),"Loss",IF(ISNUMBER(H20),"Draw",IF(AND(ISNUMBER(F20),ISNUMBER(E20),E20&gt;0,F20&gt;E20),"Profit",IF(AND(ISNUMBER(F20),ISNUMBER(E20),E20&gt;0,F20=E20),"Draw",IF(AND(ISNUMBER(F20),ISNUMBER(E20),E20&gt;0,F20=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A20="","",IF(AND(ISNUMBER(E20),E20=0,OR(ISNUMBER(SEARCH("Free",D20&amp;"")),AND(ISNUMBER(F20),F20=0))),"Subscription",IF(ISNUMBER(G20),"Profit",IF(ISNUMBER(I20),"Disqualified",IF(ISNUMBER(H20),"Draw",IF(AND(ISNUMBER(F20),ISNUMBER(E20),E20&gt;0,F20&gt;E20),"Profit",IF(AND(ISNUMBER(F20),ISNUMBER(E20),E20&gt;0,F20=E20),"Draw",IF(AND(ISNUMBER(F20),ISNUMBER(E20),E20&gt;0,F20=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L20" s="50"/>
       <x:c r="M20" s="58"/>
@@ -2135,7 +2148,7 @@
         <x:f>IF(A21="","",IF(K21="Subscription","",IF(E21=0,"",IF(ISNUMBER(G21),G21/E21,IF(ISNUMBER(I21),-ABS(I21)/E21,IF(ISNUMBER(H21),0,IF(AND(ISNUMBER(F21),ISNUMBER(E21),E21&gt;0,F21&gt;E21),(F21-E21)/E21,IF(AND(ISNUMBER(F21),ISNUMBER(E21),E21&gt;0,F21=E21),0,IF(AND(ISNUMBER(F21),ISNUMBER(E21),E21&gt;0,F21=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K21" s="50" t="str">
-        <x:f>IF(A21="","",IF(AND(ISNUMBER(E21),E21=0,OR(ISNUMBER(SEARCH("Free",D21&amp;"")),AND(ISNUMBER(F21),F21=0))),"Subscription",IF(ISNUMBER(G21),"Profit",IF(ISNUMBER(I21),"Loss",IF(ISNUMBER(H21),"Draw",IF(AND(ISNUMBER(F21),ISNUMBER(E21),E21&gt;0,F21&gt;E21),"Profit",IF(AND(ISNUMBER(F21),ISNUMBER(E21),E21&gt;0,F21=E21),"Draw",IF(AND(ISNUMBER(F21),ISNUMBER(E21),E21&gt;0,F21=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A21="","",IF(AND(ISNUMBER(E21),E21=0,OR(ISNUMBER(SEARCH("Free",D21&amp;"")),AND(ISNUMBER(F21),F21=0))),"Subscription",IF(ISNUMBER(G21),"Profit",IF(ISNUMBER(I21),"Disqualified",IF(ISNUMBER(H21),"Draw",IF(AND(ISNUMBER(F21),ISNUMBER(E21),E21&gt;0,F21&gt;E21),"Profit",IF(AND(ISNUMBER(F21),ISNUMBER(E21),E21&gt;0,F21=E21),"Draw",IF(AND(ISNUMBER(F21),ISNUMBER(E21),E21&gt;0,F21=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L21" s="50"/>
       <x:c r="M21" s="58"/>
@@ -2172,7 +2185,7 @@
         <x:f>IF(A22="","",IF(K22="Subscription","",IF(E22=0,"",IF(ISNUMBER(G22),G22/E22,IF(ISNUMBER(I22),-ABS(I22)/E22,IF(ISNUMBER(H22),0,IF(AND(ISNUMBER(F22),ISNUMBER(E22),E22&gt;0,F22&gt;E22),(F22-E22)/E22,IF(AND(ISNUMBER(F22),ISNUMBER(E22),E22&gt;0,F22=E22),0,IF(AND(ISNUMBER(F22),ISNUMBER(E22),E22&gt;0,F22=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K22" s="50" t="str">
-        <x:f>IF(A22="","",IF(AND(ISNUMBER(E22),E22=0,OR(ISNUMBER(SEARCH("Free",D22&amp;"")),AND(ISNUMBER(F22),F22=0))),"Subscription",IF(ISNUMBER(G22),"Profit",IF(ISNUMBER(I22),"Loss",IF(ISNUMBER(H22),"Draw",IF(AND(ISNUMBER(F22),ISNUMBER(E22),E22&gt;0,F22&gt;E22),"Profit",IF(AND(ISNUMBER(F22),ISNUMBER(E22),E22&gt;0,F22=E22),"Draw",IF(AND(ISNUMBER(F22),ISNUMBER(E22),E22&gt;0,F22=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A22="","",IF(AND(ISNUMBER(E22),E22=0,OR(ISNUMBER(SEARCH("Free",D22&amp;"")),AND(ISNUMBER(F22),F22=0))),"Subscription",IF(ISNUMBER(G22),"Profit",IF(ISNUMBER(I22),"Disqualified",IF(ISNUMBER(H22),"Draw",IF(AND(ISNUMBER(F22),ISNUMBER(E22),E22&gt;0,F22&gt;E22),"Profit",IF(AND(ISNUMBER(F22),ISNUMBER(E22),E22&gt;0,F22=E22),"Draw",IF(AND(ISNUMBER(F22),ISNUMBER(E22),E22&gt;0,F22=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L22" s="50"/>
       <x:c r="M22" s="58"/>
@@ -2209,7 +2222,7 @@
         <x:f>IF(A23="","",IF(K23="Subscription","",IF(E23=0,"",IF(ISNUMBER(G23),G23/E23,IF(ISNUMBER(I23),-ABS(I23)/E23,IF(ISNUMBER(H23),0,IF(AND(ISNUMBER(F23),ISNUMBER(E23),E23&gt;0,F23&gt;E23),(F23-E23)/E23,IF(AND(ISNUMBER(F23),ISNUMBER(E23),E23&gt;0,F23=E23),0,IF(AND(ISNUMBER(F23),ISNUMBER(E23),E23&gt;0,F23=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K23" s="50" t="str">
-        <x:f>IF(A23="","",IF(AND(ISNUMBER(E23),E23=0,OR(ISNUMBER(SEARCH("Free",D23&amp;"")),AND(ISNUMBER(F23),F23=0))),"Subscription",IF(ISNUMBER(G23),"Profit",IF(ISNUMBER(I23),"Loss",IF(ISNUMBER(H23),"Draw",IF(AND(ISNUMBER(F23),ISNUMBER(E23),E23&gt;0,F23&gt;E23),"Profit",IF(AND(ISNUMBER(F23),ISNUMBER(E23),E23&gt;0,F23=E23),"Draw",IF(AND(ISNUMBER(F23),ISNUMBER(E23),E23&gt;0,F23=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A23="","",IF(AND(ISNUMBER(E23),E23=0,OR(ISNUMBER(SEARCH("Free",D23&amp;"")),AND(ISNUMBER(F23),F23=0))),"Subscription",IF(ISNUMBER(G23),"Profit",IF(ISNUMBER(I23),"Disqualified",IF(ISNUMBER(H23),"Draw",IF(AND(ISNUMBER(F23),ISNUMBER(E23),E23&gt;0,F23&gt;E23),"Profit",IF(AND(ISNUMBER(F23),ISNUMBER(E23),E23&gt;0,F23=E23),"Draw",IF(AND(ISNUMBER(F23),ISNUMBER(E23),E23&gt;0,F23=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L23" s="50"/>
       <x:c r="M23" s="58"/>
@@ -2246,7 +2259,7 @@
         <x:f>IF(A24="","",IF(K24="Subscription","",IF(E24=0,"",IF(ISNUMBER(G24),G24/E24,IF(ISNUMBER(I24),-ABS(I24)/E24,IF(ISNUMBER(H24),0,IF(AND(ISNUMBER(F24),ISNUMBER(E24),E24&gt;0,F24&gt;E24),(F24-E24)/E24,IF(AND(ISNUMBER(F24),ISNUMBER(E24),E24&gt;0,F24=E24),0,IF(AND(ISNUMBER(F24),ISNUMBER(E24),E24&gt;0,F24=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K24" s="50" t="str">
-        <x:f>IF(A24="","",IF(AND(ISNUMBER(E24),E24=0,OR(ISNUMBER(SEARCH("Free",D24&amp;"")),AND(ISNUMBER(F24),F24=0))),"Subscription",IF(ISNUMBER(G24),"Profit",IF(ISNUMBER(I24),"Loss",IF(ISNUMBER(H24),"Draw",IF(AND(ISNUMBER(F24),ISNUMBER(E24),E24&gt;0,F24&gt;E24),"Profit",IF(AND(ISNUMBER(F24),ISNUMBER(E24),E24&gt;0,F24=E24),"Draw",IF(AND(ISNUMBER(F24),ISNUMBER(E24),E24&gt;0,F24=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A24="","",IF(AND(ISNUMBER(E24),E24=0,OR(ISNUMBER(SEARCH("Free",D24&amp;"")),AND(ISNUMBER(F24),F24=0))),"Subscription",IF(ISNUMBER(G24),"Profit",IF(ISNUMBER(I24),"Disqualified",IF(ISNUMBER(H24),"Draw",IF(AND(ISNUMBER(F24),ISNUMBER(E24),E24&gt;0,F24&gt;E24),"Profit",IF(AND(ISNUMBER(F24),ISNUMBER(E24),E24&gt;0,F24=E24),"Draw",IF(AND(ISNUMBER(F24),ISNUMBER(E24),E24&gt;0,F24=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L24" s="50"/>
       <x:c r="M24" s="58"/>
@@ -2283,7 +2296,7 @@
         <x:f>IF(A25="","",IF(K25="Subscription","",IF(E25=0,"",IF(ISNUMBER(G25),G25/E25,IF(ISNUMBER(I25),-ABS(I25)/E25,IF(ISNUMBER(H25),0,IF(AND(ISNUMBER(F25),ISNUMBER(E25),E25&gt;0,F25&gt;E25),(F25-E25)/E25,IF(AND(ISNUMBER(F25),ISNUMBER(E25),E25&gt;0,F25=E25),0,IF(AND(ISNUMBER(F25),ISNUMBER(E25),E25&gt;0,F25=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K25" s="50" t="str">
-        <x:f>IF(A25="","",IF(AND(ISNUMBER(E25),E25=0,OR(ISNUMBER(SEARCH("Free",D25&amp;"")),AND(ISNUMBER(F25),F25=0))),"Subscription",IF(ISNUMBER(G25),"Profit",IF(ISNUMBER(I25),"Loss",IF(ISNUMBER(H25),"Draw",IF(AND(ISNUMBER(F25),ISNUMBER(E25),E25&gt;0,F25&gt;E25),"Profit",IF(AND(ISNUMBER(F25),ISNUMBER(E25),E25&gt;0,F25=E25),"Draw",IF(AND(ISNUMBER(F25),ISNUMBER(E25),E25&gt;0,F25=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A25="","",IF(AND(ISNUMBER(E25),E25=0,OR(ISNUMBER(SEARCH("Free",D25&amp;"")),AND(ISNUMBER(F25),F25=0))),"Subscription",IF(ISNUMBER(G25),"Profit",IF(ISNUMBER(I25),"Disqualified",IF(ISNUMBER(H25),"Draw",IF(AND(ISNUMBER(F25),ISNUMBER(E25),E25&gt;0,F25&gt;E25),"Profit",IF(AND(ISNUMBER(F25),ISNUMBER(E25),E25&gt;0,F25=E25),"Draw",IF(AND(ISNUMBER(F25),ISNUMBER(E25),E25&gt;0,F25=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L25" s="50"/>
       <x:c r="M25" s="58"/>
@@ -2320,7 +2333,7 @@
         <x:f>IF(A26="","",IF(K26="Subscription","",IF(E26=0,"",IF(ISNUMBER(G26),G26/E26,IF(ISNUMBER(I26),-ABS(I26)/E26,IF(ISNUMBER(H26),0,IF(AND(ISNUMBER(F26),ISNUMBER(E26),E26&gt;0,F26&gt;E26),(F26-E26)/E26,IF(AND(ISNUMBER(F26),ISNUMBER(E26),E26&gt;0,F26=E26),0,IF(AND(ISNUMBER(F26),ISNUMBER(E26),E26&gt;0,F26=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K26" s="50" t="str">
-        <x:f>IF(A26="","",IF(AND(ISNUMBER(E26),E26=0,OR(ISNUMBER(SEARCH("Free",D26&amp;"")),AND(ISNUMBER(F26),F26=0))),"Subscription",IF(ISNUMBER(G26),"Profit",IF(ISNUMBER(I26),"Loss",IF(ISNUMBER(H26),"Draw",IF(AND(ISNUMBER(F26),ISNUMBER(E26),E26&gt;0,F26&gt;E26),"Profit",IF(AND(ISNUMBER(F26),ISNUMBER(E26),E26&gt;0,F26=E26),"Draw",IF(AND(ISNUMBER(F26),ISNUMBER(E26),E26&gt;0,F26=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A26="","",IF(AND(ISNUMBER(E26),E26=0,OR(ISNUMBER(SEARCH("Free",D26&amp;"")),AND(ISNUMBER(F26),F26=0))),"Subscription",IF(ISNUMBER(G26),"Profit",IF(ISNUMBER(I26),"Disqualified",IF(ISNUMBER(H26),"Draw",IF(AND(ISNUMBER(F26),ISNUMBER(E26),E26&gt;0,F26&gt;E26),"Profit",IF(AND(ISNUMBER(F26),ISNUMBER(E26),E26&gt;0,F26=E26),"Draw",IF(AND(ISNUMBER(F26),ISNUMBER(E26),E26&gt;0,F26=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L26" s="50"/>
       <x:c r="M26" s="58"/>
@@ -2357,7 +2370,7 @@
         <x:f>IF(A27="","",IF(K27="Subscription","",IF(E27=0,"",IF(ISNUMBER(G27),G27/E27,IF(ISNUMBER(I27),-ABS(I27)/E27,IF(ISNUMBER(H27),0,IF(AND(ISNUMBER(F27),ISNUMBER(E27),E27&gt;0,F27&gt;E27),(F27-E27)/E27,IF(AND(ISNUMBER(F27),ISNUMBER(E27),E27&gt;0,F27=E27),0,IF(AND(ISNUMBER(F27),ISNUMBER(E27),E27&gt;0,F27=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K27" s="50" t="str">
-        <x:f>IF(A27="","",IF(AND(ISNUMBER(E27),E27=0,OR(ISNUMBER(SEARCH("Free",D27&amp;"")),AND(ISNUMBER(F27),F27=0))),"Subscription",IF(ISNUMBER(G27),"Profit",IF(ISNUMBER(I27),"Loss",IF(ISNUMBER(H27),"Draw",IF(AND(ISNUMBER(F27),ISNUMBER(E27),E27&gt;0,F27&gt;E27),"Profit",IF(AND(ISNUMBER(F27),ISNUMBER(E27),E27&gt;0,F27=E27),"Draw",IF(AND(ISNUMBER(F27),ISNUMBER(E27),E27&gt;0,F27=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A27="","",IF(AND(ISNUMBER(E27),E27=0,OR(ISNUMBER(SEARCH("Free",D27&amp;"")),AND(ISNUMBER(F27),F27=0))),"Subscription",IF(ISNUMBER(G27),"Profit",IF(ISNUMBER(I27),"Disqualified",IF(ISNUMBER(H27),"Draw",IF(AND(ISNUMBER(F27),ISNUMBER(E27),E27&gt;0,F27&gt;E27),"Profit",IF(AND(ISNUMBER(F27),ISNUMBER(E27),E27&gt;0,F27=E27),"Draw",IF(AND(ISNUMBER(F27),ISNUMBER(E27),E27&gt;0,F27=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L27" s="50"/>
       <x:c r="M27" s="58"/>
@@ -2394,7 +2407,7 @@
         <x:f>IF(A28="","",IF(K28="Subscription","",IF(E28=0,"",IF(ISNUMBER(G28),G28/E28,IF(ISNUMBER(I28),-ABS(I28)/E28,IF(ISNUMBER(H28),0,IF(AND(ISNUMBER(F28),ISNUMBER(E28),E28&gt;0,F28&gt;E28),(F28-E28)/E28,IF(AND(ISNUMBER(F28),ISNUMBER(E28),E28&gt;0,F28=E28),0,IF(AND(ISNUMBER(F28),ISNUMBER(E28),E28&gt;0,F28=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K28" s="50" t="str">
-        <x:f>IF(A28="","",IF(AND(ISNUMBER(E28),E28=0,OR(ISNUMBER(SEARCH("Free",D28&amp;"")),AND(ISNUMBER(F28),F28=0))),"Subscription",IF(ISNUMBER(G28),"Profit",IF(ISNUMBER(I28),"Loss",IF(ISNUMBER(H28),"Draw",IF(AND(ISNUMBER(F28),ISNUMBER(E28),E28&gt;0,F28&gt;E28),"Profit",IF(AND(ISNUMBER(F28),ISNUMBER(E28),E28&gt;0,F28=E28),"Draw",IF(AND(ISNUMBER(F28),ISNUMBER(E28),E28&gt;0,F28=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A28="","",IF(AND(ISNUMBER(E28),E28=0,OR(ISNUMBER(SEARCH("Free",D28&amp;"")),AND(ISNUMBER(F28),F28=0))),"Subscription",IF(ISNUMBER(G28),"Profit",IF(ISNUMBER(I28),"Disqualified",IF(ISNUMBER(H28),"Draw",IF(AND(ISNUMBER(F28),ISNUMBER(E28),E28&gt;0,F28&gt;E28),"Profit",IF(AND(ISNUMBER(F28),ISNUMBER(E28),E28&gt;0,F28=E28),"Draw",IF(AND(ISNUMBER(F28),ISNUMBER(E28),E28&gt;0,F28=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L28" s="50"/>
       <x:c r="M28" s="58"/>
@@ -2431,7 +2444,7 @@
         <x:f>IF(A29="","",IF(K29="Subscription","",IF(E29=0,"",IF(ISNUMBER(G29),G29/E29,IF(ISNUMBER(I29),-ABS(I29)/E29,IF(ISNUMBER(H29),0,IF(AND(ISNUMBER(F29),ISNUMBER(E29),E29&gt;0,F29&gt;E29),(F29-E29)/E29,IF(AND(ISNUMBER(F29),ISNUMBER(E29),E29&gt;0,F29=E29),0,IF(AND(ISNUMBER(F29),ISNUMBER(E29),E29&gt;0,F29=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K29" s="50" t="str">
-        <x:f>IF(A29="","",IF(AND(ISNUMBER(E29),E29=0,OR(ISNUMBER(SEARCH("Free",D29&amp;"")),AND(ISNUMBER(F29),F29=0))),"Subscription",IF(ISNUMBER(G29),"Profit",IF(ISNUMBER(I29),"Loss",IF(ISNUMBER(H29),"Draw",IF(AND(ISNUMBER(F29),ISNUMBER(E29),E29&gt;0,F29&gt;E29),"Profit",IF(AND(ISNUMBER(F29),ISNUMBER(E29),E29&gt;0,F29=E29),"Draw",IF(AND(ISNUMBER(F29),ISNUMBER(E29),E29&gt;0,F29=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A29="","",IF(AND(ISNUMBER(E29),E29=0,OR(ISNUMBER(SEARCH("Free",D29&amp;"")),AND(ISNUMBER(F29),F29=0))),"Subscription",IF(ISNUMBER(G29),"Profit",IF(ISNUMBER(I29),"Disqualified",IF(ISNUMBER(H29),"Draw",IF(AND(ISNUMBER(F29),ISNUMBER(E29),E29&gt;0,F29&gt;E29),"Profit",IF(AND(ISNUMBER(F29),ISNUMBER(E29),E29&gt;0,F29=E29),"Draw",IF(AND(ISNUMBER(F29),ISNUMBER(E29),E29&gt;0,F29=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L29" s="50"/>
       <x:c r="M29" s="58"/>
@@ -2468,7 +2481,7 @@
         <x:f>IF(A30="","",IF(K30="Subscription","",IF(E30=0,"",IF(ISNUMBER(G30),G30/E30,IF(ISNUMBER(I30),-ABS(I30)/E30,IF(ISNUMBER(H30),0,IF(AND(ISNUMBER(F30),ISNUMBER(E30),E30&gt;0,F30&gt;E30),(F30-E30)/E30,IF(AND(ISNUMBER(F30),ISNUMBER(E30),E30&gt;0,F30=E30),0,IF(AND(ISNUMBER(F30),ISNUMBER(E30),E30&gt;0,F30=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K30" s="50" t="str">
-        <x:f>IF(A30="","",IF(AND(ISNUMBER(E30),E30=0,OR(ISNUMBER(SEARCH("Free",D30&amp;"")),AND(ISNUMBER(F30),F30=0))),"Subscription",IF(ISNUMBER(G30),"Profit",IF(ISNUMBER(I30),"Loss",IF(ISNUMBER(H30),"Draw",IF(AND(ISNUMBER(F30),ISNUMBER(E30),E30&gt;0,F30&gt;E30),"Profit",IF(AND(ISNUMBER(F30),ISNUMBER(E30),E30&gt;0,F30=E30),"Draw",IF(AND(ISNUMBER(F30),ISNUMBER(E30),E30&gt;0,F30=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A30="","",IF(AND(ISNUMBER(E30),E30=0,OR(ISNUMBER(SEARCH("Free",D30&amp;"")),AND(ISNUMBER(F30),F30=0))),"Subscription",IF(ISNUMBER(G30),"Profit",IF(ISNUMBER(I30),"Disqualified",IF(ISNUMBER(H30),"Draw",IF(AND(ISNUMBER(F30),ISNUMBER(E30),E30&gt;0,F30&gt;E30),"Profit",IF(AND(ISNUMBER(F30),ISNUMBER(E30),E30&gt;0,F30=E30),"Draw",IF(AND(ISNUMBER(F30),ISNUMBER(E30),E30&gt;0,F30=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L30" s="50"/>
       <x:c r="M30" s="58"/>
@@ -2505,7 +2518,7 @@
         <x:f>IF(A31="","",IF(K31="Subscription","",IF(E31=0,"",IF(ISNUMBER(G31),G31/E31,IF(ISNUMBER(I31),-ABS(I31)/E31,IF(ISNUMBER(H31),0,IF(AND(ISNUMBER(F31),ISNUMBER(E31),E31&gt;0,F31&gt;E31),(F31-E31)/E31,IF(AND(ISNUMBER(F31),ISNUMBER(E31),E31&gt;0,F31=E31),0,IF(AND(ISNUMBER(F31),ISNUMBER(E31),E31&gt;0,F31=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K31" s="50" t="str">
-        <x:f>IF(A31="","",IF(AND(ISNUMBER(E31),E31=0,OR(ISNUMBER(SEARCH("Free",D31&amp;"")),AND(ISNUMBER(F31),F31=0))),"Subscription",IF(ISNUMBER(G31),"Profit",IF(ISNUMBER(I31),"Loss",IF(ISNUMBER(H31),"Draw",IF(AND(ISNUMBER(F31),ISNUMBER(E31),E31&gt;0,F31&gt;E31),"Profit",IF(AND(ISNUMBER(F31),ISNUMBER(E31),E31&gt;0,F31=E31),"Draw",IF(AND(ISNUMBER(F31),ISNUMBER(E31),E31&gt;0,F31=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A31="","",IF(AND(ISNUMBER(E31),E31=0,OR(ISNUMBER(SEARCH("Free",D31&amp;"")),AND(ISNUMBER(F31),F31=0))),"Subscription",IF(ISNUMBER(G31),"Profit",IF(ISNUMBER(I31),"Disqualified",IF(ISNUMBER(H31),"Draw",IF(AND(ISNUMBER(F31),ISNUMBER(E31),E31&gt;0,F31&gt;E31),"Profit",IF(AND(ISNUMBER(F31),ISNUMBER(E31),E31&gt;0,F31=E31),"Draw",IF(AND(ISNUMBER(F31),ISNUMBER(E31),E31&gt;0,F31=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L31" s="50"/>
       <x:c r="M31" s="58"/>
@@ -2542,7 +2555,7 @@
         <x:f>IF(A32="","",IF(K32="Subscription","",IF(E32=0,"",IF(ISNUMBER(G32),G32/E32,IF(ISNUMBER(I32),-ABS(I32)/E32,IF(ISNUMBER(H32),0,IF(AND(ISNUMBER(F32),ISNUMBER(E32),E32&gt;0,F32&gt;E32),(F32-E32)/E32,IF(AND(ISNUMBER(F32),ISNUMBER(E32),E32&gt;0,F32=E32),0,IF(AND(ISNUMBER(F32),ISNUMBER(E32),E32&gt;0,F32=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K32" s="50" t="str">
-        <x:f>IF(A32="","",IF(AND(ISNUMBER(E32),E32=0,OR(ISNUMBER(SEARCH("Free",D32&amp;"")),AND(ISNUMBER(F32),F32=0))),"Subscription",IF(ISNUMBER(G32),"Profit",IF(ISNUMBER(I32),"Loss",IF(ISNUMBER(H32),"Draw",IF(AND(ISNUMBER(F32),ISNUMBER(E32),E32&gt;0,F32&gt;E32),"Profit",IF(AND(ISNUMBER(F32),ISNUMBER(E32),E32&gt;0,F32=E32),"Draw",IF(AND(ISNUMBER(F32),ISNUMBER(E32),E32&gt;0,F32=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A32="","",IF(AND(ISNUMBER(E32),E32=0,OR(ISNUMBER(SEARCH("Free",D32&amp;"")),AND(ISNUMBER(F32),F32=0))),"Subscription",IF(ISNUMBER(G32),"Profit",IF(ISNUMBER(I32),"Disqualified",IF(ISNUMBER(H32),"Draw",IF(AND(ISNUMBER(F32),ISNUMBER(E32),E32&gt;0,F32&gt;E32),"Profit",IF(AND(ISNUMBER(F32),ISNUMBER(E32),E32&gt;0,F32=E32),"Draw",IF(AND(ISNUMBER(F32),ISNUMBER(E32),E32&gt;0,F32=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L32" s="50"/>
       <x:c r="M32" s="58"/>
@@ -2579,7 +2592,7 @@
         <x:f>IF(A33="","",IF(K33="Subscription","",IF(E33=0,"",IF(ISNUMBER(G33),G33/E33,IF(ISNUMBER(I33),-ABS(I33)/E33,IF(ISNUMBER(H33),0,IF(AND(ISNUMBER(F33),ISNUMBER(E33),E33&gt;0,F33&gt;E33),(F33-E33)/E33,IF(AND(ISNUMBER(F33),ISNUMBER(E33),E33&gt;0,F33=E33),0,IF(AND(ISNUMBER(F33),ISNUMBER(E33),E33&gt;0,F33=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K33" s="50" t="str">
-        <x:f>IF(A33="","",IF(AND(ISNUMBER(E33),E33=0,OR(ISNUMBER(SEARCH("Free",D33&amp;"")),AND(ISNUMBER(F33),F33=0))),"Subscription",IF(ISNUMBER(G33),"Profit",IF(ISNUMBER(I33),"Loss",IF(ISNUMBER(H33),"Draw",IF(AND(ISNUMBER(F33),ISNUMBER(E33),E33&gt;0,F33&gt;E33),"Profit",IF(AND(ISNUMBER(F33),ISNUMBER(E33),E33&gt;0,F33=E33),"Draw",IF(AND(ISNUMBER(F33),ISNUMBER(E33),E33&gt;0,F33=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A33="","",IF(AND(ISNUMBER(E33),E33=0,OR(ISNUMBER(SEARCH("Free",D33&amp;"")),AND(ISNUMBER(F33),F33=0))),"Subscription",IF(ISNUMBER(G33),"Profit",IF(ISNUMBER(I33),"Disqualified",IF(ISNUMBER(H33),"Draw",IF(AND(ISNUMBER(F33),ISNUMBER(E33),E33&gt;0,F33&gt;E33),"Profit",IF(AND(ISNUMBER(F33),ISNUMBER(E33),E33&gt;0,F33=E33),"Draw",IF(AND(ISNUMBER(F33),ISNUMBER(E33),E33&gt;0,F33=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L33" s="50"/>
       <x:c r="M33" s="58"/>
@@ -2616,7 +2629,7 @@
         <x:f>IF(A34="","",IF(K34="Subscription","",IF(E34=0,"",IF(ISNUMBER(G34),G34/E34,IF(ISNUMBER(I34),-ABS(I34)/E34,IF(ISNUMBER(H34),0,IF(AND(ISNUMBER(F34),ISNUMBER(E34),E34&gt;0,F34&gt;E34),(F34-E34)/E34,IF(AND(ISNUMBER(F34),ISNUMBER(E34),E34&gt;0,F34=E34),0,IF(AND(ISNUMBER(F34),ISNUMBER(E34),E34&gt;0,F34=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K34" s="50" t="str">
-        <x:f>IF(A34="","",IF(AND(ISNUMBER(E34),E34=0,OR(ISNUMBER(SEARCH("Free",D34&amp;"")),AND(ISNUMBER(F34),F34=0))),"Subscription",IF(ISNUMBER(G34),"Profit",IF(ISNUMBER(I34),"Loss",IF(ISNUMBER(H34),"Draw",IF(AND(ISNUMBER(F34),ISNUMBER(E34),E34&gt;0,F34&gt;E34),"Profit",IF(AND(ISNUMBER(F34),ISNUMBER(E34),E34&gt;0,F34=E34),"Draw",IF(AND(ISNUMBER(F34),ISNUMBER(E34),E34&gt;0,F34=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A34="","",IF(AND(ISNUMBER(E34),E34=0,OR(ISNUMBER(SEARCH("Free",D34&amp;"")),AND(ISNUMBER(F34),F34=0))),"Subscription",IF(ISNUMBER(G34),"Profit",IF(ISNUMBER(I34),"Disqualified",IF(ISNUMBER(H34),"Draw",IF(AND(ISNUMBER(F34),ISNUMBER(E34),E34&gt;0,F34&gt;E34),"Profit",IF(AND(ISNUMBER(F34),ISNUMBER(E34),E34&gt;0,F34=E34),"Draw",IF(AND(ISNUMBER(F34),ISNUMBER(E34),E34&gt;0,F34=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L34" s="50"/>
       <x:c r="M34" s="58"/>
@@ -2653,7 +2666,7 @@
         <x:f>IF(A35="","",IF(K35="Subscription","",IF(E35=0,"",IF(ISNUMBER(G35),G35/E35,IF(ISNUMBER(I35),-ABS(I35)/E35,IF(ISNUMBER(H35),0,IF(AND(ISNUMBER(F35),ISNUMBER(E35),E35&gt;0,F35&gt;E35),(F35-E35)/E35,IF(AND(ISNUMBER(F35),ISNUMBER(E35),E35&gt;0,F35=E35),0,IF(AND(ISNUMBER(F35),ISNUMBER(E35),E35&gt;0,F35=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K35" s="50" t="str">
-        <x:f>IF(A35="","",IF(AND(ISNUMBER(E35),E35=0,OR(ISNUMBER(SEARCH("Free",D35&amp;"")),AND(ISNUMBER(F35),F35=0))),"Subscription",IF(ISNUMBER(G35),"Profit",IF(ISNUMBER(I35),"Loss",IF(ISNUMBER(H35),"Draw",IF(AND(ISNUMBER(F35),ISNUMBER(E35),E35&gt;0,F35&gt;E35),"Profit",IF(AND(ISNUMBER(F35),ISNUMBER(E35),E35&gt;0,F35=E35),"Draw",IF(AND(ISNUMBER(F35),ISNUMBER(E35),E35&gt;0,F35=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A35="","",IF(AND(ISNUMBER(E35),E35=0,OR(ISNUMBER(SEARCH("Free",D35&amp;"")),AND(ISNUMBER(F35),F35=0))),"Subscription",IF(ISNUMBER(G35),"Profit",IF(ISNUMBER(I35),"Disqualified",IF(ISNUMBER(H35),"Draw",IF(AND(ISNUMBER(F35),ISNUMBER(E35),E35&gt;0,F35&gt;E35),"Profit",IF(AND(ISNUMBER(F35),ISNUMBER(E35),E35&gt;0,F35=E35),"Draw",IF(AND(ISNUMBER(F35),ISNUMBER(E35),E35&gt;0,F35=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L35" s="50"/>
       <x:c r="M35" s="58"/>
@@ -2690,7 +2703,7 @@
         <x:f>IF(A36="","",IF(K36="Subscription","",IF(E36=0,"",IF(ISNUMBER(G36),G36/E36,IF(ISNUMBER(I36),-ABS(I36)/E36,IF(ISNUMBER(H36),0,IF(AND(ISNUMBER(F36),ISNUMBER(E36),E36&gt;0,F36&gt;E36),(F36-E36)/E36,IF(AND(ISNUMBER(F36),ISNUMBER(E36),E36&gt;0,F36=E36),0,IF(AND(ISNUMBER(F36),ISNUMBER(E36),E36&gt;0,F36=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K36" s="50" t="str">
-        <x:f>IF(A36="","",IF(AND(ISNUMBER(E36),E36=0,OR(ISNUMBER(SEARCH("Free",D36&amp;"")),AND(ISNUMBER(F36),F36=0))),"Subscription",IF(ISNUMBER(G36),"Profit",IF(ISNUMBER(I36),"Loss",IF(ISNUMBER(H36),"Draw",IF(AND(ISNUMBER(F36),ISNUMBER(E36),E36&gt;0,F36&gt;E36),"Profit",IF(AND(ISNUMBER(F36),ISNUMBER(E36),E36&gt;0,F36=E36),"Draw",IF(AND(ISNUMBER(F36),ISNUMBER(E36),E36&gt;0,F36=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A36="","",IF(AND(ISNUMBER(E36),E36=0,OR(ISNUMBER(SEARCH("Free",D36&amp;"")),AND(ISNUMBER(F36),F36=0))),"Subscription",IF(ISNUMBER(G36),"Profit",IF(ISNUMBER(I36),"Disqualified",IF(ISNUMBER(H36),"Draw",IF(AND(ISNUMBER(F36),ISNUMBER(E36),E36&gt;0,F36&gt;E36),"Profit",IF(AND(ISNUMBER(F36),ISNUMBER(E36),E36&gt;0,F36=E36),"Draw",IF(AND(ISNUMBER(F36),ISNUMBER(E36),E36&gt;0,F36=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L36" s="50"/>
       <x:c r="M36" s="58"/>
@@ -2727,7 +2740,7 @@
         <x:f>IF(A37="","",IF(K37="Subscription","",IF(E37=0,"",IF(ISNUMBER(G37),G37/E37,IF(ISNUMBER(I37),-ABS(I37)/E37,IF(ISNUMBER(H37),0,IF(AND(ISNUMBER(F37),ISNUMBER(E37),E37&gt;0,F37&gt;E37),(F37-E37)/E37,IF(AND(ISNUMBER(F37),ISNUMBER(E37),E37&gt;0,F37=E37),0,IF(AND(ISNUMBER(F37),ISNUMBER(E37),E37&gt;0,F37=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K37" s="50" t="str">
-        <x:f>IF(A37="","",IF(AND(ISNUMBER(E37),E37=0,OR(ISNUMBER(SEARCH("Free",D37&amp;"")),AND(ISNUMBER(F37),F37=0))),"Subscription",IF(ISNUMBER(G37),"Profit",IF(ISNUMBER(I37),"Loss",IF(ISNUMBER(H37),"Draw",IF(AND(ISNUMBER(F37),ISNUMBER(E37),E37&gt;0,F37&gt;E37),"Profit",IF(AND(ISNUMBER(F37),ISNUMBER(E37),E37&gt;0,F37=E37),"Draw",IF(AND(ISNUMBER(F37),ISNUMBER(E37),E37&gt;0,F37=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A37="","",IF(AND(ISNUMBER(E37),E37=0,OR(ISNUMBER(SEARCH("Free",D37&amp;"")),AND(ISNUMBER(F37),F37=0))),"Subscription",IF(ISNUMBER(G37),"Profit",IF(ISNUMBER(I37),"Disqualified",IF(ISNUMBER(H37),"Draw",IF(AND(ISNUMBER(F37),ISNUMBER(E37),E37&gt;0,F37&gt;E37),"Profit",IF(AND(ISNUMBER(F37),ISNUMBER(E37),E37&gt;0,F37=E37),"Draw",IF(AND(ISNUMBER(F37),ISNUMBER(E37),E37&gt;0,F37=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L37" s="50"/>
       <x:c r="M37" s="58"/>
@@ -2764,7 +2777,7 @@
         <x:f>IF(A38="","",IF(K38="Subscription","",IF(E38=0,"",IF(ISNUMBER(G38),G38/E38,IF(ISNUMBER(I38),-ABS(I38)/E38,IF(ISNUMBER(H38),0,IF(AND(ISNUMBER(F38),ISNUMBER(E38),E38&gt;0,F38&gt;E38),(F38-E38)/E38,IF(AND(ISNUMBER(F38),ISNUMBER(E38),E38&gt;0,F38=E38),0,IF(AND(ISNUMBER(F38),ISNUMBER(E38),E38&gt;0,F38=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K38" s="50" t="str">
-        <x:f>IF(A38="","",IF(AND(ISNUMBER(E38),E38=0,OR(ISNUMBER(SEARCH("Free",D38&amp;"")),AND(ISNUMBER(F38),F38=0))),"Subscription",IF(ISNUMBER(G38),"Profit",IF(ISNUMBER(I38),"Loss",IF(ISNUMBER(H38),"Draw",IF(AND(ISNUMBER(F38),ISNUMBER(E38),E38&gt;0,F38&gt;E38),"Profit",IF(AND(ISNUMBER(F38),ISNUMBER(E38),E38&gt;0,F38=E38),"Draw",IF(AND(ISNUMBER(F38),ISNUMBER(E38),E38&gt;0,F38=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A38="","",IF(AND(ISNUMBER(E38),E38=0,OR(ISNUMBER(SEARCH("Free",D38&amp;"")),AND(ISNUMBER(F38),F38=0))),"Subscription",IF(ISNUMBER(G38),"Profit",IF(ISNUMBER(I38),"Disqualified",IF(ISNUMBER(H38),"Draw",IF(AND(ISNUMBER(F38),ISNUMBER(E38),E38&gt;0,F38&gt;E38),"Profit",IF(AND(ISNUMBER(F38),ISNUMBER(E38),E38&gt;0,F38=E38),"Draw",IF(AND(ISNUMBER(F38),ISNUMBER(E38),E38&gt;0,F38=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L38" s="50"/>
       <x:c r="M38" s="58"/>
@@ -2801,7 +2814,7 @@
         <x:f>IF(A39="","",IF(K39="Subscription","",IF(E39=0,"",IF(ISNUMBER(G39),G39/E39,IF(ISNUMBER(I39),-ABS(I39)/E39,IF(ISNUMBER(H39),0,IF(AND(ISNUMBER(F39),ISNUMBER(E39),E39&gt;0,F39&gt;E39),(F39-E39)/E39,IF(AND(ISNUMBER(F39),ISNUMBER(E39),E39&gt;0,F39=E39),0,IF(AND(ISNUMBER(F39),ISNUMBER(E39),E39&gt;0,F39=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K39" s="50" t="str">
-        <x:f>IF(A39="","",IF(AND(ISNUMBER(E39),E39=0,OR(ISNUMBER(SEARCH("Free",D39&amp;"")),AND(ISNUMBER(F39),F39=0))),"Subscription",IF(ISNUMBER(G39),"Profit",IF(ISNUMBER(I39),"Loss",IF(ISNUMBER(H39),"Draw",IF(AND(ISNUMBER(F39),ISNUMBER(E39),E39&gt;0,F39&gt;E39),"Profit",IF(AND(ISNUMBER(F39),ISNUMBER(E39),E39&gt;0,F39=E39),"Draw",IF(AND(ISNUMBER(F39),ISNUMBER(E39),E39&gt;0,F39=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A39="","",IF(AND(ISNUMBER(E39),E39=0,OR(ISNUMBER(SEARCH("Free",D39&amp;"")),AND(ISNUMBER(F39),F39=0))),"Subscription",IF(ISNUMBER(G39),"Profit",IF(ISNUMBER(I39),"Disqualified",IF(ISNUMBER(H39),"Draw",IF(AND(ISNUMBER(F39),ISNUMBER(E39),E39&gt;0,F39&gt;E39),"Profit",IF(AND(ISNUMBER(F39),ISNUMBER(E39),E39&gt;0,F39=E39),"Draw",IF(AND(ISNUMBER(F39),ISNUMBER(E39),E39&gt;0,F39=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L39" s="50"/>
       <x:c r="M39" s="58"/>
@@ -2838,7 +2851,7 @@
         <x:f>IF(A40="","",IF(K40="Subscription","",IF(E40=0,"",IF(ISNUMBER(G40),G40/E40,IF(ISNUMBER(I40),-ABS(I40)/E40,IF(ISNUMBER(H40),0,IF(AND(ISNUMBER(F40),ISNUMBER(E40),E40&gt;0,F40&gt;E40),(F40-E40)/E40,IF(AND(ISNUMBER(F40),ISNUMBER(E40),E40&gt;0,F40=E40),0,IF(AND(ISNUMBER(F40),ISNUMBER(E40),E40&gt;0,F40=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K40" s="50" t="str">
-        <x:f>IF(A40="","",IF(AND(ISNUMBER(E40),E40=0,OR(ISNUMBER(SEARCH("Free",D40&amp;"")),AND(ISNUMBER(F40),F40=0))),"Subscription",IF(ISNUMBER(G40),"Profit",IF(ISNUMBER(I40),"Loss",IF(ISNUMBER(H40),"Draw",IF(AND(ISNUMBER(F40),ISNUMBER(E40),E40&gt;0,F40&gt;E40),"Profit",IF(AND(ISNUMBER(F40),ISNUMBER(E40),E40&gt;0,F40=E40),"Draw",IF(AND(ISNUMBER(F40),ISNUMBER(E40),E40&gt;0,F40=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A40="","",IF(AND(ISNUMBER(E40),E40=0,OR(ISNUMBER(SEARCH("Free",D40&amp;"")),AND(ISNUMBER(F40),F40=0))),"Subscription",IF(ISNUMBER(G40),"Profit",IF(ISNUMBER(I40),"Disqualified",IF(ISNUMBER(H40),"Draw",IF(AND(ISNUMBER(F40),ISNUMBER(E40),E40&gt;0,F40&gt;E40),"Profit",IF(AND(ISNUMBER(F40),ISNUMBER(E40),E40&gt;0,F40=E40),"Draw",IF(AND(ISNUMBER(F40),ISNUMBER(E40),E40&gt;0,F40=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L40" s="50"/>
       <x:c r="M40" s="58"/>
@@ -2875,7 +2888,7 @@
         <x:f>IF(A41="","",IF(K41="Subscription","",IF(E41=0,"",IF(ISNUMBER(G41),G41/E41,IF(ISNUMBER(I41),-ABS(I41)/E41,IF(ISNUMBER(H41),0,IF(AND(ISNUMBER(F41),ISNUMBER(E41),E41&gt;0,F41&gt;E41),(F41-E41)/E41,IF(AND(ISNUMBER(F41),ISNUMBER(E41),E41&gt;0,F41=E41),0,IF(AND(ISNUMBER(F41),ISNUMBER(E41),E41&gt;0,F41=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K41" s="50" t="str">
-        <x:f>IF(A41="","",IF(AND(ISNUMBER(E41),E41=0,OR(ISNUMBER(SEARCH("Free",D41&amp;"")),AND(ISNUMBER(F41),F41=0))),"Subscription",IF(ISNUMBER(G41),"Profit",IF(ISNUMBER(I41),"Loss",IF(ISNUMBER(H41),"Draw",IF(AND(ISNUMBER(F41),ISNUMBER(E41),E41&gt;0,F41&gt;E41),"Profit",IF(AND(ISNUMBER(F41),ISNUMBER(E41),E41&gt;0,F41=E41),"Draw",IF(AND(ISNUMBER(F41),ISNUMBER(E41),E41&gt;0,F41=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A41="","",IF(AND(ISNUMBER(E41),E41=0,OR(ISNUMBER(SEARCH("Free",D41&amp;"")),AND(ISNUMBER(F41),F41=0))),"Subscription",IF(ISNUMBER(G41),"Profit",IF(ISNUMBER(I41),"Disqualified",IF(ISNUMBER(H41),"Draw",IF(AND(ISNUMBER(F41),ISNUMBER(E41),E41&gt;0,F41&gt;E41),"Profit",IF(AND(ISNUMBER(F41),ISNUMBER(E41),E41&gt;0,F41=E41),"Draw",IF(AND(ISNUMBER(F41),ISNUMBER(E41),E41&gt;0,F41=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L41" s="50"/>
       <x:c r="M41" s="58"/>
@@ -2912,7 +2925,7 @@
         <x:f>IF(A42="","",IF(K42="Subscription","",IF(E42=0,"",IF(ISNUMBER(G42),G42/E42,IF(ISNUMBER(I42),-ABS(I42)/E42,IF(ISNUMBER(H42),0,IF(AND(ISNUMBER(F42),ISNUMBER(E42),E42&gt;0,F42&gt;E42),(F42-E42)/E42,IF(AND(ISNUMBER(F42),ISNUMBER(E42),E42&gt;0,F42=E42),0,IF(AND(ISNUMBER(F42),ISNUMBER(E42),E42&gt;0,F42=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K42" s="50" t="str">
-        <x:f>IF(A42="","",IF(AND(ISNUMBER(E42),E42=0,OR(ISNUMBER(SEARCH("Free",D42&amp;"")),AND(ISNUMBER(F42),F42=0))),"Subscription",IF(ISNUMBER(G42),"Profit",IF(ISNUMBER(I42),"Loss",IF(ISNUMBER(H42),"Draw",IF(AND(ISNUMBER(F42),ISNUMBER(E42),E42&gt;0,F42&gt;E42),"Profit",IF(AND(ISNUMBER(F42),ISNUMBER(E42),E42&gt;0,F42=E42),"Draw",IF(AND(ISNUMBER(F42),ISNUMBER(E42),E42&gt;0,F42=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A42="","",IF(AND(ISNUMBER(E42),E42=0,OR(ISNUMBER(SEARCH("Free",D42&amp;"")),AND(ISNUMBER(F42),F42=0))),"Subscription",IF(ISNUMBER(G42),"Profit",IF(ISNUMBER(I42),"Disqualified",IF(ISNUMBER(H42),"Draw",IF(AND(ISNUMBER(F42),ISNUMBER(E42),E42&gt;0,F42&gt;E42),"Profit",IF(AND(ISNUMBER(F42),ISNUMBER(E42),E42&gt;0,F42=E42),"Draw",IF(AND(ISNUMBER(F42),ISNUMBER(E42),E42&gt;0,F42=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L42" s="50"/>
       <x:c r="M42" s="58"/>
@@ -2949,7 +2962,7 @@
         <x:f>IF(A43="","",IF(K43="Subscription","",IF(E43=0,"",IF(ISNUMBER(G43),G43/E43,IF(ISNUMBER(I43),-ABS(I43)/E43,IF(ISNUMBER(H43),0,IF(AND(ISNUMBER(F43),ISNUMBER(E43),E43&gt;0,F43&gt;E43),(F43-E43)/E43,IF(AND(ISNUMBER(F43),ISNUMBER(E43),E43&gt;0,F43=E43),0,IF(AND(ISNUMBER(F43),ISNUMBER(E43),E43&gt;0,F43=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K43" s="50" t="str">
-        <x:f>IF(A43="","",IF(AND(ISNUMBER(E43),E43=0,OR(ISNUMBER(SEARCH("Free",D43&amp;"")),AND(ISNUMBER(F43),F43=0))),"Subscription",IF(ISNUMBER(G43),"Profit",IF(ISNUMBER(I43),"Loss",IF(ISNUMBER(H43),"Draw",IF(AND(ISNUMBER(F43),ISNUMBER(E43),E43&gt;0,F43&gt;E43),"Profit",IF(AND(ISNUMBER(F43),ISNUMBER(E43),E43&gt;0,F43=E43),"Draw",IF(AND(ISNUMBER(F43),ISNUMBER(E43),E43&gt;0,F43=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A43="","",IF(AND(ISNUMBER(E43),E43=0,OR(ISNUMBER(SEARCH("Free",D43&amp;"")),AND(ISNUMBER(F43),F43=0))),"Subscription",IF(ISNUMBER(G43),"Profit",IF(ISNUMBER(I43),"Disqualified",IF(ISNUMBER(H43),"Draw",IF(AND(ISNUMBER(F43),ISNUMBER(E43),E43&gt;0,F43&gt;E43),"Profit",IF(AND(ISNUMBER(F43),ISNUMBER(E43),E43&gt;0,F43=E43),"Draw",IF(AND(ISNUMBER(F43),ISNUMBER(E43),E43&gt;0,F43=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L43" s="50"/>
       <x:c r="M43" s="58"/>
@@ -2986,7 +2999,7 @@
         <x:f>IF(A44="","",IF(K44="Subscription","",IF(E44=0,"",IF(ISNUMBER(G44),G44/E44,IF(ISNUMBER(I44),-ABS(I44)/E44,IF(ISNUMBER(H44),0,IF(AND(ISNUMBER(F44),ISNUMBER(E44),E44&gt;0,F44&gt;E44),(F44-E44)/E44,IF(AND(ISNUMBER(F44),ISNUMBER(E44),E44&gt;0,F44=E44),0,IF(AND(ISNUMBER(F44),ISNUMBER(E44),E44&gt;0,F44=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K44" s="50" t="str">
-        <x:f>IF(A44="","",IF(AND(ISNUMBER(E44),E44=0,OR(ISNUMBER(SEARCH("Free",D44&amp;"")),AND(ISNUMBER(F44),F44=0))),"Subscription",IF(ISNUMBER(G44),"Profit",IF(ISNUMBER(I44),"Loss",IF(ISNUMBER(H44),"Draw",IF(AND(ISNUMBER(F44),ISNUMBER(E44),E44&gt;0,F44&gt;E44),"Profit",IF(AND(ISNUMBER(F44),ISNUMBER(E44),E44&gt;0,F44=E44),"Draw",IF(AND(ISNUMBER(F44),ISNUMBER(E44),E44&gt;0,F44=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A44="","",IF(AND(ISNUMBER(E44),E44=0,OR(ISNUMBER(SEARCH("Free",D44&amp;"")),AND(ISNUMBER(F44),F44=0))),"Subscription",IF(ISNUMBER(G44),"Profit",IF(ISNUMBER(I44),"Disqualified",IF(ISNUMBER(H44),"Draw",IF(AND(ISNUMBER(F44),ISNUMBER(E44),E44&gt;0,F44&gt;E44),"Profit",IF(AND(ISNUMBER(F44),ISNUMBER(E44),E44&gt;0,F44=E44),"Draw",IF(AND(ISNUMBER(F44),ISNUMBER(E44),E44&gt;0,F44=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L44" s="50"/>
       <x:c r="M44" s="58"/>
@@ -3023,7 +3036,7 @@
         <x:f>IF(A45="","",IF(K45="Subscription","",IF(E45=0,"",IF(ISNUMBER(G45),G45/E45,IF(ISNUMBER(I45),-ABS(I45)/E45,IF(ISNUMBER(H45),0,IF(AND(ISNUMBER(F45),ISNUMBER(E45),E45&gt;0,F45&gt;E45),(F45-E45)/E45,IF(AND(ISNUMBER(F45),ISNUMBER(E45),E45&gt;0,F45=E45),0,IF(AND(ISNUMBER(F45),ISNUMBER(E45),E45&gt;0,F45=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K45" s="50" t="str">
-        <x:f>IF(A45="","",IF(AND(ISNUMBER(E45),E45=0,OR(ISNUMBER(SEARCH("Free",D45&amp;"")),AND(ISNUMBER(F45),F45=0))),"Subscription",IF(ISNUMBER(G45),"Profit",IF(ISNUMBER(I45),"Loss",IF(ISNUMBER(H45),"Draw",IF(AND(ISNUMBER(F45),ISNUMBER(E45),E45&gt;0,F45&gt;E45),"Profit",IF(AND(ISNUMBER(F45),ISNUMBER(E45),E45&gt;0,F45=E45),"Draw",IF(AND(ISNUMBER(F45),ISNUMBER(E45),E45&gt;0,F45=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A45="","",IF(AND(ISNUMBER(E45),E45=0,OR(ISNUMBER(SEARCH("Free",D45&amp;"")),AND(ISNUMBER(F45),F45=0))),"Subscription",IF(ISNUMBER(G45),"Profit",IF(ISNUMBER(I45),"Disqualified",IF(ISNUMBER(H45),"Draw",IF(AND(ISNUMBER(F45),ISNUMBER(E45),E45&gt;0,F45&gt;E45),"Profit",IF(AND(ISNUMBER(F45),ISNUMBER(E45),E45&gt;0,F45=E45),"Draw",IF(AND(ISNUMBER(F45),ISNUMBER(E45),E45&gt;0,F45=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L45" s="50"/>
       <x:c r="M45" s="58"/>
@@ -3060,7 +3073,7 @@
         <x:f>IF(A46="","",IF(K46="Subscription","",IF(E46=0,"",IF(ISNUMBER(G46),G46/E46,IF(ISNUMBER(I46),-ABS(I46)/E46,IF(ISNUMBER(H46),0,IF(AND(ISNUMBER(F46),ISNUMBER(E46),E46&gt;0,F46&gt;E46),(F46-E46)/E46,IF(AND(ISNUMBER(F46),ISNUMBER(E46),E46&gt;0,F46=E46),0,IF(AND(ISNUMBER(F46),ISNUMBER(E46),E46&gt;0,F46=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K46" s="50" t="str">
-        <x:f>IF(A46="","",IF(AND(ISNUMBER(E46),E46=0,OR(ISNUMBER(SEARCH("Free",D46&amp;"")),AND(ISNUMBER(F46),F46=0))),"Subscription",IF(ISNUMBER(G46),"Profit",IF(ISNUMBER(I46),"Loss",IF(ISNUMBER(H46),"Draw",IF(AND(ISNUMBER(F46),ISNUMBER(E46),E46&gt;0,F46&gt;E46),"Profit",IF(AND(ISNUMBER(F46),ISNUMBER(E46),E46&gt;0,F46=E46),"Draw",IF(AND(ISNUMBER(F46),ISNUMBER(E46),E46&gt;0,F46=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A46="","",IF(AND(ISNUMBER(E46),E46=0,OR(ISNUMBER(SEARCH("Free",D46&amp;"")),AND(ISNUMBER(F46),F46=0))),"Subscription",IF(ISNUMBER(G46),"Profit",IF(ISNUMBER(I46),"Disqualified",IF(ISNUMBER(H46),"Draw",IF(AND(ISNUMBER(F46),ISNUMBER(E46),E46&gt;0,F46&gt;E46),"Profit",IF(AND(ISNUMBER(F46),ISNUMBER(E46),E46&gt;0,F46=E46),"Draw",IF(AND(ISNUMBER(F46),ISNUMBER(E46),E46&gt;0,F46=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L46" s="50"/>
       <x:c r="M46" s="58"/>
@@ -3097,7 +3110,7 @@
         <x:f>IF(A47="","",IF(K47="Subscription","",IF(E47=0,"",IF(ISNUMBER(G47),G47/E47,IF(ISNUMBER(I47),-ABS(I47)/E47,IF(ISNUMBER(H47),0,IF(AND(ISNUMBER(F47),ISNUMBER(E47),E47&gt;0,F47&gt;E47),(F47-E47)/E47,IF(AND(ISNUMBER(F47),ISNUMBER(E47),E47&gt;0,F47=E47),0,IF(AND(ISNUMBER(F47),ISNUMBER(E47),E47&gt;0,F47=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K47" s="50" t="str">
-        <x:f>IF(A47="","",IF(AND(ISNUMBER(E47),E47=0,OR(ISNUMBER(SEARCH("Free",D47&amp;"")),AND(ISNUMBER(F47),F47=0))),"Subscription",IF(ISNUMBER(G47),"Profit",IF(ISNUMBER(I47),"Loss",IF(ISNUMBER(H47),"Draw",IF(AND(ISNUMBER(F47),ISNUMBER(E47),E47&gt;0,F47&gt;E47),"Profit",IF(AND(ISNUMBER(F47),ISNUMBER(E47),E47&gt;0,F47=E47),"Draw",IF(AND(ISNUMBER(F47),ISNUMBER(E47),E47&gt;0,F47=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A47="","",IF(AND(ISNUMBER(E47),E47=0,OR(ISNUMBER(SEARCH("Free",D47&amp;"")),AND(ISNUMBER(F47),F47=0))),"Subscription",IF(ISNUMBER(G47),"Profit",IF(ISNUMBER(I47),"Disqualified",IF(ISNUMBER(H47),"Draw",IF(AND(ISNUMBER(F47),ISNUMBER(E47),E47&gt;0,F47&gt;E47),"Profit",IF(AND(ISNUMBER(F47),ISNUMBER(E47),E47&gt;0,F47=E47),"Draw",IF(AND(ISNUMBER(F47),ISNUMBER(E47),E47&gt;0,F47=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L47" s="50"/>
       <x:c r="M47" s="58"/>
@@ -3134,7 +3147,7 @@
         <x:f>IF(A48="","",IF(K48="Subscription","",IF(E48=0,"",IF(ISNUMBER(G48),G48/E48,IF(ISNUMBER(I48),-ABS(I48)/E48,IF(ISNUMBER(H48),0,IF(AND(ISNUMBER(F48),ISNUMBER(E48),E48&gt;0,F48&gt;E48),(F48-E48)/E48,IF(AND(ISNUMBER(F48),ISNUMBER(E48),E48&gt;0,F48=E48),0,IF(AND(ISNUMBER(F48),ISNUMBER(E48),E48&gt;0,F48=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K48" s="50" t="str">
-        <x:f>IF(A48="","",IF(AND(ISNUMBER(E48),E48=0,OR(ISNUMBER(SEARCH("Free",D48&amp;"")),AND(ISNUMBER(F48),F48=0))),"Subscription",IF(ISNUMBER(G48),"Profit",IF(ISNUMBER(I48),"Loss",IF(ISNUMBER(H48),"Draw",IF(AND(ISNUMBER(F48),ISNUMBER(E48),E48&gt;0,F48&gt;E48),"Profit",IF(AND(ISNUMBER(F48),ISNUMBER(E48),E48&gt;0,F48=E48),"Draw",IF(AND(ISNUMBER(F48),ISNUMBER(E48),E48&gt;0,F48=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A48="","",IF(AND(ISNUMBER(E48),E48=0,OR(ISNUMBER(SEARCH("Free",D48&amp;"")),AND(ISNUMBER(F48),F48=0))),"Subscription",IF(ISNUMBER(G48),"Profit",IF(ISNUMBER(I48),"Disqualified",IF(ISNUMBER(H48),"Draw",IF(AND(ISNUMBER(F48),ISNUMBER(E48),E48&gt;0,F48&gt;E48),"Profit",IF(AND(ISNUMBER(F48),ISNUMBER(E48),E48&gt;0,F48=E48),"Draw",IF(AND(ISNUMBER(F48),ISNUMBER(E48),E48&gt;0,F48=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L48" s="50"/>
       <x:c r="M48" s="58"/>
@@ -3171,7 +3184,7 @@
         <x:f>IF(A49="","",IF(K49="Subscription","",IF(E49=0,"",IF(ISNUMBER(G49),G49/E49,IF(ISNUMBER(I49),-ABS(I49)/E49,IF(ISNUMBER(H49),0,IF(AND(ISNUMBER(F49),ISNUMBER(E49),E49&gt;0,F49&gt;E49),(F49-E49)/E49,IF(AND(ISNUMBER(F49),ISNUMBER(E49),E49&gt;0,F49=E49),0,IF(AND(ISNUMBER(F49),ISNUMBER(E49),E49&gt;0,F49=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K49" s="50" t="str">
-        <x:f>IF(A49="","",IF(AND(ISNUMBER(E49),E49=0,OR(ISNUMBER(SEARCH("Free",D49&amp;"")),AND(ISNUMBER(F49),F49=0))),"Subscription",IF(ISNUMBER(G49),"Profit",IF(ISNUMBER(I49),"Loss",IF(ISNUMBER(H49),"Draw",IF(AND(ISNUMBER(F49),ISNUMBER(E49),E49&gt;0,F49&gt;E49),"Profit",IF(AND(ISNUMBER(F49),ISNUMBER(E49),E49&gt;0,F49=E49),"Draw",IF(AND(ISNUMBER(F49),ISNUMBER(E49),E49&gt;0,F49=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A49="","",IF(AND(ISNUMBER(E49),E49=0,OR(ISNUMBER(SEARCH("Free",D49&amp;"")),AND(ISNUMBER(F49),F49=0))),"Subscription",IF(ISNUMBER(G49),"Profit",IF(ISNUMBER(I49),"Disqualified",IF(ISNUMBER(H49),"Draw",IF(AND(ISNUMBER(F49),ISNUMBER(E49),E49&gt;0,F49&gt;E49),"Profit",IF(AND(ISNUMBER(F49),ISNUMBER(E49),E49&gt;0,F49=E49),"Draw",IF(AND(ISNUMBER(F49),ISNUMBER(E49),E49&gt;0,F49=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L49" s="50"/>
       <x:c r="M49" s="58"/>
@@ -3208,7 +3221,7 @@
         <x:f>IF(A50="","",IF(K50="Subscription","",IF(E50=0,"",IF(ISNUMBER(G50),G50/E50,IF(ISNUMBER(I50),-ABS(I50)/E50,IF(ISNUMBER(H50),0,IF(AND(ISNUMBER(F50),ISNUMBER(E50),E50&gt;0,F50&gt;E50),(F50-E50)/E50,IF(AND(ISNUMBER(F50),ISNUMBER(E50),E50&gt;0,F50=E50),0,IF(AND(ISNUMBER(F50),ISNUMBER(E50),E50&gt;0,F50=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K50" s="50" t="str">
-        <x:f>IF(A50="","",IF(AND(ISNUMBER(E50),E50=0,OR(ISNUMBER(SEARCH("Free",D50&amp;"")),AND(ISNUMBER(F50),F50=0))),"Subscription",IF(ISNUMBER(G50),"Profit",IF(ISNUMBER(I50),"Loss",IF(ISNUMBER(H50),"Draw",IF(AND(ISNUMBER(F50),ISNUMBER(E50),E50&gt;0,F50&gt;E50),"Profit",IF(AND(ISNUMBER(F50),ISNUMBER(E50),E50&gt;0,F50=E50),"Draw",IF(AND(ISNUMBER(F50),ISNUMBER(E50),E50&gt;0,F50=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A50="","",IF(AND(ISNUMBER(E50),E50=0,OR(ISNUMBER(SEARCH("Free",D50&amp;"")),AND(ISNUMBER(F50),F50=0))),"Subscription",IF(ISNUMBER(G50),"Profit",IF(ISNUMBER(I50),"Disqualified",IF(ISNUMBER(H50),"Draw",IF(AND(ISNUMBER(F50),ISNUMBER(E50),E50&gt;0,F50&gt;E50),"Profit",IF(AND(ISNUMBER(F50),ISNUMBER(E50),E50&gt;0,F50=E50),"Draw",IF(AND(ISNUMBER(F50),ISNUMBER(E50),E50&gt;0,F50=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L50" s="50"/>
       <x:c r="M50" s="58"/>
@@ -3245,7 +3258,7 @@
         <x:f>IF(A51="","",IF(K51="Subscription","",IF(E51=0,"",IF(ISNUMBER(G51),G51/E51,IF(ISNUMBER(I51),-ABS(I51)/E51,IF(ISNUMBER(H51),0,IF(AND(ISNUMBER(F51),ISNUMBER(E51),E51&gt;0,F51&gt;E51),(F51-E51)/E51,IF(AND(ISNUMBER(F51),ISNUMBER(E51),E51&gt;0,F51=E51),0,IF(AND(ISNUMBER(F51),ISNUMBER(E51),E51&gt;0,F51=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K51" s="50" t="str">
-        <x:f>IF(A51="","",IF(AND(ISNUMBER(E51),E51=0,OR(ISNUMBER(SEARCH("Free",D51&amp;"")),AND(ISNUMBER(F51),F51=0))),"Subscription",IF(ISNUMBER(G51),"Profit",IF(ISNUMBER(I51),"Loss",IF(ISNUMBER(H51),"Draw",IF(AND(ISNUMBER(F51),ISNUMBER(E51),E51&gt;0,F51&gt;E51),"Profit",IF(AND(ISNUMBER(F51),ISNUMBER(E51),E51&gt;0,F51=E51),"Draw",IF(AND(ISNUMBER(F51),ISNUMBER(E51),E51&gt;0,F51=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A51="","",IF(AND(ISNUMBER(E51),E51=0,OR(ISNUMBER(SEARCH("Free",D51&amp;"")),AND(ISNUMBER(F51),F51=0))),"Subscription",IF(ISNUMBER(G51),"Profit",IF(ISNUMBER(I51),"Disqualified",IF(ISNUMBER(H51),"Draw",IF(AND(ISNUMBER(F51),ISNUMBER(E51),E51&gt;0,F51&gt;E51),"Profit",IF(AND(ISNUMBER(F51),ISNUMBER(E51),E51&gt;0,F51=E51),"Draw",IF(AND(ISNUMBER(F51),ISNUMBER(E51),E51&gt;0,F51=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L51" s="50"/>
       <x:c r="M51" s="58"/>
@@ -3282,7 +3295,7 @@
         <x:f>IF(A52="","",IF(K52="Subscription","",IF(E52=0,"",IF(ISNUMBER(G52),G52/E52,IF(ISNUMBER(I52),-ABS(I52)/E52,IF(ISNUMBER(H52),0,IF(AND(ISNUMBER(F52),ISNUMBER(E52),E52&gt;0,F52&gt;E52),(F52-E52)/E52,IF(AND(ISNUMBER(F52),ISNUMBER(E52),E52&gt;0,F52=E52),0,IF(AND(ISNUMBER(F52),ISNUMBER(E52),E52&gt;0,F52=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K52" s="50" t="str">
-        <x:f>IF(A52="","",IF(AND(ISNUMBER(E52),E52=0,OR(ISNUMBER(SEARCH("Free",D52&amp;"")),AND(ISNUMBER(F52),F52=0))),"Subscription",IF(ISNUMBER(G52),"Profit",IF(ISNUMBER(I52),"Loss",IF(ISNUMBER(H52),"Draw",IF(AND(ISNUMBER(F52),ISNUMBER(E52),E52&gt;0,F52&gt;E52),"Profit",IF(AND(ISNUMBER(F52),ISNUMBER(E52),E52&gt;0,F52=E52),"Draw",IF(AND(ISNUMBER(F52),ISNUMBER(E52),E52&gt;0,F52=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A52="","",IF(AND(ISNUMBER(E52),E52=0,OR(ISNUMBER(SEARCH("Free",D52&amp;"")),AND(ISNUMBER(F52),F52=0))),"Subscription",IF(ISNUMBER(G52),"Profit",IF(ISNUMBER(I52),"Disqualified",IF(ISNUMBER(H52),"Draw",IF(AND(ISNUMBER(F52),ISNUMBER(E52),E52&gt;0,F52&gt;E52),"Profit",IF(AND(ISNUMBER(F52),ISNUMBER(E52),E52&gt;0,F52=E52),"Draw",IF(AND(ISNUMBER(F52),ISNUMBER(E52),E52&gt;0,F52=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L52" s="50"/>
       <x:c r="M52" s="58"/>
@@ -3319,7 +3332,7 @@
         <x:f>IF(A53="","",IF(K53="Subscription","",IF(E53=0,"",IF(ISNUMBER(G53),G53/E53,IF(ISNUMBER(I53),-ABS(I53)/E53,IF(ISNUMBER(H53),0,IF(AND(ISNUMBER(F53),ISNUMBER(E53),E53&gt;0,F53&gt;E53),(F53-E53)/E53,IF(AND(ISNUMBER(F53),ISNUMBER(E53),E53&gt;0,F53=E53),0,IF(AND(ISNUMBER(F53),ISNUMBER(E53),E53&gt;0,F53=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K53" s="50" t="str">
-        <x:f>IF(A53="","",IF(AND(ISNUMBER(E53),E53=0,OR(ISNUMBER(SEARCH("Free",D53&amp;"")),AND(ISNUMBER(F53),F53=0))),"Subscription",IF(ISNUMBER(G53),"Profit",IF(ISNUMBER(I53),"Loss",IF(ISNUMBER(H53),"Draw",IF(AND(ISNUMBER(F53),ISNUMBER(E53),E53&gt;0,F53&gt;E53),"Profit",IF(AND(ISNUMBER(F53),ISNUMBER(E53),E53&gt;0,F53=E53),"Draw",IF(AND(ISNUMBER(F53),ISNUMBER(E53),E53&gt;0,F53=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A53="","",IF(AND(ISNUMBER(E53),E53=0,OR(ISNUMBER(SEARCH("Free",D53&amp;"")),AND(ISNUMBER(F53),F53=0))),"Subscription",IF(ISNUMBER(G53),"Profit",IF(ISNUMBER(I53),"Disqualified",IF(ISNUMBER(H53),"Draw",IF(AND(ISNUMBER(F53),ISNUMBER(E53),E53&gt;0,F53&gt;E53),"Profit",IF(AND(ISNUMBER(F53),ISNUMBER(E53),E53&gt;0,F53=E53),"Draw",IF(AND(ISNUMBER(F53),ISNUMBER(E53),E53&gt;0,F53=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L53" s="50"/>
       <x:c r="M53" s="58"/>
@@ -3356,7 +3369,7 @@
         <x:f>IF(A54="","",IF(K54="Subscription","",IF(E54=0,"",IF(ISNUMBER(G54),G54/E54,IF(ISNUMBER(I54),-ABS(I54)/E54,IF(ISNUMBER(H54),0,IF(AND(ISNUMBER(F54),ISNUMBER(E54),E54&gt;0,F54&gt;E54),(F54-E54)/E54,IF(AND(ISNUMBER(F54),ISNUMBER(E54),E54&gt;0,F54=E54),0,IF(AND(ISNUMBER(F54),ISNUMBER(E54),E54&gt;0,F54=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K54" s="50" t="str">
-        <x:f>IF(A54="","",IF(AND(ISNUMBER(E54),E54=0,OR(ISNUMBER(SEARCH("Free",D54&amp;"")),AND(ISNUMBER(F54),F54=0))),"Subscription",IF(ISNUMBER(G54),"Profit",IF(ISNUMBER(I54),"Loss",IF(ISNUMBER(H54),"Draw",IF(AND(ISNUMBER(F54),ISNUMBER(E54),E54&gt;0,F54&gt;E54),"Profit",IF(AND(ISNUMBER(F54),ISNUMBER(E54),E54&gt;0,F54=E54),"Draw",IF(AND(ISNUMBER(F54),ISNUMBER(E54),E54&gt;0,F54=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A54="","",IF(AND(ISNUMBER(E54),E54=0,OR(ISNUMBER(SEARCH("Free",D54&amp;"")),AND(ISNUMBER(F54),F54=0))),"Subscription",IF(ISNUMBER(G54),"Profit",IF(ISNUMBER(I54),"Disqualified",IF(ISNUMBER(H54),"Draw",IF(AND(ISNUMBER(F54),ISNUMBER(E54),E54&gt;0,F54&gt;E54),"Profit",IF(AND(ISNUMBER(F54),ISNUMBER(E54),E54&gt;0,F54=E54),"Draw",IF(AND(ISNUMBER(F54),ISNUMBER(E54),E54&gt;0,F54=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L54" s="50"/>
       <x:c r="M54" s="58"/>
@@ -3393,7 +3406,7 @@
         <x:f>IF(A55="","",IF(K55="Subscription","",IF(E55=0,"",IF(ISNUMBER(G55),G55/E55,IF(ISNUMBER(I55),-ABS(I55)/E55,IF(ISNUMBER(H55),0,IF(AND(ISNUMBER(F55),ISNUMBER(E55),E55&gt;0,F55&gt;E55),(F55-E55)/E55,IF(AND(ISNUMBER(F55),ISNUMBER(E55),E55&gt;0,F55=E55),0,IF(AND(ISNUMBER(F55),ISNUMBER(E55),E55&gt;0,F55=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K55" s="50" t="str">
-        <x:f>IF(A55="","",IF(AND(ISNUMBER(E55),E55=0,OR(ISNUMBER(SEARCH("Free",D55&amp;"")),AND(ISNUMBER(F55),F55=0))),"Subscription",IF(ISNUMBER(G55),"Profit",IF(ISNUMBER(I55),"Loss",IF(ISNUMBER(H55),"Draw",IF(AND(ISNUMBER(F55),ISNUMBER(E55),E55&gt;0,F55&gt;E55),"Profit",IF(AND(ISNUMBER(F55),ISNUMBER(E55),E55&gt;0,F55=E55),"Draw",IF(AND(ISNUMBER(F55),ISNUMBER(E55),E55&gt;0,F55=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A55="","",IF(AND(ISNUMBER(E55),E55=0,OR(ISNUMBER(SEARCH("Free",D55&amp;"")),AND(ISNUMBER(F55),F55=0))),"Subscription",IF(ISNUMBER(G55),"Profit",IF(ISNUMBER(I55),"Disqualified",IF(ISNUMBER(H55),"Draw",IF(AND(ISNUMBER(F55),ISNUMBER(E55),E55&gt;0,F55&gt;E55),"Profit",IF(AND(ISNUMBER(F55),ISNUMBER(E55),E55&gt;0,F55=E55),"Draw",IF(AND(ISNUMBER(F55),ISNUMBER(E55),E55&gt;0,F55=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L55" s="50"/>
       <x:c r="M55" s="58"/>
@@ -3430,7 +3443,7 @@
         <x:f>IF(A56="","",IF(K56="Subscription","",IF(E56=0,"",IF(ISNUMBER(G56),G56/E56,IF(ISNUMBER(I56),-ABS(I56)/E56,IF(ISNUMBER(H56),0,IF(AND(ISNUMBER(F56),ISNUMBER(E56),E56&gt;0,F56&gt;E56),(F56-E56)/E56,IF(AND(ISNUMBER(F56),ISNUMBER(E56),E56&gt;0,F56=E56),0,IF(AND(ISNUMBER(F56),ISNUMBER(E56),E56&gt;0,F56=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K56" s="50" t="str">
-        <x:f>IF(A56="","",IF(AND(ISNUMBER(E56),E56=0,OR(ISNUMBER(SEARCH("Free",D56&amp;"")),AND(ISNUMBER(F56),F56=0))),"Subscription",IF(ISNUMBER(G56),"Profit",IF(ISNUMBER(I56),"Loss",IF(ISNUMBER(H56),"Draw",IF(AND(ISNUMBER(F56),ISNUMBER(E56),E56&gt;0,F56&gt;E56),"Profit",IF(AND(ISNUMBER(F56),ISNUMBER(E56),E56&gt;0,F56=E56),"Draw",IF(AND(ISNUMBER(F56),ISNUMBER(E56),E56&gt;0,F56=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A56="","",IF(AND(ISNUMBER(E56),E56=0,OR(ISNUMBER(SEARCH("Free",D56&amp;"")),AND(ISNUMBER(F56),F56=0))),"Subscription",IF(ISNUMBER(G56),"Profit",IF(ISNUMBER(I56),"Disqualified",IF(ISNUMBER(H56),"Draw",IF(AND(ISNUMBER(F56),ISNUMBER(E56),E56&gt;0,F56&gt;E56),"Profit",IF(AND(ISNUMBER(F56),ISNUMBER(E56),E56&gt;0,F56=E56),"Draw",IF(AND(ISNUMBER(F56),ISNUMBER(E56),E56&gt;0,F56=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L56" s="50"/>
       <x:c r="M56" s="58"/>
@@ -3467,7 +3480,7 @@
         <x:f>IF(A57="","",IF(K57="Subscription","",IF(E57=0,"",IF(ISNUMBER(G57),G57/E57,IF(ISNUMBER(I57),-ABS(I57)/E57,IF(ISNUMBER(H57),0,IF(AND(ISNUMBER(F57),ISNUMBER(E57),E57&gt;0,F57&gt;E57),(F57-E57)/E57,IF(AND(ISNUMBER(F57),ISNUMBER(E57),E57&gt;0,F57=E57),0,IF(AND(ISNUMBER(F57),ISNUMBER(E57),E57&gt;0,F57=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K57" s="50" t="str">
-        <x:f>IF(A57="","",IF(AND(ISNUMBER(E57),E57=0,OR(ISNUMBER(SEARCH("Free",D57&amp;"")),AND(ISNUMBER(F57),F57=0))),"Subscription",IF(ISNUMBER(G57),"Profit",IF(ISNUMBER(I57),"Loss",IF(ISNUMBER(H57),"Draw",IF(AND(ISNUMBER(F57),ISNUMBER(E57),E57&gt;0,F57&gt;E57),"Profit",IF(AND(ISNUMBER(F57),ISNUMBER(E57),E57&gt;0,F57=E57),"Draw",IF(AND(ISNUMBER(F57),ISNUMBER(E57),E57&gt;0,F57=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A57="","",IF(AND(ISNUMBER(E57),E57=0,OR(ISNUMBER(SEARCH("Free",D57&amp;"")),AND(ISNUMBER(F57),F57=0))),"Subscription",IF(ISNUMBER(G57),"Profit",IF(ISNUMBER(I57),"Disqualified",IF(ISNUMBER(H57),"Draw",IF(AND(ISNUMBER(F57),ISNUMBER(E57),E57&gt;0,F57&gt;E57),"Profit",IF(AND(ISNUMBER(F57),ISNUMBER(E57),E57&gt;0,F57=E57),"Draw",IF(AND(ISNUMBER(F57),ISNUMBER(E57),E57&gt;0,F57=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L57" s="50"/>
       <x:c r="M57" s="58"/>
@@ -3504,7 +3517,7 @@
         <x:f>IF(A58="","",IF(K58="Subscription","",IF(E58=0,"",IF(ISNUMBER(G58),G58/E58,IF(ISNUMBER(I58),-ABS(I58)/E58,IF(ISNUMBER(H58),0,IF(AND(ISNUMBER(F58),ISNUMBER(E58),E58&gt;0,F58&gt;E58),(F58-E58)/E58,IF(AND(ISNUMBER(F58),ISNUMBER(E58),E58&gt;0,F58=E58),0,IF(AND(ISNUMBER(F58),ISNUMBER(E58),E58&gt;0,F58=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K58" s="50" t="str">
-        <x:f>IF(A58="","",IF(AND(ISNUMBER(E58),E58=0,OR(ISNUMBER(SEARCH("Free",D58&amp;"")),AND(ISNUMBER(F58),F58=0))),"Subscription",IF(ISNUMBER(G58),"Profit",IF(ISNUMBER(I58),"Loss",IF(ISNUMBER(H58),"Draw",IF(AND(ISNUMBER(F58),ISNUMBER(E58),E58&gt;0,F58&gt;E58),"Profit",IF(AND(ISNUMBER(F58),ISNUMBER(E58),E58&gt;0,F58=E58),"Draw",IF(AND(ISNUMBER(F58),ISNUMBER(E58),E58&gt;0,F58=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A58="","",IF(AND(ISNUMBER(E58),E58=0,OR(ISNUMBER(SEARCH("Free",D58&amp;"")),AND(ISNUMBER(F58),F58=0))),"Subscription",IF(ISNUMBER(G58),"Profit",IF(ISNUMBER(I58),"Disqualified",IF(ISNUMBER(H58),"Draw",IF(AND(ISNUMBER(F58),ISNUMBER(E58),E58&gt;0,F58&gt;E58),"Profit",IF(AND(ISNUMBER(F58),ISNUMBER(E58),E58&gt;0,F58=E58),"Draw",IF(AND(ISNUMBER(F58),ISNUMBER(E58),E58&gt;0,F58=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L58" s="50"/>
       <x:c r="M58" s="58"/>
@@ -3541,7 +3554,7 @@
         <x:f>IF(A59="","",IF(K59="Subscription","",IF(E59=0,"",IF(ISNUMBER(G59),G59/E59,IF(ISNUMBER(I59),-ABS(I59)/E59,IF(ISNUMBER(H59),0,IF(AND(ISNUMBER(F59),ISNUMBER(E59),E59&gt;0,F59&gt;E59),(F59-E59)/E59,IF(AND(ISNUMBER(F59),ISNUMBER(E59),E59&gt;0,F59=E59),0,IF(AND(ISNUMBER(F59),ISNUMBER(E59),E59&gt;0,F59=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K59" s="50" t="str">
-        <x:f>IF(A59="","",IF(AND(ISNUMBER(E59),E59=0,OR(ISNUMBER(SEARCH("Free",D59&amp;"")),AND(ISNUMBER(F59),F59=0))),"Subscription",IF(ISNUMBER(G59),"Profit",IF(ISNUMBER(I59),"Loss",IF(ISNUMBER(H59),"Draw",IF(AND(ISNUMBER(F59),ISNUMBER(E59),E59&gt;0,F59&gt;E59),"Profit",IF(AND(ISNUMBER(F59),ISNUMBER(E59),E59&gt;0,F59=E59),"Draw",IF(AND(ISNUMBER(F59),ISNUMBER(E59),E59&gt;0,F59=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A59="","",IF(AND(ISNUMBER(E59),E59=0,OR(ISNUMBER(SEARCH("Free",D59&amp;"")),AND(ISNUMBER(F59),F59=0))),"Subscription",IF(ISNUMBER(G59),"Profit",IF(ISNUMBER(I59),"Disqualified",IF(ISNUMBER(H59),"Draw",IF(AND(ISNUMBER(F59),ISNUMBER(E59),E59&gt;0,F59&gt;E59),"Profit",IF(AND(ISNUMBER(F59),ISNUMBER(E59),E59&gt;0,F59=E59),"Draw",IF(AND(ISNUMBER(F59),ISNUMBER(E59),E59&gt;0,F59=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L59" s="50"/>
       <x:c r="M59" s="58"/>
@@ -3578,7 +3591,7 @@
         <x:f>IF(A60="","",IF(K60="Subscription","",IF(E60=0,"",IF(ISNUMBER(G60),G60/E60,IF(ISNUMBER(I60),-ABS(I60)/E60,IF(ISNUMBER(H60),0,IF(AND(ISNUMBER(F60),ISNUMBER(E60),E60&gt;0,F60&gt;E60),(F60-E60)/E60,IF(AND(ISNUMBER(F60),ISNUMBER(E60),E60&gt;0,F60=E60),0,IF(AND(ISNUMBER(F60),ISNUMBER(E60),E60&gt;0,F60=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K60" s="50" t="str">
-        <x:f>IF(A60="","",IF(AND(ISNUMBER(E60),E60=0,OR(ISNUMBER(SEARCH("Free",D60&amp;"")),AND(ISNUMBER(F60),F60=0))),"Subscription",IF(ISNUMBER(G60),"Profit",IF(ISNUMBER(I60),"Loss",IF(ISNUMBER(H60),"Draw",IF(AND(ISNUMBER(F60),ISNUMBER(E60),E60&gt;0,F60&gt;E60),"Profit",IF(AND(ISNUMBER(F60),ISNUMBER(E60),E60&gt;0,F60=E60),"Draw",IF(AND(ISNUMBER(F60),ISNUMBER(E60),E60&gt;0,F60=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A60="","",IF(AND(ISNUMBER(E60),E60=0,OR(ISNUMBER(SEARCH("Free",D60&amp;"")),AND(ISNUMBER(F60),F60=0))),"Subscription",IF(ISNUMBER(G60),"Profit",IF(ISNUMBER(I60),"Disqualified",IF(ISNUMBER(H60),"Draw",IF(AND(ISNUMBER(F60),ISNUMBER(E60),E60&gt;0,F60&gt;E60),"Profit",IF(AND(ISNUMBER(F60),ISNUMBER(E60),E60&gt;0,F60=E60),"Draw",IF(AND(ISNUMBER(F60),ISNUMBER(E60),E60&gt;0,F60=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L60" s="50"/>
       <x:c r="M60" s="58"/>
@@ -3615,7 +3628,7 @@
         <x:f>IF(A61="","",IF(K61="Subscription","",IF(E61=0,"",IF(ISNUMBER(G61),G61/E61,IF(ISNUMBER(I61),-ABS(I61)/E61,IF(ISNUMBER(H61),0,IF(AND(ISNUMBER(F61),ISNUMBER(E61),E61&gt;0,F61&gt;E61),(F61-E61)/E61,IF(AND(ISNUMBER(F61),ISNUMBER(E61),E61&gt;0,F61=E61),0,IF(AND(ISNUMBER(F61),ISNUMBER(E61),E61&gt;0,F61=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K61" s="50" t="str">
-        <x:f>IF(A61="","",IF(AND(ISNUMBER(E61),E61=0,OR(ISNUMBER(SEARCH("Free",D61&amp;"")),AND(ISNUMBER(F61),F61=0))),"Subscription",IF(ISNUMBER(G61),"Profit",IF(ISNUMBER(I61),"Loss",IF(ISNUMBER(H61),"Draw",IF(AND(ISNUMBER(F61),ISNUMBER(E61),E61&gt;0,F61&gt;E61),"Profit",IF(AND(ISNUMBER(F61),ISNUMBER(E61),E61&gt;0,F61=E61),"Draw",IF(AND(ISNUMBER(F61),ISNUMBER(E61),E61&gt;0,F61=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A61="","",IF(AND(ISNUMBER(E61),E61=0,OR(ISNUMBER(SEARCH("Free",D61&amp;"")),AND(ISNUMBER(F61),F61=0))),"Subscription",IF(ISNUMBER(G61),"Profit",IF(ISNUMBER(I61),"Disqualified",IF(ISNUMBER(H61),"Draw",IF(AND(ISNUMBER(F61),ISNUMBER(E61),E61&gt;0,F61&gt;E61),"Profit",IF(AND(ISNUMBER(F61),ISNUMBER(E61),E61&gt;0,F61=E61),"Draw",IF(AND(ISNUMBER(F61),ISNUMBER(E61),E61&gt;0,F61=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L61" s="50"/>
       <x:c r="M61" s="58"/>
@@ -3652,7 +3665,7 @@
         <x:f>IF(A62="","",IF(K62="Subscription","",IF(E62=0,"",IF(ISNUMBER(G62),G62/E62,IF(ISNUMBER(I62),-ABS(I62)/E62,IF(ISNUMBER(H62),0,IF(AND(ISNUMBER(F62),ISNUMBER(E62),E62&gt;0,F62&gt;E62),(F62-E62)/E62,IF(AND(ISNUMBER(F62),ISNUMBER(E62),E62&gt;0,F62=E62),0,IF(AND(ISNUMBER(F62),ISNUMBER(E62),E62&gt;0,F62=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K62" s="50" t="str">
-        <x:f>IF(A62="","",IF(AND(ISNUMBER(E62),E62=0,OR(ISNUMBER(SEARCH("Free",D62&amp;"")),AND(ISNUMBER(F62),F62=0))),"Subscription",IF(ISNUMBER(G62),"Profit",IF(ISNUMBER(I62),"Loss",IF(ISNUMBER(H62),"Draw",IF(AND(ISNUMBER(F62),ISNUMBER(E62),E62&gt;0,F62&gt;E62),"Profit",IF(AND(ISNUMBER(F62),ISNUMBER(E62),E62&gt;0,F62=E62),"Draw",IF(AND(ISNUMBER(F62),ISNUMBER(E62),E62&gt;0,F62=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A62="","",IF(AND(ISNUMBER(E62),E62=0,OR(ISNUMBER(SEARCH("Free",D62&amp;"")),AND(ISNUMBER(F62),F62=0))),"Subscription",IF(ISNUMBER(G62),"Profit",IF(ISNUMBER(I62),"Disqualified",IF(ISNUMBER(H62),"Draw",IF(AND(ISNUMBER(F62),ISNUMBER(E62),E62&gt;0,F62&gt;E62),"Profit",IF(AND(ISNUMBER(F62),ISNUMBER(E62),E62&gt;0,F62=E62),"Draw",IF(AND(ISNUMBER(F62),ISNUMBER(E62),E62&gt;0,F62=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L62" s="50"/>
       <x:c r="M62" s="58"/>
@@ -3689,7 +3702,7 @@
         <x:f>IF(A63="","",IF(K63="Subscription","",IF(E63=0,"",IF(ISNUMBER(G63),G63/E63,IF(ISNUMBER(I63),-ABS(I63)/E63,IF(ISNUMBER(H63),0,IF(AND(ISNUMBER(F63),ISNUMBER(E63),E63&gt;0,F63&gt;E63),(F63-E63)/E63,IF(AND(ISNUMBER(F63),ISNUMBER(E63),E63&gt;0,F63=E63),0,IF(AND(ISNUMBER(F63),ISNUMBER(E63),E63&gt;0,F63=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K63" s="50" t="str">
-        <x:f>IF(A63="","",IF(AND(ISNUMBER(E63),E63=0,OR(ISNUMBER(SEARCH("Free",D63&amp;"")),AND(ISNUMBER(F63),F63=0))),"Subscription",IF(ISNUMBER(G63),"Profit",IF(ISNUMBER(I63),"Loss",IF(ISNUMBER(H63),"Draw",IF(AND(ISNUMBER(F63),ISNUMBER(E63),E63&gt;0,F63&gt;E63),"Profit",IF(AND(ISNUMBER(F63),ISNUMBER(E63),E63&gt;0,F63=E63),"Draw",IF(AND(ISNUMBER(F63),ISNUMBER(E63),E63&gt;0,F63=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A63="","",IF(AND(ISNUMBER(E63),E63=0,OR(ISNUMBER(SEARCH("Free",D63&amp;"")),AND(ISNUMBER(F63),F63=0))),"Subscription",IF(ISNUMBER(G63),"Profit",IF(ISNUMBER(I63),"Disqualified",IF(ISNUMBER(H63),"Draw",IF(AND(ISNUMBER(F63),ISNUMBER(E63),E63&gt;0,F63&gt;E63),"Profit",IF(AND(ISNUMBER(F63),ISNUMBER(E63),E63&gt;0,F63=E63),"Draw",IF(AND(ISNUMBER(F63),ISNUMBER(E63),E63&gt;0,F63=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L63" s="50"/>
       <x:c r="M63" s="58"/>
@@ -3726,7 +3739,7 @@
         <x:f>IF(A64="","",IF(K64="Subscription","",IF(E64=0,"",IF(ISNUMBER(G64),G64/E64,IF(ISNUMBER(I64),-ABS(I64)/E64,IF(ISNUMBER(H64),0,IF(AND(ISNUMBER(F64),ISNUMBER(E64),E64&gt;0,F64&gt;E64),(F64-E64)/E64,IF(AND(ISNUMBER(F64),ISNUMBER(E64),E64&gt;0,F64=E64),0,IF(AND(ISNUMBER(F64),ISNUMBER(E64),E64&gt;0,F64=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K64" s="50" t="str">
-        <x:f>IF(A64="","",IF(AND(ISNUMBER(E64),E64=0,OR(ISNUMBER(SEARCH("Free",D64&amp;"")),AND(ISNUMBER(F64),F64=0))),"Subscription",IF(ISNUMBER(G64),"Profit",IF(ISNUMBER(I64),"Loss",IF(ISNUMBER(H64),"Draw",IF(AND(ISNUMBER(F64),ISNUMBER(E64),E64&gt;0,F64&gt;E64),"Profit",IF(AND(ISNUMBER(F64),ISNUMBER(E64),E64&gt;0,F64=E64),"Draw",IF(AND(ISNUMBER(F64),ISNUMBER(E64),E64&gt;0,F64=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A64="","",IF(AND(ISNUMBER(E64),E64=0,OR(ISNUMBER(SEARCH("Free",D64&amp;"")),AND(ISNUMBER(F64),F64=0))),"Subscription",IF(ISNUMBER(G64),"Profit",IF(ISNUMBER(I64),"Disqualified",IF(ISNUMBER(H64),"Draw",IF(AND(ISNUMBER(F64),ISNUMBER(E64),E64&gt;0,F64&gt;E64),"Profit",IF(AND(ISNUMBER(F64),ISNUMBER(E64),E64&gt;0,F64=E64),"Draw",IF(AND(ISNUMBER(F64),ISNUMBER(E64),E64&gt;0,F64=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L64" s="50"/>
       <x:c r="M64" s="58"/>
@@ -3763,7 +3776,7 @@
         <x:f>IF(A65="","",IF(K65="Subscription","",IF(E65=0,"",IF(ISNUMBER(G65),G65/E65,IF(ISNUMBER(I65),-ABS(I65)/E65,IF(ISNUMBER(H65),0,IF(AND(ISNUMBER(F65),ISNUMBER(E65),E65&gt;0,F65&gt;E65),(F65-E65)/E65,IF(AND(ISNUMBER(F65),ISNUMBER(E65),E65&gt;0,F65=E65),0,IF(AND(ISNUMBER(F65),ISNUMBER(E65),E65&gt;0,F65=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K65" s="50" t="str">
-        <x:f>IF(A65="","",IF(AND(ISNUMBER(E65),E65=0,OR(ISNUMBER(SEARCH("Free",D65&amp;"")),AND(ISNUMBER(F65),F65=0))),"Subscription",IF(ISNUMBER(G65),"Profit",IF(ISNUMBER(I65),"Loss",IF(ISNUMBER(H65),"Draw",IF(AND(ISNUMBER(F65),ISNUMBER(E65),E65&gt;0,F65&gt;E65),"Profit",IF(AND(ISNUMBER(F65),ISNUMBER(E65),E65&gt;0,F65=E65),"Draw",IF(AND(ISNUMBER(F65),ISNUMBER(E65),E65&gt;0,F65=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A65="","",IF(AND(ISNUMBER(E65),E65=0,OR(ISNUMBER(SEARCH("Free",D65&amp;"")),AND(ISNUMBER(F65),F65=0))),"Subscription",IF(ISNUMBER(G65),"Profit",IF(ISNUMBER(I65),"Disqualified",IF(ISNUMBER(H65),"Draw",IF(AND(ISNUMBER(F65),ISNUMBER(E65),E65&gt;0,F65&gt;E65),"Profit",IF(AND(ISNUMBER(F65),ISNUMBER(E65),E65&gt;0,F65=E65),"Draw",IF(AND(ISNUMBER(F65),ISNUMBER(E65),E65&gt;0,F65=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L65" s="50"/>
       <x:c r="M65" s="58"/>
@@ -3800,7 +3813,7 @@
         <x:f>IF(A66="","",IF(K66="Subscription","",IF(E66=0,"",IF(ISNUMBER(G66),G66/E66,IF(ISNUMBER(I66),-ABS(I66)/E66,IF(ISNUMBER(H66),0,IF(AND(ISNUMBER(F66),ISNUMBER(E66),E66&gt;0,F66&gt;E66),(F66-E66)/E66,IF(AND(ISNUMBER(F66),ISNUMBER(E66),E66&gt;0,F66=E66),0,IF(AND(ISNUMBER(F66),ISNUMBER(E66),E66&gt;0,F66=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K66" s="50" t="str">
-        <x:f>IF(A66="","",IF(AND(ISNUMBER(E66),E66=0,OR(ISNUMBER(SEARCH("Free",D66&amp;"")),AND(ISNUMBER(F66),F66=0))),"Subscription",IF(ISNUMBER(G66),"Profit",IF(ISNUMBER(I66),"Loss",IF(ISNUMBER(H66),"Draw",IF(AND(ISNUMBER(F66),ISNUMBER(E66),E66&gt;0,F66&gt;E66),"Profit",IF(AND(ISNUMBER(F66),ISNUMBER(E66),E66&gt;0,F66=E66),"Draw",IF(AND(ISNUMBER(F66),ISNUMBER(E66),E66&gt;0,F66=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A66="","",IF(AND(ISNUMBER(E66),E66=0,OR(ISNUMBER(SEARCH("Free",D66&amp;"")),AND(ISNUMBER(F66),F66=0))),"Subscription",IF(ISNUMBER(G66),"Profit",IF(ISNUMBER(I66),"Disqualified",IF(ISNUMBER(H66),"Draw",IF(AND(ISNUMBER(F66),ISNUMBER(E66),E66&gt;0,F66&gt;E66),"Profit",IF(AND(ISNUMBER(F66),ISNUMBER(E66),E66&gt;0,F66=E66),"Draw",IF(AND(ISNUMBER(F66),ISNUMBER(E66),E66&gt;0,F66=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L66" s="50"/>
       <x:c r="M66" s="58"/>
@@ -3837,7 +3850,7 @@
         <x:f>IF(A67="","",IF(K67="Subscription","",IF(E67=0,"",IF(ISNUMBER(G67),G67/E67,IF(ISNUMBER(I67),-ABS(I67)/E67,IF(ISNUMBER(H67),0,IF(AND(ISNUMBER(F67),ISNUMBER(E67),E67&gt;0,F67&gt;E67),(F67-E67)/E67,IF(AND(ISNUMBER(F67),ISNUMBER(E67),E67&gt;0,F67=E67),0,IF(AND(ISNUMBER(F67),ISNUMBER(E67),E67&gt;0,F67=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K67" s="50" t="str">
-        <x:f>IF(A67="","",IF(AND(ISNUMBER(E67),E67=0,OR(ISNUMBER(SEARCH("Free",D67&amp;"")),AND(ISNUMBER(F67),F67=0))),"Subscription",IF(ISNUMBER(G67),"Profit",IF(ISNUMBER(I67),"Loss",IF(ISNUMBER(H67),"Draw",IF(AND(ISNUMBER(F67),ISNUMBER(E67),E67&gt;0,F67&gt;E67),"Profit",IF(AND(ISNUMBER(F67),ISNUMBER(E67),E67&gt;0,F67=E67),"Draw",IF(AND(ISNUMBER(F67),ISNUMBER(E67),E67&gt;0,F67=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A67="","",IF(AND(ISNUMBER(E67),E67=0,OR(ISNUMBER(SEARCH("Free",D67&amp;"")),AND(ISNUMBER(F67),F67=0))),"Subscription",IF(ISNUMBER(G67),"Profit",IF(ISNUMBER(I67),"Disqualified",IF(ISNUMBER(H67),"Draw",IF(AND(ISNUMBER(F67),ISNUMBER(E67),E67&gt;0,F67&gt;E67),"Profit",IF(AND(ISNUMBER(F67),ISNUMBER(E67),E67&gt;0,F67=E67),"Draw",IF(AND(ISNUMBER(F67),ISNUMBER(E67),E67&gt;0,F67=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L67" s="50"/>
       <x:c r="M67" s="58"/>
@@ -3874,7 +3887,7 @@
         <x:f>IF(A68="","",IF(K68="Subscription","",IF(E68=0,"",IF(ISNUMBER(G68),G68/E68,IF(ISNUMBER(I68),-ABS(I68)/E68,IF(ISNUMBER(H68),0,IF(AND(ISNUMBER(F68),ISNUMBER(E68),E68&gt;0,F68&gt;E68),(F68-E68)/E68,IF(AND(ISNUMBER(F68),ISNUMBER(E68),E68&gt;0,F68=E68),0,IF(AND(ISNUMBER(F68),ISNUMBER(E68),E68&gt;0,F68=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K68" s="50" t="str">
-        <x:f>IF(A68="","",IF(AND(ISNUMBER(E68),E68=0,OR(ISNUMBER(SEARCH("Free",D68&amp;"")),AND(ISNUMBER(F68),F68=0))),"Subscription",IF(ISNUMBER(G68),"Profit",IF(ISNUMBER(I68),"Loss",IF(ISNUMBER(H68),"Draw",IF(AND(ISNUMBER(F68),ISNUMBER(E68),E68&gt;0,F68&gt;E68),"Profit",IF(AND(ISNUMBER(F68),ISNUMBER(E68),E68&gt;0,F68=E68),"Draw",IF(AND(ISNUMBER(F68),ISNUMBER(E68),E68&gt;0,F68=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A68="","",IF(AND(ISNUMBER(E68),E68=0,OR(ISNUMBER(SEARCH("Free",D68&amp;"")),AND(ISNUMBER(F68),F68=0))),"Subscription",IF(ISNUMBER(G68),"Profit",IF(ISNUMBER(I68),"Disqualified",IF(ISNUMBER(H68),"Draw",IF(AND(ISNUMBER(F68),ISNUMBER(E68),E68&gt;0,F68&gt;E68),"Profit",IF(AND(ISNUMBER(F68),ISNUMBER(E68),E68&gt;0,F68=E68),"Draw",IF(AND(ISNUMBER(F68),ISNUMBER(E68),E68&gt;0,F68=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L68" s="50"/>
       <x:c r="M68" s="58"/>
@@ -3911,7 +3924,7 @@
         <x:f>IF(A69="","",IF(K69="Subscription","",IF(E69=0,"",IF(ISNUMBER(G69),G69/E69,IF(ISNUMBER(I69),-ABS(I69)/E69,IF(ISNUMBER(H69),0,IF(AND(ISNUMBER(F69),ISNUMBER(E69),E69&gt;0,F69&gt;E69),(F69-E69)/E69,IF(AND(ISNUMBER(F69),ISNUMBER(E69),E69&gt;0,F69=E69),0,IF(AND(ISNUMBER(F69),ISNUMBER(E69),E69&gt;0,F69=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K69" s="50" t="str">
-        <x:f>IF(A69="","",IF(AND(ISNUMBER(E69),E69=0,OR(ISNUMBER(SEARCH("Free",D69&amp;"")),AND(ISNUMBER(F69),F69=0))),"Subscription",IF(ISNUMBER(G69),"Profit",IF(ISNUMBER(I69),"Loss",IF(ISNUMBER(H69),"Draw",IF(AND(ISNUMBER(F69),ISNUMBER(E69),E69&gt;0,F69&gt;E69),"Profit",IF(AND(ISNUMBER(F69),ISNUMBER(E69),E69&gt;0,F69=E69),"Draw",IF(AND(ISNUMBER(F69),ISNUMBER(E69),E69&gt;0,F69=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A69="","",IF(AND(ISNUMBER(E69),E69=0,OR(ISNUMBER(SEARCH("Free",D69&amp;"")),AND(ISNUMBER(F69),F69=0))),"Subscription",IF(ISNUMBER(G69),"Profit",IF(ISNUMBER(I69),"Disqualified",IF(ISNUMBER(H69),"Draw",IF(AND(ISNUMBER(F69),ISNUMBER(E69),E69&gt;0,F69&gt;E69),"Profit",IF(AND(ISNUMBER(F69),ISNUMBER(E69),E69&gt;0,F69=E69),"Draw",IF(AND(ISNUMBER(F69),ISNUMBER(E69),E69&gt;0,F69=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L69" s="50"/>
       <x:c r="M69" s="58"/>
@@ -3948,7 +3961,7 @@
         <x:f>IF(A70="","",IF(K70="Subscription","",IF(E70=0,"",IF(ISNUMBER(G70),G70/E70,IF(ISNUMBER(I70),-ABS(I70)/E70,IF(ISNUMBER(H70),0,IF(AND(ISNUMBER(F70),ISNUMBER(E70),E70&gt;0,F70&gt;E70),(F70-E70)/E70,IF(AND(ISNUMBER(F70),ISNUMBER(E70),E70&gt;0,F70=E70),0,IF(AND(ISNUMBER(F70),ISNUMBER(E70),E70&gt;0,F70=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K70" s="50" t="str">
-        <x:f>IF(A70="","",IF(AND(ISNUMBER(E70),E70=0,OR(ISNUMBER(SEARCH("Free",D70&amp;"")),AND(ISNUMBER(F70),F70=0))),"Subscription",IF(ISNUMBER(G70),"Profit",IF(ISNUMBER(I70),"Loss",IF(ISNUMBER(H70),"Draw",IF(AND(ISNUMBER(F70),ISNUMBER(E70),E70&gt;0,F70&gt;E70),"Profit",IF(AND(ISNUMBER(F70),ISNUMBER(E70),E70&gt;0,F70=E70),"Draw",IF(AND(ISNUMBER(F70),ISNUMBER(E70),E70&gt;0,F70=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A70="","",IF(AND(ISNUMBER(E70),E70=0,OR(ISNUMBER(SEARCH("Free",D70&amp;"")),AND(ISNUMBER(F70),F70=0))),"Subscription",IF(ISNUMBER(G70),"Profit",IF(ISNUMBER(I70),"Disqualified",IF(ISNUMBER(H70),"Draw",IF(AND(ISNUMBER(F70),ISNUMBER(E70),E70&gt;0,F70&gt;E70),"Profit",IF(AND(ISNUMBER(F70),ISNUMBER(E70),E70&gt;0,F70=E70),"Draw",IF(AND(ISNUMBER(F70),ISNUMBER(E70),E70&gt;0,F70=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L70" s="50"/>
       <x:c r="M70" s="58"/>
@@ -3985,7 +3998,7 @@
         <x:f>IF(A71="","",IF(K71="Subscription","",IF(E71=0,"",IF(ISNUMBER(G71),G71/E71,IF(ISNUMBER(I71),-ABS(I71)/E71,IF(ISNUMBER(H71),0,IF(AND(ISNUMBER(F71),ISNUMBER(E71),E71&gt;0,F71&gt;E71),(F71-E71)/E71,IF(AND(ISNUMBER(F71),ISNUMBER(E71),E71&gt;0,F71=E71),0,IF(AND(ISNUMBER(F71),ISNUMBER(E71),E71&gt;0,F71=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K71" s="50" t="str">
-        <x:f>IF(A71="","",IF(AND(ISNUMBER(E71),E71=0,OR(ISNUMBER(SEARCH("Free",D71&amp;"")),AND(ISNUMBER(F71),F71=0))),"Subscription",IF(ISNUMBER(G71),"Profit",IF(ISNUMBER(I71),"Loss",IF(ISNUMBER(H71),"Draw",IF(AND(ISNUMBER(F71),ISNUMBER(E71),E71&gt;0,F71&gt;E71),"Profit",IF(AND(ISNUMBER(F71),ISNUMBER(E71),E71&gt;0,F71=E71),"Draw",IF(AND(ISNUMBER(F71),ISNUMBER(E71),E71&gt;0,F71=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A71="","",IF(AND(ISNUMBER(E71),E71=0,OR(ISNUMBER(SEARCH("Free",D71&amp;"")),AND(ISNUMBER(F71),F71=0))),"Subscription",IF(ISNUMBER(G71),"Profit",IF(ISNUMBER(I71),"Disqualified",IF(ISNUMBER(H71),"Draw",IF(AND(ISNUMBER(F71),ISNUMBER(E71),E71&gt;0,F71&gt;E71),"Profit",IF(AND(ISNUMBER(F71),ISNUMBER(E71),E71&gt;0,F71=E71),"Draw",IF(AND(ISNUMBER(F71),ISNUMBER(E71),E71&gt;0,F71=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L71" s="50"/>
       <x:c r="M71" s="58"/>
@@ -4022,7 +4035,7 @@
         <x:f>IF(A72="","",IF(K72="Subscription","",IF(E72=0,"",IF(ISNUMBER(G72),G72/E72,IF(ISNUMBER(I72),-ABS(I72)/E72,IF(ISNUMBER(H72),0,IF(AND(ISNUMBER(F72),ISNUMBER(E72),E72&gt;0,F72&gt;E72),(F72-E72)/E72,IF(AND(ISNUMBER(F72),ISNUMBER(E72),E72&gt;0,F72=E72),0,IF(AND(ISNUMBER(F72),ISNUMBER(E72),E72&gt;0,F72=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K72" s="50" t="str">
-        <x:f>IF(A72="","",IF(AND(ISNUMBER(E72),E72=0,OR(ISNUMBER(SEARCH("Free",D72&amp;"")),AND(ISNUMBER(F72),F72=0))),"Subscription",IF(ISNUMBER(G72),"Profit",IF(ISNUMBER(I72),"Loss",IF(ISNUMBER(H72),"Draw",IF(AND(ISNUMBER(F72),ISNUMBER(E72),E72&gt;0,F72&gt;E72),"Profit",IF(AND(ISNUMBER(F72),ISNUMBER(E72),E72&gt;0,F72=E72),"Draw",IF(AND(ISNUMBER(F72),ISNUMBER(E72),E72&gt;0,F72=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A72="","",IF(AND(ISNUMBER(E72),E72=0,OR(ISNUMBER(SEARCH("Free",D72&amp;"")),AND(ISNUMBER(F72),F72=0))),"Subscription",IF(ISNUMBER(G72),"Profit",IF(ISNUMBER(I72),"Disqualified",IF(ISNUMBER(H72),"Draw",IF(AND(ISNUMBER(F72),ISNUMBER(E72),E72&gt;0,F72&gt;E72),"Profit",IF(AND(ISNUMBER(F72),ISNUMBER(E72),E72&gt;0,F72=E72),"Draw",IF(AND(ISNUMBER(F72),ISNUMBER(E72),E72&gt;0,F72=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L72" s="50"/>
       <x:c r="M72" s="58"/>
@@ -4059,7 +4072,7 @@
         <x:f>IF(A73="","",IF(K73="Subscription","",IF(E73=0,"",IF(ISNUMBER(G73),G73/E73,IF(ISNUMBER(I73),-ABS(I73)/E73,IF(ISNUMBER(H73),0,IF(AND(ISNUMBER(F73),ISNUMBER(E73),E73&gt;0,F73&gt;E73),(F73-E73)/E73,IF(AND(ISNUMBER(F73),ISNUMBER(E73),E73&gt;0,F73=E73),0,IF(AND(ISNUMBER(F73),ISNUMBER(E73),E73&gt;0,F73=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K73" s="50" t="str">
-        <x:f>IF(A73="","",IF(AND(ISNUMBER(E73),E73=0,OR(ISNUMBER(SEARCH("Free",D73&amp;"")),AND(ISNUMBER(F73),F73=0))),"Subscription",IF(ISNUMBER(G73),"Profit",IF(ISNUMBER(I73),"Loss",IF(ISNUMBER(H73),"Draw",IF(AND(ISNUMBER(F73),ISNUMBER(E73),E73&gt;0,F73&gt;E73),"Profit",IF(AND(ISNUMBER(F73),ISNUMBER(E73),E73&gt;0,F73=E73),"Draw",IF(AND(ISNUMBER(F73),ISNUMBER(E73),E73&gt;0,F73=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A73="","",IF(AND(ISNUMBER(E73),E73=0,OR(ISNUMBER(SEARCH("Free",D73&amp;"")),AND(ISNUMBER(F73),F73=0))),"Subscription",IF(ISNUMBER(G73),"Profit",IF(ISNUMBER(I73),"Disqualified",IF(ISNUMBER(H73),"Draw",IF(AND(ISNUMBER(F73),ISNUMBER(E73),E73&gt;0,F73&gt;E73),"Profit",IF(AND(ISNUMBER(F73),ISNUMBER(E73),E73&gt;0,F73=E73),"Draw",IF(AND(ISNUMBER(F73),ISNUMBER(E73),E73&gt;0,F73=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L73" s="50"/>
       <x:c r="M73" s="58"/>
@@ -4096,7 +4109,7 @@
         <x:f>IF(A74="","",IF(K74="Subscription","",IF(E74=0,"",IF(ISNUMBER(G74),G74/E74,IF(ISNUMBER(I74),-ABS(I74)/E74,IF(ISNUMBER(H74),0,IF(AND(ISNUMBER(F74),ISNUMBER(E74),E74&gt;0,F74&gt;E74),(F74-E74)/E74,IF(AND(ISNUMBER(F74),ISNUMBER(E74),E74&gt;0,F74=E74),0,IF(AND(ISNUMBER(F74),ISNUMBER(E74),E74&gt;0,F74=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K74" s="50" t="str">
-        <x:f>IF(A74="","",IF(AND(ISNUMBER(E74),E74=0,OR(ISNUMBER(SEARCH("Free",D74&amp;"")),AND(ISNUMBER(F74),F74=0))),"Subscription",IF(ISNUMBER(G74),"Profit",IF(ISNUMBER(I74),"Loss",IF(ISNUMBER(H74),"Draw",IF(AND(ISNUMBER(F74),ISNUMBER(E74),E74&gt;0,F74&gt;E74),"Profit",IF(AND(ISNUMBER(F74),ISNUMBER(E74),E74&gt;0,F74=E74),"Draw",IF(AND(ISNUMBER(F74),ISNUMBER(E74),E74&gt;0,F74=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A74="","",IF(AND(ISNUMBER(E74),E74=0,OR(ISNUMBER(SEARCH("Free",D74&amp;"")),AND(ISNUMBER(F74),F74=0))),"Subscription",IF(ISNUMBER(G74),"Profit",IF(ISNUMBER(I74),"Disqualified",IF(ISNUMBER(H74),"Draw",IF(AND(ISNUMBER(F74),ISNUMBER(E74),E74&gt;0,F74&gt;E74),"Profit",IF(AND(ISNUMBER(F74),ISNUMBER(E74),E74&gt;0,F74=E74),"Draw",IF(AND(ISNUMBER(F74),ISNUMBER(E74),E74&gt;0,F74=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L74" s="50"/>
       <x:c r="M74" s="58"/>
@@ -4133,7 +4146,7 @@
         <x:f>IF(A75="","",IF(K75="Subscription","",IF(E75=0,"",IF(ISNUMBER(G75),G75/E75,IF(ISNUMBER(I75),-ABS(I75)/E75,IF(ISNUMBER(H75),0,IF(AND(ISNUMBER(F75),ISNUMBER(E75),E75&gt;0,F75&gt;E75),(F75-E75)/E75,IF(AND(ISNUMBER(F75),ISNUMBER(E75),E75&gt;0,F75=E75),0,IF(AND(ISNUMBER(F75),ISNUMBER(E75),E75&gt;0,F75=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K75" s="50" t="str">
-        <x:f>IF(A75="","",IF(AND(ISNUMBER(E75),E75=0,OR(ISNUMBER(SEARCH("Free",D75&amp;"")),AND(ISNUMBER(F75),F75=0))),"Subscription",IF(ISNUMBER(G75),"Profit",IF(ISNUMBER(I75),"Loss",IF(ISNUMBER(H75),"Draw",IF(AND(ISNUMBER(F75),ISNUMBER(E75),E75&gt;0,F75&gt;E75),"Profit",IF(AND(ISNUMBER(F75),ISNUMBER(E75),E75&gt;0,F75=E75),"Draw",IF(AND(ISNUMBER(F75),ISNUMBER(E75),E75&gt;0,F75=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A75="","",IF(AND(ISNUMBER(E75),E75=0,OR(ISNUMBER(SEARCH("Free",D75&amp;"")),AND(ISNUMBER(F75),F75=0))),"Subscription",IF(ISNUMBER(G75),"Profit",IF(ISNUMBER(I75),"Disqualified",IF(ISNUMBER(H75),"Draw",IF(AND(ISNUMBER(F75),ISNUMBER(E75),E75&gt;0,F75&gt;E75),"Profit",IF(AND(ISNUMBER(F75),ISNUMBER(E75),E75&gt;0,F75=E75),"Draw",IF(AND(ISNUMBER(F75),ISNUMBER(E75),E75&gt;0,F75=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L75" s="50"/>
       <x:c r="M75" s="58"/>
@@ -4170,7 +4183,7 @@
         <x:f>IF(A76="","",IF(K76="Subscription","",IF(E76=0,"",IF(ISNUMBER(G76),G76/E76,IF(ISNUMBER(I76),-ABS(I76)/E76,IF(ISNUMBER(H76),0,IF(AND(ISNUMBER(F76),ISNUMBER(E76),E76&gt;0,F76&gt;E76),(F76-E76)/E76,IF(AND(ISNUMBER(F76),ISNUMBER(E76),E76&gt;0,F76=E76),0,IF(AND(ISNUMBER(F76),ISNUMBER(E76),E76&gt;0,F76=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K76" s="50" t="str">
-        <x:f>IF(A76="","",IF(AND(ISNUMBER(E76),E76=0,OR(ISNUMBER(SEARCH("Free",D76&amp;"")),AND(ISNUMBER(F76),F76=0))),"Subscription",IF(ISNUMBER(G76),"Profit",IF(ISNUMBER(I76),"Loss",IF(ISNUMBER(H76),"Draw",IF(AND(ISNUMBER(F76),ISNUMBER(E76),E76&gt;0,F76&gt;E76),"Profit",IF(AND(ISNUMBER(F76),ISNUMBER(E76),E76&gt;0,F76=E76),"Draw",IF(AND(ISNUMBER(F76),ISNUMBER(E76),E76&gt;0,F76=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A76="","",IF(AND(ISNUMBER(E76),E76=0,OR(ISNUMBER(SEARCH("Free",D76&amp;"")),AND(ISNUMBER(F76),F76=0))),"Subscription",IF(ISNUMBER(G76),"Profit",IF(ISNUMBER(I76),"Disqualified",IF(ISNUMBER(H76),"Draw",IF(AND(ISNUMBER(F76),ISNUMBER(E76),E76&gt;0,F76&gt;E76),"Profit",IF(AND(ISNUMBER(F76),ISNUMBER(E76),E76&gt;0,F76=E76),"Draw",IF(AND(ISNUMBER(F76),ISNUMBER(E76),E76&gt;0,F76=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L76" s="50"/>
       <x:c r="M76" s="58"/>
@@ -4207,7 +4220,7 @@
         <x:f>IF(A77="","",IF(K77="Subscription","",IF(E77=0,"",IF(ISNUMBER(G77),G77/E77,IF(ISNUMBER(I77),-ABS(I77)/E77,IF(ISNUMBER(H77),0,IF(AND(ISNUMBER(F77),ISNUMBER(E77),E77&gt;0,F77&gt;E77),(F77-E77)/E77,IF(AND(ISNUMBER(F77),ISNUMBER(E77),E77&gt;0,F77=E77),0,IF(AND(ISNUMBER(F77),ISNUMBER(E77),E77&gt;0,F77=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K77" s="50" t="str">
-        <x:f>IF(A77="","",IF(AND(ISNUMBER(E77),E77=0,OR(ISNUMBER(SEARCH("Free",D77&amp;"")),AND(ISNUMBER(F77),F77=0))),"Subscription",IF(ISNUMBER(G77),"Profit",IF(ISNUMBER(I77),"Loss",IF(ISNUMBER(H77),"Draw",IF(AND(ISNUMBER(F77),ISNUMBER(E77),E77&gt;0,F77&gt;E77),"Profit",IF(AND(ISNUMBER(F77),ISNUMBER(E77),E77&gt;0,F77=E77),"Draw",IF(AND(ISNUMBER(F77),ISNUMBER(E77),E77&gt;0,F77=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A77="","",IF(AND(ISNUMBER(E77),E77=0,OR(ISNUMBER(SEARCH("Free",D77&amp;"")),AND(ISNUMBER(F77),F77=0))),"Subscription",IF(ISNUMBER(G77),"Profit",IF(ISNUMBER(I77),"Disqualified",IF(ISNUMBER(H77),"Draw",IF(AND(ISNUMBER(F77),ISNUMBER(E77),E77&gt;0,F77&gt;E77),"Profit",IF(AND(ISNUMBER(F77),ISNUMBER(E77),E77&gt;0,F77=E77),"Draw",IF(AND(ISNUMBER(F77),ISNUMBER(E77),E77&gt;0,F77=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L77" s="50"/>
       <x:c r="M77" s="58"/>
@@ -4244,7 +4257,7 @@
         <x:f>IF(A78="","",IF(K78="Subscription","",IF(E78=0,"",IF(ISNUMBER(G78),G78/E78,IF(ISNUMBER(I78),-ABS(I78)/E78,IF(ISNUMBER(H78),0,IF(AND(ISNUMBER(F78),ISNUMBER(E78),E78&gt;0,F78&gt;E78),(F78-E78)/E78,IF(AND(ISNUMBER(F78),ISNUMBER(E78),E78&gt;0,F78=E78),0,IF(AND(ISNUMBER(F78),ISNUMBER(E78),E78&gt;0,F78=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K78" s="50" t="str">
-        <x:f>IF(A78="","",IF(AND(ISNUMBER(E78),E78=0,OR(ISNUMBER(SEARCH("Free",D78&amp;"")),AND(ISNUMBER(F78),F78=0))),"Subscription",IF(ISNUMBER(G78),"Profit",IF(ISNUMBER(I78),"Loss",IF(ISNUMBER(H78),"Draw",IF(AND(ISNUMBER(F78),ISNUMBER(E78),E78&gt;0,F78&gt;E78),"Profit",IF(AND(ISNUMBER(F78),ISNUMBER(E78),E78&gt;0,F78=E78),"Draw",IF(AND(ISNUMBER(F78),ISNUMBER(E78),E78&gt;0,F78=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A78="","",IF(AND(ISNUMBER(E78),E78=0,OR(ISNUMBER(SEARCH("Free",D78&amp;"")),AND(ISNUMBER(F78),F78=0))),"Subscription",IF(ISNUMBER(G78),"Profit",IF(ISNUMBER(I78),"Disqualified",IF(ISNUMBER(H78),"Draw",IF(AND(ISNUMBER(F78),ISNUMBER(E78),E78&gt;0,F78&gt;E78),"Profit",IF(AND(ISNUMBER(F78),ISNUMBER(E78),E78&gt;0,F78=E78),"Draw",IF(AND(ISNUMBER(F78),ISNUMBER(E78),E78&gt;0,F78=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L78" s="50"/>
       <x:c r="M78" s="58"/>
@@ -4281,7 +4294,7 @@
         <x:f>IF(A79="","",IF(K79="Subscription","",IF(E79=0,"",IF(ISNUMBER(G79),G79/E79,IF(ISNUMBER(I79),-ABS(I79)/E79,IF(ISNUMBER(H79),0,IF(AND(ISNUMBER(F79),ISNUMBER(E79),E79&gt;0,F79&gt;E79),(F79-E79)/E79,IF(AND(ISNUMBER(F79),ISNUMBER(E79),E79&gt;0,F79=E79),0,IF(AND(ISNUMBER(F79),ISNUMBER(E79),E79&gt;0,F79=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K79" s="50" t="str">
-        <x:f>IF(A79="","",IF(AND(ISNUMBER(E79),E79=0,OR(ISNUMBER(SEARCH("Free",D79&amp;"")),AND(ISNUMBER(F79),F79=0))),"Subscription",IF(ISNUMBER(G79),"Profit",IF(ISNUMBER(I79),"Loss",IF(ISNUMBER(H79),"Draw",IF(AND(ISNUMBER(F79),ISNUMBER(E79),E79&gt;0,F79&gt;E79),"Profit",IF(AND(ISNUMBER(F79),ISNUMBER(E79),E79&gt;0,F79=E79),"Draw",IF(AND(ISNUMBER(F79),ISNUMBER(E79),E79&gt;0,F79=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A79="","",IF(AND(ISNUMBER(E79),E79=0,OR(ISNUMBER(SEARCH("Free",D79&amp;"")),AND(ISNUMBER(F79),F79=0))),"Subscription",IF(ISNUMBER(G79),"Profit",IF(ISNUMBER(I79),"Disqualified",IF(ISNUMBER(H79),"Draw",IF(AND(ISNUMBER(F79),ISNUMBER(E79),E79&gt;0,F79&gt;E79),"Profit",IF(AND(ISNUMBER(F79),ISNUMBER(E79),E79&gt;0,F79=E79),"Draw",IF(AND(ISNUMBER(F79),ISNUMBER(E79),E79&gt;0,F79=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L79" s="50"/>
       <x:c r="M79" s="58"/>
@@ -4318,7 +4331,7 @@
         <x:f>IF(A80="","",IF(K80="Subscription","",IF(E80=0,"",IF(ISNUMBER(G80),G80/E80,IF(ISNUMBER(I80),-ABS(I80)/E80,IF(ISNUMBER(H80),0,IF(AND(ISNUMBER(F80),ISNUMBER(E80),E80&gt;0,F80&gt;E80),(F80-E80)/E80,IF(AND(ISNUMBER(F80),ISNUMBER(E80),E80&gt;0,F80=E80),0,IF(AND(ISNUMBER(F80),ISNUMBER(E80),E80&gt;0,F80=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K80" s="50" t="str">
-        <x:f>IF(A80="","",IF(AND(ISNUMBER(E80),E80=0,OR(ISNUMBER(SEARCH("Free",D80&amp;"")),AND(ISNUMBER(F80),F80=0))),"Subscription",IF(ISNUMBER(G80),"Profit",IF(ISNUMBER(I80),"Loss",IF(ISNUMBER(H80),"Draw",IF(AND(ISNUMBER(F80),ISNUMBER(E80),E80&gt;0,F80&gt;E80),"Profit",IF(AND(ISNUMBER(F80),ISNUMBER(E80),E80&gt;0,F80=E80),"Draw",IF(AND(ISNUMBER(F80),ISNUMBER(E80),E80&gt;0,F80=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A80="","",IF(AND(ISNUMBER(E80),E80=0,OR(ISNUMBER(SEARCH("Free",D80&amp;"")),AND(ISNUMBER(F80),F80=0))),"Subscription",IF(ISNUMBER(G80),"Profit",IF(ISNUMBER(I80),"Disqualified",IF(ISNUMBER(H80),"Draw",IF(AND(ISNUMBER(F80),ISNUMBER(E80),E80&gt;0,F80&gt;E80),"Profit",IF(AND(ISNUMBER(F80),ISNUMBER(E80),E80&gt;0,F80=E80),"Draw",IF(AND(ISNUMBER(F80),ISNUMBER(E80),E80&gt;0,F80=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L80" s="50"/>
       <x:c r="M80" s="58"/>
@@ -4355,7 +4368,7 @@
         <x:f>IF(A81="","",IF(K81="Subscription","",IF(E81=0,"",IF(ISNUMBER(G81),G81/E81,IF(ISNUMBER(I81),-ABS(I81)/E81,IF(ISNUMBER(H81),0,IF(AND(ISNUMBER(F81),ISNUMBER(E81),E81&gt;0,F81&gt;E81),(F81-E81)/E81,IF(AND(ISNUMBER(F81),ISNUMBER(E81),E81&gt;0,F81=E81),0,IF(AND(ISNUMBER(F81),ISNUMBER(E81),E81&gt;0,F81=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K81" s="50" t="str">
-        <x:f>IF(A81="","",IF(AND(ISNUMBER(E81),E81=0,OR(ISNUMBER(SEARCH("Free",D81&amp;"")),AND(ISNUMBER(F81),F81=0))),"Subscription",IF(ISNUMBER(G81),"Profit",IF(ISNUMBER(I81),"Loss",IF(ISNUMBER(H81),"Draw",IF(AND(ISNUMBER(F81),ISNUMBER(E81),E81&gt;0,F81&gt;E81),"Profit",IF(AND(ISNUMBER(F81),ISNUMBER(E81),E81&gt;0,F81=E81),"Draw",IF(AND(ISNUMBER(F81),ISNUMBER(E81),E81&gt;0,F81=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A81="","",IF(AND(ISNUMBER(E81),E81=0,OR(ISNUMBER(SEARCH("Free",D81&amp;"")),AND(ISNUMBER(F81),F81=0))),"Subscription",IF(ISNUMBER(G81),"Profit",IF(ISNUMBER(I81),"Disqualified",IF(ISNUMBER(H81),"Draw",IF(AND(ISNUMBER(F81),ISNUMBER(E81),E81&gt;0,F81&gt;E81),"Profit",IF(AND(ISNUMBER(F81),ISNUMBER(E81),E81&gt;0,F81=E81),"Draw",IF(AND(ISNUMBER(F81),ISNUMBER(E81),E81&gt;0,F81=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L81" s="50"/>
       <x:c r="M81" s="58"/>
@@ -4392,7 +4405,7 @@
         <x:f>IF(A82="","",IF(K82="Subscription","",IF(E82=0,"",IF(ISNUMBER(G82),G82/E82,IF(ISNUMBER(I82),-ABS(I82)/E82,IF(ISNUMBER(H82),0,IF(AND(ISNUMBER(F82),ISNUMBER(E82),E82&gt;0,F82&gt;E82),(F82-E82)/E82,IF(AND(ISNUMBER(F82),ISNUMBER(E82),E82&gt;0,F82=E82),0,IF(AND(ISNUMBER(F82),ISNUMBER(E82),E82&gt;0,F82=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K82" s="50" t="str">
-        <x:f>IF(A82="","",IF(AND(ISNUMBER(E82),E82=0,OR(ISNUMBER(SEARCH("Free",D82&amp;"")),AND(ISNUMBER(F82),F82=0))),"Subscription",IF(ISNUMBER(G82),"Profit",IF(ISNUMBER(I82),"Loss",IF(ISNUMBER(H82),"Draw",IF(AND(ISNUMBER(F82),ISNUMBER(E82),E82&gt;0,F82&gt;E82),"Profit",IF(AND(ISNUMBER(F82),ISNUMBER(E82),E82&gt;0,F82=E82),"Draw",IF(AND(ISNUMBER(F82),ISNUMBER(E82),E82&gt;0,F82=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A82="","",IF(AND(ISNUMBER(E82),E82=0,OR(ISNUMBER(SEARCH("Free",D82&amp;"")),AND(ISNUMBER(F82),F82=0))),"Subscription",IF(ISNUMBER(G82),"Profit",IF(ISNUMBER(I82),"Disqualified",IF(ISNUMBER(H82),"Draw",IF(AND(ISNUMBER(F82),ISNUMBER(E82),E82&gt;0,F82&gt;E82),"Profit",IF(AND(ISNUMBER(F82),ISNUMBER(E82),E82&gt;0,F82=E82),"Draw",IF(AND(ISNUMBER(F82),ISNUMBER(E82),E82&gt;0,F82=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L82" s="50"/>
       <x:c r="M82" s="58"/>
@@ -4429,7 +4442,7 @@
         <x:f>IF(A83="","",IF(K83="Subscription","",IF(E83=0,"",IF(ISNUMBER(G83),G83/E83,IF(ISNUMBER(I83),-ABS(I83)/E83,IF(ISNUMBER(H83),0,IF(AND(ISNUMBER(F83),ISNUMBER(E83),E83&gt;0,F83&gt;E83),(F83-E83)/E83,IF(AND(ISNUMBER(F83),ISNUMBER(E83),E83&gt;0,F83=E83),0,IF(AND(ISNUMBER(F83),ISNUMBER(E83),E83&gt;0,F83=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K83" s="50" t="str">
-        <x:f>IF(A83="","",IF(AND(ISNUMBER(E83),E83=0,OR(ISNUMBER(SEARCH("Free",D83&amp;"")),AND(ISNUMBER(F83),F83=0))),"Subscription",IF(ISNUMBER(G83),"Profit",IF(ISNUMBER(I83),"Loss",IF(ISNUMBER(H83),"Draw",IF(AND(ISNUMBER(F83),ISNUMBER(E83),E83&gt;0,F83&gt;E83),"Profit",IF(AND(ISNUMBER(F83),ISNUMBER(E83),E83&gt;0,F83=E83),"Draw",IF(AND(ISNUMBER(F83),ISNUMBER(E83),E83&gt;0,F83=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A83="","",IF(AND(ISNUMBER(E83),E83=0,OR(ISNUMBER(SEARCH("Free",D83&amp;"")),AND(ISNUMBER(F83),F83=0))),"Subscription",IF(ISNUMBER(G83),"Profit",IF(ISNUMBER(I83),"Disqualified",IF(ISNUMBER(H83),"Draw",IF(AND(ISNUMBER(F83),ISNUMBER(E83),E83&gt;0,F83&gt;E83),"Profit",IF(AND(ISNUMBER(F83),ISNUMBER(E83),E83&gt;0,F83=E83),"Draw",IF(AND(ISNUMBER(F83),ISNUMBER(E83),E83&gt;0,F83=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L83" s="50"/>
       <x:c r="M83" s="58"/>
@@ -4466,7 +4479,7 @@
         <x:f>IF(A84="","",IF(K84="Subscription","",IF(E84=0,"",IF(ISNUMBER(G84),G84/E84,IF(ISNUMBER(I84),-ABS(I84)/E84,IF(ISNUMBER(H84),0,IF(AND(ISNUMBER(F84),ISNUMBER(E84),E84&gt;0,F84&gt;E84),(F84-E84)/E84,IF(AND(ISNUMBER(F84),ISNUMBER(E84),E84&gt;0,F84=E84),0,IF(AND(ISNUMBER(F84),ISNUMBER(E84),E84&gt;0,F84=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K84" s="50" t="str">
-        <x:f>IF(A84="","",IF(AND(ISNUMBER(E84),E84=0,OR(ISNUMBER(SEARCH("Free",D84&amp;"")),AND(ISNUMBER(F84),F84=0))),"Subscription",IF(ISNUMBER(G84),"Profit",IF(ISNUMBER(I84),"Loss",IF(ISNUMBER(H84),"Draw",IF(AND(ISNUMBER(F84),ISNUMBER(E84),E84&gt;0,F84&gt;E84),"Profit",IF(AND(ISNUMBER(F84),ISNUMBER(E84),E84&gt;0,F84=E84),"Draw",IF(AND(ISNUMBER(F84),ISNUMBER(E84),E84&gt;0,F84=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A84="","",IF(AND(ISNUMBER(E84),E84=0,OR(ISNUMBER(SEARCH("Free",D84&amp;"")),AND(ISNUMBER(F84),F84=0))),"Subscription",IF(ISNUMBER(G84),"Profit",IF(ISNUMBER(I84),"Disqualified",IF(ISNUMBER(H84),"Draw",IF(AND(ISNUMBER(F84),ISNUMBER(E84),E84&gt;0,F84&gt;E84),"Profit",IF(AND(ISNUMBER(F84),ISNUMBER(E84),E84&gt;0,F84=E84),"Draw",IF(AND(ISNUMBER(F84),ISNUMBER(E84),E84&gt;0,F84=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L84" s="50"/>
       <x:c r="M84" s="58"/>
@@ -4503,7 +4516,7 @@
         <x:f>IF(A85="","",IF(K85="Subscription","",IF(E85=0,"",IF(ISNUMBER(G85),G85/E85,IF(ISNUMBER(I85),-ABS(I85)/E85,IF(ISNUMBER(H85),0,IF(AND(ISNUMBER(F85),ISNUMBER(E85),E85&gt;0,F85&gt;E85),(F85-E85)/E85,IF(AND(ISNUMBER(F85),ISNUMBER(E85),E85&gt;0,F85=E85),0,IF(AND(ISNUMBER(F85),ISNUMBER(E85),E85&gt;0,F85=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K85" s="50" t="str">
-        <x:f>IF(A85="","",IF(AND(ISNUMBER(E85),E85=0,OR(ISNUMBER(SEARCH("Free",D85&amp;"")),AND(ISNUMBER(F85),F85=0))),"Subscription",IF(ISNUMBER(G85),"Profit",IF(ISNUMBER(I85),"Loss",IF(ISNUMBER(H85),"Draw",IF(AND(ISNUMBER(F85),ISNUMBER(E85),E85&gt;0,F85&gt;E85),"Profit",IF(AND(ISNUMBER(F85),ISNUMBER(E85),E85&gt;0,F85=E85),"Draw",IF(AND(ISNUMBER(F85),ISNUMBER(E85),E85&gt;0,F85=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A85="","",IF(AND(ISNUMBER(E85),E85=0,OR(ISNUMBER(SEARCH("Free",D85&amp;"")),AND(ISNUMBER(F85),F85=0))),"Subscription",IF(ISNUMBER(G85),"Profit",IF(ISNUMBER(I85),"Disqualified",IF(ISNUMBER(H85),"Draw",IF(AND(ISNUMBER(F85),ISNUMBER(E85),E85&gt;0,F85&gt;E85),"Profit",IF(AND(ISNUMBER(F85),ISNUMBER(E85),E85&gt;0,F85=E85),"Draw",IF(AND(ISNUMBER(F85),ISNUMBER(E85),E85&gt;0,F85=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L85" s="50"/>
       <x:c r="M85" s="58"/>
@@ -4540,7 +4553,7 @@
         <x:f>IF(A86="","",IF(K86="Subscription","",IF(E86=0,"",IF(ISNUMBER(G86),G86/E86,IF(ISNUMBER(I86),-ABS(I86)/E86,IF(ISNUMBER(H86),0,IF(AND(ISNUMBER(F86),ISNUMBER(E86),E86&gt;0,F86&gt;E86),(F86-E86)/E86,IF(AND(ISNUMBER(F86),ISNUMBER(E86),E86&gt;0,F86=E86),0,IF(AND(ISNUMBER(F86),ISNUMBER(E86),E86&gt;0,F86=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K86" s="50" t="str">
-        <x:f>IF(A86="","",IF(AND(ISNUMBER(E86),E86=0,OR(ISNUMBER(SEARCH("Free",D86&amp;"")),AND(ISNUMBER(F86),F86=0))),"Subscription",IF(ISNUMBER(G86),"Profit",IF(ISNUMBER(I86),"Loss",IF(ISNUMBER(H86),"Draw",IF(AND(ISNUMBER(F86),ISNUMBER(E86),E86&gt;0,F86&gt;E86),"Profit",IF(AND(ISNUMBER(F86),ISNUMBER(E86),E86&gt;0,F86=E86),"Draw",IF(AND(ISNUMBER(F86),ISNUMBER(E86),E86&gt;0,F86=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A86="","",IF(AND(ISNUMBER(E86),E86=0,OR(ISNUMBER(SEARCH("Free",D86&amp;"")),AND(ISNUMBER(F86),F86=0))),"Subscription",IF(ISNUMBER(G86),"Profit",IF(ISNUMBER(I86),"Disqualified",IF(ISNUMBER(H86),"Draw",IF(AND(ISNUMBER(F86),ISNUMBER(E86),E86&gt;0,F86&gt;E86),"Profit",IF(AND(ISNUMBER(F86),ISNUMBER(E86),E86&gt;0,F86=E86),"Draw",IF(AND(ISNUMBER(F86),ISNUMBER(E86),E86&gt;0,F86=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L86" s="50"/>
       <x:c r="M86" s="58"/>
@@ -4577,7 +4590,7 @@
         <x:f>IF(A87="","",IF(K87="Subscription","",IF(E87=0,"",IF(ISNUMBER(G87),G87/E87,IF(ISNUMBER(I87),-ABS(I87)/E87,IF(ISNUMBER(H87),0,IF(AND(ISNUMBER(F87),ISNUMBER(E87),E87&gt;0,F87&gt;E87),(F87-E87)/E87,IF(AND(ISNUMBER(F87),ISNUMBER(E87),E87&gt;0,F87=E87),0,IF(AND(ISNUMBER(F87),ISNUMBER(E87),E87&gt;0,F87=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K87" s="50" t="str">
-        <x:f>IF(A87="","",IF(AND(ISNUMBER(E87),E87=0,OR(ISNUMBER(SEARCH("Free",D87&amp;"")),AND(ISNUMBER(F87),F87=0))),"Subscription",IF(ISNUMBER(G87),"Profit",IF(ISNUMBER(I87),"Loss",IF(ISNUMBER(H87),"Draw",IF(AND(ISNUMBER(F87),ISNUMBER(E87),E87&gt;0,F87&gt;E87),"Profit",IF(AND(ISNUMBER(F87),ISNUMBER(E87),E87&gt;0,F87=E87),"Draw",IF(AND(ISNUMBER(F87),ISNUMBER(E87),E87&gt;0,F87=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A87="","",IF(AND(ISNUMBER(E87),E87=0,OR(ISNUMBER(SEARCH("Free",D87&amp;"")),AND(ISNUMBER(F87),F87=0))),"Subscription",IF(ISNUMBER(G87),"Profit",IF(ISNUMBER(I87),"Disqualified",IF(ISNUMBER(H87),"Draw",IF(AND(ISNUMBER(F87),ISNUMBER(E87),E87&gt;0,F87&gt;E87),"Profit",IF(AND(ISNUMBER(F87),ISNUMBER(E87),E87&gt;0,F87=E87),"Draw",IF(AND(ISNUMBER(F87),ISNUMBER(E87),E87&gt;0,F87=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L87" s="50"/>
       <x:c r="M87" s="58"/>
@@ -4614,7 +4627,7 @@
         <x:f>IF(A88="","",IF(K88="Subscription","",IF(E88=0,"",IF(ISNUMBER(G88),G88/E88,IF(ISNUMBER(I88),-ABS(I88)/E88,IF(ISNUMBER(H88),0,IF(AND(ISNUMBER(F88),ISNUMBER(E88),E88&gt;0,F88&gt;E88),(F88-E88)/E88,IF(AND(ISNUMBER(F88),ISNUMBER(E88),E88&gt;0,F88=E88),0,IF(AND(ISNUMBER(F88),ISNUMBER(E88),E88&gt;0,F88=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K88" s="50" t="str">
-        <x:f>IF(A88="","",IF(AND(ISNUMBER(E88),E88=0,OR(ISNUMBER(SEARCH("Free",D88&amp;"")),AND(ISNUMBER(F88),F88=0))),"Subscription",IF(ISNUMBER(G88),"Profit",IF(ISNUMBER(I88),"Loss",IF(ISNUMBER(H88),"Draw",IF(AND(ISNUMBER(F88),ISNUMBER(E88),E88&gt;0,F88&gt;E88),"Profit",IF(AND(ISNUMBER(F88),ISNUMBER(E88),E88&gt;0,F88=E88),"Draw",IF(AND(ISNUMBER(F88),ISNUMBER(E88),E88&gt;0,F88=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A88="","",IF(AND(ISNUMBER(E88),E88=0,OR(ISNUMBER(SEARCH("Free",D88&amp;"")),AND(ISNUMBER(F88),F88=0))),"Subscription",IF(ISNUMBER(G88),"Profit",IF(ISNUMBER(I88),"Disqualified",IF(ISNUMBER(H88),"Draw",IF(AND(ISNUMBER(F88),ISNUMBER(E88),E88&gt;0,F88&gt;E88),"Profit",IF(AND(ISNUMBER(F88),ISNUMBER(E88),E88&gt;0,F88=E88),"Draw",IF(AND(ISNUMBER(F88),ISNUMBER(E88),E88&gt;0,F88=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L88" s="50"/>
       <x:c r="M88" s="58"/>
@@ -4651,7 +4664,7 @@
         <x:f>IF(A89="","",IF(K89="Subscription","",IF(E89=0,"",IF(ISNUMBER(G89),G89/E89,IF(ISNUMBER(I89),-ABS(I89)/E89,IF(ISNUMBER(H89),0,IF(AND(ISNUMBER(F89),ISNUMBER(E89),E89&gt;0,F89&gt;E89),(F89-E89)/E89,IF(AND(ISNUMBER(F89),ISNUMBER(E89),E89&gt;0,F89=E89),0,IF(AND(ISNUMBER(F89),ISNUMBER(E89),E89&gt;0,F89=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K89" s="50" t="str">
-        <x:f>IF(A89="","",IF(AND(ISNUMBER(E89),E89=0,OR(ISNUMBER(SEARCH("Free",D89&amp;"")),AND(ISNUMBER(F89),F89=0))),"Subscription",IF(ISNUMBER(G89),"Profit",IF(ISNUMBER(I89),"Loss",IF(ISNUMBER(H89),"Draw",IF(AND(ISNUMBER(F89),ISNUMBER(E89),E89&gt;0,F89&gt;E89),"Profit",IF(AND(ISNUMBER(F89),ISNUMBER(E89),E89&gt;0,F89=E89),"Draw",IF(AND(ISNUMBER(F89),ISNUMBER(E89),E89&gt;0,F89=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A89="","",IF(AND(ISNUMBER(E89),E89=0,OR(ISNUMBER(SEARCH("Free",D89&amp;"")),AND(ISNUMBER(F89),F89=0))),"Subscription",IF(ISNUMBER(G89),"Profit",IF(ISNUMBER(I89),"Disqualified",IF(ISNUMBER(H89),"Draw",IF(AND(ISNUMBER(F89),ISNUMBER(E89),E89&gt;0,F89&gt;E89),"Profit",IF(AND(ISNUMBER(F89),ISNUMBER(E89),E89&gt;0,F89=E89),"Draw",IF(AND(ISNUMBER(F89),ISNUMBER(E89),E89&gt;0,F89=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L89" s="50"/>
       <x:c r="M89" s="58"/>
@@ -4688,7 +4701,7 @@
         <x:f>IF(A90="","",IF(K90="Subscription","",IF(E90=0,"",IF(ISNUMBER(G90),G90/E90,IF(ISNUMBER(I90),-ABS(I90)/E90,IF(ISNUMBER(H90),0,IF(AND(ISNUMBER(F90),ISNUMBER(E90),E90&gt;0,F90&gt;E90),(F90-E90)/E90,IF(AND(ISNUMBER(F90),ISNUMBER(E90),E90&gt;0,F90=E90),0,IF(AND(ISNUMBER(F90),ISNUMBER(E90),E90&gt;0,F90=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K90" s="50" t="str">
-        <x:f>IF(A90="","",IF(AND(ISNUMBER(E90),E90=0,OR(ISNUMBER(SEARCH("Free",D90&amp;"")),AND(ISNUMBER(F90),F90=0))),"Subscription",IF(ISNUMBER(G90),"Profit",IF(ISNUMBER(I90),"Loss",IF(ISNUMBER(H90),"Draw",IF(AND(ISNUMBER(F90),ISNUMBER(E90),E90&gt;0,F90&gt;E90),"Profit",IF(AND(ISNUMBER(F90),ISNUMBER(E90),E90&gt;0,F90=E90),"Draw",IF(AND(ISNUMBER(F90),ISNUMBER(E90),E90&gt;0,F90=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A90="","",IF(AND(ISNUMBER(E90),E90=0,OR(ISNUMBER(SEARCH("Free",D90&amp;"")),AND(ISNUMBER(F90),F90=0))),"Subscription",IF(ISNUMBER(G90),"Profit",IF(ISNUMBER(I90),"Disqualified",IF(ISNUMBER(H90),"Draw",IF(AND(ISNUMBER(F90),ISNUMBER(E90),E90&gt;0,F90&gt;E90),"Profit",IF(AND(ISNUMBER(F90),ISNUMBER(E90),E90&gt;0,F90=E90),"Draw",IF(AND(ISNUMBER(F90),ISNUMBER(E90),E90&gt;0,F90=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L90" s="50"/>
       <x:c r="M90" s="58"/>
@@ -4725,7 +4738,7 @@
         <x:f>IF(A91="","",IF(K91="Subscription","",IF(E91=0,"",IF(ISNUMBER(G91),G91/E91,IF(ISNUMBER(I91),-ABS(I91)/E91,IF(ISNUMBER(H91),0,IF(AND(ISNUMBER(F91),ISNUMBER(E91),E91&gt;0,F91&gt;E91),(F91-E91)/E91,IF(AND(ISNUMBER(F91),ISNUMBER(E91),E91&gt;0,F91=E91),0,IF(AND(ISNUMBER(F91),ISNUMBER(E91),E91&gt;0,F91=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K91" s="50" t="str">
-        <x:f>IF(A91="","",IF(AND(ISNUMBER(E91),E91=0,OR(ISNUMBER(SEARCH("Free",D91&amp;"")),AND(ISNUMBER(F91),F91=0))),"Subscription",IF(ISNUMBER(G91),"Profit",IF(ISNUMBER(I91),"Loss",IF(ISNUMBER(H91),"Draw",IF(AND(ISNUMBER(F91),ISNUMBER(E91),E91&gt;0,F91&gt;E91),"Profit",IF(AND(ISNUMBER(F91),ISNUMBER(E91),E91&gt;0,F91=E91),"Draw",IF(AND(ISNUMBER(F91),ISNUMBER(E91),E91&gt;0,F91=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A91="","",IF(AND(ISNUMBER(E91),E91=0,OR(ISNUMBER(SEARCH("Free",D91&amp;"")),AND(ISNUMBER(F91),F91=0))),"Subscription",IF(ISNUMBER(G91),"Profit",IF(ISNUMBER(I91),"Disqualified",IF(ISNUMBER(H91),"Draw",IF(AND(ISNUMBER(F91),ISNUMBER(E91),E91&gt;0,F91&gt;E91),"Profit",IF(AND(ISNUMBER(F91),ISNUMBER(E91),E91&gt;0,F91=E91),"Draw",IF(AND(ISNUMBER(F91),ISNUMBER(E91),E91&gt;0,F91=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L91" s="50"/>
       <x:c r="M91" s="58"/>
@@ -4762,7 +4775,7 @@
         <x:f>IF(A92="","",IF(K92="Subscription","",IF(E92=0,"",IF(ISNUMBER(G92),G92/E92,IF(ISNUMBER(I92),-ABS(I92)/E92,IF(ISNUMBER(H92),0,IF(AND(ISNUMBER(F92),ISNUMBER(E92),E92&gt;0,F92&gt;E92),(F92-E92)/E92,IF(AND(ISNUMBER(F92),ISNUMBER(E92),E92&gt;0,F92=E92),0,IF(AND(ISNUMBER(F92),ISNUMBER(E92),E92&gt;0,F92=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K92" s="50" t="str">
-        <x:f>IF(A92="","",IF(AND(ISNUMBER(E92),E92=0,OR(ISNUMBER(SEARCH("Free",D92&amp;"")),AND(ISNUMBER(F92),F92=0))),"Subscription",IF(ISNUMBER(G92),"Profit",IF(ISNUMBER(I92),"Loss",IF(ISNUMBER(H92),"Draw",IF(AND(ISNUMBER(F92),ISNUMBER(E92),E92&gt;0,F92&gt;E92),"Profit",IF(AND(ISNUMBER(F92),ISNUMBER(E92),E92&gt;0,F92=E92),"Draw",IF(AND(ISNUMBER(F92),ISNUMBER(E92),E92&gt;0,F92=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A92="","",IF(AND(ISNUMBER(E92),E92=0,OR(ISNUMBER(SEARCH("Free",D92&amp;"")),AND(ISNUMBER(F92),F92=0))),"Subscription",IF(ISNUMBER(G92),"Profit",IF(ISNUMBER(I92),"Disqualified",IF(ISNUMBER(H92),"Draw",IF(AND(ISNUMBER(F92),ISNUMBER(E92),E92&gt;0,F92&gt;E92),"Profit",IF(AND(ISNUMBER(F92),ISNUMBER(E92),E92&gt;0,F92=E92),"Draw",IF(AND(ISNUMBER(F92),ISNUMBER(E92),E92&gt;0,F92=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L92" s="50"/>
       <x:c r="M92" s="58"/>
@@ -4799,7 +4812,7 @@
         <x:f>IF(A93="","",IF(K93="Subscription","",IF(E93=0,"",IF(ISNUMBER(G93),G93/E93,IF(ISNUMBER(I93),-ABS(I93)/E93,IF(ISNUMBER(H93),0,IF(AND(ISNUMBER(F93),ISNUMBER(E93),E93&gt;0,F93&gt;E93),(F93-E93)/E93,IF(AND(ISNUMBER(F93),ISNUMBER(E93),E93&gt;0,F93=E93),0,IF(AND(ISNUMBER(F93),ISNUMBER(E93),E93&gt;0,F93=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K93" s="50" t="str">
-        <x:f>IF(A93="","",IF(AND(ISNUMBER(E93),E93=0,OR(ISNUMBER(SEARCH("Free",D93&amp;"")),AND(ISNUMBER(F93),F93=0))),"Subscription",IF(ISNUMBER(G93),"Profit",IF(ISNUMBER(I93),"Loss",IF(ISNUMBER(H93),"Draw",IF(AND(ISNUMBER(F93),ISNUMBER(E93),E93&gt;0,F93&gt;E93),"Profit",IF(AND(ISNUMBER(F93),ISNUMBER(E93),E93&gt;0,F93=E93),"Draw",IF(AND(ISNUMBER(F93),ISNUMBER(E93),E93&gt;0,F93=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A93="","",IF(AND(ISNUMBER(E93),E93=0,OR(ISNUMBER(SEARCH("Free",D93&amp;"")),AND(ISNUMBER(F93),F93=0))),"Subscription",IF(ISNUMBER(G93),"Profit",IF(ISNUMBER(I93),"Disqualified",IF(ISNUMBER(H93),"Draw",IF(AND(ISNUMBER(F93),ISNUMBER(E93),E93&gt;0,F93&gt;E93),"Profit",IF(AND(ISNUMBER(F93),ISNUMBER(E93),E93&gt;0,F93=E93),"Draw",IF(AND(ISNUMBER(F93),ISNUMBER(E93),E93&gt;0,F93=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L93" s="50"/>
       <x:c r="M93" s="58"/>
@@ -4836,7 +4849,7 @@
         <x:f>IF(A94="","",IF(K94="Subscription","",IF(E94=0,"",IF(ISNUMBER(G94),G94/E94,IF(ISNUMBER(I94),-ABS(I94)/E94,IF(ISNUMBER(H94),0,IF(AND(ISNUMBER(F94),ISNUMBER(E94),E94&gt;0,F94&gt;E94),(F94-E94)/E94,IF(AND(ISNUMBER(F94),ISNUMBER(E94),E94&gt;0,F94=E94),0,IF(AND(ISNUMBER(F94),ISNUMBER(E94),E94&gt;0,F94=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K94" s="50" t="str">
-        <x:f>IF(A94="","",IF(AND(ISNUMBER(E94),E94=0,OR(ISNUMBER(SEARCH("Free",D94&amp;"")),AND(ISNUMBER(F94),F94=0))),"Subscription",IF(ISNUMBER(G94),"Profit",IF(ISNUMBER(I94),"Loss",IF(ISNUMBER(H94),"Draw",IF(AND(ISNUMBER(F94),ISNUMBER(E94),E94&gt;0,F94&gt;E94),"Profit",IF(AND(ISNUMBER(F94),ISNUMBER(E94),E94&gt;0,F94=E94),"Draw",IF(AND(ISNUMBER(F94),ISNUMBER(E94),E94&gt;0,F94=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A94="","",IF(AND(ISNUMBER(E94),E94=0,OR(ISNUMBER(SEARCH("Free",D94&amp;"")),AND(ISNUMBER(F94),F94=0))),"Subscription",IF(ISNUMBER(G94),"Profit",IF(ISNUMBER(I94),"Disqualified",IF(ISNUMBER(H94),"Draw",IF(AND(ISNUMBER(F94),ISNUMBER(E94),E94&gt;0,F94&gt;E94),"Profit",IF(AND(ISNUMBER(F94),ISNUMBER(E94),E94&gt;0,F94=E94),"Draw",IF(AND(ISNUMBER(F94),ISNUMBER(E94),E94&gt;0,F94=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L94" s="50"/>
       <x:c r="M94" s="58"/>
@@ -4873,7 +4886,7 @@
         <x:f>IF(A95="","",IF(K95="Subscription","",IF(E95=0,"",IF(ISNUMBER(G95),G95/E95,IF(ISNUMBER(I95),-ABS(I95)/E95,IF(ISNUMBER(H95),0,IF(AND(ISNUMBER(F95),ISNUMBER(E95),E95&gt;0,F95&gt;E95),(F95-E95)/E95,IF(AND(ISNUMBER(F95),ISNUMBER(E95),E95&gt;0,F95=E95),0,IF(AND(ISNUMBER(F95),ISNUMBER(E95),E95&gt;0,F95=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K95" s="50" t="str">
-        <x:f>IF(A95="","",IF(AND(ISNUMBER(E95),E95=0,OR(ISNUMBER(SEARCH("Free",D95&amp;"")),AND(ISNUMBER(F95),F95=0))),"Subscription",IF(ISNUMBER(G95),"Profit",IF(ISNUMBER(I95),"Loss",IF(ISNUMBER(H95),"Draw",IF(AND(ISNUMBER(F95),ISNUMBER(E95),E95&gt;0,F95&gt;E95),"Profit",IF(AND(ISNUMBER(F95),ISNUMBER(E95),E95&gt;0,F95=E95),"Draw",IF(AND(ISNUMBER(F95),ISNUMBER(E95),E95&gt;0,F95=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A95="","",IF(AND(ISNUMBER(E95),E95=0,OR(ISNUMBER(SEARCH("Free",D95&amp;"")),AND(ISNUMBER(F95),F95=0))),"Subscription",IF(ISNUMBER(G95),"Profit",IF(ISNUMBER(I95),"Disqualified",IF(ISNUMBER(H95),"Draw",IF(AND(ISNUMBER(F95),ISNUMBER(E95),E95&gt;0,F95&gt;E95),"Profit",IF(AND(ISNUMBER(F95),ISNUMBER(E95),E95&gt;0,F95=E95),"Draw",IF(AND(ISNUMBER(F95),ISNUMBER(E95),E95&gt;0,F95=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L95" s="50"/>
       <x:c r="M95" s="58"/>
@@ -4910,7 +4923,7 @@
         <x:f>IF(A96="","",IF(K96="Subscription","",IF(E96=0,"",IF(ISNUMBER(G96),G96/E96,IF(ISNUMBER(I96),-ABS(I96)/E96,IF(ISNUMBER(H96),0,IF(AND(ISNUMBER(F96),ISNUMBER(E96),E96&gt;0,F96&gt;E96),(F96-E96)/E96,IF(AND(ISNUMBER(F96),ISNUMBER(E96),E96&gt;0,F96=E96),0,IF(AND(ISNUMBER(F96),ISNUMBER(E96),E96&gt;0,F96=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K96" s="50" t="str">
-        <x:f>IF(A96="","",IF(AND(ISNUMBER(E96),E96=0,OR(ISNUMBER(SEARCH("Free",D96&amp;"")),AND(ISNUMBER(F96),F96=0))),"Subscription",IF(ISNUMBER(G96),"Profit",IF(ISNUMBER(I96),"Loss",IF(ISNUMBER(H96),"Draw",IF(AND(ISNUMBER(F96),ISNUMBER(E96),E96&gt;0,F96&gt;E96),"Profit",IF(AND(ISNUMBER(F96),ISNUMBER(E96),E96&gt;0,F96=E96),"Draw",IF(AND(ISNUMBER(F96),ISNUMBER(E96),E96&gt;0,F96=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A96="","",IF(AND(ISNUMBER(E96),E96=0,OR(ISNUMBER(SEARCH("Free",D96&amp;"")),AND(ISNUMBER(F96),F96=0))),"Subscription",IF(ISNUMBER(G96),"Profit",IF(ISNUMBER(I96),"Disqualified",IF(ISNUMBER(H96),"Draw",IF(AND(ISNUMBER(F96),ISNUMBER(E96),E96&gt;0,F96&gt;E96),"Profit",IF(AND(ISNUMBER(F96),ISNUMBER(E96),E96&gt;0,F96=E96),"Draw",IF(AND(ISNUMBER(F96),ISNUMBER(E96),E96&gt;0,F96=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L96" s="50"/>
       <x:c r="M96" s="58"/>
@@ -4947,7 +4960,7 @@
         <x:f>IF(A97="","",IF(K97="Subscription","",IF(E97=0,"",IF(ISNUMBER(G97),G97/E97,IF(ISNUMBER(I97),-ABS(I97)/E97,IF(ISNUMBER(H97),0,IF(AND(ISNUMBER(F97),ISNUMBER(E97),E97&gt;0,F97&gt;E97),(F97-E97)/E97,IF(AND(ISNUMBER(F97),ISNUMBER(E97),E97&gt;0,F97=E97),0,IF(AND(ISNUMBER(F97),ISNUMBER(E97),E97&gt;0,F97=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K97" s="50" t="str">
-        <x:f>IF(A97="","",IF(AND(ISNUMBER(E97),E97=0,OR(ISNUMBER(SEARCH("Free",D97&amp;"")),AND(ISNUMBER(F97),F97=0))),"Subscription",IF(ISNUMBER(G97),"Profit",IF(ISNUMBER(I97),"Loss",IF(ISNUMBER(H97),"Draw",IF(AND(ISNUMBER(F97),ISNUMBER(E97),E97&gt;0,F97&gt;E97),"Profit",IF(AND(ISNUMBER(F97),ISNUMBER(E97),E97&gt;0,F97=E97),"Draw",IF(AND(ISNUMBER(F97),ISNUMBER(E97),E97&gt;0,F97=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A97="","",IF(AND(ISNUMBER(E97),E97=0,OR(ISNUMBER(SEARCH("Free",D97&amp;"")),AND(ISNUMBER(F97),F97=0))),"Subscription",IF(ISNUMBER(G97),"Profit",IF(ISNUMBER(I97),"Disqualified",IF(ISNUMBER(H97),"Draw",IF(AND(ISNUMBER(F97),ISNUMBER(E97),E97&gt;0,F97&gt;E97),"Profit",IF(AND(ISNUMBER(F97),ISNUMBER(E97),E97&gt;0,F97=E97),"Draw",IF(AND(ISNUMBER(F97),ISNUMBER(E97),E97&gt;0,F97=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L97" s="50"/>
       <x:c r="M97" s="58"/>
@@ -4984,7 +4997,7 @@
         <x:f>IF(A98="","",IF(K98="Subscription","",IF(E98=0,"",IF(ISNUMBER(G98),G98/E98,IF(ISNUMBER(I98),-ABS(I98)/E98,IF(ISNUMBER(H98),0,IF(AND(ISNUMBER(F98),ISNUMBER(E98),E98&gt;0,F98&gt;E98),(F98-E98)/E98,IF(AND(ISNUMBER(F98),ISNUMBER(E98),E98&gt;0,F98=E98),0,IF(AND(ISNUMBER(F98),ISNUMBER(E98),E98&gt;0,F98=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K98" s="50" t="str">
-        <x:f>IF(A98="","",IF(AND(ISNUMBER(E98),E98=0,OR(ISNUMBER(SEARCH("Free",D98&amp;"")),AND(ISNUMBER(F98),F98=0))),"Subscription",IF(ISNUMBER(G98),"Profit",IF(ISNUMBER(I98),"Loss",IF(ISNUMBER(H98),"Draw",IF(AND(ISNUMBER(F98),ISNUMBER(E98),E98&gt;0,F98&gt;E98),"Profit",IF(AND(ISNUMBER(F98),ISNUMBER(E98),E98&gt;0,F98=E98),"Draw",IF(AND(ISNUMBER(F98),ISNUMBER(E98),E98&gt;0,F98=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A98="","",IF(AND(ISNUMBER(E98),E98=0,OR(ISNUMBER(SEARCH("Free",D98&amp;"")),AND(ISNUMBER(F98),F98=0))),"Subscription",IF(ISNUMBER(G98),"Profit",IF(ISNUMBER(I98),"Disqualified",IF(ISNUMBER(H98),"Draw",IF(AND(ISNUMBER(F98),ISNUMBER(E98),E98&gt;0,F98&gt;E98),"Profit",IF(AND(ISNUMBER(F98),ISNUMBER(E98),E98&gt;0,F98=E98),"Draw",IF(AND(ISNUMBER(F98),ISNUMBER(E98),E98&gt;0,F98=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L98" s="50"/>
       <x:c r="M98" s="58"/>
@@ -5021,7 +5034,7 @@
         <x:f>IF(A99="","",IF(K99="Subscription","",IF(E99=0,"",IF(ISNUMBER(G99),G99/E99,IF(ISNUMBER(I99),-ABS(I99)/E99,IF(ISNUMBER(H99),0,IF(AND(ISNUMBER(F99),ISNUMBER(E99),E99&gt;0,F99&gt;E99),(F99-E99)/E99,IF(AND(ISNUMBER(F99),ISNUMBER(E99),E99&gt;0,F99=E99),0,IF(AND(ISNUMBER(F99),ISNUMBER(E99),E99&gt;0,F99=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K99" s="50" t="str">
-        <x:f>IF(A99="","",IF(AND(ISNUMBER(E99),E99=0,OR(ISNUMBER(SEARCH("Free",D99&amp;"")),AND(ISNUMBER(F99),F99=0))),"Subscription",IF(ISNUMBER(G99),"Profit",IF(ISNUMBER(I99),"Loss",IF(ISNUMBER(H99),"Draw",IF(AND(ISNUMBER(F99),ISNUMBER(E99),E99&gt;0,F99&gt;E99),"Profit",IF(AND(ISNUMBER(F99),ISNUMBER(E99),E99&gt;0,F99=E99),"Draw",IF(AND(ISNUMBER(F99),ISNUMBER(E99),E99&gt;0,F99=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A99="","",IF(AND(ISNUMBER(E99),E99=0,OR(ISNUMBER(SEARCH("Free",D99&amp;"")),AND(ISNUMBER(F99),F99=0))),"Subscription",IF(ISNUMBER(G99),"Profit",IF(ISNUMBER(I99),"Disqualified",IF(ISNUMBER(H99),"Draw",IF(AND(ISNUMBER(F99),ISNUMBER(E99),E99&gt;0,F99&gt;E99),"Profit",IF(AND(ISNUMBER(F99),ISNUMBER(E99),E99&gt;0,F99=E99),"Draw",IF(AND(ISNUMBER(F99),ISNUMBER(E99),E99&gt;0,F99=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L99" s="50"/>
       <x:c r="M99" s="58"/>
@@ -5058,7 +5071,7 @@
         <x:f>IF(A100="","",IF(K100="Subscription","",IF(E100=0,"",IF(ISNUMBER(G100),G100/E100,IF(ISNUMBER(I100),-ABS(I100)/E100,IF(ISNUMBER(H100),0,IF(AND(ISNUMBER(F100),ISNUMBER(E100),E100&gt;0,F100&gt;E100),(F100-E100)/E100,IF(AND(ISNUMBER(F100),ISNUMBER(E100),E100&gt;0,F100=E100),0,IF(AND(ISNUMBER(F100),ISNUMBER(E100),E100&gt;0,F100=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K100" s="50" t="str">
-        <x:f>IF(A100="","",IF(AND(ISNUMBER(E100),E100=0,OR(ISNUMBER(SEARCH("Free",D100&amp;"")),AND(ISNUMBER(F100),F100=0))),"Subscription",IF(ISNUMBER(G100),"Profit",IF(ISNUMBER(I100),"Loss",IF(ISNUMBER(H100),"Draw",IF(AND(ISNUMBER(F100),ISNUMBER(E100),E100&gt;0,F100&gt;E100),"Profit",IF(AND(ISNUMBER(F100),ISNUMBER(E100),E100&gt;0,F100=E100),"Draw",IF(AND(ISNUMBER(F100),ISNUMBER(E100),E100&gt;0,F100=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A100="","",IF(AND(ISNUMBER(E100),E100=0,OR(ISNUMBER(SEARCH("Free",D100&amp;"")),AND(ISNUMBER(F100),F100=0))),"Subscription",IF(ISNUMBER(G100),"Profit",IF(ISNUMBER(I100),"Disqualified",IF(ISNUMBER(H100),"Draw",IF(AND(ISNUMBER(F100),ISNUMBER(E100),E100&gt;0,F100&gt;E100),"Profit",IF(AND(ISNUMBER(F100),ISNUMBER(E100),E100&gt;0,F100=E100),"Draw",IF(AND(ISNUMBER(F100),ISNUMBER(E100),E100&gt;0,F100=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L100" s="50"/>
       <x:c r="M100" s="58"/>
@@ -5095,7 +5108,7 @@
         <x:f>IF(A101="","",IF(K101="Subscription","",IF(E101=0,"",IF(ISNUMBER(G101),G101/E101,IF(ISNUMBER(I101),-ABS(I101)/E101,IF(ISNUMBER(H101),0,IF(AND(ISNUMBER(F101),ISNUMBER(E101),E101&gt;0,F101&gt;E101),(F101-E101)/E101,IF(AND(ISNUMBER(F101),ISNUMBER(E101),E101&gt;0,F101=E101),0,IF(AND(ISNUMBER(F101),ISNUMBER(E101),E101&gt;0,F101=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K101" s="50" t="str">
-        <x:f>IF(A101="","",IF(AND(ISNUMBER(E101),E101=0,OR(ISNUMBER(SEARCH("Free",D101&amp;"")),AND(ISNUMBER(F101),F101=0))),"Subscription",IF(ISNUMBER(G101),"Profit",IF(ISNUMBER(I101),"Loss",IF(ISNUMBER(H101),"Draw",IF(AND(ISNUMBER(F101),ISNUMBER(E101),E101&gt;0,F101&gt;E101),"Profit",IF(AND(ISNUMBER(F101),ISNUMBER(E101),E101&gt;0,F101=E101),"Draw",IF(AND(ISNUMBER(F101),ISNUMBER(E101),E101&gt;0,F101=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A101="","",IF(AND(ISNUMBER(E101),E101=0,OR(ISNUMBER(SEARCH("Free",D101&amp;"")),AND(ISNUMBER(F101),F101=0))),"Subscription",IF(ISNUMBER(G101),"Profit",IF(ISNUMBER(I101),"Disqualified",IF(ISNUMBER(H101),"Draw",IF(AND(ISNUMBER(F101),ISNUMBER(E101),E101&gt;0,F101&gt;E101),"Profit",IF(AND(ISNUMBER(F101),ISNUMBER(E101),E101&gt;0,F101=E101),"Draw",IF(AND(ISNUMBER(F101),ISNUMBER(E101),E101&gt;0,F101=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L101" s="50"/>
       <x:c r="M101" s="58"/>
@@ -5132,7 +5145,7 @@
         <x:f>IF(A102="","",IF(K102="Subscription","",IF(E102=0,"",IF(ISNUMBER(G102),G102/E102,IF(ISNUMBER(I102),-ABS(I102)/E102,IF(ISNUMBER(H102),0,IF(AND(ISNUMBER(F102),ISNUMBER(E102),E102&gt;0,F102&gt;E102),(F102-E102)/E102,IF(AND(ISNUMBER(F102),ISNUMBER(E102),E102&gt;0,F102=E102),0,IF(AND(ISNUMBER(F102),ISNUMBER(E102),E102&gt;0,F102=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K102" s="50" t="str">
-        <x:f>IF(A102="","",IF(AND(ISNUMBER(E102),E102=0,OR(ISNUMBER(SEARCH("Free",D102&amp;"")),AND(ISNUMBER(F102),F102=0))),"Subscription",IF(ISNUMBER(G102),"Profit",IF(ISNUMBER(I102),"Loss",IF(ISNUMBER(H102),"Draw",IF(AND(ISNUMBER(F102),ISNUMBER(E102),E102&gt;0,F102&gt;E102),"Profit",IF(AND(ISNUMBER(F102),ISNUMBER(E102),E102&gt;0,F102=E102),"Draw",IF(AND(ISNUMBER(F102),ISNUMBER(E102),E102&gt;0,F102=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A102="","",IF(AND(ISNUMBER(E102),E102=0,OR(ISNUMBER(SEARCH("Free",D102&amp;"")),AND(ISNUMBER(F102),F102=0))),"Subscription",IF(ISNUMBER(G102),"Profit",IF(ISNUMBER(I102),"Disqualified",IF(ISNUMBER(H102),"Draw",IF(AND(ISNUMBER(F102),ISNUMBER(E102),E102&gt;0,F102&gt;E102),"Profit",IF(AND(ISNUMBER(F102),ISNUMBER(E102),E102&gt;0,F102=E102),"Draw",IF(AND(ISNUMBER(F102),ISNUMBER(E102),E102&gt;0,F102=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L102" s="50"/>
       <x:c r="M102" s="58"/>
@@ -5169,7 +5182,7 @@
         <x:f>IF(A103="","",IF(K103="Subscription","",IF(E103=0,"",IF(ISNUMBER(G103),G103/E103,IF(ISNUMBER(I103),-ABS(I103)/E103,IF(ISNUMBER(H103),0,IF(AND(ISNUMBER(F103),ISNUMBER(E103),E103&gt;0,F103&gt;E103),(F103-E103)/E103,IF(AND(ISNUMBER(F103),ISNUMBER(E103),E103&gt;0,F103=E103),0,IF(AND(ISNUMBER(F103),ISNUMBER(E103),E103&gt;0,F103=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K103" s="50" t="str">
-        <x:f>IF(A103="","",IF(AND(ISNUMBER(E103),E103=0,OR(ISNUMBER(SEARCH("Free",D103&amp;"")),AND(ISNUMBER(F103),F103=0))),"Subscription",IF(ISNUMBER(G103),"Profit",IF(ISNUMBER(I103),"Loss",IF(ISNUMBER(H103),"Draw",IF(AND(ISNUMBER(F103),ISNUMBER(E103),E103&gt;0,F103&gt;E103),"Profit",IF(AND(ISNUMBER(F103),ISNUMBER(E103),E103&gt;0,F103=E103),"Draw",IF(AND(ISNUMBER(F103),ISNUMBER(E103),E103&gt;0,F103=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A103="","",IF(AND(ISNUMBER(E103),E103=0,OR(ISNUMBER(SEARCH("Free",D103&amp;"")),AND(ISNUMBER(F103),F103=0))),"Subscription",IF(ISNUMBER(G103),"Profit",IF(ISNUMBER(I103),"Disqualified",IF(ISNUMBER(H103),"Draw",IF(AND(ISNUMBER(F103),ISNUMBER(E103),E103&gt;0,F103&gt;E103),"Profit",IF(AND(ISNUMBER(F103),ISNUMBER(E103),E103&gt;0,F103=E103),"Draw",IF(AND(ISNUMBER(F103),ISNUMBER(E103),E103&gt;0,F103=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L103" s="50"/>
       <x:c r="M103" s="58"/>
@@ -5206,7 +5219,7 @@
         <x:f>IF(A104="","",IF(K104="Subscription","",IF(E104=0,"",IF(ISNUMBER(G104),G104/E104,IF(ISNUMBER(I104),-ABS(I104)/E104,IF(ISNUMBER(H104),0,IF(AND(ISNUMBER(F104),ISNUMBER(E104),E104&gt;0,F104&gt;E104),(F104-E104)/E104,IF(AND(ISNUMBER(F104),ISNUMBER(E104),E104&gt;0,F104=E104),0,IF(AND(ISNUMBER(F104),ISNUMBER(E104),E104&gt;0,F104=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K104" s="50" t="str">
-        <x:f>IF(A104="","",IF(AND(ISNUMBER(E104),E104=0,OR(ISNUMBER(SEARCH("Free",D104&amp;"")),AND(ISNUMBER(F104),F104=0))),"Subscription",IF(ISNUMBER(G104),"Profit",IF(ISNUMBER(I104),"Loss",IF(ISNUMBER(H104),"Draw",IF(AND(ISNUMBER(F104),ISNUMBER(E104),E104&gt;0,F104&gt;E104),"Profit",IF(AND(ISNUMBER(F104),ISNUMBER(E104),E104&gt;0,F104=E104),"Draw",IF(AND(ISNUMBER(F104),ISNUMBER(E104),E104&gt;0,F104=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A104="","",IF(AND(ISNUMBER(E104),E104=0,OR(ISNUMBER(SEARCH("Free",D104&amp;"")),AND(ISNUMBER(F104),F104=0))),"Subscription",IF(ISNUMBER(G104),"Profit",IF(ISNUMBER(I104),"Disqualified",IF(ISNUMBER(H104),"Draw",IF(AND(ISNUMBER(F104),ISNUMBER(E104),E104&gt;0,F104&gt;E104),"Profit",IF(AND(ISNUMBER(F104),ISNUMBER(E104),E104&gt;0,F104=E104),"Draw",IF(AND(ISNUMBER(F104),ISNUMBER(E104),E104&gt;0,F104=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L104" s="50"/>
       <x:c r="M104" s="58"/>
@@ -5243,7 +5256,7 @@
         <x:f>IF(A105="","",IF(K105="Subscription","",IF(E105=0,"",IF(ISNUMBER(G105),G105/E105,IF(ISNUMBER(I105),-ABS(I105)/E105,IF(ISNUMBER(H105),0,IF(AND(ISNUMBER(F105),ISNUMBER(E105),E105&gt;0,F105&gt;E105),(F105-E105)/E105,IF(AND(ISNUMBER(F105),ISNUMBER(E105),E105&gt;0,F105=E105),0,IF(AND(ISNUMBER(F105),ISNUMBER(E105),E105&gt;0,F105=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K105" s="50" t="str">
-        <x:f>IF(A105="","",IF(AND(ISNUMBER(E105),E105=0,OR(ISNUMBER(SEARCH("Free",D105&amp;"")),AND(ISNUMBER(F105),F105=0))),"Subscription",IF(ISNUMBER(G105),"Profit",IF(ISNUMBER(I105),"Loss",IF(ISNUMBER(H105),"Draw",IF(AND(ISNUMBER(F105),ISNUMBER(E105),E105&gt;0,F105&gt;E105),"Profit",IF(AND(ISNUMBER(F105),ISNUMBER(E105),E105&gt;0,F105=E105),"Draw",IF(AND(ISNUMBER(F105),ISNUMBER(E105),E105&gt;0,F105=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A105="","",IF(AND(ISNUMBER(E105),E105=0,OR(ISNUMBER(SEARCH("Free",D105&amp;"")),AND(ISNUMBER(F105),F105=0))),"Subscription",IF(ISNUMBER(G105),"Profit",IF(ISNUMBER(I105),"Disqualified",IF(ISNUMBER(H105),"Draw",IF(AND(ISNUMBER(F105),ISNUMBER(E105),E105&gt;0,F105&gt;E105),"Profit",IF(AND(ISNUMBER(F105),ISNUMBER(E105),E105&gt;0,F105=E105),"Draw",IF(AND(ISNUMBER(F105),ISNUMBER(E105),E105&gt;0,F105=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L105" s="50"/>
       <x:c r="M105" s="58"/>
@@ -5280,7 +5293,7 @@
         <x:f>IF(A106="","",IF(K106="Subscription","",IF(E106=0,"",IF(ISNUMBER(G106),G106/E106,IF(ISNUMBER(I106),-ABS(I106)/E106,IF(ISNUMBER(H106),0,IF(AND(ISNUMBER(F106),ISNUMBER(E106),E106&gt;0,F106&gt;E106),(F106-E106)/E106,IF(AND(ISNUMBER(F106),ISNUMBER(E106),E106&gt;0,F106=E106),0,IF(AND(ISNUMBER(F106),ISNUMBER(E106),E106&gt;0,F106=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K106" s="50" t="str">
-        <x:f>IF(A106="","",IF(AND(ISNUMBER(E106),E106=0,OR(ISNUMBER(SEARCH("Free",D106&amp;"")),AND(ISNUMBER(F106),F106=0))),"Subscription",IF(ISNUMBER(G106),"Profit",IF(ISNUMBER(I106),"Loss",IF(ISNUMBER(H106),"Draw",IF(AND(ISNUMBER(F106),ISNUMBER(E106),E106&gt;0,F106&gt;E106),"Profit",IF(AND(ISNUMBER(F106),ISNUMBER(E106),E106&gt;0,F106=E106),"Draw",IF(AND(ISNUMBER(F106),ISNUMBER(E106),E106&gt;0,F106=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A106="","",IF(AND(ISNUMBER(E106),E106=0,OR(ISNUMBER(SEARCH("Free",D106&amp;"")),AND(ISNUMBER(F106),F106=0))),"Subscription",IF(ISNUMBER(G106),"Profit",IF(ISNUMBER(I106),"Disqualified",IF(ISNUMBER(H106),"Draw",IF(AND(ISNUMBER(F106),ISNUMBER(E106),E106&gt;0,F106&gt;E106),"Profit",IF(AND(ISNUMBER(F106),ISNUMBER(E106),E106&gt;0,F106=E106),"Draw",IF(AND(ISNUMBER(F106),ISNUMBER(E106),E106&gt;0,F106=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L106" s="50"/>
       <x:c r="M106" s="58"/>
@@ -5317,7 +5330,7 @@
         <x:f>IF(A107="","",IF(K107="Subscription","",IF(E107=0,"",IF(ISNUMBER(G107),G107/E107,IF(ISNUMBER(I107),-ABS(I107)/E107,IF(ISNUMBER(H107),0,IF(AND(ISNUMBER(F107),ISNUMBER(E107),E107&gt;0,F107&gt;E107),(F107-E107)/E107,IF(AND(ISNUMBER(F107),ISNUMBER(E107),E107&gt;0,F107=E107),0,IF(AND(ISNUMBER(F107),ISNUMBER(E107),E107&gt;0,F107=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K107" s="50" t="str">
-        <x:f>IF(A107="","",IF(AND(ISNUMBER(E107),E107=0,OR(ISNUMBER(SEARCH("Free",D107&amp;"")),AND(ISNUMBER(F107),F107=0))),"Subscription",IF(ISNUMBER(G107),"Profit",IF(ISNUMBER(I107),"Loss",IF(ISNUMBER(H107),"Draw",IF(AND(ISNUMBER(F107),ISNUMBER(E107),E107&gt;0,F107&gt;E107),"Profit",IF(AND(ISNUMBER(F107),ISNUMBER(E107),E107&gt;0,F107=E107),"Draw",IF(AND(ISNUMBER(F107),ISNUMBER(E107),E107&gt;0,F107=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A107="","",IF(AND(ISNUMBER(E107),E107=0,OR(ISNUMBER(SEARCH("Free",D107&amp;"")),AND(ISNUMBER(F107),F107=0))),"Subscription",IF(ISNUMBER(G107),"Profit",IF(ISNUMBER(I107),"Disqualified",IF(ISNUMBER(H107),"Draw",IF(AND(ISNUMBER(F107),ISNUMBER(E107),E107&gt;0,F107&gt;E107),"Profit",IF(AND(ISNUMBER(F107),ISNUMBER(E107),E107&gt;0,F107=E107),"Draw",IF(AND(ISNUMBER(F107),ISNUMBER(E107),E107&gt;0,F107=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L107" s="50"/>
       <x:c r="M107" s="58"/>
@@ -5354,7 +5367,7 @@
         <x:f>IF(A108="","",IF(K108="Subscription","",IF(E108=0,"",IF(ISNUMBER(G108),G108/E108,IF(ISNUMBER(I108),-ABS(I108)/E108,IF(ISNUMBER(H108),0,IF(AND(ISNUMBER(F108),ISNUMBER(E108),E108&gt;0,F108&gt;E108),(F108-E108)/E108,IF(AND(ISNUMBER(F108),ISNUMBER(E108),E108&gt;0,F108=E108),0,IF(AND(ISNUMBER(F108),ISNUMBER(E108),E108&gt;0,F108=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K108" s="50" t="str">
-        <x:f>IF(A108="","",IF(AND(ISNUMBER(E108),E108=0,OR(ISNUMBER(SEARCH("Free",D108&amp;"")),AND(ISNUMBER(F108),F108=0))),"Subscription",IF(ISNUMBER(G108),"Profit",IF(ISNUMBER(I108),"Loss",IF(ISNUMBER(H108),"Draw",IF(AND(ISNUMBER(F108),ISNUMBER(E108),E108&gt;0,F108&gt;E108),"Profit",IF(AND(ISNUMBER(F108),ISNUMBER(E108),E108&gt;0,F108=E108),"Draw",IF(AND(ISNUMBER(F108),ISNUMBER(E108),E108&gt;0,F108=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A108="","",IF(AND(ISNUMBER(E108),E108=0,OR(ISNUMBER(SEARCH("Free",D108&amp;"")),AND(ISNUMBER(F108),F108=0))),"Subscription",IF(ISNUMBER(G108),"Profit",IF(ISNUMBER(I108),"Disqualified",IF(ISNUMBER(H108),"Draw",IF(AND(ISNUMBER(F108),ISNUMBER(E108),E108&gt;0,F108&gt;E108),"Profit",IF(AND(ISNUMBER(F108),ISNUMBER(E108),E108&gt;0,F108=E108),"Draw",IF(AND(ISNUMBER(F108),ISNUMBER(E108),E108&gt;0,F108=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L108" s="50"/>
       <x:c r="M108" s="58"/>
@@ -5391,7 +5404,7 @@
         <x:f>IF(A109="","",IF(K109="Subscription","",IF(E109=0,"",IF(ISNUMBER(G109),G109/E109,IF(ISNUMBER(I109),-ABS(I109)/E109,IF(ISNUMBER(H109),0,IF(AND(ISNUMBER(F109),ISNUMBER(E109),E109&gt;0,F109&gt;E109),(F109-E109)/E109,IF(AND(ISNUMBER(F109),ISNUMBER(E109),E109&gt;0,F109=E109),0,IF(AND(ISNUMBER(F109),ISNUMBER(E109),E109&gt;0,F109=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K109" s="50" t="str">
-        <x:f>IF(A109="","",IF(AND(ISNUMBER(E109),E109=0,OR(ISNUMBER(SEARCH("Free",D109&amp;"")),AND(ISNUMBER(F109),F109=0))),"Subscription",IF(ISNUMBER(G109),"Profit",IF(ISNUMBER(I109),"Loss",IF(ISNUMBER(H109),"Draw",IF(AND(ISNUMBER(F109),ISNUMBER(E109),E109&gt;0,F109&gt;E109),"Profit",IF(AND(ISNUMBER(F109),ISNUMBER(E109),E109&gt;0,F109=E109),"Draw",IF(AND(ISNUMBER(F109),ISNUMBER(E109),E109&gt;0,F109=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A109="","",IF(AND(ISNUMBER(E109),E109=0,OR(ISNUMBER(SEARCH("Free",D109&amp;"")),AND(ISNUMBER(F109),F109=0))),"Subscription",IF(ISNUMBER(G109),"Profit",IF(ISNUMBER(I109),"Disqualified",IF(ISNUMBER(H109),"Draw",IF(AND(ISNUMBER(F109),ISNUMBER(E109),E109&gt;0,F109&gt;E109),"Profit",IF(AND(ISNUMBER(F109),ISNUMBER(E109),E109&gt;0,F109=E109),"Draw",IF(AND(ISNUMBER(F109),ISNUMBER(E109),E109&gt;0,F109=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L109" s="50"/>
       <x:c r="M109" s="58"/>
@@ -5428,7 +5441,7 @@
         <x:f>IF(A110="","",IF(K110="Subscription","",IF(E110=0,"",IF(ISNUMBER(G110),G110/E110,IF(ISNUMBER(I110),-ABS(I110)/E110,IF(ISNUMBER(H110),0,IF(AND(ISNUMBER(F110),ISNUMBER(E110),E110&gt;0,F110&gt;E110),(F110-E110)/E110,IF(AND(ISNUMBER(F110),ISNUMBER(E110),E110&gt;0,F110=E110),0,IF(AND(ISNUMBER(F110),ISNUMBER(E110),E110&gt;0,F110=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K110" s="50" t="str">
-        <x:f>IF(A110="","",IF(AND(ISNUMBER(E110),E110=0,OR(ISNUMBER(SEARCH("Free",D110&amp;"")),AND(ISNUMBER(F110),F110=0))),"Subscription",IF(ISNUMBER(G110),"Profit",IF(ISNUMBER(I110),"Loss",IF(ISNUMBER(H110),"Draw",IF(AND(ISNUMBER(F110),ISNUMBER(E110),E110&gt;0,F110&gt;E110),"Profit",IF(AND(ISNUMBER(F110),ISNUMBER(E110),E110&gt;0,F110=E110),"Draw",IF(AND(ISNUMBER(F110),ISNUMBER(E110),E110&gt;0,F110=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A110="","",IF(AND(ISNUMBER(E110),E110=0,OR(ISNUMBER(SEARCH("Free",D110&amp;"")),AND(ISNUMBER(F110),F110=0))),"Subscription",IF(ISNUMBER(G110),"Profit",IF(ISNUMBER(I110),"Disqualified",IF(ISNUMBER(H110),"Draw",IF(AND(ISNUMBER(F110),ISNUMBER(E110),E110&gt;0,F110&gt;E110),"Profit",IF(AND(ISNUMBER(F110),ISNUMBER(E110),E110&gt;0,F110=E110),"Draw",IF(AND(ISNUMBER(F110),ISNUMBER(E110),E110&gt;0,F110=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L110" s="50"/>
       <x:c r="M110" s="58"/>
@@ -5465,7 +5478,7 @@
         <x:f>IF(A111="","",IF(K111="Subscription","",IF(E111=0,"",IF(ISNUMBER(G111),G111/E111,IF(ISNUMBER(I111),-ABS(I111)/E111,IF(ISNUMBER(H111),0,IF(AND(ISNUMBER(F111),ISNUMBER(E111),E111&gt;0,F111&gt;E111),(F111-E111)/E111,IF(AND(ISNUMBER(F111),ISNUMBER(E111),E111&gt;0,F111=E111),0,IF(AND(ISNUMBER(F111),ISNUMBER(E111),E111&gt;0,F111=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K111" s="50" t="str">
-        <x:f>IF(A111="","",IF(AND(ISNUMBER(E111),E111=0,OR(ISNUMBER(SEARCH("Free",D111&amp;"")),AND(ISNUMBER(F111),F111=0))),"Subscription",IF(ISNUMBER(G111),"Profit",IF(ISNUMBER(I111),"Loss",IF(ISNUMBER(H111),"Draw",IF(AND(ISNUMBER(F111),ISNUMBER(E111),E111&gt;0,F111&gt;E111),"Profit",IF(AND(ISNUMBER(F111),ISNUMBER(E111),E111&gt;0,F111=E111),"Draw",IF(AND(ISNUMBER(F111),ISNUMBER(E111),E111&gt;0,F111=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A111="","",IF(AND(ISNUMBER(E111),E111=0,OR(ISNUMBER(SEARCH("Free",D111&amp;"")),AND(ISNUMBER(F111),F111=0))),"Subscription",IF(ISNUMBER(G111),"Profit",IF(ISNUMBER(I111),"Disqualified",IF(ISNUMBER(H111),"Draw",IF(AND(ISNUMBER(F111),ISNUMBER(E111),E111&gt;0,F111&gt;E111),"Profit",IF(AND(ISNUMBER(F111),ISNUMBER(E111),E111&gt;0,F111=E111),"Draw",IF(AND(ISNUMBER(F111),ISNUMBER(E111),E111&gt;0,F111=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L111" s="50"/>
       <x:c r="M111" s="58"/>
@@ -5502,7 +5515,7 @@
         <x:f>IF(A112="","",IF(K112="Subscription","",IF(E112=0,"",IF(ISNUMBER(G112),G112/E112,IF(ISNUMBER(I112),-ABS(I112)/E112,IF(ISNUMBER(H112),0,IF(AND(ISNUMBER(F112),ISNUMBER(E112),E112&gt;0,F112&gt;E112),(F112-E112)/E112,IF(AND(ISNUMBER(F112),ISNUMBER(E112),E112&gt;0,F112=E112),0,IF(AND(ISNUMBER(F112),ISNUMBER(E112),E112&gt;0,F112=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K112" s="50" t="str">
-        <x:f>IF(A112="","",IF(AND(ISNUMBER(E112),E112=0,OR(ISNUMBER(SEARCH("Free",D112&amp;"")),AND(ISNUMBER(F112),F112=0))),"Subscription",IF(ISNUMBER(G112),"Profit",IF(ISNUMBER(I112),"Loss",IF(ISNUMBER(H112),"Draw",IF(AND(ISNUMBER(F112),ISNUMBER(E112),E112&gt;0,F112&gt;E112),"Profit",IF(AND(ISNUMBER(F112),ISNUMBER(E112),E112&gt;0,F112=E112),"Draw",IF(AND(ISNUMBER(F112),ISNUMBER(E112),E112&gt;0,F112=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A112="","",IF(AND(ISNUMBER(E112),E112=0,OR(ISNUMBER(SEARCH("Free",D112&amp;"")),AND(ISNUMBER(F112),F112=0))),"Subscription",IF(ISNUMBER(G112),"Profit",IF(ISNUMBER(I112),"Disqualified",IF(ISNUMBER(H112),"Draw",IF(AND(ISNUMBER(F112),ISNUMBER(E112),E112&gt;0,F112&gt;E112),"Profit",IF(AND(ISNUMBER(F112),ISNUMBER(E112),E112&gt;0,F112=E112),"Draw",IF(AND(ISNUMBER(F112),ISNUMBER(E112),E112&gt;0,F112=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L112" s="50"/>
       <x:c r="M112" s="58"/>
@@ -5539,7 +5552,7 @@
         <x:f>IF(A113="","",IF(K113="Subscription","",IF(E113=0,"",IF(ISNUMBER(G113),G113/E113,IF(ISNUMBER(I113),-ABS(I113)/E113,IF(ISNUMBER(H113),0,IF(AND(ISNUMBER(F113),ISNUMBER(E113),E113&gt;0,F113&gt;E113),(F113-E113)/E113,IF(AND(ISNUMBER(F113),ISNUMBER(E113),E113&gt;0,F113=E113),0,IF(AND(ISNUMBER(F113),ISNUMBER(E113),E113&gt;0,F113=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K113" s="50" t="str">
-        <x:f>IF(A113="","",IF(AND(ISNUMBER(E113),E113=0,OR(ISNUMBER(SEARCH("Free",D113&amp;"")),AND(ISNUMBER(F113),F113=0))),"Subscription",IF(ISNUMBER(G113),"Profit",IF(ISNUMBER(I113),"Loss",IF(ISNUMBER(H113),"Draw",IF(AND(ISNUMBER(F113),ISNUMBER(E113),E113&gt;0,F113&gt;E113),"Profit",IF(AND(ISNUMBER(F113),ISNUMBER(E113),E113&gt;0,F113=E113),"Draw",IF(AND(ISNUMBER(F113),ISNUMBER(E113),E113&gt;0,F113=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A113="","",IF(AND(ISNUMBER(E113),E113=0,OR(ISNUMBER(SEARCH("Free",D113&amp;"")),AND(ISNUMBER(F113),F113=0))),"Subscription",IF(ISNUMBER(G113),"Profit",IF(ISNUMBER(I113),"Disqualified",IF(ISNUMBER(H113),"Draw",IF(AND(ISNUMBER(F113),ISNUMBER(E113),E113&gt;0,F113&gt;E113),"Profit",IF(AND(ISNUMBER(F113),ISNUMBER(E113),E113&gt;0,F113=E113),"Draw",IF(AND(ISNUMBER(F113),ISNUMBER(E113),E113&gt;0,F113=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L113" s="50"/>
       <x:c r="M113" s="58"/>
@@ -5576,7 +5589,7 @@
         <x:f>IF(A114="","",IF(K114="Subscription","",IF(E114=0,"",IF(ISNUMBER(G114),G114/E114,IF(ISNUMBER(I114),-ABS(I114)/E114,IF(ISNUMBER(H114),0,IF(AND(ISNUMBER(F114),ISNUMBER(E114),E114&gt;0,F114&gt;E114),(F114-E114)/E114,IF(AND(ISNUMBER(F114),ISNUMBER(E114),E114&gt;0,F114=E114),0,IF(AND(ISNUMBER(F114),ISNUMBER(E114),E114&gt;0,F114=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K114" s="50" t="str">
-        <x:f>IF(A114="","",IF(AND(ISNUMBER(E114),E114=0,OR(ISNUMBER(SEARCH("Free",D114&amp;"")),AND(ISNUMBER(F114),F114=0))),"Subscription",IF(ISNUMBER(G114),"Profit",IF(ISNUMBER(I114),"Loss",IF(ISNUMBER(H114),"Draw",IF(AND(ISNUMBER(F114),ISNUMBER(E114),E114&gt;0,F114&gt;E114),"Profit",IF(AND(ISNUMBER(F114),ISNUMBER(E114),E114&gt;0,F114=E114),"Draw",IF(AND(ISNUMBER(F114),ISNUMBER(E114),E114&gt;0,F114=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A114="","",IF(AND(ISNUMBER(E114),E114=0,OR(ISNUMBER(SEARCH("Free",D114&amp;"")),AND(ISNUMBER(F114),F114=0))),"Subscription",IF(ISNUMBER(G114),"Profit",IF(ISNUMBER(I114),"Disqualified",IF(ISNUMBER(H114),"Draw",IF(AND(ISNUMBER(F114),ISNUMBER(E114),E114&gt;0,F114&gt;E114),"Profit",IF(AND(ISNUMBER(F114),ISNUMBER(E114),E114&gt;0,F114=E114),"Draw",IF(AND(ISNUMBER(F114),ISNUMBER(E114),E114&gt;0,F114=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L114" s="50"/>
       <x:c r="M114" s="58"/>
@@ -5613,7 +5626,7 @@
         <x:f>IF(A115="","",IF(K115="Subscription","",IF(E115=0,"",IF(ISNUMBER(G115),G115/E115,IF(ISNUMBER(I115),-ABS(I115)/E115,IF(ISNUMBER(H115),0,IF(AND(ISNUMBER(F115),ISNUMBER(E115),E115&gt;0,F115&gt;E115),(F115-E115)/E115,IF(AND(ISNUMBER(F115),ISNUMBER(E115),E115&gt;0,F115=E115),0,IF(AND(ISNUMBER(F115),ISNUMBER(E115),E115&gt;0,F115=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K115" s="50" t="str">
-        <x:f>IF(A115="","",IF(AND(ISNUMBER(E115),E115=0,OR(ISNUMBER(SEARCH("Free",D115&amp;"")),AND(ISNUMBER(F115),F115=0))),"Subscription",IF(ISNUMBER(G115),"Profit",IF(ISNUMBER(I115),"Loss",IF(ISNUMBER(H115),"Draw",IF(AND(ISNUMBER(F115),ISNUMBER(E115),E115&gt;0,F115&gt;E115),"Profit",IF(AND(ISNUMBER(F115),ISNUMBER(E115),E115&gt;0,F115=E115),"Draw",IF(AND(ISNUMBER(F115),ISNUMBER(E115),E115&gt;0,F115=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A115="","",IF(AND(ISNUMBER(E115),E115=0,OR(ISNUMBER(SEARCH("Free",D115&amp;"")),AND(ISNUMBER(F115),F115=0))),"Subscription",IF(ISNUMBER(G115),"Profit",IF(ISNUMBER(I115),"Disqualified",IF(ISNUMBER(H115),"Draw",IF(AND(ISNUMBER(F115),ISNUMBER(E115),E115&gt;0,F115&gt;E115),"Profit",IF(AND(ISNUMBER(F115),ISNUMBER(E115),E115&gt;0,F115=E115),"Draw",IF(AND(ISNUMBER(F115),ISNUMBER(E115),E115&gt;0,F115=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L115" s="50"/>
       <x:c r="M115" s="58"/>
@@ -5650,7 +5663,7 @@
         <x:f>IF(A116="","",IF(K116="Subscription","",IF(E116=0,"",IF(ISNUMBER(G116),G116/E116,IF(ISNUMBER(I116),-ABS(I116)/E116,IF(ISNUMBER(H116),0,IF(AND(ISNUMBER(F116),ISNUMBER(E116),E116&gt;0,F116&gt;E116),(F116-E116)/E116,IF(AND(ISNUMBER(F116),ISNUMBER(E116),E116&gt;0,F116=E116),0,IF(AND(ISNUMBER(F116),ISNUMBER(E116),E116&gt;0,F116=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K116" s="50" t="str">
-        <x:f>IF(A116="","",IF(AND(ISNUMBER(E116),E116=0,OR(ISNUMBER(SEARCH("Free",D116&amp;"")),AND(ISNUMBER(F116),F116=0))),"Subscription",IF(ISNUMBER(G116),"Profit",IF(ISNUMBER(I116),"Loss",IF(ISNUMBER(H116),"Draw",IF(AND(ISNUMBER(F116),ISNUMBER(E116),E116&gt;0,F116&gt;E116),"Profit",IF(AND(ISNUMBER(F116),ISNUMBER(E116),E116&gt;0,F116=E116),"Draw",IF(AND(ISNUMBER(F116),ISNUMBER(E116),E116&gt;0,F116=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A116="","",IF(AND(ISNUMBER(E116),E116=0,OR(ISNUMBER(SEARCH("Free",D116&amp;"")),AND(ISNUMBER(F116),F116=0))),"Subscription",IF(ISNUMBER(G116),"Profit",IF(ISNUMBER(I116),"Disqualified",IF(ISNUMBER(H116),"Draw",IF(AND(ISNUMBER(F116),ISNUMBER(E116),E116&gt;0,F116&gt;E116),"Profit",IF(AND(ISNUMBER(F116),ISNUMBER(E116),E116&gt;0,F116=E116),"Draw",IF(AND(ISNUMBER(F116),ISNUMBER(E116),E116&gt;0,F116=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L116" s="50"/>
       <x:c r="M116" s="58"/>
@@ -5687,7 +5700,7 @@
         <x:f>IF(A117="","",IF(K117="Subscription","",IF(E117=0,"",IF(ISNUMBER(G117),G117/E117,IF(ISNUMBER(I117),-ABS(I117)/E117,IF(ISNUMBER(H117),0,IF(AND(ISNUMBER(F117),ISNUMBER(E117),E117&gt;0,F117&gt;E117),(F117-E117)/E117,IF(AND(ISNUMBER(F117),ISNUMBER(E117),E117&gt;0,F117=E117),0,IF(AND(ISNUMBER(F117),ISNUMBER(E117),E117&gt;0,F117=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K117" s="50" t="str">
-        <x:f>IF(A117="","",IF(AND(ISNUMBER(E117),E117=0,OR(ISNUMBER(SEARCH("Free",D117&amp;"")),AND(ISNUMBER(F117),F117=0))),"Subscription",IF(ISNUMBER(G117),"Profit",IF(ISNUMBER(I117),"Loss",IF(ISNUMBER(H117),"Draw",IF(AND(ISNUMBER(F117),ISNUMBER(E117),E117&gt;0,F117&gt;E117),"Profit",IF(AND(ISNUMBER(F117),ISNUMBER(E117),E117&gt;0,F117=E117),"Draw",IF(AND(ISNUMBER(F117),ISNUMBER(E117),E117&gt;0,F117=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A117="","",IF(AND(ISNUMBER(E117),E117=0,OR(ISNUMBER(SEARCH("Free",D117&amp;"")),AND(ISNUMBER(F117),F117=0))),"Subscription",IF(ISNUMBER(G117),"Profit",IF(ISNUMBER(I117),"Disqualified",IF(ISNUMBER(H117),"Draw",IF(AND(ISNUMBER(F117),ISNUMBER(E117),E117&gt;0,F117&gt;E117),"Profit",IF(AND(ISNUMBER(F117),ISNUMBER(E117),E117&gt;0,F117=E117),"Draw",IF(AND(ISNUMBER(F117),ISNUMBER(E117),E117&gt;0,F117=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L117" s="50"/>
       <x:c r="M117" s="58"/>
@@ -5724,7 +5737,7 @@
         <x:f>IF(A118="","",IF(K118="Subscription","",IF(E118=0,"",IF(ISNUMBER(G118),G118/E118,IF(ISNUMBER(I118),-ABS(I118)/E118,IF(ISNUMBER(H118),0,IF(AND(ISNUMBER(F118),ISNUMBER(E118),E118&gt;0,F118&gt;E118),(F118-E118)/E118,IF(AND(ISNUMBER(F118),ISNUMBER(E118),E118&gt;0,F118=E118),0,IF(AND(ISNUMBER(F118),ISNUMBER(E118),E118&gt;0,F118=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K118" s="50" t="str">
-        <x:f>IF(A118="","",IF(AND(ISNUMBER(E118),E118=0,OR(ISNUMBER(SEARCH("Free",D118&amp;"")),AND(ISNUMBER(F118),F118=0))),"Subscription",IF(ISNUMBER(G118),"Profit",IF(ISNUMBER(I118),"Loss",IF(ISNUMBER(H118),"Draw",IF(AND(ISNUMBER(F118),ISNUMBER(E118),E118&gt;0,F118&gt;E118),"Profit",IF(AND(ISNUMBER(F118),ISNUMBER(E118),E118&gt;0,F118=E118),"Draw",IF(AND(ISNUMBER(F118),ISNUMBER(E118),E118&gt;0,F118=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A118="","",IF(AND(ISNUMBER(E118),E118=0,OR(ISNUMBER(SEARCH("Free",D118&amp;"")),AND(ISNUMBER(F118),F118=0))),"Subscription",IF(ISNUMBER(G118),"Profit",IF(ISNUMBER(I118),"Disqualified",IF(ISNUMBER(H118),"Draw",IF(AND(ISNUMBER(F118),ISNUMBER(E118),E118&gt;0,F118&gt;E118),"Profit",IF(AND(ISNUMBER(F118),ISNUMBER(E118),E118&gt;0,F118=E118),"Draw",IF(AND(ISNUMBER(F118),ISNUMBER(E118),E118&gt;0,F118=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L118" s="50"/>
       <x:c r="M118" s="58"/>
@@ -5761,7 +5774,7 @@
         <x:f>IF(A119="","",IF(K119="Subscription","",IF(E119=0,"",IF(ISNUMBER(G119),G119/E119,IF(ISNUMBER(I119),-ABS(I119)/E119,IF(ISNUMBER(H119),0,IF(AND(ISNUMBER(F119),ISNUMBER(E119),E119&gt;0,F119&gt;E119),(F119-E119)/E119,IF(AND(ISNUMBER(F119),ISNUMBER(E119),E119&gt;0,F119=E119),0,IF(AND(ISNUMBER(F119),ISNUMBER(E119),E119&gt;0,F119=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K119" s="50" t="str">
-        <x:f>IF(A119="","",IF(AND(ISNUMBER(E119),E119=0,OR(ISNUMBER(SEARCH("Free",D119&amp;"")),AND(ISNUMBER(F119),F119=0))),"Subscription",IF(ISNUMBER(G119),"Profit",IF(ISNUMBER(I119),"Loss",IF(ISNUMBER(H119),"Draw",IF(AND(ISNUMBER(F119),ISNUMBER(E119),E119&gt;0,F119&gt;E119),"Profit",IF(AND(ISNUMBER(F119),ISNUMBER(E119),E119&gt;0,F119=E119),"Draw",IF(AND(ISNUMBER(F119),ISNUMBER(E119),E119&gt;0,F119=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A119="","",IF(AND(ISNUMBER(E119),E119=0,OR(ISNUMBER(SEARCH("Free",D119&amp;"")),AND(ISNUMBER(F119),F119=0))),"Subscription",IF(ISNUMBER(G119),"Profit",IF(ISNUMBER(I119),"Disqualified",IF(ISNUMBER(H119),"Draw",IF(AND(ISNUMBER(F119),ISNUMBER(E119),E119&gt;0,F119&gt;E119),"Profit",IF(AND(ISNUMBER(F119),ISNUMBER(E119),E119&gt;0,F119=E119),"Draw",IF(AND(ISNUMBER(F119),ISNUMBER(E119),E119&gt;0,F119=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L119" s="50"/>
       <x:c r="M119" s="58"/>
@@ -5798,7 +5811,7 @@
         <x:f>IF(A120="","",IF(K120="Subscription","",IF(E120=0,"",IF(ISNUMBER(G120),G120/E120,IF(ISNUMBER(I120),-ABS(I120)/E120,IF(ISNUMBER(H120),0,IF(AND(ISNUMBER(F120),ISNUMBER(E120),E120&gt;0,F120&gt;E120),(F120-E120)/E120,IF(AND(ISNUMBER(F120),ISNUMBER(E120),E120&gt;0,F120=E120),0,IF(AND(ISNUMBER(F120),ISNUMBER(E120),E120&gt;0,F120=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K120" s="50" t="str">
-        <x:f>IF(A120="","",IF(AND(ISNUMBER(E120),E120=0,OR(ISNUMBER(SEARCH("Free",D120&amp;"")),AND(ISNUMBER(F120),F120=0))),"Subscription",IF(ISNUMBER(G120),"Profit",IF(ISNUMBER(I120),"Loss",IF(ISNUMBER(H120),"Draw",IF(AND(ISNUMBER(F120),ISNUMBER(E120),E120&gt;0,F120&gt;E120),"Profit",IF(AND(ISNUMBER(F120),ISNUMBER(E120),E120&gt;0,F120=E120),"Draw",IF(AND(ISNUMBER(F120),ISNUMBER(E120),E120&gt;0,F120=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A120="","",IF(AND(ISNUMBER(E120),E120=0,OR(ISNUMBER(SEARCH("Free",D120&amp;"")),AND(ISNUMBER(F120),F120=0))),"Subscription",IF(ISNUMBER(G120),"Profit",IF(ISNUMBER(I120),"Disqualified",IF(ISNUMBER(H120),"Draw",IF(AND(ISNUMBER(F120),ISNUMBER(E120),E120&gt;0,F120&gt;E120),"Profit",IF(AND(ISNUMBER(F120),ISNUMBER(E120),E120&gt;0,F120=E120),"Draw",IF(AND(ISNUMBER(F120),ISNUMBER(E120),E120&gt;0,F120=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L120" s="50"/>
       <x:c r="M120" s="58"/>
@@ -5835,7 +5848,7 @@
         <x:f>IF(A121="","",IF(K121="Subscription","",IF(E121=0,"",IF(ISNUMBER(G121),G121/E121,IF(ISNUMBER(I121),-ABS(I121)/E121,IF(ISNUMBER(H121),0,IF(AND(ISNUMBER(F121),ISNUMBER(E121),E121&gt;0,F121&gt;E121),(F121-E121)/E121,IF(AND(ISNUMBER(F121),ISNUMBER(E121),E121&gt;0,F121=E121),0,IF(AND(ISNUMBER(F121),ISNUMBER(E121),E121&gt;0,F121=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K121" s="50" t="str">
-        <x:f>IF(A121="","",IF(AND(ISNUMBER(E121),E121=0,OR(ISNUMBER(SEARCH("Free",D121&amp;"")),AND(ISNUMBER(F121),F121=0))),"Subscription",IF(ISNUMBER(G121),"Profit",IF(ISNUMBER(I121),"Loss",IF(ISNUMBER(H121),"Draw",IF(AND(ISNUMBER(F121),ISNUMBER(E121),E121&gt;0,F121&gt;E121),"Profit",IF(AND(ISNUMBER(F121),ISNUMBER(E121),E121&gt;0,F121=E121),"Draw",IF(AND(ISNUMBER(F121),ISNUMBER(E121),E121&gt;0,F121=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A121="","",IF(AND(ISNUMBER(E121),E121=0,OR(ISNUMBER(SEARCH("Free",D121&amp;"")),AND(ISNUMBER(F121),F121=0))),"Subscription",IF(ISNUMBER(G121),"Profit",IF(ISNUMBER(I121),"Disqualified",IF(ISNUMBER(H121),"Draw",IF(AND(ISNUMBER(F121),ISNUMBER(E121),E121&gt;0,F121&gt;E121),"Profit",IF(AND(ISNUMBER(F121),ISNUMBER(E121),E121&gt;0,F121=E121),"Draw",IF(AND(ISNUMBER(F121),ISNUMBER(E121),E121&gt;0,F121=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L121" s="50"/>
       <x:c r="M121" s="58"/>
@@ -5872,7 +5885,7 @@
         <x:f>IF(A122="","",IF(K122="Subscription","",IF(E122=0,"",IF(ISNUMBER(G122),G122/E122,IF(ISNUMBER(I122),-ABS(I122)/E122,IF(ISNUMBER(H122),0,IF(AND(ISNUMBER(F122),ISNUMBER(E122),E122&gt;0,F122&gt;E122),(F122-E122)/E122,IF(AND(ISNUMBER(F122),ISNUMBER(E122),E122&gt;0,F122=E122),0,IF(AND(ISNUMBER(F122),ISNUMBER(E122),E122&gt;0,F122=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K122" s="50" t="str">
-        <x:f>IF(A122="","",IF(AND(ISNUMBER(E122),E122=0,OR(ISNUMBER(SEARCH("Free",D122&amp;"")),AND(ISNUMBER(F122),F122=0))),"Subscription",IF(ISNUMBER(G122),"Profit",IF(ISNUMBER(I122),"Loss",IF(ISNUMBER(H122),"Draw",IF(AND(ISNUMBER(F122),ISNUMBER(E122),E122&gt;0,F122&gt;E122),"Profit",IF(AND(ISNUMBER(F122),ISNUMBER(E122),E122&gt;0,F122=E122),"Draw",IF(AND(ISNUMBER(F122),ISNUMBER(E122),E122&gt;0,F122=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A122="","",IF(AND(ISNUMBER(E122),E122=0,OR(ISNUMBER(SEARCH("Free",D122&amp;"")),AND(ISNUMBER(F122),F122=0))),"Subscription",IF(ISNUMBER(G122),"Profit",IF(ISNUMBER(I122),"Disqualified",IF(ISNUMBER(H122),"Draw",IF(AND(ISNUMBER(F122),ISNUMBER(E122),E122&gt;0,F122&gt;E122),"Profit",IF(AND(ISNUMBER(F122),ISNUMBER(E122),E122&gt;0,F122=E122),"Draw",IF(AND(ISNUMBER(F122),ISNUMBER(E122),E122&gt;0,F122=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L122" s="50"/>
       <x:c r="M122" s="58"/>
@@ -5909,7 +5922,7 @@
         <x:f>IF(A123="","",IF(K123="Subscription","",IF(E123=0,"",IF(ISNUMBER(G123),G123/E123,IF(ISNUMBER(I123),-ABS(I123)/E123,IF(ISNUMBER(H123),0,IF(AND(ISNUMBER(F123),ISNUMBER(E123),E123&gt;0,F123&gt;E123),(F123-E123)/E123,IF(AND(ISNUMBER(F123),ISNUMBER(E123),E123&gt;0,F123=E123),0,IF(AND(ISNUMBER(F123),ISNUMBER(E123),E123&gt;0,F123=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K123" s="50" t="str">
-        <x:f>IF(A123="","",IF(AND(ISNUMBER(E123),E123=0,OR(ISNUMBER(SEARCH("Free",D123&amp;"")),AND(ISNUMBER(F123),F123=0))),"Subscription",IF(ISNUMBER(G123),"Profit",IF(ISNUMBER(I123),"Loss",IF(ISNUMBER(H123),"Draw",IF(AND(ISNUMBER(F123),ISNUMBER(E123),E123&gt;0,F123&gt;E123),"Profit",IF(AND(ISNUMBER(F123),ISNUMBER(E123),E123&gt;0,F123=E123),"Draw",IF(AND(ISNUMBER(F123),ISNUMBER(E123),E123&gt;0,F123=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A123="","",IF(AND(ISNUMBER(E123),E123=0,OR(ISNUMBER(SEARCH("Free",D123&amp;"")),AND(ISNUMBER(F123),F123=0))),"Subscription",IF(ISNUMBER(G123),"Profit",IF(ISNUMBER(I123),"Disqualified",IF(ISNUMBER(H123),"Draw",IF(AND(ISNUMBER(F123),ISNUMBER(E123),E123&gt;0,F123&gt;E123),"Profit",IF(AND(ISNUMBER(F123),ISNUMBER(E123),E123&gt;0,F123=E123),"Draw",IF(AND(ISNUMBER(F123),ISNUMBER(E123),E123&gt;0,F123=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L123" s="50"/>
       <x:c r="M123" s="58"/>
@@ -5946,7 +5959,7 @@
         <x:f>IF(A124="","",IF(K124="Subscription","",IF(E124=0,"",IF(ISNUMBER(G124),G124/E124,IF(ISNUMBER(I124),-ABS(I124)/E124,IF(ISNUMBER(H124),0,IF(AND(ISNUMBER(F124),ISNUMBER(E124),E124&gt;0,F124&gt;E124),(F124-E124)/E124,IF(AND(ISNUMBER(F124),ISNUMBER(E124),E124&gt;0,F124=E124),0,IF(AND(ISNUMBER(F124),ISNUMBER(E124),E124&gt;0,F124=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K124" s="50" t="str">
-        <x:f>IF(A124="","",IF(AND(ISNUMBER(E124),E124=0,OR(ISNUMBER(SEARCH("Free",D124&amp;"")),AND(ISNUMBER(F124),F124=0))),"Subscription",IF(ISNUMBER(G124),"Profit",IF(ISNUMBER(I124),"Loss",IF(ISNUMBER(H124),"Draw",IF(AND(ISNUMBER(F124),ISNUMBER(E124),E124&gt;0,F124&gt;E124),"Profit",IF(AND(ISNUMBER(F124),ISNUMBER(E124),E124&gt;0,F124=E124),"Draw",IF(AND(ISNUMBER(F124),ISNUMBER(E124),E124&gt;0,F124=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A124="","",IF(AND(ISNUMBER(E124),E124=0,OR(ISNUMBER(SEARCH("Free",D124&amp;"")),AND(ISNUMBER(F124),F124=0))),"Subscription",IF(ISNUMBER(G124),"Profit",IF(ISNUMBER(I124),"Disqualified",IF(ISNUMBER(H124),"Draw",IF(AND(ISNUMBER(F124),ISNUMBER(E124),E124&gt;0,F124&gt;E124),"Profit",IF(AND(ISNUMBER(F124),ISNUMBER(E124),E124&gt;0,F124=E124),"Draw",IF(AND(ISNUMBER(F124),ISNUMBER(E124),E124&gt;0,F124=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L124" s="50"/>
       <x:c r="M124" s="58"/>
@@ -5983,7 +5996,7 @@
         <x:f>IF(A125="","",IF(K125="Subscription","",IF(E125=0,"",IF(ISNUMBER(G125),G125/E125,IF(ISNUMBER(I125),-ABS(I125)/E125,IF(ISNUMBER(H125),0,IF(AND(ISNUMBER(F125),ISNUMBER(E125),E125&gt;0,F125&gt;E125),(F125-E125)/E125,IF(AND(ISNUMBER(F125),ISNUMBER(E125),E125&gt;0,F125=E125),0,IF(AND(ISNUMBER(F125),ISNUMBER(E125),E125&gt;0,F125=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K125" s="50" t="str">
-        <x:f>IF(A125="","",IF(AND(ISNUMBER(E125),E125=0,OR(ISNUMBER(SEARCH("Free",D125&amp;"")),AND(ISNUMBER(F125),F125=0))),"Subscription",IF(ISNUMBER(G125),"Profit",IF(ISNUMBER(I125),"Loss",IF(ISNUMBER(H125),"Draw",IF(AND(ISNUMBER(F125),ISNUMBER(E125),E125&gt;0,F125&gt;E125),"Profit",IF(AND(ISNUMBER(F125),ISNUMBER(E125),E125&gt;0,F125=E125),"Draw",IF(AND(ISNUMBER(F125),ISNUMBER(E125),E125&gt;0,F125=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A125="","",IF(AND(ISNUMBER(E125),E125=0,OR(ISNUMBER(SEARCH("Free",D125&amp;"")),AND(ISNUMBER(F125),F125=0))),"Subscription",IF(ISNUMBER(G125),"Profit",IF(ISNUMBER(I125),"Disqualified",IF(ISNUMBER(H125),"Draw",IF(AND(ISNUMBER(F125),ISNUMBER(E125),E125&gt;0,F125&gt;E125),"Profit",IF(AND(ISNUMBER(F125),ISNUMBER(E125),E125&gt;0,F125=E125),"Draw",IF(AND(ISNUMBER(F125),ISNUMBER(E125),E125&gt;0,F125=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L125" s="50"/>
       <x:c r="M125" s="58"/>
@@ -6020,7 +6033,7 @@
         <x:f>IF(A126="","",IF(K126="Subscription","",IF(E126=0,"",IF(ISNUMBER(G126),G126/E126,IF(ISNUMBER(I126),-ABS(I126)/E126,IF(ISNUMBER(H126),0,IF(AND(ISNUMBER(F126),ISNUMBER(E126),E126&gt;0,F126&gt;E126),(F126-E126)/E126,IF(AND(ISNUMBER(F126),ISNUMBER(E126),E126&gt;0,F126=E126),0,IF(AND(ISNUMBER(F126),ISNUMBER(E126),E126&gt;0,F126=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K126" s="50" t="str">
-        <x:f>IF(A126="","",IF(AND(ISNUMBER(E126),E126=0,OR(ISNUMBER(SEARCH("Free",D126&amp;"")),AND(ISNUMBER(F126),F126=0))),"Subscription",IF(ISNUMBER(G126),"Profit",IF(ISNUMBER(I126),"Loss",IF(ISNUMBER(H126),"Draw",IF(AND(ISNUMBER(F126),ISNUMBER(E126),E126&gt;0,F126&gt;E126),"Profit",IF(AND(ISNUMBER(F126),ISNUMBER(E126),E126&gt;0,F126=E126),"Draw",IF(AND(ISNUMBER(F126),ISNUMBER(E126),E126&gt;0,F126=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A126="","",IF(AND(ISNUMBER(E126),E126=0,OR(ISNUMBER(SEARCH("Free",D126&amp;"")),AND(ISNUMBER(F126),F126=0))),"Subscription",IF(ISNUMBER(G126),"Profit",IF(ISNUMBER(I126),"Disqualified",IF(ISNUMBER(H126),"Draw",IF(AND(ISNUMBER(F126),ISNUMBER(E126),E126&gt;0,F126&gt;E126),"Profit",IF(AND(ISNUMBER(F126),ISNUMBER(E126),E126&gt;0,F126=E126),"Draw",IF(AND(ISNUMBER(F126),ISNUMBER(E126),E126&gt;0,F126=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L126" s="50"/>
       <x:c r="M126" s="58"/>
@@ -6057,7 +6070,7 @@
         <x:f>IF(A127="","",IF(K127="Subscription","",IF(E127=0,"",IF(ISNUMBER(G127),G127/E127,IF(ISNUMBER(I127),-ABS(I127)/E127,IF(ISNUMBER(H127),0,IF(AND(ISNUMBER(F127),ISNUMBER(E127),E127&gt;0,F127&gt;E127),(F127-E127)/E127,IF(AND(ISNUMBER(F127),ISNUMBER(E127),E127&gt;0,F127=E127),0,IF(AND(ISNUMBER(F127),ISNUMBER(E127),E127&gt;0,F127=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K127" s="50" t="str">
-        <x:f>IF(A127="","",IF(AND(ISNUMBER(E127),E127=0,OR(ISNUMBER(SEARCH("Free",D127&amp;"")),AND(ISNUMBER(F127),F127=0))),"Subscription",IF(ISNUMBER(G127),"Profit",IF(ISNUMBER(I127),"Loss",IF(ISNUMBER(H127),"Draw",IF(AND(ISNUMBER(F127),ISNUMBER(E127),E127&gt;0,F127&gt;E127),"Profit",IF(AND(ISNUMBER(F127),ISNUMBER(E127),E127&gt;0,F127=E127),"Draw",IF(AND(ISNUMBER(F127),ISNUMBER(E127),E127&gt;0,F127=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A127="","",IF(AND(ISNUMBER(E127),E127=0,OR(ISNUMBER(SEARCH("Free",D127&amp;"")),AND(ISNUMBER(F127),F127=0))),"Subscription",IF(ISNUMBER(G127),"Profit",IF(ISNUMBER(I127),"Disqualified",IF(ISNUMBER(H127),"Draw",IF(AND(ISNUMBER(F127),ISNUMBER(E127),E127&gt;0,F127&gt;E127),"Profit",IF(AND(ISNUMBER(F127),ISNUMBER(E127),E127&gt;0,F127=E127),"Draw",IF(AND(ISNUMBER(F127),ISNUMBER(E127),E127&gt;0,F127=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L127" s="50"/>
       <x:c r="M127" s="58"/>
@@ -6094,7 +6107,7 @@
         <x:f>IF(A128="","",IF(K128="Subscription","",IF(E128=0,"",IF(ISNUMBER(G128),G128/E128,IF(ISNUMBER(I128),-ABS(I128)/E128,IF(ISNUMBER(H128),0,IF(AND(ISNUMBER(F128),ISNUMBER(E128),E128&gt;0,F128&gt;E128),(F128-E128)/E128,IF(AND(ISNUMBER(F128),ISNUMBER(E128),E128&gt;0,F128=E128),0,IF(AND(ISNUMBER(F128),ISNUMBER(E128),E128&gt;0,F128=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K128" s="50" t="str">
-        <x:f>IF(A128="","",IF(AND(ISNUMBER(E128),E128=0,OR(ISNUMBER(SEARCH("Free",D128&amp;"")),AND(ISNUMBER(F128),F128=0))),"Subscription",IF(ISNUMBER(G128),"Profit",IF(ISNUMBER(I128),"Loss",IF(ISNUMBER(H128),"Draw",IF(AND(ISNUMBER(F128),ISNUMBER(E128),E128&gt;0,F128&gt;E128),"Profit",IF(AND(ISNUMBER(F128),ISNUMBER(E128),E128&gt;0,F128=E128),"Draw",IF(AND(ISNUMBER(F128),ISNUMBER(E128),E128&gt;0,F128=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A128="","",IF(AND(ISNUMBER(E128),E128=0,OR(ISNUMBER(SEARCH("Free",D128&amp;"")),AND(ISNUMBER(F128),F128=0))),"Subscription",IF(ISNUMBER(G128),"Profit",IF(ISNUMBER(I128),"Disqualified",IF(ISNUMBER(H128),"Draw",IF(AND(ISNUMBER(F128),ISNUMBER(E128),E128&gt;0,F128&gt;E128),"Profit",IF(AND(ISNUMBER(F128),ISNUMBER(E128),E128&gt;0,F128=E128),"Draw",IF(AND(ISNUMBER(F128),ISNUMBER(E128),E128&gt;0,F128=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L128" s="50"/>
       <x:c r="M128" s="58"/>
@@ -6131,7 +6144,7 @@
         <x:f>IF(A129="","",IF(K129="Subscription","",IF(E129=0,"",IF(ISNUMBER(G129),G129/E129,IF(ISNUMBER(I129),-ABS(I129)/E129,IF(ISNUMBER(H129),0,IF(AND(ISNUMBER(F129),ISNUMBER(E129),E129&gt;0,F129&gt;E129),(F129-E129)/E129,IF(AND(ISNUMBER(F129),ISNUMBER(E129),E129&gt;0,F129=E129),0,IF(AND(ISNUMBER(F129),ISNUMBER(E129),E129&gt;0,F129=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K129" s="50" t="str">
-        <x:f>IF(A129="","",IF(AND(ISNUMBER(E129),E129=0,OR(ISNUMBER(SEARCH("Free",D129&amp;"")),AND(ISNUMBER(F129),F129=0))),"Subscription",IF(ISNUMBER(G129),"Profit",IF(ISNUMBER(I129),"Loss",IF(ISNUMBER(H129),"Draw",IF(AND(ISNUMBER(F129),ISNUMBER(E129),E129&gt;0,F129&gt;E129),"Profit",IF(AND(ISNUMBER(F129),ISNUMBER(E129),E129&gt;0,F129=E129),"Draw",IF(AND(ISNUMBER(F129),ISNUMBER(E129),E129&gt;0,F129=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A129="","",IF(AND(ISNUMBER(E129),E129=0,OR(ISNUMBER(SEARCH("Free",D129&amp;"")),AND(ISNUMBER(F129),F129=0))),"Subscription",IF(ISNUMBER(G129),"Profit",IF(ISNUMBER(I129),"Disqualified",IF(ISNUMBER(H129),"Draw",IF(AND(ISNUMBER(F129),ISNUMBER(E129),E129&gt;0,F129&gt;E129),"Profit",IF(AND(ISNUMBER(F129),ISNUMBER(E129),E129&gt;0,F129=E129),"Draw",IF(AND(ISNUMBER(F129),ISNUMBER(E129),E129&gt;0,F129=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L129" s="50"/>
       <x:c r="M129" s="58"/>
@@ -6168,7 +6181,7 @@
         <x:f>IF(A130="","",IF(K130="Subscription","",IF(E130=0,"",IF(ISNUMBER(G130),G130/E130,IF(ISNUMBER(I130),-ABS(I130)/E130,IF(ISNUMBER(H130),0,IF(AND(ISNUMBER(F130),ISNUMBER(E130),E130&gt;0,F130&gt;E130),(F130-E130)/E130,IF(AND(ISNUMBER(F130),ISNUMBER(E130),E130&gt;0,F130=E130),0,IF(AND(ISNUMBER(F130),ISNUMBER(E130),E130&gt;0,F130=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K130" s="50" t="str">
-        <x:f>IF(A130="","",IF(AND(ISNUMBER(E130),E130=0,OR(ISNUMBER(SEARCH("Free",D130&amp;"")),AND(ISNUMBER(F130),F130=0))),"Subscription",IF(ISNUMBER(G130),"Profit",IF(ISNUMBER(I130),"Loss",IF(ISNUMBER(H130),"Draw",IF(AND(ISNUMBER(F130),ISNUMBER(E130),E130&gt;0,F130&gt;E130),"Profit",IF(AND(ISNUMBER(F130),ISNUMBER(E130),E130&gt;0,F130=E130),"Draw",IF(AND(ISNUMBER(F130),ISNUMBER(E130),E130&gt;0,F130=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A130="","",IF(AND(ISNUMBER(E130),E130=0,OR(ISNUMBER(SEARCH("Free",D130&amp;"")),AND(ISNUMBER(F130),F130=0))),"Subscription",IF(ISNUMBER(G130),"Profit",IF(ISNUMBER(I130),"Disqualified",IF(ISNUMBER(H130),"Draw",IF(AND(ISNUMBER(F130),ISNUMBER(E130),E130&gt;0,F130&gt;E130),"Profit",IF(AND(ISNUMBER(F130),ISNUMBER(E130),E130&gt;0,F130=E130),"Draw",IF(AND(ISNUMBER(F130),ISNUMBER(E130),E130&gt;0,F130=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L130" s="50"/>
       <x:c r="M130" s="58"/>
@@ -6205,7 +6218,7 @@
         <x:f>IF(A131="","",IF(K131="Subscription","",IF(E131=0,"",IF(ISNUMBER(G131),G131/E131,IF(ISNUMBER(I131),-ABS(I131)/E131,IF(ISNUMBER(H131),0,IF(AND(ISNUMBER(F131),ISNUMBER(E131),E131&gt;0,F131&gt;E131),(F131-E131)/E131,IF(AND(ISNUMBER(F131),ISNUMBER(E131),E131&gt;0,F131=E131),0,IF(AND(ISNUMBER(F131),ISNUMBER(E131),E131&gt;0,F131=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K131" s="50" t="str">
-        <x:f>IF(A131="","",IF(AND(ISNUMBER(E131),E131=0,OR(ISNUMBER(SEARCH("Free",D131&amp;"")),AND(ISNUMBER(F131),F131=0))),"Subscription",IF(ISNUMBER(G131),"Profit",IF(ISNUMBER(I131),"Loss",IF(ISNUMBER(H131),"Draw",IF(AND(ISNUMBER(F131),ISNUMBER(E131),E131&gt;0,F131&gt;E131),"Profit",IF(AND(ISNUMBER(F131),ISNUMBER(E131),E131&gt;0,F131=E131),"Draw",IF(AND(ISNUMBER(F131),ISNUMBER(E131),E131&gt;0,F131=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A131="","",IF(AND(ISNUMBER(E131),E131=0,OR(ISNUMBER(SEARCH("Free",D131&amp;"")),AND(ISNUMBER(F131),F131=0))),"Subscription",IF(ISNUMBER(G131),"Profit",IF(ISNUMBER(I131),"Disqualified",IF(ISNUMBER(H131),"Draw",IF(AND(ISNUMBER(F131),ISNUMBER(E131),E131&gt;0,F131&gt;E131),"Profit",IF(AND(ISNUMBER(F131),ISNUMBER(E131),E131&gt;0,F131=E131),"Draw",IF(AND(ISNUMBER(F131),ISNUMBER(E131),E131&gt;0,F131=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L131" s="50"/>
       <x:c r="M131" s="58"/>
@@ -6242,7 +6255,7 @@
         <x:f>IF(A132="","",IF(K132="Subscription","",IF(E132=0,"",IF(ISNUMBER(G132),G132/E132,IF(ISNUMBER(I132),-ABS(I132)/E132,IF(ISNUMBER(H132),0,IF(AND(ISNUMBER(F132),ISNUMBER(E132),E132&gt;0,F132&gt;E132),(F132-E132)/E132,IF(AND(ISNUMBER(F132),ISNUMBER(E132),E132&gt;0,F132=E132),0,IF(AND(ISNUMBER(F132),ISNUMBER(E132),E132&gt;0,F132=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K132" s="50" t="str">
-        <x:f>IF(A132="","",IF(AND(ISNUMBER(E132),E132=0,OR(ISNUMBER(SEARCH("Free",D132&amp;"")),AND(ISNUMBER(F132),F132=0))),"Subscription",IF(ISNUMBER(G132),"Profit",IF(ISNUMBER(I132),"Loss",IF(ISNUMBER(H132),"Draw",IF(AND(ISNUMBER(F132),ISNUMBER(E132),E132&gt;0,F132&gt;E132),"Profit",IF(AND(ISNUMBER(F132),ISNUMBER(E132),E132&gt;0,F132=E132),"Draw",IF(AND(ISNUMBER(F132),ISNUMBER(E132),E132&gt;0,F132=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A132="","",IF(AND(ISNUMBER(E132),E132=0,OR(ISNUMBER(SEARCH("Free",D132&amp;"")),AND(ISNUMBER(F132),F132=0))),"Subscription",IF(ISNUMBER(G132),"Profit",IF(ISNUMBER(I132),"Disqualified",IF(ISNUMBER(H132),"Draw",IF(AND(ISNUMBER(F132),ISNUMBER(E132),E132&gt;0,F132&gt;E132),"Profit",IF(AND(ISNUMBER(F132),ISNUMBER(E132),E132&gt;0,F132=E132),"Draw",IF(AND(ISNUMBER(F132),ISNUMBER(E132),E132&gt;0,F132=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L132" s="50"/>
       <x:c r="M132" s="58"/>
@@ -6279,7 +6292,7 @@
         <x:f>IF(A133="","",IF(K133="Subscription","",IF(E133=0,"",IF(ISNUMBER(G133),G133/E133,IF(ISNUMBER(I133),-ABS(I133)/E133,IF(ISNUMBER(H133),0,IF(AND(ISNUMBER(F133),ISNUMBER(E133),E133&gt;0,F133&gt;E133),(F133-E133)/E133,IF(AND(ISNUMBER(F133),ISNUMBER(E133),E133&gt;0,F133=E133),0,IF(AND(ISNUMBER(F133),ISNUMBER(E133),E133&gt;0,F133=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K133" s="50" t="str">
-        <x:f>IF(A133="","",IF(AND(ISNUMBER(E133),E133=0,OR(ISNUMBER(SEARCH("Free",D133&amp;"")),AND(ISNUMBER(F133),F133=0))),"Subscription",IF(ISNUMBER(G133),"Profit",IF(ISNUMBER(I133),"Loss",IF(ISNUMBER(H133),"Draw",IF(AND(ISNUMBER(F133),ISNUMBER(E133),E133&gt;0,F133&gt;E133),"Profit",IF(AND(ISNUMBER(F133),ISNUMBER(E133),E133&gt;0,F133=E133),"Draw",IF(AND(ISNUMBER(F133),ISNUMBER(E133),E133&gt;0,F133=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A133="","",IF(AND(ISNUMBER(E133),E133=0,OR(ISNUMBER(SEARCH("Free",D133&amp;"")),AND(ISNUMBER(F133),F133=0))),"Subscription",IF(ISNUMBER(G133),"Profit",IF(ISNUMBER(I133),"Disqualified",IF(ISNUMBER(H133),"Draw",IF(AND(ISNUMBER(F133),ISNUMBER(E133),E133&gt;0,F133&gt;E133),"Profit",IF(AND(ISNUMBER(F133),ISNUMBER(E133),E133&gt;0,F133=E133),"Draw",IF(AND(ISNUMBER(F133),ISNUMBER(E133),E133&gt;0,F133=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L133" s="50"/>
       <x:c r="M133" s="58"/>
@@ -6316,7 +6329,7 @@
         <x:f>IF(A134="","",IF(K134="Subscription","",IF(E134=0,"",IF(ISNUMBER(G134),G134/E134,IF(ISNUMBER(I134),-ABS(I134)/E134,IF(ISNUMBER(H134),0,IF(AND(ISNUMBER(F134),ISNUMBER(E134),E134&gt;0,F134&gt;E134),(F134-E134)/E134,IF(AND(ISNUMBER(F134),ISNUMBER(E134),E134&gt;0,F134=E134),0,IF(AND(ISNUMBER(F134),ISNUMBER(E134),E134&gt;0,F134=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K134" s="50" t="str">
-        <x:f>IF(A134="","",IF(AND(ISNUMBER(E134),E134=0,OR(ISNUMBER(SEARCH("Free",D134&amp;"")),AND(ISNUMBER(F134),F134=0))),"Subscription",IF(ISNUMBER(G134),"Profit",IF(ISNUMBER(I134),"Loss",IF(ISNUMBER(H134),"Draw",IF(AND(ISNUMBER(F134),ISNUMBER(E134),E134&gt;0,F134&gt;E134),"Profit",IF(AND(ISNUMBER(F134),ISNUMBER(E134),E134&gt;0,F134=E134),"Draw",IF(AND(ISNUMBER(F134),ISNUMBER(E134),E134&gt;0,F134=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A134="","",IF(AND(ISNUMBER(E134),E134=0,OR(ISNUMBER(SEARCH("Free",D134&amp;"")),AND(ISNUMBER(F134),F134=0))),"Subscription",IF(ISNUMBER(G134),"Profit",IF(ISNUMBER(I134),"Disqualified",IF(ISNUMBER(H134),"Draw",IF(AND(ISNUMBER(F134),ISNUMBER(E134),E134&gt;0,F134&gt;E134),"Profit",IF(AND(ISNUMBER(F134),ISNUMBER(E134),E134&gt;0,F134=E134),"Draw",IF(AND(ISNUMBER(F134),ISNUMBER(E134),E134&gt;0,F134=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L134" s="50"/>
       <x:c r="M134" s="58"/>
@@ -6353,7 +6366,7 @@
         <x:f>IF(A135="","",IF(K135="Subscription","",IF(E135=0,"",IF(ISNUMBER(G135),G135/E135,IF(ISNUMBER(I135),-ABS(I135)/E135,IF(ISNUMBER(H135),0,IF(AND(ISNUMBER(F135),ISNUMBER(E135),E135&gt;0,F135&gt;E135),(F135-E135)/E135,IF(AND(ISNUMBER(F135),ISNUMBER(E135),E135&gt;0,F135=E135),0,IF(AND(ISNUMBER(F135),ISNUMBER(E135),E135&gt;0,F135=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K135" s="50" t="str">
-        <x:f>IF(A135="","",IF(AND(ISNUMBER(E135),E135=0,OR(ISNUMBER(SEARCH("Free",D135&amp;"")),AND(ISNUMBER(F135),F135=0))),"Subscription",IF(ISNUMBER(G135),"Profit",IF(ISNUMBER(I135),"Loss",IF(ISNUMBER(H135),"Draw",IF(AND(ISNUMBER(F135),ISNUMBER(E135),E135&gt;0,F135&gt;E135),"Profit",IF(AND(ISNUMBER(F135),ISNUMBER(E135),E135&gt;0,F135=E135),"Draw",IF(AND(ISNUMBER(F135),ISNUMBER(E135),E135&gt;0,F135=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A135="","",IF(AND(ISNUMBER(E135),E135=0,OR(ISNUMBER(SEARCH("Free",D135&amp;"")),AND(ISNUMBER(F135),F135=0))),"Subscription",IF(ISNUMBER(G135),"Profit",IF(ISNUMBER(I135),"Disqualified",IF(ISNUMBER(H135),"Draw",IF(AND(ISNUMBER(F135),ISNUMBER(E135),E135&gt;0,F135&gt;E135),"Profit",IF(AND(ISNUMBER(F135),ISNUMBER(E135),E135&gt;0,F135=E135),"Draw",IF(AND(ISNUMBER(F135),ISNUMBER(E135),E135&gt;0,F135=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L135" s="50"/>
       <x:c r="M135" s="58"/>
@@ -6390,7 +6403,7 @@
         <x:f>IF(A136="","",IF(K136="Subscription","",IF(E136=0,"",IF(ISNUMBER(G136),G136/E136,IF(ISNUMBER(I136),-ABS(I136)/E136,IF(ISNUMBER(H136),0,IF(AND(ISNUMBER(F136),ISNUMBER(E136),E136&gt;0,F136&gt;E136),(F136-E136)/E136,IF(AND(ISNUMBER(F136),ISNUMBER(E136),E136&gt;0,F136=E136),0,IF(AND(ISNUMBER(F136),ISNUMBER(E136),E136&gt;0,F136=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K136" s="50" t="str">
-        <x:f>IF(A136="","",IF(AND(ISNUMBER(E136),E136=0,OR(ISNUMBER(SEARCH("Free",D136&amp;"")),AND(ISNUMBER(F136),F136=0))),"Subscription",IF(ISNUMBER(G136),"Profit",IF(ISNUMBER(I136),"Loss",IF(ISNUMBER(H136),"Draw",IF(AND(ISNUMBER(F136),ISNUMBER(E136),E136&gt;0,F136&gt;E136),"Profit",IF(AND(ISNUMBER(F136),ISNUMBER(E136),E136&gt;0,F136=E136),"Draw",IF(AND(ISNUMBER(F136),ISNUMBER(E136),E136&gt;0,F136=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A136="","",IF(AND(ISNUMBER(E136),E136=0,OR(ISNUMBER(SEARCH("Free",D136&amp;"")),AND(ISNUMBER(F136),F136=0))),"Subscription",IF(ISNUMBER(G136),"Profit",IF(ISNUMBER(I136),"Disqualified",IF(ISNUMBER(H136),"Draw",IF(AND(ISNUMBER(F136),ISNUMBER(E136),E136&gt;0,F136&gt;E136),"Profit",IF(AND(ISNUMBER(F136),ISNUMBER(E136),E136&gt;0,F136=E136),"Draw",IF(AND(ISNUMBER(F136),ISNUMBER(E136),E136&gt;0,F136=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L136" s="50"/>
       <x:c r="M136" s="58"/>
@@ -6427,7 +6440,7 @@
         <x:f>IF(A137="","",IF(K137="Subscription","",IF(E137=0,"",IF(ISNUMBER(G137),G137/E137,IF(ISNUMBER(I137),-ABS(I137)/E137,IF(ISNUMBER(H137),0,IF(AND(ISNUMBER(F137),ISNUMBER(E137),E137&gt;0,F137&gt;E137),(F137-E137)/E137,IF(AND(ISNUMBER(F137),ISNUMBER(E137),E137&gt;0,F137=E137),0,IF(AND(ISNUMBER(F137),ISNUMBER(E137),E137&gt;0,F137=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K137" s="50" t="str">
-        <x:f>IF(A137="","",IF(AND(ISNUMBER(E137),E137=0,OR(ISNUMBER(SEARCH("Free",D137&amp;"")),AND(ISNUMBER(F137),F137=0))),"Subscription",IF(ISNUMBER(G137),"Profit",IF(ISNUMBER(I137),"Loss",IF(ISNUMBER(H137),"Draw",IF(AND(ISNUMBER(F137),ISNUMBER(E137),E137&gt;0,F137&gt;E137),"Profit",IF(AND(ISNUMBER(F137),ISNUMBER(E137),E137&gt;0,F137=E137),"Draw",IF(AND(ISNUMBER(F137),ISNUMBER(E137),E137&gt;0,F137=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A137="","",IF(AND(ISNUMBER(E137),E137=0,OR(ISNUMBER(SEARCH("Free",D137&amp;"")),AND(ISNUMBER(F137),F137=0))),"Subscription",IF(ISNUMBER(G137),"Profit",IF(ISNUMBER(I137),"Disqualified",IF(ISNUMBER(H137),"Draw",IF(AND(ISNUMBER(F137),ISNUMBER(E137),E137&gt;0,F137&gt;E137),"Profit",IF(AND(ISNUMBER(F137),ISNUMBER(E137),E137&gt;0,F137=E137),"Draw",IF(AND(ISNUMBER(F137),ISNUMBER(E137),E137&gt;0,F137=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L137" s="50"/>
       <x:c r="M137" s="58"/>
@@ -6464,7 +6477,7 @@
         <x:f>IF(A138="","",IF(K138="Subscription","",IF(E138=0,"",IF(ISNUMBER(G138),G138/E138,IF(ISNUMBER(I138),-ABS(I138)/E138,IF(ISNUMBER(H138),0,IF(AND(ISNUMBER(F138),ISNUMBER(E138),E138&gt;0,F138&gt;E138),(F138-E138)/E138,IF(AND(ISNUMBER(F138),ISNUMBER(E138),E138&gt;0,F138=E138),0,IF(AND(ISNUMBER(F138),ISNUMBER(E138),E138&gt;0,F138=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K138" s="50" t="str">
-        <x:f>IF(A138="","",IF(AND(ISNUMBER(E138),E138=0,OR(ISNUMBER(SEARCH("Free",D138&amp;"")),AND(ISNUMBER(F138),F138=0))),"Subscription",IF(ISNUMBER(G138),"Profit",IF(ISNUMBER(I138),"Loss",IF(ISNUMBER(H138),"Draw",IF(AND(ISNUMBER(F138),ISNUMBER(E138),E138&gt;0,F138&gt;E138),"Profit",IF(AND(ISNUMBER(F138),ISNUMBER(E138),E138&gt;0,F138=E138),"Draw",IF(AND(ISNUMBER(F138),ISNUMBER(E138),E138&gt;0,F138=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A138="","",IF(AND(ISNUMBER(E138),E138=0,OR(ISNUMBER(SEARCH("Free",D138&amp;"")),AND(ISNUMBER(F138),F138=0))),"Subscription",IF(ISNUMBER(G138),"Profit",IF(ISNUMBER(I138),"Disqualified",IF(ISNUMBER(H138),"Draw",IF(AND(ISNUMBER(F138),ISNUMBER(E138),E138&gt;0,F138&gt;E138),"Profit",IF(AND(ISNUMBER(F138),ISNUMBER(E138),E138&gt;0,F138=E138),"Draw",IF(AND(ISNUMBER(F138),ISNUMBER(E138),E138&gt;0,F138=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L138" s="50"/>
       <x:c r="M138" s="58"/>
@@ -6501,7 +6514,7 @@
         <x:f>IF(A139="","",IF(K139="Subscription","",IF(E139=0,"",IF(ISNUMBER(G139),G139/E139,IF(ISNUMBER(I139),-ABS(I139)/E139,IF(ISNUMBER(H139),0,IF(AND(ISNUMBER(F139),ISNUMBER(E139),E139&gt;0,F139&gt;E139),(F139-E139)/E139,IF(AND(ISNUMBER(F139),ISNUMBER(E139),E139&gt;0,F139=E139),0,IF(AND(ISNUMBER(F139),ISNUMBER(E139),E139&gt;0,F139=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K139" s="50" t="str">
-        <x:f>IF(A139="","",IF(AND(ISNUMBER(E139),E139=0,OR(ISNUMBER(SEARCH("Free",D139&amp;"")),AND(ISNUMBER(F139),F139=0))),"Subscription",IF(ISNUMBER(G139),"Profit",IF(ISNUMBER(I139),"Loss",IF(ISNUMBER(H139),"Draw",IF(AND(ISNUMBER(F139),ISNUMBER(E139),E139&gt;0,F139&gt;E139),"Profit",IF(AND(ISNUMBER(F139),ISNUMBER(E139),E139&gt;0,F139=E139),"Draw",IF(AND(ISNUMBER(F139),ISNUMBER(E139),E139&gt;0,F139=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A139="","",IF(AND(ISNUMBER(E139),E139=0,OR(ISNUMBER(SEARCH("Free",D139&amp;"")),AND(ISNUMBER(F139),F139=0))),"Subscription",IF(ISNUMBER(G139),"Profit",IF(ISNUMBER(I139),"Disqualified",IF(ISNUMBER(H139),"Draw",IF(AND(ISNUMBER(F139),ISNUMBER(E139),E139&gt;0,F139&gt;E139),"Profit",IF(AND(ISNUMBER(F139),ISNUMBER(E139),E139&gt;0,F139=E139),"Draw",IF(AND(ISNUMBER(F139),ISNUMBER(E139),E139&gt;0,F139=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L139" s="50"/>
       <x:c r="M139" s="58"/>
@@ -6538,7 +6551,7 @@
         <x:f>IF(A140="","",IF(K140="Subscription","",IF(E140=0,"",IF(ISNUMBER(G140),G140/E140,IF(ISNUMBER(I140),-ABS(I140)/E140,IF(ISNUMBER(H140),0,IF(AND(ISNUMBER(F140),ISNUMBER(E140),E140&gt;0,F140&gt;E140),(F140-E140)/E140,IF(AND(ISNUMBER(F140),ISNUMBER(E140),E140&gt;0,F140=E140),0,IF(AND(ISNUMBER(F140),ISNUMBER(E140),E140&gt;0,F140=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K140" s="50" t="str">
-        <x:f>IF(A140="","",IF(AND(ISNUMBER(E140),E140=0,OR(ISNUMBER(SEARCH("Free",D140&amp;"")),AND(ISNUMBER(F140),F140=0))),"Subscription",IF(ISNUMBER(G140),"Profit",IF(ISNUMBER(I140),"Loss",IF(ISNUMBER(H140),"Draw",IF(AND(ISNUMBER(F140),ISNUMBER(E140),E140&gt;0,F140&gt;E140),"Profit",IF(AND(ISNUMBER(F140),ISNUMBER(E140),E140&gt;0,F140=E140),"Draw",IF(AND(ISNUMBER(F140),ISNUMBER(E140),E140&gt;0,F140=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A140="","",IF(AND(ISNUMBER(E140),E140=0,OR(ISNUMBER(SEARCH("Free",D140&amp;"")),AND(ISNUMBER(F140),F140=0))),"Subscription",IF(ISNUMBER(G140),"Profit",IF(ISNUMBER(I140),"Disqualified",IF(ISNUMBER(H140),"Draw",IF(AND(ISNUMBER(F140),ISNUMBER(E140),E140&gt;0,F140&gt;E140),"Profit",IF(AND(ISNUMBER(F140),ISNUMBER(E140),E140&gt;0,F140=E140),"Draw",IF(AND(ISNUMBER(F140),ISNUMBER(E140),E140&gt;0,F140=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L140" s="50"/>
       <x:c r="M140" s="58"/>
@@ -6575,7 +6588,7 @@
         <x:f>IF(A141="","",IF(K141="Subscription","",IF(E141=0,"",IF(ISNUMBER(G141),G141/E141,IF(ISNUMBER(I141),-ABS(I141)/E141,IF(ISNUMBER(H141),0,IF(AND(ISNUMBER(F141),ISNUMBER(E141),E141&gt;0,F141&gt;E141),(F141-E141)/E141,IF(AND(ISNUMBER(F141),ISNUMBER(E141),E141&gt;0,F141=E141),0,IF(AND(ISNUMBER(F141),ISNUMBER(E141),E141&gt;0,F141=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K141" s="50" t="str">
-        <x:f>IF(A141="","",IF(AND(ISNUMBER(E141),E141=0,OR(ISNUMBER(SEARCH("Free",D141&amp;"")),AND(ISNUMBER(F141),F141=0))),"Subscription",IF(ISNUMBER(G141),"Profit",IF(ISNUMBER(I141),"Loss",IF(ISNUMBER(H141),"Draw",IF(AND(ISNUMBER(F141),ISNUMBER(E141),E141&gt;0,F141&gt;E141),"Profit",IF(AND(ISNUMBER(F141),ISNUMBER(E141),E141&gt;0,F141=E141),"Draw",IF(AND(ISNUMBER(F141),ISNUMBER(E141),E141&gt;0,F141=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A141="","",IF(AND(ISNUMBER(E141),E141=0,OR(ISNUMBER(SEARCH("Free",D141&amp;"")),AND(ISNUMBER(F141),F141=0))),"Subscription",IF(ISNUMBER(G141),"Profit",IF(ISNUMBER(I141),"Disqualified",IF(ISNUMBER(H141),"Draw",IF(AND(ISNUMBER(F141),ISNUMBER(E141),E141&gt;0,F141&gt;E141),"Profit",IF(AND(ISNUMBER(F141),ISNUMBER(E141),E141&gt;0,F141=E141),"Draw",IF(AND(ISNUMBER(F141),ISNUMBER(E141),E141&gt;0,F141=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L141" s="50"/>
       <x:c r="M141" s="58"/>
@@ -6612,7 +6625,7 @@
         <x:f>IF(A142="","",IF(K142="Subscription","",IF(E142=0,"",IF(ISNUMBER(G142),G142/E142,IF(ISNUMBER(I142),-ABS(I142)/E142,IF(ISNUMBER(H142),0,IF(AND(ISNUMBER(F142),ISNUMBER(E142),E142&gt;0,F142&gt;E142),(F142-E142)/E142,IF(AND(ISNUMBER(F142),ISNUMBER(E142),E142&gt;0,F142=E142),0,IF(AND(ISNUMBER(F142),ISNUMBER(E142),E142&gt;0,F142=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K142" s="50" t="str">
-        <x:f>IF(A142="","",IF(AND(ISNUMBER(E142),E142=0,OR(ISNUMBER(SEARCH("Free",D142&amp;"")),AND(ISNUMBER(F142),F142=0))),"Subscription",IF(ISNUMBER(G142),"Profit",IF(ISNUMBER(I142),"Loss",IF(ISNUMBER(H142),"Draw",IF(AND(ISNUMBER(F142),ISNUMBER(E142),E142&gt;0,F142&gt;E142),"Profit",IF(AND(ISNUMBER(F142),ISNUMBER(E142),E142&gt;0,F142=E142),"Draw",IF(AND(ISNUMBER(F142),ISNUMBER(E142),E142&gt;0,F142=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A142="","",IF(AND(ISNUMBER(E142),E142=0,OR(ISNUMBER(SEARCH("Free",D142&amp;"")),AND(ISNUMBER(F142),F142=0))),"Subscription",IF(ISNUMBER(G142),"Profit",IF(ISNUMBER(I142),"Disqualified",IF(ISNUMBER(H142),"Draw",IF(AND(ISNUMBER(F142),ISNUMBER(E142),E142&gt;0,F142&gt;E142),"Profit",IF(AND(ISNUMBER(F142),ISNUMBER(E142),E142&gt;0,F142=E142),"Draw",IF(AND(ISNUMBER(F142),ISNUMBER(E142),E142&gt;0,F142=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L142" s="50"/>
       <x:c r="M142" s="58"/>
@@ -6649,7 +6662,7 @@
         <x:f>IF(A143="","",IF(K143="Subscription","",IF(E143=0,"",IF(ISNUMBER(G143),G143/E143,IF(ISNUMBER(I143),-ABS(I143)/E143,IF(ISNUMBER(H143),0,IF(AND(ISNUMBER(F143),ISNUMBER(E143),E143&gt;0,F143&gt;E143),(F143-E143)/E143,IF(AND(ISNUMBER(F143),ISNUMBER(E143),E143&gt;0,F143=E143),0,IF(AND(ISNUMBER(F143),ISNUMBER(E143),E143&gt;0,F143=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K143" s="50" t="str">
-        <x:f>IF(A143="","",IF(AND(ISNUMBER(E143),E143=0,OR(ISNUMBER(SEARCH("Free",D143&amp;"")),AND(ISNUMBER(F143),F143=0))),"Subscription",IF(ISNUMBER(G143),"Profit",IF(ISNUMBER(I143),"Loss",IF(ISNUMBER(H143),"Draw",IF(AND(ISNUMBER(F143),ISNUMBER(E143),E143&gt;0,F143&gt;E143),"Profit",IF(AND(ISNUMBER(F143),ISNUMBER(E143),E143&gt;0,F143=E143),"Draw",IF(AND(ISNUMBER(F143),ISNUMBER(E143),E143&gt;0,F143=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A143="","",IF(AND(ISNUMBER(E143),E143=0,OR(ISNUMBER(SEARCH("Free",D143&amp;"")),AND(ISNUMBER(F143),F143=0))),"Subscription",IF(ISNUMBER(G143),"Profit",IF(ISNUMBER(I143),"Disqualified",IF(ISNUMBER(H143),"Draw",IF(AND(ISNUMBER(F143),ISNUMBER(E143),E143&gt;0,F143&gt;E143),"Profit",IF(AND(ISNUMBER(F143),ISNUMBER(E143),E143&gt;0,F143=E143),"Draw",IF(AND(ISNUMBER(F143),ISNUMBER(E143),E143&gt;0,F143=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L143" s="50"/>
       <x:c r="M143" s="58"/>
@@ -6686,7 +6699,7 @@
         <x:f>IF(A144="","",IF(K144="Subscription","",IF(E144=0,"",IF(ISNUMBER(G144),G144/E144,IF(ISNUMBER(I144),-ABS(I144)/E144,IF(ISNUMBER(H144),0,IF(AND(ISNUMBER(F144),ISNUMBER(E144),E144&gt;0,F144&gt;E144),(F144-E144)/E144,IF(AND(ISNUMBER(F144),ISNUMBER(E144),E144&gt;0,F144=E144),0,IF(AND(ISNUMBER(F144),ISNUMBER(E144),E144&gt;0,F144=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K144" s="50" t="str">
-        <x:f>IF(A144="","",IF(AND(ISNUMBER(E144),E144=0,OR(ISNUMBER(SEARCH("Free",D144&amp;"")),AND(ISNUMBER(F144),F144=0))),"Subscription",IF(ISNUMBER(G144),"Profit",IF(ISNUMBER(I144),"Loss",IF(ISNUMBER(H144),"Draw",IF(AND(ISNUMBER(F144),ISNUMBER(E144),E144&gt;0,F144&gt;E144),"Profit",IF(AND(ISNUMBER(F144),ISNUMBER(E144),E144&gt;0,F144=E144),"Draw",IF(AND(ISNUMBER(F144),ISNUMBER(E144),E144&gt;0,F144=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A144="","",IF(AND(ISNUMBER(E144),E144=0,OR(ISNUMBER(SEARCH("Free",D144&amp;"")),AND(ISNUMBER(F144),F144=0))),"Subscription",IF(ISNUMBER(G144),"Profit",IF(ISNUMBER(I144),"Disqualified",IF(ISNUMBER(H144),"Draw",IF(AND(ISNUMBER(F144),ISNUMBER(E144),E144&gt;0,F144&gt;E144),"Profit",IF(AND(ISNUMBER(F144),ISNUMBER(E144),E144&gt;0,F144=E144),"Draw",IF(AND(ISNUMBER(F144),ISNUMBER(E144),E144&gt;0,F144=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L144" s="50"/>
       <x:c r="M144" s="58"/>
@@ -6723,7 +6736,7 @@
         <x:f>IF(A145="","",IF(K145="Subscription","",IF(E145=0,"",IF(ISNUMBER(G145),G145/E145,IF(ISNUMBER(I145),-ABS(I145)/E145,IF(ISNUMBER(H145),0,IF(AND(ISNUMBER(F145),ISNUMBER(E145),E145&gt;0,F145&gt;E145),(F145-E145)/E145,IF(AND(ISNUMBER(F145),ISNUMBER(E145),E145&gt;0,F145=E145),0,IF(AND(ISNUMBER(F145),ISNUMBER(E145),E145&gt;0,F145=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K145" s="50" t="str">
-        <x:f>IF(A145="","",IF(AND(ISNUMBER(E145),E145=0,OR(ISNUMBER(SEARCH("Free",D145&amp;"")),AND(ISNUMBER(F145),F145=0))),"Subscription",IF(ISNUMBER(G145),"Profit",IF(ISNUMBER(I145),"Loss",IF(ISNUMBER(H145),"Draw",IF(AND(ISNUMBER(F145),ISNUMBER(E145),E145&gt;0,F145&gt;E145),"Profit",IF(AND(ISNUMBER(F145),ISNUMBER(E145),E145&gt;0,F145=E145),"Draw",IF(AND(ISNUMBER(F145),ISNUMBER(E145),E145&gt;0,F145=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A145="","",IF(AND(ISNUMBER(E145),E145=0,OR(ISNUMBER(SEARCH("Free",D145&amp;"")),AND(ISNUMBER(F145),F145=0))),"Subscription",IF(ISNUMBER(G145),"Profit",IF(ISNUMBER(I145),"Disqualified",IF(ISNUMBER(H145),"Draw",IF(AND(ISNUMBER(F145),ISNUMBER(E145),E145&gt;0,F145&gt;E145),"Profit",IF(AND(ISNUMBER(F145),ISNUMBER(E145),E145&gt;0,F145=E145),"Draw",IF(AND(ISNUMBER(F145),ISNUMBER(E145),E145&gt;0,F145=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L145" s="50"/>
       <x:c r="M145" s="58"/>
@@ -6760,7 +6773,7 @@
         <x:f>IF(A146="","",IF(K146="Subscription","",IF(E146=0,"",IF(ISNUMBER(G146),G146/E146,IF(ISNUMBER(I146),-ABS(I146)/E146,IF(ISNUMBER(H146),0,IF(AND(ISNUMBER(F146),ISNUMBER(E146),E146&gt;0,F146&gt;E146),(F146-E146)/E146,IF(AND(ISNUMBER(F146),ISNUMBER(E146),E146&gt;0,F146=E146),0,IF(AND(ISNUMBER(F146),ISNUMBER(E146),E146&gt;0,F146=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K146" s="50" t="str">
-        <x:f>IF(A146="","",IF(AND(ISNUMBER(E146),E146=0,OR(ISNUMBER(SEARCH("Free",D146&amp;"")),AND(ISNUMBER(F146),F146=0))),"Subscription",IF(ISNUMBER(G146),"Profit",IF(ISNUMBER(I146),"Loss",IF(ISNUMBER(H146),"Draw",IF(AND(ISNUMBER(F146),ISNUMBER(E146),E146&gt;0,F146&gt;E146),"Profit",IF(AND(ISNUMBER(F146),ISNUMBER(E146),E146&gt;0,F146=E146),"Draw",IF(AND(ISNUMBER(F146),ISNUMBER(E146),E146&gt;0,F146=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A146="","",IF(AND(ISNUMBER(E146),E146=0,OR(ISNUMBER(SEARCH("Free",D146&amp;"")),AND(ISNUMBER(F146),F146=0))),"Subscription",IF(ISNUMBER(G146),"Profit",IF(ISNUMBER(I146),"Disqualified",IF(ISNUMBER(H146),"Draw",IF(AND(ISNUMBER(F146),ISNUMBER(E146),E146&gt;0,F146&gt;E146),"Profit",IF(AND(ISNUMBER(F146),ISNUMBER(E146),E146&gt;0,F146=E146),"Draw",IF(AND(ISNUMBER(F146),ISNUMBER(E146),E146&gt;0,F146=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L146" s="50"/>
       <x:c r="M146" s="58"/>
@@ -6797,7 +6810,7 @@
         <x:f>IF(A147="","",IF(K147="Subscription","",IF(E147=0,"",IF(ISNUMBER(G147),G147/E147,IF(ISNUMBER(I147),-ABS(I147)/E147,IF(ISNUMBER(H147),0,IF(AND(ISNUMBER(F147),ISNUMBER(E147),E147&gt;0,F147&gt;E147),(F147-E147)/E147,IF(AND(ISNUMBER(F147),ISNUMBER(E147),E147&gt;0,F147=E147),0,IF(AND(ISNUMBER(F147),ISNUMBER(E147),E147&gt;0,F147=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K147" s="50" t="str">
-        <x:f>IF(A147="","",IF(AND(ISNUMBER(E147),E147=0,OR(ISNUMBER(SEARCH("Free",D147&amp;"")),AND(ISNUMBER(F147),F147=0))),"Subscription",IF(ISNUMBER(G147),"Profit",IF(ISNUMBER(I147),"Loss",IF(ISNUMBER(H147),"Draw",IF(AND(ISNUMBER(F147),ISNUMBER(E147),E147&gt;0,F147&gt;E147),"Profit",IF(AND(ISNUMBER(F147),ISNUMBER(E147),E147&gt;0,F147=E147),"Draw",IF(AND(ISNUMBER(F147),ISNUMBER(E147),E147&gt;0,F147=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A147="","",IF(AND(ISNUMBER(E147),E147=0,OR(ISNUMBER(SEARCH("Free",D147&amp;"")),AND(ISNUMBER(F147),F147=0))),"Subscription",IF(ISNUMBER(G147),"Profit",IF(ISNUMBER(I147),"Disqualified",IF(ISNUMBER(H147),"Draw",IF(AND(ISNUMBER(F147),ISNUMBER(E147),E147&gt;0,F147&gt;E147),"Profit",IF(AND(ISNUMBER(F147),ISNUMBER(E147),E147&gt;0,F147=E147),"Draw",IF(AND(ISNUMBER(F147),ISNUMBER(E147),E147&gt;0,F147=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L147" s="50"/>
       <x:c r="M147" s="58"/>
@@ -6834,7 +6847,7 @@
         <x:f>IF(A148="","",IF(K148="Subscription","",IF(E148=0,"",IF(ISNUMBER(G148),G148/E148,IF(ISNUMBER(I148),-ABS(I148)/E148,IF(ISNUMBER(H148),0,IF(AND(ISNUMBER(F148),ISNUMBER(E148),E148&gt;0,F148&gt;E148),(F148-E148)/E148,IF(AND(ISNUMBER(F148),ISNUMBER(E148),E148&gt;0,F148=E148),0,IF(AND(ISNUMBER(F148),ISNUMBER(E148),E148&gt;0,F148=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K148" s="50" t="str">
-        <x:f>IF(A148="","",IF(AND(ISNUMBER(E148),E148=0,OR(ISNUMBER(SEARCH("Free",D148&amp;"")),AND(ISNUMBER(F148),F148=0))),"Subscription",IF(ISNUMBER(G148),"Profit",IF(ISNUMBER(I148),"Loss",IF(ISNUMBER(H148),"Draw",IF(AND(ISNUMBER(F148),ISNUMBER(E148),E148&gt;0,F148&gt;E148),"Profit",IF(AND(ISNUMBER(F148),ISNUMBER(E148),E148&gt;0,F148=E148),"Draw",IF(AND(ISNUMBER(F148),ISNUMBER(E148),E148&gt;0,F148=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A148="","",IF(AND(ISNUMBER(E148),E148=0,OR(ISNUMBER(SEARCH("Free",D148&amp;"")),AND(ISNUMBER(F148),F148=0))),"Subscription",IF(ISNUMBER(G148),"Profit",IF(ISNUMBER(I148),"Disqualified",IF(ISNUMBER(H148),"Draw",IF(AND(ISNUMBER(F148),ISNUMBER(E148),E148&gt;0,F148&gt;E148),"Profit",IF(AND(ISNUMBER(F148),ISNUMBER(E148),E148&gt;0,F148=E148),"Draw",IF(AND(ISNUMBER(F148),ISNUMBER(E148),E148&gt;0,F148=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L148" s="50"/>
       <x:c r="M148" s="58"/>
@@ -6871,7 +6884,7 @@
         <x:f>IF(A149="","",IF(K149="Subscription","",IF(E149=0,"",IF(ISNUMBER(G149),G149/E149,IF(ISNUMBER(I149),-ABS(I149)/E149,IF(ISNUMBER(H149),0,IF(AND(ISNUMBER(F149),ISNUMBER(E149),E149&gt;0,F149&gt;E149),(F149-E149)/E149,IF(AND(ISNUMBER(F149),ISNUMBER(E149),E149&gt;0,F149=E149),0,IF(AND(ISNUMBER(F149),ISNUMBER(E149),E149&gt;0,F149=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K149" s="50" t="str">
-        <x:f>IF(A149="","",IF(AND(ISNUMBER(E149),E149=0,OR(ISNUMBER(SEARCH("Free",D149&amp;"")),AND(ISNUMBER(F149),F149=0))),"Subscription",IF(ISNUMBER(G149),"Profit",IF(ISNUMBER(I149),"Loss",IF(ISNUMBER(H149),"Draw",IF(AND(ISNUMBER(F149),ISNUMBER(E149),E149&gt;0,F149&gt;E149),"Profit",IF(AND(ISNUMBER(F149),ISNUMBER(E149),E149&gt;0,F149=E149),"Draw",IF(AND(ISNUMBER(F149),ISNUMBER(E149),E149&gt;0,F149=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A149="","",IF(AND(ISNUMBER(E149),E149=0,OR(ISNUMBER(SEARCH("Free",D149&amp;"")),AND(ISNUMBER(F149),F149=0))),"Subscription",IF(ISNUMBER(G149),"Profit",IF(ISNUMBER(I149),"Disqualified",IF(ISNUMBER(H149),"Draw",IF(AND(ISNUMBER(F149),ISNUMBER(E149),E149&gt;0,F149&gt;E149),"Profit",IF(AND(ISNUMBER(F149),ISNUMBER(E149),E149&gt;0,F149=E149),"Draw",IF(AND(ISNUMBER(F149),ISNUMBER(E149),E149&gt;0,F149=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L149" s="50"/>
       <x:c r="M149" s="58"/>
@@ -6908,7 +6921,7 @@
         <x:f>IF(A150="","",IF(K150="Subscription","",IF(E150=0,"",IF(ISNUMBER(G150),G150/E150,IF(ISNUMBER(I150),-ABS(I150)/E150,IF(ISNUMBER(H150),0,IF(AND(ISNUMBER(F150),ISNUMBER(E150),E150&gt;0,F150&gt;E150),(F150-E150)/E150,IF(AND(ISNUMBER(F150),ISNUMBER(E150),E150&gt;0,F150=E150),0,IF(AND(ISNUMBER(F150),ISNUMBER(E150),E150&gt;0,F150=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K150" s="50" t="str">
-        <x:f>IF(A150="","",IF(AND(ISNUMBER(E150),E150=0,OR(ISNUMBER(SEARCH("Free",D150&amp;"")),AND(ISNUMBER(F150),F150=0))),"Subscription",IF(ISNUMBER(G150),"Profit",IF(ISNUMBER(I150),"Loss",IF(ISNUMBER(H150),"Draw",IF(AND(ISNUMBER(F150),ISNUMBER(E150),E150&gt;0,F150&gt;E150),"Profit",IF(AND(ISNUMBER(F150),ISNUMBER(E150),E150&gt;0,F150=E150),"Draw",IF(AND(ISNUMBER(F150),ISNUMBER(E150),E150&gt;0,F150=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A150="","",IF(AND(ISNUMBER(E150),E150=0,OR(ISNUMBER(SEARCH("Free",D150&amp;"")),AND(ISNUMBER(F150),F150=0))),"Subscription",IF(ISNUMBER(G150),"Profit",IF(ISNUMBER(I150),"Disqualified",IF(ISNUMBER(H150),"Draw",IF(AND(ISNUMBER(F150),ISNUMBER(E150),E150&gt;0,F150&gt;E150),"Profit",IF(AND(ISNUMBER(F150),ISNUMBER(E150),E150&gt;0,F150=E150),"Draw",IF(AND(ISNUMBER(F150),ISNUMBER(E150),E150&gt;0,F150=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L150" s="50"/>
       <x:c r="M150" s="58"/>
@@ -6945,7 +6958,7 @@
         <x:f>IF(A151="","",IF(K151="Subscription","",IF(E151=0,"",IF(ISNUMBER(G151),G151/E151,IF(ISNUMBER(I151),-ABS(I151)/E151,IF(ISNUMBER(H151),0,IF(AND(ISNUMBER(F151),ISNUMBER(E151),E151&gt;0,F151&gt;E151),(F151-E151)/E151,IF(AND(ISNUMBER(F151),ISNUMBER(E151),E151&gt;0,F151=E151),0,IF(AND(ISNUMBER(F151),ISNUMBER(E151),E151&gt;0,F151=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K151" s="50" t="str">
-        <x:f>IF(A151="","",IF(AND(ISNUMBER(E151),E151=0,OR(ISNUMBER(SEARCH("Free",D151&amp;"")),AND(ISNUMBER(F151),F151=0))),"Subscription",IF(ISNUMBER(G151),"Profit",IF(ISNUMBER(I151),"Loss",IF(ISNUMBER(H151),"Draw",IF(AND(ISNUMBER(F151),ISNUMBER(E151),E151&gt;0,F151&gt;E151),"Profit",IF(AND(ISNUMBER(F151),ISNUMBER(E151),E151&gt;0,F151=E151),"Draw",IF(AND(ISNUMBER(F151),ISNUMBER(E151),E151&gt;0,F151=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A151="","",IF(AND(ISNUMBER(E151),E151=0,OR(ISNUMBER(SEARCH("Free",D151&amp;"")),AND(ISNUMBER(F151),F151=0))),"Subscription",IF(ISNUMBER(G151),"Profit",IF(ISNUMBER(I151),"Disqualified",IF(ISNUMBER(H151),"Draw",IF(AND(ISNUMBER(F151),ISNUMBER(E151),E151&gt;0,F151&gt;E151),"Profit",IF(AND(ISNUMBER(F151),ISNUMBER(E151),E151&gt;0,F151=E151),"Draw",IF(AND(ISNUMBER(F151),ISNUMBER(E151),E151&gt;0,F151=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L151" s="50"/>
       <x:c r="M151" s="58"/>
@@ -6982,7 +6995,7 @@
         <x:f>IF(A152="","",IF(K152="Subscription","",IF(E152=0,"",IF(ISNUMBER(G152),G152/E152,IF(ISNUMBER(I152),-ABS(I152)/E152,IF(ISNUMBER(H152),0,IF(AND(ISNUMBER(F152),ISNUMBER(E152),E152&gt;0,F152&gt;E152),(F152-E152)/E152,IF(AND(ISNUMBER(F152),ISNUMBER(E152),E152&gt;0,F152=E152),0,IF(AND(ISNUMBER(F152),ISNUMBER(E152),E152&gt;0,F152=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K152" s="50" t="str">
-        <x:f>IF(A152="","",IF(AND(ISNUMBER(E152),E152=0,OR(ISNUMBER(SEARCH("Free",D152&amp;"")),AND(ISNUMBER(F152),F152=0))),"Subscription",IF(ISNUMBER(G152),"Profit",IF(ISNUMBER(I152),"Loss",IF(ISNUMBER(H152),"Draw",IF(AND(ISNUMBER(F152),ISNUMBER(E152),E152&gt;0,F152&gt;E152),"Profit",IF(AND(ISNUMBER(F152),ISNUMBER(E152),E152&gt;0,F152=E152),"Draw",IF(AND(ISNUMBER(F152),ISNUMBER(E152),E152&gt;0,F152=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A152="","",IF(AND(ISNUMBER(E152),E152=0,OR(ISNUMBER(SEARCH("Free",D152&amp;"")),AND(ISNUMBER(F152),F152=0))),"Subscription",IF(ISNUMBER(G152),"Profit",IF(ISNUMBER(I152),"Disqualified",IF(ISNUMBER(H152),"Draw",IF(AND(ISNUMBER(F152),ISNUMBER(E152),E152&gt;0,F152&gt;E152),"Profit",IF(AND(ISNUMBER(F152),ISNUMBER(E152),E152&gt;0,F152=E152),"Draw",IF(AND(ISNUMBER(F152),ISNUMBER(E152),E152&gt;0,F152=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L152" s="50"/>
       <x:c r="M152" s="58"/>
@@ -7019,7 +7032,7 @@
         <x:f>IF(A153="","",IF(K153="Subscription","",IF(E153=0,"",IF(ISNUMBER(G153),G153/E153,IF(ISNUMBER(I153),-ABS(I153)/E153,IF(ISNUMBER(H153),0,IF(AND(ISNUMBER(F153),ISNUMBER(E153),E153&gt;0,F153&gt;E153),(F153-E153)/E153,IF(AND(ISNUMBER(F153),ISNUMBER(E153),E153&gt;0,F153=E153),0,IF(AND(ISNUMBER(F153),ISNUMBER(E153),E153&gt;0,F153=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K153" s="50" t="str">
-        <x:f>IF(A153="","",IF(AND(ISNUMBER(E153),E153=0,OR(ISNUMBER(SEARCH("Free",D153&amp;"")),AND(ISNUMBER(F153),F153=0))),"Subscription",IF(ISNUMBER(G153),"Profit",IF(ISNUMBER(I153),"Loss",IF(ISNUMBER(H153),"Draw",IF(AND(ISNUMBER(F153),ISNUMBER(E153),E153&gt;0,F153&gt;E153),"Profit",IF(AND(ISNUMBER(F153),ISNUMBER(E153),E153&gt;0,F153=E153),"Draw",IF(AND(ISNUMBER(F153),ISNUMBER(E153),E153&gt;0,F153=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A153="","",IF(AND(ISNUMBER(E153),E153=0,OR(ISNUMBER(SEARCH("Free",D153&amp;"")),AND(ISNUMBER(F153),F153=0))),"Subscription",IF(ISNUMBER(G153),"Profit",IF(ISNUMBER(I153),"Disqualified",IF(ISNUMBER(H153),"Draw",IF(AND(ISNUMBER(F153),ISNUMBER(E153),E153&gt;0,F153&gt;E153),"Profit",IF(AND(ISNUMBER(F153),ISNUMBER(E153),E153&gt;0,F153=E153),"Draw",IF(AND(ISNUMBER(F153),ISNUMBER(E153),E153&gt;0,F153=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L153" s="50"/>
       <x:c r="M153" s="58"/>
@@ -7056,7 +7069,7 @@
         <x:f>IF(A154="","",IF(K154="Subscription","",IF(E154=0,"",IF(ISNUMBER(G154),G154/E154,IF(ISNUMBER(I154),-ABS(I154)/E154,IF(ISNUMBER(H154),0,IF(AND(ISNUMBER(F154),ISNUMBER(E154),E154&gt;0,F154&gt;E154),(F154-E154)/E154,IF(AND(ISNUMBER(F154),ISNUMBER(E154),E154&gt;0,F154=E154),0,IF(AND(ISNUMBER(F154),ISNUMBER(E154),E154&gt;0,F154=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K154" s="50" t="str">
-        <x:f>IF(A154="","",IF(AND(ISNUMBER(E154),E154=0,OR(ISNUMBER(SEARCH("Free",D154&amp;"")),AND(ISNUMBER(F154),F154=0))),"Subscription",IF(ISNUMBER(G154),"Profit",IF(ISNUMBER(I154),"Loss",IF(ISNUMBER(H154),"Draw",IF(AND(ISNUMBER(F154),ISNUMBER(E154),E154&gt;0,F154&gt;E154),"Profit",IF(AND(ISNUMBER(F154),ISNUMBER(E154),E154&gt;0,F154=E154),"Draw",IF(AND(ISNUMBER(F154),ISNUMBER(E154),E154&gt;0,F154=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A154="","",IF(AND(ISNUMBER(E154),E154=0,OR(ISNUMBER(SEARCH("Free",D154&amp;"")),AND(ISNUMBER(F154),F154=0))),"Subscription",IF(ISNUMBER(G154),"Profit",IF(ISNUMBER(I154),"Disqualified",IF(ISNUMBER(H154),"Draw",IF(AND(ISNUMBER(F154),ISNUMBER(E154),E154&gt;0,F154&gt;E154),"Profit",IF(AND(ISNUMBER(F154),ISNUMBER(E154),E154&gt;0,F154=E154),"Draw",IF(AND(ISNUMBER(F154),ISNUMBER(E154),E154&gt;0,F154=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L154" s="50"/>
       <x:c r="M154" s="58"/>
@@ -7093,7 +7106,7 @@
         <x:f>IF(A155="","",IF(K155="Subscription","",IF(E155=0,"",IF(ISNUMBER(G155),G155/E155,IF(ISNUMBER(I155),-ABS(I155)/E155,IF(ISNUMBER(H155),0,IF(AND(ISNUMBER(F155),ISNUMBER(E155),E155&gt;0,F155&gt;E155),(F155-E155)/E155,IF(AND(ISNUMBER(F155),ISNUMBER(E155),E155&gt;0,F155=E155),0,IF(AND(ISNUMBER(F155),ISNUMBER(E155),E155&gt;0,F155=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K155" s="50" t="str">
-        <x:f>IF(A155="","",IF(AND(ISNUMBER(E155),E155=0,OR(ISNUMBER(SEARCH("Free",D155&amp;"")),AND(ISNUMBER(F155),F155=0))),"Subscription",IF(ISNUMBER(G155),"Profit",IF(ISNUMBER(I155),"Loss",IF(ISNUMBER(H155),"Draw",IF(AND(ISNUMBER(F155),ISNUMBER(E155),E155&gt;0,F155&gt;E155),"Profit",IF(AND(ISNUMBER(F155),ISNUMBER(E155),E155&gt;0,F155=E155),"Draw",IF(AND(ISNUMBER(F155),ISNUMBER(E155),E155&gt;0,F155=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A155="","",IF(AND(ISNUMBER(E155),E155=0,OR(ISNUMBER(SEARCH("Free",D155&amp;"")),AND(ISNUMBER(F155),F155=0))),"Subscription",IF(ISNUMBER(G155),"Profit",IF(ISNUMBER(I155),"Disqualified",IF(ISNUMBER(H155),"Draw",IF(AND(ISNUMBER(F155),ISNUMBER(E155),E155&gt;0,F155&gt;E155),"Profit",IF(AND(ISNUMBER(F155),ISNUMBER(E155),E155&gt;0,F155=E155),"Draw",IF(AND(ISNUMBER(F155),ISNUMBER(E155),E155&gt;0,F155=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L155" s="50"/>
       <x:c r="M155" s="58"/>
@@ -7130,7 +7143,7 @@
         <x:f>IF(A156="","",IF(K156="Subscription","",IF(E156=0,"",IF(ISNUMBER(G156),G156/E156,IF(ISNUMBER(I156),-ABS(I156)/E156,IF(ISNUMBER(H156),0,IF(AND(ISNUMBER(F156),ISNUMBER(E156),E156&gt;0,F156&gt;E156),(F156-E156)/E156,IF(AND(ISNUMBER(F156),ISNUMBER(E156),E156&gt;0,F156=E156),0,IF(AND(ISNUMBER(F156),ISNUMBER(E156),E156&gt;0,F156=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K156" s="50" t="str">
-        <x:f>IF(A156="","",IF(AND(ISNUMBER(E156),E156=0,OR(ISNUMBER(SEARCH("Free",D156&amp;"")),AND(ISNUMBER(F156),F156=0))),"Subscription",IF(ISNUMBER(G156),"Profit",IF(ISNUMBER(I156),"Loss",IF(ISNUMBER(H156),"Draw",IF(AND(ISNUMBER(F156),ISNUMBER(E156),E156&gt;0,F156&gt;E156),"Profit",IF(AND(ISNUMBER(F156),ISNUMBER(E156),E156&gt;0,F156=E156),"Draw",IF(AND(ISNUMBER(F156),ISNUMBER(E156),E156&gt;0,F156=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A156="","",IF(AND(ISNUMBER(E156),E156=0,OR(ISNUMBER(SEARCH("Free",D156&amp;"")),AND(ISNUMBER(F156),F156=0))),"Subscription",IF(ISNUMBER(G156),"Profit",IF(ISNUMBER(I156),"Disqualified",IF(ISNUMBER(H156),"Draw",IF(AND(ISNUMBER(F156),ISNUMBER(E156),E156&gt;0,F156&gt;E156),"Profit",IF(AND(ISNUMBER(F156),ISNUMBER(E156),E156&gt;0,F156=E156),"Draw",IF(AND(ISNUMBER(F156),ISNUMBER(E156),E156&gt;0,F156=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L156" s="50"/>
       <x:c r="M156" s="58"/>
@@ -7167,7 +7180,7 @@
         <x:f>IF(A157="","",IF(K157="Subscription","",IF(E157=0,"",IF(ISNUMBER(G157),G157/E157,IF(ISNUMBER(I157),-ABS(I157)/E157,IF(ISNUMBER(H157),0,IF(AND(ISNUMBER(F157),ISNUMBER(E157),E157&gt;0,F157&gt;E157),(F157-E157)/E157,IF(AND(ISNUMBER(F157),ISNUMBER(E157),E157&gt;0,F157=E157),0,IF(AND(ISNUMBER(F157),ISNUMBER(E157),E157&gt;0,F157=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K157" s="50" t="str">
-        <x:f>IF(A157="","",IF(AND(ISNUMBER(E157),E157=0,OR(ISNUMBER(SEARCH("Free",D157&amp;"")),AND(ISNUMBER(F157),F157=0))),"Subscription",IF(ISNUMBER(G157),"Profit",IF(ISNUMBER(I157),"Loss",IF(ISNUMBER(H157),"Draw",IF(AND(ISNUMBER(F157),ISNUMBER(E157),E157&gt;0,F157&gt;E157),"Profit",IF(AND(ISNUMBER(F157),ISNUMBER(E157),E157&gt;0,F157=E157),"Draw",IF(AND(ISNUMBER(F157),ISNUMBER(E157),E157&gt;0,F157=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A157="","",IF(AND(ISNUMBER(E157),E157=0,OR(ISNUMBER(SEARCH("Free",D157&amp;"")),AND(ISNUMBER(F157),F157=0))),"Subscription",IF(ISNUMBER(G157),"Profit",IF(ISNUMBER(I157),"Disqualified",IF(ISNUMBER(H157),"Draw",IF(AND(ISNUMBER(F157),ISNUMBER(E157),E157&gt;0,F157&gt;E157),"Profit",IF(AND(ISNUMBER(F157),ISNUMBER(E157),E157&gt;0,F157=E157),"Draw",IF(AND(ISNUMBER(F157),ISNUMBER(E157),E157&gt;0,F157=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L157" s="50"/>
       <x:c r="M157" s="58"/>
@@ -7204,7 +7217,7 @@
         <x:f>IF(A158="","",IF(K158="Subscription","",IF(E158=0,"",IF(ISNUMBER(G158),G158/E158,IF(ISNUMBER(I158),-ABS(I158)/E158,IF(ISNUMBER(H158),0,IF(AND(ISNUMBER(F158),ISNUMBER(E158),E158&gt;0,F158&gt;E158),(F158-E158)/E158,IF(AND(ISNUMBER(F158),ISNUMBER(E158),E158&gt;0,F158=E158),0,IF(AND(ISNUMBER(F158),ISNUMBER(E158),E158&gt;0,F158=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K158" s="50" t="str">
-        <x:f>IF(A158="","",IF(AND(ISNUMBER(E158),E158=0,OR(ISNUMBER(SEARCH("Free",D158&amp;"")),AND(ISNUMBER(F158),F158=0))),"Subscription",IF(ISNUMBER(G158),"Profit",IF(ISNUMBER(I158),"Loss",IF(ISNUMBER(H158),"Draw",IF(AND(ISNUMBER(F158),ISNUMBER(E158),E158&gt;0,F158&gt;E158),"Profit",IF(AND(ISNUMBER(F158),ISNUMBER(E158),E158&gt;0,F158=E158),"Draw",IF(AND(ISNUMBER(F158),ISNUMBER(E158),E158&gt;0,F158=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A158="","",IF(AND(ISNUMBER(E158),E158=0,OR(ISNUMBER(SEARCH("Free",D158&amp;"")),AND(ISNUMBER(F158),F158=0))),"Subscription",IF(ISNUMBER(G158),"Profit",IF(ISNUMBER(I158),"Disqualified",IF(ISNUMBER(H158),"Draw",IF(AND(ISNUMBER(F158),ISNUMBER(E158),E158&gt;0,F158&gt;E158),"Profit",IF(AND(ISNUMBER(F158),ISNUMBER(E158),E158&gt;0,F158=E158),"Draw",IF(AND(ISNUMBER(F158),ISNUMBER(E158),E158&gt;0,F158=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L158" s="50"/>
       <x:c r="M158" s="58"/>
@@ -7241,7 +7254,7 @@
         <x:f>IF(A159="","",IF(K159="Subscription","",IF(E159=0,"",IF(ISNUMBER(G159),G159/E159,IF(ISNUMBER(I159),-ABS(I159)/E159,IF(ISNUMBER(H159),0,IF(AND(ISNUMBER(F159),ISNUMBER(E159),E159&gt;0,F159&gt;E159),(F159-E159)/E159,IF(AND(ISNUMBER(F159),ISNUMBER(E159),E159&gt;0,F159=E159),0,IF(AND(ISNUMBER(F159),ISNUMBER(E159),E159&gt;0,F159=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K159" s="50" t="str">
-        <x:f>IF(A159="","",IF(AND(ISNUMBER(E159),E159=0,OR(ISNUMBER(SEARCH("Free",D159&amp;"")),AND(ISNUMBER(F159),F159=0))),"Subscription",IF(ISNUMBER(G159),"Profit",IF(ISNUMBER(I159),"Loss",IF(ISNUMBER(H159),"Draw",IF(AND(ISNUMBER(F159),ISNUMBER(E159),E159&gt;0,F159&gt;E159),"Profit",IF(AND(ISNUMBER(F159),ISNUMBER(E159),E159&gt;0,F159=E159),"Draw",IF(AND(ISNUMBER(F159),ISNUMBER(E159),E159&gt;0,F159=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A159="","",IF(AND(ISNUMBER(E159),E159=0,OR(ISNUMBER(SEARCH("Free",D159&amp;"")),AND(ISNUMBER(F159),F159=0))),"Subscription",IF(ISNUMBER(G159),"Profit",IF(ISNUMBER(I159),"Disqualified",IF(ISNUMBER(H159),"Draw",IF(AND(ISNUMBER(F159),ISNUMBER(E159),E159&gt;0,F159&gt;E159),"Profit",IF(AND(ISNUMBER(F159),ISNUMBER(E159),E159&gt;0,F159=E159),"Draw",IF(AND(ISNUMBER(F159),ISNUMBER(E159),E159&gt;0,F159=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L159" s="50"/>
       <x:c r="M159" s="58"/>
@@ -7278,7 +7291,7 @@
         <x:f>IF(A160="","",IF(K160="Subscription","",IF(E160=0,"",IF(ISNUMBER(G160),G160/E160,IF(ISNUMBER(I160),-ABS(I160)/E160,IF(ISNUMBER(H160),0,IF(AND(ISNUMBER(F160),ISNUMBER(E160),E160&gt;0,F160&gt;E160),(F160-E160)/E160,IF(AND(ISNUMBER(F160),ISNUMBER(E160),E160&gt;0,F160=E160),0,IF(AND(ISNUMBER(F160),ISNUMBER(E160),E160&gt;0,F160=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K160" s="50" t="str">
-        <x:f>IF(A160="","",IF(AND(ISNUMBER(E160),E160=0,OR(ISNUMBER(SEARCH("Free",D160&amp;"")),AND(ISNUMBER(F160),F160=0))),"Subscription",IF(ISNUMBER(G160),"Profit",IF(ISNUMBER(I160),"Loss",IF(ISNUMBER(H160),"Draw",IF(AND(ISNUMBER(F160),ISNUMBER(E160),E160&gt;0,F160&gt;E160),"Profit",IF(AND(ISNUMBER(F160),ISNUMBER(E160),E160&gt;0,F160=E160),"Draw",IF(AND(ISNUMBER(F160),ISNUMBER(E160),E160&gt;0,F160=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A160="","",IF(AND(ISNUMBER(E160),E160=0,OR(ISNUMBER(SEARCH("Free",D160&amp;"")),AND(ISNUMBER(F160),F160=0))),"Subscription",IF(ISNUMBER(G160),"Profit",IF(ISNUMBER(I160),"Disqualified",IF(ISNUMBER(H160),"Draw",IF(AND(ISNUMBER(F160),ISNUMBER(E160),E160&gt;0,F160&gt;E160),"Profit",IF(AND(ISNUMBER(F160),ISNUMBER(E160),E160&gt;0,F160=E160),"Draw",IF(AND(ISNUMBER(F160),ISNUMBER(E160),E160&gt;0,F160=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L160" s="50"/>
       <x:c r="M160" s="58"/>
@@ -7315,7 +7328,7 @@
         <x:f>IF(A161="","",IF(K161="Subscription","",IF(E161=0,"",IF(ISNUMBER(G161),G161/E161,IF(ISNUMBER(I161),-ABS(I161)/E161,IF(ISNUMBER(H161),0,IF(AND(ISNUMBER(F161),ISNUMBER(E161),E161&gt;0,F161&gt;E161),(F161-E161)/E161,IF(AND(ISNUMBER(F161),ISNUMBER(E161),E161&gt;0,F161=E161),0,IF(AND(ISNUMBER(F161),ISNUMBER(E161),E161&gt;0,F161=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K161" s="50" t="str">
-        <x:f>IF(A161="","",IF(AND(ISNUMBER(E161),E161=0,OR(ISNUMBER(SEARCH("Free",D161&amp;"")),AND(ISNUMBER(F161),F161=0))),"Subscription",IF(ISNUMBER(G161),"Profit",IF(ISNUMBER(I161),"Loss",IF(ISNUMBER(H161),"Draw",IF(AND(ISNUMBER(F161),ISNUMBER(E161),E161&gt;0,F161&gt;E161),"Profit",IF(AND(ISNUMBER(F161),ISNUMBER(E161),E161&gt;0,F161=E161),"Draw",IF(AND(ISNUMBER(F161),ISNUMBER(E161),E161&gt;0,F161=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A161="","",IF(AND(ISNUMBER(E161),E161=0,OR(ISNUMBER(SEARCH("Free",D161&amp;"")),AND(ISNUMBER(F161),F161=0))),"Subscription",IF(ISNUMBER(G161),"Profit",IF(ISNUMBER(I161),"Disqualified",IF(ISNUMBER(H161),"Draw",IF(AND(ISNUMBER(F161),ISNUMBER(E161),E161&gt;0,F161&gt;E161),"Profit",IF(AND(ISNUMBER(F161),ISNUMBER(E161),E161&gt;0,F161=E161),"Draw",IF(AND(ISNUMBER(F161),ISNUMBER(E161),E161&gt;0,F161=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L161" s="50"/>
       <x:c r="M161" s="58"/>
@@ -7352,7 +7365,7 @@
         <x:f>IF(A162="","",IF(K162="Subscription","",IF(E162=0,"",IF(ISNUMBER(G162),G162/E162,IF(ISNUMBER(I162),-ABS(I162)/E162,IF(ISNUMBER(H162),0,IF(AND(ISNUMBER(F162),ISNUMBER(E162),E162&gt;0,F162&gt;E162),(F162-E162)/E162,IF(AND(ISNUMBER(F162),ISNUMBER(E162),E162&gt;0,F162=E162),0,IF(AND(ISNUMBER(F162),ISNUMBER(E162),E162&gt;0,F162=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K162" s="50" t="str">
-        <x:f>IF(A162="","",IF(AND(ISNUMBER(E162),E162=0,OR(ISNUMBER(SEARCH("Free",D162&amp;"")),AND(ISNUMBER(F162),F162=0))),"Subscription",IF(ISNUMBER(G162),"Profit",IF(ISNUMBER(I162),"Loss",IF(ISNUMBER(H162),"Draw",IF(AND(ISNUMBER(F162),ISNUMBER(E162),E162&gt;0,F162&gt;E162),"Profit",IF(AND(ISNUMBER(F162),ISNUMBER(E162),E162&gt;0,F162=E162),"Draw",IF(AND(ISNUMBER(F162),ISNUMBER(E162),E162&gt;0,F162=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A162="","",IF(AND(ISNUMBER(E162),E162=0,OR(ISNUMBER(SEARCH("Free",D162&amp;"")),AND(ISNUMBER(F162),F162=0))),"Subscription",IF(ISNUMBER(G162),"Profit",IF(ISNUMBER(I162),"Disqualified",IF(ISNUMBER(H162),"Draw",IF(AND(ISNUMBER(F162),ISNUMBER(E162),E162&gt;0,F162&gt;E162),"Profit",IF(AND(ISNUMBER(F162),ISNUMBER(E162),E162&gt;0,F162=E162),"Draw",IF(AND(ISNUMBER(F162),ISNUMBER(E162),E162&gt;0,F162=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L162" s="50"/>
       <x:c r="M162" s="58"/>
@@ -7389,7 +7402,7 @@
         <x:f>IF(A163="","",IF(K163="Subscription","",IF(E163=0,"",IF(ISNUMBER(G163),G163/E163,IF(ISNUMBER(I163),-ABS(I163)/E163,IF(ISNUMBER(H163),0,IF(AND(ISNUMBER(F163),ISNUMBER(E163),E163&gt;0,F163&gt;E163),(F163-E163)/E163,IF(AND(ISNUMBER(F163),ISNUMBER(E163),E163&gt;0,F163=E163),0,IF(AND(ISNUMBER(F163),ISNUMBER(E163),E163&gt;0,F163=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K163" s="50" t="str">
-        <x:f>IF(A163="","",IF(AND(ISNUMBER(E163),E163=0,OR(ISNUMBER(SEARCH("Free",D163&amp;"")),AND(ISNUMBER(F163),F163=0))),"Subscription",IF(ISNUMBER(G163),"Profit",IF(ISNUMBER(I163),"Loss",IF(ISNUMBER(H163),"Draw",IF(AND(ISNUMBER(F163),ISNUMBER(E163),E163&gt;0,F163&gt;E163),"Profit",IF(AND(ISNUMBER(F163),ISNUMBER(E163),E163&gt;0,F163=E163),"Draw",IF(AND(ISNUMBER(F163),ISNUMBER(E163),E163&gt;0,F163=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A163="","",IF(AND(ISNUMBER(E163),E163=0,OR(ISNUMBER(SEARCH("Free",D163&amp;"")),AND(ISNUMBER(F163),F163=0))),"Subscription",IF(ISNUMBER(G163),"Profit",IF(ISNUMBER(I163),"Disqualified",IF(ISNUMBER(H163),"Draw",IF(AND(ISNUMBER(F163),ISNUMBER(E163),E163&gt;0,F163&gt;E163),"Profit",IF(AND(ISNUMBER(F163),ISNUMBER(E163),E163&gt;0,F163=E163),"Draw",IF(AND(ISNUMBER(F163),ISNUMBER(E163),E163&gt;0,F163=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L163" s="50"/>
       <x:c r="M163" s="58"/>
@@ -7426,7 +7439,7 @@
         <x:f>IF(A164="","",IF(K164="Subscription","",IF(E164=0,"",IF(ISNUMBER(G164),G164/E164,IF(ISNUMBER(I164),-ABS(I164)/E164,IF(ISNUMBER(H164),0,IF(AND(ISNUMBER(F164),ISNUMBER(E164),E164&gt;0,F164&gt;E164),(F164-E164)/E164,IF(AND(ISNUMBER(F164),ISNUMBER(E164),E164&gt;0,F164=E164),0,IF(AND(ISNUMBER(F164),ISNUMBER(E164),E164&gt;0,F164=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K164" s="50" t="str">
-        <x:f>IF(A164="","",IF(AND(ISNUMBER(E164),E164=0,OR(ISNUMBER(SEARCH("Free",D164&amp;"")),AND(ISNUMBER(F164),F164=0))),"Subscription",IF(ISNUMBER(G164),"Profit",IF(ISNUMBER(I164),"Loss",IF(ISNUMBER(H164),"Draw",IF(AND(ISNUMBER(F164),ISNUMBER(E164),E164&gt;0,F164&gt;E164),"Profit",IF(AND(ISNUMBER(F164),ISNUMBER(E164),E164&gt;0,F164=E164),"Draw",IF(AND(ISNUMBER(F164),ISNUMBER(E164),E164&gt;0,F164=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A164="","",IF(AND(ISNUMBER(E164),E164=0,OR(ISNUMBER(SEARCH("Free",D164&amp;"")),AND(ISNUMBER(F164),F164=0))),"Subscription",IF(ISNUMBER(G164),"Profit",IF(ISNUMBER(I164),"Disqualified",IF(ISNUMBER(H164),"Draw",IF(AND(ISNUMBER(F164),ISNUMBER(E164),E164&gt;0,F164&gt;E164),"Profit",IF(AND(ISNUMBER(F164),ISNUMBER(E164),E164&gt;0,F164=E164),"Draw",IF(AND(ISNUMBER(F164),ISNUMBER(E164),E164&gt;0,F164=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L164" s="50"/>
       <x:c r="M164" s="58"/>
@@ -7463,7 +7476,7 @@
         <x:f>IF(A165="","",IF(K165="Subscription","",IF(E165=0,"",IF(ISNUMBER(G165),G165/E165,IF(ISNUMBER(I165),-ABS(I165)/E165,IF(ISNUMBER(H165),0,IF(AND(ISNUMBER(F165),ISNUMBER(E165),E165&gt;0,F165&gt;E165),(F165-E165)/E165,IF(AND(ISNUMBER(F165),ISNUMBER(E165),E165&gt;0,F165=E165),0,IF(AND(ISNUMBER(F165),ISNUMBER(E165),E165&gt;0,F165=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K165" s="50" t="str">
-        <x:f>IF(A165="","",IF(AND(ISNUMBER(E165),E165=0,OR(ISNUMBER(SEARCH("Free",D165&amp;"")),AND(ISNUMBER(F165),F165=0))),"Subscription",IF(ISNUMBER(G165),"Profit",IF(ISNUMBER(I165),"Loss",IF(ISNUMBER(H165),"Draw",IF(AND(ISNUMBER(F165),ISNUMBER(E165),E165&gt;0,F165&gt;E165),"Profit",IF(AND(ISNUMBER(F165),ISNUMBER(E165),E165&gt;0,F165=E165),"Draw",IF(AND(ISNUMBER(F165),ISNUMBER(E165),E165&gt;0,F165=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A165="","",IF(AND(ISNUMBER(E165),E165=0,OR(ISNUMBER(SEARCH("Free",D165&amp;"")),AND(ISNUMBER(F165),F165=0))),"Subscription",IF(ISNUMBER(G165),"Profit",IF(ISNUMBER(I165),"Disqualified",IF(ISNUMBER(H165),"Draw",IF(AND(ISNUMBER(F165),ISNUMBER(E165),E165&gt;0,F165&gt;E165),"Profit",IF(AND(ISNUMBER(F165),ISNUMBER(E165),E165&gt;0,F165=E165),"Draw",IF(AND(ISNUMBER(F165),ISNUMBER(E165),E165&gt;0,F165=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L165" s="50"/>
       <x:c r="M165" s="58"/>
@@ -7500,7 +7513,7 @@
         <x:f>IF(A166="","",IF(K166="Subscription","",IF(E166=0,"",IF(ISNUMBER(G166),G166/E166,IF(ISNUMBER(I166),-ABS(I166)/E166,IF(ISNUMBER(H166),0,IF(AND(ISNUMBER(F166),ISNUMBER(E166),E166&gt;0,F166&gt;E166),(F166-E166)/E166,IF(AND(ISNUMBER(F166),ISNUMBER(E166),E166&gt;0,F166=E166),0,IF(AND(ISNUMBER(F166),ISNUMBER(E166),E166&gt;0,F166=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K166" s="50" t="str">
-        <x:f>IF(A166="","",IF(AND(ISNUMBER(E166),E166=0,OR(ISNUMBER(SEARCH("Free",D166&amp;"")),AND(ISNUMBER(F166),F166=0))),"Subscription",IF(ISNUMBER(G166),"Profit",IF(ISNUMBER(I166),"Loss",IF(ISNUMBER(H166),"Draw",IF(AND(ISNUMBER(F166),ISNUMBER(E166),E166&gt;0,F166&gt;E166),"Profit",IF(AND(ISNUMBER(F166),ISNUMBER(E166),E166&gt;0,F166=E166),"Draw",IF(AND(ISNUMBER(F166),ISNUMBER(E166),E166&gt;0,F166=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A166="","",IF(AND(ISNUMBER(E166),E166=0,OR(ISNUMBER(SEARCH("Free",D166&amp;"")),AND(ISNUMBER(F166),F166=0))),"Subscription",IF(ISNUMBER(G166),"Profit",IF(ISNUMBER(I166),"Disqualified",IF(ISNUMBER(H166),"Draw",IF(AND(ISNUMBER(F166),ISNUMBER(E166),E166&gt;0,F166&gt;E166),"Profit",IF(AND(ISNUMBER(F166),ISNUMBER(E166),E166&gt;0,F166=E166),"Draw",IF(AND(ISNUMBER(F166),ISNUMBER(E166),E166&gt;0,F166=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L166" s="50"/>
       <x:c r="M166" s="58"/>
@@ -7537,7 +7550,7 @@
         <x:f>IF(A167="","",IF(K167="Subscription","",IF(E167=0,"",IF(ISNUMBER(G167),G167/E167,IF(ISNUMBER(I167),-ABS(I167)/E167,IF(ISNUMBER(H167),0,IF(AND(ISNUMBER(F167),ISNUMBER(E167),E167&gt;0,F167&gt;E167),(F167-E167)/E167,IF(AND(ISNUMBER(F167),ISNUMBER(E167),E167&gt;0,F167=E167),0,IF(AND(ISNUMBER(F167),ISNUMBER(E167),E167&gt;0,F167=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K167" s="50" t="str">
-        <x:f>IF(A167="","",IF(AND(ISNUMBER(E167),E167=0,OR(ISNUMBER(SEARCH("Free",D167&amp;"")),AND(ISNUMBER(F167),F167=0))),"Subscription",IF(ISNUMBER(G167),"Profit",IF(ISNUMBER(I167),"Loss",IF(ISNUMBER(H167),"Draw",IF(AND(ISNUMBER(F167),ISNUMBER(E167),E167&gt;0,F167&gt;E167),"Profit",IF(AND(ISNUMBER(F167),ISNUMBER(E167),E167&gt;0,F167=E167),"Draw",IF(AND(ISNUMBER(F167),ISNUMBER(E167),E167&gt;0,F167=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A167="","",IF(AND(ISNUMBER(E167),E167=0,OR(ISNUMBER(SEARCH("Free",D167&amp;"")),AND(ISNUMBER(F167),F167=0))),"Subscription",IF(ISNUMBER(G167),"Profit",IF(ISNUMBER(I167),"Disqualified",IF(ISNUMBER(H167),"Draw",IF(AND(ISNUMBER(F167),ISNUMBER(E167),E167&gt;0,F167&gt;E167),"Profit",IF(AND(ISNUMBER(F167),ISNUMBER(E167),E167&gt;0,F167=E167),"Draw",IF(AND(ISNUMBER(F167),ISNUMBER(E167),E167&gt;0,F167=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L167" s="50"/>
       <x:c r="M167" s="58"/>
@@ -7574,7 +7587,7 @@
         <x:f>IF(A168="","",IF(K168="Subscription","",IF(E168=0,"",IF(ISNUMBER(G168),G168/E168,IF(ISNUMBER(I168),-ABS(I168)/E168,IF(ISNUMBER(H168),0,IF(AND(ISNUMBER(F168),ISNUMBER(E168),E168&gt;0,F168&gt;E168),(F168-E168)/E168,IF(AND(ISNUMBER(F168),ISNUMBER(E168),E168&gt;0,F168=E168),0,IF(AND(ISNUMBER(F168),ISNUMBER(E168),E168&gt;0,F168=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K168" s="50" t="str">
-        <x:f>IF(A168="","",IF(AND(ISNUMBER(E168),E168=0,OR(ISNUMBER(SEARCH("Free",D168&amp;"")),AND(ISNUMBER(F168),F168=0))),"Subscription",IF(ISNUMBER(G168),"Profit",IF(ISNUMBER(I168),"Loss",IF(ISNUMBER(H168),"Draw",IF(AND(ISNUMBER(F168),ISNUMBER(E168),E168&gt;0,F168&gt;E168),"Profit",IF(AND(ISNUMBER(F168),ISNUMBER(E168),E168&gt;0,F168=E168),"Draw",IF(AND(ISNUMBER(F168),ISNUMBER(E168),E168&gt;0,F168=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A168="","",IF(AND(ISNUMBER(E168),E168=0,OR(ISNUMBER(SEARCH("Free",D168&amp;"")),AND(ISNUMBER(F168),F168=0))),"Subscription",IF(ISNUMBER(G168),"Profit",IF(ISNUMBER(I168),"Disqualified",IF(ISNUMBER(H168),"Draw",IF(AND(ISNUMBER(F168),ISNUMBER(E168),E168&gt;0,F168&gt;E168),"Profit",IF(AND(ISNUMBER(F168),ISNUMBER(E168),E168&gt;0,F168=E168),"Draw",IF(AND(ISNUMBER(F168),ISNUMBER(E168),E168&gt;0,F168=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L168" s="50"/>
       <x:c r="M168" s="58"/>
@@ -7611,7 +7624,7 @@
         <x:f>IF(A169="","",IF(K169="Subscription","",IF(E169=0,"",IF(ISNUMBER(G169),G169/E169,IF(ISNUMBER(I169),-ABS(I169)/E169,IF(ISNUMBER(H169),0,IF(AND(ISNUMBER(F169),ISNUMBER(E169),E169&gt;0,F169&gt;E169),(F169-E169)/E169,IF(AND(ISNUMBER(F169),ISNUMBER(E169),E169&gt;0,F169=E169),0,IF(AND(ISNUMBER(F169),ISNUMBER(E169),E169&gt;0,F169=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K169" s="50" t="str">
-        <x:f>IF(A169="","",IF(AND(ISNUMBER(E169),E169=0,OR(ISNUMBER(SEARCH("Free",D169&amp;"")),AND(ISNUMBER(F169),F169=0))),"Subscription",IF(ISNUMBER(G169),"Profit",IF(ISNUMBER(I169),"Loss",IF(ISNUMBER(H169),"Draw",IF(AND(ISNUMBER(F169),ISNUMBER(E169),E169&gt;0,F169&gt;E169),"Profit",IF(AND(ISNUMBER(F169),ISNUMBER(E169),E169&gt;0,F169=E169),"Draw",IF(AND(ISNUMBER(F169),ISNUMBER(E169),E169&gt;0,F169=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A169="","",IF(AND(ISNUMBER(E169),E169=0,OR(ISNUMBER(SEARCH("Free",D169&amp;"")),AND(ISNUMBER(F169),F169=0))),"Subscription",IF(ISNUMBER(G169),"Profit",IF(ISNUMBER(I169),"Disqualified",IF(ISNUMBER(H169),"Draw",IF(AND(ISNUMBER(F169),ISNUMBER(E169),E169&gt;0,F169&gt;E169),"Profit",IF(AND(ISNUMBER(F169),ISNUMBER(E169),E169&gt;0,F169=E169),"Draw",IF(AND(ISNUMBER(F169),ISNUMBER(E169),E169&gt;0,F169=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L169" s="50"/>
       <x:c r="M169" s="58"/>
@@ -7648,7 +7661,7 @@
         <x:f>IF(A170="","",IF(K170="Subscription","",IF(E170=0,"",IF(ISNUMBER(G170),G170/E170,IF(ISNUMBER(I170),-ABS(I170)/E170,IF(ISNUMBER(H170),0,IF(AND(ISNUMBER(F170),ISNUMBER(E170),E170&gt;0,F170&gt;E170),(F170-E170)/E170,IF(AND(ISNUMBER(F170),ISNUMBER(E170),E170&gt;0,F170=E170),0,IF(AND(ISNUMBER(F170),ISNUMBER(E170),E170&gt;0,F170=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K170" s="50" t="str">
-        <x:f>IF(A170="","",IF(AND(ISNUMBER(E170),E170=0,OR(ISNUMBER(SEARCH("Free",D170&amp;"")),AND(ISNUMBER(F170),F170=0))),"Subscription",IF(ISNUMBER(G170),"Profit",IF(ISNUMBER(I170),"Loss",IF(ISNUMBER(H170),"Draw",IF(AND(ISNUMBER(F170),ISNUMBER(E170),E170&gt;0,F170&gt;E170),"Profit",IF(AND(ISNUMBER(F170),ISNUMBER(E170),E170&gt;0,F170=E170),"Draw",IF(AND(ISNUMBER(F170),ISNUMBER(E170),E170&gt;0,F170=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A170="","",IF(AND(ISNUMBER(E170),E170=0,OR(ISNUMBER(SEARCH("Free",D170&amp;"")),AND(ISNUMBER(F170),F170=0))),"Subscription",IF(ISNUMBER(G170),"Profit",IF(ISNUMBER(I170),"Disqualified",IF(ISNUMBER(H170),"Draw",IF(AND(ISNUMBER(F170),ISNUMBER(E170),E170&gt;0,F170&gt;E170),"Profit",IF(AND(ISNUMBER(F170),ISNUMBER(E170),E170&gt;0,F170=E170),"Draw",IF(AND(ISNUMBER(F170),ISNUMBER(E170),E170&gt;0,F170=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L170" s="50"/>
       <x:c r="M170" s="58"/>
@@ -7685,7 +7698,7 @@
         <x:f>IF(A171="","",IF(K171="Subscription","",IF(E171=0,"",IF(ISNUMBER(G171),G171/E171,IF(ISNUMBER(I171),-ABS(I171)/E171,IF(ISNUMBER(H171),0,IF(AND(ISNUMBER(F171),ISNUMBER(E171),E171&gt;0,F171&gt;E171),(F171-E171)/E171,IF(AND(ISNUMBER(F171),ISNUMBER(E171),E171&gt;0,F171=E171),0,IF(AND(ISNUMBER(F171),ISNUMBER(E171),E171&gt;0,F171=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K171" s="50" t="str">
-        <x:f>IF(A171="","",IF(AND(ISNUMBER(E171),E171=0,OR(ISNUMBER(SEARCH("Free",D171&amp;"")),AND(ISNUMBER(F171),F171=0))),"Subscription",IF(ISNUMBER(G171),"Profit",IF(ISNUMBER(I171),"Loss",IF(ISNUMBER(H171),"Draw",IF(AND(ISNUMBER(F171),ISNUMBER(E171),E171&gt;0,F171&gt;E171),"Profit",IF(AND(ISNUMBER(F171),ISNUMBER(E171),E171&gt;0,F171=E171),"Draw",IF(AND(ISNUMBER(F171),ISNUMBER(E171),E171&gt;0,F171=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A171="","",IF(AND(ISNUMBER(E171),E171=0,OR(ISNUMBER(SEARCH("Free",D171&amp;"")),AND(ISNUMBER(F171),F171=0))),"Subscription",IF(ISNUMBER(G171),"Profit",IF(ISNUMBER(I171),"Disqualified",IF(ISNUMBER(H171),"Draw",IF(AND(ISNUMBER(F171),ISNUMBER(E171),E171&gt;0,F171&gt;E171),"Profit",IF(AND(ISNUMBER(F171),ISNUMBER(E171),E171&gt;0,F171=E171),"Draw",IF(AND(ISNUMBER(F171),ISNUMBER(E171),E171&gt;0,F171=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L171" s="50"/>
       <x:c r="M171" s="58"/>
@@ -7722,7 +7735,7 @@
         <x:f>IF(A172="","",IF(K172="Subscription","",IF(E172=0,"",IF(ISNUMBER(G172),G172/E172,IF(ISNUMBER(I172),-ABS(I172)/E172,IF(ISNUMBER(H172),0,IF(AND(ISNUMBER(F172),ISNUMBER(E172),E172&gt;0,F172&gt;E172),(F172-E172)/E172,IF(AND(ISNUMBER(F172),ISNUMBER(E172),E172&gt;0,F172=E172),0,IF(AND(ISNUMBER(F172),ISNUMBER(E172),E172&gt;0,F172=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K172" s="50" t="str">
-        <x:f>IF(A172="","",IF(AND(ISNUMBER(E172),E172=0,OR(ISNUMBER(SEARCH("Free",D172&amp;"")),AND(ISNUMBER(F172),F172=0))),"Subscription",IF(ISNUMBER(G172),"Profit",IF(ISNUMBER(I172),"Loss",IF(ISNUMBER(H172),"Draw",IF(AND(ISNUMBER(F172),ISNUMBER(E172),E172&gt;0,F172&gt;E172),"Profit",IF(AND(ISNUMBER(F172),ISNUMBER(E172),E172&gt;0,F172=E172),"Draw",IF(AND(ISNUMBER(F172),ISNUMBER(E172),E172&gt;0,F172=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A172="","",IF(AND(ISNUMBER(E172),E172=0,OR(ISNUMBER(SEARCH("Free",D172&amp;"")),AND(ISNUMBER(F172),F172=0))),"Subscription",IF(ISNUMBER(G172),"Profit",IF(ISNUMBER(I172),"Disqualified",IF(ISNUMBER(H172),"Draw",IF(AND(ISNUMBER(F172),ISNUMBER(E172),E172&gt;0,F172&gt;E172),"Profit",IF(AND(ISNUMBER(F172),ISNUMBER(E172),E172&gt;0,F172=E172),"Draw",IF(AND(ISNUMBER(F172),ISNUMBER(E172),E172&gt;0,F172=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L172" s="50"/>
       <x:c r="M172" s="58"/>
@@ -7759,7 +7772,7 @@
         <x:f>IF(A173="","",IF(K173="Subscription","",IF(E173=0,"",IF(ISNUMBER(G173),G173/E173,IF(ISNUMBER(I173),-ABS(I173)/E173,IF(ISNUMBER(H173),0,IF(AND(ISNUMBER(F173),ISNUMBER(E173),E173&gt;0,F173&gt;E173),(F173-E173)/E173,IF(AND(ISNUMBER(F173),ISNUMBER(E173),E173&gt;0,F173=E173),0,IF(AND(ISNUMBER(F173),ISNUMBER(E173),E173&gt;0,F173=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K173" s="50" t="str">
-        <x:f>IF(A173="","",IF(AND(ISNUMBER(E173),E173=0,OR(ISNUMBER(SEARCH("Free",D173&amp;"")),AND(ISNUMBER(F173),F173=0))),"Subscription",IF(ISNUMBER(G173),"Profit",IF(ISNUMBER(I173),"Loss",IF(ISNUMBER(H173),"Draw",IF(AND(ISNUMBER(F173),ISNUMBER(E173),E173&gt;0,F173&gt;E173),"Profit",IF(AND(ISNUMBER(F173),ISNUMBER(E173),E173&gt;0,F173=E173),"Draw",IF(AND(ISNUMBER(F173),ISNUMBER(E173),E173&gt;0,F173=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A173="","",IF(AND(ISNUMBER(E173),E173=0,OR(ISNUMBER(SEARCH("Free",D173&amp;"")),AND(ISNUMBER(F173),F173=0))),"Subscription",IF(ISNUMBER(G173),"Profit",IF(ISNUMBER(I173),"Disqualified",IF(ISNUMBER(H173),"Draw",IF(AND(ISNUMBER(F173),ISNUMBER(E173),E173&gt;0,F173&gt;E173),"Profit",IF(AND(ISNUMBER(F173),ISNUMBER(E173),E173&gt;0,F173=E173),"Draw",IF(AND(ISNUMBER(F173),ISNUMBER(E173),E173&gt;0,F173=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L173" s="50"/>
       <x:c r="M173" s="58"/>
@@ -7796,7 +7809,7 @@
         <x:f>IF(A174="","",IF(K174="Subscription","",IF(E174=0,"",IF(ISNUMBER(G174),G174/E174,IF(ISNUMBER(I174),-ABS(I174)/E174,IF(ISNUMBER(H174),0,IF(AND(ISNUMBER(F174),ISNUMBER(E174),E174&gt;0,F174&gt;E174),(F174-E174)/E174,IF(AND(ISNUMBER(F174),ISNUMBER(E174),E174&gt;0,F174=E174),0,IF(AND(ISNUMBER(F174),ISNUMBER(E174),E174&gt;0,F174=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K174" s="50" t="str">
-        <x:f>IF(A174="","",IF(AND(ISNUMBER(E174),E174=0,OR(ISNUMBER(SEARCH("Free",D174&amp;"")),AND(ISNUMBER(F174),F174=0))),"Subscription",IF(ISNUMBER(G174),"Profit",IF(ISNUMBER(I174),"Loss",IF(ISNUMBER(H174),"Draw",IF(AND(ISNUMBER(F174),ISNUMBER(E174),E174&gt;0,F174&gt;E174),"Profit",IF(AND(ISNUMBER(F174),ISNUMBER(E174),E174&gt;0,F174=E174),"Draw",IF(AND(ISNUMBER(F174),ISNUMBER(E174),E174&gt;0,F174=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A174="","",IF(AND(ISNUMBER(E174),E174=0,OR(ISNUMBER(SEARCH("Free",D174&amp;"")),AND(ISNUMBER(F174),F174=0))),"Subscription",IF(ISNUMBER(G174),"Profit",IF(ISNUMBER(I174),"Disqualified",IF(ISNUMBER(H174),"Draw",IF(AND(ISNUMBER(F174),ISNUMBER(E174),E174&gt;0,F174&gt;E174),"Profit",IF(AND(ISNUMBER(F174),ISNUMBER(E174),E174&gt;0,F174=E174),"Draw",IF(AND(ISNUMBER(F174),ISNUMBER(E174),E174&gt;0,F174=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L174" s="50"/>
       <x:c r="M174" s="58"/>
@@ -7833,7 +7846,7 @@
         <x:f>IF(A175="","",IF(K175="Subscription","",IF(E175=0,"",IF(ISNUMBER(G175),G175/E175,IF(ISNUMBER(I175),-ABS(I175)/E175,IF(ISNUMBER(H175),0,IF(AND(ISNUMBER(F175),ISNUMBER(E175),E175&gt;0,F175&gt;E175),(F175-E175)/E175,IF(AND(ISNUMBER(F175),ISNUMBER(E175),E175&gt;0,F175=E175),0,IF(AND(ISNUMBER(F175),ISNUMBER(E175),E175&gt;0,F175=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K175" s="50" t="str">
-        <x:f>IF(A175="","",IF(AND(ISNUMBER(E175),E175=0,OR(ISNUMBER(SEARCH("Free",D175&amp;"")),AND(ISNUMBER(F175),F175=0))),"Subscription",IF(ISNUMBER(G175),"Profit",IF(ISNUMBER(I175),"Loss",IF(ISNUMBER(H175),"Draw",IF(AND(ISNUMBER(F175),ISNUMBER(E175),E175&gt;0,F175&gt;E175),"Profit",IF(AND(ISNUMBER(F175),ISNUMBER(E175),E175&gt;0,F175=E175),"Draw",IF(AND(ISNUMBER(F175),ISNUMBER(E175),E175&gt;0,F175=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A175="","",IF(AND(ISNUMBER(E175),E175=0,OR(ISNUMBER(SEARCH("Free",D175&amp;"")),AND(ISNUMBER(F175),F175=0))),"Subscription",IF(ISNUMBER(G175),"Profit",IF(ISNUMBER(I175),"Disqualified",IF(ISNUMBER(H175),"Draw",IF(AND(ISNUMBER(F175),ISNUMBER(E175),E175&gt;0,F175&gt;E175),"Profit",IF(AND(ISNUMBER(F175),ISNUMBER(E175),E175&gt;0,F175=E175),"Draw",IF(AND(ISNUMBER(F175),ISNUMBER(E175),E175&gt;0,F175=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L175" s="50"/>
       <x:c r="M175" s="58"/>
@@ -7870,7 +7883,7 @@
         <x:f>IF(A176="","",IF(K176="Subscription","",IF(E176=0,"",IF(ISNUMBER(G176),G176/E176,IF(ISNUMBER(I176),-ABS(I176)/E176,IF(ISNUMBER(H176),0,IF(AND(ISNUMBER(F176),ISNUMBER(E176),E176&gt;0,F176&gt;E176),(F176-E176)/E176,IF(AND(ISNUMBER(F176),ISNUMBER(E176),E176&gt;0,F176=E176),0,IF(AND(ISNUMBER(F176),ISNUMBER(E176),E176&gt;0,F176=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K176" s="50" t="str">
-        <x:f>IF(A176="","",IF(AND(ISNUMBER(E176),E176=0,OR(ISNUMBER(SEARCH("Free",D176&amp;"")),AND(ISNUMBER(F176),F176=0))),"Subscription",IF(ISNUMBER(G176),"Profit",IF(ISNUMBER(I176),"Loss",IF(ISNUMBER(H176),"Draw",IF(AND(ISNUMBER(F176),ISNUMBER(E176),E176&gt;0,F176&gt;E176),"Profit",IF(AND(ISNUMBER(F176),ISNUMBER(E176),E176&gt;0,F176=E176),"Draw",IF(AND(ISNUMBER(F176),ISNUMBER(E176),E176&gt;0,F176=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A176="","",IF(AND(ISNUMBER(E176),E176=0,OR(ISNUMBER(SEARCH("Free",D176&amp;"")),AND(ISNUMBER(F176),F176=0))),"Subscription",IF(ISNUMBER(G176),"Profit",IF(ISNUMBER(I176),"Disqualified",IF(ISNUMBER(H176),"Draw",IF(AND(ISNUMBER(F176),ISNUMBER(E176),E176&gt;0,F176&gt;E176),"Profit",IF(AND(ISNUMBER(F176),ISNUMBER(E176),E176&gt;0,F176=E176),"Draw",IF(AND(ISNUMBER(F176),ISNUMBER(E176),E176&gt;0,F176=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L176" s="50"/>
       <x:c r="M176" s="58"/>
@@ -7907,7 +7920,7 @@
         <x:f>IF(A177="","",IF(K177="Subscription","",IF(E177=0,"",IF(ISNUMBER(G177),G177/E177,IF(ISNUMBER(I177),-ABS(I177)/E177,IF(ISNUMBER(H177),0,IF(AND(ISNUMBER(F177),ISNUMBER(E177),E177&gt;0,F177&gt;E177),(F177-E177)/E177,IF(AND(ISNUMBER(F177),ISNUMBER(E177),E177&gt;0,F177=E177),0,IF(AND(ISNUMBER(F177),ISNUMBER(E177),E177&gt;0,F177=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K177" s="50" t="str">
-        <x:f>IF(A177="","",IF(AND(ISNUMBER(E177),E177=0,OR(ISNUMBER(SEARCH("Free",D177&amp;"")),AND(ISNUMBER(F177),F177=0))),"Subscription",IF(ISNUMBER(G177),"Profit",IF(ISNUMBER(I177),"Loss",IF(ISNUMBER(H177),"Draw",IF(AND(ISNUMBER(F177),ISNUMBER(E177),E177&gt;0,F177&gt;E177),"Profit",IF(AND(ISNUMBER(F177),ISNUMBER(E177),E177&gt;0,F177=E177),"Draw",IF(AND(ISNUMBER(F177),ISNUMBER(E177),E177&gt;0,F177=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A177="","",IF(AND(ISNUMBER(E177),E177=0,OR(ISNUMBER(SEARCH("Free",D177&amp;"")),AND(ISNUMBER(F177),F177=0))),"Subscription",IF(ISNUMBER(G177),"Profit",IF(ISNUMBER(I177),"Disqualified",IF(ISNUMBER(H177),"Draw",IF(AND(ISNUMBER(F177),ISNUMBER(E177),E177&gt;0,F177&gt;E177),"Profit",IF(AND(ISNUMBER(F177),ISNUMBER(E177),E177&gt;0,F177=E177),"Draw",IF(AND(ISNUMBER(F177),ISNUMBER(E177),E177&gt;0,F177=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L177" s="50"/>
       <x:c r="M177" s="58"/>
@@ -7944,7 +7957,7 @@
         <x:f>IF(A178="","",IF(K178="Subscription","",IF(E178=0,"",IF(ISNUMBER(G178),G178/E178,IF(ISNUMBER(I178),-ABS(I178)/E178,IF(ISNUMBER(H178),0,IF(AND(ISNUMBER(F178),ISNUMBER(E178),E178&gt;0,F178&gt;E178),(F178-E178)/E178,IF(AND(ISNUMBER(F178),ISNUMBER(E178),E178&gt;0,F178=E178),0,IF(AND(ISNUMBER(F178),ISNUMBER(E178),E178&gt;0,F178=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K178" s="50" t="str">
-        <x:f>IF(A178="","",IF(AND(ISNUMBER(E178),E178=0,OR(ISNUMBER(SEARCH("Free",D178&amp;"")),AND(ISNUMBER(F178),F178=0))),"Subscription",IF(ISNUMBER(G178),"Profit",IF(ISNUMBER(I178),"Loss",IF(ISNUMBER(H178),"Draw",IF(AND(ISNUMBER(F178),ISNUMBER(E178),E178&gt;0,F178&gt;E178),"Profit",IF(AND(ISNUMBER(F178),ISNUMBER(E178),E178&gt;0,F178=E178),"Draw",IF(AND(ISNUMBER(F178),ISNUMBER(E178),E178&gt;0,F178=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A178="","",IF(AND(ISNUMBER(E178),E178=0,OR(ISNUMBER(SEARCH("Free",D178&amp;"")),AND(ISNUMBER(F178),F178=0))),"Subscription",IF(ISNUMBER(G178),"Profit",IF(ISNUMBER(I178),"Disqualified",IF(ISNUMBER(H178),"Draw",IF(AND(ISNUMBER(F178),ISNUMBER(E178),E178&gt;0,F178&gt;E178),"Profit",IF(AND(ISNUMBER(F178),ISNUMBER(E178),E178&gt;0,F178=E178),"Draw",IF(AND(ISNUMBER(F178),ISNUMBER(E178),E178&gt;0,F178=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L178" s="50"/>
       <x:c r="M178" s="58"/>
@@ -7981,7 +7994,7 @@
         <x:f>IF(A179="","",IF(K179="Subscription","",IF(E179=0,"",IF(ISNUMBER(G179),G179/E179,IF(ISNUMBER(I179),-ABS(I179)/E179,IF(ISNUMBER(H179),0,IF(AND(ISNUMBER(F179),ISNUMBER(E179),E179&gt;0,F179&gt;E179),(F179-E179)/E179,IF(AND(ISNUMBER(F179),ISNUMBER(E179),E179&gt;0,F179=E179),0,IF(AND(ISNUMBER(F179),ISNUMBER(E179),E179&gt;0,F179=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K179" s="50" t="str">
-        <x:f>IF(A179="","",IF(AND(ISNUMBER(E179),E179=0,OR(ISNUMBER(SEARCH("Free",D179&amp;"")),AND(ISNUMBER(F179),F179=0))),"Subscription",IF(ISNUMBER(G179),"Profit",IF(ISNUMBER(I179),"Loss",IF(ISNUMBER(H179),"Draw",IF(AND(ISNUMBER(F179),ISNUMBER(E179),E179&gt;0,F179&gt;E179),"Profit",IF(AND(ISNUMBER(F179),ISNUMBER(E179),E179&gt;0,F179=E179),"Draw",IF(AND(ISNUMBER(F179),ISNUMBER(E179),E179&gt;0,F179=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A179="","",IF(AND(ISNUMBER(E179),E179=0,OR(ISNUMBER(SEARCH("Free",D179&amp;"")),AND(ISNUMBER(F179),F179=0))),"Subscription",IF(ISNUMBER(G179),"Profit",IF(ISNUMBER(I179),"Disqualified",IF(ISNUMBER(H179),"Draw",IF(AND(ISNUMBER(F179),ISNUMBER(E179),E179&gt;0,F179&gt;E179),"Profit",IF(AND(ISNUMBER(F179),ISNUMBER(E179),E179&gt;0,F179=E179),"Draw",IF(AND(ISNUMBER(F179),ISNUMBER(E179),E179&gt;0,F179=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L179" s="50"/>
       <x:c r="M179" s="58"/>
@@ -8018,7 +8031,7 @@
         <x:f>IF(A180="","",IF(K180="Subscription","",IF(E180=0,"",IF(ISNUMBER(G180),G180/E180,IF(ISNUMBER(I180),-ABS(I180)/E180,IF(ISNUMBER(H180),0,IF(AND(ISNUMBER(F180),ISNUMBER(E180),E180&gt;0,F180&gt;E180),(F180-E180)/E180,IF(AND(ISNUMBER(F180),ISNUMBER(E180),E180&gt;0,F180=E180),0,IF(AND(ISNUMBER(F180),ISNUMBER(E180),E180&gt;0,F180=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K180" s="50" t="str">
-        <x:f>IF(A180="","",IF(AND(ISNUMBER(E180),E180=0,OR(ISNUMBER(SEARCH("Free",D180&amp;"")),AND(ISNUMBER(F180),F180=0))),"Subscription",IF(ISNUMBER(G180),"Profit",IF(ISNUMBER(I180),"Loss",IF(ISNUMBER(H180),"Draw",IF(AND(ISNUMBER(F180),ISNUMBER(E180),E180&gt;0,F180&gt;E180),"Profit",IF(AND(ISNUMBER(F180),ISNUMBER(E180),E180&gt;0,F180=E180),"Draw",IF(AND(ISNUMBER(F180),ISNUMBER(E180),E180&gt;0,F180=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A180="","",IF(AND(ISNUMBER(E180),E180=0,OR(ISNUMBER(SEARCH("Free",D180&amp;"")),AND(ISNUMBER(F180),F180=0))),"Subscription",IF(ISNUMBER(G180),"Profit",IF(ISNUMBER(I180),"Disqualified",IF(ISNUMBER(H180),"Draw",IF(AND(ISNUMBER(F180),ISNUMBER(E180),E180&gt;0,F180&gt;E180),"Profit",IF(AND(ISNUMBER(F180),ISNUMBER(E180),E180&gt;0,F180=E180),"Draw",IF(AND(ISNUMBER(F180),ISNUMBER(E180),E180&gt;0,F180=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L180" s="50"/>
       <x:c r="M180" s="58"/>
@@ -8055,7 +8068,7 @@
         <x:f>IF(A181="","",IF(K181="Subscription","",IF(E181=0,"",IF(ISNUMBER(G181),G181/E181,IF(ISNUMBER(I181),-ABS(I181)/E181,IF(ISNUMBER(H181),0,IF(AND(ISNUMBER(F181),ISNUMBER(E181),E181&gt;0,F181&gt;E181),(F181-E181)/E181,IF(AND(ISNUMBER(F181),ISNUMBER(E181),E181&gt;0,F181=E181),0,IF(AND(ISNUMBER(F181),ISNUMBER(E181),E181&gt;0,F181=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K181" s="50" t="str">
-        <x:f>IF(A181="","",IF(AND(ISNUMBER(E181),E181=0,OR(ISNUMBER(SEARCH("Free",D181&amp;"")),AND(ISNUMBER(F181),F181=0))),"Subscription",IF(ISNUMBER(G181),"Profit",IF(ISNUMBER(I181),"Loss",IF(ISNUMBER(H181),"Draw",IF(AND(ISNUMBER(F181),ISNUMBER(E181),E181&gt;0,F181&gt;E181),"Profit",IF(AND(ISNUMBER(F181),ISNUMBER(E181),E181&gt;0,F181=E181),"Draw",IF(AND(ISNUMBER(F181),ISNUMBER(E181),E181&gt;0,F181=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A181="","",IF(AND(ISNUMBER(E181),E181=0,OR(ISNUMBER(SEARCH("Free",D181&amp;"")),AND(ISNUMBER(F181),F181=0))),"Subscription",IF(ISNUMBER(G181),"Profit",IF(ISNUMBER(I181),"Disqualified",IF(ISNUMBER(H181),"Draw",IF(AND(ISNUMBER(F181),ISNUMBER(E181),E181&gt;0,F181&gt;E181),"Profit",IF(AND(ISNUMBER(F181),ISNUMBER(E181),E181&gt;0,F181=E181),"Draw",IF(AND(ISNUMBER(F181),ISNUMBER(E181),E181&gt;0,F181=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L181" s="50"/>
       <x:c r="M181" s="58"/>
@@ -8092,7 +8105,7 @@
         <x:f>IF(A182="","",IF(K182="Subscription","",IF(E182=0,"",IF(ISNUMBER(G182),G182/E182,IF(ISNUMBER(I182),-ABS(I182)/E182,IF(ISNUMBER(H182),0,IF(AND(ISNUMBER(F182),ISNUMBER(E182),E182&gt;0,F182&gt;E182),(F182-E182)/E182,IF(AND(ISNUMBER(F182),ISNUMBER(E182),E182&gt;0,F182=E182),0,IF(AND(ISNUMBER(F182),ISNUMBER(E182),E182&gt;0,F182=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K182" s="50" t="str">
-        <x:f>IF(A182="","",IF(AND(ISNUMBER(E182),E182=0,OR(ISNUMBER(SEARCH("Free",D182&amp;"")),AND(ISNUMBER(F182),F182=0))),"Subscription",IF(ISNUMBER(G182),"Profit",IF(ISNUMBER(I182),"Loss",IF(ISNUMBER(H182),"Draw",IF(AND(ISNUMBER(F182),ISNUMBER(E182),E182&gt;0,F182&gt;E182),"Profit",IF(AND(ISNUMBER(F182),ISNUMBER(E182),E182&gt;0,F182=E182),"Draw",IF(AND(ISNUMBER(F182),ISNUMBER(E182),E182&gt;0,F182=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A182="","",IF(AND(ISNUMBER(E182),E182=0,OR(ISNUMBER(SEARCH("Free",D182&amp;"")),AND(ISNUMBER(F182),F182=0))),"Subscription",IF(ISNUMBER(G182),"Profit",IF(ISNUMBER(I182),"Disqualified",IF(ISNUMBER(H182),"Draw",IF(AND(ISNUMBER(F182),ISNUMBER(E182),E182&gt;0,F182&gt;E182),"Profit",IF(AND(ISNUMBER(F182),ISNUMBER(E182),E182&gt;0,F182=E182),"Draw",IF(AND(ISNUMBER(F182),ISNUMBER(E182),E182&gt;0,F182=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L182" s="50"/>
       <x:c r="M182" s="58"/>
@@ -8129,7 +8142,7 @@
         <x:f>IF(A183="","",IF(K183="Subscription","",IF(E183=0,"",IF(ISNUMBER(G183),G183/E183,IF(ISNUMBER(I183),-ABS(I183)/E183,IF(ISNUMBER(H183),0,IF(AND(ISNUMBER(F183),ISNUMBER(E183),E183&gt;0,F183&gt;E183),(F183-E183)/E183,IF(AND(ISNUMBER(F183),ISNUMBER(E183),E183&gt;0,F183=E183),0,IF(AND(ISNUMBER(F183),ISNUMBER(E183),E183&gt;0,F183=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K183" s="50" t="str">
-        <x:f>IF(A183="","",IF(AND(ISNUMBER(E183),E183=0,OR(ISNUMBER(SEARCH("Free",D183&amp;"")),AND(ISNUMBER(F183),F183=0))),"Subscription",IF(ISNUMBER(G183),"Profit",IF(ISNUMBER(I183),"Loss",IF(ISNUMBER(H183),"Draw",IF(AND(ISNUMBER(F183),ISNUMBER(E183),E183&gt;0,F183&gt;E183),"Profit",IF(AND(ISNUMBER(F183),ISNUMBER(E183),E183&gt;0,F183=E183),"Draw",IF(AND(ISNUMBER(F183),ISNUMBER(E183),E183&gt;0,F183=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A183="","",IF(AND(ISNUMBER(E183),E183=0,OR(ISNUMBER(SEARCH("Free",D183&amp;"")),AND(ISNUMBER(F183),F183=0))),"Subscription",IF(ISNUMBER(G183),"Profit",IF(ISNUMBER(I183),"Disqualified",IF(ISNUMBER(H183),"Draw",IF(AND(ISNUMBER(F183),ISNUMBER(E183),E183&gt;0,F183&gt;E183),"Profit",IF(AND(ISNUMBER(F183),ISNUMBER(E183),E183&gt;0,F183=E183),"Draw",IF(AND(ISNUMBER(F183),ISNUMBER(E183),E183&gt;0,F183=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L183" s="50"/>
       <x:c r="M183" s="58"/>
@@ -8166,7 +8179,7 @@
         <x:f>IF(A184="","",IF(K184="Subscription","",IF(E184=0,"",IF(ISNUMBER(G184),G184/E184,IF(ISNUMBER(I184),-ABS(I184)/E184,IF(ISNUMBER(H184),0,IF(AND(ISNUMBER(F184),ISNUMBER(E184),E184&gt;0,F184&gt;E184),(F184-E184)/E184,IF(AND(ISNUMBER(F184),ISNUMBER(E184),E184&gt;0,F184=E184),0,IF(AND(ISNUMBER(F184),ISNUMBER(E184),E184&gt;0,F184=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K184" s="50" t="str">
-        <x:f>IF(A184="","",IF(AND(ISNUMBER(E184),E184=0,OR(ISNUMBER(SEARCH("Free",D184&amp;"")),AND(ISNUMBER(F184),F184=0))),"Subscription",IF(ISNUMBER(G184),"Profit",IF(ISNUMBER(I184),"Loss",IF(ISNUMBER(H184),"Draw",IF(AND(ISNUMBER(F184),ISNUMBER(E184),E184&gt;0,F184&gt;E184),"Profit",IF(AND(ISNUMBER(F184),ISNUMBER(E184),E184&gt;0,F184=E184),"Draw",IF(AND(ISNUMBER(F184),ISNUMBER(E184),E184&gt;0,F184=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A184="","",IF(AND(ISNUMBER(E184),E184=0,OR(ISNUMBER(SEARCH("Free",D184&amp;"")),AND(ISNUMBER(F184),F184=0))),"Subscription",IF(ISNUMBER(G184),"Profit",IF(ISNUMBER(I184),"Disqualified",IF(ISNUMBER(H184),"Draw",IF(AND(ISNUMBER(F184),ISNUMBER(E184),E184&gt;0,F184&gt;E184),"Profit",IF(AND(ISNUMBER(F184),ISNUMBER(E184),E184&gt;0,F184=E184),"Draw",IF(AND(ISNUMBER(F184),ISNUMBER(E184),E184&gt;0,F184=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L184" s="50"/>
       <x:c r="M184" s="58"/>
@@ -8203,7 +8216,7 @@
         <x:f>IF(A185="","",IF(K185="Subscription","",IF(E185=0,"",IF(ISNUMBER(G185),G185/E185,IF(ISNUMBER(I185),-ABS(I185)/E185,IF(ISNUMBER(H185),0,IF(AND(ISNUMBER(F185),ISNUMBER(E185),E185&gt;0,F185&gt;E185),(F185-E185)/E185,IF(AND(ISNUMBER(F185),ISNUMBER(E185),E185&gt;0,F185=E185),0,IF(AND(ISNUMBER(F185),ISNUMBER(E185),E185&gt;0,F185=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K185" s="50" t="str">
-        <x:f>IF(A185="","",IF(AND(ISNUMBER(E185),E185=0,OR(ISNUMBER(SEARCH("Free",D185&amp;"")),AND(ISNUMBER(F185),F185=0))),"Subscription",IF(ISNUMBER(G185),"Profit",IF(ISNUMBER(I185),"Loss",IF(ISNUMBER(H185),"Draw",IF(AND(ISNUMBER(F185),ISNUMBER(E185),E185&gt;0,F185&gt;E185),"Profit",IF(AND(ISNUMBER(F185),ISNUMBER(E185),E185&gt;0,F185=E185),"Draw",IF(AND(ISNUMBER(F185),ISNUMBER(E185),E185&gt;0,F185=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A185="","",IF(AND(ISNUMBER(E185),E185=0,OR(ISNUMBER(SEARCH("Free",D185&amp;"")),AND(ISNUMBER(F185),F185=0))),"Subscription",IF(ISNUMBER(G185),"Profit",IF(ISNUMBER(I185),"Disqualified",IF(ISNUMBER(H185),"Draw",IF(AND(ISNUMBER(F185),ISNUMBER(E185),E185&gt;0,F185&gt;E185),"Profit",IF(AND(ISNUMBER(F185),ISNUMBER(E185),E185&gt;0,F185=E185),"Draw",IF(AND(ISNUMBER(F185),ISNUMBER(E185),E185&gt;0,F185=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L185" s="50"/>
       <x:c r="M185" s="58"/>
@@ -8240,7 +8253,7 @@
         <x:f>IF(A186="","",IF(K186="Subscription","",IF(E186=0,"",IF(ISNUMBER(G186),G186/E186,IF(ISNUMBER(I186),-ABS(I186)/E186,IF(ISNUMBER(H186),0,IF(AND(ISNUMBER(F186),ISNUMBER(E186),E186&gt;0,F186&gt;E186),(F186-E186)/E186,IF(AND(ISNUMBER(F186),ISNUMBER(E186),E186&gt;0,F186=E186),0,IF(AND(ISNUMBER(F186),ISNUMBER(E186),E186&gt;0,F186=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K186" s="50" t="str">
-        <x:f>IF(A186="","",IF(AND(ISNUMBER(E186),E186=0,OR(ISNUMBER(SEARCH("Free",D186&amp;"")),AND(ISNUMBER(F186),F186=0))),"Subscription",IF(ISNUMBER(G186),"Profit",IF(ISNUMBER(I186),"Loss",IF(ISNUMBER(H186),"Draw",IF(AND(ISNUMBER(F186),ISNUMBER(E186),E186&gt;0,F186&gt;E186),"Profit",IF(AND(ISNUMBER(F186),ISNUMBER(E186),E186&gt;0,F186=E186),"Draw",IF(AND(ISNUMBER(F186),ISNUMBER(E186),E186&gt;0,F186=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A186="","",IF(AND(ISNUMBER(E186),E186=0,OR(ISNUMBER(SEARCH("Free",D186&amp;"")),AND(ISNUMBER(F186),F186=0))),"Subscription",IF(ISNUMBER(G186),"Profit",IF(ISNUMBER(I186),"Disqualified",IF(ISNUMBER(H186),"Draw",IF(AND(ISNUMBER(F186),ISNUMBER(E186),E186&gt;0,F186&gt;E186),"Profit",IF(AND(ISNUMBER(F186),ISNUMBER(E186),E186&gt;0,F186=E186),"Draw",IF(AND(ISNUMBER(F186),ISNUMBER(E186),E186&gt;0,F186=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L186" s="50"/>
       <x:c r="M186" s="58"/>
@@ -8277,7 +8290,7 @@
         <x:f>IF(A187="","",IF(K187="Subscription","",IF(E187=0,"",IF(ISNUMBER(G187),G187/E187,IF(ISNUMBER(I187),-ABS(I187)/E187,IF(ISNUMBER(H187),0,IF(AND(ISNUMBER(F187),ISNUMBER(E187),E187&gt;0,F187&gt;E187),(F187-E187)/E187,IF(AND(ISNUMBER(F187),ISNUMBER(E187),E187&gt;0,F187=E187),0,IF(AND(ISNUMBER(F187),ISNUMBER(E187),E187&gt;0,F187=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K187" s="50" t="str">
-        <x:f>IF(A187="","",IF(AND(ISNUMBER(E187),E187=0,OR(ISNUMBER(SEARCH("Free",D187&amp;"")),AND(ISNUMBER(F187),F187=0))),"Subscription",IF(ISNUMBER(G187),"Profit",IF(ISNUMBER(I187),"Loss",IF(ISNUMBER(H187),"Draw",IF(AND(ISNUMBER(F187),ISNUMBER(E187),E187&gt;0,F187&gt;E187),"Profit",IF(AND(ISNUMBER(F187),ISNUMBER(E187),E187&gt;0,F187=E187),"Draw",IF(AND(ISNUMBER(F187),ISNUMBER(E187),E187&gt;0,F187=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A187="","",IF(AND(ISNUMBER(E187),E187=0,OR(ISNUMBER(SEARCH("Free",D187&amp;"")),AND(ISNUMBER(F187),F187=0))),"Subscription",IF(ISNUMBER(G187),"Profit",IF(ISNUMBER(I187),"Disqualified",IF(ISNUMBER(H187),"Draw",IF(AND(ISNUMBER(F187),ISNUMBER(E187),E187&gt;0,F187&gt;E187),"Profit",IF(AND(ISNUMBER(F187),ISNUMBER(E187),E187&gt;0,F187=E187),"Draw",IF(AND(ISNUMBER(F187),ISNUMBER(E187),E187&gt;0,F187=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L187" s="50"/>
       <x:c r="M187" s="58"/>
@@ -8314,7 +8327,7 @@
         <x:f>IF(A188="","",IF(K188="Subscription","",IF(E188=0,"",IF(ISNUMBER(G188),G188/E188,IF(ISNUMBER(I188),-ABS(I188)/E188,IF(ISNUMBER(H188),0,IF(AND(ISNUMBER(F188),ISNUMBER(E188),E188&gt;0,F188&gt;E188),(F188-E188)/E188,IF(AND(ISNUMBER(F188),ISNUMBER(E188),E188&gt;0,F188=E188),0,IF(AND(ISNUMBER(F188),ISNUMBER(E188),E188&gt;0,F188=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K188" s="50" t="str">
-        <x:f>IF(A188="","",IF(AND(ISNUMBER(E188),E188=0,OR(ISNUMBER(SEARCH("Free",D188&amp;"")),AND(ISNUMBER(F188),F188=0))),"Subscription",IF(ISNUMBER(G188),"Profit",IF(ISNUMBER(I188),"Loss",IF(ISNUMBER(H188),"Draw",IF(AND(ISNUMBER(F188),ISNUMBER(E188),E188&gt;0,F188&gt;E188),"Profit",IF(AND(ISNUMBER(F188),ISNUMBER(E188),E188&gt;0,F188=E188),"Draw",IF(AND(ISNUMBER(F188),ISNUMBER(E188),E188&gt;0,F188=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A188="","",IF(AND(ISNUMBER(E188),E188=0,OR(ISNUMBER(SEARCH("Free",D188&amp;"")),AND(ISNUMBER(F188),F188=0))),"Subscription",IF(ISNUMBER(G188),"Profit",IF(ISNUMBER(I188),"Disqualified",IF(ISNUMBER(H188),"Draw",IF(AND(ISNUMBER(F188),ISNUMBER(E188),E188&gt;0,F188&gt;E188),"Profit",IF(AND(ISNUMBER(F188),ISNUMBER(E188),E188&gt;0,F188=E188),"Draw",IF(AND(ISNUMBER(F188),ISNUMBER(E188),E188&gt;0,F188=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L188" s="50"/>
       <x:c r="M188" s="58"/>
@@ -8351,7 +8364,7 @@
         <x:f>IF(A189="","",IF(K189="Subscription","",IF(E189=0,"",IF(ISNUMBER(G189),G189/E189,IF(ISNUMBER(I189),-ABS(I189)/E189,IF(ISNUMBER(H189),0,IF(AND(ISNUMBER(F189),ISNUMBER(E189),E189&gt;0,F189&gt;E189),(F189-E189)/E189,IF(AND(ISNUMBER(F189),ISNUMBER(E189),E189&gt;0,F189=E189),0,IF(AND(ISNUMBER(F189),ISNUMBER(E189),E189&gt;0,F189=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K189" s="50" t="str">
-        <x:f>IF(A189="","",IF(AND(ISNUMBER(E189),E189=0,OR(ISNUMBER(SEARCH("Free",D189&amp;"")),AND(ISNUMBER(F189),F189=0))),"Subscription",IF(ISNUMBER(G189),"Profit",IF(ISNUMBER(I189),"Loss",IF(ISNUMBER(H189),"Draw",IF(AND(ISNUMBER(F189),ISNUMBER(E189),E189&gt;0,F189&gt;E189),"Profit",IF(AND(ISNUMBER(F189),ISNUMBER(E189),E189&gt;0,F189=E189),"Draw",IF(AND(ISNUMBER(F189),ISNUMBER(E189),E189&gt;0,F189=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A189="","",IF(AND(ISNUMBER(E189),E189=0,OR(ISNUMBER(SEARCH("Free",D189&amp;"")),AND(ISNUMBER(F189),F189=0))),"Subscription",IF(ISNUMBER(G189),"Profit",IF(ISNUMBER(I189),"Disqualified",IF(ISNUMBER(H189),"Draw",IF(AND(ISNUMBER(F189),ISNUMBER(E189),E189&gt;0,F189&gt;E189),"Profit",IF(AND(ISNUMBER(F189),ISNUMBER(E189),E189&gt;0,F189=E189),"Draw",IF(AND(ISNUMBER(F189),ISNUMBER(E189),E189&gt;0,F189=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L189" s="50"/>
       <x:c r="M189" s="58"/>
@@ -8388,7 +8401,7 @@
         <x:f>IF(A190="","",IF(K190="Subscription","",IF(E190=0,"",IF(ISNUMBER(G190),G190/E190,IF(ISNUMBER(I190),-ABS(I190)/E190,IF(ISNUMBER(H190),0,IF(AND(ISNUMBER(F190),ISNUMBER(E190),E190&gt;0,F190&gt;E190),(F190-E190)/E190,IF(AND(ISNUMBER(F190),ISNUMBER(E190),E190&gt;0,F190=E190),0,IF(AND(ISNUMBER(F190),ISNUMBER(E190),E190&gt;0,F190=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K190" s="50" t="str">
-        <x:f>IF(A190="","",IF(AND(ISNUMBER(E190),E190=0,OR(ISNUMBER(SEARCH("Free",D190&amp;"")),AND(ISNUMBER(F190),F190=0))),"Subscription",IF(ISNUMBER(G190),"Profit",IF(ISNUMBER(I190),"Loss",IF(ISNUMBER(H190),"Draw",IF(AND(ISNUMBER(F190),ISNUMBER(E190),E190&gt;0,F190&gt;E190),"Profit",IF(AND(ISNUMBER(F190),ISNUMBER(E190),E190&gt;0,F190=E190),"Draw",IF(AND(ISNUMBER(F190),ISNUMBER(E190),E190&gt;0,F190=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A190="","",IF(AND(ISNUMBER(E190),E190=0,OR(ISNUMBER(SEARCH("Free",D190&amp;"")),AND(ISNUMBER(F190),F190=0))),"Subscription",IF(ISNUMBER(G190),"Profit",IF(ISNUMBER(I190),"Disqualified",IF(ISNUMBER(H190),"Draw",IF(AND(ISNUMBER(F190),ISNUMBER(E190),E190&gt;0,F190&gt;E190),"Profit",IF(AND(ISNUMBER(F190),ISNUMBER(E190),E190&gt;0,F190=E190),"Draw",IF(AND(ISNUMBER(F190),ISNUMBER(E190),E190&gt;0,F190=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L190" s="50"/>
       <x:c r="M190" s="58"/>
@@ -8425,7 +8438,7 @@
         <x:f>IF(A191="","",IF(K191="Subscription","",IF(E191=0,"",IF(ISNUMBER(G191),G191/E191,IF(ISNUMBER(I191),-ABS(I191)/E191,IF(ISNUMBER(H191),0,IF(AND(ISNUMBER(F191),ISNUMBER(E191),E191&gt;0,F191&gt;E191),(F191-E191)/E191,IF(AND(ISNUMBER(F191),ISNUMBER(E191),E191&gt;0,F191=E191),0,IF(AND(ISNUMBER(F191),ISNUMBER(E191),E191&gt;0,F191=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K191" s="50" t="str">
-        <x:f>IF(A191="","",IF(AND(ISNUMBER(E191),E191=0,OR(ISNUMBER(SEARCH("Free",D191&amp;"")),AND(ISNUMBER(F191),F191=0))),"Subscription",IF(ISNUMBER(G191),"Profit",IF(ISNUMBER(I191),"Loss",IF(ISNUMBER(H191),"Draw",IF(AND(ISNUMBER(F191),ISNUMBER(E191),E191&gt;0,F191&gt;E191),"Profit",IF(AND(ISNUMBER(F191),ISNUMBER(E191),E191&gt;0,F191=E191),"Draw",IF(AND(ISNUMBER(F191),ISNUMBER(E191),E191&gt;0,F191=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A191="","",IF(AND(ISNUMBER(E191),E191=0,OR(ISNUMBER(SEARCH("Free",D191&amp;"")),AND(ISNUMBER(F191),F191=0))),"Subscription",IF(ISNUMBER(G191),"Profit",IF(ISNUMBER(I191),"Disqualified",IF(ISNUMBER(H191),"Draw",IF(AND(ISNUMBER(F191),ISNUMBER(E191),E191&gt;0,F191&gt;E191),"Profit",IF(AND(ISNUMBER(F191),ISNUMBER(E191),E191&gt;0,F191=E191),"Draw",IF(AND(ISNUMBER(F191),ISNUMBER(E191),E191&gt;0,F191=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L191" s="50"/>
       <x:c r="M191" s="58"/>
@@ -8462,7 +8475,7 @@
         <x:f>IF(A192="","",IF(K192="Subscription","",IF(E192=0,"",IF(ISNUMBER(G192),G192/E192,IF(ISNUMBER(I192),-ABS(I192)/E192,IF(ISNUMBER(H192),0,IF(AND(ISNUMBER(F192),ISNUMBER(E192),E192&gt;0,F192&gt;E192),(F192-E192)/E192,IF(AND(ISNUMBER(F192),ISNUMBER(E192),E192&gt;0,F192=E192),0,IF(AND(ISNUMBER(F192),ISNUMBER(E192),E192&gt;0,F192=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K192" s="50" t="str">
-        <x:f>IF(A192="","",IF(AND(ISNUMBER(E192),E192=0,OR(ISNUMBER(SEARCH("Free",D192&amp;"")),AND(ISNUMBER(F192),F192=0))),"Subscription",IF(ISNUMBER(G192),"Profit",IF(ISNUMBER(I192),"Loss",IF(ISNUMBER(H192),"Draw",IF(AND(ISNUMBER(F192),ISNUMBER(E192),E192&gt;0,F192&gt;E192),"Profit",IF(AND(ISNUMBER(F192),ISNUMBER(E192),E192&gt;0,F192=E192),"Draw",IF(AND(ISNUMBER(F192),ISNUMBER(E192),E192&gt;0,F192=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A192="","",IF(AND(ISNUMBER(E192),E192=0,OR(ISNUMBER(SEARCH("Free",D192&amp;"")),AND(ISNUMBER(F192),F192=0))),"Subscription",IF(ISNUMBER(G192),"Profit",IF(ISNUMBER(I192),"Disqualified",IF(ISNUMBER(H192),"Draw",IF(AND(ISNUMBER(F192),ISNUMBER(E192),E192&gt;0,F192&gt;E192),"Profit",IF(AND(ISNUMBER(F192),ISNUMBER(E192),E192&gt;0,F192=E192),"Draw",IF(AND(ISNUMBER(F192),ISNUMBER(E192),E192&gt;0,F192=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L192" s="50"/>
       <x:c r="M192" s="58"/>
@@ -8499,7 +8512,7 @@
         <x:f>IF(A193="","",IF(K193="Subscription","",IF(E193=0,"",IF(ISNUMBER(G193),G193/E193,IF(ISNUMBER(I193),-ABS(I193)/E193,IF(ISNUMBER(H193),0,IF(AND(ISNUMBER(F193),ISNUMBER(E193),E193&gt;0,F193&gt;E193),(F193-E193)/E193,IF(AND(ISNUMBER(F193),ISNUMBER(E193),E193&gt;0,F193=E193),0,IF(AND(ISNUMBER(F193),ISNUMBER(E193),E193&gt;0,F193=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K193" s="50" t="str">
-        <x:f>IF(A193="","",IF(AND(ISNUMBER(E193),E193=0,OR(ISNUMBER(SEARCH("Free",D193&amp;"")),AND(ISNUMBER(F193),F193=0))),"Subscription",IF(ISNUMBER(G193),"Profit",IF(ISNUMBER(I193),"Loss",IF(ISNUMBER(H193),"Draw",IF(AND(ISNUMBER(F193),ISNUMBER(E193),E193&gt;0,F193&gt;E193),"Profit",IF(AND(ISNUMBER(F193),ISNUMBER(E193),E193&gt;0,F193=E193),"Draw",IF(AND(ISNUMBER(F193),ISNUMBER(E193),E193&gt;0,F193=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A193="","",IF(AND(ISNUMBER(E193),E193=0,OR(ISNUMBER(SEARCH("Free",D193&amp;"")),AND(ISNUMBER(F193),F193=0))),"Subscription",IF(ISNUMBER(G193),"Profit",IF(ISNUMBER(I193),"Disqualified",IF(ISNUMBER(H193),"Draw",IF(AND(ISNUMBER(F193),ISNUMBER(E193),E193&gt;0,F193&gt;E193),"Profit",IF(AND(ISNUMBER(F193),ISNUMBER(E193),E193&gt;0,F193=E193),"Draw",IF(AND(ISNUMBER(F193),ISNUMBER(E193),E193&gt;0,F193=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L193" s="50"/>
       <x:c r="M193" s="58"/>
@@ -8536,7 +8549,7 @@
         <x:f>IF(A194="","",IF(K194="Subscription","",IF(E194=0,"",IF(ISNUMBER(G194),G194/E194,IF(ISNUMBER(I194),-ABS(I194)/E194,IF(ISNUMBER(H194),0,IF(AND(ISNUMBER(F194),ISNUMBER(E194),E194&gt;0,F194&gt;E194),(F194-E194)/E194,IF(AND(ISNUMBER(F194),ISNUMBER(E194),E194&gt;0,F194=E194),0,IF(AND(ISNUMBER(F194),ISNUMBER(E194),E194&gt;0,F194=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K194" s="50" t="str">
-        <x:f>IF(A194="","",IF(AND(ISNUMBER(E194),E194=0,OR(ISNUMBER(SEARCH("Free",D194&amp;"")),AND(ISNUMBER(F194),F194=0))),"Subscription",IF(ISNUMBER(G194),"Profit",IF(ISNUMBER(I194),"Loss",IF(ISNUMBER(H194),"Draw",IF(AND(ISNUMBER(F194),ISNUMBER(E194),E194&gt;0,F194&gt;E194),"Profit",IF(AND(ISNUMBER(F194),ISNUMBER(E194),E194&gt;0,F194=E194),"Draw",IF(AND(ISNUMBER(F194),ISNUMBER(E194),E194&gt;0,F194=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A194="","",IF(AND(ISNUMBER(E194),E194=0,OR(ISNUMBER(SEARCH("Free",D194&amp;"")),AND(ISNUMBER(F194),F194=0))),"Subscription",IF(ISNUMBER(G194),"Profit",IF(ISNUMBER(I194),"Disqualified",IF(ISNUMBER(H194),"Draw",IF(AND(ISNUMBER(F194),ISNUMBER(E194),E194&gt;0,F194&gt;E194),"Profit",IF(AND(ISNUMBER(F194),ISNUMBER(E194),E194&gt;0,F194=E194),"Draw",IF(AND(ISNUMBER(F194),ISNUMBER(E194),E194&gt;0,F194=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L194" s="50"/>
       <x:c r="M194" s="58"/>
@@ -8573,7 +8586,7 @@
         <x:f>IF(A195="","",IF(K195="Subscription","",IF(E195=0,"",IF(ISNUMBER(G195),G195/E195,IF(ISNUMBER(I195),-ABS(I195)/E195,IF(ISNUMBER(H195),0,IF(AND(ISNUMBER(F195),ISNUMBER(E195),E195&gt;0,F195&gt;E195),(F195-E195)/E195,IF(AND(ISNUMBER(F195),ISNUMBER(E195),E195&gt;0,F195=E195),0,IF(AND(ISNUMBER(F195),ISNUMBER(E195),E195&gt;0,F195=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K195" s="50" t="str">
-        <x:f>IF(A195="","",IF(AND(ISNUMBER(E195),E195=0,OR(ISNUMBER(SEARCH("Free",D195&amp;"")),AND(ISNUMBER(F195),F195=0))),"Subscription",IF(ISNUMBER(G195),"Profit",IF(ISNUMBER(I195),"Loss",IF(ISNUMBER(H195),"Draw",IF(AND(ISNUMBER(F195),ISNUMBER(E195),E195&gt;0,F195&gt;E195),"Profit",IF(AND(ISNUMBER(F195),ISNUMBER(E195),E195&gt;0,F195=E195),"Draw",IF(AND(ISNUMBER(F195),ISNUMBER(E195),E195&gt;0,F195=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A195="","",IF(AND(ISNUMBER(E195),E195=0,OR(ISNUMBER(SEARCH("Free",D195&amp;"")),AND(ISNUMBER(F195),F195=0))),"Subscription",IF(ISNUMBER(G195),"Profit",IF(ISNUMBER(I195),"Disqualified",IF(ISNUMBER(H195),"Draw",IF(AND(ISNUMBER(F195),ISNUMBER(E195),E195&gt;0,F195&gt;E195),"Profit",IF(AND(ISNUMBER(F195),ISNUMBER(E195),E195&gt;0,F195=E195),"Draw",IF(AND(ISNUMBER(F195),ISNUMBER(E195),E195&gt;0,F195=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L195" s="50"/>
       <x:c r="M195" s="58"/>
@@ -8610,7 +8623,7 @@
         <x:f>IF(A196="","",IF(K196="Subscription","",IF(E196=0,"",IF(ISNUMBER(G196),G196/E196,IF(ISNUMBER(I196),-ABS(I196)/E196,IF(ISNUMBER(H196),0,IF(AND(ISNUMBER(F196),ISNUMBER(E196),E196&gt;0,F196&gt;E196),(F196-E196)/E196,IF(AND(ISNUMBER(F196),ISNUMBER(E196),E196&gt;0,F196=E196),0,IF(AND(ISNUMBER(F196),ISNUMBER(E196),E196&gt;0,F196=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K196" s="50" t="str">
-        <x:f>IF(A196="","",IF(AND(ISNUMBER(E196),E196=0,OR(ISNUMBER(SEARCH("Free",D196&amp;"")),AND(ISNUMBER(F196),F196=0))),"Subscription",IF(ISNUMBER(G196),"Profit",IF(ISNUMBER(I196),"Loss",IF(ISNUMBER(H196),"Draw",IF(AND(ISNUMBER(F196),ISNUMBER(E196),E196&gt;0,F196&gt;E196),"Profit",IF(AND(ISNUMBER(F196),ISNUMBER(E196),E196&gt;0,F196=E196),"Draw",IF(AND(ISNUMBER(F196),ISNUMBER(E196),E196&gt;0,F196=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A196="","",IF(AND(ISNUMBER(E196),E196=0,OR(ISNUMBER(SEARCH("Free",D196&amp;"")),AND(ISNUMBER(F196),F196=0))),"Subscription",IF(ISNUMBER(G196),"Profit",IF(ISNUMBER(I196),"Disqualified",IF(ISNUMBER(H196),"Draw",IF(AND(ISNUMBER(F196),ISNUMBER(E196),E196&gt;0,F196&gt;E196),"Profit",IF(AND(ISNUMBER(F196),ISNUMBER(E196),E196&gt;0,F196=E196),"Draw",IF(AND(ISNUMBER(F196),ISNUMBER(E196),E196&gt;0,F196=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L196" s="50"/>
       <x:c r="M196" s="58"/>
@@ -8647,7 +8660,7 @@
         <x:f>IF(A197="","",IF(K197="Subscription","",IF(E197=0,"",IF(ISNUMBER(G197),G197/E197,IF(ISNUMBER(I197),-ABS(I197)/E197,IF(ISNUMBER(H197),0,IF(AND(ISNUMBER(F197),ISNUMBER(E197),E197&gt;0,F197&gt;E197),(F197-E197)/E197,IF(AND(ISNUMBER(F197),ISNUMBER(E197),E197&gt;0,F197=E197),0,IF(AND(ISNUMBER(F197),ISNUMBER(E197),E197&gt;0,F197=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K197" s="50" t="str">
-        <x:f>IF(A197="","",IF(AND(ISNUMBER(E197),E197=0,OR(ISNUMBER(SEARCH("Free",D197&amp;"")),AND(ISNUMBER(F197),F197=0))),"Subscription",IF(ISNUMBER(G197),"Profit",IF(ISNUMBER(I197),"Loss",IF(ISNUMBER(H197),"Draw",IF(AND(ISNUMBER(F197),ISNUMBER(E197),E197&gt;0,F197&gt;E197),"Profit",IF(AND(ISNUMBER(F197),ISNUMBER(E197),E197&gt;0,F197=E197),"Draw",IF(AND(ISNUMBER(F197),ISNUMBER(E197),E197&gt;0,F197=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A197="","",IF(AND(ISNUMBER(E197),E197=0,OR(ISNUMBER(SEARCH("Free",D197&amp;"")),AND(ISNUMBER(F197),F197=0))),"Subscription",IF(ISNUMBER(G197),"Profit",IF(ISNUMBER(I197),"Disqualified",IF(ISNUMBER(H197),"Draw",IF(AND(ISNUMBER(F197),ISNUMBER(E197),E197&gt;0,F197&gt;E197),"Profit",IF(AND(ISNUMBER(F197),ISNUMBER(E197),E197&gt;0,F197=E197),"Draw",IF(AND(ISNUMBER(F197),ISNUMBER(E197),E197&gt;0,F197=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L197" s="50"/>
       <x:c r="M197" s="58"/>
@@ -8684,7 +8697,7 @@
         <x:f>IF(A198="","",IF(K198="Subscription","",IF(E198=0,"",IF(ISNUMBER(G198),G198/E198,IF(ISNUMBER(I198),-ABS(I198)/E198,IF(ISNUMBER(H198),0,IF(AND(ISNUMBER(F198),ISNUMBER(E198),E198&gt;0,F198&gt;E198),(F198-E198)/E198,IF(AND(ISNUMBER(F198),ISNUMBER(E198),E198&gt;0,F198=E198),0,IF(AND(ISNUMBER(F198),ISNUMBER(E198),E198&gt;0,F198=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K198" s="50" t="str">
-        <x:f>IF(A198="","",IF(AND(ISNUMBER(E198),E198=0,OR(ISNUMBER(SEARCH("Free",D198&amp;"")),AND(ISNUMBER(F198),F198=0))),"Subscription",IF(ISNUMBER(G198),"Profit",IF(ISNUMBER(I198),"Loss",IF(ISNUMBER(H198),"Draw",IF(AND(ISNUMBER(F198),ISNUMBER(E198),E198&gt;0,F198&gt;E198),"Profit",IF(AND(ISNUMBER(F198),ISNUMBER(E198),E198&gt;0,F198=E198),"Draw",IF(AND(ISNUMBER(F198),ISNUMBER(E198),E198&gt;0,F198=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A198="","",IF(AND(ISNUMBER(E198),E198=0,OR(ISNUMBER(SEARCH("Free",D198&amp;"")),AND(ISNUMBER(F198),F198=0))),"Subscription",IF(ISNUMBER(G198),"Profit",IF(ISNUMBER(I198),"Disqualified",IF(ISNUMBER(H198),"Draw",IF(AND(ISNUMBER(F198),ISNUMBER(E198),E198&gt;0,F198&gt;E198),"Profit",IF(AND(ISNUMBER(F198),ISNUMBER(E198),E198&gt;0,F198=E198),"Draw",IF(AND(ISNUMBER(F198),ISNUMBER(E198),E198&gt;0,F198=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L198" s="50"/>
       <x:c r="M198" s="58"/>
@@ -8721,7 +8734,7 @@
         <x:f>IF(A199="","",IF(K199="Subscription","",IF(E199=0,"",IF(ISNUMBER(G199),G199/E199,IF(ISNUMBER(I199),-ABS(I199)/E199,IF(ISNUMBER(H199),0,IF(AND(ISNUMBER(F199),ISNUMBER(E199),E199&gt;0,F199&gt;E199),(F199-E199)/E199,IF(AND(ISNUMBER(F199),ISNUMBER(E199),E199&gt;0,F199=E199),0,IF(AND(ISNUMBER(F199),ISNUMBER(E199),E199&gt;0,F199=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K199" s="50" t="str">
-        <x:f>IF(A199="","",IF(AND(ISNUMBER(E199),E199=0,OR(ISNUMBER(SEARCH("Free",D199&amp;"")),AND(ISNUMBER(F199),F199=0))),"Subscription",IF(ISNUMBER(G199),"Profit",IF(ISNUMBER(I199),"Loss",IF(ISNUMBER(H199),"Draw",IF(AND(ISNUMBER(F199),ISNUMBER(E199),E199&gt;0,F199&gt;E199),"Profit",IF(AND(ISNUMBER(F199),ISNUMBER(E199),E199&gt;0,F199=E199),"Draw",IF(AND(ISNUMBER(F199),ISNUMBER(E199),E199&gt;0,F199=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A199="","",IF(AND(ISNUMBER(E199),E199=0,OR(ISNUMBER(SEARCH("Free",D199&amp;"")),AND(ISNUMBER(F199),F199=0))),"Subscription",IF(ISNUMBER(G199),"Profit",IF(ISNUMBER(I199),"Disqualified",IF(ISNUMBER(H199),"Draw",IF(AND(ISNUMBER(F199),ISNUMBER(E199),E199&gt;0,F199&gt;E199),"Profit",IF(AND(ISNUMBER(F199),ISNUMBER(E199),E199&gt;0,F199=E199),"Draw",IF(AND(ISNUMBER(F199),ISNUMBER(E199),E199&gt;0,F199=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L199" s="50"/>
       <x:c r="M199" s="58"/>
@@ -8758,7 +8771,7 @@
         <x:f>IF(A200="","",IF(K200="Subscription","",IF(E200=0,"",IF(ISNUMBER(G200),G200/E200,IF(ISNUMBER(I200),-ABS(I200)/E200,IF(ISNUMBER(H200),0,IF(AND(ISNUMBER(F200),ISNUMBER(E200),E200&gt;0,F200&gt;E200),(F200-E200)/E200,IF(AND(ISNUMBER(F200),ISNUMBER(E200),E200&gt;0,F200=E200),0,IF(AND(ISNUMBER(F200),ISNUMBER(E200),E200&gt;0,F200=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K200" s="50" t="str">
-        <x:f>IF(A200="","",IF(AND(ISNUMBER(E200),E200=0,OR(ISNUMBER(SEARCH("Free",D200&amp;"")),AND(ISNUMBER(F200),F200=0))),"Subscription",IF(ISNUMBER(G200),"Profit",IF(ISNUMBER(I200),"Loss",IF(ISNUMBER(H200),"Draw",IF(AND(ISNUMBER(F200),ISNUMBER(E200),E200&gt;0,F200&gt;E200),"Profit",IF(AND(ISNUMBER(F200),ISNUMBER(E200),E200&gt;0,F200=E200),"Draw",IF(AND(ISNUMBER(F200),ISNUMBER(E200),E200&gt;0,F200=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A200="","",IF(AND(ISNUMBER(E200),E200=0,OR(ISNUMBER(SEARCH("Free",D200&amp;"")),AND(ISNUMBER(F200),F200=0))),"Subscription",IF(ISNUMBER(G200),"Profit",IF(ISNUMBER(I200),"Disqualified",IF(ISNUMBER(H200),"Draw",IF(AND(ISNUMBER(F200),ISNUMBER(E200),E200&gt;0,F200&gt;E200),"Profit",IF(AND(ISNUMBER(F200),ISNUMBER(E200),E200&gt;0,F200=E200),"Draw",IF(AND(ISNUMBER(F200),ISNUMBER(E200),E200&gt;0,F200=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L200" s="50"/>
       <x:c r="M200" s="58"/>
@@ -8795,7 +8808,7 @@
         <x:f>IF(A201="","",IF(K201="Subscription","",IF(E201=0,"",IF(ISNUMBER(G201),G201/E201,IF(ISNUMBER(I201),-ABS(I201)/E201,IF(ISNUMBER(H201),0,IF(AND(ISNUMBER(F201),ISNUMBER(E201),E201&gt;0,F201&gt;E201),(F201-E201)/E201,IF(AND(ISNUMBER(F201),ISNUMBER(E201),E201&gt;0,F201=E201),0,IF(AND(ISNUMBER(F201),ISNUMBER(E201),E201&gt;0,F201=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K201" s="50" t="str">
-        <x:f>IF(A201="","",IF(AND(ISNUMBER(E201),E201=0,OR(ISNUMBER(SEARCH("Free",D201&amp;"")),AND(ISNUMBER(F201),F201=0))),"Subscription",IF(ISNUMBER(G201),"Profit",IF(ISNUMBER(I201),"Loss",IF(ISNUMBER(H201),"Draw",IF(AND(ISNUMBER(F201),ISNUMBER(E201),E201&gt;0,F201&gt;E201),"Profit",IF(AND(ISNUMBER(F201),ISNUMBER(E201),E201&gt;0,F201=E201),"Draw",IF(AND(ISNUMBER(F201),ISNUMBER(E201),E201&gt;0,F201=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A201="","",IF(AND(ISNUMBER(E201),E201=0,OR(ISNUMBER(SEARCH("Free",D201&amp;"")),AND(ISNUMBER(F201),F201=0))),"Subscription",IF(ISNUMBER(G201),"Profit",IF(ISNUMBER(I201),"Disqualified",IF(ISNUMBER(H201),"Draw",IF(AND(ISNUMBER(F201),ISNUMBER(E201),E201&gt;0,F201&gt;E201),"Profit",IF(AND(ISNUMBER(F201),ISNUMBER(E201),E201&gt;0,F201=E201),"Draw",IF(AND(ISNUMBER(F201),ISNUMBER(E201),E201&gt;0,F201=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L201" s="50"/>
       <x:c r="M201" s="58"/>
@@ -8832,7 +8845,7 @@
         <x:f>IF(A202="","",IF(K202="Subscription","",IF(E202=0,"",IF(ISNUMBER(G202),G202/E202,IF(ISNUMBER(I202),-ABS(I202)/E202,IF(ISNUMBER(H202),0,IF(AND(ISNUMBER(F202),ISNUMBER(E202),E202&gt;0,F202&gt;E202),(F202-E202)/E202,IF(AND(ISNUMBER(F202),ISNUMBER(E202),E202&gt;0,F202=E202),0,IF(AND(ISNUMBER(F202),ISNUMBER(E202),E202&gt;0,F202=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K202" s="50" t="str">
-        <x:f>IF(A202="","",IF(AND(ISNUMBER(E202),E202=0,OR(ISNUMBER(SEARCH("Free",D202&amp;"")),AND(ISNUMBER(F202),F202=0))),"Subscription",IF(ISNUMBER(G202),"Profit",IF(ISNUMBER(I202),"Loss",IF(ISNUMBER(H202),"Draw",IF(AND(ISNUMBER(F202),ISNUMBER(E202),E202&gt;0,F202&gt;E202),"Profit",IF(AND(ISNUMBER(F202),ISNUMBER(E202),E202&gt;0,F202=E202),"Draw",IF(AND(ISNUMBER(F202),ISNUMBER(E202),E202&gt;0,F202=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A202="","",IF(AND(ISNUMBER(E202),E202=0,OR(ISNUMBER(SEARCH("Free",D202&amp;"")),AND(ISNUMBER(F202),F202=0))),"Subscription",IF(ISNUMBER(G202),"Profit",IF(ISNUMBER(I202),"Disqualified",IF(ISNUMBER(H202),"Draw",IF(AND(ISNUMBER(F202),ISNUMBER(E202),E202&gt;0,F202&gt;E202),"Profit",IF(AND(ISNUMBER(F202),ISNUMBER(E202),E202&gt;0,F202=E202),"Draw",IF(AND(ISNUMBER(F202),ISNUMBER(E202),E202&gt;0,F202=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L202" s="50"/>
       <x:c r="M202" s="58"/>
@@ -8869,7 +8882,7 @@
         <x:f>IF(A203="","",IF(K203="Subscription","",IF(E203=0,"",IF(ISNUMBER(G203),G203/E203,IF(ISNUMBER(I203),-ABS(I203)/E203,IF(ISNUMBER(H203),0,IF(AND(ISNUMBER(F203),ISNUMBER(E203),E203&gt;0,F203&gt;E203),(F203-E203)/E203,IF(AND(ISNUMBER(F203),ISNUMBER(E203),E203&gt;0,F203=E203),0,IF(AND(ISNUMBER(F203),ISNUMBER(E203),E203&gt;0,F203=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K203" s="50" t="str">
-        <x:f>IF(A203="","",IF(AND(ISNUMBER(E203),E203=0,OR(ISNUMBER(SEARCH("Free",D203&amp;"")),AND(ISNUMBER(F203),F203=0))),"Subscription",IF(ISNUMBER(G203),"Profit",IF(ISNUMBER(I203),"Loss",IF(ISNUMBER(H203),"Draw",IF(AND(ISNUMBER(F203),ISNUMBER(E203),E203&gt;0,F203&gt;E203),"Profit",IF(AND(ISNUMBER(F203),ISNUMBER(E203),E203&gt;0,F203=E203),"Draw",IF(AND(ISNUMBER(F203),ISNUMBER(E203),E203&gt;0,F203=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A203="","",IF(AND(ISNUMBER(E203),E203=0,OR(ISNUMBER(SEARCH("Free",D203&amp;"")),AND(ISNUMBER(F203),F203=0))),"Subscription",IF(ISNUMBER(G203),"Profit",IF(ISNUMBER(I203),"Disqualified",IF(ISNUMBER(H203),"Draw",IF(AND(ISNUMBER(F203),ISNUMBER(E203),E203&gt;0,F203&gt;E203),"Profit",IF(AND(ISNUMBER(F203),ISNUMBER(E203),E203&gt;0,F203=E203),"Draw",IF(AND(ISNUMBER(F203),ISNUMBER(E203),E203&gt;0,F203=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L203" s="50"/>
       <x:c r="M203" s="58"/>
@@ -8906,7 +8919,7 @@
         <x:f>IF(A204="","",IF(K204="Subscription","",IF(E204=0,"",IF(ISNUMBER(G204),G204/E204,IF(ISNUMBER(I204),-ABS(I204)/E204,IF(ISNUMBER(H204),0,IF(AND(ISNUMBER(F204),ISNUMBER(E204),E204&gt;0,F204&gt;E204),(F204-E204)/E204,IF(AND(ISNUMBER(F204),ISNUMBER(E204),E204&gt;0,F204=E204),0,IF(AND(ISNUMBER(F204),ISNUMBER(E204),E204&gt;0,F204=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K204" s="50" t="str">
-        <x:f>IF(A204="","",IF(AND(ISNUMBER(E204),E204=0,OR(ISNUMBER(SEARCH("Free",D204&amp;"")),AND(ISNUMBER(F204),F204=0))),"Subscription",IF(ISNUMBER(G204),"Profit",IF(ISNUMBER(I204),"Loss",IF(ISNUMBER(H204),"Draw",IF(AND(ISNUMBER(F204),ISNUMBER(E204),E204&gt;0,F204&gt;E204),"Profit",IF(AND(ISNUMBER(F204),ISNUMBER(E204),E204&gt;0,F204=E204),"Draw",IF(AND(ISNUMBER(F204),ISNUMBER(E204),E204&gt;0,F204=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A204="","",IF(AND(ISNUMBER(E204),E204=0,OR(ISNUMBER(SEARCH("Free",D204&amp;"")),AND(ISNUMBER(F204),F204=0))),"Subscription",IF(ISNUMBER(G204),"Profit",IF(ISNUMBER(I204),"Disqualified",IF(ISNUMBER(H204),"Draw",IF(AND(ISNUMBER(F204),ISNUMBER(E204),E204&gt;0,F204&gt;E204),"Profit",IF(AND(ISNUMBER(F204),ISNUMBER(E204),E204&gt;0,F204=E204),"Draw",IF(AND(ISNUMBER(F204),ISNUMBER(E204),E204&gt;0,F204=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L204" s="50"/>
       <x:c r="M204" s="58"/>
@@ -8943,7 +8956,7 @@
         <x:f>IF(A205="","",IF(K205="Subscription","",IF(E205=0,"",IF(ISNUMBER(G205),G205/E205,IF(ISNUMBER(I205),-ABS(I205)/E205,IF(ISNUMBER(H205),0,IF(AND(ISNUMBER(F205),ISNUMBER(E205),E205&gt;0,F205&gt;E205),(F205-E205)/E205,IF(AND(ISNUMBER(F205),ISNUMBER(E205),E205&gt;0,F205=E205),0,IF(AND(ISNUMBER(F205),ISNUMBER(E205),E205&gt;0,F205=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K205" s="50" t="str">
-        <x:f>IF(A205="","",IF(AND(ISNUMBER(E205),E205=0,OR(ISNUMBER(SEARCH("Free",D205&amp;"")),AND(ISNUMBER(F205),F205=0))),"Subscription",IF(ISNUMBER(G205),"Profit",IF(ISNUMBER(I205),"Loss",IF(ISNUMBER(H205),"Draw",IF(AND(ISNUMBER(F205),ISNUMBER(E205),E205&gt;0,F205&gt;E205),"Profit",IF(AND(ISNUMBER(F205),ISNUMBER(E205),E205&gt;0,F205=E205),"Draw",IF(AND(ISNUMBER(F205),ISNUMBER(E205),E205&gt;0,F205=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A205="","",IF(AND(ISNUMBER(E205),E205=0,OR(ISNUMBER(SEARCH("Free",D205&amp;"")),AND(ISNUMBER(F205),F205=0))),"Subscription",IF(ISNUMBER(G205),"Profit",IF(ISNUMBER(I205),"Disqualified",IF(ISNUMBER(H205),"Draw",IF(AND(ISNUMBER(F205),ISNUMBER(E205),E205&gt;0,F205&gt;E205),"Profit",IF(AND(ISNUMBER(F205),ISNUMBER(E205),E205&gt;0,F205=E205),"Draw",IF(AND(ISNUMBER(F205),ISNUMBER(E205),E205&gt;0,F205=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L205" s="50"/>
       <x:c r="M205" s="58"/>
@@ -8980,7 +8993,7 @@
         <x:f>IF(A206="","",IF(K206="Subscription","",IF(E206=0,"",IF(ISNUMBER(G206),G206/E206,IF(ISNUMBER(I206),-ABS(I206)/E206,IF(ISNUMBER(H206),0,IF(AND(ISNUMBER(F206),ISNUMBER(E206),E206&gt;0,F206&gt;E206),(F206-E206)/E206,IF(AND(ISNUMBER(F206),ISNUMBER(E206),E206&gt;0,F206=E206),0,IF(AND(ISNUMBER(F206),ISNUMBER(E206),E206&gt;0,F206=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K206" s="50" t="str">
-        <x:f>IF(A206="","",IF(AND(ISNUMBER(E206),E206=0,OR(ISNUMBER(SEARCH("Free",D206&amp;"")),AND(ISNUMBER(F206),F206=0))),"Subscription",IF(ISNUMBER(G206),"Profit",IF(ISNUMBER(I206),"Loss",IF(ISNUMBER(H206),"Draw",IF(AND(ISNUMBER(F206),ISNUMBER(E206),E206&gt;0,F206&gt;E206),"Profit",IF(AND(ISNUMBER(F206),ISNUMBER(E206),E206&gt;0,F206=E206),"Draw",IF(AND(ISNUMBER(F206),ISNUMBER(E206),E206&gt;0,F206=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A206="","",IF(AND(ISNUMBER(E206),E206=0,OR(ISNUMBER(SEARCH("Free",D206&amp;"")),AND(ISNUMBER(F206),F206=0))),"Subscription",IF(ISNUMBER(G206),"Profit",IF(ISNUMBER(I206),"Disqualified",IF(ISNUMBER(H206),"Draw",IF(AND(ISNUMBER(F206),ISNUMBER(E206),E206&gt;0,F206&gt;E206),"Profit",IF(AND(ISNUMBER(F206),ISNUMBER(E206),E206&gt;0,F206=E206),"Draw",IF(AND(ISNUMBER(F206),ISNUMBER(E206),E206&gt;0,F206=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L206" s="50"/>
       <x:c r="M206" s="58"/>
@@ -9017,7 +9030,7 @@
         <x:f>IF(A207="","",IF(K207="Subscription","",IF(E207=0,"",IF(ISNUMBER(G207),G207/E207,IF(ISNUMBER(I207),-ABS(I207)/E207,IF(ISNUMBER(H207),0,IF(AND(ISNUMBER(F207),ISNUMBER(E207),E207&gt;0,F207&gt;E207),(F207-E207)/E207,IF(AND(ISNUMBER(F207),ISNUMBER(E207),E207&gt;0,F207=E207),0,IF(AND(ISNUMBER(F207),ISNUMBER(E207),E207&gt;0,F207=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K207" s="50" t="str">
-        <x:f>IF(A207="","",IF(AND(ISNUMBER(E207),E207=0,OR(ISNUMBER(SEARCH("Free",D207&amp;"")),AND(ISNUMBER(F207),F207=0))),"Subscription",IF(ISNUMBER(G207),"Profit",IF(ISNUMBER(I207),"Loss",IF(ISNUMBER(H207),"Draw",IF(AND(ISNUMBER(F207),ISNUMBER(E207),E207&gt;0,F207&gt;E207),"Profit",IF(AND(ISNUMBER(F207),ISNUMBER(E207),E207&gt;0,F207=E207),"Draw",IF(AND(ISNUMBER(F207),ISNUMBER(E207),E207&gt;0,F207=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A207="","",IF(AND(ISNUMBER(E207),E207=0,OR(ISNUMBER(SEARCH("Free",D207&amp;"")),AND(ISNUMBER(F207),F207=0))),"Subscription",IF(ISNUMBER(G207),"Profit",IF(ISNUMBER(I207),"Disqualified",IF(ISNUMBER(H207),"Draw",IF(AND(ISNUMBER(F207),ISNUMBER(E207),E207&gt;0,F207&gt;E207),"Profit",IF(AND(ISNUMBER(F207),ISNUMBER(E207),E207&gt;0,F207=E207),"Draw",IF(AND(ISNUMBER(F207),ISNUMBER(E207),E207&gt;0,F207=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L207" s="50"/>
       <x:c r="M207" s="58"/>
@@ -9054,7 +9067,7 @@
         <x:f>IF(A208="","",IF(K208="Subscription","",IF(E208=0,"",IF(ISNUMBER(G208),G208/E208,IF(ISNUMBER(I208),-ABS(I208)/E208,IF(ISNUMBER(H208),0,IF(AND(ISNUMBER(F208),ISNUMBER(E208),E208&gt;0,F208&gt;E208),(F208-E208)/E208,IF(AND(ISNUMBER(F208),ISNUMBER(E208),E208&gt;0,F208=E208),0,IF(AND(ISNUMBER(F208),ISNUMBER(E208),E208&gt;0,F208=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K208" s="50" t="str">
-        <x:f>IF(A208="","",IF(AND(ISNUMBER(E208),E208=0,OR(ISNUMBER(SEARCH("Free",D208&amp;"")),AND(ISNUMBER(F208),F208=0))),"Subscription",IF(ISNUMBER(G208),"Profit",IF(ISNUMBER(I208),"Loss",IF(ISNUMBER(H208),"Draw",IF(AND(ISNUMBER(F208),ISNUMBER(E208),E208&gt;0,F208&gt;E208),"Profit",IF(AND(ISNUMBER(F208),ISNUMBER(E208),E208&gt;0,F208=E208),"Draw",IF(AND(ISNUMBER(F208),ISNUMBER(E208),E208&gt;0,F208=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A208="","",IF(AND(ISNUMBER(E208),E208=0,OR(ISNUMBER(SEARCH("Free",D208&amp;"")),AND(ISNUMBER(F208),F208=0))),"Subscription",IF(ISNUMBER(G208),"Profit",IF(ISNUMBER(I208),"Disqualified",IF(ISNUMBER(H208),"Draw",IF(AND(ISNUMBER(F208),ISNUMBER(E208),E208&gt;0,F208&gt;E208),"Profit",IF(AND(ISNUMBER(F208),ISNUMBER(E208),E208&gt;0,F208=E208),"Draw",IF(AND(ISNUMBER(F208),ISNUMBER(E208),E208&gt;0,F208=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L208" s="50"/>
       <x:c r="M208" s="58"/>
@@ -9091,7 +9104,7 @@
         <x:f>IF(A209="","",IF(K209="Subscription","",IF(E209=0,"",IF(ISNUMBER(G209),G209/E209,IF(ISNUMBER(I209),-ABS(I209)/E209,IF(ISNUMBER(H209),0,IF(AND(ISNUMBER(F209),ISNUMBER(E209),E209&gt;0,F209&gt;E209),(F209-E209)/E209,IF(AND(ISNUMBER(F209),ISNUMBER(E209),E209&gt;0,F209=E209),0,IF(AND(ISNUMBER(F209),ISNUMBER(E209),E209&gt;0,F209=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K209" s="50" t="str">
-        <x:f>IF(A209="","",IF(AND(ISNUMBER(E209),E209=0,OR(ISNUMBER(SEARCH("Free",D209&amp;"")),AND(ISNUMBER(F209),F209=0))),"Subscription",IF(ISNUMBER(G209),"Profit",IF(ISNUMBER(I209),"Loss",IF(ISNUMBER(H209),"Draw",IF(AND(ISNUMBER(F209),ISNUMBER(E209),E209&gt;0,F209&gt;E209),"Profit",IF(AND(ISNUMBER(F209),ISNUMBER(E209),E209&gt;0,F209=E209),"Draw",IF(AND(ISNUMBER(F209),ISNUMBER(E209),E209&gt;0,F209=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A209="","",IF(AND(ISNUMBER(E209),E209=0,OR(ISNUMBER(SEARCH("Free",D209&amp;"")),AND(ISNUMBER(F209),F209=0))),"Subscription",IF(ISNUMBER(G209),"Profit",IF(ISNUMBER(I209),"Disqualified",IF(ISNUMBER(H209),"Draw",IF(AND(ISNUMBER(F209),ISNUMBER(E209),E209&gt;0,F209&gt;E209),"Profit",IF(AND(ISNUMBER(F209),ISNUMBER(E209),E209&gt;0,F209=E209),"Draw",IF(AND(ISNUMBER(F209),ISNUMBER(E209),E209&gt;0,F209=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L209" s="50"/>
       <x:c r="M209" s="58"/>
@@ -9128,7 +9141,7 @@
         <x:f>IF(A210="","",IF(K210="Subscription","",IF(E210=0,"",IF(ISNUMBER(G210),G210/E210,IF(ISNUMBER(I210),-ABS(I210)/E210,IF(ISNUMBER(H210),0,IF(AND(ISNUMBER(F210),ISNUMBER(E210),E210&gt;0,F210&gt;E210),(F210-E210)/E210,IF(AND(ISNUMBER(F210),ISNUMBER(E210),E210&gt;0,F210=E210),0,IF(AND(ISNUMBER(F210),ISNUMBER(E210),E210&gt;0,F210=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K210" s="50" t="str">
-        <x:f>IF(A210="","",IF(AND(ISNUMBER(E210),E210=0,OR(ISNUMBER(SEARCH("Free",D210&amp;"")),AND(ISNUMBER(F210),F210=0))),"Subscription",IF(ISNUMBER(G210),"Profit",IF(ISNUMBER(I210),"Loss",IF(ISNUMBER(H210),"Draw",IF(AND(ISNUMBER(F210),ISNUMBER(E210),E210&gt;0,F210&gt;E210),"Profit",IF(AND(ISNUMBER(F210),ISNUMBER(E210),E210&gt;0,F210=E210),"Draw",IF(AND(ISNUMBER(F210),ISNUMBER(E210),E210&gt;0,F210=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A210="","",IF(AND(ISNUMBER(E210),E210=0,OR(ISNUMBER(SEARCH("Free",D210&amp;"")),AND(ISNUMBER(F210),F210=0))),"Subscription",IF(ISNUMBER(G210),"Profit",IF(ISNUMBER(I210),"Disqualified",IF(ISNUMBER(H210),"Draw",IF(AND(ISNUMBER(F210),ISNUMBER(E210),E210&gt;0,F210&gt;E210),"Profit",IF(AND(ISNUMBER(F210),ISNUMBER(E210),E210&gt;0,F210=E210),"Draw",IF(AND(ISNUMBER(F210),ISNUMBER(E210),E210&gt;0,F210=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L210" s="50"/>
       <x:c r="M210" s="58"/>
@@ -9165,7 +9178,7 @@
         <x:f>IF(A211="","",IF(K211="Subscription","",IF(E211=0,"",IF(ISNUMBER(G211),G211/E211,IF(ISNUMBER(I211),-ABS(I211)/E211,IF(ISNUMBER(H211),0,IF(AND(ISNUMBER(F211),ISNUMBER(E211),E211&gt;0,F211&gt;E211),(F211-E211)/E211,IF(AND(ISNUMBER(F211),ISNUMBER(E211),E211&gt;0,F211=E211),0,IF(AND(ISNUMBER(F211),ISNUMBER(E211),E211&gt;0,F211=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K211" s="50" t="str">
-        <x:f>IF(A211="","",IF(AND(ISNUMBER(E211),E211=0,OR(ISNUMBER(SEARCH("Free",D211&amp;"")),AND(ISNUMBER(F211),F211=0))),"Subscription",IF(ISNUMBER(G211),"Profit",IF(ISNUMBER(I211),"Loss",IF(ISNUMBER(H211),"Draw",IF(AND(ISNUMBER(F211),ISNUMBER(E211),E211&gt;0,F211&gt;E211),"Profit",IF(AND(ISNUMBER(F211),ISNUMBER(E211),E211&gt;0,F211=E211),"Draw",IF(AND(ISNUMBER(F211),ISNUMBER(E211),E211&gt;0,F211=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A211="","",IF(AND(ISNUMBER(E211),E211=0,OR(ISNUMBER(SEARCH("Free",D211&amp;"")),AND(ISNUMBER(F211),F211=0))),"Subscription",IF(ISNUMBER(G211),"Profit",IF(ISNUMBER(I211),"Disqualified",IF(ISNUMBER(H211),"Draw",IF(AND(ISNUMBER(F211),ISNUMBER(E211),E211&gt;0,F211&gt;E211),"Profit",IF(AND(ISNUMBER(F211),ISNUMBER(E211),E211&gt;0,F211=E211),"Draw",IF(AND(ISNUMBER(F211),ISNUMBER(E211),E211&gt;0,F211=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L211" s="50"/>
       <x:c r="M211" s="58"/>
@@ -9202,7 +9215,7 @@
         <x:f>IF(A212="","",IF(K212="Subscription","",IF(E212=0,"",IF(ISNUMBER(G212),G212/E212,IF(ISNUMBER(I212),-ABS(I212)/E212,IF(ISNUMBER(H212),0,IF(AND(ISNUMBER(F212),ISNUMBER(E212),E212&gt;0,F212&gt;E212),(F212-E212)/E212,IF(AND(ISNUMBER(F212),ISNUMBER(E212),E212&gt;0,F212=E212),0,IF(AND(ISNUMBER(F212),ISNUMBER(E212),E212&gt;0,F212=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K212" s="50" t="str">
-        <x:f>IF(A212="","",IF(AND(ISNUMBER(E212),E212=0,OR(ISNUMBER(SEARCH("Free",D212&amp;"")),AND(ISNUMBER(F212),F212=0))),"Subscription",IF(ISNUMBER(G212),"Profit",IF(ISNUMBER(I212),"Loss",IF(ISNUMBER(H212),"Draw",IF(AND(ISNUMBER(F212),ISNUMBER(E212),E212&gt;0,F212&gt;E212),"Profit",IF(AND(ISNUMBER(F212),ISNUMBER(E212),E212&gt;0,F212=E212),"Draw",IF(AND(ISNUMBER(F212),ISNUMBER(E212),E212&gt;0,F212=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A212="","",IF(AND(ISNUMBER(E212),E212=0,OR(ISNUMBER(SEARCH("Free",D212&amp;"")),AND(ISNUMBER(F212),F212=0))),"Subscription",IF(ISNUMBER(G212),"Profit",IF(ISNUMBER(I212),"Disqualified",IF(ISNUMBER(H212),"Draw",IF(AND(ISNUMBER(F212),ISNUMBER(E212),E212&gt;0,F212&gt;E212),"Profit",IF(AND(ISNUMBER(F212),ISNUMBER(E212),E212&gt;0,F212=E212),"Draw",IF(AND(ISNUMBER(F212),ISNUMBER(E212),E212&gt;0,F212=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L212" s="50"/>
       <x:c r="M212" s="58"/>
@@ -9239,7 +9252,7 @@
         <x:f>IF(A213="","",IF(K213="Subscription","",IF(E213=0,"",IF(ISNUMBER(G213),G213/E213,IF(ISNUMBER(I213),-ABS(I213)/E213,IF(ISNUMBER(H213),0,IF(AND(ISNUMBER(F213),ISNUMBER(E213),E213&gt;0,F213&gt;E213),(F213-E213)/E213,IF(AND(ISNUMBER(F213),ISNUMBER(E213),E213&gt;0,F213=E213),0,IF(AND(ISNUMBER(F213),ISNUMBER(E213),E213&gt;0,F213=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K213" s="50" t="str">
-        <x:f>IF(A213="","",IF(AND(ISNUMBER(E213),E213=0,OR(ISNUMBER(SEARCH("Free",D213&amp;"")),AND(ISNUMBER(F213),F213=0))),"Subscription",IF(ISNUMBER(G213),"Profit",IF(ISNUMBER(I213),"Loss",IF(ISNUMBER(H213),"Draw",IF(AND(ISNUMBER(F213),ISNUMBER(E213),E213&gt;0,F213&gt;E213),"Profit",IF(AND(ISNUMBER(F213),ISNUMBER(E213),E213&gt;0,F213=E213),"Draw",IF(AND(ISNUMBER(F213),ISNUMBER(E213),E213&gt;0,F213=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A213="","",IF(AND(ISNUMBER(E213),E213=0,OR(ISNUMBER(SEARCH("Free",D213&amp;"")),AND(ISNUMBER(F213),F213=0))),"Subscription",IF(ISNUMBER(G213),"Profit",IF(ISNUMBER(I213),"Disqualified",IF(ISNUMBER(H213),"Draw",IF(AND(ISNUMBER(F213),ISNUMBER(E213),E213&gt;0,F213&gt;E213),"Profit",IF(AND(ISNUMBER(F213),ISNUMBER(E213),E213&gt;0,F213=E213),"Draw",IF(AND(ISNUMBER(F213),ISNUMBER(E213),E213&gt;0,F213=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L213" s="50"/>
       <x:c r="M213" s="58"/>
@@ -9276,7 +9289,7 @@
         <x:f>IF(A214="","",IF(K214="Subscription","",IF(E214=0,"",IF(ISNUMBER(G214),G214/E214,IF(ISNUMBER(I214),-ABS(I214)/E214,IF(ISNUMBER(H214),0,IF(AND(ISNUMBER(F214),ISNUMBER(E214),E214&gt;0,F214&gt;E214),(F214-E214)/E214,IF(AND(ISNUMBER(F214),ISNUMBER(E214),E214&gt;0,F214=E214),0,IF(AND(ISNUMBER(F214),ISNUMBER(E214),E214&gt;0,F214=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K214" s="50" t="str">
-        <x:f>IF(A214="","",IF(AND(ISNUMBER(E214),E214=0,OR(ISNUMBER(SEARCH("Free",D214&amp;"")),AND(ISNUMBER(F214),F214=0))),"Subscription",IF(ISNUMBER(G214),"Profit",IF(ISNUMBER(I214),"Loss",IF(ISNUMBER(H214),"Draw",IF(AND(ISNUMBER(F214),ISNUMBER(E214),E214&gt;0,F214&gt;E214),"Profit",IF(AND(ISNUMBER(F214),ISNUMBER(E214),E214&gt;0,F214=E214),"Draw",IF(AND(ISNUMBER(F214),ISNUMBER(E214),E214&gt;0,F214=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A214="","",IF(AND(ISNUMBER(E214),E214=0,OR(ISNUMBER(SEARCH("Free",D214&amp;"")),AND(ISNUMBER(F214),F214=0))),"Subscription",IF(ISNUMBER(G214),"Profit",IF(ISNUMBER(I214),"Disqualified",IF(ISNUMBER(H214),"Draw",IF(AND(ISNUMBER(F214),ISNUMBER(E214),E214&gt;0,F214&gt;E214),"Profit",IF(AND(ISNUMBER(F214),ISNUMBER(E214),E214&gt;0,F214=E214),"Draw",IF(AND(ISNUMBER(F214),ISNUMBER(E214),E214&gt;0,F214=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L214" s="50"/>
       <x:c r="M214" s="58"/>
@@ -9313,7 +9326,7 @@
         <x:f>IF(A215="","",IF(K215="Subscription","",IF(E215=0,"",IF(ISNUMBER(G215),G215/E215,IF(ISNUMBER(I215),-ABS(I215)/E215,IF(ISNUMBER(H215),0,IF(AND(ISNUMBER(F215),ISNUMBER(E215),E215&gt;0,F215&gt;E215),(F215-E215)/E215,IF(AND(ISNUMBER(F215),ISNUMBER(E215),E215&gt;0,F215=E215),0,IF(AND(ISNUMBER(F215),ISNUMBER(E215),E215&gt;0,F215=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K215" s="50" t="str">
-        <x:f>IF(A215="","",IF(AND(ISNUMBER(E215),E215=0,OR(ISNUMBER(SEARCH("Free",D215&amp;"")),AND(ISNUMBER(F215),F215=0))),"Subscription",IF(ISNUMBER(G215),"Profit",IF(ISNUMBER(I215),"Loss",IF(ISNUMBER(H215),"Draw",IF(AND(ISNUMBER(F215),ISNUMBER(E215),E215&gt;0,F215&gt;E215),"Profit",IF(AND(ISNUMBER(F215),ISNUMBER(E215),E215&gt;0,F215=E215),"Draw",IF(AND(ISNUMBER(F215),ISNUMBER(E215),E215&gt;0,F215=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A215="","",IF(AND(ISNUMBER(E215),E215=0,OR(ISNUMBER(SEARCH("Free",D215&amp;"")),AND(ISNUMBER(F215),F215=0))),"Subscription",IF(ISNUMBER(G215),"Profit",IF(ISNUMBER(I215),"Disqualified",IF(ISNUMBER(H215),"Draw",IF(AND(ISNUMBER(F215),ISNUMBER(E215),E215&gt;0,F215&gt;E215),"Profit",IF(AND(ISNUMBER(F215),ISNUMBER(E215),E215&gt;0,F215=E215),"Draw",IF(AND(ISNUMBER(F215),ISNUMBER(E215),E215&gt;0,F215=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L215" s="50"/>
       <x:c r="M215" s="58"/>
@@ -9350,7 +9363,7 @@
         <x:f>IF(A216="","",IF(K216="Subscription","",IF(E216=0,"",IF(ISNUMBER(G216),G216/E216,IF(ISNUMBER(I216),-ABS(I216)/E216,IF(ISNUMBER(H216),0,IF(AND(ISNUMBER(F216),ISNUMBER(E216),E216&gt;0,F216&gt;E216),(F216-E216)/E216,IF(AND(ISNUMBER(F216),ISNUMBER(E216),E216&gt;0,F216=E216),0,IF(AND(ISNUMBER(F216),ISNUMBER(E216),E216&gt;0,F216=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K216" s="50" t="str">
-        <x:f>IF(A216="","",IF(AND(ISNUMBER(E216),E216=0,OR(ISNUMBER(SEARCH("Free",D216&amp;"")),AND(ISNUMBER(F216),F216=0))),"Subscription",IF(ISNUMBER(G216),"Profit",IF(ISNUMBER(I216),"Loss",IF(ISNUMBER(H216),"Draw",IF(AND(ISNUMBER(F216),ISNUMBER(E216),E216&gt;0,F216&gt;E216),"Profit",IF(AND(ISNUMBER(F216),ISNUMBER(E216),E216&gt;0,F216=E216),"Draw",IF(AND(ISNUMBER(F216),ISNUMBER(E216),E216&gt;0,F216=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A216="","",IF(AND(ISNUMBER(E216),E216=0,OR(ISNUMBER(SEARCH("Free",D216&amp;"")),AND(ISNUMBER(F216),F216=0))),"Subscription",IF(ISNUMBER(G216),"Profit",IF(ISNUMBER(I216),"Disqualified",IF(ISNUMBER(H216),"Draw",IF(AND(ISNUMBER(F216),ISNUMBER(E216),E216&gt;0,F216&gt;E216),"Profit",IF(AND(ISNUMBER(F216),ISNUMBER(E216),E216&gt;0,F216=E216),"Draw",IF(AND(ISNUMBER(F216),ISNUMBER(E216),E216&gt;0,F216=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L216" s="50"/>
       <x:c r="M216" s="58"/>
@@ -9387,7 +9400,7 @@
         <x:f>IF(A217="","",IF(K217="Subscription","",IF(E217=0,"",IF(ISNUMBER(G217),G217/E217,IF(ISNUMBER(I217),-ABS(I217)/E217,IF(ISNUMBER(H217),0,IF(AND(ISNUMBER(F217),ISNUMBER(E217),E217&gt;0,F217&gt;E217),(F217-E217)/E217,IF(AND(ISNUMBER(F217),ISNUMBER(E217),E217&gt;0,F217=E217),0,IF(AND(ISNUMBER(F217),ISNUMBER(E217),E217&gt;0,F217=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K217" s="50" t="str">
-        <x:f>IF(A217="","",IF(AND(ISNUMBER(E217),E217=0,OR(ISNUMBER(SEARCH("Free",D217&amp;"")),AND(ISNUMBER(F217),F217=0))),"Subscription",IF(ISNUMBER(G217),"Profit",IF(ISNUMBER(I217),"Loss",IF(ISNUMBER(H217),"Draw",IF(AND(ISNUMBER(F217),ISNUMBER(E217),E217&gt;0,F217&gt;E217),"Profit",IF(AND(ISNUMBER(F217),ISNUMBER(E217),E217&gt;0,F217=E217),"Draw",IF(AND(ISNUMBER(F217),ISNUMBER(E217),E217&gt;0,F217=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A217="","",IF(AND(ISNUMBER(E217),E217=0,OR(ISNUMBER(SEARCH("Free",D217&amp;"")),AND(ISNUMBER(F217),F217=0))),"Subscription",IF(ISNUMBER(G217),"Profit",IF(ISNUMBER(I217),"Disqualified",IF(ISNUMBER(H217),"Draw",IF(AND(ISNUMBER(F217),ISNUMBER(E217),E217&gt;0,F217&gt;E217),"Profit",IF(AND(ISNUMBER(F217),ISNUMBER(E217),E217&gt;0,F217=E217),"Draw",IF(AND(ISNUMBER(F217),ISNUMBER(E217),E217&gt;0,F217=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L217" s="50"/>
       <x:c r="M217" s="58"/>
@@ -9424,7 +9437,7 @@
         <x:f>IF(A218="","",IF(K218="Subscription","",IF(E218=0,"",IF(ISNUMBER(G218),G218/E218,IF(ISNUMBER(I218),-ABS(I218)/E218,IF(ISNUMBER(H218),0,IF(AND(ISNUMBER(F218),ISNUMBER(E218),E218&gt;0,F218&gt;E218),(F218-E218)/E218,IF(AND(ISNUMBER(F218),ISNUMBER(E218),E218&gt;0,F218=E218),0,IF(AND(ISNUMBER(F218),ISNUMBER(E218),E218&gt;0,F218=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K218" s="50" t="str">
-        <x:f>IF(A218="","",IF(AND(ISNUMBER(E218),E218=0,OR(ISNUMBER(SEARCH("Free",D218&amp;"")),AND(ISNUMBER(F218),F218=0))),"Subscription",IF(ISNUMBER(G218),"Profit",IF(ISNUMBER(I218),"Loss",IF(ISNUMBER(H218),"Draw",IF(AND(ISNUMBER(F218),ISNUMBER(E218),E218&gt;0,F218&gt;E218),"Profit",IF(AND(ISNUMBER(F218),ISNUMBER(E218),E218&gt;0,F218=E218),"Draw",IF(AND(ISNUMBER(F218),ISNUMBER(E218),E218&gt;0,F218=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A218="","",IF(AND(ISNUMBER(E218),E218=0,OR(ISNUMBER(SEARCH("Free",D218&amp;"")),AND(ISNUMBER(F218),F218=0))),"Subscription",IF(ISNUMBER(G218),"Profit",IF(ISNUMBER(I218),"Disqualified",IF(ISNUMBER(H218),"Draw",IF(AND(ISNUMBER(F218),ISNUMBER(E218),E218&gt;0,F218&gt;E218),"Profit",IF(AND(ISNUMBER(F218),ISNUMBER(E218),E218&gt;0,F218=E218),"Draw",IF(AND(ISNUMBER(F218),ISNUMBER(E218),E218&gt;0,F218=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L218" s="50"/>
       <x:c r="M218" s="58"/>
@@ -9461,7 +9474,7 @@
         <x:f>IF(A219="","",IF(K219="Subscription","",IF(E219=0,"",IF(ISNUMBER(G219),G219/E219,IF(ISNUMBER(I219),-ABS(I219)/E219,IF(ISNUMBER(H219),0,IF(AND(ISNUMBER(F219),ISNUMBER(E219),E219&gt;0,F219&gt;E219),(F219-E219)/E219,IF(AND(ISNUMBER(F219),ISNUMBER(E219),E219&gt;0,F219=E219),0,IF(AND(ISNUMBER(F219),ISNUMBER(E219),E219&gt;0,F219=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K219" s="50" t="str">
-        <x:f>IF(A219="","",IF(AND(ISNUMBER(E219),E219=0,OR(ISNUMBER(SEARCH("Free",D219&amp;"")),AND(ISNUMBER(F219),F219=0))),"Subscription",IF(ISNUMBER(G219),"Profit",IF(ISNUMBER(I219),"Loss",IF(ISNUMBER(H219),"Draw",IF(AND(ISNUMBER(F219),ISNUMBER(E219),E219&gt;0,F219&gt;E219),"Profit",IF(AND(ISNUMBER(F219),ISNUMBER(E219),E219&gt;0,F219=E219),"Draw",IF(AND(ISNUMBER(F219),ISNUMBER(E219),E219&gt;0,F219=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A219="","",IF(AND(ISNUMBER(E219),E219=0,OR(ISNUMBER(SEARCH("Free",D219&amp;"")),AND(ISNUMBER(F219),F219=0))),"Subscription",IF(ISNUMBER(G219),"Profit",IF(ISNUMBER(I219),"Disqualified",IF(ISNUMBER(H219),"Draw",IF(AND(ISNUMBER(F219),ISNUMBER(E219),E219&gt;0,F219&gt;E219),"Profit",IF(AND(ISNUMBER(F219),ISNUMBER(E219),E219&gt;0,F219=E219),"Draw",IF(AND(ISNUMBER(F219),ISNUMBER(E219),E219&gt;0,F219=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L219" s="50"/>
       <x:c r="M219" s="58"/>
@@ -9498,7 +9511,7 @@
         <x:f>IF(A220="","",IF(K220="Subscription","",IF(E220=0,"",IF(ISNUMBER(G220),G220/E220,IF(ISNUMBER(I220),-ABS(I220)/E220,IF(ISNUMBER(H220),0,IF(AND(ISNUMBER(F220),ISNUMBER(E220),E220&gt;0,F220&gt;E220),(F220-E220)/E220,IF(AND(ISNUMBER(F220),ISNUMBER(E220),E220&gt;0,F220=E220),0,IF(AND(ISNUMBER(F220),ISNUMBER(E220),E220&gt;0,F220=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K220" s="50" t="str">
-        <x:f>IF(A220="","",IF(AND(ISNUMBER(E220),E220=0,OR(ISNUMBER(SEARCH("Free",D220&amp;"")),AND(ISNUMBER(F220),F220=0))),"Subscription",IF(ISNUMBER(G220),"Profit",IF(ISNUMBER(I220),"Loss",IF(ISNUMBER(H220),"Draw",IF(AND(ISNUMBER(F220),ISNUMBER(E220),E220&gt;0,F220&gt;E220),"Profit",IF(AND(ISNUMBER(F220),ISNUMBER(E220),E220&gt;0,F220=E220),"Draw",IF(AND(ISNUMBER(F220),ISNUMBER(E220),E220&gt;0,F220=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A220="","",IF(AND(ISNUMBER(E220),E220=0,OR(ISNUMBER(SEARCH("Free",D220&amp;"")),AND(ISNUMBER(F220),F220=0))),"Subscription",IF(ISNUMBER(G220),"Profit",IF(ISNUMBER(I220),"Disqualified",IF(ISNUMBER(H220),"Draw",IF(AND(ISNUMBER(F220),ISNUMBER(E220),E220&gt;0,F220&gt;E220),"Profit",IF(AND(ISNUMBER(F220),ISNUMBER(E220),E220&gt;0,F220=E220),"Draw",IF(AND(ISNUMBER(F220),ISNUMBER(E220),E220&gt;0,F220=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L220" s="50"/>
       <x:c r="M220" s="58"/>
@@ -9535,7 +9548,7 @@
         <x:f>IF(A221="","",IF(K221="Subscription","",IF(E221=0,"",IF(ISNUMBER(G221),G221/E221,IF(ISNUMBER(I221),-ABS(I221)/E221,IF(ISNUMBER(H221),0,IF(AND(ISNUMBER(F221),ISNUMBER(E221),E221&gt;0,F221&gt;E221),(F221-E221)/E221,IF(AND(ISNUMBER(F221),ISNUMBER(E221),E221&gt;0,F221=E221),0,IF(AND(ISNUMBER(F221),ISNUMBER(E221),E221&gt;0,F221=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K221" s="50" t="str">
-        <x:f>IF(A221="","",IF(AND(ISNUMBER(E221),E221=0,OR(ISNUMBER(SEARCH("Free",D221&amp;"")),AND(ISNUMBER(F221),F221=0))),"Subscription",IF(ISNUMBER(G221),"Profit",IF(ISNUMBER(I221),"Loss",IF(ISNUMBER(H221),"Draw",IF(AND(ISNUMBER(F221),ISNUMBER(E221),E221&gt;0,F221&gt;E221),"Profit",IF(AND(ISNUMBER(F221),ISNUMBER(E221),E221&gt;0,F221=E221),"Draw",IF(AND(ISNUMBER(F221),ISNUMBER(E221),E221&gt;0,F221=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A221="","",IF(AND(ISNUMBER(E221),E221=0,OR(ISNUMBER(SEARCH("Free",D221&amp;"")),AND(ISNUMBER(F221),F221=0))),"Subscription",IF(ISNUMBER(G221),"Profit",IF(ISNUMBER(I221),"Disqualified",IF(ISNUMBER(H221),"Draw",IF(AND(ISNUMBER(F221),ISNUMBER(E221),E221&gt;0,F221&gt;E221),"Profit",IF(AND(ISNUMBER(F221),ISNUMBER(E221),E221&gt;0,F221=E221),"Draw",IF(AND(ISNUMBER(F221),ISNUMBER(E221),E221&gt;0,F221=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L221" s="50"/>
       <x:c r="M221" s="58"/>
@@ -9572,7 +9585,7 @@
         <x:f>IF(A222="","",IF(K222="Subscription","",IF(E222=0,"",IF(ISNUMBER(G222),G222/E222,IF(ISNUMBER(I222),-ABS(I222)/E222,IF(ISNUMBER(H222),0,IF(AND(ISNUMBER(F222),ISNUMBER(E222),E222&gt;0,F222&gt;E222),(F222-E222)/E222,IF(AND(ISNUMBER(F222),ISNUMBER(E222),E222&gt;0,F222=E222),0,IF(AND(ISNUMBER(F222),ISNUMBER(E222),E222&gt;0,F222=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K222" s="50" t="str">
-        <x:f>IF(A222="","",IF(AND(ISNUMBER(E222),E222=0,OR(ISNUMBER(SEARCH("Free",D222&amp;"")),AND(ISNUMBER(F222),F222=0))),"Subscription",IF(ISNUMBER(G222),"Profit",IF(ISNUMBER(I222),"Loss",IF(ISNUMBER(H222),"Draw",IF(AND(ISNUMBER(F222),ISNUMBER(E222),E222&gt;0,F222&gt;E222),"Profit",IF(AND(ISNUMBER(F222),ISNUMBER(E222),E222&gt;0,F222=E222),"Draw",IF(AND(ISNUMBER(F222),ISNUMBER(E222),E222&gt;0,F222=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A222="","",IF(AND(ISNUMBER(E222),E222=0,OR(ISNUMBER(SEARCH("Free",D222&amp;"")),AND(ISNUMBER(F222),F222=0))),"Subscription",IF(ISNUMBER(G222),"Profit",IF(ISNUMBER(I222),"Disqualified",IF(ISNUMBER(H222),"Draw",IF(AND(ISNUMBER(F222),ISNUMBER(E222),E222&gt;0,F222&gt;E222),"Profit",IF(AND(ISNUMBER(F222),ISNUMBER(E222),E222&gt;0,F222=E222),"Draw",IF(AND(ISNUMBER(F222),ISNUMBER(E222),E222&gt;0,F222=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L222" s="50"/>
       <x:c r="M222" s="58"/>
@@ -9609,7 +9622,7 @@
         <x:f>IF(A223="","",IF(K223="Subscription","",IF(E223=0,"",IF(ISNUMBER(G223),G223/E223,IF(ISNUMBER(I223),-ABS(I223)/E223,IF(ISNUMBER(H223),0,IF(AND(ISNUMBER(F223),ISNUMBER(E223),E223&gt;0,F223&gt;E223),(F223-E223)/E223,IF(AND(ISNUMBER(F223),ISNUMBER(E223),E223&gt;0,F223=E223),0,IF(AND(ISNUMBER(F223),ISNUMBER(E223),E223&gt;0,F223=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K223" s="50" t="str">
-        <x:f>IF(A223="","",IF(AND(ISNUMBER(E223),E223=0,OR(ISNUMBER(SEARCH("Free",D223&amp;"")),AND(ISNUMBER(F223),F223=0))),"Subscription",IF(ISNUMBER(G223),"Profit",IF(ISNUMBER(I223),"Loss",IF(ISNUMBER(H223),"Draw",IF(AND(ISNUMBER(F223),ISNUMBER(E223),E223&gt;0,F223&gt;E223),"Profit",IF(AND(ISNUMBER(F223),ISNUMBER(E223),E223&gt;0,F223=E223),"Draw",IF(AND(ISNUMBER(F223),ISNUMBER(E223),E223&gt;0,F223=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A223="","",IF(AND(ISNUMBER(E223),E223=0,OR(ISNUMBER(SEARCH("Free",D223&amp;"")),AND(ISNUMBER(F223),F223=0))),"Subscription",IF(ISNUMBER(G223),"Profit",IF(ISNUMBER(I223),"Disqualified",IF(ISNUMBER(H223),"Draw",IF(AND(ISNUMBER(F223),ISNUMBER(E223),E223&gt;0,F223&gt;E223),"Profit",IF(AND(ISNUMBER(F223),ISNUMBER(E223),E223&gt;0,F223=E223),"Draw",IF(AND(ISNUMBER(F223),ISNUMBER(E223),E223&gt;0,F223=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L223" s="50"/>
       <x:c r="M223" s="58"/>
@@ -9646,7 +9659,7 @@
         <x:f>IF(A224="","",IF(K224="Subscription","",IF(E224=0,"",IF(ISNUMBER(G224),G224/E224,IF(ISNUMBER(I224),-ABS(I224)/E224,IF(ISNUMBER(H224),0,IF(AND(ISNUMBER(F224),ISNUMBER(E224),E224&gt;0,F224&gt;E224),(F224-E224)/E224,IF(AND(ISNUMBER(F224),ISNUMBER(E224),E224&gt;0,F224=E224),0,IF(AND(ISNUMBER(F224),ISNUMBER(E224),E224&gt;0,F224=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K224" s="50" t="str">
-        <x:f>IF(A224="","",IF(AND(ISNUMBER(E224),E224=0,OR(ISNUMBER(SEARCH("Free",D224&amp;"")),AND(ISNUMBER(F224),F224=0))),"Subscription",IF(ISNUMBER(G224),"Profit",IF(ISNUMBER(I224),"Loss",IF(ISNUMBER(H224),"Draw",IF(AND(ISNUMBER(F224),ISNUMBER(E224),E224&gt;0,F224&gt;E224),"Profit",IF(AND(ISNUMBER(F224),ISNUMBER(E224),E224&gt;0,F224=E224),"Draw",IF(AND(ISNUMBER(F224),ISNUMBER(E224),E224&gt;0,F224=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A224="","",IF(AND(ISNUMBER(E224),E224=0,OR(ISNUMBER(SEARCH("Free",D224&amp;"")),AND(ISNUMBER(F224),F224=0))),"Subscription",IF(ISNUMBER(G224),"Profit",IF(ISNUMBER(I224),"Disqualified",IF(ISNUMBER(H224),"Draw",IF(AND(ISNUMBER(F224),ISNUMBER(E224),E224&gt;0,F224&gt;E224),"Profit",IF(AND(ISNUMBER(F224),ISNUMBER(E224),E224&gt;0,F224=E224),"Draw",IF(AND(ISNUMBER(F224),ISNUMBER(E224),E224&gt;0,F224=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L224" s="50"/>
       <x:c r="M224" s="58"/>
@@ -9683,7 +9696,7 @@
         <x:f>IF(A225="","",IF(K225="Subscription","",IF(E225=0,"",IF(ISNUMBER(G225),G225/E225,IF(ISNUMBER(I225),-ABS(I225)/E225,IF(ISNUMBER(H225),0,IF(AND(ISNUMBER(F225),ISNUMBER(E225),E225&gt;0,F225&gt;E225),(F225-E225)/E225,IF(AND(ISNUMBER(F225),ISNUMBER(E225),E225&gt;0,F225=E225),0,IF(AND(ISNUMBER(F225),ISNUMBER(E225),E225&gt;0,F225=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K225" s="50" t="str">
-        <x:f>IF(A225="","",IF(AND(ISNUMBER(E225),E225=0,OR(ISNUMBER(SEARCH("Free",D225&amp;"")),AND(ISNUMBER(F225),F225=0))),"Subscription",IF(ISNUMBER(G225),"Profit",IF(ISNUMBER(I225),"Loss",IF(ISNUMBER(H225),"Draw",IF(AND(ISNUMBER(F225),ISNUMBER(E225),E225&gt;0,F225&gt;E225),"Profit",IF(AND(ISNUMBER(F225),ISNUMBER(E225),E225&gt;0,F225=E225),"Draw",IF(AND(ISNUMBER(F225),ISNUMBER(E225),E225&gt;0,F225=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A225="","",IF(AND(ISNUMBER(E225),E225=0,OR(ISNUMBER(SEARCH("Free",D225&amp;"")),AND(ISNUMBER(F225),F225=0))),"Subscription",IF(ISNUMBER(G225),"Profit",IF(ISNUMBER(I225),"Disqualified",IF(ISNUMBER(H225),"Draw",IF(AND(ISNUMBER(F225),ISNUMBER(E225),E225&gt;0,F225&gt;E225),"Profit",IF(AND(ISNUMBER(F225),ISNUMBER(E225),E225&gt;0,F225=E225),"Draw",IF(AND(ISNUMBER(F225),ISNUMBER(E225),E225&gt;0,F225=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L225" s="50"/>
       <x:c r="M225" s="58"/>
@@ -9720,7 +9733,7 @@
         <x:f>IF(A226="","",IF(K226="Subscription","",IF(E226=0,"",IF(ISNUMBER(G226),G226/E226,IF(ISNUMBER(I226),-ABS(I226)/E226,IF(ISNUMBER(H226),0,IF(AND(ISNUMBER(F226),ISNUMBER(E226),E226&gt;0,F226&gt;E226),(F226-E226)/E226,IF(AND(ISNUMBER(F226),ISNUMBER(E226),E226&gt;0,F226=E226),0,IF(AND(ISNUMBER(F226),ISNUMBER(E226),E226&gt;0,F226=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K226" s="50" t="str">
-        <x:f>IF(A226="","",IF(AND(ISNUMBER(E226),E226=0,OR(ISNUMBER(SEARCH("Free",D226&amp;"")),AND(ISNUMBER(F226),F226=0))),"Subscription",IF(ISNUMBER(G226),"Profit",IF(ISNUMBER(I226),"Loss",IF(ISNUMBER(H226),"Draw",IF(AND(ISNUMBER(F226),ISNUMBER(E226),E226&gt;0,F226&gt;E226),"Profit",IF(AND(ISNUMBER(F226),ISNUMBER(E226),E226&gt;0,F226=E226),"Draw",IF(AND(ISNUMBER(F226),ISNUMBER(E226),E226&gt;0,F226=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A226="","",IF(AND(ISNUMBER(E226),E226=0,OR(ISNUMBER(SEARCH("Free",D226&amp;"")),AND(ISNUMBER(F226),F226=0))),"Subscription",IF(ISNUMBER(G226),"Profit",IF(ISNUMBER(I226),"Disqualified",IF(ISNUMBER(H226),"Draw",IF(AND(ISNUMBER(F226),ISNUMBER(E226),E226&gt;0,F226&gt;E226),"Profit",IF(AND(ISNUMBER(F226),ISNUMBER(E226),E226&gt;0,F226=E226),"Draw",IF(AND(ISNUMBER(F226),ISNUMBER(E226),E226&gt;0,F226=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L226" s="50"/>
       <x:c r="M226" s="58"/>
@@ -9757,7 +9770,7 @@
         <x:f>IF(A227="","",IF(K227="Subscription","",IF(E227=0,"",IF(ISNUMBER(G227),G227/E227,IF(ISNUMBER(I227),-ABS(I227)/E227,IF(ISNUMBER(H227),0,IF(AND(ISNUMBER(F227),ISNUMBER(E227),E227&gt;0,F227&gt;E227),(F227-E227)/E227,IF(AND(ISNUMBER(F227),ISNUMBER(E227),E227&gt;0,F227=E227),0,IF(AND(ISNUMBER(F227),ISNUMBER(E227),E227&gt;0,F227=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K227" s="50" t="str">
-        <x:f>IF(A227="","",IF(AND(ISNUMBER(E227),E227=0,OR(ISNUMBER(SEARCH("Free",D227&amp;"")),AND(ISNUMBER(F227),F227=0))),"Subscription",IF(ISNUMBER(G227),"Profit",IF(ISNUMBER(I227),"Loss",IF(ISNUMBER(H227),"Draw",IF(AND(ISNUMBER(F227),ISNUMBER(E227),E227&gt;0,F227&gt;E227),"Profit",IF(AND(ISNUMBER(F227),ISNUMBER(E227),E227&gt;0,F227=E227),"Draw",IF(AND(ISNUMBER(F227),ISNUMBER(E227),E227&gt;0,F227=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A227="","",IF(AND(ISNUMBER(E227),E227=0,OR(ISNUMBER(SEARCH("Free",D227&amp;"")),AND(ISNUMBER(F227),F227=0))),"Subscription",IF(ISNUMBER(G227),"Profit",IF(ISNUMBER(I227),"Disqualified",IF(ISNUMBER(H227),"Draw",IF(AND(ISNUMBER(F227),ISNUMBER(E227),E227&gt;0,F227&gt;E227),"Profit",IF(AND(ISNUMBER(F227),ISNUMBER(E227),E227&gt;0,F227=E227),"Draw",IF(AND(ISNUMBER(F227),ISNUMBER(E227),E227&gt;0,F227=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L227" s="50"/>
       <x:c r="M227" s="58"/>
@@ -9794,7 +9807,7 @@
         <x:f>IF(A228="","",IF(K228="Subscription","",IF(E228=0,"",IF(ISNUMBER(G228),G228/E228,IF(ISNUMBER(I228),-ABS(I228)/E228,IF(ISNUMBER(H228),0,IF(AND(ISNUMBER(F228),ISNUMBER(E228),E228&gt;0,F228&gt;E228),(F228-E228)/E228,IF(AND(ISNUMBER(F228),ISNUMBER(E228),E228&gt;0,F228=E228),0,IF(AND(ISNUMBER(F228),ISNUMBER(E228),E228&gt;0,F228=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K228" s="50" t="str">
-        <x:f>IF(A228="","",IF(AND(ISNUMBER(E228),E228=0,OR(ISNUMBER(SEARCH("Free",D228&amp;"")),AND(ISNUMBER(F228),F228=0))),"Subscription",IF(ISNUMBER(G228),"Profit",IF(ISNUMBER(I228),"Loss",IF(ISNUMBER(H228),"Draw",IF(AND(ISNUMBER(F228),ISNUMBER(E228),E228&gt;0,F228&gt;E228),"Profit",IF(AND(ISNUMBER(F228),ISNUMBER(E228),E228&gt;0,F228=E228),"Draw",IF(AND(ISNUMBER(F228),ISNUMBER(E228),E228&gt;0,F228=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A228="","",IF(AND(ISNUMBER(E228),E228=0,OR(ISNUMBER(SEARCH("Free",D228&amp;"")),AND(ISNUMBER(F228),F228=0))),"Subscription",IF(ISNUMBER(G228),"Profit",IF(ISNUMBER(I228),"Disqualified",IF(ISNUMBER(H228),"Draw",IF(AND(ISNUMBER(F228),ISNUMBER(E228),E228&gt;0,F228&gt;E228),"Profit",IF(AND(ISNUMBER(F228),ISNUMBER(E228),E228&gt;0,F228=E228),"Draw",IF(AND(ISNUMBER(F228),ISNUMBER(E228),E228&gt;0,F228=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L228" s="50"/>
       <x:c r="M228" s="58"/>
@@ -9831,7 +9844,7 @@
         <x:f>IF(A229="","",IF(K229="Subscription","",IF(E229=0,"",IF(ISNUMBER(G229),G229/E229,IF(ISNUMBER(I229),-ABS(I229)/E229,IF(ISNUMBER(H229),0,IF(AND(ISNUMBER(F229),ISNUMBER(E229),E229&gt;0,F229&gt;E229),(F229-E229)/E229,IF(AND(ISNUMBER(F229),ISNUMBER(E229),E229&gt;0,F229=E229),0,IF(AND(ISNUMBER(F229),ISNUMBER(E229),E229&gt;0,F229=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K229" s="50" t="str">
-        <x:f>IF(A229="","",IF(AND(ISNUMBER(E229),E229=0,OR(ISNUMBER(SEARCH("Free",D229&amp;"")),AND(ISNUMBER(F229),F229=0))),"Subscription",IF(ISNUMBER(G229),"Profit",IF(ISNUMBER(I229),"Loss",IF(ISNUMBER(H229),"Draw",IF(AND(ISNUMBER(F229),ISNUMBER(E229),E229&gt;0,F229&gt;E229),"Profit",IF(AND(ISNUMBER(F229),ISNUMBER(E229),E229&gt;0,F229=E229),"Draw",IF(AND(ISNUMBER(F229),ISNUMBER(E229),E229&gt;0,F229=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A229="","",IF(AND(ISNUMBER(E229),E229=0,OR(ISNUMBER(SEARCH("Free",D229&amp;"")),AND(ISNUMBER(F229),F229=0))),"Subscription",IF(ISNUMBER(G229),"Profit",IF(ISNUMBER(I229),"Disqualified",IF(ISNUMBER(H229),"Draw",IF(AND(ISNUMBER(F229),ISNUMBER(E229),E229&gt;0,F229&gt;E229),"Profit",IF(AND(ISNUMBER(F229),ISNUMBER(E229),E229&gt;0,F229=E229),"Draw",IF(AND(ISNUMBER(F229),ISNUMBER(E229),E229&gt;0,F229=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L229" s="50"/>
       <x:c r="M229" s="58"/>
@@ -9868,7 +9881,7 @@
         <x:f>IF(A230="","",IF(K230="Subscription","",IF(E230=0,"",IF(ISNUMBER(G230),G230/E230,IF(ISNUMBER(I230),-ABS(I230)/E230,IF(ISNUMBER(H230),0,IF(AND(ISNUMBER(F230),ISNUMBER(E230),E230&gt;0,F230&gt;E230),(F230-E230)/E230,IF(AND(ISNUMBER(F230),ISNUMBER(E230),E230&gt;0,F230=E230),0,IF(AND(ISNUMBER(F230),ISNUMBER(E230),E230&gt;0,F230=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K230" s="50" t="str">
-        <x:f>IF(A230="","",IF(AND(ISNUMBER(E230),E230=0,OR(ISNUMBER(SEARCH("Free",D230&amp;"")),AND(ISNUMBER(F230),F230=0))),"Subscription",IF(ISNUMBER(G230),"Profit",IF(ISNUMBER(I230),"Loss",IF(ISNUMBER(H230),"Draw",IF(AND(ISNUMBER(F230),ISNUMBER(E230),E230&gt;0,F230&gt;E230),"Profit",IF(AND(ISNUMBER(F230),ISNUMBER(E230),E230&gt;0,F230=E230),"Draw",IF(AND(ISNUMBER(F230),ISNUMBER(E230),E230&gt;0,F230=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A230="","",IF(AND(ISNUMBER(E230),E230=0,OR(ISNUMBER(SEARCH("Free",D230&amp;"")),AND(ISNUMBER(F230),F230=0))),"Subscription",IF(ISNUMBER(G230),"Profit",IF(ISNUMBER(I230),"Disqualified",IF(ISNUMBER(H230),"Draw",IF(AND(ISNUMBER(F230),ISNUMBER(E230),E230&gt;0,F230&gt;E230),"Profit",IF(AND(ISNUMBER(F230),ISNUMBER(E230),E230&gt;0,F230=E230),"Draw",IF(AND(ISNUMBER(F230),ISNUMBER(E230),E230&gt;0,F230=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L230" s="50"/>
       <x:c r="M230" s="58"/>
@@ -9905,7 +9918,7 @@
         <x:f>IF(A231="","",IF(K231="Subscription","",IF(E231=0,"",IF(ISNUMBER(G231),G231/E231,IF(ISNUMBER(I231),-ABS(I231)/E231,IF(ISNUMBER(H231),0,IF(AND(ISNUMBER(F231),ISNUMBER(E231),E231&gt;0,F231&gt;E231),(F231-E231)/E231,IF(AND(ISNUMBER(F231),ISNUMBER(E231),E231&gt;0,F231=E231),0,IF(AND(ISNUMBER(F231),ISNUMBER(E231),E231&gt;0,F231=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K231" s="50" t="str">
-        <x:f>IF(A231="","",IF(AND(ISNUMBER(E231),E231=0,OR(ISNUMBER(SEARCH("Free",D231&amp;"")),AND(ISNUMBER(F231),F231=0))),"Subscription",IF(ISNUMBER(G231),"Profit",IF(ISNUMBER(I231),"Loss",IF(ISNUMBER(H231),"Draw",IF(AND(ISNUMBER(F231),ISNUMBER(E231),E231&gt;0,F231&gt;E231),"Profit",IF(AND(ISNUMBER(F231),ISNUMBER(E231),E231&gt;0,F231=E231),"Draw",IF(AND(ISNUMBER(F231),ISNUMBER(E231),E231&gt;0,F231=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A231="","",IF(AND(ISNUMBER(E231),E231=0,OR(ISNUMBER(SEARCH("Free",D231&amp;"")),AND(ISNUMBER(F231),F231=0))),"Subscription",IF(ISNUMBER(G231),"Profit",IF(ISNUMBER(I231),"Disqualified",IF(ISNUMBER(H231),"Draw",IF(AND(ISNUMBER(F231),ISNUMBER(E231),E231&gt;0,F231&gt;E231),"Profit",IF(AND(ISNUMBER(F231),ISNUMBER(E231),E231&gt;0,F231=E231),"Draw",IF(AND(ISNUMBER(F231),ISNUMBER(E231),E231&gt;0,F231=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L231" s="50"/>
       <x:c r="M231" s="58"/>
@@ -9942,7 +9955,7 @@
         <x:f>IF(A232="","",IF(K232="Subscription","",IF(E232=0,"",IF(ISNUMBER(G232),G232/E232,IF(ISNUMBER(I232),-ABS(I232)/E232,IF(ISNUMBER(H232),0,IF(AND(ISNUMBER(F232),ISNUMBER(E232),E232&gt;0,F232&gt;E232),(F232-E232)/E232,IF(AND(ISNUMBER(F232),ISNUMBER(E232),E232&gt;0,F232=E232),0,IF(AND(ISNUMBER(F232),ISNUMBER(E232),E232&gt;0,F232=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K232" s="50" t="str">
-        <x:f>IF(A232="","",IF(AND(ISNUMBER(E232),E232=0,OR(ISNUMBER(SEARCH("Free",D232&amp;"")),AND(ISNUMBER(F232),F232=0))),"Subscription",IF(ISNUMBER(G232),"Profit",IF(ISNUMBER(I232),"Loss",IF(ISNUMBER(H232),"Draw",IF(AND(ISNUMBER(F232),ISNUMBER(E232),E232&gt;0,F232&gt;E232),"Profit",IF(AND(ISNUMBER(F232),ISNUMBER(E232),E232&gt;0,F232=E232),"Draw",IF(AND(ISNUMBER(F232),ISNUMBER(E232),E232&gt;0,F232=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A232="","",IF(AND(ISNUMBER(E232),E232=0,OR(ISNUMBER(SEARCH("Free",D232&amp;"")),AND(ISNUMBER(F232),F232=0))),"Subscription",IF(ISNUMBER(G232),"Profit",IF(ISNUMBER(I232),"Disqualified",IF(ISNUMBER(H232),"Draw",IF(AND(ISNUMBER(F232),ISNUMBER(E232),E232&gt;0,F232&gt;E232),"Profit",IF(AND(ISNUMBER(F232),ISNUMBER(E232),E232&gt;0,F232=E232),"Draw",IF(AND(ISNUMBER(F232),ISNUMBER(E232),E232&gt;0,F232=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L232" s="50"/>
       <x:c r="M232" s="58"/>
@@ -9979,7 +9992,7 @@
         <x:f>IF(A233="","",IF(K233="Subscription","",IF(E233=0,"",IF(ISNUMBER(G233),G233/E233,IF(ISNUMBER(I233),-ABS(I233)/E233,IF(ISNUMBER(H233),0,IF(AND(ISNUMBER(F233),ISNUMBER(E233),E233&gt;0,F233&gt;E233),(F233-E233)/E233,IF(AND(ISNUMBER(F233),ISNUMBER(E233),E233&gt;0,F233=E233),0,IF(AND(ISNUMBER(F233),ISNUMBER(E233),E233&gt;0,F233=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K233" s="50" t="str">
-        <x:f>IF(A233="","",IF(AND(ISNUMBER(E233),E233=0,OR(ISNUMBER(SEARCH("Free",D233&amp;"")),AND(ISNUMBER(F233),F233=0))),"Subscription",IF(ISNUMBER(G233),"Profit",IF(ISNUMBER(I233),"Loss",IF(ISNUMBER(H233),"Draw",IF(AND(ISNUMBER(F233),ISNUMBER(E233),E233&gt;0,F233&gt;E233),"Profit",IF(AND(ISNUMBER(F233),ISNUMBER(E233),E233&gt;0,F233=E233),"Draw",IF(AND(ISNUMBER(F233),ISNUMBER(E233),E233&gt;0,F233=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A233="","",IF(AND(ISNUMBER(E233),E233=0,OR(ISNUMBER(SEARCH("Free",D233&amp;"")),AND(ISNUMBER(F233),F233=0))),"Subscription",IF(ISNUMBER(G233),"Profit",IF(ISNUMBER(I233),"Disqualified",IF(ISNUMBER(H233),"Draw",IF(AND(ISNUMBER(F233),ISNUMBER(E233),E233&gt;0,F233&gt;E233),"Profit",IF(AND(ISNUMBER(F233),ISNUMBER(E233),E233&gt;0,F233=E233),"Draw",IF(AND(ISNUMBER(F233),ISNUMBER(E233),E233&gt;0,F233=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L233" s="50"/>
       <x:c r="M233" s="58"/>
@@ -10016,7 +10029,7 @@
         <x:f>IF(A234="","",IF(K234="Subscription","",IF(E234=0,"",IF(ISNUMBER(G234),G234/E234,IF(ISNUMBER(I234),-ABS(I234)/E234,IF(ISNUMBER(H234),0,IF(AND(ISNUMBER(F234),ISNUMBER(E234),E234&gt;0,F234&gt;E234),(F234-E234)/E234,IF(AND(ISNUMBER(F234),ISNUMBER(E234),E234&gt;0,F234=E234),0,IF(AND(ISNUMBER(F234),ISNUMBER(E234),E234&gt;0,F234=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K234" s="50" t="str">
-        <x:f>IF(A234="","",IF(AND(ISNUMBER(E234),E234=0,OR(ISNUMBER(SEARCH("Free",D234&amp;"")),AND(ISNUMBER(F234),F234=0))),"Subscription",IF(ISNUMBER(G234),"Profit",IF(ISNUMBER(I234),"Loss",IF(ISNUMBER(H234),"Draw",IF(AND(ISNUMBER(F234),ISNUMBER(E234),E234&gt;0,F234&gt;E234),"Profit",IF(AND(ISNUMBER(F234),ISNUMBER(E234),E234&gt;0,F234=E234),"Draw",IF(AND(ISNUMBER(F234),ISNUMBER(E234),E234&gt;0,F234=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A234="","",IF(AND(ISNUMBER(E234),E234=0,OR(ISNUMBER(SEARCH("Free",D234&amp;"")),AND(ISNUMBER(F234),F234=0))),"Subscription",IF(ISNUMBER(G234),"Profit",IF(ISNUMBER(I234),"Disqualified",IF(ISNUMBER(H234),"Draw",IF(AND(ISNUMBER(F234),ISNUMBER(E234),E234&gt;0,F234&gt;E234),"Profit",IF(AND(ISNUMBER(F234),ISNUMBER(E234),E234&gt;0,F234=E234),"Draw",IF(AND(ISNUMBER(F234),ISNUMBER(E234),E234&gt;0,F234=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L234" s="50"/>
       <x:c r="M234" s="58"/>
@@ -10053,7 +10066,7 @@
         <x:f>IF(A235="","",IF(K235="Subscription","",IF(E235=0,"",IF(ISNUMBER(G235),G235/E235,IF(ISNUMBER(I235),-ABS(I235)/E235,IF(ISNUMBER(H235),0,IF(AND(ISNUMBER(F235),ISNUMBER(E235),E235&gt;0,F235&gt;E235),(F235-E235)/E235,IF(AND(ISNUMBER(F235),ISNUMBER(E235),E235&gt;0,F235=E235),0,IF(AND(ISNUMBER(F235),ISNUMBER(E235),E235&gt;0,F235=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K235" s="50" t="str">
-        <x:f>IF(A235="","",IF(AND(ISNUMBER(E235),E235=0,OR(ISNUMBER(SEARCH("Free",D235&amp;"")),AND(ISNUMBER(F235),F235=0))),"Subscription",IF(ISNUMBER(G235),"Profit",IF(ISNUMBER(I235),"Loss",IF(ISNUMBER(H235),"Draw",IF(AND(ISNUMBER(F235),ISNUMBER(E235),E235&gt;0,F235&gt;E235),"Profit",IF(AND(ISNUMBER(F235),ISNUMBER(E235),E235&gt;0,F235=E235),"Draw",IF(AND(ISNUMBER(F235),ISNUMBER(E235),E235&gt;0,F235=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A235="","",IF(AND(ISNUMBER(E235),E235=0,OR(ISNUMBER(SEARCH("Free",D235&amp;"")),AND(ISNUMBER(F235),F235=0))),"Subscription",IF(ISNUMBER(G235),"Profit",IF(ISNUMBER(I235),"Disqualified",IF(ISNUMBER(H235),"Draw",IF(AND(ISNUMBER(F235),ISNUMBER(E235),E235&gt;0,F235&gt;E235),"Profit",IF(AND(ISNUMBER(F235),ISNUMBER(E235),E235&gt;0,F235=E235),"Draw",IF(AND(ISNUMBER(F235),ISNUMBER(E235),E235&gt;0,F235=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L235" s="50"/>
       <x:c r="M235" s="58"/>
@@ -10090,7 +10103,7 @@
         <x:f>IF(A236="","",IF(K236="Subscription","",IF(E236=0,"",IF(ISNUMBER(G236),G236/E236,IF(ISNUMBER(I236),-ABS(I236)/E236,IF(ISNUMBER(H236),0,IF(AND(ISNUMBER(F236),ISNUMBER(E236),E236&gt;0,F236&gt;E236),(F236-E236)/E236,IF(AND(ISNUMBER(F236),ISNUMBER(E236),E236&gt;0,F236=E236),0,IF(AND(ISNUMBER(F236),ISNUMBER(E236),E236&gt;0,F236=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K236" s="50" t="str">
-        <x:f>IF(A236="","",IF(AND(ISNUMBER(E236),E236=0,OR(ISNUMBER(SEARCH("Free",D236&amp;"")),AND(ISNUMBER(F236),F236=0))),"Subscription",IF(ISNUMBER(G236),"Profit",IF(ISNUMBER(I236),"Loss",IF(ISNUMBER(H236),"Draw",IF(AND(ISNUMBER(F236),ISNUMBER(E236),E236&gt;0,F236&gt;E236),"Profit",IF(AND(ISNUMBER(F236),ISNUMBER(E236),E236&gt;0,F236=E236),"Draw",IF(AND(ISNUMBER(F236),ISNUMBER(E236),E236&gt;0,F236=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A236="","",IF(AND(ISNUMBER(E236),E236=0,OR(ISNUMBER(SEARCH("Free",D236&amp;"")),AND(ISNUMBER(F236),F236=0))),"Subscription",IF(ISNUMBER(G236),"Profit",IF(ISNUMBER(I236),"Disqualified",IF(ISNUMBER(H236),"Draw",IF(AND(ISNUMBER(F236),ISNUMBER(E236),E236&gt;0,F236&gt;E236),"Profit",IF(AND(ISNUMBER(F236),ISNUMBER(E236),E236&gt;0,F236=E236),"Draw",IF(AND(ISNUMBER(F236),ISNUMBER(E236),E236&gt;0,F236=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L236" s="50"/>
       <x:c r="M236" s="58"/>
@@ -10127,7 +10140,7 @@
         <x:f>IF(A237="","",IF(K237="Subscription","",IF(E237=0,"",IF(ISNUMBER(G237),G237/E237,IF(ISNUMBER(I237),-ABS(I237)/E237,IF(ISNUMBER(H237),0,IF(AND(ISNUMBER(F237),ISNUMBER(E237),E237&gt;0,F237&gt;E237),(F237-E237)/E237,IF(AND(ISNUMBER(F237),ISNUMBER(E237),E237&gt;0,F237=E237),0,IF(AND(ISNUMBER(F237),ISNUMBER(E237),E237&gt;0,F237=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K237" s="50" t="str">
-        <x:f>IF(A237="","",IF(AND(ISNUMBER(E237),E237=0,OR(ISNUMBER(SEARCH("Free",D237&amp;"")),AND(ISNUMBER(F237),F237=0))),"Subscription",IF(ISNUMBER(G237),"Profit",IF(ISNUMBER(I237),"Loss",IF(ISNUMBER(H237),"Draw",IF(AND(ISNUMBER(F237),ISNUMBER(E237),E237&gt;0,F237&gt;E237),"Profit",IF(AND(ISNUMBER(F237),ISNUMBER(E237),E237&gt;0,F237=E237),"Draw",IF(AND(ISNUMBER(F237),ISNUMBER(E237),E237&gt;0,F237=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A237="","",IF(AND(ISNUMBER(E237),E237=0,OR(ISNUMBER(SEARCH("Free",D237&amp;"")),AND(ISNUMBER(F237),F237=0))),"Subscription",IF(ISNUMBER(G237),"Profit",IF(ISNUMBER(I237),"Disqualified",IF(ISNUMBER(H237),"Draw",IF(AND(ISNUMBER(F237),ISNUMBER(E237),E237&gt;0,F237&gt;E237),"Profit",IF(AND(ISNUMBER(F237),ISNUMBER(E237),E237&gt;0,F237=E237),"Draw",IF(AND(ISNUMBER(F237),ISNUMBER(E237),E237&gt;0,F237=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L237" s="50"/>
       <x:c r="M237" s="58"/>
@@ -10164,7 +10177,7 @@
         <x:f>IF(A238="","",IF(K238="Subscription","",IF(E238=0,"",IF(ISNUMBER(G238),G238/E238,IF(ISNUMBER(I238),-ABS(I238)/E238,IF(ISNUMBER(H238),0,IF(AND(ISNUMBER(F238),ISNUMBER(E238),E238&gt;0,F238&gt;E238),(F238-E238)/E238,IF(AND(ISNUMBER(F238),ISNUMBER(E238),E238&gt;0,F238=E238),0,IF(AND(ISNUMBER(F238),ISNUMBER(E238),E238&gt;0,F238=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K238" s="50" t="str">
-        <x:f>IF(A238="","",IF(AND(ISNUMBER(E238),E238=0,OR(ISNUMBER(SEARCH("Free",D238&amp;"")),AND(ISNUMBER(F238),F238=0))),"Subscription",IF(ISNUMBER(G238),"Profit",IF(ISNUMBER(I238),"Loss",IF(ISNUMBER(H238),"Draw",IF(AND(ISNUMBER(F238),ISNUMBER(E238),E238&gt;0,F238&gt;E238),"Profit",IF(AND(ISNUMBER(F238),ISNUMBER(E238),E238&gt;0,F238=E238),"Draw",IF(AND(ISNUMBER(F238),ISNUMBER(E238),E238&gt;0,F238=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A238="","",IF(AND(ISNUMBER(E238),E238=0,OR(ISNUMBER(SEARCH("Free",D238&amp;"")),AND(ISNUMBER(F238),F238=0))),"Subscription",IF(ISNUMBER(G238),"Profit",IF(ISNUMBER(I238),"Disqualified",IF(ISNUMBER(H238),"Draw",IF(AND(ISNUMBER(F238),ISNUMBER(E238),E238&gt;0,F238&gt;E238),"Profit",IF(AND(ISNUMBER(F238),ISNUMBER(E238),E238&gt;0,F238=E238),"Draw",IF(AND(ISNUMBER(F238),ISNUMBER(E238),E238&gt;0,F238=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L238" s="50"/>
       <x:c r="M238" s="58"/>
@@ -10201,7 +10214,7 @@
         <x:f>IF(A239="","",IF(K239="Subscription","",IF(E239=0,"",IF(ISNUMBER(G239),G239/E239,IF(ISNUMBER(I239),-ABS(I239)/E239,IF(ISNUMBER(H239),0,IF(AND(ISNUMBER(F239),ISNUMBER(E239),E239&gt;0,F239&gt;E239),(F239-E239)/E239,IF(AND(ISNUMBER(F239),ISNUMBER(E239),E239&gt;0,F239=E239),0,IF(AND(ISNUMBER(F239),ISNUMBER(E239),E239&gt;0,F239=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K239" s="50" t="str">
-        <x:f>IF(A239="","",IF(AND(ISNUMBER(E239),E239=0,OR(ISNUMBER(SEARCH("Free",D239&amp;"")),AND(ISNUMBER(F239),F239=0))),"Subscription",IF(ISNUMBER(G239),"Profit",IF(ISNUMBER(I239),"Loss",IF(ISNUMBER(H239),"Draw",IF(AND(ISNUMBER(F239),ISNUMBER(E239),E239&gt;0,F239&gt;E239),"Profit",IF(AND(ISNUMBER(F239),ISNUMBER(E239),E239&gt;0,F239=E239),"Draw",IF(AND(ISNUMBER(F239),ISNUMBER(E239),E239&gt;0,F239=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A239="","",IF(AND(ISNUMBER(E239),E239=0,OR(ISNUMBER(SEARCH("Free",D239&amp;"")),AND(ISNUMBER(F239),F239=0))),"Subscription",IF(ISNUMBER(G239),"Profit",IF(ISNUMBER(I239),"Disqualified",IF(ISNUMBER(H239),"Draw",IF(AND(ISNUMBER(F239),ISNUMBER(E239),E239&gt;0,F239&gt;E239),"Profit",IF(AND(ISNUMBER(F239),ISNUMBER(E239),E239&gt;0,F239=E239),"Draw",IF(AND(ISNUMBER(F239),ISNUMBER(E239),E239&gt;0,F239=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L239" s="50"/>
       <x:c r="M239" s="58"/>
@@ -10238,7 +10251,7 @@
         <x:f>IF(A240="","",IF(K240="Subscription","",IF(E240=0,"",IF(ISNUMBER(G240),G240/E240,IF(ISNUMBER(I240),-ABS(I240)/E240,IF(ISNUMBER(H240),0,IF(AND(ISNUMBER(F240),ISNUMBER(E240),E240&gt;0,F240&gt;E240),(F240-E240)/E240,IF(AND(ISNUMBER(F240),ISNUMBER(E240),E240&gt;0,F240=E240),0,IF(AND(ISNUMBER(F240),ISNUMBER(E240),E240&gt;0,F240=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K240" s="50" t="str">
-        <x:f>IF(A240="","",IF(AND(ISNUMBER(E240),E240=0,OR(ISNUMBER(SEARCH("Free",D240&amp;"")),AND(ISNUMBER(F240),F240=0))),"Subscription",IF(ISNUMBER(G240),"Profit",IF(ISNUMBER(I240),"Loss",IF(ISNUMBER(H240),"Draw",IF(AND(ISNUMBER(F240),ISNUMBER(E240),E240&gt;0,F240&gt;E240),"Profit",IF(AND(ISNUMBER(F240),ISNUMBER(E240),E240&gt;0,F240=E240),"Draw",IF(AND(ISNUMBER(F240),ISNUMBER(E240),E240&gt;0,F240=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A240="","",IF(AND(ISNUMBER(E240),E240=0,OR(ISNUMBER(SEARCH("Free",D240&amp;"")),AND(ISNUMBER(F240),F240=0))),"Subscription",IF(ISNUMBER(G240),"Profit",IF(ISNUMBER(I240),"Disqualified",IF(ISNUMBER(H240),"Draw",IF(AND(ISNUMBER(F240),ISNUMBER(E240),E240&gt;0,F240&gt;E240),"Profit",IF(AND(ISNUMBER(F240),ISNUMBER(E240),E240&gt;0,F240=E240),"Draw",IF(AND(ISNUMBER(F240),ISNUMBER(E240),E240&gt;0,F240=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L240" s="50"/>
       <x:c r="M240" s="58"/>
@@ -10275,7 +10288,7 @@
         <x:f>IF(A241="","",IF(K241="Subscription","",IF(E241=0,"",IF(ISNUMBER(G241),G241/E241,IF(ISNUMBER(I241),-ABS(I241)/E241,IF(ISNUMBER(H241),0,IF(AND(ISNUMBER(F241),ISNUMBER(E241),E241&gt;0,F241&gt;E241),(F241-E241)/E241,IF(AND(ISNUMBER(F241),ISNUMBER(E241),E241&gt;0,F241=E241),0,IF(AND(ISNUMBER(F241),ISNUMBER(E241),E241&gt;0,F241=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K241" s="50" t="str">
-        <x:f>IF(A241="","",IF(AND(ISNUMBER(E241),E241=0,OR(ISNUMBER(SEARCH("Free",D241&amp;"")),AND(ISNUMBER(F241),F241=0))),"Subscription",IF(ISNUMBER(G241),"Profit",IF(ISNUMBER(I241),"Loss",IF(ISNUMBER(H241),"Draw",IF(AND(ISNUMBER(F241),ISNUMBER(E241),E241&gt;0,F241&gt;E241),"Profit",IF(AND(ISNUMBER(F241),ISNUMBER(E241),E241&gt;0,F241=E241),"Draw",IF(AND(ISNUMBER(F241),ISNUMBER(E241),E241&gt;0,F241=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A241="","",IF(AND(ISNUMBER(E241),E241=0,OR(ISNUMBER(SEARCH("Free",D241&amp;"")),AND(ISNUMBER(F241),F241=0))),"Subscription",IF(ISNUMBER(G241),"Profit",IF(ISNUMBER(I241),"Disqualified",IF(ISNUMBER(H241),"Draw",IF(AND(ISNUMBER(F241),ISNUMBER(E241),E241&gt;0,F241&gt;E241),"Profit",IF(AND(ISNUMBER(F241),ISNUMBER(E241),E241&gt;0,F241=E241),"Draw",IF(AND(ISNUMBER(F241),ISNUMBER(E241),E241&gt;0,F241=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L241" s="50"/>
       <x:c r="M241" s="58"/>
@@ -10312,7 +10325,7 @@
         <x:f>IF(A242="","",IF(K242="Subscription","",IF(E242=0,"",IF(ISNUMBER(G242),G242/E242,IF(ISNUMBER(I242),-ABS(I242)/E242,IF(ISNUMBER(H242),0,IF(AND(ISNUMBER(F242),ISNUMBER(E242),E242&gt;0,F242&gt;E242),(F242-E242)/E242,IF(AND(ISNUMBER(F242),ISNUMBER(E242),E242&gt;0,F242=E242),0,IF(AND(ISNUMBER(F242),ISNUMBER(E242),E242&gt;0,F242=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K242" s="50" t="str">
-        <x:f>IF(A242="","",IF(AND(ISNUMBER(E242),E242=0,OR(ISNUMBER(SEARCH("Free",D242&amp;"")),AND(ISNUMBER(F242),F242=0))),"Subscription",IF(ISNUMBER(G242),"Profit",IF(ISNUMBER(I242),"Loss",IF(ISNUMBER(H242),"Draw",IF(AND(ISNUMBER(F242),ISNUMBER(E242),E242&gt;0,F242&gt;E242),"Profit",IF(AND(ISNUMBER(F242),ISNUMBER(E242),E242&gt;0,F242=E242),"Draw",IF(AND(ISNUMBER(F242),ISNUMBER(E242),E242&gt;0,F242=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A242="","",IF(AND(ISNUMBER(E242),E242=0,OR(ISNUMBER(SEARCH("Free",D242&amp;"")),AND(ISNUMBER(F242),F242=0))),"Subscription",IF(ISNUMBER(G242),"Profit",IF(ISNUMBER(I242),"Disqualified",IF(ISNUMBER(H242),"Draw",IF(AND(ISNUMBER(F242),ISNUMBER(E242),E242&gt;0,F242&gt;E242),"Profit",IF(AND(ISNUMBER(F242),ISNUMBER(E242),E242&gt;0,F242=E242),"Draw",IF(AND(ISNUMBER(F242),ISNUMBER(E242),E242&gt;0,F242=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L242" s="50"/>
       <x:c r="M242" s="58"/>
@@ -10349,7 +10362,7 @@
         <x:f>IF(A243="","",IF(K243="Subscription","",IF(E243=0,"",IF(ISNUMBER(G243),G243/E243,IF(ISNUMBER(I243),-ABS(I243)/E243,IF(ISNUMBER(H243),0,IF(AND(ISNUMBER(F243),ISNUMBER(E243),E243&gt;0,F243&gt;E243),(F243-E243)/E243,IF(AND(ISNUMBER(F243),ISNUMBER(E243),E243&gt;0,F243=E243),0,IF(AND(ISNUMBER(F243),ISNUMBER(E243),E243&gt;0,F243=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K243" s="50" t="str">
-        <x:f>IF(A243="","",IF(AND(ISNUMBER(E243),E243=0,OR(ISNUMBER(SEARCH("Free",D243&amp;"")),AND(ISNUMBER(F243),F243=0))),"Subscription",IF(ISNUMBER(G243),"Profit",IF(ISNUMBER(I243),"Loss",IF(ISNUMBER(H243),"Draw",IF(AND(ISNUMBER(F243),ISNUMBER(E243),E243&gt;0,F243&gt;E243),"Profit",IF(AND(ISNUMBER(F243),ISNUMBER(E243),E243&gt;0,F243=E243),"Draw",IF(AND(ISNUMBER(F243),ISNUMBER(E243),E243&gt;0,F243=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A243="","",IF(AND(ISNUMBER(E243),E243=0,OR(ISNUMBER(SEARCH("Free",D243&amp;"")),AND(ISNUMBER(F243),F243=0))),"Subscription",IF(ISNUMBER(G243),"Profit",IF(ISNUMBER(I243),"Disqualified",IF(ISNUMBER(H243),"Draw",IF(AND(ISNUMBER(F243),ISNUMBER(E243),E243&gt;0,F243&gt;E243),"Profit",IF(AND(ISNUMBER(F243),ISNUMBER(E243),E243&gt;0,F243=E243),"Draw",IF(AND(ISNUMBER(F243),ISNUMBER(E243),E243&gt;0,F243=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L243" s="50"/>
       <x:c r="M243" s="58"/>
@@ -10386,7 +10399,7 @@
         <x:f>IF(A244="","",IF(K244="Subscription","",IF(E244=0,"",IF(ISNUMBER(G244),G244/E244,IF(ISNUMBER(I244),-ABS(I244)/E244,IF(ISNUMBER(H244),0,IF(AND(ISNUMBER(F244),ISNUMBER(E244),E244&gt;0,F244&gt;E244),(F244-E244)/E244,IF(AND(ISNUMBER(F244),ISNUMBER(E244),E244&gt;0,F244=E244),0,IF(AND(ISNUMBER(F244),ISNUMBER(E244),E244&gt;0,F244=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K244" s="50" t="str">
-        <x:f>IF(A244="","",IF(AND(ISNUMBER(E244),E244=0,OR(ISNUMBER(SEARCH("Free",D244&amp;"")),AND(ISNUMBER(F244),F244=0))),"Subscription",IF(ISNUMBER(G244),"Profit",IF(ISNUMBER(I244),"Loss",IF(ISNUMBER(H244),"Draw",IF(AND(ISNUMBER(F244),ISNUMBER(E244),E244&gt;0,F244&gt;E244),"Profit",IF(AND(ISNUMBER(F244),ISNUMBER(E244),E244&gt;0,F244=E244),"Draw",IF(AND(ISNUMBER(F244),ISNUMBER(E244),E244&gt;0,F244=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A244="","",IF(AND(ISNUMBER(E244),E244=0,OR(ISNUMBER(SEARCH("Free",D244&amp;"")),AND(ISNUMBER(F244),F244=0))),"Subscription",IF(ISNUMBER(G244),"Profit",IF(ISNUMBER(I244),"Disqualified",IF(ISNUMBER(H244),"Draw",IF(AND(ISNUMBER(F244),ISNUMBER(E244),E244&gt;0,F244&gt;E244),"Profit",IF(AND(ISNUMBER(F244),ISNUMBER(E244),E244&gt;0,F244=E244),"Draw",IF(AND(ISNUMBER(F244),ISNUMBER(E244),E244&gt;0,F244=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L244" s="50"/>
       <x:c r="M244" s="58"/>
@@ -10423,7 +10436,7 @@
         <x:f>IF(A245="","",IF(K245="Subscription","",IF(E245=0,"",IF(ISNUMBER(G245),G245/E245,IF(ISNUMBER(I245),-ABS(I245)/E245,IF(ISNUMBER(H245),0,IF(AND(ISNUMBER(F245),ISNUMBER(E245),E245&gt;0,F245&gt;E245),(F245-E245)/E245,IF(AND(ISNUMBER(F245),ISNUMBER(E245),E245&gt;0,F245=E245),0,IF(AND(ISNUMBER(F245),ISNUMBER(E245),E245&gt;0,F245=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K245" s="50" t="str">
-        <x:f>IF(A245="","",IF(AND(ISNUMBER(E245),E245=0,OR(ISNUMBER(SEARCH("Free",D245&amp;"")),AND(ISNUMBER(F245),F245=0))),"Subscription",IF(ISNUMBER(G245),"Profit",IF(ISNUMBER(I245),"Loss",IF(ISNUMBER(H245),"Draw",IF(AND(ISNUMBER(F245),ISNUMBER(E245),E245&gt;0,F245&gt;E245),"Profit",IF(AND(ISNUMBER(F245),ISNUMBER(E245),E245&gt;0,F245=E245),"Draw",IF(AND(ISNUMBER(F245),ISNUMBER(E245),E245&gt;0,F245=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A245="","",IF(AND(ISNUMBER(E245),E245=0,OR(ISNUMBER(SEARCH("Free",D245&amp;"")),AND(ISNUMBER(F245),F245=0))),"Subscription",IF(ISNUMBER(G245),"Profit",IF(ISNUMBER(I245),"Disqualified",IF(ISNUMBER(H245),"Draw",IF(AND(ISNUMBER(F245),ISNUMBER(E245),E245&gt;0,F245&gt;E245),"Profit",IF(AND(ISNUMBER(F245),ISNUMBER(E245),E245&gt;0,F245=E245),"Draw",IF(AND(ISNUMBER(F245),ISNUMBER(E245),E245&gt;0,F245=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L245" s="50"/>
       <x:c r="M245" s="58"/>
@@ -10460,7 +10473,7 @@
         <x:f>IF(A246="","",IF(K246="Subscription","",IF(E246=0,"",IF(ISNUMBER(G246),G246/E246,IF(ISNUMBER(I246),-ABS(I246)/E246,IF(ISNUMBER(H246),0,IF(AND(ISNUMBER(F246),ISNUMBER(E246),E246&gt;0,F246&gt;E246),(F246-E246)/E246,IF(AND(ISNUMBER(F246),ISNUMBER(E246),E246&gt;0,F246=E246),0,IF(AND(ISNUMBER(F246),ISNUMBER(E246),E246&gt;0,F246=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K246" s="50" t="str">
-        <x:f>IF(A246="","",IF(AND(ISNUMBER(E246),E246=0,OR(ISNUMBER(SEARCH("Free",D246&amp;"")),AND(ISNUMBER(F246),F246=0))),"Subscription",IF(ISNUMBER(G246),"Profit",IF(ISNUMBER(I246),"Loss",IF(ISNUMBER(H246),"Draw",IF(AND(ISNUMBER(F246),ISNUMBER(E246),E246&gt;0,F246&gt;E246),"Profit",IF(AND(ISNUMBER(F246),ISNUMBER(E246),E246&gt;0,F246=E246),"Draw",IF(AND(ISNUMBER(F246),ISNUMBER(E246),E246&gt;0,F246=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A246="","",IF(AND(ISNUMBER(E246),E246=0,OR(ISNUMBER(SEARCH("Free",D246&amp;"")),AND(ISNUMBER(F246),F246=0))),"Subscription",IF(ISNUMBER(G246),"Profit",IF(ISNUMBER(I246),"Disqualified",IF(ISNUMBER(H246),"Draw",IF(AND(ISNUMBER(F246),ISNUMBER(E246),E246&gt;0,F246&gt;E246),"Profit",IF(AND(ISNUMBER(F246),ISNUMBER(E246),E246&gt;0,F246=E246),"Draw",IF(AND(ISNUMBER(F246),ISNUMBER(E246),E246&gt;0,F246=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L246" s="50"/>
       <x:c r="M246" s="58"/>
@@ -10497,7 +10510,7 @@
         <x:f>IF(A247="","",IF(K247="Subscription","",IF(E247=0,"",IF(ISNUMBER(G247),G247/E247,IF(ISNUMBER(I247),-ABS(I247)/E247,IF(ISNUMBER(H247),0,IF(AND(ISNUMBER(F247),ISNUMBER(E247),E247&gt;0,F247&gt;E247),(F247-E247)/E247,IF(AND(ISNUMBER(F247),ISNUMBER(E247),E247&gt;0,F247=E247),0,IF(AND(ISNUMBER(F247),ISNUMBER(E247),E247&gt;0,F247=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K247" s="50" t="str">
-        <x:f>IF(A247="","",IF(AND(ISNUMBER(E247),E247=0,OR(ISNUMBER(SEARCH("Free",D247&amp;"")),AND(ISNUMBER(F247),F247=0))),"Subscription",IF(ISNUMBER(G247),"Profit",IF(ISNUMBER(I247),"Loss",IF(ISNUMBER(H247),"Draw",IF(AND(ISNUMBER(F247),ISNUMBER(E247),E247&gt;0,F247&gt;E247),"Profit",IF(AND(ISNUMBER(F247),ISNUMBER(E247),E247&gt;0,F247=E247),"Draw",IF(AND(ISNUMBER(F247),ISNUMBER(E247),E247&gt;0,F247=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A247="","",IF(AND(ISNUMBER(E247),E247=0,OR(ISNUMBER(SEARCH("Free",D247&amp;"")),AND(ISNUMBER(F247),F247=0))),"Subscription",IF(ISNUMBER(G247),"Profit",IF(ISNUMBER(I247),"Disqualified",IF(ISNUMBER(H247),"Draw",IF(AND(ISNUMBER(F247),ISNUMBER(E247),E247&gt;0,F247&gt;E247),"Profit",IF(AND(ISNUMBER(F247),ISNUMBER(E247),E247&gt;0,F247=E247),"Draw",IF(AND(ISNUMBER(F247),ISNUMBER(E247),E247&gt;0,F247=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L247" s="50"/>
       <x:c r="M247" s="58"/>
@@ -10534,7 +10547,7 @@
         <x:f>IF(A248="","",IF(K248="Subscription","",IF(E248=0,"",IF(ISNUMBER(G248),G248/E248,IF(ISNUMBER(I248),-ABS(I248)/E248,IF(ISNUMBER(H248),0,IF(AND(ISNUMBER(F248),ISNUMBER(E248),E248&gt;0,F248&gt;E248),(F248-E248)/E248,IF(AND(ISNUMBER(F248),ISNUMBER(E248),E248&gt;0,F248=E248),0,IF(AND(ISNUMBER(F248),ISNUMBER(E248),E248&gt;0,F248=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K248" s="50" t="str">
-        <x:f>IF(A248="","",IF(AND(ISNUMBER(E248),E248=0,OR(ISNUMBER(SEARCH("Free",D248&amp;"")),AND(ISNUMBER(F248),F248=0))),"Subscription",IF(ISNUMBER(G248),"Profit",IF(ISNUMBER(I248),"Loss",IF(ISNUMBER(H248),"Draw",IF(AND(ISNUMBER(F248),ISNUMBER(E248),E248&gt;0,F248&gt;E248),"Profit",IF(AND(ISNUMBER(F248),ISNUMBER(E248),E248&gt;0,F248=E248),"Draw",IF(AND(ISNUMBER(F248),ISNUMBER(E248),E248&gt;0,F248=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A248="","",IF(AND(ISNUMBER(E248),E248=0,OR(ISNUMBER(SEARCH("Free",D248&amp;"")),AND(ISNUMBER(F248),F248=0))),"Subscription",IF(ISNUMBER(G248),"Profit",IF(ISNUMBER(I248),"Disqualified",IF(ISNUMBER(H248),"Draw",IF(AND(ISNUMBER(F248),ISNUMBER(E248),E248&gt;0,F248&gt;E248),"Profit",IF(AND(ISNUMBER(F248),ISNUMBER(E248),E248&gt;0,F248=E248),"Draw",IF(AND(ISNUMBER(F248),ISNUMBER(E248),E248&gt;0,F248=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L248" s="50"/>
       <x:c r="M248" s="58"/>
@@ -10571,7 +10584,7 @@
         <x:f>IF(A249="","",IF(K249="Subscription","",IF(E249=0,"",IF(ISNUMBER(G249),G249/E249,IF(ISNUMBER(I249),-ABS(I249)/E249,IF(ISNUMBER(H249),0,IF(AND(ISNUMBER(F249),ISNUMBER(E249),E249&gt;0,F249&gt;E249),(F249-E249)/E249,IF(AND(ISNUMBER(F249),ISNUMBER(E249),E249&gt;0,F249=E249),0,IF(AND(ISNUMBER(F249),ISNUMBER(E249),E249&gt;0,F249=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K249" s="50" t="str">
-        <x:f>IF(A249="","",IF(AND(ISNUMBER(E249),E249=0,OR(ISNUMBER(SEARCH("Free",D249&amp;"")),AND(ISNUMBER(F249),F249=0))),"Subscription",IF(ISNUMBER(G249),"Profit",IF(ISNUMBER(I249),"Loss",IF(ISNUMBER(H249),"Draw",IF(AND(ISNUMBER(F249),ISNUMBER(E249),E249&gt;0,F249&gt;E249),"Profit",IF(AND(ISNUMBER(F249),ISNUMBER(E249),E249&gt;0,F249=E249),"Draw",IF(AND(ISNUMBER(F249),ISNUMBER(E249),E249&gt;0,F249=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A249="","",IF(AND(ISNUMBER(E249),E249=0,OR(ISNUMBER(SEARCH("Free",D249&amp;"")),AND(ISNUMBER(F249),F249=0))),"Subscription",IF(ISNUMBER(G249),"Profit",IF(ISNUMBER(I249),"Disqualified",IF(ISNUMBER(H249),"Draw",IF(AND(ISNUMBER(F249),ISNUMBER(E249),E249&gt;0,F249&gt;E249),"Profit",IF(AND(ISNUMBER(F249),ISNUMBER(E249),E249&gt;0,F249=E249),"Draw",IF(AND(ISNUMBER(F249),ISNUMBER(E249),E249&gt;0,F249=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L249" s="50"/>
       <x:c r="M249" s="58"/>
@@ -10608,7 +10621,7 @@
         <x:f>IF(A250="","",IF(K250="Subscription","",IF(E250=0,"",IF(ISNUMBER(G250),G250/E250,IF(ISNUMBER(I250),-ABS(I250)/E250,IF(ISNUMBER(H250),0,IF(AND(ISNUMBER(F250),ISNUMBER(E250),E250&gt;0,F250&gt;E250),(F250-E250)/E250,IF(AND(ISNUMBER(F250),ISNUMBER(E250),E250&gt;0,F250=E250),0,IF(AND(ISNUMBER(F250),ISNUMBER(E250),E250&gt;0,F250=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K250" s="50" t="str">
-        <x:f>IF(A250="","",IF(AND(ISNUMBER(E250),E250=0,OR(ISNUMBER(SEARCH("Free",D250&amp;"")),AND(ISNUMBER(F250),F250=0))),"Subscription",IF(ISNUMBER(G250),"Profit",IF(ISNUMBER(I250),"Loss",IF(ISNUMBER(H250),"Draw",IF(AND(ISNUMBER(F250),ISNUMBER(E250),E250&gt;0,F250&gt;E250),"Profit",IF(AND(ISNUMBER(F250),ISNUMBER(E250),E250&gt;0,F250=E250),"Draw",IF(AND(ISNUMBER(F250),ISNUMBER(E250),E250&gt;0,F250=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A250="","",IF(AND(ISNUMBER(E250),E250=0,OR(ISNUMBER(SEARCH("Free",D250&amp;"")),AND(ISNUMBER(F250),F250=0))),"Subscription",IF(ISNUMBER(G250),"Profit",IF(ISNUMBER(I250),"Disqualified",IF(ISNUMBER(H250),"Draw",IF(AND(ISNUMBER(F250),ISNUMBER(E250),E250&gt;0,F250&gt;E250),"Profit",IF(AND(ISNUMBER(F250),ISNUMBER(E250),E250&gt;0,F250=E250),"Draw",IF(AND(ISNUMBER(F250),ISNUMBER(E250),E250&gt;0,F250=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L250" s="50"/>
       <x:c r="M250" s="58"/>
@@ -10645,7 +10658,7 @@
         <x:f>IF(A251="","",IF(K251="Subscription","",IF(E251=0,"",IF(ISNUMBER(G251),G251/E251,IF(ISNUMBER(I251),-ABS(I251)/E251,IF(ISNUMBER(H251),0,IF(AND(ISNUMBER(F251),ISNUMBER(E251),E251&gt;0,F251&gt;E251),(F251-E251)/E251,IF(AND(ISNUMBER(F251),ISNUMBER(E251),E251&gt;0,F251=E251),0,IF(AND(ISNUMBER(F251),ISNUMBER(E251),E251&gt;0,F251=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K251" s="50" t="str">
-        <x:f>IF(A251="","",IF(AND(ISNUMBER(E251),E251=0,OR(ISNUMBER(SEARCH("Free",D251&amp;"")),AND(ISNUMBER(F251),F251=0))),"Subscription",IF(ISNUMBER(G251),"Profit",IF(ISNUMBER(I251),"Loss",IF(ISNUMBER(H251),"Draw",IF(AND(ISNUMBER(F251),ISNUMBER(E251),E251&gt;0,F251&gt;E251),"Profit",IF(AND(ISNUMBER(F251),ISNUMBER(E251),E251&gt;0,F251=E251),"Draw",IF(AND(ISNUMBER(F251),ISNUMBER(E251),E251&gt;0,F251=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A251="","",IF(AND(ISNUMBER(E251),E251=0,OR(ISNUMBER(SEARCH("Free",D251&amp;"")),AND(ISNUMBER(F251),F251=0))),"Subscription",IF(ISNUMBER(G251),"Profit",IF(ISNUMBER(I251),"Disqualified",IF(ISNUMBER(H251),"Draw",IF(AND(ISNUMBER(F251),ISNUMBER(E251),E251&gt;0,F251&gt;E251),"Profit",IF(AND(ISNUMBER(F251),ISNUMBER(E251),E251&gt;0,F251=E251),"Draw",IF(AND(ISNUMBER(F251),ISNUMBER(E251),E251&gt;0,F251=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L251" s="50"/>
       <x:c r="M251" s="58"/>
@@ -10682,7 +10695,7 @@
         <x:f>IF(A252="","",IF(K252="Subscription","",IF(E252=0,"",IF(ISNUMBER(G252),G252/E252,IF(ISNUMBER(I252),-ABS(I252)/E252,IF(ISNUMBER(H252),0,IF(AND(ISNUMBER(F252),ISNUMBER(E252),E252&gt;0,F252&gt;E252),(F252-E252)/E252,IF(AND(ISNUMBER(F252),ISNUMBER(E252),E252&gt;0,F252=E252),0,IF(AND(ISNUMBER(F252),ISNUMBER(E252),E252&gt;0,F252=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K252" s="50" t="str">
-        <x:f>IF(A252="","",IF(AND(ISNUMBER(E252),E252=0,OR(ISNUMBER(SEARCH("Free",D252&amp;"")),AND(ISNUMBER(F252),F252=0))),"Subscription",IF(ISNUMBER(G252),"Profit",IF(ISNUMBER(I252),"Loss",IF(ISNUMBER(H252),"Draw",IF(AND(ISNUMBER(F252),ISNUMBER(E252),E252&gt;0,F252&gt;E252),"Profit",IF(AND(ISNUMBER(F252),ISNUMBER(E252),E252&gt;0,F252=E252),"Draw",IF(AND(ISNUMBER(F252),ISNUMBER(E252),E252&gt;0,F252=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A252="","",IF(AND(ISNUMBER(E252),E252=0,OR(ISNUMBER(SEARCH("Free",D252&amp;"")),AND(ISNUMBER(F252),F252=0))),"Subscription",IF(ISNUMBER(G252),"Profit",IF(ISNUMBER(I252),"Disqualified",IF(ISNUMBER(H252),"Draw",IF(AND(ISNUMBER(F252),ISNUMBER(E252),E252&gt;0,F252&gt;E252),"Profit",IF(AND(ISNUMBER(F252),ISNUMBER(E252),E252&gt;0,F252=E252),"Draw",IF(AND(ISNUMBER(F252),ISNUMBER(E252),E252&gt;0,F252=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L252" s="50"/>
       <x:c r="M252" s="58"/>
@@ -10719,7 +10732,7 @@
         <x:f>IF(A253="","",IF(K253="Subscription","",IF(E253=0,"",IF(ISNUMBER(G253),G253/E253,IF(ISNUMBER(I253),-ABS(I253)/E253,IF(ISNUMBER(H253),0,IF(AND(ISNUMBER(F253),ISNUMBER(E253),E253&gt;0,F253&gt;E253),(F253-E253)/E253,IF(AND(ISNUMBER(F253),ISNUMBER(E253),E253&gt;0,F253=E253),0,IF(AND(ISNUMBER(F253),ISNUMBER(E253),E253&gt;0,F253=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K253" s="50" t="str">
-        <x:f>IF(A253="","",IF(AND(ISNUMBER(E253),E253=0,OR(ISNUMBER(SEARCH("Free",D253&amp;"")),AND(ISNUMBER(F253),F253=0))),"Subscription",IF(ISNUMBER(G253),"Profit",IF(ISNUMBER(I253),"Loss",IF(ISNUMBER(H253),"Draw",IF(AND(ISNUMBER(F253),ISNUMBER(E253),E253&gt;0,F253&gt;E253),"Profit",IF(AND(ISNUMBER(F253),ISNUMBER(E253),E253&gt;0,F253=E253),"Draw",IF(AND(ISNUMBER(F253),ISNUMBER(E253),E253&gt;0,F253=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A253="","",IF(AND(ISNUMBER(E253),E253=0,OR(ISNUMBER(SEARCH("Free",D253&amp;"")),AND(ISNUMBER(F253),F253=0))),"Subscription",IF(ISNUMBER(G253),"Profit",IF(ISNUMBER(I253),"Disqualified",IF(ISNUMBER(H253),"Draw",IF(AND(ISNUMBER(F253),ISNUMBER(E253),E253&gt;0,F253&gt;E253),"Profit",IF(AND(ISNUMBER(F253),ISNUMBER(E253),E253&gt;0,F253=E253),"Draw",IF(AND(ISNUMBER(F253),ISNUMBER(E253),E253&gt;0,F253=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L253" s="50"/>
       <x:c r="M253" s="58"/>
@@ -10756,7 +10769,7 @@
         <x:f>IF(A254="","",IF(K254="Subscription","",IF(E254=0,"",IF(ISNUMBER(G254),G254/E254,IF(ISNUMBER(I254),-ABS(I254)/E254,IF(ISNUMBER(H254),0,IF(AND(ISNUMBER(F254),ISNUMBER(E254),E254&gt;0,F254&gt;E254),(F254-E254)/E254,IF(AND(ISNUMBER(F254),ISNUMBER(E254),E254&gt;0,F254=E254),0,IF(AND(ISNUMBER(F254),ISNUMBER(E254),E254&gt;0,F254=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K254" s="50" t="str">
-        <x:f>IF(A254="","",IF(AND(ISNUMBER(E254),E254=0,OR(ISNUMBER(SEARCH("Free",D254&amp;"")),AND(ISNUMBER(F254),F254=0))),"Subscription",IF(ISNUMBER(G254),"Profit",IF(ISNUMBER(I254),"Loss",IF(ISNUMBER(H254),"Draw",IF(AND(ISNUMBER(F254),ISNUMBER(E254),E254&gt;0,F254&gt;E254),"Profit",IF(AND(ISNUMBER(F254),ISNUMBER(E254),E254&gt;0,F254=E254),"Draw",IF(AND(ISNUMBER(F254),ISNUMBER(E254),E254&gt;0,F254=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A254="","",IF(AND(ISNUMBER(E254),E254=0,OR(ISNUMBER(SEARCH("Free",D254&amp;"")),AND(ISNUMBER(F254),F254=0))),"Subscription",IF(ISNUMBER(G254),"Profit",IF(ISNUMBER(I254),"Disqualified",IF(ISNUMBER(H254),"Draw",IF(AND(ISNUMBER(F254),ISNUMBER(E254),E254&gt;0,F254&gt;E254),"Profit",IF(AND(ISNUMBER(F254),ISNUMBER(E254),E254&gt;0,F254=E254),"Draw",IF(AND(ISNUMBER(F254),ISNUMBER(E254),E254&gt;0,F254=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L254" s="50"/>
       <x:c r="M254" s="58"/>
@@ -10793,7 +10806,7 @@
         <x:f>IF(A255="","",IF(K255="Subscription","",IF(E255=0,"",IF(ISNUMBER(G255),G255/E255,IF(ISNUMBER(I255),-ABS(I255)/E255,IF(ISNUMBER(H255),0,IF(AND(ISNUMBER(F255),ISNUMBER(E255),E255&gt;0,F255&gt;E255),(F255-E255)/E255,IF(AND(ISNUMBER(F255),ISNUMBER(E255),E255&gt;0,F255=E255),0,IF(AND(ISNUMBER(F255),ISNUMBER(E255),E255&gt;0,F255=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K255" s="50" t="str">
-        <x:f>IF(A255="","",IF(AND(ISNUMBER(E255),E255=0,OR(ISNUMBER(SEARCH("Free",D255&amp;"")),AND(ISNUMBER(F255),F255=0))),"Subscription",IF(ISNUMBER(G255),"Profit",IF(ISNUMBER(I255),"Loss",IF(ISNUMBER(H255),"Draw",IF(AND(ISNUMBER(F255),ISNUMBER(E255),E255&gt;0,F255&gt;E255),"Profit",IF(AND(ISNUMBER(F255),ISNUMBER(E255),E255&gt;0,F255=E255),"Draw",IF(AND(ISNUMBER(F255),ISNUMBER(E255),E255&gt;0,F255=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A255="","",IF(AND(ISNUMBER(E255),E255=0,OR(ISNUMBER(SEARCH("Free",D255&amp;"")),AND(ISNUMBER(F255),F255=0))),"Subscription",IF(ISNUMBER(G255),"Profit",IF(ISNUMBER(I255),"Disqualified",IF(ISNUMBER(H255),"Draw",IF(AND(ISNUMBER(F255),ISNUMBER(E255),E255&gt;0,F255&gt;E255),"Profit",IF(AND(ISNUMBER(F255),ISNUMBER(E255),E255&gt;0,F255=E255),"Draw",IF(AND(ISNUMBER(F255),ISNUMBER(E255),E255&gt;0,F255=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L255" s="50"/>
       <x:c r="M255" s="58"/>
@@ -10830,7 +10843,7 @@
         <x:f>IF(A256="","",IF(K256="Subscription","",IF(E256=0,"",IF(ISNUMBER(G256),G256/E256,IF(ISNUMBER(I256),-ABS(I256)/E256,IF(ISNUMBER(H256),0,IF(AND(ISNUMBER(F256),ISNUMBER(E256),E256&gt;0,F256&gt;E256),(F256-E256)/E256,IF(AND(ISNUMBER(F256),ISNUMBER(E256),E256&gt;0,F256=E256),0,IF(AND(ISNUMBER(F256),ISNUMBER(E256),E256&gt;0,F256=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K256" s="50" t="str">
-        <x:f>IF(A256="","",IF(AND(ISNUMBER(E256),E256=0,OR(ISNUMBER(SEARCH("Free",D256&amp;"")),AND(ISNUMBER(F256),F256=0))),"Subscription",IF(ISNUMBER(G256),"Profit",IF(ISNUMBER(I256),"Loss",IF(ISNUMBER(H256),"Draw",IF(AND(ISNUMBER(F256),ISNUMBER(E256),E256&gt;0,F256&gt;E256),"Profit",IF(AND(ISNUMBER(F256),ISNUMBER(E256),E256&gt;0,F256=E256),"Draw",IF(AND(ISNUMBER(F256),ISNUMBER(E256),E256&gt;0,F256=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A256="","",IF(AND(ISNUMBER(E256),E256=0,OR(ISNUMBER(SEARCH("Free",D256&amp;"")),AND(ISNUMBER(F256),F256=0))),"Subscription",IF(ISNUMBER(G256),"Profit",IF(ISNUMBER(I256),"Disqualified",IF(ISNUMBER(H256),"Draw",IF(AND(ISNUMBER(F256),ISNUMBER(E256),E256&gt;0,F256&gt;E256),"Profit",IF(AND(ISNUMBER(F256),ISNUMBER(E256),E256&gt;0,F256=E256),"Draw",IF(AND(ISNUMBER(F256),ISNUMBER(E256),E256&gt;0,F256=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L256" s="50"/>
       <x:c r="M256" s="58"/>
@@ -10867,7 +10880,7 @@
         <x:f>IF(A257="","",IF(K257="Subscription","",IF(E257=0,"",IF(ISNUMBER(G257),G257/E257,IF(ISNUMBER(I257),-ABS(I257)/E257,IF(ISNUMBER(H257),0,IF(AND(ISNUMBER(F257),ISNUMBER(E257),E257&gt;0,F257&gt;E257),(F257-E257)/E257,IF(AND(ISNUMBER(F257),ISNUMBER(E257),E257&gt;0,F257=E257),0,IF(AND(ISNUMBER(F257),ISNUMBER(E257),E257&gt;0,F257=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K257" s="50" t="str">
-        <x:f>IF(A257="","",IF(AND(ISNUMBER(E257),E257=0,OR(ISNUMBER(SEARCH("Free",D257&amp;"")),AND(ISNUMBER(F257),F257=0))),"Subscription",IF(ISNUMBER(G257),"Profit",IF(ISNUMBER(I257),"Loss",IF(ISNUMBER(H257),"Draw",IF(AND(ISNUMBER(F257),ISNUMBER(E257),E257&gt;0,F257&gt;E257),"Profit",IF(AND(ISNUMBER(F257),ISNUMBER(E257),E257&gt;0,F257=E257),"Draw",IF(AND(ISNUMBER(F257),ISNUMBER(E257),E257&gt;0,F257=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A257="","",IF(AND(ISNUMBER(E257),E257=0,OR(ISNUMBER(SEARCH("Free",D257&amp;"")),AND(ISNUMBER(F257),F257=0))),"Subscription",IF(ISNUMBER(G257),"Profit",IF(ISNUMBER(I257),"Disqualified",IF(ISNUMBER(H257),"Draw",IF(AND(ISNUMBER(F257),ISNUMBER(E257),E257&gt;0,F257&gt;E257),"Profit",IF(AND(ISNUMBER(F257),ISNUMBER(E257),E257&gt;0,F257=E257),"Draw",IF(AND(ISNUMBER(F257),ISNUMBER(E257),E257&gt;0,F257=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L257" s="50"/>
       <x:c r="M257" s="58"/>
@@ -10904,7 +10917,7 @@
         <x:f>IF(A258="","",IF(K258="Subscription","",IF(E258=0,"",IF(ISNUMBER(G258),G258/E258,IF(ISNUMBER(I258),-ABS(I258)/E258,IF(ISNUMBER(H258),0,IF(AND(ISNUMBER(F258),ISNUMBER(E258),E258&gt;0,F258&gt;E258),(F258-E258)/E258,IF(AND(ISNUMBER(F258),ISNUMBER(E258),E258&gt;0,F258=E258),0,IF(AND(ISNUMBER(F258),ISNUMBER(E258),E258&gt;0,F258=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K258" s="50" t="str">
-        <x:f>IF(A258="","",IF(AND(ISNUMBER(E258),E258=0,OR(ISNUMBER(SEARCH("Free",D258&amp;"")),AND(ISNUMBER(F258),F258=0))),"Subscription",IF(ISNUMBER(G258),"Profit",IF(ISNUMBER(I258),"Loss",IF(ISNUMBER(H258),"Draw",IF(AND(ISNUMBER(F258),ISNUMBER(E258),E258&gt;0,F258&gt;E258),"Profit",IF(AND(ISNUMBER(F258),ISNUMBER(E258),E258&gt;0,F258=E258),"Draw",IF(AND(ISNUMBER(F258),ISNUMBER(E258),E258&gt;0,F258=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A258="","",IF(AND(ISNUMBER(E258),E258=0,OR(ISNUMBER(SEARCH("Free",D258&amp;"")),AND(ISNUMBER(F258),F258=0))),"Subscription",IF(ISNUMBER(G258),"Profit",IF(ISNUMBER(I258),"Disqualified",IF(ISNUMBER(H258),"Draw",IF(AND(ISNUMBER(F258),ISNUMBER(E258),E258&gt;0,F258&gt;E258),"Profit",IF(AND(ISNUMBER(F258),ISNUMBER(E258),E258&gt;0,F258=E258),"Draw",IF(AND(ISNUMBER(F258),ISNUMBER(E258),E258&gt;0,F258=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L258" s="50"/>
       <x:c r="M258" s="58"/>
@@ -10941,7 +10954,7 @@
         <x:f>IF(A259="","",IF(K259="Subscription","",IF(E259=0,"",IF(ISNUMBER(G259),G259/E259,IF(ISNUMBER(I259),-ABS(I259)/E259,IF(ISNUMBER(H259),0,IF(AND(ISNUMBER(F259),ISNUMBER(E259),E259&gt;0,F259&gt;E259),(F259-E259)/E259,IF(AND(ISNUMBER(F259),ISNUMBER(E259),E259&gt;0,F259=E259),0,IF(AND(ISNUMBER(F259),ISNUMBER(E259),E259&gt;0,F259=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K259" s="50" t="str">
-        <x:f>IF(A259="","",IF(AND(ISNUMBER(E259),E259=0,OR(ISNUMBER(SEARCH("Free",D259&amp;"")),AND(ISNUMBER(F259),F259=0))),"Subscription",IF(ISNUMBER(G259),"Profit",IF(ISNUMBER(I259),"Loss",IF(ISNUMBER(H259),"Draw",IF(AND(ISNUMBER(F259),ISNUMBER(E259),E259&gt;0,F259&gt;E259),"Profit",IF(AND(ISNUMBER(F259),ISNUMBER(E259),E259&gt;0,F259=E259),"Draw",IF(AND(ISNUMBER(F259),ISNUMBER(E259),E259&gt;0,F259=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A259="","",IF(AND(ISNUMBER(E259),E259=0,OR(ISNUMBER(SEARCH("Free",D259&amp;"")),AND(ISNUMBER(F259),F259=0))),"Subscription",IF(ISNUMBER(G259),"Profit",IF(ISNUMBER(I259),"Disqualified",IF(ISNUMBER(H259),"Draw",IF(AND(ISNUMBER(F259),ISNUMBER(E259),E259&gt;0,F259&gt;E259),"Profit",IF(AND(ISNUMBER(F259),ISNUMBER(E259),E259&gt;0,F259=E259),"Draw",IF(AND(ISNUMBER(F259),ISNUMBER(E259),E259&gt;0,F259=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L259" s="50"/>
       <x:c r="M259" s="58"/>
@@ -10978,7 +10991,7 @@
         <x:f>IF(A260="","",IF(K260="Subscription","",IF(E260=0,"",IF(ISNUMBER(G260),G260/E260,IF(ISNUMBER(I260),-ABS(I260)/E260,IF(ISNUMBER(H260),0,IF(AND(ISNUMBER(F260),ISNUMBER(E260),E260&gt;0,F260&gt;E260),(F260-E260)/E260,IF(AND(ISNUMBER(F260),ISNUMBER(E260),E260&gt;0,F260=E260),0,IF(AND(ISNUMBER(F260),ISNUMBER(E260),E260&gt;0,F260=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K260" s="50" t="str">
-        <x:f>IF(A260="","",IF(AND(ISNUMBER(E260),E260=0,OR(ISNUMBER(SEARCH("Free",D260&amp;"")),AND(ISNUMBER(F260),F260=0))),"Subscription",IF(ISNUMBER(G260),"Profit",IF(ISNUMBER(I260),"Loss",IF(ISNUMBER(H260),"Draw",IF(AND(ISNUMBER(F260),ISNUMBER(E260),E260&gt;0,F260&gt;E260),"Profit",IF(AND(ISNUMBER(F260),ISNUMBER(E260),E260&gt;0,F260=E260),"Draw",IF(AND(ISNUMBER(F260),ISNUMBER(E260),E260&gt;0,F260=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A260="","",IF(AND(ISNUMBER(E260),E260=0,OR(ISNUMBER(SEARCH("Free",D260&amp;"")),AND(ISNUMBER(F260),F260=0))),"Subscription",IF(ISNUMBER(G260),"Profit",IF(ISNUMBER(I260),"Disqualified",IF(ISNUMBER(H260),"Draw",IF(AND(ISNUMBER(F260),ISNUMBER(E260),E260&gt;0,F260&gt;E260),"Profit",IF(AND(ISNUMBER(F260),ISNUMBER(E260),E260&gt;0,F260=E260),"Draw",IF(AND(ISNUMBER(F260),ISNUMBER(E260),E260&gt;0,F260=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L260" s="50"/>
       <x:c r="M260" s="58"/>
@@ -11015,7 +11028,7 @@
         <x:f>IF(A261="","",IF(K261="Subscription","",IF(E261=0,"",IF(ISNUMBER(G261),G261/E261,IF(ISNUMBER(I261),-ABS(I261)/E261,IF(ISNUMBER(H261),0,IF(AND(ISNUMBER(F261),ISNUMBER(E261),E261&gt;0,F261&gt;E261),(F261-E261)/E261,IF(AND(ISNUMBER(F261),ISNUMBER(E261),E261&gt;0,F261=E261),0,IF(AND(ISNUMBER(F261),ISNUMBER(E261),E261&gt;0,F261=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K261" s="50" t="str">
-        <x:f>IF(A261="","",IF(AND(ISNUMBER(E261),E261=0,OR(ISNUMBER(SEARCH("Free",D261&amp;"")),AND(ISNUMBER(F261),F261=0))),"Subscription",IF(ISNUMBER(G261),"Profit",IF(ISNUMBER(I261),"Loss",IF(ISNUMBER(H261),"Draw",IF(AND(ISNUMBER(F261),ISNUMBER(E261),E261&gt;0,F261&gt;E261),"Profit",IF(AND(ISNUMBER(F261),ISNUMBER(E261),E261&gt;0,F261=E261),"Draw",IF(AND(ISNUMBER(F261),ISNUMBER(E261),E261&gt;0,F261=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A261="","",IF(AND(ISNUMBER(E261),E261=0,OR(ISNUMBER(SEARCH("Free",D261&amp;"")),AND(ISNUMBER(F261),F261=0))),"Subscription",IF(ISNUMBER(G261),"Profit",IF(ISNUMBER(I261),"Disqualified",IF(ISNUMBER(H261),"Draw",IF(AND(ISNUMBER(F261),ISNUMBER(E261),E261&gt;0,F261&gt;E261),"Profit",IF(AND(ISNUMBER(F261),ISNUMBER(E261),E261&gt;0,F261=E261),"Draw",IF(AND(ISNUMBER(F261),ISNUMBER(E261),E261&gt;0,F261=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L261" s="50"/>
       <x:c r="M261" s="58"/>
@@ -11052,7 +11065,7 @@
         <x:f>IF(A262="","",IF(K262="Subscription","",IF(E262=0,"",IF(ISNUMBER(G262),G262/E262,IF(ISNUMBER(I262),-ABS(I262)/E262,IF(ISNUMBER(H262),0,IF(AND(ISNUMBER(F262),ISNUMBER(E262),E262&gt;0,F262&gt;E262),(F262-E262)/E262,IF(AND(ISNUMBER(F262),ISNUMBER(E262),E262&gt;0,F262=E262),0,IF(AND(ISNUMBER(F262),ISNUMBER(E262),E262&gt;0,F262=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K262" s="50" t="str">
-        <x:f>IF(A262="","",IF(AND(ISNUMBER(E262),E262=0,OR(ISNUMBER(SEARCH("Free",D262&amp;"")),AND(ISNUMBER(F262),F262=0))),"Subscription",IF(ISNUMBER(G262),"Profit",IF(ISNUMBER(I262),"Loss",IF(ISNUMBER(H262),"Draw",IF(AND(ISNUMBER(F262),ISNUMBER(E262),E262&gt;0,F262&gt;E262),"Profit",IF(AND(ISNUMBER(F262),ISNUMBER(E262),E262&gt;0,F262=E262),"Draw",IF(AND(ISNUMBER(F262),ISNUMBER(E262),E262&gt;0,F262=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A262="","",IF(AND(ISNUMBER(E262),E262=0,OR(ISNUMBER(SEARCH("Free",D262&amp;"")),AND(ISNUMBER(F262),F262=0))),"Subscription",IF(ISNUMBER(G262),"Profit",IF(ISNUMBER(I262),"Disqualified",IF(ISNUMBER(H262),"Draw",IF(AND(ISNUMBER(F262),ISNUMBER(E262),E262&gt;0,F262&gt;E262),"Profit",IF(AND(ISNUMBER(F262),ISNUMBER(E262),E262&gt;0,F262=E262),"Draw",IF(AND(ISNUMBER(F262),ISNUMBER(E262),E262&gt;0,F262=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L262" s="50"/>
       <x:c r="M262" s="58"/>
@@ -11089,7 +11102,7 @@
         <x:f>IF(A263="","",IF(K263="Subscription","",IF(E263=0,"",IF(ISNUMBER(G263),G263/E263,IF(ISNUMBER(I263),-ABS(I263)/E263,IF(ISNUMBER(H263),0,IF(AND(ISNUMBER(F263),ISNUMBER(E263),E263&gt;0,F263&gt;E263),(F263-E263)/E263,IF(AND(ISNUMBER(F263),ISNUMBER(E263),E263&gt;0,F263=E263),0,IF(AND(ISNUMBER(F263),ISNUMBER(E263),E263&gt;0,F263=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K263" s="50" t="str">
-        <x:f>IF(A263="","",IF(AND(ISNUMBER(E263),E263=0,OR(ISNUMBER(SEARCH("Free",D263&amp;"")),AND(ISNUMBER(F263),F263=0))),"Subscription",IF(ISNUMBER(G263),"Profit",IF(ISNUMBER(I263),"Loss",IF(ISNUMBER(H263),"Draw",IF(AND(ISNUMBER(F263),ISNUMBER(E263),E263&gt;0,F263&gt;E263),"Profit",IF(AND(ISNUMBER(F263),ISNUMBER(E263),E263&gt;0,F263=E263),"Draw",IF(AND(ISNUMBER(F263),ISNUMBER(E263),E263&gt;0,F263=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A263="","",IF(AND(ISNUMBER(E263),E263=0,OR(ISNUMBER(SEARCH("Free",D263&amp;"")),AND(ISNUMBER(F263),F263=0))),"Subscription",IF(ISNUMBER(G263),"Profit",IF(ISNUMBER(I263),"Disqualified",IF(ISNUMBER(H263),"Draw",IF(AND(ISNUMBER(F263),ISNUMBER(E263),E263&gt;0,F263&gt;E263),"Profit",IF(AND(ISNUMBER(F263),ISNUMBER(E263),E263&gt;0,F263=E263),"Draw",IF(AND(ISNUMBER(F263),ISNUMBER(E263),E263&gt;0,F263=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L263" s="50"/>
       <x:c r="M263" s="58"/>
@@ -11126,7 +11139,7 @@
         <x:f>IF(A264="","",IF(K264="Subscription","",IF(E264=0,"",IF(ISNUMBER(G264),G264/E264,IF(ISNUMBER(I264),-ABS(I264)/E264,IF(ISNUMBER(H264),0,IF(AND(ISNUMBER(F264),ISNUMBER(E264),E264&gt;0,F264&gt;E264),(F264-E264)/E264,IF(AND(ISNUMBER(F264),ISNUMBER(E264),E264&gt;0,F264=E264),0,IF(AND(ISNUMBER(F264),ISNUMBER(E264),E264&gt;0,F264=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K264" s="50" t="str">
-        <x:f>IF(A264="","",IF(AND(ISNUMBER(E264),E264=0,OR(ISNUMBER(SEARCH("Free",D264&amp;"")),AND(ISNUMBER(F264),F264=0))),"Subscription",IF(ISNUMBER(G264),"Profit",IF(ISNUMBER(I264),"Loss",IF(ISNUMBER(H264),"Draw",IF(AND(ISNUMBER(F264),ISNUMBER(E264),E264&gt;0,F264&gt;E264),"Profit",IF(AND(ISNUMBER(F264),ISNUMBER(E264),E264&gt;0,F264=E264),"Draw",IF(AND(ISNUMBER(F264),ISNUMBER(E264),E264&gt;0,F264=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A264="","",IF(AND(ISNUMBER(E264),E264=0,OR(ISNUMBER(SEARCH("Free",D264&amp;"")),AND(ISNUMBER(F264),F264=0))),"Subscription",IF(ISNUMBER(G264),"Profit",IF(ISNUMBER(I264),"Disqualified",IF(ISNUMBER(H264),"Draw",IF(AND(ISNUMBER(F264),ISNUMBER(E264),E264&gt;0,F264&gt;E264),"Profit",IF(AND(ISNUMBER(F264),ISNUMBER(E264),E264&gt;0,F264=E264),"Draw",IF(AND(ISNUMBER(F264),ISNUMBER(E264),E264&gt;0,F264=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L264" s="50"/>
       <x:c r="M264" s="58"/>
@@ -11163,7 +11176,7 @@
         <x:f>IF(A265="","",IF(K265="Subscription","",IF(E265=0,"",IF(ISNUMBER(G265),G265/E265,IF(ISNUMBER(I265),-ABS(I265)/E265,IF(ISNUMBER(H265),0,IF(AND(ISNUMBER(F265),ISNUMBER(E265),E265&gt;0,F265&gt;E265),(F265-E265)/E265,IF(AND(ISNUMBER(F265),ISNUMBER(E265),E265&gt;0,F265=E265),0,IF(AND(ISNUMBER(F265),ISNUMBER(E265),E265&gt;0,F265=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K265" s="50" t="str">
-        <x:f>IF(A265="","",IF(AND(ISNUMBER(E265),E265=0,OR(ISNUMBER(SEARCH("Free",D265&amp;"")),AND(ISNUMBER(F265),F265=0))),"Subscription",IF(ISNUMBER(G265),"Profit",IF(ISNUMBER(I265),"Loss",IF(ISNUMBER(H265),"Draw",IF(AND(ISNUMBER(F265),ISNUMBER(E265),E265&gt;0,F265&gt;E265),"Profit",IF(AND(ISNUMBER(F265),ISNUMBER(E265),E265&gt;0,F265=E265),"Draw",IF(AND(ISNUMBER(F265),ISNUMBER(E265),E265&gt;0,F265=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A265="","",IF(AND(ISNUMBER(E265),E265=0,OR(ISNUMBER(SEARCH("Free",D265&amp;"")),AND(ISNUMBER(F265),F265=0))),"Subscription",IF(ISNUMBER(G265),"Profit",IF(ISNUMBER(I265),"Disqualified",IF(ISNUMBER(H265),"Draw",IF(AND(ISNUMBER(F265),ISNUMBER(E265),E265&gt;0,F265&gt;E265),"Profit",IF(AND(ISNUMBER(F265),ISNUMBER(E265),E265&gt;0,F265=E265),"Draw",IF(AND(ISNUMBER(F265),ISNUMBER(E265),E265&gt;0,F265=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L265" s="50"/>
       <x:c r="M265" s="58"/>
@@ -11200,7 +11213,7 @@
         <x:f>IF(A266="","",IF(K266="Subscription","",IF(E266=0,"",IF(ISNUMBER(G266),G266/E266,IF(ISNUMBER(I266),-ABS(I266)/E266,IF(ISNUMBER(H266),0,IF(AND(ISNUMBER(F266),ISNUMBER(E266),E266&gt;0,F266&gt;E266),(F266-E266)/E266,IF(AND(ISNUMBER(F266),ISNUMBER(E266),E266&gt;0,F266=E266),0,IF(AND(ISNUMBER(F266),ISNUMBER(E266),E266&gt;0,F266=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K266" s="50" t="str">
-        <x:f>IF(A266="","",IF(AND(ISNUMBER(E266),E266=0,OR(ISNUMBER(SEARCH("Free",D266&amp;"")),AND(ISNUMBER(F266),F266=0))),"Subscription",IF(ISNUMBER(G266),"Profit",IF(ISNUMBER(I266),"Loss",IF(ISNUMBER(H266),"Draw",IF(AND(ISNUMBER(F266),ISNUMBER(E266),E266&gt;0,F266&gt;E266),"Profit",IF(AND(ISNUMBER(F266),ISNUMBER(E266),E266&gt;0,F266=E266),"Draw",IF(AND(ISNUMBER(F266),ISNUMBER(E266),E266&gt;0,F266=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A266="","",IF(AND(ISNUMBER(E266),E266=0,OR(ISNUMBER(SEARCH("Free",D266&amp;"")),AND(ISNUMBER(F266),F266=0))),"Subscription",IF(ISNUMBER(G266),"Profit",IF(ISNUMBER(I266),"Disqualified",IF(ISNUMBER(H266),"Draw",IF(AND(ISNUMBER(F266),ISNUMBER(E266),E266&gt;0,F266&gt;E266),"Profit",IF(AND(ISNUMBER(F266),ISNUMBER(E266),E266&gt;0,F266=E266),"Draw",IF(AND(ISNUMBER(F266),ISNUMBER(E266),E266&gt;0,F266=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L266" s="50"/>
       <x:c r="M266" s="58"/>
@@ -11237,7 +11250,7 @@
         <x:f>IF(A267="","",IF(K267="Subscription","",IF(E267=0,"",IF(ISNUMBER(G267),G267/E267,IF(ISNUMBER(I267),-ABS(I267)/E267,IF(ISNUMBER(H267),0,IF(AND(ISNUMBER(F267),ISNUMBER(E267),E267&gt;0,F267&gt;E267),(F267-E267)/E267,IF(AND(ISNUMBER(F267),ISNUMBER(E267),E267&gt;0,F267=E267),0,IF(AND(ISNUMBER(F267),ISNUMBER(E267),E267&gt;0,F267=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K267" s="50" t="str">
-        <x:f>IF(A267="","",IF(AND(ISNUMBER(E267),E267=0,OR(ISNUMBER(SEARCH("Free",D267&amp;"")),AND(ISNUMBER(F267),F267=0))),"Subscription",IF(ISNUMBER(G267),"Profit",IF(ISNUMBER(I267),"Loss",IF(ISNUMBER(H267),"Draw",IF(AND(ISNUMBER(F267),ISNUMBER(E267),E267&gt;0,F267&gt;E267),"Profit",IF(AND(ISNUMBER(F267),ISNUMBER(E267),E267&gt;0,F267=E267),"Draw",IF(AND(ISNUMBER(F267),ISNUMBER(E267),E267&gt;0,F267=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A267="","",IF(AND(ISNUMBER(E267),E267=0,OR(ISNUMBER(SEARCH("Free",D267&amp;"")),AND(ISNUMBER(F267),F267=0))),"Subscription",IF(ISNUMBER(G267),"Profit",IF(ISNUMBER(I267),"Disqualified",IF(ISNUMBER(H267),"Draw",IF(AND(ISNUMBER(F267),ISNUMBER(E267),E267&gt;0,F267&gt;E267),"Profit",IF(AND(ISNUMBER(F267),ISNUMBER(E267),E267&gt;0,F267=E267),"Draw",IF(AND(ISNUMBER(F267),ISNUMBER(E267),E267&gt;0,F267=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L267" s="50"/>
       <x:c r="M267" s="58"/>
@@ -11274,7 +11287,7 @@
         <x:f>IF(A268="","",IF(K268="Subscription","",IF(E268=0,"",IF(ISNUMBER(G268),G268/E268,IF(ISNUMBER(I268),-ABS(I268)/E268,IF(ISNUMBER(H268),0,IF(AND(ISNUMBER(F268),ISNUMBER(E268),E268&gt;0,F268&gt;E268),(F268-E268)/E268,IF(AND(ISNUMBER(F268),ISNUMBER(E268),E268&gt;0,F268=E268),0,IF(AND(ISNUMBER(F268),ISNUMBER(E268),E268&gt;0,F268=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K268" s="50" t="str">
-        <x:f>IF(A268="","",IF(AND(ISNUMBER(E268),E268=0,OR(ISNUMBER(SEARCH("Free",D268&amp;"")),AND(ISNUMBER(F268),F268=0))),"Subscription",IF(ISNUMBER(G268),"Profit",IF(ISNUMBER(I268),"Loss",IF(ISNUMBER(H268),"Draw",IF(AND(ISNUMBER(F268),ISNUMBER(E268),E268&gt;0,F268&gt;E268),"Profit",IF(AND(ISNUMBER(F268),ISNUMBER(E268),E268&gt;0,F268=E268),"Draw",IF(AND(ISNUMBER(F268),ISNUMBER(E268),E268&gt;0,F268=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A268="","",IF(AND(ISNUMBER(E268),E268=0,OR(ISNUMBER(SEARCH("Free",D268&amp;"")),AND(ISNUMBER(F268),F268=0))),"Subscription",IF(ISNUMBER(G268),"Profit",IF(ISNUMBER(I268),"Disqualified",IF(ISNUMBER(H268),"Draw",IF(AND(ISNUMBER(F268),ISNUMBER(E268),E268&gt;0,F268&gt;E268),"Profit",IF(AND(ISNUMBER(F268),ISNUMBER(E268),E268&gt;0,F268=E268),"Draw",IF(AND(ISNUMBER(F268),ISNUMBER(E268),E268&gt;0,F268=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L268" s="50"/>
       <x:c r="M268" s="58"/>
@@ -11311,7 +11324,7 @@
         <x:f>IF(A269="","",IF(K269="Subscription","",IF(E269=0,"",IF(ISNUMBER(G269),G269/E269,IF(ISNUMBER(I269),-ABS(I269)/E269,IF(ISNUMBER(H269),0,IF(AND(ISNUMBER(F269),ISNUMBER(E269),E269&gt;0,F269&gt;E269),(F269-E269)/E269,IF(AND(ISNUMBER(F269),ISNUMBER(E269),E269&gt;0,F269=E269),0,IF(AND(ISNUMBER(F269),ISNUMBER(E269),E269&gt;0,F269=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K269" s="50" t="str">
-        <x:f>IF(A269="","",IF(AND(ISNUMBER(E269),E269=0,OR(ISNUMBER(SEARCH("Free",D269&amp;"")),AND(ISNUMBER(F269),F269=0))),"Subscription",IF(ISNUMBER(G269),"Profit",IF(ISNUMBER(I269),"Loss",IF(ISNUMBER(H269),"Draw",IF(AND(ISNUMBER(F269),ISNUMBER(E269),E269&gt;0,F269&gt;E269),"Profit",IF(AND(ISNUMBER(F269),ISNUMBER(E269),E269&gt;0,F269=E269),"Draw",IF(AND(ISNUMBER(F269),ISNUMBER(E269),E269&gt;0,F269=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A269="","",IF(AND(ISNUMBER(E269),E269=0,OR(ISNUMBER(SEARCH("Free",D269&amp;"")),AND(ISNUMBER(F269),F269=0))),"Subscription",IF(ISNUMBER(G269),"Profit",IF(ISNUMBER(I269),"Disqualified",IF(ISNUMBER(H269),"Draw",IF(AND(ISNUMBER(F269),ISNUMBER(E269),E269&gt;0,F269&gt;E269),"Profit",IF(AND(ISNUMBER(F269),ISNUMBER(E269),E269&gt;0,F269=E269),"Draw",IF(AND(ISNUMBER(F269),ISNUMBER(E269),E269&gt;0,F269=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L269" s="50"/>
       <x:c r="M269" s="58"/>
@@ -11348,7 +11361,7 @@
         <x:f>IF(A270="","",IF(K270="Subscription","",IF(E270=0,"",IF(ISNUMBER(G270),G270/E270,IF(ISNUMBER(I270),-ABS(I270)/E270,IF(ISNUMBER(H270),0,IF(AND(ISNUMBER(F270),ISNUMBER(E270),E270&gt;0,F270&gt;E270),(F270-E270)/E270,IF(AND(ISNUMBER(F270),ISNUMBER(E270),E270&gt;0,F270=E270),0,IF(AND(ISNUMBER(F270),ISNUMBER(E270),E270&gt;0,F270=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K270" s="50" t="str">
-        <x:f>IF(A270="","",IF(AND(ISNUMBER(E270),E270=0,OR(ISNUMBER(SEARCH("Free",D270&amp;"")),AND(ISNUMBER(F270),F270=0))),"Subscription",IF(ISNUMBER(G270),"Profit",IF(ISNUMBER(I270),"Loss",IF(ISNUMBER(H270),"Draw",IF(AND(ISNUMBER(F270),ISNUMBER(E270),E270&gt;0,F270&gt;E270),"Profit",IF(AND(ISNUMBER(F270),ISNUMBER(E270),E270&gt;0,F270=E270),"Draw",IF(AND(ISNUMBER(F270),ISNUMBER(E270),E270&gt;0,F270=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A270="","",IF(AND(ISNUMBER(E270),E270=0,OR(ISNUMBER(SEARCH("Free",D270&amp;"")),AND(ISNUMBER(F270),F270=0))),"Subscription",IF(ISNUMBER(G270),"Profit",IF(ISNUMBER(I270),"Disqualified",IF(ISNUMBER(H270),"Draw",IF(AND(ISNUMBER(F270),ISNUMBER(E270),E270&gt;0,F270&gt;E270),"Profit",IF(AND(ISNUMBER(F270),ISNUMBER(E270),E270&gt;0,F270=E270),"Draw",IF(AND(ISNUMBER(F270),ISNUMBER(E270),E270&gt;0,F270=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L270" s="50"/>
       <x:c r="M270" s="58"/>
@@ -11385,7 +11398,7 @@
         <x:f>IF(A271="","",IF(K271="Subscription","",IF(E271=0,"",IF(ISNUMBER(G271),G271/E271,IF(ISNUMBER(I271),-ABS(I271)/E271,IF(ISNUMBER(H271),0,IF(AND(ISNUMBER(F271),ISNUMBER(E271),E271&gt;0,F271&gt;E271),(F271-E271)/E271,IF(AND(ISNUMBER(F271),ISNUMBER(E271),E271&gt;0,F271=E271),0,IF(AND(ISNUMBER(F271),ISNUMBER(E271),E271&gt;0,F271=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K271" s="50" t="str">
-        <x:f>IF(A271="","",IF(AND(ISNUMBER(E271),E271=0,OR(ISNUMBER(SEARCH("Free",D271&amp;"")),AND(ISNUMBER(F271),F271=0))),"Subscription",IF(ISNUMBER(G271),"Profit",IF(ISNUMBER(I271),"Loss",IF(ISNUMBER(H271),"Draw",IF(AND(ISNUMBER(F271),ISNUMBER(E271),E271&gt;0,F271&gt;E271),"Profit",IF(AND(ISNUMBER(F271),ISNUMBER(E271),E271&gt;0,F271=E271),"Draw",IF(AND(ISNUMBER(F271),ISNUMBER(E271),E271&gt;0,F271=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A271="","",IF(AND(ISNUMBER(E271),E271=0,OR(ISNUMBER(SEARCH("Free",D271&amp;"")),AND(ISNUMBER(F271),F271=0))),"Subscription",IF(ISNUMBER(G271),"Profit",IF(ISNUMBER(I271),"Disqualified",IF(ISNUMBER(H271),"Draw",IF(AND(ISNUMBER(F271),ISNUMBER(E271),E271&gt;0,F271&gt;E271),"Profit",IF(AND(ISNUMBER(F271),ISNUMBER(E271),E271&gt;0,F271=E271),"Draw",IF(AND(ISNUMBER(F271),ISNUMBER(E271),E271&gt;0,F271=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L271" s="50"/>
       <x:c r="M271" s="58"/>
@@ -11422,7 +11435,7 @@
         <x:f>IF(A272="","",IF(K272="Subscription","",IF(E272=0,"",IF(ISNUMBER(G272),G272/E272,IF(ISNUMBER(I272),-ABS(I272)/E272,IF(ISNUMBER(H272),0,IF(AND(ISNUMBER(F272),ISNUMBER(E272),E272&gt;0,F272&gt;E272),(F272-E272)/E272,IF(AND(ISNUMBER(F272),ISNUMBER(E272),E272&gt;0,F272=E272),0,IF(AND(ISNUMBER(F272),ISNUMBER(E272),E272&gt;0,F272=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K272" s="50" t="str">
-        <x:f>IF(A272="","",IF(AND(ISNUMBER(E272),E272=0,OR(ISNUMBER(SEARCH("Free",D272&amp;"")),AND(ISNUMBER(F272),F272=0))),"Subscription",IF(ISNUMBER(G272),"Profit",IF(ISNUMBER(I272),"Loss",IF(ISNUMBER(H272),"Draw",IF(AND(ISNUMBER(F272),ISNUMBER(E272),E272&gt;0,F272&gt;E272),"Profit",IF(AND(ISNUMBER(F272),ISNUMBER(E272),E272&gt;0,F272=E272),"Draw",IF(AND(ISNUMBER(F272),ISNUMBER(E272),E272&gt;0,F272=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A272="","",IF(AND(ISNUMBER(E272),E272=0,OR(ISNUMBER(SEARCH("Free",D272&amp;"")),AND(ISNUMBER(F272),F272=0))),"Subscription",IF(ISNUMBER(G272),"Profit",IF(ISNUMBER(I272),"Disqualified",IF(ISNUMBER(H272),"Draw",IF(AND(ISNUMBER(F272),ISNUMBER(E272),E272&gt;0,F272&gt;E272),"Profit",IF(AND(ISNUMBER(F272),ISNUMBER(E272),E272&gt;0,F272=E272),"Draw",IF(AND(ISNUMBER(F272),ISNUMBER(E272),E272&gt;0,F272=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L272" s="50"/>
       <x:c r="M272" s="58"/>
@@ -11459,7 +11472,7 @@
         <x:f>IF(A273="","",IF(K273="Subscription","",IF(E273=0,"",IF(ISNUMBER(G273),G273/E273,IF(ISNUMBER(I273),-ABS(I273)/E273,IF(ISNUMBER(H273),0,IF(AND(ISNUMBER(F273),ISNUMBER(E273),E273&gt;0,F273&gt;E273),(F273-E273)/E273,IF(AND(ISNUMBER(F273),ISNUMBER(E273),E273&gt;0,F273=E273),0,IF(AND(ISNUMBER(F273),ISNUMBER(E273),E273&gt;0,F273=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K273" s="50" t="str">
-        <x:f>IF(A273="","",IF(AND(ISNUMBER(E273),E273=0,OR(ISNUMBER(SEARCH("Free",D273&amp;"")),AND(ISNUMBER(F273),F273=0))),"Subscription",IF(ISNUMBER(G273),"Profit",IF(ISNUMBER(I273),"Loss",IF(ISNUMBER(H273),"Draw",IF(AND(ISNUMBER(F273),ISNUMBER(E273),E273&gt;0,F273&gt;E273),"Profit",IF(AND(ISNUMBER(F273),ISNUMBER(E273),E273&gt;0,F273=E273),"Draw",IF(AND(ISNUMBER(F273),ISNUMBER(E273),E273&gt;0,F273=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A273="","",IF(AND(ISNUMBER(E273),E273=0,OR(ISNUMBER(SEARCH("Free",D273&amp;"")),AND(ISNUMBER(F273),F273=0))),"Subscription",IF(ISNUMBER(G273),"Profit",IF(ISNUMBER(I273),"Disqualified",IF(ISNUMBER(H273),"Draw",IF(AND(ISNUMBER(F273),ISNUMBER(E273),E273&gt;0,F273&gt;E273),"Profit",IF(AND(ISNUMBER(F273),ISNUMBER(E273),E273&gt;0,F273=E273),"Draw",IF(AND(ISNUMBER(F273),ISNUMBER(E273),E273&gt;0,F273=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L273" s="50"/>
       <x:c r="M273" s="58"/>
@@ -11496,7 +11509,7 @@
         <x:f>IF(A274="","",IF(K274="Subscription","",IF(E274=0,"",IF(ISNUMBER(G274),G274/E274,IF(ISNUMBER(I274),-ABS(I274)/E274,IF(ISNUMBER(H274),0,IF(AND(ISNUMBER(F274),ISNUMBER(E274),E274&gt;0,F274&gt;E274),(F274-E274)/E274,IF(AND(ISNUMBER(F274),ISNUMBER(E274),E274&gt;0,F274=E274),0,IF(AND(ISNUMBER(F274),ISNUMBER(E274),E274&gt;0,F274=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K274" s="50" t="str">
-        <x:f>IF(A274="","",IF(AND(ISNUMBER(E274),E274=0,OR(ISNUMBER(SEARCH("Free",D274&amp;"")),AND(ISNUMBER(F274),F274=0))),"Subscription",IF(ISNUMBER(G274),"Profit",IF(ISNUMBER(I274),"Loss",IF(ISNUMBER(H274),"Draw",IF(AND(ISNUMBER(F274),ISNUMBER(E274),E274&gt;0,F274&gt;E274),"Profit",IF(AND(ISNUMBER(F274),ISNUMBER(E274),E274&gt;0,F274=E274),"Draw",IF(AND(ISNUMBER(F274),ISNUMBER(E274),E274&gt;0,F274=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A274="","",IF(AND(ISNUMBER(E274),E274=0,OR(ISNUMBER(SEARCH("Free",D274&amp;"")),AND(ISNUMBER(F274),F274=0))),"Subscription",IF(ISNUMBER(G274),"Profit",IF(ISNUMBER(I274),"Disqualified",IF(ISNUMBER(H274),"Draw",IF(AND(ISNUMBER(F274),ISNUMBER(E274),E274&gt;0,F274&gt;E274),"Profit",IF(AND(ISNUMBER(F274),ISNUMBER(E274),E274&gt;0,F274=E274),"Draw",IF(AND(ISNUMBER(F274),ISNUMBER(E274),E274&gt;0,F274=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L274" s="50"/>
       <x:c r="M274" s="58"/>
@@ -11533,7 +11546,7 @@
         <x:f>IF(A275="","",IF(K275="Subscription","",IF(E275=0,"",IF(ISNUMBER(G275),G275/E275,IF(ISNUMBER(I275),-ABS(I275)/E275,IF(ISNUMBER(H275),0,IF(AND(ISNUMBER(F275),ISNUMBER(E275),E275&gt;0,F275&gt;E275),(F275-E275)/E275,IF(AND(ISNUMBER(F275),ISNUMBER(E275),E275&gt;0,F275=E275),0,IF(AND(ISNUMBER(F275),ISNUMBER(E275),E275&gt;0,F275=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K275" s="50" t="str">
-        <x:f>IF(A275="","",IF(AND(ISNUMBER(E275),E275=0,OR(ISNUMBER(SEARCH("Free",D275&amp;"")),AND(ISNUMBER(F275),F275=0))),"Subscription",IF(ISNUMBER(G275),"Profit",IF(ISNUMBER(I275),"Loss",IF(ISNUMBER(H275),"Draw",IF(AND(ISNUMBER(F275),ISNUMBER(E275),E275&gt;0,F275&gt;E275),"Profit",IF(AND(ISNUMBER(F275),ISNUMBER(E275),E275&gt;0,F275=E275),"Draw",IF(AND(ISNUMBER(F275),ISNUMBER(E275),E275&gt;0,F275=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A275="","",IF(AND(ISNUMBER(E275),E275=0,OR(ISNUMBER(SEARCH("Free",D275&amp;"")),AND(ISNUMBER(F275),F275=0))),"Subscription",IF(ISNUMBER(G275),"Profit",IF(ISNUMBER(I275),"Disqualified",IF(ISNUMBER(H275),"Draw",IF(AND(ISNUMBER(F275),ISNUMBER(E275),E275&gt;0,F275&gt;E275),"Profit",IF(AND(ISNUMBER(F275),ISNUMBER(E275),E275&gt;0,F275=E275),"Draw",IF(AND(ISNUMBER(F275),ISNUMBER(E275),E275&gt;0,F275=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L275" s="50"/>
       <x:c r="M275" s="58"/>
@@ -11570,7 +11583,7 @@
         <x:f>IF(A276="","",IF(K276="Subscription","",IF(E276=0,"",IF(ISNUMBER(G276),G276/E276,IF(ISNUMBER(I276),-ABS(I276)/E276,IF(ISNUMBER(H276),0,IF(AND(ISNUMBER(F276),ISNUMBER(E276),E276&gt;0,F276&gt;E276),(F276-E276)/E276,IF(AND(ISNUMBER(F276),ISNUMBER(E276),E276&gt;0,F276=E276),0,IF(AND(ISNUMBER(F276),ISNUMBER(E276),E276&gt;0,F276=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K276" s="50" t="str">
-        <x:f>IF(A276="","",IF(AND(ISNUMBER(E276),E276=0,OR(ISNUMBER(SEARCH("Free",D276&amp;"")),AND(ISNUMBER(F276),F276=0))),"Subscription",IF(ISNUMBER(G276),"Profit",IF(ISNUMBER(I276),"Loss",IF(ISNUMBER(H276),"Draw",IF(AND(ISNUMBER(F276),ISNUMBER(E276),E276&gt;0,F276&gt;E276),"Profit",IF(AND(ISNUMBER(F276),ISNUMBER(E276),E276&gt;0,F276=E276),"Draw",IF(AND(ISNUMBER(F276),ISNUMBER(E276),E276&gt;0,F276=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A276="","",IF(AND(ISNUMBER(E276),E276=0,OR(ISNUMBER(SEARCH("Free",D276&amp;"")),AND(ISNUMBER(F276),F276=0))),"Subscription",IF(ISNUMBER(G276),"Profit",IF(ISNUMBER(I276),"Disqualified",IF(ISNUMBER(H276),"Draw",IF(AND(ISNUMBER(F276),ISNUMBER(E276),E276&gt;0,F276&gt;E276),"Profit",IF(AND(ISNUMBER(F276),ISNUMBER(E276),E276&gt;0,F276=E276),"Draw",IF(AND(ISNUMBER(F276),ISNUMBER(E276),E276&gt;0,F276=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L276" s="50"/>
       <x:c r="M276" s="58"/>
@@ -11607,7 +11620,7 @@
         <x:f>IF(A277="","",IF(K277="Subscription","",IF(E277=0,"",IF(ISNUMBER(G277),G277/E277,IF(ISNUMBER(I277),-ABS(I277)/E277,IF(ISNUMBER(H277),0,IF(AND(ISNUMBER(F277),ISNUMBER(E277),E277&gt;0,F277&gt;E277),(F277-E277)/E277,IF(AND(ISNUMBER(F277),ISNUMBER(E277),E277&gt;0,F277=E277),0,IF(AND(ISNUMBER(F277),ISNUMBER(E277),E277&gt;0,F277=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K277" s="50" t="str">
-        <x:f>IF(A277="","",IF(AND(ISNUMBER(E277),E277=0,OR(ISNUMBER(SEARCH("Free",D277&amp;"")),AND(ISNUMBER(F277),F277=0))),"Subscription",IF(ISNUMBER(G277),"Profit",IF(ISNUMBER(I277),"Loss",IF(ISNUMBER(H277),"Draw",IF(AND(ISNUMBER(F277),ISNUMBER(E277),E277&gt;0,F277&gt;E277),"Profit",IF(AND(ISNUMBER(F277),ISNUMBER(E277),E277&gt;0,F277=E277),"Draw",IF(AND(ISNUMBER(F277),ISNUMBER(E277),E277&gt;0,F277=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A277="","",IF(AND(ISNUMBER(E277),E277=0,OR(ISNUMBER(SEARCH("Free",D277&amp;"")),AND(ISNUMBER(F277),F277=0))),"Subscription",IF(ISNUMBER(G277),"Profit",IF(ISNUMBER(I277),"Disqualified",IF(ISNUMBER(H277),"Draw",IF(AND(ISNUMBER(F277),ISNUMBER(E277),E277&gt;0,F277&gt;E277),"Profit",IF(AND(ISNUMBER(F277),ISNUMBER(E277),E277&gt;0,F277=E277),"Draw",IF(AND(ISNUMBER(F277),ISNUMBER(E277),E277&gt;0,F277=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L277" s="50"/>
       <x:c r="M277" s="58"/>
@@ -11644,7 +11657,7 @@
         <x:f>IF(A278="","",IF(K278="Subscription","",IF(E278=0,"",IF(ISNUMBER(G278),G278/E278,IF(ISNUMBER(I278),-ABS(I278)/E278,IF(ISNUMBER(H278),0,IF(AND(ISNUMBER(F278),ISNUMBER(E278),E278&gt;0,F278&gt;E278),(F278-E278)/E278,IF(AND(ISNUMBER(F278),ISNUMBER(E278),E278&gt;0,F278=E278),0,IF(AND(ISNUMBER(F278),ISNUMBER(E278),E278&gt;0,F278=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K278" s="50" t="str">
-        <x:f>IF(A278="","",IF(AND(ISNUMBER(E278),E278=0,OR(ISNUMBER(SEARCH("Free",D278&amp;"")),AND(ISNUMBER(F278),F278=0))),"Subscription",IF(ISNUMBER(G278),"Profit",IF(ISNUMBER(I278),"Loss",IF(ISNUMBER(H278),"Draw",IF(AND(ISNUMBER(F278),ISNUMBER(E278),E278&gt;0,F278&gt;E278),"Profit",IF(AND(ISNUMBER(F278),ISNUMBER(E278),E278&gt;0,F278=E278),"Draw",IF(AND(ISNUMBER(F278),ISNUMBER(E278),E278&gt;0,F278=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A278="","",IF(AND(ISNUMBER(E278),E278=0,OR(ISNUMBER(SEARCH("Free",D278&amp;"")),AND(ISNUMBER(F278),F278=0))),"Subscription",IF(ISNUMBER(G278),"Profit",IF(ISNUMBER(I278),"Disqualified",IF(ISNUMBER(H278),"Draw",IF(AND(ISNUMBER(F278),ISNUMBER(E278),E278&gt;0,F278&gt;E278),"Profit",IF(AND(ISNUMBER(F278),ISNUMBER(E278),E278&gt;0,F278=E278),"Draw",IF(AND(ISNUMBER(F278),ISNUMBER(E278),E278&gt;0,F278=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L278" s="50"/>
       <x:c r="M278" s="58"/>
@@ -11681,7 +11694,7 @@
         <x:f>IF(A279="","",IF(K279="Subscription","",IF(E279=0,"",IF(ISNUMBER(G279),G279/E279,IF(ISNUMBER(I279),-ABS(I279)/E279,IF(ISNUMBER(H279),0,IF(AND(ISNUMBER(F279),ISNUMBER(E279),E279&gt;0,F279&gt;E279),(F279-E279)/E279,IF(AND(ISNUMBER(F279),ISNUMBER(E279),E279&gt;0,F279=E279),0,IF(AND(ISNUMBER(F279),ISNUMBER(E279),E279&gt;0,F279=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K279" s="50" t="str">
-        <x:f>IF(A279="","",IF(AND(ISNUMBER(E279),E279=0,OR(ISNUMBER(SEARCH("Free",D279&amp;"")),AND(ISNUMBER(F279),F279=0))),"Subscription",IF(ISNUMBER(G279),"Profit",IF(ISNUMBER(I279),"Loss",IF(ISNUMBER(H279),"Draw",IF(AND(ISNUMBER(F279),ISNUMBER(E279),E279&gt;0,F279&gt;E279),"Profit",IF(AND(ISNUMBER(F279),ISNUMBER(E279),E279&gt;0,F279=E279),"Draw",IF(AND(ISNUMBER(F279),ISNUMBER(E279),E279&gt;0,F279=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A279="","",IF(AND(ISNUMBER(E279),E279=0,OR(ISNUMBER(SEARCH("Free",D279&amp;"")),AND(ISNUMBER(F279),F279=0))),"Subscription",IF(ISNUMBER(G279),"Profit",IF(ISNUMBER(I279),"Disqualified",IF(ISNUMBER(H279),"Draw",IF(AND(ISNUMBER(F279),ISNUMBER(E279),E279&gt;0,F279&gt;E279),"Profit",IF(AND(ISNUMBER(F279),ISNUMBER(E279),E279&gt;0,F279=E279),"Draw",IF(AND(ISNUMBER(F279),ISNUMBER(E279),E279&gt;0,F279=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L279" s="50"/>
       <x:c r="M279" s="58"/>
@@ -11718,7 +11731,7 @@
         <x:f>IF(A280="","",IF(K280="Subscription","",IF(E280=0,"",IF(ISNUMBER(G280),G280/E280,IF(ISNUMBER(I280),-ABS(I280)/E280,IF(ISNUMBER(H280),0,IF(AND(ISNUMBER(F280),ISNUMBER(E280),E280&gt;0,F280&gt;E280),(F280-E280)/E280,IF(AND(ISNUMBER(F280),ISNUMBER(E280),E280&gt;0,F280=E280),0,IF(AND(ISNUMBER(F280),ISNUMBER(E280),E280&gt;0,F280=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K280" s="50" t="str">
-        <x:f>IF(A280="","",IF(AND(ISNUMBER(E280),E280=0,OR(ISNUMBER(SEARCH("Free",D280&amp;"")),AND(ISNUMBER(F280),F280=0))),"Subscription",IF(ISNUMBER(G280),"Profit",IF(ISNUMBER(I280),"Loss",IF(ISNUMBER(H280),"Draw",IF(AND(ISNUMBER(F280),ISNUMBER(E280),E280&gt;0,F280&gt;E280),"Profit",IF(AND(ISNUMBER(F280),ISNUMBER(E280),E280&gt;0,F280=E280),"Draw",IF(AND(ISNUMBER(F280),ISNUMBER(E280),E280&gt;0,F280=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A280="","",IF(AND(ISNUMBER(E280),E280=0,OR(ISNUMBER(SEARCH("Free",D280&amp;"")),AND(ISNUMBER(F280),F280=0))),"Subscription",IF(ISNUMBER(G280),"Profit",IF(ISNUMBER(I280),"Disqualified",IF(ISNUMBER(H280),"Draw",IF(AND(ISNUMBER(F280),ISNUMBER(E280),E280&gt;0,F280&gt;E280),"Profit",IF(AND(ISNUMBER(F280),ISNUMBER(E280),E280&gt;0,F280=E280),"Draw",IF(AND(ISNUMBER(F280),ISNUMBER(E280),E280&gt;0,F280=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L280" s="50"/>
       <x:c r="M280" s="58"/>
@@ -11755,7 +11768,7 @@
         <x:f>IF(A281="","",IF(K281="Subscription","",IF(E281=0,"",IF(ISNUMBER(G281),G281/E281,IF(ISNUMBER(I281),-ABS(I281)/E281,IF(ISNUMBER(H281),0,IF(AND(ISNUMBER(F281),ISNUMBER(E281),E281&gt;0,F281&gt;E281),(F281-E281)/E281,IF(AND(ISNUMBER(F281),ISNUMBER(E281),E281&gt;0,F281=E281),0,IF(AND(ISNUMBER(F281),ISNUMBER(E281),E281&gt;0,F281=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K281" s="50" t="str">
-        <x:f>IF(A281="","",IF(AND(ISNUMBER(E281),E281=0,OR(ISNUMBER(SEARCH("Free",D281&amp;"")),AND(ISNUMBER(F281),F281=0))),"Subscription",IF(ISNUMBER(G281),"Profit",IF(ISNUMBER(I281),"Loss",IF(ISNUMBER(H281),"Draw",IF(AND(ISNUMBER(F281),ISNUMBER(E281),E281&gt;0,F281&gt;E281),"Profit",IF(AND(ISNUMBER(F281),ISNUMBER(E281),E281&gt;0,F281=E281),"Draw",IF(AND(ISNUMBER(F281),ISNUMBER(E281),E281&gt;0,F281=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A281="","",IF(AND(ISNUMBER(E281),E281=0,OR(ISNUMBER(SEARCH("Free",D281&amp;"")),AND(ISNUMBER(F281),F281=0))),"Subscription",IF(ISNUMBER(G281),"Profit",IF(ISNUMBER(I281),"Disqualified",IF(ISNUMBER(H281),"Draw",IF(AND(ISNUMBER(F281),ISNUMBER(E281),E281&gt;0,F281&gt;E281),"Profit",IF(AND(ISNUMBER(F281),ISNUMBER(E281),E281&gt;0,F281=E281),"Draw",IF(AND(ISNUMBER(F281),ISNUMBER(E281),E281&gt;0,F281=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L281" s="50"/>
       <x:c r="M281" s="58"/>
@@ -11792,7 +11805,7 @@
         <x:f>IF(A282="","",IF(K282="Subscription","",IF(E282=0,"",IF(ISNUMBER(G282),G282/E282,IF(ISNUMBER(I282),-ABS(I282)/E282,IF(ISNUMBER(H282),0,IF(AND(ISNUMBER(F282),ISNUMBER(E282),E282&gt;0,F282&gt;E282),(F282-E282)/E282,IF(AND(ISNUMBER(F282),ISNUMBER(E282),E282&gt;0,F282=E282),0,IF(AND(ISNUMBER(F282),ISNUMBER(E282),E282&gt;0,F282=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K282" s="50" t="str">
-        <x:f>IF(A282="","",IF(AND(ISNUMBER(E282),E282=0,OR(ISNUMBER(SEARCH("Free",D282&amp;"")),AND(ISNUMBER(F282),F282=0))),"Subscription",IF(ISNUMBER(G282),"Profit",IF(ISNUMBER(I282),"Loss",IF(ISNUMBER(H282),"Draw",IF(AND(ISNUMBER(F282),ISNUMBER(E282),E282&gt;0,F282&gt;E282),"Profit",IF(AND(ISNUMBER(F282),ISNUMBER(E282),E282&gt;0,F282=E282),"Draw",IF(AND(ISNUMBER(F282),ISNUMBER(E282),E282&gt;0,F282=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A282="","",IF(AND(ISNUMBER(E282),E282=0,OR(ISNUMBER(SEARCH("Free",D282&amp;"")),AND(ISNUMBER(F282),F282=0))),"Subscription",IF(ISNUMBER(G282),"Profit",IF(ISNUMBER(I282),"Disqualified",IF(ISNUMBER(H282),"Draw",IF(AND(ISNUMBER(F282),ISNUMBER(E282),E282&gt;0,F282&gt;E282),"Profit",IF(AND(ISNUMBER(F282),ISNUMBER(E282),E282&gt;0,F282=E282),"Draw",IF(AND(ISNUMBER(F282),ISNUMBER(E282),E282&gt;0,F282=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L282" s="50"/>
       <x:c r="M282" s="58"/>
@@ -11829,7 +11842,7 @@
         <x:f>IF(A283="","",IF(K283="Subscription","",IF(E283=0,"",IF(ISNUMBER(G283),G283/E283,IF(ISNUMBER(I283),-ABS(I283)/E283,IF(ISNUMBER(H283),0,IF(AND(ISNUMBER(F283),ISNUMBER(E283),E283&gt;0,F283&gt;E283),(F283-E283)/E283,IF(AND(ISNUMBER(F283),ISNUMBER(E283),E283&gt;0,F283=E283),0,IF(AND(ISNUMBER(F283),ISNUMBER(E283),E283&gt;0,F283=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K283" s="50" t="str">
-        <x:f>IF(A283="","",IF(AND(ISNUMBER(E283),E283=0,OR(ISNUMBER(SEARCH("Free",D283&amp;"")),AND(ISNUMBER(F283),F283=0))),"Subscription",IF(ISNUMBER(G283),"Profit",IF(ISNUMBER(I283),"Loss",IF(ISNUMBER(H283),"Draw",IF(AND(ISNUMBER(F283),ISNUMBER(E283),E283&gt;0,F283&gt;E283),"Profit",IF(AND(ISNUMBER(F283),ISNUMBER(E283),E283&gt;0,F283=E283),"Draw",IF(AND(ISNUMBER(F283),ISNUMBER(E283),E283&gt;0,F283=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A283="","",IF(AND(ISNUMBER(E283),E283=0,OR(ISNUMBER(SEARCH("Free",D283&amp;"")),AND(ISNUMBER(F283),F283=0))),"Subscription",IF(ISNUMBER(G283),"Profit",IF(ISNUMBER(I283),"Disqualified",IF(ISNUMBER(H283),"Draw",IF(AND(ISNUMBER(F283),ISNUMBER(E283),E283&gt;0,F283&gt;E283),"Profit",IF(AND(ISNUMBER(F283),ISNUMBER(E283),E283&gt;0,F283=E283),"Draw",IF(AND(ISNUMBER(F283),ISNUMBER(E283),E283&gt;0,F283=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L283" s="50"/>
       <x:c r="M283" s="58"/>
@@ -11866,7 +11879,7 @@
         <x:f>IF(A284="","",IF(K284="Subscription","",IF(E284=0,"",IF(ISNUMBER(G284),G284/E284,IF(ISNUMBER(I284),-ABS(I284)/E284,IF(ISNUMBER(H284),0,IF(AND(ISNUMBER(F284),ISNUMBER(E284),E284&gt;0,F284&gt;E284),(F284-E284)/E284,IF(AND(ISNUMBER(F284),ISNUMBER(E284),E284&gt;0,F284=E284),0,IF(AND(ISNUMBER(F284),ISNUMBER(E284),E284&gt;0,F284=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K284" s="50" t="str">
-        <x:f>IF(A284="","",IF(AND(ISNUMBER(E284),E284=0,OR(ISNUMBER(SEARCH("Free",D284&amp;"")),AND(ISNUMBER(F284),F284=0))),"Subscription",IF(ISNUMBER(G284),"Profit",IF(ISNUMBER(I284),"Loss",IF(ISNUMBER(H284),"Draw",IF(AND(ISNUMBER(F284),ISNUMBER(E284),E284&gt;0,F284&gt;E284),"Profit",IF(AND(ISNUMBER(F284),ISNUMBER(E284),E284&gt;0,F284=E284),"Draw",IF(AND(ISNUMBER(F284),ISNUMBER(E284),E284&gt;0,F284=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A284="","",IF(AND(ISNUMBER(E284),E284=0,OR(ISNUMBER(SEARCH("Free",D284&amp;"")),AND(ISNUMBER(F284),F284=0))),"Subscription",IF(ISNUMBER(G284),"Profit",IF(ISNUMBER(I284),"Disqualified",IF(ISNUMBER(H284),"Draw",IF(AND(ISNUMBER(F284),ISNUMBER(E284),E284&gt;0,F284&gt;E284),"Profit",IF(AND(ISNUMBER(F284),ISNUMBER(E284),E284&gt;0,F284=E284),"Draw",IF(AND(ISNUMBER(F284),ISNUMBER(E284),E284&gt;0,F284=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L284" s="50"/>
       <x:c r="M284" s="58"/>
@@ -11903,7 +11916,7 @@
         <x:f>IF(A285="","",IF(K285="Subscription","",IF(E285=0,"",IF(ISNUMBER(G285),G285/E285,IF(ISNUMBER(I285),-ABS(I285)/E285,IF(ISNUMBER(H285),0,IF(AND(ISNUMBER(F285),ISNUMBER(E285),E285&gt;0,F285&gt;E285),(F285-E285)/E285,IF(AND(ISNUMBER(F285),ISNUMBER(E285),E285&gt;0,F285=E285),0,IF(AND(ISNUMBER(F285),ISNUMBER(E285),E285&gt;0,F285=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K285" s="50" t="str">
-        <x:f>IF(A285="","",IF(AND(ISNUMBER(E285),E285=0,OR(ISNUMBER(SEARCH("Free",D285&amp;"")),AND(ISNUMBER(F285),F285=0))),"Subscription",IF(ISNUMBER(G285),"Profit",IF(ISNUMBER(I285),"Loss",IF(ISNUMBER(H285),"Draw",IF(AND(ISNUMBER(F285),ISNUMBER(E285),E285&gt;0,F285&gt;E285),"Profit",IF(AND(ISNUMBER(F285),ISNUMBER(E285),E285&gt;0,F285=E285),"Draw",IF(AND(ISNUMBER(F285),ISNUMBER(E285),E285&gt;0,F285=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A285="","",IF(AND(ISNUMBER(E285),E285=0,OR(ISNUMBER(SEARCH("Free",D285&amp;"")),AND(ISNUMBER(F285),F285=0))),"Subscription",IF(ISNUMBER(G285),"Profit",IF(ISNUMBER(I285),"Disqualified",IF(ISNUMBER(H285),"Draw",IF(AND(ISNUMBER(F285),ISNUMBER(E285),E285&gt;0,F285&gt;E285),"Profit",IF(AND(ISNUMBER(F285),ISNUMBER(E285),E285&gt;0,F285=E285),"Draw",IF(AND(ISNUMBER(F285),ISNUMBER(E285),E285&gt;0,F285=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L285" s="50"/>
       <x:c r="M285" s="58"/>
@@ -11940,7 +11953,7 @@
         <x:f>IF(A286="","",IF(K286="Subscription","",IF(E286=0,"",IF(ISNUMBER(G286),G286/E286,IF(ISNUMBER(I286),-ABS(I286)/E286,IF(ISNUMBER(H286),0,IF(AND(ISNUMBER(F286),ISNUMBER(E286),E286&gt;0,F286&gt;E286),(F286-E286)/E286,IF(AND(ISNUMBER(F286),ISNUMBER(E286),E286&gt;0,F286=E286),0,IF(AND(ISNUMBER(F286),ISNUMBER(E286),E286&gt;0,F286=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K286" s="50" t="str">
-        <x:f>IF(A286="","",IF(AND(ISNUMBER(E286),E286=0,OR(ISNUMBER(SEARCH("Free",D286&amp;"")),AND(ISNUMBER(F286),F286=0))),"Subscription",IF(ISNUMBER(G286),"Profit",IF(ISNUMBER(I286),"Loss",IF(ISNUMBER(H286),"Draw",IF(AND(ISNUMBER(F286),ISNUMBER(E286),E286&gt;0,F286&gt;E286),"Profit",IF(AND(ISNUMBER(F286),ISNUMBER(E286),E286&gt;0,F286=E286),"Draw",IF(AND(ISNUMBER(F286),ISNUMBER(E286),E286&gt;0,F286=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A286="","",IF(AND(ISNUMBER(E286),E286=0,OR(ISNUMBER(SEARCH("Free",D286&amp;"")),AND(ISNUMBER(F286),F286=0))),"Subscription",IF(ISNUMBER(G286),"Profit",IF(ISNUMBER(I286),"Disqualified",IF(ISNUMBER(H286),"Draw",IF(AND(ISNUMBER(F286),ISNUMBER(E286),E286&gt;0,F286&gt;E286),"Profit",IF(AND(ISNUMBER(F286),ISNUMBER(E286),E286&gt;0,F286=E286),"Draw",IF(AND(ISNUMBER(F286),ISNUMBER(E286),E286&gt;0,F286=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L286" s="50"/>
       <x:c r="M286" s="58"/>
@@ -11977,7 +11990,7 @@
         <x:f>IF(A287="","",IF(K287="Subscription","",IF(E287=0,"",IF(ISNUMBER(G287),G287/E287,IF(ISNUMBER(I287),-ABS(I287)/E287,IF(ISNUMBER(H287),0,IF(AND(ISNUMBER(F287),ISNUMBER(E287),E287&gt;0,F287&gt;E287),(F287-E287)/E287,IF(AND(ISNUMBER(F287),ISNUMBER(E287),E287&gt;0,F287=E287),0,IF(AND(ISNUMBER(F287),ISNUMBER(E287),E287&gt;0,F287=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K287" s="50" t="str">
-        <x:f>IF(A287="","",IF(AND(ISNUMBER(E287),E287=0,OR(ISNUMBER(SEARCH("Free",D287&amp;"")),AND(ISNUMBER(F287),F287=0))),"Subscription",IF(ISNUMBER(G287),"Profit",IF(ISNUMBER(I287),"Loss",IF(ISNUMBER(H287),"Draw",IF(AND(ISNUMBER(F287),ISNUMBER(E287),E287&gt;0,F287&gt;E287),"Profit",IF(AND(ISNUMBER(F287),ISNUMBER(E287),E287&gt;0,F287=E287),"Draw",IF(AND(ISNUMBER(F287),ISNUMBER(E287),E287&gt;0,F287=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A287="","",IF(AND(ISNUMBER(E287),E287=0,OR(ISNUMBER(SEARCH("Free",D287&amp;"")),AND(ISNUMBER(F287),F287=0))),"Subscription",IF(ISNUMBER(G287),"Profit",IF(ISNUMBER(I287),"Disqualified",IF(ISNUMBER(H287),"Draw",IF(AND(ISNUMBER(F287),ISNUMBER(E287),E287&gt;0,F287&gt;E287),"Profit",IF(AND(ISNUMBER(F287),ISNUMBER(E287),E287&gt;0,F287=E287),"Draw",IF(AND(ISNUMBER(F287),ISNUMBER(E287),E287&gt;0,F287=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L287" s="50"/>
       <x:c r="M287" s="58"/>
@@ -12014,7 +12027,7 @@
         <x:f>IF(A288="","",IF(K288="Subscription","",IF(E288=0,"",IF(ISNUMBER(G288),G288/E288,IF(ISNUMBER(I288),-ABS(I288)/E288,IF(ISNUMBER(H288),0,IF(AND(ISNUMBER(F288),ISNUMBER(E288),E288&gt;0,F288&gt;E288),(F288-E288)/E288,IF(AND(ISNUMBER(F288),ISNUMBER(E288),E288&gt;0,F288=E288),0,IF(AND(ISNUMBER(F288),ISNUMBER(E288),E288&gt;0,F288=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K288" s="50" t="str">
-        <x:f>IF(A288="","",IF(AND(ISNUMBER(E288),E288=0,OR(ISNUMBER(SEARCH("Free",D288&amp;"")),AND(ISNUMBER(F288),F288=0))),"Subscription",IF(ISNUMBER(G288),"Profit",IF(ISNUMBER(I288),"Loss",IF(ISNUMBER(H288),"Draw",IF(AND(ISNUMBER(F288),ISNUMBER(E288),E288&gt;0,F288&gt;E288),"Profit",IF(AND(ISNUMBER(F288),ISNUMBER(E288),E288&gt;0,F288=E288),"Draw",IF(AND(ISNUMBER(F288),ISNUMBER(E288),E288&gt;0,F288=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A288="","",IF(AND(ISNUMBER(E288),E288=0,OR(ISNUMBER(SEARCH("Free",D288&amp;"")),AND(ISNUMBER(F288),F288=0))),"Subscription",IF(ISNUMBER(G288),"Profit",IF(ISNUMBER(I288),"Disqualified",IF(ISNUMBER(H288),"Draw",IF(AND(ISNUMBER(F288),ISNUMBER(E288),E288&gt;0,F288&gt;E288),"Profit",IF(AND(ISNUMBER(F288),ISNUMBER(E288),E288&gt;0,F288=E288),"Draw",IF(AND(ISNUMBER(F288),ISNUMBER(E288),E288&gt;0,F288=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L288" s="50"/>
       <x:c r="M288" s="58"/>
@@ -12051,7 +12064,7 @@
         <x:f>IF(A289="","",IF(K289="Subscription","",IF(E289=0,"",IF(ISNUMBER(G289),G289/E289,IF(ISNUMBER(I289),-ABS(I289)/E289,IF(ISNUMBER(H289),0,IF(AND(ISNUMBER(F289),ISNUMBER(E289),E289&gt;0,F289&gt;E289),(F289-E289)/E289,IF(AND(ISNUMBER(F289),ISNUMBER(E289),E289&gt;0,F289=E289),0,IF(AND(ISNUMBER(F289),ISNUMBER(E289),E289&gt;0,F289=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K289" s="50" t="str">
-        <x:f>IF(A289="","",IF(AND(ISNUMBER(E289),E289=0,OR(ISNUMBER(SEARCH("Free",D289&amp;"")),AND(ISNUMBER(F289),F289=0))),"Subscription",IF(ISNUMBER(G289),"Profit",IF(ISNUMBER(I289),"Loss",IF(ISNUMBER(H289),"Draw",IF(AND(ISNUMBER(F289),ISNUMBER(E289),E289&gt;0,F289&gt;E289),"Profit",IF(AND(ISNUMBER(F289),ISNUMBER(E289),E289&gt;0,F289=E289),"Draw",IF(AND(ISNUMBER(F289),ISNUMBER(E289),E289&gt;0,F289=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A289="","",IF(AND(ISNUMBER(E289),E289=0,OR(ISNUMBER(SEARCH("Free",D289&amp;"")),AND(ISNUMBER(F289),F289=0))),"Subscription",IF(ISNUMBER(G289),"Profit",IF(ISNUMBER(I289),"Disqualified",IF(ISNUMBER(H289),"Draw",IF(AND(ISNUMBER(F289),ISNUMBER(E289),E289&gt;0,F289&gt;E289),"Profit",IF(AND(ISNUMBER(F289),ISNUMBER(E289),E289&gt;0,F289=E289),"Draw",IF(AND(ISNUMBER(F289),ISNUMBER(E289),E289&gt;0,F289=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L289" s="50"/>
       <x:c r="M289" s="58"/>
@@ -12088,7 +12101,7 @@
         <x:f>IF(A290="","",IF(K290="Subscription","",IF(E290=0,"",IF(ISNUMBER(G290),G290/E290,IF(ISNUMBER(I290),-ABS(I290)/E290,IF(ISNUMBER(H290),0,IF(AND(ISNUMBER(F290),ISNUMBER(E290),E290&gt;0,F290&gt;E290),(F290-E290)/E290,IF(AND(ISNUMBER(F290),ISNUMBER(E290),E290&gt;0,F290=E290),0,IF(AND(ISNUMBER(F290),ISNUMBER(E290),E290&gt;0,F290=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K290" s="50" t="str">
-        <x:f>IF(A290="","",IF(AND(ISNUMBER(E290),E290=0,OR(ISNUMBER(SEARCH("Free",D290&amp;"")),AND(ISNUMBER(F290),F290=0))),"Subscription",IF(ISNUMBER(G290),"Profit",IF(ISNUMBER(I290),"Loss",IF(ISNUMBER(H290),"Draw",IF(AND(ISNUMBER(F290),ISNUMBER(E290),E290&gt;0,F290&gt;E290),"Profit",IF(AND(ISNUMBER(F290),ISNUMBER(E290),E290&gt;0,F290=E290),"Draw",IF(AND(ISNUMBER(F290),ISNUMBER(E290),E290&gt;0,F290=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A290="","",IF(AND(ISNUMBER(E290),E290=0,OR(ISNUMBER(SEARCH("Free",D290&amp;"")),AND(ISNUMBER(F290),F290=0))),"Subscription",IF(ISNUMBER(G290),"Profit",IF(ISNUMBER(I290),"Disqualified",IF(ISNUMBER(H290),"Draw",IF(AND(ISNUMBER(F290),ISNUMBER(E290),E290&gt;0,F290&gt;E290),"Profit",IF(AND(ISNUMBER(F290),ISNUMBER(E290),E290&gt;0,F290=E290),"Draw",IF(AND(ISNUMBER(F290),ISNUMBER(E290),E290&gt;0,F290=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L290" s="50"/>
       <x:c r="M290" s="58"/>
@@ -12125,7 +12138,7 @@
         <x:f>IF(A291="","",IF(K291="Subscription","",IF(E291=0,"",IF(ISNUMBER(G291),G291/E291,IF(ISNUMBER(I291),-ABS(I291)/E291,IF(ISNUMBER(H291),0,IF(AND(ISNUMBER(F291),ISNUMBER(E291),E291&gt;0,F291&gt;E291),(F291-E291)/E291,IF(AND(ISNUMBER(F291),ISNUMBER(E291),E291&gt;0,F291=E291),0,IF(AND(ISNUMBER(F291),ISNUMBER(E291),E291&gt;0,F291=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K291" s="50" t="str">
-        <x:f>IF(A291="","",IF(AND(ISNUMBER(E291),E291=0,OR(ISNUMBER(SEARCH("Free",D291&amp;"")),AND(ISNUMBER(F291),F291=0))),"Subscription",IF(ISNUMBER(G291),"Profit",IF(ISNUMBER(I291),"Loss",IF(ISNUMBER(H291),"Draw",IF(AND(ISNUMBER(F291),ISNUMBER(E291),E291&gt;0,F291&gt;E291),"Profit",IF(AND(ISNUMBER(F291),ISNUMBER(E291),E291&gt;0,F291=E291),"Draw",IF(AND(ISNUMBER(F291),ISNUMBER(E291),E291&gt;0,F291=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A291="","",IF(AND(ISNUMBER(E291),E291=0,OR(ISNUMBER(SEARCH("Free",D291&amp;"")),AND(ISNUMBER(F291),F291=0))),"Subscription",IF(ISNUMBER(G291),"Profit",IF(ISNUMBER(I291),"Disqualified",IF(ISNUMBER(H291),"Draw",IF(AND(ISNUMBER(F291),ISNUMBER(E291),E291&gt;0,F291&gt;E291),"Profit",IF(AND(ISNUMBER(F291),ISNUMBER(E291),E291&gt;0,F291=E291),"Draw",IF(AND(ISNUMBER(F291),ISNUMBER(E291),E291&gt;0,F291=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L291" s="50"/>
       <x:c r="M291" s="58"/>
@@ -12162,7 +12175,7 @@
         <x:f>IF(A292="","",IF(K292="Subscription","",IF(E292=0,"",IF(ISNUMBER(G292),G292/E292,IF(ISNUMBER(I292),-ABS(I292)/E292,IF(ISNUMBER(H292),0,IF(AND(ISNUMBER(F292),ISNUMBER(E292),E292&gt;0,F292&gt;E292),(F292-E292)/E292,IF(AND(ISNUMBER(F292),ISNUMBER(E292),E292&gt;0,F292=E292),0,IF(AND(ISNUMBER(F292),ISNUMBER(E292),E292&gt;0,F292=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K292" s="50" t="str">
-        <x:f>IF(A292="","",IF(AND(ISNUMBER(E292),E292=0,OR(ISNUMBER(SEARCH("Free",D292&amp;"")),AND(ISNUMBER(F292),F292=0))),"Subscription",IF(ISNUMBER(G292),"Profit",IF(ISNUMBER(I292),"Loss",IF(ISNUMBER(H292),"Draw",IF(AND(ISNUMBER(F292),ISNUMBER(E292),E292&gt;0,F292&gt;E292),"Profit",IF(AND(ISNUMBER(F292),ISNUMBER(E292),E292&gt;0,F292=E292),"Draw",IF(AND(ISNUMBER(F292),ISNUMBER(E292),E292&gt;0,F292=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A292="","",IF(AND(ISNUMBER(E292),E292=0,OR(ISNUMBER(SEARCH("Free",D292&amp;"")),AND(ISNUMBER(F292),F292=0))),"Subscription",IF(ISNUMBER(G292),"Profit",IF(ISNUMBER(I292),"Disqualified",IF(ISNUMBER(H292),"Draw",IF(AND(ISNUMBER(F292),ISNUMBER(E292),E292&gt;0,F292&gt;E292),"Profit",IF(AND(ISNUMBER(F292),ISNUMBER(E292),E292&gt;0,F292=E292),"Draw",IF(AND(ISNUMBER(F292),ISNUMBER(E292),E292&gt;0,F292=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L292" s="50"/>
       <x:c r="M292" s="58"/>
@@ -12199,7 +12212,7 @@
         <x:f>IF(A293="","",IF(K293="Subscription","",IF(E293=0,"",IF(ISNUMBER(G293),G293/E293,IF(ISNUMBER(I293),-ABS(I293)/E293,IF(ISNUMBER(H293),0,IF(AND(ISNUMBER(F293),ISNUMBER(E293),E293&gt;0,F293&gt;E293),(F293-E293)/E293,IF(AND(ISNUMBER(F293),ISNUMBER(E293),E293&gt;0,F293=E293),0,IF(AND(ISNUMBER(F293),ISNUMBER(E293),E293&gt;0,F293=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K293" s="50" t="str">
-        <x:f>IF(A293="","",IF(AND(ISNUMBER(E293),E293=0,OR(ISNUMBER(SEARCH("Free",D293&amp;"")),AND(ISNUMBER(F293),F293=0))),"Subscription",IF(ISNUMBER(G293),"Profit",IF(ISNUMBER(I293),"Loss",IF(ISNUMBER(H293),"Draw",IF(AND(ISNUMBER(F293),ISNUMBER(E293),E293&gt;0,F293&gt;E293),"Profit",IF(AND(ISNUMBER(F293),ISNUMBER(E293),E293&gt;0,F293=E293),"Draw",IF(AND(ISNUMBER(F293),ISNUMBER(E293),E293&gt;0,F293=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A293="","",IF(AND(ISNUMBER(E293),E293=0,OR(ISNUMBER(SEARCH("Free",D293&amp;"")),AND(ISNUMBER(F293),F293=0))),"Subscription",IF(ISNUMBER(G293),"Profit",IF(ISNUMBER(I293),"Disqualified",IF(ISNUMBER(H293),"Draw",IF(AND(ISNUMBER(F293),ISNUMBER(E293),E293&gt;0,F293&gt;E293),"Profit",IF(AND(ISNUMBER(F293),ISNUMBER(E293),E293&gt;0,F293=E293),"Draw",IF(AND(ISNUMBER(F293),ISNUMBER(E293),E293&gt;0,F293=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L293" s="50"/>
       <x:c r="M293" s="58"/>
@@ -12236,7 +12249,7 @@
         <x:f>IF(A294="","",IF(K294="Subscription","",IF(E294=0,"",IF(ISNUMBER(G294),G294/E294,IF(ISNUMBER(I294),-ABS(I294)/E294,IF(ISNUMBER(H294),0,IF(AND(ISNUMBER(F294),ISNUMBER(E294),E294&gt;0,F294&gt;E294),(F294-E294)/E294,IF(AND(ISNUMBER(F294),ISNUMBER(E294),E294&gt;0,F294=E294),0,IF(AND(ISNUMBER(F294),ISNUMBER(E294),E294&gt;0,F294=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K294" s="50" t="str">
-        <x:f>IF(A294="","",IF(AND(ISNUMBER(E294),E294=0,OR(ISNUMBER(SEARCH("Free",D294&amp;"")),AND(ISNUMBER(F294),F294=0))),"Subscription",IF(ISNUMBER(G294),"Profit",IF(ISNUMBER(I294),"Loss",IF(ISNUMBER(H294),"Draw",IF(AND(ISNUMBER(F294),ISNUMBER(E294),E294&gt;0,F294&gt;E294),"Profit",IF(AND(ISNUMBER(F294),ISNUMBER(E294),E294&gt;0,F294=E294),"Draw",IF(AND(ISNUMBER(F294),ISNUMBER(E294),E294&gt;0,F294=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A294="","",IF(AND(ISNUMBER(E294),E294=0,OR(ISNUMBER(SEARCH("Free",D294&amp;"")),AND(ISNUMBER(F294),F294=0))),"Subscription",IF(ISNUMBER(G294),"Profit",IF(ISNUMBER(I294),"Disqualified",IF(ISNUMBER(H294),"Draw",IF(AND(ISNUMBER(F294),ISNUMBER(E294),E294&gt;0,F294&gt;E294),"Profit",IF(AND(ISNUMBER(F294),ISNUMBER(E294),E294&gt;0,F294=E294),"Draw",IF(AND(ISNUMBER(F294),ISNUMBER(E294),E294&gt;0,F294=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L294" s="50"/>
       <x:c r="M294" s="58"/>
@@ -12273,7 +12286,7 @@
         <x:f>IF(A295="","",IF(K295="Subscription","",IF(E295=0,"",IF(ISNUMBER(G295),G295/E295,IF(ISNUMBER(I295),-ABS(I295)/E295,IF(ISNUMBER(H295),0,IF(AND(ISNUMBER(F295),ISNUMBER(E295),E295&gt;0,F295&gt;E295),(F295-E295)/E295,IF(AND(ISNUMBER(F295),ISNUMBER(E295),E295&gt;0,F295=E295),0,IF(AND(ISNUMBER(F295),ISNUMBER(E295),E295&gt;0,F295=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K295" s="50" t="str">
-        <x:f>IF(A295="","",IF(AND(ISNUMBER(E295),E295=0,OR(ISNUMBER(SEARCH("Free",D295&amp;"")),AND(ISNUMBER(F295),F295=0))),"Subscription",IF(ISNUMBER(G295),"Profit",IF(ISNUMBER(I295),"Loss",IF(ISNUMBER(H295),"Draw",IF(AND(ISNUMBER(F295),ISNUMBER(E295),E295&gt;0,F295&gt;E295),"Profit",IF(AND(ISNUMBER(F295),ISNUMBER(E295),E295&gt;0,F295=E295),"Draw",IF(AND(ISNUMBER(F295),ISNUMBER(E295),E295&gt;0,F295=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A295="","",IF(AND(ISNUMBER(E295),E295=0,OR(ISNUMBER(SEARCH("Free",D295&amp;"")),AND(ISNUMBER(F295),F295=0))),"Subscription",IF(ISNUMBER(G295),"Profit",IF(ISNUMBER(I295),"Disqualified",IF(ISNUMBER(H295),"Draw",IF(AND(ISNUMBER(F295),ISNUMBER(E295),E295&gt;0,F295&gt;E295),"Profit",IF(AND(ISNUMBER(F295),ISNUMBER(E295),E295&gt;0,F295=E295),"Draw",IF(AND(ISNUMBER(F295),ISNUMBER(E295),E295&gt;0,F295=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L295" s="50"/>
       <x:c r="M295" s="58"/>
@@ -12310,7 +12323,7 @@
         <x:f>IF(A296="","",IF(K296="Subscription","",IF(E296=0,"",IF(ISNUMBER(G296),G296/E296,IF(ISNUMBER(I296),-ABS(I296)/E296,IF(ISNUMBER(H296),0,IF(AND(ISNUMBER(F296),ISNUMBER(E296),E296&gt;0,F296&gt;E296),(F296-E296)/E296,IF(AND(ISNUMBER(F296),ISNUMBER(E296),E296&gt;0,F296=E296),0,IF(AND(ISNUMBER(F296),ISNUMBER(E296),E296&gt;0,F296=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K296" s="50" t="str">
-        <x:f>IF(A296="","",IF(AND(ISNUMBER(E296),E296=0,OR(ISNUMBER(SEARCH("Free",D296&amp;"")),AND(ISNUMBER(F296),F296=0))),"Subscription",IF(ISNUMBER(G296),"Profit",IF(ISNUMBER(I296),"Loss",IF(ISNUMBER(H296),"Draw",IF(AND(ISNUMBER(F296),ISNUMBER(E296),E296&gt;0,F296&gt;E296),"Profit",IF(AND(ISNUMBER(F296),ISNUMBER(E296),E296&gt;0,F296=E296),"Draw",IF(AND(ISNUMBER(F296),ISNUMBER(E296),E296&gt;0,F296=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A296="","",IF(AND(ISNUMBER(E296),E296=0,OR(ISNUMBER(SEARCH("Free",D296&amp;"")),AND(ISNUMBER(F296),F296=0))),"Subscription",IF(ISNUMBER(G296),"Profit",IF(ISNUMBER(I296),"Disqualified",IF(ISNUMBER(H296),"Draw",IF(AND(ISNUMBER(F296),ISNUMBER(E296),E296&gt;0,F296&gt;E296),"Profit",IF(AND(ISNUMBER(F296),ISNUMBER(E296),E296&gt;0,F296=E296),"Draw",IF(AND(ISNUMBER(F296),ISNUMBER(E296),E296&gt;0,F296=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L296" s="50"/>
       <x:c r="M296" s="58"/>
@@ -12347,7 +12360,7 @@
         <x:f>IF(A297="","",IF(K297="Subscription","",IF(E297=0,"",IF(ISNUMBER(G297),G297/E297,IF(ISNUMBER(I297),-ABS(I297)/E297,IF(ISNUMBER(H297),0,IF(AND(ISNUMBER(F297),ISNUMBER(E297),E297&gt;0,F297&gt;E297),(F297-E297)/E297,IF(AND(ISNUMBER(F297),ISNUMBER(E297),E297&gt;0,F297=E297),0,IF(AND(ISNUMBER(F297),ISNUMBER(E297),E297&gt;0,F297=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K297" s="50" t="str">
-        <x:f>IF(A297="","",IF(AND(ISNUMBER(E297),E297=0,OR(ISNUMBER(SEARCH("Free",D297&amp;"")),AND(ISNUMBER(F297),F297=0))),"Subscription",IF(ISNUMBER(G297),"Profit",IF(ISNUMBER(I297),"Loss",IF(ISNUMBER(H297),"Draw",IF(AND(ISNUMBER(F297),ISNUMBER(E297),E297&gt;0,F297&gt;E297),"Profit",IF(AND(ISNUMBER(F297),ISNUMBER(E297),E297&gt;0,F297=E297),"Draw",IF(AND(ISNUMBER(F297),ISNUMBER(E297),E297&gt;0,F297=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A297="","",IF(AND(ISNUMBER(E297),E297=0,OR(ISNUMBER(SEARCH("Free",D297&amp;"")),AND(ISNUMBER(F297),F297=0))),"Subscription",IF(ISNUMBER(G297),"Profit",IF(ISNUMBER(I297),"Disqualified",IF(ISNUMBER(H297),"Draw",IF(AND(ISNUMBER(F297),ISNUMBER(E297),E297&gt;0,F297&gt;E297),"Profit",IF(AND(ISNUMBER(F297),ISNUMBER(E297),E297&gt;0,F297=E297),"Draw",IF(AND(ISNUMBER(F297),ISNUMBER(E297),E297&gt;0,F297=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L297" s="50"/>
       <x:c r="M297" s="58"/>
@@ -12384,7 +12397,7 @@
         <x:f>IF(A298="","",IF(K298="Subscription","",IF(E298=0,"",IF(ISNUMBER(G298),G298/E298,IF(ISNUMBER(I298),-ABS(I298)/E298,IF(ISNUMBER(H298),0,IF(AND(ISNUMBER(F298),ISNUMBER(E298),E298&gt;0,F298&gt;E298),(F298-E298)/E298,IF(AND(ISNUMBER(F298),ISNUMBER(E298),E298&gt;0,F298=E298),0,IF(AND(ISNUMBER(F298),ISNUMBER(E298),E298&gt;0,F298=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K298" s="50" t="str">
-        <x:f>IF(A298="","",IF(AND(ISNUMBER(E298),E298=0,OR(ISNUMBER(SEARCH("Free",D298&amp;"")),AND(ISNUMBER(F298),F298=0))),"Subscription",IF(ISNUMBER(G298),"Profit",IF(ISNUMBER(I298),"Loss",IF(ISNUMBER(H298),"Draw",IF(AND(ISNUMBER(F298),ISNUMBER(E298),E298&gt;0,F298&gt;E298),"Profit",IF(AND(ISNUMBER(F298),ISNUMBER(E298),E298&gt;0,F298=E298),"Draw",IF(AND(ISNUMBER(F298),ISNUMBER(E298),E298&gt;0,F298=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A298="","",IF(AND(ISNUMBER(E298),E298=0,OR(ISNUMBER(SEARCH("Free",D298&amp;"")),AND(ISNUMBER(F298),F298=0))),"Subscription",IF(ISNUMBER(G298),"Profit",IF(ISNUMBER(I298),"Disqualified",IF(ISNUMBER(H298),"Draw",IF(AND(ISNUMBER(F298),ISNUMBER(E298),E298&gt;0,F298&gt;E298),"Profit",IF(AND(ISNUMBER(F298),ISNUMBER(E298),E298&gt;0,F298=E298),"Draw",IF(AND(ISNUMBER(F298),ISNUMBER(E298),E298&gt;0,F298=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L298" s="50"/>
       <x:c r="M298" s="58"/>
@@ -12421,7 +12434,7 @@
         <x:f>IF(A299="","",IF(K299="Subscription","",IF(E299=0,"",IF(ISNUMBER(G299),G299/E299,IF(ISNUMBER(I299),-ABS(I299)/E299,IF(ISNUMBER(H299),0,IF(AND(ISNUMBER(F299),ISNUMBER(E299),E299&gt;0,F299&gt;E299),(F299-E299)/E299,IF(AND(ISNUMBER(F299),ISNUMBER(E299),E299&gt;0,F299=E299),0,IF(AND(ISNUMBER(F299),ISNUMBER(E299),E299&gt;0,F299=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K299" s="50" t="str">
-        <x:f>IF(A299="","",IF(AND(ISNUMBER(E299),E299=0,OR(ISNUMBER(SEARCH("Free",D299&amp;"")),AND(ISNUMBER(F299),F299=0))),"Subscription",IF(ISNUMBER(G299),"Profit",IF(ISNUMBER(I299),"Loss",IF(ISNUMBER(H299),"Draw",IF(AND(ISNUMBER(F299),ISNUMBER(E299),E299&gt;0,F299&gt;E299),"Profit",IF(AND(ISNUMBER(F299),ISNUMBER(E299),E299&gt;0,F299=E299),"Draw",IF(AND(ISNUMBER(F299),ISNUMBER(E299),E299&gt;0,F299=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A299="","",IF(AND(ISNUMBER(E299),E299=0,OR(ISNUMBER(SEARCH("Free",D299&amp;"")),AND(ISNUMBER(F299),F299=0))),"Subscription",IF(ISNUMBER(G299),"Profit",IF(ISNUMBER(I299),"Disqualified",IF(ISNUMBER(H299),"Draw",IF(AND(ISNUMBER(F299),ISNUMBER(E299),E299&gt;0,F299&gt;E299),"Profit",IF(AND(ISNUMBER(F299),ISNUMBER(E299),E299&gt;0,F299=E299),"Draw",IF(AND(ISNUMBER(F299),ISNUMBER(E299),E299&gt;0,F299=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L299" s="50"/>
       <x:c r="M299" s="58"/>
@@ -12458,7 +12471,7 @@
         <x:f>IF(A300="","",IF(K300="Subscription","",IF(E300=0,"",IF(ISNUMBER(G300),G300/E300,IF(ISNUMBER(I300),-ABS(I300)/E300,IF(ISNUMBER(H300),0,IF(AND(ISNUMBER(F300),ISNUMBER(E300),E300&gt;0,F300&gt;E300),(F300-E300)/E300,IF(AND(ISNUMBER(F300),ISNUMBER(E300),E300&gt;0,F300=E300),0,IF(AND(ISNUMBER(F300),ISNUMBER(E300),E300&gt;0,F300=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K300" s="50" t="str">
-        <x:f>IF(A300="","",IF(AND(ISNUMBER(E300),E300=0,OR(ISNUMBER(SEARCH("Free",D300&amp;"")),AND(ISNUMBER(F300),F300=0))),"Subscription",IF(ISNUMBER(G300),"Profit",IF(ISNUMBER(I300),"Loss",IF(ISNUMBER(H300),"Draw",IF(AND(ISNUMBER(F300),ISNUMBER(E300),E300&gt;0,F300&gt;E300),"Profit",IF(AND(ISNUMBER(F300),ISNUMBER(E300),E300&gt;0,F300=E300),"Draw",IF(AND(ISNUMBER(F300),ISNUMBER(E300),E300&gt;0,F300=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A300="","",IF(AND(ISNUMBER(E300),E300=0,OR(ISNUMBER(SEARCH("Free",D300&amp;"")),AND(ISNUMBER(F300),F300=0))),"Subscription",IF(ISNUMBER(G300),"Profit",IF(ISNUMBER(I300),"Disqualified",IF(ISNUMBER(H300),"Draw",IF(AND(ISNUMBER(F300),ISNUMBER(E300),E300&gt;0,F300&gt;E300),"Profit",IF(AND(ISNUMBER(F300),ISNUMBER(E300),E300&gt;0,F300=E300),"Draw",IF(AND(ISNUMBER(F300),ISNUMBER(E300),E300&gt;0,F300=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L300" s="50"/>
       <x:c r="M300" s="58"/>
@@ -12495,7 +12508,7 @@
         <x:f>IF(A301="","",IF(K301="Subscription","",IF(E301=0,"",IF(ISNUMBER(G301),G301/E301,IF(ISNUMBER(I301),-ABS(I301)/E301,IF(ISNUMBER(H301),0,IF(AND(ISNUMBER(F301),ISNUMBER(E301),E301&gt;0,F301&gt;E301),(F301-E301)/E301,IF(AND(ISNUMBER(F301),ISNUMBER(E301),E301&gt;0,F301=E301),0,IF(AND(ISNUMBER(F301),ISNUMBER(E301),E301&gt;0,F301=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K301" s="50" t="str">
-        <x:f>IF(A301="","",IF(AND(ISNUMBER(E301),E301=0,OR(ISNUMBER(SEARCH("Free",D301&amp;"")),AND(ISNUMBER(F301),F301=0))),"Subscription",IF(ISNUMBER(G301),"Profit",IF(ISNUMBER(I301),"Loss",IF(ISNUMBER(H301),"Draw",IF(AND(ISNUMBER(F301),ISNUMBER(E301),E301&gt;0,F301&gt;E301),"Profit",IF(AND(ISNUMBER(F301),ISNUMBER(E301),E301&gt;0,F301=E301),"Draw",IF(AND(ISNUMBER(F301),ISNUMBER(E301),E301&gt;0,F301=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A301="","",IF(AND(ISNUMBER(E301),E301=0,OR(ISNUMBER(SEARCH("Free",D301&amp;"")),AND(ISNUMBER(F301),F301=0))),"Subscription",IF(ISNUMBER(G301),"Profit",IF(ISNUMBER(I301),"Disqualified",IF(ISNUMBER(H301),"Draw",IF(AND(ISNUMBER(F301),ISNUMBER(E301),E301&gt;0,F301&gt;E301),"Profit",IF(AND(ISNUMBER(F301),ISNUMBER(E301),E301&gt;0,F301=E301),"Draw",IF(AND(ISNUMBER(F301),ISNUMBER(E301),E301&gt;0,F301=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L301" s="50"/>
       <x:c r="M301" s="58"/>
@@ -12532,7 +12545,7 @@
         <x:f>IF(A302="","",IF(K302="Subscription","",IF(E302=0,"",IF(ISNUMBER(G302),G302/E302,IF(ISNUMBER(I302),-ABS(I302)/E302,IF(ISNUMBER(H302),0,IF(AND(ISNUMBER(F302),ISNUMBER(E302),E302&gt;0,F302&gt;E302),(F302-E302)/E302,IF(AND(ISNUMBER(F302),ISNUMBER(E302),E302&gt;0,F302=E302),0,IF(AND(ISNUMBER(F302),ISNUMBER(E302),E302&gt;0,F302=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K302" s="50" t="str">
-        <x:f>IF(A302="","",IF(AND(ISNUMBER(E302),E302=0,OR(ISNUMBER(SEARCH("Free",D302&amp;"")),AND(ISNUMBER(F302),F302=0))),"Subscription",IF(ISNUMBER(G302),"Profit",IF(ISNUMBER(I302),"Loss",IF(ISNUMBER(H302),"Draw",IF(AND(ISNUMBER(F302),ISNUMBER(E302),E302&gt;0,F302&gt;E302),"Profit",IF(AND(ISNUMBER(F302),ISNUMBER(E302),E302&gt;0,F302=E302),"Draw",IF(AND(ISNUMBER(F302),ISNUMBER(E302),E302&gt;0,F302=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A302="","",IF(AND(ISNUMBER(E302),E302=0,OR(ISNUMBER(SEARCH("Free",D302&amp;"")),AND(ISNUMBER(F302),F302=0))),"Subscription",IF(ISNUMBER(G302),"Profit",IF(ISNUMBER(I302),"Disqualified",IF(ISNUMBER(H302),"Draw",IF(AND(ISNUMBER(F302),ISNUMBER(E302),E302&gt;0,F302&gt;E302),"Profit",IF(AND(ISNUMBER(F302),ISNUMBER(E302),E302&gt;0,F302=E302),"Draw",IF(AND(ISNUMBER(F302),ISNUMBER(E302),E302&gt;0,F302=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L302" s="50"/>
       <x:c r="M302" s="58"/>
@@ -12569,7 +12582,7 @@
         <x:f>IF(A303="","",IF(K303="Subscription","",IF(E303=0,"",IF(ISNUMBER(G303),G303/E303,IF(ISNUMBER(I303),-ABS(I303)/E303,IF(ISNUMBER(H303),0,IF(AND(ISNUMBER(F303),ISNUMBER(E303),E303&gt;0,F303&gt;E303),(F303-E303)/E303,IF(AND(ISNUMBER(F303),ISNUMBER(E303),E303&gt;0,F303=E303),0,IF(AND(ISNUMBER(F303),ISNUMBER(E303),E303&gt;0,F303=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K303" s="50" t="str">
-        <x:f>IF(A303="","",IF(AND(ISNUMBER(E303),E303=0,OR(ISNUMBER(SEARCH("Free",D303&amp;"")),AND(ISNUMBER(F303),F303=0))),"Subscription",IF(ISNUMBER(G303),"Profit",IF(ISNUMBER(I303),"Loss",IF(ISNUMBER(H303),"Draw",IF(AND(ISNUMBER(F303),ISNUMBER(E303),E303&gt;0,F303&gt;E303),"Profit",IF(AND(ISNUMBER(F303),ISNUMBER(E303),E303&gt;0,F303=E303),"Draw",IF(AND(ISNUMBER(F303),ISNUMBER(E303),E303&gt;0,F303=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A303="","",IF(AND(ISNUMBER(E303),E303=0,OR(ISNUMBER(SEARCH("Free",D303&amp;"")),AND(ISNUMBER(F303),F303=0))),"Subscription",IF(ISNUMBER(G303),"Profit",IF(ISNUMBER(I303),"Disqualified",IF(ISNUMBER(H303),"Draw",IF(AND(ISNUMBER(F303),ISNUMBER(E303),E303&gt;0,F303&gt;E303),"Profit",IF(AND(ISNUMBER(F303),ISNUMBER(E303),E303&gt;0,F303=E303),"Draw",IF(AND(ISNUMBER(F303),ISNUMBER(E303),E303&gt;0,F303=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L303" s="50"/>
       <x:c r="M303" s="58"/>
@@ -12606,7 +12619,7 @@
         <x:f>IF(A304="","",IF(K304="Subscription","",IF(E304=0,"",IF(ISNUMBER(G304),G304/E304,IF(ISNUMBER(I304),-ABS(I304)/E304,IF(ISNUMBER(H304),0,IF(AND(ISNUMBER(F304),ISNUMBER(E304),E304&gt;0,F304&gt;E304),(F304-E304)/E304,IF(AND(ISNUMBER(F304),ISNUMBER(E304),E304&gt;0,F304=E304),0,IF(AND(ISNUMBER(F304),ISNUMBER(E304),E304&gt;0,F304=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K304" s="50" t="str">
-        <x:f>IF(A304="","",IF(AND(ISNUMBER(E304),E304=0,OR(ISNUMBER(SEARCH("Free",D304&amp;"")),AND(ISNUMBER(F304),F304=0))),"Subscription",IF(ISNUMBER(G304),"Profit",IF(ISNUMBER(I304),"Loss",IF(ISNUMBER(H304),"Draw",IF(AND(ISNUMBER(F304),ISNUMBER(E304),E304&gt;0,F304&gt;E304),"Profit",IF(AND(ISNUMBER(F304),ISNUMBER(E304),E304&gt;0,F304=E304),"Draw",IF(AND(ISNUMBER(F304),ISNUMBER(E304),E304&gt;0,F304=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A304="","",IF(AND(ISNUMBER(E304),E304=0,OR(ISNUMBER(SEARCH("Free",D304&amp;"")),AND(ISNUMBER(F304),F304=0))),"Subscription",IF(ISNUMBER(G304),"Profit",IF(ISNUMBER(I304),"Disqualified",IF(ISNUMBER(H304),"Draw",IF(AND(ISNUMBER(F304),ISNUMBER(E304),E304&gt;0,F304&gt;E304),"Profit",IF(AND(ISNUMBER(F304),ISNUMBER(E304),E304&gt;0,F304=E304),"Draw",IF(AND(ISNUMBER(F304),ISNUMBER(E304),E304&gt;0,F304=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L304" s="50"/>
       <x:c r="M304" s="58"/>
@@ -12643,7 +12656,7 @@
         <x:f>IF(A305="","",IF(K305="Subscription","",IF(E305=0,"",IF(ISNUMBER(G305),G305/E305,IF(ISNUMBER(I305),-ABS(I305)/E305,IF(ISNUMBER(H305),0,IF(AND(ISNUMBER(F305),ISNUMBER(E305),E305&gt;0,F305&gt;E305),(F305-E305)/E305,IF(AND(ISNUMBER(F305),ISNUMBER(E305),E305&gt;0,F305=E305),0,IF(AND(ISNUMBER(F305),ISNUMBER(E305),E305&gt;0,F305=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K305" s="50" t="str">
-        <x:f>IF(A305="","",IF(AND(ISNUMBER(E305),E305=0,OR(ISNUMBER(SEARCH("Free",D305&amp;"")),AND(ISNUMBER(F305),F305=0))),"Subscription",IF(ISNUMBER(G305),"Profit",IF(ISNUMBER(I305),"Loss",IF(ISNUMBER(H305),"Draw",IF(AND(ISNUMBER(F305),ISNUMBER(E305),E305&gt;0,F305&gt;E305),"Profit",IF(AND(ISNUMBER(F305),ISNUMBER(E305),E305&gt;0,F305=E305),"Draw",IF(AND(ISNUMBER(F305),ISNUMBER(E305),E305&gt;0,F305=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A305="","",IF(AND(ISNUMBER(E305),E305=0,OR(ISNUMBER(SEARCH("Free",D305&amp;"")),AND(ISNUMBER(F305),F305=0))),"Subscription",IF(ISNUMBER(G305),"Profit",IF(ISNUMBER(I305),"Disqualified",IF(ISNUMBER(H305),"Draw",IF(AND(ISNUMBER(F305),ISNUMBER(E305),E305&gt;0,F305&gt;E305),"Profit",IF(AND(ISNUMBER(F305),ISNUMBER(E305),E305&gt;0,F305=E305),"Draw",IF(AND(ISNUMBER(F305),ISNUMBER(E305),E305&gt;0,F305=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L305" s="50"/>
       <x:c r="M305" s="58"/>
@@ -12680,7 +12693,7 @@
         <x:f>IF(A306="","",IF(K306="Subscription","",IF(E306=0,"",IF(ISNUMBER(G306),G306/E306,IF(ISNUMBER(I306),-ABS(I306)/E306,IF(ISNUMBER(H306),0,IF(AND(ISNUMBER(F306),ISNUMBER(E306),E306&gt;0,F306&gt;E306),(F306-E306)/E306,IF(AND(ISNUMBER(F306),ISNUMBER(E306),E306&gt;0,F306=E306),0,IF(AND(ISNUMBER(F306),ISNUMBER(E306),E306&gt;0,F306=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K306" s="50" t="str">
-        <x:f>IF(A306="","",IF(AND(ISNUMBER(E306),E306=0,OR(ISNUMBER(SEARCH("Free",D306&amp;"")),AND(ISNUMBER(F306),F306=0))),"Subscription",IF(ISNUMBER(G306),"Profit",IF(ISNUMBER(I306),"Loss",IF(ISNUMBER(H306),"Draw",IF(AND(ISNUMBER(F306),ISNUMBER(E306),E306&gt;0,F306&gt;E306),"Profit",IF(AND(ISNUMBER(F306),ISNUMBER(E306),E306&gt;0,F306=E306),"Draw",IF(AND(ISNUMBER(F306),ISNUMBER(E306),E306&gt;0,F306=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A306="","",IF(AND(ISNUMBER(E306),E306=0,OR(ISNUMBER(SEARCH("Free",D306&amp;"")),AND(ISNUMBER(F306),F306=0))),"Subscription",IF(ISNUMBER(G306),"Profit",IF(ISNUMBER(I306),"Disqualified",IF(ISNUMBER(H306),"Draw",IF(AND(ISNUMBER(F306),ISNUMBER(E306),E306&gt;0,F306&gt;E306),"Profit",IF(AND(ISNUMBER(F306),ISNUMBER(E306),E306&gt;0,F306=E306),"Draw",IF(AND(ISNUMBER(F306),ISNUMBER(E306),E306&gt;0,F306=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L306" s="50"/>
       <x:c r="M306" s="58"/>
@@ -12717,7 +12730,7 @@
         <x:f>IF(A307="","",IF(K307="Subscription","",IF(E307=0,"",IF(ISNUMBER(G307),G307/E307,IF(ISNUMBER(I307),-ABS(I307)/E307,IF(ISNUMBER(H307),0,IF(AND(ISNUMBER(F307),ISNUMBER(E307),E307&gt;0,F307&gt;E307),(F307-E307)/E307,IF(AND(ISNUMBER(F307),ISNUMBER(E307),E307&gt;0,F307=E307),0,IF(AND(ISNUMBER(F307),ISNUMBER(E307),E307&gt;0,F307=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K307" s="50" t="str">
-        <x:f>IF(A307="","",IF(AND(ISNUMBER(E307),E307=0,OR(ISNUMBER(SEARCH("Free",D307&amp;"")),AND(ISNUMBER(F307),F307=0))),"Subscription",IF(ISNUMBER(G307),"Profit",IF(ISNUMBER(I307),"Loss",IF(ISNUMBER(H307),"Draw",IF(AND(ISNUMBER(F307),ISNUMBER(E307),E307&gt;0,F307&gt;E307),"Profit",IF(AND(ISNUMBER(F307),ISNUMBER(E307),E307&gt;0,F307=E307),"Draw",IF(AND(ISNUMBER(F307),ISNUMBER(E307),E307&gt;0,F307=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A307="","",IF(AND(ISNUMBER(E307),E307=0,OR(ISNUMBER(SEARCH("Free",D307&amp;"")),AND(ISNUMBER(F307),F307=0))),"Subscription",IF(ISNUMBER(G307),"Profit",IF(ISNUMBER(I307),"Disqualified",IF(ISNUMBER(H307),"Draw",IF(AND(ISNUMBER(F307),ISNUMBER(E307),E307&gt;0,F307&gt;E307),"Profit",IF(AND(ISNUMBER(F307),ISNUMBER(E307),E307&gt;0,F307=E307),"Draw",IF(AND(ISNUMBER(F307),ISNUMBER(E307),E307&gt;0,F307=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L307" s="50"/>
       <x:c r="M307" s="58"/>
@@ -12754,7 +12767,7 @@
         <x:f>IF(A308="","",IF(K308="Subscription","",IF(E308=0,"",IF(ISNUMBER(G308),G308/E308,IF(ISNUMBER(I308),-ABS(I308)/E308,IF(ISNUMBER(H308),0,IF(AND(ISNUMBER(F308),ISNUMBER(E308),E308&gt;0,F308&gt;E308),(F308-E308)/E308,IF(AND(ISNUMBER(F308),ISNUMBER(E308),E308&gt;0,F308=E308),0,IF(AND(ISNUMBER(F308),ISNUMBER(E308),E308&gt;0,F308=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K308" s="50" t="str">
-        <x:f>IF(A308="","",IF(AND(ISNUMBER(E308),E308=0,OR(ISNUMBER(SEARCH("Free",D308&amp;"")),AND(ISNUMBER(F308),F308=0))),"Subscription",IF(ISNUMBER(G308),"Profit",IF(ISNUMBER(I308),"Loss",IF(ISNUMBER(H308),"Draw",IF(AND(ISNUMBER(F308),ISNUMBER(E308),E308&gt;0,F308&gt;E308),"Profit",IF(AND(ISNUMBER(F308),ISNUMBER(E308),E308&gt;0,F308=E308),"Draw",IF(AND(ISNUMBER(F308),ISNUMBER(E308),E308&gt;0,F308=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A308="","",IF(AND(ISNUMBER(E308),E308=0,OR(ISNUMBER(SEARCH("Free",D308&amp;"")),AND(ISNUMBER(F308),F308=0))),"Subscription",IF(ISNUMBER(G308),"Profit",IF(ISNUMBER(I308),"Disqualified",IF(ISNUMBER(H308),"Draw",IF(AND(ISNUMBER(F308),ISNUMBER(E308),E308&gt;0,F308&gt;E308),"Profit",IF(AND(ISNUMBER(F308),ISNUMBER(E308),E308&gt;0,F308=E308),"Draw",IF(AND(ISNUMBER(F308),ISNUMBER(E308),E308&gt;0,F308=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L308" s="50"/>
       <x:c r="M308" s="58"/>
@@ -12791,7 +12804,7 @@
         <x:f>IF(A309="","",IF(K309="Subscription","",IF(E309=0,"",IF(ISNUMBER(G309),G309/E309,IF(ISNUMBER(I309),-ABS(I309)/E309,IF(ISNUMBER(H309),0,IF(AND(ISNUMBER(F309),ISNUMBER(E309),E309&gt;0,F309&gt;E309),(F309-E309)/E309,IF(AND(ISNUMBER(F309),ISNUMBER(E309),E309&gt;0,F309=E309),0,IF(AND(ISNUMBER(F309),ISNUMBER(E309),E309&gt;0,F309=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K309" s="50" t="str">
-        <x:f>IF(A309="","",IF(AND(ISNUMBER(E309),E309=0,OR(ISNUMBER(SEARCH("Free",D309&amp;"")),AND(ISNUMBER(F309),F309=0))),"Subscription",IF(ISNUMBER(G309),"Profit",IF(ISNUMBER(I309),"Loss",IF(ISNUMBER(H309),"Draw",IF(AND(ISNUMBER(F309),ISNUMBER(E309),E309&gt;0,F309&gt;E309),"Profit",IF(AND(ISNUMBER(F309),ISNUMBER(E309),E309&gt;0,F309=E309),"Draw",IF(AND(ISNUMBER(F309),ISNUMBER(E309),E309&gt;0,F309=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A309="","",IF(AND(ISNUMBER(E309),E309=0,OR(ISNUMBER(SEARCH("Free",D309&amp;"")),AND(ISNUMBER(F309),F309=0))),"Subscription",IF(ISNUMBER(G309),"Profit",IF(ISNUMBER(I309),"Disqualified",IF(ISNUMBER(H309),"Draw",IF(AND(ISNUMBER(F309),ISNUMBER(E309),E309&gt;0,F309&gt;E309),"Profit",IF(AND(ISNUMBER(F309),ISNUMBER(E309),E309&gt;0,F309=E309),"Draw",IF(AND(ISNUMBER(F309),ISNUMBER(E309),E309&gt;0,F309=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L309" s="50"/>
       <x:c r="M309" s="58"/>
@@ -12828,7 +12841,7 @@
         <x:f>IF(A310="","",IF(K310="Subscription","",IF(E310=0,"",IF(ISNUMBER(G310),G310/E310,IF(ISNUMBER(I310),-ABS(I310)/E310,IF(ISNUMBER(H310),0,IF(AND(ISNUMBER(F310),ISNUMBER(E310),E310&gt;0,F310&gt;E310),(F310-E310)/E310,IF(AND(ISNUMBER(F310),ISNUMBER(E310),E310&gt;0,F310=E310),0,IF(AND(ISNUMBER(F310),ISNUMBER(E310),E310&gt;0,F310=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K310" s="50" t="str">
-        <x:f>IF(A310="","",IF(AND(ISNUMBER(E310),E310=0,OR(ISNUMBER(SEARCH("Free",D310&amp;"")),AND(ISNUMBER(F310),F310=0))),"Subscription",IF(ISNUMBER(G310),"Profit",IF(ISNUMBER(I310),"Loss",IF(ISNUMBER(H310),"Draw",IF(AND(ISNUMBER(F310),ISNUMBER(E310),E310&gt;0,F310&gt;E310),"Profit",IF(AND(ISNUMBER(F310),ISNUMBER(E310),E310&gt;0,F310=E310),"Draw",IF(AND(ISNUMBER(F310),ISNUMBER(E310),E310&gt;0,F310=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A310="","",IF(AND(ISNUMBER(E310),E310=0,OR(ISNUMBER(SEARCH("Free",D310&amp;"")),AND(ISNUMBER(F310),F310=0))),"Subscription",IF(ISNUMBER(G310),"Profit",IF(ISNUMBER(I310),"Disqualified",IF(ISNUMBER(H310),"Draw",IF(AND(ISNUMBER(F310),ISNUMBER(E310),E310&gt;0,F310&gt;E310),"Profit",IF(AND(ISNUMBER(F310),ISNUMBER(E310),E310&gt;0,F310=E310),"Draw",IF(AND(ISNUMBER(F310),ISNUMBER(E310),E310&gt;0,F310=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L310" s="50"/>
       <x:c r="M310" s="58"/>
@@ -12865,7 +12878,7 @@
         <x:f>IF(A311="","",IF(K311="Subscription","",IF(E311=0,"",IF(ISNUMBER(G311),G311/E311,IF(ISNUMBER(I311),-ABS(I311)/E311,IF(ISNUMBER(H311),0,IF(AND(ISNUMBER(F311),ISNUMBER(E311),E311&gt;0,F311&gt;E311),(F311-E311)/E311,IF(AND(ISNUMBER(F311),ISNUMBER(E311),E311&gt;0,F311=E311),0,IF(AND(ISNUMBER(F311),ISNUMBER(E311),E311&gt;0,F311=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K311" s="50" t="str">
-        <x:f>IF(A311="","",IF(AND(ISNUMBER(E311),E311=0,OR(ISNUMBER(SEARCH("Free",D311&amp;"")),AND(ISNUMBER(F311),F311=0))),"Subscription",IF(ISNUMBER(G311),"Profit",IF(ISNUMBER(I311),"Loss",IF(ISNUMBER(H311),"Draw",IF(AND(ISNUMBER(F311),ISNUMBER(E311),E311&gt;0,F311&gt;E311),"Profit",IF(AND(ISNUMBER(F311),ISNUMBER(E311),E311&gt;0,F311=E311),"Draw",IF(AND(ISNUMBER(F311),ISNUMBER(E311),E311&gt;0,F311=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A311="","",IF(AND(ISNUMBER(E311),E311=0,OR(ISNUMBER(SEARCH("Free",D311&amp;"")),AND(ISNUMBER(F311),F311=0))),"Subscription",IF(ISNUMBER(G311),"Profit",IF(ISNUMBER(I311),"Disqualified",IF(ISNUMBER(H311),"Draw",IF(AND(ISNUMBER(F311),ISNUMBER(E311),E311&gt;0,F311&gt;E311),"Profit",IF(AND(ISNUMBER(F311),ISNUMBER(E311),E311&gt;0,F311=E311),"Draw",IF(AND(ISNUMBER(F311),ISNUMBER(E311),E311&gt;0,F311=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L311" s="50"/>
       <x:c r="M311" s="58"/>
@@ -12902,7 +12915,7 @@
         <x:f>IF(A312="","",IF(K312="Subscription","",IF(E312=0,"",IF(ISNUMBER(G312),G312/E312,IF(ISNUMBER(I312),-ABS(I312)/E312,IF(ISNUMBER(H312),0,IF(AND(ISNUMBER(F312),ISNUMBER(E312),E312&gt;0,F312&gt;E312),(F312-E312)/E312,IF(AND(ISNUMBER(F312),ISNUMBER(E312),E312&gt;0,F312=E312),0,IF(AND(ISNUMBER(F312),ISNUMBER(E312),E312&gt;0,F312=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K312" s="50" t="str">
-        <x:f>IF(A312="","",IF(AND(ISNUMBER(E312),E312=0,OR(ISNUMBER(SEARCH("Free",D312&amp;"")),AND(ISNUMBER(F312),F312=0))),"Subscription",IF(ISNUMBER(G312),"Profit",IF(ISNUMBER(I312),"Loss",IF(ISNUMBER(H312),"Draw",IF(AND(ISNUMBER(F312),ISNUMBER(E312),E312&gt;0,F312&gt;E312),"Profit",IF(AND(ISNUMBER(F312),ISNUMBER(E312),E312&gt;0,F312=E312),"Draw",IF(AND(ISNUMBER(F312),ISNUMBER(E312),E312&gt;0,F312=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A312="","",IF(AND(ISNUMBER(E312),E312=0,OR(ISNUMBER(SEARCH("Free",D312&amp;"")),AND(ISNUMBER(F312),F312=0))),"Subscription",IF(ISNUMBER(G312),"Profit",IF(ISNUMBER(I312),"Disqualified",IF(ISNUMBER(H312),"Draw",IF(AND(ISNUMBER(F312),ISNUMBER(E312),E312&gt;0,F312&gt;E312),"Profit",IF(AND(ISNUMBER(F312),ISNUMBER(E312),E312&gt;0,F312=E312),"Draw",IF(AND(ISNUMBER(F312),ISNUMBER(E312),E312&gt;0,F312=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L312" s="50"/>
       <x:c r="M312" s="58"/>
@@ -12939,7 +12952,7 @@
         <x:f>IF(A313="","",IF(K313="Subscription","",IF(E313=0,"",IF(ISNUMBER(G313),G313/E313,IF(ISNUMBER(I313),-ABS(I313)/E313,IF(ISNUMBER(H313),0,IF(AND(ISNUMBER(F313),ISNUMBER(E313),E313&gt;0,F313&gt;E313),(F313-E313)/E313,IF(AND(ISNUMBER(F313),ISNUMBER(E313),E313&gt;0,F313=E313),0,IF(AND(ISNUMBER(F313),ISNUMBER(E313),E313&gt;0,F313=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K313" s="50" t="str">
-        <x:f>IF(A313="","",IF(AND(ISNUMBER(E313),E313=0,OR(ISNUMBER(SEARCH("Free",D313&amp;"")),AND(ISNUMBER(F313),F313=0))),"Subscription",IF(ISNUMBER(G313),"Profit",IF(ISNUMBER(I313),"Loss",IF(ISNUMBER(H313),"Draw",IF(AND(ISNUMBER(F313),ISNUMBER(E313),E313&gt;0,F313&gt;E313),"Profit",IF(AND(ISNUMBER(F313),ISNUMBER(E313),E313&gt;0,F313=E313),"Draw",IF(AND(ISNUMBER(F313),ISNUMBER(E313),E313&gt;0,F313=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A313="","",IF(AND(ISNUMBER(E313),E313=0,OR(ISNUMBER(SEARCH("Free",D313&amp;"")),AND(ISNUMBER(F313),F313=0))),"Subscription",IF(ISNUMBER(G313),"Profit",IF(ISNUMBER(I313),"Disqualified",IF(ISNUMBER(H313),"Draw",IF(AND(ISNUMBER(F313),ISNUMBER(E313),E313&gt;0,F313&gt;E313),"Profit",IF(AND(ISNUMBER(F313),ISNUMBER(E313),E313&gt;0,F313=E313),"Draw",IF(AND(ISNUMBER(F313),ISNUMBER(E313),E313&gt;0,F313=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L313" s="50"/>
       <x:c r="M313" s="58"/>
@@ -12976,7 +12989,7 @@
         <x:f>IF(A314="","",IF(K314="Subscription","",IF(E314=0,"",IF(ISNUMBER(G314),G314/E314,IF(ISNUMBER(I314),-ABS(I314)/E314,IF(ISNUMBER(H314),0,IF(AND(ISNUMBER(F314),ISNUMBER(E314),E314&gt;0,F314&gt;E314),(F314-E314)/E314,IF(AND(ISNUMBER(F314),ISNUMBER(E314),E314&gt;0,F314=E314),0,IF(AND(ISNUMBER(F314),ISNUMBER(E314),E314&gt;0,F314=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K314" s="50" t="str">
-        <x:f>IF(A314="","",IF(AND(ISNUMBER(E314),E314=0,OR(ISNUMBER(SEARCH("Free",D314&amp;"")),AND(ISNUMBER(F314),F314=0))),"Subscription",IF(ISNUMBER(G314),"Profit",IF(ISNUMBER(I314),"Loss",IF(ISNUMBER(H314),"Draw",IF(AND(ISNUMBER(F314),ISNUMBER(E314),E314&gt;0,F314&gt;E314),"Profit",IF(AND(ISNUMBER(F314),ISNUMBER(E314),E314&gt;0,F314=E314),"Draw",IF(AND(ISNUMBER(F314),ISNUMBER(E314),E314&gt;0,F314=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A314="","",IF(AND(ISNUMBER(E314),E314=0,OR(ISNUMBER(SEARCH("Free",D314&amp;"")),AND(ISNUMBER(F314),F314=0))),"Subscription",IF(ISNUMBER(G314),"Profit",IF(ISNUMBER(I314),"Disqualified",IF(ISNUMBER(H314),"Draw",IF(AND(ISNUMBER(F314),ISNUMBER(E314),E314&gt;0,F314&gt;E314),"Profit",IF(AND(ISNUMBER(F314),ISNUMBER(E314),E314&gt;0,F314=E314),"Draw",IF(AND(ISNUMBER(F314),ISNUMBER(E314),E314&gt;0,F314=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L314" s="50"/>
       <x:c r="M314" s="58"/>
@@ -13013,7 +13026,7 @@
         <x:f>IF(A315="","",IF(K315="Subscription","",IF(E315=0,"",IF(ISNUMBER(G315),G315/E315,IF(ISNUMBER(I315),-ABS(I315)/E315,IF(ISNUMBER(H315),0,IF(AND(ISNUMBER(F315),ISNUMBER(E315),E315&gt;0,F315&gt;E315),(F315-E315)/E315,IF(AND(ISNUMBER(F315),ISNUMBER(E315),E315&gt;0,F315=E315),0,IF(AND(ISNUMBER(F315),ISNUMBER(E315),E315&gt;0,F315=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K315" s="50" t="str">
-        <x:f>IF(A315="","",IF(AND(ISNUMBER(E315),E315=0,OR(ISNUMBER(SEARCH("Free",D315&amp;"")),AND(ISNUMBER(F315),F315=0))),"Subscription",IF(ISNUMBER(G315),"Profit",IF(ISNUMBER(I315),"Loss",IF(ISNUMBER(H315),"Draw",IF(AND(ISNUMBER(F315),ISNUMBER(E315),E315&gt;0,F315&gt;E315),"Profit",IF(AND(ISNUMBER(F315),ISNUMBER(E315),E315&gt;0,F315=E315),"Draw",IF(AND(ISNUMBER(F315),ISNUMBER(E315),E315&gt;0,F315=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A315="","",IF(AND(ISNUMBER(E315),E315=0,OR(ISNUMBER(SEARCH("Free",D315&amp;"")),AND(ISNUMBER(F315),F315=0))),"Subscription",IF(ISNUMBER(G315),"Profit",IF(ISNUMBER(I315),"Disqualified",IF(ISNUMBER(H315),"Draw",IF(AND(ISNUMBER(F315),ISNUMBER(E315),E315&gt;0,F315&gt;E315),"Profit",IF(AND(ISNUMBER(F315),ISNUMBER(E315),E315&gt;0,F315=E315),"Draw",IF(AND(ISNUMBER(F315),ISNUMBER(E315),E315&gt;0,F315=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L315" s="50"/>
       <x:c r="M315" s="58"/>
@@ -13050,7 +13063,7 @@
         <x:f>IF(A316="","",IF(K316="Subscription","",IF(E316=0,"",IF(ISNUMBER(G316),G316/E316,IF(ISNUMBER(I316),-ABS(I316)/E316,IF(ISNUMBER(H316),0,IF(AND(ISNUMBER(F316),ISNUMBER(E316),E316&gt;0,F316&gt;E316),(F316-E316)/E316,IF(AND(ISNUMBER(F316),ISNUMBER(E316),E316&gt;0,F316=E316),0,IF(AND(ISNUMBER(F316),ISNUMBER(E316),E316&gt;0,F316=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K316" s="50" t="str">
-        <x:f>IF(A316="","",IF(AND(ISNUMBER(E316),E316=0,OR(ISNUMBER(SEARCH("Free",D316&amp;"")),AND(ISNUMBER(F316),F316=0))),"Subscription",IF(ISNUMBER(G316),"Profit",IF(ISNUMBER(I316),"Loss",IF(ISNUMBER(H316),"Draw",IF(AND(ISNUMBER(F316),ISNUMBER(E316),E316&gt;0,F316&gt;E316),"Profit",IF(AND(ISNUMBER(F316),ISNUMBER(E316),E316&gt;0,F316=E316),"Draw",IF(AND(ISNUMBER(F316),ISNUMBER(E316),E316&gt;0,F316=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A316="","",IF(AND(ISNUMBER(E316),E316=0,OR(ISNUMBER(SEARCH("Free",D316&amp;"")),AND(ISNUMBER(F316),F316=0))),"Subscription",IF(ISNUMBER(G316),"Profit",IF(ISNUMBER(I316),"Disqualified",IF(ISNUMBER(H316),"Draw",IF(AND(ISNUMBER(F316),ISNUMBER(E316),E316&gt;0,F316&gt;E316),"Profit",IF(AND(ISNUMBER(F316),ISNUMBER(E316),E316&gt;0,F316=E316),"Draw",IF(AND(ISNUMBER(F316),ISNUMBER(E316),E316&gt;0,F316=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L316" s="50"/>
       <x:c r="M316" s="58"/>
@@ -13087,7 +13100,7 @@
         <x:f>IF(A317="","",IF(K317="Subscription","",IF(E317=0,"",IF(ISNUMBER(G317),G317/E317,IF(ISNUMBER(I317),-ABS(I317)/E317,IF(ISNUMBER(H317),0,IF(AND(ISNUMBER(F317),ISNUMBER(E317),E317&gt;0,F317&gt;E317),(F317-E317)/E317,IF(AND(ISNUMBER(F317),ISNUMBER(E317),E317&gt;0,F317=E317),0,IF(AND(ISNUMBER(F317),ISNUMBER(E317),E317&gt;0,F317=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K317" s="50" t="str">
-        <x:f>IF(A317="","",IF(AND(ISNUMBER(E317),E317=0,OR(ISNUMBER(SEARCH("Free",D317&amp;"")),AND(ISNUMBER(F317),F317=0))),"Subscription",IF(ISNUMBER(G317),"Profit",IF(ISNUMBER(I317),"Loss",IF(ISNUMBER(H317),"Draw",IF(AND(ISNUMBER(F317),ISNUMBER(E317),E317&gt;0,F317&gt;E317),"Profit",IF(AND(ISNUMBER(F317),ISNUMBER(E317),E317&gt;0,F317=E317),"Draw",IF(AND(ISNUMBER(F317),ISNUMBER(E317),E317&gt;0,F317=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A317="","",IF(AND(ISNUMBER(E317),E317=0,OR(ISNUMBER(SEARCH("Free",D317&amp;"")),AND(ISNUMBER(F317),F317=0))),"Subscription",IF(ISNUMBER(G317),"Profit",IF(ISNUMBER(I317),"Disqualified",IF(ISNUMBER(H317),"Draw",IF(AND(ISNUMBER(F317),ISNUMBER(E317),E317&gt;0,F317&gt;E317),"Profit",IF(AND(ISNUMBER(F317),ISNUMBER(E317),E317&gt;0,F317=E317),"Draw",IF(AND(ISNUMBER(F317),ISNUMBER(E317),E317&gt;0,F317=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L317" s="50"/>
       <x:c r="M317" s="58"/>
@@ -13124,7 +13137,7 @@
         <x:f>IF(A318="","",IF(K318="Subscription","",IF(E318=0,"",IF(ISNUMBER(G318),G318/E318,IF(ISNUMBER(I318),-ABS(I318)/E318,IF(ISNUMBER(H318),0,IF(AND(ISNUMBER(F318),ISNUMBER(E318),E318&gt;0,F318&gt;E318),(F318-E318)/E318,IF(AND(ISNUMBER(F318),ISNUMBER(E318),E318&gt;0,F318=E318),0,IF(AND(ISNUMBER(F318),ISNUMBER(E318),E318&gt;0,F318=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K318" s="50" t="str">
-        <x:f>IF(A318="","",IF(AND(ISNUMBER(E318),E318=0,OR(ISNUMBER(SEARCH("Free",D318&amp;"")),AND(ISNUMBER(F318),F318=0))),"Subscription",IF(ISNUMBER(G318),"Profit",IF(ISNUMBER(I318),"Loss",IF(ISNUMBER(H318),"Draw",IF(AND(ISNUMBER(F318),ISNUMBER(E318),E318&gt;0,F318&gt;E318),"Profit",IF(AND(ISNUMBER(F318),ISNUMBER(E318),E318&gt;0,F318=E318),"Draw",IF(AND(ISNUMBER(F318),ISNUMBER(E318),E318&gt;0,F318=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A318="","",IF(AND(ISNUMBER(E318),E318=0,OR(ISNUMBER(SEARCH("Free",D318&amp;"")),AND(ISNUMBER(F318),F318=0))),"Subscription",IF(ISNUMBER(G318),"Profit",IF(ISNUMBER(I318),"Disqualified",IF(ISNUMBER(H318),"Draw",IF(AND(ISNUMBER(F318),ISNUMBER(E318),E318&gt;0,F318&gt;E318),"Profit",IF(AND(ISNUMBER(F318),ISNUMBER(E318),E318&gt;0,F318=E318),"Draw",IF(AND(ISNUMBER(F318),ISNUMBER(E318),E318&gt;0,F318=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L318" s="50"/>
       <x:c r="M318" s="58"/>
@@ -13161,7 +13174,7 @@
         <x:f>IF(A319="","",IF(K319="Subscription","",IF(E319=0,"",IF(ISNUMBER(G319),G319/E319,IF(ISNUMBER(I319),-ABS(I319)/E319,IF(ISNUMBER(H319),0,IF(AND(ISNUMBER(F319),ISNUMBER(E319),E319&gt;0,F319&gt;E319),(F319-E319)/E319,IF(AND(ISNUMBER(F319),ISNUMBER(E319),E319&gt;0,F319=E319),0,IF(AND(ISNUMBER(F319),ISNUMBER(E319),E319&gt;0,F319=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K319" s="50" t="str">
-        <x:f>IF(A319="","",IF(AND(ISNUMBER(E319),E319=0,OR(ISNUMBER(SEARCH("Free",D319&amp;"")),AND(ISNUMBER(F319),F319=0))),"Subscription",IF(ISNUMBER(G319),"Profit",IF(ISNUMBER(I319),"Loss",IF(ISNUMBER(H319),"Draw",IF(AND(ISNUMBER(F319),ISNUMBER(E319),E319&gt;0,F319&gt;E319),"Profit",IF(AND(ISNUMBER(F319),ISNUMBER(E319),E319&gt;0,F319=E319),"Draw",IF(AND(ISNUMBER(F319),ISNUMBER(E319),E319&gt;0,F319=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A319="","",IF(AND(ISNUMBER(E319),E319=0,OR(ISNUMBER(SEARCH("Free",D319&amp;"")),AND(ISNUMBER(F319),F319=0))),"Subscription",IF(ISNUMBER(G319),"Profit",IF(ISNUMBER(I319),"Disqualified",IF(ISNUMBER(H319),"Draw",IF(AND(ISNUMBER(F319),ISNUMBER(E319),E319&gt;0,F319&gt;E319),"Profit",IF(AND(ISNUMBER(F319),ISNUMBER(E319),E319&gt;0,F319=E319),"Draw",IF(AND(ISNUMBER(F319),ISNUMBER(E319),E319&gt;0,F319=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L319" s="50"/>
       <x:c r="M319" s="58"/>
@@ -13198,7 +13211,7 @@
         <x:f>IF(A320="","",IF(K320="Subscription","",IF(E320=0,"",IF(ISNUMBER(G320),G320/E320,IF(ISNUMBER(I320),-ABS(I320)/E320,IF(ISNUMBER(H320),0,IF(AND(ISNUMBER(F320),ISNUMBER(E320),E320&gt;0,F320&gt;E320),(F320-E320)/E320,IF(AND(ISNUMBER(F320),ISNUMBER(E320),E320&gt;0,F320=E320),0,IF(AND(ISNUMBER(F320),ISNUMBER(E320),E320&gt;0,F320=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K320" s="50" t="str">
-        <x:f>IF(A320="","",IF(AND(ISNUMBER(E320),E320=0,OR(ISNUMBER(SEARCH("Free",D320&amp;"")),AND(ISNUMBER(F320),F320=0))),"Subscription",IF(ISNUMBER(G320),"Profit",IF(ISNUMBER(I320),"Loss",IF(ISNUMBER(H320),"Draw",IF(AND(ISNUMBER(F320),ISNUMBER(E320),E320&gt;0,F320&gt;E320),"Profit",IF(AND(ISNUMBER(F320),ISNUMBER(E320),E320&gt;0,F320=E320),"Draw",IF(AND(ISNUMBER(F320),ISNUMBER(E320),E320&gt;0,F320=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A320="","",IF(AND(ISNUMBER(E320),E320=0,OR(ISNUMBER(SEARCH("Free",D320&amp;"")),AND(ISNUMBER(F320),F320=0))),"Subscription",IF(ISNUMBER(G320),"Profit",IF(ISNUMBER(I320),"Disqualified",IF(ISNUMBER(H320),"Draw",IF(AND(ISNUMBER(F320),ISNUMBER(E320),E320&gt;0,F320&gt;E320),"Profit",IF(AND(ISNUMBER(F320),ISNUMBER(E320),E320&gt;0,F320=E320),"Draw",IF(AND(ISNUMBER(F320),ISNUMBER(E320),E320&gt;0,F320=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L320" s="50"/>
       <x:c r="M320" s="58"/>
@@ -13235,7 +13248,7 @@
         <x:f>IF(A321="","",IF(K321="Subscription","",IF(E321=0,"",IF(ISNUMBER(G321),G321/E321,IF(ISNUMBER(I321),-ABS(I321)/E321,IF(ISNUMBER(H321),0,IF(AND(ISNUMBER(F321),ISNUMBER(E321),E321&gt;0,F321&gt;E321),(F321-E321)/E321,IF(AND(ISNUMBER(F321),ISNUMBER(E321),E321&gt;0,F321=E321),0,IF(AND(ISNUMBER(F321),ISNUMBER(E321),E321&gt;0,F321=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K321" s="50" t="str">
-        <x:f>IF(A321="","",IF(AND(ISNUMBER(E321),E321=0,OR(ISNUMBER(SEARCH("Free",D321&amp;"")),AND(ISNUMBER(F321),F321=0))),"Subscription",IF(ISNUMBER(G321),"Profit",IF(ISNUMBER(I321),"Loss",IF(ISNUMBER(H321),"Draw",IF(AND(ISNUMBER(F321),ISNUMBER(E321),E321&gt;0,F321&gt;E321),"Profit",IF(AND(ISNUMBER(F321),ISNUMBER(E321),E321&gt;0,F321=E321),"Draw",IF(AND(ISNUMBER(F321),ISNUMBER(E321),E321&gt;0,F321=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A321="","",IF(AND(ISNUMBER(E321),E321=0,OR(ISNUMBER(SEARCH("Free",D321&amp;"")),AND(ISNUMBER(F321),F321=0))),"Subscription",IF(ISNUMBER(G321),"Profit",IF(ISNUMBER(I321),"Disqualified",IF(ISNUMBER(H321),"Draw",IF(AND(ISNUMBER(F321),ISNUMBER(E321),E321&gt;0,F321&gt;E321),"Profit",IF(AND(ISNUMBER(F321),ISNUMBER(E321),E321&gt;0,F321=E321),"Draw",IF(AND(ISNUMBER(F321),ISNUMBER(E321),E321&gt;0,F321=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L321" s="50"/>
       <x:c r="M321" s="58"/>
@@ -13272,7 +13285,7 @@
         <x:f>IF(A322="","",IF(K322="Subscription","",IF(E322=0,"",IF(ISNUMBER(G322),G322/E322,IF(ISNUMBER(I322),-ABS(I322)/E322,IF(ISNUMBER(H322),0,IF(AND(ISNUMBER(F322),ISNUMBER(E322),E322&gt;0,F322&gt;E322),(F322-E322)/E322,IF(AND(ISNUMBER(F322),ISNUMBER(E322),E322&gt;0,F322=E322),0,IF(AND(ISNUMBER(F322),ISNUMBER(E322),E322&gt;0,F322=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K322" s="50" t="str">
-        <x:f>IF(A322="","",IF(AND(ISNUMBER(E322),E322=0,OR(ISNUMBER(SEARCH("Free",D322&amp;"")),AND(ISNUMBER(F322),F322=0))),"Subscription",IF(ISNUMBER(G322),"Profit",IF(ISNUMBER(I322),"Loss",IF(ISNUMBER(H322),"Draw",IF(AND(ISNUMBER(F322),ISNUMBER(E322),E322&gt;0,F322&gt;E322),"Profit",IF(AND(ISNUMBER(F322),ISNUMBER(E322),E322&gt;0,F322=E322),"Draw",IF(AND(ISNUMBER(F322),ISNUMBER(E322),E322&gt;0,F322=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A322="","",IF(AND(ISNUMBER(E322),E322=0,OR(ISNUMBER(SEARCH("Free",D322&amp;"")),AND(ISNUMBER(F322),F322=0))),"Subscription",IF(ISNUMBER(G322),"Profit",IF(ISNUMBER(I322),"Disqualified",IF(ISNUMBER(H322),"Draw",IF(AND(ISNUMBER(F322),ISNUMBER(E322),E322&gt;0,F322&gt;E322),"Profit",IF(AND(ISNUMBER(F322),ISNUMBER(E322),E322&gt;0,F322=E322),"Draw",IF(AND(ISNUMBER(F322),ISNUMBER(E322),E322&gt;0,F322=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L322" s="50"/>
       <x:c r="M322" s="58"/>
@@ -13309,7 +13322,7 @@
         <x:f>IF(A323="","",IF(K323="Subscription","",IF(E323=0,"",IF(ISNUMBER(G323),G323/E323,IF(ISNUMBER(I323),-ABS(I323)/E323,IF(ISNUMBER(H323),0,IF(AND(ISNUMBER(F323),ISNUMBER(E323),E323&gt;0,F323&gt;E323),(F323-E323)/E323,IF(AND(ISNUMBER(F323),ISNUMBER(E323),E323&gt;0,F323=E323),0,IF(AND(ISNUMBER(F323),ISNUMBER(E323),E323&gt;0,F323=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K323" s="50" t="str">
-        <x:f>IF(A323="","",IF(AND(ISNUMBER(E323),E323=0,OR(ISNUMBER(SEARCH("Free",D323&amp;"")),AND(ISNUMBER(F323),F323=0))),"Subscription",IF(ISNUMBER(G323),"Profit",IF(ISNUMBER(I323),"Loss",IF(ISNUMBER(H323),"Draw",IF(AND(ISNUMBER(F323),ISNUMBER(E323),E323&gt;0,F323&gt;E323),"Profit",IF(AND(ISNUMBER(F323),ISNUMBER(E323),E323&gt;0,F323=E323),"Draw",IF(AND(ISNUMBER(F323),ISNUMBER(E323),E323&gt;0,F323=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A323="","",IF(AND(ISNUMBER(E323),E323=0,OR(ISNUMBER(SEARCH("Free",D323&amp;"")),AND(ISNUMBER(F323),F323=0))),"Subscription",IF(ISNUMBER(G323),"Profit",IF(ISNUMBER(I323),"Disqualified",IF(ISNUMBER(H323),"Draw",IF(AND(ISNUMBER(F323),ISNUMBER(E323),E323&gt;0,F323&gt;E323),"Profit",IF(AND(ISNUMBER(F323),ISNUMBER(E323),E323&gt;0,F323=E323),"Draw",IF(AND(ISNUMBER(F323),ISNUMBER(E323),E323&gt;0,F323=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L323" s="50"/>
       <x:c r="M323" s="58"/>
@@ -13346,7 +13359,7 @@
         <x:f>IF(A324="","",IF(K324="Subscription","",IF(E324=0,"",IF(ISNUMBER(G324),G324/E324,IF(ISNUMBER(I324),-ABS(I324)/E324,IF(ISNUMBER(H324),0,IF(AND(ISNUMBER(F324),ISNUMBER(E324),E324&gt;0,F324&gt;E324),(F324-E324)/E324,IF(AND(ISNUMBER(F324),ISNUMBER(E324),E324&gt;0,F324=E324),0,IF(AND(ISNUMBER(F324),ISNUMBER(E324),E324&gt;0,F324=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K324" s="50" t="str">
-        <x:f>IF(A324="","",IF(AND(ISNUMBER(E324),E324=0,OR(ISNUMBER(SEARCH("Free",D324&amp;"")),AND(ISNUMBER(F324),F324=0))),"Subscription",IF(ISNUMBER(G324),"Profit",IF(ISNUMBER(I324),"Loss",IF(ISNUMBER(H324),"Draw",IF(AND(ISNUMBER(F324),ISNUMBER(E324),E324&gt;0,F324&gt;E324),"Profit",IF(AND(ISNUMBER(F324),ISNUMBER(E324),E324&gt;0,F324=E324),"Draw",IF(AND(ISNUMBER(F324),ISNUMBER(E324),E324&gt;0,F324=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A324="","",IF(AND(ISNUMBER(E324),E324=0,OR(ISNUMBER(SEARCH("Free",D324&amp;"")),AND(ISNUMBER(F324),F324=0))),"Subscription",IF(ISNUMBER(G324),"Profit",IF(ISNUMBER(I324),"Disqualified",IF(ISNUMBER(H324),"Draw",IF(AND(ISNUMBER(F324),ISNUMBER(E324),E324&gt;0,F324&gt;E324),"Profit",IF(AND(ISNUMBER(F324),ISNUMBER(E324),E324&gt;0,F324=E324),"Draw",IF(AND(ISNUMBER(F324),ISNUMBER(E324),E324&gt;0,F324=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L324" s="50"/>
       <x:c r="M324" s="58"/>
@@ -13383,7 +13396,7 @@
         <x:f>IF(A325="","",IF(K325="Subscription","",IF(E325=0,"",IF(ISNUMBER(G325),G325/E325,IF(ISNUMBER(I325),-ABS(I325)/E325,IF(ISNUMBER(H325),0,IF(AND(ISNUMBER(F325),ISNUMBER(E325),E325&gt;0,F325&gt;E325),(F325-E325)/E325,IF(AND(ISNUMBER(F325),ISNUMBER(E325),E325&gt;0,F325=E325),0,IF(AND(ISNUMBER(F325),ISNUMBER(E325),E325&gt;0,F325=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K325" s="50" t="str">
-        <x:f>IF(A325="","",IF(AND(ISNUMBER(E325),E325=0,OR(ISNUMBER(SEARCH("Free",D325&amp;"")),AND(ISNUMBER(F325),F325=0))),"Subscription",IF(ISNUMBER(G325),"Profit",IF(ISNUMBER(I325),"Loss",IF(ISNUMBER(H325),"Draw",IF(AND(ISNUMBER(F325),ISNUMBER(E325),E325&gt;0,F325&gt;E325),"Profit",IF(AND(ISNUMBER(F325),ISNUMBER(E325),E325&gt;0,F325=E325),"Draw",IF(AND(ISNUMBER(F325),ISNUMBER(E325),E325&gt;0,F325=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A325="","",IF(AND(ISNUMBER(E325),E325=0,OR(ISNUMBER(SEARCH("Free",D325&amp;"")),AND(ISNUMBER(F325),F325=0))),"Subscription",IF(ISNUMBER(G325),"Profit",IF(ISNUMBER(I325),"Disqualified",IF(ISNUMBER(H325),"Draw",IF(AND(ISNUMBER(F325),ISNUMBER(E325),E325&gt;0,F325&gt;E325),"Profit",IF(AND(ISNUMBER(F325),ISNUMBER(E325),E325&gt;0,F325=E325),"Draw",IF(AND(ISNUMBER(F325),ISNUMBER(E325),E325&gt;0,F325=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L325" s="50"/>
       <x:c r="M325" s="58"/>
@@ -13420,7 +13433,7 @@
         <x:f>IF(A326="","",IF(K326="Subscription","",IF(E326=0,"",IF(ISNUMBER(G326),G326/E326,IF(ISNUMBER(I326),-ABS(I326)/E326,IF(ISNUMBER(H326),0,IF(AND(ISNUMBER(F326),ISNUMBER(E326),E326&gt;0,F326&gt;E326),(F326-E326)/E326,IF(AND(ISNUMBER(F326),ISNUMBER(E326),E326&gt;0,F326=E326),0,IF(AND(ISNUMBER(F326),ISNUMBER(E326),E326&gt;0,F326=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K326" s="50" t="str">
-        <x:f>IF(A326="","",IF(AND(ISNUMBER(E326),E326=0,OR(ISNUMBER(SEARCH("Free",D326&amp;"")),AND(ISNUMBER(F326),F326=0))),"Subscription",IF(ISNUMBER(G326),"Profit",IF(ISNUMBER(I326),"Loss",IF(ISNUMBER(H326),"Draw",IF(AND(ISNUMBER(F326),ISNUMBER(E326),E326&gt;0,F326&gt;E326),"Profit",IF(AND(ISNUMBER(F326),ISNUMBER(E326),E326&gt;0,F326=E326),"Draw",IF(AND(ISNUMBER(F326),ISNUMBER(E326),E326&gt;0,F326=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A326="","",IF(AND(ISNUMBER(E326),E326=0,OR(ISNUMBER(SEARCH("Free",D326&amp;"")),AND(ISNUMBER(F326),F326=0))),"Subscription",IF(ISNUMBER(G326),"Profit",IF(ISNUMBER(I326),"Disqualified",IF(ISNUMBER(H326),"Draw",IF(AND(ISNUMBER(F326),ISNUMBER(E326),E326&gt;0,F326&gt;E326),"Profit",IF(AND(ISNUMBER(F326),ISNUMBER(E326),E326&gt;0,F326=E326),"Draw",IF(AND(ISNUMBER(F326),ISNUMBER(E326),E326&gt;0,F326=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L326" s="50"/>
       <x:c r="M326" s="58"/>
@@ -13457,7 +13470,7 @@
         <x:f>IF(A327="","",IF(K327="Subscription","",IF(E327=0,"",IF(ISNUMBER(G327),G327/E327,IF(ISNUMBER(I327),-ABS(I327)/E327,IF(ISNUMBER(H327),0,IF(AND(ISNUMBER(F327),ISNUMBER(E327),E327&gt;0,F327&gt;E327),(F327-E327)/E327,IF(AND(ISNUMBER(F327),ISNUMBER(E327),E327&gt;0,F327=E327),0,IF(AND(ISNUMBER(F327),ISNUMBER(E327),E327&gt;0,F327=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K327" s="50" t="str">
-        <x:f>IF(A327="","",IF(AND(ISNUMBER(E327),E327=0,OR(ISNUMBER(SEARCH("Free",D327&amp;"")),AND(ISNUMBER(F327),F327=0))),"Subscription",IF(ISNUMBER(G327),"Profit",IF(ISNUMBER(I327),"Loss",IF(ISNUMBER(H327),"Draw",IF(AND(ISNUMBER(F327),ISNUMBER(E327),E327&gt;0,F327&gt;E327),"Profit",IF(AND(ISNUMBER(F327),ISNUMBER(E327),E327&gt;0,F327=E327),"Draw",IF(AND(ISNUMBER(F327),ISNUMBER(E327),E327&gt;0,F327=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A327="","",IF(AND(ISNUMBER(E327),E327=0,OR(ISNUMBER(SEARCH("Free",D327&amp;"")),AND(ISNUMBER(F327),F327=0))),"Subscription",IF(ISNUMBER(G327),"Profit",IF(ISNUMBER(I327),"Disqualified",IF(ISNUMBER(H327),"Draw",IF(AND(ISNUMBER(F327),ISNUMBER(E327),E327&gt;0,F327&gt;E327),"Profit",IF(AND(ISNUMBER(F327),ISNUMBER(E327),E327&gt;0,F327=E327),"Draw",IF(AND(ISNUMBER(F327),ISNUMBER(E327),E327&gt;0,F327=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L327" s="50"/>
       <x:c r="M327" s="58"/>
@@ -13494,7 +13507,7 @@
         <x:f>IF(A328="","",IF(K328="Subscription","",IF(E328=0,"",IF(ISNUMBER(G328),G328/E328,IF(ISNUMBER(I328),-ABS(I328)/E328,IF(ISNUMBER(H328),0,IF(AND(ISNUMBER(F328),ISNUMBER(E328),E328&gt;0,F328&gt;E328),(F328-E328)/E328,IF(AND(ISNUMBER(F328),ISNUMBER(E328),E328&gt;0,F328=E328),0,IF(AND(ISNUMBER(F328),ISNUMBER(E328),E328&gt;0,F328=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K328" s="50" t="str">
-        <x:f>IF(A328="","",IF(AND(ISNUMBER(E328),E328=0,OR(ISNUMBER(SEARCH("Free",D328&amp;"")),AND(ISNUMBER(F328),F328=0))),"Subscription",IF(ISNUMBER(G328),"Profit",IF(ISNUMBER(I328),"Loss",IF(ISNUMBER(H328),"Draw",IF(AND(ISNUMBER(F328),ISNUMBER(E328),E328&gt;0,F328&gt;E328),"Profit",IF(AND(ISNUMBER(F328),ISNUMBER(E328),E328&gt;0,F328=E328),"Draw",IF(AND(ISNUMBER(F328),ISNUMBER(E328),E328&gt;0,F328=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A328="","",IF(AND(ISNUMBER(E328),E328=0,OR(ISNUMBER(SEARCH("Free",D328&amp;"")),AND(ISNUMBER(F328),F328=0))),"Subscription",IF(ISNUMBER(G328),"Profit",IF(ISNUMBER(I328),"Disqualified",IF(ISNUMBER(H328),"Draw",IF(AND(ISNUMBER(F328),ISNUMBER(E328),E328&gt;0,F328&gt;E328),"Profit",IF(AND(ISNUMBER(F328),ISNUMBER(E328),E328&gt;0,F328=E328),"Draw",IF(AND(ISNUMBER(F328),ISNUMBER(E328),E328&gt;0,F328=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L328" s="50"/>
       <x:c r="M328" s="58"/>
@@ -13531,7 +13544,7 @@
         <x:f>IF(A329="","",IF(K329="Subscription","",IF(E329=0,"",IF(ISNUMBER(G329),G329/E329,IF(ISNUMBER(I329),-ABS(I329)/E329,IF(ISNUMBER(H329),0,IF(AND(ISNUMBER(F329),ISNUMBER(E329),E329&gt;0,F329&gt;E329),(F329-E329)/E329,IF(AND(ISNUMBER(F329),ISNUMBER(E329),E329&gt;0,F329=E329),0,IF(AND(ISNUMBER(F329),ISNUMBER(E329),E329&gt;0,F329=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K329" s="50" t="str">
-        <x:f>IF(A329="","",IF(AND(ISNUMBER(E329),E329=0,OR(ISNUMBER(SEARCH("Free",D329&amp;"")),AND(ISNUMBER(F329),F329=0))),"Subscription",IF(ISNUMBER(G329),"Profit",IF(ISNUMBER(I329),"Loss",IF(ISNUMBER(H329),"Draw",IF(AND(ISNUMBER(F329),ISNUMBER(E329),E329&gt;0,F329&gt;E329),"Profit",IF(AND(ISNUMBER(F329),ISNUMBER(E329),E329&gt;0,F329=E329),"Draw",IF(AND(ISNUMBER(F329),ISNUMBER(E329),E329&gt;0,F329=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A329="","",IF(AND(ISNUMBER(E329),E329=0,OR(ISNUMBER(SEARCH("Free",D329&amp;"")),AND(ISNUMBER(F329),F329=0))),"Subscription",IF(ISNUMBER(G329),"Profit",IF(ISNUMBER(I329),"Disqualified",IF(ISNUMBER(H329),"Draw",IF(AND(ISNUMBER(F329),ISNUMBER(E329),E329&gt;0,F329&gt;E329),"Profit",IF(AND(ISNUMBER(F329),ISNUMBER(E329),E329&gt;0,F329=E329),"Draw",IF(AND(ISNUMBER(F329),ISNUMBER(E329),E329&gt;0,F329=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L329" s="50"/>
       <x:c r="M329" s="58"/>
@@ -13568,7 +13581,7 @@
         <x:f>IF(A330="","",IF(K330="Subscription","",IF(E330=0,"",IF(ISNUMBER(G330),G330/E330,IF(ISNUMBER(I330),-ABS(I330)/E330,IF(ISNUMBER(H330),0,IF(AND(ISNUMBER(F330),ISNUMBER(E330),E330&gt;0,F330&gt;E330),(F330-E330)/E330,IF(AND(ISNUMBER(F330),ISNUMBER(E330),E330&gt;0,F330=E330),0,IF(AND(ISNUMBER(F330),ISNUMBER(E330),E330&gt;0,F330=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K330" s="50" t="str">
-        <x:f>IF(A330="","",IF(AND(ISNUMBER(E330),E330=0,OR(ISNUMBER(SEARCH("Free",D330&amp;"")),AND(ISNUMBER(F330),F330=0))),"Subscription",IF(ISNUMBER(G330),"Profit",IF(ISNUMBER(I330),"Loss",IF(ISNUMBER(H330),"Draw",IF(AND(ISNUMBER(F330),ISNUMBER(E330),E330&gt;0,F330&gt;E330),"Profit",IF(AND(ISNUMBER(F330),ISNUMBER(E330),E330&gt;0,F330=E330),"Draw",IF(AND(ISNUMBER(F330),ISNUMBER(E330),E330&gt;0,F330=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A330="","",IF(AND(ISNUMBER(E330),E330=0,OR(ISNUMBER(SEARCH("Free",D330&amp;"")),AND(ISNUMBER(F330),F330=0))),"Subscription",IF(ISNUMBER(G330),"Profit",IF(ISNUMBER(I330),"Disqualified",IF(ISNUMBER(H330),"Draw",IF(AND(ISNUMBER(F330),ISNUMBER(E330),E330&gt;0,F330&gt;E330),"Profit",IF(AND(ISNUMBER(F330),ISNUMBER(E330),E330&gt;0,F330=E330),"Draw",IF(AND(ISNUMBER(F330),ISNUMBER(E330),E330&gt;0,F330=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L330" s="50"/>
       <x:c r="M330" s="58"/>
@@ -13605,7 +13618,7 @@
         <x:f>IF(A331="","",IF(K331="Subscription","",IF(E331=0,"",IF(ISNUMBER(G331),G331/E331,IF(ISNUMBER(I331),-ABS(I331)/E331,IF(ISNUMBER(H331),0,IF(AND(ISNUMBER(F331),ISNUMBER(E331),E331&gt;0,F331&gt;E331),(F331-E331)/E331,IF(AND(ISNUMBER(F331),ISNUMBER(E331),E331&gt;0,F331=E331),0,IF(AND(ISNUMBER(F331),ISNUMBER(E331),E331&gt;0,F331=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K331" s="50" t="str">
-        <x:f>IF(A331="","",IF(AND(ISNUMBER(E331),E331=0,OR(ISNUMBER(SEARCH("Free",D331&amp;"")),AND(ISNUMBER(F331),F331=0))),"Subscription",IF(ISNUMBER(G331),"Profit",IF(ISNUMBER(I331),"Loss",IF(ISNUMBER(H331),"Draw",IF(AND(ISNUMBER(F331),ISNUMBER(E331),E331&gt;0,F331&gt;E331),"Profit",IF(AND(ISNUMBER(F331),ISNUMBER(E331),E331&gt;0,F331=E331),"Draw",IF(AND(ISNUMBER(F331),ISNUMBER(E331),E331&gt;0,F331=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A331="","",IF(AND(ISNUMBER(E331),E331=0,OR(ISNUMBER(SEARCH("Free",D331&amp;"")),AND(ISNUMBER(F331),F331=0))),"Subscription",IF(ISNUMBER(G331),"Profit",IF(ISNUMBER(I331),"Disqualified",IF(ISNUMBER(H331),"Draw",IF(AND(ISNUMBER(F331),ISNUMBER(E331),E331&gt;0,F331&gt;E331),"Profit",IF(AND(ISNUMBER(F331),ISNUMBER(E331),E331&gt;0,F331=E331),"Draw",IF(AND(ISNUMBER(F331),ISNUMBER(E331),E331&gt;0,F331=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L331" s="50"/>
       <x:c r="M331" s="58"/>
@@ -13642,7 +13655,7 @@
         <x:f>IF(A332="","",IF(K332="Subscription","",IF(E332=0,"",IF(ISNUMBER(G332),G332/E332,IF(ISNUMBER(I332),-ABS(I332)/E332,IF(ISNUMBER(H332),0,IF(AND(ISNUMBER(F332),ISNUMBER(E332),E332&gt;0,F332&gt;E332),(F332-E332)/E332,IF(AND(ISNUMBER(F332),ISNUMBER(E332),E332&gt;0,F332=E332),0,IF(AND(ISNUMBER(F332),ISNUMBER(E332),E332&gt;0,F332=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K332" s="50" t="str">
-        <x:f>IF(A332="","",IF(AND(ISNUMBER(E332),E332=0,OR(ISNUMBER(SEARCH("Free",D332&amp;"")),AND(ISNUMBER(F332),F332=0))),"Subscription",IF(ISNUMBER(G332),"Profit",IF(ISNUMBER(I332),"Loss",IF(ISNUMBER(H332),"Draw",IF(AND(ISNUMBER(F332),ISNUMBER(E332),E332&gt;0,F332&gt;E332),"Profit",IF(AND(ISNUMBER(F332),ISNUMBER(E332),E332&gt;0,F332=E332),"Draw",IF(AND(ISNUMBER(F332),ISNUMBER(E332),E332&gt;0,F332=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A332="","",IF(AND(ISNUMBER(E332),E332=0,OR(ISNUMBER(SEARCH("Free",D332&amp;"")),AND(ISNUMBER(F332),F332=0))),"Subscription",IF(ISNUMBER(G332),"Profit",IF(ISNUMBER(I332),"Disqualified",IF(ISNUMBER(H332),"Draw",IF(AND(ISNUMBER(F332),ISNUMBER(E332),E332&gt;0,F332&gt;E332),"Profit",IF(AND(ISNUMBER(F332),ISNUMBER(E332),E332&gt;0,F332=E332),"Draw",IF(AND(ISNUMBER(F332),ISNUMBER(E332),E332&gt;0,F332=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L332" s="50"/>
       <x:c r="M332" s="58"/>
@@ -13679,7 +13692,7 @@
         <x:f>IF(A333="","",IF(K333="Subscription","",IF(E333=0,"",IF(ISNUMBER(G333),G333/E333,IF(ISNUMBER(I333),-ABS(I333)/E333,IF(ISNUMBER(H333),0,IF(AND(ISNUMBER(F333),ISNUMBER(E333),E333&gt;0,F333&gt;E333),(F333-E333)/E333,IF(AND(ISNUMBER(F333),ISNUMBER(E333),E333&gt;0,F333=E333),0,IF(AND(ISNUMBER(F333),ISNUMBER(E333),E333&gt;0,F333=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K333" s="50" t="str">
-        <x:f>IF(A333="","",IF(AND(ISNUMBER(E333),E333=0,OR(ISNUMBER(SEARCH("Free",D333&amp;"")),AND(ISNUMBER(F333),F333=0))),"Subscription",IF(ISNUMBER(G333),"Profit",IF(ISNUMBER(I333),"Loss",IF(ISNUMBER(H333),"Draw",IF(AND(ISNUMBER(F333),ISNUMBER(E333),E333&gt;0,F333&gt;E333),"Profit",IF(AND(ISNUMBER(F333),ISNUMBER(E333),E333&gt;0,F333=E333),"Draw",IF(AND(ISNUMBER(F333),ISNUMBER(E333),E333&gt;0,F333=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A333="","",IF(AND(ISNUMBER(E333),E333=0,OR(ISNUMBER(SEARCH("Free",D333&amp;"")),AND(ISNUMBER(F333),F333=0))),"Subscription",IF(ISNUMBER(G333),"Profit",IF(ISNUMBER(I333),"Disqualified",IF(ISNUMBER(H333),"Draw",IF(AND(ISNUMBER(F333),ISNUMBER(E333),E333&gt;0,F333&gt;E333),"Profit",IF(AND(ISNUMBER(F333),ISNUMBER(E333),E333&gt;0,F333=E333),"Draw",IF(AND(ISNUMBER(F333),ISNUMBER(E333),E333&gt;0,F333=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L333" s="50"/>
       <x:c r="M333" s="58"/>
@@ -13716,7 +13729,7 @@
         <x:f>IF(A334="","",IF(K334="Subscription","",IF(E334=0,"",IF(ISNUMBER(G334),G334/E334,IF(ISNUMBER(I334),-ABS(I334)/E334,IF(ISNUMBER(H334),0,IF(AND(ISNUMBER(F334),ISNUMBER(E334),E334&gt;0,F334&gt;E334),(F334-E334)/E334,IF(AND(ISNUMBER(F334),ISNUMBER(E334),E334&gt;0,F334=E334),0,IF(AND(ISNUMBER(F334),ISNUMBER(E334),E334&gt;0,F334=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K334" s="50" t="str">
-        <x:f>IF(A334="","",IF(AND(ISNUMBER(E334),E334=0,OR(ISNUMBER(SEARCH("Free",D334&amp;"")),AND(ISNUMBER(F334),F334=0))),"Subscription",IF(ISNUMBER(G334),"Profit",IF(ISNUMBER(I334),"Loss",IF(ISNUMBER(H334),"Draw",IF(AND(ISNUMBER(F334),ISNUMBER(E334),E334&gt;0,F334&gt;E334),"Profit",IF(AND(ISNUMBER(F334),ISNUMBER(E334),E334&gt;0,F334=E334),"Draw",IF(AND(ISNUMBER(F334),ISNUMBER(E334),E334&gt;0,F334=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A334="","",IF(AND(ISNUMBER(E334),E334=0,OR(ISNUMBER(SEARCH("Free",D334&amp;"")),AND(ISNUMBER(F334),F334=0))),"Subscription",IF(ISNUMBER(G334),"Profit",IF(ISNUMBER(I334),"Disqualified",IF(ISNUMBER(H334),"Draw",IF(AND(ISNUMBER(F334),ISNUMBER(E334),E334&gt;0,F334&gt;E334),"Profit",IF(AND(ISNUMBER(F334),ISNUMBER(E334),E334&gt;0,F334=E334),"Draw",IF(AND(ISNUMBER(F334),ISNUMBER(E334),E334&gt;0,F334=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L334" s="50"/>
       <x:c r="M334" s="58"/>
@@ -13753,7 +13766,7 @@
         <x:f>IF(A335="","",IF(K335="Subscription","",IF(E335=0,"",IF(ISNUMBER(G335),G335/E335,IF(ISNUMBER(I335),-ABS(I335)/E335,IF(ISNUMBER(H335),0,IF(AND(ISNUMBER(F335),ISNUMBER(E335),E335&gt;0,F335&gt;E335),(F335-E335)/E335,IF(AND(ISNUMBER(F335),ISNUMBER(E335),E335&gt;0,F335=E335),0,IF(AND(ISNUMBER(F335),ISNUMBER(E335),E335&gt;0,F335=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K335" s="50" t="str">
-        <x:f>IF(A335="","",IF(AND(ISNUMBER(E335),E335=0,OR(ISNUMBER(SEARCH("Free",D335&amp;"")),AND(ISNUMBER(F335),F335=0))),"Subscription",IF(ISNUMBER(G335),"Profit",IF(ISNUMBER(I335),"Loss",IF(ISNUMBER(H335),"Draw",IF(AND(ISNUMBER(F335),ISNUMBER(E335),E335&gt;0,F335&gt;E335),"Profit",IF(AND(ISNUMBER(F335),ISNUMBER(E335),E335&gt;0,F335=E335),"Draw",IF(AND(ISNUMBER(F335),ISNUMBER(E335),E335&gt;0,F335=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A335="","",IF(AND(ISNUMBER(E335),E335=0,OR(ISNUMBER(SEARCH("Free",D335&amp;"")),AND(ISNUMBER(F335),F335=0))),"Subscription",IF(ISNUMBER(G335),"Profit",IF(ISNUMBER(I335),"Disqualified",IF(ISNUMBER(H335),"Draw",IF(AND(ISNUMBER(F335),ISNUMBER(E335),E335&gt;0,F335&gt;E335),"Profit",IF(AND(ISNUMBER(F335),ISNUMBER(E335),E335&gt;0,F335=E335),"Draw",IF(AND(ISNUMBER(F335),ISNUMBER(E335),E335&gt;0,F335=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L335" s="50"/>
       <x:c r="M335" s="58"/>
@@ -13790,7 +13803,7 @@
         <x:f>IF(A336="","",IF(K336="Subscription","",IF(E336=0,"",IF(ISNUMBER(G336),G336/E336,IF(ISNUMBER(I336),-ABS(I336)/E336,IF(ISNUMBER(H336),0,IF(AND(ISNUMBER(F336),ISNUMBER(E336),E336&gt;0,F336&gt;E336),(F336-E336)/E336,IF(AND(ISNUMBER(F336),ISNUMBER(E336),E336&gt;0,F336=E336),0,IF(AND(ISNUMBER(F336),ISNUMBER(E336),E336&gt;0,F336=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K336" s="50" t="str">
-        <x:f>IF(A336="","",IF(AND(ISNUMBER(E336),E336=0,OR(ISNUMBER(SEARCH("Free",D336&amp;"")),AND(ISNUMBER(F336),F336=0))),"Subscription",IF(ISNUMBER(G336),"Profit",IF(ISNUMBER(I336),"Loss",IF(ISNUMBER(H336),"Draw",IF(AND(ISNUMBER(F336),ISNUMBER(E336),E336&gt;0,F336&gt;E336),"Profit",IF(AND(ISNUMBER(F336),ISNUMBER(E336),E336&gt;0,F336=E336),"Draw",IF(AND(ISNUMBER(F336),ISNUMBER(E336),E336&gt;0,F336=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A336="","",IF(AND(ISNUMBER(E336),E336=0,OR(ISNUMBER(SEARCH("Free",D336&amp;"")),AND(ISNUMBER(F336),F336=0))),"Subscription",IF(ISNUMBER(G336),"Profit",IF(ISNUMBER(I336),"Disqualified",IF(ISNUMBER(H336),"Draw",IF(AND(ISNUMBER(F336),ISNUMBER(E336),E336&gt;0,F336&gt;E336),"Profit",IF(AND(ISNUMBER(F336),ISNUMBER(E336),E336&gt;0,F336=E336),"Draw",IF(AND(ISNUMBER(F336),ISNUMBER(E336),E336&gt;0,F336=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L336" s="50"/>
       <x:c r="M336" s="58"/>
@@ -13827,7 +13840,7 @@
         <x:f>IF(A337="","",IF(K337="Subscription","",IF(E337=0,"",IF(ISNUMBER(G337),G337/E337,IF(ISNUMBER(I337),-ABS(I337)/E337,IF(ISNUMBER(H337),0,IF(AND(ISNUMBER(F337),ISNUMBER(E337),E337&gt;0,F337&gt;E337),(F337-E337)/E337,IF(AND(ISNUMBER(F337),ISNUMBER(E337),E337&gt;0,F337=E337),0,IF(AND(ISNUMBER(F337),ISNUMBER(E337),E337&gt;0,F337=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K337" s="50" t="str">
-        <x:f>IF(A337="","",IF(AND(ISNUMBER(E337),E337=0,OR(ISNUMBER(SEARCH("Free",D337&amp;"")),AND(ISNUMBER(F337),F337=0))),"Subscription",IF(ISNUMBER(G337),"Profit",IF(ISNUMBER(I337),"Loss",IF(ISNUMBER(H337),"Draw",IF(AND(ISNUMBER(F337),ISNUMBER(E337),E337&gt;0,F337&gt;E337),"Profit",IF(AND(ISNUMBER(F337),ISNUMBER(E337),E337&gt;0,F337=E337),"Draw",IF(AND(ISNUMBER(F337),ISNUMBER(E337),E337&gt;0,F337=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A337="","",IF(AND(ISNUMBER(E337),E337=0,OR(ISNUMBER(SEARCH("Free",D337&amp;"")),AND(ISNUMBER(F337),F337=0))),"Subscription",IF(ISNUMBER(G337),"Profit",IF(ISNUMBER(I337),"Disqualified",IF(ISNUMBER(H337),"Draw",IF(AND(ISNUMBER(F337),ISNUMBER(E337),E337&gt;0,F337&gt;E337),"Profit",IF(AND(ISNUMBER(F337),ISNUMBER(E337),E337&gt;0,F337=E337),"Draw",IF(AND(ISNUMBER(F337),ISNUMBER(E337),E337&gt;0,F337=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L337" s="50"/>
       <x:c r="M337" s="58"/>
@@ -13864,7 +13877,7 @@
         <x:f>IF(A338="","",IF(K338="Subscription","",IF(E338=0,"",IF(ISNUMBER(G338),G338/E338,IF(ISNUMBER(I338),-ABS(I338)/E338,IF(ISNUMBER(H338),0,IF(AND(ISNUMBER(F338),ISNUMBER(E338),E338&gt;0,F338&gt;E338),(F338-E338)/E338,IF(AND(ISNUMBER(F338),ISNUMBER(E338),E338&gt;0,F338=E338),0,IF(AND(ISNUMBER(F338),ISNUMBER(E338),E338&gt;0,F338=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K338" s="50" t="str">
-        <x:f>IF(A338="","",IF(AND(ISNUMBER(E338),E338=0,OR(ISNUMBER(SEARCH("Free",D338&amp;"")),AND(ISNUMBER(F338),F338=0))),"Subscription",IF(ISNUMBER(G338),"Profit",IF(ISNUMBER(I338),"Loss",IF(ISNUMBER(H338),"Draw",IF(AND(ISNUMBER(F338),ISNUMBER(E338),E338&gt;0,F338&gt;E338),"Profit",IF(AND(ISNUMBER(F338),ISNUMBER(E338),E338&gt;0,F338=E338),"Draw",IF(AND(ISNUMBER(F338),ISNUMBER(E338),E338&gt;0,F338=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A338="","",IF(AND(ISNUMBER(E338),E338=0,OR(ISNUMBER(SEARCH("Free",D338&amp;"")),AND(ISNUMBER(F338),F338=0))),"Subscription",IF(ISNUMBER(G338),"Profit",IF(ISNUMBER(I338),"Disqualified",IF(ISNUMBER(H338),"Draw",IF(AND(ISNUMBER(F338),ISNUMBER(E338),E338&gt;0,F338&gt;E338),"Profit",IF(AND(ISNUMBER(F338),ISNUMBER(E338),E338&gt;0,F338=E338),"Draw",IF(AND(ISNUMBER(F338),ISNUMBER(E338),E338&gt;0,F338=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L338" s="50"/>
       <x:c r="M338" s="58"/>
@@ -13901,7 +13914,7 @@
         <x:f>IF(A339="","",IF(K339="Subscription","",IF(E339=0,"",IF(ISNUMBER(G339),G339/E339,IF(ISNUMBER(I339),-ABS(I339)/E339,IF(ISNUMBER(H339),0,IF(AND(ISNUMBER(F339),ISNUMBER(E339),E339&gt;0,F339&gt;E339),(F339-E339)/E339,IF(AND(ISNUMBER(F339),ISNUMBER(E339),E339&gt;0,F339=E339),0,IF(AND(ISNUMBER(F339),ISNUMBER(E339),E339&gt;0,F339=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K339" s="50" t="str">
-        <x:f>IF(A339="","",IF(AND(ISNUMBER(E339),E339=0,OR(ISNUMBER(SEARCH("Free",D339&amp;"")),AND(ISNUMBER(F339),F339=0))),"Subscription",IF(ISNUMBER(G339),"Profit",IF(ISNUMBER(I339),"Loss",IF(ISNUMBER(H339),"Draw",IF(AND(ISNUMBER(F339),ISNUMBER(E339),E339&gt;0,F339&gt;E339),"Profit",IF(AND(ISNUMBER(F339),ISNUMBER(E339),E339&gt;0,F339=E339),"Draw",IF(AND(ISNUMBER(F339),ISNUMBER(E339),E339&gt;0,F339=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A339="","",IF(AND(ISNUMBER(E339),E339=0,OR(ISNUMBER(SEARCH("Free",D339&amp;"")),AND(ISNUMBER(F339),F339=0))),"Subscription",IF(ISNUMBER(G339),"Profit",IF(ISNUMBER(I339),"Disqualified",IF(ISNUMBER(H339),"Draw",IF(AND(ISNUMBER(F339),ISNUMBER(E339),E339&gt;0,F339&gt;E339),"Profit",IF(AND(ISNUMBER(F339),ISNUMBER(E339),E339&gt;0,F339=E339),"Draw",IF(AND(ISNUMBER(F339),ISNUMBER(E339),E339&gt;0,F339=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L339" s="50"/>
       <x:c r="M339" s="58"/>
@@ -13938,7 +13951,7 @@
         <x:f>IF(A340="","",IF(K340="Subscription","",IF(E340=0,"",IF(ISNUMBER(G340),G340/E340,IF(ISNUMBER(I340),-ABS(I340)/E340,IF(ISNUMBER(H340),0,IF(AND(ISNUMBER(F340),ISNUMBER(E340),E340&gt;0,F340&gt;E340),(F340-E340)/E340,IF(AND(ISNUMBER(F340),ISNUMBER(E340),E340&gt;0,F340=E340),0,IF(AND(ISNUMBER(F340),ISNUMBER(E340),E340&gt;0,F340=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K340" s="50" t="str">
-        <x:f>IF(A340="","",IF(AND(ISNUMBER(E340),E340=0,OR(ISNUMBER(SEARCH("Free",D340&amp;"")),AND(ISNUMBER(F340),F340=0))),"Subscription",IF(ISNUMBER(G340),"Profit",IF(ISNUMBER(I340),"Loss",IF(ISNUMBER(H340),"Draw",IF(AND(ISNUMBER(F340),ISNUMBER(E340),E340&gt;0,F340&gt;E340),"Profit",IF(AND(ISNUMBER(F340),ISNUMBER(E340),E340&gt;0,F340=E340),"Draw",IF(AND(ISNUMBER(F340),ISNUMBER(E340),E340&gt;0,F340=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A340="","",IF(AND(ISNUMBER(E340),E340=0,OR(ISNUMBER(SEARCH("Free",D340&amp;"")),AND(ISNUMBER(F340),F340=0))),"Subscription",IF(ISNUMBER(G340),"Profit",IF(ISNUMBER(I340),"Disqualified",IF(ISNUMBER(H340),"Draw",IF(AND(ISNUMBER(F340),ISNUMBER(E340),E340&gt;0,F340&gt;E340),"Profit",IF(AND(ISNUMBER(F340),ISNUMBER(E340),E340&gt;0,F340=E340),"Draw",IF(AND(ISNUMBER(F340),ISNUMBER(E340),E340&gt;0,F340=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L340" s="50"/>
       <x:c r="M340" s="58"/>
@@ -13975,7 +13988,7 @@
         <x:f>IF(A341="","",IF(K341="Subscription","",IF(E341=0,"",IF(ISNUMBER(G341),G341/E341,IF(ISNUMBER(I341),-ABS(I341)/E341,IF(ISNUMBER(H341),0,IF(AND(ISNUMBER(F341),ISNUMBER(E341),E341&gt;0,F341&gt;E341),(F341-E341)/E341,IF(AND(ISNUMBER(F341),ISNUMBER(E341),E341&gt;0,F341=E341),0,IF(AND(ISNUMBER(F341),ISNUMBER(E341),E341&gt;0,F341=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K341" s="50" t="str">
-        <x:f>IF(A341="","",IF(AND(ISNUMBER(E341),E341=0,OR(ISNUMBER(SEARCH("Free",D341&amp;"")),AND(ISNUMBER(F341),F341=0))),"Subscription",IF(ISNUMBER(G341),"Profit",IF(ISNUMBER(I341),"Loss",IF(ISNUMBER(H341),"Draw",IF(AND(ISNUMBER(F341),ISNUMBER(E341),E341&gt;0,F341&gt;E341),"Profit",IF(AND(ISNUMBER(F341),ISNUMBER(E341),E341&gt;0,F341=E341),"Draw",IF(AND(ISNUMBER(F341),ISNUMBER(E341),E341&gt;0,F341=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A341="","",IF(AND(ISNUMBER(E341),E341=0,OR(ISNUMBER(SEARCH("Free",D341&amp;"")),AND(ISNUMBER(F341),F341=0))),"Subscription",IF(ISNUMBER(G341),"Profit",IF(ISNUMBER(I341),"Disqualified",IF(ISNUMBER(H341),"Draw",IF(AND(ISNUMBER(F341),ISNUMBER(E341),E341&gt;0,F341&gt;E341),"Profit",IF(AND(ISNUMBER(F341),ISNUMBER(E341),E341&gt;0,F341=E341),"Draw",IF(AND(ISNUMBER(F341),ISNUMBER(E341),E341&gt;0,F341=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L341" s="50"/>
       <x:c r="M341" s="58"/>
@@ -14012,7 +14025,7 @@
         <x:f>IF(A342="","",IF(K342="Subscription","",IF(E342=0,"",IF(ISNUMBER(G342),G342/E342,IF(ISNUMBER(I342),-ABS(I342)/E342,IF(ISNUMBER(H342),0,IF(AND(ISNUMBER(F342),ISNUMBER(E342),E342&gt;0,F342&gt;E342),(F342-E342)/E342,IF(AND(ISNUMBER(F342),ISNUMBER(E342),E342&gt;0,F342=E342),0,IF(AND(ISNUMBER(F342),ISNUMBER(E342),E342&gt;0,F342=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K342" s="50" t="str">
-        <x:f>IF(A342="","",IF(AND(ISNUMBER(E342),E342=0,OR(ISNUMBER(SEARCH("Free",D342&amp;"")),AND(ISNUMBER(F342),F342=0))),"Subscription",IF(ISNUMBER(G342),"Profit",IF(ISNUMBER(I342),"Loss",IF(ISNUMBER(H342),"Draw",IF(AND(ISNUMBER(F342),ISNUMBER(E342),E342&gt;0,F342&gt;E342),"Profit",IF(AND(ISNUMBER(F342),ISNUMBER(E342),E342&gt;0,F342=E342),"Draw",IF(AND(ISNUMBER(F342),ISNUMBER(E342),E342&gt;0,F342=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A342="","",IF(AND(ISNUMBER(E342),E342=0,OR(ISNUMBER(SEARCH("Free",D342&amp;"")),AND(ISNUMBER(F342),F342=0))),"Subscription",IF(ISNUMBER(G342),"Profit",IF(ISNUMBER(I342),"Disqualified",IF(ISNUMBER(H342),"Draw",IF(AND(ISNUMBER(F342),ISNUMBER(E342),E342&gt;0,F342&gt;E342),"Profit",IF(AND(ISNUMBER(F342),ISNUMBER(E342),E342&gt;0,F342=E342),"Draw",IF(AND(ISNUMBER(F342),ISNUMBER(E342),E342&gt;0,F342=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L342" s="50"/>
       <x:c r="M342" s="58"/>
@@ -14049,7 +14062,7 @@
         <x:f>IF(A343="","",IF(K343="Subscription","",IF(E343=0,"",IF(ISNUMBER(G343),G343/E343,IF(ISNUMBER(I343),-ABS(I343)/E343,IF(ISNUMBER(H343),0,IF(AND(ISNUMBER(F343),ISNUMBER(E343),E343&gt;0,F343&gt;E343),(F343-E343)/E343,IF(AND(ISNUMBER(F343),ISNUMBER(E343),E343&gt;0,F343=E343),0,IF(AND(ISNUMBER(F343),ISNUMBER(E343),E343&gt;0,F343=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K343" s="50" t="str">
-        <x:f>IF(A343="","",IF(AND(ISNUMBER(E343),E343=0,OR(ISNUMBER(SEARCH("Free",D343&amp;"")),AND(ISNUMBER(F343),F343=0))),"Subscription",IF(ISNUMBER(G343),"Profit",IF(ISNUMBER(I343),"Loss",IF(ISNUMBER(H343),"Draw",IF(AND(ISNUMBER(F343),ISNUMBER(E343),E343&gt;0,F343&gt;E343),"Profit",IF(AND(ISNUMBER(F343),ISNUMBER(E343),E343&gt;0,F343=E343),"Draw",IF(AND(ISNUMBER(F343),ISNUMBER(E343),E343&gt;0,F343=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A343="","",IF(AND(ISNUMBER(E343),E343=0,OR(ISNUMBER(SEARCH("Free",D343&amp;"")),AND(ISNUMBER(F343),F343=0))),"Subscription",IF(ISNUMBER(G343),"Profit",IF(ISNUMBER(I343),"Disqualified",IF(ISNUMBER(H343),"Draw",IF(AND(ISNUMBER(F343),ISNUMBER(E343),E343&gt;0,F343&gt;E343),"Profit",IF(AND(ISNUMBER(F343),ISNUMBER(E343),E343&gt;0,F343=E343),"Draw",IF(AND(ISNUMBER(F343),ISNUMBER(E343),E343&gt;0,F343=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L343" s="50"/>
       <x:c r="M343" s="58"/>
@@ -14086,7 +14099,7 @@
         <x:f>IF(A344="","",IF(K344="Subscription","",IF(E344=0,"",IF(ISNUMBER(G344),G344/E344,IF(ISNUMBER(I344),-ABS(I344)/E344,IF(ISNUMBER(H344),0,IF(AND(ISNUMBER(F344),ISNUMBER(E344),E344&gt;0,F344&gt;E344),(F344-E344)/E344,IF(AND(ISNUMBER(F344),ISNUMBER(E344),E344&gt;0,F344=E344),0,IF(AND(ISNUMBER(F344),ISNUMBER(E344),E344&gt;0,F344=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K344" s="50" t="str">
-        <x:f>IF(A344="","",IF(AND(ISNUMBER(E344),E344=0,OR(ISNUMBER(SEARCH("Free",D344&amp;"")),AND(ISNUMBER(F344),F344=0))),"Subscription",IF(ISNUMBER(G344),"Profit",IF(ISNUMBER(I344),"Loss",IF(ISNUMBER(H344),"Draw",IF(AND(ISNUMBER(F344),ISNUMBER(E344),E344&gt;0,F344&gt;E344),"Profit",IF(AND(ISNUMBER(F344),ISNUMBER(E344),E344&gt;0,F344=E344),"Draw",IF(AND(ISNUMBER(F344),ISNUMBER(E344),E344&gt;0,F344=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A344="","",IF(AND(ISNUMBER(E344),E344=0,OR(ISNUMBER(SEARCH("Free",D344&amp;"")),AND(ISNUMBER(F344),F344=0))),"Subscription",IF(ISNUMBER(G344),"Profit",IF(ISNUMBER(I344),"Disqualified",IF(ISNUMBER(H344),"Draw",IF(AND(ISNUMBER(F344),ISNUMBER(E344),E344&gt;0,F344&gt;E344),"Profit",IF(AND(ISNUMBER(F344),ISNUMBER(E344),E344&gt;0,F344=E344),"Draw",IF(AND(ISNUMBER(F344),ISNUMBER(E344),E344&gt;0,F344=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L344" s="50"/>
       <x:c r="M344" s="58"/>
@@ -14123,7 +14136,7 @@
         <x:f>IF(A345="","",IF(K345="Subscription","",IF(E345=0,"",IF(ISNUMBER(G345),G345/E345,IF(ISNUMBER(I345),-ABS(I345)/E345,IF(ISNUMBER(H345),0,IF(AND(ISNUMBER(F345),ISNUMBER(E345),E345&gt;0,F345&gt;E345),(F345-E345)/E345,IF(AND(ISNUMBER(F345),ISNUMBER(E345),E345&gt;0,F345=E345),0,IF(AND(ISNUMBER(F345),ISNUMBER(E345),E345&gt;0,F345=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K345" s="50" t="str">
-        <x:f>IF(A345="","",IF(AND(ISNUMBER(E345),E345=0,OR(ISNUMBER(SEARCH("Free",D345&amp;"")),AND(ISNUMBER(F345),F345=0))),"Subscription",IF(ISNUMBER(G345),"Profit",IF(ISNUMBER(I345),"Loss",IF(ISNUMBER(H345),"Draw",IF(AND(ISNUMBER(F345),ISNUMBER(E345),E345&gt;0,F345&gt;E345),"Profit",IF(AND(ISNUMBER(F345),ISNUMBER(E345),E345&gt;0,F345=E345),"Draw",IF(AND(ISNUMBER(F345),ISNUMBER(E345),E345&gt;0,F345=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A345="","",IF(AND(ISNUMBER(E345),E345=0,OR(ISNUMBER(SEARCH("Free",D345&amp;"")),AND(ISNUMBER(F345),F345=0))),"Subscription",IF(ISNUMBER(G345),"Profit",IF(ISNUMBER(I345),"Disqualified",IF(ISNUMBER(H345),"Draw",IF(AND(ISNUMBER(F345),ISNUMBER(E345),E345&gt;0,F345&gt;E345),"Profit",IF(AND(ISNUMBER(F345),ISNUMBER(E345),E345&gt;0,F345=E345),"Draw",IF(AND(ISNUMBER(F345),ISNUMBER(E345),E345&gt;0,F345=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L345" s="50"/>
       <x:c r="M345" s="58"/>
@@ -14160,7 +14173,7 @@
         <x:f>IF(A346="","",IF(K346="Subscription","",IF(E346=0,"",IF(ISNUMBER(G346),G346/E346,IF(ISNUMBER(I346),-ABS(I346)/E346,IF(ISNUMBER(H346),0,IF(AND(ISNUMBER(F346),ISNUMBER(E346),E346&gt;0,F346&gt;E346),(F346-E346)/E346,IF(AND(ISNUMBER(F346),ISNUMBER(E346),E346&gt;0,F346=E346),0,IF(AND(ISNUMBER(F346),ISNUMBER(E346),E346&gt;0,F346=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K346" s="50" t="str">
-        <x:f>IF(A346="","",IF(AND(ISNUMBER(E346),E346=0,OR(ISNUMBER(SEARCH("Free",D346&amp;"")),AND(ISNUMBER(F346),F346=0))),"Subscription",IF(ISNUMBER(G346),"Profit",IF(ISNUMBER(I346),"Loss",IF(ISNUMBER(H346),"Draw",IF(AND(ISNUMBER(F346),ISNUMBER(E346),E346&gt;0,F346&gt;E346),"Profit",IF(AND(ISNUMBER(F346),ISNUMBER(E346),E346&gt;0,F346=E346),"Draw",IF(AND(ISNUMBER(F346),ISNUMBER(E346),E346&gt;0,F346=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A346="","",IF(AND(ISNUMBER(E346),E346=0,OR(ISNUMBER(SEARCH("Free",D346&amp;"")),AND(ISNUMBER(F346),F346=0))),"Subscription",IF(ISNUMBER(G346),"Profit",IF(ISNUMBER(I346),"Disqualified",IF(ISNUMBER(H346),"Draw",IF(AND(ISNUMBER(F346),ISNUMBER(E346),E346&gt;0,F346&gt;E346),"Profit",IF(AND(ISNUMBER(F346),ISNUMBER(E346),E346&gt;0,F346=E346),"Draw",IF(AND(ISNUMBER(F346),ISNUMBER(E346),E346&gt;0,F346=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L346" s="50"/>
       <x:c r="M346" s="58"/>
@@ -14197,7 +14210,7 @@
         <x:f>IF(A347="","",IF(K347="Subscription","",IF(E347=0,"",IF(ISNUMBER(G347),G347/E347,IF(ISNUMBER(I347),-ABS(I347)/E347,IF(ISNUMBER(H347),0,IF(AND(ISNUMBER(F347),ISNUMBER(E347),E347&gt;0,F347&gt;E347),(F347-E347)/E347,IF(AND(ISNUMBER(F347),ISNUMBER(E347),E347&gt;0,F347=E347),0,IF(AND(ISNUMBER(F347),ISNUMBER(E347),E347&gt;0,F347=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K347" s="50" t="str">
-        <x:f>IF(A347="","",IF(AND(ISNUMBER(E347),E347=0,OR(ISNUMBER(SEARCH("Free",D347&amp;"")),AND(ISNUMBER(F347),F347=0))),"Subscription",IF(ISNUMBER(G347),"Profit",IF(ISNUMBER(I347),"Loss",IF(ISNUMBER(H347),"Draw",IF(AND(ISNUMBER(F347),ISNUMBER(E347),E347&gt;0,F347&gt;E347),"Profit",IF(AND(ISNUMBER(F347),ISNUMBER(E347),E347&gt;0,F347=E347),"Draw",IF(AND(ISNUMBER(F347),ISNUMBER(E347),E347&gt;0,F347=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A347="","",IF(AND(ISNUMBER(E347),E347=0,OR(ISNUMBER(SEARCH("Free",D347&amp;"")),AND(ISNUMBER(F347),F347=0))),"Subscription",IF(ISNUMBER(G347),"Profit",IF(ISNUMBER(I347),"Disqualified",IF(ISNUMBER(H347),"Draw",IF(AND(ISNUMBER(F347),ISNUMBER(E347),E347&gt;0,F347&gt;E347),"Profit",IF(AND(ISNUMBER(F347),ISNUMBER(E347),E347&gt;0,F347=E347),"Draw",IF(AND(ISNUMBER(F347),ISNUMBER(E347),E347&gt;0,F347=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L347" s="50"/>
       <x:c r="M347" s="58"/>
@@ -14234,7 +14247,7 @@
         <x:f>IF(A348="","",IF(K348="Subscription","",IF(E348=0,"",IF(ISNUMBER(G348),G348/E348,IF(ISNUMBER(I348),-ABS(I348)/E348,IF(ISNUMBER(H348),0,IF(AND(ISNUMBER(F348),ISNUMBER(E348),E348&gt;0,F348&gt;E348),(F348-E348)/E348,IF(AND(ISNUMBER(F348),ISNUMBER(E348),E348&gt;0,F348=E348),0,IF(AND(ISNUMBER(F348),ISNUMBER(E348),E348&gt;0,F348=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K348" s="50" t="str">
-        <x:f>IF(A348="","",IF(AND(ISNUMBER(E348),E348=0,OR(ISNUMBER(SEARCH("Free",D348&amp;"")),AND(ISNUMBER(F348),F348=0))),"Subscription",IF(ISNUMBER(G348),"Profit",IF(ISNUMBER(I348),"Loss",IF(ISNUMBER(H348),"Draw",IF(AND(ISNUMBER(F348),ISNUMBER(E348),E348&gt;0,F348&gt;E348),"Profit",IF(AND(ISNUMBER(F348),ISNUMBER(E348),E348&gt;0,F348=E348),"Draw",IF(AND(ISNUMBER(F348),ISNUMBER(E348),E348&gt;0,F348=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A348="","",IF(AND(ISNUMBER(E348),E348=0,OR(ISNUMBER(SEARCH("Free",D348&amp;"")),AND(ISNUMBER(F348),F348=0))),"Subscription",IF(ISNUMBER(G348),"Profit",IF(ISNUMBER(I348),"Disqualified",IF(ISNUMBER(H348),"Draw",IF(AND(ISNUMBER(F348),ISNUMBER(E348),E348&gt;0,F348&gt;E348),"Profit",IF(AND(ISNUMBER(F348),ISNUMBER(E348),E348&gt;0,F348=E348),"Draw",IF(AND(ISNUMBER(F348),ISNUMBER(E348),E348&gt;0,F348=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L348" s="50"/>
       <x:c r="M348" s="58"/>
@@ -14271,7 +14284,7 @@
         <x:f>IF(A349="","",IF(K349="Subscription","",IF(E349=0,"",IF(ISNUMBER(G349),G349/E349,IF(ISNUMBER(I349),-ABS(I349)/E349,IF(ISNUMBER(H349),0,IF(AND(ISNUMBER(F349),ISNUMBER(E349),E349&gt;0,F349&gt;E349),(F349-E349)/E349,IF(AND(ISNUMBER(F349),ISNUMBER(E349),E349&gt;0,F349=E349),0,IF(AND(ISNUMBER(F349),ISNUMBER(E349),E349&gt;0,F349=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K349" s="50" t="str">
-        <x:f>IF(A349="","",IF(AND(ISNUMBER(E349),E349=0,OR(ISNUMBER(SEARCH("Free",D349&amp;"")),AND(ISNUMBER(F349),F349=0))),"Subscription",IF(ISNUMBER(G349),"Profit",IF(ISNUMBER(I349),"Loss",IF(ISNUMBER(H349),"Draw",IF(AND(ISNUMBER(F349),ISNUMBER(E349),E349&gt;0,F349&gt;E349),"Profit",IF(AND(ISNUMBER(F349),ISNUMBER(E349),E349&gt;0,F349=E349),"Draw",IF(AND(ISNUMBER(F349),ISNUMBER(E349),E349&gt;0,F349=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A349="","",IF(AND(ISNUMBER(E349),E349=0,OR(ISNUMBER(SEARCH("Free",D349&amp;"")),AND(ISNUMBER(F349),F349=0))),"Subscription",IF(ISNUMBER(G349),"Profit",IF(ISNUMBER(I349),"Disqualified",IF(ISNUMBER(H349),"Draw",IF(AND(ISNUMBER(F349),ISNUMBER(E349),E349&gt;0,F349&gt;E349),"Profit",IF(AND(ISNUMBER(F349),ISNUMBER(E349),E349&gt;0,F349=E349),"Draw",IF(AND(ISNUMBER(F349),ISNUMBER(E349),E349&gt;0,F349=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L349" s="50"/>
       <x:c r="M349" s="58"/>
@@ -14308,7 +14321,7 @@
         <x:f>IF(A350="","",IF(K350="Subscription","",IF(E350=0,"",IF(ISNUMBER(G350),G350/E350,IF(ISNUMBER(I350),-ABS(I350)/E350,IF(ISNUMBER(H350),0,IF(AND(ISNUMBER(F350),ISNUMBER(E350),E350&gt;0,F350&gt;E350),(F350-E350)/E350,IF(AND(ISNUMBER(F350),ISNUMBER(E350),E350&gt;0,F350=E350),0,IF(AND(ISNUMBER(F350),ISNUMBER(E350),E350&gt;0,F350=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K350" s="50" t="str">
-        <x:f>IF(A350="","",IF(AND(ISNUMBER(E350),E350=0,OR(ISNUMBER(SEARCH("Free",D350&amp;"")),AND(ISNUMBER(F350),F350=0))),"Subscription",IF(ISNUMBER(G350),"Profit",IF(ISNUMBER(I350),"Loss",IF(ISNUMBER(H350),"Draw",IF(AND(ISNUMBER(F350),ISNUMBER(E350),E350&gt;0,F350&gt;E350),"Profit",IF(AND(ISNUMBER(F350),ISNUMBER(E350),E350&gt;0,F350=E350),"Draw",IF(AND(ISNUMBER(F350),ISNUMBER(E350),E350&gt;0,F350=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A350="","",IF(AND(ISNUMBER(E350),E350=0,OR(ISNUMBER(SEARCH("Free",D350&amp;"")),AND(ISNUMBER(F350),F350=0))),"Subscription",IF(ISNUMBER(G350),"Profit",IF(ISNUMBER(I350),"Disqualified",IF(ISNUMBER(H350),"Draw",IF(AND(ISNUMBER(F350),ISNUMBER(E350),E350&gt;0,F350&gt;E350),"Profit",IF(AND(ISNUMBER(F350),ISNUMBER(E350),E350&gt;0,F350=E350),"Draw",IF(AND(ISNUMBER(F350),ISNUMBER(E350),E350&gt;0,F350=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L350" s="50"/>
       <x:c r="M350" s="58"/>
@@ -14345,7 +14358,7 @@
         <x:f>IF(A351="","",IF(K351="Subscription","",IF(E351=0,"",IF(ISNUMBER(G351),G351/E351,IF(ISNUMBER(I351),-ABS(I351)/E351,IF(ISNUMBER(H351),0,IF(AND(ISNUMBER(F351),ISNUMBER(E351),E351&gt;0,F351&gt;E351),(F351-E351)/E351,IF(AND(ISNUMBER(F351),ISNUMBER(E351),E351&gt;0,F351=E351),0,IF(AND(ISNUMBER(F351),ISNUMBER(E351),E351&gt;0,F351=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K351" s="50" t="str">
-        <x:f>IF(A351="","",IF(AND(ISNUMBER(E351),E351=0,OR(ISNUMBER(SEARCH("Free",D351&amp;"")),AND(ISNUMBER(F351),F351=0))),"Subscription",IF(ISNUMBER(G351),"Profit",IF(ISNUMBER(I351),"Loss",IF(ISNUMBER(H351),"Draw",IF(AND(ISNUMBER(F351),ISNUMBER(E351),E351&gt;0,F351&gt;E351),"Profit",IF(AND(ISNUMBER(F351),ISNUMBER(E351),E351&gt;0,F351=E351),"Draw",IF(AND(ISNUMBER(F351),ISNUMBER(E351),E351&gt;0,F351=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A351="","",IF(AND(ISNUMBER(E351),E351=0,OR(ISNUMBER(SEARCH("Free",D351&amp;"")),AND(ISNUMBER(F351),F351=0))),"Subscription",IF(ISNUMBER(G351),"Profit",IF(ISNUMBER(I351),"Disqualified",IF(ISNUMBER(H351),"Draw",IF(AND(ISNUMBER(F351),ISNUMBER(E351),E351&gt;0,F351&gt;E351),"Profit",IF(AND(ISNUMBER(F351),ISNUMBER(E351),E351&gt;0,F351=E351),"Draw",IF(AND(ISNUMBER(F351),ISNUMBER(E351),E351&gt;0,F351=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L351" s="50"/>
       <x:c r="M351" s="58"/>
@@ -14382,7 +14395,7 @@
         <x:f>IF(A352="","",IF(K352="Subscription","",IF(E352=0,"",IF(ISNUMBER(G352),G352/E352,IF(ISNUMBER(I352),-ABS(I352)/E352,IF(ISNUMBER(H352),0,IF(AND(ISNUMBER(F352),ISNUMBER(E352),E352&gt;0,F352&gt;E352),(F352-E352)/E352,IF(AND(ISNUMBER(F352),ISNUMBER(E352),E352&gt;0,F352=E352),0,IF(AND(ISNUMBER(F352),ISNUMBER(E352),E352&gt;0,F352=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K352" s="50" t="str">
-        <x:f>IF(A352="","",IF(AND(ISNUMBER(E352),E352=0,OR(ISNUMBER(SEARCH("Free",D352&amp;"")),AND(ISNUMBER(F352),F352=0))),"Subscription",IF(ISNUMBER(G352),"Profit",IF(ISNUMBER(I352),"Loss",IF(ISNUMBER(H352),"Draw",IF(AND(ISNUMBER(F352),ISNUMBER(E352),E352&gt;0,F352&gt;E352),"Profit",IF(AND(ISNUMBER(F352),ISNUMBER(E352),E352&gt;0,F352=E352),"Draw",IF(AND(ISNUMBER(F352),ISNUMBER(E352),E352&gt;0,F352=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A352="","",IF(AND(ISNUMBER(E352),E352=0,OR(ISNUMBER(SEARCH("Free",D352&amp;"")),AND(ISNUMBER(F352),F352=0))),"Subscription",IF(ISNUMBER(G352),"Profit",IF(ISNUMBER(I352),"Disqualified",IF(ISNUMBER(H352),"Draw",IF(AND(ISNUMBER(F352),ISNUMBER(E352),E352&gt;0,F352&gt;E352),"Profit",IF(AND(ISNUMBER(F352),ISNUMBER(E352),E352&gt;0,F352=E352),"Draw",IF(AND(ISNUMBER(F352),ISNUMBER(E352),E352&gt;0,F352=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L352" s="50"/>
       <x:c r="M352" s="58"/>
@@ -14419,7 +14432,7 @@
         <x:f>IF(A353="","",IF(K353="Subscription","",IF(E353=0,"",IF(ISNUMBER(G353),G353/E353,IF(ISNUMBER(I353),-ABS(I353)/E353,IF(ISNUMBER(H353),0,IF(AND(ISNUMBER(F353),ISNUMBER(E353),E353&gt;0,F353&gt;E353),(F353-E353)/E353,IF(AND(ISNUMBER(F353),ISNUMBER(E353),E353&gt;0,F353=E353),0,IF(AND(ISNUMBER(F353),ISNUMBER(E353),E353&gt;0,F353=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K353" s="50" t="str">
-        <x:f>IF(A353="","",IF(AND(ISNUMBER(E353),E353=0,OR(ISNUMBER(SEARCH("Free",D353&amp;"")),AND(ISNUMBER(F353),F353=0))),"Subscription",IF(ISNUMBER(G353),"Profit",IF(ISNUMBER(I353),"Loss",IF(ISNUMBER(H353),"Draw",IF(AND(ISNUMBER(F353),ISNUMBER(E353),E353&gt;0,F353&gt;E353),"Profit",IF(AND(ISNUMBER(F353),ISNUMBER(E353),E353&gt;0,F353=E353),"Draw",IF(AND(ISNUMBER(F353),ISNUMBER(E353),E353&gt;0,F353=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A353="","",IF(AND(ISNUMBER(E353),E353=0,OR(ISNUMBER(SEARCH("Free",D353&amp;"")),AND(ISNUMBER(F353),F353=0))),"Subscription",IF(ISNUMBER(G353),"Profit",IF(ISNUMBER(I353),"Disqualified",IF(ISNUMBER(H353),"Draw",IF(AND(ISNUMBER(F353),ISNUMBER(E353),E353&gt;0,F353&gt;E353),"Profit",IF(AND(ISNUMBER(F353),ISNUMBER(E353),E353&gt;0,F353=E353),"Draw",IF(AND(ISNUMBER(F353),ISNUMBER(E353),E353&gt;0,F353=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L353" s="50"/>
       <x:c r="M353" s="58"/>
@@ -14456,7 +14469,7 @@
         <x:f>IF(A354="","",IF(K354="Subscription","",IF(E354=0,"",IF(ISNUMBER(G354),G354/E354,IF(ISNUMBER(I354),-ABS(I354)/E354,IF(ISNUMBER(H354),0,IF(AND(ISNUMBER(F354),ISNUMBER(E354),E354&gt;0,F354&gt;E354),(F354-E354)/E354,IF(AND(ISNUMBER(F354),ISNUMBER(E354),E354&gt;0,F354=E354),0,IF(AND(ISNUMBER(F354),ISNUMBER(E354),E354&gt;0,F354=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K354" s="50" t="str">
-        <x:f>IF(A354="","",IF(AND(ISNUMBER(E354),E354=0,OR(ISNUMBER(SEARCH("Free",D354&amp;"")),AND(ISNUMBER(F354),F354=0))),"Subscription",IF(ISNUMBER(G354),"Profit",IF(ISNUMBER(I354),"Loss",IF(ISNUMBER(H354),"Draw",IF(AND(ISNUMBER(F354),ISNUMBER(E354),E354&gt;0,F354&gt;E354),"Profit",IF(AND(ISNUMBER(F354),ISNUMBER(E354),E354&gt;0,F354=E354),"Draw",IF(AND(ISNUMBER(F354),ISNUMBER(E354),E354&gt;0,F354=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A354="","",IF(AND(ISNUMBER(E354),E354=0,OR(ISNUMBER(SEARCH("Free",D354&amp;"")),AND(ISNUMBER(F354),F354=0))),"Subscription",IF(ISNUMBER(G354),"Profit",IF(ISNUMBER(I354),"Disqualified",IF(ISNUMBER(H354),"Draw",IF(AND(ISNUMBER(F354),ISNUMBER(E354),E354&gt;0,F354&gt;E354),"Profit",IF(AND(ISNUMBER(F354),ISNUMBER(E354),E354&gt;0,F354=E354),"Draw",IF(AND(ISNUMBER(F354),ISNUMBER(E354),E354&gt;0,F354=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L354" s="50"/>
       <x:c r="M354" s="58"/>
@@ -14493,7 +14506,7 @@
         <x:f>IF(A355="","",IF(K355="Subscription","",IF(E355=0,"",IF(ISNUMBER(G355),G355/E355,IF(ISNUMBER(I355),-ABS(I355)/E355,IF(ISNUMBER(H355),0,IF(AND(ISNUMBER(F355),ISNUMBER(E355),E355&gt;0,F355&gt;E355),(F355-E355)/E355,IF(AND(ISNUMBER(F355),ISNUMBER(E355),E355&gt;0,F355=E355),0,IF(AND(ISNUMBER(F355),ISNUMBER(E355),E355&gt;0,F355=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K355" s="50" t="str">
-        <x:f>IF(A355="","",IF(AND(ISNUMBER(E355),E355=0,OR(ISNUMBER(SEARCH("Free",D355&amp;"")),AND(ISNUMBER(F355),F355=0))),"Subscription",IF(ISNUMBER(G355),"Profit",IF(ISNUMBER(I355),"Loss",IF(ISNUMBER(H355),"Draw",IF(AND(ISNUMBER(F355),ISNUMBER(E355),E355&gt;0,F355&gt;E355),"Profit",IF(AND(ISNUMBER(F355),ISNUMBER(E355),E355&gt;0,F355=E355),"Draw",IF(AND(ISNUMBER(F355),ISNUMBER(E355),E355&gt;0,F355=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A355="","",IF(AND(ISNUMBER(E355),E355=0,OR(ISNUMBER(SEARCH("Free",D355&amp;"")),AND(ISNUMBER(F355),F355=0))),"Subscription",IF(ISNUMBER(G355),"Profit",IF(ISNUMBER(I355),"Disqualified",IF(ISNUMBER(H355),"Draw",IF(AND(ISNUMBER(F355),ISNUMBER(E355),E355&gt;0,F355&gt;E355),"Profit",IF(AND(ISNUMBER(F355),ISNUMBER(E355),E355&gt;0,F355=E355),"Draw",IF(AND(ISNUMBER(F355),ISNUMBER(E355),E355&gt;0,F355=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L355" s="50"/>
       <x:c r="M355" s="58"/>
@@ -14530,7 +14543,7 @@
         <x:f>IF(A356="","",IF(K356="Subscription","",IF(E356=0,"",IF(ISNUMBER(G356),G356/E356,IF(ISNUMBER(I356),-ABS(I356)/E356,IF(ISNUMBER(H356),0,IF(AND(ISNUMBER(F356),ISNUMBER(E356),E356&gt;0,F356&gt;E356),(F356-E356)/E356,IF(AND(ISNUMBER(F356),ISNUMBER(E356),E356&gt;0,F356=E356),0,IF(AND(ISNUMBER(F356),ISNUMBER(E356),E356&gt;0,F356=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K356" s="50" t="str">
-        <x:f>IF(A356="","",IF(AND(ISNUMBER(E356),E356=0,OR(ISNUMBER(SEARCH("Free",D356&amp;"")),AND(ISNUMBER(F356),F356=0))),"Subscription",IF(ISNUMBER(G356),"Profit",IF(ISNUMBER(I356),"Loss",IF(ISNUMBER(H356),"Draw",IF(AND(ISNUMBER(F356),ISNUMBER(E356),E356&gt;0,F356&gt;E356),"Profit",IF(AND(ISNUMBER(F356),ISNUMBER(E356),E356&gt;0,F356=E356),"Draw",IF(AND(ISNUMBER(F356),ISNUMBER(E356),E356&gt;0,F356=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A356="","",IF(AND(ISNUMBER(E356),E356=0,OR(ISNUMBER(SEARCH("Free",D356&amp;"")),AND(ISNUMBER(F356),F356=0))),"Subscription",IF(ISNUMBER(G356),"Profit",IF(ISNUMBER(I356),"Disqualified",IF(ISNUMBER(H356),"Draw",IF(AND(ISNUMBER(F356),ISNUMBER(E356),E356&gt;0,F356&gt;E356),"Profit",IF(AND(ISNUMBER(F356),ISNUMBER(E356),E356&gt;0,F356=E356),"Draw",IF(AND(ISNUMBER(F356),ISNUMBER(E356),E356&gt;0,F356=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L356" s="50"/>
       <x:c r="M356" s="58"/>
@@ -14567,7 +14580,7 @@
         <x:f>IF(A357="","",IF(K357="Subscription","",IF(E357=0,"",IF(ISNUMBER(G357),G357/E357,IF(ISNUMBER(I357),-ABS(I357)/E357,IF(ISNUMBER(H357),0,IF(AND(ISNUMBER(F357),ISNUMBER(E357),E357&gt;0,F357&gt;E357),(F357-E357)/E357,IF(AND(ISNUMBER(F357),ISNUMBER(E357),E357&gt;0,F357=E357),0,IF(AND(ISNUMBER(F357),ISNUMBER(E357),E357&gt;0,F357=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K357" s="50" t="str">
-        <x:f>IF(A357="","",IF(AND(ISNUMBER(E357),E357=0,OR(ISNUMBER(SEARCH("Free",D357&amp;"")),AND(ISNUMBER(F357),F357=0))),"Subscription",IF(ISNUMBER(G357),"Profit",IF(ISNUMBER(I357),"Loss",IF(ISNUMBER(H357),"Draw",IF(AND(ISNUMBER(F357),ISNUMBER(E357),E357&gt;0,F357&gt;E357),"Profit",IF(AND(ISNUMBER(F357),ISNUMBER(E357),E357&gt;0,F357=E357),"Draw",IF(AND(ISNUMBER(F357),ISNUMBER(E357),E357&gt;0,F357=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A357="","",IF(AND(ISNUMBER(E357),E357=0,OR(ISNUMBER(SEARCH("Free",D357&amp;"")),AND(ISNUMBER(F357),F357=0))),"Subscription",IF(ISNUMBER(G357),"Profit",IF(ISNUMBER(I357),"Disqualified",IF(ISNUMBER(H357),"Draw",IF(AND(ISNUMBER(F357),ISNUMBER(E357),E357&gt;0,F357&gt;E357),"Profit",IF(AND(ISNUMBER(F357),ISNUMBER(E357),E357&gt;0,F357=E357),"Draw",IF(AND(ISNUMBER(F357),ISNUMBER(E357),E357&gt;0,F357=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L357" s="50"/>
       <x:c r="M357" s="58"/>
@@ -14604,7 +14617,7 @@
         <x:f>IF(A358="","",IF(K358="Subscription","",IF(E358=0,"",IF(ISNUMBER(G358),G358/E358,IF(ISNUMBER(I358),-ABS(I358)/E358,IF(ISNUMBER(H358),0,IF(AND(ISNUMBER(F358),ISNUMBER(E358),E358&gt;0,F358&gt;E358),(F358-E358)/E358,IF(AND(ISNUMBER(F358),ISNUMBER(E358),E358&gt;0,F358=E358),0,IF(AND(ISNUMBER(F358),ISNUMBER(E358),E358&gt;0,F358=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K358" s="50" t="str">
-        <x:f>IF(A358="","",IF(AND(ISNUMBER(E358),E358=0,OR(ISNUMBER(SEARCH("Free",D358&amp;"")),AND(ISNUMBER(F358),F358=0))),"Subscription",IF(ISNUMBER(G358),"Profit",IF(ISNUMBER(I358),"Loss",IF(ISNUMBER(H358),"Draw",IF(AND(ISNUMBER(F358),ISNUMBER(E358),E358&gt;0,F358&gt;E358),"Profit",IF(AND(ISNUMBER(F358),ISNUMBER(E358),E358&gt;0,F358=E358),"Draw",IF(AND(ISNUMBER(F358),ISNUMBER(E358),E358&gt;0,F358=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A358="","",IF(AND(ISNUMBER(E358),E358=0,OR(ISNUMBER(SEARCH("Free",D358&amp;"")),AND(ISNUMBER(F358),F358=0))),"Subscription",IF(ISNUMBER(G358),"Profit",IF(ISNUMBER(I358),"Disqualified",IF(ISNUMBER(H358),"Draw",IF(AND(ISNUMBER(F358),ISNUMBER(E358),E358&gt;0,F358&gt;E358),"Profit",IF(AND(ISNUMBER(F358),ISNUMBER(E358),E358&gt;0,F358=E358),"Draw",IF(AND(ISNUMBER(F358),ISNUMBER(E358),E358&gt;0,F358=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L358" s="50"/>
       <x:c r="M358" s="58"/>
@@ -14641,7 +14654,7 @@
         <x:f>IF(A359="","",IF(K359="Subscription","",IF(E359=0,"",IF(ISNUMBER(G359),G359/E359,IF(ISNUMBER(I359),-ABS(I359)/E359,IF(ISNUMBER(H359),0,IF(AND(ISNUMBER(F359),ISNUMBER(E359),E359&gt;0,F359&gt;E359),(F359-E359)/E359,IF(AND(ISNUMBER(F359),ISNUMBER(E359),E359&gt;0,F359=E359),0,IF(AND(ISNUMBER(F359),ISNUMBER(E359),E359&gt;0,F359=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K359" s="50" t="str">
-        <x:f>IF(A359="","",IF(AND(ISNUMBER(E359),E359=0,OR(ISNUMBER(SEARCH("Free",D359&amp;"")),AND(ISNUMBER(F359),F359=0))),"Subscription",IF(ISNUMBER(G359),"Profit",IF(ISNUMBER(I359),"Loss",IF(ISNUMBER(H359),"Draw",IF(AND(ISNUMBER(F359),ISNUMBER(E359),E359&gt;0,F359&gt;E359),"Profit",IF(AND(ISNUMBER(F359),ISNUMBER(E359),E359&gt;0,F359=E359),"Draw",IF(AND(ISNUMBER(F359),ISNUMBER(E359),E359&gt;0,F359=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A359="","",IF(AND(ISNUMBER(E359),E359=0,OR(ISNUMBER(SEARCH("Free",D359&amp;"")),AND(ISNUMBER(F359),F359=0))),"Subscription",IF(ISNUMBER(G359),"Profit",IF(ISNUMBER(I359),"Disqualified",IF(ISNUMBER(H359),"Draw",IF(AND(ISNUMBER(F359),ISNUMBER(E359),E359&gt;0,F359&gt;E359),"Profit",IF(AND(ISNUMBER(F359),ISNUMBER(E359),E359&gt;0,F359=E359),"Draw",IF(AND(ISNUMBER(F359),ISNUMBER(E359),E359&gt;0,F359=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L359" s="50"/>
       <x:c r="M359" s="58"/>
@@ -14678,7 +14691,7 @@
         <x:f>IF(A360="","",IF(K360="Subscription","",IF(E360=0,"",IF(ISNUMBER(G360),G360/E360,IF(ISNUMBER(I360),-ABS(I360)/E360,IF(ISNUMBER(H360),0,IF(AND(ISNUMBER(F360),ISNUMBER(E360),E360&gt;0,F360&gt;E360),(F360-E360)/E360,IF(AND(ISNUMBER(F360),ISNUMBER(E360),E360&gt;0,F360=E360),0,IF(AND(ISNUMBER(F360),ISNUMBER(E360),E360&gt;0,F360=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K360" s="50" t="str">
-        <x:f>IF(A360="","",IF(AND(ISNUMBER(E360),E360=0,OR(ISNUMBER(SEARCH("Free",D360&amp;"")),AND(ISNUMBER(F360),F360=0))),"Subscription",IF(ISNUMBER(G360),"Profit",IF(ISNUMBER(I360),"Loss",IF(ISNUMBER(H360),"Draw",IF(AND(ISNUMBER(F360),ISNUMBER(E360),E360&gt;0,F360&gt;E360),"Profit",IF(AND(ISNUMBER(F360),ISNUMBER(E360),E360&gt;0,F360=E360),"Draw",IF(AND(ISNUMBER(F360),ISNUMBER(E360),E360&gt;0,F360=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A360="","",IF(AND(ISNUMBER(E360),E360=0,OR(ISNUMBER(SEARCH("Free",D360&amp;"")),AND(ISNUMBER(F360),F360=0))),"Subscription",IF(ISNUMBER(G360),"Profit",IF(ISNUMBER(I360),"Disqualified",IF(ISNUMBER(H360),"Draw",IF(AND(ISNUMBER(F360),ISNUMBER(E360),E360&gt;0,F360&gt;E360),"Profit",IF(AND(ISNUMBER(F360),ISNUMBER(E360),E360&gt;0,F360=E360),"Draw",IF(AND(ISNUMBER(F360),ISNUMBER(E360),E360&gt;0,F360=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L360" s="50"/>
       <x:c r="M360" s="58"/>
@@ -14715,7 +14728,7 @@
         <x:f>IF(A361="","",IF(K361="Subscription","",IF(E361=0,"",IF(ISNUMBER(G361),G361/E361,IF(ISNUMBER(I361),-ABS(I361)/E361,IF(ISNUMBER(H361),0,IF(AND(ISNUMBER(F361),ISNUMBER(E361),E361&gt;0,F361&gt;E361),(F361-E361)/E361,IF(AND(ISNUMBER(F361),ISNUMBER(E361),E361&gt;0,F361=E361),0,IF(AND(ISNUMBER(F361),ISNUMBER(E361),E361&gt;0,F361=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K361" s="50" t="str">
-        <x:f>IF(A361="","",IF(AND(ISNUMBER(E361),E361=0,OR(ISNUMBER(SEARCH("Free",D361&amp;"")),AND(ISNUMBER(F361),F361=0))),"Subscription",IF(ISNUMBER(G361),"Profit",IF(ISNUMBER(I361),"Loss",IF(ISNUMBER(H361),"Draw",IF(AND(ISNUMBER(F361),ISNUMBER(E361),E361&gt;0,F361&gt;E361),"Profit",IF(AND(ISNUMBER(F361),ISNUMBER(E361),E361&gt;0,F361=E361),"Draw",IF(AND(ISNUMBER(F361),ISNUMBER(E361),E361&gt;0,F361=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A361="","",IF(AND(ISNUMBER(E361),E361=0,OR(ISNUMBER(SEARCH("Free",D361&amp;"")),AND(ISNUMBER(F361),F361=0))),"Subscription",IF(ISNUMBER(G361),"Profit",IF(ISNUMBER(I361),"Disqualified",IF(ISNUMBER(H361),"Draw",IF(AND(ISNUMBER(F361),ISNUMBER(E361),E361&gt;0,F361&gt;E361),"Profit",IF(AND(ISNUMBER(F361),ISNUMBER(E361),E361&gt;0,F361=E361),"Draw",IF(AND(ISNUMBER(F361),ISNUMBER(E361),E361&gt;0,F361=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L361" s="50"/>
       <x:c r="M361" s="58"/>
@@ -14752,7 +14765,7 @@
         <x:f>IF(A362="","",IF(K362="Subscription","",IF(E362=0,"",IF(ISNUMBER(G362),G362/E362,IF(ISNUMBER(I362),-ABS(I362)/E362,IF(ISNUMBER(H362),0,IF(AND(ISNUMBER(F362),ISNUMBER(E362),E362&gt;0,F362&gt;E362),(F362-E362)/E362,IF(AND(ISNUMBER(F362),ISNUMBER(E362),E362&gt;0,F362=E362),0,IF(AND(ISNUMBER(F362),ISNUMBER(E362),E362&gt;0,F362=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K362" s="50" t="str">
-        <x:f>IF(A362="","",IF(AND(ISNUMBER(E362),E362=0,OR(ISNUMBER(SEARCH("Free",D362&amp;"")),AND(ISNUMBER(F362),F362=0))),"Subscription",IF(ISNUMBER(G362),"Profit",IF(ISNUMBER(I362),"Loss",IF(ISNUMBER(H362),"Draw",IF(AND(ISNUMBER(F362),ISNUMBER(E362),E362&gt;0,F362&gt;E362),"Profit",IF(AND(ISNUMBER(F362),ISNUMBER(E362),E362&gt;0,F362=E362),"Draw",IF(AND(ISNUMBER(F362),ISNUMBER(E362),E362&gt;0,F362=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A362="","",IF(AND(ISNUMBER(E362),E362=0,OR(ISNUMBER(SEARCH("Free",D362&amp;"")),AND(ISNUMBER(F362),F362=0))),"Subscription",IF(ISNUMBER(G362),"Profit",IF(ISNUMBER(I362),"Disqualified",IF(ISNUMBER(H362),"Draw",IF(AND(ISNUMBER(F362),ISNUMBER(E362),E362&gt;0,F362&gt;E362),"Profit",IF(AND(ISNUMBER(F362),ISNUMBER(E362),E362&gt;0,F362=E362),"Draw",IF(AND(ISNUMBER(F362),ISNUMBER(E362),E362&gt;0,F362=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L362" s="50"/>
       <x:c r="M362" s="58"/>
@@ -14789,7 +14802,7 @@
         <x:f>IF(A363="","",IF(K363="Subscription","",IF(E363=0,"",IF(ISNUMBER(G363),G363/E363,IF(ISNUMBER(I363),-ABS(I363)/E363,IF(ISNUMBER(H363),0,IF(AND(ISNUMBER(F363),ISNUMBER(E363),E363&gt;0,F363&gt;E363),(F363-E363)/E363,IF(AND(ISNUMBER(F363),ISNUMBER(E363),E363&gt;0,F363=E363),0,IF(AND(ISNUMBER(F363),ISNUMBER(E363),E363&gt;0,F363=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K363" s="50" t="str">
-        <x:f>IF(A363="","",IF(AND(ISNUMBER(E363),E363=0,OR(ISNUMBER(SEARCH("Free",D363&amp;"")),AND(ISNUMBER(F363),F363=0))),"Subscription",IF(ISNUMBER(G363),"Profit",IF(ISNUMBER(I363),"Loss",IF(ISNUMBER(H363),"Draw",IF(AND(ISNUMBER(F363),ISNUMBER(E363),E363&gt;0,F363&gt;E363),"Profit",IF(AND(ISNUMBER(F363),ISNUMBER(E363),E363&gt;0,F363=E363),"Draw",IF(AND(ISNUMBER(F363),ISNUMBER(E363),E363&gt;0,F363=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A363="","",IF(AND(ISNUMBER(E363),E363=0,OR(ISNUMBER(SEARCH("Free",D363&amp;"")),AND(ISNUMBER(F363),F363=0))),"Subscription",IF(ISNUMBER(G363),"Profit",IF(ISNUMBER(I363),"Disqualified",IF(ISNUMBER(H363),"Draw",IF(AND(ISNUMBER(F363),ISNUMBER(E363),E363&gt;0,F363&gt;E363),"Profit",IF(AND(ISNUMBER(F363),ISNUMBER(E363),E363&gt;0,F363=E363),"Draw",IF(AND(ISNUMBER(F363),ISNUMBER(E363),E363&gt;0,F363=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L363" s="50"/>
       <x:c r="M363" s="58"/>
@@ -14826,7 +14839,7 @@
         <x:f>IF(A364="","",IF(K364="Subscription","",IF(E364=0,"",IF(ISNUMBER(G364),G364/E364,IF(ISNUMBER(I364),-ABS(I364)/E364,IF(ISNUMBER(H364),0,IF(AND(ISNUMBER(F364),ISNUMBER(E364),E364&gt;0,F364&gt;E364),(F364-E364)/E364,IF(AND(ISNUMBER(F364),ISNUMBER(E364),E364&gt;0,F364=E364),0,IF(AND(ISNUMBER(F364),ISNUMBER(E364),E364&gt;0,F364=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K364" s="50" t="str">
-        <x:f>IF(A364="","",IF(AND(ISNUMBER(E364),E364=0,OR(ISNUMBER(SEARCH("Free",D364&amp;"")),AND(ISNUMBER(F364),F364=0))),"Subscription",IF(ISNUMBER(G364),"Profit",IF(ISNUMBER(I364),"Loss",IF(ISNUMBER(H364),"Draw",IF(AND(ISNUMBER(F364),ISNUMBER(E364),E364&gt;0,F364&gt;E364),"Profit",IF(AND(ISNUMBER(F364),ISNUMBER(E364),E364&gt;0,F364=E364),"Draw",IF(AND(ISNUMBER(F364),ISNUMBER(E364),E364&gt;0,F364=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A364="","",IF(AND(ISNUMBER(E364),E364=0,OR(ISNUMBER(SEARCH("Free",D364&amp;"")),AND(ISNUMBER(F364),F364=0))),"Subscription",IF(ISNUMBER(G364),"Profit",IF(ISNUMBER(I364),"Disqualified",IF(ISNUMBER(H364),"Draw",IF(AND(ISNUMBER(F364),ISNUMBER(E364),E364&gt;0,F364&gt;E364),"Profit",IF(AND(ISNUMBER(F364),ISNUMBER(E364),E364&gt;0,F364=E364),"Draw",IF(AND(ISNUMBER(F364),ISNUMBER(E364),E364&gt;0,F364=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L364" s="50"/>
       <x:c r="M364" s="58"/>
@@ -14863,7 +14876,7 @@
         <x:f>IF(A365="","",IF(K365="Subscription","",IF(E365=0,"",IF(ISNUMBER(G365),G365/E365,IF(ISNUMBER(I365),-ABS(I365)/E365,IF(ISNUMBER(H365),0,IF(AND(ISNUMBER(F365),ISNUMBER(E365),E365&gt;0,F365&gt;E365),(F365-E365)/E365,IF(AND(ISNUMBER(F365),ISNUMBER(E365),E365&gt;0,F365=E365),0,IF(AND(ISNUMBER(F365),ISNUMBER(E365),E365&gt;0,F365=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K365" s="50" t="str">
-        <x:f>IF(A365="","",IF(AND(ISNUMBER(E365),E365=0,OR(ISNUMBER(SEARCH("Free",D365&amp;"")),AND(ISNUMBER(F365),F365=0))),"Subscription",IF(ISNUMBER(G365),"Profit",IF(ISNUMBER(I365),"Loss",IF(ISNUMBER(H365),"Draw",IF(AND(ISNUMBER(F365),ISNUMBER(E365),E365&gt;0,F365&gt;E365),"Profit",IF(AND(ISNUMBER(F365),ISNUMBER(E365),E365&gt;0,F365=E365),"Draw",IF(AND(ISNUMBER(F365),ISNUMBER(E365),E365&gt;0,F365=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A365="","",IF(AND(ISNUMBER(E365),E365=0,OR(ISNUMBER(SEARCH("Free",D365&amp;"")),AND(ISNUMBER(F365),F365=0))),"Subscription",IF(ISNUMBER(G365),"Profit",IF(ISNUMBER(I365),"Disqualified",IF(ISNUMBER(H365),"Draw",IF(AND(ISNUMBER(F365),ISNUMBER(E365),E365&gt;0,F365&gt;E365),"Profit",IF(AND(ISNUMBER(F365),ISNUMBER(E365),E365&gt;0,F365=E365),"Draw",IF(AND(ISNUMBER(F365),ISNUMBER(E365),E365&gt;0,F365=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L365" s="50"/>
       <x:c r="M365" s="58"/>
@@ -14900,7 +14913,7 @@
         <x:f>IF(A366="","",IF(K366="Subscription","",IF(E366=0,"",IF(ISNUMBER(G366),G366/E366,IF(ISNUMBER(I366),-ABS(I366)/E366,IF(ISNUMBER(H366),0,IF(AND(ISNUMBER(F366),ISNUMBER(E366),E366&gt;0,F366&gt;E366),(F366-E366)/E366,IF(AND(ISNUMBER(F366),ISNUMBER(E366),E366&gt;0,F366=E366),0,IF(AND(ISNUMBER(F366),ISNUMBER(E366),E366&gt;0,F366=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K366" s="50" t="str">
-        <x:f>IF(A366="","",IF(AND(ISNUMBER(E366),E366=0,OR(ISNUMBER(SEARCH("Free",D366&amp;"")),AND(ISNUMBER(F366),F366=0))),"Subscription",IF(ISNUMBER(G366),"Profit",IF(ISNUMBER(I366),"Loss",IF(ISNUMBER(H366),"Draw",IF(AND(ISNUMBER(F366),ISNUMBER(E366),E366&gt;0,F366&gt;E366),"Profit",IF(AND(ISNUMBER(F366),ISNUMBER(E366),E366&gt;0,F366=E366),"Draw",IF(AND(ISNUMBER(F366),ISNUMBER(E366),E366&gt;0,F366=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A366="","",IF(AND(ISNUMBER(E366),E366=0,OR(ISNUMBER(SEARCH("Free",D366&amp;"")),AND(ISNUMBER(F366),F366=0))),"Subscription",IF(ISNUMBER(G366),"Profit",IF(ISNUMBER(I366),"Disqualified",IF(ISNUMBER(H366),"Draw",IF(AND(ISNUMBER(F366),ISNUMBER(E366),E366&gt;0,F366&gt;E366),"Profit",IF(AND(ISNUMBER(F366),ISNUMBER(E366),E366&gt;0,F366=E366),"Draw",IF(AND(ISNUMBER(F366),ISNUMBER(E366),E366&gt;0,F366=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L366" s="50"/>
       <x:c r="M366" s="58"/>
@@ -14937,7 +14950,7 @@
         <x:f>IF(A367="","",IF(K367="Subscription","",IF(E367=0,"",IF(ISNUMBER(G367),G367/E367,IF(ISNUMBER(I367),-ABS(I367)/E367,IF(ISNUMBER(H367),0,IF(AND(ISNUMBER(F367),ISNUMBER(E367),E367&gt;0,F367&gt;E367),(F367-E367)/E367,IF(AND(ISNUMBER(F367),ISNUMBER(E367),E367&gt;0,F367=E367),0,IF(AND(ISNUMBER(F367),ISNUMBER(E367),E367&gt;0,F367=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K367" s="50" t="str">
-        <x:f>IF(A367="","",IF(AND(ISNUMBER(E367),E367=0,OR(ISNUMBER(SEARCH("Free",D367&amp;"")),AND(ISNUMBER(F367),F367=0))),"Subscription",IF(ISNUMBER(G367),"Profit",IF(ISNUMBER(I367),"Loss",IF(ISNUMBER(H367),"Draw",IF(AND(ISNUMBER(F367),ISNUMBER(E367),E367&gt;0,F367&gt;E367),"Profit",IF(AND(ISNUMBER(F367),ISNUMBER(E367),E367&gt;0,F367=E367),"Draw",IF(AND(ISNUMBER(F367),ISNUMBER(E367),E367&gt;0,F367=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A367="","",IF(AND(ISNUMBER(E367),E367=0,OR(ISNUMBER(SEARCH("Free",D367&amp;"")),AND(ISNUMBER(F367),F367=0))),"Subscription",IF(ISNUMBER(G367),"Profit",IF(ISNUMBER(I367),"Disqualified",IF(ISNUMBER(H367),"Draw",IF(AND(ISNUMBER(F367),ISNUMBER(E367),E367&gt;0,F367&gt;E367),"Profit",IF(AND(ISNUMBER(F367),ISNUMBER(E367),E367&gt;0,F367=E367),"Draw",IF(AND(ISNUMBER(F367),ISNUMBER(E367),E367&gt;0,F367=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L367" s="50"/>
       <x:c r="M367" s="58"/>
@@ -14974,7 +14987,7 @@
         <x:f>IF(A368="","",IF(K368="Subscription","",IF(E368=0,"",IF(ISNUMBER(G368),G368/E368,IF(ISNUMBER(I368),-ABS(I368)/E368,IF(ISNUMBER(H368),0,IF(AND(ISNUMBER(F368),ISNUMBER(E368),E368&gt;0,F368&gt;E368),(F368-E368)/E368,IF(AND(ISNUMBER(F368),ISNUMBER(E368),E368&gt;0,F368=E368),0,IF(AND(ISNUMBER(F368),ISNUMBER(E368),E368&gt;0,F368=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K368" s="50" t="str">
-        <x:f>IF(A368="","",IF(AND(ISNUMBER(E368),E368=0,OR(ISNUMBER(SEARCH("Free",D368&amp;"")),AND(ISNUMBER(F368),F368=0))),"Subscription",IF(ISNUMBER(G368),"Profit",IF(ISNUMBER(I368),"Loss",IF(ISNUMBER(H368),"Draw",IF(AND(ISNUMBER(F368),ISNUMBER(E368),E368&gt;0,F368&gt;E368),"Profit",IF(AND(ISNUMBER(F368),ISNUMBER(E368),E368&gt;0,F368=E368),"Draw",IF(AND(ISNUMBER(F368),ISNUMBER(E368),E368&gt;0,F368=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A368="","",IF(AND(ISNUMBER(E368),E368=0,OR(ISNUMBER(SEARCH("Free",D368&amp;"")),AND(ISNUMBER(F368),F368=0))),"Subscription",IF(ISNUMBER(G368),"Profit",IF(ISNUMBER(I368),"Disqualified",IF(ISNUMBER(H368),"Draw",IF(AND(ISNUMBER(F368),ISNUMBER(E368),E368&gt;0,F368&gt;E368),"Profit",IF(AND(ISNUMBER(F368),ISNUMBER(E368),E368&gt;0,F368=E368),"Draw",IF(AND(ISNUMBER(F368),ISNUMBER(E368),E368&gt;0,F368=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L368" s="50"/>
       <x:c r="M368" s="58"/>
@@ -15011,7 +15024,7 @@
         <x:f>IF(A369="","",IF(K369="Subscription","",IF(E369=0,"",IF(ISNUMBER(G369),G369/E369,IF(ISNUMBER(I369),-ABS(I369)/E369,IF(ISNUMBER(H369),0,IF(AND(ISNUMBER(F369),ISNUMBER(E369),E369&gt;0,F369&gt;E369),(F369-E369)/E369,IF(AND(ISNUMBER(F369),ISNUMBER(E369),E369&gt;0,F369=E369),0,IF(AND(ISNUMBER(F369),ISNUMBER(E369),E369&gt;0,F369=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K369" s="50" t="str">
-        <x:f>IF(A369="","",IF(AND(ISNUMBER(E369),E369=0,OR(ISNUMBER(SEARCH("Free",D369&amp;"")),AND(ISNUMBER(F369),F369=0))),"Subscription",IF(ISNUMBER(G369),"Profit",IF(ISNUMBER(I369),"Loss",IF(ISNUMBER(H369),"Draw",IF(AND(ISNUMBER(F369),ISNUMBER(E369),E369&gt;0,F369&gt;E369),"Profit",IF(AND(ISNUMBER(F369),ISNUMBER(E369),E369&gt;0,F369=E369),"Draw",IF(AND(ISNUMBER(F369),ISNUMBER(E369),E369&gt;0,F369=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A369="","",IF(AND(ISNUMBER(E369),E369=0,OR(ISNUMBER(SEARCH("Free",D369&amp;"")),AND(ISNUMBER(F369),F369=0))),"Subscription",IF(ISNUMBER(G369),"Profit",IF(ISNUMBER(I369),"Disqualified",IF(ISNUMBER(H369),"Draw",IF(AND(ISNUMBER(F369),ISNUMBER(E369),E369&gt;0,F369&gt;E369),"Profit",IF(AND(ISNUMBER(F369),ISNUMBER(E369),E369&gt;0,F369=E369),"Draw",IF(AND(ISNUMBER(F369),ISNUMBER(E369),E369&gt;0,F369=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L369" s="50"/>
       <x:c r="M369" s="58"/>
@@ -15048,7 +15061,7 @@
         <x:f>IF(A370="","",IF(K370="Subscription","",IF(E370=0,"",IF(ISNUMBER(G370),G370/E370,IF(ISNUMBER(I370),-ABS(I370)/E370,IF(ISNUMBER(H370),0,IF(AND(ISNUMBER(F370),ISNUMBER(E370),E370&gt;0,F370&gt;E370),(F370-E370)/E370,IF(AND(ISNUMBER(F370),ISNUMBER(E370),E370&gt;0,F370=E370),0,IF(AND(ISNUMBER(F370),ISNUMBER(E370),E370&gt;0,F370=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K370" s="50" t="str">
-        <x:f>IF(A370="","",IF(AND(ISNUMBER(E370),E370=0,OR(ISNUMBER(SEARCH("Free",D370&amp;"")),AND(ISNUMBER(F370),F370=0))),"Subscription",IF(ISNUMBER(G370),"Profit",IF(ISNUMBER(I370),"Loss",IF(ISNUMBER(H370),"Draw",IF(AND(ISNUMBER(F370),ISNUMBER(E370),E370&gt;0,F370&gt;E370),"Profit",IF(AND(ISNUMBER(F370),ISNUMBER(E370),E370&gt;0,F370=E370),"Draw",IF(AND(ISNUMBER(F370),ISNUMBER(E370),E370&gt;0,F370=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A370="","",IF(AND(ISNUMBER(E370),E370=0,OR(ISNUMBER(SEARCH("Free",D370&amp;"")),AND(ISNUMBER(F370),F370=0))),"Subscription",IF(ISNUMBER(G370),"Profit",IF(ISNUMBER(I370),"Disqualified",IF(ISNUMBER(H370),"Draw",IF(AND(ISNUMBER(F370),ISNUMBER(E370),E370&gt;0,F370&gt;E370),"Profit",IF(AND(ISNUMBER(F370),ISNUMBER(E370),E370&gt;0,F370=E370),"Draw",IF(AND(ISNUMBER(F370),ISNUMBER(E370),E370&gt;0,F370=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L370" s="50"/>
       <x:c r="M370" s="58"/>
@@ -15085,7 +15098,7 @@
         <x:f>IF(A371="","",IF(K371="Subscription","",IF(E371=0,"",IF(ISNUMBER(G371),G371/E371,IF(ISNUMBER(I371),-ABS(I371)/E371,IF(ISNUMBER(H371),0,IF(AND(ISNUMBER(F371),ISNUMBER(E371),E371&gt;0,F371&gt;E371),(F371-E371)/E371,IF(AND(ISNUMBER(F371),ISNUMBER(E371),E371&gt;0,F371=E371),0,IF(AND(ISNUMBER(F371),ISNUMBER(E371),E371&gt;0,F371=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K371" s="50" t="str">
-        <x:f>IF(A371="","",IF(AND(ISNUMBER(E371),E371=0,OR(ISNUMBER(SEARCH("Free",D371&amp;"")),AND(ISNUMBER(F371),F371=0))),"Subscription",IF(ISNUMBER(G371),"Profit",IF(ISNUMBER(I371),"Loss",IF(ISNUMBER(H371),"Draw",IF(AND(ISNUMBER(F371),ISNUMBER(E371),E371&gt;0,F371&gt;E371),"Profit",IF(AND(ISNUMBER(F371),ISNUMBER(E371),E371&gt;0,F371=E371),"Draw",IF(AND(ISNUMBER(F371),ISNUMBER(E371),E371&gt;0,F371=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A371="","",IF(AND(ISNUMBER(E371),E371=0,OR(ISNUMBER(SEARCH("Free",D371&amp;"")),AND(ISNUMBER(F371),F371=0))),"Subscription",IF(ISNUMBER(G371),"Profit",IF(ISNUMBER(I371),"Disqualified",IF(ISNUMBER(H371),"Draw",IF(AND(ISNUMBER(F371),ISNUMBER(E371),E371&gt;0,F371&gt;E371),"Profit",IF(AND(ISNUMBER(F371),ISNUMBER(E371),E371&gt;0,F371=E371),"Draw",IF(AND(ISNUMBER(F371),ISNUMBER(E371),E371&gt;0,F371=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L371" s="50"/>
       <x:c r="M371" s="58"/>
@@ -15122,7 +15135,7 @@
         <x:f>IF(A372="","",IF(K372="Subscription","",IF(E372=0,"",IF(ISNUMBER(G372),G372/E372,IF(ISNUMBER(I372),-ABS(I372)/E372,IF(ISNUMBER(H372),0,IF(AND(ISNUMBER(F372),ISNUMBER(E372),E372&gt;0,F372&gt;E372),(F372-E372)/E372,IF(AND(ISNUMBER(F372),ISNUMBER(E372),E372&gt;0,F372=E372),0,IF(AND(ISNUMBER(F372),ISNUMBER(E372),E372&gt;0,F372=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K372" s="50" t="str">
-        <x:f>IF(A372="","",IF(AND(ISNUMBER(E372),E372=0,OR(ISNUMBER(SEARCH("Free",D372&amp;"")),AND(ISNUMBER(F372),F372=0))),"Subscription",IF(ISNUMBER(G372),"Profit",IF(ISNUMBER(I372),"Loss",IF(ISNUMBER(H372),"Draw",IF(AND(ISNUMBER(F372),ISNUMBER(E372),E372&gt;0,F372&gt;E372),"Profit",IF(AND(ISNUMBER(F372),ISNUMBER(E372),E372&gt;0,F372=E372),"Draw",IF(AND(ISNUMBER(F372),ISNUMBER(E372),E372&gt;0,F372=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A372="","",IF(AND(ISNUMBER(E372),E372=0,OR(ISNUMBER(SEARCH("Free",D372&amp;"")),AND(ISNUMBER(F372),F372=0))),"Subscription",IF(ISNUMBER(G372),"Profit",IF(ISNUMBER(I372),"Disqualified",IF(ISNUMBER(H372),"Draw",IF(AND(ISNUMBER(F372),ISNUMBER(E372),E372&gt;0,F372&gt;E372),"Profit",IF(AND(ISNUMBER(F372),ISNUMBER(E372),E372&gt;0,F372=E372),"Draw",IF(AND(ISNUMBER(F372),ISNUMBER(E372),E372&gt;0,F372=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L372" s="50"/>
       <x:c r="M372" s="58"/>
@@ -15159,7 +15172,7 @@
         <x:f>IF(A373="","",IF(K373="Subscription","",IF(E373=0,"",IF(ISNUMBER(G373),G373/E373,IF(ISNUMBER(I373),-ABS(I373)/E373,IF(ISNUMBER(H373),0,IF(AND(ISNUMBER(F373),ISNUMBER(E373),E373&gt;0,F373&gt;E373),(F373-E373)/E373,IF(AND(ISNUMBER(F373),ISNUMBER(E373),E373&gt;0,F373=E373),0,IF(AND(ISNUMBER(F373),ISNUMBER(E373),E373&gt;0,F373=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K373" s="50" t="str">
-        <x:f>IF(A373="","",IF(AND(ISNUMBER(E373),E373=0,OR(ISNUMBER(SEARCH("Free",D373&amp;"")),AND(ISNUMBER(F373),F373=0))),"Subscription",IF(ISNUMBER(G373),"Profit",IF(ISNUMBER(I373),"Loss",IF(ISNUMBER(H373),"Draw",IF(AND(ISNUMBER(F373),ISNUMBER(E373),E373&gt;0,F373&gt;E373),"Profit",IF(AND(ISNUMBER(F373),ISNUMBER(E373),E373&gt;0,F373=E373),"Draw",IF(AND(ISNUMBER(F373),ISNUMBER(E373),E373&gt;0,F373=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A373="","",IF(AND(ISNUMBER(E373),E373=0,OR(ISNUMBER(SEARCH("Free",D373&amp;"")),AND(ISNUMBER(F373),F373=0))),"Subscription",IF(ISNUMBER(G373),"Profit",IF(ISNUMBER(I373),"Disqualified",IF(ISNUMBER(H373),"Draw",IF(AND(ISNUMBER(F373),ISNUMBER(E373),E373&gt;0,F373&gt;E373),"Profit",IF(AND(ISNUMBER(F373),ISNUMBER(E373),E373&gt;0,F373=E373),"Draw",IF(AND(ISNUMBER(F373),ISNUMBER(E373),E373&gt;0,F373=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L373" s="50"/>
       <x:c r="M373" s="58"/>
@@ -15196,7 +15209,7 @@
         <x:f>IF(A374="","",IF(K374="Subscription","",IF(E374=0,"",IF(ISNUMBER(G374),G374/E374,IF(ISNUMBER(I374),-ABS(I374)/E374,IF(ISNUMBER(H374),0,IF(AND(ISNUMBER(F374),ISNUMBER(E374),E374&gt;0,F374&gt;E374),(F374-E374)/E374,IF(AND(ISNUMBER(F374),ISNUMBER(E374),E374&gt;0,F374=E374),0,IF(AND(ISNUMBER(F374),ISNUMBER(E374),E374&gt;0,F374=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K374" s="50" t="str">
-        <x:f>IF(A374="","",IF(AND(ISNUMBER(E374),E374=0,OR(ISNUMBER(SEARCH("Free",D374&amp;"")),AND(ISNUMBER(F374),F374=0))),"Subscription",IF(ISNUMBER(G374),"Profit",IF(ISNUMBER(I374),"Loss",IF(ISNUMBER(H374),"Draw",IF(AND(ISNUMBER(F374),ISNUMBER(E374),E374&gt;0,F374&gt;E374),"Profit",IF(AND(ISNUMBER(F374),ISNUMBER(E374),E374&gt;0,F374=E374),"Draw",IF(AND(ISNUMBER(F374),ISNUMBER(E374),E374&gt;0,F374=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A374="","",IF(AND(ISNUMBER(E374),E374=0,OR(ISNUMBER(SEARCH("Free",D374&amp;"")),AND(ISNUMBER(F374),F374=0))),"Subscription",IF(ISNUMBER(G374),"Profit",IF(ISNUMBER(I374),"Disqualified",IF(ISNUMBER(H374),"Draw",IF(AND(ISNUMBER(F374),ISNUMBER(E374),E374&gt;0,F374&gt;E374),"Profit",IF(AND(ISNUMBER(F374),ISNUMBER(E374),E374&gt;0,F374=E374),"Draw",IF(AND(ISNUMBER(F374),ISNUMBER(E374),E374&gt;0,F374=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L374" s="50"/>
       <x:c r="M374" s="58"/>
@@ -15233,7 +15246,7 @@
         <x:f>IF(A375="","",IF(K375="Subscription","",IF(E375=0,"",IF(ISNUMBER(G375),G375/E375,IF(ISNUMBER(I375),-ABS(I375)/E375,IF(ISNUMBER(H375),0,IF(AND(ISNUMBER(F375),ISNUMBER(E375),E375&gt;0,F375&gt;E375),(F375-E375)/E375,IF(AND(ISNUMBER(F375),ISNUMBER(E375),E375&gt;0,F375=E375),0,IF(AND(ISNUMBER(F375),ISNUMBER(E375),E375&gt;0,F375=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K375" s="50" t="str">
-        <x:f>IF(A375="","",IF(AND(ISNUMBER(E375),E375=0,OR(ISNUMBER(SEARCH("Free",D375&amp;"")),AND(ISNUMBER(F375),F375=0))),"Subscription",IF(ISNUMBER(G375),"Profit",IF(ISNUMBER(I375),"Loss",IF(ISNUMBER(H375),"Draw",IF(AND(ISNUMBER(F375),ISNUMBER(E375),E375&gt;0,F375&gt;E375),"Profit",IF(AND(ISNUMBER(F375),ISNUMBER(E375),E375&gt;0,F375=E375),"Draw",IF(AND(ISNUMBER(F375),ISNUMBER(E375),E375&gt;0,F375=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A375="","",IF(AND(ISNUMBER(E375),E375=0,OR(ISNUMBER(SEARCH("Free",D375&amp;"")),AND(ISNUMBER(F375),F375=0))),"Subscription",IF(ISNUMBER(G375),"Profit",IF(ISNUMBER(I375),"Disqualified",IF(ISNUMBER(H375),"Draw",IF(AND(ISNUMBER(F375),ISNUMBER(E375),E375&gt;0,F375&gt;E375),"Profit",IF(AND(ISNUMBER(F375),ISNUMBER(E375),E375&gt;0,F375=E375),"Draw",IF(AND(ISNUMBER(F375),ISNUMBER(E375),E375&gt;0,F375=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L375" s="50"/>
       <x:c r="M375" s="58"/>
@@ -15270,7 +15283,7 @@
         <x:f>IF(A376="","",IF(K376="Subscription","",IF(E376=0,"",IF(ISNUMBER(G376),G376/E376,IF(ISNUMBER(I376),-ABS(I376)/E376,IF(ISNUMBER(H376),0,IF(AND(ISNUMBER(F376),ISNUMBER(E376),E376&gt;0,F376&gt;E376),(F376-E376)/E376,IF(AND(ISNUMBER(F376),ISNUMBER(E376),E376&gt;0,F376=E376),0,IF(AND(ISNUMBER(F376),ISNUMBER(E376),E376&gt;0,F376=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K376" s="50" t="str">
-        <x:f>IF(A376="","",IF(AND(ISNUMBER(E376),E376=0,OR(ISNUMBER(SEARCH("Free",D376&amp;"")),AND(ISNUMBER(F376),F376=0))),"Subscription",IF(ISNUMBER(G376),"Profit",IF(ISNUMBER(I376),"Loss",IF(ISNUMBER(H376),"Draw",IF(AND(ISNUMBER(F376),ISNUMBER(E376),E376&gt;0,F376&gt;E376),"Profit",IF(AND(ISNUMBER(F376),ISNUMBER(E376),E376&gt;0,F376=E376),"Draw",IF(AND(ISNUMBER(F376),ISNUMBER(E376),E376&gt;0,F376=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A376="","",IF(AND(ISNUMBER(E376),E376=0,OR(ISNUMBER(SEARCH("Free",D376&amp;"")),AND(ISNUMBER(F376),F376=0))),"Subscription",IF(ISNUMBER(G376),"Profit",IF(ISNUMBER(I376),"Disqualified",IF(ISNUMBER(H376),"Draw",IF(AND(ISNUMBER(F376),ISNUMBER(E376),E376&gt;0,F376&gt;E376),"Profit",IF(AND(ISNUMBER(F376),ISNUMBER(E376),E376&gt;0,F376=E376),"Draw",IF(AND(ISNUMBER(F376),ISNUMBER(E376),E376&gt;0,F376=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L376" s="50"/>
       <x:c r="M376" s="58"/>
@@ -15307,7 +15320,7 @@
         <x:f>IF(A377="","",IF(K377="Subscription","",IF(E377=0,"",IF(ISNUMBER(G377),G377/E377,IF(ISNUMBER(I377),-ABS(I377)/E377,IF(ISNUMBER(H377),0,IF(AND(ISNUMBER(F377),ISNUMBER(E377),E377&gt;0,F377&gt;E377),(F377-E377)/E377,IF(AND(ISNUMBER(F377),ISNUMBER(E377),E377&gt;0,F377=E377),0,IF(AND(ISNUMBER(F377),ISNUMBER(E377),E377&gt;0,F377=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K377" s="50" t="str">
-        <x:f>IF(A377="","",IF(AND(ISNUMBER(E377),E377=0,OR(ISNUMBER(SEARCH("Free",D377&amp;"")),AND(ISNUMBER(F377),F377=0))),"Subscription",IF(ISNUMBER(G377),"Profit",IF(ISNUMBER(I377),"Loss",IF(ISNUMBER(H377),"Draw",IF(AND(ISNUMBER(F377),ISNUMBER(E377),E377&gt;0,F377&gt;E377),"Profit",IF(AND(ISNUMBER(F377),ISNUMBER(E377),E377&gt;0,F377=E377),"Draw",IF(AND(ISNUMBER(F377),ISNUMBER(E377),E377&gt;0,F377=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A377="","",IF(AND(ISNUMBER(E377),E377=0,OR(ISNUMBER(SEARCH("Free",D377&amp;"")),AND(ISNUMBER(F377),F377=0))),"Subscription",IF(ISNUMBER(G377),"Profit",IF(ISNUMBER(I377),"Disqualified",IF(ISNUMBER(H377),"Draw",IF(AND(ISNUMBER(F377),ISNUMBER(E377),E377&gt;0,F377&gt;E377),"Profit",IF(AND(ISNUMBER(F377),ISNUMBER(E377),E377&gt;0,F377=E377),"Draw",IF(AND(ISNUMBER(F377),ISNUMBER(E377),E377&gt;0,F377=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L377" s="50"/>
       <x:c r="M377" s="58"/>
@@ -15344,7 +15357,7 @@
         <x:f>IF(A378="","",IF(K378="Subscription","",IF(E378=0,"",IF(ISNUMBER(G378),G378/E378,IF(ISNUMBER(I378),-ABS(I378)/E378,IF(ISNUMBER(H378),0,IF(AND(ISNUMBER(F378),ISNUMBER(E378),E378&gt;0,F378&gt;E378),(F378-E378)/E378,IF(AND(ISNUMBER(F378),ISNUMBER(E378),E378&gt;0,F378=E378),0,IF(AND(ISNUMBER(F378),ISNUMBER(E378),E378&gt;0,F378=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K378" s="50" t="str">
-        <x:f>IF(A378="","",IF(AND(ISNUMBER(E378),E378=0,OR(ISNUMBER(SEARCH("Free",D378&amp;"")),AND(ISNUMBER(F378),F378=0))),"Subscription",IF(ISNUMBER(G378),"Profit",IF(ISNUMBER(I378),"Loss",IF(ISNUMBER(H378),"Draw",IF(AND(ISNUMBER(F378),ISNUMBER(E378),E378&gt;0,F378&gt;E378),"Profit",IF(AND(ISNUMBER(F378),ISNUMBER(E378),E378&gt;0,F378=E378),"Draw",IF(AND(ISNUMBER(F378),ISNUMBER(E378),E378&gt;0,F378=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A378="","",IF(AND(ISNUMBER(E378),E378=0,OR(ISNUMBER(SEARCH("Free",D378&amp;"")),AND(ISNUMBER(F378),F378=0))),"Subscription",IF(ISNUMBER(G378),"Profit",IF(ISNUMBER(I378),"Disqualified",IF(ISNUMBER(H378),"Draw",IF(AND(ISNUMBER(F378),ISNUMBER(E378),E378&gt;0,F378&gt;E378),"Profit",IF(AND(ISNUMBER(F378),ISNUMBER(E378),E378&gt;0,F378=E378),"Draw",IF(AND(ISNUMBER(F378),ISNUMBER(E378),E378&gt;0,F378=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L378" s="50"/>
       <x:c r="M378" s="58"/>
@@ -15381,7 +15394,7 @@
         <x:f>IF(A379="","",IF(K379="Subscription","",IF(E379=0,"",IF(ISNUMBER(G379),G379/E379,IF(ISNUMBER(I379),-ABS(I379)/E379,IF(ISNUMBER(H379),0,IF(AND(ISNUMBER(F379),ISNUMBER(E379),E379&gt;0,F379&gt;E379),(F379-E379)/E379,IF(AND(ISNUMBER(F379),ISNUMBER(E379),E379&gt;0,F379=E379),0,IF(AND(ISNUMBER(F379),ISNUMBER(E379),E379&gt;0,F379=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K379" s="50" t="str">
-        <x:f>IF(A379="","",IF(AND(ISNUMBER(E379),E379=0,OR(ISNUMBER(SEARCH("Free",D379&amp;"")),AND(ISNUMBER(F379),F379=0))),"Subscription",IF(ISNUMBER(G379),"Profit",IF(ISNUMBER(I379),"Loss",IF(ISNUMBER(H379),"Draw",IF(AND(ISNUMBER(F379),ISNUMBER(E379),E379&gt;0,F379&gt;E379),"Profit",IF(AND(ISNUMBER(F379),ISNUMBER(E379),E379&gt;0,F379=E379),"Draw",IF(AND(ISNUMBER(F379),ISNUMBER(E379),E379&gt;0,F379=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A379="","",IF(AND(ISNUMBER(E379),E379=0,OR(ISNUMBER(SEARCH("Free",D379&amp;"")),AND(ISNUMBER(F379),F379=0))),"Subscription",IF(ISNUMBER(G379),"Profit",IF(ISNUMBER(I379),"Disqualified",IF(ISNUMBER(H379),"Draw",IF(AND(ISNUMBER(F379),ISNUMBER(E379),E379&gt;0,F379&gt;E379),"Profit",IF(AND(ISNUMBER(F379),ISNUMBER(E379),E379&gt;0,F379=E379),"Draw",IF(AND(ISNUMBER(F379),ISNUMBER(E379),E379&gt;0,F379=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L379" s="50"/>
       <x:c r="M379" s="58"/>
@@ -15418,7 +15431,7 @@
         <x:f>IF(A380="","",IF(K380="Subscription","",IF(E380=0,"",IF(ISNUMBER(G380),G380/E380,IF(ISNUMBER(I380),-ABS(I380)/E380,IF(ISNUMBER(H380),0,IF(AND(ISNUMBER(F380),ISNUMBER(E380),E380&gt;0,F380&gt;E380),(F380-E380)/E380,IF(AND(ISNUMBER(F380),ISNUMBER(E380),E380&gt;0,F380=E380),0,IF(AND(ISNUMBER(F380),ISNUMBER(E380),E380&gt;0,F380=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K380" s="50" t="str">
-        <x:f>IF(A380="","",IF(AND(ISNUMBER(E380),E380=0,OR(ISNUMBER(SEARCH("Free",D380&amp;"")),AND(ISNUMBER(F380),F380=0))),"Subscription",IF(ISNUMBER(G380),"Profit",IF(ISNUMBER(I380),"Loss",IF(ISNUMBER(H380),"Draw",IF(AND(ISNUMBER(F380),ISNUMBER(E380),E380&gt;0,F380&gt;E380),"Profit",IF(AND(ISNUMBER(F380),ISNUMBER(E380),E380&gt;0,F380=E380),"Draw",IF(AND(ISNUMBER(F380),ISNUMBER(E380),E380&gt;0,F380=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A380="","",IF(AND(ISNUMBER(E380),E380=0,OR(ISNUMBER(SEARCH("Free",D380&amp;"")),AND(ISNUMBER(F380),F380=0))),"Subscription",IF(ISNUMBER(G380),"Profit",IF(ISNUMBER(I380),"Disqualified",IF(ISNUMBER(H380),"Draw",IF(AND(ISNUMBER(F380),ISNUMBER(E380),E380&gt;0,F380&gt;E380),"Profit",IF(AND(ISNUMBER(F380),ISNUMBER(E380),E380&gt;0,F380=E380),"Draw",IF(AND(ISNUMBER(F380),ISNUMBER(E380),E380&gt;0,F380=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L380" s="50"/>
       <x:c r="M380" s="58"/>
@@ -15455,7 +15468,7 @@
         <x:f>IF(A381="","",IF(K381="Subscription","",IF(E381=0,"",IF(ISNUMBER(G381),G381/E381,IF(ISNUMBER(I381),-ABS(I381)/E381,IF(ISNUMBER(H381),0,IF(AND(ISNUMBER(F381),ISNUMBER(E381),E381&gt;0,F381&gt;E381),(F381-E381)/E381,IF(AND(ISNUMBER(F381),ISNUMBER(E381),E381&gt;0,F381=E381),0,IF(AND(ISNUMBER(F381),ISNUMBER(E381),E381&gt;0,F381=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K381" s="50" t="str">
-        <x:f>IF(A381="","",IF(AND(ISNUMBER(E381),E381=0,OR(ISNUMBER(SEARCH("Free",D381&amp;"")),AND(ISNUMBER(F381),F381=0))),"Subscription",IF(ISNUMBER(G381),"Profit",IF(ISNUMBER(I381),"Loss",IF(ISNUMBER(H381),"Draw",IF(AND(ISNUMBER(F381),ISNUMBER(E381),E381&gt;0,F381&gt;E381),"Profit",IF(AND(ISNUMBER(F381),ISNUMBER(E381),E381&gt;0,F381=E381),"Draw",IF(AND(ISNUMBER(F381),ISNUMBER(E381),E381&gt;0,F381=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A381="","",IF(AND(ISNUMBER(E381),E381=0,OR(ISNUMBER(SEARCH("Free",D381&amp;"")),AND(ISNUMBER(F381),F381=0))),"Subscription",IF(ISNUMBER(G381),"Profit",IF(ISNUMBER(I381),"Disqualified",IF(ISNUMBER(H381),"Draw",IF(AND(ISNUMBER(F381),ISNUMBER(E381),E381&gt;0,F381&gt;E381),"Profit",IF(AND(ISNUMBER(F381),ISNUMBER(E381),E381&gt;0,F381=E381),"Draw",IF(AND(ISNUMBER(F381),ISNUMBER(E381),E381&gt;0,F381=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L381" s="50"/>
       <x:c r="M381" s="58"/>
@@ -15492,7 +15505,7 @@
         <x:f>IF(A382="","",IF(K382="Subscription","",IF(E382=0,"",IF(ISNUMBER(G382),G382/E382,IF(ISNUMBER(I382),-ABS(I382)/E382,IF(ISNUMBER(H382),0,IF(AND(ISNUMBER(F382),ISNUMBER(E382),E382&gt;0,F382&gt;E382),(F382-E382)/E382,IF(AND(ISNUMBER(F382),ISNUMBER(E382),E382&gt;0,F382=E382),0,IF(AND(ISNUMBER(F382),ISNUMBER(E382),E382&gt;0,F382=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K382" s="50" t="str">
-        <x:f>IF(A382="","",IF(AND(ISNUMBER(E382),E382=0,OR(ISNUMBER(SEARCH("Free",D382&amp;"")),AND(ISNUMBER(F382),F382=0))),"Subscription",IF(ISNUMBER(G382),"Profit",IF(ISNUMBER(I382),"Loss",IF(ISNUMBER(H382),"Draw",IF(AND(ISNUMBER(F382),ISNUMBER(E382),E382&gt;0,F382&gt;E382),"Profit",IF(AND(ISNUMBER(F382),ISNUMBER(E382),E382&gt;0,F382=E382),"Draw",IF(AND(ISNUMBER(F382),ISNUMBER(E382),E382&gt;0,F382=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A382="","",IF(AND(ISNUMBER(E382),E382=0,OR(ISNUMBER(SEARCH("Free",D382&amp;"")),AND(ISNUMBER(F382),F382=0))),"Subscription",IF(ISNUMBER(G382),"Profit",IF(ISNUMBER(I382),"Disqualified",IF(ISNUMBER(H382),"Draw",IF(AND(ISNUMBER(F382),ISNUMBER(E382),E382&gt;0,F382&gt;E382),"Profit",IF(AND(ISNUMBER(F382),ISNUMBER(E382),E382&gt;0,F382=E382),"Draw",IF(AND(ISNUMBER(F382),ISNUMBER(E382),E382&gt;0,F382=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L382" s="50"/>
       <x:c r="M382" s="58"/>
@@ -15529,7 +15542,7 @@
         <x:f>IF(A383="","",IF(K383="Subscription","",IF(E383=0,"",IF(ISNUMBER(G383),G383/E383,IF(ISNUMBER(I383),-ABS(I383)/E383,IF(ISNUMBER(H383),0,IF(AND(ISNUMBER(F383),ISNUMBER(E383),E383&gt;0,F383&gt;E383),(F383-E383)/E383,IF(AND(ISNUMBER(F383),ISNUMBER(E383),E383&gt;0,F383=E383),0,IF(AND(ISNUMBER(F383),ISNUMBER(E383),E383&gt;0,F383=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K383" s="50" t="str">
-        <x:f>IF(A383="","",IF(AND(ISNUMBER(E383),E383=0,OR(ISNUMBER(SEARCH("Free",D383&amp;"")),AND(ISNUMBER(F383),F383=0))),"Subscription",IF(ISNUMBER(G383),"Profit",IF(ISNUMBER(I383),"Loss",IF(ISNUMBER(H383),"Draw",IF(AND(ISNUMBER(F383),ISNUMBER(E383),E383&gt;0,F383&gt;E383),"Profit",IF(AND(ISNUMBER(F383),ISNUMBER(E383),E383&gt;0,F383=E383),"Draw",IF(AND(ISNUMBER(F383),ISNUMBER(E383),E383&gt;0,F383=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A383="","",IF(AND(ISNUMBER(E383),E383=0,OR(ISNUMBER(SEARCH("Free",D383&amp;"")),AND(ISNUMBER(F383),F383=0))),"Subscription",IF(ISNUMBER(G383),"Profit",IF(ISNUMBER(I383),"Disqualified",IF(ISNUMBER(H383),"Draw",IF(AND(ISNUMBER(F383),ISNUMBER(E383),E383&gt;0,F383&gt;E383),"Profit",IF(AND(ISNUMBER(F383),ISNUMBER(E383),E383&gt;0,F383=E383),"Draw",IF(AND(ISNUMBER(F383),ISNUMBER(E383),E383&gt;0,F383=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L383" s="50"/>
       <x:c r="M383" s="58"/>
@@ -15566,7 +15579,7 @@
         <x:f>IF(A384="","",IF(K384="Subscription","",IF(E384=0,"",IF(ISNUMBER(G384),G384/E384,IF(ISNUMBER(I384),-ABS(I384)/E384,IF(ISNUMBER(H384),0,IF(AND(ISNUMBER(F384),ISNUMBER(E384),E384&gt;0,F384&gt;E384),(F384-E384)/E384,IF(AND(ISNUMBER(F384),ISNUMBER(E384),E384&gt;0,F384=E384),0,IF(AND(ISNUMBER(F384),ISNUMBER(E384),E384&gt;0,F384=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K384" s="50" t="str">
-        <x:f>IF(A384="","",IF(AND(ISNUMBER(E384),E384=0,OR(ISNUMBER(SEARCH("Free",D384&amp;"")),AND(ISNUMBER(F384),F384=0))),"Subscription",IF(ISNUMBER(G384),"Profit",IF(ISNUMBER(I384),"Loss",IF(ISNUMBER(H384),"Draw",IF(AND(ISNUMBER(F384),ISNUMBER(E384),E384&gt;0,F384&gt;E384),"Profit",IF(AND(ISNUMBER(F384),ISNUMBER(E384),E384&gt;0,F384=E384),"Draw",IF(AND(ISNUMBER(F384),ISNUMBER(E384),E384&gt;0,F384=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A384="","",IF(AND(ISNUMBER(E384),E384=0,OR(ISNUMBER(SEARCH("Free",D384&amp;"")),AND(ISNUMBER(F384),F384=0))),"Subscription",IF(ISNUMBER(G384),"Profit",IF(ISNUMBER(I384),"Disqualified",IF(ISNUMBER(H384),"Draw",IF(AND(ISNUMBER(F384),ISNUMBER(E384),E384&gt;0,F384&gt;E384),"Profit",IF(AND(ISNUMBER(F384),ISNUMBER(E384),E384&gt;0,F384=E384),"Draw",IF(AND(ISNUMBER(F384),ISNUMBER(E384),E384&gt;0,F384=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L384" s="50"/>
       <x:c r="M384" s="58"/>
@@ -15603,7 +15616,7 @@
         <x:f>IF(A385="","",IF(K385="Subscription","",IF(E385=0,"",IF(ISNUMBER(G385),G385/E385,IF(ISNUMBER(I385),-ABS(I385)/E385,IF(ISNUMBER(H385),0,IF(AND(ISNUMBER(F385),ISNUMBER(E385),E385&gt;0,F385&gt;E385),(F385-E385)/E385,IF(AND(ISNUMBER(F385),ISNUMBER(E385),E385&gt;0,F385=E385),0,IF(AND(ISNUMBER(F385),ISNUMBER(E385),E385&gt;0,F385=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K385" s="50" t="str">
-        <x:f>IF(A385="","",IF(AND(ISNUMBER(E385),E385=0,OR(ISNUMBER(SEARCH("Free",D385&amp;"")),AND(ISNUMBER(F385),F385=0))),"Subscription",IF(ISNUMBER(G385),"Profit",IF(ISNUMBER(I385),"Loss",IF(ISNUMBER(H385),"Draw",IF(AND(ISNUMBER(F385),ISNUMBER(E385),E385&gt;0,F385&gt;E385),"Profit",IF(AND(ISNUMBER(F385),ISNUMBER(E385),E385&gt;0,F385=E385),"Draw",IF(AND(ISNUMBER(F385),ISNUMBER(E385),E385&gt;0,F385=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A385="","",IF(AND(ISNUMBER(E385),E385=0,OR(ISNUMBER(SEARCH("Free",D385&amp;"")),AND(ISNUMBER(F385),F385=0))),"Subscription",IF(ISNUMBER(G385),"Profit",IF(ISNUMBER(I385),"Disqualified",IF(ISNUMBER(H385),"Draw",IF(AND(ISNUMBER(F385),ISNUMBER(E385),E385&gt;0,F385&gt;E385),"Profit",IF(AND(ISNUMBER(F385),ISNUMBER(E385),E385&gt;0,F385=E385),"Draw",IF(AND(ISNUMBER(F385),ISNUMBER(E385),E385&gt;0,F385=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L385" s="50"/>
       <x:c r="M385" s="58"/>
@@ -15640,7 +15653,7 @@
         <x:f>IF(A386="","",IF(K386="Subscription","",IF(E386=0,"",IF(ISNUMBER(G386),G386/E386,IF(ISNUMBER(I386),-ABS(I386)/E386,IF(ISNUMBER(H386),0,IF(AND(ISNUMBER(F386),ISNUMBER(E386),E386&gt;0,F386&gt;E386),(F386-E386)/E386,IF(AND(ISNUMBER(F386),ISNUMBER(E386),E386&gt;0,F386=E386),0,IF(AND(ISNUMBER(F386),ISNUMBER(E386),E386&gt;0,F386=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K386" s="50" t="str">
-        <x:f>IF(A386="","",IF(AND(ISNUMBER(E386),E386=0,OR(ISNUMBER(SEARCH("Free",D386&amp;"")),AND(ISNUMBER(F386),F386=0))),"Subscription",IF(ISNUMBER(G386),"Profit",IF(ISNUMBER(I386),"Loss",IF(ISNUMBER(H386),"Draw",IF(AND(ISNUMBER(F386),ISNUMBER(E386),E386&gt;0,F386&gt;E386),"Profit",IF(AND(ISNUMBER(F386),ISNUMBER(E386),E386&gt;0,F386=E386),"Draw",IF(AND(ISNUMBER(F386),ISNUMBER(E386),E386&gt;0,F386=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A386="","",IF(AND(ISNUMBER(E386),E386=0,OR(ISNUMBER(SEARCH("Free",D386&amp;"")),AND(ISNUMBER(F386),F386=0))),"Subscription",IF(ISNUMBER(G386),"Profit",IF(ISNUMBER(I386),"Disqualified",IF(ISNUMBER(H386),"Draw",IF(AND(ISNUMBER(F386),ISNUMBER(E386),E386&gt;0,F386&gt;E386),"Profit",IF(AND(ISNUMBER(F386),ISNUMBER(E386),E386&gt;0,F386=E386),"Draw",IF(AND(ISNUMBER(F386),ISNUMBER(E386),E386&gt;0,F386=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L386" s="50"/>
       <x:c r="M386" s="58"/>
@@ -15677,7 +15690,7 @@
         <x:f>IF(A387="","",IF(K387="Subscription","",IF(E387=0,"",IF(ISNUMBER(G387),G387/E387,IF(ISNUMBER(I387),-ABS(I387)/E387,IF(ISNUMBER(H387),0,IF(AND(ISNUMBER(F387),ISNUMBER(E387),E387&gt;0,F387&gt;E387),(F387-E387)/E387,IF(AND(ISNUMBER(F387),ISNUMBER(E387),E387&gt;0,F387=E387),0,IF(AND(ISNUMBER(F387),ISNUMBER(E387),E387&gt;0,F387=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K387" s="50" t="str">
-        <x:f>IF(A387="","",IF(AND(ISNUMBER(E387),E387=0,OR(ISNUMBER(SEARCH("Free",D387&amp;"")),AND(ISNUMBER(F387),F387=0))),"Subscription",IF(ISNUMBER(G387),"Profit",IF(ISNUMBER(I387),"Loss",IF(ISNUMBER(H387),"Draw",IF(AND(ISNUMBER(F387),ISNUMBER(E387),E387&gt;0,F387&gt;E387),"Profit",IF(AND(ISNUMBER(F387),ISNUMBER(E387),E387&gt;0,F387=E387),"Draw",IF(AND(ISNUMBER(F387),ISNUMBER(E387),E387&gt;0,F387=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A387="","",IF(AND(ISNUMBER(E387),E387=0,OR(ISNUMBER(SEARCH("Free",D387&amp;"")),AND(ISNUMBER(F387),F387=0))),"Subscription",IF(ISNUMBER(G387),"Profit",IF(ISNUMBER(I387),"Disqualified",IF(ISNUMBER(H387),"Draw",IF(AND(ISNUMBER(F387),ISNUMBER(E387),E387&gt;0,F387&gt;E387),"Profit",IF(AND(ISNUMBER(F387),ISNUMBER(E387),E387&gt;0,F387=E387),"Draw",IF(AND(ISNUMBER(F387),ISNUMBER(E387),E387&gt;0,F387=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L387" s="50"/>
       <x:c r="M387" s="58"/>
@@ -15714,7 +15727,7 @@
         <x:f>IF(A388="","",IF(K388="Subscription","",IF(E388=0,"",IF(ISNUMBER(G388),G388/E388,IF(ISNUMBER(I388),-ABS(I388)/E388,IF(ISNUMBER(H388),0,IF(AND(ISNUMBER(F388),ISNUMBER(E388),E388&gt;0,F388&gt;E388),(F388-E388)/E388,IF(AND(ISNUMBER(F388),ISNUMBER(E388),E388&gt;0,F388=E388),0,IF(AND(ISNUMBER(F388),ISNUMBER(E388),E388&gt;0,F388=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K388" s="50" t="str">
-        <x:f>IF(A388="","",IF(AND(ISNUMBER(E388),E388=0,OR(ISNUMBER(SEARCH("Free",D388&amp;"")),AND(ISNUMBER(F388),F388=0))),"Subscription",IF(ISNUMBER(G388),"Profit",IF(ISNUMBER(I388),"Loss",IF(ISNUMBER(H388),"Draw",IF(AND(ISNUMBER(F388),ISNUMBER(E388),E388&gt;0,F388&gt;E388),"Profit",IF(AND(ISNUMBER(F388),ISNUMBER(E388),E388&gt;0,F388=E388),"Draw",IF(AND(ISNUMBER(F388),ISNUMBER(E388),E388&gt;0,F388=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A388="","",IF(AND(ISNUMBER(E388),E388=0,OR(ISNUMBER(SEARCH("Free",D388&amp;"")),AND(ISNUMBER(F388),F388=0))),"Subscription",IF(ISNUMBER(G388),"Profit",IF(ISNUMBER(I388),"Disqualified",IF(ISNUMBER(H388),"Draw",IF(AND(ISNUMBER(F388),ISNUMBER(E388),E388&gt;0,F388&gt;E388),"Profit",IF(AND(ISNUMBER(F388),ISNUMBER(E388),E388&gt;0,F388=E388),"Draw",IF(AND(ISNUMBER(F388),ISNUMBER(E388),E388&gt;0,F388=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L388" s="50"/>
       <x:c r="M388" s="58"/>
@@ -15751,7 +15764,7 @@
         <x:f>IF(A389="","",IF(K389="Subscription","",IF(E389=0,"",IF(ISNUMBER(G389),G389/E389,IF(ISNUMBER(I389),-ABS(I389)/E389,IF(ISNUMBER(H389),0,IF(AND(ISNUMBER(F389),ISNUMBER(E389),E389&gt;0,F389&gt;E389),(F389-E389)/E389,IF(AND(ISNUMBER(F389),ISNUMBER(E389),E389&gt;0,F389=E389),0,IF(AND(ISNUMBER(F389),ISNUMBER(E389),E389&gt;0,F389=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K389" s="50" t="str">
-        <x:f>IF(A389="","",IF(AND(ISNUMBER(E389),E389=0,OR(ISNUMBER(SEARCH("Free",D389&amp;"")),AND(ISNUMBER(F389),F389=0))),"Subscription",IF(ISNUMBER(G389),"Profit",IF(ISNUMBER(I389),"Loss",IF(ISNUMBER(H389),"Draw",IF(AND(ISNUMBER(F389),ISNUMBER(E389),E389&gt;0,F389&gt;E389),"Profit",IF(AND(ISNUMBER(F389),ISNUMBER(E389),E389&gt;0,F389=E389),"Draw",IF(AND(ISNUMBER(F389),ISNUMBER(E389),E389&gt;0,F389=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A389="","",IF(AND(ISNUMBER(E389),E389=0,OR(ISNUMBER(SEARCH("Free",D389&amp;"")),AND(ISNUMBER(F389),F389=0))),"Subscription",IF(ISNUMBER(G389),"Profit",IF(ISNUMBER(I389),"Disqualified",IF(ISNUMBER(H389),"Draw",IF(AND(ISNUMBER(F389),ISNUMBER(E389),E389&gt;0,F389&gt;E389),"Profit",IF(AND(ISNUMBER(F389),ISNUMBER(E389),E389&gt;0,F389=E389),"Draw",IF(AND(ISNUMBER(F389),ISNUMBER(E389),E389&gt;0,F389=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L389" s="50"/>
       <x:c r="M389" s="58"/>
@@ -15788,7 +15801,7 @@
         <x:f>IF(A390="","",IF(K390="Subscription","",IF(E390=0,"",IF(ISNUMBER(G390),G390/E390,IF(ISNUMBER(I390),-ABS(I390)/E390,IF(ISNUMBER(H390),0,IF(AND(ISNUMBER(F390),ISNUMBER(E390),E390&gt;0,F390&gt;E390),(F390-E390)/E390,IF(AND(ISNUMBER(F390),ISNUMBER(E390),E390&gt;0,F390=E390),0,IF(AND(ISNUMBER(F390),ISNUMBER(E390),E390&gt;0,F390=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K390" s="50" t="str">
-        <x:f>IF(A390="","",IF(AND(ISNUMBER(E390),E390=0,OR(ISNUMBER(SEARCH("Free",D390&amp;"")),AND(ISNUMBER(F390),F390=0))),"Subscription",IF(ISNUMBER(G390),"Profit",IF(ISNUMBER(I390),"Loss",IF(ISNUMBER(H390),"Draw",IF(AND(ISNUMBER(F390),ISNUMBER(E390),E390&gt;0,F390&gt;E390),"Profit",IF(AND(ISNUMBER(F390),ISNUMBER(E390),E390&gt;0,F390=E390),"Draw",IF(AND(ISNUMBER(F390),ISNUMBER(E390),E390&gt;0,F390=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A390="","",IF(AND(ISNUMBER(E390),E390=0,OR(ISNUMBER(SEARCH("Free",D390&amp;"")),AND(ISNUMBER(F390),F390=0))),"Subscription",IF(ISNUMBER(G390),"Profit",IF(ISNUMBER(I390),"Disqualified",IF(ISNUMBER(H390),"Draw",IF(AND(ISNUMBER(F390),ISNUMBER(E390),E390&gt;0,F390&gt;E390),"Profit",IF(AND(ISNUMBER(F390),ISNUMBER(E390),E390&gt;0,F390=E390),"Draw",IF(AND(ISNUMBER(F390),ISNUMBER(E390),E390&gt;0,F390=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L390" s="50"/>
       <x:c r="M390" s="58"/>
@@ -15825,7 +15838,7 @@
         <x:f>IF(A391="","",IF(K391="Subscription","",IF(E391=0,"",IF(ISNUMBER(G391),G391/E391,IF(ISNUMBER(I391),-ABS(I391)/E391,IF(ISNUMBER(H391),0,IF(AND(ISNUMBER(F391),ISNUMBER(E391),E391&gt;0,F391&gt;E391),(F391-E391)/E391,IF(AND(ISNUMBER(F391),ISNUMBER(E391),E391&gt;0,F391=E391),0,IF(AND(ISNUMBER(F391),ISNUMBER(E391),E391&gt;0,F391=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K391" s="50" t="str">
-        <x:f>IF(A391="","",IF(AND(ISNUMBER(E391),E391=0,OR(ISNUMBER(SEARCH("Free",D391&amp;"")),AND(ISNUMBER(F391),F391=0))),"Subscription",IF(ISNUMBER(G391),"Profit",IF(ISNUMBER(I391),"Loss",IF(ISNUMBER(H391),"Draw",IF(AND(ISNUMBER(F391),ISNUMBER(E391),E391&gt;0,F391&gt;E391),"Profit",IF(AND(ISNUMBER(F391),ISNUMBER(E391),E391&gt;0,F391=E391),"Draw",IF(AND(ISNUMBER(F391),ISNUMBER(E391),E391&gt;0,F391=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A391="","",IF(AND(ISNUMBER(E391),E391=0,OR(ISNUMBER(SEARCH("Free",D391&amp;"")),AND(ISNUMBER(F391),F391=0))),"Subscription",IF(ISNUMBER(G391),"Profit",IF(ISNUMBER(I391),"Disqualified",IF(ISNUMBER(H391),"Draw",IF(AND(ISNUMBER(F391),ISNUMBER(E391),E391&gt;0,F391&gt;E391),"Profit",IF(AND(ISNUMBER(F391),ISNUMBER(E391),E391&gt;0,F391=E391),"Draw",IF(AND(ISNUMBER(F391),ISNUMBER(E391),E391&gt;0,F391=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L391" s="50"/>
       <x:c r="M391" s="58"/>
@@ -15862,7 +15875,7 @@
         <x:f>IF(A392="","",IF(K392="Subscription","",IF(E392=0,"",IF(ISNUMBER(G392),G392/E392,IF(ISNUMBER(I392),-ABS(I392)/E392,IF(ISNUMBER(H392),0,IF(AND(ISNUMBER(F392),ISNUMBER(E392),E392&gt;0,F392&gt;E392),(F392-E392)/E392,IF(AND(ISNUMBER(F392),ISNUMBER(E392),E392&gt;0,F392=E392),0,IF(AND(ISNUMBER(F392),ISNUMBER(E392),E392&gt;0,F392=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K392" s="50" t="str">
-        <x:f>IF(A392="","",IF(AND(ISNUMBER(E392),E392=0,OR(ISNUMBER(SEARCH("Free",D392&amp;"")),AND(ISNUMBER(F392),F392=0))),"Subscription",IF(ISNUMBER(G392),"Profit",IF(ISNUMBER(I392),"Loss",IF(ISNUMBER(H392),"Draw",IF(AND(ISNUMBER(F392),ISNUMBER(E392),E392&gt;0,F392&gt;E392),"Profit",IF(AND(ISNUMBER(F392),ISNUMBER(E392),E392&gt;0,F392=E392),"Draw",IF(AND(ISNUMBER(F392),ISNUMBER(E392),E392&gt;0,F392=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A392="","",IF(AND(ISNUMBER(E392),E392=0,OR(ISNUMBER(SEARCH("Free",D392&amp;"")),AND(ISNUMBER(F392),F392=0))),"Subscription",IF(ISNUMBER(G392),"Profit",IF(ISNUMBER(I392),"Disqualified",IF(ISNUMBER(H392),"Draw",IF(AND(ISNUMBER(F392),ISNUMBER(E392),E392&gt;0,F392&gt;E392),"Profit",IF(AND(ISNUMBER(F392),ISNUMBER(E392),E392&gt;0,F392=E392),"Draw",IF(AND(ISNUMBER(F392),ISNUMBER(E392),E392&gt;0,F392=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L392" s="50"/>
       <x:c r="M392" s="58"/>
@@ -15899,7 +15912,7 @@
         <x:f>IF(A393="","",IF(K393="Subscription","",IF(E393=0,"",IF(ISNUMBER(G393),G393/E393,IF(ISNUMBER(I393),-ABS(I393)/E393,IF(ISNUMBER(H393),0,IF(AND(ISNUMBER(F393),ISNUMBER(E393),E393&gt;0,F393&gt;E393),(F393-E393)/E393,IF(AND(ISNUMBER(F393),ISNUMBER(E393),E393&gt;0,F393=E393),0,IF(AND(ISNUMBER(F393),ISNUMBER(E393),E393&gt;0,F393=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K393" s="50" t="str">
-        <x:f>IF(A393="","",IF(AND(ISNUMBER(E393),E393=0,OR(ISNUMBER(SEARCH("Free",D393&amp;"")),AND(ISNUMBER(F393),F393=0))),"Subscription",IF(ISNUMBER(G393),"Profit",IF(ISNUMBER(I393),"Loss",IF(ISNUMBER(H393),"Draw",IF(AND(ISNUMBER(F393),ISNUMBER(E393),E393&gt;0,F393&gt;E393),"Profit",IF(AND(ISNUMBER(F393),ISNUMBER(E393),E393&gt;0,F393=E393),"Draw",IF(AND(ISNUMBER(F393),ISNUMBER(E393),E393&gt;0,F393=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A393="","",IF(AND(ISNUMBER(E393),E393=0,OR(ISNUMBER(SEARCH("Free",D393&amp;"")),AND(ISNUMBER(F393),F393=0))),"Subscription",IF(ISNUMBER(G393),"Profit",IF(ISNUMBER(I393),"Disqualified",IF(ISNUMBER(H393),"Draw",IF(AND(ISNUMBER(F393),ISNUMBER(E393),E393&gt;0,F393&gt;E393),"Profit",IF(AND(ISNUMBER(F393),ISNUMBER(E393),E393&gt;0,F393=E393),"Draw",IF(AND(ISNUMBER(F393),ISNUMBER(E393),E393&gt;0,F393=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L393" s="50"/>
       <x:c r="M393" s="58"/>
@@ -15936,7 +15949,7 @@
         <x:f>IF(A394="","",IF(K394="Subscription","",IF(E394=0,"",IF(ISNUMBER(G394),G394/E394,IF(ISNUMBER(I394),-ABS(I394)/E394,IF(ISNUMBER(H394),0,IF(AND(ISNUMBER(F394),ISNUMBER(E394),E394&gt;0,F394&gt;E394),(F394-E394)/E394,IF(AND(ISNUMBER(F394),ISNUMBER(E394),E394&gt;0,F394=E394),0,IF(AND(ISNUMBER(F394),ISNUMBER(E394),E394&gt;0,F394=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K394" s="50" t="str">
-        <x:f>IF(A394="","",IF(AND(ISNUMBER(E394),E394=0,OR(ISNUMBER(SEARCH("Free",D394&amp;"")),AND(ISNUMBER(F394),F394=0))),"Subscription",IF(ISNUMBER(G394),"Profit",IF(ISNUMBER(I394),"Loss",IF(ISNUMBER(H394),"Draw",IF(AND(ISNUMBER(F394),ISNUMBER(E394),E394&gt;0,F394&gt;E394),"Profit",IF(AND(ISNUMBER(F394),ISNUMBER(E394),E394&gt;0,F394=E394),"Draw",IF(AND(ISNUMBER(F394),ISNUMBER(E394),E394&gt;0,F394=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A394="","",IF(AND(ISNUMBER(E394),E394=0,OR(ISNUMBER(SEARCH("Free",D394&amp;"")),AND(ISNUMBER(F394),F394=0))),"Subscription",IF(ISNUMBER(G394),"Profit",IF(ISNUMBER(I394),"Disqualified",IF(ISNUMBER(H394),"Draw",IF(AND(ISNUMBER(F394),ISNUMBER(E394),E394&gt;0,F394&gt;E394),"Profit",IF(AND(ISNUMBER(F394),ISNUMBER(E394),E394&gt;0,F394=E394),"Draw",IF(AND(ISNUMBER(F394),ISNUMBER(E394),E394&gt;0,F394=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L394" s="50"/>
       <x:c r="M394" s="58"/>
@@ -15973,7 +15986,7 @@
         <x:f>IF(A395="","",IF(K395="Subscription","",IF(E395=0,"",IF(ISNUMBER(G395),G395/E395,IF(ISNUMBER(I395),-ABS(I395)/E395,IF(ISNUMBER(H395),0,IF(AND(ISNUMBER(F395),ISNUMBER(E395),E395&gt;0,F395&gt;E395),(F395-E395)/E395,IF(AND(ISNUMBER(F395),ISNUMBER(E395),E395&gt;0,F395=E395),0,IF(AND(ISNUMBER(F395),ISNUMBER(E395),E395&gt;0,F395=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K395" s="50" t="str">
-        <x:f>IF(A395="","",IF(AND(ISNUMBER(E395),E395=0,OR(ISNUMBER(SEARCH("Free",D395&amp;"")),AND(ISNUMBER(F395),F395=0))),"Subscription",IF(ISNUMBER(G395),"Profit",IF(ISNUMBER(I395),"Loss",IF(ISNUMBER(H395),"Draw",IF(AND(ISNUMBER(F395),ISNUMBER(E395),E395&gt;0,F395&gt;E395),"Profit",IF(AND(ISNUMBER(F395),ISNUMBER(E395),E395&gt;0,F395=E395),"Draw",IF(AND(ISNUMBER(F395),ISNUMBER(E395),E395&gt;0,F395=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A395="","",IF(AND(ISNUMBER(E395),E395=0,OR(ISNUMBER(SEARCH("Free",D395&amp;"")),AND(ISNUMBER(F395),F395=0))),"Subscription",IF(ISNUMBER(G395),"Profit",IF(ISNUMBER(I395),"Disqualified",IF(ISNUMBER(H395),"Draw",IF(AND(ISNUMBER(F395),ISNUMBER(E395),E395&gt;0,F395&gt;E395),"Profit",IF(AND(ISNUMBER(F395),ISNUMBER(E395),E395&gt;0,F395=E395),"Draw",IF(AND(ISNUMBER(F395),ISNUMBER(E395),E395&gt;0,F395=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L395" s="50"/>
       <x:c r="M395" s="58"/>
@@ -16010,7 +16023,7 @@
         <x:f>IF(A396="","",IF(K396="Subscription","",IF(E396=0,"",IF(ISNUMBER(G396),G396/E396,IF(ISNUMBER(I396),-ABS(I396)/E396,IF(ISNUMBER(H396),0,IF(AND(ISNUMBER(F396),ISNUMBER(E396),E396&gt;0,F396&gt;E396),(F396-E396)/E396,IF(AND(ISNUMBER(F396),ISNUMBER(E396),E396&gt;0,F396=E396),0,IF(AND(ISNUMBER(F396),ISNUMBER(E396),E396&gt;0,F396=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K396" s="50" t="str">
-        <x:f>IF(A396="","",IF(AND(ISNUMBER(E396),E396=0,OR(ISNUMBER(SEARCH("Free",D396&amp;"")),AND(ISNUMBER(F396),F396=0))),"Subscription",IF(ISNUMBER(G396),"Profit",IF(ISNUMBER(I396),"Loss",IF(ISNUMBER(H396),"Draw",IF(AND(ISNUMBER(F396),ISNUMBER(E396),E396&gt;0,F396&gt;E396),"Profit",IF(AND(ISNUMBER(F396),ISNUMBER(E396),E396&gt;0,F396=E396),"Draw",IF(AND(ISNUMBER(F396),ISNUMBER(E396),E396&gt;0,F396=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A396="","",IF(AND(ISNUMBER(E396),E396=0,OR(ISNUMBER(SEARCH("Free",D396&amp;"")),AND(ISNUMBER(F396),F396=0))),"Subscription",IF(ISNUMBER(G396),"Profit",IF(ISNUMBER(I396),"Disqualified",IF(ISNUMBER(H396),"Draw",IF(AND(ISNUMBER(F396),ISNUMBER(E396),E396&gt;0,F396&gt;E396),"Profit",IF(AND(ISNUMBER(F396),ISNUMBER(E396),E396&gt;0,F396=E396),"Draw",IF(AND(ISNUMBER(F396),ISNUMBER(E396),E396&gt;0,F396=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L396" s="50"/>
       <x:c r="M396" s="58"/>
@@ -16047,7 +16060,7 @@
         <x:f>IF(A397="","",IF(K397="Subscription","",IF(E397=0,"",IF(ISNUMBER(G397),G397/E397,IF(ISNUMBER(I397),-ABS(I397)/E397,IF(ISNUMBER(H397),0,IF(AND(ISNUMBER(F397),ISNUMBER(E397),E397&gt;0,F397&gt;E397),(F397-E397)/E397,IF(AND(ISNUMBER(F397),ISNUMBER(E397),E397&gt;0,F397=E397),0,IF(AND(ISNUMBER(F397),ISNUMBER(E397),E397&gt;0,F397=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K397" s="50" t="str">
-        <x:f>IF(A397="","",IF(AND(ISNUMBER(E397),E397=0,OR(ISNUMBER(SEARCH("Free",D397&amp;"")),AND(ISNUMBER(F397),F397=0))),"Subscription",IF(ISNUMBER(G397),"Profit",IF(ISNUMBER(I397),"Loss",IF(ISNUMBER(H397),"Draw",IF(AND(ISNUMBER(F397),ISNUMBER(E397),E397&gt;0,F397&gt;E397),"Profit",IF(AND(ISNUMBER(F397),ISNUMBER(E397),E397&gt;0,F397=E397),"Draw",IF(AND(ISNUMBER(F397),ISNUMBER(E397),E397&gt;0,F397=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A397="","",IF(AND(ISNUMBER(E397),E397=0,OR(ISNUMBER(SEARCH("Free",D397&amp;"")),AND(ISNUMBER(F397),F397=0))),"Subscription",IF(ISNUMBER(G397),"Profit",IF(ISNUMBER(I397),"Disqualified",IF(ISNUMBER(H397),"Draw",IF(AND(ISNUMBER(F397),ISNUMBER(E397),E397&gt;0,F397&gt;E397),"Profit",IF(AND(ISNUMBER(F397),ISNUMBER(E397),E397&gt;0,F397=E397),"Draw",IF(AND(ISNUMBER(F397),ISNUMBER(E397),E397&gt;0,F397=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L397" s="50"/>
       <x:c r="M397" s="58"/>
@@ -16084,7 +16097,7 @@
         <x:f>IF(A398="","",IF(K398="Subscription","",IF(E398=0,"",IF(ISNUMBER(G398),G398/E398,IF(ISNUMBER(I398),-ABS(I398)/E398,IF(ISNUMBER(H398),0,IF(AND(ISNUMBER(F398),ISNUMBER(E398),E398&gt;0,F398&gt;E398),(F398-E398)/E398,IF(AND(ISNUMBER(F398),ISNUMBER(E398),E398&gt;0,F398=E398),0,IF(AND(ISNUMBER(F398),ISNUMBER(E398),E398&gt;0,F398=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K398" s="50" t="str">
-        <x:f>IF(A398="","",IF(AND(ISNUMBER(E398),E398=0,OR(ISNUMBER(SEARCH("Free",D398&amp;"")),AND(ISNUMBER(F398),F398=0))),"Subscription",IF(ISNUMBER(G398),"Profit",IF(ISNUMBER(I398),"Loss",IF(ISNUMBER(H398),"Draw",IF(AND(ISNUMBER(F398),ISNUMBER(E398),E398&gt;0,F398&gt;E398),"Profit",IF(AND(ISNUMBER(F398),ISNUMBER(E398),E398&gt;0,F398=E398),"Draw",IF(AND(ISNUMBER(F398),ISNUMBER(E398),E398&gt;0,F398=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A398="","",IF(AND(ISNUMBER(E398),E398=0,OR(ISNUMBER(SEARCH("Free",D398&amp;"")),AND(ISNUMBER(F398),F398=0))),"Subscription",IF(ISNUMBER(G398),"Profit",IF(ISNUMBER(I398),"Disqualified",IF(ISNUMBER(H398),"Draw",IF(AND(ISNUMBER(F398),ISNUMBER(E398),E398&gt;0,F398&gt;E398),"Profit",IF(AND(ISNUMBER(F398),ISNUMBER(E398),E398&gt;0,F398=E398),"Draw",IF(AND(ISNUMBER(F398),ISNUMBER(E398),E398&gt;0,F398=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L398" s="50"/>
       <x:c r="M398" s="58"/>
@@ -16121,7 +16134,7 @@
         <x:f>IF(A399="","",IF(K399="Subscription","",IF(E399=0,"",IF(ISNUMBER(G399),G399/E399,IF(ISNUMBER(I399),-ABS(I399)/E399,IF(ISNUMBER(H399),0,IF(AND(ISNUMBER(F399),ISNUMBER(E399),E399&gt;0,F399&gt;E399),(F399-E399)/E399,IF(AND(ISNUMBER(F399),ISNUMBER(E399),E399&gt;0,F399=E399),0,IF(AND(ISNUMBER(F399),ISNUMBER(E399),E399&gt;0,F399=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K399" s="50" t="str">
-        <x:f>IF(A399="","",IF(AND(ISNUMBER(E399),E399=0,OR(ISNUMBER(SEARCH("Free",D399&amp;"")),AND(ISNUMBER(F399),F399=0))),"Subscription",IF(ISNUMBER(G399),"Profit",IF(ISNUMBER(I399),"Loss",IF(ISNUMBER(H399),"Draw",IF(AND(ISNUMBER(F399),ISNUMBER(E399),E399&gt;0,F399&gt;E399),"Profit",IF(AND(ISNUMBER(F399),ISNUMBER(E399),E399&gt;0,F399=E399),"Draw",IF(AND(ISNUMBER(F399),ISNUMBER(E399),E399&gt;0,F399=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A399="","",IF(AND(ISNUMBER(E399),E399=0,OR(ISNUMBER(SEARCH("Free",D399&amp;"")),AND(ISNUMBER(F399),F399=0))),"Subscription",IF(ISNUMBER(G399),"Profit",IF(ISNUMBER(I399),"Disqualified",IF(ISNUMBER(H399),"Draw",IF(AND(ISNUMBER(F399),ISNUMBER(E399),E399&gt;0,F399&gt;E399),"Profit",IF(AND(ISNUMBER(F399),ISNUMBER(E399),E399&gt;0,F399=E399),"Draw",IF(AND(ISNUMBER(F399),ISNUMBER(E399),E399&gt;0,F399=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L399" s="50"/>
       <x:c r="M399" s="58"/>
@@ -16158,7 +16171,7 @@
         <x:f>IF(A400="","",IF(K400="Subscription","",IF(E400=0,"",IF(ISNUMBER(G400),G400/E400,IF(ISNUMBER(I400),-ABS(I400)/E400,IF(ISNUMBER(H400),0,IF(AND(ISNUMBER(F400),ISNUMBER(E400),E400&gt;0,F400&gt;E400),(F400-E400)/E400,IF(AND(ISNUMBER(F400),ISNUMBER(E400),E400&gt;0,F400=E400),0,IF(AND(ISNUMBER(F400),ISNUMBER(E400),E400&gt;0,F400=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K400" s="50" t="str">
-        <x:f>IF(A400="","",IF(AND(ISNUMBER(E400),E400=0,OR(ISNUMBER(SEARCH("Free",D400&amp;"")),AND(ISNUMBER(F400),F400=0))),"Subscription",IF(ISNUMBER(G400),"Profit",IF(ISNUMBER(I400),"Loss",IF(ISNUMBER(H400),"Draw",IF(AND(ISNUMBER(F400),ISNUMBER(E400),E400&gt;0,F400&gt;E400),"Profit",IF(AND(ISNUMBER(F400),ISNUMBER(E400),E400&gt;0,F400=E400),"Draw",IF(AND(ISNUMBER(F400),ISNUMBER(E400),E400&gt;0,F400=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A400="","",IF(AND(ISNUMBER(E400),E400=0,OR(ISNUMBER(SEARCH("Free",D400&amp;"")),AND(ISNUMBER(F400),F400=0))),"Subscription",IF(ISNUMBER(G400),"Profit",IF(ISNUMBER(I400),"Disqualified",IF(ISNUMBER(H400),"Draw",IF(AND(ISNUMBER(F400),ISNUMBER(E400),E400&gt;0,F400&gt;E400),"Profit",IF(AND(ISNUMBER(F400),ISNUMBER(E400),E400&gt;0,F400=E400),"Draw",IF(AND(ISNUMBER(F400),ISNUMBER(E400),E400&gt;0,F400=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L400" s="50"/>
       <x:c r="M400" s="58"/>
@@ -16195,7 +16208,7 @@
         <x:f>IF(A401="","",IF(K401="Subscription","",IF(E401=0,"",IF(ISNUMBER(G401),G401/E401,IF(ISNUMBER(I401),-ABS(I401)/E401,IF(ISNUMBER(H401),0,IF(AND(ISNUMBER(F401),ISNUMBER(E401),E401&gt;0,F401&gt;E401),(F401-E401)/E401,IF(AND(ISNUMBER(F401),ISNUMBER(E401),E401&gt;0,F401=E401),0,IF(AND(ISNUMBER(F401),ISNUMBER(E401),E401&gt;0,F401=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K401" s="50" t="str">
-        <x:f>IF(A401="","",IF(AND(ISNUMBER(E401),E401=0,OR(ISNUMBER(SEARCH("Free",D401&amp;"")),AND(ISNUMBER(F401),F401=0))),"Subscription",IF(ISNUMBER(G401),"Profit",IF(ISNUMBER(I401),"Loss",IF(ISNUMBER(H401),"Draw",IF(AND(ISNUMBER(F401),ISNUMBER(E401),E401&gt;0,F401&gt;E401),"Profit",IF(AND(ISNUMBER(F401),ISNUMBER(E401),E401&gt;0,F401=E401),"Draw",IF(AND(ISNUMBER(F401),ISNUMBER(E401),E401&gt;0,F401=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A401="","",IF(AND(ISNUMBER(E401),E401=0,OR(ISNUMBER(SEARCH("Free",D401&amp;"")),AND(ISNUMBER(F401),F401=0))),"Subscription",IF(ISNUMBER(G401),"Profit",IF(ISNUMBER(I401),"Disqualified",IF(ISNUMBER(H401),"Draw",IF(AND(ISNUMBER(F401),ISNUMBER(E401),E401&gt;0,F401&gt;E401),"Profit",IF(AND(ISNUMBER(F401),ISNUMBER(E401),E401&gt;0,F401=E401),"Draw",IF(AND(ISNUMBER(F401),ISNUMBER(E401),E401&gt;0,F401=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L401" s="50"/>
       <x:c r="M401" s="58"/>
@@ -16232,7 +16245,7 @@
         <x:f>IF(A402="","",IF(K402="Subscription","",IF(E402=0,"",IF(ISNUMBER(G402),G402/E402,IF(ISNUMBER(I402),-ABS(I402)/E402,IF(ISNUMBER(H402),0,IF(AND(ISNUMBER(F402),ISNUMBER(E402),E402&gt;0,F402&gt;E402),(F402-E402)/E402,IF(AND(ISNUMBER(F402),ISNUMBER(E402),E402&gt;0,F402=E402),0,IF(AND(ISNUMBER(F402),ISNUMBER(E402),E402&gt;0,F402=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K402" s="50" t="str">
-        <x:f>IF(A402="","",IF(AND(ISNUMBER(E402),E402=0,OR(ISNUMBER(SEARCH("Free",D402&amp;"")),AND(ISNUMBER(F402),F402=0))),"Subscription",IF(ISNUMBER(G402),"Profit",IF(ISNUMBER(I402),"Loss",IF(ISNUMBER(H402),"Draw",IF(AND(ISNUMBER(F402),ISNUMBER(E402),E402&gt;0,F402&gt;E402),"Profit",IF(AND(ISNUMBER(F402),ISNUMBER(E402),E402&gt;0,F402=E402),"Draw",IF(AND(ISNUMBER(F402),ISNUMBER(E402),E402&gt;0,F402=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A402="","",IF(AND(ISNUMBER(E402),E402=0,OR(ISNUMBER(SEARCH("Free",D402&amp;"")),AND(ISNUMBER(F402),F402=0))),"Subscription",IF(ISNUMBER(G402),"Profit",IF(ISNUMBER(I402),"Disqualified",IF(ISNUMBER(H402),"Draw",IF(AND(ISNUMBER(F402),ISNUMBER(E402),E402&gt;0,F402&gt;E402),"Profit",IF(AND(ISNUMBER(F402),ISNUMBER(E402),E402&gt;0,F402=E402),"Draw",IF(AND(ISNUMBER(F402),ISNUMBER(E402),E402&gt;0,F402=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L402" s="50"/>
       <x:c r="M402" s="58"/>
@@ -16269,7 +16282,7 @@
         <x:f>IF(A403="","",IF(K403="Subscription","",IF(E403=0,"",IF(ISNUMBER(G403),G403/E403,IF(ISNUMBER(I403),-ABS(I403)/E403,IF(ISNUMBER(H403),0,IF(AND(ISNUMBER(F403),ISNUMBER(E403),E403&gt;0,F403&gt;E403),(F403-E403)/E403,IF(AND(ISNUMBER(F403),ISNUMBER(E403),E403&gt;0,F403=E403),0,IF(AND(ISNUMBER(F403),ISNUMBER(E403),E403&gt;0,F403=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K403" s="50" t="str">
-        <x:f>IF(A403="","",IF(AND(ISNUMBER(E403),E403=0,OR(ISNUMBER(SEARCH("Free",D403&amp;"")),AND(ISNUMBER(F403),F403=0))),"Subscription",IF(ISNUMBER(G403),"Profit",IF(ISNUMBER(I403),"Loss",IF(ISNUMBER(H403),"Draw",IF(AND(ISNUMBER(F403),ISNUMBER(E403),E403&gt;0,F403&gt;E403),"Profit",IF(AND(ISNUMBER(F403),ISNUMBER(E403),E403&gt;0,F403=E403),"Draw",IF(AND(ISNUMBER(F403),ISNUMBER(E403),E403&gt;0,F403=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A403="","",IF(AND(ISNUMBER(E403),E403=0,OR(ISNUMBER(SEARCH("Free",D403&amp;"")),AND(ISNUMBER(F403),F403=0))),"Subscription",IF(ISNUMBER(G403),"Profit",IF(ISNUMBER(I403),"Disqualified",IF(ISNUMBER(H403),"Draw",IF(AND(ISNUMBER(F403),ISNUMBER(E403),E403&gt;0,F403&gt;E403),"Profit",IF(AND(ISNUMBER(F403),ISNUMBER(E403),E403&gt;0,F403=E403),"Draw",IF(AND(ISNUMBER(F403),ISNUMBER(E403),E403&gt;0,F403=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L403" s="50"/>
       <x:c r="M403" s="58"/>
@@ -16306,7 +16319,7 @@
         <x:f>IF(A404="","",IF(K404="Subscription","",IF(E404=0,"",IF(ISNUMBER(G404),G404/E404,IF(ISNUMBER(I404),-ABS(I404)/E404,IF(ISNUMBER(H404),0,IF(AND(ISNUMBER(F404),ISNUMBER(E404),E404&gt;0,F404&gt;E404),(F404-E404)/E404,IF(AND(ISNUMBER(F404),ISNUMBER(E404),E404&gt;0,F404=E404),0,IF(AND(ISNUMBER(F404),ISNUMBER(E404),E404&gt;0,F404=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K404" s="50" t="str">
-        <x:f>IF(A404="","",IF(AND(ISNUMBER(E404),E404=0,OR(ISNUMBER(SEARCH("Free",D404&amp;"")),AND(ISNUMBER(F404),F404=0))),"Subscription",IF(ISNUMBER(G404),"Profit",IF(ISNUMBER(I404),"Loss",IF(ISNUMBER(H404),"Draw",IF(AND(ISNUMBER(F404),ISNUMBER(E404),E404&gt;0,F404&gt;E404),"Profit",IF(AND(ISNUMBER(F404),ISNUMBER(E404),E404&gt;0,F404=E404),"Draw",IF(AND(ISNUMBER(F404),ISNUMBER(E404),E404&gt;0,F404=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A404="","",IF(AND(ISNUMBER(E404),E404=0,OR(ISNUMBER(SEARCH("Free",D404&amp;"")),AND(ISNUMBER(F404),F404=0))),"Subscription",IF(ISNUMBER(G404),"Profit",IF(ISNUMBER(I404),"Disqualified",IF(ISNUMBER(H404),"Draw",IF(AND(ISNUMBER(F404),ISNUMBER(E404),E404&gt;0,F404&gt;E404),"Profit",IF(AND(ISNUMBER(F404),ISNUMBER(E404),E404&gt;0,F404=E404),"Draw",IF(AND(ISNUMBER(F404),ISNUMBER(E404),E404&gt;0,F404=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L404" s="50"/>
       <x:c r="M404" s="58"/>
@@ -16343,7 +16356,7 @@
         <x:f>IF(A405="","",IF(K405="Subscription","",IF(E405=0,"",IF(ISNUMBER(G405),G405/E405,IF(ISNUMBER(I405),-ABS(I405)/E405,IF(ISNUMBER(H405),0,IF(AND(ISNUMBER(F405),ISNUMBER(E405),E405&gt;0,F405&gt;E405),(F405-E405)/E405,IF(AND(ISNUMBER(F405),ISNUMBER(E405),E405&gt;0,F405=E405),0,IF(AND(ISNUMBER(F405),ISNUMBER(E405),E405&gt;0,F405=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K405" s="50" t="str">
-        <x:f>IF(A405="","",IF(AND(ISNUMBER(E405),E405=0,OR(ISNUMBER(SEARCH("Free",D405&amp;"")),AND(ISNUMBER(F405),F405=0))),"Subscription",IF(ISNUMBER(G405),"Profit",IF(ISNUMBER(I405),"Loss",IF(ISNUMBER(H405),"Draw",IF(AND(ISNUMBER(F405),ISNUMBER(E405),E405&gt;0,F405&gt;E405),"Profit",IF(AND(ISNUMBER(F405),ISNUMBER(E405),E405&gt;0,F405=E405),"Draw",IF(AND(ISNUMBER(F405),ISNUMBER(E405),E405&gt;0,F405=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A405="","",IF(AND(ISNUMBER(E405),E405=0,OR(ISNUMBER(SEARCH("Free",D405&amp;"")),AND(ISNUMBER(F405),F405=0))),"Subscription",IF(ISNUMBER(G405),"Profit",IF(ISNUMBER(I405),"Disqualified",IF(ISNUMBER(H405),"Draw",IF(AND(ISNUMBER(F405),ISNUMBER(E405),E405&gt;0,F405&gt;E405),"Profit",IF(AND(ISNUMBER(F405),ISNUMBER(E405),E405&gt;0,F405=E405),"Draw",IF(AND(ISNUMBER(F405),ISNUMBER(E405),E405&gt;0,F405=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L405" s="50"/>
       <x:c r="M405" s="58"/>
@@ -16380,7 +16393,7 @@
         <x:f>IF(A406="","",IF(K406="Subscription","",IF(E406=0,"",IF(ISNUMBER(G406),G406/E406,IF(ISNUMBER(I406),-ABS(I406)/E406,IF(ISNUMBER(H406),0,IF(AND(ISNUMBER(F406),ISNUMBER(E406),E406&gt;0,F406&gt;E406),(F406-E406)/E406,IF(AND(ISNUMBER(F406),ISNUMBER(E406),E406&gt;0,F406=E406),0,IF(AND(ISNUMBER(F406),ISNUMBER(E406),E406&gt;0,F406=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K406" s="50" t="str">
-        <x:f>IF(A406="","",IF(AND(ISNUMBER(E406),E406=0,OR(ISNUMBER(SEARCH("Free",D406&amp;"")),AND(ISNUMBER(F406),F406=0))),"Subscription",IF(ISNUMBER(G406),"Profit",IF(ISNUMBER(I406),"Loss",IF(ISNUMBER(H406),"Draw",IF(AND(ISNUMBER(F406),ISNUMBER(E406),E406&gt;0,F406&gt;E406),"Profit",IF(AND(ISNUMBER(F406),ISNUMBER(E406),E406&gt;0,F406=E406),"Draw",IF(AND(ISNUMBER(F406),ISNUMBER(E406),E406&gt;0,F406=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A406="","",IF(AND(ISNUMBER(E406),E406=0,OR(ISNUMBER(SEARCH("Free",D406&amp;"")),AND(ISNUMBER(F406),F406=0))),"Subscription",IF(ISNUMBER(G406),"Profit",IF(ISNUMBER(I406),"Disqualified",IF(ISNUMBER(H406),"Draw",IF(AND(ISNUMBER(F406),ISNUMBER(E406),E406&gt;0,F406&gt;E406),"Profit",IF(AND(ISNUMBER(F406),ISNUMBER(E406),E406&gt;0,F406=E406),"Draw",IF(AND(ISNUMBER(F406),ISNUMBER(E406),E406&gt;0,F406=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L406" s="50"/>
       <x:c r="M406" s="58"/>
@@ -16417,7 +16430,7 @@
         <x:f>IF(A407="","",IF(K407="Subscription","",IF(E407=0,"",IF(ISNUMBER(G407),G407/E407,IF(ISNUMBER(I407),-ABS(I407)/E407,IF(ISNUMBER(H407),0,IF(AND(ISNUMBER(F407),ISNUMBER(E407),E407&gt;0,F407&gt;E407),(F407-E407)/E407,IF(AND(ISNUMBER(F407),ISNUMBER(E407),E407&gt;0,F407=E407),0,IF(AND(ISNUMBER(F407),ISNUMBER(E407),E407&gt;0,F407=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K407" s="50" t="str">
-        <x:f>IF(A407="","",IF(AND(ISNUMBER(E407),E407=0,OR(ISNUMBER(SEARCH("Free",D407&amp;"")),AND(ISNUMBER(F407),F407=0))),"Subscription",IF(ISNUMBER(G407),"Profit",IF(ISNUMBER(I407),"Loss",IF(ISNUMBER(H407),"Draw",IF(AND(ISNUMBER(F407),ISNUMBER(E407),E407&gt;0,F407&gt;E407),"Profit",IF(AND(ISNUMBER(F407),ISNUMBER(E407),E407&gt;0,F407=E407),"Draw",IF(AND(ISNUMBER(F407),ISNUMBER(E407),E407&gt;0,F407=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A407="","",IF(AND(ISNUMBER(E407),E407=0,OR(ISNUMBER(SEARCH("Free",D407&amp;"")),AND(ISNUMBER(F407),F407=0))),"Subscription",IF(ISNUMBER(G407),"Profit",IF(ISNUMBER(I407),"Disqualified",IF(ISNUMBER(H407),"Draw",IF(AND(ISNUMBER(F407),ISNUMBER(E407),E407&gt;0,F407&gt;E407),"Profit",IF(AND(ISNUMBER(F407),ISNUMBER(E407),E407&gt;0,F407=E407),"Draw",IF(AND(ISNUMBER(F407),ISNUMBER(E407),E407&gt;0,F407=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L407" s="50"/>
       <x:c r="M407" s="58"/>
@@ -16454,7 +16467,7 @@
         <x:f>IF(A408="","",IF(K408="Subscription","",IF(E408=0,"",IF(ISNUMBER(G408),G408/E408,IF(ISNUMBER(I408),-ABS(I408)/E408,IF(ISNUMBER(H408),0,IF(AND(ISNUMBER(F408),ISNUMBER(E408),E408&gt;0,F408&gt;E408),(F408-E408)/E408,IF(AND(ISNUMBER(F408),ISNUMBER(E408),E408&gt;0,F408=E408),0,IF(AND(ISNUMBER(F408),ISNUMBER(E408),E408&gt;0,F408=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K408" s="50" t="str">
-        <x:f>IF(A408="","",IF(AND(ISNUMBER(E408),E408=0,OR(ISNUMBER(SEARCH("Free",D408&amp;"")),AND(ISNUMBER(F408),F408=0))),"Subscription",IF(ISNUMBER(G408),"Profit",IF(ISNUMBER(I408),"Loss",IF(ISNUMBER(H408),"Draw",IF(AND(ISNUMBER(F408),ISNUMBER(E408),E408&gt;0,F408&gt;E408),"Profit",IF(AND(ISNUMBER(F408),ISNUMBER(E408),E408&gt;0,F408=E408),"Draw",IF(AND(ISNUMBER(F408),ISNUMBER(E408),E408&gt;0,F408=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A408="","",IF(AND(ISNUMBER(E408),E408=0,OR(ISNUMBER(SEARCH("Free",D408&amp;"")),AND(ISNUMBER(F408),F408=0))),"Subscription",IF(ISNUMBER(G408),"Profit",IF(ISNUMBER(I408),"Disqualified",IF(ISNUMBER(H408),"Draw",IF(AND(ISNUMBER(F408),ISNUMBER(E408),E408&gt;0,F408&gt;E408),"Profit",IF(AND(ISNUMBER(F408),ISNUMBER(E408),E408&gt;0,F408=E408),"Draw",IF(AND(ISNUMBER(F408),ISNUMBER(E408),E408&gt;0,F408=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L408" s="50"/>
       <x:c r="M408" s="58"/>
@@ -16491,7 +16504,7 @@
         <x:f>IF(A409="","",IF(K409="Subscription","",IF(E409=0,"",IF(ISNUMBER(G409),G409/E409,IF(ISNUMBER(I409),-ABS(I409)/E409,IF(ISNUMBER(H409),0,IF(AND(ISNUMBER(F409),ISNUMBER(E409),E409&gt;0,F409&gt;E409),(F409-E409)/E409,IF(AND(ISNUMBER(F409),ISNUMBER(E409),E409&gt;0,F409=E409),0,IF(AND(ISNUMBER(F409),ISNUMBER(E409),E409&gt;0,F409=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K409" s="50" t="str">
-        <x:f>IF(A409="","",IF(AND(ISNUMBER(E409),E409=0,OR(ISNUMBER(SEARCH("Free",D409&amp;"")),AND(ISNUMBER(F409),F409=0))),"Subscription",IF(ISNUMBER(G409),"Profit",IF(ISNUMBER(I409),"Loss",IF(ISNUMBER(H409),"Draw",IF(AND(ISNUMBER(F409),ISNUMBER(E409),E409&gt;0,F409&gt;E409),"Profit",IF(AND(ISNUMBER(F409),ISNUMBER(E409),E409&gt;0,F409=E409),"Draw",IF(AND(ISNUMBER(F409),ISNUMBER(E409),E409&gt;0,F409=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A409="","",IF(AND(ISNUMBER(E409),E409=0,OR(ISNUMBER(SEARCH("Free",D409&amp;"")),AND(ISNUMBER(F409),F409=0))),"Subscription",IF(ISNUMBER(G409),"Profit",IF(ISNUMBER(I409),"Disqualified",IF(ISNUMBER(H409),"Draw",IF(AND(ISNUMBER(F409),ISNUMBER(E409),E409&gt;0,F409&gt;E409),"Profit",IF(AND(ISNUMBER(F409),ISNUMBER(E409),E409&gt;0,F409=E409),"Draw",IF(AND(ISNUMBER(F409),ISNUMBER(E409),E409&gt;0,F409=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L409" s="50"/>
       <x:c r="M409" s="58"/>
@@ -16528,7 +16541,7 @@
         <x:f>IF(A410="","",IF(K410="Subscription","",IF(E410=0,"",IF(ISNUMBER(G410),G410/E410,IF(ISNUMBER(I410),-ABS(I410)/E410,IF(ISNUMBER(H410),0,IF(AND(ISNUMBER(F410),ISNUMBER(E410),E410&gt;0,F410&gt;E410),(F410-E410)/E410,IF(AND(ISNUMBER(F410),ISNUMBER(E410),E410&gt;0,F410=E410),0,IF(AND(ISNUMBER(F410),ISNUMBER(E410),E410&gt;0,F410=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K410" s="50" t="str">
-        <x:f>IF(A410="","",IF(AND(ISNUMBER(E410),E410=0,OR(ISNUMBER(SEARCH("Free",D410&amp;"")),AND(ISNUMBER(F410),F410=0))),"Subscription",IF(ISNUMBER(G410),"Profit",IF(ISNUMBER(I410),"Loss",IF(ISNUMBER(H410),"Draw",IF(AND(ISNUMBER(F410),ISNUMBER(E410),E410&gt;0,F410&gt;E410),"Profit",IF(AND(ISNUMBER(F410),ISNUMBER(E410),E410&gt;0,F410=E410),"Draw",IF(AND(ISNUMBER(F410),ISNUMBER(E410),E410&gt;0,F410=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A410="","",IF(AND(ISNUMBER(E410),E410=0,OR(ISNUMBER(SEARCH("Free",D410&amp;"")),AND(ISNUMBER(F410),F410=0))),"Subscription",IF(ISNUMBER(G410),"Profit",IF(ISNUMBER(I410),"Disqualified",IF(ISNUMBER(H410),"Draw",IF(AND(ISNUMBER(F410),ISNUMBER(E410),E410&gt;0,F410&gt;E410),"Profit",IF(AND(ISNUMBER(F410),ISNUMBER(E410),E410&gt;0,F410=E410),"Draw",IF(AND(ISNUMBER(F410),ISNUMBER(E410),E410&gt;0,F410=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L410" s="50"/>
       <x:c r="M410" s="58"/>
@@ -16565,7 +16578,7 @@
         <x:f>IF(A411="","",IF(K411="Subscription","",IF(E411=0,"",IF(ISNUMBER(G411),G411/E411,IF(ISNUMBER(I411),-ABS(I411)/E411,IF(ISNUMBER(H411),0,IF(AND(ISNUMBER(F411),ISNUMBER(E411),E411&gt;0,F411&gt;E411),(F411-E411)/E411,IF(AND(ISNUMBER(F411),ISNUMBER(E411),E411&gt;0,F411=E411),0,IF(AND(ISNUMBER(F411),ISNUMBER(E411),E411&gt;0,F411=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K411" s="50" t="str">
-        <x:f>IF(A411="","",IF(AND(ISNUMBER(E411),E411=0,OR(ISNUMBER(SEARCH("Free",D411&amp;"")),AND(ISNUMBER(F411),F411=0))),"Subscription",IF(ISNUMBER(G411),"Profit",IF(ISNUMBER(I411),"Loss",IF(ISNUMBER(H411),"Draw",IF(AND(ISNUMBER(F411),ISNUMBER(E411),E411&gt;0,F411&gt;E411),"Profit",IF(AND(ISNUMBER(F411),ISNUMBER(E411),E411&gt;0,F411=E411),"Draw",IF(AND(ISNUMBER(F411),ISNUMBER(E411),E411&gt;0,F411=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A411="","",IF(AND(ISNUMBER(E411),E411=0,OR(ISNUMBER(SEARCH("Free",D411&amp;"")),AND(ISNUMBER(F411),F411=0))),"Subscription",IF(ISNUMBER(G411),"Profit",IF(ISNUMBER(I411),"Disqualified",IF(ISNUMBER(H411),"Draw",IF(AND(ISNUMBER(F411),ISNUMBER(E411),E411&gt;0,F411&gt;E411),"Profit",IF(AND(ISNUMBER(F411),ISNUMBER(E411),E411&gt;0,F411=E411),"Draw",IF(AND(ISNUMBER(F411),ISNUMBER(E411),E411&gt;0,F411=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L411" s="50"/>
       <x:c r="M411" s="58"/>
@@ -16602,7 +16615,7 @@
         <x:f>IF(A412="","",IF(K412="Subscription","",IF(E412=0,"",IF(ISNUMBER(G412),G412/E412,IF(ISNUMBER(I412),-ABS(I412)/E412,IF(ISNUMBER(H412),0,IF(AND(ISNUMBER(F412),ISNUMBER(E412),E412&gt;0,F412&gt;E412),(F412-E412)/E412,IF(AND(ISNUMBER(F412),ISNUMBER(E412),E412&gt;0,F412=E412),0,IF(AND(ISNUMBER(F412),ISNUMBER(E412),E412&gt;0,F412=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K412" s="50" t="str">
-        <x:f>IF(A412="","",IF(AND(ISNUMBER(E412),E412=0,OR(ISNUMBER(SEARCH("Free",D412&amp;"")),AND(ISNUMBER(F412),F412=0))),"Subscription",IF(ISNUMBER(G412),"Profit",IF(ISNUMBER(I412),"Loss",IF(ISNUMBER(H412),"Draw",IF(AND(ISNUMBER(F412),ISNUMBER(E412),E412&gt;0,F412&gt;E412),"Profit",IF(AND(ISNUMBER(F412),ISNUMBER(E412),E412&gt;0,F412=E412),"Draw",IF(AND(ISNUMBER(F412),ISNUMBER(E412),E412&gt;0,F412=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A412="","",IF(AND(ISNUMBER(E412),E412=0,OR(ISNUMBER(SEARCH("Free",D412&amp;"")),AND(ISNUMBER(F412),F412=0))),"Subscription",IF(ISNUMBER(G412),"Profit",IF(ISNUMBER(I412),"Disqualified",IF(ISNUMBER(H412),"Draw",IF(AND(ISNUMBER(F412),ISNUMBER(E412),E412&gt;0,F412&gt;E412),"Profit",IF(AND(ISNUMBER(F412),ISNUMBER(E412),E412&gt;0,F412=E412),"Draw",IF(AND(ISNUMBER(F412),ISNUMBER(E412),E412&gt;0,F412=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L412" s="50"/>
       <x:c r="M412" s="58"/>
@@ -16639,7 +16652,7 @@
         <x:f>IF(A413="","",IF(K413="Subscription","",IF(E413=0,"",IF(ISNUMBER(G413),G413/E413,IF(ISNUMBER(I413),-ABS(I413)/E413,IF(ISNUMBER(H413),0,IF(AND(ISNUMBER(F413),ISNUMBER(E413),E413&gt;0,F413&gt;E413),(F413-E413)/E413,IF(AND(ISNUMBER(F413),ISNUMBER(E413),E413&gt;0,F413=E413),0,IF(AND(ISNUMBER(F413),ISNUMBER(E413),E413&gt;0,F413=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K413" s="50" t="str">
-        <x:f>IF(A413="","",IF(AND(ISNUMBER(E413),E413=0,OR(ISNUMBER(SEARCH("Free",D413&amp;"")),AND(ISNUMBER(F413),F413=0))),"Subscription",IF(ISNUMBER(G413),"Profit",IF(ISNUMBER(I413),"Loss",IF(ISNUMBER(H413),"Draw",IF(AND(ISNUMBER(F413),ISNUMBER(E413),E413&gt;0,F413&gt;E413),"Profit",IF(AND(ISNUMBER(F413),ISNUMBER(E413),E413&gt;0,F413=E413),"Draw",IF(AND(ISNUMBER(F413),ISNUMBER(E413),E413&gt;0,F413=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A413="","",IF(AND(ISNUMBER(E413),E413=0,OR(ISNUMBER(SEARCH("Free",D413&amp;"")),AND(ISNUMBER(F413),F413=0))),"Subscription",IF(ISNUMBER(G413),"Profit",IF(ISNUMBER(I413),"Disqualified",IF(ISNUMBER(H413),"Draw",IF(AND(ISNUMBER(F413),ISNUMBER(E413),E413&gt;0,F413&gt;E413),"Profit",IF(AND(ISNUMBER(F413),ISNUMBER(E413),E413&gt;0,F413=E413),"Draw",IF(AND(ISNUMBER(F413),ISNUMBER(E413),E413&gt;0,F413=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L413" s="50"/>
       <x:c r="M413" s="58"/>
@@ -16676,7 +16689,7 @@
         <x:f>IF(A414="","",IF(K414="Subscription","",IF(E414=0,"",IF(ISNUMBER(G414),G414/E414,IF(ISNUMBER(I414),-ABS(I414)/E414,IF(ISNUMBER(H414),0,IF(AND(ISNUMBER(F414),ISNUMBER(E414),E414&gt;0,F414&gt;E414),(F414-E414)/E414,IF(AND(ISNUMBER(F414),ISNUMBER(E414),E414&gt;0,F414=E414),0,IF(AND(ISNUMBER(F414),ISNUMBER(E414),E414&gt;0,F414=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K414" s="50" t="str">
-        <x:f>IF(A414="","",IF(AND(ISNUMBER(E414),E414=0,OR(ISNUMBER(SEARCH("Free",D414&amp;"")),AND(ISNUMBER(F414),F414=0))),"Subscription",IF(ISNUMBER(G414),"Profit",IF(ISNUMBER(I414),"Loss",IF(ISNUMBER(H414),"Draw",IF(AND(ISNUMBER(F414),ISNUMBER(E414),E414&gt;0,F414&gt;E414),"Profit",IF(AND(ISNUMBER(F414),ISNUMBER(E414),E414&gt;0,F414=E414),"Draw",IF(AND(ISNUMBER(F414),ISNUMBER(E414),E414&gt;0,F414=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A414="","",IF(AND(ISNUMBER(E414),E414=0,OR(ISNUMBER(SEARCH("Free",D414&amp;"")),AND(ISNUMBER(F414),F414=0))),"Subscription",IF(ISNUMBER(G414),"Profit",IF(ISNUMBER(I414),"Disqualified",IF(ISNUMBER(H414),"Draw",IF(AND(ISNUMBER(F414),ISNUMBER(E414),E414&gt;0,F414&gt;E414),"Profit",IF(AND(ISNUMBER(F414),ISNUMBER(E414),E414&gt;0,F414=E414),"Draw",IF(AND(ISNUMBER(F414),ISNUMBER(E414),E414&gt;0,F414=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L414" s="50"/>
       <x:c r="M414" s="58"/>
@@ -16713,7 +16726,7 @@
         <x:f>IF(A415="","",IF(K415="Subscription","",IF(E415=0,"",IF(ISNUMBER(G415),G415/E415,IF(ISNUMBER(I415),-ABS(I415)/E415,IF(ISNUMBER(H415),0,IF(AND(ISNUMBER(F415),ISNUMBER(E415),E415&gt;0,F415&gt;E415),(F415-E415)/E415,IF(AND(ISNUMBER(F415),ISNUMBER(E415),E415&gt;0,F415=E415),0,IF(AND(ISNUMBER(F415),ISNUMBER(E415),E415&gt;0,F415=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K415" s="50" t="str">
-        <x:f>IF(A415="","",IF(AND(ISNUMBER(E415),E415=0,OR(ISNUMBER(SEARCH("Free",D415&amp;"")),AND(ISNUMBER(F415),F415=0))),"Subscription",IF(ISNUMBER(G415),"Profit",IF(ISNUMBER(I415),"Loss",IF(ISNUMBER(H415),"Draw",IF(AND(ISNUMBER(F415),ISNUMBER(E415),E415&gt;0,F415&gt;E415),"Profit",IF(AND(ISNUMBER(F415),ISNUMBER(E415),E415&gt;0,F415=E415),"Draw",IF(AND(ISNUMBER(F415),ISNUMBER(E415),E415&gt;0,F415=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A415="","",IF(AND(ISNUMBER(E415),E415=0,OR(ISNUMBER(SEARCH("Free",D415&amp;"")),AND(ISNUMBER(F415),F415=0))),"Subscription",IF(ISNUMBER(G415),"Profit",IF(ISNUMBER(I415),"Disqualified",IF(ISNUMBER(H415),"Draw",IF(AND(ISNUMBER(F415),ISNUMBER(E415),E415&gt;0,F415&gt;E415),"Profit",IF(AND(ISNUMBER(F415),ISNUMBER(E415),E415&gt;0,F415=E415),"Draw",IF(AND(ISNUMBER(F415),ISNUMBER(E415),E415&gt;0,F415=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L415" s="50"/>
       <x:c r="M415" s="58"/>
@@ -16750,7 +16763,7 @@
         <x:f>IF(A416="","",IF(K416="Subscription","",IF(E416=0,"",IF(ISNUMBER(G416),G416/E416,IF(ISNUMBER(I416),-ABS(I416)/E416,IF(ISNUMBER(H416),0,IF(AND(ISNUMBER(F416),ISNUMBER(E416),E416&gt;0,F416&gt;E416),(F416-E416)/E416,IF(AND(ISNUMBER(F416),ISNUMBER(E416),E416&gt;0,F416=E416),0,IF(AND(ISNUMBER(F416),ISNUMBER(E416),E416&gt;0,F416=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K416" s="50" t="str">
-        <x:f>IF(A416="","",IF(AND(ISNUMBER(E416),E416=0,OR(ISNUMBER(SEARCH("Free",D416&amp;"")),AND(ISNUMBER(F416),F416=0))),"Subscription",IF(ISNUMBER(G416),"Profit",IF(ISNUMBER(I416),"Loss",IF(ISNUMBER(H416),"Draw",IF(AND(ISNUMBER(F416),ISNUMBER(E416),E416&gt;0,F416&gt;E416),"Profit",IF(AND(ISNUMBER(F416),ISNUMBER(E416),E416&gt;0,F416=E416),"Draw",IF(AND(ISNUMBER(F416),ISNUMBER(E416),E416&gt;0,F416=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A416="","",IF(AND(ISNUMBER(E416),E416=0,OR(ISNUMBER(SEARCH("Free",D416&amp;"")),AND(ISNUMBER(F416),F416=0))),"Subscription",IF(ISNUMBER(G416),"Profit",IF(ISNUMBER(I416),"Disqualified",IF(ISNUMBER(H416),"Draw",IF(AND(ISNUMBER(F416),ISNUMBER(E416),E416&gt;0,F416&gt;E416),"Profit",IF(AND(ISNUMBER(F416),ISNUMBER(E416),E416&gt;0,F416=E416),"Draw",IF(AND(ISNUMBER(F416),ISNUMBER(E416),E416&gt;0,F416=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L416" s="50"/>
       <x:c r="M416" s="58"/>
@@ -16787,7 +16800,7 @@
         <x:f>IF(A417="","",IF(K417="Subscription","",IF(E417=0,"",IF(ISNUMBER(G417),G417/E417,IF(ISNUMBER(I417),-ABS(I417)/E417,IF(ISNUMBER(H417),0,IF(AND(ISNUMBER(F417),ISNUMBER(E417),E417&gt;0,F417&gt;E417),(F417-E417)/E417,IF(AND(ISNUMBER(F417),ISNUMBER(E417),E417&gt;0,F417=E417),0,IF(AND(ISNUMBER(F417),ISNUMBER(E417),E417&gt;0,F417=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K417" s="50" t="str">
-        <x:f>IF(A417="","",IF(AND(ISNUMBER(E417),E417=0,OR(ISNUMBER(SEARCH("Free",D417&amp;"")),AND(ISNUMBER(F417),F417=0))),"Subscription",IF(ISNUMBER(G417),"Profit",IF(ISNUMBER(I417),"Loss",IF(ISNUMBER(H417),"Draw",IF(AND(ISNUMBER(F417),ISNUMBER(E417),E417&gt;0,F417&gt;E417),"Profit",IF(AND(ISNUMBER(F417),ISNUMBER(E417),E417&gt;0,F417=E417),"Draw",IF(AND(ISNUMBER(F417),ISNUMBER(E417),E417&gt;0,F417=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A417="","",IF(AND(ISNUMBER(E417),E417=0,OR(ISNUMBER(SEARCH("Free",D417&amp;"")),AND(ISNUMBER(F417),F417=0))),"Subscription",IF(ISNUMBER(G417),"Profit",IF(ISNUMBER(I417),"Disqualified",IF(ISNUMBER(H417),"Draw",IF(AND(ISNUMBER(F417),ISNUMBER(E417),E417&gt;0,F417&gt;E417),"Profit",IF(AND(ISNUMBER(F417),ISNUMBER(E417),E417&gt;0,F417=E417),"Draw",IF(AND(ISNUMBER(F417),ISNUMBER(E417),E417&gt;0,F417=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L417" s="50"/>
       <x:c r="M417" s="58"/>
@@ -16824,7 +16837,7 @@
         <x:f>IF(A418="","",IF(K418="Subscription","",IF(E418=0,"",IF(ISNUMBER(G418),G418/E418,IF(ISNUMBER(I418),-ABS(I418)/E418,IF(ISNUMBER(H418),0,IF(AND(ISNUMBER(F418),ISNUMBER(E418),E418&gt;0,F418&gt;E418),(F418-E418)/E418,IF(AND(ISNUMBER(F418),ISNUMBER(E418),E418&gt;0,F418=E418),0,IF(AND(ISNUMBER(F418),ISNUMBER(E418),E418&gt;0,F418=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K418" s="50" t="str">
-        <x:f>IF(A418="","",IF(AND(ISNUMBER(E418),E418=0,OR(ISNUMBER(SEARCH("Free",D418&amp;"")),AND(ISNUMBER(F418),F418=0))),"Subscription",IF(ISNUMBER(G418),"Profit",IF(ISNUMBER(I418),"Loss",IF(ISNUMBER(H418),"Draw",IF(AND(ISNUMBER(F418),ISNUMBER(E418),E418&gt;0,F418&gt;E418),"Profit",IF(AND(ISNUMBER(F418),ISNUMBER(E418),E418&gt;0,F418=E418),"Draw",IF(AND(ISNUMBER(F418),ISNUMBER(E418),E418&gt;0,F418=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A418="","",IF(AND(ISNUMBER(E418),E418=0,OR(ISNUMBER(SEARCH("Free",D418&amp;"")),AND(ISNUMBER(F418),F418=0))),"Subscription",IF(ISNUMBER(G418),"Profit",IF(ISNUMBER(I418),"Disqualified",IF(ISNUMBER(H418),"Draw",IF(AND(ISNUMBER(F418),ISNUMBER(E418),E418&gt;0,F418&gt;E418),"Profit",IF(AND(ISNUMBER(F418),ISNUMBER(E418),E418&gt;0,F418=E418),"Draw",IF(AND(ISNUMBER(F418),ISNUMBER(E418),E418&gt;0,F418=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L418" s="50"/>
       <x:c r="M418" s="58"/>
@@ -16861,7 +16874,7 @@
         <x:f>IF(A419="","",IF(K419="Subscription","",IF(E419=0,"",IF(ISNUMBER(G419),G419/E419,IF(ISNUMBER(I419),-ABS(I419)/E419,IF(ISNUMBER(H419),0,IF(AND(ISNUMBER(F419),ISNUMBER(E419),E419&gt;0,F419&gt;E419),(F419-E419)/E419,IF(AND(ISNUMBER(F419),ISNUMBER(E419),E419&gt;0,F419=E419),0,IF(AND(ISNUMBER(F419),ISNUMBER(E419),E419&gt;0,F419=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K419" s="50" t="str">
-        <x:f>IF(A419="","",IF(AND(ISNUMBER(E419),E419=0,OR(ISNUMBER(SEARCH("Free",D419&amp;"")),AND(ISNUMBER(F419),F419=0))),"Subscription",IF(ISNUMBER(G419),"Profit",IF(ISNUMBER(I419),"Loss",IF(ISNUMBER(H419),"Draw",IF(AND(ISNUMBER(F419),ISNUMBER(E419),E419&gt;0,F419&gt;E419),"Profit",IF(AND(ISNUMBER(F419),ISNUMBER(E419),E419&gt;0,F419=E419),"Draw",IF(AND(ISNUMBER(F419),ISNUMBER(E419),E419&gt;0,F419=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A419="","",IF(AND(ISNUMBER(E419),E419=0,OR(ISNUMBER(SEARCH("Free",D419&amp;"")),AND(ISNUMBER(F419),F419=0))),"Subscription",IF(ISNUMBER(G419),"Profit",IF(ISNUMBER(I419),"Disqualified",IF(ISNUMBER(H419),"Draw",IF(AND(ISNUMBER(F419),ISNUMBER(E419),E419&gt;0,F419&gt;E419),"Profit",IF(AND(ISNUMBER(F419),ISNUMBER(E419),E419&gt;0,F419=E419),"Draw",IF(AND(ISNUMBER(F419),ISNUMBER(E419),E419&gt;0,F419=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L419" s="50"/>
       <x:c r="M419" s="58"/>
@@ -16898,7 +16911,7 @@
         <x:f>IF(A420="","",IF(K420="Subscription","",IF(E420=0,"",IF(ISNUMBER(G420),G420/E420,IF(ISNUMBER(I420),-ABS(I420)/E420,IF(ISNUMBER(H420),0,IF(AND(ISNUMBER(F420),ISNUMBER(E420),E420&gt;0,F420&gt;E420),(F420-E420)/E420,IF(AND(ISNUMBER(F420),ISNUMBER(E420),E420&gt;0,F420=E420),0,IF(AND(ISNUMBER(F420),ISNUMBER(E420),E420&gt;0,F420=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K420" s="50" t="str">
-        <x:f>IF(A420="","",IF(AND(ISNUMBER(E420),E420=0,OR(ISNUMBER(SEARCH("Free",D420&amp;"")),AND(ISNUMBER(F420),F420=0))),"Subscription",IF(ISNUMBER(G420),"Profit",IF(ISNUMBER(I420),"Loss",IF(ISNUMBER(H420),"Draw",IF(AND(ISNUMBER(F420),ISNUMBER(E420),E420&gt;0,F420&gt;E420),"Profit",IF(AND(ISNUMBER(F420),ISNUMBER(E420),E420&gt;0,F420=E420),"Draw",IF(AND(ISNUMBER(F420),ISNUMBER(E420),E420&gt;0,F420=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A420="","",IF(AND(ISNUMBER(E420),E420=0,OR(ISNUMBER(SEARCH("Free",D420&amp;"")),AND(ISNUMBER(F420),F420=0))),"Subscription",IF(ISNUMBER(G420),"Profit",IF(ISNUMBER(I420),"Disqualified",IF(ISNUMBER(H420),"Draw",IF(AND(ISNUMBER(F420),ISNUMBER(E420),E420&gt;0,F420&gt;E420),"Profit",IF(AND(ISNUMBER(F420),ISNUMBER(E420),E420&gt;0,F420=E420),"Draw",IF(AND(ISNUMBER(F420),ISNUMBER(E420),E420&gt;0,F420=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L420" s="50"/>
       <x:c r="M420" s="58"/>
@@ -16935,7 +16948,7 @@
         <x:f>IF(A421="","",IF(K421="Subscription","",IF(E421=0,"",IF(ISNUMBER(G421),G421/E421,IF(ISNUMBER(I421),-ABS(I421)/E421,IF(ISNUMBER(H421),0,IF(AND(ISNUMBER(F421),ISNUMBER(E421),E421&gt;0,F421&gt;E421),(F421-E421)/E421,IF(AND(ISNUMBER(F421),ISNUMBER(E421),E421&gt;0,F421=E421),0,IF(AND(ISNUMBER(F421),ISNUMBER(E421),E421&gt;0,F421=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K421" s="50" t="str">
-        <x:f>IF(A421="","",IF(AND(ISNUMBER(E421),E421=0,OR(ISNUMBER(SEARCH("Free",D421&amp;"")),AND(ISNUMBER(F421),F421=0))),"Subscription",IF(ISNUMBER(G421),"Profit",IF(ISNUMBER(I421),"Loss",IF(ISNUMBER(H421),"Draw",IF(AND(ISNUMBER(F421),ISNUMBER(E421),E421&gt;0,F421&gt;E421),"Profit",IF(AND(ISNUMBER(F421),ISNUMBER(E421),E421&gt;0,F421=E421),"Draw",IF(AND(ISNUMBER(F421),ISNUMBER(E421),E421&gt;0,F421=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A421="","",IF(AND(ISNUMBER(E421),E421=0,OR(ISNUMBER(SEARCH("Free",D421&amp;"")),AND(ISNUMBER(F421),F421=0))),"Subscription",IF(ISNUMBER(G421),"Profit",IF(ISNUMBER(I421),"Disqualified",IF(ISNUMBER(H421),"Draw",IF(AND(ISNUMBER(F421),ISNUMBER(E421),E421&gt;0,F421&gt;E421),"Profit",IF(AND(ISNUMBER(F421),ISNUMBER(E421),E421&gt;0,F421=E421),"Draw",IF(AND(ISNUMBER(F421),ISNUMBER(E421),E421&gt;0,F421=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L421" s="50"/>
       <x:c r="M421" s="58"/>
@@ -16972,7 +16985,7 @@
         <x:f>IF(A422="","",IF(K422="Subscription","",IF(E422=0,"",IF(ISNUMBER(G422),G422/E422,IF(ISNUMBER(I422),-ABS(I422)/E422,IF(ISNUMBER(H422),0,IF(AND(ISNUMBER(F422),ISNUMBER(E422),E422&gt;0,F422&gt;E422),(F422-E422)/E422,IF(AND(ISNUMBER(F422),ISNUMBER(E422),E422&gt;0,F422=E422),0,IF(AND(ISNUMBER(F422),ISNUMBER(E422),E422&gt;0,F422=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K422" s="50" t="str">
-        <x:f>IF(A422="","",IF(AND(ISNUMBER(E422),E422=0,OR(ISNUMBER(SEARCH("Free",D422&amp;"")),AND(ISNUMBER(F422),F422=0))),"Subscription",IF(ISNUMBER(G422),"Profit",IF(ISNUMBER(I422),"Loss",IF(ISNUMBER(H422),"Draw",IF(AND(ISNUMBER(F422),ISNUMBER(E422),E422&gt;0,F422&gt;E422),"Profit",IF(AND(ISNUMBER(F422),ISNUMBER(E422),E422&gt;0,F422=E422),"Draw",IF(AND(ISNUMBER(F422),ISNUMBER(E422),E422&gt;0,F422=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A422="","",IF(AND(ISNUMBER(E422),E422=0,OR(ISNUMBER(SEARCH("Free",D422&amp;"")),AND(ISNUMBER(F422),F422=0))),"Subscription",IF(ISNUMBER(G422),"Profit",IF(ISNUMBER(I422),"Disqualified",IF(ISNUMBER(H422),"Draw",IF(AND(ISNUMBER(F422),ISNUMBER(E422),E422&gt;0,F422&gt;E422),"Profit",IF(AND(ISNUMBER(F422),ISNUMBER(E422),E422&gt;0,F422=E422),"Draw",IF(AND(ISNUMBER(F422),ISNUMBER(E422),E422&gt;0,F422=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L422" s="50"/>
       <x:c r="M422" s="58"/>
@@ -17009,7 +17022,7 @@
         <x:f>IF(A423="","",IF(K423="Subscription","",IF(E423=0,"",IF(ISNUMBER(G423),G423/E423,IF(ISNUMBER(I423),-ABS(I423)/E423,IF(ISNUMBER(H423),0,IF(AND(ISNUMBER(F423),ISNUMBER(E423),E423&gt;0,F423&gt;E423),(F423-E423)/E423,IF(AND(ISNUMBER(F423),ISNUMBER(E423),E423&gt;0,F423=E423),0,IF(AND(ISNUMBER(F423),ISNUMBER(E423),E423&gt;0,F423=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K423" s="50" t="str">
-        <x:f>IF(A423="","",IF(AND(ISNUMBER(E423),E423=0,OR(ISNUMBER(SEARCH("Free",D423&amp;"")),AND(ISNUMBER(F423),F423=0))),"Subscription",IF(ISNUMBER(G423),"Profit",IF(ISNUMBER(I423),"Loss",IF(ISNUMBER(H423),"Draw",IF(AND(ISNUMBER(F423),ISNUMBER(E423),E423&gt;0,F423&gt;E423),"Profit",IF(AND(ISNUMBER(F423),ISNUMBER(E423),E423&gt;0,F423=E423),"Draw",IF(AND(ISNUMBER(F423),ISNUMBER(E423),E423&gt;0,F423=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A423="","",IF(AND(ISNUMBER(E423),E423=0,OR(ISNUMBER(SEARCH("Free",D423&amp;"")),AND(ISNUMBER(F423),F423=0))),"Subscription",IF(ISNUMBER(G423),"Profit",IF(ISNUMBER(I423),"Disqualified",IF(ISNUMBER(H423),"Draw",IF(AND(ISNUMBER(F423),ISNUMBER(E423),E423&gt;0,F423&gt;E423),"Profit",IF(AND(ISNUMBER(F423),ISNUMBER(E423),E423&gt;0,F423=E423),"Draw",IF(AND(ISNUMBER(F423),ISNUMBER(E423),E423&gt;0,F423=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L423" s="50"/>
       <x:c r="M423" s="58"/>
@@ -17046,7 +17059,7 @@
         <x:f>IF(A424="","",IF(K424="Subscription","",IF(E424=0,"",IF(ISNUMBER(G424),G424/E424,IF(ISNUMBER(I424),-ABS(I424)/E424,IF(ISNUMBER(H424),0,IF(AND(ISNUMBER(F424),ISNUMBER(E424),E424&gt;0,F424&gt;E424),(F424-E424)/E424,IF(AND(ISNUMBER(F424),ISNUMBER(E424),E424&gt;0,F424=E424),0,IF(AND(ISNUMBER(F424),ISNUMBER(E424),E424&gt;0,F424=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K424" s="50" t="str">
-        <x:f>IF(A424="","",IF(AND(ISNUMBER(E424),E424=0,OR(ISNUMBER(SEARCH("Free",D424&amp;"")),AND(ISNUMBER(F424),F424=0))),"Subscription",IF(ISNUMBER(G424),"Profit",IF(ISNUMBER(I424),"Loss",IF(ISNUMBER(H424),"Draw",IF(AND(ISNUMBER(F424),ISNUMBER(E424),E424&gt;0,F424&gt;E424),"Profit",IF(AND(ISNUMBER(F424),ISNUMBER(E424),E424&gt;0,F424=E424),"Draw",IF(AND(ISNUMBER(F424),ISNUMBER(E424),E424&gt;0,F424=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A424="","",IF(AND(ISNUMBER(E424),E424=0,OR(ISNUMBER(SEARCH("Free",D424&amp;"")),AND(ISNUMBER(F424),F424=0))),"Subscription",IF(ISNUMBER(G424),"Profit",IF(ISNUMBER(I424),"Disqualified",IF(ISNUMBER(H424),"Draw",IF(AND(ISNUMBER(F424),ISNUMBER(E424),E424&gt;0,F424&gt;E424),"Profit",IF(AND(ISNUMBER(F424),ISNUMBER(E424),E424&gt;0,F424=E424),"Draw",IF(AND(ISNUMBER(F424),ISNUMBER(E424),E424&gt;0,F424=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L424" s="50"/>
       <x:c r="M424" s="58"/>
@@ -17083,7 +17096,7 @@
         <x:f>IF(A425="","",IF(K425="Subscription","",IF(E425=0,"",IF(ISNUMBER(G425),G425/E425,IF(ISNUMBER(I425),-ABS(I425)/E425,IF(ISNUMBER(H425),0,IF(AND(ISNUMBER(F425),ISNUMBER(E425),E425&gt;0,F425&gt;E425),(F425-E425)/E425,IF(AND(ISNUMBER(F425),ISNUMBER(E425),E425&gt;0,F425=E425),0,IF(AND(ISNUMBER(F425),ISNUMBER(E425),E425&gt;0,F425=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K425" s="50" t="str">
-        <x:f>IF(A425="","",IF(AND(ISNUMBER(E425),E425=0,OR(ISNUMBER(SEARCH("Free",D425&amp;"")),AND(ISNUMBER(F425),F425=0))),"Subscription",IF(ISNUMBER(G425),"Profit",IF(ISNUMBER(I425),"Loss",IF(ISNUMBER(H425),"Draw",IF(AND(ISNUMBER(F425),ISNUMBER(E425),E425&gt;0,F425&gt;E425),"Profit",IF(AND(ISNUMBER(F425),ISNUMBER(E425),E425&gt;0,F425=E425),"Draw",IF(AND(ISNUMBER(F425),ISNUMBER(E425),E425&gt;0,F425=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A425="","",IF(AND(ISNUMBER(E425),E425=0,OR(ISNUMBER(SEARCH("Free",D425&amp;"")),AND(ISNUMBER(F425),F425=0))),"Subscription",IF(ISNUMBER(G425),"Profit",IF(ISNUMBER(I425),"Disqualified",IF(ISNUMBER(H425),"Draw",IF(AND(ISNUMBER(F425),ISNUMBER(E425),E425&gt;0,F425&gt;E425),"Profit",IF(AND(ISNUMBER(F425),ISNUMBER(E425),E425&gt;0,F425=E425),"Draw",IF(AND(ISNUMBER(F425),ISNUMBER(E425),E425&gt;0,F425=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L425" s="50"/>
       <x:c r="M425" s="58"/>
@@ -17120,7 +17133,7 @@
         <x:f>IF(A426="","",IF(K426="Subscription","",IF(E426=0,"",IF(ISNUMBER(G426),G426/E426,IF(ISNUMBER(I426),-ABS(I426)/E426,IF(ISNUMBER(H426),0,IF(AND(ISNUMBER(F426),ISNUMBER(E426),E426&gt;0,F426&gt;E426),(F426-E426)/E426,IF(AND(ISNUMBER(F426),ISNUMBER(E426),E426&gt;0,F426=E426),0,IF(AND(ISNUMBER(F426),ISNUMBER(E426),E426&gt;0,F426=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K426" s="50" t="str">
-        <x:f>IF(A426="","",IF(AND(ISNUMBER(E426),E426=0,OR(ISNUMBER(SEARCH("Free",D426&amp;"")),AND(ISNUMBER(F426),F426=0))),"Subscription",IF(ISNUMBER(G426),"Profit",IF(ISNUMBER(I426),"Loss",IF(ISNUMBER(H426),"Draw",IF(AND(ISNUMBER(F426),ISNUMBER(E426),E426&gt;0,F426&gt;E426),"Profit",IF(AND(ISNUMBER(F426),ISNUMBER(E426),E426&gt;0,F426=E426),"Draw",IF(AND(ISNUMBER(F426),ISNUMBER(E426),E426&gt;0,F426=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A426="","",IF(AND(ISNUMBER(E426),E426=0,OR(ISNUMBER(SEARCH("Free",D426&amp;"")),AND(ISNUMBER(F426),F426=0))),"Subscription",IF(ISNUMBER(G426),"Profit",IF(ISNUMBER(I426),"Disqualified",IF(ISNUMBER(H426),"Draw",IF(AND(ISNUMBER(F426),ISNUMBER(E426),E426&gt;0,F426&gt;E426),"Profit",IF(AND(ISNUMBER(F426),ISNUMBER(E426),E426&gt;0,F426=E426),"Draw",IF(AND(ISNUMBER(F426),ISNUMBER(E426),E426&gt;0,F426=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L426" s="50"/>
       <x:c r="M426" s="58"/>
@@ -17157,7 +17170,7 @@
         <x:f>IF(A427="","",IF(K427="Subscription","",IF(E427=0,"",IF(ISNUMBER(G427),G427/E427,IF(ISNUMBER(I427),-ABS(I427)/E427,IF(ISNUMBER(H427),0,IF(AND(ISNUMBER(F427),ISNUMBER(E427),E427&gt;0,F427&gt;E427),(F427-E427)/E427,IF(AND(ISNUMBER(F427),ISNUMBER(E427),E427&gt;0,F427=E427),0,IF(AND(ISNUMBER(F427),ISNUMBER(E427),E427&gt;0,F427=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K427" s="50" t="str">
-        <x:f>IF(A427="","",IF(AND(ISNUMBER(E427),E427=0,OR(ISNUMBER(SEARCH("Free",D427&amp;"")),AND(ISNUMBER(F427),F427=0))),"Subscription",IF(ISNUMBER(G427),"Profit",IF(ISNUMBER(I427),"Loss",IF(ISNUMBER(H427),"Draw",IF(AND(ISNUMBER(F427),ISNUMBER(E427),E427&gt;0,F427&gt;E427),"Profit",IF(AND(ISNUMBER(F427),ISNUMBER(E427),E427&gt;0,F427=E427),"Draw",IF(AND(ISNUMBER(F427),ISNUMBER(E427),E427&gt;0,F427=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A427="","",IF(AND(ISNUMBER(E427),E427=0,OR(ISNUMBER(SEARCH("Free",D427&amp;"")),AND(ISNUMBER(F427),F427=0))),"Subscription",IF(ISNUMBER(G427),"Profit",IF(ISNUMBER(I427),"Disqualified",IF(ISNUMBER(H427),"Draw",IF(AND(ISNUMBER(F427),ISNUMBER(E427),E427&gt;0,F427&gt;E427),"Profit",IF(AND(ISNUMBER(F427),ISNUMBER(E427),E427&gt;0,F427=E427),"Draw",IF(AND(ISNUMBER(F427),ISNUMBER(E427),E427&gt;0,F427=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L427" s="50"/>
       <x:c r="M427" s="58"/>
@@ -17194,7 +17207,7 @@
         <x:f>IF(A428="","",IF(K428="Subscription","",IF(E428=0,"",IF(ISNUMBER(G428),G428/E428,IF(ISNUMBER(I428),-ABS(I428)/E428,IF(ISNUMBER(H428),0,IF(AND(ISNUMBER(F428),ISNUMBER(E428),E428&gt;0,F428&gt;E428),(F428-E428)/E428,IF(AND(ISNUMBER(F428),ISNUMBER(E428),E428&gt;0,F428=E428),0,IF(AND(ISNUMBER(F428),ISNUMBER(E428),E428&gt;0,F428=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K428" s="50" t="str">
-        <x:f>IF(A428="","",IF(AND(ISNUMBER(E428),E428=0,OR(ISNUMBER(SEARCH("Free",D428&amp;"")),AND(ISNUMBER(F428),F428=0))),"Subscription",IF(ISNUMBER(G428),"Profit",IF(ISNUMBER(I428),"Loss",IF(ISNUMBER(H428),"Draw",IF(AND(ISNUMBER(F428),ISNUMBER(E428),E428&gt;0,F428&gt;E428),"Profit",IF(AND(ISNUMBER(F428),ISNUMBER(E428),E428&gt;0,F428=E428),"Draw",IF(AND(ISNUMBER(F428),ISNUMBER(E428),E428&gt;0,F428=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A428="","",IF(AND(ISNUMBER(E428),E428=0,OR(ISNUMBER(SEARCH("Free",D428&amp;"")),AND(ISNUMBER(F428),F428=0))),"Subscription",IF(ISNUMBER(G428),"Profit",IF(ISNUMBER(I428),"Disqualified",IF(ISNUMBER(H428),"Draw",IF(AND(ISNUMBER(F428),ISNUMBER(E428),E428&gt;0,F428&gt;E428),"Profit",IF(AND(ISNUMBER(F428),ISNUMBER(E428),E428&gt;0,F428=E428),"Draw",IF(AND(ISNUMBER(F428),ISNUMBER(E428),E428&gt;0,F428=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L428" s="50"/>
       <x:c r="M428" s="58"/>
@@ -17231,7 +17244,7 @@
         <x:f>IF(A429="","",IF(K429="Subscription","",IF(E429=0,"",IF(ISNUMBER(G429),G429/E429,IF(ISNUMBER(I429),-ABS(I429)/E429,IF(ISNUMBER(H429),0,IF(AND(ISNUMBER(F429),ISNUMBER(E429),E429&gt;0,F429&gt;E429),(F429-E429)/E429,IF(AND(ISNUMBER(F429),ISNUMBER(E429),E429&gt;0,F429=E429),0,IF(AND(ISNUMBER(F429),ISNUMBER(E429),E429&gt;0,F429=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K429" s="50" t="str">
-        <x:f>IF(A429="","",IF(AND(ISNUMBER(E429),E429=0,OR(ISNUMBER(SEARCH("Free",D429&amp;"")),AND(ISNUMBER(F429),F429=0))),"Subscription",IF(ISNUMBER(G429),"Profit",IF(ISNUMBER(I429),"Loss",IF(ISNUMBER(H429),"Draw",IF(AND(ISNUMBER(F429),ISNUMBER(E429),E429&gt;0,F429&gt;E429),"Profit",IF(AND(ISNUMBER(F429),ISNUMBER(E429),E429&gt;0,F429=E429),"Draw",IF(AND(ISNUMBER(F429),ISNUMBER(E429),E429&gt;0,F429=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A429="","",IF(AND(ISNUMBER(E429),E429=0,OR(ISNUMBER(SEARCH("Free",D429&amp;"")),AND(ISNUMBER(F429),F429=0))),"Subscription",IF(ISNUMBER(G429),"Profit",IF(ISNUMBER(I429),"Disqualified",IF(ISNUMBER(H429),"Draw",IF(AND(ISNUMBER(F429),ISNUMBER(E429),E429&gt;0,F429&gt;E429),"Profit",IF(AND(ISNUMBER(F429),ISNUMBER(E429),E429&gt;0,F429=E429),"Draw",IF(AND(ISNUMBER(F429),ISNUMBER(E429),E429&gt;0,F429=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L429" s="50"/>
       <x:c r="M429" s="58"/>
@@ -17268,7 +17281,7 @@
         <x:f>IF(A430="","",IF(K430="Subscription","",IF(E430=0,"",IF(ISNUMBER(G430),G430/E430,IF(ISNUMBER(I430),-ABS(I430)/E430,IF(ISNUMBER(H430),0,IF(AND(ISNUMBER(F430),ISNUMBER(E430),E430&gt;0,F430&gt;E430),(F430-E430)/E430,IF(AND(ISNUMBER(F430),ISNUMBER(E430),E430&gt;0,F430=E430),0,IF(AND(ISNUMBER(F430),ISNUMBER(E430),E430&gt;0,F430=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K430" s="50" t="str">
-        <x:f>IF(A430="","",IF(AND(ISNUMBER(E430),E430=0,OR(ISNUMBER(SEARCH("Free",D430&amp;"")),AND(ISNUMBER(F430),F430=0))),"Subscription",IF(ISNUMBER(G430),"Profit",IF(ISNUMBER(I430),"Loss",IF(ISNUMBER(H430),"Draw",IF(AND(ISNUMBER(F430),ISNUMBER(E430),E430&gt;0,F430&gt;E430),"Profit",IF(AND(ISNUMBER(F430),ISNUMBER(E430),E430&gt;0,F430=E430),"Draw",IF(AND(ISNUMBER(F430),ISNUMBER(E430),E430&gt;0,F430=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A430="","",IF(AND(ISNUMBER(E430),E430=0,OR(ISNUMBER(SEARCH("Free",D430&amp;"")),AND(ISNUMBER(F430),F430=0))),"Subscription",IF(ISNUMBER(G430),"Profit",IF(ISNUMBER(I430),"Disqualified",IF(ISNUMBER(H430),"Draw",IF(AND(ISNUMBER(F430),ISNUMBER(E430),E430&gt;0,F430&gt;E430),"Profit",IF(AND(ISNUMBER(F430),ISNUMBER(E430),E430&gt;0,F430=E430),"Draw",IF(AND(ISNUMBER(F430),ISNUMBER(E430),E430&gt;0,F430=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L430" s="50"/>
       <x:c r="M430" s="58"/>
@@ -17305,7 +17318,7 @@
         <x:f>IF(A431="","",IF(K431="Subscription","",IF(E431=0,"",IF(ISNUMBER(G431),G431/E431,IF(ISNUMBER(I431),-ABS(I431)/E431,IF(ISNUMBER(H431),0,IF(AND(ISNUMBER(F431),ISNUMBER(E431),E431&gt;0,F431&gt;E431),(F431-E431)/E431,IF(AND(ISNUMBER(F431),ISNUMBER(E431),E431&gt;0,F431=E431),0,IF(AND(ISNUMBER(F431),ISNUMBER(E431),E431&gt;0,F431=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K431" s="50" t="str">
-        <x:f>IF(A431="","",IF(AND(ISNUMBER(E431),E431=0,OR(ISNUMBER(SEARCH("Free",D431&amp;"")),AND(ISNUMBER(F431),F431=0))),"Subscription",IF(ISNUMBER(G431),"Profit",IF(ISNUMBER(I431),"Loss",IF(ISNUMBER(H431),"Draw",IF(AND(ISNUMBER(F431),ISNUMBER(E431),E431&gt;0,F431&gt;E431),"Profit",IF(AND(ISNUMBER(F431),ISNUMBER(E431),E431&gt;0,F431=E431),"Draw",IF(AND(ISNUMBER(F431),ISNUMBER(E431),E431&gt;0,F431=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A431="","",IF(AND(ISNUMBER(E431),E431=0,OR(ISNUMBER(SEARCH("Free",D431&amp;"")),AND(ISNUMBER(F431),F431=0))),"Subscription",IF(ISNUMBER(G431),"Profit",IF(ISNUMBER(I431),"Disqualified",IF(ISNUMBER(H431),"Draw",IF(AND(ISNUMBER(F431),ISNUMBER(E431),E431&gt;0,F431&gt;E431),"Profit",IF(AND(ISNUMBER(F431),ISNUMBER(E431),E431&gt;0,F431=E431),"Draw",IF(AND(ISNUMBER(F431),ISNUMBER(E431),E431&gt;0,F431=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L431" s="50"/>
       <x:c r="M431" s="58"/>
@@ -17342,7 +17355,7 @@
         <x:f>IF(A432="","",IF(K432="Subscription","",IF(E432=0,"",IF(ISNUMBER(G432),G432/E432,IF(ISNUMBER(I432),-ABS(I432)/E432,IF(ISNUMBER(H432),0,IF(AND(ISNUMBER(F432),ISNUMBER(E432),E432&gt;0,F432&gt;E432),(F432-E432)/E432,IF(AND(ISNUMBER(F432),ISNUMBER(E432),E432&gt;0,F432=E432),0,IF(AND(ISNUMBER(F432),ISNUMBER(E432),E432&gt;0,F432=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K432" s="50" t="str">
-        <x:f>IF(A432="","",IF(AND(ISNUMBER(E432),E432=0,OR(ISNUMBER(SEARCH("Free",D432&amp;"")),AND(ISNUMBER(F432),F432=0))),"Subscription",IF(ISNUMBER(G432),"Profit",IF(ISNUMBER(I432),"Loss",IF(ISNUMBER(H432),"Draw",IF(AND(ISNUMBER(F432),ISNUMBER(E432),E432&gt;0,F432&gt;E432),"Profit",IF(AND(ISNUMBER(F432),ISNUMBER(E432),E432&gt;0,F432=E432),"Draw",IF(AND(ISNUMBER(F432),ISNUMBER(E432),E432&gt;0,F432=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A432="","",IF(AND(ISNUMBER(E432),E432=0,OR(ISNUMBER(SEARCH("Free",D432&amp;"")),AND(ISNUMBER(F432),F432=0))),"Subscription",IF(ISNUMBER(G432),"Profit",IF(ISNUMBER(I432),"Disqualified",IF(ISNUMBER(H432),"Draw",IF(AND(ISNUMBER(F432),ISNUMBER(E432),E432&gt;0,F432&gt;E432),"Profit",IF(AND(ISNUMBER(F432),ISNUMBER(E432),E432&gt;0,F432=E432),"Draw",IF(AND(ISNUMBER(F432),ISNUMBER(E432),E432&gt;0,F432=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L432" s="50"/>
       <x:c r="M432" s="58"/>
@@ -17379,7 +17392,7 @@
         <x:f>IF(A433="","",IF(K433="Subscription","",IF(E433=0,"",IF(ISNUMBER(G433),G433/E433,IF(ISNUMBER(I433),-ABS(I433)/E433,IF(ISNUMBER(H433),0,IF(AND(ISNUMBER(F433),ISNUMBER(E433),E433&gt;0,F433&gt;E433),(F433-E433)/E433,IF(AND(ISNUMBER(F433),ISNUMBER(E433),E433&gt;0,F433=E433),0,IF(AND(ISNUMBER(F433),ISNUMBER(E433),E433&gt;0,F433=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K433" s="50" t="str">
-        <x:f>IF(A433="","",IF(AND(ISNUMBER(E433),E433=0,OR(ISNUMBER(SEARCH("Free",D433&amp;"")),AND(ISNUMBER(F433),F433=0))),"Subscription",IF(ISNUMBER(G433),"Profit",IF(ISNUMBER(I433),"Loss",IF(ISNUMBER(H433),"Draw",IF(AND(ISNUMBER(F433),ISNUMBER(E433),E433&gt;0,F433&gt;E433),"Profit",IF(AND(ISNUMBER(F433),ISNUMBER(E433),E433&gt;0,F433=E433),"Draw",IF(AND(ISNUMBER(F433),ISNUMBER(E433),E433&gt;0,F433=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A433="","",IF(AND(ISNUMBER(E433),E433=0,OR(ISNUMBER(SEARCH("Free",D433&amp;"")),AND(ISNUMBER(F433),F433=0))),"Subscription",IF(ISNUMBER(G433),"Profit",IF(ISNUMBER(I433),"Disqualified",IF(ISNUMBER(H433),"Draw",IF(AND(ISNUMBER(F433),ISNUMBER(E433),E433&gt;0,F433&gt;E433),"Profit",IF(AND(ISNUMBER(F433),ISNUMBER(E433),E433&gt;0,F433=E433),"Draw",IF(AND(ISNUMBER(F433),ISNUMBER(E433),E433&gt;0,F433=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L433" s="50"/>
       <x:c r="M433" s="58"/>
@@ -17416,7 +17429,7 @@
         <x:f>IF(A434="","",IF(K434="Subscription","",IF(E434=0,"",IF(ISNUMBER(G434),G434/E434,IF(ISNUMBER(I434),-ABS(I434)/E434,IF(ISNUMBER(H434),0,IF(AND(ISNUMBER(F434),ISNUMBER(E434),E434&gt;0,F434&gt;E434),(F434-E434)/E434,IF(AND(ISNUMBER(F434),ISNUMBER(E434),E434&gt;0,F434=E434),0,IF(AND(ISNUMBER(F434),ISNUMBER(E434),E434&gt;0,F434=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K434" s="50" t="str">
-        <x:f>IF(A434="","",IF(AND(ISNUMBER(E434),E434=0,OR(ISNUMBER(SEARCH("Free",D434&amp;"")),AND(ISNUMBER(F434),F434=0))),"Subscription",IF(ISNUMBER(G434),"Profit",IF(ISNUMBER(I434),"Loss",IF(ISNUMBER(H434),"Draw",IF(AND(ISNUMBER(F434),ISNUMBER(E434),E434&gt;0,F434&gt;E434),"Profit",IF(AND(ISNUMBER(F434),ISNUMBER(E434),E434&gt;0,F434=E434),"Draw",IF(AND(ISNUMBER(F434),ISNUMBER(E434),E434&gt;0,F434=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A434="","",IF(AND(ISNUMBER(E434),E434=0,OR(ISNUMBER(SEARCH("Free",D434&amp;"")),AND(ISNUMBER(F434),F434=0))),"Subscription",IF(ISNUMBER(G434),"Profit",IF(ISNUMBER(I434),"Disqualified",IF(ISNUMBER(H434),"Draw",IF(AND(ISNUMBER(F434),ISNUMBER(E434),E434&gt;0,F434&gt;E434),"Profit",IF(AND(ISNUMBER(F434),ISNUMBER(E434),E434&gt;0,F434=E434),"Draw",IF(AND(ISNUMBER(F434),ISNUMBER(E434),E434&gt;0,F434=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L434" s="50"/>
       <x:c r="M434" s="58"/>
@@ -17453,7 +17466,7 @@
         <x:f>IF(A435="","",IF(K435="Subscription","",IF(E435=0,"",IF(ISNUMBER(G435),G435/E435,IF(ISNUMBER(I435),-ABS(I435)/E435,IF(ISNUMBER(H435),0,IF(AND(ISNUMBER(F435),ISNUMBER(E435),E435&gt;0,F435&gt;E435),(F435-E435)/E435,IF(AND(ISNUMBER(F435),ISNUMBER(E435),E435&gt;0,F435=E435),0,IF(AND(ISNUMBER(F435),ISNUMBER(E435),E435&gt;0,F435=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K435" s="50" t="str">
-        <x:f>IF(A435="","",IF(AND(ISNUMBER(E435),E435=0,OR(ISNUMBER(SEARCH("Free",D435&amp;"")),AND(ISNUMBER(F435),F435=0))),"Subscription",IF(ISNUMBER(G435),"Profit",IF(ISNUMBER(I435),"Loss",IF(ISNUMBER(H435),"Draw",IF(AND(ISNUMBER(F435),ISNUMBER(E435),E435&gt;0,F435&gt;E435),"Profit",IF(AND(ISNUMBER(F435),ISNUMBER(E435),E435&gt;0,F435=E435),"Draw",IF(AND(ISNUMBER(F435),ISNUMBER(E435),E435&gt;0,F435=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A435="","",IF(AND(ISNUMBER(E435),E435=0,OR(ISNUMBER(SEARCH("Free",D435&amp;"")),AND(ISNUMBER(F435),F435=0))),"Subscription",IF(ISNUMBER(G435),"Profit",IF(ISNUMBER(I435),"Disqualified",IF(ISNUMBER(H435),"Draw",IF(AND(ISNUMBER(F435),ISNUMBER(E435),E435&gt;0,F435&gt;E435),"Profit",IF(AND(ISNUMBER(F435),ISNUMBER(E435),E435&gt;0,F435=E435),"Draw",IF(AND(ISNUMBER(F435),ISNUMBER(E435),E435&gt;0,F435=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L435" s="50"/>
       <x:c r="M435" s="58"/>
@@ -17490,7 +17503,7 @@
         <x:f>IF(A436="","",IF(K436="Subscription","",IF(E436=0,"",IF(ISNUMBER(G436),G436/E436,IF(ISNUMBER(I436),-ABS(I436)/E436,IF(ISNUMBER(H436),0,IF(AND(ISNUMBER(F436),ISNUMBER(E436),E436&gt;0,F436&gt;E436),(F436-E436)/E436,IF(AND(ISNUMBER(F436),ISNUMBER(E436),E436&gt;0,F436=E436),0,IF(AND(ISNUMBER(F436),ISNUMBER(E436),E436&gt;0,F436=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K436" s="50" t="str">
-        <x:f>IF(A436="","",IF(AND(ISNUMBER(E436),E436=0,OR(ISNUMBER(SEARCH("Free",D436&amp;"")),AND(ISNUMBER(F436),F436=0))),"Subscription",IF(ISNUMBER(G436),"Profit",IF(ISNUMBER(I436),"Loss",IF(ISNUMBER(H436),"Draw",IF(AND(ISNUMBER(F436),ISNUMBER(E436),E436&gt;0,F436&gt;E436),"Profit",IF(AND(ISNUMBER(F436),ISNUMBER(E436),E436&gt;0,F436=E436),"Draw",IF(AND(ISNUMBER(F436),ISNUMBER(E436),E436&gt;0,F436=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A436="","",IF(AND(ISNUMBER(E436),E436=0,OR(ISNUMBER(SEARCH("Free",D436&amp;"")),AND(ISNUMBER(F436),F436=0))),"Subscription",IF(ISNUMBER(G436),"Profit",IF(ISNUMBER(I436),"Disqualified",IF(ISNUMBER(H436),"Draw",IF(AND(ISNUMBER(F436),ISNUMBER(E436),E436&gt;0,F436&gt;E436),"Profit",IF(AND(ISNUMBER(F436),ISNUMBER(E436),E436&gt;0,F436=E436),"Draw",IF(AND(ISNUMBER(F436),ISNUMBER(E436),E436&gt;0,F436=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L436" s="50"/>
       <x:c r="M436" s="58"/>
@@ -17527,7 +17540,7 @@
         <x:f>IF(A437="","",IF(K437="Subscription","",IF(E437=0,"",IF(ISNUMBER(G437),G437/E437,IF(ISNUMBER(I437),-ABS(I437)/E437,IF(ISNUMBER(H437),0,IF(AND(ISNUMBER(F437),ISNUMBER(E437),E437&gt;0,F437&gt;E437),(F437-E437)/E437,IF(AND(ISNUMBER(F437),ISNUMBER(E437),E437&gt;0,F437=E437),0,IF(AND(ISNUMBER(F437),ISNUMBER(E437),E437&gt;0,F437=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K437" s="50" t="str">
-        <x:f>IF(A437="","",IF(AND(ISNUMBER(E437),E437=0,OR(ISNUMBER(SEARCH("Free",D437&amp;"")),AND(ISNUMBER(F437),F437=0))),"Subscription",IF(ISNUMBER(G437),"Profit",IF(ISNUMBER(I437),"Loss",IF(ISNUMBER(H437),"Draw",IF(AND(ISNUMBER(F437),ISNUMBER(E437),E437&gt;0,F437&gt;E437),"Profit",IF(AND(ISNUMBER(F437),ISNUMBER(E437),E437&gt;0,F437=E437),"Draw",IF(AND(ISNUMBER(F437),ISNUMBER(E437),E437&gt;0,F437=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A437="","",IF(AND(ISNUMBER(E437),E437=0,OR(ISNUMBER(SEARCH("Free",D437&amp;"")),AND(ISNUMBER(F437),F437=0))),"Subscription",IF(ISNUMBER(G437),"Profit",IF(ISNUMBER(I437),"Disqualified",IF(ISNUMBER(H437),"Draw",IF(AND(ISNUMBER(F437),ISNUMBER(E437),E437&gt;0,F437&gt;E437),"Profit",IF(AND(ISNUMBER(F437),ISNUMBER(E437),E437&gt;0,F437=E437),"Draw",IF(AND(ISNUMBER(F437),ISNUMBER(E437),E437&gt;0,F437=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L437" s="50"/>
       <x:c r="M437" s="58"/>
@@ -17564,7 +17577,7 @@
         <x:f>IF(A438="","",IF(K438="Subscription","",IF(E438=0,"",IF(ISNUMBER(G438),G438/E438,IF(ISNUMBER(I438),-ABS(I438)/E438,IF(ISNUMBER(H438),0,IF(AND(ISNUMBER(F438),ISNUMBER(E438),E438&gt;0,F438&gt;E438),(F438-E438)/E438,IF(AND(ISNUMBER(F438),ISNUMBER(E438),E438&gt;0,F438=E438),0,IF(AND(ISNUMBER(F438),ISNUMBER(E438),E438&gt;0,F438=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K438" s="50" t="str">
-        <x:f>IF(A438="","",IF(AND(ISNUMBER(E438),E438=0,OR(ISNUMBER(SEARCH("Free",D438&amp;"")),AND(ISNUMBER(F438),F438=0))),"Subscription",IF(ISNUMBER(G438),"Profit",IF(ISNUMBER(I438),"Loss",IF(ISNUMBER(H438),"Draw",IF(AND(ISNUMBER(F438),ISNUMBER(E438),E438&gt;0,F438&gt;E438),"Profit",IF(AND(ISNUMBER(F438),ISNUMBER(E438),E438&gt;0,F438=E438),"Draw",IF(AND(ISNUMBER(F438),ISNUMBER(E438),E438&gt;0,F438=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A438="","",IF(AND(ISNUMBER(E438),E438=0,OR(ISNUMBER(SEARCH("Free",D438&amp;"")),AND(ISNUMBER(F438),F438=0))),"Subscription",IF(ISNUMBER(G438),"Profit",IF(ISNUMBER(I438),"Disqualified",IF(ISNUMBER(H438),"Draw",IF(AND(ISNUMBER(F438),ISNUMBER(E438),E438&gt;0,F438&gt;E438),"Profit",IF(AND(ISNUMBER(F438),ISNUMBER(E438),E438&gt;0,F438=E438),"Draw",IF(AND(ISNUMBER(F438),ISNUMBER(E438),E438&gt;0,F438=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L438" s="50"/>
       <x:c r="M438" s="58"/>
@@ -17601,7 +17614,7 @@
         <x:f>IF(A439="","",IF(K439="Subscription","",IF(E439=0,"",IF(ISNUMBER(G439),G439/E439,IF(ISNUMBER(I439),-ABS(I439)/E439,IF(ISNUMBER(H439),0,IF(AND(ISNUMBER(F439),ISNUMBER(E439),E439&gt;0,F439&gt;E439),(F439-E439)/E439,IF(AND(ISNUMBER(F439),ISNUMBER(E439),E439&gt;0,F439=E439),0,IF(AND(ISNUMBER(F439),ISNUMBER(E439),E439&gt;0,F439=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K439" s="50" t="str">
-        <x:f>IF(A439="","",IF(AND(ISNUMBER(E439),E439=0,OR(ISNUMBER(SEARCH("Free",D439&amp;"")),AND(ISNUMBER(F439),F439=0))),"Subscription",IF(ISNUMBER(G439),"Profit",IF(ISNUMBER(I439),"Loss",IF(ISNUMBER(H439),"Draw",IF(AND(ISNUMBER(F439),ISNUMBER(E439),E439&gt;0,F439&gt;E439),"Profit",IF(AND(ISNUMBER(F439),ISNUMBER(E439),E439&gt;0,F439=E439),"Draw",IF(AND(ISNUMBER(F439),ISNUMBER(E439),E439&gt;0,F439=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A439="","",IF(AND(ISNUMBER(E439),E439=0,OR(ISNUMBER(SEARCH("Free",D439&amp;"")),AND(ISNUMBER(F439),F439=0))),"Subscription",IF(ISNUMBER(G439),"Profit",IF(ISNUMBER(I439),"Disqualified",IF(ISNUMBER(H439),"Draw",IF(AND(ISNUMBER(F439),ISNUMBER(E439),E439&gt;0,F439&gt;E439),"Profit",IF(AND(ISNUMBER(F439),ISNUMBER(E439),E439&gt;0,F439=E439),"Draw",IF(AND(ISNUMBER(F439),ISNUMBER(E439),E439&gt;0,F439=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L439" s="50"/>
       <x:c r="M439" s="58"/>
@@ -17638,7 +17651,7 @@
         <x:f>IF(A440="","",IF(K440="Subscription","",IF(E440=0,"",IF(ISNUMBER(G440),G440/E440,IF(ISNUMBER(I440),-ABS(I440)/E440,IF(ISNUMBER(H440),0,IF(AND(ISNUMBER(F440),ISNUMBER(E440),E440&gt;0,F440&gt;E440),(F440-E440)/E440,IF(AND(ISNUMBER(F440),ISNUMBER(E440),E440&gt;0,F440=E440),0,IF(AND(ISNUMBER(F440),ISNUMBER(E440),E440&gt;0,F440=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K440" s="50" t="str">
-        <x:f>IF(A440="","",IF(AND(ISNUMBER(E440),E440=0,OR(ISNUMBER(SEARCH("Free",D440&amp;"")),AND(ISNUMBER(F440),F440=0))),"Subscription",IF(ISNUMBER(G440),"Profit",IF(ISNUMBER(I440),"Loss",IF(ISNUMBER(H440),"Draw",IF(AND(ISNUMBER(F440),ISNUMBER(E440),E440&gt;0,F440&gt;E440),"Profit",IF(AND(ISNUMBER(F440),ISNUMBER(E440),E440&gt;0,F440=E440),"Draw",IF(AND(ISNUMBER(F440),ISNUMBER(E440),E440&gt;0,F440=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A440="","",IF(AND(ISNUMBER(E440),E440=0,OR(ISNUMBER(SEARCH("Free",D440&amp;"")),AND(ISNUMBER(F440),F440=0))),"Subscription",IF(ISNUMBER(G440),"Profit",IF(ISNUMBER(I440),"Disqualified",IF(ISNUMBER(H440),"Draw",IF(AND(ISNUMBER(F440),ISNUMBER(E440),E440&gt;0,F440&gt;E440),"Profit",IF(AND(ISNUMBER(F440),ISNUMBER(E440),E440&gt;0,F440=E440),"Draw",IF(AND(ISNUMBER(F440),ISNUMBER(E440),E440&gt;0,F440=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L440" s="50"/>
       <x:c r="M440" s="58"/>
@@ -17675,7 +17688,7 @@
         <x:f>IF(A441="","",IF(K441="Subscription","",IF(E441=0,"",IF(ISNUMBER(G441),G441/E441,IF(ISNUMBER(I441),-ABS(I441)/E441,IF(ISNUMBER(H441),0,IF(AND(ISNUMBER(F441),ISNUMBER(E441),E441&gt;0,F441&gt;E441),(F441-E441)/E441,IF(AND(ISNUMBER(F441),ISNUMBER(E441),E441&gt;0,F441=E441),0,IF(AND(ISNUMBER(F441),ISNUMBER(E441),E441&gt;0,F441=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K441" s="50" t="str">
-        <x:f>IF(A441="","",IF(AND(ISNUMBER(E441),E441=0,OR(ISNUMBER(SEARCH("Free",D441&amp;"")),AND(ISNUMBER(F441),F441=0))),"Subscription",IF(ISNUMBER(G441),"Profit",IF(ISNUMBER(I441),"Loss",IF(ISNUMBER(H441),"Draw",IF(AND(ISNUMBER(F441),ISNUMBER(E441),E441&gt;0,F441&gt;E441),"Profit",IF(AND(ISNUMBER(F441),ISNUMBER(E441),E441&gt;0,F441=E441),"Draw",IF(AND(ISNUMBER(F441),ISNUMBER(E441),E441&gt;0,F441=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A441="","",IF(AND(ISNUMBER(E441),E441=0,OR(ISNUMBER(SEARCH("Free",D441&amp;"")),AND(ISNUMBER(F441),F441=0))),"Subscription",IF(ISNUMBER(G441),"Profit",IF(ISNUMBER(I441),"Disqualified",IF(ISNUMBER(H441),"Draw",IF(AND(ISNUMBER(F441),ISNUMBER(E441),E441&gt;0,F441&gt;E441),"Profit",IF(AND(ISNUMBER(F441),ISNUMBER(E441),E441&gt;0,F441=E441),"Draw",IF(AND(ISNUMBER(F441),ISNUMBER(E441),E441&gt;0,F441=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L441" s="50"/>
       <x:c r="M441" s="58"/>
@@ -17712,7 +17725,7 @@
         <x:f>IF(A442="","",IF(K442="Subscription","",IF(E442=0,"",IF(ISNUMBER(G442),G442/E442,IF(ISNUMBER(I442),-ABS(I442)/E442,IF(ISNUMBER(H442),0,IF(AND(ISNUMBER(F442),ISNUMBER(E442),E442&gt;0,F442&gt;E442),(F442-E442)/E442,IF(AND(ISNUMBER(F442),ISNUMBER(E442),E442&gt;0,F442=E442),0,IF(AND(ISNUMBER(F442),ISNUMBER(E442),E442&gt;0,F442=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K442" s="50" t="str">
-        <x:f>IF(A442="","",IF(AND(ISNUMBER(E442),E442=0,OR(ISNUMBER(SEARCH("Free",D442&amp;"")),AND(ISNUMBER(F442),F442=0))),"Subscription",IF(ISNUMBER(G442),"Profit",IF(ISNUMBER(I442),"Loss",IF(ISNUMBER(H442),"Draw",IF(AND(ISNUMBER(F442),ISNUMBER(E442),E442&gt;0,F442&gt;E442),"Profit",IF(AND(ISNUMBER(F442),ISNUMBER(E442),E442&gt;0,F442=E442),"Draw",IF(AND(ISNUMBER(F442),ISNUMBER(E442),E442&gt;0,F442=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A442="","",IF(AND(ISNUMBER(E442),E442=0,OR(ISNUMBER(SEARCH("Free",D442&amp;"")),AND(ISNUMBER(F442),F442=0))),"Subscription",IF(ISNUMBER(G442),"Profit",IF(ISNUMBER(I442),"Disqualified",IF(ISNUMBER(H442),"Draw",IF(AND(ISNUMBER(F442),ISNUMBER(E442),E442&gt;0,F442&gt;E442),"Profit",IF(AND(ISNUMBER(F442),ISNUMBER(E442),E442&gt;0,F442=E442),"Draw",IF(AND(ISNUMBER(F442),ISNUMBER(E442),E442&gt;0,F442=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L442" s="50"/>
       <x:c r="M442" s="58"/>
@@ -17749,7 +17762,7 @@
         <x:f>IF(A443="","",IF(K443="Subscription","",IF(E443=0,"",IF(ISNUMBER(G443),G443/E443,IF(ISNUMBER(I443),-ABS(I443)/E443,IF(ISNUMBER(H443),0,IF(AND(ISNUMBER(F443),ISNUMBER(E443),E443&gt;0,F443&gt;E443),(F443-E443)/E443,IF(AND(ISNUMBER(F443),ISNUMBER(E443),E443&gt;0,F443=E443),0,IF(AND(ISNUMBER(F443),ISNUMBER(E443),E443&gt;0,F443=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K443" s="50" t="str">
-        <x:f>IF(A443="","",IF(AND(ISNUMBER(E443),E443=0,OR(ISNUMBER(SEARCH("Free",D443&amp;"")),AND(ISNUMBER(F443),F443=0))),"Subscription",IF(ISNUMBER(G443),"Profit",IF(ISNUMBER(I443),"Loss",IF(ISNUMBER(H443),"Draw",IF(AND(ISNUMBER(F443),ISNUMBER(E443),E443&gt;0,F443&gt;E443),"Profit",IF(AND(ISNUMBER(F443),ISNUMBER(E443),E443&gt;0,F443=E443),"Draw",IF(AND(ISNUMBER(F443),ISNUMBER(E443),E443&gt;0,F443=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A443="","",IF(AND(ISNUMBER(E443),E443=0,OR(ISNUMBER(SEARCH("Free",D443&amp;"")),AND(ISNUMBER(F443),F443=0))),"Subscription",IF(ISNUMBER(G443),"Profit",IF(ISNUMBER(I443),"Disqualified",IF(ISNUMBER(H443),"Draw",IF(AND(ISNUMBER(F443),ISNUMBER(E443),E443&gt;0,F443&gt;E443),"Profit",IF(AND(ISNUMBER(F443),ISNUMBER(E443),E443&gt;0,F443=E443),"Draw",IF(AND(ISNUMBER(F443),ISNUMBER(E443),E443&gt;0,F443=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L443" s="50"/>
       <x:c r="M443" s="58"/>
@@ -17786,7 +17799,7 @@
         <x:f>IF(A444="","",IF(K444="Subscription","",IF(E444=0,"",IF(ISNUMBER(G444),G444/E444,IF(ISNUMBER(I444),-ABS(I444)/E444,IF(ISNUMBER(H444),0,IF(AND(ISNUMBER(F444),ISNUMBER(E444),E444&gt;0,F444&gt;E444),(F444-E444)/E444,IF(AND(ISNUMBER(F444),ISNUMBER(E444),E444&gt;0,F444=E444),0,IF(AND(ISNUMBER(F444),ISNUMBER(E444),E444&gt;0,F444=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K444" s="50" t="str">
-        <x:f>IF(A444="","",IF(AND(ISNUMBER(E444),E444=0,OR(ISNUMBER(SEARCH("Free",D444&amp;"")),AND(ISNUMBER(F444),F444=0))),"Subscription",IF(ISNUMBER(G444),"Profit",IF(ISNUMBER(I444),"Loss",IF(ISNUMBER(H444),"Draw",IF(AND(ISNUMBER(F444),ISNUMBER(E444),E444&gt;0,F444&gt;E444),"Profit",IF(AND(ISNUMBER(F444),ISNUMBER(E444),E444&gt;0,F444=E444),"Draw",IF(AND(ISNUMBER(F444),ISNUMBER(E444),E444&gt;0,F444=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A444="","",IF(AND(ISNUMBER(E444),E444=0,OR(ISNUMBER(SEARCH("Free",D444&amp;"")),AND(ISNUMBER(F444),F444=0))),"Subscription",IF(ISNUMBER(G444),"Profit",IF(ISNUMBER(I444),"Disqualified",IF(ISNUMBER(H444),"Draw",IF(AND(ISNUMBER(F444),ISNUMBER(E444),E444&gt;0,F444&gt;E444),"Profit",IF(AND(ISNUMBER(F444),ISNUMBER(E444),E444&gt;0,F444=E444),"Draw",IF(AND(ISNUMBER(F444),ISNUMBER(E444),E444&gt;0,F444=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L444" s="50"/>
       <x:c r="M444" s="58"/>
@@ -17823,7 +17836,7 @@
         <x:f>IF(A445="","",IF(K445="Subscription","",IF(E445=0,"",IF(ISNUMBER(G445),G445/E445,IF(ISNUMBER(I445),-ABS(I445)/E445,IF(ISNUMBER(H445),0,IF(AND(ISNUMBER(F445),ISNUMBER(E445),E445&gt;0,F445&gt;E445),(F445-E445)/E445,IF(AND(ISNUMBER(F445),ISNUMBER(E445),E445&gt;0,F445=E445),0,IF(AND(ISNUMBER(F445),ISNUMBER(E445),E445&gt;0,F445=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K445" s="50" t="str">
-        <x:f>IF(A445="","",IF(AND(ISNUMBER(E445),E445=0,OR(ISNUMBER(SEARCH("Free",D445&amp;"")),AND(ISNUMBER(F445),F445=0))),"Subscription",IF(ISNUMBER(G445),"Profit",IF(ISNUMBER(I445),"Loss",IF(ISNUMBER(H445),"Draw",IF(AND(ISNUMBER(F445),ISNUMBER(E445),E445&gt;0,F445&gt;E445),"Profit",IF(AND(ISNUMBER(F445),ISNUMBER(E445),E445&gt;0,F445=E445),"Draw",IF(AND(ISNUMBER(F445),ISNUMBER(E445),E445&gt;0,F445=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A445="","",IF(AND(ISNUMBER(E445),E445=0,OR(ISNUMBER(SEARCH("Free",D445&amp;"")),AND(ISNUMBER(F445),F445=0))),"Subscription",IF(ISNUMBER(G445),"Profit",IF(ISNUMBER(I445),"Disqualified",IF(ISNUMBER(H445),"Draw",IF(AND(ISNUMBER(F445),ISNUMBER(E445),E445&gt;0,F445&gt;E445),"Profit",IF(AND(ISNUMBER(F445),ISNUMBER(E445),E445&gt;0,F445=E445),"Draw",IF(AND(ISNUMBER(F445),ISNUMBER(E445),E445&gt;0,F445=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L445" s="50"/>
       <x:c r="M445" s="58"/>
@@ -17860,7 +17873,7 @@
         <x:f>IF(A446="","",IF(K446="Subscription","",IF(E446=0,"",IF(ISNUMBER(G446),G446/E446,IF(ISNUMBER(I446),-ABS(I446)/E446,IF(ISNUMBER(H446),0,IF(AND(ISNUMBER(F446),ISNUMBER(E446),E446&gt;0,F446&gt;E446),(F446-E446)/E446,IF(AND(ISNUMBER(F446),ISNUMBER(E446),E446&gt;0,F446=E446),0,IF(AND(ISNUMBER(F446),ISNUMBER(E446),E446&gt;0,F446=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K446" s="50" t="str">
-        <x:f>IF(A446="","",IF(AND(ISNUMBER(E446),E446=0,OR(ISNUMBER(SEARCH("Free",D446&amp;"")),AND(ISNUMBER(F446),F446=0))),"Subscription",IF(ISNUMBER(G446),"Profit",IF(ISNUMBER(I446),"Loss",IF(ISNUMBER(H446),"Draw",IF(AND(ISNUMBER(F446),ISNUMBER(E446),E446&gt;0,F446&gt;E446),"Profit",IF(AND(ISNUMBER(F446),ISNUMBER(E446),E446&gt;0,F446=E446),"Draw",IF(AND(ISNUMBER(F446),ISNUMBER(E446),E446&gt;0,F446=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A446="","",IF(AND(ISNUMBER(E446),E446=0,OR(ISNUMBER(SEARCH("Free",D446&amp;"")),AND(ISNUMBER(F446),F446=0))),"Subscription",IF(ISNUMBER(G446),"Profit",IF(ISNUMBER(I446),"Disqualified",IF(ISNUMBER(H446),"Draw",IF(AND(ISNUMBER(F446),ISNUMBER(E446),E446&gt;0,F446&gt;E446),"Profit",IF(AND(ISNUMBER(F446),ISNUMBER(E446),E446&gt;0,F446=E446),"Draw",IF(AND(ISNUMBER(F446),ISNUMBER(E446),E446&gt;0,F446=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L446" s="50"/>
       <x:c r="M446" s="58"/>
@@ -17897,7 +17910,7 @@
         <x:f>IF(A447="","",IF(K447="Subscription","",IF(E447=0,"",IF(ISNUMBER(G447),G447/E447,IF(ISNUMBER(I447),-ABS(I447)/E447,IF(ISNUMBER(H447),0,IF(AND(ISNUMBER(F447),ISNUMBER(E447),E447&gt;0,F447&gt;E447),(F447-E447)/E447,IF(AND(ISNUMBER(F447),ISNUMBER(E447),E447&gt;0,F447=E447),0,IF(AND(ISNUMBER(F447),ISNUMBER(E447),E447&gt;0,F447=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K447" s="50" t="str">
-        <x:f>IF(A447="","",IF(AND(ISNUMBER(E447),E447=0,OR(ISNUMBER(SEARCH("Free",D447&amp;"")),AND(ISNUMBER(F447),F447=0))),"Subscription",IF(ISNUMBER(G447),"Profit",IF(ISNUMBER(I447),"Loss",IF(ISNUMBER(H447),"Draw",IF(AND(ISNUMBER(F447),ISNUMBER(E447),E447&gt;0,F447&gt;E447),"Profit",IF(AND(ISNUMBER(F447),ISNUMBER(E447),E447&gt;0,F447=E447),"Draw",IF(AND(ISNUMBER(F447),ISNUMBER(E447),E447&gt;0,F447=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A447="","",IF(AND(ISNUMBER(E447),E447=0,OR(ISNUMBER(SEARCH("Free",D447&amp;"")),AND(ISNUMBER(F447),F447=0))),"Subscription",IF(ISNUMBER(G447),"Profit",IF(ISNUMBER(I447),"Disqualified",IF(ISNUMBER(H447),"Draw",IF(AND(ISNUMBER(F447),ISNUMBER(E447),E447&gt;0,F447&gt;E447),"Profit",IF(AND(ISNUMBER(F447),ISNUMBER(E447),E447&gt;0,F447=E447),"Draw",IF(AND(ISNUMBER(F447),ISNUMBER(E447),E447&gt;0,F447=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L447" s="50"/>
       <x:c r="M447" s="58"/>
@@ -17934,7 +17947,7 @@
         <x:f>IF(A448="","",IF(K448="Subscription","",IF(E448=0,"",IF(ISNUMBER(G448),G448/E448,IF(ISNUMBER(I448),-ABS(I448)/E448,IF(ISNUMBER(H448),0,IF(AND(ISNUMBER(F448),ISNUMBER(E448),E448&gt;0,F448&gt;E448),(F448-E448)/E448,IF(AND(ISNUMBER(F448),ISNUMBER(E448),E448&gt;0,F448=E448),0,IF(AND(ISNUMBER(F448),ISNUMBER(E448),E448&gt;0,F448=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K448" s="50" t="str">
-        <x:f>IF(A448="","",IF(AND(ISNUMBER(E448),E448=0,OR(ISNUMBER(SEARCH("Free",D448&amp;"")),AND(ISNUMBER(F448),F448=0))),"Subscription",IF(ISNUMBER(G448),"Profit",IF(ISNUMBER(I448),"Loss",IF(ISNUMBER(H448),"Draw",IF(AND(ISNUMBER(F448),ISNUMBER(E448),E448&gt;0,F448&gt;E448),"Profit",IF(AND(ISNUMBER(F448),ISNUMBER(E448),E448&gt;0,F448=E448),"Draw",IF(AND(ISNUMBER(F448),ISNUMBER(E448),E448&gt;0,F448=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A448="","",IF(AND(ISNUMBER(E448),E448=0,OR(ISNUMBER(SEARCH("Free",D448&amp;"")),AND(ISNUMBER(F448),F448=0))),"Subscription",IF(ISNUMBER(G448),"Profit",IF(ISNUMBER(I448),"Disqualified",IF(ISNUMBER(H448),"Draw",IF(AND(ISNUMBER(F448),ISNUMBER(E448),E448&gt;0,F448&gt;E448),"Profit",IF(AND(ISNUMBER(F448),ISNUMBER(E448),E448&gt;0,F448=E448),"Draw",IF(AND(ISNUMBER(F448),ISNUMBER(E448),E448&gt;0,F448=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L448" s="50"/>
       <x:c r="M448" s="58"/>
@@ -17971,7 +17984,7 @@
         <x:f>IF(A449="","",IF(K449="Subscription","",IF(E449=0,"",IF(ISNUMBER(G449),G449/E449,IF(ISNUMBER(I449),-ABS(I449)/E449,IF(ISNUMBER(H449),0,IF(AND(ISNUMBER(F449),ISNUMBER(E449),E449&gt;0,F449&gt;E449),(F449-E449)/E449,IF(AND(ISNUMBER(F449),ISNUMBER(E449),E449&gt;0,F449=E449),0,IF(AND(ISNUMBER(F449),ISNUMBER(E449),E449&gt;0,F449=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K449" s="50" t="str">
-        <x:f>IF(A449="","",IF(AND(ISNUMBER(E449),E449=0,OR(ISNUMBER(SEARCH("Free",D449&amp;"")),AND(ISNUMBER(F449),F449=0))),"Subscription",IF(ISNUMBER(G449),"Profit",IF(ISNUMBER(I449),"Loss",IF(ISNUMBER(H449),"Draw",IF(AND(ISNUMBER(F449),ISNUMBER(E449),E449&gt;0,F449&gt;E449),"Profit",IF(AND(ISNUMBER(F449),ISNUMBER(E449),E449&gt;0,F449=E449),"Draw",IF(AND(ISNUMBER(F449),ISNUMBER(E449),E449&gt;0,F449=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A449="","",IF(AND(ISNUMBER(E449),E449=0,OR(ISNUMBER(SEARCH("Free",D449&amp;"")),AND(ISNUMBER(F449),F449=0))),"Subscription",IF(ISNUMBER(G449),"Profit",IF(ISNUMBER(I449),"Disqualified",IF(ISNUMBER(H449),"Draw",IF(AND(ISNUMBER(F449),ISNUMBER(E449),E449&gt;0,F449&gt;E449),"Profit",IF(AND(ISNUMBER(F449),ISNUMBER(E449),E449&gt;0,F449=E449),"Draw",IF(AND(ISNUMBER(F449),ISNUMBER(E449),E449&gt;0,F449=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L449" s="50"/>
       <x:c r="M449" s="58"/>
@@ -18008,7 +18021,7 @@
         <x:f>IF(A450="","",IF(K450="Subscription","",IF(E450=0,"",IF(ISNUMBER(G450),G450/E450,IF(ISNUMBER(I450),-ABS(I450)/E450,IF(ISNUMBER(H450),0,IF(AND(ISNUMBER(F450),ISNUMBER(E450),E450&gt;0,F450&gt;E450),(F450-E450)/E450,IF(AND(ISNUMBER(F450),ISNUMBER(E450),E450&gt;0,F450=E450),0,IF(AND(ISNUMBER(F450),ISNUMBER(E450),E450&gt;0,F450=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K450" s="50" t="str">
-        <x:f>IF(A450="","",IF(AND(ISNUMBER(E450),E450=0,OR(ISNUMBER(SEARCH("Free",D450&amp;"")),AND(ISNUMBER(F450),F450=0))),"Subscription",IF(ISNUMBER(G450),"Profit",IF(ISNUMBER(I450),"Loss",IF(ISNUMBER(H450),"Draw",IF(AND(ISNUMBER(F450),ISNUMBER(E450),E450&gt;0,F450&gt;E450),"Profit",IF(AND(ISNUMBER(F450),ISNUMBER(E450),E450&gt;0,F450=E450),"Draw",IF(AND(ISNUMBER(F450),ISNUMBER(E450),E450&gt;0,F450=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A450="","",IF(AND(ISNUMBER(E450),E450=0,OR(ISNUMBER(SEARCH("Free",D450&amp;"")),AND(ISNUMBER(F450),F450=0))),"Subscription",IF(ISNUMBER(G450),"Profit",IF(ISNUMBER(I450),"Disqualified",IF(ISNUMBER(H450),"Draw",IF(AND(ISNUMBER(F450),ISNUMBER(E450),E450&gt;0,F450&gt;E450),"Profit",IF(AND(ISNUMBER(F450),ISNUMBER(E450),E450&gt;0,F450=E450),"Draw",IF(AND(ISNUMBER(F450),ISNUMBER(E450),E450&gt;0,F450=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L450" s="50"/>
       <x:c r="M450" s="58"/>
@@ -18045,7 +18058,7 @@
         <x:f>IF(A451="","",IF(K451="Subscription","",IF(E451=0,"",IF(ISNUMBER(G451),G451/E451,IF(ISNUMBER(I451),-ABS(I451)/E451,IF(ISNUMBER(H451),0,IF(AND(ISNUMBER(F451),ISNUMBER(E451),E451&gt;0,F451&gt;E451),(F451-E451)/E451,IF(AND(ISNUMBER(F451),ISNUMBER(E451),E451&gt;0,F451=E451),0,IF(AND(ISNUMBER(F451),ISNUMBER(E451),E451&gt;0,F451=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K451" s="50" t="str">
-        <x:f>IF(A451="","",IF(AND(ISNUMBER(E451),E451=0,OR(ISNUMBER(SEARCH("Free",D451&amp;"")),AND(ISNUMBER(F451),F451=0))),"Subscription",IF(ISNUMBER(G451),"Profit",IF(ISNUMBER(I451),"Loss",IF(ISNUMBER(H451),"Draw",IF(AND(ISNUMBER(F451),ISNUMBER(E451),E451&gt;0,F451&gt;E451),"Profit",IF(AND(ISNUMBER(F451),ISNUMBER(E451),E451&gt;0,F451=E451),"Draw",IF(AND(ISNUMBER(F451),ISNUMBER(E451),E451&gt;0,F451=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A451="","",IF(AND(ISNUMBER(E451),E451=0,OR(ISNUMBER(SEARCH("Free",D451&amp;"")),AND(ISNUMBER(F451),F451=0))),"Subscription",IF(ISNUMBER(G451),"Profit",IF(ISNUMBER(I451),"Disqualified",IF(ISNUMBER(H451),"Draw",IF(AND(ISNUMBER(F451),ISNUMBER(E451),E451&gt;0,F451&gt;E451),"Profit",IF(AND(ISNUMBER(F451),ISNUMBER(E451),E451&gt;0,F451=E451),"Draw",IF(AND(ISNUMBER(F451),ISNUMBER(E451),E451&gt;0,F451=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L451" s="50"/>
       <x:c r="M451" s="58"/>
@@ -18082,7 +18095,7 @@
         <x:f>IF(A452="","",IF(K452="Subscription","",IF(E452=0,"",IF(ISNUMBER(G452),G452/E452,IF(ISNUMBER(I452),-ABS(I452)/E452,IF(ISNUMBER(H452),0,IF(AND(ISNUMBER(F452),ISNUMBER(E452),E452&gt;0,F452&gt;E452),(F452-E452)/E452,IF(AND(ISNUMBER(F452),ISNUMBER(E452),E452&gt;0,F452=E452),0,IF(AND(ISNUMBER(F452),ISNUMBER(E452),E452&gt;0,F452=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K452" s="50" t="str">
-        <x:f>IF(A452="","",IF(AND(ISNUMBER(E452),E452=0,OR(ISNUMBER(SEARCH("Free",D452&amp;"")),AND(ISNUMBER(F452),F452=0))),"Subscription",IF(ISNUMBER(G452),"Profit",IF(ISNUMBER(I452),"Loss",IF(ISNUMBER(H452),"Draw",IF(AND(ISNUMBER(F452),ISNUMBER(E452),E452&gt;0,F452&gt;E452),"Profit",IF(AND(ISNUMBER(F452),ISNUMBER(E452),E452&gt;0,F452=E452),"Draw",IF(AND(ISNUMBER(F452),ISNUMBER(E452),E452&gt;0,F452=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A452="","",IF(AND(ISNUMBER(E452),E452=0,OR(ISNUMBER(SEARCH("Free",D452&amp;"")),AND(ISNUMBER(F452),F452=0))),"Subscription",IF(ISNUMBER(G452),"Profit",IF(ISNUMBER(I452),"Disqualified",IF(ISNUMBER(H452),"Draw",IF(AND(ISNUMBER(F452),ISNUMBER(E452),E452&gt;0,F452&gt;E452),"Profit",IF(AND(ISNUMBER(F452),ISNUMBER(E452),E452&gt;0,F452=E452),"Draw",IF(AND(ISNUMBER(F452),ISNUMBER(E452),E452&gt;0,F452=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L452" s="50"/>
       <x:c r="M452" s="58"/>
@@ -18119,7 +18132,7 @@
         <x:f>IF(A453="","",IF(K453="Subscription","",IF(E453=0,"",IF(ISNUMBER(G453),G453/E453,IF(ISNUMBER(I453),-ABS(I453)/E453,IF(ISNUMBER(H453),0,IF(AND(ISNUMBER(F453),ISNUMBER(E453),E453&gt;0,F453&gt;E453),(F453-E453)/E453,IF(AND(ISNUMBER(F453),ISNUMBER(E453),E453&gt;0,F453=E453),0,IF(AND(ISNUMBER(F453),ISNUMBER(E453),E453&gt;0,F453=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K453" s="50" t="str">
-        <x:f>IF(A453="","",IF(AND(ISNUMBER(E453),E453=0,OR(ISNUMBER(SEARCH("Free",D453&amp;"")),AND(ISNUMBER(F453),F453=0))),"Subscription",IF(ISNUMBER(G453),"Profit",IF(ISNUMBER(I453),"Loss",IF(ISNUMBER(H453),"Draw",IF(AND(ISNUMBER(F453),ISNUMBER(E453),E453&gt;0,F453&gt;E453),"Profit",IF(AND(ISNUMBER(F453),ISNUMBER(E453),E453&gt;0,F453=E453),"Draw",IF(AND(ISNUMBER(F453),ISNUMBER(E453),E453&gt;0,F453=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A453="","",IF(AND(ISNUMBER(E453),E453=0,OR(ISNUMBER(SEARCH("Free",D453&amp;"")),AND(ISNUMBER(F453),F453=0))),"Subscription",IF(ISNUMBER(G453),"Profit",IF(ISNUMBER(I453),"Disqualified",IF(ISNUMBER(H453),"Draw",IF(AND(ISNUMBER(F453),ISNUMBER(E453),E453&gt;0,F453&gt;E453),"Profit",IF(AND(ISNUMBER(F453),ISNUMBER(E453),E453&gt;0,F453=E453),"Draw",IF(AND(ISNUMBER(F453),ISNUMBER(E453),E453&gt;0,F453=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L453" s="50"/>
       <x:c r="M453" s="58"/>
@@ -18156,7 +18169,7 @@
         <x:f>IF(A454="","",IF(K454="Subscription","",IF(E454=0,"",IF(ISNUMBER(G454),G454/E454,IF(ISNUMBER(I454),-ABS(I454)/E454,IF(ISNUMBER(H454),0,IF(AND(ISNUMBER(F454),ISNUMBER(E454),E454&gt;0,F454&gt;E454),(F454-E454)/E454,IF(AND(ISNUMBER(F454),ISNUMBER(E454),E454&gt;0,F454=E454),0,IF(AND(ISNUMBER(F454),ISNUMBER(E454),E454&gt;0,F454=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K454" s="50" t="str">
-        <x:f>IF(A454="","",IF(AND(ISNUMBER(E454),E454=0,OR(ISNUMBER(SEARCH("Free",D454&amp;"")),AND(ISNUMBER(F454),F454=0))),"Subscription",IF(ISNUMBER(G454),"Profit",IF(ISNUMBER(I454),"Loss",IF(ISNUMBER(H454),"Draw",IF(AND(ISNUMBER(F454),ISNUMBER(E454),E454&gt;0,F454&gt;E454),"Profit",IF(AND(ISNUMBER(F454),ISNUMBER(E454),E454&gt;0,F454=E454),"Draw",IF(AND(ISNUMBER(F454),ISNUMBER(E454),E454&gt;0,F454=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A454="","",IF(AND(ISNUMBER(E454),E454=0,OR(ISNUMBER(SEARCH("Free",D454&amp;"")),AND(ISNUMBER(F454),F454=0))),"Subscription",IF(ISNUMBER(G454),"Profit",IF(ISNUMBER(I454),"Disqualified",IF(ISNUMBER(H454),"Draw",IF(AND(ISNUMBER(F454),ISNUMBER(E454),E454&gt;0,F454&gt;E454),"Profit",IF(AND(ISNUMBER(F454),ISNUMBER(E454),E454&gt;0,F454=E454),"Draw",IF(AND(ISNUMBER(F454),ISNUMBER(E454),E454&gt;0,F454=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L454" s="50"/>
       <x:c r="M454" s="58"/>
@@ -18193,7 +18206,7 @@
         <x:f>IF(A455="","",IF(K455="Subscription","",IF(E455=0,"",IF(ISNUMBER(G455),G455/E455,IF(ISNUMBER(I455),-ABS(I455)/E455,IF(ISNUMBER(H455),0,IF(AND(ISNUMBER(F455),ISNUMBER(E455),E455&gt;0,F455&gt;E455),(F455-E455)/E455,IF(AND(ISNUMBER(F455),ISNUMBER(E455),E455&gt;0,F455=E455),0,IF(AND(ISNUMBER(F455),ISNUMBER(E455),E455&gt;0,F455=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K455" s="50" t="str">
-        <x:f>IF(A455="","",IF(AND(ISNUMBER(E455),E455=0,OR(ISNUMBER(SEARCH("Free",D455&amp;"")),AND(ISNUMBER(F455),F455=0))),"Subscription",IF(ISNUMBER(G455),"Profit",IF(ISNUMBER(I455),"Loss",IF(ISNUMBER(H455),"Draw",IF(AND(ISNUMBER(F455),ISNUMBER(E455),E455&gt;0,F455&gt;E455),"Profit",IF(AND(ISNUMBER(F455),ISNUMBER(E455),E455&gt;0,F455=E455),"Draw",IF(AND(ISNUMBER(F455),ISNUMBER(E455),E455&gt;0,F455=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A455="","",IF(AND(ISNUMBER(E455),E455=0,OR(ISNUMBER(SEARCH("Free",D455&amp;"")),AND(ISNUMBER(F455),F455=0))),"Subscription",IF(ISNUMBER(G455),"Profit",IF(ISNUMBER(I455),"Disqualified",IF(ISNUMBER(H455),"Draw",IF(AND(ISNUMBER(F455),ISNUMBER(E455),E455&gt;0,F455&gt;E455),"Profit",IF(AND(ISNUMBER(F455),ISNUMBER(E455),E455&gt;0,F455=E455),"Draw",IF(AND(ISNUMBER(F455),ISNUMBER(E455),E455&gt;0,F455=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L455" s="50"/>
       <x:c r="M455" s="58"/>
@@ -18230,7 +18243,7 @@
         <x:f>IF(A456="","",IF(K456="Subscription","",IF(E456=0,"",IF(ISNUMBER(G456),G456/E456,IF(ISNUMBER(I456),-ABS(I456)/E456,IF(ISNUMBER(H456),0,IF(AND(ISNUMBER(F456),ISNUMBER(E456),E456&gt;0,F456&gt;E456),(F456-E456)/E456,IF(AND(ISNUMBER(F456),ISNUMBER(E456),E456&gt;0,F456=E456),0,IF(AND(ISNUMBER(F456),ISNUMBER(E456),E456&gt;0,F456=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K456" s="50" t="str">
-        <x:f>IF(A456="","",IF(AND(ISNUMBER(E456),E456=0,OR(ISNUMBER(SEARCH("Free",D456&amp;"")),AND(ISNUMBER(F456),F456=0))),"Subscription",IF(ISNUMBER(G456),"Profit",IF(ISNUMBER(I456),"Loss",IF(ISNUMBER(H456),"Draw",IF(AND(ISNUMBER(F456),ISNUMBER(E456),E456&gt;0,F456&gt;E456),"Profit",IF(AND(ISNUMBER(F456),ISNUMBER(E456),E456&gt;0,F456=E456),"Draw",IF(AND(ISNUMBER(F456),ISNUMBER(E456),E456&gt;0,F456=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A456="","",IF(AND(ISNUMBER(E456),E456=0,OR(ISNUMBER(SEARCH("Free",D456&amp;"")),AND(ISNUMBER(F456),F456=0))),"Subscription",IF(ISNUMBER(G456),"Profit",IF(ISNUMBER(I456),"Disqualified",IF(ISNUMBER(H456),"Draw",IF(AND(ISNUMBER(F456),ISNUMBER(E456),E456&gt;0,F456&gt;E456),"Profit",IF(AND(ISNUMBER(F456),ISNUMBER(E456),E456&gt;0,F456=E456),"Draw",IF(AND(ISNUMBER(F456),ISNUMBER(E456),E456&gt;0,F456=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L456" s="50"/>
       <x:c r="M456" s="58"/>
@@ -18267,7 +18280,7 @@
         <x:f>IF(A457="","",IF(K457="Subscription","",IF(E457=0,"",IF(ISNUMBER(G457),G457/E457,IF(ISNUMBER(I457),-ABS(I457)/E457,IF(ISNUMBER(H457),0,IF(AND(ISNUMBER(F457),ISNUMBER(E457),E457&gt;0,F457&gt;E457),(F457-E457)/E457,IF(AND(ISNUMBER(F457),ISNUMBER(E457),E457&gt;0,F457=E457),0,IF(AND(ISNUMBER(F457),ISNUMBER(E457),E457&gt;0,F457=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K457" s="50" t="str">
-        <x:f>IF(A457="","",IF(AND(ISNUMBER(E457),E457=0,OR(ISNUMBER(SEARCH("Free",D457&amp;"")),AND(ISNUMBER(F457),F457=0))),"Subscription",IF(ISNUMBER(G457),"Profit",IF(ISNUMBER(I457),"Loss",IF(ISNUMBER(H457),"Draw",IF(AND(ISNUMBER(F457),ISNUMBER(E457),E457&gt;0,F457&gt;E457),"Profit",IF(AND(ISNUMBER(F457),ISNUMBER(E457),E457&gt;0,F457=E457),"Draw",IF(AND(ISNUMBER(F457),ISNUMBER(E457),E457&gt;0,F457=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A457="","",IF(AND(ISNUMBER(E457),E457=0,OR(ISNUMBER(SEARCH("Free",D457&amp;"")),AND(ISNUMBER(F457),F457=0))),"Subscription",IF(ISNUMBER(G457),"Profit",IF(ISNUMBER(I457),"Disqualified",IF(ISNUMBER(H457),"Draw",IF(AND(ISNUMBER(F457),ISNUMBER(E457),E457&gt;0,F457&gt;E457),"Profit",IF(AND(ISNUMBER(F457),ISNUMBER(E457),E457&gt;0,F457=E457),"Draw",IF(AND(ISNUMBER(F457),ISNUMBER(E457),E457&gt;0,F457=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L457" s="50"/>
       <x:c r="M457" s="58"/>
@@ -18304,7 +18317,7 @@
         <x:f>IF(A458="","",IF(K458="Subscription","",IF(E458=0,"",IF(ISNUMBER(G458),G458/E458,IF(ISNUMBER(I458),-ABS(I458)/E458,IF(ISNUMBER(H458),0,IF(AND(ISNUMBER(F458),ISNUMBER(E458),E458&gt;0,F458&gt;E458),(F458-E458)/E458,IF(AND(ISNUMBER(F458),ISNUMBER(E458),E458&gt;0,F458=E458),0,IF(AND(ISNUMBER(F458),ISNUMBER(E458),E458&gt;0,F458=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K458" s="50" t="str">
-        <x:f>IF(A458="","",IF(AND(ISNUMBER(E458),E458=0,OR(ISNUMBER(SEARCH("Free",D458&amp;"")),AND(ISNUMBER(F458),F458=0))),"Subscription",IF(ISNUMBER(G458),"Profit",IF(ISNUMBER(I458),"Loss",IF(ISNUMBER(H458),"Draw",IF(AND(ISNUMBER(F458),ISNUMBER(E458),E458&gt;0,F458&gt;E458),"Profit",IF(AND(ISNUMBER(F458),ISNUMBER(E458),E458&gt;0,F458=E458),"Draw",IF(AND(ISNUMBER(F458),ISNUMBER(E458),E458&gt;0,F458=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A458="","",IF(AND(ISNUMBER(E458),E458=0,OR(ISNUMBER(SEARCH("Free",D458&amp;"")),AND(ISNUMBER(F458),F458=0))),"Subscription",IF(ISNUMBER(G458),"Profit",IF(ISNUMBER(I458),"Disqualified",IF(ISNUMBER(H458),"Draw",IF(AND(ISNUMBER(F458),ISNUMBER(E458),E458&gt;0,F458&gt;E458),"Profit",IF(AND(ISNUMBER(F458),ISNUMBER(E458),E458&gt;0,F458=E458),"Draw",IF(AND(ISNUMBER(F458),ISNUMBER(E458),E458&gt;0,F458=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L458" s="50"/>
       <x:c r="M458" s="58"/>
@@ -18341,7 +18354,7 @@
         <x:f>IF(A459="","",IF(K459="Subscription","",IF(E459=0,"",IF(ISNUMBER(G459),G459/E459,IF(ISNUMBER(I459),-ABS(I459)/E459,IF(ISNUMBER(H459),0,IF(AND(ISNUMBER(F459),ISNUMBER(E459),E459&gt;0,F459&gt;E459),(F459-E459)/E459,IF(AND(ISNUMBER(F459),ISNUMBER(E459),E459&gt;0,F459=E459),0,IF(AND(ISNUMBER(F459),ISNUMBER(E459),E459&gt;0,F459=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K459" s="50" t="str">
-        <x:f>IF(A459="","",IF(AND(ISNUMBER(E459),E459=0,OR(ISNUMBER(SEARCH("Free",D459&amp;"")),AND(ISNUMBER(F459),F459=0))),"Subscription",IF(ISNUMBER(G459),"Profit",IF(ISNUMBER(I459),"Loss",IF(ISNUMBER(H459),"Draw",IF(AND(ISNUMBER(F459),ISNUMBER(E459),E459&gt;0,F459&gt;E459),"Profit",IF(AND(ISNUMBER(F459),ISNUMBER(E459),E459&gt;0,F459=E459),"Draw",IF(AND(ISNUMBER(F459),ISNUMBER(E459),E459&gt;0,F459=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A459="","",IF(AND(ISNUMBER(E459),E459=0,OR(ISNUMBER(SEARCH("Free",D459&amp;"")),AND(ISNUMBER(F459),F459=0))),"Subscription",IF(ISNUMBER(G459),"Profit",IF(ISNUMBER(I459),"Disqualified",IF(ISNUMBER(H459),"Draw",IF(AND(ISNUMBER(F459),ISNUMBER(E459),E459&gt;0,F459&gt;E459),"Profit",IF(AND(ISNUMBER(F459),ISNUMBER(E459),E459&gt;0,F459=E459),"Draw",IF(AND(ISNUMBER(F459),ISNUMBER(E459),E459&gt;0,F459=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L459" s="50"/>
       <x:c r="M459" s="58"/>
@@ -18378,7 +18391,7 @@
         <x:f>IF(A460="","",IF(K460="Subscription","",IF(E460=0,"",IF(ISNUMBER(G460),G460/E460,IF(ISNUMBER(I460),-ABS(I460)/E460,IF(ISNUMBER(H460),0,IF(AND(ISNUMBER(F460),ISNUMBER(E460),E460&gt;0,F460&gt;E460),(F460-E460)/E460,IF(AND(ISNUMBER(F460),ISNUMBER(E460),E460&gt;0,F460=E460),0,IF(AND(ISNUMBER(F460),ISNUMBER(E460),E460&gt;0,F460=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K460" s="50" t="str">
-        <x:f>IF(A460="","",IF(AND(ISNUMBER(E460),E460=0,OR(ISNUMBER(SEARCH("Free",D460&amp;"")),AND(ISNUMBER(F460),F460=0))),"Subscription",IF(ISNUMBER(G460),"Profit",IF(ISNUMBER(I460),"Loss",IF(ISNUMBER(H460),"Draw",IF(AND(ISNUMBER(F460),ISNUMBER(E460),E460&gt;0,F460&gt;E460),"Profit",IF(AND(ISNUMBER(F460),ISNUMBER(E460),E460&gt;0,F460=E460),"Draw",IF(AND(ISNUMBER(F460),ISNUMBER(E460),E460&gt;0,F460=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A460="","",IF(AND(ISNUMBER(E460),E460=0,OR(ISNUMBER(SEARCH("Free",D460&amp;"")),AND(ISNUMBER(F460),F460=0))),"Subscription",IF(ISNUMBER(G460),"Profit",IF(ISNUMBER(I460),"Disqualified",IF(ISNUMBER(H460),"Draw",IF(AND(ISNUMBER(F460),ISNUMBER(E460),E460&gt;0,F460&gt;E460),"Profit",IF(AND(ISNUMBER(F460),ISNUMBER(E460),E460&gt;0,F460=E460),"Draw",IF(AND(ISNUMBER(F460),ISNUMBER(E460),E460&gt;0,F460=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L460" s="50"/>
       <x:c r="M460" s="58"/>
@@ -18415,7 +18428,7 @@
         <x:f>IF(A461="","",IF(K461="Subscription","",IF(E461=0,"",IF(ISNUMBER(G461),G461/E461,IF(ISNUMBER(I461),-ABS(I461)/E461,IF(ISNUMBER(H461),0,IF(AND(ISNUMBER(F461),ISNUMBER(E461),E461&gt;0,F461&gt;E461),(F461-E461)/E461,IF(AND(ISNUMBER(F461),ISNUMBER(E461),E461&gt;0,F461=E461),0,IF(AND(ISNUMBER(F461),ISNUMBER(E461),E461&gt;0,F461=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K461" s="50" t="str">
-        <x:f>IF(A461="","",IF(AND(ISNUMBER(E461),E461=0,OR(ISNUMBER(SEARCH("Free",D461&amp;"")),AND(ISNUMBER(F461),F461=0))),"Subscription",IF(ISNUMBER(G461),"Profit",IF(ISNUMBER(I461),"Loss",IF(ISNUMBER(H461),"Draw",IF(AND(ISNUMBER(F461),ISNUMBER(E461),E461&gt;0,F461&gt;E461),"Profit",IF(AND(ISNUMBER(F461),ISNUMBER(E461),E461&gt;0,F461=E461),"Draw",IF(AND(ISNUMBER(F461),ISNUMBER(E461),E461&gt;0,F461=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A461="","",IF(AND(ISNUMBER(E461),E461=0,OR(ISNUMBER(SEARCH("Free",D461&amp;"")),AND(ISNUMBER(F461),F461=0))),"Subscription",IF(ISNUMBER(G461),"Profit",IF(ISNUMBER(I461),"Disqualified",IF(ISNUMBER(H461),"Draw",IF(AND(ISNUMBER(F461),ISNUMBER(E461),E461&gt;0,F461&gt;E461),"Profit",IF(AND(ISNUMBER(F461),ISNUMBER(E461),E461&gt;0,F461=E461),"Draw",IF(AND(ISNUMBER(F461),ISNUMBER(E461),E461&gt;0,F461=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L461" s="50"/>
       <x:c r="M461" s="58"/>
@@ -18452,7 +18465,7 @@
         <x:f>IF(A462="","",IF(K462="Subscription","",IF(E462=0,"",IF(ISNUMBER(G462),G462/E462,IF(ISNUMBER(I462),-ABS(I462)/E462,IF(ISNUMBER(H462),0,IF(AND(ISNUMBER(F462),ISNUMBER(E462),E462&gt;0,F462&gt;E462),(F462-E462)/E462,IF(AND(ISNUMBER(F462),ISNUMBER(E462),E462&gt;0,F462=E462),0,IF(AND(ISNUMBER(F462),ISNUMBER(E462),E462&gt;0,F462=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K462" s="50" t="str">
-        <x:f>IF(A462="","",IF(AND(ISNUMBER(E462),E462=0,OR(ISNUMBER(SEARCH("Free",D462&amp;"")),AND(ISNUMBER(F462),F462=0))),"Subscription",IF(ISNUMBER(G462),"Profit",IF(ISNUMBER(I462),"Loss",IF(ISNUMBER(H462),"Draw",IF(AND(ISNUMBER(F462),ISNUMBER(E462),E462&gt;0,F462&gt;E462),"Profit",IF(AND(ISNUMBER(F462),ISNUMBER(E462),E462&gt;0,F462=E462),"Draw",IF(AND(ISNUMBER(F462),ISNUMBER(E462),E462&gt;0,F462=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A462="","",IF(AND(ISNUMBER(E462),E462=0,OR(ISNUMBER(SEARCH("Free",D462&amp;"")),AND(ISNUMBER(F462),F462=0))),"Subscription",IF(ISNUMBER(G462),"Profit",IF(ISNUMBER(I462),"Disqualified",IF(ISNUMBER(H462),"Draw",IF(AND(ISNUMBER(F462),ISNUMBER(E462),E462&gt;0,F462&gt;E462),"Profit",IF(AND(ISNUMBER(F462),ISNUMBER(E462),E462&gt;0,F462=E462),"Draw",IF(AND(ISNUMBER(F462),ISNUMBER(E462),E462&gt;0,F462=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L462" s="50"/>
       <x:c r="M462" s="58"/>
@@ -18489,7 +18502,7 @@
         <x:f>IF(A463="","",IF(K463="Subscription","",IF(E463=0,"",IF(ISNUMBER(G463),G463/E463,IF(ISNUMBER(I463),-ABS(I463)/E463,IF(ISNUMBER(H463),0,IF(AND(ISNUMBER(F463),ISNUMBER(E463),E463&gt;0,F463&gt;E463),(F463-E463)/E463,IF(AND(ISNUMBER(F463),ISNUMBER(E463),E463&gt;0,F463=E463),0,IF(AND(ISNUMBER(F463),ISNUMBER(E463),E463&gt;0,F463=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K463" s="50" t="str">
-        <x:f>IF(A463="","",IF(AND(ISNUMBER(E463),E463=0,OR(ISNUMBER(SEARCH("Free",D463&amp;"")),AND(ISNUMBER(F463),F463=0))),"Subscription",IF(ISNUMBER(G463),"Profit",IF(ISNUMBER(I463),"Loss",IF(ISNUMBER(H463),"Draw",IF(AND(ISNUMBER(F463),ISNUMBER(E463),E463&gt;0,F463&gt;E463),"Profit",IF(AND(ISNUMBER(F463),ISNUMBER(E463),E463&gt;0,F463=E463),"Draw",IF(AND(ISNUMBER(F463),ISNUMBER(E463),E463&gt;0,F463=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A463="","",IF(AND(ISNUMBER(E463),E463=0,OR(ISNUMBER(SEARCH("Free",D463&amp;"")),AND(ISNUMBER(F463),F463=0))),"Subscription",IF(ISNUMBER(G463),"Profit",IF(ISNUMBER(I463),"Disqualified",IF(ISNUMBER(H463),"Draw",IF(AND(ISNUMBER(F463),ISNUMBER(E463),E463&gt;0,F463&gt;E463),"Profit",IF(AND(ISNUMBER(F463),ISNUMBER(E463),E463&gt;0,F463=E463),"Draw",IF(AND(ISNUMBER(F463),ISNUMBER(E463),E463&gt;0,F463=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L463" s="50"/>
       <x:c r="M463" s="58"/>
@@ -18526,7 +18539,7 @@
         <x:f>IF(A464="","",IF(K464="Subscription","",IF(E464=0,"",IF(ISNUMBER(G464),G464/E464,IF(ISNUMBER(I464),-ABS(I464)/E464,IF(ISNUMBER(H464),0,IF(AND(ISNUMBER(F464),ISNUMBER(E464),E464&gt;0,F464&gt;E464),(F464-E464)/E464,IF(AND(ISNUMBER(F464),ISNUMBER(E464),E464&gt;0,F464=E464),0,IF(AND(ISNUMBER(F464),ISNUMBER(E464),E464&gt;0,F464=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K464" s="50" t="str">
-        <x:f>IF(A464="","",IF(AND(ISNUMBER(E464),E464=0,OR(ISNUMBER(SEARCH("Free",D464&amp;"")),AND(ISNUMBER(F464),F464=0))),"Subscription",IF(ISNUMBER(G464),"Profit",IF(ISNUMBER(I464),"Loss",IF(ISNUMBER(H464),"Draw",IF(AND(ISNUMBER(F464),ISNUMBER(E464),E464&gt;0,F464&gt;E464),"Profit",IF(AND(ISNUMBER(F464),ISNUMBER(E464),E464&gt;0,F464=E464),"Draw",IF(AND(ISNUMBER(F464),ISNUMBER(E464),E464&gt;0,F464=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A464="","",IF(AND(ISNUMBER(E464),E464=0,OR(ISNUMBER(SEARCH("Free",D464&amp;"")),AND(ISNUMBER(F464),F464=0))),"Subscription",IF(ISNUMBER(G464),"Profit",IF(ISNUMBER(I464),"Disqualified",IF(ISNUMBER(H464),"Draw",IF(AND(ISNUMBER(F464),ISNUMBER(E464),E464&gt;0,F464&gt;E464),"Profit",IF(AND(ISNUMBER(F464),ISNUMBER(E464),E464&gt;0,F464=E464),"Draw",IF(AND(ISNUMBER(F464),ISNUMBER(E464),E464&gt;0,F464=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L464" s="50"/>
       <x:c r="M464" s="58"/>
@@ -18563,7 +18576,7 @@
         <x:f>IF(A465="","",IF(K465="Subscription","",IF(E465=0,"",IF(ISNUMBER(G465),G465/E465,IF(ISNUMBER(I465),-ABS(I465)/E465,IF(ISNUMBER(H465),0,IF(AND(ISNUMBER(F465),ISNUMBER(E465),E465&gt;0,F465&gt;E465),(F465-E465)/E465,IF(AND(ISNUMBER(F465),ISNUMBER(E465),E465&gt;0,F465=E465),0,IF(AND(ISNUMBER(F465),ISNUMBER(E465),E465&gt;0,F465=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K465" s="50" t="str">
-        <x:f>IF(A465="","",IF(AND(ISNUMBER(E465),E465=0,OR(ISNUMBER(SEARCH("Free",D465&amp;"")),AND(ISNUMBER(F465),F465=0))),"Subscription",IF(ISNUMBER(G465),"Profit",IF(ISNUMBER(I465),"Loss",IF(ISNUMBER(H465),"Draw",IF(AND(ISNUMBER(F465),ISNUMBER(E465),E465&gt;0,F465&gt;E465),"Profit",IF(AND(ISNUMBER(F465),ISNUMBER(E465),E465&gt;0,F465=E465),"Draw",IF(AND(ISNUMBER(F465),ISNUMBER(E465),E465&gt;0,F465=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A465="","",IF(AND(ISNUMBER(E465),E465=0,OR(ISNUMBER(SEARCH("Free",D465&amp;"")),AND(ISNUMBER(F465),F465=0))),"Subscription",IF(ISNUMBER(G465),"Profit",IF(ISNUMBER(I465),"Disqualified",IF(ISNUMBER(H465),"Draw",IF(AND(ISNUMBER(F465),ISNUMBER(E465),E465&gt;0,F465&gt;E465),"Profit",IF(AND(ISNUMBER(F465),ISNUMBER(E465),E465&gt;0,F465=E465),"Draw",IF(AND(ISNUMBER(F465),ISNUMBER(E465),E465&gt;0,F465=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L465" s="50"/>
       <x:c r="M465" s="58"/>
@@ -18600,7 +18613,7 @@
         <x:f>IF(A466="","",IF(K466="Subscription","",IF(E466=0,"",IF(ISNUMBER(G466),G466/E466,IF(ISNUMBER(I466),-ABS(I466)/E466,IF(ISNUMBER(H466),0,IF(AND(ISNUMBER(F466),ISNUMBER(E466),E466&gt;0,F466&gt;E466),(F466-E466)/E466,IF(AND(ISNUMBER(F466),ISNUMBER(E466),E466&gt;0,F466=E466),0,IF(AND(ISNUMBER(F466),ISNUMBER(E466),E466&gt;0,F466=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K466" s="50" t="str">
-        <x:f>IF(A466="","",IF(AND(ISNUMBER(E466),E466=0,OR(ISNUMBER(SEARCH("Free",D466&amp;"")),AND(ISNUMBER(F466),F466=0))),"Subscription",IF(ISNUMBER(G466),"Profit",IF(ISNUMBER(I466),"Loss",IF(ISNUMBER(H466),"Draw",IF(AND(ISNUMBER(F466),ISNUMBER(E466),E466&gt;0,F466&gt;E466),"Profit",IF(AND(ISNUMBER(F466),ISNUMBER(E466),E466&gt;0,F466=E466),"Draw",IF(AND(ISNUMBER(F466),ISNUMBER(E466),E466&gt;0,F466=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A466="","",IF(AND(ISNUMBER(E466),E466=0,OR(ISNUMBER(SEARCH("Free",D466&amp;"")),AND(ISNUMBER(F466),F466=0))),"Subscription",IF(ISNUMBER(G466),"Profit",IF(ISNUMBER(I466),"Disqualified",IF(ISNUMBER(H466),"Draw",IF(AND(ISNUMBER(F466),ISNUMBER(E466),E466&gt;0,F466&gt;E466),"Profit",IF(AND(ISNUMBER(F466),ISNUMBER(E466),E466&gt;0,F466=E466),"Draw",IF(AND(ISNUMBER(F466),ISNUMBER(E466),E466&gt;0,F466=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L466" s="50"/>
       <x:c r="M466" s="58"/>
@@ -18637,7 +18650,7 @@
         <x:f>IF(A467="","",IF(K467="Subscription","",IF(E467=0,"",IF(ISNUMBER(G467),G467/E467,IF(ISNUMBER(I467),-ABS(I467)/E467,IF(ISNUMBER(H467),0,IF(AND(ISNUMBER(F467),ISNUMBER(E467),E467&gt;0,F467&gt;E467),(F467-E467)/E467,IF(AND(ISNUMBER(F467),ISNUMBER(E467),E467&gt;0,F467=E467),0,IF(AND(ISNUMBER(F467),ISNUMBER(E467),E467&gt;0,F467=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K467" s="50" t="str">
-        <x:f>IF(A467="","",IF(AND(ISNUMBER(E467),E467=0,OR(ISNUMBER(SEARCH("Free",D467&amp;"")),AND(ISNUMBER(F467),F467=0))),"Subscription",IF(ISNUMBER(G467),"Profit",IF(ISNUMBER(I467),"Loss",IF(ISNUMBER(H467),"Draw",IF(AND(ISNUMBER(F467),ISNUMBER(E467),E467&gt;0,F467&gt;E467),"Profit",IF(AND(ISNUMBER(F467),ISNUMBER(E467),E467&gt;0,F467=E467),"Draw",IF(AND(ISNUMBER(F467),ISNUMBER(E467),E467&gt;0,F467=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A467="","",IF(AND(ISNUMBER(E467),E467=0,OR(ISNUMBER(SEARCH("Free",D467&amp;"")),AND(ISNUMBER(F467),F467=0))),"Subscription",IF(ISNUMBER(G467),"Profit",IF(ISNUMBER(I467),"Disqualified",IF(ISNUMBER(H467),"Draw",IF(AND(ISNUMBER(F467),ISNUMBER(E467),E467&gt;0,F467&gt;E467),"Profit",IF(AND(ISNUMBER(F467),ISNUMBER(E467),E467&gt;0,F467=E467),"Draw",IF(AND(ISNUMBER(F467),ISNUMBER(E467),E467&gt;0,F467=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L467" s="50"/>
       <x:c r="M467" s="58"/>
@@ -18674,7 +18687,7 @@
         <x:f>IF(A468="","",IF(K468="Subscription","",IF(E468=0,"",IF(ISNUMBER(G468),G468/E468,IF(ISNUMBER(I468),-ABS(I468)/E468,IF(ISNUMBER(H468),0,IF(AND(ISNUMBER(F468),ISNUMBER(E468),E468&gt;0,F468&gt;E468),(F468-E468)/E468,IF(AND(ISNUMBER(F468),ISNUMBER(E468),E468&gt;0,F468=E468),0,IF(AND(ISNUMBER(F468),ISNUMBER(E468),E468&gt;0,F468=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K468" s="50" t="str">
-        <x:f>IF(A468="","",IF(AND(ISNUMBER(E468),E468=0,OR(ISNUMBER(SEARCH("Free",D468&amp;"")),AND(ISNUMBER(F468),F468=0))),"Subscription",IF(ISNUMBER(G468),"Profit",IF(ISNUMBER(I468),"Loss",IF(ISNUMBER(H468),"Draw",IF(AND(ISNUMBER(F468),ISNUMBER(E468),E468&gt;0,F468&gt;E468),"Profit",IF(AND(ISNUMBER(F468),ISNUMBER(E468),E468&gt;0,F468=E468),"Draw",IF(AND(ISNUMBER(F468),ISNUMBER(E468),E468&gt;0,F468=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A468="","",IF(AND(ISNUMBER(E468),E468=0,OR(ISNUMBER(SEARCH("Free",D468&amp;"")),AND(ISNUMBER(F468),F468=0))),"Subscription",IF(ISNUMBER(G468),"Profit",IF(ISNUMBER(I468),"Disqualified",IF(ISNUMBER(H468),"Draw",IF(AND(ISNUMBER(F468),ISNUMBER(E468),E468&gt;0,F468&gt;E468),"Profit",IF(AND(ISNUMBER(F468),ISNUMBER(E468),E468&gt;0,F468=E468),"Draw",IF(AND(ISNUMBER(F468),ISNUMBER(E468),E468&gt;0,F468=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L468" s="50"/>
       <x:c r="M468" s="58"/>
@@ -18711,7 +18724,7 @@
         <x:f>IF(A469="","",IF(K469="Subscription","",IF(E469=0,"",IF(ISNUMBER(G469),G469/E469,IF(ISNUMBER(I469),-ABS(I469)/E469,IF(ISNUMBER(H469),0,IF(AND(ISNUMBER(F469),ISNUMBER(E469),E469&gt;0,F469&gt;E469),(F469-E469)/E469,IF(AND(ISNUMBER(F469),ISNUMBER(E469),E469&gt;0,F469=E469),0,IF(AND(ISNUMBER(F469),ISNUMBER(E469),E469&gt;0,F469=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K469" s="50" t="str">
-        <x:f>IF(A469="","",IF(AND(ISNUMBER(E469),E469=0,OR(ISNUMBER(SEARCH("Free",D469&amp;"")),AND(ISNUMBER(F469),F469=0))),"Subscription",IF(ISNUMBER(G469),"Profit",IF(ISNUMBER(I469),"Loss",IF(ISNUMBER(H469),"Draw",IF(AND(ISNUMBER(F469),ISNUMBER(E469),E469&gt;0,F469&gt;E469),"Profit",IF(AND(ISNUMBER(F469),ISNUMBER(E469),E469&gt;0,F469=E469),"Draw",IF(AND(ISNUMBER(F469),ISNUMBER(E469),E469&gt;0,F469=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A469="","",IF(AND(ISNUMBER(E469),E469=0,OR(ISNUMBER(SEARCH("Free",D469&amp;"")),AND(ISNUMBER(F469),F469=0))),"Subscription",IF(ISNUMBER(G469),"Profit",IF(ISNUMBER(I469),"Disqualified",IF(ISNUMBER(H469),"Draw",IF(AND(ISNUMBER(F469),ISNUMBER(E469),E469&gt;0,F469&gt;E469),"Profit",IF(AND(ISNUMBER(F469),ISNUMBER(E469),E469&gt;0,F469=E469),"Draw",IF(AND(ISNUMBER(F469),ISNUMBER(E469),E469&gt;0,F469=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L469" s="50"/>
       <x:c r="M469" s="58"/>
@@ -18748,7 +18761,7 @@
         <x:f>IF(A470="","",IF(K470="Subscription","",IF(E470=0,"",IF(ISNUMBER(G470),G470/E470,IF(ISNUMBER(I470),-ABS(I470)/E470,IF(ISNUMBER(H470),0,IF(AND(ISNUMBER(F470),ISNUMBER(E470),E470&gt;0,F470&gt;E470),(F470-E470)/E470,IF(AND(ISNUMBER(F470),ISNUMBER(E470),E470&gt;0,F470=E470),0,IF(AND(ISNUMBER(F470),ISNUMBER(E470),E470&gt;0,F470=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K470" s="50" t="str">
-        <x:f>IF(A470="","",IF(AND(ISNUMBER(E470),E470=0,OR(ISNUMBER(SEARCH("Free",D470&amp;"")),AND(ISNUMBER(F470),F470=0))),"Subscription",IF(ISNUMBER(G470),"Profit",IF(ISNUMBER(I470),"Loss",IF(ISNUMBER(H470),"Draw",IF(AND(ISNUMBER(F470),ISNUMBER(E470),E470&gt;0,F470&gt;E470),"Profit",IF(AND(ISNUMBER(F470),ISNUMBER(E470),E470&gt;0,F470=E470),"Draw",IF(AND(ISNUMBER(F470),ISNUMBER(E470),E470&gt;0,F470=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A470="","",IF(AND(ISNUMBER(E470),E470=0,OR(ISNUMBER(SEARCH("Free",D470&amp;"")),AND(ISNUMBER(F470),F470=0))),"Subscription",IF(ISNUMBER(G470),"Profit",IF(ISNUMBER(I470),"Disqualified",IF(ISNUMBER(H470),"Draw",IF(AND(ISNUMBER(F470),ISNUMBER(E470),E470&gt;0,F470&gt;E470),"Profit",IF(AND(ISNUMBER(F470),ISNUMBER(E470),E470&gt;0,F470=E470),"Draw",IF(AND(ISNUMBER(F470),ISNUMBER(E470),E470&gt;0,F470=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L470" s="50"/>
       <x:c r="M470" s="58"/>
@@ -18785,7 +18798,7 @@
         <x:f>IF(A471="","",IF(K471="Subscription","",IF(E471=0,"",IF(ISNUMBER(G471),G471/E471,IF(ISNUMBER(I471),-ABS(I471)/E471,IF(ISNUMBER(H471),0,IF(AND(ISNUMBER(F471),ISNUMBER(E471),E471&gt;0,F471&gt;E471),(F471-E471)/E471,IF(AND(ISNUMBER(F471),ISNUMBER(E471),E471&gt;0,F471=E471),0,IF(AND(ISNUMBER(F471),ISNUMBER(E471),E471&gt;0,F471=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K471" s="50" t="str">
-        <x:f>IF(A471="","",IF(AND(ISNUMBER(E471),E471=0,OR(ISNUMBER(SEARCH("Free",D471&amp;"")),AND(ISNUMBER(F471),F471=0))),"Subscription",IF(ISNUMBER(G471),"Profit",IF(ISNUMBER(I471),"Loss",IF(ISNUMBER(H471),"Draw",IF(AND(ISNUMBER(F471),ISNUMBER(E471),E471&gt;0,F471&gt;E471),"Profit",IF(AND(ISNUMBER(F471),ISNUMBER(E471),E471&gt;0,F471=E471),"Draw",IF(AND(ISNUMBER(F471),ISNUMBER(E471),E471&gt;0,F471=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A471="","",IF(AND(ISNUMBER(E471),E471=0,OR(ISNUMBER(SEARCH("Free",D471&amp;"")),AND(ISNUMBER(F471),F471=0))),"Subscription",IF(ISNUMBER(G471),"Profit",IF(ISNUMBER(I471),"Disqualified",IF(ISNUMBER(H471),"Draw",IF(AND(ISNUMBER(F471),ISNUMBER(E471),E471&gt;0,F471&gt;E471),"Profit",IF(AND(ISNUMBER(F471),ISNUMBER(E471),E471&gt;0,F471=E471),"Draw",IF(AND(ISNUMBER(F471),ISNUMBER(E471),E471&gt;0,F471=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L471" s="50"/>
       <x:c r="M471" s="58"/>
@@ -18822,7 +18835,7 @@
         <x:f>IF(A472="","",IF(K472="Subscription","",IF(E472=0,"",IF(ISNUMBER(G472),G472/E472,IF(ISNUMBER(I472),-ABS(I472)/E472,IF(ISNUMBER(H472),0,IF(AND(ISNUMBER(F472),ISNUMBER(E472),E472&gt;0,F472&gt;E472),(F472-E472)/E472,IF(AND(ISNUMBER(F472),ISNUMBER(E472),E472&gt;0,F472=E472),0,IF(AND(ISNUMBER(F472),ISNUMBER(E472),E472&gt;0,F472=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K472" s="50" t="str">
-        <x:f>IF(A472="","",IF(AND(ISNUMBER(E472),E472=0,OR(ISNUMBER(SEARCH("Free",D472&amp;"")),AND(ISNUMBER(F472),F472=0))),"Subscription",IF(ISNUMBER(G472),"Profit",IF(ISNUMBER(I472),"Loss",IF(ISNUMBER(H472),"Draw",IF(AND(ISNUMBER(F472),ISNUMBER(E472),E472&gt;0,F472&gt;E472),"Profit",IF(AND(ISNUMBER(F472),ISNUMBER(E472),E472&gt;0,F472=E472),"Draw",IF(AND(ISNUMBER(F472),ISNUMBER(E472),E472&gt;0,F472=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A472="","",IF(AND(ISNUMBER(E472),E472=0,OR(ISNUMBER(SEARCH("Free",D472&amp;"")),AND(ISNUMBER(F472),F472=0))),"Subscription",IF(ISNUMBER(G472),"Profit",IF(ISNUMBER(I472),"Disqualified",IF(ISNUMBER(H472),"Draw",IF(AND(ISNUMBER(F472),ISNUMBER(E472),E472&gt;0,F472&gt;E472),"Profit",IF(AND(ISNUMBER(F472),ISNUMBER(E472),E472&gt;0,F472=E472),"Draw",IF(AND(ISNUMBER(F472),ISNUMBER(E472),E472&gt;0,F472=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L472" s="50"/>
       <x:c r="M472" s="58"/>
@@ -18859,7 +18872,7 @@
         <x:f>IF(A473="","",IF(K473="Subscription","",IF(E473=0,"",IF(ISNUMBER(G473),G473/E473,IF(ISNUMBER(I473),-ABS(I473)/E473,IF(ISNUMBER(H473),0,IF(AND(ISNUMBER(F473),ISNUMBER(E473),E473&gt;0,F473&gt;E473),(F473-E473)/E473,IF(AND(ISNUMBER(F473),ISNUMBER(E473),E473&gt;0,F473=E473),0,IF(AND(ISNUMBER(F473),ISNUMBER(E473),E473&gt;0,F473=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K473" s="50" t="str">
-        <x:f>IF(A473="","",IF(AND(ISNUMBER(E473),E473=0,OR(ISNUMBER(SEARCH("Free",D473&amp;"")),AND(ISNUMBER(F473),F473=0))),"Subscription",IF(ISNUMBER(G473),"Profit",IF(ISNUMBER(I473),"Loss",IF(ISNUMBER(H473),"Draw",IF(AND(ISNUMBER(F473),ISNUMBER(E473),E473&gt;0,F473&gt;E473),"Profit",IF(AND(ISNUMBER(F473),ISNUMBER(E473),E473&gt;0,F473=E473),"Draw",IF(AND(ISNUMBER(F473),ISNUMBER(E473),E473&gt;0,F473=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A473="","",IF(AND(ISNUMBER(E473),E473=0,OR(ISNUMBER(SEARCH("Free",D473&amp;"")),AND(ISNUMBER(F473),F473=0))),"Subscription",IF(ISNUMBER(G473),"Profit",IF(ISNUMBER(I473),"Disqualified",IF(ISNUMBER(H473),"Draw",IF(AND(ISNUMBER(F473),ISNUMBER(E473),E473&gt;0,F473&gt;E473),"Profit",IF(AND(ISNUMBER(F473),ISNUMBER(E473),E473&gt;0,F473=E473),"Draw",IF(AND(ISNUMBER(F473),ISNUMBER(E473),E473&gt;0,F473=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L473" s="50"/>
       <x:c r="M473" s="58"/>
@@ -18896,7 +18909,7 @@
         <x:f>IF(A474="","",IF(K474="Subscription","",IF(E474=0,"",IF(ISNUMBER(G474),G474/E474,IF(ISNUMBER(I474),-ABS(I474)/E474,IF(ISNUMBER(H474),0,IF(AND(ISNUMBER(F474),ISNUMBER(E474),E474&gt;0,F474&gt;E474),(F474-E474)/E474,IF(AND(ISNUMBER(F474),ISNUMBER(E474),E474&gt;0,F474=E474),0,IF(AND(ISNUMBER(F474),ISNUMBER(E474),E474&gt;0,F474=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K474" s="50" t="str">
-        <x:f>IF(A474="","",IF(AND(ISNUMBER(E474),E474=0,OR(ISNUMBER(SEARCH("Free",D474&amp;"")),AND(ISNUMBER(F474),F474=0))),"Subscription",IF(ISNUMBER(G474),"Profit",IF(ISNUMBER(I474),"Loss",IF(ISNUMBER(H474),"Draw",IF(AND(ISNUMBER(F474),ISNUMBER(E474),E474&gt;0,F474&gt;E474),"Profit",IF(AND(ISNUMBER(F474),ISNUMBER(E474),E474&gt;0,F474=E474),"Draw",IF(AND(ISNUMBER(F474),ISNUMBER(E474),E474&gt;0,F474=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A474="","",IF(AND(ISNUMBER(E474),E474=0,OR(ISNUMBER(SEARCH("Free",D474&amp;"")),AND(ISNUMBER(F474),F474=0))),"Subscription",IF(ISNUMBER(G474),"Profit",IF(ISNUMBER(I474),"Disqualified",IF(ISNUMBER(H474),"Draw",IF(AND(ISNUMBER(F474),ISNUMBER(E474),E474&gt;0,F474&gt;E474),"Profit",IF(AND(ISNUMBER(F474),ISNUMBER(E474),E474&gt;0,F474=E474),"Draw",IF(AND(ISNUMBER(F474),ISNUMBER(E474),E474&gt;0,F474=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L474" s="50"/>
       <x:c r="M474" s="58"/>
@@ -18933,7 +18946,7 @@
         <x:f>IF(A475="","",IF(K475="Subscription","",IF(E475=0,"",IF(ISNUMBER(G475),G475/E475,IF(ISNUMBER(I475),-ABS(I475)/E475,IF(ISNUMBER(H475),0,IF(AND(ISNUMBER(F475),ISNUMBER(E475),E475&gt;0,F475&gt;E475),(F475-E475)/E475,IF(AND(ISNUMBER(F475),ISNUMBER(E475),E475&gt;0,F475=E475),0,IF(AND(ISNUMBER(F475),ISNUMBER(E475),E475&gt;0,F475=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K475" s="50" t="str">
-        <x:f>IF(A475="","",IF(AND(ISNUMBER(E475),E475=0,OR(ISNUMBER(SEARCH("Free",D475&amp;"")),AND(ISNUMBER(F475),F475=0))),"Subscription",IF(ISNUMBER(G475),"Profit",IF(ISNUMBER(I475),"Loss",IF(ISNUMBER(H475),"Draw",IF(AND(ISNUMBER(F475),ISNUMBER(E475),E475&gt;0,F475&gt;E475),"Profit",IF(AND(ISNUMBER(F475),ISNUMBER(E475),E475&gt;0,F475=E475),"Draw",IF(AND(ISNUMBER(F475),ISNUMBER(E475),E475&gt;0,F475=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A475="","",IF(AND(ISNUMBER(E475),E475=0,OR(ISNUMBER(SEARCH("Free",D475&amp;"")),AND(ISNUMBER(F475),F475=0))),"Subscription",IF(ISNUMBER(G475),"Profit",IF(ISNUMBER(I475),"Disqualified",IF(ISNUMBER(H475),"Draw",IF(AND(ISNUMBER(F475),ISNUMBER(E475),E475&gt;0,F475&gt;E475),"Profit",IF(AND(ISNUMBER(F475),ISNUMBER(E475),E475&gt;0,F475=E475),"Draw",IF(AND(ISNUMBER(F475),ISNUMBER(E475),E475&gt;0,F475=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L475" s="50"/>
       <x:c r="M475" s="58"/>
@@ -18970,7 +18983,7 @@
         <x:f>IF(A476="","",IF(K476="Subscription","",IF(E476=0,"",IF(ISNUMBER(G476),G476/E476,IF(ISNUMBER(I476),-ABS(I476)/E476,IF(ISNUMBER(H476),0,IF(AND(ISNUMBER(F476),ISNUMBER(E476),E476&gt;0,F476&gt;E476),(F476-E476)/E476,IF(AND(ISNUMBER(F476),ISNUMBER(E476),E476&gt;0,F476=E476),0,IF(AND(ISNUMBER(F476),ISNUMBER(E476),E476&gt;0,F476=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K476" s="50" t="str">
-        <x:f>IF(A476="","",IF(AND(ISNUMBER(E476),E476=0,OR(ISNUMBER(SEARCH("Free",D476&amp;"")),AND(ISNUMBER(F476),F476=0))),"Subscription",IF(ISNUMBER(G476),"Profit",IF(ISNUMBER(I476),"Loss",IF(ISNUMBER(H476),"Draw",IF(AND(ISNUMBER(F476),ISNUMBER(E476),E476&gt;0,F476&gt;E476),"Profit",IF(AND(ISNUMBER(F476),ISNUMBER(E476),E476&gt;0,F476=E476),"Draw",IF(AND(ISNUMBER(F476),ISNUMBER(E476),E476&gt;0,F476=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A476="","",IF(AND(ISNUMBER(E476),E476=0,OR(ISNUMBER(SEARCH("Free",D476&amp;"")),AND(ISNUMBER(F476),F476=0))),"Subscription",IF(ISNUMBER(G476),"Profit",IF(ISNUMBER(I476),"Disqualified",IF(ISNUMBER(H476),"Draw",IF(AND(ISNUMBER(F476),ISNUMBER(E476),E476&gt;0,F476&gt;E476),"Profit",IF(AND(ISNUMBER(F476),ISNUMBER(E476),E476&gt;0,F476=E476),"Draw",IF(AND(ISNUMBER(F476),ISNUMBER(E476),E476&gt;0,F476=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L476" s="50"/>
       <x:c r="M476" s="58"/>
@@ -19007,7 +19020,7 @@
         <x:f>IF(A477="","",IF(K477="Subscription","",IF(E477=0,"",IF(ISNUMBER(G477),G477/E477,IF(ISNUMBER(I477),-ABS(I477)/E477,IF(ISNUMBER(H477),0,IF(AND(ISNUMBER(F477),ISNUMBER(E477),E477&gt;0,F477&gt;E477),(F477-E477)/E477,IF(AND(ISNUMBER(F477),ISNUMBER(E477),E477&gt;0,F477=E477),0,IF(AND(ISNUMBER(F477),ISNUMBER(E477),E477&gt;0,F477=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K477" s="50" t="str">
-        <x:f>IF(A477="","",IF(AND(ISNUMBER(E477),E477=0,OR(ISNUMBER(SEARCH("Free",D477&amp;"")),AND(ISNUMBER(F477),F477=0))),"Subscription",IF(ISNUMBER(G477),"Profit",IF(ISNUMBER(I477),"Loss",IF(ISNUMBER(H477),"Draw",IF(AND(ISNUMBER(F477),ISNUMBER(E477),E477&gt;0,F477&gt;E477),"Profit",IF(AND(ISNUMBER(F477),ISNUMBER(E477),E477&gt;0,F477=E477),"Draw",IF(AND(ISNUMBER(F477),ISNUMBER(E477),E477&gt;0,F477=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A477="","",IF(AND(ISNUMBER(E477),E477=0,OR(ISNUMBER(SEARCH("Free",D477&amp;"")),AND(ISNUMBER(F477),F477=0))),"Subscription",IF(ISNUMBER(G477),"Profit",IF(ISNUMBER(I477),"Disqualified",IF(ISNUMBER(H477),"Draw",IF(AND(ISNUMBER(F477),ISNUMBER(E477),E477&gt;0,F477&gt;E477),"Profit",IF(AND(ISNUMBER(F477),ISNUMBER(E477),E477&gt;0,F477=E477),"Draw",IF(AND(ISNUMBER(F477),ISNUMBER(E477),E477&gt;0,F477=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L477" s="50"/>
       <x:c r="M477" s="58"/>
@@ -19044,7 +19057,7 @@
         <x:f>IF(A478="","",IF(K478="Subscription","",IF(E478=0,"",IF(ISNUMBER(G478),G478/E478,IF(ISNUMBER(I478),-ABS(I478)/E478,IF(ISNUMBER(H478),0,IF(AND(ISNUMBER(F478),ISNUMBER(E478),E478&gt;0,F478&gt;E478),(F478-E478)/E478,IF(AND(ISNUMBER(F478),ISNUMBER(E478),E478&gt;0,F478=E478),0,IF(AND(ISNUMBER(F478),ISNUMBER(E478),E478&gt;0,F478=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K478" s="50" t="str">
-        <x:f>IF(A478="","",IF(AND(ISNUMBER(E478),E478=0,OR(ISNUMBER(SEARCH("Free",D478&amp;"")),AND(ISNUMBER(F478),F478=0))),"Subscription",IF(ISNUMBER(G478),"Profit",IF(ISNUMBER(I478),"Loss",IF(ISNUMBER(H478),"Draw",IF(AND(ISNUMBER(F478),ISNUMBER(E478),E478&gt;0,F478&gt;E478),"Profit",IF(AND(ISNUMBER(F478),ISNUMBER(E478),E478&gt;0,F478=E478),"Draw",IF(AND(ISNUMBER(F478),ISNUMBER(E478),E478&gt;0,F478=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A478="","",IF(AND(ISNUMBER(E478),E478=0,OR(ISNUMBER(SEARCH("Free",D478&amp;"")),AND(ISNUMBER(F478),F478=0))),"Subscription",IF(ISNUMBER(G478),"Profit",IF(ISNUMBER(I478),"Disqualified",IF(ISNUMBER(H478),"Draw",IF(AND(ISNUMBER(F478),ISNUMBER(E478),E478&gt;0,F478&gt;E478),"Profit",IF(AND(ISNUMBER(F478),ISNUMBER(E478),E478&gt;0,F478=E478),"Draw",IF(AND(ISNUMBER(F478),ISNUMBER(E478),E478&gt;0,F478=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L478" s="50"/>
       <x:c r="M478" s="58"/>
@@ -19081,7 +19094,7 @@
         <x:f>IF(A479="","",IF(K479="Subscription","",IF(E479=0,"",IF(ISNUMBER(G479),G479/E479,IF(ISNUMBER(I479),-ABS(I479)/E479,IF(ISNUMBER(H479),0,IF(AND(ISNUMBER(F479),ISNUMBER(E479),E479&gt;0,F479&gt;E479),(F479-E479)/E479,IF(AND(ISNUMBER(F479),ISNUMBER(E479),E479&gt;0,F479=E479),0,IF(AND(ISNUMBER(F479),ISNUMBER(E479),E479&gt;0,F479=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K479" s="50" t="str">
-        <x:f>IF(A479="","",IF(AND(ISNUMBER(E479),E479=0,OR(ISNUMBER(SEARCH("Free",D479&amp;"")),AND(ISNUMBER(F479),F479=0))),"Subscription",IF(ISNUMBER(G479),"Profit",IF(ISNUMBER(I479),"Loss",IF(ISNUMBER(H479),"Draw",IF(AND(ISNUMBER(F479),ISNUMBER(E479),E479&gt;0,F479&gt;E479),"Profit",IF(AND(ISNUMBER(F479),ISNUMBER(E479),E479&gt;0,F479=E479),"Draw",IF(AND(ISNUMBER(F479),ISNUMBER(E479),E479&gt;0,F479=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A479="","",IF(AND(ISNUMBER(E479),E479=0,OR(ISNUMBER(SEARCH("Free",D479&amp;"")),AND(ISNUMBER(F479),F479=0))),"Subscription",IF(ISNUMBER(G479),"Profit",IF(ISNUMBER(I479),"Disqualified",IF(ISNUMBER(H479),"Draw",IF(AND(ISNUMBER(F479),ISNUMBER(E479),E479&gt;0,F479&gt;E479),"Profit",IF(AND(ISNUMBER(F479),ISNUMBER(E479),E479&gt;0,F479=E479),"Draw",IF(AND(ISNUMBER(F479),ISNUMBER(E479),E479&gt;0,F479=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L479" s="50"/>
       <x:c r="M479" s="58"/>
@@ -19118,7 +19131,7 @@
         <x:f>IF(A480="","",IF(K480="Subscription","",IF(E480=0,"",IF(ISNUMBER(G480),G480/E480,IF(ISNUMBER(I480),-ABS(I480)/E480,IF(ISNUMBER(H480),0,IF(AND(ISNUMBER(F480),ISNUMBER(E480),E480&gt;0,F480&gt;E480),(F480-E480)/E480,IF(AND(ISNUMBER(F480),ISNUMBER(E480),E480&gt;0,F480=E480),0,IF(AND(ISNUMBER(F480),ISNUMBER(E480),E480&gt;0,F480=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K480" s="50" t="str">
-        <x:f>IF(A480="","",IF(AND(ISNUMBER(E480),E480=0,OR(ISNUMBER(SEARCH("Free",D480&amp;"")),AND(ISNUMBER(F480),F480=0))),"Subscription",IF(ISNUMBER(G480),"Profit",IF(ISNUMBER(I480),"Loss",IF(ISNUMBER(H480),"Draw",IF(AND(ISNUMBER(F480),ISNUMBER(E480),E480&gt;0,F480&gt;E480),"Profit",IF(AND(ISNUMBER(F480),ISNUMBER(E480),E480&gt;0,F480=E480),"Draw",IF(AND(ISNUMBER(F480),ISNUMBER(E480),E480&gt;0,F480=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A480="","",IF(AND(ISNUMBER(E480),E480=0,OR(ISNUMBER(SEARCH("Free",D480&amp;"")),AND(ISNUMBER(F480),F480=0))),"Subscription",IF(ISNUMBER(G480),"Profit",IF(ISNUMBER(I480),"Disqualified",IF(ISNUMBER(H480),"Draw",IF(AND(ISNUMBER(F480),ISNUMBER(E480),E480&gt;0,F480&gt;E480),"Profit",IF(AND(ISNUMBER(F480),ISNUMBER(E480),E480&gt;0,F480=E480),"Draw",IF(AND(ISNUMBER(F480),ISNUMBER(E480),E480&gt;0,F480=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L480" s="50"/>
       <x:c r="M480" s="58"/>
@@ -19155,7 +19168,7 @@
         <x:f>IF(A481="","",IF(K481="Subscription","",IF(E481=0,"",IF(ISNUMBER(G481),G481/E481,IF(ISNUMBER(I481),-ABS(I481)/E481,IF(ISNUMBER(H481),0,IF(AND(ISNUMBER(F481),ISNUMBER(E481),E481&gt;0,F481&gt;E481),(F481-E481)/E481,IF(AND(ISNUMBER(F481),ISNUMBER(E481),E481&gt;0,F481=E481),0,IF(AND(ISNUMBER(F481),ISNUMBER(E481),E481&gt;0,F481=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K481" s="50" t="str">
-        <x:f>IF(A481="","",IF(AND(ISNUMBER(E481),E481=0,OR(ISNUMBER(SEARCH("Free",D481&amp;"")),AND(ISNUMBER(F481),F481=0))),"Subscription",IF(ISNUMBER(G481),"Profit",IF(ISNUMBER(I481),"Loss",IF(ISNUMBER(H481),"Draw",IF(AND(ISNUMBER(F481),ISNUMBER(E481),E481&gt;0,F481&gt;E481),"Profit",IF(AND(ISNUMBER(F481),ISNUMBER(E481),E481&gt;0,F481=E481),"Draw",IF(AND(ISNUMBER(F481),ISNUMBER(E481),E481&gt;0,F481=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A481="","",IF(AND(ISNUMBER(E481),E481=0,OR(ISNUMBER(SEARCH("Free",D481&amp;"")),AND(ISNUMBER(F481),F481=0))),"Subscription",IF(ISNUMBER(G481),"Profit",IF(ISNUMBER(I481),"Disqualified",IF(ISNUMBER(H481),"Draw",IF(AND(ISNUMBER(F481),ISNUMBER(E481),E481&gt;0,F481&gt;E481),"Profit",IF(AND(ISNUMBER(F481),ISNUMBER(E481),E481&gt;0,F481=E481),"Draw",IF(AND(ISNUMBER(F481),ISNUMBER(E481),E481&gt;0,F481=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L481" s="50"/>
       <x:c r="M481" s="58"/>
@@ -19192,7 +19205,7 @@
         <x:f>IF(A482="","",IF(K482="Subscription","",IF(E482=0,"",IF(ISNUMBER(G482),G482/E482,IF(ISNUMBER(I482),-ABS(I482)/E482,IF(ISNUMBER(H482),0,IF(AND(ISNUMBER(F482),ISNUMBER(E482),E482&gt;0,F482&gt;E482),(F482-E482)/E482,IF(AND(ISNUMBER(F482),ISNUMBER(E482),E482&gt;0,F482=E482),0,IF(AND(ISNUMBER(F482),ISNUMBER(E482),E482&gt;0,F482=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K482" s="50" t="str">
-        <x:f>IF(A482="","",IF(AND(ISNUMBER(E482),E482=0,OR(ISNUMBER(SEARCH("Free",D482&amp;"")),AND(ISNUMBER(F482),F482=0))),"Subscription",IF(ISNUMBER(G482),"Profit",IF(ISNUMBER(I482),"Loss",IF(ISNUMBER(H482),"Draw",IF(AND(ISNUMBER(F482),ISNUMBER(E482),E482&gt;0,F482&gt;E482),"Profit",IF(AND(ISNUMBER(F482),ISNUMBER(E482),E482&gt;0,F482=E482),"Draw",IF(AND(ISNUMBER(F482),ISNUMBER(E482),E482&gt;0,F482=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A482="","",IF(AND(ISNUMBER(E482),E482=0,OR(ISNUMBER(SEARCH("Free",D482&amp;"")),AND(ISNUMBER(F482),F482=0))),"Subscription",IF(ISNUMBER(G482),"Profit",IF(ISNUMBER(I482),"Disqualified",IF(ISNUMBER(H482),"Draw",IF(AND(ISNUMBER(F482),ISNUMBER(E482),E482&gt;0,F482&gt;E482),"Profit",IF(AND(ISNUMBER(F482),ISNUMBER(E482),E482&gt;0,F482=E482),"Draw",IF(AND(ISNUMBER(F482),ISNUMBER(E482),E482&gt;0,F482=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L482" s="50"/>
       <x:c r="M482" s="58"/>
@@ -19229,7 +19242,7 @@
         <x:f>IF(A483="","",IF(K483="Subscription","",IF(E483=0,"",IF(ISNUMBER(G483),G483/E483,IF(ISNUMBER(I483),-ABS(I483)/E483,IF(ISNUMBER(H483),0,IF(AND(ISNUMBER(F483),ISNUMBER(E483),E483&gt;0,F483&gt;E483),(F483-E483)/E483,IF(AND(ISNUMBER(F483),ISNUMBER(E483),E483&gt;0,F483=E483),0,IF(AND(ISNUMBER(F483),ISNUMBER(E483),E483&gt;0,F483=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K483" s="50" t="str">
-        <x:f>IF(A483="","",IF(AND(ISNUMBER(E483),E483=0,OR(ISNUMBER(SEARCH("Free",D483&amp;"")),AND(ISNUMBER(F483),F483=0))),"Subscription",IF(ISNUMBER(G483),"Profit",IF(ISNUMBER(I483),"Loss",IF(ISNUMBER(H483),"Draw",IF(AND(ISNUMBER(F483),ISNUMBER(E483),E483&gt;0,F483&gt;E483),"Profit",IF(AND(ISNUMBER(F483),ISNUMBER(E483),E483&gt;0,F483=E483),"Draw",IF(AND(ISNUMBER(F483),ISNUMBER(E483),E483&gt;0,F483=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A483="","",IF(AND(ISNUMBER(E483),E483=0,OR(ISNUMBER(SEARCH("Free",D483&amp;"")),AND(ISNUMBER(F483),F483=0))),"Subscription",IF(ISNUMBER(G483),"Profit",IF(ISNUMBER(I483),"Disqualified",IF(ISNUMBER(H483),"Draw",IF(AND(ISNUMBER(F483),ISNUMBER(E483),E483&gt;0,F483&gt;E483),"Profit",IF(AND(ISNUMBER(F483),ISNUMBER(E483),E483&gt;0,F483=E483),"Draw",IF(AND(ISNUMBER(F483),ISNUMBER(E483),E483&gt;0,F483=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L483" s="50"/>
       <x:c r="M483" s="58"/>
@@ -19266,7 +19279,7 @@
         <x:f>IF(A484="","",IF(K484="Subscription","",IF(E484=0,"",IF(ISNUMBER(G484),G484/E484,IF(ISNUMBER(I484),-ABS(I484)/E484,IF(ISNUMBER(H484),0,IF(AND(ISNUMBER(F484),ISNUMBER(E484),E484&gt;0,F484&gt;E484),(F484-E484)/E484,IF(AND(ISNUMBER(F484),ISNUMBER(E484),E484&gt;0,F484=E484),0,IF(AND(ISNUMBER(F484),ISNUMBER(E484),E484&gt;0,F484=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K484" s="50" t="str">
-        <x:f>IF(A484="","",IF(AND(ISNUMBER(E484),E484=0,OR(ISNUMBER(SEARCH("Free",D484&amp;"")),AND(ISNUMBER(F484),F484=0))),"Subscription",IF(ISNUMBER(G484),"Profit",IF(ISNUMBER(I484),"Loss",IF(ISNUMBER(H484),"Draw",IF(AND(ISNUMBER(F484),ISNUMBER(E484),E484&gt;0,F484&gt;E484),"Profit",IF(AND(ISNUMBER(F484),ISNUMBER(E484),E484&gt;0,F484=E484),"Draw",IF(AND(ISNUMBER(F484),ISNUMBER(E484),E484&gt;0,F484=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A484="","",IF(AND(ISNUMBER(E484),E484=0,OR(ISNUMBER(SEARCH("Free",D484&amp;"")),AND(ISNUMBER(F484),F484=0))),"Subscription",IF(ISNUMBER(G484),"Profit",IF(ISNUMBER(I484),"Disqualified",IF(ISNUMBER(H484),"Draw",IF(AND(ISNUMBER(F484),ISNUMBER(E484),E484&gt;0,F484&gt;E484),"Profit",IF(AND(ISNUMBER(F484),ISNUMBER(E484),E484&gt;0,F484=E484),"Draw",IF(AND(ISNUMBER(F484),ISNUMBER(E484),E484&gt;0,F484=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L484" s="50"/>
       <x:c r="M484" s="58"/>
@@ -19303,7 +19316,7 @@
         <x:f>IF(A485="","",IF(K485="Subscription","",IF(E485=0,"",IF(ISNUMBER(G485),G485/E485,IF(ISNUMBER(I485),-ABS(I485)/E485,IF(ISNUMBER(H485),0,IF(AND(ISNUMBER(F485),ISNUMBER(E485),E485&gt;0,F485&gt;E485),(F485-E485)/E485,IF(AND(ISNUMBER(F485),ISNUMBER(E485),E485&gt;0,F485=E485),0,IF(AND(ISNUMBER(F485),ISNUMBER(E485),E485&gt;0,F485=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K485" s="50" t="str">
-        <x:f>IF(A485="","",IF(AND(ISNUMBER(E485),E485=0,OR(ISNUMBER(SEARCH("Free",D485&amp;"")),AND(ISNUMBER(F485),F485=0))),"Subscription",IF(ISNUMBER(G485),"Profit",IF(ISNUMBER(I485),"Loss",IF(ISNUMBER(H485),"Draw",IF(AND(ISNUMBER(F485),ISNUMBER(E485),E485&gt;0,F485&gt;E485),"Profit",IF(AND(ISNUMBER(F485),ISNUMBER(E485),E485&gt;0,F485=E485),"Draw",IF(AND(ISNUMBER(F485),ISNUMBER(E485),E485&gt;0,F485=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A485="","",IF(AND(ISNUMBER(E485),E485=0,OR(ISNUMBER(SEARCH("Free",D485&amp;"")),AND(ISNUMBER(F485),F485=0))),"Subscription",IF(ISNUMBER(G485),"Profit",IF(ISNUMBER(I485),"Disqualified",IF(ISNUMBER(H485),"Draw",IF(AND(ISNUMBER(F485),ISNUMBER(E485),E485&gt;0,F485&gt;E485),"Profit",IF(AND(ISNUMBER(F485),ISNUMBER(E485),E485&gt;0,F485=E485),"Draw",IF(AND(ISNUMBER(F485),ISNUMBER(E485),E485&gt;0,F485=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L485" s="50"/>
       <x:c r="M485" s="58"/>
@@ -19340,7 +19353,7 @@
         <x:f>IF(A486="","",IF(K486="Subscription","",IF(E486=0,"",IF(ISNUMBER(G486),G486/E486,IF(ISNUMBER(I486),-ABS(I486)/E486,IF(ISNUMBER(H486),0,IF(AND(ISNUMBER(F486),ISNUMBER(E486),E486&gt;0,F486&gt;E486),(F486-E486)/E486,IF(AND(ISNUMBER(F486),ISNUMBER(E486),E486&gt;0,F486=E486),0,IF(AND(ISNUMBER(F486),ISNUMBER(E486),E486&gt;0,F486=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K486" s="50" t="str">
-        <x:f>IF(A486="","",IF(AND(ISNUMBER(E486),E486=0,OR(ISNUMBER(SEARCH("Free",D486&amp;"")),AND(ISNUMBER(F486),F486=0))),"Subscription",IF(ISNUMBER(G486),"Profit",IF(ISNUMBER(I486),"Loss",IF(ISNUMBER(H486),"Draw",IF(AND(ISNUMBER(F486),ISNUMBER(E486),E486&gt;0,F486&gt;E486),"Profit",IF(AND(ISNUMBER(F486),ISNUMBER(E486),E486&gt;0,F486=E486),"Draw",IF(AND(ISNUMBER(F486),ISNUMBER(E486),E486&gt;0,F486=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A486="","",IF(AND(ISNUMBER(E486),E486=0,OR(ISNUMBER(SEARCH("Free",D486&amp;"")),AND(ISNUMBER(F486),F486=0))),"Subscription",IF(ISNUMBER(G486),"Profit",IF(ISNUMBER(I486),"Disqualified",IF(ISNUMBER(H486),"Draw",IF(AND(ISNUMBER(F486),ISNUMBER(E486),E486&gt;0,F486&gt;E486),"Profit",IF(AND(ISNUMBER(F486),ISNUMBER(E486),E486&gt;0,F486=E486),"Draw",IF(AND(ISNUMBER(F486),ISNUMBER(E486),E486&gt;0,F486=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L486" s="50"/>
       <x:c r="M486" s="58"/>
@@ -19377,7 +19390,7 @@
         <x:f>IF(A487="","",IF(K487="Subscription","",IF(E487=0,"",IF(ISNUMBER(G487),G487/E487,IF(ISNUMBER(I487),-ABS(I487)/E487,IF(ISNUMBER(H487),0,IF(AND(ISNUMBER(F487),ISNUMBER(E487),E487&gt;0,F487&gt;E487),(F487-E487)/E487,IF(AND(ISNUMBER(F487),ISNUMBER(E487),E487&gt;0,F487=E487),0,IF(AND(ISNUMBER(F487),ISNUMBER(E487),E487&gt;0,F487=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K487" s="50" t="str">
-        <x:f>IF(A487="","",IF(AND(ISNUMBER(E487),E487=0,OR(ISNUMBER(SEARCH("Free",D487&amp;"")),AND(ISNUMBER(F487),F487=0))),"Subscription",IF(ISNUMBER(G487),"Profit",IF(ISNUMBER(I487),"Loss",IF(ISNUMBER(H487),"Draw",IF(AND(ISNUMBER(F487),ISNUMBER(E487),E487&gt;0,F487&gt;E487),"Profit",IF(AND(ISNUMBER(F487),ISNUMBER(E487),E487&gt;0,F487=E487),"Draw",IF(AND(ISNUMBER(F487),ISNUMBER(E487),E487&gt;0,F487=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A487="","",IF(AND(ISNUMBER(E487),E487=0,OR(ISNUMBER(SEARCH("Free",D487&amp;"")),AND(ISNUMBER(F487),F487=0))),"Subscription",IF(ISNUMBER(G487),"Profit",IF(ISNUMBER(I487),"Disqualified",IF(ISNUMBER(H487),"Draw",IF(AND(ISNUMBER(F487),ISNUMBER(E487),E487&gt;0,F487&gt;E487),"Profit",IF(AND(ISNUMBER(F487),ISNUMBER(E487),E487&gt;0,F487=E487),"Draw",IF(AND(ISNUMBER(F487),ISNUMBER(E487),E487&gt;0,F487=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L487" s="50"/>
       <x:c r="M487" s="58"/>
@@ -19414,7 +19427,7 @@
         <x:f>IF(A488="","",IF(K488="Subscription","",IF(E488=0,"",IF(ISNUMBER(G488),G488/E488,IF(ISNUMBER(I488),-ABS(I488)/E488,IF(ISNUMBER(H488),0,IF(AND(ISNUMBER(F488),ISNUMBER(E488),E488&gt;0,F488&gt;E488),(F488-E488)/E488,IF(AND(ISNUMBER(F488),ISNUMBER(E488),E488&gt;0,F488=E488),0,IF(AND(ISNUMBER(F488),ISNUMBER(E488),E488&gt;0,F488=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K488" s="50" t="str">
-        <x:f>IF(A488="","",IF(AND(ISNUMBER(E488),E488=0,OR(ISNUMBER(SEARCH("Free",D488&amp;"")),AND(ISNUMBER(F488),F488=0))),"Subscription",IF(ISNUMBER(G488),"Profit",IF(ISNUMBER(I488),"Loss",IF(ISNUMBER(H488),"Draw",IF(AND(ISNUMBER(F488),ISNUMBER(E488),E488&gt;0,F488&gt;E488),"Profit",IF(AND(ISNUMBER(F488),ISNUMBER(E488),E488&gt;0,F488=E488),"Draw",IF(AND(ISNUMBER(F488),ISNUMBER(E488),E488&gt;0,F488=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A488="","",IF(AND(ISNUMBER(E488),E488=0,OR(ISNUMBER(SEARCH("Free",D488&amp;"")),AND(ISNUMBER(F488),F488=0))),"Subscription",IF(ISNUMBER(G488),"Profit",IF(ISNUMBER(I488),"Disqualified",IF(ISNUMBER(H488),"Draw",IF(AND(ISNUMBER(F488),ISNUMBER(E488),E488&gt;0,F488&gt;E488),"Profit",IF(AND(ISNUMBER(F488),ISNUMBER(E488),E488&gt;0,F488=E488),"Draw",IF(AND(ISNUMBER(F488),ISNUMBER(E488),E488&gt;0,F488=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L488" s="50"/>
       <x:c r="M488" s="58"/>
@@ -19451,7 +19464,7 @@
         <x:f>IF(A489="","",IF(K489="Subscription","",IF(E489=0,"",IF(ISNUMBER(G489),G489/E489,IF(ISNUMBER(I489),-ABS(I489)/E489,IF(ISNUMBER(H489),0,IF(AND(ISNUMBER(F489),ISNUMBER(E489),E489&gt;0,F489&gt;E489),(F489-E489)/E489,IF(AND(ISNUMBER(F489),ISNUMBER(E489),E489&gt;0,F489=E489),0,IF(AND(ISNUMBER(F489),ISNUMBER(E489),E489&gt;0,F489=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K489" s="50" t="str">
-        <x:f>IF(A489="","",IF(AND(ISNUMBER(E489),E489=0,OR(ISNUMBER(SEARCH("Free",D489&amp;"")),AND(ISNUMBER(F489),F489=0))),"Subscription",IF(ISNUMBER(G489),"Profit",IF(ISNUMBER(I489),"Loss",IF(ISNUMBER(H489),"Draw",IF(AND(ISNUMBER(F489),ISNUMBER(E489),E489&gt;0,F489&gt;E489),"Profit",IF(AND(ISNUMBER(F489),ISNUMBER(E489),E489&gt;0,F489=E489),"Draw",IF(AND(ISNUMBER(F489),ISNUMBER(E489),E489&gt;0,F489=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A489="","",IF(AND(ISNUMBER(E489),E489=0,OR(ISNUMBER(SEARCH("Free",D489&amp;"")),AND(ISNUMBER(F489),F489=0))),"Subscription",IF(ISNUMBER(G489),"Profit",IF(ISNUMBER(I489),"Disqualified",IF(ISNUMBER(H489),"Draw",IF(AND(ISNUMBER(F489),ISNUMBER(E489),E489&gt;0,F489&gt;E489),"Profit",IF(AND(ISNUMBER(F489),ISNUMBER(E489),E489&gt;0,F489=E489),"Draw",IF(AND(ISNUMBER(F489),ISNUMBER(E489),E489&gt;0,F489=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L489" s="50"/>
       <x:c r="M489" s="58"/>
@@ -19488,7 +19501,7 @@
         <x:f>IF(A490="","",IF(K490="Subscription","",IF(E490=0,"",IF(ISNUMBER(G490),G490/E490,IF(ISNUMBER(I490),-ABS(I490)/E490,IF(ISNUMBER(H490),0,IF(AND(ISNUMBER(F490),ISNUMBER(E490),E490&gt;0,F490&gt;E490),(F490-E490)/E490,IF(AND(ISNUMBER(F490),ISNUMBER(E490),E490&gt;0,F490=E490),0,IF(AND(ISNUMBER(F490),ISNUMBER(E490),E490&gt;0,F490=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K490" s="50" t="str">
-        <x:f>IF(A490="","",IF(AND(ISNUMBER(E490),E490=0,OR(ISNUMBER(SEARCH("Free",D490&amp;"")),AND(ISNUMBER(F490),F490=0))),"Subscription",IF(ISNUMBER(G490),"Profit",IF(ISNUMBER(I490),"Loss",IF(ISNUMBER(H490),"Draw",IF(AND(ISNUMBER(F490),ISNUMBER(E490),E490&gt;0,F490&gt;E490),"Profit",IF(AND(ISNUMBER(F490),ISNUMBER(E490),E490&gt;0,F490=E490),"Draw",IF(AND(ISNUMBER(F490),ISNUMBER(E490),E490&gt;0,F490=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A490="","",IF(AND(ISNUMBER(E490),E490=0,OR(ISNUMBER(SEARCH("Free",D490&amp;"")),AND(ISNUMBER(F490),F490=0))),"Subscription",IF(ISNUMBER(G490),"Profit",IF(ISNUMBER(I490),"Disqualified",IF(ISNUMBER(H490),"Draw",IF(AND(ISNUMBER(F490),ISNUMBER(E490),E490&gt;0,F490&gt;E490),"Profit",IF(AND(ISNUMBER(F490),ISNUMBER(E490),E490&gt;0,F490=E490),"Draw",IF(AND(ISNUMBER(F490),ISNUMBER(E490),E490&gt;0,F490=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L490" s="50"/>
       <x:c r="M490" s="58"/>
@@ -19525,7 +19538,7 @@
         <x:f>IF(A491="","",IF(K491="Subscription","",IF(E491=0,"",IF(ISNUMBER(G491),G491/E491,IF(ISNUMBER(I491),-ABS(I491)/E491,IF(ISNUMBER(H491),0,IF(AND(ISNUMBER(F491),ISNUMBER(E491),E491&gt;0,F491&gt;E491),(F491-E491)/E491,IF(AND(ISNUMBER(F491),ISNUMBER(E491),E491&gt;0,F491=E491),0,IF(AND(ISNUMBER(F491),ISNUMBER(E491),E491&gt;0,F491=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K491" s="50" t="str">
-        <x:f>IF(A491="","",IF(AND(ISNUMBER(E491),E491=0,OR(ISNUMBER(SEARCH("Free",D491&amp;"")),AND(ISNUMBER(F491),F491=0))),"Subscription",IF(ISNUMBER(G491),"Profit",IF(ISNUMBER(I491),"Loss",IF(ISNUMBER(H491),"Draw",IF(AND(ISNUMBER(F491),ISNUMBER(E491),E491&gt;0,F491&gt;E491),"Profit",IF(AND(ISNUMBER(F491),ISNUMBER(E491),E491&gt;0,F491=E491),"Draw",IF(AND(ISNUMBER(F491),ISNUMBER(E491),E491&gt;0,F491=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A491="","",IF(AND(ISNUMBER(E491),E491=0,OR(ISNUMBER(SEARCH("Free",D491&amp;"")),AND(ISNUMBER(F491),F491=0))),"Subscription",IF(ISNUMBER(G491),"Profit",IF(ISNUMBER(I491),"Disqualified",IF(ISNUMBER(H491),"Draw",IF(AND(ISNUMBER(F491),ISNUMBER(E491),E491&gt;0,F491&gt;E491),"Profit",IF(AND(ISNUMBER(F491),ISNUMBER(E491),E491&gt;0,F491=E491),"Draw",IF(AND(ISNUMBER(F491),ISNUMBER(E491),E491&gt;0,F491=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L491" s="50"/>
       <x:c r="M491" s="58"/>
@@ -19562,7 +19575,7 @@
         <x:f>IF(A492="","",IF(K492="Subscription","",IF(E492=0,"",IF(ISNUMBER(G492),G492/E492,IF(ISNUMBER(I492),-ABS(I492)/E492,IF(ISNUMBER(H492),0,IF(AND(ISNUMBER(F492),ISNUMBER(E492),E492&gt;0,F492&gt;E492),(F492-E492)/E492,IF(AND(ISNUMBER(F492),ISNUMBER(E492),E492&gt;0,F492=E492),0,IF(AND(ISNUMBER(F492),ISNUMBER(E492),E492&gt;0,F492=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K492" s="50" t="str">
-        <x:f>IF(A492="","",IF(AND(ISNUMBER(E492),E492=0,OR(ISNUMBER(SEARCH("Free",D492&amp;"")),AND(ISNUMBER(F492),F492=0))),"Subscription",IF(ISNUMBER(G492),"Profit",IF(ISNUMBER(I492),"Loss",IF(ISNUMBER(H492),"Draw",IF(AND(ISNUMBER(F492),ISNUMBER(E492),E492&gt;0,F492&gt;E492),"Profit",IF(AND(ISNUMBER(F492),ISNUMBER(E492),E492&gt;0,F492=E492),"Draw",IF(AND(ISNUMBER(F492),ISNUMBER(E492),E492&gt;0,F492=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A492="","",IF(AND(ISNUMBER(E492),E492=0,OR(ISNUMBER(SEARCH("Free",D492&amp;"")),AND(ISNUMBER(F492),F492=0))),"Subscription",IF(ISNUMBER(G492),"Profit",IF(ISNUMBER(I492),"Disqualified",IF(ISNUMBER(H492),"Draw",IF(AND(ISNUMBER(F492),ISNUMBER(E492),E492&gt;0,F492&gt;E492),"Profit",IF(AND(ISNUMBER(F492),ISNUMBER(E492),E492&gt;0,F492=E492),"Draw",IF(AND(ISNUMBER(F492),ISNUMBER(E492),E492&gt;0,F492=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L492" s="50"/>
       <x:c r="M492" s="58"/>
@@ -19599,7 +19612,7 @@
         <x:f>IF(A493="","",IF(K493="Subscription","",IF(E493=0,"",IF(ISNUMBER(G493),G493/E493,IF(ISNUMBER(I493),-ABS(I493)/E493,IF(ISNUMBER(H493),0,IF(AND(ISNUMBER(F493),ISNUMBER(E493),E493&gt;0,F493&gt;E493),(F493-E493)/E493,IF(AND(ISNUMBER(F493),ISNUMBER(E493),E493&gt;0,F493=E493),0,IF(AND(ISNUMBER(F493),ISNUMBER(E493),E493&gt;0,F493=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K493" s="50" t="str">
-        <x:f>IF(A493="","",IF(AND(ISNUMBER(E493),E493=0,OR(ISNUMBER(SEARCH("Free",D493&amp;"")),AND(ISNUMBER(F493),F493=0))),"Subscription",IF(ISNUMBER(G493),"Profit",IF(ISNUMBER(I493),"Loss",IF(ISNUMBER(H493),"Draw",IF(AND(ISNUMBER(F493),ISNUMBER(E493),E493&gt;0,F493&gt;E493),"Profit",IF(AND(ISNUMBER(F493),ISNUMBER(E493),E493&gt;0,F493=E493),"Draw",IF(AND(ISNUMBER(F493),ISNUMBER(E493),E493&gt;0,F493=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A493="","",IF(AND(ISNUMBER(E493),E493=0,OR(ISNUMBER(SEARCH("Free",D493&amp;"")),AND(ISNUMBER(F493),F493=0))),"Subscription",IF(ISNUMBER(G493),"Profit",IF(ISNUMBER(I493),"Disqualified",IF(ISNUMBER(H493),"Draw",IF(AND(ISNUMBER(F493),ISNUMBER(E493),E493&gt;0,F493&gt;E493),"Profit",IF(AND(ISNUMBER(F493),ISNUMBER(E493),E493&gt;0,F493=E493),"Draw",IF(AND(ISNUMBER(F493),ISNUMBER(E493),E493&gt;0,F493=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L493" s="50"/>
       <x:c r="M493" s="58"/>
@@ -19636,7 +19649,7 @@
         <x:f>IF(A494="","",IF(K494="Subscription","",IF(E494=0,"",IF(ISNUMBER(G494),G494/E494,IF(ISNUMBER(I494),-ABS(I494)/E494,IF(ISNUMBER(H494),0,IF(AND(ISNUMBER(F494),ISNUMBER(E494),E494&gt;0,F494&gt;E494),(F494-E494)/E494,IF(AND(ISNUMBER(F494),ISNUMBER(E494),E494&gt;0,F494=E494),0,IF(AND(ISNUMBER(F494),ISNUMBER(E494),E494&gt;0,F494=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K494" s="50" t="str">
-        <x:f>IF(A494="","",IF(AND(ISNUMBER(E494),E494=0,OR(ISNUMBER(SEARCH("Free",D494&amp;"")),AND(ISNUMBER(F494),F494=0))),"Subscription",IF(ISNUMBER(G494),"Profit",IF(ISNUMBER(I494),"Loss",IF(ISNUMBER(H494),"Draw",IF(AND(ISNUMBER(F494),ISNUMBER(E494),E494&gt;0,F494&gt;E494),"Profit",IF(AND(ISNUMBER(F494),ISNUMBER(E494),E494&gt;0,F494=E494),"Draw",IF(AND(ISNUMBER(F494),ISNUMBER(E494),E494&gt;0,F494=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A494="","",IF(AND(ISNUMBER(E494),E494=0,OR(ISNUMBER(SEARCH("Free",D494&amp;"")),AND(ISNUMBER(F494),F494=0))),"Subscription",IF(ISNUMBER(G494),"Profit",IF(ISNUMBER(I494),"Disqualified",IF(ISNUMBER(H494),"Draw",IF(AND(ISNUMBER(F494),ISNUMBER(E494),E494&gt;0,F494&gt;E494),"Profit",IF(AND(ISNUMBER(F494),ISNUMBER(E494),E494&gt;0,F494=E494),"Draw",IF(AND(ISNUMBER(F494),ISNUMBER(E494),E494&gt;0,F494=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L494" s="50"/>
       <x:c r="M494" s="58"/>
@@ -19673,7 +19686,7 @@
         <x:f>IF(A495="","",IF(K495="Subscription","",IF(E495=0,"",IF(ISNUMBER(G495),G495/E495,IF(ISNUMBER(I495),-ABS(I495)/E495,IF(ISNUMBER(H495),0,IF(AND(ISNUMBER(F495),ISNUMBER(E495),E495&gt;0,F495&gt;E495),(F495-E495)/E495,IF(AND(ISNUMBER(F495),ISNUMBER(E495),E495&gt;0,F495=E495),0,IF(AND(ISNUMBER(F495),ISNUMBER(E495),E495&gt;0,F495=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K495" s="50" t="str">
-        <x:f>IF(A495="","",IF(AND(ISNUMBER(E495),E495=0,OR(ISNUMBER(SEARCH("Free",D495&amp;"")),AND(ISNUMBER(F495),F495=0))),"Subscription",IF(ISNUMBER(G495),"Profit",IF(ISNUMBER(I495),"Loss",IF(ISNUMBER(H495),"Draw",IF(AND(ISNUMBER(F495),ISNUMBER(E495),E495&gt;0,F495&gt;E495),"Profit",IF(AND(ISNUMBER(F495),ISNUMBER(E495),E495&gt;0,F495=E495),"Draw",IF(AND(ISNUMBER(F495),ISNUMBER(E495),E495&gt;0,F495=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A495="","",IF(AND(ISNUMBER(E495),E495=0,OR(ISNUMBER(SEARCH("Free",D495&amp;"")),AND(ISNUMBER(F495),F495=0))),"Subscription",IF(ISNUMBER(G495),"Profit",IF(ISNUMBER(I495),"Disqualified",IF(ISNUMBER(H495),"Draw",IF(AND(ISNUMBER(F495),ISNUMBER(E495),E495&gt;0,F495&gt;E495),"Profit",IF(AND(ISNUMBER(F495),ISNUMBER(E495),E495&gt;0,F495=E495),"Draw",IF(AND(ISNUMBER(F495),ISNUMBER(E495),E495&gt;0,F495=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L495" s="50"/>
       <x:c r="M495" s="58"/>
@@ -19710,7 +19723,7 @@
         <x:f>IF(A496="","",IF(K496="Subscription","",IF(E496=0,"",IF(ISNUMBER(G496),G496/E496,IF(ISNUMBER(I496),-ABS(I496)/E496,IF(ISNUMBER(H496),0,IF(AND(ISNUMBER(F496),ISNUMBER(E496),E496&gt;0,F496&gt;E496),(F496-E496)/E496,IF(AND(ISNUMBER(F496),ISNUMBER(E496),E496&gt;0,F496=E496),0,IF(AND(ISNUMBER(F496),ISNUMBER(E496),E496&gt;0,F496=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K496" s="50" t="str">
-        <x:f>IF(A496="","",IF(AND(ISNUMBER(E496),E496=0,OR(ISNUMBER(SEARCH("Free",D496&amp;"")),AND(ISNUMBER(F496),F496=0))),"Subscription",IF(ISNUMBER(G496),"Profit",IF(ISNUMBER(I496),"Loss",IF(ISNUMBER(H496),"Draw",IF(AND(ISNUMBER(F496),ISNUMBER(E496),E496&gt;0,F496&gt;E496),"Profit",IF(AND(ISNUMBER(F496),ISNUMBER(E496),E496&gt;0,F496=E496),"Draw",IF(AND(ISNUMBER(F496),ISNUMBER(E496),E496&gt;0,F496=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A496="","",IF(AND(ISNUMBER(E496),E496=0,OR(ISNUMBER(SEARCH("Free",D496&amp;"")),AND(ISNUMBER(F496),F496=0))),"Subscription",IF(ISNUMBER(G496),"Profit",IF(ISNUMBER(I496),"Disqualified",IF(ISNUMBER(H496),"Draw",IF(AND(ISNUMBER(F496),ISNUMBER(E496),E496&gt;0,F496&gt;E496),"Profit",IF(AND(ISNUMBER(F496),ISNUMBER(E496),E496&gt;0,F496=E496),"Draw",IF(AND(ISNUMBER(F496),ISNUMBER(E496),E496&gt;0,F496=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L496" s="50"/>
       <x:c r="M496" s="58"/>
@@ -19747,7 +19760,7 @@
         <x:f>IF(A497="","",IF(K497="Subscription","",IF(E497=0,"",IF(ISNUMBER(G497),G497/E497,IF(ISNUMBER(I497),-ABS(I497)/E497,IF(ISNUMBER(H497),0,IF(AND(ISNUMBER(F497),ISNUMBER(E497),E497&gt;0,F497&gt;E497),(F497-E497)/E497,IF(AND(ISNUMBER(F497),ISNUMBER(E497),E497&gt;0,F497=E497),0,IF(AND(ISNUMBER(F497),ISNUMBER(E497),E497&gt;0,F497=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K497" s="50" t="str">
-        <x:f>IF(A497="","",IF(AND(ISNUMBER(E497),E497=0,OR(ISNUMBER(SEARCH("Free",D497&amp;"")),AND(ISNUMBER(F497),F497=0))),"Subscription",IF(ISNUMBER(G497),"Profit",IF(ISNUMBER(I497),"Loss",IF(ISNUMBER(H497),"Draw",IF(AND(ISNUMBER(F497),ISNUMBER(E497),E497&gt;0,F497&gt;E497),"Profit",IF(AND(ISNUMBER(F497),ISNUMBER(E497),E497&gt;0,F497=E497),"Draw",IF(AND(ISNUMBER(F497),ISNUMBER(E497),E497&gt;0,F497=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A497="","",IF(AND(ISNUMBER(E497),E497=0,OR(ISNUMBER(SEARCH("Free",D497&amp;"")),AND(ISNUMBER(F497),F497=0))),"Subscription",IF(ISNUMBER(G497),"Profit",IF(ISNUMBER(I497),"Disqualified",IF(ISNUMBER(H497),"Draw",IF(AND(ISNUMBER(F497),ISNUMBER(E497),E497&gt;0,F497&gt;E497),"Profit",IF(AND(ISNUMBER(F497),ISNUMBER(E497),E497&gt;0,F497=E497),"Draw",IF(AND(ISNUMBER(F497),ISNUMBER(E497),E497&gt;0,F497=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L497" s="50"/>
       <x:c r="M497" s="58"/>
@@ -19784,7 +19797,7 @@
         <x:f>IF(A498="","",IF(K498="Subscription","",IF(E498=0,"",IF(ISNUMBER(G498),G498/E498,IF(ISNUMBER(I498),-ABS(I498)/E498,IF(ISNUMBER(H498),0,IF(AND(ISNUMBER(F498),ISNUMBER(E498),E498&gt;0,F498&gt;E498),(F498-E498)/E498,IF(AND(ISNUMBER(F498),ISNUMBER(E498),E498&gt;0,F498=E498),0,IF(AND(ISNUMBER(F498),ISNUMBER(E498),E498&gt;0,F498=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K498" s="50" t="str">
-        <x:f>IF(A498="","",IF(AND(ISNUMBER(E498),E498=0,OR(ISNUMBER(SEARCH("Free",D498&amp;"")),AND(ISNUMBER(F498),F498=0))),"Subscription",IF(ISNUMBER(G498),"Profit",IF(ISNUMBER(I498),"Loss",IF(ISNUMBER(H498),"Draw",IF(AND(ISNUMBER(F498),ISNUMBER(E498),E498&gt;0,F498&gt;E498),"Profit",IF(AND(ISNUMBER(F498),ISNUMBER(E498),E498&gt;0,F498=E498),"Draw",IF(AND(ISNUMBER(F498),ISNUMBER(E498),E498&gt;0,F498=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A498="","",IF(AND(ISNUMBER(E498),E498=0,OR(ISNUMBER(SEARCH("Free",D498&amp;"")),AND(ISNUMBER(F498),F498=0))),"Subscription",IF(ISNUMBER(G498),"Profit",IF(ISNUMBER(I498),"Disqualified",IF(ISNUMBER(H498),"Draw",IF(AND(ISNUMBER(F498),ISNUMBER(E498),E498&gt;0,F498&gt;E498),"Profit",IF(AND(ISNUMBER(F498),ISNUMBER(E498),E498&gt;0,F498=E498),"Draw",IF(AND(ISNUMBER(F498),ISNUMBER(E498),E498&gt;0,F498=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L498" s="50"/>
       <x:c r="M498" s="58"/>
@@ -19821,7 +19834,7 @@
         <x:f>IF(A499="","",IF(K499="Subscription","",IF(E499=0,"",IF(ISNUMBER(G499),G499/E499,IF(ISNUMBER(I499),-ABS(I499)/E499,IF(ISNUMBER(H499),0,IF(AND(ISNUMBER(F499),ISNUMBER(E499),E499&gt;0,F499&gt;E499),(F499-E499)/E499,IF(AND(ISNUMBER(F499),ISNUMBER(E499),E499&gt;0,F499=E499),0,IF(AND(ISNUMBER(F499),ISNUMBER(E499),E499&gt;0,F499=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K499" s="50" t="str">
-        <x:f>IF(A499="","",IF(AND(ISNUMBER(E499),E499=0,OR(ISNUMBER(SEARCH("Free",D499&amp;"")),AND(ISNUMBER(F499),F499=0))),"Subscription",IF(ISNUMBER(G499),"Profit",IF(ISNUMBER(I499),"Loss",IF(ISNUMBER(H499),"Draw",IF(AND(ISNUMBER(F499),ISNUMBER(E499),E499&gt;0,F499&gt;E499),"Profit",IF(AND(ISNUMBER(F499),ISNUMBER(E499),E499&gt;0,F499=E499),"Draw",IF(AND(ISNUMBER(F499),ISNUMBER(E499),E499&gt;0,F499=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A499="","",IF(AND(ISNUMBER(E499),E499=0,OR(ISNUMBER(SEARCH("Free",D499&amp;"")),AND(ISNUMBER(F499),F499=0))),"Subscription",IF(ISNUMBER(G499),"Profit",IF(ISNUMBER(I499),"Disqualified",IF(ISNUMBER(H499),"Draw",IF(AND(ISNUMBER(F499),ISNUMBER(E499),E499&gt;0,F499&gt;E499),"Profit",IF(AND(ISNUMBER(F499),ISNUMBER(E499),E499&gt;0,F499=E499),"Draw",IF(AND(ISNUMBER(F499),ISNUMBER(E499),E499&gt;0,F499=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L499" s="50"/>
       <x:c r="M499" s="58"/>
@@ -19858,7 +19871,7 @@
         <x:f>IF(A500="","",IF(K500="Subscription","",IF(E500=0,"",IF(ISNUMBER(G500),G500/E500,IF(ISNUMBER(I500),-ABS(I500)/E500,IF(ISNUMBER(H500),0,IF(AND(ISNUMBER(F500),ISNUMBER(E500),E500&gt;0,F500&gt;E500),(F500-E500)/E500,IF(AND(ISNUMBER(F500),ISNUMBER(E500),E500&gt;0,F500=E500),0,IF(AND(ISNUMBER(F500),ISNUMBER(E500),E500&gt;0,F500=0),-1,"")))))))))</x:f>
       </x:c>
       <x:c r="K500" s="50" t="str">
-        <x:f>IF(A500="","",IF(AND(ISNUMBER(E500),E500=0,OR(ISNUMBER(SEARCH("Free",D500&amp;"")),AND(ISNUMBER(F500),F500=0))),"Subscription",IF(ISNUMBER(G500),"Profit",IF(ISNUMBER(I500),"Loss",IF(ISNUMBER(H500),"Draw",IF(AND(ISNUMBER(F500),ISNUMBER(E500),E500&gt;0,F500&gt;E500),"Profit",IF(AND(ISNUMBER(F500),ISNUMBER(E500),E500&gt;0,F500=E500),"Draw",IF(AND(ISNUMBER(F500),ISNUMBER(E500),E500&gt;0,F500=0),"Loss",""))))))))</x:f>
+        <x:f>IF(A500="","",IF(AND(ISNUMBER(E500),E500=0,OR(ISNUMBER(SEARCH("Free",D500&amp;"")),AND(ISNUMBER(F500),F500=0))),"Subscription",IF(ISNUMBER(G500),"Profit",IF(ISNUMBER(I500),"Disqualified",IF(ISNUMBER(H500),"Draw",IF(AND(ISNUMBER(F500),ISNUMBER(E500),E500&gt;0,F500&gt;E500),"Profit",IF(AND(ISNUMBER(F500),ISNUMBER(E500),E500&gt;0,F500=E500),"Draw",IF(AND(ISNUMBER(F500),ISNUMBER(E500),E500&gt;0,F500=0),"Disqualified",""))))))))</x:f>
       </x:c>
       <x:c r="L500" s="50"/>
       <x:c r="M500" s="58"/>
@@ -19892,7 +19905,9 @@
       <x:c r="H501" s="58"/>
       <x:c r="I501" s="58"/>
       <x:c r="J501" s="60"/>
-      <x:c r="K501" s="50"/>
+      <x:c r="K501" s="50" t="str">
+        <x:f>IF(A501="","",IF(AND(ISNUMBER(E501),E501=0,OR(ISNUMBER(SEARCH("Free",D501&amp;"")),AND(ISNUMBER(F501),F501=0))),"Subscription",IF(ISNUMBER(G501),"Profit",IF(ISNUMBER(I501),"Disqualified",IF(ISNUMBER(H501),"Draw",IF(AND(ISNUMBER(F501),ISNUMBER(E501),E501&gt;0,F501&gt;E501),"Profit",IF(AND(ISNUMBER(F501),ISNUMBER(E501),E501&gt;0,F501=E501),"Draw",IF(AND(ISNUMBER(F501),ISNUMBER(E501),E501&gt;0,F501=0),"Disqualified",""))))))))</x:f>
+      </x:c>
       <x:c r="L501" s="50"/>
       <x:c r="M501" s="58"/>
       <x:c r="N501" s="58"/>
@@ -19925,7 +19940,9 @@
       <x:c r="H502" s="58"/>
       <x:c r="I502" s="58"/>
       <x:c r="J502" s="60"/>
-      <x:c r="K502" s="50"/>
+      <x:c r="K502" s="50" t="str">
+        <x:f>IF(A502="","",IF(AND(ISNUMBER(E502),E502=0,OR(ISNUMBER(SEARCH("Free",D502&amp;"")),AND(ISNUMBER(F502),F502=0))),"Subscription",IF(ISNUMBER(G502),"Profit",IF(ISNUMBER(I502),"Disqualified",IF(ISNUMBER(H502),"Draw",IF(AND(ISNUMBER(F502),ISNUMBER(E502),E502&gt;0,F502&gt;E502),"Profit",IF(AND(ISNUMBER(F502),ISNUMBER(E502),E502&gt;0,F502=E502),"Draw",IF(AND(ISNUMBER(F502),ISNUMBER(E502),E502&gt;0,F502=0),"Disqualified",""))))))))</x:f>
+      </x:c>
       <x:c r="L502" s="50"/>
       <x:c r="M502" s="58"/>
       <x:c r="N502" s="58"/>
@@ -19958,7 +19975,9 @@
       <x:c r="H503" s="58"/>
       <x:c r="I503" s="58"/>
       <x:c r="J503" s="60"/>
-      <x:c r="K503" s="50"/>
+      <x:c r="K503" s="50" t="str">
+        <x:f>IF(A503="","",IF(AND(ISNUMBER(E503),E503=0,OR(ISNUMBER(SEARCH("Free",D503&amp;"")),AND(ISNUMBER(F503),F503=0))),"Subscription",IF(ISNUMBER(G503),"Profit",IF(ISNUMBER(I503),"Disqualified",IF(ISNUMBER(H503),"Draw",IF(AND(ISNUMBER(F503),ISNUMBER(E503),E503&gt;0,F503&gt;E503),"Profit",IF(AND(ISNUMBER(F503),ISNUMBER(E503),E503&gt;0,F503=E503),"Draw",IF(AND(ISNUMBER(F503),ISNUMBER(E503),E503&gt;0,F503=0),"Disqualified",""))))))))</x:f>
+      </x:c>
       <x:c r="L503" s="50"/>
       <x:c r="M503" s="58"/>
       <x:c r="N503" s="58"/>
@@ -19991,7 +20010,9 @@
       <x:c r="H504" s="58"/>
       <x:c r="I504" s="58"/>
       <x:c r="J504" s="60"/>
-      <x:c r="K504" s="50"/>
+      <x:c r="K504" s="50" t="str">
+        <x:f>IF(A504="","",IF(AND(ISNUMBER(E504),E504=0,OR(ISNUMBER(SEARCH("Free",D504&amp;"")),AND(ISNUMBER(F504),F504=0))),"Subscription",IF(ISNUMBER(G504),"Profit",IF(ISNUMBER(I504),"Disqualified",IF(ISNUMBER(H504),"Draw",IF(AND(ISNUMBER(F504),ISNUMBER(E504),E504&gt;0,F504&gt;E504),"Profit",IF(AND(ISNUMBER(F504),ISNUMBER(E504),E504&gt;0,F504=E504),"Draw",IF(AND(ISNUMBER(F504),ISNUMBER(E504),E504&gt;0,F504=0),"Disqualified",""))))))))</x:f>
+      </x:c>
       <x:c r="L504" s="50"/>
       <x:c r="M504" s="58"/>
       <x:c r="N504" s="58"/>
@@ -20063,7 +20084,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb52e0862851145dd"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0a262baeaeef40ae"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -20336,7 +20357,7 @@
     <x:mergeCell ref="A22:H25"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1251be5e45c2476d"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R91c3517ea3174e29"/>
 </x:worksheet>
 </file>
 
@@ -21502,7 +21523,7 @@
     <x:mergeCell ref="A48:H48"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R072d216a6a55410d"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd6ac504635644184"/>
 </x:worksheet>
 </file>
 

--- a/StepCat_Blank_Profitability_Analysis_Template.xlsx
+++ b/StepCat_Blank_Profitability_Analysis_Template.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instructions" sheetId="1" r:id="Rccd59d7cc3e64379"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Game Records" sheetId="2" r:id="Rd57f65cb88604185"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="3" r:id="R3d63860c223f4868"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Game Comparisons" sheetId="4" r:id="R6d3c51b78bbc4514"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Best Results" sheetId="5" r:id="R5abb206f4c294488"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instructions" sheetId="1" r:id="R324d79818888466d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Game Records" sheetId="2" r:id="Re939be780d1e402c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="3" r:id="Ref6a303033e94fa6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Game Comparisons" sheetId="4" r:id="R024983d60d9a450b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Best Results" sheetId="5" r:id="Rdd9eea6b1ba047c0"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -94,7 +94,7 @@
       <x:name val="Carlito"/>
     </x:font>
   </x:fonts>
-  <x:fills count="15">
+  <x:fills count="16">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -166,6 +166,11 @@
         <x:fgColor rgb="FF38761D"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFF2CC"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
   <x:borders count="2">
     <x:border/>
@@ -174,7 +179,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="131">
+  <x:cellXfs count="139">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -505,6 +510,26 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="11" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="8" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="8" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -898,7 +923,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R472665c701104544"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Raac6e594508248b9"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -933,7 +958,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R3f0261c555224ee0"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R1c0afa57be634643"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1132,8 +1157,8 @@
     <x:col min="8" max="8" width="14" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" ht="108" hidden="0" customHeight="1">
-      <x:c r="A1" s="130" t="str">
+    <x:row r="1" ht="21.600000381469727" hidden="0" customHeight="1">
+      <x:c r="A1" s="137" t="str">
         <x:v>StepCat v200 Profitability Analysis Template</x:v>
       </x:c>
       <x:c r="B1" s="5"/>
@@ -1144,7 +1169,7 @@
       <x:c r="G1" s="5"/>
       <x:c r="H1" s="5"/>
     </x:row>
-    <x:row r="2" ht="105.5999984741211" hidden="0" customHeight="1">
+    <x:row r="2" ht="15" hidden="0" customHeight="1">
       <x:c r="A2" s="14" t="str">
         <x:v>A blank, optional template for comparing completed StepCat games. No personal records are included.</x:v>
       </x:c>
@@ -1159,7 +1184,7 @@
     <x:row r="3" ht="15" hidden="0" customHeight="1">
       <x:c r="A3" s="48"/>
     </x:row>
-    <x:row r="4" ht="28.799999237060547" hidden="0" customHeight="1">
+    <x:row r="4" ht="15" hidden="0" customHeight="1">
       <x:c r="A4" s="92" t="str">
         <x:v>1. Where to paste</x:v>
       </x:c>
@@ -1171,7 +1196,7 @@
       <x:c r="G4" s="23"/>
       <x:c r="H4" s="23"/>
     </x:row>
-    <x:row r="5" ht="26.399999618530273" hidden="0" customHeight="1">
+    <x:row r="5" ht="15" hidden="0" customHeight="1">
       <x:c r="A5" s="32" t="str">
         <x:v>• Row 4 is the header row.</x:v>
       </x:c>
@@ -1183,7 +1208,7 @@
       <x:c r="G5" s="32"/>
       <x:c r="H5" s="32"/>
     </x:row>
-    <x:row r="6" ht="39.599998474121094" hidden="0" customHeight="1">
+    <x:row r="6" ht="15" hidden="0" customHeight="1">
       <x:c r="A6" s="32" t="str">
         <x:v>• Row 5 and below are for game records.</x:v>
       </x:c>
@@ -1195,7 +1220,7 @@
       <x:c r="G6" s="32"/>
       <x:c r="H6" s="32"/>
     </x:row>
-    <x:row r="7" ht="39.599998474121094" hidden="0" customHeight="1">
+    <x:row r="7" ht="15" hidden="0" customHeight="1">
       <x:c r="A7" s="32" t="str">
         <x:v>• Paste StepCat result rows starting in A5.</x:v>
       </x:c>
@@ -1207,7 +1232,7 @@
       <x:c r="G7" s="32"/>
       <x:c r="H7" s="32"/>
     </x:row>
-    <x:row r="8" ht="92.4000015258789" hidden="0" customHeight="1">
+    <x:row r="8" ht="15" hidden="0" customHeight="1">
       <x:c r="A8" s="48" t="str">
         <x:v>• Use Copy Header only for a blank/custom sheet, or if this template's row 4 headers were deleted.</x:v>
       </x:c>
@@ -1222,7 +1247,7 @@
       <x:c r="G9" s="23"/>
       <x:c r="H9" s="23"/>
     </x:row>
-    <x:row r="10" ht="26.399999618530273" hidden="0" customHeight="1">
+    <x:row r="10" ht="15" hidden="0" customHeight="1">
       <x:c r="A10" s="32" t="str">
         <x:v>2. Formula columns</x:v>
       </x:c>
@@ -1234,7 +1259,7 @@
       <x:c r="G10" s="32"/>
       <x:c r="H10" s="32"/>
     </x:row>
-    <x:row r="11" ht="39.599998474121094" hidden="0" customHeight="1">
+    <x:row r="11" ht="15" hidden="0" customHeight="1">
       <x:c r="A11" s="32" t="str">
         <x:v>• Formula columns calculate for you.</x:v>
       </x:c>
@@ -1246,7 +1271,7 @@
       <x:c r="G11" s="32"/>
       <x:c r="H11" s="32"/>
     </x:row>
-    <x:row r="12" ht="132" hidden="0" customHeight="1">
+    <x:row r="12" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A12" s="32" t="str">
         <x:v>• In Game Records, formula columns are J = ROI, K = Result, Q = Challenge Length, U = Net Profit, V = Eliminated Players, and W = Elimination Rate.</x:v>
       </x:c>
@@ -1258,7 +1283,7 @@
       <x:c r="G12" s="32"/>
       <x:c r="H12" s="32"/>
     </x:row>
-    <x:row r="13" ht="66" hidden="0" customHeight="1">
+    <x:row r="13" ht="15" hidden="0" customHeight="1">
       <x:c r="A13" s="32" t="str">
         <x:v>• Do not type over formula cells unless you want to replace the formula.</x:v>
       </x:c>
@@ -1270,7 +1295,7 @@
       <x:c r="G13" s="32"/>
       <x:c r="H13" s="32"/>
     </x:row>
-    <x:row r="14" ht="132" hidden="0" customHeight="1">
+    <x:row r="14" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A14" s="32" t="str">
         <x:v>• If a formula cell is blank or missing, use another row where that same column is working, then copy that formula into the blank cell.</x:v>
       </x:c>
@@ -1285,9 +1310,9 @@
     <x:row r="15" ht="15" hidden="0" customHeight="1">
       <x:c r="A15" s="48"/>
     </x:row>
-    <x:row r="16" ht="43.20000076293945" hidden="0" customHeight="1">
+    <x:row r="16" ht="15" hidden="0" customHeight="1">
       <x:c r="A16" s="92" t="str">
-        <x:v>3. Older or in-progress games</x:v>
+        <x:v>3. How to copy formula cells into a custom sheet</x:v>
       </x:c>
       <x:c r="B16" s="23"/>
       <x:c r="C16" s="23"/>
@@ -1297,9 +1322,9 @@
       <x:c r="G16" s="23"/>
       <x:c r="H16" s="23"/>
     </x:row>
-    <x:row r="17" ht="52.79999923706055" hidden="0" customHeight="1">
+    <x:row r="17" ht="15" hidden="0" customHeight="1">
       <x:c r="A17" s="32" t="str">
-        <x:v>• Add or update games under the matching column names.</x:v>
+        <x:v>• Open the StepCat v200 template.</x:v>
       </x:c>
       <x:c r="B17" s="32"/>
       <x:c r="C17" s="32"/>
@@ -1309,9 +1334,9 @@
       <x:c r="G17" s="32"/>
       <x:c r="H17" s="32"/>
     </x:row>
-    <x:row r="18" ht="79.19999694824219" hidden="0" customHeight="1">
+    <x:row r="18" ht="15" hidden="0" customHeight="1">
       <x:c r="A18" s="32" t="str">
-        <x:v>• StepCat copied rows already include ROI and Result for completed entries.</x:v>
+        <x:v>• Go to the Game Records sheet.</x:v>
       </x:c>
       <x:c r="B18" s="32"/>
       <x:c r="C18" s="32"/>
@@ -1321,9 +1346,9 @@
       <x:c r="G18" s="32"/>
       <x:c r="H18" s="32"/>
     </x:row>
-    <x:row r="19" ht="66" hidden="0" customHeight="1">
+    <x:row r="19" ht="15" hidden="0" customHeight="1">
       <x:c r="A19" s="32" t="str">
-        <x:v>• Template formulas are mainly helpful for older, manual, or in-progress rows.</x:v>
+        <x:v>• Find a working formula cell in the column you want to use. Example: ROI is column J and Result is column K.</x:v>
       </x:c>
       <x:c r="B19" s="32"/>
       <x:c r="C19" s="32"/>
@@ -1334,7 +1359,9 @@
       <x:c r="H19" s="32"/>
     </x:row>
     <x:row r="20" ht="15" hidden="0" customHeight="1">
-      <x:c r="A20" s="32"/>
+      <x:c r="A20" s="32" t="str">
+        <x:v>• Copy that formula cell.</x:v>
+      </x:c>
       <x:c r="B20" s="32"/>
       <x:c r="C20" s="32"/>
       <x:c r="D20" s="32"/>
@@ -1345,7 +1372,7 @@
     </x:row>
     <x:row r="21" ht="15" hidden="0" customHeight="1">
       <x:c r="A21" s="32" t="str">
-        <x:v>4. Player counts</x:v>
+        <x:v>• Go to your custom sheet.</x:v>
       </x:c>
       <x:c r="B21" s="32"/>
       <x:c r="C21" s="32"/>
@@ -1355,9 +1382,9 @@
       <x:c r="G21" s="32"/>
       <x:c r="H21" s="32"/>
     </x:row>
-    <x:row r="22" ht="52.79999923706055" hidden="0" customHeight="1">
+    <x:row r="22" ht="15" hidden="0" customHeight="1">
       <x:c r="A22" s="32" t="str">
-        <x:v>• Total Players = everyone who entered the challenge.</x:v>
+        <x:v>• Paste it into the same matching column on the row where you want the formula.</x:v>
       </x:c>
       <x:c r="B22" s="32"/>
       <x:c r="C22" s="32"/>
@@ -1367,9 +1394,9 @@
       <x:c r="G22" s="32"/>
       <x:c r="H22" s="32"/>
     </x:row>
-    <x:row r="23" ht="52.79999923706055" hidden="0" customHeight="1">
+    <x:row r="23" ht="15" hidden="0" customHeight="1">
       <x:c r="A23" s="32" t="str">
-        <x:v>• Eligible Players = players still eligible to win / not disqualified.</x:v>
+        <x:v>• If you need the formula for more rows, copy that cell down the same column.</x:v>
       </x:c>
       <x:c r="B23" s="32"/>
       <x:c r="C23" s="32"/>
@@ -1379,9 +1406,9 @@
       <x:c r="G23" s="32"/>
       <x:c r="H23" s="32"/>
     </x:row>
-    <x:row r="24" ht="79.19999694824219" hidden="0" customHeight="1">
+    <x:row r="24" ht="15" hidden="0" customHeight="1">
       <x:c r="A24" s="48" t="str">
-        <x:v>• Eligible Players drives payout estimates. Total Players is context for tracking eliminations.</x:v>
+        <x:v>• Keep formula cells in the same matching columns so the formulas read the correct game information.</x:v>
       </x:c>
     </x:row>
     <x:row r="25" ht="15" hidden="0" customHeight="1">
@@ -1394,9 +1421,9 @@
       <x:c r="G25" s="23"/>
       <x:c r="H25" s="23"/>
     </x:row>
-    <x:row r="26" ht="26.399999618530273" hidden="0" customHeight="1">
+    <x:row r="26" ht="15" hidden="0" customHeight="1">
       <x:c r="A26" s="32" t="str">
-        <x:v>5. Warm-up week estimate tip</x:v>
+        <x:v>4. Older or in-progress games</x:v>
       </x:c>
       <x:c r="B26" s="32"/>
       <x:c r="C26" s="32"/>
@@ -1406,9 +1433,9 @@
       <x:c r="G26" s="32"/>
       <x:c r="H26" s="32"/>
     </x:row>
-    <x:row r="27" ht="79.19999694824219" hidden="0" customHeight="1">
+    <x:row r="27" ht="15" hidden="0" customHeight="1">
       <x:c r="A27" s="32" t="str">
-        <x:v>• For best estimate accuracy, add challenges after warm-up week ends.</x:v>
+        <x:v>• Add or update games under the matching column names.</x:v>
       </x:c>
       <x:c r="B27" s="32"/>
       <x:c r="C27" s="32"/>
@@ -1418,9 +1445,9 @@
       <x:c r="G27" s="32"/>
       <x:c r="H27" s="32"/>
     </x:row>
-    <x:row r="28" ht="66" hidden="0" customHeight="1">
+    <x:row r="28" ht="15" hidden="0" customHeight="1">
       <x:c r="A28" s="32" t="str">
-        <x:v>• Gross Pot and Total Players are usually more reliable after warm-up week.</x:v>
+        <x:v>• StepCat copied rows already include ROI and Result for completed entries.</x:v>
       </x:c>
       <x:c r="B28" s="32"/>
       <x:c r="C28" s="32"/>
@@ -1430,9 +1457,9 @@
       <x:c r="G28" s="32"/>
       <x:c r="H28" s="32"/>
     </x:row>
-    <x:row r="29" ht="52.79999923706055" hidden="0" customHeight="1">
+    <x:row r="29" ht="15" hidden="0" customHeight="1">
       <x:c r="A29" s="48" t="str">
-        <x:v>• Update Eligible Players as the challenge progresses.</x:v>
+        <x:v>• Template formulas are mainly helpful for older, manual, or in-progress rows.</x:v>
       </x:c>
     </x:row>
     <x:row r="30" ht="15" hidden="0" customHeight="1">
@@ -1445,9 +1472,9 @@
       <x:c r="G30" s="23"/>
       <x:c r="H30" s="23"/>
     </x:row>
-    <x:row r="31" ht="26.399999618530273" hidden="0" customHeight="1">
+    <x:row r="31" ht="15" hidden="0" customHeight="1">
       <x:c r="A31" s="32" t="str">
-        <x:v>6. What updates automatically</x:v>
+        <x:v>5. Player counts</x:v>
       </x:c>
       <x:c r="B31" s="32"/>
       <x:c r="C31" s="32"/>
@@ -1457,9 +1484,9 @@
       <x:c r="G31" s="32"/>
       <x:c r="H31" s="32"/>
     </x:row>
-    <x:row r="32" ht="39.599998474121094" hidden="0" customHeight="1">
+    <x:row r="32" ht="15" hidden="0" customHeight="1">
       <x:c r="A32" s="32" t="str">
-        <x:v>• Summary shows totals, averages, and result rates.</x:v>
+        <x:v>• Total Players = everyone who entered the challenge.</x:v>
       </x:c>
       <x:c r="B32" s="32"/>
       <x:c r="C32" s="32"/>
@@ -1469,9 +1496,9 @@
       <x:c r="G32" s="32"/>
       <x:c r="H32" s="32"/>
     </x:row>
-    <x:row r="33" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="33" ht="15" hidden="0" customHeight="1">
       <x:c r="A33" s="32" t="str">
-        <x:v>• Game Comparisons compares game type, challenge length, entry fee, payment type, player ranges, and elimination rates.</x:v>
+        <x:v>• Eligible Players = players still eligible to win / not disqualified.</x:v>
       </x:c>
       <x:c r="B33" s="32"/>
       <x:c r="C33" s="32"/>
@@ -1481,16 +1508,62 @@
       <x:c r="G33" s="32"/>
       <x:c r="H33" s="32"/>
     </x:row>
-    <x:row r="34" ht="52.79999923706055" hidden="0" customHeight="1">
+    <x:row r="34" ht="15" hidden="0" customHeight="1">
       <x:c r="A34" s="48" t="str">
-        <x:v>• Best Results lists the highest Net Profit and ROI values.</x:v>
+        <x:v>• Eligible Players drives payout estimates. Total Players is context for tracking eliminations.</x:v>
       </x:c>
     </x:row>
     <x:row r="35" ht="15" hidden="0" customHeight="1">
       <x:c r="A35" s="48"/>
     </x:row>
-    <x:row r="36" ht="66" hidden="0" customHeight="1">
+    <x:row r="36" ht="15" hidden="0" customHeight="1">
       <x:c r="A36" s="48" t="str">
+        <x:v>6. Warm-up week estimate tip</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37" ht="15" hidden="0" customHeight="1">
+      <x:c r="A37" s="48" t="str">
+        <x:v>• For best estimate accuracy, add challenges after warm-up week ends.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38" ht="15" hidden="0" customHeight="1">
+      <x:c r="A38" s="48" t="str">
+        <x:v>• Gross Pot and Total Players are usually more reliable after warm-up week.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39" ht="15" hidden="0" customHeight="1">
+      <x:c r="A39" s="48" t="str">
+        <x:v>• Update Eligible Players as the challenge progresses.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40" ht="15" hidden="0" customHeight="1">
+      <x:c r="A40" s="48"/>
+    </x:row>
+    <x:row r="41" ht="15" hidden="0" customHeight="1">
+      <x:c r="A41" s="48" t="str">
+        <x:v>7. What updates automatically</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42" ht="15" hidden="0" customHeight="1">
+      <x:c r="A42" s="48" t="str">
+        <x:v>• Summary shows totals, averages, and result rates.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43" ht="15" hidden="0" customHeight="1">
+      <x:c r="A43" s="48" t="str">
+        <x:v>• Game Comparisons compares game type, challenge length, entry fee, payment type, player ranges, and elimination rates.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44" ht="15" hidden="0" customHeight="1">
+      <x:c r="A44" s="48" t="str">
+        <x:v>• Best Results lists the highest Net Profit and ROI values.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45" ht="15" hidden="0" customHeight="1">
+      <x:c r="A45" s="48"/>
+    </x:row>
+    <x:row r="46" ht="15" hidden="0" customHeight="1">
+      <x:c r="A46" s="48" t="str">
         <x:v>The official posted game result should always be treated as authoritative.</x:v>
       </x:c>
     </x:row>
@@ -1612,32 +1685,32 @@
       <x:c r="V2" s="110"/>
       <x:c r="W2" s="110"/>
     </x:row>
-    <x:row r="3" ht="38" customHeight="1">
-      <x:c r="A3" s="114" t="str">
-        <x:v>If a formula cell is blank or missing, use another row where that same column is working, then copy that formula into the blank cell.</x:v>
-      </x:c>
-      <x:c r="B3" s="114"/>
-      <x:c r="C3" s="114"/>
-      <x:c r="D3" s="114"/>
-      <x:c r="E3" s="114"/>
-      <x:c r="F3" s="114"/>
-      <x:c r="G3" s="114"/>
-      <x:c r="H3" s="114"/>
-      <x:c r="I3" s="114"/>
-      <x:c r="J3" s="114"/>
-      <x:c r="K3" s="114"/>
-      <x:c r="L3" s="114"/>
-      <x:c r="M3" s="114"/>
-      <x:c r="N3" s="114"/>
-      <x:c r="O3" s="114"/>
-      <x:c r="P3" s="114"/>
-      <x:c r="Q3" s="114"/>
-      <x:c r="R3" s="114"/>
-      <x:c r="S3" s="114"/>
-      <x:c r="T3" s="114"/>
-      <x:c r="U3" s="114"/>
-      <x:c r="V3" s="114"/>
-      <x:c r="W3" s="114"/>
+    <x:row r="3" ht="46" customHeight="1">
+      <x:c r="A3" s="138" t="str">
+        <x:v>If a formula cell is blank or missing, use another row where that same column is working, then copy that formula into the blank cell. For custom sheets, keep formulas in the same matching columns.</x:v>
+      </x:c>
+      <x:c r="B3" s="138"/>
+      <x:c r="C3" s="138"/>
+      <x:c r="D3" s="138"/>
+      <x:c r="E3" s="138"/>
+      <x:c r="F3" s="138"/>
+      <x:c r="G3" s="138"/>
+      <x:c r="H3" s="138"/>
+      <x:c r="I3" s="138"/>
+      <x:c r="J3" s="138"/>
+      <x:c r="K3" s="138"/>
+      <x:c r="L3" s="138"/>
+      <x:c r="M3" s="138"/>
+      <x:c r="N3" s="138"/>
+      <x:c r="O3" s="138"/>
+      <x:c r="P3" s="138"/>
+      <x:c r="Q3" s="138"/>
+      <x:c r="R3" s="138"/>
+      <x:c r="S3" s="138"/>
+      <x:c r="T3" s="138"/>
+      <x:c r="U3" s="138"/>
+      <x:c r="V3" s="138"/>
+      <x:c r="W3" s="138"/>
     </x:row>
     <x:row r="4" ht="34" customHeight="1">
       <x:c r="A4" s="115" t="str">
@@ -20252,7 +20325,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra1b7764e57a04d64"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R220bfb6228934ab9"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -20525,7 +20598,7 @@
     <x:mergeCell ref="A22:H25"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7ba5e2016a874c78"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R13a19c98f48e4777"/>
 </x:worksheet>
 </file>
 
@@ -21691,7 +21764,7 @@
     <x:mergeCell ref="A48:H48"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7af3e52145ac443d"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R16b193129b044cf4"/>
 </x:worksheet>
 </file>
 

--- a/StepCat_Blank_Profitability_Analysis_Template.xlsx
+++ b/StepCat_Blank_Profitability_Analysis_Template.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instructions" sheetId="1" r:id="Rcaf62e9a075f403c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Game Records" sheetId="2" r:id="R0603d59b34a642a7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="3" r:id="Rce45ddc12055427a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Game Comparisons" sheetId="4" r:id="R456202b901b64ead"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Best Results" sheetId="5" r:id="R06b239b2c3cd45a9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instructions" sheetId="1" r:id="R2edba123171f43ca"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Game Records" sheetId="2" r:id="R835ab0076b6a4c5a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="3" r:id="R63983ef0d1e94a1f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Game Comparisons" sheetId="4" r:id="R7984b606655a42d0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Best Results" sheetId="5" r:id="Rd66b6901ef844bc6"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -94,7 +94,7 @@
       <x:name val="Carlito"/>
     </x:font>
   </x:fonts>
-  <x:fills count="20">
+  <x:fills count="21">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -191,6 +191,11 @@
         <x:fgColor rgb="FF38761D"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFF2CC"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
   <x:borders count="2">
     <x:border/>
@@ -199,7 +204,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="151">
+  <x:cellXfs count="153">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -586,6 +591,12 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="11" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="20" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="20" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -979,7 +990,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Reb53d9436cf94cfe"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rb76e51da2dc24aae"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1014,7 +1025,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R6848b50fde7f4866"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Re34b263e2d0843bf"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1729,59 +1740,57 @@
       <x:c r="V1" s="5"/>
       <x:c r="W1" s="5"/>
     </x:row>
-    <x:row r="2" ht="24" customHeight="1">
-      <x:c r="A2" s="139" t="str">
-        <x:v>Paste StepCat rows starting in A5. Full formula help is on the Instructions tab.</x:v>
-      </x:c>
-      <x:c r="B2" s="139"/>
-      <x:c r="C2" s="139"/>
-      <x:c r="D2" s="139"/>
-      <x:c r="E2" s="139"/>
-      <x:c r="F2" s="139"/>
-      <x:c r="G2" s="139"/>
-      <x:c r="H2" s="139"/>
-      <x:c r="I2" s="139"/>
-      <x:c r="J2" s="139"/>
-      <x:c r="K2" s="139"/>
-      <x:c r="L2" s="139"/>
-      <x:c r="M2" s="139"/>
-      <x:c r="N2" s="139"/>
-      <x:c r="O2" s="139"/>
-      <x:c r="P2" s="139"/>
-      <x:c r="Q2" s="139"/>
-      <x:c r="R2" s="139"/>
-      <x:c r="S2" s="139"/>
-      <x:c r="T2" s="139"/>
-      <x:c r="U2" s="139"/>
-      <x:c r="V2" s="139"/>
-      <x:c r="W2" s="139"/>
-    </x:row>
-    <x:row r="3" ht="24" customHeight="1">
-      <x:c r="A3" s="140" t="str">
-        <x:v>Formula columns: J ROI, K Result, Q Length, U Net Profit, V Eliminated, W Rate.</x:v>
-      </x:c>
-      <x:c r="B3" s="140"/>
-      <x:c r="C3" s="140"/>
-      <x:c r="D3" s="140"/>
-      <x:c r="E3" s="140"/>
-      <x:c r="F3" s="140"/>
-      <x:c r="G3" s="140"/>
-      <x:c r="H3" s="140"/>
-      <x:c r="I3" s="140"/>
-      <x:c r="J3" s="140"/>
-      <x:c r="K3" s="140"/>
-      <x:c r="L3" s="140"/>
-      <x:c r="M3" s="140"/>
-      <x:c r="N3" s="140"/>
-      <x:c r="O3" s="140"/>
-      <x:c r="P3" s="140"/>
-      <x:c r="Q3" s="140"/>
-      <x:c r="R3" s="140"/>
-      <x:c r="S3" s="140"/>
-      <x:c r="T3" s="140"/>
-      <x:c r="U3" s="140"/>
-      <x:c r="V3" s="140"/>
-      <x:c r="W3" s="140"/>
+    <x:row r="2" ht="22" customHeight="1">
+      <x:c r="A2" s="151" t="str">
+        <x:v>Paste StepCat rows starting in A5. See Instructions tab for formula help.</x:v>
+      </x:c>
+      <x:c r="B2" s="151"/>
+      <x:c r="C2" s="151"/>
+      <x:c r="D2" s="151"/>
+      <x:c r="E2" s="151"/>
+      <x:c r="F2" s="151"/>
+      <x:c r="G2" s="151"/>
+      <x:c r="H2" s="151"/>
+      <x:c r="I2" s="151"/>
+      <x:c r="J2" s="151"/>
+      <x:c r="K2" s="151"/>
+      <x:c r="L2" s="151"/>
+      <x:c r="M2" s="151"/>
+      <x:c r="N2" s="151"/>
+      <x:c r="O2" s="151"/>
+      <x:c r="P2" s="151"/>
+      <x:c r="Q2" s="151"/>
+      <x:c r="R2" s="151"/>
+      <x:c r="S2" s="151"/>
+      <x:c r="T2" s="151"/>
+      <x:c r="U2" s="151"/>
+      <x:c r="V2" s="151"/>
+      <x:c r="W2" s="151"/>
+    </x:row>
+    <x:row r="3" ht="22" customHeight="1">
+      <x:c r="A3" s="152"/>
+      <x:c r="B3" s="152"/>
+      <x:c r="C3" s="152"/>
+      <x:c r="D3" s="152"/>
+      <x:c r="E3" s="152"/>
+      <x:c r="F3" s="152"/>
+      <x:c r="G3" s="152"/>
+      <x:c r="H3" s="152"/>
+      <x:c r="I3" s="152"/>
+      <x:c r="J3" s="152"/>
+      <x:c r="K3" s="152"/>
+      <x:c r="L3" s="152"/>
+      <x:c r="M3" s="152"/>
+      <x:c r="N3" s="152"/>
+      <x:c r="O3" s="152"/>
+      <x:c r="P3" s="152"/>
+      <x:c r="Q3" s="152"/>
+      <x:c r="R3" s="152"/>
+      <x:c r="S3" s="152"/>
+      <x:c r="T3" s="152"/>
+      <x:c r="U3" s="152"/>
+      <x:c r="V3" s="152"/>
+      <x:c r="W3" s="152"/>
     </x:row>
     <x:row r="4" ht="34" customHeight="1">
       <x:c r="A4" s="141" t="str">
@@ -20396,7 +20405,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1db804d2b3c64be8"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Recac93173450419f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -20669,7 +20678,7 @@
     <x:mergeCell ref="A22:H25"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1cca442aeb2a4db1"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2caa45ab70a242c7"/>
 </x:worksheet>
 </file>
 
@@ -21835,7 +21844,7 @@
     <x:mergeCell ref="A48:H48"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc01e4ebbe64347ef"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R86d8cebe2f1840d5"/>
 </x:worksheet>
 </file>
 

--- a/StepCat_Blank_Profitability_Analysis_Template.xlsx
+++ b/StepCat_Blank_Profitability_Analysis_Template.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instructions" sheetId="1" r:id="R2edba123171f43ca"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Game Records" sheetId="2" r:id="R835ab0076b6a4c5a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="3" r:id="R63983ef0d1e94a1f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Game Comparisons" sheetId="4" r:id="R7984b606655a42d0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Best Results" sheetId="5" r:id="Rd66b6901ef844bc6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instructions" sheetId="1" r:id="Rd991c0cafc014520"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Game Records" sheetId="2" r:id="Rb2589606705c460d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="3" r:id="Ree9c1d1172a14712"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Game Comparisons" sheetId="4" r:id="R3500dea867cd4d8a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Best Results" sheetId="5" r:id="R37a179e7d90647f6"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -94,7 +94,7 @@
       <x:name val="Carlito"/>
     </x:font>
   </x:fonts>
-  <x:fills count="21">
+  <x:fills count="22">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -196,6 +196,11 @@
         <x:fgColor rgb="FFFFF2CC"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFF2CC"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
   <x:borders count="2">
     <x:border/>
@@ -204,7 +209,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="153">
+  <x:cellXfs count="156">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -598,6 +603,15 @@
     <x:xf numFmtId="0" fontId="8" fillId="20" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="21" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="21" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="21" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -990,7 +1004,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rb76e51da2dc24aae"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R1cd64466e3d64bae"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1025,7 +1039,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Re34b263e2d0843bf"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rd0216a5b499849df"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1214,7 +1228,7 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="92" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="96" hidden="0" customWidth="1"/>
     <x:col min="2" max="2" width="14" hidden="0" customWidth="1"/>
     <x:col min="3" max="3" width="14" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="14" hidden="0" customWidth="1"/>
@@ -1225,7 +1239,7 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="21.600000381469727" hidden="0" customHeight="1">
-      <x:c r="A1" s="150" t="str">
+      <x:c r="A1" s="155" t="str">
         <x:v>StepCat v200 Profitability Analysis Template</x:v>
       </x:c>
       <x:c r="B1" s="5"/>
@@ -1350,9 +1364,9 @@
       <x:c r="G12" s="32"/>
       <x:c r="H12" s="32"/>
     </x:row>
-    <x:row r="13" ht="15" hidden="0" customHeight="1">
+    <x:row r="13" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A13" s="32" t="str">
-        <x:v>• Formula columns calculate for you.</x:v>
+        <x:v>• If you are using the StepCat v200 template, you usually do not need to copy formula cells. They are already built into the template.</x:v>
       </x:c>
       <x:c r="B13" s="32"/>
       <x:c r="C13" s="32"/>
@@ -1362,9 +1376,9 @@
       <x:c r="G13" s="32"/>
       <x:c r="H13" s="32"/>
     </x:row>
-    <x:row r="14" ht="26.399999618530273" hidden="0" customHeight="1">
+    <x:row r="14" ht="15" hidden="0" customHeight="1">
       <x:c r="A14" s="32" t="str">
-        <x:v>• In Game Records, formula columns are J = ROI, K = Result, Q = Challenge Length, U = Net Profit, V = Eliminated Players, and W = Elimination Rate.</x:v>
+        <x:v>• Only copy formula cells if you are making a custom sheet or replacing a missing formula.</x:v>
       </x:c>
       <x:c r="B14" s="32"/>
       <x:c r="C14" s="32"/>
@@ -1376,12 +1390,12 @@
     </x:row>
     <x:row r="15" ht="15" hidden="0" customHeight="1">
       <x:c r="A15" s="48" t="str">
-        <x:v>• Do not type over formula cells unless you want to replace the formula.</x:v>
+        <x:v>• Formula cells may look empty, but they are not the same as empty cells.</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="28.799999237060547" hidden="0" customHeight="1">
       <x:c r="A16" s="92" t="str">
-        <x:v>• If a formula cell is blank or missing, use another row where that same column is working, then copy that formula into the blank cell.</x:v>
+        <x:v>• Tap the cell and check the formula bar. If it starts with =, it is a formula. If the formula bar is empty, it is just a blank cell.</x:v>
       </x:c>
       <x:c r="B16" s="23"/>
       <x:c r="C16" s="23"/>
@@ -1393,7 +1407,7 @@
     </x:row>
     <x:row r="17" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A17" s="32" t="str">
-        <x:v>• A working formula cell is usually in a blank row below your pasted entries. Do not copy from a cell that already contains a pasted value.</x:v>
+        <x:v>• In Game Records, formula columns are J = ROI, K = Result, Q = Challenge Length, U = Net Profit, V = Eliminated Players, and W = Elimination Rate.</x:v>
       </x:c>
       <x:c r="B17" s="32"/>
       <x:c r="C17" s="32"/>
@@ -1404,7 +1418,9 @@
       <x:c r="H17" s="32"/>
     </x:row>
     <x:row r="18" ht="15" hidden="0" customHeight="1">
-      <x:c r="A18" s="32"/>
+      <x:c r="A18" s="32" t="str">
+        <x:v>• Do not type over formula cells unless you want to replace the formula.</x:v>
+      </x:c>
       <x:c r="B18" s="32"/>
       <x:c r="C18" s="32"/>
       <x:c r="D18" s="32"/>
@@ -1414,9 +1430,7 @@
       <x:c r="H18" s="32"/>
     </x:row>
     <x:row r="19" ht="15" hidden="0" customHeight="1">
-      <x:c r="A19" s="32" t="str">
-        <x:v>3. How to copy formula cells into a custom sheet</x:v>
-      </x:c>
+      <x:c r="A19" s="32"/>
       <x:c r="B19" s="32"/>
       <x:c r="C19" s="32"/>
       <x:c r="D19" s="32"/>
@@ -1427,7 +1441,7 @@
     </x:row>
     <x:row r="20" ht="15" hidden="0" customHeight="1">
       <x:c r="A20" s="32" t="str">
-        <x:v>• Open the StepCat v200 template.</x:v>
+        <x:v>3. How to copy formula cells into a custom sheet</x:v>
       </x:c>
       <x:c r="B20" s="32"/>
       <x:c r="C20" s="32"/>
@@ -1439,7 +1453,7 @@
     </x:row>
     <x:row r="21" ht="15" hidden="0" customHeight="1">
       <x:c r="A21" s="32" t="str">
-        <x:v>• Go to the Game Records sheet.</x:v>
+        <x:v>• Open the StepCat v200 template.</x:v>
       </x:c>
       <x:c r="B21" s="32"/>
       <x:c r="C21" s="32"/>
@@ -1451,7 +1465,7 @@
     </x:row>
     <x:row r="22" ht="15" hidden="0" customHeight="1">
       <x:c r="A22" s="32" t="str">
-        <x:v>• Find a working formula cell in the column you want to use.</x:v>
+        <x:v>• Go to the Game Records sheet.</x:v>
       </x:c>
       <x:c r="B22" s="32"/>
       <x:c r="C22" s="32"/>
@@ -1463,7 +1477,7 @@
     </x:row>
     <x:row r="23" ht="15" hidden="0" customHeight="1">
       <x:c r="A23" s="32" t="str">
-        <x:v>• Copy that formula cell.</x:v>
+        <x:v>• Find the formula column you want:</x:v>
       </x:c>
       <x:c r="B23" s="32"/>
       <x:c r="C23" s="32"/>
@@ -1475,12 +1489,12 @@
     </x:row>
     <x:row r="24" ht="15" hidden="0" customHeight="1">
       <x:c r="A24" s="48" t="str">
-        <x:v>• Go to your custom sheet.</x:v>
+        <x:v>  J = ROI</x:v>
       </x:c>
     </x:row>
     <x:row r="25" ht="15" hidden="0" customHeight="1">
       <x:c r="A25" s="92" t="str">
-        <x:v>• Paste it into the same matching column on the row where you want the formula.</x:v>
+        <x:v>  K = Result</x:v>
       </x:c>
       <x:c r="B25" s="23"/>
       <x:c r="C25" s="23"/>
@@ -1492,7 +1506,7 @@
     </x:row>
     <x:row r="26" ht="15" hidden="0" customHeight="1">
       <x:c r="A26" s="32" t="str">
-        <x:v>• If you need the formula for more rows, copy that cell down the same column.</x:v>
+        <x:v>  Q = Challenge Length</x:v>
       </x:c>
       <x:c r="B26" s="32"/>
       <x:c r="C26" s="32"/>
@@ -1504,7 +1518,7 @@
     </x:row>
     <x:row r="27" ht="15" hidden="0" customHeight="1">
       <x:c r="A27" s="32" t="str">
-        <x:v>• Keep formula cells in the same matching columns so the formulas read the correct game information.</x:v>
+        <x:v>  U = Net Profit</x:v>
       </x:c>
       <x:c r="B27" s="32"/>
       <x:c r="C27" s="32"/>
@@ -1515,7 +1529,9 @@
       <x:c r="H27" s="32"/>
     </x:row>
     <x:row r="28" ht="15" hidden="0" customHeight="1">
-      <x:c r="A28" s="32"/>
+      <x:c r="A28" s="32" t="str">
+        <x:v>  V = Eliminated Players</x:v>
+      </x:c>
       <x:c r="B28" s="32"/>
       <x:c r="C28" s="32"/>
       <x:c r="D28" s="32"/>
@@ -1526,12 +1542,12 @@
     </x:row>
     <x:row r="29" ht="15" hidden="0" customHeight="1">
       <x:c r="A29" s="48" t="str">
-        <x:v>4. Older or in-progress games</x:v>
+        <x:v>  W = Elimination Rate</x:v>
       </x:c>
     </x:row>
     <x:row r="30" ht="15" hidden="0" customHeight="1">
       <x:c r="A30" s="92" t="str">
-        <x:v>• Add or update games under the matching column names.</x:v>
+        <x:v>• Go to a blank row below your pasted game rows.</x:v>
       </x:c>
       <x:c r="B30" s="23"/>
       <x:c r="C30" s="23"/>
@@ -1543,7 +1559,7 @@
     </x:row>
     <x:row r="31" ht="15" hidden="0" customHeight="1">
       <x:c r="A31" s="32" t="str">
-        <x:v>• StepCat copied rows already include ROI and Result for completed entries.</x:v>
+        <x:v>• Tap a cell in the formula column you want to copy.</x:v>
       </x:c>
       <x:c r="B31" s="32"/>
       <x:c r="C31" s="32"/>
@@ -1555,7 +1571,7 @@
     </x:row>
     <x:row r="32" ht="15" hidden="0" customHeight="1">
       <x:c r="A32" s="32" t="str">
-        <x:v>• Template formulas are mainly helpful for older, manual, or in-progress rows.</x:v>
+        <x:v>• Check the formula bar.</x:v>
       </x:c>
       <x:c r="B32" s="32"/>
       <x:c r="C32" s="32"/>
@@ -1566,7 +1582,9 @@
       <x:c r="H32" s="32"/>
     </x:row>
     <x:row r="33" ht="15" hidden="0" customHeight="1">
-      <x:c r="A33" s="32"/>
+      <x:c r="A33" s="32" t="str">
+        <x:v>• A reusable formula cell should show a formula that starts with =.</x:v>
+      </x:c>
       <x:c r="B33" s="32"/>
       <x:c r="C33" s="32"/>
       <x:c r="D33" s="32"/>
@@ -1577,75 +1595,126 @@
     </x:row>
     <x:row r="34" ht="15" hidden="0" customHeight="1">
       <x:c r="A34" s="48" t="str">
-        <x:v>5. Player counts</x:v>
+        <x:v>• If the formula bar is empty, that cell is just blank. Do not copy it.</x:v>
       </x:c>
     </x:row>
     <x:row r="35" ht="15" hidden="0" customHeight="1">
       <x:c r="A35" s="48" t="str">
-        <x:v>• Total Players = everyone who entered the challenge.</x:v>
+        <x:v>• If the cell contains a pasted StepCat value instead of a formula, do not copy it as a reusable formula.</x:v>
       </x:c>
     </x:row>
     <x:row r="36" ht="15" hidden="0" customHeight="1">
       <x:c r="A36" s="48" t="str">
-        <x:v>• Eligible Players = players still eligible to win / not disqualified.</x:v>
+        <x:v>• Once you find a formula cell, copy it.</x:v>
       </x:c>
     </x:row>
     <x:row r="37" ht="15" hidden="0" customHeight="1">
       <x:c r="A37" s="48" t="str">
-        <x:v>• Eligible Players drives payout estimates. Total Players is context for tracking eliminations.</x:v>
+        <x:v>• In your custom sheet, paste it into the same matching column.</x:v>
       </x:c>
     </x:row>
     <x:row r="38" ht="15" hidden="0" customHeight="1">
-      <x:c r="A38" s="48"/>
+      <x:c r="A38" s="48" t="str">
+        <x:v>• Keep formulas in the same columns so they read the correct game information.</x:v>
+      </x:c>
     </x:row>
     <x:row r="39" ht="15" hidden="0" customHeight="1">
-      <x:c r="A39" s="48" t="str">
-        <x:v>6. Warm-up week estimate tip</x:v>
-      </x:c>
+      <x:c r="A39" s="48"/>
     </x:row>
     <x:row r="40" ht="15" hidden="0" customHeight="1">
       <x:c r="A40" s="48" t="str">
-        <x:v>• For best estimate accuracy, add challenges after warm-up week ends.</x:v>
+        <x:v>4. Older or in-progress games</x:v>
       </x:c>
     </x:row>
     <x:row r="41" ht="15" hidden="0" customHeight="1">
       <x:c r="A41" s="48" t="str">
-        <x:v>• Gross Pot and Total Players are usually more reliable after warm-up week.</x:v>
+        <x:v>• Add or update games under the matching column names.</x:v>
       </x:c>
     </x:row>
     <x:row r="42" ht="15" hidden="0" customHeight="1">
       <x:c r="A42" s="48" t="str">
-        <x:v>• Update Eligible Players as the challenge progresses.</x:v>
+        <x:v>• StepCat copied rows already include ROI and Result for completed entries.</x:v>
       </x:c>
     </x:row>
     <x:row r="43" ht="15" hidden="0" customHeight="1">
-      <x:c r="A43" s="48"/>
+      <x:c r="A43" s="48" t="str">
+        <x:v>• Template formulas are mainly helpful for older, manual, or in-progress rows.</x:v>
+      </x:c>
     </x:row>
     <x:row r="44" ht="15" hidden="0" customHeight="1">
-      <x:c r="A44" s="48" t="str">
-        <x:v>7. What updates automatically</x:v>
-      </x:c>
+      <x:c r="A44" s="48"/>
     </x:row>
     <x:row r="45" ht="15" hidden="0" customHeight="1">
       <x:c r="A45" s="48" t="str">
-        <x:v>• Summary shows totals, averages, and result rates.</x:v>
+        <x:v>5. Player counts</x:v>
       </x:c>
     </x:row>
     <x:row r="46" ht="15" hidden="0" customHeight="1">
       <x:c r="A46" s="48" t="str">
-        <x:v>• Game Comparisons compares game type, challenge length, entry fee, payment type, player ranges, and elimination rates.</x:v>
+        <x:v>• Total Players = everyone who entered the challenge.</x:v>
       </x:c>
     </x:row>
     <x:row r="47" ht="15" hidden="0" customHeight="1">
       <x:c r="A47" s="48" t="str">
+        <x:v>• Eligible Players = players still eligible to win / not disqualified.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="48" ht="15" hidden="0" customHeight="1">
+      <x:c r="A48" s="48" t="str">
+        <x:v>• Eligible Players drives payout estimates. Total Players is context for tracking eliminations.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="49" ht="15" hidden="0" customHeight="1">
+      <x:c r="A49" s="48"/>
+    </x:row>
+    <x:row r="50" ht="15" hidden="0" customHeight="1">
+      <x:c r="A50" s="48" t="str">
+        <x:v>6. Warm-up week estimate tip</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="51" ht="15" hidden="0" customHeight="1">
+      <x:c r="A51" s="48" t="str">
+        <x:v>• For best estimate accuracy, add challenges after warm-up week ends.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="52" ht="15" hidden="0" customHeight="1">
+      <x:c r="A52" s="48" t="str">
+        <x:v>• Gross Pot and Total Players are usually more reliable after warm-up week.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="53" ht="15" hidden="0" customHeight="1">
+      <x:c r="A53" s="48" t="str">
+        <x:v>• Update Eligible Players as the challenge progresses.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="54" ht="15" hidden="0" customHeight="1">
+      <x:c r="A54" s="48"/>
+    </x:row>
+    <x:row r="55" ht="15" hidden="0" customHeight="1">
+      <x:c r="A55" s="48" t="str">
+        <x:v>7. What updates automatically</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="56" ht="15" hidden="0" customHeight="1">
+      <x:c r="A56" s="48" t="str">
+        <x:v>• Summary shows totals, averages, and result rates.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="57" ht="15" hidden="0" customHeight="1">
+      <x:c r="A57" s="48" t="str">
+        <x:v>• Game Comparisons compares game type, challenge length, entry fee, payment type, player ranges, and elimination rates.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="58" ht="15" hidden="0" customHeight="1">
+      <x:c r="A58" s="48" t="str">
         <x:v>• Best Results lists the highest Net Profit and ROI values.</x:v>
       </x:c>
     </x:row>
-    <x:row r="48" ht="15" hidden="0" customHeight="1">
-      <x:c r="A48" s="48"/>
-    </x:row>
-    <x:row r="49" ht="15" hidden="0" customHeight="1">
-      <x:c r="A49" s="48" t="str">
+    <x:row r="59" ht="15" hidden="0" customHeight="1">
+      <x:c r="A59" s="48"/>
+    </x:row>
+    <x:row r="60" ht="15" hidden="0" customHeight="1">
+      <x:c r="A60" s="48" t="str">
         <x:v>The official posted game result should always be treated as authoritative.</x:v>
       </x:c>
     </x:row>
@@ -1741,56 +1810,56 @@
       <x:c r="W1" s="5"/>
     </x:row>
     <x:row r="2" ht="22" customHeight="1">
-      <x:c r="A2" s="151" t="str">
+      <x:c r="A2" s="153" t="str">
         <x:v>Paste StepCat rows starting in A5. See Instructions tab for formula help.</x:v>
       </x:c>
-      <x:c r="B2" s="151"/>
-      <x:c r="C2" s="151"/>
-      <x:c r="D2" s="151"/>
-      <x:c r="E2" s="151"/>
-      <x:c r="F2" s="151"/>
-      <x:c r="G2" s="151"/>
-      <x:c r="H2" s="151"/>
-      <x:c r="I2" s="151"/>
-      <x:c r="J2" s="151"/>
-      <x:c r="K2" s="151"/>
-      <x:c r="L2" s="151"/>
-      <x:c r="M2" s="151"/>
-      <x:c r="N2" s="151"/>
-      <x:c r="O2" s="151"/>
-      <x:c r="P2" s="151"/>
-      <x:c r="Q2" s="151"/>
-      <x:c r="R2" s="151"/>
-      <x:c r="S2" s="151"/>
-      <x:c r="T2" s="151"/>
-      <x:c r="U2" s="151"/>
-      <x:c r="V2" s="151"/>
-      <x:c r="W2" s="151"/>
+      <x:c r="B2" s="153"/>
+      <x:c r="C2" s="153"/>
+      <x:c r="D2" s="153"/>
+      <x:c r="E2" s="153"/>
+      <x:c r="F2" s="153"/>
+      <x:c r="G2" s="153"/>
+      <x:c r="H2" s="153"/>
+      <x:c r="I2" s="153"/>
+      <x:c r="J2" s="153"/>
+      <x:c r="K2" s="153"/>
+      <x:c r="L2" s="153"/>
+      <x:c r="M2" s="153"/>
+      <x:c r="N2" s="153"/>
+      <x:c r="O2" s="153"/>
+      <x:c r="P2" s="153"/>
+      <x:c r="Q2" s="153"/>
+      <x:c r="R2" s="153"/>
+      <x:c r="S2" s="153"/>
+      <x:c r="T2" s="153"/>
+      <x:c r="U2" s="153"/>
+      <x:c r="V2" s="153"/>
+      <x:c r="W2" s="153"/>
     </x:row>
     <x:row r="3" ht="22" customHeight="1">
-      <x:c r="A3" s="152"/>
-      <x:c r="B3" s="152"/>
-      <x:c r="C3" s="152"/>
-      <x:c r="D3" s="152"/>
-      <x:c r="E3" s="152"/>
-      <x:c r="F3" s="152"/>
-      <x:c r="G3" s="152"/>
-      <x:c r="H3" s="152"/>
-      <x:c r="I3" s="152"/>
-      <x:c r="J3" s="152"/>
-      <x:c r="K3" s="152"/>
-      <x:c r="L3" s="152"/>
-      <x:c r="M3" s="152"/>
-      <x:c r="N3" s="152"/>
-      <x:c r="O3" s="152"/>
-      <x:c r="P3" s="152"/>
-      <x:c r="Q3" s="152"/>
-      <x:c r="R3" s="152"/>
-      <x:c r="S3" s="152"/>
-      <x:c r="T3" s="152"/>
-      <x:c r="U3" s="152"/>
-      <x:c r="V3" s="152"/>
-      <x:c r="W3" s="152"/>
+      <x:c r="A3" s="154"/>
+      <x:c r="B3" s="154"/>
+      <x:c r="C3" s="154"/>
+      <x:c r="D3" s="154"/>
+      <x:c r="E3" s="154"/>
+      <x:c r="F3" s="154"/>
+      <x:c r="G3" s="154"/>
+      <x:c r="H3" s="154"/>
+      <x:c r="I3" s="154"/>
+      <x:c r="J3" s="154"/>
+      <x:c r="K3" s="154"/>
+      <x:c r="L3" s="154"/>
+      <x:c r="M3" s="154"/>
+      <x:c r="N3" s="154"/>
+      <x:c r="O3" s="154"/>
+      <x:c r="P3" s="154"/>
+      <x:c r="Q3" s="154"/>
+      <x:c r="R3" s="154"/>
+      <x:c r="S3" s="154"/>
+      <x:c r="T3" s="154"/>
+      <x:c r="U3" s="154"/>
+      <x:c r="V3" s="154"/>
+      <x:c r="W3" s="154"/>
     </x:row>
     <x:row r="4" ht="34" customHeight="1">
       <x:c r="A4" s="141" t="str">
@@ -20405,7 +20474,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Recac93173450419f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra6850faf76c74b85"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -20678,7 +20747,7 @@
     <x:mergeCell ref="A22:H25"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2caa45ab70a242c7"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re28df1dc5e8d415d"/>
 </x:worksheet>
 </file>
 
@@ -21844,7 +21913,7 @@
     <x:mergeCell ref="A48:H48"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R86d8cebe2f1840d5"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3384b75903124ab8"/>
 </x:worksheet>
 </file>
 

--- a/StepCat_Blank_Profitability_Analysis_Template.xlsx
+++ b/StepCat_Blank_Profitability_Analysis_Template.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instructions" sheetId="1" r:id="Rd991c0cafc014520"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Game Records" sheetId="2" r:id="Rb2589606705c460d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="3" r:id="Ree9c1d1172a14712"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Game Comparisons" sheetId="4" r:id="R3500dea867cd4d8a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Best Results" sheetId="5" r:id="R37a179e7d90647f6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instructions" sheetId="1" r:id="R3823ff4547bf44e8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Game Records" sheetId="2" r:id="Rc295ed2f9fd2424a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="3" r:id="R223f70ea972846f1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Game Comparisons" sheetId="4" r:id="R2defa68931de4d92"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Best Results" sheetId="5" r:id="R3c213b91376540b1"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -17,11 +17,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="4">
+  <x:numFmts count="6">
     <x:numFmt numFmtId="200" formatCode="mm/dd/yyyy"/>
     <x:numFmt numFmtId="201" formatCode="$0.00"/>
     <x:numFmt numFmtId="202" formatCode="0.0%"/>
     <x:numFmt numFmtId="203" formatCode="0"/>
+    <x:numFmt numFmtId="204" formatCode="$#,##0.00"/>
+    <x:numFmt numFmtId="205" formatCode="mm-dd-yyyy"/>
   </x:numFmts>
   <x:fonts count="12">
     <x:font>
@@ -209,7 +211,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="156">
+  <x:cellXfs count="160">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -612,6 +614,18 @@
     <x:xf numFmtId="0" fontId="11" fillId="21" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center" wrapText="1"/>
     </x:xf>
+    <x:xf numFmtId="204" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="203" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="205" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -1004,7 +1018,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R1cd64466e3d64bae"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Reb487123ef454f71"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1039,7 +1053,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rd0216a5b499849df"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R35641721863d4ffe"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1786,28 +1800,28 @@
       <x:c r="A1" s="5" t="str">
         <x:v>Game Records - StepCat v200</x:v>
       </x:c>
-      <x:c r="B1" s="5"/>
-      <x:c r="C1" s="5"/>
+      <x:c r="B1" s="159"/>
+      <x:c r="C1" s="159"/>
       <x:c r="D1" s="5"/>
-      <x:c r="E1" s="5"/>
-      <x:c r="F1" s="5"/>
-      <x:c r="G1" s="5"/>
-      <x:c r="H1" s="5"/>
-      <x:c r="I1" s="5"/>
-      <x:c r="J1" s="5"/>
+      <x:c r="E1" s="156"/>
+      <x:c r="F1" s="156"/>
+      <x:c r="G1" s="156"/>
+      <x:c r="H1" s="156"/>
+      <x:c r="I1" s="156"/>
+      <x:c r="J1" s="157"/>
       <x:c r="K1" s="5"/>
       <x:c r="L1" s="5"/>
-      <x:c r="M1" s="5"/>
-      <x:c r="N1" s="5"/>
-      <x:c r="O1" s="5"/>
-      <x:c r="P1" s="5"/>
+      <x:c r="M1" s="156"/>
+      <x:c r="N1" s="156"/>
+      <x:c r="O1" s="158"/>
+      <x:c r="P1" s="158"/>
       <x:c r="Q1" s="5"/>
       <x:c r="R1" s="5"/>
       <x:c r="S1" s="5"/>
       <x:c r="T1" s="5"/>
-      <x:c r="U1" s="5"/>
-      <x:c r="V1" s="5"/>
-      <x:c r="W1" s="5"/>
+      <x:c r="U1" s="156"/>
+      <x:c r="V1" s="158"/>
+      <x:c r="W1" s="157"/>
     </x:row>
     <x:row r="2" ht="22" customHeight="1">
       <x:c r="A2" s="153" t="str">
@@ -20474,7 +20488,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra6850faf76c74b85"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re57efeb46e924eba"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -20747,7 +20761,7 @@
     <x:mergeCell ref="A22:H25"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re28df1dc5e8d415d"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3804b0ced32f49db"/>
 </x:worksheet>
 </file>
 
@@ -21913,7 +21927,7 @@
     <x:mergeCell ref="A48:H48"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3384b75903124ab8"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rebdb99ecd1b846d6"/>
 </x:worksheet>
 </file>
 

--- a/StepCat_Blank_Profitability_Analysis_Template.xlsx
+++ b/StepCat_Blank_Profitability_Analysis_Template.xlsx
@@ -2213,7 +2213,7 @@
     <x:row r="1" s="106" customFormat="1" ht="21.600000381469727" customHeight="1">
       <x:c r="A1" s="239" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">StepCat v205 Profitability Analysis Template</x:t>
+          <x:t xml:space="preserve">StepCat v206 Profitability Analysis Template</x:t>
         </x:is>
       </x:c>
       <x:c r="B1" s="1" t="n"/>
@@ -2367,7 +2367,7 @@
     <x:row r="12" s="106" customFormat="1" ht="15" customHeight="1">
       <x:c r="A12" s="243" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">• Do not paste over formula columns N through Y unless you intentionally want to replace the v205 formulas and result colors.</x:t>
+          <x:t xml:space="preserve">• Do not paste over formula columns N through Y unless you intentionally want to replace the v206 formulas and result colors.</x:t>
         </x:is>
       </x:c>
       <x:c r="B12" s="1" t="n"/>
@@ -2865,7 +2865,7 @@
     <x:row r="1" s="106" customFormat="1" ht="32" customHeight="1">
       <x:c r="A1" s="246" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Game Records - StepCat v205</x:t>
+          <x:t xml:space="preserve">Game Records - StepCat v206</x:t>
         </x:is>
       </x:c>
       <x:c r="B1" s="1" t="n"/>
@@ -2896,7 +2896,7 @@
     <x:row r="2" s="106" customFormat="1" ht="22" customHeight="1">
       <x:c r="A2" s="247" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Paste StepCat rows into input columns A through M starting in A5. Moving from an older spreadsheet? Paste old game information into A through M only. Do not paste over N through Y; those columns contain the final v205 formulas and result colors.</x:t>
+          <x:t xml:space="preserve">Paste StepCat rows into input columns A through M starting in A5. Moving from an older spreadsheet? Paste old game information into A through M only. Do not paste over N through Y; those columns contain the final v206 formulas and result colors.</x:t>
         </x:is>
       </x:c>
       <x:c r="B2" s="1" t="n"/>
@@ -13324,7 +13324,7 @@
       <x:c r="U205" s="254">
         <x:f>IF($A205="","",IF(LOWER($L205&amp;"")="yes","Disqualified",IF($P205&gt;$H205,"Profit","Draw")))</x:f>
       </x:c>
-      <x:c r="V205" s="253">
+      <x:c r="V206" s="253">
         <x:f>IF(OR($B205="",$C205=""),"",IFERROR(ROUNDUP((IF(ISNUMBER($C205),$C205,DATEVALUE($C205))-IF(ISNUMBER($B205),$B205,DATEVALUE($B205)))/7,0),""))</x:f>
       </x:c>
       <x:c r="W205" s="254">
